--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE6E31D-19FA-467B-AFAF-A591B1946FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A26BD4-2960-453D-9305-0A146AD6DFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -85,26 +85,27 @@
     <t>elements</t>
   </si>
   <si>
-    <t>3:2:3:3:4:7:7:2:8:3:6:1:2:1:8:7:7:2:2:1:6:2:3:1:5:5:3:2:1:8:7:3:3:3:23:2:3:3:1:8:2:3:8:6:5:8:2:5:1:1:1:8:4:4:4:2:5:2:1:6:1:4:5:2:1:2:5:5:6:23:3:8:8:8:1:2:1:3:4:4:4:1:5:7:2:5:1:4:2:1:2:7:2:1:5:2:1:2:2:3:4:2:7:3:23:1:2:4:2:6:6:6:4:1:2:6:3:7:1:3:1:4:1:2:1:3:2:2:1:4:2:9:4:3:1:7:4:2:1:23:6:4:2:9:4:9:9:4:6:5:2:7:6:2:3:2:1:5:6:3:2:3:2:1:2:5:4:1:6:3:5:1:5:5:23:5:8:5:1:2:5:1:8:2:4:1:2:3:1:2:1:8:8:1:6:4:1:4:5:2:1:8:6:1:9:1:3:2:6:23:6:3:7:2:5:2:8:3:4:7:2:9:3:9:1:1:6:7:9:5:7:1:1:2:1:7:1:2:1:5:7:4:4:4:23:3:1:2:3:1:3:5:5:5:2:5:1:2:8:8:7:4:1:2:2:4:2:1:2:14:1:6:4:1:3:8:2:8:5:23:6:3:1:1:3:3:1:1:1:3:2:1:1:1:2:4:6:1:2:6:6:3:1:7:5:1:4:3:4:5:1:4:3:5:23:8:7:7:3:2:4:2:3:3:2:8:3:4:7:1:2:5:4:2:5:1:9:2:2:2:6:4:3:7:2:3:1:2:6:23:5:4:1:11:4:2:4:1:3:2:1:5:2:2:1:2:6:4:6:2:3:4:2:4:2:3:5:4:2:4:6:3:4:2:23:3:2:5:12:5:3:2:3:3:4:4:1:5:1:2:6:1:3:5:2:6:7:7:7:6:4:3:2:6:6:6:8:4:2:4:4:2:6:3:1:1:6:17:2:1:2:1:2:9:8:2:2:1:2:3:1:2:5:4:8:2:1:3:1:6:3:7:2:3:4:2:1:2:4:8:8:1:4:3:7:1:1:2:4:1:9:3:2:7:2:1:2:1:5:2:2:2:1:5:4:2:1:4:1:10:3:4:1:4:9:1:9:7:1:1:6:6:4:5:5:1:6:2:2:1:5:1:4:4:2:3:4:3:1:1:3:19:3:2:8:2:2:1:5:5:9:4:4:3:3:1:3:3:1:2:8:8:4:1:1:2:1:4:1:1:3:9:4:2:4:23:4:1:3:4:4:7:3:3:7:1:8:2:1:1:5:4:2:11:3:8:8:2:2:3:2:6:1:2:4:3:2:2:1:5:5:8:1:4:23:6:6:4:4:1:7:1:2:9:1:3:3:1:6:3:1:3:7:7:1:5:9:2:6:6:10:3:7:5:2:4:1:1:6:3:7:7:5:9:4:4:3:7:2:9:10:5:5:2:7:6:5:2:2:3:3:4:1:7:9:1:7:3:8:11:9:9:2:2:1:2:4:23:8:1:4:4:1:5:1:3:1:3:4:1:3:14:7:2:6:5:1:2:5:4:4:1:5:6:3:1:8:2:1:2:2:7:5:5:6:2:1:8:6:1:3:4:7:8:8:7:2:4:1:9:8:2:2:23:1:7:3:7:4:1:5:4:8:1:1:7:10:5:5:6:3:3:6:3:1:6:7:7:5:6:1:8:1:12:2:3:1:4:5:2:6:3:3:2:5:8:2:2:1:3:1:1:8:1:9:8:4:1:3:23:9:3:5:5:3:5:2:4:3:5:2:6:7:2:2:3:5:2:1:4:5:2:4:1:2:2:4:2:7:7:4:3:23:4:3:3:2:1:4:9:9:2:1:3:6:4:4:3:9:1:1:7:1:3:3:2:6:3:2:9:9:6:3:3:8:23:9:1:2:2:3:2:6:2:5:5:1:8:4:3:3:5:5:4:3:6:6:1:1:4:1:2:4:2:5:2:1:3:23:1:6:1:8:1:4:2:4:2:1:4:1:1:7:2:2:3:2:6:1:2:2:6:6:5:5:8:4:5:4:4:7:23:1:2:1:2:17:3:4:6:6:7:2:3:4:4:2:1:1:2:3:2:6:6:4:8:7:7:2:1:2:6:5:9:23:3:8:3:1:4:2:9:5:6:3:2:1:3:8:8:2:2:1:5:4:8:1:8:1:1:3:4:4:1:3:1:4:23:6:1:3:2:3:1:1:2:6:5:1:1:2:3:1:3:3:4:2:4:1:5:5:2:1:1:4:5:1:2:4:6:23:6:2:8:8:2:3:1:6:3:1:4:6:6:2:1:2:8:8:3:3:7:2:8:8:4:2:5:2:5:7:1:3:23:2:6:6:9:9:5:5:1:2:5:5:7:1:4:4:1:5:3:3:4:1:4:2:3:2:1:8:7:6:2:4:7:23:5:1:3:1:1:4:2:2:4:8:2:5:4:1:4:2:12:1:2:2:7:7:1:1:3:3:5:6:8:2:5:1:23:9:9:4:4:7:7:1:7:7:1:4:7:2:6:4:1:5:4:1:1:2:8:8:2:8:1:1:7:2:3:1:2:23:1:3:2:3:4:2:8:1:2:11:4:8:6:7:2:2:6:7:3:6:5:3:2:1:2:3:3:7:6:6:7:2:23:1:2:7:2:6:1:8:1:2:2:4:2:1:3:3:2:3:3:1:5:2:2:6:6:1:3:7:7:5:5:4:7:23:4:1:14:5:8:4:2:2:6:2:1:4:2:1:1:5:1:1:2:1:1:4:2:5:1:2:2:9:9:2:2:3:10:1:2:5:2:3:1:2:5:3:2:2:4:2:1:5:4:1:3:2:5:3:1:2:2:4:4:1:1:4:2:7:1:10:3:8:1:3:2:3:2:3:3:4:7:7:2:8:3:6:1:2:1:8:7:7:2:2:1:6:2:3:1:5:5:3:2:1:8:7:3:3:3:3:2:3:3:1:8:2:3:8:6:5:8:2:5:1:1</t>
-  </si>
-  <si>
-    <t>1:3:2:6:1:5:1:2:3:4:5:9:23:6:4:3:5:4:1:5:8:8:2:2:4:5:4:3:9:9:4:8:8:8:23:2:3:5:6:3:2:4:6:3:5:6:3:7:2:9:2:3:2:3:2:6:5:2:7:2:4:5:6:6:5:3:6:2:8:23:2:7:2:6:9:2:3:2:3:7:3:7:3:4:9:5:5:8:4:8:3:4:6:7:3:5:3:5:3:9:5:23:1:3:3:5:7:8:5:2:3:2:3:3:5:9:9:9:7:2:3:3:5:3:1:5:4:6:3:5:3:5:2:6:3:5:3:5:3:23:6:3:1:2:5:5:5:2:3:8:3:1:2:3:2:3:7:2:6:5:2:3:5:2:3:6:2:2:5:3:4:7:5:6:23:2:5:3:3:6:2:3:2:2:7:5:1:7:7:7:13:6:9:9:3:8:3:2:3:1:1:4:7:5:1:5:1:8:4:23:3:3:4:1:3:2:5:7:4:6:3:8:8:8:5:8:1:3:9:1:5:2:6:7:3:5:4:5:3:5:5:5:3:3:23:4:5:3:5:2:1:8:3:5:3:7:1:3:3:6:2:2:2:3:5:4:5:5:1:3:4:2:1:3:7:3:6:2:9:23:8:8:1:4:1:5:7:3:2:5:8:4:7:2:3:5:3:7:5:3:3:3:1:12:5:2:3:5:7:5:1:8:3:2:23:2:6:1:9:5:9:7:3:4:5:5:3:5:5:7:3:5:4:6:5:1:3:5:6:5:3:6:2:6:4:2:3:2:6:23:5:3:9:2:3:5:7:6:5:3:3:2:3:6:5:6:3:5:7:3:2:2:3:2:1:8:6:7:3:1:1:3:5:2:23:5:4:4:4:7:5:5:4:5:5:2:3:6:5:5:5:2:3:2:5:3:5:3:6:5:3:2:2:3:5:3:11:7:3:2:5:3:6:3:3:3:7:6:6:6:5:7:4:3:6:3:5:2:8:3:2:5:3:7:4:4:3:5:3:8:3:2:3:5:5:3:4:3:5:6:8:1:3:5:3:6:2:5:7:3:5:8:5:6:3:23:3:5:5:5:7:1:4:3:2:5:4:3:3:10:3:5:3:5:2:6:2:3:5:9:2:2:3:2:1:4:3:7:3:4:6:1:4:8:1:8:5:2:5:7:2:3:1:1:9:1:1:2:3:4:1:8:4:4:2:3:8:4:5:2:8:1:11:8:5:8:3:1:5:7:1:2:7:2:4:4:1:2:5:9:9:8:2:1:2:1:4:4:3:7:3:2:9:3:6:6:4:1:8:8:1:6:6:9:9:2:4:6:4:8:5:5:8:8:1:2:2:6:1:9:9:5:1:5:18:3:1:1:6:7:6:23:4:1:2:9:8:9:3:3:1:4:7:7:3:3:1:1:7:7:1:1:2:2:9:1:1:12:2:6:6:4:4:3:3:2:6:7:5:2:1:3:8:3:2:6:5:4:4:1:4:5:5:2:5:2:6:23:6:1:4:4:6:3:5:7:5:2:6:6:5:2:1:1:3:2:2:4:1:11:2:5:9:2:1:4:2:1:5:4:7:6:2:2:1:1:2:1:8:8:2:2:7:7:9:9:3:3:4:10:2:5:5:23:3:4:4:1:4:2:2:4:1:1:2:2:3:3:5:3:2:11:3:2:2:8:1:4:4:3:3:7:5:23:1:3:4:3:3:1:3:3:1:5:5:1:6:7:2:10:8:5:4:2:1:1:1:1:1:23:12:8:8:6:8:8:2:1:3:3:5:5:7:2:7:5:7:2:6:8:3:3:6:3:3:2:4:2:1:1:7:6:23:7:5:3:4:2:3:8:2:3:5:5:6:4:1:8:2:4:3:9:3:3:5:3:7:1:1:2:5:3:3:5:4:23:8:3:5:3:2:4:3:5:3:7:3:3:5:6:5:2:5:3:5:3:7:3:3:8:8:3:2:5:7:7:5:2:23:2:3:5:7:3:2:5:5:2:2:13:6:3:6:6:7:2:2:6:3:7:6:7:3:5:8:8:4:3:2:5:3:23:2:8:3:2:4:2:5:5:6:3:5:4:2:5:5:3:5:6:4:4:3:5:7:1:1:3:4:5:4:3:7:6:23:1:3:6:6:5:5:2:5:3:6:1:5:9:7:7:5:2:2:5:2:7:3:6:6:3:4:3:3:5:5:6:3:23:5:3:1:1:7:9:3:6:5:5:8:4:4:5:9:5:1:6:2:3:3:2:1:5:3:5:4:2:3:9:5:1:23:1:5:3:6:4:4:5:3:4:3:2:5:5:2:4:2:9:6:1:1:3:5:3:4:4:3:2:3:7:2:1:6:23:6:2:7:9:1:8:5:2:3:4:5:7:6:4:3:5:9:3:5:3:8:5:2:5:2:3:6:7:5:6:1:3:23:5:3:7:6:2:5:3:5:6:2:2:3:3:5:5:1:8:5:7:2:5:5:3:5:1:2:2:4:2:5:3:7:23:2:3:2:9:5:8:3:3:4:3:2:3:7:3:7:2:8:4:3:2:6:3:1:7:7:6:3:6:6:4:3:8:23:5:3:7:2:2:9:3:5:1:5:3:8:1:2:4:4:5:3:4:5:2:8:8:6:5:5:2:6:3:2:5:7:23:8:8:3:4:3:5:3:3:2:2:5:3:3:9:3:5:8:8:6:2:11:3:2:3:5:2:6:2:3:5:6:9:23:9:2:3:9:9:3:3:6:1:1:5:7:5:3:3:7:5:6:4:3:5:3:3:5:3:1:1:5:9:6:3:5:10:4:3:6:5:3:5:5:1:5:3:5:9:9:4:5:7:3:2:5:4:5:2:5:3:5:2:3:5:3:2:2:5:10:3:3:5:1:3:1:3:2:6:1:5:1:2:3:4:5:9:2:6:4:3:5:4:1:5:8:8:2:2:4:5:4:3:9:9:4:8:8:8:2:2:3:5:6:3:2:4:6:3:5:6:3:7:2:9</t>
-  </si>
-  <si>
-    <t>11:3:1:2:7:1:9:9:3:1:1:4:8:2:3:1:5:4:8:2:7:3:4:8:1:3:4:2:3:2:1:3:1:7:23:8:3:3:4:6:1:4:1:7:5:2:2:1:2:5:2:1:2:3:2:7:2:6:4:7:1:1:2:1:1:2:3:3:3:23:4:2:3:2:3:1:4:5:4:4:4:7:7:7:3:2:6:3:7:1:3:5:3:1:1:1:5:8:1:1:2:7:1:3:23:7:6:3:1:2:5:2:2:5:2:2:2:6:6:6:4:3:4:3:1:3:8:1:3:2:4:12:3:1:1:1:2:3:5:23:5:5:3:5:4:9:9:2:4:2:5:2:3:2:1:2:2:8:2:1:2:3:3:5:1:6:1:8:1:3:5:1:2:1:23:5:1:4:1:6:4:1:8:4:3:1:4:1:6:6:1:2:1:5:8:3:6:2:4:4:4:2:6:6:7:6:2:9:1:23:7:3:2:1:7:1:2:1:1:1:2:4:1:13:7:2:1:4:8:2:1:2:7:2:2:1:4:5:6:2:8:2:9:4:23:8:2:1:2:1:2:1:1:3:6:5:3:2:6:6:2:3:1:8:8:8:5:8:2:1:5:2:5:5:4:2:8:2:1:23:2:8:2:7:3:1:3:1:5:4:2:5:8:2:5:1:4:1:4:8:8:7:5:3:9:2:4:2:1:4:1:5:1:7:23:4:2:8:6:2:1:2:4:3:6:4:2:8:6:2:2:2:1:5:4:5:1:2:3:2:7:2:3:8:2:2:1:3:3:23:5:2:1:2:4:2:3:2:2:2:4:8:2:5:5:3:4:7:1:3:2:4:3:1:2:3:2:3:6:6:2:4:1:2:23:3:2:1:9:3:5:1:7:9:2:1:4:2:9:2:3:2:1:2:9:7:1:7:2:7:7:4:3:7:9:2:1:2:3:4:2:2:3:2:1:1:4:2:2:1:2:8:2:3:3:4:3:4:2:5:4:4:2:3:4:1:2:4:2:4:2:4:6:1:9:2:2:2:9:2:4:1:2:5:2:4:5:5:5:8:4:2:4:1:5:1:4:9:5:3:5:2:1:4:2:3:1:4:5:10:6:2:5:2:7:7:4:1:2:1:3:1:5:7:7:6:6:9:3:5:5:4:1:2:1:2:5:5:1:3:3:1:2:3:3:1:3:2:2:9:7:10:5:8:1:5:4:9:5:4:2:6:4:11:5:2:1:5:1:3:9:2:9:4:1:4:9:9:2:2:1:2:1:2:1:1:3:4:2:2:4:5:5:1:1:6:7:4:4:7:6:3:5:1:2:2:6:11:9:4:8:3:4:4:8:3:3:9:9:1:5:5:1:1:5:5:6:5:5:1:7:23:2:8:6:6:9:2:1:2:2:7:2:1:7:8:1:3:2:2:4:9:3:2:2:8:6:9:1:5:9:9:3:3:4:4:10:4:9:3:3:2:8:7:7:4:8:7:4:8:8:1:5:6:7:2:5:23:6:2:7:1:4:4:3:17:1:7:2:3:2:3:1:4:3:3:2:4:7:6:2:2:6:1:2:1:1:3:3:7:4:4:6:1:13:7:6:2:6:4:4:2:1:1:2:1:1:5:3:2:1:1:4:23:3:4:1:3:3:1:7:7:3:8:3:8:10:2:1:2:6:4:6:5:4:2:1:2:6:2:12:6:1:1:3:7:4:4:1:6:2:1:8:8:4:3:1:5:1:15:4:3:1:6:2:4:1:8:1:23:9:9:5:6:2:7:1:3:3:2:3:7:1:3:1:2:3:2:4:2:1:5:9:3:7:7:2:6:2:3:23:2:1:6:5:5:7:2:7:1:2:2:7:8:8:2:1:1:2:3:3:1:7:3:1:2:4:4:1:1:3:23:3:4:1:11:2:1:6:1:4:2:2:5:2:2:7:2:5:2:1:9:1:2:8:4:2:2:4:3:2:4:23:2:6:6:2:5:1:4:1:5:3:5:4:2:1:2:3:2:9:7:7:3:3:7:2:2:8:4:4:5:1:23:7:4:7:4:5:3:2:1:5:1:2:5:7:7:4:6:8:5:3:3:1:2:1:2:2:4:6:2:9:1:23:3:1:1:8:2:6:3:1:7:8:8:1:2:5:3:3:2:2:6:9:7:4:1:1:4:3:4:2:1:3:23:1:3:2:4:1:1:4:1:8:8:2:4:3:3:1:1:5:5:8:5:1:6:6:2:3:5:1:7:7:4:23:1:4:8:3:2:1:8:1:2:1:2:2:5:2:5:2:3:3:9:4:4:2:1:4:1:3:7:2:3:1:23:4:8:1:2:2:4:1:2:1:4:4:1:1:4:8:7:4:4:2:3:2:3:2:1:4:2:2:9:2:7:23:1:8:8:6:4:2:2:6:8:8:1:5:1:2:3:4:3:6:3:1:2:2:7:4:7:7:8:8:1:2:23:9:3:3:2:1:6:1:1:2:6:2:1:2:2:4:2:2:5:6:1:4:5:4:6:6:3:3:8:8:5:23:4:1:4:5:2:1:3:2:4:4:1:2:2:8:3:3:12:2:6:2:2:4:2:2:1:5:3:4:3:2:23:6:2:1:3:9:9:6:2:1:5:2:1:4:1:5:2:1:5:5:2:1:2:2:8:8:1:4:1:4:2:23:1:6:1:2:2:1:1:5:4:2:7:5:9:3:3:1:4:3:3:6:1:1:2:4:3:2:5:4:8:3:23:5:2:2:4:2:5:4:2:5:1:5:5:1:7:6:2:2:8:1:5:1:3:2:4:2:2:4:7:4:1:10:7:5:3:5:5:2:3:4:3:3:13:1:4:1:2:1:2:5:2:3:3:7:4:3:1:1:2:1:2:4:10:1:1:9:2:1:3:1:2:7:1:9:9:3:1:1:4:8:2:3:1:5:4:8:2:7:3:4:8:1:3:4:2:3:2:1:3:1:7:2:8:3:3:4:6:1:4:1:7:5:2:2:1:2:5</t>
-  </si>
-  <si>
-    <t>4:4:3:2:4:4:5:3:6:3:1:1:5:6:6:6:4:4:1:6:1:3:2:3:3:1:9:2:4:3:2:6:4:3:23:8:4:5:3:8:2:4:6:3:7:9:6:3:1:3:4:3:1:4:6:1:2:8:6:3:6:4:1:8:4:7:5:3:8:23:7:4:5:4:3:5:1:2:7:1:5:5:3:6:1:7:4:3:8:1:4:3:8:3:3:1:1:5:3:4:1:3:8:6:4:8:23:3:5:7:8:1:8:2:2:1:3:6:3:3:3:4:6:4:4:4:1:6:3:1:4:4:1:6:3:9:3:2:4:23:1:4:5:3:2:4:1:6:4:8:9:1:5:3:4:5:1:2:3:12:1:2:5:9:6:7:7:7:3:1:3:4:6:8:23:3:1:8:5:3:2:3:2:4:2:3:5:1:1:1:2:7:2:1:3:1:2:5:4:3:4:3:8:3:2:6:7:6:3:23:6:3:8:8:7:4:3:4:4:4:3:3:2:8:3:4:3:7:1:1:3:1:3:3:3:1:1:7:3:5:1:7:2:3:23:1:6:5:2:2:2:9:7:3:4:7:4:5:3:3:3:4:3:4:4:4:5:3:8:6:1:5:3:8:8:8:2:4:6:23:5:7:3:4:2:9:5:6:6:6:1:7:7:7:4:3:1:1:4:3:2:3:4:3:5:4:5:8:3:4:1:6:3:8:23:3:1:4:1:1:1:2:6:4:8:4:5:3:8:4:9:16:1:7:7:3:8:3:6:1:3:8:3:1:4:1:1:2:4:23:3:1:8:1:1:3:8:1:4:3:3:3:4:1:3:2:8:3:4:3:2:3:5:4:8:4:3:5:4:3:8:4:5:9:5:11:6:4:4:3:7:1:8:3:4:4:1:3:8:4:1:3:4:8:9:3:5:4:1:3:4:1:15:3:1:3:2:1:6:23:6:6:3:1:3:4:4:4:5:7:1:3:4:3:2:1:1:1:7:4:8:4:3:5:3:9:9:3:1:5:3:1:3:5:5:8:1:1:5:3:3:3:1:5:3:2:5:1:2:5:3:1:3:1:23:2:3:8:3:5:2:3:9:3:5:9:1:1:3:10:2:5:5:3:2:3:8:3:4:3:5:5:3:1:1:3:1:2:4:4:10:3:3:6:6:1:8:1:3:8:8:3:1:1:5:9:3:3:5:10:3:8:2:3:1:3:8:7:3:5:9:9:3:3:2:8:6:6:5:5:15:1:7:8:8:3:4:4:1:2:2:5:8:3:5:3:1:1:3:23:4:2:2:1:3:6:4:5:5:3:6:3:3:4:4:5:2:2:7:12:1:9:6:6:1:4:2:2:1:4:9:2:7:5:1:1:6:5:1:1:7:3:6:1:8:3:10:7:1:1:7:7:2:2:7:7:9:7:3:3:5:4:3:5:4:2:1:1:2:23:1:3:2:4:5:1:1:9:4:1:2:1:3:1:1:9:4:8:4:3:12:1:2:2:6:8:2:4:4:5:5:4:6:6:4:6:3:7:4:6:2:2:10:2:7:7:4:7:2:2:7:4:4:2:6:5:8:7:1:4:2:7:1:1:2:2:5:5:1:23:6:2:4:9:9:1:4:2:7:1:3:11:4:8:8:1:7:3:1:4:1:3:2:3:10:4:4:7:6:5:5:2:2:5:5:9:8:7:2:2:3:4:1:23:9:3:1:2:3:3:2:4:2:2:1:1:9:6:11:7:2:3:5:4:1:4:1:2:5:23:4:3:5:1:2:2:6:3:3:1:1:3:6:3:2:3:3:4:1:6:3:6:7:7:2:1:2:7:9:7:7:5:23:7:2:1:8:2:3:4:6:6:8:4:3:4:8:2:3:4:4:3:9:8:8:4:1:7:7:3:6:6:3:1:3:23:2:4:3:4:3:2:7:1:3:3:4:4:3:1:3:1:4:5:1:4:3:5:3:2:2:4:12:3:8:6:8:4:23:4:3:1:9:8:6:1:2:1:1:3:5:1:4:7:4:3:1:1:8:8:5:1:5:1:1:4:3:8:1:4:1:23:1:2:1:7:1:4:3:1:4:3:4:3:6:4:8:6:6:1:1:4:6:4:4:1:3:4:8:4:1:3:8:1:23:3:1:5:2:4:4:6:8:4:4:3:1:8:4:4:1:4:3:1:3:6:3:7:3:5:3:5:8:3:8:5:3:23:3:5:3:5:3:3:4:3:8:5:5:6:6:7:7:1:4:2:8:8:3:5:4:5:4:3:8:1:6:8:3:5:23:8:3:3:1:8:6:8:3:4:4:8:8:3:4:1:4:2:3:5:3:7:5:5:9:1:3:2:2:1:3:4:3:23:7:7:8:5:2:7:9:9:8:6:4:5:4:3:6:3:4:4:1:7:4:8:2:4:3:1:1:4:1:3:3:7:23:6:3:2:2:7:6:1:3:1:2:3:5:2:11:6:6:3:3:7:2:3:6:9:1:8:5:5:4:1:5:9:9:23:5:8:5:4:3:1:5:3:6:2:6:1:3:6:8:2:7:1:4:1:3:3:7:1:4:8:1:4:2:5:4:3:23:3:16:2:1:3:8:3:2:3:6:1:3:4:5:6:3:1:4:1:5:9:3:1:3:1:4:3:5:4:4:9:3:23:3:4:2:1:3:3:4:1:3:5:3:3:1:3:6:4:4:6:8:1:5:1:3:3:4:3:3:1:1:15:4:4:23:2:2:3:4:4:2:1:4:8:7:3:5:4:6:3:9:3:4:5:3:4:1:7:1:1:8:6:1:5:2:2:4:10:3:3:4:8:5:7:5:5:3:5:9:4:4:3:9:4:1:3:4:1:3:3:1:1:4:3:2:3:5:2:3:2:10:1:3:3:1:3:4:4:3:2:4:4:5:3:6:3:1:1:5:6:6:6:4:4:1:6:1:3:2:3:3:1:9:2:4:3:2:6:4:3:3:8:4:5:3:8:2:4:6:3:7:9:6:3:1:3</t>
-  </si>
-  <si>
-    <t>1:6:1:5:1:9:7:5:5:7:7:3:8:2:2:4:4:1:3:5:13:5:1:2:6:3:6:3:8:1:4:3:5:5:1:4:4:23:8:5:6:6:6:3:1:6:3:3:5:5:6:9:2:5:5:5:1:8:8:4:1:3:5:4:3:5:1:3:3:5:2:4:3:1:5:23:4:9:6:9:4:8:1:3:1:7:3:1:7:3:1:4:6:2:3:3:6:1:4:3:2:1:4:1:6:1:6:9:4:8:3:9:9:23:6:3:1:5:3:3:1:1:8:4:3:6:9:9:4:9:1:2:3:8:2:3:1:1:1:8:9:4:9:7:4:7:4:5:3:2:9:23:2:1:9:5:4:8:3:1:3:3:3:1:9:3:9:4:1:4:9:6:8:7:1:4:1:2:3:4:7:1:4:2:2:1:2:2:2:23:6:3:7:1:8:7:5:1:7:9:7:3:1:5:6:8:4:1:4:1:4:2:4:4:6:3:1:3:1:8:4:4:7:2:5:5:5:23:2:8:3:7:3:6:7:8:1:8:5:2:8:4:1:6:1:2:3:1:5:8:7:1:7:8:1:3:3:3:2:4:5:2:4:5:8:23:3:3:4:3:1:2:5:6:4:4:5:3:5:2:1:2:1:4:7:3:4:1:2:1:5:9:4:2:1:2:1:8:4:6:1:6:4:23:1:6:6:8:2:1:3:4:1:1:1:4:5:1:2:3:3:7:2:6:6:6:5:1:2:7:5:5:6:5:6:8:1:4:1:6:1:23:8:4:4:7:6:7:5:8:5:5:1:3:8:4:5:12:4:1:9:4:3:1:4:3:2:4:6:4:2:1:1:2:1:1:3:2:5:23:7:5:1:4:7:1:2:6:4:1:3:1:5:1:2:4:7:3:7:1:7:4:6:1:1:1:3:1:8:4:7:4:5:1:1:7:2:6:5:4:6:5:6:1:7:1:4:1:2:1:4:1:7:2:4:5:5:5:2:4:1:7:3:1:9:5:5:4:3:1:4:5:6:3:8:10:1:3:8:9:9:9:4:8:1:11:4:8:1:4:3:1:7:5:23:8:4:3:7:4:8:7:4:1:4:3:7:4:1:4:6:4:1:10:2:8:4:1:4:1:1:9:9:2:2:1:4:5:5:3:1:2:4:5:7:2:4:7:3:1:1:2:3:4:4:5:2:2:7:1:7:10:2:8:1:2:1:11:4:4:3:8:3:1:8:23:1:2:3:2:2:1:2:5:5:1:1:4:2:9:9:3:6:7:4:6:3:3:1:3:10:2:2:3:5:8:7:6:9:3:1:4:4:5:2:5:2:8:2:2:1:23:1:8:1:7:6:7:3:7:7:2:4:8:8:3:5:5:2:2:10:2:9:9:3:5:1:2:2:1:4:2:7:7:9:11:1:3:9:4:1:4:4:5:9:1:8:23:4:3:1:4:1:3:2:1:1:6:8:9:4:5:1:1:9:2:3:4:11:1:6:6:10:2:2:7:1:9:2:2:1:3:3:4:1:2:4:3:1:3:3:5:5:23:1:2:5:5:8:8:1:3:1:6:1:2:9:5:5:7:5:3:2:4:3:3:1:6:14:2:3:6:2:2:5:4:4:1:4:4:8:3:6:6:7:7:3:5:1:23:4:4:2:2:3:4:8:3:3:2:7:4:1:3:12:1:6:4:4:6:4:3:1:5:2:1:3:1:8:1:1:3:7:3:8:7:7:1:6:6:1:5:6:3:1:23:5:1:6:13:7:8:1:1:5:7:3:8:4:5:5:7:1:4:9:4:4:9:6:4:1:1:6:6:3:2:5:9:4:2:2:4:23:7:2:6:8:8:5:5:1:1:3:3:1:5:9:3:6:6:5:7:7:4:2:2:1:4:2:4:1:3:1:1:7:23:7:5:1:5:5:4:8:4:3:1:3:2:4:4:6:5:5:4:5:1:2:1:3:2:3:8:1:3:9:1:1:8:23:1:4:1:5:7:1:1:5:2:1:7:8:1:1:3:6:6:2:1:12:6:8:6:7:3:5:3:6:6:3:4:5:23:3:8:8:6:3:4:1:1:5:1:5:5:4:7:7:6:3:1:3:1:1:6:6:4:3:6:9:1:3:1:1:4:23:2:6:7:7:5:6:7:2:7:6:1:4:4:3:1:2:1:13:2:4:6:1:4:4:2:6:1:2:5:2:7:8:23:8:1:2:7:3:4:3:4:4:7:7:4:3:5:5:4:3:1:2:7:7:4:3:4:3:1:6:6:1:8:8:9:23:2:1:4:2:2:4:9:1:5:1:3:6:4:2:5:7:4:1:3:4:4:8:5:4:1:2:1:4:3:1:5:5:23:4:6:1:1:5:3:3:1:4:6:3:6:8:3:3:1:4:7:7:3:2:1:4:8:8:4:4:9:3:2:8:8:23:2:1:5:3:3:8:1:5:5:7:7:5:4:1:4:6:6:8:4:4:1:2:1:1:6:6:3:4:9:1:4:9:23:2:5:1:5:5:1:9:9:1:7:1:4:5:3:3:9:3:5:1:8:7:2:3:2:4:1:1:3:4:2:7:5:23:4:3:5:4:9:6:4:7:1:4:4:1:2:2:4:1:4:7:3:1:2:4:9:8:3:2:9:9:3:9:1:8:23:1:3:9:1:1:8:4:4:3:1:7:5:7:9:8:4:1:8:6:5:1:9:1:3:1:1:2:7:2:5:5:9:23:4:11:8:5:1:5:1:2:4:4:5:5:3:5:3:1:5:3:1:6:1:8:1:1:2:4:2:7:5:3:3:1:10:5:2:4:1:1:3:8:3:8:5:8:3:4:6:2:4:8:6:6:7:1:9:3:7:3:3:1:1:4:3:4:1:10:5:1:6:1:1:1:6:1:5:1:9:7:5:5:7:7:3:8:2:2:4:4:1:3:5:3:5:1:2:6:3:6:3:8:1:4:3:5:5:1:4:4:2:8:5:6:6:6:3:1:6:3:3:5:5</t>
-  </si>
-  <si>
-    <t>1,1&amp;500;2,501&amp;780;3,781&amp;1280;4,1281&amp;1330</t>
-  </si>
-  <si>
     <t>Map&lt;int{,}List&lt;int&gt;{&amp;}&gt;{;}</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>2:2:10:10:5:5:7:7:7:11:11:11:5:12:5:4:4:10:10:10:10:3:3:4:4:4:5:12:7:17:7:4:4:4:4:11:11:5:5:1:1:8:12:8:10:10:3:3:3:3:8:8:8:6:6:4:12:11:11:17:11:5:5:5:5:2:2:11:9:9:1:12:1:1:1:5:5:1:1:1:1:10:10:2:6:12:6:6:4:17:4:9:9:9:10:10:2:6:6:9:12:9:9:3:3:3:5:2:2:2:3:3:3:3:12:7:7:8:8:17:1:1:8:8:4:6:6:6:7:12:7:11:11:11:1:1:1:1:11:3:3:2:2:12:2:9:10:10:4:17:1:9:1:1:7:7:3:3:12:3:5:5:5:9:9:6:6:6:6:9:9:9:12:9:1:1:6:6:6:17:8:8:6:6:8:4:4:12:10:10:11:11:11:11:8:8:8:1:1:1:10:12:10:2:2:2:3:3:2:17:7:7:8:8:10:10:12:10:10:7:7:2:2:11:11:11:9:9:7:7:12:7:8:8:8:7:7:7:3:17:3:3:3:2:2:12:2:4:9:9:9:8:8:4:4:4:5:5:5:12:5:6:6:5:5:5:5:9:9:17:9:9:4:4:12:4:6:6:7:7:7:7:8:8:6:6:4:1:12:2:2:2:2:4:10:10:3:10:8:17:10:10:10:10:1:14:1:1:6:6:6:14:6:7:7:2:2:14:7:7:1:1:2:14:2:2:2:7:7:14:8:8:6:5:5:14:8:8:8:10:10:14:10:8:8:10:10:14:8:8:8:8:3:14:3:3:3:1:1:14:1:6:6:5:5:14:2:2:4:4:4:14:11:11:7:7:4:14:4:4:4:6:6:14:7:10:10:10:10:14:1:1:11:11:11:14:11:7:7:7:8:14:8:8:8:1:1:14:1:1:3:3:9:14:9:9:9:4:4:14:3:3:5:5:5:14:5:2:2:4:4:14:7:7:2:2:11:14:11:11:5:5:5:14:2:1:1:2:2:14:2:6:6:9:9:13:9:6:6:10:10:13:10:9:9:7:7:13:6:6:6:6:2:13:2:2:4:4:4:13:5:5:5:4:4:13:9:11:11:6:6:13:6:5:1:1:1:13:8:11:2:2:7:13:7:7:3:3:3:13:5:5:5:5:4:13:4:10:10:3:3:13:2:2:5:3:3:13:11:11:11:9:9:13:8:8:8:8:11:13:11:1:1:1:1:13:9:9:6:6:6:13:2:2:3:3:3:13:4:4:5:5:5:13:4:5:5:11:11:13:6:6:9:9:9:13:10:10:3:3:3:13:9:9:11:9:1:13:1:4:4:4:3:13:7:3:4:3:3:13:5:5:5:8:8:8:2:2:2:2:7:2:2:4:4:11:11:11:10:10:10:1:1:5:5:6:6:6:4:4:4:5:5:5:10:10:3:3:7:7:7:7:10:10:1:1:1:8:6:6:6:7:2:2:2:3:3:3:4:3:3:9:9:4:1:1:3:3:9:9:9:9:8:8:5:2:2:7:7:2:2:9:9:2:2:2:7:7:1:1:1:2:8:8:8:6:6:11:11:1:1:1:1:10:10:8:8:10:1:4:4:4:9:9:9:1:1:1:10:10:10:10:2:2:2:2:1:1:3:3:3:5:5:5:7:7:8:8:8:6:6:6:5:4:4:6:6:9:9:8:8:8:7:7:7:7:2:2:6:6:6:11:11:11:3:3:3:6:6:3:3:9:9:9:3:7:7:3:3:3:3:4:4:4:4:9:10:10:11:11:11:6:6:4:3:3:3:4:4:4:4:1:1:9:9:9:9:5:6:6:6:4:4:4:7:7:7:4:4:4:4:11:5:5:6:6:8:8:8:8:6:7:9:9:10:10:2:2:2:5:5:2:11:11:11:10:10:10:5:5:3:1:1:1:6:6:8:8:5:5:5:10:10:10:7:7:7:2:2:11:11:4:4:1:1:1:3:3:2:8:8:5:5:10:5:5:11:11:11:3:3:1:1:9:9:6:6:5:5:5</t>
+  </si>
+  <si>
+    <t>8:8:8:8:5:5:5:7:7:7:1:1:7:12:7:7:7:10:10:10:10:6:6:6:5:5:1:12:1:17:1:1:8:8:8:8:3:3:3:1:1:2:12:2:2:11:11:10:10:10:3:11:11:3:3:3:12:3:1:17:1:10:10:10:9:6:6:6:6:9:9:12:7:3:3:6:2:2:11:11:11:4:4:1:1:12:3:3:11:17:11:10:4:4:4:9:9:9:11:11:12:11:11:4:4:2:2:10:10:10:8:8:8:8:12:10:10:10:2:17:2:4:5:5:5:5:1:1:8:12:8:9:8:8:8:9:9:5:5:5:4:1:1:12:1:6:10:10:10:17:8:6:6:6:5:5:5:7:12:7:7:5:5:2:4:5:9:9:7:7:7:9:12:9:10:10:2:2:2:17:2:11:11:2:2:2:2:12:11:11:3:3:6:6:6:7:7:7:6:6:2:12:2:7:4:3:5:5:6:17:6:4:4:2:2:3:12:3:3:1:1:9:9:9:9:11:11:8:8:4:12:4:4:3:3:3:1:1:1:17:6:6:4:4:4:12:7:7:7:9:9:5:7:7:7:9:9:9:9:12:11:3:3:3:4:4:4:4:3:17:4:8:8:10:12:10:10:7:8:8:8:5:5:4:6:6:6:9:12:9:6:1:1:5:5:2:2:1:2:17:7:7:7:9:9:14:3:3:8:8:8:14:10:5:8:8:2:14:2:9:9:9:11:14:11:5:5:7:7:14:5:5:4:4:4:14:4:3:3:11:11:14:11:10:10:2:5:14:5:1:1:10:10:14:10:10:8:8:8:14:10:10:2:2:2:14:2:4:4:4:4:14:11:11:11:11:4:14:4:4:4:6:6:14:10:10:10:10:2:14:2:2:3:3:2:14:2:5:5:5:5:14:10:10:11:11:11:14:7:7:7:4:4:14:11:11:9:9:7:14:7:3:3:1:1:14:1:2:2:2:2:14:6:6:6:7:7:14:6:4:4:4:4:14:1:1:3:3:3:14:11:11:1:1:1:13:9:9:8:11:11:13:11:2:2:2:5:13:5:5:5:7:7:13:7:3:3:2:2:13:6:6:6:8:8:13:1:1:8:8:1:13:1:1:9:9:9:13:9:1:1:6:6:13:6:6:3:3:9:13:9:9:1:1:9:13:9:9:4:4:4:13:6:6:1:1:1:13:2:5:5:4:4:13:4:4:8:8:8:13:6:6:6:6:10:13:10:10:8:8:8:13:8:7:7:9:6:13:6:7:7:7:3:13:3:6:6:3:3:13:3:5:5:1:1:13:3:3:10:3:5:13:5:2:2:11:6:13:6:1:5:5:5:13:10:5:3:3:2:13:10:10:10:7:7:3:3:8:8:1:2:7:4:4:4:3:3:11:11:2:2:2:2:4:4:4:9:9:9:9:7:7:5:5:10:10:8:8:1:6:6:1:11:11:2:2:1:1:1:8:8:8:6:6:6:9:9:1:1:1:5:5:5:7:7:7:3:3:3:8:8:8:4:4:2:2:2:4:4:4:5:5:5:6:10:10:8:8:3:3:3:7:7:9:9:9:10:10:10:11:11:9:9:9:9:7:7:8:8:8:5:5:4:4:4:7:7:7:9:9:9:4:4:2:11:11:11:7:7:7:1:1:6:6:7:7:7:7:1:1:1:10:9:11:11:3:3:2:2:8:8:8:8:4:4:10:10:10:3:3:4:4:4:4:2:2:4:4:6:6:2:2:6:6:2:2:11:11:11:1:1:3:3:3:3:5:5:5:3:1:1:1:2:6:11:11:10:10:10:7:7:5:5:5:4:4:9:9:5:5:5:5:3:3:3:3:10:10:5:5:1:1:11:11:11:2:2:2:2:1:1:10:10:10:3:3:6:6:6:6:8:8:8:8:6:6:9:9:2:2:2:9:9:9:5:5:5:5:6:6:6:6:3:3:10:10:1:1:1:1:6:5:5:5:9:8:8:2:2:6:6:6:6:10:3:3:1:4:4:4:5:7:11:4:3:6:6:2:1:1</t>
+  </si>
+  <si>
+    <t>4:4:9:9:9:7:7:7:2:2:10:10:10:12:3:3:3:2:2:4:4:4:4:10:10:10:10:12:8:17:8:7:10:10:6:6:11:11:7:7:7:7:12:9:3:3:3:1:1:1:3:3:3:1:1:9:12:9:2:17:2:2:4:4:9:9:9:4:4:4:8:12:7:1:1:1:8:8:8:9:9:9:8:8:8:12:5:5:3:17:3:9:9:9:9:6:6:6:10:10:12:10:6:6:6:3:3:3:11:4:4:4:4:8:12:8:8:1:1:17:1:1:11:11:11:7:4:4:4:12:5:5:5:6:6:2:2:6:7:7:7:4:4:12:5:5:5:10:10:17:1:1:1:11:11:9:9:11:12:11:6:6:11:11:11:11:8:8:8:8:4:4:12:4:11:5:5:5:8:17:8:8:1:1:2:2:11:12:11:5:2:2:5:5:5:8:8:8:10:3:3:12:5:5:1:1:7:7:7:17:7:6:6:6:8:8:12:10:10:10:10:6:6:7:2:2:9:9:9:9:12:3:11:11:11:2:2:1:1:17:1:1:5:5:5:12:5:7:7:3:3:3:3:2:2:6:6:6:9:12:5:5:5:6:6:6:1:1:10:17:10:10:2:2:12:4:4:2:2:2:2:9:9:3:3:5:7:7:12:7:7:8:3:3:7:10:10:10:6:17:11:11:8:8:1:14:1:1:1:9:9:14:6:6:6:5:1:14:1:1:1:2:2:14:11:11:11:8:8:14:10:10:3:3:3:14:5:5:5:8:1:14:1:6:7:7:8:14:8:9:9:11:2:14:6:6:6:3:3:14:9:9:10:10:10:14:5:5:5:5:4:14:4:9:9:9:9:14:3:3:4:10:10:14:2:2:4:4:4:14:2:2:2:1:1:14:2:10:10:1:1:14:1:10:10:3:3:14:3:3:6:6:5:14:5:4:4:4:8:14:8:1:1:1:1:14:2:2:2:6:6:14:6:4:4:4:6:14:6:6:8:8:8:14:3:4:4:4:4:14:3:3:3:5:5:13:5:8:8:8:8:13:1:1:11:11:11:13:10:10:11:11:11:13:11:6:6:7:7:13:2:2:2:7:7:13:7:4:4:2:2:13:3:3:5:5:9:13:6:6:6:6:4:13:4:7:7:8:8:13:8:8:3:3:11:13:11:11:4:4:4:13:2:2:5:5:3:13:3:2:2:7:7:13:3:3:3:3:6:13:6:9:9:6:6:13:9:9:1:1:1:13:11:11:7:7:10:13:10:10:10:9:9:13:9:5:5:9:9:13:1:10:10:5:5:13:5:5:7:7:7:13:7:2:2:2:4:13:2:11:11:7:7:13:5:5:7:10:4:13:3:3:3:3:4:4:3:11:11:2:2:7:7:7:1:1:6:6:6:6:7:3:3:3:10:10:4:4:7:7:8:8:8:5:5:4:4:4:9:9:4:4:5:5:2:2:2:2:3:3:3:3:8:8:8:9:9:10:10:1:1:1:4:4:10:10:10:6:6:3:3:9:9:9:8:8:11:11:11:7:7:7:7:9:9:9:2:2:6:6:6:5:3:3:3:10:1:1:1:6:6:6:2:2:3:3:8:8:8:4:4:8:8:8:4:4:4:10:10:10:10:5:5:2:2:1:1:7:7:5:5:5:10:10:10:2:2:3:3:11:11:7:1:1:5:5:5:6:11:11:1:1:9:9:9:2:2:11:2:6:6:4:4:4:2:2:11:11:1:1:1:8:8:2:2:2:2:9:9:9:4:4:4:4:1:1:9:9:1:1:10:10:10:10:5:7:7:1:1:1:1:11:11:4:4:6:6:6:8:8:9:9:11:11:5:5:5:9:2:2:2:7:7:7:7:5:3:3:3:1:1:5:7:7:7:5:5:5:5:3:3:4:4:4:10:10:10:10:6:6:6:2:5:5:5:6:6:1:1:1:3:6:6:10:10:4:4:6:6:5:5:5:5:7:7:6:6:6:11:11:11:3:3:3:9:9:9:9:8:8:8:2:2:2:7:11:8:8:8:8</t>
+  </si>
+  <si>
+    <t>8:8:8:5:5:1:1:1:4:4:4:6:2:6:6:8:8:8:8:11:2:2:11:11:5:5:2:2:2:17:4:4:6:6:2:2:1:1:1:2:6:6:6:6:1:1:3:3:4:4:4:4:6:6:3:5:5:5:1:17:1:1:1:2:2:6:8:8:8:4:4:4:4:9:9:2:2:2:2:5:5:1:1:5:8:8:8:8:5:17:7:7:7:10:10:6:5:5:5:3:3:3:3:5:5:5:2:11:5:5:10:10:10:11:1:1:9:9:9:17:4:4:3:3:11:11:8:8:1:1:5:5:5:5:6:6:6:6:7:3:10:10:10:6:6:9:9:11:11:17:2:2:11:11:7:10:10:10:10:11:1:1:1:1:4:2:2:11:11:4:4:10:3:3:3:3:7:7:7:17:7:4:4:4:3:3:3:6:7:7:6:6:6:11:11:10:8:8:8:7:7:7:7:9:9:7:9:9:6:17:1:1:1:6:6:2:7:3:10:9:9:8:8:6:2:2:2:11:11:11:11:4:4:4:3:3:4:4:8:17:2:2:2:5:5:5:5:10:4:4:6:6:3:7:7:1:1:3:3:3:7:7:7:1:1:1:2:2:2:17:7:7:7:9:9:3:3:4:4:3:3:10:10:10:10:8:8:9:9:9:5:5:6:9:9:5:8:3:3:17:5:5:5:10:4:4:3:3:9:3:3:3:8:8:8:8:3:3:5:5:5:2:2:2:2:7:7:7:7:2:2:2:11:11:1:1:5:5:10:5:5:9:9:9:2:2:2:2:7:7:1:1:9:9:9:3:3:3:3:6:6:6:4:4:6:6:7:3:3:3:2:2:3:3:9:1:1:1:1:5:2:2:7:7:7:7:10:6:6:4:4:9:5:5:5:1:1:8:8:8:4:4:10:10:10:5:5:4:4:4:6:9:9:9:9:3:3:3:10:10:10:11:11:3:3:3:3:8:8:4:4:1:1:9:9:10:10:10:2:2:2:8:8:10:10:10:1:11:11:2:2:10:10:10:5:5:5:5:10:10:7:7:7:11:11:7:7:6:6:11:11:4:11:11:1:1:8:8:6:6:6:8:8:8:8:10:8:8:8:1:11:11:11:11:2:2:2:2:4:4:4:1:1:7:7:7:7:6:6:6:1:1:9:9:1:1:3:7:7:7:7:4:4:4:4:6:6:3:3:3:3:9:9:9:5:6:4:4:4:6:6:2:2:2:11:11:11:1:6:8:10:9:9:5:5:5:1:1:9:9:10:10:10:5:5:5:2:2:4:4:4:9:5:5:1:8:8:8:6:6:3:3:1:1:6:6:5:6:6:6:1:1:11:6:8:4:4:2:7:4:1:1:1:1:8:8:8:1:1:10:10:10:9:9:3:9:10:10:4:4:4:4:6:6:5:5:2:2:2:10:10:10:5:5:5:5:2:2:3:3:3:2:2:9:1:1:9:9:8:8:8:6:7:7:10:10:1:1:1:1:6:6:6:6:3:3:3:4:4:5:5:5:5:4:4:4:4:6:6:6:7:7:1:1:9:9:2:6:6:6:4:4:9:6:6:6:7:7:9:8:8:9:9:2:2:2:2:1:1:1:10:10:2:2:11:11:1:1:1:3:3:3:7:11:11:5:5:9:9:9:11:11:11:11:1:1:1:7:7:7:10:10:10:5:5:9:5:5:5:5:2:2:2:4:4:3:3:3:9:9:9:5:5:5:8:8:8:11:11:7:7:7:1:1:11:11:11:10:10:10:10:7:8:8:8:2:2:2:2:9:9:6:6:6:7:7:8:8:8:7:7:5:5:5:6:6:1:1:1:2:2:3:3:3:7:4:4:11:11:11:6:6:4:4:4:4:3:3:5:5:2:2:3:3:3:4:4:11:11:6:6:2:2:1:1:10:10:9:9:6:6:7:7:7:7:4:4:4:4:3:9:5:7:7:4:2:2:2:5:5:5:6:6:8:10:10:4:4:4:11:11:3:3:3:10:8:8:6:8:8:3:3:10:3:3:9:8:8:3:8</t>
+  </si>
+  <si>
+    <t>1,1&amp;300;2,301&amp;600;3,601&amp;900</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:10:10:8:8:2:2:8:8:5:5:5:5:2:2:2:2:5:5:5:11:11:11:2:2:2:4:7:7:17:7:2:2:3:3:8:2:2:2:2:9:4:4:7:7:3:3:2:2:2:2:8:8:7:7:7:11:6:11:17:11:11:11:5:5:2:2:2:10:10:2:2:5:5:5:9:9:6:6:6:3:3:1:1:4:4:4:9:9:17:1:1:8:8:8:6:6:6:8:8:3:3:3:3:11:11:11:9:9:4:4:7:7:7:8:8:8:3:1:17:1:1:7:7:7:7:3:3:3:6:6:10:10:10:10:7:7:11:11:5:5:5:1:1:7:7:6:6:10:17:10:8:8:9:2:2:4:4:8:8:8:8:5:5:5:5:4:4:4:4:10:10:1:3:3:3:7:7:7:17:7:6:6:1:10:10:10:6:9:9:2:2:2:3:3:3:3:5:5:8:8:3:3:1:1:1:3:3:3:17:6:6:4:4:11:11:11:3:1:1:8:6:6:10:10:10:6:4:4:11:11:6:6:3:3:4:4:4:4:17:5:5:2:9:9:6:6:6:6:4:4:8:6:6:9:9:5:1:1:1:5:5:1:1:1:9:1:1:6:17:6:6:1:1:1:1:11:11:4:4:7:7:1:1:4:4:10:9:9:4:4:9:9:5:5:9:5:5:3:17:11:11:3:6:6:9:9:5:5:9:9:9:2:2:2:7:7:7:7:6:6:4:4:4:4:2:2:2:3:3:3:5:5:8:8:3:3:3:2:2:6:6:6:2:2:2:11:11:11:11:4:6:7:3:3:3:8:8:7:7:7:7:1:1:1:9:9:9:9:6:6:3:3:10:10:10:7:7:1:1:10:10:7:7:7:8:8:4:4:4:9:9:11:11:5:5:5:8:7:7:7:7:9:9:9:11:5:5:5:1:1:1:9:2:2:3:3:10:1:1:2:10:3:3:8:8:3:3:3:11:11:4:5:5:5:5:3:9:9:10:10:10:2:2:2:4:4:11:11:11:11:6:6:1:1:8:3:3:3:7:7:4:4:1:1:11:11:11:11:3:3:4:4:10:10:10:10:6:6:6:5:5:6:1:1:1:8:8:5:5:9:7:7:7:7:2:2:2:10:10:10:10:2:2:6:6:4:4:4:4:1:1:1:5:5:5:2:2:2:4:4:4:8:2:2:3:9:9:4:4:4:4:5:5:8:8:6:6:10:10:10:8:8:8:5:5:1:1:6:6:6:6:5:5:4:4:1:1:1:9:9:6:6:1:1:1:10:10:10:6:1:1:8:8:8:7:10:9:9:6:6:2:9:3:3:3:8:5:5:2:2:11:4:4:5:8:6:8:8:3:3:3:2:2:2:2:7:7:7:9:9:6:3:3:9:9:4:4:5:5:10:10:10:5:5:2:2:2:2:6:6:6:7:10:10:10:9:9:4:4:4:4:8:8:10:10:10:3:3:3:11:11:11:4:10:10:10:10:4:5:9:9:8:8:8:7:7:7:5:5:4:4:4:2:2:2:2:3:3:11:11:11:10:10:10:2:2:2:3:3:3:1:1:8:8:6:6:1:5:8:8:6:6:6:6:3:3:3:9:9:9:9:1:1:1:7:7:7:4:4:4:2:2:8:8:4:4:4:4:11:11:4:4:4:4:7:7:7:10:10:10:1:1:1:7:7:1:1:1:5:5:5:5:6:6:6:6:9:9:5:5:7:7:7:5:5:5:10:10:10:5:5:1:1:7:7:7:6:6:3:3:9:9:9:9:1:1:8:8:8:10:9:11:5:7:7:4:4:3:3:3:3:5:5:5:7:7:5:5:5:2:2:2:6:6:6:11:9:9:9:3:3:3:11:11:11:11:3:3:3:3:2:2:10:10:1:8:2:2:2:2:4:4:4:1:1:8:8:8:8:6:6:6:5:5:1:8:2:2:6:11:11:11:1:1:1:1:9:9:6:1:6:6:6:8:8:6:6:6:1:2:2:11:11:8:1:8:8:3:11:4:4:5:5:1:1:1:3:9:4</t>
   </si>
 </sst>
 </file>
@@ -123,23 +124,27 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -543,7 +548,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>6</v>
@@ -582,11 +587,11 @@
       <c r="C5" s="3">
         <v>1</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -599,7 +604,7 @@
       <c r="C6" s="3">
         <v>2</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="4" t="s">
@@ -616,7 +621,7 @@
       <c r="C7" s="3">
         <v>3</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="4" t="s">
@@ -633,7 +638,7 @@
       <c r="C8" s="3">
         <v>4</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="4" t="s">
@@ -650,7 +655,7 @@
       <c r="C9" s="3">
         <v>5</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="4" t="s">

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A26BD4-2960-453D-9305-0A146AD6DFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{086271A4-CF99-47E1-BCFE-86E25FC45DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,23 +89,23 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>2:2:10:10:5:5:7:7:7:11:11:11:5:12:5:4:4:10:10:10:10:3:3:4:4:4:5:12:7:17:7:4:4:4:4:11:11:5:5:1:1:8:12:8:10:10:3:3:3:3:8:8:8:6:6:4:12:11:11:17:11:5:5:5:5:2:2:11:9:9:1:12:1:1:1:5:5:1:1:1:1:10:10:2:6:12:6:6:4:17:4:9:9:9:10:10:2:6:6:9:12:9:9:3:3:3:5:2:2:2:3:3:3:3:12:7:7:8:8:17:1:1:8:8:4:6:6:6:7:12:7:11:11:11:1:1:1:1:11:3:3:2:2:12:2:9:10:10:4:17:1:9:1:1:7:7:3:3:12:3:5:5:5:9:9:6:6:6:6:9:9:9:12:9:1:1:6:6:6:17:8:8:6:6:8:4:4:12:10:10:11:11:11:11:8:8:8:1:1:1:10:12:10:2:2:2:3:3:2:17:7:7:8:8:10:10:12:10:10:7:7:2:2:11:11:11:9:9:7:7:12:7:8:8:8:7:7:7:3:17:3:3:3:2:2:12:2:4:9:9:9:8:8:4:4:4:5:5:5:12:5:6:6:5:5:5:5:9:9:17:9:9:4:4:12:4:6:6:7:7:7:7:8:8:6:6:4:1:12:2:2:2:2:4:10:10:3:10:8:17:10:10:10:10:1:14:1:1:6:6:6:14:6:7:7:2:2:14:7:7:1:1:2:14:2:2:2:7:7:14:8:8:6:5:5:14:8:8:8:10:10:14:10:8:8:10:10:14:8:8:8:8:3:14:3:3:3:1:1:14:1:6:6:5:5:14:2:2:4:4:4:14:11:11:7:7:4:14:4:4:4:6:6:14:7:10:10:10:10:14:1:1:11:11:11:14:11:7:7:7:8:14:8:8:8:1:1:14:1:1:3:3:9:14:9:9:9:4:4:14:3:3:5:5:5:14:5:2:2:4:4:14:7:7:2:2:11:14:11:11:5:5:5:14:2:1:1:2:2:14:2:6:6:9:9:13:9:6:6:10:10:13:10:9:9:7:7:13:6:6:6:6:2:13:2:2:4:4:4:13:5:5:5:4:4:13:9:11:11:6:6:13:6:5:1:1:1:13:8:11:2:2:7:13:7:7:3:3:3:13:5:5:5:5:4:13:4:10:10:3:3:13:2:2:5:3:3:13:11:11:11:9:9:13:8:8:8:8:11:13:11:1:1:1:1:13:9:9:6:6:6:13:2:2:3:3:3:13:4:4:5:5:5:13:4:5:5:11:11:13:6:6:9:9:9:13:10:10:3:3:3:13:9:9:11:9:1:13:1:4:4:4:3:13:7:3:4:3:3:13:5:5:5:8:8:8:2:2:2:2:7:2:2:4:4:11:11:11:10:10:10:1:1:5:5:6:6:6:4:4:4:5:5:5:10:10:3:3:7:7:7:7:10:10:1:1:1:8:6:6:6:7:2:2:2:3:3:3:4:3:3:9:9:4:1:1:3:3:9:9:9:9:8:8:5:2:2:7:7:2:2:9:9:2:2:2:7:7:1:1:1:2:8:8:8:6:6:11:11:1:1:1:1:10:10:8:8:10:1:4:4:4:9:9:9:1:1:1:10:10:10:10:2:2:2:2:1:1:3:3:3:5:5:5:7:7:8:8:8:6:6:6:5:4:4:6:6:9:9:8:8:8:7:7:7:7:2:2:6:6:6:11:11:11:3:3:3:6:6:3:3:9:9:9:3:7:7:3:3:3:3:4:4:4:4:9:10:10:11:11:11:6:6:4:3:3:3:4:4:4:4:1:1:9:9:9:9:5:6:6:6:4:4:4:7:7:7:4:4:4:4:11:5:5:6:6:8:8:8:8:6:7:9:9:10:10:2:2:2:5:5:2:11:11:11:10:10:10:5:5:3:1:1:1:6:6:8:8:5:5:5:10:10:10:7:7:7:2:2:11:11:4:4:1:1:1:3:3:2:8:8:5:5:10:5:5:11:11:11:3:3:1:1:9:9:6:6:5:5:5</t>
-  </si>
-  <si>
-    <t>8:8:8:8:5:5:5:7:7:7:1:1:7:12:7:7:7:10:10:10:10:6:6:6:5:5:1:12:1:17:1:1:8:8:8:8:3:3:3:1:1:2:12:2:2:11:11:10:10:10:3:11:11:3:3:3:12:3:1:17:1:10:10:10:9:6:6:6:6:9:9:12:7:3:3:6:2:2:11:11:11:4:4:1:1:12:3:3:11:17:11:10:4:4:4:9:9:9:11:11:12:11:11:4:4:2:2:10:10:10:8:8:8:8:12:10:10:10:2:17:2:4:5:5:5:5:1:1:8:12:8:9:8:8:8:9:9:5:5:5:4:1:1:12:1:6:10:10:10:17:8:6:6:6:5:5:5:7:12:7:7:5:5:2:4:5:9:9:7:7:7:9:12:9:10:10:2:2:2:17:2:11:11:2:2:2:2:12:11:11:3:3:6:6:6:7:7:7:6:6:2:12:2:7:4:3:5:5:6:17:6:4:4:2:2:3:12:3:3:1:1:9:9:9:9:11:11:8:8:4:12:4:4:3:3:3:1:1:1:17:6:6:4:4:4:12:7:7:7:9:9:5:7:7:7:9:9:9:9:12:11:3:3:3:4:4:4:4:3:17:4:8:8:10:12:10:10:7:8:8:8:5:5:4:6:6:6:9:12:9:6:1:1:5:5:2:2:1:2:17:7:7:7:9:9:14:3:3:8:8:8:14:10:5:8:8:2:14:2:9:9:9:11:14:11:5:5:7:7:14:5:5:4:4:4:14:4:3:3:11:11:14:11:10:10:2:5:14:5:1:1:10:10:14:10:10:8:8:8:14:10:10:2:2:2:14:2:4:4:4:4:14:11:11:11:11:4:14:4:4:4:6:6:14:10:10:10:10:2:14:2:2:3:3:2:14:2:5:5:5:5:14:10:10:11:11:11:14:7:7:7:4:4:14:11:11:9:9:7:14:7:3:3:1:1:14:1:2:2:2:2:14:6:6:6:7:7:14:6:4:4:4:4:14:1:1:3:3:3:14:11:11:1:1:1:13:9:9:8:11:11:13:11:2:2:2:5:13:5:5:5:7:7:13:7:3:3:2:2:13:6:6:6:8:8:13:1:1:8:8:1:13:1:1:9:9:9:13:9:1:1:6:6:13:6:6:3:3:9:13:9:9:1:1:9:13:9:9:4:4:4:13:6:6:1:1:1:13:2:5:5:4:4:13:4:4:8:8:8:13:6:6:6:6:10:13:10:10:8:8:8:13:8:7:7:9:6:13:6:7:7:7:3:13:3:6:6:3:3:13:3:5:5:1:1:13:3:3:10:3:5:13:5:2:2:11:6:13:6:1:5:5:5:13:10:5:3:3:2:13:10:10:10:7:7:3:3:8:8:1:2:7:4:4:4:3:3:11:11:2:2:2:2:4:4:4:9:9:9:9:7:7:5:5:10:10:8:8:1:6:6:1:11:11:2:2:1:1:1:8:8:8:6:6:6:9:9:1:1:1:5:5:5:7:7:7:3:3:3:8:8:8:4:4:2:2:2:4:4:4:5:5:5:6:10:10:8:8:3:3:3:7:7:9:9:9:10:10:10:11:11:9:9:9:9:7:7:8:8:8:5:5:4:4:4:7:7:7:9:9:9:4:4:2:11:11:11:7:7:7:1:1:6:6:7:7:7:7:1:1:1:10:9:11:11:3:3:2:2:8:8:8:8:4:4:10:10:10:3:3:4:4:4:4:2:2:4:4:6:6:2:2:6:6:2:2:11:11:11:1:1:3:3:3:3:5:5:5:3:1:1:1:2:6:11:11:10:10:10:7:7:5:5:5:4:4:9:9:5:5:5:5:3:3:3:3:10:10:5:5:1:1:11:11:11:2:2:2:2:1:1:10:10:10:3:3:6:6:6:6:8:8:8:8:6:6:9:9:2:2:2:9:9:9:5:5:5:5:6:6:6:6:3:3:10:10:1:1:1:1:6:5:5:5:9:8:8:2:2:6:6:6:6:10:3:3:1:4:4:4:5:7:11:4:3:6:6:2:1:1</t>
-  </si>
-  <si>
-    <t>4:4:9:9:9:7:7:7:2:2:10:10:10:12:3:3:3:2:2:4:4:4:4:10:10:10:10:12:8:17:8:7:10:10:6:6:11:11:7:7:7:7:12:9:3:3:3:1:1:1:3:3:3:1:1:9:12:9:2:17:2:2:4:4:9:9:9:4:4:4:8:12:7:1:1:1:8:8:8:9:9:9:8:8:8:12:5:5:3:17:3:9:9:9:9:6:6:6:10:10:12:10:6:6:6:3:3:3:11:4:4:4:4:8:12:8:8:1:1:17:1:1:11:11:11:7:4:4:4:12:5:5:5:6:6:2:2:6:7:7:7:4:4:12:5:5:5:10:10:17:1:1:1:11:11:9:9:11:12:11:6:6:11:11:11:11:8:8:8:8:4:4:12:4:11:5:5:5:8:17:8:8:1:1:2:2:11:12:11:5:2:2:5:5:5:8:8:8:10:3:3:12:5:5:1:1:7:7:7:17:7:6:6:6:8:8:12:10:10:10:10:6:6:7:2:2:9:9:9:9:12:3:11:11:11:2:2:1:1:17:1:1:5:5:5:12:5:7:7:3:3:3:3:2:2:6:6:6:9:12:5:5:5:6:6:6:1:1:10:17:10:10:2:2:12:4:4:2:2:2:2:9:9:3:3:5:7:7:12:7:7:8:3:3:7:10:10:10:6:17:11:11:8:8:1:14:1:1:1:9:9:14:6:6:6:5:1:14:1:1:1:2:2:14:11:11:11:8:8:14:10:10:3:3:3:14:5:5:5:8:1:14:1:6:7:7:8:14:8:9:9:11:2:14:6:6:6:3:3:14:9:9:10:10:10:14:5:5:5:5:4:14:4:9:9:9:9:14:3:3:4:10:10:14:2:2:4:4:4:14:2:2:2:1:1:14:2:10:10:1:1:14:1:10:10:3:3:14:3:3:6:6:5:14:5:4:4:4:8:14:8:1:1:1:1:14:2:2:2:6:6:14:6:4:4:4:6:14:6:6:8:8:8:14:3:4:4:4:4:14:3:3:3:5:5:13:5:8:8:8:8:13:1:1:11:11:11:13:10:10:11:11:11:13:11:6:6:7:7:13:2:2:2:7:7:13:7:4:4:2:2:13:3:3:5:5:9:13:6:6:6:6:4:13:4:7:7:8:8:13:8:8:3:3:11:13:11:11:4:4:4:13:2:2:5:5:3:13:3:2:2:7:7:13:3:3:3:3:6:13:6:9:9:6:6:13:9:9:1:1:1:13:11:11:7:7:10:13:10:10:10:9:9:13:9:5:5:9:9:13:1:10:10:5:5:13:5:5:7:7:7:13:7:2:2:2:4:13:2:11:11:7:7:13:5:5:7:10:4:13:3:3:3:3:4:4:3:11:11:2:2:7:7:7:1:1:6:6:6:6:7:3:3:3:10:10:4:4:7:7:8:8:8:5:5:4:4:4:9:9:4:4:5:5:2:2:2:2:3:3:3:3:8:8:8:9:9:10:10:1:1:1:4:4:10:10:10:6:6:3:3:9:9:9:8:8:11:11:11:7:7:7:7:9:9:9:2:2:6:6:6:5:3:3:3:10:1:1:1:6:6:6:2:2:3:3:8:8:8:4:4:8:8:8:4:4:4:10:10:10:10:5:5:2:2:1:1:7:7:5:5:5:10:10:10:2:2:3:3:11:11:7:1:1:5:5:5:6:11:11:1:1:9:9:9:2:2:11:2:6:6:4:4:4:2:2:11:11:1:1:1:8:8:2:2:2:2:9:9:9:4:4:4:4:1:1:9:9:1:1:10:10:10:10:5:7:7:1:1:1:1:11:11:4:4:6:6:6:8:8:9:9:11:11:5:5:5:9:2:2:2:7:7:7:7:5:3:3:3:1:1:5:7:7:7:5:5:5:5:3:3:4:4:4:10:10:10:10:6:6:6:2:5:5:5:6:6:1:1:1:3:6:6:10:10:4:4:6:6:5:5:5:5:7:7:6:6:6:11:11:11:3:3:3:9:9:9:9:8:8:8:2:2:2:7:11:8:8:8:8</t>
-  </si>
-  <si>
-    <t>8:8:8:5:5:1:1:1:4:4:4:6:2:6:6:8:8:8:8:11:2:2:11:11:5:5:2:2:2:17:4:4:6:6:2:2:1:1:1:2:6:6:6:6:1:1:3:3:4:4:4:4:6:6:3:5:5:5:1:17:1:1:1:2:2:6:8:8:8:4:4:4:4:9:9:2:2:2:2:5:5:1:1:5:8:8:8:8:5:17:7:7:7:10:10:6:5:5:5:3:3:3:3:5:5:5:2:11:5:5:10:10:10:11:1:1:9:9:9:17:4:4:3:3:11:11:8:8:1:1:5:5:5:5:6:6:6:6:7:3:10:10:10:6:6:9:9:11:11:17:2:2:11:11:7:10:10:10:10:11:1:1:1:1:4:2:2:11:11:4:4:10:3:3:3:3:7:7:7:17:7:4:4:4:3:3:3:6:7:7:6:6:6:11:11:10:8:8:8:7:7:7:7:9:9:7:9:9:6:17:1:1:1:6:6:2:7:3:10:9:9:8:8:6:2:2:2:11:11:11:11:4:4:4:3:3:4:4:8:17:2:2:2:5:5:5:5:10:4:4:6:6:3:7:7:1:1:3:3:3:7:7:7:1:1:1:2:2:2:17:7:7:7:9:9:3:3:4:4:3:3:10:10:10:10:8:8:9:9:9:5:5:6:9:9:5:8:3:3:17:5:5:5:10:4:4:3:3:9:3:3:3:8:8:8:8:3:3:5:5:5:2:2:2:2:7:7:7:7:2:2:2:11:11:1:1:5:5:10:5:5:9:9:9:2:2:2:2:7:7:1:1:9:9:9:3:3:3:3:6:6:6:4:4:6:6:7:3:3:3:2:2:3:3:9:1:1:1:1:5:2:2:7:7:7:7:10:6:6:4:4:9:5:5:5:1:1:8:8:8:4:4:10:10:10:5:5:4:4:4:6:9:9:9:9:3:3:3:10:10:10:11:11:3:3:3:3:8:8:4:4:1:1:9:9:10:10:10:2:2:2:8:8:10:10:10:1:11:11:2:2:10:10:10:5:5:5:5:10:10:7:7:7:11:11:7:7:6:6:11:11:4:11:11:1:1:8:8:6:6:6:8:8:8:8:10:8:8:8:1:11:11:11:11:2:2:2:2:4:4:4:1:1:7:7:7:7:6:6:6:1:1:9:9:1:1:3:7:7:7:7:4:4:4:4:6:6:3:3:3:3:9:9:9:5:6:4:4:4:6:6:2:2:2:11:11:11:1:6:8:10:9:9:5:5:5:1:1:9:9:10:10:10:5:5:5:2:2:4:4:4:9:5:5:1:8:8:8:6:6:3:3:1:1:6:6:5:6:6:6:1:1:11:6:8:4:4:2:7:4:1:1:1:1:8:8:8:1:1:10:10:10:9:9:3:9:10:10:4:4:4:4:6:6:5:5:2:2:2:10:10:10:5:5:5:5:2:2:3:3:3:2:2:9:1:1:9:9:8:8:8:6:7:7:10:10:1:1:1:1:6:6:6:6:3:3:3:4:4:5:5:5:5:4:4:4:4:6:6:6:7:7:1:1:9:9:2:6:6:6:4:4:9:6:6:6:7:7:9:8:8:9:9:2:2:2:2:1:1:1:10:10:2:2:11:11:1:1:1:3:3:3:7:11:11:5:5:9:9:9:11:11:11:11:1:1:1:7:7:7:10:10:10:5:5:9:5:5:5:5:2:2:2:4:4:3:3:3:9:9:9:5:5:5:8:8:8:11:11:7:7:7:1:1:11:11:11:10:10:10:10:7:8:8:8:2:2:2:2:9:9:6:6:6:7:7:8:8:8:7:7:5:5:5:6:6:1:1:1:2:2:3:3:3:7:4:4:11:11:11:6:6:4:4:4:4:3:3:5:5:2:2:3:3:3:4:4:11:11:6:6:2:2:1:1:10:10:9:9:6:6:7:7:7:7:4:4:4:4:3:9:5:7:7:4:2:2:2:5:5:5:6:6:8:10:10:4:4:4:11:11:3:3:3:10:8:8:6:8:8:3:3:10:3:3:9:8:8:3:8</t>
-  </si>
-  <si>
     <t>1,1&amp;300;2,301&amp;600;3,601&amp;900</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>10:10:10:8:8:2:2:8:8:5:5:5:5:2:2:2:2:5:5:5:11:11:11:2:2:2:4:7:7:17:7:2:2:3:3:8:2:2:2:2:9:4:4:7:7:3:3:2:2:2:2:8:8:7:7:7:11:6:11:17:11:11:11:5:5:2:2:2:10:10:2:2:5:5:5:9:9:6:6:6:3:3:1:1:4:4:4:9:9:17:1:1:8:8:8:6:6:6:8:8:3:3:3:3:11:11:11:9:9:4:4:7:7:7:8:8:8:3:1:17:1:1:7:7:7:7:3:3:3:6:6:10:10:10:10:7:7:11:11:5:5:5:1:1:7:7:6:6:10:17:10:8:8:9:2:2:4:4:8:8:8:8:5:5:5:5:4:4:4:4:10:10:1:3:3:3:7:7:7:17:7:6:6:1:10:10:10:6:9:9:2:2:2:3:3:3:3:5:5:8:8:3:3:1:1:1:3:3:3:17:6:6:4:4:11:11:11:3:1:1:8:6:6:10:10:10:6:4:4:11:11:6:6:3:3:4:4:4:4:17:5:5:2:9:9:6:6:6:6:4:4:8:6:6:9:9:5:1:1:1:5:5:1:1:1:9:1:1:6:17:6:6:1:1:1:1:11:11:4:4:7:7:1:1:4:4:10:9:9:4:4:9:9:5:5:9:5:5:3:17:11:11:3:6:6:9:9:5:5:9:9:9:2:2:2:7:7:7:7:6:6:4:4:4:4:2:2:2:3:3:3:5:5:8:8:3:3:3:2:2:6:6:6:2:2:2:11:11:11:11:4:6:7:3:3:3:8:8:7:7:7:7:1:1:1:9:9:9:9:6:6:3:3:10:10:10:7:7:1:1:10:10:7:7:7:8:8:4:4:4:9:9:11:11:5:5:5:8:7:7:7:7:9:9:9:11:5:5:5:1:1:1:9:2:2:3:3:10:1:1:2:10:3:3:8:8:3:3:3:11:11:4:5:5:5:5:3:9:9:10:10:10:2:2:2:4:4:11:11:11:11:6:6:1:1:8:3:3:3:7:7:4:4:1:1:11:11:11:11:3:3:4:4:10:10:10:10:6:6:6:5:5:6:1:1:1:8:8:5:5:9:7:7:7:7:2:2:2:10:10:10:10:2:2:6:6:4:4:4:4:1:1:1:5:5:5:2:2:2:4:4:4:8:2:2:3:9:9:4:4:4:4:5:5:8:8:6:6:10:10:10:8:8:8:5:5:1:1:6:6:6:6:5:5:4:4:1:1:1:9:9:6:6:1:1:1:10:10:10:6:1:1:8:8:8:7:10:9:9:6:6:2:9:3:3:3:8:5:5:2:2:11:4:4:5:8:6:8:8:3:3:3:2:2:2:2:7:7:7:9:9:6:3:3:9:9:4:4:5:5:10:10:10:5:5:2:2:2:2:6:6:6:7:10:10:10:9:9:4:4:4:4:8:8:10:10:10:3:3:3:11:11:11:4:10:10:10:10:4:5:9:9:8:8:8:7:7:7:5:5:4:4:4:2:2:2:2:3:3:11:11:11:10:10:10:2:2:2:3:3:3:1:1:8:8:6:6:1:5:8:8:6:6:6:6:3:3:3:9:9:9:9:1:1:1:7:7:7:4:4:4:2:2:8:8:4:4:4:4:11:11:4:4:4:4:7:7:7:10:10:10:1:1:1:7:7:1:1:1:5:5:5:5:6:6:6:6:9:9:5:5:7:7:7:5:5:5:10:10:10:5:5:1:1:7:7:7:6:6:3:3:9:9:9:9:1:1:8:8:8:10:9:11:5:7:7:4:4:3:3:3:3:5:5:5:7:7:5:5:5:2:2:2:6:6:6:11:9:9:9:3:3:3:11:11:11:11:3:3:3:3:2:2:10:10:1:8:2:2:2:2:4:4:4:1:1:8:8:8:8:6:6:6:5:5:1:8:2:2:6:11:11:11:1:1:1:1:9:9:6:1:6:6:6:8:8:6:6:6:1:2:2:11:11:8:1:8:8:3:11:4:4:5:5:1:1:1:3:9:4</t>
+  </si>
+  <si>
+    <t>2:2:10:10:5:5:7:7:7:11:11:11:5:12:5:4:4:10:10:10:10:3:3:4:4:4:5:12:7:17:7:4:4:4:4:11:11:5:5:1:1:8:12:8:10:10:3:3:3:3:8:8:8:6:6:4:12:11:11:17:11:5:5:5:5:2:2:11:9:9:1:12:1:1:1:5:5:1:1:1:1:10:10:2:6:12:6:6:4:17:4:9:9:9:10:10:2:6:6:9:12:9:9:3:3:3:5:2:2:2:3:3:3:3:12:7:7:8:8:17:1:1:8:8:4:6:6:6:7:12:7:11:11:11:1:1:1:1:11:3:3:2:2:12:2:9:10:10:4:17:1:9:1:1:7:7:3:3:12:3:5:5:5:9:9:6:6:6:6:9:9:9:12:9:1:1:6:6:6:17:8:8:6:6:8:4:4:12:10:10:11:11:11:11:8:8:8:1:1:1:10:12:10:2:2:2:3:3:2:17:7:7:8:8:10:10:12:10:10:7:7:2:2:11:11:11:9:9:7:7:12:7:8:8:8:7:7:7:3:17:3:3:3:2:2:12:2:4:9:9:9:8:8:4:4:4:5:5:5:12:5:6:6:5:5:5:5:9:9:17:9:9:4:4:12:4:6:6:7:7:7:7:8:8:6:6:4:1:12:2:2:2:2:4:10:10:3:10:8:17:10:10:10:10:1:14:1:1:6:6:6:14:6:7:7:2:2:14:7:7:1:1:2:14:2:2:2:7:7:14:8:8:6:5:5:14:8:8:8:10:10:14:10:8:8:10:10:14:8:8:8:8:3:14:3:3:3:1:1:14:1:6:6:5:5:14:2:2:4:4:4:14:11:11:7:7:4:14:4:4:4:6:6:14:7:10:10:10:10:14:1:1:11:11:11:14:11:7:7:7:8:14:8:8:8:1:1:14:1:1:3:3:9:14:9:9:9:4:4:14:3:3:5:5:5:14:5:2:2:4:4:14:7:7:2:2:11:14:11:11:5:5:5:14:2:1:1:2:2:14:2:6:6:9:9:13:9:6:6:10:10:13:10:9:9:7:7:13:6:6:6:6:2:13:2:2:4:4:4:13:5:5:5:4:4:13:9:11:11:6:6:13:6:5:1:1:1:13:8:11:2:2:7:13:7:7:3:3:3:13:5:5:5:5:4:13:4:10:10:3:3:13:2:2:5:3:3:13:11:11:11:9:9:13:8:8:8:8:11:13:11:1:1:1:1:13:9:9:6:6:6:13:2:2:3:3:3:13:4:4:5:5:5:13:4:5:5:11:11:13:6:6:9:9:9:13:10:10:3:3:3:13:9:9:11:9:1:13:1:4:4:4:3:13:7:3:4:3:3:13:5:5:5:8:8:8:2:2:2:2:7:2:2:4:4:11:11:11:10:10:10:1:1:5:5:6:6:6:4:4:4:5:5:5:10:10:3:3:7:7:7:7:10:10:1:1:1:8:6:6:6:7:2:2:2:3:3:3:4:3:3:9:9:4:1:1:3:3:9:9:9:9:8:8:5:2:2:7:7:2:2:9:9:2:2:2:7:7:1:1:1:2:8:8:8:6:6:11:11:1:1:1:1:10:10:8:8:10:1:4:4:4:9:9:9:1:1:1:10:10:10:10:2:2:2:2:1:1:3:3:3:5:5:5:7:7:8:8:8:6:6:6:5:4:4:6:6:9:9:8:8:8:7:7:7:7:2:2:6:6:6:11:11:11:3:3:3:6:6:3:3:9:9:9:3:7:7:3:3:3:3:4:4:4:4:9:10:10:11:11:11:6:6:4:3:3:3:4:4:4:4:1:1:9:9:9:9:5:6:6:6:4:4:4:7:7:7:4:4:4:4:11:5:5:6:6:8:8:8:8:6:7:9:9:10:10:2:2:2:5:5:2:11:11:11:10:10:10:5:5:3:1:1:1:6:6:8:8:5:5:5:10:10:10:7:7:7:2:2:11:11:4:4:1:1:1:3:3:2:8:8:5:5:10:5:5:11:11:11:3:3:1:1:9:9:6:6:5:5:5</t>
+  </si>
+  <si>
+    <t>8:8:8:8:5:5:5:7:7:7:1:1:7:12:7:7:7:10:10:10:10:6:6:6:5:5:1:12:1:17:1:1:8:8:8:8:3:3:3:1:1:2:12:2:2:11:11:10:10:10:3:11:11:3:3:3:12:3:1:17:1:10:10:10:9:6:6:6:6:9:9:12:7:3:3:6:2:2:11:11:11:4:4:1:1:12:3:3:11:17:11:10:4:4:4:9:9:9:11:11:12:11:11:4:4:2:2:10:10:10:8:8:8:8:12:10:10:10:2:17:2:4:5:5:5:5:1:1:8:12:8:9:8:8:8:9:9:5:5:5:4:1:1:12:1:6:10:10:10:17:8:6:6:6:5:5:5:7:12:7:7:5:5:2:4:5:9:9:7:7:7:9:12:9:10:10:2:2:2:17:2:11:11:2:2:2:2:12:11:11:3:3:6:6:6:7:7:7:6:6:2:12:2:7:4:3:5:5:6:17:6:4:4:2:2:3:12:3:3:1:1:9:9:9:9:11:11:8:8:4:12:4:4:3:3:3:1:1:1:17:6:6:4:4:4:12:7:7:7:9:9:5:7:7:7:9:9:9:9:12:11:3:3:3:4:4:4:4:3:17:4:8:8:10:12:10:10:7:8:8:8:5:5:4:6:6:6:9:12:9:6:1:1:5:5:2:2:1:2:17:7:7:7:9:9:14:3:3:8:8:8:14:10:5:8:8:2:14:2:9:9:9:11:14:11:5:5:7:7:14:5:5:4:4:4:14:4:3:3:11:11:14:11:10:10:2:5:14:5:1:1:10:10:14:10:10:8:8:8:14:10:10:2:2:2:14:2:4:4:4:4:14:11:11:11:11:4:14:4:4:4:6:6:14:10:10:10:10:2:14:2:2:3:3:2:14:2:5:5:5:5:14:10:10:11:11:11:14:7:7:7:4:4:14:11:11:9:9:7:14:7:3:3:1:1:14:1:2:2:2:2:14:6:6:6:7:7:14:6:4:4:4:4:14:1:1:3:3:3:14:11:11:1:1:1:13:9:9:8:11:11:13:11:2:2:2:5:13:5:5:5:7:7:13:7:3:3:2:2:13:6:6:6:8:8:13:1:1:8:8:1:13:1:1:9:9:9:13:9:1:1:6:6:13:6:6:3:3:9:13:9:9:1:1:9:13:9:9:4:4:4:13:6:6:1:1:1:13:2:5:5:4:4:13:4:4:8:8:8:13:6:6:6:6:10:13:10:10:8:8:8:13:8:7:7:9:6:13:6:7:7:7:3:13:3:6:6:3:3:13:3:5:5:1:1:13:3:3:10:3:5:13:5:2:2:11:6:13:6:1:5:5:5:13:10:5:3:3:2:13:10:10:10:7:7:3:3:8:8:1:2:7:4:4:4:3:3:11:11:2:2:2:2:4:4:4:9:9:9:9:7:7:5:5:10:10:8:8:1:6:6:1:11:11:2:2:1:1:1:8:8:8:6:6:6:9:9:1:1:1:5:5:5:7:7:7:3:3:3:8:8:8:4:4:2:2:2:4:4:4:5:5:5:6:10:10:8:8:3:3:3:7:7:9:9:9:10:10:10:11:11:9:9:9:9:7:7:8:8:8:5:5:4:4:4:7:7:7:9:9:9:4:4:2:11:11:11:7:7:7:1:1:6:6:7:7:7:7:1:1:1:10:9:11:11:3:3:2:2:8:8:8:8:4:4:10:10:10:3:3:4:4:4:4:2:2:4:4:6:6:2:2:6:6:2:2:11:11:11:1:1:3:3:3:3:5:5:5:3:1:1:1:2:6:11:11:10:10:10:7:7:5:5:5:4:4:9:9:5:5:5:5:3:3:3:3:10:10:5:5:1:1:11:11:11:2:2:2:2:1:1:10:10:10:3:3:6:6:6:6:8:8:8:8:6:6:9:9:2:2:2:9:9:9:5:5:5:5:6:6:6:6:3:3:10:10:1:1:1:1:6:5:5:5:9:8:8:2:2:6:6:6:6:10:3:3:1:4:4:4:5:7:11:4:3:6:6:2:1:1</t>
+  </si>
+  <si>
+    <t>4:4:9:9:9:7:7:7:2:2:10:10:10:12:3:3:3:2:2:4:4:4:4:10:10:10:10:12:8:17:8:7:10:10:6:6:11:11:7:7:7:7:12:9:3:3:3:1:1:1:3:3:3:1:1:9:12:9:2:17:2:2:4:4:9:9:9:4:4:4:8:12:7:1:1:1:8:8:8:9:9:9:8:8:8:12:5:5:3:17:3:9:9:9:9:6:6:6:10:10:12:10:6:6:6:3:3:3:11:4:4:4:4:8:12:8:8:1:1:17:1:1:11:11:11:7:4:4:4:12:5:5:5:6:6:2:2:6:7:7:7:4:4:12:5:5:5:10:10:17:1:1:1:11:11:9:9:11:12:11:6:6:11:11:11:11:8:8:8:8:4:4:12:4:11:5:5:5:8:17:8:8:1:1:2:2:11:12:11:5:2:2:5:5:5:8:8:8:10:3:3:12:5:5:1:1:7:7:7:17:7:6:6:6:8:8:12:10:10:10:10:6:6:7:2:2:9:9:9:9:12:3:11:11:11:2:2:1:1:17:1:1:5:5:5:12:5:7:7:3:3:3:3:2:2:6:6:6:9:12:5:5:5:6:6:6:1:1:10:17:10:10:2:2:12:4:4:2:2:2:2:9:9:3:3:5:7:7:12:7:7:8:3:3:7:10:10:10:6:17:11:11:8:8:1:14:1:1:1:9:9:14:6:6:6:5:1:14:1:1:1:2:2:14:11:11:11:8:8:14:10:10:3:3:3:14:5:5:5:8:1:14:1:6:7:7:8:14:8:9:9:11:2:14:6:6:6:3:3:14:9:9:10:10:10:14:5:5:5:5:4:14:4:9:9:9:9:14:3:3:4:10:10:14:2:2:4:4:4:14:2:2:2:1:1:14:2:10:10:1:1:14:1:10:10:3:3:14:3:3:6:6:5:14:5:4:4:4:8:14:8:1:1:1:1:14:2:2:2:6:6:14:6:4:4:4:6:14:6:6:8:8:8:14:3:4:4:4:4:14:3:3:3:5:5:13:5:8:8:8:8:13:1:1:11:11:11:13:10:10:11:11:11:13:11:6:6:7:7:13:2:2:2:7:7:13:7:4:4:2:2:13:3:3:5:5:9:13:6:6:6:6:4:13:4:7:7:8:8:13:8:8:3:3:11:13:11:11:4:4:4:13:2:2:5:5:3:13:3:2:2:7:7:13:3:3:3:3:6:13:6:9:9:6:6:13:9:9:1:1:1:13:11:11:7:7:10:13:10:10:10:9:9:13:9:5:5:9:9:13:1:10:10:5:5:13:5:5:7:7:7:13:7:2:2:2:4:13:2:11:11:7:7:13:5:5:7:10:4:13:3:3:3:3:4:4:3:11:11:2:2:7:7:7:1:1:6:6:6:6:7:3:3:3:10:10:4:4:7:7:8:8:8:5:5:4:4:4:9:9:4:4:5:5:2:2:2:2:3:3:3:3:8:8:8:9:9:10:10:1:1:1:4:4:10:10:10:6:6:3:3:9:9:9:8:8:11:11:11:7:7:7:7:9:9:9:2:2:6:6:6:5:3:3:3:10:1:1:1:6:6:6:2:2:3:3:8:8:8:4:4:8:8:8:4:4:4:10:10:10:10:5:5:2:2:1:1:7:7:5:5:5:10:10:10:2:2:3:3:11:11:7:1:1:5:5:5:6:11:11:1:1:9:9:9:2:2:11:2:6:6:4:4:4:2:2:11:11:1:1:1:8:8:2:2:2:2:9:9:9:4:4:4:4:1:1:9:9:1:1:10:10:10:10:5:7:7:1:1:1:1:11:11:4:4:6:6:6:8:8:9:9:11:11:5:5:5:9:2:2:2:7:7:7:7:5:3:3:3:1:1:5:7:7:7:5:5:5:5:3:3:4:4:4:10:10:10:10:6:6:6:2:5:5:5:6:6:1:1:1:3:6:6:10:10:4:4:6:6:5:5:5:5:7:7:6:6:6:11:11:11:3:3:3:9:9:9:9:8:8:8:2:2:2:7:11:8:8:8:8</t>
+  </si>
+  <si>
+    <t>8:8:8:5:5:1:1:1:4:4:4:6:2:6:6:8:8:8:8:11:2:2:11:11:5:5:2:2:2:17:4:4:6:6:2:2:1:1:1:2:6:6:6:6:1:1:3:3:4:4:4:4:6:6:3:5:5:5:1:17:1:1:1:2:2:6:8:8:8:4:4:4:4:9:9:2:2:2:2:5:5:1:1:5:8:8:8:8:5:17:7:7:7:10:10:6:5:5:5:3:3:3:3:5:5:5:2:11:5:5:10:10:10:11:1:1:9:9:9:17:4:4:3:3:11:11:8:8:1:1:5:5:5:5:6:6:6:6:7:3:10:10:10:6:6:9:9:11:11:17:2:2:11:11:7:10:10:10:10:11:1:1:1:1:4:2:2:11:11:4:4:10:3:3:3:3:7:7:7:17:7:4:4:4:3:3:3:6:7:7:6:6:6:11:11:10:8:8:8:7:7:7:7:9:9:7:9:9:6:17:1:1:1:6:6:2:7:3:10:9:9:8:8:6:2:2:2:11:11:11:11:4:4:4:3:3:4:4:8:17:2:2:2:5:5:5:5:10:4:4:6:6:3:7:7:1:1:3:3:3:7:7:7:1:1:1:2:2:2:17:7:7:7:9:9:3:3:4:4:3:3:10:10:10:10:8:8:9:9:9:5:5:6:9:9:5:8:3:3:17:5:5:5:10:4:4:3:3:9:3:3:3:8:8:8:8:3:3:5:5:5:2:2:2:2:7:7:7:7:2:2:2:11:11:1:1:5:5:10:5:5:9:9:9:2:2:2:2:7:7:1:1:9:9:9:3:3:3:3:6:6:6:4:4:6:6:7:3:3:3:2:2:3:3:9:1:1:1:1:5:2:2:7:7:7:7:10:6:6:4:4:9:5:5:5:1:1:8:8:8:4:4:10:10:10:5:5:4:4:4:6:9:9:9:9:3:3:3:10:10:10:11:11:3:3:3:3:8:8:4:4:1:1:9:9:10:10:10:2:2:2:8:8:10:10:10:1:11:11:2:2:10:10:10:5:5:5:5:10:10:7:7:7:11:11:7:7:6:6:11:11:4:11:11:1:1:8:8:6:6:6:8:8:8:8:10:8:8:8:1:11:11:11:11:2:2:2:2:4:4:4:1:1:7:7:7:7:6:6:6:1:1:9:9:1:1:3:7:7:7:7:4:4:4:4:6:6:3:3:3:3:9:9:9:5:6:4:4:4:6:6:2:2:2:11:11:11:1:6:8:10:9:9:5:5:5:1:1:9:9:10:10:10:5:5:5:2:2:4:4:4:9:5:5:1:8:8:8:6:6:3:3:1:1:6:6:5:6:6:6:1:1:11:6:8:4:4:2:7:4:1:1:1:1:8:8:8:1:1:10:10:10:9:9:3:9:10:10:4:4:4:4:6:6:5:5:2:2:2:10:10:10:5:5:5:5:2:2:3:3:3:2:2:9:1:1:9:9:8:8:8:6:7:7:10:10:1:1:1:1:6:6:6:6:3:3:3:4:4:5:5:5:5:4:4:4:4:6:6:6:7:7:1:1:9:9:2:6:6:6:4:4:9:6:6:6:7:7:9:8:8:9:9:2:2:2:2:1:1:1:10:10:2:2:11:11:1:1:1:3:3:3:7:11:11:5:5:9:9:9:11:11:11:11:1:1:1:7:7:7:10:10:10:5:5:9:5:5:5:5:2:2:2:4:4:3:3:3:9:9:9:5:5:5:8:8:8:11:11:7:7:7:1:1:11:11:11:10:10:10:10:7:8:8:8:2:2:2:2:9:9:6:6:6:7:7:8:8:8:7:7:5:5:5:6:6:1:1:1:2:2:3:3:3:7:4:4:11:11:11:6:6:4:4:4:4:3:3:5:5:2:2:3:3:3:4:4:11:11:6:6:2:2:1:1:10:10:9:9:6:6:7:7:7:7:4:4:4:4:3:9:5:7:7:4:2:2:2:5:5:5:6:6:8:10:10:4:4:4:11:11:3:3:3:10:8:8:6:8:8:3:3:10:3:3:9:8:8:3:8</t>
   </si>
 </sst>
 </file>
@@ -588,10 +588,10 @@
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -605,10 +605,10 @@
         <v>2</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -622,10 +622,10 @@
         <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -639,10 +639,10 @@
         <v>4</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -656,10 +656,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{086271A4-CF99-47E1-BCFE-86E25FC45DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122829D3-F209-42EA-A781-BED120AD3D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -93,19 +93,19 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>10:10:10:8:8:2:2:8:8:5:5:5:5:2:2:2:2:5:5:5:11:11:11:2:2:2:4:7:7:17:7:2:2:3:3:8:2:2:2:2:9:4:4:7:7:3:3:2:2:2:2:8:8:7:7:7:11:6:11:17:11:11:11:5:5:2:2:2:10:10:2:2:5:5:5:9:9:6:6:6:3:3:1:1:4:4:4:9:9:17:1:1:8:8:8:6:6:6:8:8:3:3:3:3:11:11:11:9:9:4:4:7:7:7:8:8:8:3:1:17:1:1:7:7:7:7:3:3:3:6:6:10:10:10:10:7:7:11:11:5:5:5:1:1:7:7:6:6:10:17:10:8:8:9:2:2:4:4:8:8:8:8:5:5:5:5:4:4:4:4:10:10:1:3:3:3:7:7:7:17:7:6:6:1:10:10:10:6:9:9:2:2:2:3:3:3:3:5:5:8:8:3:3:1:1:1:3:3:3:17:6:6:4:4:11:11:11:3:1:1:8:6:6:10:10:10:6:4:4:11:11:6:6:3:3:4:4:4:4:17:5:5:2:9:9:6:6:6:6:4:4:8:6:6:9:9:5:1:1:1:5:5:1:1:1:9:1:1:6:17:6:6:1:1:1:1:11:11:4:4:7:7:1:1:4:4:10:9:9:4:4:9:9:5:5:9:5:5:3:17:11:11:3:6:6:9:9:5:5:9:9:9:2:2:2:7:7:7:7:6:6:4:4:4:4:2:2:2:3:3:3:5:5:8:8:3:3:3:2:2:6:6:6:2:2:2:11:11:11:11:4:6:7:3:3:3:8:8:7:7:7:7:1:1:1:9:9:9:9:6:6:3:3:10:10:10:7:7:1:1:10:10:7:7:7:8:8:4:4:4:9:9:11:11:5:5:5:8:7:7:7:7:9:9:9:11:5:5:5:1:1:1:9:2:2:3:3:10:1:1:2:10:3:3:8:8:3:3:3:11:11:4:5:5:5:5:3:9:9:10:10:10:2:2:2:4:4:11:11:11:11:6:6:1:1:8:3:3:3:7:7:4:4:1:1:11:11:11:11:3:3:4:4:10:10:10:10:6:6:6:5:5:6:1:1:1:8:8:5:5:9:7:7:7:7:2:2:2:10:10:10:10:2:2:6:6:4:4:4:4:1:1:1:5:5:5:2:2:2:4:4:4:8:2:2:3:9:9:4:4:4:4:5:5:8:8:6:6:10:10:10:8:8:8:5:5:1:1:6:6:6:6:5:5:4:4:1:1:1:9:9:6:6:1:1:1:10:10:10:6:1:1:8:8:8:7:10:9:9:6:6:2:9:3:3:3:8:5:5:2:2:11:4:4:5:8:6:8:8:3:3:3:2:2:2:2:7:7:7:9:9:6:3:3:9:9:4:4:5:5:10:10:10:5:5:2:2:2:2:6:6:6:7:10:10:10:9:9:4:4:4:4:8:8:10:10:10:3:3:3:11:11:11:4:10:10:10:10:4:5:9:9:8:8:8:7:7:7:5:5:4:4:4:2:2:2:2:3:3:11:11:11:10:10:10:2:2:2:3:3:3:1:1:8:8:6:6:1:5:8:8:6:6:6:6:3:3:3:9:9:9:9:1:1:1:7:7:7:4:4:4:2:2:8:8:4:4:4:4:11:11:4:4:4:4:7:7:7:10:10:10:1:1:1:7:7:1:1:1:5:5:5:5:6:6:6:6:9:9:5:5:7:7:7:5:5:5:10:10:10:5:5:1:1:7:7:7:6:6:3:3:9:9:9:9:1:1:8:8:8:10:9:11:5:7:7:4:4:3:3:3:3:5:5:5:7:7:5:5:5:2:2:2:6:6:6:11:9:9:9:3:3:3:11:11:11:11:3:3:3:3:2:2:10:10:1:8:2:2:2:2:4:4:4:1:1:8:8:8:8:6:6:6:5:5:1:8:2:2:6:11:11:11:1:1:1:1:9:9:6:1:6:6:6:8:8:6:6:6:1:2:2:11:11:8:1:8:8:3:11:4:4:5:5:1:1:1:3:9:4</t>
-  </si>
-  <si>
-    <t>2:2:10:10:5:5:7:7:7:11:11:11:5:12:5:4:4:10:10:10:10:3:3:4:4:4:5:12:7:17:7:4:4:4:4:11:11:5:5:1:1:8:12:8:10:10:3:3:3:3:8:8:8:6:6:4:12:11:11:17:11:5:5:5:5:2:2:11:9:9:1:12:1:1:1:5:5:1:1:1:1:10:10:2:6:12:6:6:4:17:4:9:9:9:10:10:2:6:6:9:12:9:9:3:3:3:5:2:2:2:3:3:3:3:12:7:7:8:8:17:1:1:8:8:4:6:6:6:7:12:7:11:11:11:1:1:1:1:11:3:3:2:2:12:2:9:10:10:4:17:1:9:1:1:7:7:3:3:12:3:5:5:5:9:9:6:6:6:6:9:9:9:12:9:1:1:6:6:6:17:8:8:6:6:8:4:4:12:10:10:11:11:11:11:8:8:8:1:1:1:10:12:10:2:2:2:3:3:2:17:7:7:8:8:10:10:12:10:10:7:7:2:2:11:11:11:9:9:7:7:12:7:8:8:8:7:7:7:3:17:3:3:3:2:2:12:2:4:9:9:9:8:8:4:4:4:5:5:5:12:5:6:6:5:5:5:5:9:9:17:9:9:4:4:12:4:6:6:7:7:7:7:8:8:6:6:4:1:12:2:2:2:2:4:10:10:3:10:8:17:10:10:10:10:1:14:1:1:6:6:6:14:6:7:7:2:2:14:7:7:1:1:2:14:2:2:2:7:7:14:8:8:6:5:5:14:8:8:8:10:10:14:10:8:8:10:10:14:8:8:8:8:3:14:3:3:3:1:1:14:1:6:6:5:5:14:2:2:4:4:4:14:11:11:7:7:4:14:4:4:4:6:6:14:7:10:10:10:10:14:1:1:11:11:11:14:11:7:7:7:8:14:8:8:8:1:1:14:1:1:3:3:9:14:9:9:9:4:4:14:3:3:5:5:5:14:5:2:2:4:4:14:7:7:2:2:11:14:11:11:5:5:5:14:2:1:1:2:2:14:2:6:6:9:9:13:9:6:6:10:10:13:10:9:9:7:7:13:6:6:6:6:2:13:2:2:4:4:4:13:5:5:5:4:4:13:9:11:11:6:6:13:6:5:1:1:1:13:8:11:2:2:7:13:7:7:3:3:3:13:5:5:5:5:4:13:4:10:10:3:3:13:2:2:5:3:3:13:11:11:11:9:9:13:8:8:8:8:11:13:11:1:1:1:1:13:9:9:6:6:6:13:2:2:3:3:3:13:4:4:5:5:5:13:4:5:5:11:11:13:6:6:9:9:9:13:10:10:3:3:3:13:9:9:11:9:1:13:1:4:4:4:3:13:7:3:4:3:3:13:5:5:5:8:8:8:2:2:2:2:7:2:2:4:4:11:11:11:10:10:10:1:1:5:5:6:6:6:4:4:4:5:5:5:10:10:3:3:7:7:7:7:10:10:1:1:1:8:6:6:6:7:2:2:2:3:3:3:4:3:3:9:9:4:1:1:3:3:9:9:9:9:8:8:5:2:2:7:7:2:2:9:9:2:2:2:7:7:1:1:1:2:8:8:8:6:6:11:11:1:1:1:1:10:10:8:8:10:1:4:4:4:9:9:9:1:1:1:10:10:10:10:2:2:2:2:1:1:3:3:3:5:5:5:7:7:8:8:8:6:6:6:5:4:4:6:6:9:9:8:8:8:7:7:7:7:2:2:6:6:6:11:11:11:3:3:3:6:6:3:3:9:9:9:3:7:7:3:3:3:3:4:4:4:4:9:10:10:11:11:11:6:6:4:3:3:3:4:4:4:4:1:1:9:9:9:9:5:6:6:6:4:4:4:7:7:7:4:4:4:4:11:5:5:6:6:8:8:8:8:6:7:9:9:10:10:2:2:2:5:5:2:11:11:11:10:10:10:5:5:3:1:1:1:6:6:8:8:5:5:5:10:10:10:7:7:7:2:2:11:11:4:4:1:1:1:3:3:2:8:8:5:5:10:5:5:11:11:11:3:3:1:1:9:9:6:6:5:5:5</t>
-  </si>
-  <si>
-    <t>8:8:8:8:5:5:5:7:7:7:1:1:7:12:7:7:7:10:10:10:10:6:6:6:5:5:1:12:1:17:1:1:8:8:8:8:3:3:3:1:1:2:12:2:2:11:11:10:10:10:3:11:11:3:3:3:12:3:1:17:1:10:10:10:9:6:6:6:6:9:9:12:7:3:3:6:2:2:11:11:11:4:4:1:1:12:3:3:11:17:11:10:4:4:4:9:9:9:11:11:12:11:11:4:4:2:2:10:10:10:8:8:8:8:12:10:10:10:2:17:2:4:5:5:5:5:1:1:8:12:8:9:8:8:8:9:9:5:5:5:4:1:1:12:1:6:10:10:10:17:8:6:6:6:5:5:5:7:12:7:7:5:5:2:4:5:9:9:7:7:7:9:12:9:10:10:2:2:2:17:2:11:11:2:2:2:2:12:11:11:3:3:6:6:6:7:7:7:6:6:2:12:2:7:4:3:5:5:6:17:6:4:4:2:2:3:12:3:3:1:1:9:9:9:9:11:11:8:8:4:12:4:4:3:3:3:1:1:1:17:6:6:4:4:4:12:7:7:7:9:9:5:7:7:7:9:9:9:9:12:11:3:3:3:4:4:4:4:3:17:4:8:8:10:12:10:10:7:8:8:8:5:5:4:6:6:6:9:12:9:6:1:1:5:5:2:2:1:2:17:7:7:7:9:9:14:3:3:8:8:8:14:10:5:8:8:2:14:2:9:9:9:11:14:11:5:5:7:7:14:5:5:4:4:4:14:4:3:3:11:11:14:11:10:10:2:5:14:5:1:1:10:10:14:10:10:8:8:8:14:10:10:2:2:2:14:2:4:4:4:4:14:11:11:11:11:4:14:4:4:4:6:6:14:10:10:10:10:2:14:2:2:3:3:2:14:2:5:5:5:5:14:10:10:11:11:11:14:7:7:7:4:4:14:11:11:9:9:7:14:7:3:3:1:1:14:1:2:2:2:2:14:6:6:6:7:7:14:6:4:4:4:4:14:1:1:3:3:3:14:11:11:1:1:1:13:9:9:8:11:11:13:11:2:2:2:5:13:5:5:5:7:7:13:7:3:3:2:2:13:6:6:6:8:8:13:1:1:8:8:1:13:1:1:9:9:9:13:9:1:1:6:6:13:6:6:3:3:9:13:9:9:1:1:9:13:9:9:4:4:4:13:6:6:1:1:1:13:2:5:5:4:4:13:4:4:8:8:8:13:6:6:6:6:10:13:10:10:8:8:8:13:8:7:7:9:6:13:6:7:7:7:3:13:3:6:6:3:3:13:3:5:5:1:1:13:3:3:10:3:5:13:5:2:2:11:6:13:6:1:5:5:5:13:10:5:3:3:2:13:10:10:10:7:7:3:3:8:8:1:2:7:4:4:4:3:3:11:11:2:2:2:2:4:4:4:9:9:9:9:7:7:5:5:10:10:8:8:1:6:6:1:11:11:2:2:1:1:1:8:8:8:6:6:6:9:9:1:1:1:5:5:5:7:7:7:3:3:3:8:8:8:4:4:2:2:2:4:4:4:5:5:5:6:10:10:8:8:3:3:3:7:7:9:9:9:10:10:10:11:11:9:9:9:9:7:7:8:8:8:5:5:4:4:4:7:7:7:9:9:9:4:4:2:11:11:11:7:7:7:1:1:6:6:7:7:7:7:1:1:1:10:9:11:11:3:3:2:2:8:8:8:8:4:4:10:10:10:3:3:4:4:4:4:2:2:4:4:6:6:2:2:6:6:2:2:11:11:11:1:1:3:3:3:3:5:5:5:3:1:1:1:2:6:11:11:10:10:10:7:7:5:5:5:4:4:9:9:5:5:5:5:3:3:3:3:10:10:5:5:1:1:11:11:11:2:2:2:2:1:1:10:10:10:3:3:6:6:6:6:8:8:8:8:6:6:9:9:2:2:2:9:9:9:5:5:5:5:6:6:6:6:3:3:10:10:1:1:1:1:6:5:5:5:9:8:8:2:2:6:6:6:6:10:3:3:1:4:4:4:5:7:11:4:3:6:6:2:1:1</t>
-  </si>
-  <si>
-    <t>4:4:9:9:9:7:7:7:2:2:10:10:10:12:3:3:3:2:2:4:4:4:4:10:10:10:10:12:8:17:8:7:10:10:6:6:11:11:7:7:7:7:12:9:3:3:3:1:1:1:3:3:3:1:1:9:12:9:2:17:2:2:4:4:9:9:9:4:4:4:8:12:7:1:1:1:8:8:8:9:9:9:8:8:8:12:5:5:3:17:3:9:9:9:9:6:6:6:10:10:12:10:6:6:6:3:3:3:11:4:4:4:4:8:12:8:8:1:1:17:1:1:11:11:11:7:4:4:4:12:5:5:5:6:6:2:2:6:7:7:7:4:4:12:5:5:5:10:10:17:1:1:1:11:11:9:9:11:12:11:6:6:11:11:11:11:8:8:8:8:4:4:12:4:11:5:5:5:8:17:8:8:1:1:2:2:11:12:11:5:2:2:5:5:5:8:8:8:10:3:3:12:5:5:1:1:7:7:7:17:7:6:6:6:8:8:12:10:10:10:10:6:6:7:2:2:9:9:9:9:12:3:11:11:11:2:2:1:1:17:1:1:5:5:5:12:5:7:7:3:3:3:3:2:2:6:6:6:9:12:5:5:5:6:6:6:1:1:10:17:10:10:2:2:12:4:4:2:2:2:2:9:9:3:3:5:7:7:12:7:7:8:3:3:7:10:10:10:6:17:11:11:8:8:1:14:1:1:1:9:9:14:6:6:6:5:1:14:1:1:1:2:2:14:11:11:11:8:8:14:10:10:3:3:3:14:5:5:5:8:1:14:1:6:7:7:8:14:8:9:9:11:2:14:6:6:6:3:3:14:9:9:10:10:10:14:5:5:5:5:4:14:4:9:9:9:9:14:3:3:4:10:10:14:2:2:4:4:4:14:2:2:2:1:1:14:2:10:10:1:1:14:1:10:10:3:3:14:3:3:6:6:5:14:5:4:4:4:8:14:8:1:1:1:1:14:2:2:2:6:6:14:6:4:4:4:6:14:6:6:8:8:8:14:3:4:4:4:4:14:3:3:3:5:5:13:5:8:8:8:8:13:1:1:11:11:11:13:10:10:11:11:11:13:11:6:6:7:7:13:2:2:2:7:7:13:7:4:4:2:2:13:3:3:5:5:9:13:6:6:6:6:4:13:4:7:7:8:8:13:8:8:3:3:11:13:11:11:4:4:4:13:2:2:5:5:3:13:3:2:2:7:7:13:3:3:3:3:6:13:6:9:9:6:6:13:9:9:1:1:1:13:11:11:7:7:10:13:10:10:10:9:9:13:9:5:5:9:9:13:1:10:10:5:5:13:5:5:7:7:7:13:7:2:2:2:4:13:2:11:11:7:7:13:5:5:7:10:4:13:3:3:3:3:4:4:3:11:11:2:2:7:7:7:1:1:6:6:6:6:7:3:3:3:10:10:4:4:7:7:8:8:8:5:5:4:4:4:9:9:4:4:5:5:2:2:2:2:3:3:3:3:8:8:8:9:9:10:10:1:1:1:4:4:10:10:10:6:6:3:3:9:9:9:8:8:11:11:11:7:7:7:7:9:9:9:2:2:6:6:6:5:3:3:3:10:1:1:1:6:6:6:2:2:3:3:8:8:8:4:4:8:8:8:4:4:4:10:10:10:10:5:5:2:2:1:1:7:7:5:5:5:10:10:10:2:2:3:3:11:11:7:1:1:5:5:5:6:11:11:1:1:9:9:9:2:2:11:2:6:6:4:4:4:2:2:11:11:1:1:1:8:8:2:2:2:2:9:9:9:4:4:4:4:1:1:9:9:1:1:10:10:10:10:5:7:7:1:1:1:1:11:11:4:4:6:6:6:8:8:9:9:11:11:5:5:5:9:2:2:2:7:7:7:7:5:3:3:3:1:1:5:7:7:7:5:5:5:5:3:3:4:4:4:10:10:10:10:6:6:6:2:5:5:5:6:6:1:1:1:3:6:6:10:10:4:4:6:6:5:5:5:5:7:7:6:6:6:11:11:11:3:3:3:9:9:9:9:8:8:8:2:2:2:7:11:8:8:8:8</t>
-  </si>
-  <si>
-    <t>8:8:8:5:5:1:1:1:4:4:4:6:2:6:6:8:8:8:8:11:2:2:11:11:5:5:2:2:2:17:4:4:6:6:2:2:1:1:1:2:6:6:6:6:1:1:3:3:4:4:4:4:6:6:3:5:5:5:1:17:1:1:1:2:2:6:8:8:8:4:4:4:4:9:9:2:2:2:2:5:5:1:1:5:8:8:8:8:5:17:7:7:7:10:10:6:5:5:5:3:3:3:3:5:5:5:2:11:5:5:10:10:10:11:1:1:9:9:9:17:4:4:3:3:11:11:8:8:1:1:5:5:5:5:6:6:6:6:7:3:10:10:10:6:6:9:9:11:11:17:2:2:11:11:7:10:10:10:10:11:1:1:1:1:4:2:2:11:11:4:4:10:3:3:3:3:7:7:7:17:7:4:4:4:3:3:3:6:7:7:6:6:6:11:11:10:8:8:8:7:7:7:7:9:9:7:9:9:6:17:1:1:1:6:6:2:7:3:10:9:9:8:8:6:2:2:2:11:11:11:11:4:4:4:3:3:4:4:8:17:2:2:2:5:5:5:5:10:4:4:6:6:3:7:7:1:1:3:3:3:7:7:7:1:1:1:2:2:2:17:7:7:7:9:9:3:3:4:4:3:3:10:10:10:10:8:8:9:9:9:5:5:6:9:9:5:8:3:3:17:5:5:5:10:4:4:3:3:9:3:3:3:8:8:8:8:3:3:5:5:5:2:2:2:2:7:7:7:7:2:2:2:11:11:1:1:5:5:10:5:5:9:9:9:2:2:2:2:7:7:1:1:9:9:9:3:3:3:3:6:6:6:4:4:6:6:7:3:3:3:2:2:3:3:9:1:1:1:1:5:2:2:7:7:7:7:10:6:6:4:4:9:5:5:5:1:1:8:8:8:4:4:10:10:10:5:5:4:4:4:6:9:9:9:9:3:3:3:10:10:10:11:11:3:3:3:3:8:8:4:4:1:1:9:9:10:10:10:2:2:2:8:8:10:10:10:1:11:11:2:2:10:10:10:5:5:5:5:10:10:7:7:7:11:11:7:7:6:6:11:11:4:11:11:1:1:8:8:6:6:6:8:8:8:8:10:8:8:8:1:11:11:11:11:2:2:2:2:4:4:4:1:1:7:7:7:7:6:6:6:1:1:9:9:1:1:3:7:7:7:7:4:4:4:4:6:6:3:3:3:3:9:9:9:5:6:4:4:4:6:6:2:2:2:11:11:11:1:6:8:10:9:9:5:5:5:1:1:9:9:10:10:10:5:5:5:2:2:4:4:4:9:5:5:1:8:8:8:6:6:3:3:1:1:6:6:5:6:6:6:1:1:11:6:8:4:4:2:7:4:1:1:1:1:8:8:8:1:1:10:10:10:9:9:3:9:10:10:4:4:4:4:6:6:5:5:2:2:2:10:10:10:5:5:5:5:2:2:3:3:3:2:2:9:1:1:9:9:8:8:8:6:7:7:10:10:1:1:1:1:6:6:6:6:3:3:3:4:4:5:5:5:5:4:4:4:4:6:6:6:7:7:1:1:9:9:2:6:6:6:4:4:9:6:6:6:7:7:9:8:8:9:9:2:2:2:2:1:1:1:10:10:2:2:11:11:1:1:1:3:3:3:7:11:11:5:5:9:9:9:11:11:11:11:1:1:1:7:7:7:10:10:10:5:5:9:5:5:5:5:2:2:2:4:4:3:3:3:9:9:9:5:5:5:8:8:8:11:11:7:7:7:1:1:11:11:11:10:10:10:10:7:8:8:8:2:2:2:2:9:9:6:6:6:7:7:8:8:8:7:7:5:5:5:6:6:1:1:1:2:2:3:3:3:7:4:4:11:11:11:6:6:4:4:4:4:3:3:5:5:2:2:3:3:3:4:4:11:11:6:6:2:2:1:1:10:10:9:9:6:6:7:7:7:7:4:4:4:4:3:9:5:7:7:4:2:2:2:5:5:5:6:6:8:10:10:4:4:4:11:11:3:3:3:10:8:8:6:8:8:3:3:10:3:3:9:8:8:3:8</t>
+    <t>7:7:19:1:1:20:2:2:8:8:8:8:20:19:11:10:5:5:6:6:6:4:4:4:4:6:6:6:6:17:5:5:5:1:1:1:1:7:7:3:3:3:9:9:2:2:2:2:8:3:3:7:7:7:7:6:6:2:2:17:2:1:1:8:8:4:4:11:11:11:1:1:1:19:5:4:10:10:10:11:1:1:20:10:10:2:2:2:4:17:4:4:4:21:3:3:9:9:9:9:3:3:19:21:7:7:3:3:8:8:2:2:19:5:5:6:6:8:8:17:7:7:7:3:3:3:3:20:21:10:10:4:4:5:5:5:5:20:10:10:10:6:6:1:1:1:1:6:6:17:6:5:5:5:5:8:8:4:4:4:4:7:7:7:7:21:22:10:10:10:6:6:8:4:4:3:3:3:5:17:4:4:4:4:3:3:3:7:5:5:7:7:7:10:10:2:5:5:5:8:8:8:1:1:1:1:2:8:8:17:8:8:6:6:6:1:1:11:11:6:6:6:6:9:9:5:5:2:3:2:2:9:9:2:2:9:9:9:1:17:1:4:4:8:8:8:8:9:9:4:3:3:5:5:7:7:7:6:6:6:2:3:3:3:5:5:5:4:4:17:1:1:1:2:2:2:4:4:4:11:11:9:9:20:21:7:7:3:3:1:1:2:2:6:6:2:2:11:2:17:11:11:3:6:6:9:9:5:5:9:9:9:2:2:2:7:7:7:7:6:6:4:4:4:4:2:2:2:3:3:3:5:5:8:8:3:3:3:2:2:6:6:6:2:2:2:11:11:11:11:4:6:7:3:3:3:8:8:7:7:7:7:1:1:1:9:9:9:9:6:6:3:3:10:10:10:7:7:1:1:10:10:7:7:7:8:8:4:4:4:9:9:11:11:5:5:5:8:7:7:7:7:9:9:9:11:5:5:5:1:1:1:9:2:2:3:3:10:1:1:2:10:3:3:8:8:3:3:3:11:11:4:5:5:5:5:3:9:9:10:10:10:2:2:2:4:4:11:11:11:11:6:6:1:1:8:3:3:3:7:7:4:4:1:1:11:11:11:11:3:3:4:4:10:10:10:10:6:6:6:5:5:6:1:1:1:8:8:5:5:9:7:7:7:7:2:2:2:10:10:10:10:2:2:6:6:4:4:4:4:1:1:1:5:5:5:2:2:2:4:4:4:8:2:2:3:9:9:4:4:4:4:5:5:8:8:6:6:10:10:10:8:8:8:5:5:1:1:6:6:6:6:5:5:4:4:1:1:1:9:9:6:6:1:1:1:10:10:10:6:1:1:8:8:8:7:10:9:9:6:6:2:9:3:3:3:8:5:5:2:2:11:4:4:5:8:6:8:8:3:3:3:2:2:2:2:7:7:7:9:9:6:3:3:9:9:4:4:5:5:10:10:10:5:5:2:2:2:2:6:6:6:7:10:10:10:9:9:4:4:4:4:8:8:10:10:10:3:3:3:11:11:11:4:10:10:10:10:4:5:9:9:8:8:8:7:7:7:5:5:4:4:4:2:2:2:2:3:3:11:11:11:10:10:10:2:2:2:3:3:3:1:1:8:8:6:6:1:5:8:8:6:6:6:6:3:3:3:9:9:9:9:1:1:1:7:7:7:4:4:4:2:2:8:8:4:4:4:4:11:11:4:4:4:4:7:7:7:10:10:10:1:1:1:7:7:1:1:1:5:5:5:5:6:6:6:6:9:9:5:5:7:7:7:5:5:5:10:10:10:5:5:1:1:7:7:7:6:6:3:3:9:9:9:9:1:1:8:8:8:10:9:11:5:7:7:4:4:3:3:3:3:5:5:5:7:7:5:5:5:2:2:2:6:6:6:11:9:9:9:3:3:3:11:11:11:11:3:3:3:3:2:2:10:10:1:8:2:2:2:2:4:4:4:1:1:8:8:8:8:6:6:6:5:5:1:8:2:2:6:11:11:11:1:1:1:1:9:9:6:1:6:6:6:8:8:6:6:6:1:2:2:11:11:8:1:8:8:3:11:4:4:5:5:1:1:1:3:9:4</t>
+  </si>
+  <si>
+    <t>1:1:1:1:9:9:9:19:11:11:11:4:4:4:19:8:5:12:5:5:5:2:1:4:4:4:4:10:9:17:9:9:6:6:10:10:12:10:3:3:3:20:9:9:9:1:1:20:1:4:4:4:11:11:12:8:9:9:7:17:7:3:3:5:3:3:19:6:6:6:11:11:11:12:3:3:2:2:2:21:10:10:6:6:6:6:2:2:2:17:2:8:8:12:10:10:10:4:9:9:9:7:7:8:20:1:4:4:4:2:12:10:10:5:8:8:8:8:7:17:7:5:5:19:20:3:3:3:4:12:4:4:6:6:7:10:11:11:19:21:2:1:1:10:10:12:6:6:6:17:6:10:10:10:10:19:21:3:3:3:3:8:8:8:2:2:12:6:6:7:7:7:5:5:8:5:5:1:1:17:3:3:1:8:8:12:4:4:9:9:9:4:4:4:6:6:2:1:1:7:7:2:2:12:5:5:2:2:2:17:9:9:5:5:10:10:10:5:5:4:4:4:12:3:3:3:3:20:9:9:6:6:5:7:22:1:1:9:9:17:5:5:5:12:7:7:6:6:7:7:8:8:7:7:7:7:8:8:8:12:7:7:7:8:8:1:1:1:5:17:5:5:3:3:2:2:1:2:12:2:2:2:1:1:8:19:9:9:6:6:8:8:20:8:7:6:3:11:2:17:10:10:10:10:1:14:1:1:6:6:6:14:6:7:7:2:2:14:7:7:1:1:2:14:2:2:2:7:7:14:8:8:6:5:5:14:8:8:8:10:10:14:10:8:8:10:10:14:8:8:8:8:3:14:3:3:3:1:1:14:1:6:6:5:5:14:2:2:4:4:4:14:11:11:7:7:4:14:4:4:4:6:6:14:7:10:10:10:10:14:1:1:11:11:11:14:11:7:7:7:8:14:8:8:8:1:1:14:1:1:3:3:9:14:9:9:9:4:4:14:3:3:5:5:5:14:5:2:2:4:4:14:7:7:2:2:11:14:11:11:5:5:5:14:2:1:1:2:2:14:2:6:6:9:9:13:9:6:6:10:10:13:10:9:9:7:7:13:6:6:6:6:2:13:2:2:4:4:4:13:5:5:5:4:4:13:9:11:11:6:6:13:6:5:1:1:1:13:8:11:2:2:7:13:7:7:3:3:3:13:5:5:5:5:4:13:4:10:10:3:3:13:2:2:5:3:3:13:11:11:11:9:9:13:8:8:8:8:11:13:11:1:1:1:1:13:9:9:6:6:6:13:2:2:3:3:3:13:4:4:5:5:5:13:4:5:5:11:11:13:6:6:9:9:9:13:10:10:3:3:3:13:9:9:11:9:1:13:1:4:4:4:3:13:7:3:4:3:3:13:5:5:5:8:8:8:2:2:2:2:7:2:2:4:4:11:11:11:10:10:10:1:1:5:5:6:6:6:4:4:4:5:5:5:10:10:3:3:7:7:7:7:10:10:1:1:1:8:6:6:6:7:2:2:2:3:3:3:4:3:3:9:9:4:1:1:3:3:9:9:9:9:8:8:5:2:2:7:7:2:2:9:9:2:2:2:7:7:1:1:1:2:8:8:8:6:6:11:11:1:1:1:1:10:10:8:8:10:1:4:4:4:9:9:9:1:1:1:10:10:10:10:2:2:2:2:1:1:3:3:3:5:5:5:7:7:8:8:8:6:6:6:5:4:4:6:6:9:9:8:8:8:7:7:7:7:2:2:6:6:6:11:11:11:3:3:3:6:6:3:3:9:9:9:3:7:7:3:3:3:3:4:4:4:4:9:10:10:11:11:11:6:6:4:3:3:3:4:4:4:4:1:1:9:9:9:9:5:6:6:6:4:4:4:7:7:7:4:4:4:4:11:5:5:6:6:8:8:8:8:6:7:9:9:10:10:2:2:2:5:5:2:11:11:11:10:10:10:5:5:3:1:1:1:6:6:8:8:5:5:5:10:10:10:7:7:7:2:2:11:11:4:4:1:1:1:3:3:2:8:8:5:5:10:5:5:11:11:11:3:3:1:1:9:9:6:6:5:5:5</t>
+  </si>
+  <si>
+    <t>1:1:1:1:9:9:9:19:11:11:11:4:4:4:19:8:5:12:5:5:5:2:1:4:4:4:4:10:9:17:9:9:6:6:10:10:12:10:3:3:3:20:9:9:9:1:1:20:1:4:4:4:11:11:12:8:9:9:7:17:7:3:3:5:3:3:19:6:6:6:11:11:11:12:3:3:2:2:2:21:10:10:6:6:6:6:2:2:2:17:2:8:8:12:10:10:10:4:9:9:9:7:7:8:20:1:4:4:4:2:12:10:10:5:8:8:8:8:7:17:7:5:5:19:20:3:3:3:4:12:4:4:6:6:7:10:11:11:19:21:2:1:1:10:10:12:6:6:6:17:6:10:10:10:10:19:21:3:3:3:3:8:8:8:2:2:12:6:6:7:7:7:5:5:8:5:5:1:1:17:3:3:1:8:8:12:4:4:9:9:9:4:4:4:6:6:2:1:1:7:7:2:2:12:5:5:2:2:2:17:9:9:5:5:10:10:10:5:5:4:4:4:12:3:3:3:3:20:9:9:6:6:5:7:22:1:1:9:9:17:5:5:5:12:7:7:6:6:7:7:8:8:7:7:7:7:8:8:8:12:7:7:7:8:8:1:1:1:5:17:5:5:3:3:2:2:1:2:12:2:2:2:1:1:8:19:9:9:6:6:8:8:20:8:7:6:3:11:2:17:7:7:7:9:9:14:3:3:8:8:8:14:10:5:8:8:2:14:2:9:9:9:11:14:11:5:5:7:7:14:5:5:4:4:4:14:4:3:3:11:11:14:11:10:10:2:5:14:5:1:1:10:10:14:10:10:8:8:8:14:10:10:2:2:2:14:2:4:4:4:4:14:11:11:11:11:4:14:4:4:4:6:6:14:10:10:10:10:2:14:2:2:3:3:2:14:2:5:5:5:5:14:10:10:11:11:11:14:7:7:7:4:4:14:11:11:9:9:7:14:7:3:3:1:1:14:1:2:2:2:2:14:6:6:6:7:7:14:6:4:4:4:4:14:1:1:3:3:3:14:11:11:1:1:1:13:9:9:8:11:11:13:11:2:2:2:5:13:5:5:5:7:7:13:7:3:3:2:2:13:6:6:6:8:8:13:1:1:8:8:1:13:1:1:9:9:9:13:9:1:1:6:6:13:6:6:3:3:9:13:9:9:1:1:9:13:9:9:4:4:4:13:6:6:1:1:1:13:2:5:5:4:4:13:4:4:8:8:8:13:6:6:6:6:10:13:10:10:8:8:8:13:8:7:7:9:6:13:6:7:7:7:3:13:3:6:6:3:3:13:3:5:5:1:1:13:3:3:10:3:5:13:5:2:2:11:6:13:6:1:5:5:5:13:10:5:3:3:2:13:10:10:10:7:7:3:3:8:8:1:2:7:4:4:4:3:3:11:11:2:2:2:2:4:4:4:9:9:9:9:7:7:5:5:10:10:8:8:1:6:6:1:11:11:2:2:1:1:1:8:8:8:6:6:6:9:9:1:1:1:5:5:5:7:7:7:3:3:3:8:8:8:4:4:2:2:2:4:4:4:5:5:5:6:10:10:8:8:3:3:3:7:7:9:9:9:10:10:10:11:11:9:9:9:9:7:7:8:8:8:5:5:4:4:4:7:7:7:9:9:9:4:4:2:11:11:11:7:7:7:1:1:6:6:7:7:7:7:1:1:1:10:9:11:11:3:3:2:2:8:8:8:8:4:4:10:10:10:3:3:4:4:4:4:2:2:4:4:6:6:2:2:6:6:2:2:11:11:11:1:1:3:3:3:3:5:5:5:3:1:1:1:2:6:11:11:10:10:10:7:7:5:5:5:4:4:9:9:5:5:5:5:3:3:3:3:10:10:5:5:1:1:11:11:11:2:2:2:2:1:1:10:10:10:3:3:6:6:6:6:8:8:8:8:6:6:9:9:2:2:2:9:9:9:5:5:5:5:6:6:6:6:3:3:10:10:1:1:1:1:6:5:5:5:9:8:8:2:2:6:6:6:6:10:3:3:1:4:4:4:5:7:11:4:3:6:6:2:1:1</t>
+  </si>
+  <si>
+    <t>1:1:1:1:9:9:9:19:11:11:11:4:4:4:19:8:5:12:5:5:5:2:1:4:4:4:4:10:9:17:9:9:6:6:10:10:12:10:3:3:3:20:9:9:9:1:1:20:1:4:4:4:11:11:12:8:9:9:7:17:7:3:3:5:3:3:19:6:6:6:11:11:11:12:3:3:2:2:2:21:10:10:6:6:6:6:2:2:2:17:2:8:8:12:10:10:10:4:9:9:9:7:7:8:20:1:4:4:4:2:12:10:10:5:8:8:8:8:7:17:7:5:5:19:20:3:3:3:4:12:4:4:6:6:7:10:11:11:19:21:2:1:1:10:10:12:6:6:6:17:6:10:10:10:10:19:21:3:3:3:3:8:8:8:2:2:12:6:6:7:7:7:5:5:8:5:5:1:1:17:3:3:1:8:8:12:4:4:9:9:9:4:4:4:6:6:2:1:1:7:7:2:2:12:5:5:2:2:2:17:9:9:5:5:10:10:10:5:5:4:4:4:12:3:3:3:3:20:9:9:6:6:5:7:22:1:1:9:9:17:5:5:5:12:7:7:6:6:7:7:8:8:7:7:7:7:8:8:8:12:7:7:7:8:8:1:1:1:5:17:5:5:3:3:2:2:1:2:12:2:2:2:1:1:8:19:9:9:6:6:8:8:20:8:7:6:3:11:2:17:11:11:8:8:1:14:1:1:1:9:9:14:6:6:6:5:1:14:1:1:1:2:2:14:11:11:11:8:8:14:10:10:3:3:3:14:5:5:5:8:1:14:1:6:7:7:8:14:8:9:9:11:2:14:6:6:6:3:3:14:9:9:10:10:10:14:5:5:5:5:4:14:4:9:9:9:9:14:3:3:4:10:10:14:2:2:4:4:4:14:2:2:2:1:1:14:2:10:10:1:1:14:1:10:10:3:3:14:3:3:6:6:5:14:5:4:4:4:8:14:8:1:1:1:1:14:2:2:2:6:6:14:6:4:4:4:6:14:6:6:8:8:8:14:3:4:4:4:4:14:3:3:3:5:5:13:5:8:8:8:8:13:1:1:11:11:11:13:10:10:11:11:11:13:11:6:6:7:7:13:2:2:2:7:7:13:7:4:4:2:2:13:3:3:5:5:9:13:6:6:6:6:4:13:4:7:7:8:8:13:8:8:3:3:11:13:11:11:4:4:4:13:2:2:5:5:3:13:3:2:2:7:7:13:3:3:3:3:6:13:6:9:9:6:6:13:9:9:1:1:1:13:11:11:7:7:10:13:10:10:10:9:9:13:9:5:5:9:9:13:1:10:10:5:5:13:5:5:7:7:7:13:7:2:2:2:4:13:2:11:11:7:7:13:5:5:7:10:4:13:3:3:3:3:4:4:3:11:11:2:2:7:7:7:1:1:6:6:6:6:7:3:3:3:10:10:4:4:7:7:8:8:8:5:5:4:4:4:9:9:4:4:5:5:2:2:2:2:3:3:3:3:8:8:8:9:9:10:10:1:1:1:4:4:10:10:10:6:6:3:3:9:9:9:8:8:11:11:11:7:7:7:7:9:9:9:2:2:6:6:6:5:3:3:3:10:1:1:1:6:6:6:2:2:3:3:8:8:8:4:4:8:8:8:4:4:4:10:10:10:10:5:5:2:2:1:1:7:7:5:5:5:10:10:10:2:2:3:3:11:11:7:1:1:5:5:5:6:11:11:1:1:9:9:9:2:2:11:2:6:6:4:4:4:2:2:11:11:1:1:1:8:8:2:2:2:2:9:9:9:4:4:4:4:1:1:9:9:1:1:10:10:10:10:5:7:7:1:1:1:1:11:11:4:4:6:6:6:8:8:9:9:11:11:5:5:5:9:2:2:2:7:7:7:7:5:3:3:3:1:1:5:7:7:7:5:5:5:5:3:3:4:4:4:10:10:10:10:6:6:6:2:5:5:5:6:6:1:1:1:3:6:6:10:10:4:4:6:6:5:5:5:5:7:7:6:6:6:11:11:11:3:3:3:9:9:9:9:8:8:8:2:2:2:7:11:8:8:8:8</t>
+  </si>
+  <si>
+    <t>3:3:3:9:9:6:6:2:2:17:2:7:7:7:1:1:6:6:6:17:4:4:11:11:6:1:1:3:10:17:10:8:4:4:1:1:5:5:6:17:3:3:3:3:4:4:4:4:2:17:2:4:2:2:2:9:9:9:5:17:5:5:5:4:4:4:3:3:7:17:7:7:5:5:5:5:2:2:3:17:3:8:8:8:1:7:7:7:3:17:1:9:9:2:2:2:2:1:1:17:4:4:9:9:7:7:7:7:6:15:6:6:7:7:6:6:11:11:6:16:6:6:6:7:7:7:6:6:1:15:2:6:6:6:6:4:4:4:11:16:11:11:5:5:5:4:3:3:8:15:5:5:5:1:1:5:2:2:2:16:6:6:6:8:8:7:1:1:7:15:7:7:9:9:5:8:7:7:9:16:9:2:2:1:1:1:2:2:2:16:9:9:4:4:4:1:1:1:1:16:10:10:1:1:1:3:3:11:11:15:11:8:8:4:4:4:4:10:10:15:10:5:5:5:5:1:1:1:6:16:6:6:6:3:3:3:8:8:11:15:3:3:3:10:10:10:10:11:11:15:11:8:8:8:8:10:10:5:5:16:4:4:1:1:8:8:8:2:2:15:2:2:10:10:3:3:3:3:5:16:2:2:2:8:6:7:4:4:3:15:11:5:5:4:3:3:5:5:5:16:5:5:5:10:4:4:3:3:9:3:3:3:8:8:8:8:3:3:5:5:5:2:2:2:2:7:7:7:7:2:2:2:11:11:1:1:5:5:10:5:5:9:9:9:2:2:2:2:7:7:1:1:9:9:9:3:3:3:3:6:6:6:4:4:6:6:7:3:3:3:2:2:3:3:9:1:1:1:1:5:2:2:7:7:7:7:10:6:6:4:4:9:5:5:5:1:1:8:8:8:4:4:10:10:10:5:5:4:4:4:6:9:9:9:9:3:3:3:10:10:10:11:11:3:3:3:3:8:8:4:4:1:1:9:9:10:10:10:2:2:2:8:8:10:10:10:1:11:11:2:2:10:10:10:5:5:5:5:10:10:7:7:7:11:11:7:7:6:6:11:11:4:11:11:1:1:8:8:6:6:6:8:8:8:8:10:8:8:8:1:11:11:11:11:2:2:2:2:4:4:4:1:1:7:7:7:7:6:6:6:1:1:9:9:1:1:3:7:7:7:7:4:4:4:4:6:6:3:3:3:3:9:9:9:5:6:4:4:4:6:6:2:2:2:11:11:11:1:6:8:10:9:9:5:5:5:1:1:9:9:10:10:10:5:5:5:2:2:4:4:4:9:5:5:1:8:8:8:6:6:3:3:1:1:6:6:5:6:6:6:1:1:11:6:8:4:4:2:7:4:1:1:1:1:8:8:8:1:1:10:10:10:9:9:3:9:10:10:4:4:4:4:6:6:5:5:2:2:2:10:10:10:5:5:5:5:2:2:3:3:3:2:2:9:1:1:9:9:8:8:8:6:7:7:10:10:1:1:1:1:6:6:6:6:3:3:3:4:4:5:5:5:5:4:4:4:4:6:6:6:7:7:1:1:9:9:2:6:6:6:4:4:9:6:6:6:7:7:9:8:8:9:9:2:2:2:2:1:1:1:10:10:2:2:11:11:1:1:1:3:3:3:7:11:11:5:5:9:9:9:11:11:11:11:1:1:1:7:7:7:10:10:10:5:5:9:5:5:5:5:2:2:2:4:4:3:3:3:9:9:9:5:5:5:8:8:8:11:11:7:7:7:1:1:11:11:11:10:10:10:10:7:8:8:8:2:2:2:2:9:9:6:6:6:7:7:8:8:8:7:7:5:5:5:6:6:1:1:1:2:2:3:3:3:7:4:4:11:11:11:6:6:4:4:4:4:3:3:5:5:2:2:3:3:3:4:4:11:11:6:6:2:2:1:1:10:10:9:9:6:6:7:7:7:7:4:4:4:4:3:9:5:7:7:4:2:2:2:5:5:5:6:6:8:10:10:4:4:4:11:11:3:3:3:10:8:8:6:8:8:3:3:10:3:3:9:8:8:3:8</t>
   </si>
 </sst>
 </file>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122829D3-F209-42EA-A781-BED120AD3D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB199D5C-D233-4B3A-B9C5-2E31EA2079B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -93,19 +93,21 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>1:1:1:1:9:9:9:19:11:11:11:4:4:4:19:8:5:12:5:5:5:2:1:4:4:4:4:10:9:17:9:9:6:6:10:10:12:10:3:3:3:20:9:9:9:1:1:20:1:4:4:4:11:11:12:8:9:9:7:17:7:3:3:5:3:3:19:6:6:6:11:11:11:12:3:3:2:2:2:21:10:10:6:6:6:6:2:2:2:17:2:8:8:12:10:10:10:4:9:9:9:7:7:8:20:1:4:4:4:2:12:10:10:5:8:8:8:8:7:17:7:5:5:19:20:3:3:3:4:12:4:4:6:6:7:10:11:11:19:21:2:1:1:10:10:12:6:6:6:17:6:10:10:10:10:19:21:3:3:3:3:8:8:8:2:2:12:6:6:7:7:7:5:5:8:5:5:1:1:17:3:3:1:8:8:12:4:4:9:9:9:4:4:4:6:6:2:1:1:7:7:2:2:12:5:5:2:2:2:17:9:9:5:5:10:10:10:5:5:4:4:4:12:3:3:3:3:20:9:9:6:6:5:7:22:1:1:9:9:17:5:5:5:12:7:7:6:6:7:7:8:8:7:7:7:7:8:8:8:12:7:7:7:8:8:1:1:1:5:17:5:5:3:3:2:2:1:2:12:2:2:2:1:1:8:19:9:9:6:6:8:8:20:8:7:6:3:11:2:17:7:7:7:9:9:14:3:3:8:8:8:14:10:5:8:8:2:14:2:9:9:9:11:14:11:5:5:7:7:14:5:5:4:4:4:14:4:3:3:11:11:14:11:10:10:2:5:14:5:1:1:10:10:14:10:10:8:8:8:14:10:10:2:2:2:14:2:4:4:4:4:14:11:11:11:11:4:14:4:4:4:6:6:14:10:10:10:10:2:14:2:2:3:3:2:14:2:5:5:5:5:14:10:10:11:11:11:14:7:7:7:4:4:14:11:11:9:9:7:14:7:3:3:1:1:14:1:2:2:2:2:14:6:6:6:7:7:14:6:4:4:4:4:14:1:1:3:3:3:14:11:11:1:1:1:13:9:9:8:11:11:13:11:2:2:2:5:13:5:5:5:7:7:13:7:3:3:2:2:13:6:6:6:8:8:13:1:1:8:8:1:13:1:1:9:9:9:13:9:1:1:6:6:13:6:6:3:3:9:13:9:9:1:1:9:13:9:9:4:4:4:13:6:6:1:1:1:13:2:5:5:4:4:13:4:4:8:8:8:13:6:6:6:6:10:13:10:10:8:8:8:13:8:7:7:9:6:13:6:7:7:7:3:13:3:6:6:3:3:13:3:5:5:1:1:13:3:3:10:3:5:13:5:2:2:11:6:13:6:1:5:5:5:13:10:5:3:3:2:13:10:10:10:7:7:3:3:8:8:1:2:7:4:4:4:3:3:11:11:2:2:2:2:4:4:4:9:9:9:9:7:7:5:5:10:10:8:8:1:6:6:1:11:11:2:2:1:1:1:8:8:8:6:6:6:9:9:1:1:1:5:5:5:7:7:7:3:3:3:8:8:8:4:4:2:2:2:4:4:4:5:5:5:6:10:10:8:8:3:3:3:7:7:9:9:9:10:10:10:11:11:9:9:9:9:7:7:8:8:8:5:5:4:4:4:7:7:7:9:9:9:4:4:2:11:11:11:7:7:7:1:1:6:6:7:7:7:7:1:1:1:10:9:11:11:3:3:2:2:8:8:8:8:4:4:10:10:10:3:3:4:4:4:4:2:2:4:4:6:6:2:2:6:6:2:2:11:11:11:1:1:3:3:3:3:5:5:5:3:1:1:1:2:6:11:11:10:10:10:7:7:5:5:5:4:4:9:9:5:5:5:5:3:3:3:3:10:10:5:5:1:1:11:11:11:2:2:2:2:1:1:10:10:10:3:3:6:6:6:6:8:8:8:8:6:6:9:9:2:2:2:9:9:9:5:5:5:5:6:6:6:6:3:3:10:10:1:1:1:1:6:5:5:5:9:8:8:2:2:6:6:6:6:10:3:3:1:4:4:4:5:7:11:4:3:6:6:2:1:1</t>
+  </si>
+  <si>
+    <t>1:1:1:1:9:9:9:19:11:11:11:4:4:4:19:8:5:12:5:5:5:2:1:4:4:4:4:10:9:17:9:9:6:6:10:10:12:10:3:3:3:20:9:9:9:1:1:20:1:4:4:4:11:11:12:8:9:9:7:17:7:3:3:5:3:3:19:6:6:6:11:11:11:12:3:3:2:2:2:21:10:10:6:6:6:6:2:2:2:17:2:8:8:12:10:10:10:4:9:9:9:7:7:8:20:1:4:4:4:2:12:10:10:5:8:8:8:8:7:17:7:5:5:19:20:3:3:3:4:12:4:4:6:6:7:10:11:11:19:21:2:1:1:10:10:12:6:6:6:17:6:10:10:10:10:19:21:3:3:3:3:8:8:8:2:2:12:6:6:7:7:7:5:5:8:5:5:1:1:17:3:3:1:8:8:12:4:4:9:9:9:4:4:4:6:6:2:1:1:7:7:2:2:12:5:5:2:2:2:17:9:9:5:5:10:10:10:5:5:4:4:4:12:3:3:3:3:20:9:9:6:6:5:7:22:1:1:9:9:17:5:5:5:12:7:7:6:6:7:7:8:8:7:7:7:7:8:8:8:12:7:7:7:8:8:1:1:1:5:17:5:5:3:3:2:2:1:2:12:2:2:2:1:1:8:19:9:9:6:6:8:8:20:8:7:6:3:11:2:17:11:11:8:8:1:14:1:1:1:9:9:14:6:6:6:5:1:14:1:1:1:2:2:14:11:11:11:8:8:14:10:10:3:3:3:14:5:5:5:8:1:14:1:6:7:7:8:14:8:9:9:11:2:14:6:6:6:3:3:14:9:9:10:10:10:14:5:5:5:5:4:14:4:9:9:9:9:14:3:3:4:10:10:14:2:2:4:4:4:14:2:2:2:1:1:14:2:10:10:1:1:14:1:10:10:3:3:14:3:3:6:6:5:14:5:4:4:4:8:14:8:1:1:1:1:14:2:2:2:6:6:14:6:4:4:4:6:14:6:6:8:8:8:14:3:4:4:4:4:14:3:3:3:5:5:13:5:8:8:8:8:13:1:1:11:11:11:13:10:10:11:11:11:13:11:6:6:7:7:13:2:2:2:7:7:13:7:4:4:2:2:13:3:3:5:5:9:13:6:6:6:6:4:13:4:7:7:8:8:13:8:8:3:3:11:13:11:11:4:4:4:13:2:2:5:5:3:13:3:2:2:7:7:13:3:3:3:3:6:13:6:9:9:6:6:13:9:9:1:1:1:13:11:11:7:7:10:13:10:10:10:9:9:13:9:5:5:9:9:13:1:10:10:5:5:13:5:5:7:7:7:13:7:2:2:2:4:13:2:11:11:7:7:13:5:5:7:10:4:13:3:3:3:3:4:4:3:11:11:2:2:7:7:7:1:1:6:6:6:6:7:3:3:3:10:10:4:4:7:7:8:8:8:5:5:4:4:4:9:9:4:4:5:5:2:2:2:2:3:3:3:3:8:8:8:9:9:10:10:1:1:1:4:4:10:10:10:6:6:3:3:9:9:9:8:8:11:11:11:7:7:7:7:9:9:9:2:2:6:6:6:5:3:3:3:10:1:1:1:6:6:6:2:2:3:3:8:8:8:4:4:8:8:8:4:4:4:10:10:10:10:5:5:2:2:1:1:7:7:5:5:5:10:10:10:2:2:3:3:11:11:7:1:1:5:5:5:6:11:11:1:1:9:9:9:2:2:11:2:6:6:4:4:4:2:2:11:11:1:1:1:8:8:2:2:2:2:9:9:9:4:4:4:4:1:1:9:9:1:1:10:10:10:10:5:7:7:1:1:1:1:11:11:4:4:6:6:6:8:8:9:9:11:11:5:5:5:9:2:2:2:7:7:7:7:5:3:3:3:1:1:5:7:7:7:5:5:5:5:3:3:4:4:4:10:10:10:10:6:6:6:2:5:5:5:6:6:1:1:1:3:6:6:10:10:4:4:6:6:5:5:5:5:7:7:6:6:6:11:11:11:3:3:3:9:9:9:9:8:8:8:2:2:2:7:11:8:8:8:8</t>
+  </si>
+  <si>
+    <t>3:3:3:9:9:6:6:2:2:17:2:7:7:7:1:1:6:6:6:17:4:4:11:11:6:1:1:3:10:17:10:8:4:4:1:1:5:5:6:17:3:3:3:3:4:4:4:4:2:17:2:4:2:2:2:9:9:9:5:17:5:5:5:4:4:4:3:3:7:17:7:7:5:5:5:5:2:2:3:17:3:8:8:8:1:7:7:7:3:17:1:9:9:2:2:2:2:1:1:17:4:4:9:9:7:7:7:7:6:15:6:6:7:7:6:6:11:11:6:16:6:6:6:7:7:7:6:6:1:15:2:6:6:6:6:4:4:4:11:16:11:11:5:5:5:4:3:3:8:15:5:5:5:1:1:5:2:2:2:16:6:6:6:8:8:7:1:1:7:15:7:7:9:9:5:8:7:7:9:16:9:2:2:1:1:1:2:2:2:16:9:9:4:4:4:1:1:1:1:16:10:10:1:1:1:3:3:11:11:15:11:8:8:4:4:4:4:10:10:15:10:5:5:5:5:1:1:1:6:16:6:6:6:3:3:3:8:8:11:15:3:3:3:10:10:10:10:11:11:15:11:8:8:8:8:10:10:5:5:16:4:4:1:1:8:8:8:2:2:15:2:2:10:10:3:3:3:3:5:16:2:2:2:8:6:7:4:4:3:15:11:5:5:4:3:3:5:5:5:16:5:5:5:10:4:4:3:3:9:3:3:3:8:8:8:8:3:3:5:5:5:2:2:2:2:7:7:7:7:2:2:2:11:11:1:1:5:5:10:5:5:9:9:9:2:2:2:2:7:7:1:1:9:9:9:3:3:3:3:6:6:6:4:4:6:6:7:3:3:3:2:2:3:3:9:1:1:1:1:5:2:2:7:7:7:7:10:6:6:4:4:9:5:5:5:1:1:8:8:8:4:4:10:10:10:5:5:4:4:4:6:9:9:9:9:3:3:3:10:10:10:11:11:3:3:3:3:8:8:4:4:1:1:9:9:10:10:10:2:2:2:8:8:10:10:10:1:11:11:2:2:10:10:10:5:5:5:5:10:10:7:7:7:11:11:7:7:6:6:11:11:4:11:11:1:1:8:8:6:6:6:8:8:8:8:10:8:8:8:1:11:11:11:11:2:2:2:2:4:4:4:1:1:7:7:7:7:6:6:6:1:1:9:9:1:1:3:7:7:7:7:4:4:4:4:6:6:3:3:3:3:9:9:9:5:6:4:4:4:6:6:2:2:2:11:11:11:1:6:8:10:9:9:5:5:5:1:1:9:9:10:10:10:5:5:5:2:2:4:4:4:9:5:5:1:8:8:8:6:6:3:3:1:1:6:6:5:6:6:6:1:1:11:6:8:4:4:2:7:4:1:1:1:1:8:8:8:1:1:10:10:10:9:9:3:9:10:10:4:4:4:4:6:6:5:5:2:2:2:10:10:10:5:5:5:5:2:2:3:3:3:2:2:9:1:1:9:9:8:8:8:6:7:7:10:10:1:1:1:1:6:6:6:6:3:3:3:4:4:5:5:5:5:4:4:4:4:6:6:6:7:7:1:1:9:9:2:6:6:6:4:4:9:6:6:6:7:7:9:8:8:9:9:2:2:2:2:1:1:1:10:10:2:2:11:11:1:1:1:3:3:3:7:11:11:5:5:9:9:9:11:11:11:11:1:1:1:7:7:7:10:10:10:5:5:9:5:5:5:5:2:2:2:4:4:3:3:3:9:9:9:5:5:5:8:8:8:11:11:7:7:7:1:1:11:11:11:10:10:10:10:7:8:8:8:2:2:2:2:9:9:6:6:6:7:7:8:8:8:7:7:5:5:5:6:6:1:1:1:2:2:3:3:3:7:4:4:11:11:11:6:6:4:4:4:4:3:3:5:5:2:2:3:3:3:4:4:11:11:6:6:2:2:1:1:10:10:9:9:6:6:7:7:7:7:4:4:4:4:3:9:5:7:7:4:2:2:2:5:5:5:6:6:8:10:10:4:4:4:11:11:3:3:3:10:8:8:6:8:8:3:3:10:3:3:9:8:8:3:8</t>
+  </si>
+  <si>
     <t>7:7:19:1:1:20:2:2:8:8:8:8:20:19:11:10:5:5:6:6:6:4:4:4:4:6:6:6:6:17:5:5:5:1:1:1:1:7:7:3:3:3:9:9:2:2:2:2:8:3:3:7:7:7:7:6:6:2:2:17:2:1:1:8:8:4:4:11:11:11:1:1:1:19:5:4:10:10:10:11:1:1:20:10:10:2:2:2:4:17:4:4:4:21:3:3:9:9:9:9:3:3:19:21:7:7:3:3:8:8:2:2:19:5:5:6:6:8:8:17:7:7:7:3:3:3:3:20:21:10:10:4:4:5:5:5:5:20:10:10:10:6:6:1:1:1:1:6:6:17:6:5:5:5:5:8:8:4:4:4:4:7:7:7:7:21:22:10:10:10:6:6:8:4:4:3:3:3:5:17:4:4:4:4:3:3:3:7:5:5:7:7:7:10:10:2:5:5:5:8:8:8:1:1:1:1:2:8:8:17:8:8:6:6:6:1:1:11:11:6:6:6:6:9:9:5:5:2:3:2:2:9:9:2:2:9:9:9:1:17:1:4:4:8:8:8:8:9:9:4:3:3:5:5:7:7:7:6:6:6:2:3:3:3:5:5:5:4:4:17:1:1:1:2:2:2:4:4:4:11:11:9:9:20:21:7:7:3:3:1:1:2:2:6:6:2:2:11:2:17:11:11:3:6:6:9:9:5:5:9:9:9:2:2:2:7:7:7:7:6:6:4:4:4:4:2:2:2:3:3:3:5:5:8:8:3:3:3:2:2:6:6:6:2:2:2:11:11:11:11:4:6:7:3:3:3:8:8:7:7:7:7:1:1:1:9:9:9:9:6:6:3:3:10:10:10:7:7:1:1:10:10:7:7:7:8:8:4:4:4:9:9:11:11:5:5:5:8:7:7:7:7:9:9:9:11:5:5:5:1:1:1:9:2:2:3:3:10:1:1:2:10:3:3:8:8:3:3:3:11:11:4:5:5:5:5:3:9:9:10:10:10:2:2:2:4:4:11:11:11:11:6:6:1:1:8:3:3:3:7:7:4:4:1:1:11:11:11:11:3:3:4:4:10:10:10:10:6:6:6:5:5:6:1:1:1:8:8:5:5:9:7:7:7:7:2:2:2:10:10:10:10:2:2:6:6:4:4:4:4:1:1:1:5:5:5:2:2:2:4:4:4:8:2:2:3:9:9:4:4:4:4:5:5:8:8:6:6:10:10:10:8:8:8:5:5:1:1:6:6:6:6:5:5:4:4:1:1:1:9:9:6:6:1:1:1:10:10:10:6:1:1:8:8:8:7:10:9:9:6:6:2:9:3:3:3:8:5:5:2:2:11:4:4:5:8:6:8:8:3:3:3:2:2:2:2:7:7:7:9:9:6:3:3:9:9:4:4:5:5:10:10:10:5:5:2:2:2:2:6:6:6:7:10:10:10:9:9:4:4:4:4:8:8:10:10:10:3:3:3:11:11:11:4:10:10:10:10:4:5:9:9:8:8:8:7:7:7:5:5:4:4:4:2:2:2:2:3:3:11:11:11:10:10:10:2:2:2:3:3:3:1:1:8:8:6:6:1:5:8:8:6:6:6:6:3:3:3:9:9:9:9:1:1:1:7:7:7:4:4:4:2:2:8:8:4:4:4:4:11:11:4:4:4:4:7:7:7:10:10:10:1:1:1:7:7:1:1:1:5:5:5:5:6:6:6:6:9:9:5:5:7:7:7:5:5:5:10:10:10:5:5:1:1:7:7:7:6:6:3:3:9:9:9:9:1:1:8:8:8:10:9:11:5:7:7:4:4:3:3:3:3:5:5:5:7:7:5:5:5:2:2:2:6:6:6:11:9:9:9:3:3:3:11:11:11:11:3:3:3:3:2:2:10:10:1:8:2:2:2:2:4:4:4:1:1:8:8:8:8:6:6:6:5:5:1:8:2:2:6:11:11:11:1:1:1:1:9:9:6:1:6:6:6:8:8:6:6:6:1:2:2:11:11:8:1:8:8:3:11:4:4:5:5:1:1:1:3:9:4</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>1:1:1:1:9:9:9:19:11:11:11:4:4:4:19:8:5:12:5:5:5:2:1:4:4:4:4:10:9:17:9:9:6:6:10:10:12:10:3:3:3:20:9:9:9:1:1:20:1:4:4:4:11:11:12:8:9:9:7:17:7:3:3:5:3:3:19:6:6:6:11:11:11:12:3:3:2:2:2:21:10:10:6:6:6:6:2:2:2:17:2:8:8:12:10:10:10:4:9:9:9:7:7:8:20:1:4:4:4:2:12:10:10:5:8:8:8:8:7:17:7:5:5:19:20:3:3:3:4:12:4:4:6:6:7:10:11:11:19:21:2:1:1:10:10:12:6:6:6:17:6:10:10:10:10:19:21:3:3:3:3:8:8:8:2:2:12:6:6:7:7:7:5:5:8:5:5:1:1:17:3:3:1:8:8:12:4:4:9:9:9:4:4:4:6:6:2:1:1:7:7:2:2:12:5:5:2:2:2:17:9:9:5:5:10:10:10:5:5:4:4:4:12:3:3:3:3:20:9:9:6:6:5:7:22:1:1:9:9:17:5:5:5:12:7:7:6:6:7:7:8:8:7:7:7:7:8:8:8:12:7:7:7:8:8:1:1:1:5:17:5:5:3:3:2:2:1:2:12:2:2:2:1:1:8:19:9:9:6:6:8:8:20:8:7:6:3:11:2:17:10:10:10:10:1:14:1:1:6:6:6:14:6:7:7:2:2:14:7:7:1:1:2:14:2:2:2:7:7:14:8:8:6:5:5:14:8:8:8:10:10:14:10:8:8:10:10:14:8:8:8:8:3:14:3:3:3:1:1:14:1:6:6:5:5:14:2:2:4:4:4:14:11:11:7:7:4:14:4:4:4:6:6:14:7:10:10:10:10:14:1:1:11:11:11:14:11:7:7:7:8:14:8:8:8:1:1:14:1:1:3:3:9:14:9:9:9:4:4:14:3:3:5:5:5:14:5:2:2:4:4:14:7:7:2:2:11:14:11:11:5:5:5:14:2:1:1:2:2:14:2:6:6:9:9:13:9:6:6:10:10:13:10:9:9:7:7:13:6:6:6:6:2:13:2:2:4:4:4:13:5:5:5:4:4:13:9:11:11:6:6:13:6:5:1:1:1:13:8:11:2:2:7:13:7:7:3:3:3:13:5:5:5:5:4:13:4:10:10:3:3:13:2:2:5:3:3:13:11:11:11:9:9:13:8:8:8:8:11:13:11:1:1:1:1:13:9:9:6:6:6:13:2:2:3:3:3:13:4:4:5:5:5:13:4:5:5:11:11:13:6:6:9:9:9:13:10:10:3:3:3:13:9:9:11:9:1:13:1:4:4:4:3:13:7:3:4:3:3:13:5:5:5:8:8:8:2:2:2:2:7:2:2:4:4:11:11:11:10:10:10:1:1:5:5:6:6:6:4:4:4:5:5:5:10:10:3:3:7:7:7:7:10:10:1:1:1:8:6:6:6:7:2:2:2:3:3:3:4:3:3:9:9:4:1:1:3:3:9:9:9:9:8:8:5:2:2:7:7:2:2:9:9:2:2:2:7:7:1:1:1:2:8:8:8:6:6:11:11:1:1:1:1:10:10:8:8:10:1:4:4:4:9:9:9:1:1:1:10:10:10:10:2:2:2:2:1:1:3:3:3:5:5:5:7:7:8:8:8:6:6:6:5:4:4:6:6:9:9:8:8:8:7:7:7:7:2:2:6:6:6:11:11:11:3:3:3:6:6:3:3:9:9:9:3:7:7:3:3:3:3:4:4:4:4:9:10:10:11:11:11:6:6:4:3:3:3:4:4:4:4:1:1:9:9:9:9:5:6:6:6:4:4:4:7:7:7:4:4:4:4:11:5:5:6:6:8:8:8:8:6:7:9:9:10:10:2:2:2:5:5:2:11:11:11:10:10:10:5:5:3:1:1:1:6:6:8:8:5:5:5:10:10:10:7:7:7:2:2:11:11:4:4:1:1:1:3:3:2:8:8:5:5:10:5:5:11:11:11:3:3:1:1:9:9:6:6:5:5:5</t>
-  </si>
-  <si>
-    <t>1:1:1:1:9:9:9:19:11:11:11:4:4:4:19:8:5:12:5:5:5:2:1:4:4:4:4:10:9:17:9:9:6:6:10:10:12:10:3:3:3:20:9:9:9:1:1:20:1:4:4:4:11:11:12:8:9:9:7:17:7:3:3:5:3:3:19:6:6:6:11:11:11:12:3:3:2:2:2:21:10:10:6:6:6:6:2:2:2:17:2:8:8:12:10:10:10:4:9:9:9:7:7:8:20:1:4:4:4:2:12:10:10:5:8:8:8:8:7:17:7:5:5:19:20:3:3:3:4:12:4:4:6:6:7:10:11:11:19:21:2:1:1:10:10:12:6:6:6:17:6:10:10:10:10:19:21:3:3:3:3:8:8:8:2:2:12:6:6:7:7:7:5:5:8:5:5:1:1:17:3:3:1:8:8:12:4:4:9:9:9:4:4:4:6:6:2:1:1:7:7:2:2:12:5:5:2:2:2:17:9:9:5:5:10:10:10:5:5:4:4:4:12:3:3:3:3:20:9:9:6:6:5:7:22:1:1:9:9:17:5:5:5:12:7:7:6:6:7:7:8:8:7:7:7:7:8:8:8:12:7:7:7:8:8:1:1:1:5:17:5:5:3:3:2:2:1:2:12:2:2:2:1:1:8:19:9:9:6:6:8:8:20:8:7:6:3:11:2:17:7:7:7:9:9:14:3:3:8:8:8:14:10:5:8:8:2:14:2:9:9:9:11:14:11:5:5:7:7:14:5:5:4:4:4:14:4:3:3:11:11:14:11:10:10:2:5:14:5:1:1:10:10:14:10:10:8:8:8:14:10:10:2:2:2:14:2:4:4:4:4:14:11:11:11:11:4:14:4:4:4:6:6:14:10:10:10:10:2:14:2:2:3:3:2:14:2:5:5:5:5:14:10:10:11:11:11:14:7:7:7:4:4:14:11:11:9:9:7:14:7:3:3:1:1:14:1:2:2:2:2:14:6:6:6:7:7:14:6:4:4:4:4:14:1:1:3:3:3:14:11:11:1:1:1:13:9:9:8:11:11:13:11:2:2:2:5:13:5:5:5:7:7:13:7:3:3:2:2:13:6:6:6:8:8:13:1:1:8:8:1:13:1:1:9:9:9:13:9:1:1:6:6:13:6:6:3:3:9:13:9:9:1:1:9:13:9:9:4:4:4:13:6:6:1:1:1:13:2:5:5:4:4:13:4:4:8:8:8:13:6:6:6:6:10:13:10:10:8:8:8:13:8:7:7:9:6:13:6:7:7:7:3:13:3:6:6:3:3:13:3:5:5:1:1:13:3:3:10:3:5:13:5:2:2:11:6:13:6:1:5:5:5:13:10:5:3:3:2:13:10:10:10:7:7:3:3:8:8:1:2:7:4:4:4:3:3:11:11:2:2:2:2:4:4:4:9:9:9:9:7:7:5:5:10:10:8:8:1:6:6:1:11:11:2:2:1:1:1:8:8:8:6:6:6:9:9:1:1:1:5:5:5:7:7:7:3:3:3:8:8:8:4:4:2:2:2:4:4:4:5:5:5:6:10:10:8:8:3:3:3:7:7:9:9:9:10:10:10:11:11:9:9:9:9:7:7:8:8:8:5:5:4:4:4:7:7:7:9:9:9:4:4:2:11:11:11:7:7:7:1:1:6:6:7:7:7:7:1:1:1:10:9:11:11:3:3:2:2:8:8:8:8:4:4:10:10:10:3:3:4:4:4:4:2:2:4:4:6:6:2:2:6:6:2:2:11:11:11:1:1:3:3:3:3:5:5:5:3:1:1:1:2:6:11:11:10:10:10:7:7:5:5:5:4:4:9:9:5:5:5:5:3:3:3:3:10:10:5:5:1:1:11:11:11:2:2:2:2:1:1:10:10:10:3:3:6:6:6:6:8:8:8:8:6:6:9:9:2:2:2:9:9:9:5:5:5:5:6:6:6:6:3:3:10:10:1:1:1:1:6:5:5:5:9:8:8:2:2:6:6:6:6:10:3:3:1:4:4:4:5:7:11:4:3:6:6:2:1:1</t>
-  </si>
-  <si>
-    <t>1:1:1:1:9:9:9:19:11:11:11:4:4:4:19:8:5:12:5:5:5:2:1:4:4:4:4:10:9:17:9:9:6:6:10:10:12:10:3:3:3:20:9:9:9:1:1:20:1:4:4:4:11:11:12:8:9:9:7:17:7:3:3:5:3:3:19:6:6:6:11:11:11:12:3:3:2:2:2:21:10:10:6:6:6:6:2:2:2:17:2:8:8:12:10:10:10:4:9:9:9:7:7:8:20:1:4:4:4:2:12:10:10:5:8:8:8:8:7:17:7:5:5:19:20:3:3:3:4:12:4:4:6:6:7:10:11:11:19:21:2:1:1:10:10:12:6:6:6:17:6:10:10:10:10:19:21:3:3:3:3:8:8:8:2:2:12:6:6:7:7:7:5:5:8:5:5:1:1:17:3:3:1:8:8:12:4:4:9:9:9:4:4:4:6:6:2:1:1:7:7:2:2:12:5:5:2:2:2:17:9:9:5:5:10:10:10:5:5:4:4:4:12:3:3:3:3:20:9:9:6:6:5:7:22:1:1:9:9:17:5:5:5:12:7:7:6:6:7:7:8:8:7:7:7:7:8:8:8:12:7:7:7:8:8:1:1:1:5:17:5:5:3:3:2:2:1:2:12:2:2:2:1:1:8:19:9:9:6:6:8:8:20:8:7:6:3:11:2:17:11:11:8:8:1:14:1:1:1:9:9:14:6:6:6:5:1:14:1:1:1:2:2:14:11:11:11:8:8:14:10:10:3:3:3:14:5:5:5:8:1:14:1:6:7:7:8:14:8:9:9:11:2:14:6:6:6:3:3:14:9:9:10:10:10:14:5:5:5:5:4:14:4:9:9:9:9:14:3:3:4:10:10:14:2:2:4:4:4:14:2:2:2:1:1:14:2:10:10:1:1:14:1:10:10:3:3:14:3:3:6:6:5:14:5:4:4:4:8:14:8:1:1:1:1:14:2:2:2:6:6:14:6:4:4:4:6:14:6:6:8:8:8:14:3:4:4:4:4:14:3:3:3:5:5:13:5:8:8:8:8:13:1:1:11:11:11:13:10:10:11:11:11:13:11:6:6:7:7:13:2:2:2:7:7:13:7:4:4:2:2:13:3:3:5:5:9:13:6:6:6:6:4:13:4:7:7:8:8:13:8:8:3:3:11:13:11:11:4:4:4:13:2:2:5:5:3:13:3:2:2:7:7:13:3:3:3:3:6:13:6:9:9:6:6:13:9:9:1:1:1:13:11:11:7:7:10:13:10:10:10:9:9:13:9:5:5:9:9:13:1:10:10:5:5:13:5:5:7:7:7:13:7:2:2:2:4:13:2:11:11:7:7:13:5:5:7:10:4:13:3:3:3:3:4:4:3:11:11:2:2:7:7:7:1:1:6:6:6:6:7:3:3:3:10:10:4:4:7:7:8:8:8:5:5:4:4:4:9:9:4:4:5:5:2:2:2:2:3:3:3:3:8:8:8:9:9:10:10:1:1:1:4:4:10:10:10:6:6:3:3:9:9:9:8:8:11:11:11:7:7:7:7:9:9:9:2:2:6:6:6:5:3:3:3:10:1:1:1:6:6:6:2:2:3:3:8:8:8:4:4:8:8:8:4:4:4:10:10:10:10:5:5:2:2:1:1:7:7:5:5:5:10:10:10:2:2:3:3:11:11:7:1:1:5:5:5:6:11:11:1:1:9:9:9:2:2:11:2:6:6:4:4:4:2:2:11:11:1:1:1:8:8:2:2:2:2:9:9:9:4:4:4:4:1:1:9:9:1:1:10:10:10:10:5:7:7:1:1:1:1:11:11:4:4:6:6:6:8:8:9:9:11:11:5:5:5:9:2:2:2:7:7:7:7:5:3:3:3:1:1:5:7:7:7:5:5:5:5:3:3:4:4:4:10:10:10:10:6:6:6:2:5:5:5:6:6:1:1:1:3:6:6:10:10:4:4:6:6:5:5:5:5:7:7:6:6:6:11:11:11:3:3:3:9:9:9:9:8:8:8:2:2:2:7:11:8:8:8:8</t>
-  </si>
-  <si>
-    <t>3:3:3:9:9:6:6:2:2:17:2:7:7:7:1:1:6:6:6:17:4:4:11:11:6:1:1:3:10:17:10:8:4:4:1:1:5:5:6:17:3:3:3:3:4:4:4:4:2:17:2:4:2:2:2:9:9:9:5:17:5:5:5:4:4:4:3:3:7:17:7:7:5:5:5:5:2:2:3:17:3:8:8:8:1:7:7:7:3:17:1:9:9:2:2:2:2:1:1:17:4:4:9:9:7:7:7:7:6:15:6:6:7:7:6:6:11:11:6:16:6:6:6:7:7:7:6:6:1:15:2:6:6:6:6:4:4:4:11:16:11:11:5:5:5:4:3:3:8:15:5:5:5:1:1:5:2:2:2:16:6:6:6:8:8:7:1:1:7:15:7:7:9:9:5:8:7:7:9:16:9:2:2:1:1:1:2:2:2:16:9:9:4:4:4:1:1:1:1:16:10:10:1:1:1:3:3:11:11:15:11:8:8:4:4:4:4:10:10:15:10:5:5:5:5:1:1:1:6:16:6:6:6:3:3:3:8:8:11:15:3:3:3:10:10:10:10:11:11:15:11:8:8:8:8:10:10:5:5:16:4:4:1:1:8:8:8:2:2:15:2:2:10:10:3:3:3:3:5:16:2:2:2:8:6:7:4:4:3:15:11:5:5:4:3:3:5:5:5:16:5:5:5:10:4:4:3:3:9:3:3:3:8:8:8:8:3:3:5:5:5:2:2:2:2:7:7:7:7:2:2:2:11:11:1:1:5:5:10:5:5:9:9:9:2:2:2:2:7:7:1:1:9:9:9:3:3:3:3:6:6:6:4:4:6:6:7:3:3:3:2:2:3:3:9:1:1:1:1:5:2:2:7:7:7:7:10:6:6:4:4:9:5:5:5:1:1:8:8:8:4:4:10:10:10:5:5:4:4:4:6:9:9:9:9:3:3:3:10:10:10:11:11:3:3:3:3:8:8:4:4:1:1:9:9:10:10:10:2:2:2:8:8:10:10:10:1:11:11:2:2:10:10:10:5:5:5:5:10:10:7:7:7:11:11:7:7:6:6:11:11:4:11:11:1:1:8:8:6:6:6:8:8:8:8:10:8:8:8:1:11:11:11:11:2:2:2:2:4:4:4:1:1:7:7:7:7:6:6:6:1:1:9:9:1:1:3:7:7:7:7:4:4:4:4:6:6:3:3:3:3:9:9:9:5:6:4:4:4:6:6:2:2:2:11:11:11:1:6:8:10:9:9:5:5:5:1:1:9:9:10:10:10:5:5:5:2:2:4:4:4:9:5:5:1:8:8:8:6:6:3:3:1:1:6:6:5:6:6:6:1:1:11:6:8:4:4:2:7:4:1:1:1:1:8:8:8:1:1:10:10:10:9:9:3:9:10:10:4:4:4:4:6:6:5:5:2:2:2:10:10:10:5:5:5:5:2:2:3:3:3:2:2:9:1:1:9:9:8:8:8:6:7:7:10:10:1:1:1:1:6:6:6:6:3:3:3:4:4:5:5:5:5:4:4:4:4:6:6:6:7:7:1:1:9:9:2:6:6:6:4:4:9:6:6:6:7:7:9:8:8:9:9:2:2:2:2:1:1:1:10:10:2:2:11:11:1:1:1:3:3:3:7:11:11:5:5:9:9:9:11:11:11:11:1:1:1:7:7:7:10:10:10:5:5:9:5:5:5:5:2:2:2:4:4:3:3:3:9:9:9:5:5:5:8:8:8:11:11:7:7:7:1:1:11:11:11:10:10:10:10:7:8:8:8:2:2:2:2:9:9:6:6:6:7:7:8:8:8:7:7:5:5:5:6:6:1:1:1:2:2:3:3:3:7:4:4:11:11:11:6:6:4:4:4:4:3:3:5:5:2:2:3:3:3:4:4:11:11:6:6:2:2:1:1:10:10:9:9:6:6:7:7:7:7:4:4:4:4:3:9:5:7:7:4:2:2:2:5:5:5:6:6:8:10:10:4:4:4:11:11:3:3:3:10:8:8:6:8:8:3:3:10:3:3:9:8:8:3:8</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -591,7 +593,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -608,7 +610,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -625,7 +627,7 @@
         <v>12</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -642,7 +644,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -659,7 +661,7 @@
         <v>12</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB199D5C-D233-4B3A-B9C5-2E31EA2079B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA282FA-7F24-46EA-A39E-BF355AB9CD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoller" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -25,13 +38,12 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{3FD10EDE-449E-4D9B-84EC-E672D9B939DE}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
             <family val="3"/>
             <charset val="134"/>
@@ -70,6 +82,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>Map&lt;int{,}List&lt;int&gt;{&amp;}&gt;{;}</t>
+  </si>
+  <si>
     <t>List&lt;int&gt;{:}</t>
   </si>
   <si>
@@ -85,36 +100,29 @@
     <t>elements</t>
   </si>
   <si>
-    <t>Map&lt;int{,}List&lt;int&gt;{&amp;}&gt;{;}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1&amp;300;2,301&amp;600;3,601&amp;900</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:1:1:1:9:9:9:19:11:11:11:4:4:4:19:8:5:12:5:5:5:2:1:4:4:4:4:10:9:17:9:9:6:6:10:10:12:10:3:3:3:20:9:9:9:1:1:20:1:4:4:4:11:11:12:8:9:9:7:17:7:3:3:5:3:3:19:6:6:6:11:11:11:12:3:3:2:2:2:21:10:10:6:6:6:6:2:2:2:17:2:8:8:12:10:10:10:4:9:9:9:7:7:8:20:1:4:4:4:2:12:10:10:5:8:8:8:8:7:17:7:5:5:19:20:3:3:3:4:12:4:4:6:6:7:10:11:11:19:21:2:1:1:10:10:12:6:6:6:17:6:10:10:10:10:19:21:3:3:3:3:8:8:8:2:2:12:6:6:7:7:7:5:5:8:5:5:1:1:17:3:3:1:8:8:12:4:4:9:9:9:4:4:4:6:6:2:1:1:7:7:2:2:12:5:5:2:2:2:17:9:9:5:5:10:10:10:5:5:4:4:4:12:3:3:3:3:20:9:9:6:6:5:7:22:1:1:9:9:17:5:5:5:12:7:7:6:6:7:7:8:8:7:7:7:7:8:8:8:12:7:7:7:8:8:1:1:1:5:17:5:5:3:3:2:2:1:2:12:2:2:2:1:1:8:19:9:9:6:6:8:8:20:8:7:6:3:11:2:17:7:7:7:9:9:14:3:3:8:8:8:14:10:5:8:8:2:14:2:9:9:9:11:14:11:5:5:7:7:14:5:5:4:4:4:14:4:3:3:11:11:14:11:10:10:2:5:14:5:1:1:10:10:14:10:10:8:8:8:14:10:10:2:2:2:14:2:4:4:4:4:14:11:11:11:11:4:14:4:4:4:6:6:14:10:10:10:10:2:14:2:2:3:3:2:14:2:5:5:5:5:14:10:10:11:11:11:14:7:7:7:4:4:14:11:11:9:9:7:14:7:3:3:1:1:14:1:2:2:2:2:14:6:6:6:7:7:14:6:4:4:4:4:14:1:1:3:3:3:14:11:11:1:1:1:13:9:9:8:11:11:13:11:2:2:2:5:13:5:5:5:7:7:13:7:3:3:2:2:13:6:6:6:8:8:13:1:1:8:8:1:13:1:1:9:9:9:13:9:1:1:6:6:13:6:6:3:3:9:13:9:9:1:1:9:13:9:9:4:4:4:13:6:6:1:1:1:13:2:5:5:4:4:13:4:4:8:8:8:13:6:6:6:6:10:13:10:10:8:8:8:13:8:7:7:9:6:13:6:7:7:7:3:13:3:6:6:3:3:13:3:5:5:1:1:13:3:3:10:3:5:13:5:2:2:11:6:13:6:1:5:5:5:13:10:5:3:3:2:13:10:10:10:7:7:3:3:8:8:1:2:7:4:4:4:3:3:11:11:2:2:2:2:4:4:4:9:9:9:9:7:7:5:5:10:10:8:8:1:6:6:1:11:11:2:2:1:1:1:8:8:8:6:6:6:9:9:1:1:1:5:5:5:7:7:7:3:3:3:8:8:8:4:4:2:2:2:4:4:4:5:5:5:6:10:10:8:8:3:3:3:7:7:9:9:9:10:10:10:11:11:9:9:9:9:7:7:8:8:8:5:5:4:4:4:7:7:7:9:9:9:4:4:2:11:11:11:7:7:7:1:1:6:6:7:7:7:7:1:1:1:10:9:11:11:3:3:2:2:8:8:8:8:4:4:10:10:10:3:3:4:4:4:4:2:2:4:4:6:6:2:2:6:6:2:2:11:11:11:1:1:3:3:3:3:5:5:5:3:1:1:1:2:6:11:11:10:10:10:7:7:5:5:5:4:4:9:9:5:5:5:5:3:3:3:3:10:10:5:5:1:1:11:11:11:2:2:2:2:1:1:10:10:10:3:3:6:6:6:6:8:8:8:8:6:6:9:9:2:2:2:9:9:9:5:5:5:5:6:6:6:6:3:3:10:10:1:1:1:1:6:5:5:5:9:8:8:2:2:6:6:6:6:10:3:3:1:4:4:4:5:7:11:4:3:6:6:2:1:1</t>
-  </si>
-  <si>
-    <t>1:1:1:1:9:9:9:19:11:11:11:4:4:4:19:8:5:12:5:5:5:2:1:4:4:4:4:10:9:17:9:9:6:6:10:10:12:10:3:3:3:20:9:9:9:1:1:20:1:4:4:4:11:11:12:8:9:9:7:17:7:3:3:5:3:3:19:6:6:6:11:11:11:12:3:3:2:2:2:21:10:10:6:6:6:6:2:2:2:17:2:8:8:12:10:10:10:4:9:9:9:7:7:8:20:1:4:4:4:2:12:10:10:5:8:8:8:8:7:17:7:5:5:19:20:3:3:3:4:12:4:4:6:6:7:10:11:11:19:21:2:1:1:10:10:12:6:6:6:17:6:10:10:10:10:19:21:3:3:3:3:8:8:8:2:2:12:6:6:7:7:7:5:5:8:5:5:1:1:17:3:3:1:8:8:12:4:4:9:9:9:4:4:4:6:6:2:1:1:7:7:2:2:12:5:5:2:2:2:17:9:9:5:5:10:10:10:5:5:4:4:4:12:3:3:3:3:20:9:9:6:6:5:7:22:1:1:9:9:17:5:5:5:12:7:7:6:6:7:7:8:8:7:7:7:7:8:8:8:12:7:7:7:8:8:1:1:1:5:17:5:5:3:3:2:2:1:2:12:2:2:2:1:1:8:19:9:9:6:6:8:8:20:8:7:6:3:11:2:17:11:11:8:8:1:14:1:1:1:9:9:14:6:6:6:5:1:14:1:1:1:2:2:14:11:11:11:8:8:14:10:10:3:3:3:14:5:5:5:8:1:14:1:6:7:7:8:14:8:9:9:11:2:14:6:6:6:3:3:14:9:9:10:10:10:14:5:5:5:5:4:14:4:9:9:9:9:14:3:3:4:10:10:14:2:2:4:4:4:14:2:2:2:1:1:14:2:10:10:1:1:14:1:10:10:3:3:14:3:3:6:6:5:14:5:4:4:4:8:14:8:1:1:1:1:14:2:2:2:6:6:14:6:4:4:4:6:14:6:6:8:8:8:14:3:4:4:4:4:14:3:3:3:5:5:13:5:8:8:8:8:13:1:1:11:11:11:13:10:10:11:11:11:13:11:6:6:7:7:13:2:2:2:7:7:13:7:4:4:2:2:13:3:3:5:5:9:13:6:6:6:6:4:13:4:7:7:8:8:13:8:8:3:3:11:13:11:11:4:4:4:13:2:2:5:5:3:13:3:2:2:7:7:13:3:3:3:3:6:13:6:9:9:6:6:13:9:9:1:1:1:13:11:11:7:7:10:13:10:10:10:9:9:13:9:5:5:9:9:13:1:10:10:5:5:13:5:5:7:7:7:13:7:2:2:2:4:13:2:11:11:7:7:13:5:5:7:10:4:13:3:3:3:3:4:4:3:11:11:2:2:7:7:7:1:1:6:6:6:6:7:3:3:3:10:10:4:4:7:7:8:8:8:5:5:4:4:4:9:9:4:4:5:5:2:2:2:2:3:3:3:3:8:8:8:9:9:10:10:1:1:1:4:4:10:10:10:6:6:3:3:9:9:9:8:8:11:11:11:7:7:7:7:9:9:9:2:2:6:6:6:5:3:3:3:10:1:1:1:6:6:6:2:2:3:3:8:8:8:4:4:8:8:8:4:4:4:10:10:10:10:5:5:2:2:1:1:7:7:5:5:5:10:10:10:2:2:3:3:11:11:7:1:1:5:5:5:6:11:11:1:1:9:9:9:2:2:11:2:6:6:4:4:4:2:2:11:11:1:1:1:8:8:2:2:2:2:9:9:9:4:4:4:4:1:1:9:9:1:1:10:10:10:10:5:7:7:1:1:1:1:11:11:4:4:6:6:6:8:8:9:9:11:11:5:5:5:9:2:2:2:7:7:7:7:5:3:3:3:1:1:5:7:7:7:5:5:5:5:3:3:4:4:4:10:10:10:10:6:6:6:2:5:5:5:6:6:1:1:1:3:6:6:10:10:4:4:6:6:5:5:5:5:7:7:6:6:6:11:11:11:3:3:3:9:9:9:9:8:8:8:2:2:2:7:11:8:8:8:8</t>
-  </si>
-  <si>
-    <t>3:3:3:9:9:6:6:2:2:17:2:7:7:7:1:1:6:6:6:17:4:4:11:11:6:1:1:3:10:17:10:8:4:4:1:1:5:5:6:17:3:3:3:3:4:4:4:4:2:17:2:4:2:2:2:9:9:9:5:17:5:5:5:4:4:4:3:3:7:17:7:7:5:5:5:5:2:2:3:17:3:8:8:8:1:7:7:7:3:17:1:9:9:2:2:2:2:1:1:17:4:4:9:9:7:7:7:7:6:15:6:6:7:7:6:6:11:11:6:16:6:6:6:7:7:7:6:6:1:15:2:6:6:6:6:4:4:4:11:16:11:11:5:5:5:4:3:3:8:15:5:5:5:1:1:5:2:2:2:16:6:6:6:8:8:7:1:1:7:15:7:7:9:9:5:8:7:7:9:16:9:2:2:1:1:1:2:2:2:16:9:9:4:4:4:1:1:1:1:16:10:10:1:1:1:3:3:11:11:15:11:8:8:4:4:4:4:10:10:15:10:5:5:5:5:1:1:1:6:16:6:6:6:3:3:3:8:8:11:15:3:3:3:10:10:10:10:11:11:15:11:8:8:8:8:10:10:5:5:16:4:4:1:1:8:8:8:2:2:15:2:2:10:10:3:3:3:3:5:16:2:2:2:8:6:7:4:4:3:15:11:5:5:4:3:3:5:5:5:16:5:5:5:10:4:4:3:3:9:3:3:3:8:8:8:8:3:3:5:5:5:2:2:2:2:7:7:7:7:2:2:2:11:11:1:1:5:5:10:5:5:9:9:9:2:2:2:2:7:7:1:1:9:9:9:3:3:3:3:6:6:6:4:4:6:6:7:3:3:3:2:2:3:3:9:1:1:1:1:5:2:2:7:7:7:7:10:6:6:4:4:9:5:5:5:1:1:8:8:8:4:4:10:10:10:5:5:4:4:4:6:9:9:9:9:3:3:3:10:10:10:11:11:3:3:3:3:8:8:4:4:1:1:9:9:10:10:10:2:2:2:8:8:10:10:10:1:11:11:2:2:10:10:10:5:5:5:5:10:10:7:7:7:11:11:7:7:6:6:11:11:4:11:11:1:1:8:8:6:6:6:8:8:8:8:10:8:8:8:1:11:11:11:11:2:2:2:2:4:4:4:1:1:7:7:7:7:6:6:6:1:1:9:9:1:1:3:7:7:7:7:4:4:4:4:6:6:3:3:3:3:9:9:9:5:6:4:4:4:6:6:2:2:2:11:11:11:1:6:8:10:9:9:5:5:5:1:1:9:9:10:10:10:5:5:5:2:2:4:4:4:9:5:5:1:8:8:8:6:6:3:3:1:1:6:6:5:6:6:6:1:1:11:6:8:4:4:2:7:4:1:1:1:1:8:8:8:1:1:10:10:10:9:9:3:9:10:10:4:4:4:4:6:6:5:5:2:2:2:10:10:10:5:5:5:5:2:2:3:3:3:2:2:9:1:1:9:9:8:8:8:6:7:7:10:10:1:1:1:1:6:6:6:6:3:3:3:4:4:5:5:5:5:4:4:4:4:6:6:6:7:7:1:1:9:9:2:6:6:6:4:4:9:6:6:6:7:7:9:8:8:9:9:2:2:2:2:1:1:1:10:10:2:2:11:11:1:1:1:3:3:3:7:11:11:5:5:9:9:9:11:11:11:11:1:1:1:7:7:7:10:10:10:5:5:9:5:5:5:5:2:2:2:4:4:3:3:3:9:9:9:5:5:5:8:8:8:11:11:7:7:7:1:1:11:11:11:10:10:10:10:7:8:8:8:2:2:2:2:9:9:6:6:6:7:7:8:8:8:7:7:5:5:5:6:6:1:1:1:2:2:3:3:3:7:4:4:11:11:11:6:6:4:4:4:4:3:3:5:5:2:2:3:3:3:4:4:11:11:6:6:2:2:1:1:10:10:9:9:6:6:7:7:7:7:4:4:4:4:3:9:5:7:7:4:2:2:2:5:5:5:6:6:8:10:10:4:4:4:11:11:3:3:3:10:8:8:6:8:8:3:3:10:3:3:9:8:8:3:8</t>
-  </si>
-  <si>
-    <t>7:7:19:1:1:20:2:2:8:8:8:8:20:19:11:10:5:5:6:6:6:4:4:4:4:6:6:6:6:17:5:5:5:1:1:1:1:7:7:3:3:3:9:9:2:2:2:2:8:3:3:7:7:7:7:6:6:2:2:17:2:1:1:8:8:4:4:11:11:11:1:1:1:19:5:4:10:10:10:11:1:1:20:10:10:2:2:2:4:17:4:4:4:21:3:3:9:9:9:9:3:3:19:21:7:7:3:3:8:8:2:2:19:5:5:6:6:8:8:17:7:7:7:3:3:3:3:20:21:10:10:4:4:5:5:5:5:20:10:10:10:6:6:1:1:1:1:6:6:17:6:5:5:5:5:8:8:4:4:4:4:7:7:7:7:21:22:10:10:10:6:6:8:4:4:3:3:3:5:17:4:4:4:4:3:3:3:7:5:5:7:7:7:10:10:2:5:5:5:8:8:8:1:1:1:1:2:8:8:17:8:8:6:6:6:1:1:11:11:6:6:6:6:9:9:5:5:2:3:2:2:9:9:2:2:9:9:9:1:17:1:4:4:8:8:8:8:9:9:4:3:3:5:5:7:7:7:6:6:6:2:3:3:3:5:5:5:4:4:17:1:1:1:2:2:2:4:4:4:11:11:9:9:20:21:7:7:3:3:1:1:2:2:6:6:2:2:11:2:17:11:11:3:6:6:9:9:5:5:9:9:9:2:2:2:7:7:7:7:6:6:4:4:4:4:2:2:2:3:3:3:5:5:8:8:3:3:3:2:2:6:6:6:2:2:2:11:11:11:11:4:6:7:3:3:3:8:8:7:7:7:7:1:1:1:9:9:9:9:6:6:3:3:10:10:10:7:7:1:1:10:10:7:7:7:8:8:4:4:4:9:9:11:11:5:5:5:8:7:7:7:7:9:9:9:11:5:5:5:1:1:1:9:2:2:3:3:10:1:1:2:10:3:3:8:8:3:3:3:11:11:4:5:5:5:5:3:9:9:10:10:10:2:2:2:4:4:11:11:11:11:6:6:1:1:8:3:3:3:7:7:4:4:1:1:11:11:11:11:3:3:4:4:10:10:10:10:6:6:6:5:5:6:1:1:1:8:8:5:5:9:7:7:7:7:2:2:2:10:10:10:10:2:2:6:6:4:4:4:4:1:1:1:5:5:5:2:2:2:4:4:4:8:2:2:3:9:9:4:4:4:4:5:5:8:8:6:6:10:10:10:8:8:8:5:5:1:1:6:6:6:6:5:5:4:4:1:1:1:9:9:6:6:1:1:1:10:10:10:6:1:1:8:8:8:7:10:9:9:6:6:2:9:3:3:3:8:5:5:2:2:11:4:4:5:8:6:8:8:3:3:3:2:2:2:2:7:7:7:9:9:6:3:3:9:9:4:4:5:5:10:10:10:5:5:2:2:2:2:6:6:6:7:10:10:10:9:9:4:4:4:4:8:8:10:10:10:3:3:3:11:11:11:4:10:10:10:10:4:5:9:9:8:8:8:7:7:7:5:5:4:4:4:2:2:2:2:3:3:11:11:11:10:10:10:2:2:2:3:3:3:1:1:8:8:6:6:1:5:8:8:6:6:6:6:3:3:3:9:9:9:9:1:1:1:7:7:7:4:4:4:2:2:8:8:4:4:4:4:11:11:4:4:4:4:7:7:7:10:10:10:1:1:1:7:7:1:1:1:5:5:5:5:6:6:6:6:9:9:5:5:7:7:7:5:5:5:10:10:10:5:5:1:1:7:7:7:6:6:3:3:9:9:9:9:1:1:8:8:8:10:9:11:5:7:7:4:4:3:3:3:3:5:5:5:7:7:5:5:5:2:2:2:6:6:6:11:9:9:9:3:3:3:11:11:11:11:3:3:3:3:2:2:10:10:1:8:2:2:2:2:4:4:4:1:1:8:8:8:8:6:6:6:5:5:1:8:2:2:6:11:11:11:1:1:1:1:9:9:6:1:6:6:6:8:8:6:6:6:1:2:2:11:11:8:1:8:8:3:11:4:4:5:5:1:1:1:3:9:4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:1:1:1:9:9:9:19:11:11:11:4:4:4:19:8:5:12:5:5:5:2:1:4:4:4:4:10:9:17:9:9:6:6:10:10:12:10:3:3:3:20:9:9:9:1:1:20:1:4:4:4:11:11:12:8:9:9:7:17:7:3:3:5:3:3:19:6:6:6:11:11:11:12:3:3:2:2:2:21:10:10:6:6:6:6:2:2:2:17:2:8:8:12:10:10:10:4:9:9:9:7:7:8:20:1:4:4:4:2:12:10:10:5:8:8:8:8:7:17:7:5:5:19:20:3:3:3:4:12:4:4:6:6:7:10:11:11:19:21:2:1:1:10:10:12:6:6:6:17:6:10:10:10:10:19:21:3:3:3:3:8:8:8:2:2:12:6:6:7:7:7:5:5:8:5:5:1:1:17:3:3:1:8:8:12:4:4:9:9:9:4:4:4:6:6:2:1:1:7:7:2:2:12:5:5:2:2:2:17:9:9:5:5:10:10:10:5:5:4:4:4:12:3:3:3:3:20:9:9:6:6:5:7:22:1:1:9:9:17:5:5:5:12:7:7:6:6:7:7:8:8:7:7:7:7:8:8:8:12:7:7:7:8:8:1:1:1:5:17:5:5:3:3:2:2:1:2:12:2:2:2:1:1:8:19:9:9:6:6:8:8:20:8:7:6:3:11:2:17:10:10:10:10:1:14:1:1:6:6:6:14:6:7:7:2:2:14:7:7:1:1:2:14:2:2:2:7:7:14:8:8:6:5:5:14:8:8:8:10:10:14:10:8:8:10:10:14:8:8:8:8:3:14:3:3:3:1:1:14:1:6:6:5:5:14:2:2:4:4:4:14:11:11:7:7:4:14:4:4:4:6:6:14:7:10:10:10:10:14:1:1:11:11:11:14:11:7:7:7:8:14:8:8:8:1:1:14:1:1:3:3:9:14:9:9:9:4:4:14:3:3:5:5:5:14:5:2:2:4:4:14:7:7:2:2:11:14:11:11:5:5:5:14:2:1:1:2:2:14:2:6:6:9:9:13:9:6:6:10:10:13:10:9:9:7:7:13:6:6:6:6:2:13:2:2:4:4:4:13:5:5:5:4:4:13:9:11:11:6:6:13:6:5:1:1:1:13:8:11:2:2:7:13:7:7:3:3:3:13:5:5:5:5:4:13:4:10:10:3:3:13:2:2:5:3:3:13:11:11:11:9:9:13:8:8:8:8:11:13:11:1:1:1:1:13:9:9:6:6:6:13:2:2:3:3:3:13:4:4:5:5:5:13:4:5:5:11:11:13:6:6:9:9:9:13:10:10:3:3:3:13:9:9:11:9:1:13:1:4:4:4:3:13:7:3:4:3:3:13:5:5:5:8:8:8:2:2:2:2:7:2:2:4:4:11:11:11:10:10:10:1:1:5:5:6:6:6:4:4:4:5:5:5:10:10:3:3:7:7:7:7:10:10:1:1:1:8:6:6:6:7:2:2:2:3:3:3:4:3:3:9:9:4:1:1:3:3:9:9:9:9:8:8:5:2:2:7:7:2:2:9:9:2:2:2:7:7:1:1:1:2:8:8:8:6:6:11:11:1:1:1:1:10:10:8:8:10:1:4:4:4:9:9:9:1:1:1:10:10:10:10:2:2:2:2:1:1:3:3:3:5:5:5:7:7:8:8:8:6:6:6:5:4:4:6:6:9:9:8:8:8:7:7:7:7:2:2:6:6:6:11:11:11:3:3:3:6:6:3:3:9:9:9:3:7:7:3:3:3:3:4:4:4:4:9:10:10:11:11:11:6:6:4:3:3:3:4:4:4:4:1:1:9:9:9:9:5:6:6:6:4:4:4:7:7:7:4:4:4:4:11:5:5:6:6:8:8:8:8:6:7:9:9:10:10:2:2:2:5:5:2:11:11:11:10:10:10:5:5:3:1:1:1:6:6:8:8:5:5:5:10:10:10:7:7:7:2:2:11:11:4:4:1:1:1:3:3:2:8:8:5:5:10:5:5:11:11:11:3:3:1:1:9:9:6:6:5:5:5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>1,1&amp;300;2,301&amp;600;3,601&amp;750;4,751&amp;1050;5,1051&amp;1350;6,1351&amp;1500;7,1501&amp;1800;8,1801&amp;2100;9,2101&amp;2250;10,2251&amp;2550;11,2551&amp;2850;12,2851&amp;3000;13,3001&amp;3300;14,3301&amp;3600;15,3601&amp;3750;16,3751&amp;4050;17,4051&amp;4350;18,4351&amp;4500;19,4501&amp;4800;20,4801&amp;5100;21,5101&amp;5250</t>
+  </si>
+  <si>
+    <t>6:6:2:2:3:17:4:4:2:2:19:8:4:4:6:6:17:2:2:8:8:19:9:9:9:8:8:11:11:4:4:19:1:1:1:4:19:1:1:7:7:19:1:3:3:19:2:3:3:17:2:6:6:3:3:3:21:3:3:3:6:6:7:7:2:2:3:21:19:6:6:6:5:5:20:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:21:1:1:3:1:1:20:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:21:11:1:1:6:6:7:7:2:2:4:4:4:4:20:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:20:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:20:7:4:4:9:9:21:3:3:3:5:5:8:8:2:17:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:21:4:4:1:8:8:17:10:10:10:20:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:20:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:17:10:10:11:11:1:1:6:6:7:8:8:10:10:10:9:9:10:10:4:4:5:5:11:11:1:1:4:4:6:6:8:8:8:5:5:10:10:10:11:11:11:9:9:3:3:3:1:1:4:4:4:7:7:11:11:11:11:2:2:1:1:5:5:6:6:6:7:8:8:5:5:11:11:11:6:6:6:8:8:1:1:8:8:10:10:2:2:4:4:4:7:7:5:5:5:5:11:11:9:9:9:8:8:11:11:8:8:6:6:10:10:6:6:4:4:4:8:8:6:1:1:1:8:8:10:10:11:4:4:7:7:7:9:9:10:10:10:6:6:11:11:11:2:2:2:7:7:8:8:8:3:3:3:2:2:2:5:5:5:6:6:6:7:7:7:7:10:10:10:9:9:9:6:6:11:11:1:1:10:10:5:5:3:3:2:2:2:8:8:8:8:10:10:7:7:1:1:11:11:11:11:5:5:5:8:8:10:10:7:7:5:5:9:9:10:10:8:8:8:4:4:11:11:11:8:8:8:7:7:9:9:11:11:7:7:9:9:7:9:9:9:11:11:7:7:9:9:4:4:6:6:9:9:6:6:4:7:7:4:4:9:9:9:7:7:9:9:10:10:6:6:6:5:9:9:10:10:2:2:10:10:2:11:11:10:10:4:11:11:11:3:11:10:10:10:3:3:7:1:3:9:9:10:10:11:11:11:9:9:9:8:8:10:10:9:9:10:10:11:11:8:8:8:11:11:10:10:8:8:10:10:8:8:9:9:10:10:11:11:11:10:10:10:9:9:8:8:11:11:11:9:9:8:8:9:9:8:8:9:9:10:10:9:9:11:11:8:8:9:9:11:11:8:8:11:10:10:10:8:8:8:9:9:10:10:8:8:8:9:9:8:8:8:9:9:9:8:8:10:10:11:11:8:8:10:10:8:8:11:11:10:10:9:9:11:11:11:8:8:10:10:11:11:9:10:10:9:9:9:11:11:8:8:10:10:10:9:9:11:11:9:9:11:11:9:9:11:11:8:8:6:6:2:2:3:17:4:4:2:2:19:8:4:4:6:6:6:2:2:8:8:19:9:9:9:8:8:11:11:4:4:19:1:1:1:4:19:1:1:7:7:19:1:3:3:19:2:3:3:17:2:6:6:3:3:3:21:3:3:3:6:6:7:7:2:2:3:21:19:6:6:6:5:5:20:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:21:1:1:3:1:1:20:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:21:11:1:1:6:6:7:7:2:2:4:4:4:4:20:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:20:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:20:7:4:4:9:9:21:3:3:3:5:5:8:8:2:17:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:21:4:4:1:8:8:17:10:10:10:20:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:20:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:17:2:2:2:6:6:7:7:7:11:11:6:6:10:10:3:3:3:5:5:5:10:10:10:5:5:5:11:11:8:8:7:7:7:1:1:6:6:9:2:2:8:8:4:4:4:7:7:7:6:6:2:2:11:11:2:2:2:11:11:2:2:8:8:9:9:9:4:4:7:10:10:11:11:5:5:10:10:10:9:9:7:6:6:1:1:3:3:7:7:3:3:5:5:6:6:6:9:9:7:7:7:6:6:7:7:10:10:10:10:9:9:10:10:9:9:9:3:3:3:7:7:2:2:7:7:7:11:11:1:1:7:7:8:8:8:5:5:11:11:5:5:4:4:10:10:5:5:9:9:4:4:3:3:9:9:9:11:11:11:8:8:9:9:9:2:4:4:6:4:4:4:11:11:2:2:11:11:10:10:5:5:5:5:3:3:3:8:1:1:10:10:10:10:4:4:8:8:8:1:1:8:8:1:1:2:2:1:1:8:8:6:6:6:6:5:5:3:3:3:3:4:4:5:5:10:10:9:9:1:1:11:11:6:6:9:9:9:11:11:8:8:8:7:7:1:1:4:4:1:1:7:7:8:8:10:10:6:6:6:11:11:11:11:8:8:8:8:10:10:4:4:9:9:4:4:6:6:9:9:6:6:6:7:7:4:5:5:5:8:8:5:5:5:4:4:4:1:2:2:3:9:9:10:10:11:11:11:9:9:9:8:8:10:10:9:9:10:10:11:11:8:8:8:11:11:10:10:8:8:10:10:8:8:9:9:10:10:11:11:11:10:10:10:9:9:8:8:11:11:11:9:9:8:8:9:9:8:8:9:9:10:10:9:9:11:11:8:8:9:9:11:11:8:8:11:10:10:10:8:8:8:9:9:10:10:8:8:8:9:9:8:8:8:9:9:9:8:8:10:10:11:11:8:8:10:10:8:8:11:11:10:10:9:9:11:11:11:8:8:10:10:11:11:9:10:10:9:9:9:11:11:8:8:10:10:10:9:9:11:11:9:9:11:11:9:9:11:11:8:8:6:6:2:2:3:3:4:4:2:2:19:8:4:4:6:6:6:2:2:8:8:19:9:9:9:8:8:11:11:4:4:19:1:1:1:4:19:1:1:7:7:19:1:3:3:19:2:3:3:17:2:6:6:3:3:3:21:3:3:3:6:6:7:7:2:2:3:21:19:6:6:6:5:5:20:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:21:1:1:3:1:1:20:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:21:11:1:1:6:6:7:7:2:2:4:4:4:4:20:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:20:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:20:7:4:4:9:9:21:3:3:3:5:5:8:8:2:17:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:21:4:4:1:8:8:17:10:10:10:20:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:20:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:17:10:10:5:5:2:2:9:9:9:5:5:5:4:4:4:8:8:10:10:7:7:11:11:3:3:5:5:6:6:7:7:7:7:1:1:5:5:6:6:6:4:4:9:9:9:10:10:10:3:3:6:6:6:8:8:6:6:8:8:2:2:1:1:10:10:10:10:6:6:6:7:7:4:4:1:1:7:7:5:5:6:6:4:4:10:10:3:3:3:2:2:2:11:11:8:8:8:8:1:7:7:3:3:5:5:3:3:10:10:10:3:3:11:11:6:6:6:6:1:1:8:8:1:1:1:11:11:7:7:9:9:7:7:7:2:2:2:11:11:5:5:5:1:1:1:5:5:10:1:1:7:7:11:11:9:9:10:10:10:2:2:3:3:5:5:9:9:7:7:4:4:4:1:7:7:10:10:1:1:8:8:9:9:4:4:5:5:7:7:9:9:11:11:6:6:8:8:6:6:8:8:6:6:8:8:2:2:10:10:2:2:6:6:6:4:4:10:10:10:9:9:9:7:7:7:9:9:11:11:11:5:5:5:8:8:6:6:3:3:3:2:2:2:9:9:9:7:7:7:4:4:3:3:8:8:9:9:1:11:11:8:8:11:11:11:5:5:5:5:11:11:11:10:10:9:9:9:8:8:2:2:4:4:2:2:5:9:4:4:4:8:8:4:4:2:2:4:4:4:10:9:9:10:10:11:11:11:9:9:9:8:8:10:10:9:9:10:10:11:11:8:8:8:11:11:10:10:8:8:10:10:8:8:9:9:10:10:11:11:11:10:10:10:9:9:8:8:11:11:11:9:9:8:8:9:9:8:8:9:9:10:10:9:9:11:11:8:8:9:9:11:11:8:8:11:10:10:10:8:8:8:9:9:10:10:8:8:8:9:9:8:8:8:9:9:9:8:8:10:10:11:11:8:8:10:10:8:8:11:11:10:10:9:9:11:11:11:8:8:10:10:11:11:9:10:10:9:9:9:11:11:8:8:10:10:10:9:9:11:11:9:9:11:11:9:9:11:11:8:8:6:6:2:2:3:3:4:4:2:2:8:8:4:4:6:6:6:2:2:8:8:19:9:9:9:8:8:11:11:4:4:19:1:1:1:4:19:1:1:7:7:19:1:3:3:19:2:3:3:17:2:6:6:3:3:3:21:3:3:3:6:6:7:7:2:2:3:21:19:6:6:6:5:5:5:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:6:1:1:3:1:1:20:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:21:11:1:1:6:6:7:7:2:2:4:4:4:4:20:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:20:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:20:7:4:4:9:9:21:3:3:3:5:5:8:8:2:17:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:21:4:4:1:8:8:17:10:10:10:20:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:20:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:17:4:4:4:10:10:1:1:9:9:7:7:7:5:5:6:6:4:4:7:7:10:10:5:5:4:4:10:10:10:9:9:9:11:11:9:9:7:7:9:9:9:8:8:6:6:6:6:7:7:6:6:7:7:7:1:1:1:2:2:1:1:8:8:8:2:2:6:6:6:1:1:3:3:1:1:3:3:3:3:10:10:11:11:7:7:11:11:9:9:4:4:4:10:10:10:10:9:9:4:4:5:5:2:2:5:5:2:2:4:4:1:1:1:6:6:7:7:8:8:8:5:5:5:6:6:6:4:4:8:8:6:6:6:9:9:9:10:10:5:7:7:8:8:8:2:2:8:8:4:4:8:8:8:5:5:7:7:2:2:2:6:6:7:7:3:3:6:6:5:5:9:9:10:10:10:5:5:5:6:6:4:4:1:1:10:10:11:11:7:7:3:3:5:5:10:10:10:8:8:1:1:7:7:10:10:8:8:6:2:2:3:3:5:5:11:11:3:3:4:4:11:11:7:7:2:2:2:8:8:11:11:2:2:2:9:9:9:1:1:11:11:5:11:11:11:9:9:11:11:9:11:11:8:8:10:10:10:10:6:6:6:11:11:8:8:4:4:2:2:9:9:8:8:5:5:7:9:9:9:1:6:4:4:2:2:4:4:5:5:7:7:3:3:5:5:3:3:10:3:3:11:11:10:10:8:8:8:8:11:11:10:10:11:11:9:9:8:8:11:11:11:8:8:9:9:8:8:11:11:11:8:8:11:11:10:10:9:9:9:8:8:10:10:10:9:9:11:11:8:8:10:10:10:9:9:10:10:9:9:8:8:9:10:10:10:10:8:8:10:10:10:9:9:9:10:10:10:11:11:8:8:8:8:9:9:9:9:11:11:11:10:10:8:8:10:10:10:8:8:9:9:9:8:8:10:10:9:9:8:8:11:11:10:10:9:9:11:11:9:9:9:11:11:8:8:9:9:8:8:9:9:10:10:8:8:11:11:11:9:9:9:11:11:9:9:11:11:11:8:8:6:6:2:2:3:3:4:4:2:2:8:8:4:4:6:6:6:2:2:8:8:19:9:9:9:8:8:11:11:4:4:19:1:1:1:4:19:1:1:7:7:19:1:3:3:19:2:3:3:17:2:6:6:3:3:3:21:3:3:3:6:6:7:7:2:2:3:21:19:6:6:6:5:5:5:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:6:1:1:3:1:1:20:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:21:11:1:1:6:6:7:7:2:2:4:4:4:4:20:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:20:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:20:7:4:4:9:9:21:3:3:3:5:5:8:8:2:17:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:21:4:4:1:8:8:17:10:10:10:20:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:20:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:17:2:2:11:11:5:5:1:1:1:11:11:11:4:4:4:8:8:4:4:10:10:7:7:5:5:9:9:9:1:1:2:2:3:3:10:10:10:9:9:6:6:8:8:11:10:10:1:1:9:9:1:1:10:2:2:3:3:3:11:11:5:5:9:9:5:5:10:10:10:6:8:8:5:5:5:8:8:2:2:8:8:10:10:9:9:3:3:3:3:7:7:6:6:9:9:7:7:7:4:4:5:5:1:7:7:7:6:6:5:5:5:11:11:11:6:6:9:9:7:7:2:2:8:9:3:3:5:5:5:5:6:6:6:2:2:4:4:11:11:8:8:2:2:2:10:10:9:9:1:1:4:4:5:5:7:7:7:7:3:3:10:10:1:1:8:8:8:2:2:4:4:4:7:7:7:9:9:9:9:7:7:2:2:11:11:11:11:9:9:8:8:6:6:11:11:4:4:8:8:6:8:8:8:5:3:3:11:11:11:5:5:4:4:9:9:9:10:10:7:1:1:1:1:8:8:11:11:5:5:3:3:3:10:10:4:4:4:4:10:10:6:6:7:7:2:2:2:8:8:7:7:6:6:6:10:10:6:10:10:6:6:4:4:3:3:6:6:6:6:1:1:4:4:7:7:7:7:8:8:8:1:5:5:9:5:2:2:4:4:11:10:10:9:9:6:6:7:2:10:6:11:11:9:9:8:8:8:10:10:11:11:8:8:8:9:9:8:8:11:11:8:10:10:8:8:8:10:10:10:11:11:8:8:8:8:10:10:9:9:8:8:9:9:10:10:10:9:9:9:10:10:9:9:9:11:11:11:10:10:11:11:10:10:9:9:9:11:11:11:8:8:8:11:11:8:8:8:9:9:10:10:9:9:9:11:11:9:9:8:8:11:11:9:9:9:11:11:9:9:10:10:10:8:8:8:8:11:11:8:8:9:9:8:8:11:11:10:10:10:8:8:8:8:9:9:8:8:9:9:10:10:10:10:11:11:9:9:10:10:11:11:11:11:9:9:10:10:11:9:10:6:6:2:2:3:3:4:4:2:2:8:8:4:4:6:6:6:2:2:8:8:19:9:9:9:8:8:11:11:4:4:19:1:1:1:4:19:1:1:7:7:19:1:3:3:19:2:3:3:17:2:6:6:3:3:3:21:3:3:3:6:6:7:7:2:2:3:21:19:6:6:6:5:5:5:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:6:1:1:3:1:1:20:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:21:11:1:1:6:6:7:7:2:2:4:4:4:4:20:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:20:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:20:7:4:4:9:9:21:3:3:3:5:5:8:8:2:17:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:21:4:4:1:8:8:17:10:10:10:20:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:20:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:17:11:11:11:7:7:8:8:8:7:7:7:8:8:9:9:10:10:2:2:6:6:6:10:10:7:7:1:1:9:9:1:1:1:6:6:6:8:8:4:4:4:11:11:2:2:7:7:4:4:4:11:11:11:8:3:3:2:2:9:9:10:10:10:10:8:8:8:5:5:5:7:7:7:7:6:6:9:3:3:3:4:4:11:11:11:9:9:4:4:8:8:8:8:2:2:11:11:6:6:6:7:7:10:10:8:8:9:9:7:7:8:8:3:3:6:6:6:11:11:11:11:1:1:1:8:8:1:1:1:7:7:10:10:8:8:8:10:10:10:9:9:9:5:5:1:9:9:4:4:2:2:11:11:10:10:2:2:9:9:10:10:2:2:6:6:4:4:10:10:4:4:2:2:2:11:11:11:11:3:3:3:6:6:5:5:5:10:10:10:10:3:3:9:5:5:6:6:6:9:9:10:4:4:2:2:7:7:9:9:6:6:7:7:5:5:2:2:2:1:1:1:7:7:9:9:1:1:5:5:5:9:9:6:6:6:9:9:5:5:5:7:7:5:5:5:2:2:9:3:3:10:10:3:3:3:5:5:1:1:8:8:7:7:6:6:11:11:10:10:1:1:7:7:5:4:4:5:5:5:4:4:4:6:6:5:5:3:3:4:4:4:5:8:8:3:8:8:4:4:2:8:8:11:11:10:10:9:9:8:8:8:8:10:10:9:9:11:11:11:8:8:10:10:10:8:8:10:10:11:11:11:11:10:10:9:9:11:11:11:11:8:8:9:9:8:8:10:10:8:8:9:9:11:11:10:10:10:8:8:9:9:11:11:9:9:10:10:9:9:9:8:8:8:9:9:11:11:11:10:10:11:11:9:9:8:8:11:11:11:9:9:10:10:9:9:11:11:10:10:11:11:8:8:11:11:11:8:8:10:10:8:8:8:8:9:9:8:8:10:10:8:8:10:8:8:10:10:9:9:9:10:10:10:8:8:8:9:9:9:11:11:9:9:10:9:9:9:11:9:9:6:6:2:2:3:3:4:4:2:2:8:8:4:4:6:6:6:2:2:8:8:19:9:9:9:8:8:11:11:4:4:19:1:1:1:4:19:1:1:7:7:19:1:3:3:2:2:3:3:17:2:6:6:3:3:3:21:3:3:3:6:6:7:7:2:2:3:21:6:6:6:6:5:5:5:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:6:1:1:3:1:1:1:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:11:11:1:1:6:6:7:7:2:2:4:4:4:4:20:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:20:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:20:7:4:4:9:9:21:3:3:3:5:5:8:8:2:17:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:21:4:4:1:8:8:17:10:10:10:20:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:20:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:6:2:2:11:11:5:5:1:1:1:11:11:11:4:4:4:8:8:4:4:10:10:7:7:5:5:9:9:9:1:1:2:2:3:3:10:10:10:9:9:6:6:8:8:11:10:10:1:1:9:9:1:1:10:2:2:3:3:3:11:11:5:5:9:9:5:5:10:10:10:6:8:8:5:5:5:8:8:2:2:8:8:10:10:9:9:3:3:3:3:7:7:6:6:9:9:7:7:7:4:4:5:5:1:7:7:7:6:6:5:5:5:11:11:11:6:6:9:9:7:7:2:2:8:9:3:3:5:5:5:5:6:6:6:2:2:4:4:11:11:8:8:2:2:2:10:10:9:9:1:1:4:4:5:5:7:7:7:7:3:3:10:10:1:1:8:8:8:2:2:4:4:4:7:7:7:9:9:9:9:7:7:2:2:11:11:11:11:9:9:8:8:6:6:11:11:4:4:8:8:6:8:8:8:5:3:3:11:11:11:5:5:4:4:9:9:9:10:10:7:1:1:1:1:8:8:11:11:5:5:3:3:3:10:10:4:4:4:4:10:10:6:6:7:7:2:2:2:8:8:7:7:6:6:6:10:10:6:10:10:6:6:4:4:3:3:6:6:6:6:1:1:4:4:7:7:7:7:8:8:8:1:5:5:9:5:2:2:4:4:11:10:10:9:9:6:6:7:2:10:6:11:11:11:11:9:9:10:10:10:8:8:11:11:10:10:9:9:11:11:10:10:10:9:9:11:11:10:10:8:8:9:9:8:8:9:9:10:10:8:8:9:9:9:11:11:9:9:9:9:10:10:9:9:8:8:10:10:9:9:8:8:8:11:11:10:10:8:8:10:10:8:8:10:10:8:8:8:10:10:8:8:10:10:11:11:9:9:11:11:10:10:9:9:8:8:11:11:8:8:8:9:9:8:8:8:9:9:11:11:9:9:9:8:8:11:11:11:10:10:10:11:11:11:11:8:8:11:9:9:10:10:8:8:11:11:9:9:11:11:8:8:8:9:9:9:9:11:10:10:8:</t>
+  </si>
+  <si>
+    <t>9:9:10:7:7:7:11:11:6:6:12:10:10:10:20:21:6:6:6:2:2:12:2:2:10:10:20:2:2:9:9:5:12:5:5:10:10:10:12:2:10:11:11:12:2:2:9:9:5:17:5:5:20:3:3:12:6:6:3:3:3:21:5:5:4:4:12:4:7:7:6:20:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:12:6:6:10:10:8:8:17:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:21:1:1:5:5:9:12:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:12:8:2:2:2:17:3:4:4:4:19:2:2:3:3:12:10:10:10:8:8:1:1:12:7:7:8:8:4:12:11:11:7:7:12:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:19:8:8:8:17:6:6:8:8:12:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:12:5:4:4:4:1:1:21:7:7:7:12:4:4:8:8:17:10:1:1:20:2:2:4:9:9:9:19:1:8:11:17:11:11:3:13:3:8:11:13:11:10:10:13:11:9:9:13:6:6:6:13:9:11:11:13:9:9:9:13:7:7:7:13:6:6:8:13:8:5:5:13:11:4:4:13:4:7:7:13:9:9:2:13:2:6:6:13:6:10:10:13:10:9:9:13:1:1:8:13:8:8:10:13:10:10:10:13:2:2:9:13:9:9:6:13:6:11:11:14:7:7:9:14:9:9:3:14:3:1:1:14:4:4:1:14:4:11:11:14:10:10:11:14:11:6:6:14:9:9:9:14:10:10:10:14:10:11:11:14:9:9:11:14:11:8:8:14:8:7:7:14:11:11:1:14:1:11:10:14:10:8:8:14:3:3:7:14:7:1:1:14:10:10:7:14:7:6:6:14:6:11:11:14:10:10:2:14:2:2:2:14:8:8:8:14:2:5:11:14:11:7:7:14:10:10:4:14:4:1:1:14:9:9:3:14:3:8:8:14:3:3:11:14:11:11:3:14:3:1:1:14:5:5:3:14:3:3:5:14:5:2:2:14:2:2:5:14:5:7:7:14:10:10:10:14:2:2:2:14:4:4:4:14:4:11:11:14:5:5:5:14:6:6:5:14:5:10:10:14:7:7:7:14:5:4:4:14:8:4:4:14:9:9:10:14:10:9:9:11:11:6:6:10:10:8:8:9:8:11:4:6:7:6:6:7:7:6:6:7:7:5:5:5:6:6:5:5:7:7:7:5:5:6:6:7:7:5:5:7:6:6:6:5:5:7:7:6:6:6:5:5:6:6:6:6:7:6:6:7:7:7:6:7:7:5:5:5:6:6:6:7:7:5:5:7:7:6:5:5:7:7:7:7:6:6:5:5:6:6:6:7:7:7:6:6:5:5:7:7:6:6:5:5:7:7:5:5:6:6:5:5:5:6:6:7:7:6:6:5:5:5:7:7:5:5:5:7:7:7:6:6:7:7:7:5:5:6:6:5:5:5:6:6:5:5:7:7:6:6:5:5:5:5:6:6:5:5:7:7:7:7:9:9:10:7:7:7:11:11:6:6:12:10:10:10:20:21:6:6:6:2:2:12:2:2:10:10:20:2:2:9:9:5:12:5:5:10:10:10:12:2:10:11:11:12:2:2:9:9:5:17:5:5:20:3:3:12:6:6:3:3:3:21:5:5:4:4:12:4:7:7:6:20:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:12:6:6:10:10:8:8:17:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:21:1:1:5:5:9:12:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:12:8:2:2:2:17:3:4:4:4:19:2:2:3:3:12:10:10:10:8:8:1:1:12:7:7:8:8:4:12:11:11:7:7:12:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:19:8:8:8:17:6:6:8:8:12:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:12:5:4:4:4:1:1:21:7:7:7:12:4:4:8:8:17:10:1:1:20:2:2:4:9:9:9:19:1:8:11:17:3:3:3:13:10:10:3:13:3:9:9:13:9:8:8:13:1:1:1:13:2:2:7:13:7:7:1:13:1:4:4:13:2:2:2:13:2:4:4:13:11:11:5:13:5:5:4:13:4:6:6:13:3:3:8:13:8:5:5:13:1:1:2:13:2:7:7:13:11:11:4:13:4:7:7:13:11:11:6:13:6:9:9:13:8:8:5:13:5:7:7:13:10:10:9:13:9:5:5:13:5:8:8:13:11:11:11:13:11:6:6:14:10:10:3:14:3:6:6:14:6:5:5:14:5:6:6:14:1:1:5:14:5:2:2:14:2:1:1:14:5:5:7:14:7:7:9:14:9:11:11:14:8:8:10:14:10:3:3:14:3:9:9:14:9:10:10:14:6:6:1:14:1:5:5:14:9:9:9:14:8:8:10:14:10:10:11:14:11:2:2:14:4:4:3:14:3:1:1:14:4:4:9:14:9:10:10:14:10:7:7:14:4:4:9:14:9:9:2:14:2:4:4:14:4:4:7:14:9:9:7:14:7:6:6:14:4:10:10:14:11:11:8:14:8:8:2:14:2:3:3:14:6:6:10:14:10:11:11:14:10:10:10:14:8:8:3:14:3:8:8:14:8:7:7:14:6:6:11:14:11:10:10:14:11:11:1:1:3:3:2:11:11:6:11:11:11:5:7:1:7:6:6:7:7:6:6:7:7:5:5:5:6:6:5:5:7:7:7:5:5:6:6:7:7:5:5:7:6:6:6:5:5:7:7:6:6:6:5:5:6:6:6:6:7:6:6:7:7:7:6:7:7:5:5:5:6:6:6:7:7:5:5:7:7:6:5:5:7:7:7:7:6:6:5:5:6:6:6:7:7:7:6:6:5:5:7:7:6:6:5:5:7:7:5:5:6:6:5:5:5:6:6:7:7:6:6:5:5:5:7:7:5:5:5:7:7:7:6:6:7:7:7:5:5:6:6:5:5:5:6:6:5:5:7:7:6:6:5:5:5:5:6:6:5:5:7:7:7:7:9:9:10:7:7:7:11:11:6:6:12:10:10:10:20:2:6:6:6:2:2:12:2:2:10:10:20:2:2:9:9:5:12:5:5:10:10:10:12:2:10:11:11:12:2:2:9:9:5:17:5:5:20:3:3:12:6:6:3:3:3:21:5:5:4:4:12:4:7:7:6:20:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:12:6:6:10:10:8:8:17:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:21:1:1:5:5:9:12:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:12:8:2:2:2:17:3:4:4:4:19:2:2:3:3:12:10:10:10:8:8:1:1:12:7:7:8:8:4:12:11:11:7:7:12:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:19:8:8:8:17:6:6:8:8:12:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:12:5:4:4:4:1:1:21:7:7:7:12:4:4:8:8:17:10:1:1:20:2:2:4:9:9:9:19:1:8:11:17:9:9:9:13:5:5:5:13:5:6:6:13:9:10:10:13:3:1:1:13:1:3:3:13:9:9:9:13:9:7:7:13:2:2:7:13:7:11:11:13:11:1:1:13:1:3:3:13:3:2:2:13:2:2:4:13:4:11:11:13:11:2:2:13:5:5:8:13:8:8:9:13:9:6:6:13:11:11:4:13:4:8:4:13:4:4:10:13:10:4:4:13:3:3:5:13:5:1:1:13:5:5:5:13:7:7:9:13:9:10:10:13:11:11:9:13:9:9:6:14:6:6:6:14:10:10:8:14:8:8:2:14:2:2:10:14:10:7:7:14:9:5:5:14:5:8:11:14:11:8:8:14:8:1:1:14:1:3:3:14:2:2:2:14:11:11:8:14:8:8:3:14:3:4:4:14:7:7:1:14:1:9:9:14:3:7:7:14:7:1:1:14:6:6:6:14:11:11:10:14:10:8:8:14:8:5:9:14:9:9:1:14:1:8:8:14:10:10:2:14:2:10:10:14:4:4:6:14:6:11:11:14:11:3:3:14:4:4:2:14:2:10:10:14:10:11:11:14:3:3:5:14:5:10:10:14:4:4:11:14:11:6:6:14:7:6:6:14:6:6:3:14:3:7:10:14:10:5:5:14:6:3:7:14:7:10:10:11:11:2:2:1:4:4:9:8:5:7:7:7:7:6:6:7:7:6:6:7:7:5:5:5:6:6:5:5:7:7:7:5:5:6:6:7:7:5:5:7:6:6:6:5:5:7:7:6:6:6:5:5:6:6:6:6:7:6:6:7:7:7:6:7:7:5:5:5:6:6:6:7:7:5:5:7:7:6:5:5:7:7:7:7:6:6:5:5:6:6:6:7:7:7:6:6:5:5:7:7:6:6:5:5:7:7:5:5:6:6:5:5:5:6:6:7:7:6:6:5:5:5:7:7:5:5:5:7:7:7:6:6:7:7:7:5:5:6:6:5:5:5:6:6:5:5:7:7:6:6:5:5:5:5:6:6:5:5:7:7:7:7:9:9:10:7:7:7:11:11:6:6:12:10:10:10:20:2:6:6:6:2:2:12:2:2:10:10:20:2:2:9:9:5:12:5:5:10:10:10:12:2:10:11:11:12:2:2:9:9:5:17:5:5:20:3:3:12:6:6:3:3:3:21:5:5:4:4:12:4:7:7:6:20:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:12:6:6:10:10:8:8:17:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:21:1:1:5:5:9:12:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:12:8:2:2:2:17:3:4:4:4:19:2:2:3:3:12:10:10:10:8:8:1:1:12:7:7:8:8:4:4:11:11:7:7:12:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:19:8:8:8:17:6:6:8:8:12:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:12:5:4:4:4:1:1:21:7:7:7:12:4:4:8:8:10:10:1:1:20:2:2:4:9:9:9:19:1:8:11:17:7:7:9:13:9:9:11:13:11:10:10:13:10:7:7:13:7:8:6:13:6:2:2:13:1:1:10:13:4:4:8:13:8:8:1:13:1:10:10:13:2:9:9:13:10:10:10:13:10:9:9:13:9:1:1:13:1:6:6:13:7:7:7:13:6:6:9:13:9:9:11:13:11:11:8:13:8:5:5:13:6:6:1:13:1:11:11:13:11:5:5:13:10:10:4:13:4:1:1:13:9:9:8:13:8:2:2:13:11:11:9:13:9:9:3:13:3:9:9:13:10:10:9:13:9:9:3:13:3:3:6:14:6:6:2:14:2:5:5:14:5:10:10:14:4:4:8:14:8:4:4:14:7:7:7:14:8:8:1:14:1:2:2:14:3:3:11:14:11:3:3:14:10:10:11:14:8:8:8:14:6:6:4:14:4:1:1:14:2:7:7:14:1:1:1:14:3:3:3:14:11:11:11:14:4:2:2:14:8:8:3:14:3:2:2:14:10:10:3:14:3:2:2:14:8:8:7:14:7:4:4:14:10:10:11:14:11:11:4:14:4:3:3:14:3:10:10:14:6:6:5:14:5:2:2:14:2:7:7:14:11:11:6:14:6:7:7:14:3:6:5:14:5:4:7:14:9:5:5:14:6:6:5:14:5:4:4:11:11:11:4:11:5:5:5:8:5:5:2:10:5:5:7:7:5:5:7:7:7:6:6:7:7:6:6:6:7:7:5:5:7:7:5:6:6:7:7:5:5:6:6:7:7:6:6:5:5:6:6:5:5:7:7:5:7:7:5:5:6:7:6:6:7:7:6:5:5:6:6:5:5:5:7:6:6:7:7:6:6:5:6:6:5:5:5:7:7:7:5:5:7:7:6:6:7:7:7:6:6:6:5:5:7:7:5:5:6:6:6:7:7:5:5:7:7:5:5:7:7:7:5:5:7:7:7:7:6:6:6:5:5:6:6:6:5:5:5:6:6:5:5:6:6:7:7:6:6:6:5:5:6:6:5:5:6:6:7:7:5:5:9:9:10:7:7:7:11:11:6:6:12:10:10:10:20:2:6:6:6:2:2:12:2:2:10:10:20:2:2:9:9:5:12:5:5:10:10:10:2:2:10:11:11:12:2:2:9:9:5:17:5:5:20:3:3:12:6:6:3:3:3:21:5:5:4:4:12:4:7:7:6:20:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:9:6:6:10:10:8:8:17:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:21:1:1:5:5:9:12:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:12:8:2:2:2:17:3:4:4:4:19:2:2:3:3:12:10:10:10:8:8:1:1:12:7:7:8:8:4:4:11:11:7:7:12:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:19:8:8:8:17:6:6:8:8:12:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:12:5:4:4:4:1:1:21:7:7:7:12:4:4:8:8:10:10:1:1:20:2:2:4:9:9:9:19:1:8:11:17:3:3:7:13:7:7:10:13:10:10:10:13:1:1:1:13:10:10:10:13:8:8:9:13:9:2:2:13:1:1:3:13:3:1:1:13:1:8:8:13:8:8:4:13:4:11:11:13:5:5:5:13:3:3:3:13:9:9:10:13:10:10:3:13:3:4:2:13:9:9:7:13:6:6:6:13:9:8:8:13:1:2:2:13:2:5:5:13:5:7:7:13:7:2:2:13:4:4:4:13:4:5:5:13:5:11:11:13:10:10:3:13:3:3:3:13:7:7:7:13:5:5:6:13:6:6:8:13:9:9:10:13:5:5:5:13:5:8:8:13:11:11:3:14:3:10:10:14:11:11:8:14:8:8:7:14:7:10:10:14:6:6:2:14:2:4:4:14:11:11:7:14:7:8:8:14:3:3:6:14:6:6:7:14:7:7:4:14:4:10:10:14:10:3:3:14:4:4:2:14:2:1:1:14:11:11:9:14:9:4:4:14:6:6:5:14:5:2:2:14:5:5:5:14:1:1:8:14:8:9:9:14:9:11:11:14:11:2:2:14:1:1:9:14:9:4:4:14:10:10:11:14:11:2:2:14:2:2:1:14:1:11:11:14:7:7:10:14:10:8:8:14:6:6:9:14:9:1:9:14:9:6:6:9:9:4:4:11:11:6:6:7:11:11:3:4:11:11:6:10:5:5:5:6:6:5:5:6:6:7:7:7:5:5:5:7:7:5:5:6:6:7:5:5:6:6:5:5:6:6:7:7:6:6:6:5:5:7:7:5:5:6:6:6:7:7:5:5:7:7:5:5:7:7:6:6:7:7:7:7:6:6:6:5:5:5:6:6:7:7:6:6:6:5:5:7:7:5:5:6:6:7:5:5:7:7:5:5:6:6:6:5:6:6:7:5:5:5:7:7:7:6:6:7:7:6:6:7:7:7:7:6:6:5:5:6:6:6:5:5:5:6:6:7:7:6:6:6:5:5:5:7:7:5:5:7:6:6:7:7:6:7:7:5:5:7:7:5:7:7:9:9:10:7:7:7:11:11:6:6:12:10:10:10:20:2:6:6:6:2:2:12:2:2:10:10:20:2:2:9:9:5:12:5:5:10:10:10:2:2:10:11:11:2:2:2:9:9:5:17:5:5:20:3:3:12:6:6:3:3:3:21:5:5:4:4:12:4:7:7:6:20:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:9:6:6:10:10:8:8:17:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:21:1:1:5:5:9:12:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:12:8:2:2:2:17:3:4:4:4:19:2:2:3:3:12:10:10:10:8:8:1:1:12:7:7:8:8:4:4:11:11:7:7:12:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:19:8:8:8:17:6:6:8:8:12:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:12:5:4:4:4:1:1:21:7:7:7:12:4:4:8:8:10:10:1:1:20:2:2:4:9:9:9:19:1:8:11:17:6:6:10:13:10:10:4:13:4:11:11:13:3:3:7:13:7:7:10:13:10:6:6:13:6:9:9:13:10:10:4:13:4:4:4:13:11:11:8:13:8:1:1:13:8:8:5:13:9:9:1:13:1:2:2:13:2:8:8:13:9:9:5:13:4:4:9:13:9:9:11:13:11:11:11:13:10:10:10:13:10:8:8:13:9:9:9:13:10:10:2:13:2:2:11:13:11:11:10:13:10:6:6:13:7:7:1:13:1:3:3:13:3:6:6:13:4:4:7:13:7:7:3:13:3:3:1:14:1:3:3:14:3:2:2:14:5:5:7:14:7:3:3:14:10:10:10:14:7:7:2:14:2:5:5:14:5:11:11:14:6:6:6:14:9:9:4:14:11:11:11:14:1:1:6:14:6:2:2:14:6:6:4:14:4:2:2:14:2:1:1:14:1:5:5:14:11:11:11:14:8:8:10:14:10:5:5:14:8:8:10:14:10:10:10:14:8:8:4:14:4:3:3:14:3:4:4:14:8:8:5:14:5:2:2:14:9:9:4:14:4:3:3:14:5:5:5:14:1:1:7:14:7:11:11:14:6:6:7:14:7:7:1:14:1:11:11:14:2:2:9:14:9:7:7:4:3:3:1:7:7:9:9:6:6:11:11:8:8:5:5:5:5:9:9:8:2:8:9:10:6:6:5:5:6:6:6:7:7:6:6:7:7:7:7:6:6:6:6:5:5:7:7:7:5:5:6:6:5:5:5:6:6:6:5:5:7:7:5:5:6:6:7:7:6:6:5:5:5:6:6:7:7:7:7:6:6:6:5:5:6:6:6:7:7:6:6:5:5:5:7:7:5:5:7:7:7:6:6:6:6:7:7:5:5:7:7:6:6:5:5:7:7:6:6:7:7:6:6:6:5:5:7:7:5:5:7:7:5:5:5:7:7:5:6:6:7:7:7:5:5:7:7:5:5:6:6:7:7:5:5:6:6:7:7:7:5:5:5:7:7:6:6:6:5:5:5:5:5:5:9:9:10:7:7:7:11:11:6:6:8:10:10:10:20:2:6:6:6:2:2:12:2:2:10:10:20:2:2:9:9:5:12:5:5:10:10:10:2:2:10:11:11:2:2:2:9:9:5:17:5:5:20:3:3:3:6:6:3:3:3:21:5:5:4:4:7:4:7:7:6:6:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:9:6:6:10:10:8:8:17:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:3:1:1:5:5:9:9:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:12:8:2:2:2:17:3:4:4:4:19:2:2:3:3:3:10:10:10:8:8:1:1:12:7:7:8:8:4:4:11:11:7:7:12:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:19:8:8:8:17:6:6:8:8:3:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:5:5:4:4:4:1:1:21:7:7:7:12:4:4:8:8:10:10:1:1:20:2:2:4:9:9:9:19:1:8:11:11:3:3:7:7:7:7:10:13:10:10:10:13:1:1:1:13:10:10:10:13:8:8:9:13:9:2:2:1:1:1:3:3:3:1:1:13:1:8:8:13:8:8:4:13:4:11:11:13:5:5:5:13:3:3:3:9:9:9:10:13:10:10:3:13:3:4:2:13:9:9:7:7:6:6:6:8:9:8:8:13:1:2:2:13:2:5:5:13:5:7:7:13:7:2:2:13:4:4:4:13:4:5:5:13:5:11:11:13:10:10:3:13:3:3:3:13:7:7:7:13:5:5:6:13:6:6:8:13:9:9:10:13:5:5:5:13:5:8:8:13:11:11:3:14:3:10:10:14:11:11:8:14:8:8:7:14:7:10:10:14:6:6:2:14:2:4:4:14:11:11:7:7:7:8:8:14:3:3:6:14:6:6:7:14:7:7:4:14:4:10:10:14:10:3:3:14:4:4:2:14:2:1:1:14:11:11:9:14:9:4:4:14:6:6:5:14:5:2:2:14:5:5:5:14:1:1:8:14:8:9:9:14:9:11:11:14:11:2:2:14:1:1:9:14:9:4:4:14:10:10:11:14:11:2:2:14:2:2:1:14:1:11:11:14:7:7:10:14:10:8:8:14:6:6:9:14:9:1:9:14:9:6:6:9:9:4:4:11:11:6:6:7:11:11:3:4:11:11:6:10:7:7:5:5:5:7:7:5:5:6:6:5:5:7:7:5:5:5:7:7:5:5:7:7:7:6:6:7:7:6:6:7:7:6:6:7:7:7:5:5:6:6:6:5:5:7:7:7:5:5:7:7:6:6:5:5:7:7:7:6:6:5:5:6:6:6:7:7:5:5:5:5:7:7:5:5:5:6:6:7:7:6:6:5:5:5:7:7:6:6:7:7:5:7:7:6:6:6:5:5:5:6:6:5:5:6:6:6:7:7:5:5:6:6:5:5:6:6:6:7:7:5:5:7:7:6:6:5:5:6:6:6:5:5:5:6:6:7:7:6:6:5:6:6:7:7:7:6:7:6:</t>
+  </si>
+  <si>
+    <t>8:8:8:5:5:2:2:9:9:11:12:11:6:6:6:4:4:8:8:9:11:12:11:5:5:5:20:19:6:10:10:10:12:8:8:8:20:1:1:12:9:9:8:12:8:2:2:6:6:17:1:1:3:3:9:12:9:3:3:3:3:20:6:4:4:5:12:6:6:4:4:21:19:3:3:3:6:12:6:2:2:21:2:2:2:3:3:3:12:3:9:9:20:9:7:7:17:3:3:3:12:3:11:11:4:7:7:21:1:1:8:12:8:1:1:7:7:22:9:4:1:1:12:6:6:5:5:20:8:8:2:2:2:12:5:10:10:5:5:19:9:9:1:1:12:4:4:10:10:17:10:6:6:5:5:9:12:9:9:9:19:8:8:11:11:7:7:12:7:10:10:1:19:10:7:7:5:5:12:10:10:5:5:17:7:6:6:6:6:12:4:4:4:1:1:19:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:21:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:12:3:3:3:3:11:11:12:11:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:21:10:8:12:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:19:2:2:1:12:8:8:7:20:6:8:7:8:17:11:11:2:13:5:4:4:13:9:9:7:13:7:7:3:13:3:10:10:13:6:6:10:13:10:10:1:13:1:1:5:13:5:4:4:13:4:4:10:13:10:10:8:13:8:6:5:13:5:5:3:13:3:3:10:13:10:10:10:13:1:1:3:13:3:3:4:13:4:5:5:13:10:10:9:13:9:3:3:13:9:9:5:13:5:5:6:13:6:8:8:13:5:5:11:13:9:9:9:14:4:10:10:14:2:2:1:14:1:6:6:14:4:11:11:14:4:4:1:14:1:3:3:14:11:11:4:14:4:4:4:14:8:8:7:14:7:5:5:14:5:5:2:14:11:11:6:14:6:8:8:14:5:5:2:14:2:2:7:14:7:2:2:14:8:8:3:14:3:4:4:14:10:10:10:14:9:9:7:14:7:2:2:14:8:8:8:14:8:7:7:14:8:8:8:14:9:9:7:14:7:9:9:14:9:7:7:14:6:6:10:14:10:3:10:14:10:11:11:14:9:9:3:14:3:3:11:14:11:6:6:14:6:2:2:14:3:9:9:14:11:11:1:14:1:1:7:14:7:7:1:14:1:2:2:14:11:11:5:14:4:4:10:14:10:6:6:14:11:11:11:14:9:9:9:14:7:1:1:14:11:11:11:14:1:11:11:7:2:2:2:2:8:8:6:6:2:6:6:11:4:4:2:2:3:3:3:2:2:3:3:4:4:3:3:3:1:1:2:2:4:4:3:3:4:4:1:1:4:4:4:1:1:1:3:3:3:4:4:1:1:1:4:4:4:2:2:4:4:1:1:3:3:1:1:4:4:2:2:4:4:3:3:3:2:2:3:3:4:4:1:1:4:4:3:4:4:4:2:2:2:4:4:4:2:2:2:1:1:4:4:2:2:3:1:1:3:3:1:1:2:2:3:3:2:2:3:3:2:2:1:1:3:3:4:4:1:1:3:3:2:2:2:3:3:1:1:3:3:2:2:1:1:4:4:4:4:2:2:3:3:2:2:3:3:2:2:2:2:2:8:8:8:5:5:2:2:9:9:11:12:11:6:6:6:4:4:8:8:9:11:12:11:5:5:5:20:19:6:10:10:10:12:8:8:8:20:1:1:12:9:9:8:12:8:2:2:6:6:17:1:1:3:3:9:12:9:3:3:3:3:20:6:4:4:5:12:6:6:4:4:21:19:3:3:3:6:12:6:2:2:21:2:2:2:3:3:3:12:3:9:9:20:9:7:7:17:3:3:3:12:3:11:11:4:7:7:21:1:1:8:12:8:1:1:7:7:22:9:4:1:1:12:6:6:5:5:20:8:8:2:2:2:12:5:10:10:5:5:19:9:9:1:1:12:4:4:10:10:17:10:6:6:5:5:9:12:9:9:9:19:8:8:11:11:7:7:12:7:10:10:1:19:10:7:7:5:5:12:10:10:5:5:17:7:6:6:6:6:12:4:4:4:1:1:19:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:21:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:12:3:3:3:3:11:11:12:11:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:21:10:8:12:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:19:2:2:1:12:8:8:7:20:6:8:7:8:17:1:1:3:13:3:7:7:13:3:3:3:13:3:10:10:13:6:6:11:13:11:10:10:13:1:1:4:13:4:2:2:13:2:6:6:13:5:5:8:13:8:8:4:13:4:10:10:13:7:7:2:13:2:2:2:13:4:4:4:13:10:10:3:13:3:9:9:13:9:3:3:13:3:11:11:13:7:7:7:13:4:4:11:13:11:2:2:13:2:9:9:13:3:3:9:13:9:10:10:13:7:7:5:13:5:5:1:13:1:4:4:13:4:11:11:13:6:6:10:13:10:10:4:13:7:7:9:14:9:6:6:14:4:4:4:14:11:11:1:14:1:2:2:14:2:5:5:14:11:11:9:14:9:9:2:14:2:2:2:14:8:8:11:14:11:11:11:14:8:5:5:14:5:1:1:14:7:7:3:14:3:1:1:14:10:10:10:14:8:8:3:14:3:3:11:14:11:11:5:14:5:9:9:14:4:4:1:14:1:1:6:14:6:6:11:14:11:6:6:14:7:7:10:14:10:8:8:14:8:8:11:14:11:10:10:14:2:2:8:14:8:10:10:14:8:8:6:14:6:6:1:14:8:8:5:14:5:5:10:14:10:10:7:14:7:1:1:14:9:9:11:14:11:9:9:14:2:5:5:14:3:3:7:14:7:4:4:5:5:6:6:8:7:9:9:6:6:1:1:5:4:4:2:2:3:3:3:2:2:3:3:4:4:3:3:3:1:1:2:2:4:4:3:3:4:4:1:1:4:4:4:1:1:1:3:3:3:4:4:1:1:1:4:4:4:2:2:4:4:1:1:3:3:1:1:4:4:2:2:4:4:3:3:3:2:2:3:3:4:4:1:1:4:4:3:4:4:4:2:2:2:4:4:4:2:2:2:1:1:4:4:2:2:3:1:1:3:3:1:1:2:2:3:3:2:2:3:3:2:2:1:1:3:3:4:4:1:1:3:3:2:2:2:3:3:1:1:3:3:2:2:1:1:4:4:4:4:2:2:3:3:2:2:3:3:2:2:2:2:2:8:8:8:5:5:2:2:9:9:11:12:11:6:6:6:4:4:8:8:9:11:12:11:5:5:5:20:19:6:10:10:10:12:8:8:8:20:1:1:12:9:9:8:12:8:2:2:6:6:17:1:1:3:3:9:12:9:3:3:3:3:20:6:4:4:5:12:6:6:4:4:4:19:3:3:3:6:12:6:2:2:21:2:2:2:3:3:3:12:3:9:9:20:9:7:7:17:3:3:3:12:3:11:11:4:7:7:21:1:1:8:12:8:1:1:7:7:22:9:4:1:1:12:6:6:5:5:20:8:8:2:2:2:12:5:10:10:5:5:19:9:9:1:1:12:4:4:10:10:17:10:6:6:5:5:9:12:9:9:9:19:8:8:11:11:7:7:12:7:10:10:1:19:10:7:7:5:5:12:10:10:5:5:7:7:6:6:6:6:12:4:4:4:1:1:19:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:21:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:12:3:3:3:3:11:11:12:11:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:21:10:8:12:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:19:2:2:1:12:8:8:7:20:6:8:7:8:17:1:11:11:13:11:1:1:13:11:11:6:13:6:7:7:13:10:10:10:13:9:9:11:13:11:9:9:13:9:11:11:13:11:6:6:13:3:3:3:13:9:5:5:13:1:1:5:13:5:9:9:13:9:11:11:13:1:1:5:13:7:7:6:13:6:6:5:13:5:9:9:13:9:4:4:13:7:7:7:13:10:10:4:13:4:4:1:13:1:1:8:13:8:5:5:13:5:3:3:13:3:2:2:13:6:6:6:13:1:1:4:13:4:4:11:13:11:4:4:13:4:4:2:13:2:3:3:13:4:4:6:14:6:11:11:14:10:10:10:14:10:11:11:14:7:7:7:14:7:11:11:14:2:2:2:14:7:7:4:14:4:2:10:14:10:1:1:14:3:3:3:14:9:9:10:14:10:6:6:14:6:10:10:14:4:4:4:14:9:9:9:14:2:2:5:14:11:11:7:14:7:11:11:14:8:8:2:14:2:2:3:14:3:6:6:14:6:10:1:14:1:1:1:14:2:2:2:14:10:10:5:14:5:10:10:14:7:8:8:14:3:3:9:14:9:5:5:14:7:7:10:14:10:10:1:14:1:8:8:14:8:3:3:14:7:7:3:14:3:8:8:14:8:5:5:14:6:6:8:14:5:5:5:14:2:2:2:4:9:10:10:3:8:8:2:8:8:11:8:8:4:4:2:2:3:3:3:2:2:3:3:4:4:3:3:3:1:1:2:2:4:4:3:3:4:4:1:1:4:4:4:1:1:1:3:3:3:4:4:1:1:1:4:4:4:2:2:4:4:1:1:3:3:1:1:4:4:2:2:4:4:3:3:3:2:2:3:3:4:4:1:1:4:4:3:4:4:4:2:2:2:4:4:4:2:2:2:1:1:4:4:2:2:3:1:1:3:3:1:1:2:2:3:3:2:2:3:3:2:2:1:1:3:3:4:4:1:1:3:3:2:2:2:3:3:1:1:3:3:2:2:1:1:4:4:4:4:2:2:3:3:2:2:3:3:2:2:2:2:2:8:8:8:5:5:2:2:9:9:11:12:11:6:6:6:4:4:8:8:9:11:12:11:5:5:5:20:19:6:10:10:10:12:8:8:8:20:1:1:12:9:9:8:12:8:2:2:6:6:17:1:1:3:3:9:12:9:3:3:3:3:20:6:4:4:5:12:6:6:4:4:4:4:3:3:3:6:12:6:2:2:21:2:2:2:3:3:3:12:3:9:9:20:9:7:7:17:3:3:3:12:3:11:11:4:7:7:21:1:1:8:12:8:1:1:7:7:22:9:4:1:1:12:6:6:5:5:20:8:8:2:2:2:12:5:10:10:5:5:19:9:9:1:1:12:4:4:10:10:17:10:6:6:5:5:9:12:9:9:9:19:8:8:11:11:7:7:12:7:10:10:1:19:10:7:7:5:5:12:10:10:5:5:7:7:6:6:6:6:12:4:4:4:1:1:19:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:21:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:2:3:3:3:3:11:11:12:11:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:21:10:8:12:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:19:2:2:1:12:8:8:7:20:6:8:7:8:17:4:4:4:13:11:11:1:13:1:10:10:13:7:7:7:13:5:5:6:13:6:3:3:13:7:7:11:13:11:4:4:13:3:3:10:13:10:10:9:13:9:9:6:13:6:6:7:13:7:9:9:13:9:8:8:13:5:5:5:13:5:7:7:13:6:6:7:13:7:7:1:13:1:1:2:13:2:1:1:13:8:8:8:13:2:2:6:13:6:6:7:13:5:5:2:13:5:5:11:13:11:11:5:13:5:5:5:13:1:1:4:13:4:4:4:13:3:3:3:13:9:9:10:13:10:10:11:13:11:11:9:13:9:8:8:13:3:3:5:14:5:4:4:14:9:9:6:14:11:11:2:14:2:3:3:14:10:10:6:14:6:6:3:14:3:8:8:14:5:5:5:14:9:9:9:14:10:10:4:14:8:8:9:14:9:9:1:14:1:8:8:14:3:3:8:14:8:8:4:14:4:7:7:14:1:1:1:14:6:6:7:14:7:2:2:14:6:6:4:14:4:10:10:14:11:11:6:14:6:3:3:14:1:1:11:14:11:8:8:14:2:2:4:14:4:10:10:14:10:9:9:14:10:4:4:14:8:10:10:14:7:1:1:14:2:2:3:14:3:11:11:14:2:2:10:14:10:10:7:14:7:2:2:14:2:1:1:11:11:11:11:10:10:11:11:2:2:11:5:3:3:3:3:4:4:1:1:2:2:4:4:2:2:2:1:1:3:3:1:1:2:2:1:1:1:3:3:1:1:1:3:3:1:1:1:3:3:3:1:1:3:3:4:4:2:2:2:3:3:2:2:4:4:3:3:1:1:2:2:1:1:4:4:4:2:2:2:3:3:1:1:2:2:3:3:3:3:2:2:4:2:2:2:2:1:1:4:4:4:2:2:4:4:2:2:2:3:3:4:4:1:1:4:4:4:2:2:2:2:3:3:3:3:4:4:4:3:3:3:4:4:3:3:4:4:3:3:4:4:1:1:1:2:2:2:4:4:4:2:2:4:4:3:3:4:4:4:2:4:3:8:8:8:5:5:2:2:9:9:11:12:11:6:6:6:4:4:8:8:9:11:12:11:5:5:5:20:19:6:10:10:10:12:8:8:8:20:1:1:1:9:9:8:12:8:2:2:6:6:17:1:1:3:3:9:12:9:3:3:3:3:20:6:4:4:5:12:6:6:4:4:4:4:3:3:3:6:12:6:2:2:21:2:2:2:3:3:3:12:3:9:9:20:9:7:7:17:3:3:3:12:3:11:11:4:7:7:21:1:1:8:12:8:1:1:7:7:22:9:4:1:1:12:6:6:5:5:20:8:8:2:2:2:12:5:10:10:5:5:19:9:9:1:1:12:4:4:10:10:17:10:6:6:5:5:9:12:9:9:9:19:8:8:11:11:7:7:12:7:10:10:1:19:10:7:7:5:5:12:10:10:5:5:7:7:6:6:6:6:12:4:4:4:1:1:19:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:21:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:2:3:3:3:3:11:11:12:11:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:21:10:8:12:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:19:2:2:1:5:8:8:7:20:6:8:7:8:17:2:2:11:13:11:5:5:13:1:1:1:13:11:11:11:13:4:4:4:13:8:8:3:13:3:10:10:13:7:7:5:13:5:10:10:13:10:1:1:13:2:2:3:13:3:10:10:13:10:9:9:13:6:6:8:13:8:11:7:13:10:10:1:13:1:10:2:13:2:3:3:13:3:11:11:13:5:5:9:13:9:4:4:13:11:11:11:13:6:9:9:13:4:4:4:13:8:8:2:13:2:8:8:13:10:10:8:13:8:11:11:13:4:4:5:13:5:5:6:13:6:6:7:13:7:7:4:13:4:3:1:13:1:9:9:13:3:3:9:13:9:9:9:14:6:6:10:14:10:7:7:14:2:2:8:14:9:2:2:14:5:5:5:14:5:6:6:14:6:1:1:14:3:3:11:14:11:7:7:14:1:1:1:14:10:10:3:14:2:2:7:14:7:5:5:14:7:7:7:14:7:3:3:14:10:10:1:14:1:8:8:14:8:2:2:14:4:4:4:14:7:7:7:14:10:10:10:14:10:9:9:14:2:2:8:14:8:8:11:14:11:11:6:14:6:4:4:14:5:5:11:14:11:3:3:14:9:9:8:14:8:1:1:14:9:9:1:14:1:4:4:14:4:10:10:14:5:5:9:14:11:11:6:2:2:8:11:11:6:6:3:3:3:11:6:6:6:6:7:5:3:3:3:2:2:3:3:4:4:3:3:3:1:1:3:3:2:2:3:2:2:1:1:1:3:3:3:2:2:1:1:3:3:1:1:1:2:2:3:3:3:1:1:4:4:4:1:1:3:3:2:2:1:1:4:4:1:1:4:4:4:4:3:2:2:4:4:4:4:2:2:4:4:2:2:3:3:4:4:1:1:4:4:4:1:1:2:2:4:4:3:3:2:2:2:4:4:2:2:2:3:3:4:4:3:3:2:2:3:3:4:4:3:3:1:1:2:2:2:3:3:4:4:1:1:4:4:3:3:2:2:3:3:2:2:1:1:1:2:2:4:4:2:2:4:4:2:4:4:1:8:8:8:5:5:2:2:9:9:11:12:11:6:6:6:4:4:8:8:9:11:12:11:5:5:5:20:19:6:10:10:10:12:8:8:8:20:1:1:1:9:9:8:5:8:2:2:6:6:17:1:1:3:3:9:12:9:3:3:3:3:20:6:4:4:5:12:6:6:4:4:4:4:3:3:3:6:12:6:2:2:21:2:2:2:3:3:3:12:3:9:9:20:9:7:7:17:3:3:3:12:3:11:11:4:7:7:21:1:1:8:12:8:1:1:7:7:22:9:4:1:1:12:6:6:5:5:20:8:8:2:2:2:12:5:10:10:5:5:19:9:9:1:1:12:4:4:10:10:17:10:6:6:5:5:9:12:9:9:9:19:8:8:11:11:7:7:12:7:10:10:1:19:10:7:7:5:5:12:10:10:5:5:7:7:6:6:6:6:12:4:4:4:1:1:19:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:21:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:2:3:3:3:3:11:11:12:11:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:21:10:8:12:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:19:2:2:1:5:8:8:7:20:6:8:7:8:17:2:2:6:13:6:6:4:13:4:2:2:13:2:10:10:13:11:11:5:13:5:11:3:13:3:3:6:13:6:4:4:13:10:10:11:13:11:7:7:13:3:3:6:13:6:6:3:13:3:3:1:13:3:3:11:13:11:10:10:13:10:10:7:13:7:9:9:13:7:7:9:13:9:8:8:13:5:5:7:13:7:7:2:13:2:9:9:13:10:10:11:13:11:3:3:13:4:1:1:13:1:1:6:13:6:6:4:13:4:4:5:13:5:8:8:13:1:1:7:13:7:8:7:13:7:9:9:13:1:1:10:13:10:6:6:13:10:10:1:14:1:1:5:14:5:11:11:14:4:4:4:14:10:10:11:14:11:5:1:14:1:4:4:14:4:6:6:14:2:2:10:14:10:10:11:14:11:8:8:14:7:7:8:14:8:5:5:14:5:11:11:14:3:3:11:14:11:8:8:14:2:2:5:14:5:6:6:14:6:7:7:14:7:9:9:14:2:2:4:14:4:11:11:14:2:2:2:14:8:8:9:14:9:1:1:14:1:10:10:14:10:10:5:14:5:11:11:14:8:8:8:14:2:2:9:14:9:9:10:14:10:7:7:14:3:3:3:14:5:5:6:14:6:11:11:9:9:9:3:3:4:4:5:5:8:8:1:1:8:8:8:8:3:4:4:9:9:2:2:1:2:2:4:4:1:1:4:4:2:2:4:4:2:2:2:3:3:3:1:1:3:3:1:1:3:3:3:2:2:4:4:3:3:1:1:1:3:3:1:1:3:3:4:4:4:2:2:3:3:2:2:2:3:3:2:2:4:4:3:3:2:2:3:3:1:1:2:2:2:4:4:4:4:2:2:3:3:3:2:2:4:4:3:3:1:1:2:2:1:1:2:2:4:4:3:3:1:1:1:2:2:4:4:1:1:4:4:3:3:3:4:4:2:2:4:4:1:1:4:4:3:3:1:1:4:4:2:2:4:1:1:4:4:3:3:2:2:3:3:2:2:3:3:4:4:1:1:4:4:2:8:8:8:5:5:2:2:9:9:11:11:11:6:6:6:4:4:8:8:9:11:12:11:5:5:5:20:19:6:10:10:10:12:8:8:8:20:1:1:1:9:9:8:5:8:2:2:6:6:17:1:1:3:3:9:9:9:3:3:3:3:20:6:4:4:5:9:6:6:4:4:4:4:3:3:3:6:12:6:2:2:21:2:2:2:3:3:3:12:3:9:9:20:9:7:7:17:3:3:3:12:3:11:11:4:1:7:21:1:1:8:12:8:1:1:7:7:22:9:4:1:1:12:6:6:5:5:20:8:8:2:2:2:5:5:10:10:5:5:19:9:9:1:1:12:4:4:10:10:17:10:6:6:5:5:9:12:9:9:9:19:8:8:11:11:7:7:12:7:10:10:1:19:10:7:7:5:5:12:10:10:5:5:7:7:6:6:6:6:12:4:4:4:1:1:19:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:21:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:2:3:3:3:3:11:11:12:11:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:21:10:8:12:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:19:2:2:1:5:8:8:7:20:6:8:7:8:17:2:2:11:11:11:5:5:13:1:1:1:13:11:11:11:13:4:4:4:13:8:8:3:13:3:10:10:13:7:7:5:5:5:10:10:13:10:1:1:13:2:2:3:13:3:10:10:13:10:9:9:13:6:6:8:8:8:11:7:7:10:10:1:13:1:10:2:13:2:3:3:13:3:11:11:13:5:5:9:13:9:4:4:13:11:11:11:13:6:9:9:13:4:4:4:13:8:8:2:13:2:8:8:13:10:10:8:8:8:11:11:13:4:4:5:13:5:5:6:13:6:6:7:13:7:7:4:13:4:3:1:13:1:9:9:13:3:3:9:13:9:9:9:14:6:6:10:10:10:7:7:14:2:2:8:14:9:2:2:14:5:5:5:14:5:6:6:14:6:1:1:8:3:3:11:14:11:7:7:14:1:1:1:14:10:10:3:3:2:2:7:14:7:5:5:14:7:7:7:14:7:3:3:14:10:10:1:14:1:8:8:14:8:2:2:14:4:4:4:14:7:7:7:14:10:10:10:14:10:9:9:14:2:2:8:14:8:8:11:14:11:11:6:14:6:4:4:14:5:5:11:14:11:3:3:14:9:9:8:14:8:1:1:14:9:9:1:14:1:4:4:14:4:10:10:14:5:5:9:14:11:11:6:2:2:8:11:11:6:6:3:3:3:11:6:6:6:6:7:5:2:2:3:3:2:2:1:1:2:4:4:4:3:3:3:4:4:3:3:4:4:1:1:2:2:2:1:1:3:3:4:4:4:2:2:2:2:3:3:4:3:3:1:1:2:2:2:4:4:4:2:2:3:3:4:4:3:3:4:4:1:1:3:3:4:4:4:3:3:3:2:2:1:1:1:3:3:3:1:1:3:3:3:4:4:2:2:2:4:4:4:4:3:3:3:4:4:1:1:1:2:2:2:1:1:1:2:2:2:1:1:4:4:4:4:1:1:4:4:2:2:1:1:2:2:3:4:4:2:2:3:3:2:3:3:2:2:2:2:1:1:1:4:4:4:3:3:3:3:2:</t>
+  </si>
+  <si>
+    <t>8:8:4:4:4:10:10:2:2:10:12:10:4:4:4:4:10:10:12:8:8:3:19:3:3:1:1:19:11:11:11:2:2:19:8:8:2:12:7:7:2:12:2:2:9:19:10:10:9:17:7:9:9:1:1:12:8:8:3:3:3:19:7:1:1:6:12:6:5:5:2:19:3:3:10:10:5:12:5:8:8:9:9:9:21:3:3:7:12:7:9:9:5:5:5:17:3:3:3:3:12:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:12:7:7:6:6:12:6:7:7:7:20:21:11:11:7:7:12:7:6:9:9:17:3:3:3:20:1:1:10:12:11:11:3:19:21:5:5:4:4:12:4:6:6:6:21:19:10:3:3:5:5:12:10:10:2:2:22:20:2:8:8:12:8:5:5:5:12:7:7:7:7:17:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:20:1:6:6:17:4:4:8:8:12:10:10:6:6:7:7:7:9:9:10:12:10:8:8:4:4:20:9:9:9:8:12:8:4:4:8:17:11:11:12:7:7:8:8:6:6:19:4:4:6:4:17:7:7:10:13:10:1:1:13:8:8:8:13:5:5:5:13:1:1:11:13:11:7:7:13:3:3:7:13:7:10:10:13:7:7:2:13:2:2:2:13:9:9:9:13:8:8:11:13:11:4:4:13:4:6:6:13:3:3:9:13:9:10:10:13:7:7:6:13:6:6:8:13:8:11:11:13:11:1:1:13:1:6:6:13:4:4:5:14:5:5:11:14:11:11:10:14:10:10:2:14:2:5:5:14:9:9:9:14:9:2:2:14:9:9:11:14:11:11:11:14:4:4:5:14:5:7:7:14:7:7:11:14:11:4:4:14:1:1:8:14:8:10:10:14:9:9:2:14:2:8:8:14:8:9:9:14:3:3:3:14:9:9:5:14:5:5:1:14:1:5:5:14:9:9:9:14:3:3:5:14:5:11:11:14:4:4:4:14:10:10:9:14:9:6:6:14:7:7:1:14:1:1:3:14:3:3:5:14:5:5:11:14:11:11:10:14:10:10:7:14:7:2:7:14:7:6:6:14:9:9:2:14:2:1:1:14:10:10:2:14:2:2:3:14:3:8:8:14:6:6:8:14:8:11:11:14:4:4:10:14:10:1:1:14:10:10:10:14:3:3:4:14:4:8:8:14:4:4:6:14:6:6:3:14:3:3:6:6:6:10:10:9:10:10:4:4:11:10:10:6:2:2:2:6:6:6:10:10:9:9:3:3:3:1:1:7:7:7:8:8:10:10:10:1:1:6:6:4:4:6:6:8:8:10:10:2:2:2:9:9:9:9:5:5:5:8:8:11:11:11:7:7:7:1:1:4:4:3:3:11:11:1:1:10:10:4:4:8:8:11:11:9:9:7:7:8:8:6:6:5:1:1:8:8:7:7:1:1:1:7:7:5:11:11:3:3:10:10:6:7:7:7:9:9:9:4:4:10:10:10:3:3:11:11:11:8:8:2:2:2:5:5:2:2:2:11:11:11:2:2:9:1:1:5:5:5:3:3:8:10:4:4:9:9:3:3:2:3:3:9:8:8:4:4:4:10:10:2:2:10:12:10:4:4:4:4:10:10:12:8:8:3:19:3:3:1:1:19:11:11:11:2:2:19:8:8:2:12:7:7:2:12:2:2:9:19:10:10:9:17:7:9:9:1:1:12:8:8:3:3:3:19:7:1:1:6:12:6:5:5:2:19:3:3:10:10:5:12:5:8:8:9:9:9:21:3:3:7:12:7:9:9:5:5:5:17:3:3:3:3:12:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:12:7:7:6:6:12:6:7:7:7:20:21:11:11:7:7:12:7:6:9:9:17:3:3:3:20:1:1:10:12:11:11:3:19:21:5:5:4:4:12:4:6:6:6:21:19:10:3:3:5:5:12:10:10:2:2:22:20:2:8:8:12:8:5:5:5:12:7:7:7:7:17:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:20:1:6:6:17:4:4:8:8:12:10:10:6:6:7:7:7:9:9:10:12:10:8:8:4:4:20:9:9:9:8:12:8:4:4:8:17:11:11:12:7:7:8:8:6:6:19:4:4:6:4:17:8:8:8:13:2:2:6:13:6:4:4:13:6:6:10:13:10:4:4:13:10:10:11:13:11:11:3:13:3:1:1:13:5:5:4:13:4:5:5:13:7:7:1:13:1:7:7:13:6:6:6:13:10:10:2:13:2:2:5:13:5:11:11:13:4:4:6:13:6:8:8:13:9:9:8:13:8:11:11:13:7:7:9:13:9:9:8:13:8:11:11:13:9:9:1:13:1:3:3:13:2:2:7:13:7:8:8:13:8:7:7:14:7:2:2:14:3:3:7:14:7:7:7:14:11:11:4:14:4:9:9:14:10:10:7:14:7:9:9:14:4:4:4:14:6:6:6:14:1:1:3:14:3:9:9:14:8:8:8:14:8:1:1:14:6:6:9:14:9:4:4:14:5:5:5:14:11:11:11:14:10:10:10:14:11:11:11:14:3:3:3:14:2:2:4:14:4:4:4:14:1:1:1:14:9:9:9:14:9:11:11:14:5:5:11:14:11:3:3:14:10:10:10:14:3:3:1:14:1:5:2:14:2:6:6:14:6:5:5:14:10:10:9:14:9:2:2:14:5:5:8:14:8:6:6:14:5:5:5:14:5:10:10:14:3:3:3:14:10:10:1:14:1:1:2:14:2:10:10:14:9:9:3:14:10:10:1:1:6:7:7:10:9:2:2:8:2:4:7:8:2:2:2:6:6:6:10:10:9:9:3:3:3:1:1:7:7:7:8:8:10:10:10:1:1:6:6:4:4:6:6:8:8:10:10:2:2:2:9:9:9:9:5:5:5:8:8:11:11:11:7:7:7:1:1:4:4:3:3:11:11:1:1:10:10:4:4:8:8:11:11:9:9:7:7:8:8:6:6:5:1:1:8:8:7:7:1:1:1:7:7:5:11:11:3:3:10:10:6:7:7:7:9:9:9:4:4:10:10:10:3:3:11:11:11:8:8:2:2:2:5:5:2:2:2:11:11:11:2:2:9:1:1:5:5:5:3:3:8:10:4:4:9:9:3:3:2:3:3:9:8:8:4:4:4:10:10:2:2:10:12:10:4:4:4:4:10:10:12:8:8:3:19:3:3:1:1:19:11:11:11:2:2:19:8:8:2:12:7:7:2:12:2:2:9:19:10:10:9:17:7:9:9:1:1:12:8:8:3:3:3:19:7:1:1:6:12:6:5:5:2:19:3:3:10:10:5:12:5:8:8:9:9:9:21:3:3:7:12:7:9:9:5:5:5:17:3:3:3:3:12:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:12:7:7:6:6:12:6:7:7:7:20:11:11:11:7:7:12:7:6:9:9:17:3:3:3:20:1:1:10:12:11:11:3:19:21:5:5:4:4:12:4:6:6:6:21:19:10:3:3:5:5:12:10:10:2:2:22:20:2:8:8:12:8:5:5:5:12:7:7:7:7:17:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:20:1:6:6:17:4:4:8:8:12:10:10:6:6:7:7:7:9:9:10:12:10:8:8:4:4:20:9:9:9:8:12:8:4:4:8:17:11:11:12:7:7:8:8:6:6:19:4:4:6:4:17:9:9:6:13:6:3:3:13:3:4:4:13:5:5:5:13:1:1:1:13:9:9:11:13:11:3:3:13:11:11:3:13:3:4:4:13:6:6:6:13:10:10:10:13:11:11:9:13:9:9:1:13:1:1:5:13:5:5:4:13:4:4:2:13:2:5:5:13:8:8:8:13:10:10:4:13:4:1:1:13:9:9:7:13:7:7:9:13:9:3:3:13:3:3:7:13:7:10:10:13:3:3:9:13:9:7:7:13:7:6:6:13:2:2:9:13:9:4:4:14:10:10:10:14:7:3:3:14:2:2:2:14:2:3:3:14:3:3:4:14:4:4:9:14:9:8:8:14:5:5:6:14:6:9:9:14:9:8:8:14:6:6:1:14:1:6:6:14:11:11:2:14:2:8:8:14:4:10:10:14:10:8:8:14:7:7:7:14:5:5:11:14:11:11:5:14:5:10:10:14:10:9:9:14:1:1:1:14:7:7:11:14:11:2:2:14:2:10:10:14:1:1:1:14:1:9:9:14:11:11:6:14:6:6:2:14:2:5:5:14:11:11:11:14:10:10:10:14:10:7:7:14:6:6:6:14:6:10:10:14:10:2:2:14:5:5:5:14:2:2:4:14:4:7:7:14:8:8:3:14:11:11:8:14:8:1:1:4:4:4:2:8:8:7:7:5:8:8:8:1:2:2:2:6:6:6:10:10:9:9:3:3:3:1:1:7:7:7:8:8:10:10:10:1:1:6:6:4:4:6:6:8:8:10:10:2:2:2:9:9:9:9:5:5:5:8:8:11:11:11:7:7:7:1:1:4:4:3:3:11:11:1:1:10:10:4:4:8:8:11:11:9:9:7:7:8:8:6:6:5:1:1:8:8:7:7:1:1:1:7:7:5:11:11:3:3:10:10:6:7:7:7:9:9:9:4:4:10:10:10:3:3:11:11:11:8:8:2:2:2:5:5:2:2:2:11:11:11:2:2:9:1:1:5:5:5:3:3:8:10:4:4:9:9:3:3:2:3:3:9:8:8:4:4:4:10:10:2:2:10:12:10:4:4:4:4:10:10:12:8:8:3:19:3:3:1:1:19:11:11:11:2:2:19:8:8:2:12:7:7:2:12:2:2:9:19:10:10:9:17:7:9:9:1:1:12:8:8:3:3:3:19:7:1:1:6:12:6:5:5:2:19:3:3:10:10:5:12:5:8:8:9:9:9:21:3:3:7:12:7:9:9:5:5:5:17:3:3:3:3:12:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:12:7:7:6:6:12:6:7:7:7:7:11:11:11:7:7:12:7:6:9:9:17:3:3:3:20:1:1:10:12:11:11:3:19:21:5:5:4:4:12:4:6:6:6:21:19:10:3:3:5:5:12:10:10:2:2:22:20:2:8:8:12:8:5:5:5:5:7:7:7:7:17:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:20:1:6:6:17:4:4:8:8:12:10:10:6:6:7:7:7:9:9:10:12:10:8:8:4:4:20:9:9:9:8:12:8:4:4:8:8:11:11:12:7:7:8:8:6:6:9:4:4:6:4:17:8:8:8:13:8:5:5:13:5:5:9:13:9:10:10:13:9:9:11:13:11:1:1:13:9:4:4:13:1:1:3:13:3:8:8:13:1:1:4:13:4:3:3:13:3:5:5:13:11:11:11:13:7:7:1:13:1:9:4:13:4:9:9:13:8:8:2:13:2:2:9:13:9:4:4:13:4:10:10:13:1:1:9:13:9:9:11:13:11:1:1:13:1:11:11:13:7:7:8:13:8:5:5:13:5:4:4:13:4:6:6:13:10:10:10:13:3:3:10:13:10:11:11:13:3:3:6:13:6:11:11:14:7:7:9:14:9:7:7:14:7:8:8:14:6:6:9:14:9:9:9:14:4:4:4:14:7:7:6:14:6:10:10:14:8:8:8:14:10:10:6:14:6:3:3:14:5:6:6:14:6:11:11:14:4:4:10:14:10:5:5:14:5:5:7:14:7:9:9:14:3:3:2:14:2:4:4:14:2:2:2:14:6:6:9:14:9:3:4:14:2:2:3:14:3:7:7:14:7:1:1:14:10:10:2:14:2:1:1:14:5:5:7:14:7:8:8:14:7:7:10:14:1:1:1:14:6:6:6:14:10:10:10:14:8:8:11:14:11:2:2:14:5:5:2:14:2:2:9:14:2:2:11:14:11:6:6:8:10:10:3:3:10:10:5:5:11:2:3:3:2:10:10:10:10:9:9:9:1:1:1:4:4:3:3:8:8:5:5:11:11:2:11:11:1:1:9:9:1:1:11:11:7:7:7:8:8:10:10:10:11:11:3:3:9:9:7:7:11:11:11:9:9:10:10:10:5:5:1:1:4:4:6:6:8:8:1:1:6:6:5:5:10:10:9:9:6:6:7:7:7:11:11:7:7:7:10:10:3:3:8:8:8:6:6:6:8:8:4:4:2:2:2:3:3:3:2:2:3:3:2:2:8:8:6:9:9:9:2:2:4:4:3:3:5:5:3:3:4:4:1:1:7:7:7:1:1:2:2:2:7:2:11:11:10:5:5:8:8:9:8:8:4:4:4:10:10:2:2:10:12:10:4:4:4:4:10:10:12:8:8:3:19:3:3:1:1:19:11:11:11:2:2:19:8:8:2:12:7:7:2:12:2:2:9:19:10:10:9:17:7:9:9:1:1:12:8:8:3:3:3:19:7:1:1:6:12:6:5:5:2:19:3:3:10:10:5:12:5:8:8:9:9:9:21:3:3:7:12:7:9:9:5:5:5:17:3:3:3:3:12:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:4:7:7:6:6:12:6:7:7:7:7:11:11:11:7:7:12:7:6:9:9:17:3:3:3:20:1:1:10:12:11:11:3:19:21:5:5:4:4:12:4:6:6:6:21:19:10:3:3:5:5:12:10:10:2:2:22:20:2:8:8:12:8:5:5:5:5:7:7:7:7:17:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:20:1:6:6:17:4:4:8:8:12:10:10:6:6:7:7:7:9:9:10:12:10:8:8:4:4:20:9:9:9:8:12:8:4:4:8:8:11:11:4:7:7:8:8:6:6:9:4:4:6:4:17:3:3:3:13:2:2:11:13:11:8:8:13:8:7:7:13:11:11:9:13:9:7:7:13:6:6:6:13:5:5:2:13:2:1:1:13:7:7:11:13:11:2:2:13:5:5:11:13:11:7:7:13:6:6:6:13:1:1:11:13:11:11:5:13:5:5:5:13:3:3:1:13:1:6:6:13:6:8:8:13:8:11:11:13:7:7:7:13:3:3:1:13:1:9:9:13:1:1:3:13:3:3:3:13:7:7:1:13:1:2:2:13:4:4:9:13:9:2:2:13:6:6:9:13:9:4:11:13:11:9:9:13:5:5:1:13:1:8:4:13:4:2:2:14:2:2:4:14:4:1:1:14:1:9:9:14:9:6:6:14:10:10:2:14:9:9:10:14:10:4:4:14:10:10:10:14:8:8:8:14:4:4:2:14:2:1:1:14:10:10:4:14:4:10:10:14:5:5:8:14:8:9:9:14:9:3:3:14:10:10:10:14:10:7:7:14:3:3:4:14:4:4:5:14:5:7:7:14:7:4:4:14:4:10:10:14:5:5:5:14:8:6:6:14:5:5:5:14:3:3:2:14:2:7:7:14:3:3:3:14:11:10:10:14:6:6:6:14:9:9:8:14:8:9:9:14:10:10:8:14:8:8:10:11:11:9:9:9:6:6:4:2:8:10:10:1:11:11:10:8:11:11:1:1:2:2:7:7:4:4:4:4:2:2:5:5:10:10:7:7:7:2:2:2:2:5:5:5:3:3:11:11:11:7:7:8:8:3:3:4:4:4:10:10:3:3:2:2:2:7:7:4:1:1:1:11:11:9:9:10:7:7:5:8:8:10:10:10:9:9:2:2:1:1:1:3:3:1:1:3:3:10:10:10:8:8:9:9:9:4:4:10:10:8:8:5:5:8:8:9:9:7:7:7:2:11:11:3:3:3:9:9:6:6:6:3:3:8:8:11:6:6:6:1:1:1:8:8:8:7:11:11:6:6:6:9:9:2:6:5:5:11:11:1:1:9:9:11:10:10:8:8:4:4:4:10:10:2:2:10:12:10:4:4:4:4:10:10:12:8:8:3:19:3:3:1:1:19:11:11:11:2:2:19:8:8:2:7:7:7:2:12:2:2:9:19:10:10:9:17:7:9:9:1:1:12:8:8:3:3:3:19:7:1:1:6:12:6:5:5:2:19:3:3:10:10:5:12:5:8:8:9:9:9:21:3:3:7:12:7:9:9:5:5:5:17:3:3:3:3:12:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:4:7:7:6:6:12:6:7:7:7:7:11:11:11:7:7:12:7:6:9:9:17:3:3:3:20:1:1:10:12:11:11:3:19:21:5:5:4:4:12:4:6:6:6:21:19:10:3:3:5:5:12:10:10:2:2:22:20:2:8:8:12:8:5:5:5:5:7:7:7:7:17:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:20:1:6:6:17:4:4:8:8:12:10:10:6:6:7:7:7:9:9:10:12:10:8:8:4:4:20:9:9:9:8:12:8:4:4:8:8:11:11:4:7:7:8:8:6:6:9:4:4:6:4:17:9:9:9:13:11:11:6:13:6:6:6:13:9:9:8:13:8:10:10:13:9:9:8:13:8:4:4:13:3:3:11:13:11:1:1:13:7:7:5:13:5:9:9:13:10:4:4:13:8:8:5:13:5:3:3:13:3:4:4:13:4:7:7:13:11:11:10:13:10:3:3:13:6:6:3:13:3:5:5:13:7:7:9:13:9:2:2:13:5:5:11:13:11:11:4:13:7:9:9:13:1:1:6:13:6:9:9:13:10:10:10:13:10:1:1:13:10:10:8:13:8:3:3:13:3:10:10:13:7:7:5:14:5:9:9:14:2:2:4:14:4:4:4:14:6:6:9:14:9:9:6:14:6:2:2:14:2:9:9:14:8:8:8:14:8:10:10:14:1:1:2:14:2:6:6:14:7:7:5:14:5:5:5:14:10:10:5:14:5:5:11:14:11:11:4:14:4:3:3:14:9:9:9:14:4:4:4:14:2:2:2:14:2:7:7:14:7:7:4:14:4:10:10:14:3:3:8:14:8:11:11:14:1:1:11:14:11:6:6:14:7:7:1:14:1:8:8:14:8:8:3:14:3:1:1:14:2:2:1:14:1:8:8:14:9:11:11:14:1:1:10:14:10:7:7:7:5:5:10:10:2:2:11:11:4:3:3:1:1:6:6:6:6:2:2:2:10:10:1:5:1:1:4:4:4:6:6:6:8:8:2:2:9:9:10:10:1:1:2:2:2:2:1:1:3:3:9:9:9:1:10:10:7:7:10:10:10:6:6:5:5:7:7:3:3:7:7:9:9:9:8:8:11:11:11:10:10:10:3:3:11:3:3:6:6:5:5:2:2:6:8:8:8:7:7:7:8:5:5:8:8:11:11:9:9:9:11:11:11:7:7:4:4:4:5:5:3:3:7:7:6:6:8:8:3:3:11:11:11:5:5:9:9:9:8:8:10:10:11:11:1:1:8:1:1:7:2:2:1:1:3:3:3:9:2:2:2:11:2:2:4:4:10:10:1:1:10:7:4:4:8:8:4:4:4:10:10:2:2:10:10:10:4:4:4:4:10:10:12:8:8:3:19:3:3:1:1:19:11:11:11:2:2:19:8:8:2:7:7:7:2:12:2:2:9:10:10:10:9:17:7:9:9:1:1:1:8:8:3:3:3:19:7:1:1:6:6:6:5:5:2:2:3:3:10:10:5:12:5:8:8:9:9:9:21:3:3:7:12:7:9:9:5:5:5:17:3:3:3:3:5:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:4:7:7:6:6:12:6:7:7:7:7:11:11:11:7:7:12:7:6:9:9:17:3:3:3:20:1:1:10:10:11:11:3:19:21:5:5:4:4:12:4:6:6:6:21:10:10:3:3:5:5:12:10:10:2:2:22:20:2:8:8:12:8:5:5:5:5:7:7:7:7:17:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:20:1:6:6:4:4:4:8:8:10:10:10:6:6:7:7:7:9:9:10:10:10:8:8:4:4:20:9:9:9:8:8:8:4:4:8:8:11:11:4:7:7:8:8:6:6:9:4:4:6:4:4:3:3:3:2:2:2:11:13:11:8:8:13:8:7:7:13:11:11:9:13:9:7:7:13:6:6:6:5:5:5:2:13:2:1:1:13:7:7:11:13:11:2:2:13:5:5:11:13:11:7:7:13:6:6:6:1:1:1:11:13:11:11:5:13:5:5:5:13:3:3:1:1:1:6:6:13:6:8:8:13:8:11:11:13:7:7:7:13:3:3:1:13:1:9:9:13:1:1:3:13:3:3:3:13:7:7:1:1:1:2:2:13:4:4:9:13:9:2:2:13:6:6:9:13:9:4:11:13:11:9:9:13:5:5:1:13:1:8:4:13:4:2:2:14:2:2:4:14:4:1:1:14:1:9:9:14:9:6:6:14:10:10:2:14:9:9:10:14:10:4:4:9:10:10:10:14:8:8:8:14:4:4:2:14:2:1:1:14:10:10:4:14:4:10:10:14:5:5:8:14:8:9:9:14:9:3:3:14:10:10:10:14:10:7:7:14:3:3:4:14:4:4:5:14:5:7:7:14:7:4:4:14:4:10:10:14:5:5:5:14:8:6:6:14:5:5:5:14:3:3:2:14:2:7:7:14:3:3:3:14:11:10:10:14:6:6:6:14:9:9:8:14:8:9:9:14:10:10:8:14:8:8:10:11:11:9:9:9:6:6:4:2:8:10:10:1:11:11:10:8:1:1:10:10:1:1:1:8:8:5:5:5:10:10:2:3:3:8:8:2:2:9:10:10:5:5:2:2:7:7:3:3:3:7:7:9:9:2:2:11:11:6:6:7:7:8:8:9:9:11:11:11:5:5:11:11:4:4:8:8:8:8:6:6:11:11:1:1:11:11:1:1:3:3:2:2:3:3:1:1:1:4:4:9:7:7:10:10:5:5:10:10:5:4:4:6:6:11:11:10:10:10:2:2:7:7:7:3:3:9:9:4:4:4:7:7:9:9:9:10:10:6:6:3:3:4:11:11:9:9:9:2:2:3:3:9:1:1:7:7:2:2:6:6:8:8:1:8:8:8:</t>
+  </si>
+  <si>
+    <t>2:2:5:5:2:2:9:9:7:7:6:3:2:2:2:4:17:4:6:6:6:8:8:8:1:1:1:6:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:6:2:2:10:10:4:4:17:4:6:6:11:11:11:3:3:7:7:7:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:3:6:6:6:10:17:10:4:4:2:2:2:10:10:6:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:5:5:5:7:7:7:11:11:5:17:5:11:11:11:2:2:2:5:5:4:4:6:6:6:7:7:7:6:6:8:8:8:7:7:7:7:1:1:9:9:4:4:4:5:5:1:1:3:3:5:5:9:9:9:6:11:11:11:9:9:9:2:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:15:11:11:1:1:6:1:1:7:7:4:4:4:4:9:9:1:1:1:2:2:2:4:4:4:6:6:6:1:3:3:5:5:1:1:1:8:8:8:1:1:6:6:5:5:5:4:4:2:2:2:6:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:15:7:3:3:3:2:2:6:3:1:1:5:5:5:3:3:4:4:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:15:7:7:10:6:2:2:2:1:1:7:1:7:7:3:3:3:3:7:7:6:6:11:11:8:8:4:4:10:10:2:2:5:5:4:4:6:6:6:6:1:1:10:10:6:6:7:7:11:11:9:9:1:1:9:9:11:11:11:11:9:9:9:3:3:6:6:5:5:2:2:8:8:2:2:1:1:1:5:5:10:10:10:10:8:8:8:8:10:10:5:5:2:11:11:9:9:9:10:10:1:1:9:9:5:6:6:8:8:4:4:11:11:11:11:9:9:7:7:3:3:3:1:1:5:5:6:6:4:4:10:10:9:9:9:8:8:1:1:1:10:10:10:5:5:3:3:2:2:9:9:9:6:6:6:10:10:8:8:8:6:6:6:6:3:3:3:9:9:8:8:10:10:1:1:1:7:7:1:1:1:3:3:3:10:10:4:4:7:7:7:5:5:5:5:11:11:4:4:7:5:5:7:7:7:11:11:9:9:9:8:8:4:4:5:5:2:2:2:6:6:11:11:4:4:5:9:9:10:10:9:9:9:11:11:9:9:9:6:6:8:8:8:11:11:3:3:3:8:8:8:8:2:2:10:10:4:4:5:5:10:10:1:1:1:1:10:2:2:11:11:7:7:7:3:3:4:4:8:8:4:4:7:7:8:2:2:11:11:11:6:6:6:7:7:4:4:4:5:5:2:7:11:6:6:5:5:1:5:9:9:5:3:10:10:10:7:7:7:11:11:5:5:1:1:10:10:10:11:11:3:3:6:6:8:8:9:9:9:7:7:4:4:3:3:3:8:8:1:1:2:2:1:1:1:4:4:4:6:6:9:9:8:8:7:7:7:9:9:9:1:1:11:11:6:6:2:2:5:5:1:1:1:2:2:2:7:7:11:11:10:10:10:4:4:1:1:8:8:8:6:6:4:4:11:11:11:9:9:8:8:9:9:7:7:7:5:5:1:5:5:5:8:8:8:2:2:3:3:3:3:2:2:3:3:3:10:10:7:7:10:10:10:11:11:5:2:2:11:11:9:9:6:6:9:3:3:2:2:4:8:10:2:2:5:5:2:15:9:9:7:7:3:3:2:2:2:4:17:4:6:6:6:8:8:8:15:1:1:5:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:6:2:2:10:10:4:4:17:4:6:6:11:11:16:3:3:7:7:16:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:16:6:6:6:10:17:10:4:4:2:2:2:10:10:16:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:16:5:5:7:7:16:11:11:5:17:5:11:11:11:2:2:2:16:5:4:4:6:6:9:7:7:15:6:6:8:8:16:7:7:7:7:1:1:9:9:16:4:4:5:5:15:1:3:3:5:5:9:9:9:16:11:11:11:9:9:15:9:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:15:11:11:1:1:6:1:1:7:7:4:4:16:4:9:9:1:15:1:2:2:2:4:4:4:16:6:6:1:3:3:5:5:1:15:1:8:8:8:1:1:6:6:16:5:5:4:4:2:2:2:15:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:15:7:3:3:3:2:2:16:3:1:1:5:5:5:3:3:4:15:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:15:7:7:10:6:2:2:16:1:1:7:1:4:4:9:9:4:4:6:6:8:8:3:3:9:4:4:10:10:4:4:5:5:9:9:7:7:5:5:4:8:8:6:6:8:8:4:4:2:2:10:10:11:11:3:3:7:7:10:10:10:2:2:10:10:8:8:11:11:2:2:5:5:5:1:1:8:8:8:11:11:11:11:8:8:2:2:5:5:11:11:10:10:6:6:3:3:9:9:10:10:8:8:4:4:6:6:6:1:1:7:7:11:11:7:7:1:1:5:5:6:6:6:4:4:4:9:9:9:11:11:7:7:1:1:1:6:6:6:3:3:8:8:8:9:9:9:10:10:10:10:1:1:6:6:2:2:2:1:1:5:5:7:7:5:5:2:2:10:10:9:9:9:10:10:5:5:4:3:3:10:10:8:8:3:3:1:1:6:6:10:10:6:6:1:1:5:5:10:10:4:4:2:2:5:2:2:2:2:8:8:3:3:6:2:2:2:2:5:5:7:7:4:4:11:11:11:3:3:3:3:1:1:9:9:9:11:11:1:1:3:3:3:3:7:7:9:9:9:5:5:6:6:11:11:11:8:8:8:4:4:1:1:6:6:6:10:10:10:5:5:11:11:11:11:7:7:9:9:6:6:7:7:6:5:5:8:8:5:5:9:9:1:1:4:4:8:8:7:7:3:3:9:9:11:11:7:7:9:9:7:3:3:10:10:10:7:7:7:11:11:5:5:1:1:10:10:10:11:11:3:3:6:6:8:8:9:9:9:7:7:4:4:3:3:3:8:8:1:1:2:2:1:1:1:4:4:4:6:6:9:9:8:8:7:7:7:9:9:9:1:1:11:11:6:6:2:2:5:5:1:1:1:2:2:2:7:7:11:11:10:10:10:4:4:1:1:8:8:8:6:6:4:4:11:11:11:9:9:8:8:9:9:7:7:7:5:5:1:5:5:5:8:8:8:2:2:3:3:3:3:2:2:3:3:3:10:10:7:7:10:10:10:11:11:5:2:2:11:11:9:9:6:6:9:3:3:2:2:4:8:10:2:2:5:5:2:2:9:9:7:7:3:3:2:2:2:4:17:4:6:6:6:8:8:8:15:1:1:5:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:6:2:2:10:10:4:4:17:4:6:6:11:11:3:3:3:7:7:16:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:16:6:6:6:10:17:10:4:4:2:2:2:10:10:16:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:16:5:5:7:7:16:11:11:5:17:5:11:11:11:2:2:2:16:5:4:4:6:6:9:7:7:15:6:6:8:8:16:7:7:7:7:1:1:9:9:16:4:4:5:5:15:1:3:3:5:5:9:9:9:16:11:11:11:9:9:15:9:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:15:11:11:1:1:6:1:1:7:7:4:4:16:4:9:9:1:15:1:2:2:2:4:4:4:16:6:6:1:3:3:5:5:1:15:1:8:8:8:1:1:6:6:16:5:5:4:4:2:2:2:15:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:15:7:3:3:3:2:2:3:3:1:1:5:5:5:3:3:4:15:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:15:7:7:10:6:2:2:2:1:1:7:1:11:11:10:10:11:11:7:7:3:3:9:9:9:9:10:10:10:8:8:10:10:2:2:5:5:1:1:1:1:10:10:11:11:5:5:10:10:10:9:9:4:4:9:6:6:6:5:5:11:11:5:5:5:10:10:10:8:8:5:5:8:8:4:4:8:8:8:2:2:5:5:8:8:1:1:1:11:11:7:7:5:5:2:2:11:11:11:2:2:7:7:4:4:8:8:8:7:7:4:4:6:6:10:10:10:7:7:7:10:10:10:6:6:9:9:8:8:9:9:9:8:8:8:6:6:9:9:3:3:5:5:5:2:2:11:11:1:1:2:2:8:8:5:5:3:3:3:6:6:8:8:11:11:10:10:3:3:2:2:4:4:5:5:5:8:8:2:2:5:5:5:7:7:6:6:6:9:9:9:11:11:1:1:7:7:8:8:10:10:10:11:11:11:6:6:7:7:1:1:6:6:6:4:4:1:1:4:4:5:5:1:1:3:3:4:4:2:2:10:10:10:1:1:1:2:2:1:1:1:1:4:4:9:9:9:9:7:7:7:3:3:11:11:11:4:4:7:7:5:5:3:3:6:6:9:9:4:4:4:8:10:4:4:3:3:3:3:6:6:2:2:3:3:1:2:2:6:6:6:7:7:3:3:3:2:7:9:9:9:8:8:3:6:6:9:9:6:6:9:9:3:10:10:10:7:7:7:11:11:5:5:1:1:10:10:10:11:11:3:3:6:6:8:8:9:9:9:7:7:4:4:3:3:3:8:8:1:1:2:2:1:1:1:4:4:4:6:6:9:9:8:8:7:7:7:9:9:9:1:1:11:11:6:6:2:2:5:5:1:1:1:2:2:2:7:7:11:11:10:10:10:4:4:1:1:8:8:8:6:6:4:4:11:11:11:9:9:8:8:9:9:7:7:7:5:5:1:5:5:5:8:8:8:2:2:3:3:3:3:2:2:3:3:3:10:10:7:7:10:10:10:11:11:5:2:2:11:11:9:9:6:6:9:3:3:2:2:4:8:10:2:2:5:5:2:2:9:9:7:7:3:3:2:2:2:4:17:4:6:6:6:8:8:8:8:1:1:5:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:6:2:2:10:10:4:4:17:4:6:6:11:11:3:3:3:7:7:3:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:16:6:6:6:10:17:10:4:4:2:2:2:10:10:16:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:16:5:5:7:7:16:11:11:5:17:5:11:11:11:2:2:2:16:5:4:4:6:6:9:7:7:15:6:6:8:8:16:7:7:7:7:1:1:9:9:16:4:4:5:5:15:1:3:3:5:5:9:9:9:16:11:11:11:9:9:15:9:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:15:11:11:1:1:6:1:1:7:7:4:4:16:4:9:9:1:15:1:2:2:2:4:4:4:16:6:6:1:3:3:5:5:1:15:1:8:8:8:1:1:6:6:6:5:5:4:4:2:2:2:15:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:15:7:3:3:3:2:2:3:3:1:1:5:5:5:3:3:4:15:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:15:7:7:10:6:2:2:2:1:1:7:1:11:11:2:2:2:5:5:4:4:6:6:3:3:7:7:6:6:5:5:5:8:8:5:5:9:9:9:6:6:1:1:2:2:3:3:2:2:4:2:2:6:6:10:10:10:9:9:9:2:2:4:5:5:5:3:3:2:2:2:10:10:5:5:2:2:11:11:4:4:5:5:7:7:5:5:1:1:8:8:3:3:1:1:8:8:7:7:7:3:3:3:6:6:6:10:10:4:4:11:11:10:10:11:11:9:9:10:10:2:2:1:1:1:3:3:11:11:11:6:6:6:8:8:8:1:1:10:10:7:7:3:3:4:4:10:10:7:7:5:5:4:4:4:7:7:11:5:5:7:7:1:1:1:9:9:11:11:4:4:6:6:9:9:7:4:8:8:8:1:1:8:8:6:6:10:10:11:11:11:3:3:3:9:9:9:7:7:9:9:9:3:3:3:5:5:5:1:1:1:10:10:7:7:7:7:2:2:4:4:8:8:6:6:11:11:2:2:8:8:8:8:7:7:4:4:9:9:9:11:11:4:4:11:11:2:2:10:10:1:1:1:7:10:10:1:1:8:8:3:3:3:8:8:8:6:6:8:8:10:10:10:6:6:9:9:8:8:9:9:6:6:10:10:4:4:6:6:9:9:6:6:4:10:10:8:1:2:5:5:11:11:5:5:9:9:5:5:3:9:5:8:8:8:7:7:5:5:8:8:6:6:9:9:5:5:8:8:3:3:8:8:4:4:2:2:2:3:3:10:10:10:9:9:9:1:1:1:8:8:7:7:7:4:4:4:4:10:10:3:3:5:5:8:8:2:2:10:10:1:1:8:8:7:7:7:7:9:9:10:10:10:3:3:11:11:11:2:2:1:11:11:3:3:3:4:4:1:1:1:11:11:7:7:1:1:9:9:2:2:2:1:1:4:4:6:6:7:7:7:2:2:7:9:9:11:11:6:6:9:9:9:1:1:11:11:11:3:3:11:11:2:2:6:6:10:10:5:5:5:2:10:10:10:3:3:6:6:11:9:5:2:2:5:5:2:2:9:9:7:7:3:3:2:2:2:4:17:4:6:6:6:8:8:8:8:1:1:5:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:6:2:2:10:10:4:4:17:4:6:6:11:11:3:3:3:7:7:3:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:16:6:6:6:10:17:10:4:4:2:2:2:10:10:16:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:16:5:5:7:7:16:11:11:5:17:5:11:11:11:2:2:2:16:5:4:4:6:6:9:7:7:15:6:6:8:8:16:7:7:7:7:1:1:9:9:16:4:4:5:5:15:1:3:3:5:5:9:9:9:16:11:11:11:9:9:15:9:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:15:11:11:1:1:6:1:1:7:7:4:4:16:4:9:9:1:15:1:2:2:2:4:4:4:16:6:6:1:3:3:5:5:1:15:1:8:8:8:1:1:6:6:6:5:5:4:4:2:2:2:15:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:15:7:3:3:3:2:2:3:3:1:1:5:5:5:3:3:4:15:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:15:7:7:10:6:2:2:2:1:1:7:1:5:5:7:7:7:7:4:4:4:2:2:3:3:11:11:8:8:10:10:6:6:3:3:3:7:7:7:2:2:8:11:10:10:2:9:9:4:4:4:5:5:9:9:10:10:9:9:3:3:7:7:7:10:10:10:10:6:6:11:11:6:6:6:9:8:8:9:9:1:1:1:8:8:1:1:9:9:5:9:5:5:6:6:4:4:10:10:4:4:4:6:6:11:11:7:7:7:4:4:3:3:8:8:8:9:9:8:8:8:3:3:3:7:7:7:2:2:7:7:7:2:2:1:1:3:3:3:8:8:5:5:4:4:2:2:10:5:5:6:6:6:4:4:3:3:5:5:8:8:9:9:1:1:10:10:9:9:6:6:2:2:10:10:6:6:1:1:1:6:6:4:4:4:11:11:9:9:9:9:8:8:8:5:5:6:6:11:6:6:6:11:11:11:11:7:7:5:5:11:11:10:10:11:11:9:9:10:10:1:1:10:10:9:9:9:5:5:11:11:2:2:3:7:7:1:1:8:10:10:5:5:1:1:11:11:4:4:4:2:2:3:3:3:11:11:5:5:6:6:3:3:1:1:10:10:10:10:5:5:8:8:8:1:1:8:8:1:1:2:2:8:8:8:4:4:2:2:2:2:6:6:5:5:8:6:11:9:9:9:3:3:5:5:7:7:10:5:2:2:1:10:10:10:10:9:9:6:6:6:7:7:7:9:2:2:6:6:8:8:3:3:5:5:11:11:8:8:3:3:4:4:4:1:1:2:1:1:7:7:9:9:5:5:6:6:2:2:1:1:7:7:11:11:11:8:2:2:1:1:11:11:11:11:3:3:3:4:4:10:10:11:11:2:2:7:7:7:8:8:8:10:10:2:2:2:2:7:7:1:1:6:6:3:3:3:4:4:9:9:10:10:8:8:9:9:9:3:3:3:11:11:5:5:11:11:9:9:8:8:1:1:1:5:5:5:10:10:8:8:2:2:4:4:7:7:7:10:10:8:5:9:9:9:1:1:3:3:10:4:6:2:2:5:5:2:2:9:9:7:7:3:3:2:2:2:4:17:4:6:6:6:8:8:8:8:1:1:5:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:6:2:2:10:10:4:4:17:4:6:6:11:11:3:3:3:7:7:3:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:16:6:6:6:10:17:10:4:4:2:2:2:10:10:16:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:16:5:5:7:7:16:11:11:5:17:5:11:11:11:2:2:2:16:5:4:4:6:6:9:7:7:15:6:6:8:8:16:7:7:7:7:1:1:9:9:16:4:4:5:5:15:1:3:3:5:5:9:9:9:16:11:11:11:9:9:15:9:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:15:11:11:1:1:6:1:1:7:7:4:4:16:4:9:9:1:15:1:2:2:2:4:4:4:16:6:6:1:3:3:5:5:1:15:1:8:8:8:1:1:6:6:6:5:5:4:4:2:2:2:15:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:15:7:3:3:3:2:2:3:3:1:1:5:5:5:3:3:4:15:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:15:7:7:10:6:2:2:2:1:1:7:1:9:9:8:8:10:10:10:5:5:3:3:9:9:6:4:8:8:8:10:10:1:1:11:11:11:6:6:6:3:3:9:9:9:3:3:3:7:7:6:8:8:4:4:1:1:5:5:5:5:11:11:11:7:7:7:11:11:1:1:1:9:9:2:2:11:11:1:1:11:11:4:4:2:2:3:3:3:5:5:2:2:2:2:3:3:6:6:3:3:4:4:3:3:3:7:7:2:2:11:11:10:10:1:1:6:6:8:8:2:2:10:10:10:8:8:6:6:9:9:10:10:5:8:8:10:10:10:4:4:7:1:1:1:3:3:5:5:8:8:3:3:3:7:7:4:4:7:3:3:2:2:5:5:5:4:4:1:1:4:4:4:1:1:1:5:5:5:2:2:9:9:9:7:7:11:11:2:2:2:6:6:6:6:1:1:8:8:3:11:11:5:5:5:6:6:6:2:2:2:7:7:9:9:5:5:7:7:10:10:8:8:8:6:6:10:9:9:11:11:7:7:10:10:4:4:8:8:6:6:8:10:10:8:8:8:2:2:4:4:9:9:9:9:10:10:7:7:7:6:6:8:8:6:6:10:10:9:9:6:7:7:7:10:10:5:5:6:6:8:8:10:10:1:1:4:4:4:9:9:2:11:11:6:5:5:9:9:9:9:1:1:4:4:11:11:5:5:5:11:5:5:5:11:11:9:9:10:10:4:4:2:2:8:8:8:8:11:11:11:4:2:2:2:2:10:10:10:1:1:8:8:8:11:11:11:11:9:9:3:3:9:9:6:6:5:5:8:8:7:7:7:1:1:2:2:2:1:1:5:5:11:11:10:10:4:4:8:8:9:9:6:6:3:3:4:4:4:4:5:5:7:7:7:2:2:3:3:3:5:5:3:3:10:10:10:1:1:6:6:2:2:2:7:7:11:11:11:9:9:1:1:6:6:3:3:9:9:9:9:3:3:1:1:8:8:8:3:3:10:10:7:11:6:6:7:7:1:7:7:7:7:10:10:1:1:8:2:9:10:4:2:2:5:5:2:2:9:9:7:7:3:3:2:2:2:4:17:4:6:6:6:8:8:8:8:1:1:5:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:6:2:2:10:10:4:4:17:4:6:6:11:11:3:3:3:7:7:3:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:16:6:6:6:10:17:10:4:4:2:2:2:10:10:16:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:16:5:5:7:7:16:11:11:5:17:5:11:11:11:2:2:2:5:5:4:4:6:6:9:7:7:15:6:6:8:8:16:7:7:7:7:1:1:9:9:9:4:4:5:5:1:1:3:3:5:5:9:9:9:16:11:11:11:9:9:15:9:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:15:11:11:1:1:6:1:1:7:7:4:4:16:4:9:9:1:15:1:2:2:2:4:4:4:16:6:6:1:3:3:5:5:1:15:1:8:8:8:1:1:6:6:6:5:5:4:4:2:2:2:15:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:15:7:3:3:3:2:2:3:3:1:1:5:5:5:3:3:4:15:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:15:7:7:10:6:2:2:2:1:1:7:1:5:5:7:7:7:7:4:4:4:2:2:3:3:11:11:8:8:10:10:6:6:3:3:3:7:7:7:2:2:8:11:10:10:2:9:9:4:4:4:5:5:9:9:10:10:9:9:3:3:7:7:7:10:10:10:10:6:6:11:11:6:6:6:9:8:8:9:9:1:1:1:8:8:1:1:9:9:5:9:5:5:6:6:4:4:10:10:4:4:4:6:6:11:11:7:7:7:4:4:3:3:8:8:8:9:9:8:8:8:3:3:3:7:7:7:2:2:7:7:7:2:2:1:1:3:3:3:8:8:5:5:4:4:2:2:10:5:5:6:6:6:4:4:3:3:5:5:8:8:9:9:1:1:10:10:9:9:6:6:2:2:10:10:6:6:1:1:1:6:6:4:4:4:11:11:9:9:9:9:8:8:8:5:5:6:6:11:6:6:6:11:11:11:11:7:7:5:5:11:11:10:10:11:11:9:9:10:10:1:1:10:10:9:9:9:5:5:11:11:2:2:3:7:7:1:1:8:10:10:5:5:1:1:11:11:4:4:4:2:2:3:3:3:11:11:5:5:6:6:3:3:1:1:10:10:10:10:5:5:8:8:8:1:1:8:8:1:1:2:2:8:8:8:4:4:2:2:2:2:6:6:5:5:8:6:11:9:9:9:3:3:5:5:7:7:10:5:2:2:1:9:9:8:8:2:2:10:10:4:4:3:3:1:1:11:11:11:11:10:10:8:8:8:8:6:6:7:7:7:3:3:7:7:1:1:1:3:3:11:11:4:4:4:11:11:9:9:2:2:2:2:3:3:10:10:10:8:8:8:10:10:7:7:10:10:1:1:9:9:9:1:1:6:6:7:7:1:1:8:8:9:9:7:7:11:11:9:9:2:2:2:10:10:11:11:2:2:5:5:8:8:7:8:8:3:3:3:5:5:5:3:3:10:10:2:2:3:3:6:4:4:6:6:6:5:5:1:1:1:9:9:2:2:7:7:4:4:11:11:11:9:9:5:5:6:6:4:7:1:5:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -143,6 +151,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -156,20 +171,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -212,9 +213,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -226,9 +227,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -247,13 +245,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -549,31 +540,31 @@
       <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>11</v>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="4"/>
@@ -593,7 +584,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -610,7 +601,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -627,7 +618,7 @@
         <v>12</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -644,7 +635,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -661,11 +652,11 @@
         <v>12</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA282FA-7F24-46EA-A39E-BF355AB9CD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoller" sheetId="1" r:id="rId1"/>
@@ -33,19 +27,18 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>滚轴ID，起始，结尾;
@@ -100,29 +93,35 @@
     <t>elements</t>
   </si>
   <si>
-    <t>1,1&amp;300;2,301&amp;600;3,601&amp;750;4,751&amp;1050;5,1051&amp;1350;6,1351&amp;1500;7,1501&amp;1800;8,1801&amp;2100;9,2101&amp;2250;10,2251&amp;2550;11,2551&amp;2850;12,2851&amp;3000;13,3001&amp;3300;14,3301&amp;3600;15,3601&amp;3750;16,3751&amp;4050;17,4051&amp;4350;18,4351&amp;4500;19,4501&amp;4800;20,4801&amp;5100;21,5101&amp;5250</t>
-  </si>
-  <si>
-    <t>6:6:2:2:3:17:4:4:2:2:19:8:4:4:6:6:17:2:2:8:8:19:9:9:9:8:8:11:11:4:4:19:1:1:1:4:19:1:1:7:7:19:1:3:3:19:2:3:3:17:2:6:6:3:3:3:21:3:3:3:6:6:7:7:2:2:3:21:19:6:6:6:5:5:20:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:21:1:1:3:1:1:20:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:21:11:1:1:6:6:7:7:2:2:4:4:4:4:20:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:20:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:20:7:4:4:9:9:21:3:3:3:5:5:8:8:2:17:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:21:4:4:1:8:8:17:10:10:10:20:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:20:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:17:10:10:11:11:1:1:6:6:7:8:8:10:10:10:9:9:10:10:4:4:5:5:11:11:1:1:4:4:6:6:8:8:8:5:5:10:10:10:11:11:11:9:9:3:3:3:1:1:4:4:4:7:7:11:11:11:11:2:2:1:1:5:5:6:6:6:7:8:8:5:5:11:11:11:6:6:6:8:8:1:1:8:8:10:10:2:2:4:4:4:7:7:5:5:5:5:11:11:9:9:9:8:8:11:11:8:8:6:6:10:10:6:6:4:4:4:8:8:6:1:1:1:8:8:10:10:11:4:4:7:7:7:9:9:10:10:10:6:6:11:11:11:2:2:2:7:7:8:8:8:3:3:3:2:2:2:5:5:5:6:6:6:7:7:7:7:10:10:10:9:9:9:6:6:11:11:1:1:10:10:5:5:3:3:2:2:2:8:8:8:8:10:10:7:7:1:1:11:11:11:11:5:5:5:8:8:10:10:7:7:5:5:9:9:10:10:8:8:8:4:4:11:11:11:8:8:8:7:7:9:9:11:11:7:7:9:9:7:9:9:9:11:11:7:7:9:9:4:4:6:6:9:9:6:6:4:7:7:4:4:9:9:9:7:7:9:9:10:10:6:6:6:5:9:9:10:10:2:2:10:10:2:11:11:10:10:4:11:11:11:3:11:10:10:10:3:3:7:1:3:9:9:10:10:11:11:11:9:9:9:8:8:10:10:9:9:10:10:11:11:8:8:8:11:11:10:10:8:8:10:10:8:8:9:9:10:10:11:11:11:10:10:10:9:9:8:8:11:11:11:9:9:8:8:9:9:8:8:9:9:10:10:9:9:11:11:8:8:9:9:11:11:8:8:11:10:10:10:8:8:8:9:9:10:10:8:8:8:9:9:8:8:8:9:9:9:8:8:10:10:11:11:8:8:10:10:8:8:11:11:10:10:9:9:11:11:11:8:8:10:10:11:11:9:10:10:9:9:9:11:11:8:8:10:10:10:9:9:11:11:9:9:11:11:9:9:11:11:8:8:6:6:2:2:3:17:4:4:2:2:19:8:4:4:6:6:6:2:2:8:8:19:9:9:9:8:8:11:11:4:4:19:1:1:1:4:19:1:1:7:7:19:1:3:3:19:2:3:3:17:2:6:6:3:3:3:21:3:3:3:6:6:7:7:2:2:3:21:19:6:6:6:5:5:20:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:21:1:1:3:1:1:20:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:21:11:1:1:6:6:7:7:2:2:4:4:4:4:20:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:20:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:20:7:4:4:9:9:21:3:3:3:5:5:8:8:2:17:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:21:4:4:1:8:8:17:10:10:10:20:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:20:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:17:2:2:2:6:6:7:7:7:11:11:6:6:10:10:3:3:3:5:5:5:10:10:10:5:5:5:11:11:8:8:7:7:7:1:1:6:6:9:2:2:8:8:4:4:4:7:7:7:6:6:2:2:11:11:2:2:2:11:11:2:2:8:8:9:9:9:4:4:7:10:10:11:11:5:5:10:10:10:9:9:7:6:6:1:1:3:3:7:7:3:3:5:5:6:6:6:9:9:7:7:7:6:6:7:7:10:10:10:10:9:9:10:10:9:9:9:3:3:3:7:7:2:2:7:7:7:11:11:1:1:7:7:8:8:8:5:5:11:11:5:5:4:4:10:10:5:5:9:9:4:4:3:3:9:9:9:11:11:11:8:8:9:9:9:2:4:4:6:4:4:4:11:11:2:2:11:11:10:10:5:5:5:5:3:3:3:8:1:1:10:10:10:10:4:4:8:8:8:1:1:8:8:1:1:2:2:1:1:8:8:6:6:6:6:5:5:3:3:3:3:4:4:5:5:10:10:9:9:1:1:11:11:6:6:9:9:9:11:11:8:8:8:7:7:1:1:4:4:1:1:7:7:8:8:10:10:6:6:6:11:11:11:11:8:8:8:8:10:10:4:4:9:9:4:4:6:6:9:9:6:6:6:7:7:4:5:5:5:8:8:5:5:5:4:4:4:1:2:2:3:9:9:10:10:11:11:11:9:9:9:8:8:10:10:9:9:10:10:11:11:8:8:8:11:11:10:10:8:8:10:10:8:8:9:9:10:10:11:11:11:10:10:10:9:9:8:8:11:11:11:9:9:8:8:9:9:8:8:9:9:10:10:9:9:11:11:8:8:9:9:11:11:8:8:11:10:10:10:8:8:8:9:9:10:10:8:8:8:9:9:8:8:8:9:9:9:8:8:10:10:11:11:8:8:10:10:8:8:11:11:10:10:9:9:11:11:11:8:8:10:10:11:11:9:10:10:9:9:9:11:11:8:8:10:10:10:9:9:11:11:9:9:11:11:9:9:11:11:8:8:6:6:2:2:3:3:4:4:2:2:19:8:4:4:6:6:6:2:2:8:8:19:9:9:9:8:8:11:11:4:4:19:1:1:1:4:19:1:1:7:7:19:1:3:3:19:2:3:3:17:2:6:6:3:3:3:21:3:3:3:6:6:7:7:2:2:3:21:19:6:6:6:5:5:20:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:21:1:1:3:1:1:20:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:21:11:1:1:6:6:7:7:2:2:4:4:4:4:20:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:20:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:20:7:4:4:9:9:21:3:3:3:5:5:8:8:2:17:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:21:4:4:1:8:8:17:10:10:10:20:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:20:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:17:10:10:5:5:2:2:9:9:9:5:5:5:4:4:4:8:8:10:10:7:7:11:11:3:3:5:5:6:6:7:7:7:7:1:1:5:5:6:6:6:4:4:9:9:9:10:10:10:3:3:6:6:6:8:8:6:6:8:8:2:2:1:1:10:10:10:10:6:6:6:7:7:4:4:1:1:7:7:5:5:6:6:4:4:10:10:3:3:3:2:2:2:11:11:8:8:8:8:1:7:7:3:3:5:5:3:3:10:10:10:3:3:11:11:6:6:6:6:1:1:8:8:1:1:1:11:11:7:7:9:9:7:7:7:2:2:2:11:11:5:5:5:1:1:1:5:5:10:1:1:7:7:11:11:9:9:10:10:10:2:2:3:3:5:5:9:9:7:7:4:4:4:1:7:7:10:10:1:1:8:8:9:9:4:4:5:5:7:7:9:9:11:11:6:6:8:8:6:6:8:8:6:6:8:8:2:2:10:10:2:2:6:6:6:4:4:10:10:10:9:9:9:7:7:7:9:9:11:11:11:5:5:5:8:8:6:6:3:3:3:2:2:2:9:9:9:7:7:7:4:4:3:3:8:8:9:9:1:11:11:8:8:11:11:11:5:5:5:5:11:11:11:10:10:9:9:9:8:8:2:2:4:4:2:2:5:9:4:4:4:8:8:4:4:2:2:4:4:4:10:9:9:10:10:11:11:11:9:9:9:8:8:10:10:9:9:10:10:11:11:8:8:8:11:11:10:10:8:8:10:10:8:8:9:9:10:10:11:11:11:10:10:10:9:9:8:8:11:11:11:9:9:8:8:9:9:8:8:9:9:10:10:9:9:11:11:8:8:9:9:11:11:8:8:11:10:10:10:8:8:8:9:9:10:10:8:8:8:9:9:8:8:8:9:9:9:8:8:10:10:11:11:8:8:10:10:8:8:11:11:10:10:9:9:11:11:11:8:8:10:10:11:11:9:10:10:9:9:9:11:11:8:8:10:10:10:9:9:11:11:9:9:11:11:9:9:11:11:8:8:6:6:2:2:3:3:4:4:2:2:8:8:4:4:6:6:6:2:2:8:8:19:9:9:9:8:8:11:11:4:4:19:1:1:1:4:19:1:1:7:7:19:1:3:3:19:2:3:3:17:2:6:6:3:3:3:21:3:3:3:6:6:7:7:2:2:3:21:19:6:6:6:5:5:5:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:6:1:1:3:1:1:20:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:21:11:1:1:6:6:7:7:2:2:4:4:4:4:20:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:20:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:20:7:4:4:9:9:21:3:3:3:5:5:8:8:2:17:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:21:4:4:1:8:8:17:10:10:10:20:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:20:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:17:4:4:4:10:10:1:1:9:9:7:7:7:5:5:6:6:4:4:7:7:10:10:5:5:4:4:10:10:10:9:9:9:11:11:9:9:7:7:9:9:9:8:8:6:6:6:6:7:7:6:6:7:7:7:1:1:1:2:2:1:1:8:8:8:2:2:6:6:6:1:1:3:3:1:1:3:3:3:3:10:10:11:11:7:7:11:11:9:9:4:4:4:10:10:10:10:9:9:4:4:5:5:2:2:5:5:2:2:4:4:1:1:1:6:6:7:7:8:8:8:5:5:5:6:6:6:4:4:8:8:6:6:6:9:9:9:10:10:5:7:7:8:8:8:2:2:8:8:4:4:8:8:8:5:5:7:7:2:2:2:6:6:7:7:3:3:6:6:5:5:9:9:10:10:10:5:5:5:6:6:4:4:1:1:10:10:11:11:7:7:3:3:5:5:10:10:10:8:8:1:1:7:7:10:10:8:8:6:2:2:3:3:5:5:11:11:3:3:4:4:11:11:7:7:2:2:2:8:8:11:11:2:2:2:9:9:9:1:1:11:11:5:11:11:11:9:9:11:11:9:11:11:8:8:10:10:10:10:6:6:6:11:11:8:8:4:4:2:2:9:9:8:8:5:5:7:9:9:9:1:6:4:4:2:2:4:4:5:5:7:7:3:3:5:5:3:3:10:3:3:11:11:10:10:8:8:8:8:11:11:10:10:11:11:9:9:8:8:11:11:11:8:8:9:9:8:8:11:11:11:8:8:11:11:10:10:9:9:9:8:8:10:10:10:9:9:11:11:8:8:10:10:10:9:9:10:10:9:9:8:8:9:10:10:10:10:8:8:10:10:10:9:9:9:10:10:10:11:11:8:8:8:8:9:9:9:9:11:11:11:10:10:8:8:10:10:10:8:8:9:9:9:8:8:10:10:9:9:8:8:11:11:10:10:9:9:11:11:9:9:9:11:11:8:8:9:9:8:8:9:9:10:10:8:8:11:11:11:9:9:9:11:11:9:9:11:11:11:8:8:6:6:2:2:3:3:4:4:2:2:8:8:4:4:6:6:6:2:2:8:8:19:9:9:9:8:8:11:11:4:4:19:1:1:1:4:19:1:1:7:7:19:1:3:3:19:2:3:3:17:2:6:6:3:3:3:21:3:3:3:6:6:7:7:2:2:3:21:19:6:6:6:5:5:5:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:6:1:1:3:1:1:20:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:21:11:1:1:6:6:7:7:2:2:4:4:4:4:20:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:20:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:20:7:4:4:9:9:21:3:3:3:5:5:8:8:2:17:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:21:4:4:1:8:8:17:10:10:10:20:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:20:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:17:2:2:11:11:5:5:1:1:1:11:11:11:4:4:4:8:8:4:4:10:10:7:7:5:5:9:9:9:1:1:2:2:3:3:10:10:10:9:9:6:6:8:8:11:10:10:1:1:9:9:1:1:10:2:2:3:3:3:11:11:5:5:9:9:5:5:10:10:10:6:8:8:5:5:5:8:8:2:2:8:8:10:10:9:9:3:3:3:3:7:7:6:6:9:9:7:7:7:4:4:5:5:1:7:7:7:6:6:5:5:5:11:11:11:6:6:9:9:7:7:2:2:8:9:3:3:5:5:5:5:6:6:6:2:2:4:4:11:11:8:8:2:2:2:10:10:9:9:1:1:4:4:5:5:7:7:7:7:3:3:10:10:1:1:8:8:8:2:2:4:4:4:7:7:7:9:9:9:9:7:7:2:2:11:11:11:11:9:9:8:8:6:6:11:11:4:4:8:8:6:8:8:8:5:3:3:11:11:11:5:5:4:4:9:9:9:10:10:7:1:1:1:1:8:8:11:11:5:5:3:3:3:10:10:4:4:4:4:10:10:6:6:7:7:2:2:2:8:8:7:7:6:6:6:10:10:6:10:10:6:6:4:4:3:3:6:6:6:6:1:1:4:4:7:7:7:7:8:8:8:1:5:5:9:5:2:2:4:4:11:10:10:9:9:6:6:7:2:10:6:11:11:9:9:8:8:8:10:10:11:11:8:8:8:9:9:8:8:11:11:8:10:10:8:8:8:10:10:10:11:11:8:8:8:8:10:10:9:9:8:8:9:9:10:10:10:9:9:9:10:10:9:9:9:11:11:11:10:10:11:11:10:10:9:9:9:11:11:11:8:8:8:11:11:8:8:8:9:9:10:10:9:9:9:11:11:9:9:8:8:11:11:9:9:9:11:11:9:9:10:10:10:8:8:8:8:11:11:8:8:9:9:8:8:11:11:10:10:10:8:8:8:8:9:9:8:8:9:9:10:10:10:10:11:11:9:9:10:10:11:11:11:11:9:9:10:10:11:9:10:6:6:2:2:3:3:4:4:2:2:8:8:4:4:6:6:6:2:2:8:8:19:9:9:9:8:8:11:11:4:4:19:1:1:1:4:19:1:1:7:7:19:1:3:3:19:2:3:3:17:2:6:6:3:3:3:21:3:3:3:6:6:7:7:2:2:3:21:19:6:6:6:5:5:5:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:6:1:1:3:1:1:20:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:21:11:1:1:6:6:7:7:2:2:4:4:4:4:20:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:20:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:20:7:4:4:9:9:21:3:3:3:5:5:8:8:2:17:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:21:4:4:1:8:8:17:10:10:10:20:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:20:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:17:11:11:11:7:7:8:8:8:7:7:7:8:8:9:9:10:10:2:2:6:6:6:10:10:7:7:1:1:9:9:1:1:1:6:6:6:8:8:4:4:4:11:11:2:2:7:7:4:4:4:11:11:11:8:3:3:2:2:9:9:10:10:10:10:8:8:8:5:5:5:7:7:7:7:6:6:9:3:3:3:4:4:11:11:11:9:9:4:4:8:8:8:8:2:2:11:11:6:6:6:7:7:10:10:8:8:9:9:7:7:8:8:3:3:6:6:6:11:11:11:11:1:1:1:8:8:1:1:1:7:7:10:10:8:8:8:10:10:10:9:9:9:5:5:1:9:9:4:4:2:2:11:11:10:10:2:2:9:9:10:10:2:2:6:6:4:4:10:10:4:4:2:2:2:11:11:11:11:3:3:3:6:6:5:5:5:10:10:10:10:3:3:9:5:5:6:6:6:9:9:10:4:4:2:2:7:7:9:9:6:6:7:7:5:5:2:2:2:1:1:1:7:7:9:9:1:1:5:5:5:9:9:6:6:6:9:9:5:5:5:7:7:5:5:5:2:2:9:3:3:10:10:3:3:3:5:5:1:1:8:8:7:7:6:6:11:11:10:10:1:1:7:7:5:4:4:5:5:5:4:4:4:6:6:5:5:3:3:4:4:4:5:8:8:3:8:8:4:4:2:8:8:11:11:10:10:9:9:8:8:8:8:10:10:9:9:11:11:11:8:8:10:10:10:8:8:10:10:11:11:11:11:10:10:9:9:11:11:11:11:8:8:9:9:8:8:10:10:8:8:9:9:11:11:10:10:10:8:8:9:9:11:11:9:9:10:10:9:9:9:8:8:8:9:9:11:11:11:10:10:11:11:9:9:8:8:11:11:11:9:9:10:10:9:9:11:11:10:10:11:11:8:8:11:11:11:8:8:10:10:8:8:8:8:9:9:8:8:10:10:8:8:10:8:8:10:10:9:9:9:10:10:10:8:8:8:9:9:9:11:11:9:9:10:9:9:9:11:9:9:6:6:2:2:3:3:4:4:2:2:8:8:4:4:6:6:6:2:2:8:8:19:9:9:9:8:8:11:11:4:4:19:1:1:1:4:19:1:1:7:7:19:1:3:3:2:2:3:3:17:2:6:6:3:3:3:21:3:3:3:6:6:7:7:2:2:3:21:6:6:6:6:5:5:5:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:6:1:1:3:1:1:1:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:11:11:1:1:6:6:7:7:2:2:4:4:4:4:20:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:20:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:20:7:4:4:9:9:21:3:3:3:5:5:8:8:2:17:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:21:4:4:1:8:8:17:10:10:10:20:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:20:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:6:2:2:11:11:5:5:1:1:1:11:11:11:4:4:4:8:8:4:4:10:10:7:7:5:5:9:9:9:1:1:2:2:3:3:10:10:10:9:9:6:6:8:8:11:10:10:1:1:9:9:1:1:10:2:2:3:3:3:11:11:5:5:9:9:5:5:10:10:10:6:8:8:5:5:5:8:8:2:2:8:8:10:10:9:9:3:3:3:3:7:7:6:6:9:9:7:7:7:4:4:5:5:1:7:7:7:6:6:5:5:5:11:11:11:6:6:9:9:7:7:2:2:8:9:3:3:5:5:5:5:6:6:6:2:2:4:4:11:11:8:8:2:2:2:10:10:9:9:1:1:4:4:5:5:7:7:7:7:3:3:10:10:1:1:8:8:8:2:2:4:4:4:7:7:7:9:9:9:9:7:7:2:2:11:11:11:11:9:9:8:8:6:6:11:11:4:4:8:8:6:8:8:8:5:3:3:11:11:11:5:5:4:4:9:9:9:10:10:7:1:1:1:1:8:8:11:11:5:5:3:3:3:10:10:4:4:4:4:10:10:6:6:7:7:2:2:2:8:8:7:7:6:6:6:10:10:6:10:10:6:6:4:4:3:3:6:6:6:6:1:1:4:4:7:7:7:7:8:8:8:1:5:5:9:5:2:2:4:4:11:10:10:9:9:6:6:7:2:10:6:11:11:11:11:9:9:10:10:10:8:8:11:11:10:10:9:9:11:11:10:10:10:9:9:11:11:10:10:8:8:9:9:8:8:9:9:10:10:8:8:9:9:9:11:11:9:9:9:9:10:10:9:9:8:8:10:10:9:9:8:8:8:11:11:10:10:8:8:10:10:8:8:10:10:8:8:8:10:10:8:8:10:10:11:11:9:9:11:11:10:10:9:9:8:8:11:11:8:8:8:9:9:8:8:8:9:9:11:11:9:9:9:8:8:11:11:11:10:10:10:11:11:11:11:8:8:11:9:9:10:10:8:8:11:11:9:9:11:11:8:8:8:9:9:9:9:11:10:10:8:</t>
-  </si>
-  <si>
-    <t>9:9:10:7:7:7:11:11:6:6:12:10:10:10:20:21:6:6:6:2:2:12:2:2:10:10:20:2:2:9:9:5:12:5:5:10:10:10:12:2:10:11:11:12:2:2:9:9:5:17:5:5:20:3:3:12:6:6:3:3:3:21:5:5:4:4:12:4:7:7:6:20:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:12:6:6:10:10:8:8:17:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:21:1:1:5:5:9:12:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:12:8:2:2:2:17:3:4:4:4:19:2:2:3:3:12:10:10:10:8:8:1:1:12:7:7:8:8:4:12:11:11:7:7:12:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:19:8:8:8:17:6:6:8:8:12:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:12:5:4:4:4:1:1:21:7:7:7:12:4:4:8:8:17:10:1:1:20:2:2:4:9:9:9:19:1:8:11:17:11:11:3:13:3:8:11:13:11:10:10:13:11:9:9:13:6:6:6:13:9:11:11:13:9:9:9:13:7:7:7:13:6:6:8:13:8:5:5:13:11:4:4:13:4:7:7:13:9:9:2:13:2:6:6:13:6:10:10:13:10:9:9:13:1:1:8:13:8:8:10:13:10:10:10:13:2:2:9:13:9:9:6:13:6:11:11:14:7:7:9:14:9:9:3:14:3:1:1:14:4:4:1:14:4:11:11:14:10:10:11:14:11:6:6:14:9:9:9:14:10:10:10:14:10:11:11:14:9:9:11:14:11:8:8:14:8:7:7:14:11:11:1:14:1:11:10:14:10:8:8:14:3:3:7:14:7:1:1:14:10:10:7:14:7:6:6:14:6:11:11:14:10:10:2:14:2:2:2:14:8:8:8:14:2:5:11:14:11:7:7:14:10:10:4:14:4:1:1:14:9:9:3:14:3:8:8:14:3:3:11:14:11:11:3:14:3:1:1:14:5:5:3:14:3:3:5:14:5:2:2:14:2:2:5:14:5:7:7:14:10:10:10:14:2:2:2:14:4:4:4:14:4:11:11:14:5:5:5:14:6:6:5:14:5:10:10:14:7:7:7:14:5:4:4:14:8:4:4:14:9:9:10:14:10:9:9:11:11:6:6:10:10:8:8:9:8:11:4:6:7:6:6:7:7:6:6:7:7:5:5:5:6:6:5:5:7:7:7:5:5:6:6:7:7:5:5:7:6:6:6:5:5:7:7:6:6:6:5:5:6:6:6:6:7:6:6:7:7:7:6:7:7:5:5:5:6:6:6:7:7:5:5:7:7:6:5:5:7:7:7:7:6:6:5:5:6:6:6:7:7:7:6:6:5:5:7:7:6:6:5:5:7:7:5:5:6:6:5:5:5:6:6:7:7:6:6:5:5:5:7:7:5:5:5:7:7:7:6:6:7:7:7:5:5:6:6:5:5:5:6:6:5:5:7:7:6:6:5:5:5:5:6:6:5:5:7:7:7:7:9:9:10:7:7:7:11:11:6:6:12:10:10:10:20:21:6:6:6:2:2:12:2:2:10:10:20:2:2:9:9:5:12:5:5:10:10:10:12:2:10:11:11:12:2:2:9:9:5:17:5:5:20:3:3:12:6:6:3:3:3:21:5:5:4:4:12:4:7:7:6:20:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:12:6:6:10:10:8:8:17:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:21:1:1:5:5:9:12:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:12:8:2:2:2:17:3:4:4:4:19:2:2:3:3:12:10:10:10:8:8:1:1:12:7:7:8:8:4:12:11:11:7:7:12:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:19:8:8:8:17:6:6:8:8:12:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:12:5:4:4:4:1:1:21:7:7:7:12:4:4:8:8:17:10:1:1:20:2:2:4:9:9:9:19:1:8:11:17:3:3:3:13:10:10:3:13:3:9:9:13:9:8:8:13:1:1:1:13:2:2:7:13:7:7:1:13:1:4:4:13:2:2:2:13:2:4:4:13:11:11:5:13:5:5:4:13:4:6:6:13:3:3:8:13:8:5:5:13:1:1:2:13:2:7:7:13:11:11:4:13:4:7:7:13:11:11:6:13:6:9:9:13:8:8:5:13:5:7:7:13:10:10:9:13:9:5:5:13:5:8:8:13:11:11:11:13:11:6:6:14:10:10:3:14:3:6:6:14:6:5:5:14:5:6:6:14:1:1:5:14:5:2:2:14:2:1:1:14:5:5:7:14:7:7:9:14:9:11:11:14:8:8:10:14:10:3:3:14:3:9:9:14:9:10:10:14:6:6:1:14:1:5:5:14:9:9:9:14:8:8:10:14:10:10:11:14:11:2:2:14:4:4:3:14:3:1:1:14:4:4:9:14:9:10:10:14:10:7:7:14:4:4:9:14:9:9:2:14:2:4:4:14:4:4:7:14:9:9:7:14:7:6:6:14:4:10:10:14:11:11:8:14:8:8:2:14:2:3:3:14:6:6:10:14:10:11:11:14:10:10:10:14:8:8:3:14:3:8:8:14:8:7:7:14:6:6:11:14:11:10:10:14:11:11:1:1:3:3:2:11:11:6:11:11:11:5:7:1:7:6:6:7:7:6:6:7:7:5:5:5:6:6:5:5:7:7:7:5:5:6:6:7:7:5:5:7:6:6:6:5:5:7:7:6:6:6:5:5:6:6:6:6:7:6:6:7:7:7:6:7:7:5:5:5:6:6:6:7:7:5:5:7:7:6:5:5:7:7:7:7:6:6:5:5:6:6:6:7:7:7:6:6:5:5:7:7:6:6:5:5:7:7:5:5:6:6:5:5:5:6:6:7:7:6:6:5:5:5:7:7:5:5:5:7:7:7:6:6:7:7:7:5:5:6:6:5:5:5:6:6:5:5:7:7:6:6:5:5:5:5:6:6:5:5:7:7:7:7:9:9:10:7:7:7:11:11:6:6:12:10:10:10:20:2:6:6:6:2:2:12:2:2:10:10:20:2:2:9:9:5:12:5:5:10:10:10:12:2:10:11:11:12:2:2:9:9:5:17:5:5:20:3:3:12:6:6:3:3:3:21:5:5:4:4:12:4:7:7:6:20:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:12:6:6:10:10:8:8:17:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:21:1:1:5:5:9:12:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:12:8:2:2:2:17:3:4:4:4:19:2:2:3:3:12:10:10:10:8:8:1:1:12:7:7:8:8:4:12:11:11:7:7:12:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:19:8:8:8:17:6:6:8:8:12:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:12:5:4:4:4:1:1:21:7:7:7:12:4:4:8:8:17:10:1:1:20:2:2:4:9:9:9:19:1:8:11:17:9:9:9:13:5:5:5:13:5:6:6:13:9:10:10:13:3:1:1:13:1:3:3:13:9:9:9:13:9:7:7:13:2:2:7:13:7:11:11:13:11:1:1:13:1:3:3:13:3:2:2:13:2:2:4:13:4:11:11:13:11:2:2:13:5:5:8:13:8:8:9:13:9:6:6:13:11:11:4:13:4:8:4:13:4:4:10:13:10:4:4:13:3:3:5:13:5:1:1:13:5:5:5:13:7:7:9:13:9:10:10:13:11:11:9:13:9:9:6:14:6:6:6:14:10:10:8:14:8:8:2:14:2:2:10:14:10:7:7:14:9:5:5:14:5:8:11:14:11:8:8:14:8:1:1:14:1:3:3:14:2:2:2:14:11:11:8:14:8:8:3:14:3:4:4:14:7:7:1:14:1:9:9:14:3:7:7:14:7:1:1:14:6:6:6:14:11:11:10:14:10:8:8:14:8:5:9:14:9:9:1:14:1:8:8:14:10:10:2:14:2:10:10:14:4:4:6:14:6:11:11:14:11:3:3:14:4:4:2:14:2:10:10:14:10:11:11:14:3:3:5:14:5:10:10:14:4:4:11:14:11:6:6:14:7:6:6:14:6:6:3:14:3:7:10:14:10:5:5:14:6:3:7:14:7:10:10:11:11:2:2:1:4:4:9:8:5:7:7:7:7:6:6:7:7:6:6:7:7:5:5:5:6:6:5:5:7:7:7:5:5:6:6:7:7:5:5:7:6:6:6:5:5:7:7:6:6:6:5:5:6:6:6:6:7:6:6:7:7:7:6:7:7:5:5:5:6:6:6:7:7:5:5:7:7:6:5:5:7:7:7:7:6:6:5:5:6:6:6:7:7:7:6:6:5:5:7:7:6:6:5:5:7:7:5:5:6:6:5:5:5:6:6:7:7:6:6:5:5:5:7:7:5:5:5:7:7:7:6:6:7:7:7:5:5:6:6:5:5:5:6:6:5:5:7:7:6:6:5:5:5:5:6:6:5:5:7:7:7:7:9:9:10:7:7:7:11:11:6:6:12:10:10:10:20:2:6:6:6:2:2:12:2:2:10:10:20:2:2:9:9:5:12:5:5:10:10:10:12:2:10:11:11:12:2:2:9:9:5:17:5:5:20:3:3:12:6:6:3:3:3:21:5:5:4:4:12:4:7:7:6:20:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:12:6:6:10:10:8:8:17:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:21:1:1:5:5:9:12:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:12:8:2:2:2:17:3:4:4:4:19:2:2:3:3:12:10:10:10:8:8:1:1:12:7:7:8:8:4:4:11:11:7:7:12:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:19:8:8:8:17:6:6:8:8:12:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:12:5:4:4:4:1:1:21:7:7:7:12:4:4:8:8:10:10:1:1:20:2:2:4:9:9:9:19:1:8:11:17:7:7:9:13:9:9:11:13:11:10:10:13:10:7:7:13:7:8:6:13:6:2:2:13:1:1:10:13:4:4:8:13:8:8:1:13:1:10:10:13:2:9:9:13:10:10:10:13:10:9:9:13:9:1:1:13:1:6:6:13:7:7:7:13:6:6:9:13:9:9:11:13:11:11:8:13:8:5:5:13:6:6:1:13:1:11:11:13:11:5:5:13:10:10:4:13:4:1:1:13:9:9:8:13:8:2:2:13:11:11:9:13:9:9:3:13:3:9:9:13:10:10:9:13:9:9:3:13:3:3:6:14:6:6:2:14:2:5:5:14:5:10:10:14:4:4:8:14:8:4:4:14:7:7:7:14:8:8:1:14:1:2:2:14:3:3:11:14:11:3:3:14:10:10:11:14:8:8:8:14:6:6:4:14:4:1:1:14:2:7:7:14:1:1:1:14:3:3:3:14:11:11:11:14:4:2:2:14:8:8:3:14:3:2:2:14:10:10:3:14:3:2:2:14:8:8:7:14:7:4:4:14:10:10:11:14:11:11:4:14:4:3:3:14:3:10:10:14:6:6:5:14:5:2:2:14:2:7:7:14:11:11:6:14:6:7:7:14:3:6:5:14:5:4:7:14:9:5:5:14:6:6:5:14:5:4:4:11:11:11:4:11:5:5:5:8:5:5:2:10:5:5:7:7:5:5:7:7:7:6:6:7:7:6:6:6:7:7:5:5:7:7:5:6:6:7:7:5:5:6:6:7:7:6:6:5:5:6:6:5:5:7:7:5:7:7:5:5:6:7:6:6:7:7:6:5:5:6:6:5:5:5:7:6:6:7:7:6:6:5:6:6:5:5:5:7:7:7:5:5:7:7:6:6:7:7:7:6:6:6:5:5:7:7:5:5:6:6:6:7:7:5:5:7:7:5:5:7:7:7:5:5:7:7:7:7:6:6:6:5:5:6:6:6:5:5:5:6:6:5:5:6:6:7:7:6:6:6:5:5:6:6:5:5:6:6:7:7:5:5:9:9:10:7:7:7:11:11:6:6:12:10:10:10:20:2:6:6:6:2:2:12:2:2:10:10:20:2:2:9:9:5:12:5:5:10:10:10:2:2:10:11:11:12:2:2:9:9:5:17:5:5:20:3:3:12:6:6:3:3:3:21:5:5:4:4:12:4:7:7:6:20:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:9:6:6:10:10:8:8:17:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:21:1:1:5:5:9:12:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:12:8:2:2:2:17:3:4:4:4:19:2:2:3:3:12:10:10:10:8:8:1:1:12:7:7:8:8:4:4:11:11:7:7:12:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:19:8:8:8:17:6:6:8:8:12:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:12:5:4:4:4:1:1:21:7:7:7:12:4:4:8:8:10:10:1:1:20:2:2:4:9:9:9:19:1:8:11:17:3:3:7:13:7:7:10:13:10:10:10:13:1:1:1:13:10:10:10:13:8:8:9:13:9:2:2:13:1:1:3:13:3:1:1:13:1:8:8:13:8:8:4:13:4:11:11:13:5:5:5:13:3:3:3:13:9:9:10:13:10:10:3:13:3:4:2:13:9:9:7:13:6:6:6:13:9:8:8:13:1:2:2:13:2:5:5:13:5:7:7:13:7:2:2:13:4:4:4:13:4:5:5:13:5:11:11:13:10:10:3:13:3:3:3:13:7:7:7:13:5:5:6:13:6:6:8:13:9:9:10:13:5:5:5:13:5:8:8:13:11:11:3:14:3:10:10:14:11:11:8:14:8:8:7:14:7:10:10:14:6:6:2:14:2:4:4:14:11:11:7:14:7:8:8:14:3:3:6:14:6:6:7:14:7:7:4:14:4:10:10:14:10:3:3:14:4:4:2:14:2:1:1:14:11:11:9:14:9:4:4:14:6:6:5:14:5:2:2:14:5:5:5:14:1:1:8:14:8:9:9:14:9:11:11:14:11:2:2:14:1:1:9:14:9:4:4:14:10:10:11:14:11:2:2:14:2:2:1:14:1:11:11:14:7:7:10:14:10:8:8:14:6:6:9:14:9:1:9:14:9:6:6:9:9:4:4:11:11:6:6:7:11:11:3:4:11:11:6:10:5:5:5:6:6:5:5:6:6:7:7:7:5:5:5:7:7:5:5:6:6:7:5:5:6:6:5:5:6:6:7:7:6:6:6:5:5:7:7:5:5:6:6:6:7:7:5:5:7:7:5:5:7:7:6:6:7:7:7:7:6:6:6:5:5:5:6:6:7:7:6:6:6:5:5:7:7:5:5:6:6:7:5:5:7:7:5:5:6:6:6:5:6:6:7:5:5:5:7:7:7:6:6:7:7:6:6:7:7:7:7:6:6:5:5:6:6:6:5:5:5:6:6:7:7:6:6:6:5:5:5:7:7:5:5:7:6:6:7:7:6:7:7:5:5:7:7:5:7:7:9:9:10:7:7:7:11:11:6:6:12:10:10:10:20:2:6:6:6:2:2:12:2:2:10:10:20:2:2:9:9:5:12:5:5:10:10:10:2:2:10:11:11:2:2:2:9:9:5:17:5:5:20:3:3:12:6:6:3:3:3:21:5:5:4:4:12:4:7:7:6:20:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:9:6:6:10:10:8:8:17:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:21:1:1:5:5:9:12:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:12:8:2:2:2:17:3:4:4:4:19:2:2:3:3:12:10:10:10:8:8:1:1:12:7:7:8:8:4:4:11:11:7:7:12:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:19:8:8:8:17:6:6:8:8:12:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:12:5:4:4:4:1:1:21:7:7:7:12:4:4:8:8:10:10:1:1:20:2:2:4:9:9:9:19:1:8:11:17:6:6:10:13:10:10:4:13:4:11:11:13:3:3:7:13:7:7:10:13:10:6:6:13:6:9:9:13:10:10:4:13:4:4:4:13:11:11:8:13:8:1:1:13:8:8:5:13:9:9:1:13:1:2:2:13:2:8:8:13:9:9:5:13:4:4:9:13:9:9:11:13:11:11:11:13:10:10:10:13:10:8:8:13:9:9:9:13:10:10:2:13:2:2:11:13:11:11:10:13:10:6:6:13:7:7:1:13:1:3:3:13:3:6:6:13:4:4:7:13:7:7:3:13:3:3:1:14:1:3:3:14:3:2:2:14:5:5:7:14:7:3:3:14:10:10:10:14:7:7:2:14:2:5:5:14:5:11:11:14:6:6:6:14:9:9:4:14:11:11:11:14:1:1:6:14:6:2:2:14:6:6:4:14:4:2:2:14:2:1:1:14:1:5:5:14:11:11:11:14:8:8:10:14:10:5:5:14:8:8:10:14:10:10:10:14:8:8:4:14:4:3:3:14:3:4:4:14:8:8:5:14:5:2:2:14:9:9:4:14:4:3:3:14:5:5:5:14:1:1:7:14:7:11:11:14:6:6:7:14:7:7:1:14:1:11:11:14:2:2:9:14:9:7:7:4:3:3:1:7:7:9:9:6:6:11:11:8:8:5:5:5:5:9:9:8:2:8:9:10:6:6:5:5:6:6:6:7:7:6:6:7:7:7:7:6:6:6:6:5:5:7:7:7:5:5:6:6:5:5:5:6:6:6:5:5:7:7:5:5:6:6:7:7:6:6:5:5:5:6:6:7:7:7:7:6:6:6:5:5:6:6:6:7:7:6:6:5:5:5:7:7:5:5:7:7:7:6:6:6:6:7:7:5:5:7:7:6:6:5:5:7:7:6:6:7:7:6:6:6:5:5:7:7:5:5:7:7:5:5:5:7:7:5:6:6:7:7:7:5:5:7:7:5:5:6:6:7:7:5:5:6:6:7:7:7:5:5:5:7:7:6:6:6:5:5:5:5:5:5:9:9:10:7:7:7:11:11:6:6:8:10:10:10:20:2:6:6:6:2:2:12:2:2:10:10:20:2:2:9:9:5:12:5:5:10:10:10:2:2:10:11:11:2:2:2:9:9:5:17:5:5:20:3:3:3:6:6:3:3:3:21:5:5:4:4:7:4:7:7:6:6:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:9:6:6:10:10:8:8:17:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:3:1:1:5:5:9:9:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:12:8:2:2:2:17:3:4:4:4:19:2:2:3:3:3:10:10:10:8:8:1:1:12:7:7:8:8:4:4:11:11:7:7:12:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:19:8:8:8:17:6:6:8:8:3:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:5:5:4:4:4:1:1:21:7:7:7:12:4:4:8:8:10:10:1:1:20:2:2:4:9:9:9:19:1:8:11:11:3:3:7:7:7:7:10:13:10:10:10:13:1:1:1:13:10:10:10:13:8:8:9:13:9:2:2:1:1:1:3:3:3:1:1:13:1:8:8:13:8:8:4:13:4:11:11:13:5:5:5:13:3:3:3:9:9:9:10:13:10:10:3:13:3:4:2:13:9:9:7:7:6:6:6:8:9:8:8:13:1:2:2:13:2:5:5:13:5:7:7:13:7:2:2:13:4:4:4:13:4:5:5:13:5:11:11:13:10:10:3:13:3:3:3:13:7:7:7:13:5:5:6:13:6:6:8:13:9:9:10:13:5:5:5:13:5:8:8:13:11:11:3:14:3:10:10:14:11:11:8:14:8:8:7:14:7:10:10:14:6:6:2:14:2:4:4:14:11:11:7:7:7:8:8:14:3:3:6:14:6:6:7:14:7:7:4:14:4:10:10:14:10:3:3:14:4:4:2:14:2:1:1:14:11:11:9:14:9:4:4:14:6:6:5:14:5:2:2:14:5:5:5:14:1:1:8:14:8:9:9:14:9:11:11:14:11:2:2:14:1:1:9:14:9:4:4:14:10:10:11:14:11:2:2:14:2:2:1:14:1:11:11:14:7:7:10:14:10:8:8:14:6:6:9:14:9:1:9:14:9:6:6:9:9:4:4:11:11:6:6:7:11:11:3:4:11:11:6:10:7:7:5:5:5:7:7:5:5:6:6:5:5:7:7:5:5:5:7:7:5:5:7:7:7:6:6:7:7:6:6:7:7:6:6:7:7:7:5:5:6:6:6:5:5:7:7:7:5:5:7:7:6:6:5:5:7:7:7:6:6:5:5:6:6:6:7:7:5:5:5:5:7:7:5:5:5:6:6:7:7:6:6:5:5:5:7:7:6:6:7:7:5:7:7:6:6:6:5:5:5:6:6:5:5:6:6:6:7:7:5:5:6:6:5:5:6:6:6:7:7:5:5:7:7:6:6:5:5:6:6:6:5:5:5:6:6:7:7:6:6:5:6:6:7:7:7:6:7:6:</t>
-  </si>
-  <si>
-    <t>8:8:8:5:5:2:2:9:9:11:12:11:6:6:6:4:4:8:8:9:11:12:11:5:5:5:20:19:6:10:10:10:12:8:8:8:20:1:1:12:9:9:8:12:8:2:2:6:6:17:1:1:3:3:9:12:9:3:3:3:3:20:6:4:4:5:12:6:6:4:4:21:19:3:3:3:6:12:6:2:2:21:2:2:2:3:3:3:12:3:9:9:20:9:7:7:17:3:3:3:12:3:11:11:4:7:7:21:1:1:8:12:8:1:1:7:7:22:9:4:1:1:12:6:6:5:5:20:8:8:2:2:2:12:5:10:10:5:5:19:9:9:1:1:12:4:4:10:10:17:10:6:6:5:5:9:12:9:9:9:19:8:8:11:11:7:7:12:7:10:10:1:19:10:7:7:5:5:12:10:10:5:5:17:7:6:6:6:6:12:4:4:4:1:1:19:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:21:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:12:3:3:3:3:11:11:12:11:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:21:10:8:12:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:19:2:2:1:12:8:8:7:20:6:8:7:8:17:11:11:2:13:5:4:4:13:9:9:7:13:7:7:3:13:3:10:10:13:6:6:10:13:10:10:1:13:1:1:5:13:5:4:4:13:4:4:10:13:10:10:8:13:8:6:5:13:5:5:3:13:3:3:10:13:10:10:10:13:1:1:3:13:3:3:4:13:4:5:5:13:10:10:9:13:9:3:3:13:9:9:5:13:5:5:6:13:6:8:8:13:5:5:11:13:9:9:9:14:4:10:10:14:2:2:1:14:1:6:6:14:4:11:11:14:4:4:1:14:1:3:3:14:11:11:4:14:4:4:4:14:8:8:7:14:7:5:5:14:5:5:2:14:11:11:6:14:6:8:8:14:5:5:2:14:2:2:7:14:7:2:2:14:8:8:3:14:3:4:4:14:10:10:10:14:9:9:7:14:7:2:2:14:8:8:8:14:8:7:7:14:8:8:8:14:9:9:7:14:7:9:9:14:9:7:7:14:6:6:10:14:10:3:10:14:10:11:11:14:9:9:3:14:3:3:11:14:11:6:6:14:6:2:2:14:3:9:9:14:11:11:1:14:1:1:7:14:7:7:1:14:1:2:2:14:11:11:5:14:4:4:10:14:10:6:6:14:11:11:11:14:9:9:9:14:7:1:1:14:11:11:11:14:1:11:11:7:2:2:2:2:8:8:6:6:2:6:6:11:4:4:2:2:3:3:3:2:2:3:3:4:4:3:3:3:1:1:2:2:4:4:3:3:4:4:1:1:4:4:4:1:1:1:3:3:3:4:4:1:1:1:4:4:4:2:2:4:4:1:1:3:3:1:1:4:4:2:2:4:4:3:3:3:2:2:3:3:4:4:1:1:4:4:3:4:4:4:2:2:2:4:4:4:2:2:2:1:1:4:4:2:2:3:1:1:3:3:1:1:2:2:3:3:2:2:3:3:2:2:1:1:3:3:4:4:1:1:3:3:2:2:2:3:3:1:1:3:3:2:2:1:1:4:4:4:4:2:2:3:3:2:2:3:3:2:2:2:2:2:8:8:8:5:5:2:2:9:9:11:12:11:6:6:6:4:4:8:8:9:11:12:11:5:5:5:20:19:6:10:10:10:12:8:8:8:20:1:1:12:9:9:8:12:8:2:2:6:6:17:1:1:3:3:9:12:9:3:3:3:3:20:6:4:4:5:12:6:6:4:4:21:19:3:3:3:6:12:6:2:2:21:2:2:2:3:3:3:12:3:9:9:20:9:7:7:17:3:3:3:12:3:11:11:4:7:7:21:1:1:8:12:8:1:1:7:7:22:9:4:1:1:12:6:6:5:5:20:8:8:2:2:2:12:5:10:10:5:5:19:9:9:1:1:12:4:4:10:10:17:10:6:6:5:5:9:12:9:9:9:19:8:8:11:11:7:7:12:7:10:10:1:19:10:7:7:5:5:12:10:10:5:5:17:7:6:6:6:6:12:4:4:4:1:1:19:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:21:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:12:3:3:3:3:11:11:12:11:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:21:10:8:12:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:19:2:2:1:12:8:8:7:20:6:8:7:8:17:1:1:3:13:3:7:7:13:3:3:3:13:3:10:10:13:6:6:11:13:11:10:10:13:1:1:4:13:4:2:2:13:2:6:6:13:5:5:8:13:8:8:4:13:4:10:10:13:7:7:2:13:2:2:2:13:4:4:4:13:10:10:3:13:3:9:9:13:9:3:3:13:3:11:11:13:7:7:7:13:4:4:11:13:11:2:2:13:2:9:9:13:3:3:9:13:9:10:10:13:7:7:5:13:5:5:1:13:1:4:4:13:4:11:11:13:6:6:10:13:10:10:4:13:7:7:9:14:9:6:6:14:4:4:4:14:11:11:1:14:1:2:2:14:2:5:5:14:11:11:9:14:9:9:2:14:2:2:2:14:8:8:11:14:11:11:11:14:8:5:5:14:5:1:1:14:7:7:3:14:3:1:1:14:10:10:10:14:8:8:3:14:3:3:11:14:11:11:5:14:5:9:9:14:4:4:1:14:1:1:6:14:6:6:11:14:11:6:6:14:7:7:10:14:10:8:8:14:8:8:11:14:11:10:10:14:2:2:8:14:8:10:10:14:8:8:6:14:6:6:1:14:8:8:5:14:5:5:10:14:10:10:7:14:7:1:1:14:9:9:11:14:11:9:9:14:2:5:5:14:3:3:7:14:7:4:4:5:5:6:6:8:7:9:9:6:6:1:1:5:4:4:2:2:3:3:3:2:2:3:3:4:4:3:3:3:1:1:2:2:4:4:3:3:4:4:1:1:4:4:4:1:1:1:3:3:3:4:4:1:1:1:4:4:4:2:2:4:4:1:1:3:3:1:1:4:4:2:2:4:4:3:3:3:2:2:3:3:4:4:1:1:4:4:3:4:4:4:2:2:2:4:4:4:2:2:2:1:1:4:4:2:2:3:1:1:3:3:1:1:2:2:3:3:2:2:3:3:2:2:1:1:3:3:4:4:1:1:3:3:2:2:2:3:3:1:1:3:3:2:2:1:1:4:4:4:4:2:2:3:3:2:2:3:3:2:2:2:2:2:8:8:8:5:5:2:2:9:9:11:12:11:6:6:6:4:4:8:8:9:11:12:11:5:5:5:20:19:6:10:10:10:12:8:8:8:20:1:1:12:9:9:8:12:8:2:2:6:6:17:1:1:3:3:9:12:9:3:3:3:3:20:6:4:4:5:12:6:6:4:4:4:19:3:3:3:6:12:6:2:2:21:2:2:2:3:3:3:12:3:9:9:20:9:7:7:17:3:3:3:12:3:11:11:4:7:7:21:1:1:8:12:8:1:1:7:7:22:9:4:1:1:12:6:6:5:5:20:8:8:2:2:2:12:5:10:10:5:5:19:9:9:1:1:12:4:4:10:10:17:10:6:6:5:5:9:12:9:9:9:19:8:8:11:11:7:7:12:7:10:10:1:19:10:7:7:5:5:12:10:10:5:5:7:7:6:6:6:6:12:4:4:4:1:1:19:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:21:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:12:3:3:3:3:11:11:12:11:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:21:10:8:12:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:19:2:2:1:12:8:8:7:20:6:8:7:8:17:1:11:11:13:11:1:1:13:11:11:6:13:6:7:7:13:10:10:10:13:9:9:11:13:11:9:9:13:9:11:11:13:11:6:6:13:3:3:3:13:9:5:5:13:1:1:5:13:5:9:9:13:9:11:11:13:1:1:5:13:7:7:6:13:6:6:5:13:5:9:9:13:9:4:4:13:7:7:7:13:10:10:4:13:4:4:1:13:1:1:8:13:8:5:5:13:5:3:3:13:3:2:2:13:6:6:6:13:1:1:4:13:4:4:11:13:11:4:4:13:4:4:2:13:2:3:3:13:4:4:6:14:6:11:11:14:10:10:10:14:10:11:11:14:7:7:7:14:7:11:11:14:2:2:2:14:7:7:4:14:4:2:10:14:10:1:1:14:3:3:3:14:9:9:10:14:10:6:6:14:6:10:10:14:4:4:4:14:9:9:9:14:2:2:5:14:11:11:7:14:7:11:11:14:8:8:2:14:2:2:3:14:3:6:6:14:6:10:1:14:1:1:1:14:2:2:2:14:10:10:5:14:5:10:10:14:7:8:8:14:3:3:9:14:9:5:5:14:7:7:10:14:10:10:1:14:1:8:8:14:8:3:3:14:7:7:3:14:3:8:8:14:8:5:5:14:6:6:8:14:5:5:5:14:2:2:2:4:9:10:10:3:8:8:2:8:8:11:8:8:4:4:2:2:3:3:3:2:2:3:3:4:4:3:3:3:1:1:2:2:4:4:3:3:4:4:1:1:4:4:4:1:1:1:3:3:3:4:4:1:1:1:4:4:4:2:2:4:4:1:1:3:3:1:1:4:4:2:2:4:4:3:3:3:2:2:3:3:4:4:1:1:4:4:3:4:4:4:2:2:2:4:4:4:2:2:2:1:1:4:4:2:2:3:1:1:3:3:1:1:2:2:3:3:2:2:3:3:2:2:1:1:3:3:4:4:1:1:3:3:2:2:2:3:3:1:1:3:3:2:2:1:1:4:4:4:4:2:2:3:3:2:2:3:3:2:2:2:2:2:8:8:8:5:5:2:2:9:9:11:12:11:6:6:6:4:4:8:8:9:11:12:11:5:5:5:20:19:6:10:10:10:12:8:8:8:20:1:1:12:9:9:8:12:8:2:2:6:6:17:1:1:3:3:9:12:9:3:3:3:3:20:6:4:4:5:12:6:6:4:4:4:4:3:3:3:6:12:6:2:2:21:2:2:2:3:3:3:12:3:9:9:20:9:7:7:17:3:3:3:12:3:11:11:4:7:7:21:1:1:8:12:8:1:1:7:7:22:9:4:1:1:12:6:6:5:5:20:8:8:2:2:2:12:5:10:10:5:5:19:9:9:1:1:12:4:4:10:10:17:10:6:6:5:5:9:12:9:9:9:19:8:8:11:11:7:7:12:7:10:10:1:19:10:7:7:5:5:12:10:10:5:5:7:7:6:6:6:6:12:4:4:4:1:1:19:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:21:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:2:3:3:3:3:11:11:12:11:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:21:10:8:12:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:19:2:2:1:12:8:8:7:20:6:8:7:8:17:4:4:4:13:11:11:1:13:1:10:10:13:7:7:7:13:5:5:6:13:6:3:3:13:7:7:11:13:11:4:4:13:3:3:10:13:10:10:9:13:9:9:6:13:6:6:7:13:7:9:9:13:9:8:8:13:5:5:5:13:5:7:7:13:6:6:7:13:7:7:1:13:1:1:2:13:2:1:1:13:8:8:8:13:2:2:6:13:6:6:7:13:5:5:2:13:5:5:11:13:11:11:5:13:5:5:5:13:1:1:4:13:4:4:4:13:3:3:3:13:9:9:10:13:10:10:11:13:11:11:9:13:9:8:8:13:3:3:5:14:5:4:4:14:9:9:6:14:11:11:2:14:2:3:3:14:10:10:6:14:6:6:3:14:3:8:8:14:5:5:5:14:9:9:9:14:10:10:4:14:8:8:9:14:9:9:1:14:1:8:8:14:3:3:8:14:8:8:4:14:4:7:7:14:1:1:1:14:6:6:7:14:7:2:2:14:6:6:4:14:4:10:10:14:11:11:6:14:6:3:3:14:1:1:11:14:11:8:8:14:2:2:4:14:4:10:10:14:10:9:9:14:10:4:4:14:8:10:10:14:7:1:1:14:2:2:3:14:3:11:11:14:2:2:10:14:10:10:7:14:7:2:2:14:2:1:1:11:11:11:11:10:10:11:11:2:2:11:5:3:3:3:3:4:4:1:1:2:2:4:4:2:2:2:1:1:3:3:1:1:2:2:1:1:1:3:3:1:1:1:3:3:1:1:1:3:3:3:1:1:3:3:4:4:2:2:2:3:3:2:2:4:4:3:3:1:1:2:2:1:1:4:4:4:2:2:2:3:3:1:1:2:2:3:3:3:3:2:2:4:2:2:2:2:1:1:4:4:4:2:2:4:4:2:2:2:3:3:4:4:1:1:4:4:4:2:2:2:2:3:3:3:3:4:4:4:3:3:3:4:4:3:3:4:4:3:3:4:4:1:1:1:2:2:2:4:4:4:2:2:4:4:3:3:4:4:4:2:4:3:8:8:8:5:5:2:2:9:9:11:12:11:6:6:6:4:4:8:8:9:11:12:11:5:5:5:20:19:6:10:10:10:12:8:8:8:20:1:1:1:9:9:8:12:8:2:2:6:6:17:1:1:3:3:9:12:9:3:3:3:3:20:6:4:4:5:12:6:6:4:4:4:4:3:3:3:6:12:6:2:2:21:2:2:2:3:3:3:12:3:9:9:20:9:7:7:17:3:3:3:12:3:11:11:4:7:7:21:1:1:8:12:8:1:1:7:7:22:9:4:1:1:12:6:6:5:5:20:8:8:2:2:2:12:5:10:10:5:5:19:9:9:1:1:12:4:4:10:10:17:10:6:6:5:5:9:12:9:9:9:19:8:8:11:11:7:7:12:7:10:10:1:19:10:7:7:5:5:12:10:10:5:5:7:7:6:6:6:6:12:4:4:4:1:1:19:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:21:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:2:3:3:3:3:11:11:12:11:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:21:10:8:12:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:19:2:2:1:5:8:8:7:20:6:8:7:8:17:2:2:11:13:11:5:5:13:1:1:1:13:11:11:11:13:4:4:4:13:8:8:3:13:3:10:10:13:7:7:5:13:5:10:10:13:10:1:1:13:2:2:3:13:3:10:10:13:10:9:9:13:6:6:8:13:8:11:7:13:10:10:1:13:1:10:2:13:2:3:3:13:3:11:11:13:5:5:9:13:9:4:4:13:11:11:11:13:6:9:9:13:4:4:4:13:8:8:2:13:2:8:8:13:10:10:8:13:8:11:11:13:4:4:5:13:5:5:6:13:6:6:7:13:7:7:4:13:4:3:1:13:1:9:9:13:3:3:9:13:9:9:9:14:6:6:10:14:10:7:7:14:2:2:8:14:9:2:2:14:5:5:5:14:5:6:6:14:6:1:1:14:3:3:11:14:11:7:7:14:1:1:1:14:10:10:3:14:2:2:7:14:7:5:5:14:7:7:7:14:7:3:3:14:10:10:1:14:1:8:8:14:8:2:2:14:4:4:4:14:7:7:7:14:10:10:10:14:10:9:9:14:2:2:8:14:8:8:11:14:11:11:6:14:6:4:4:14:5:5:11:14:11:3:3:14:9:9:8:14:8:1:1:14:9:9:1:14:1:4:4:14:4:10:10:14:5:5:9:14:11:11:6:2:2:8:11:11:6:6:3:3:3:11:6:6:6:6:7:5:3:3:3:2:2:3:3:4:4:3:3:3:1:1:3:3:2:2:3:2:2:1:1:1:3:3:3:2:2:1:1:3:3:1:1:1:2:2:3:3:3:1:1:4:4:4:1:1:3:3:2:2:1:1:4:4:1:1:4:4:4:4:3:2:2:4:4:4:4:2:2:4:4:2:2:3:3:4:4:1:1:4:4:4:1:1:2:2:4:4:3:3:2:2:2:4:4:2:2:2:3:3:4:4:3:3:2:2:3:3:4:4:3:3:1:1:2:2:2:3:3:4:4:1:1:4:4:3:3:2:2:3:3:2:2:1:1:1:2:2:4:4:2:2:4:4:2:4:4:1:8:8:8:5:5:2:2:9:9:11:12:11:6:6:6:4:4:8:8:9:11:12:11:5:5:5:20:19:6:10:10:10:12:8:8:8:20:1:1:1:9:9:8:5:8:2:2:6:6:17:1:1:3:3:9:12:9:3:3:3:3:20:6:4:4:5:12:6:6:4:4:4:4:3:3:3:6:12:6:2:2:21:2:2:2:3:3:3:12:3:9:9:20:9:7:7:17:3:3:3:12:3:11:11:4:7:7:21:1:1:8:12:8:1:1:7:7:22:9:4:1:1:12:6:6:5:5:20:8:8:2:2:2:12:5:10:10:5:5:19:9:9:1:1:12:4:4:10:10:17:10:6:6:5:5:9:12:9:9:9:19:8:8:11:11:7:7:12:7:10:10:1:19:10:7:7:5:5:12:10:10:5:5:7:7:6:6:6:6:12:4:4:4:1:1:19:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:21:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:2:3:3:3:3:11:11:12:11:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:21:10:8:12:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:19:2:2:1:5:8:8:7:20:6:8:7:8:17:2:2:6:13:6:6:4:13:4:2:2:13:2:10:10:13:11:11:5:13:5:11:3:13:3:3:6:13:6:4:4:13:10:10:11:13:11:7:7:13:3:3:6:13:6:6:3:13:3:3:1:13:3:3:11:13:11:10:10:13:10:10:7:13:7:9:9:13:7:7:9:13:9:8:8:13:5:5:7:13:7:7:2:13:2:9:9:13:10:10:11:13:11:3:3:13:4:1:1:13:1:1:6:13:6:6:4:13:4:4:5:13:5:8:8:13:1:1:7:13:7:8:7:13:7:9:9:13:1:1:10:13:10:6:6:13:10:10:1:14:1:1:5:14:5:11:11:14:4:4:4:14:10:10:11:14:11:5:1:14:1:4:4:14:4:6:6:14:2:2:10:14:10:10:11:14:11:8:8:14:7:7:8:14:8:5:5:14:5:11:11:14:3:3:11:14:11:8:8:14:2:2:5:14:5:6:6:14:6:7:7:14:7:9:9:14:2:2:4:14:4:11:11:14:2:2:2:14:8:8:9:14:9:1:1:14:1:10:10:14:10:10:5:14:5:11:11:14:8:8:8:14:2:2:9:14:9:9:10:14:10:7:7:14:3:3:3:14:5:5:6:14:6:11:11:9:9:9:3:3:4:4:5:5:8:8:1:1:8:8:8:8:3:4:4:9:9:2:2:1:2:2:4:4:1:1:4:4:2:2:4:4:2:2:2:3:3:3:1:1:3:3:1:1:3:3:3:2:2:4:4:3:3:1:1:1:3:3:1:1:3:3:4:4:4:2:2:3:3:2:2:2:3:3:2:2:4:4:3:3:2:2:3:3:1:1:2:2:2:4:4:4:4:2:2:3:3:3:2:2:4:4:3:3:1:1:2:2:1:1:2:2:4:4:3:3:1:1:1:2:2:4:4:1:1:4:4:3:3:3:4:4:2:2:4:4:1:1:4:4:3:3:1:1:4:4:2:2:4:1:1:4:4:3:3:2:2:3:3:2:2:3:3:4:4:1:1:4:4:2:8:8:8:5:5:2:2:9:9:11:11:11:6:6:6:4:4:8:8:9:11:12:11:5:5:5:20:19:6:10:10:10:12:8:8:8:20:1:1:1:9:9:8:5:8:2:2:6:6:17:1:1:3:3:9:9:9:3:3:3:3:20:6:4:4:5:9:6:6:4:4:4:4:3:3:3:6:12:6:2:2:21:2:2:2:3:3:3:12:3:9:9:20:9:7:7:17:3:3:3:12:3:11:11:4:1:7:21:1:1:8:12:8:1:1:7:7:22:9:4:1:1:12:6:6:5:5:20:8:8:2:2:2:5:5:10:10:5:5:19:9:9:1:1:12:4:4:10:10:17:10:6:6:5:5:9:12:9:9:9:19:8:8:11:11:7:7:12:7:10:10:1:19:10:7:7:5:5:12:10:10:5:5:7:7:6:6:6:6:12:4:4:4:1:1:19:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:21:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:2:3:3:3:3:11:11:12:11:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:21:10:8:12:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:19:2:2:1:5:8:8:7:20:6:8:7:8:17:2:2:11:11:11:5:5:13:1:1:1:13:11:11:11:13:4:4:4:13:8:8:3:13:3:10:10:13:7:7:5:5:5:10:10:13:10:1:1:13:2:2:3:13:3:10:10:13:10:9:9:13:6:6:8:8:8:11:7:7:10:10:1:13:1:10:2:13:2:3:3:13:3:11:11:13:5:5:9:13:9:4:4:13:11:11:11:13:6:9:9:13:4:4:4:13:8:8:2:13:2:8:8:13:10:10:8:8:8:11:11:13:4:4:5:13:5:5:6:13:6:6:7:13:7:7:4:13:4:3:1:13:1:9:9:13:3:3:9:13:9:9:9:14:6:6:10:10:10:7:7:14:2:2:8:14:9:2:2:14:5:5:5:14:5:6:6:14:6:1:1:8:3:3:11:14:11:7:7:14:1:1:1:14:10:10:3:3:2:2:7:14:7:5:5:14:7:7:7:14:7:3:3:14:10:10:1:14:1:8:8:14:8:2:2:14:4:4:4:14:7:7:7:14:10:10:10:14:10:9:9:14:2:2:8:14:8:8:11:14:11:11:6:14:6:4:4:14:5:5:11:14:11:3:3:14:9:9:8:14:8:1:1:14:9:9:1:14:1:4:4:14:4:10:10:14:5:5:9:14:11:11:6:2:2:8:11:11:6:6:3:3:3:11:6:6:6:6:7:5:2:2:3:3:2:2:1:1:2:4:4:4:3:3:3:4:4:3:3:4:4:1:1:2:2:2:1:1:3:3:4:4:4:2:2:2:2:3:3:4:3:3:1:1:2:2:2:4:4:4:2:2:3:3:4:4:3:3:4:4:1:1:3:3:4:4:4:3:3:3:2:2:1:1:1:3:3:3:1:1:3:3:3:4:4:2:2:2:4:4:4:4:3:3:3:4:4:1:1:1:2:2:2:1:1:1:2:2:2:1:1:4:4:4:4:1:1:4:4:2:2:1:1:2:2:3:4:4:2:2:3:3:2:3:3:2:2:2:2:1:1:1:4:4:4:3:3:3:3:2:</t>
-  </si>
-  <si>
-    <t>8:8:4:4:4:10:10:2:2:10:12:10:4:4:4:4:10:10:12:8:8:3:19:3:3:1:1:19:11:11:11:2:2:19:8:8:2:12:7:7:2:12:2:2:9:19:10:10:9:17:7:9:9:1:1:12:8:8:3:3:3:19:7:1:1:6:12:6:5:5:2:19:3:3:10:10:5:12:5:8:8:9:9:9:21:3:3:7:12:7:9:9:5:5:5:17:3:3:3:3:12:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:12:7:7:6:6:12:6:7:7:7:20:21:11:11:7:7:12:7:6:9:9:17:3:3:3:20:1:1:10:12:11:11:3:19:21:5:5:4:4:12:4:6:6:6:21:19:10:3:3:5:5:12:10:10:2:2:22:20:2:8:8:12:8:5:5:5:12:7:7:7:7:17:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:20:1:6:6:17:4:4:8:8:12:10:10:6:6:7:7:7:9:9:10:12:10:8:8:4:4:20:9:9:9:8:12:8:4:4:8:17:11:11:12:7:7:8:8:6:6:19:4:4:6:4:17:7:7:10:13:10:1:1:13:8:8:8:13:5:5:5:13:1:1:11:13:11:7:7:13:3:3:7:13:7:10:10:13:7:7:2:13:2:2:2:13:9:9:9:13:8:8:11:13:11:4:4:13:4:6:6:13:3:3:9:13:9:10:10:13:7:7:6:13:6:6:8:13:8:11:11:13:11:1:1:13:1:6:6:13:4:4:5:14:5:5:11:14:11:11:10:14:10:10:2:14:2:5:5:14:9:9:9:14:9:2:2:14:9:9:11:14:11:11:11:14:4:4:5:14:5:7:7:14:7:7:11:14:11:4:4:14:1:1:8:14:8:10:10:14:9:9:2:14:2:8:8:14:8:9:9:14:3:3:3:14:9:9:5:14:5:5:1:14:1:5:5:14:9:9:9:14:3:3:5:14:5:11:11:14:4:4:4:14:10:10:9:14:9:6:6:14:7:7:1:14:1:1:3:14:3:3:5:14:5:5:11:14:11:11:10:14:10:10:7:14:7:2:7:14:7:6:6:14:9:9:2:14:2:1:1:14:10:10:2:14:2:2:3:14:3:8:8:14:6:6:8:14:8:11:11:14:4:4:10:14:10:1:1:14:10:10:10:14:3:3:4:14:4:8:8:14:4:4:6:14:6:6:3:14:3:3:6:6:6:10:10:9:10:10:4:4:11:10:10:6:2:2:2:6:6:6:10:10:9:9:3:3:3:1:1:7:7:7:8:8:10:10:10:1:1:6:6:4:4:6:6:8:8:10:10:2:2:2:9:9:9:9:5:5:5:8:8:11:11:11:7:7:7:1:1:4:4:3:3:11:11:1:1:10:10:4:4:8:8:11:11:9:9:7:7:8:8:6:6:5:1:1:8:8:7:7:1:1:1:7:7:5:11:11:3:3:10:10:6:7:7:7:9:9:9:4:4:10:10:10:3:3:11:11:11:8:8:2:2:2:5:5:2:2:2:11:11:11:2:2:9:1:1:5:5:5:3:3:8:10:4:4:9:9:3:3:2:3:3:9:8:8:4:4:4:10:10:2:2:10:12:10:4:4:4:4:10:10:12:8:8:3:19:3:3:1:1:19:11:11:11:2:2:19:8:8:2:12:7:7:2:12:2:2:9:19:10:10:9:17:7:9:9:1:1:12:8:8:3:3:3:19:7:1:1:6:12:6:5:5:2:19:3:3:10:10:5:12:5:8:8:9:9:9:21:3:3:7:12:7:9:9:5:5:5:17:3:3:3:3:12:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:12:7:7:6:6:12:6:7:7:7:20:21:11:11:7:7:12:7:6:9:9:17:3:3:3:20:1:1:10:12:11:11:3:19:21:5:5:4:4:12:4:6:6:6:21:19:10:3:3:5:5:12:10:10:2:2:22:20:2:8:8:12:8:5:5:5:12:7:7:7:7:17:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:20:1:6:6:17:4:4:8:8:12:10:10:6:6:7:7:7:9:9:10:12:10:8:8:4:4:20:9:9:9:8:12:8:4:4:8:17:11:11:12:7:7:8:8:6:6:19:4:4:6:4:17:8:8:8:13:2:2:6:13:6:4:4:13:6:6:10:13:10:4:4:13:10:10:11:13:11:11:3:13:3:1:1:13:5:5:4:13:4:5:5:13:7:7:1:13:1:7:7:13:6:6:6:13:10:10:2:13:2:2:5:13:5:11:11:13:4:4:6:13:6:8:8:13:9:9:8:13:8:11:11:13:7:7:9:13:9:9:8:13:8:11:11:13:9:9:1:13:1:3:3:13:2:2:7:13:7:8:8:13:8:7:7:14:7:2:2:14:3:3:7:14:7:7:7:14:11:11:4:14:4:9:9:14:10:10:7:14:7:9:9:14:4:4:4:14:6:6:6:14:1:1:3:14:3:9:9:14:8:8:8:14:8:1:1:14:6:6:9:14:9:4:4:14:5:5:5:14:11:11:11:14:10:10:10:14:11:11:11:14:3:3:3:14:2:2:4:14:4:4:4:14:1:1:1:14:9:9:9:14:9:11:11:14:5:5:11:14:11:3:3:14:10:10:10:14:3:3:1:14:1:5:2:14:2:6:6:14:6:5:5:14:10:10:9:14:9:2:2:14:5:5:8:14:8:6:6:14:5:5:5:14:5:10:10:14:3:3:3:14:10:10:1:14:1:1:2:14:2:10:10:14:9:9:3:14:10:10:1:1:6:7:7:10:9:2:2:8:2:4:7:8:2:2:2:6:6:6:10:10:9:9:3:3:3:1:1:7:7:7:8:8:10:10:10:1:1:6:6:4:4:6:6:8:8:10:10:2:2:2:9:9:9:9:5:5:5:8:8:11:11:11:7:7:7:1:1:4:4:3:3:11:11:1:1:10:10:4:4:8:8:11:11:9:9:7:7:8:8:6:6:5:1:1:8:8:7:7:1:1:1:7:7:5:11:11:3:3:10:10:6:7:7:7:9:9:9:4:4:10:10:10:3:3:11:11:11:8:8:2:2:2:5:5:2:2:2:11:11:11:2:2:9:1:1:5:5:5:3:3:8:10:4:4:9:9:3:3:2:3:3:9:8:8:4:4:4:10:10:2:2:10:12:10:4:4:4:4:10:10:12:8:8:3:19:3:3:1:1:19:11:11:11:2:2:19:8:8:2:12:7:7:2:12:2:2:9:19:10:10:9:17:7:9:9:1:1:12:8:8:3:3:3:19:7:1:1:6:12:6:5:5:2:19:3:3:10:10:5:12:5:8:8:9:9:9:21:3:3:7:12:7:9:9:5:5:5:17:3:3:3:3:12:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:12:7:7:6:6:12:6:7:7:7:20:11:11:11:7:7:12:7:6:9:9:17:3:3:3:20:1:1:10:12:11:11:3:19:21:5:5:4:4:12:4:6:6:6:21:19:10:3:3:5:5:12:10:10:2:2:22:20:2:8:8:12:8:5:5:5:12:7:7:7:7:17:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:20:1:6:6:17:4:4:8:8:12:10:10:6:6:7:7:7:9:9:10:12:10:8:8:4:4:20:9:9:9:8:12:8:4:4:8:17:11:11:12:7:7:8:8:6:6:19:4:4:6:4:17:9:9:6:13:6:3:3:13:3:4:4:13:5:5:5:13:1:1:1:13:9:9:11:13:11:3:3:13:11:11:3:13:3:4:4:13:6:6:6:13:10:10:10:13:11:11:9:13:9:9:1:13:1:1:5:13:5:5:4:13:4:4:2:13:2:5:5:13:8:8:8:13:10:10:4:13:4:1:1:13:9:9:7:13:7:7:9:13:9:3:3:13:3:3:7:13:7:10:10:13:3:3:9:13:9:7:7:13:7:6:6:13:2:2:9:13:9:4:4:14:10:10:10:14:7:3:3:14:2:2:2:14:2:3:3:14:3:3:4:14:4:4:9:14:9:8:8:14:5:5:6:14:6:9:9:14:9:8:8:14:6:6:1:14:1:6:6:14:11:11:2:14:2:8:8:14:4:10:10:14:10:8:8:14:7:7:7:14:5:5:11:14:11:11:5:14:5:10:10:14:10:9:9:14:1:1:1:14:7:7:11:14:11:2:2:14:2:10:10:14:1:1:1:14:1:9:9:14:11:11:6:14:6:6:2:14:2:5:5:14:11:11:11:14:10:10:10:14:10:7:7:14:6:6:6:14:6:10:10:14:10:2:2:14:5:5:5:14:2:2:4:14:4:7:7:14:8:8:3:14:11:11:8:14:8:1:1:4:4:4:2:8:8:7:7:5:8:8:8:1:2:2:2:6:6:6:10:10:9:9:3:3:3:1:1:7:7:7:8:8:10:10:10:1:1:6:6:4:4:6:6:8:8:10:10:2:2:2:9:9:9:9:5:5:5:8:8:11:11:11:7:7:7:1:1:4:4:3:3:11:11:1:1:10:10:4:4:8:8:11:11:9:9:7:7:8:8:6:6:5:1:1:8:8:7:7:1:1:1:7:7:5:11:11:3:3:10:10:6:7:7:7:9:9:9:4:4:10:10:10:3:3:11:11:11:8:8:2:2:2:5:5:2:2:2:11:11:11:2:2:9:1:1:5:5:5:3:3:8:10:4:4:9:9:3:3:2:3:3:9:8:8:4:4:4:10:10:2:2:10:12:10:4:4:4:4:10:10:12:8:8:3:19:3:3:1:1:19:11:11:11:2:2:19:8:8:2:12:7:7:2:12:2:2:9:19:10:10:9:17:7:9:9:1:1:12:8:8:3:3:3:19:7:1:1:6:12:6:5:5:2:19:3:3:10:10:5:12:5:8:8:9:9:9:21:3:3:7:12:7:9:9:5:5:5:17:3:3:3:3:12:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:12:7:7:6:6:12:6:7:7:7:7:11:11:11:7:7:12:7:6:9:9:17:3:3:3:20:1:1:10:12:11:11:3:19:21:5:5:4:4:12:4:6:6:6:21:19:10:3:3:5:5:12:10:10:2:2:22:20:2:8:8:12:8:5:5:5:5:7:7:7:7:17:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:20:1:6:6:17:4:4:8:8:12:10:10:6:6:7:7:7:9:9:10:12:10:8:8:4:4:20:9:9:9:8:12:8:4:4:8:8:11:11:12:7:7:8:8:6:6:9:4:4:6:4:17:8:8:8:13:8:5:5:13:5:5:9:13:9:10:10:13:9:9:11:13:11:1:1:13:9:4:4:13:1:1:3:13:3:8:8:13:1:1:4:13:4:3:3:13:3:5:5:13:11:11:11:13:7:7:1:13:1:9:4:13:4:9:9:13:8:8:2:13:2:2:9:13:9:4:4:13:4:10:10:13:1:1:9:13:9:9:11:13:11:1:1:13:1:11:11:13:7:7:8:13:8:5:5:13:5:4:4:13:4:6:6:13:10:10:10:13:3:3:10:13:10:11:11:13:3:3:6:13:6:11:11:14:7:7:9:14:9:7:7:14:7:8:8:14:6:6:9:14:9:9:9:14:4:4:4:14:7:7:6:14:6:10:10:14:8:8:8:14:10:10:6:14:6:3:3:14:5:6:6:14:6:11:11:14:4:4:10:14:10:5:5:14:5:5:7:14:7:9:9:14:3:3:2:14:2:4:4:14:2:2:2:14:6:6:9:14:9:3:4:14:2:2:3:14:3:7:7:14:7:1:1:14:10:10:2:14:2:1:1:14:5:5:7:14:7:8:8:14:7:7:10:14:1:1:1:14:6:6:6:14:10:10:10:14:8:8:11:14:11:2:2:14:5:5:2:14:2:2:9:14:2:2:11:14:11:6:6:8:10:10:3:3:10:10:5:5:11:2:3:3:2:10:10:10:10:9:9:9:1:1:1:4:4:3:3:8:8:5:5:11:11:2:11:11:1:1:9:9:1:1:11:11:7:7:7:8:8:10:10:10:11:11:3:3:9:9:7:7:11:11:11:9:9:10:10:10:5:5:1:1:4:4:6:6:8:8:1:1:6:6:5:5:10:10:9:9:6:6:7:7:7:11:11:7:7:7:10:10:3:3:8:8:8:6:6:6:8:8:4:4:2:2:2:3:3:3:2:2:3:3:2:2:8:8:6:9:9:9:2:2:4:4:3:3:5:5:3:3:4:4:1:1:7:7:7:1:1:2:2:2:7:2:11:11:10:5:5:8:8:9:8:8:4:4:4:10:10:2:2:10:12:10:4:4:4:4:10:10:12:8:8:3:19:3:3:1:1:19:11:11:11:2:2:19:8:8:2:12:7:7:2:12:2:2:9:19:10:10:9:17:7:9:9:1:1:12:8:8:3:3:3:19:7:1:1:6:12:6:5:5:2:19:3:3:10:10:5:12:5:8:8:9:9:9:21:3:3:7:12:7:9:9:5:5:5:17:3:3:3:3:12:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:4:7:7:6:6:12:6:7:7:7:7:11:11:11:7:7:12:7:6:9:9:17:3:3:3:20:1:1:10:12:11:11:3:19:21:5:5:4:4:12:4:6:6:6:21:19:10:3:3:5:5:12:10:10:2:2:22:20:2:8:8:12:8:5:5:5:5:7:7:7:7:17:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:20:1:6:6:17:4:4:8:8:12:10:10:6:6:7:7:7:9:9:10:12:10:8:8:4:4:20:9:9:9:8:12:8:4:4:8:8:11:11:4:7:7:8:8:6:6:9:4:4:6:4:17:3:3:3:13:2:2:11:13:11:8:8:13:8:7:7:13:11:11:9:13:9:7:7:13:6:6:6:13:5:5:2:13:2:1:1:13:7:7:11:13:11:2:2:13:5:5:11:13:11:7:7:13:6:6:6:13:1:1:11:13:11:11:5:13:5:5:5:13:3:3:1:13:1:6:6:13:6:8:8:13:8:11:11:13:7:7:7:13:3:3:1:13:1:9:9:13:1:1:3:13:3:3:3:13:7:7:1:13:1:2:2:13:4:4:9:13:9:2:2:13:6:6:9:13:9:4:11:13:11:9:9:13:5:5:1:13:1:8:4:13:4:2:2:14:2:2:4:14:4:1:1:14:1:9:9:14:9:6:6:14:10:10:2:14:9:9:10:14:10:4:4:14:10:10:10:14:8:8:8:14:4:4:2:14:2:1:1:14:10:10:4:14:4:10:10:14:5:5:8:14:8:9:9:14:9:3:3:14:10:10:10:14:10:7:7:14:3:3:4:14:4:4:5:14:5:7:7:14:7:4:4:14:4:10:10:14:5:5:5:14:8:6:6:14:5:5:5:14:3:3:2:14:2:7:7:14:3:3:3:14:11:10:10:14:6:6:6:14:9:9:8:14:8:9:9:14:10:10:8:14:8:8:10:11:11:9:9:9:6:6:4:2:8:10:10:1:11:11:10:8:11:11:1:1:2:2:7:7:4:4:4:4:2:2:5:5:10:10:7:7:7:2:2:2:2:5:5:5:3:3:11:11:11:7:7:8:8:3:3:4:4:4:10:10:3:3:2:2:2:7:7:4:1:1:1:11:11:9:9:10:7:7:5:8:8:10:10:10:9:9:2:2:1:1:1:3:3:1:1:3:3:10:10:10:8:8:9:9:9:4:4:10:10:8:8:5:5:8:8:9:9:7:7:7:2:11:11:3:3:3:9:9:6:6:6:3:3:8:8:11:6:6:6:1:1:1:8:8:8:7:11:11:6:6:6:9:9:2:6:5:5:11:11:1:1:9:9:11:10:10:8:8:4:4:4:10:10:2:2:10:12:10:4:4:4:4:10:10:12:8:8:3:19:3:3:1:1:19:11:11:11:2:2:19:8:8:2:7:7:7:2:12:2:2:9:19:10:10:9:17:7:9:9:1:1:12:8:8:3:3:3:19:7:1:1:6:12:6:5:5:2:19:3:3:10:10:5:12:5:8:8:9:9:9:21:3:3:7:12:7:9:9:5:5:5:17:3:3:3:3:12:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:4:7:7:6:6:12:6:7:7:7:7:11:11:11:7:7:12:7:6:9:9:17:3:3:3:20:1:1:10:12:11:11:3:19:21:5:5:4:4:12:4:6:6:6:21:19:10:3:3:5:5:12:10:10:2:2:22:20:2:8:8:12:8:5:5:5:5:7:7:7:7:17:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:20:1:6:6:17:4:4:8:8:12:10:10:6:6:7:7:7:9:9:10:12:10:8:8:4:4:20:9:9:9:8:12:8:4:4:8:8:11:11:4:7:7:8:8:6:6:9:4:4:6:4:17:9:9:9:13:11:11:6:13:6:6:6:13:9:9:8:13:8:10:10:13:9:9:8:13:8:4:4:13:3:3:11:13:11:1:1:13:7:7:5:13:5:9:9:13:10:4:4:13:8:8:5:13:5:3:3:13:3:4:4:13:4:7:7:13:11:11:10:13:10:3:3:13:6:6:3:13:3:5:5:13:7:7:9:13:9:2:2:13:5:5:11:13:11:11:4:13:7:9:9:13:1:1:6:13:6:9:9:13:10:10:10:13:10:1:1:13:10:10:8:13:8:3:3:13:3:10:10:13:7:7:5:14:5:9:9:14:2:2:4:14:4:4:4:14:6:6:9:14:9:9:6:14:6:2:2:14:2:9:9:14:8:8:8:14:8:10:10:14:1:1:2:14:2:6:6:14:7:7:5:14:5:5:5:14:10:10:5:14:5:5:11:14:11:11:4:14:4:3:3:14:9:9:9:14:4:4:4:14:2:2:2:14:2:7:7:14:7:7:4:14:4:10:10:14:3:3:8:14:8:11:11:14:1:1:11:14:11:6:6:14:7:7:1:14:1:8:8:14:8:8:3:14:3:1:1:14:2:2:1:14:1:8:8:14:9:11:11:14:1:1:10:14:10:7:7:7:5:5:10:10:2:2:11:11:4:3:3:1:1:6:6:6:6:2:2:2:10:10:1:5:1:1:4:4:4:6:6:6:8:8:2:2:9:9:10:10:1:1:2:2:2:2:1:1:3:3:9:9:9:1:10:10:7:7:10:10:10:6:6:5:5:7:7:3:3:7:7:9:9:9:8:8:11:11:11:10:10:10:3:3:11:3:3:6:6:5:5:2:2:6:8:8:8:7:7:7:8:5:5:8:8:11:11:9:9:9:11:11:11:7:7:4:4:4:5:5:3:3:7:7:6:6:8:8:3:3:11:11:11:5:5:9:9:9:8:8:10:10:11:11:1:1:8:1:1:7:2:2:1:1:3:3:3:9:2:2:2:11:2:2:4:4:10:10:1:1:10:7:4:4:8:8:4:4:4:10:10:2:2:10:10:10:4:4:4:4:10:10:12:8:8:3:19:3:3:1:1:19:11:11:11:2:2:19:8:8:2:7:7:7:2:12:2:2:9:10:10:10:9:17:7:9:9:1:1:1:8:8:3:3:3:19:7:1:1:6:6:6:5:5:2:2:3:3:10:10:5:12:5:8:8:9:9:9:21:3:3:7:12:7:9:9:5:5:5:17:3:3:3:3:5:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:4:7:7:6:6:12:6:7:7:7:7:11:11:11:7:7:12:7:6:9:9:17:3:3:3:20:1:1:10:10:11:11:3:19:21:5:5:4:4:12:4:6:6:6:21:10:10:3:3:5:5:12:10:10:2:2:22:20:2:8:8:12:8:5:5:5:5:7:7:7:7:17:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:20:1:6:6:4:4:4:8:8:10:10:10:6:6:7:7:7:9:9:10:10:10:8:8:4:4:20:9:9:9:8:8:8:4:4:8:8:11:11:4:7:7:8:8:6:6:9:4:4:6:4:4:3:3:3:2:2:2:11:13:11:8:8:13:8:7:7:13:11:11:9:13:9:7:7:13:6:6:6:5:5:5:2:13:2:1:1:13:7:7:11:13:11:2:2:13:5:5:11:13:11:7:7:13:6:6:6:1:1:1:11:13:11:11:5:13:5:5:5:13:3:3:1:1:1:6:6:13:6:8:8:13:8:11:11:13:7:7:7:13:3:3:1:13:1:9:9:13:1:1:3:13:3:3:3:13:7:7:1:1:1:2:2:13:4:4:9:13:9:2:2:13:6:6:9:13:9:4:11:13:11:9:9:13:5:5:1:13:1:8:4:13:4:2:2:14:2:2:4:14:4:1:1:14:1:9:9:14:9:6:6:14:10:10:2:14:9:9:10:14:10:4:4:9:10:10:10:14:8:8:8:14:4:4:2:14:2:1:1:14:10:10:4:14:4:10:10:14:5:5:8:14:8:9:9:14:9:3:3:14:10:10:10:14:10:7:7:14:3:3:4:14:4:4:5:14:5:7:7:14:7:4:4:14:4:10:10:14:5:5:5:14:8:6:6:14:5:5:5:14:3:3:2:14:2:7:7:14:3:3:3:14:11:10:10:14:6:6:6:14:9:9:8:14:8:9:9:14:10:10:8:14:8:8:10:11:11:9:9:9:6:6:4:2:8:10:10:1:11:11:10:8:1:1:10:10:1:1:1:8:8:5:5:5:10:10:2:3:3:8:8:2:2:9:10:10:5:5:2:2:7:7:3:3:3:7:7:9:9:2:2:11:11:6:6:7:7:8:8:9:9:11:11:11:5:5:11:11:4:4:8:8:8:8:6:6:11:11:1:1:11:11:1:1:3:3:2:2:3:3:1:1:1:4:4:9:7:7:10:10:5:5:10:10:5:4:4:6:6:11:11:10:10:10:2:2:7:7:7:3:3:9:9:4:4:4:7:7:9:9:9:10:10:6:6:3:3:4:11:11:9:9:9:2:2:3:3:9:1:1:7:7:2:2:6:6:8:8:1:8:8:8:</t>
-  </si>
-  <si>
-    <t>2:2:5:5:2:2:9:9:7:7:6:3:2:2:2:4:17:4:6:6:6:8:8:8:1:1:1:6:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:6:2:2:10:10:4:4:17:4:6:6:11:11:11:3:3:7:7:7:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:3:6:6:6:10:17:10:4:4:2:2:2:10:10:6:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:5:5:5:7:7:7:11:11:5:17:5:11:11:11:2:2:2:5:5:4:4:6:6:6:7:7:7:6:6:8:8:8:7:7:7:7:1:1:9:9:4:4:4:5:5:1:1:3:3:5:5:9:9:9:6:11:11:11:9:9:9:2:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:15:11:11:1:1:6:1:1:7:7:4:4:4:4:9:9:1:1:1:2:2:2:4:4:4:6:6:6:1:3:3:5:5:1:1:1:8:8:8:1:1:6:6:5:5:5:4:4:2:2:2:6:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:15:7:3:3:3:2:2:6:3:1:1:5:5:5:3:3:4:4:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:15:7:7:10:6:2:2:2:1:1:7:1:7:7:3:3:3:3:7:7:6:6:11:11:8:8:4:4:10:10:2:2:5:5:4:4:6:6:6:6:1:1:10:10:6:6:7:7:11:11:9:9:1:1:9:9:11:11:11:11:9:9:9:3:3:6:6:5:5:2:2:8:8:2:2:1:1:1:5:5:10:10:10:10:8:8:8:8:10:10:5:5:2:11:11:9:9:9:10:10:1:1:9:9:5:6:6:8:8:4:4:11:11:11:11:9:9:7:7:3:3:3:1:1:5:5:6:6:4:4:10:10:9:9:9:8:8:1:1:1:10:10:10:5:5:3:3:2:2:9:9:9:6:6:6:10:10:8:8:8:6:6:6:6:3:3:3:9:9:8:8:10:10:1:1:1:7:7:1:1:1:3:3:3:10:10:4:4:7:7:7:5:5:5:5:11:11:4:4:7:5:5:7:7:7:11:11:9:9:9:8:8:4:4:5:5:2:2:2:6:6:11:11:4:4:5:9:9:10:10:9:9:9:11:11:9:9:9:6:6:8:8:8:11:11:3:3:3:8:8:8:8:2:2:10:10:4:4:5:5:10:10:1:1:1:1:10:2:2:11:11:7:7:7:3:3:4:4:8:8:4:4:7:7:8:2:2:11:11:11:6:6:6:7:7:4:4:4:5:5:2:7:11:6:6:5:5:1:5:9:9:5:3:10:10:10:7:7:7:11:11:5:5:1:1:10:10:10:11:11:3:3:6:6:8:8:9:9:9:7:7:4:4:3:3:3:8:8:1:1:2:2:1:1:1:4:4:4:6:6:9:9:8:8:7:7:7:9:9:9:1:1:11:11:6:6:2:2:5:5:1:1:1:2:2:2:7:7:11:11:10:10:10:4:4:1:1:8:8:8:6:6:4:4:11:11:11:9:9:8:8:9:9:7:7:7:5:5:1:5:5:5:8:8:8:2:2:3:3:3:3:2:2:3:3:3:10:10:7:7:10:10:10:11:11:5:2:2:11:11:9:9:6:6:9:3:3:2:2:4:8:10:2:2:5:5:2:15:9:9:7:7:3:3:2:2:2:4:17:4:6:6:6:8:8:8:15:1:1:5:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:6:2:2:10:10:4:4:17:4:6:6:11:11:16:3:3:7:7:16:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:16:6:6:6:10:17:10:4:4:2:2:2:10:10:16:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:16:5:5:7:7:16:11:11:5:17:5:11:11:11:2:2:2:16:5:4:4:6:6:9:7:7:15:6:6:8:8:16:7:7:7:7:1:1:9:9:16:4:4:5:5:15:1:3:3:5:5:9:9:9:16:11:11:11:9:9:15:9:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:15:11:11:1:1:6:1:1:7:7:4:4:16:4:9:9:1:15:1:2:2:2:4:4:4:16:6:6:1:3:3:5:5:1:15:1:8:8:8:1:1:6:6:16:5:5:4:4:2:2:2:15:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:15:7:3:3:3:2:2:16:3:1:1:5:5:5:3:3:4:15:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:15:7:7:10:6:2:2:16:1:1:7:1:4:4:9:9:4:4:6:6:8:8:3:3:9:4:4:10:10:4:4:5:5:9:9:7:7:5:5:4:8:8:6:6:8:8:4:4:2:2:10:10:11:11:3:3:7:7:10:10:10:2:2:10:10:8:8:11:11:2:2:5:5:5:1:1:8:8:8:11:11:11:11:8:8:2:2:5:5:11:11:10:10:6:6:3:3:9:9:10:10:8:8:4:4:6:6:6:1:1:7:7:11:11:7:7:1:1:5:5:6:6:6:4:4:4:9:9:9:11:11:7:7:1:1:1:6:6:6:3:3:8:8:8:9:9:9:10:10:10:10:1:1:6:6:2:2:2:1:1:5:5:7:7:5:5:2:2:10:10:9:9:9:10:10:5:5:4:3:3:10:10:8:8:3:3:1:1:6:6:10:10:6:6:1:1:5:5:10:10:4:4:2:2:5:2:2:2:2:8:8:3:3:6:2:2:2:2:5:5:7:7:4:4:11:11:11:3:3:3:3:1:1:9:9:9:11:11:1:1:3:3:3:3:7:7:9:9:9:5:5:6:6:11:11:11:8:8:8:4:4:1:1:6:6:6:10:10:10:5:5:11:11:11:11:7:7:9:9:6:6:7:7:6:5:5:8:8:5:5:9:9:1:1:4:4:8:8:7:7:3:3:9:9:11:11:7:7:9:9:7:3:3:10:10:10:7:7:7:11:11:5:5:1:1:10:10:10:11:11:3:3:6:6:8:8:9:9:9:7:7:4:4:3:3:3:8:8:1:1:2:2:1:1:1:4:4:4:6:6:9:9:8:8:7:7:7:9:9:9:1:1:11:11:6:6:2:2:5:5:1:1:1:2:2:2:7:7:11:11:10:10:10:4:4:1:1:8:8:8:6:6:4:4:11:11:11:9:9:8:8:9:9:7:7:7:5:5:1:5:5:5:8:8:8:2:2:3:3:3:3:2:2:3:3:3:10:10:7:7:10:10:10:11:11:5:2:2:11:11:9:9:6:6:9:3:3:2:2:4:8:10:2:2:5:5:2:2:9:9:7:7:3:3:2:2:2:4:17:4:6:6:6:8:8:8:15:1:1:5:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:6:2:2:10:10:4:4:17:4:6:6:11:11:3:3:3:7:7:16:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:16:6:6:6:10:17:10:4:4:2:2:2:10:10:16:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:16:5:5:7:7:16:11:11:5:17:5:11:11:11:2:2:2:16:5:4:4:6:6:9:7:7:15:6:6:8:8:16:7:7:7:7:1:1:9:9:16:4:4:5:5:15:1:3:3:5:5:9:9:9:16:11:11:11:9:9:15:9:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:15:11:11:1:1:6:1:1:7:7:4:4:16:4:9:9:1:15:1:2:2:2:4:4:4:16:6:6:1:3:3:5:5:1:15:1:8:8:8:1:1:6:6:16:5:5:4:4:2:2:2:15:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:15:7:3:3:3:2:2:3:3:1:1:5:5:5:3:3:4:15:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:15:7:7:10:6:2:2:2:1:1:7:1:11:11:10:10:11:11:7:7:3:3:9:9:9:9:10:10:10:8:8:10:10:2:2:5:5:1:1:1:1:10:10:11:11:5:5:10:10:10:9:9:4:4:9:6:6:6:5:5:11:11:5:5:5:10:10:10:8:8:5:5:8:8:4:4:8:8:8:2:2:5:5:8:8:1:1:1:11:11:7:7:5:5:2:2:11:11:11:2:2:7:7:4:4:8:8:8:7:7:4:4:6:6:10:10:10:7:7:7:10:10:10:6:6:9:9:8:8:9:9:9:8:8:8:6:6:9:9:3:3:5:5:5:2:2:11:11:1:1:2:2:8:8:5:5:3:3:3:6:6:8:8:11:11:10:10:3:3:2:2:4:4:5:5:5:8:8:2:2:5:5:5:7:7:6:6:6:9:9:9:11:11:1:1:7:7:8:8:10:10:10:11:11:11:6:6:7:7:1:1:6:6:6:4:4:1:1:4:4:5:5:1:1:3:3:4:4:2:2:10:10:10:1:1:1:2:2:1:1:1:1:4:4:9:9:9:9:7:7:7:3:3:11:11:11:4:4:7:7:5:5:3:3:6:6:9:9:4:4:4:8:10:4:4:3:3:3:3:6:6:2:2:3:3:1:2:2:6:6:6:7:7:3:3:3:2:7:9:9:9:8:8:3:6:6:9:9:6:6:9:9:3:10:10:10:7:7:7:11:11:5:5:1:1:10:10:10:11:11:3:3:6:6:8:8:9:9:9:7:7:4:4:3:3:3:8:8:1:1:2:2:1:1:1:4:4:4:6:6:9:9:8:8:7:7:7:9:9:9:1:1:11:11:6:6:2:2:5:5:1:1:1:2:2:2:7:7:11:11:10:10:10:4:4:1:1:8:8:8:6:6:4:4:11:11:11:9:9:8:8:9:9:7:7:7:5:5:1:5:5:5:8:8:8:2:2:3:3:3:3:2:2:3:3:3:10:10:7:7:10:10:10:11:11:5:2:2:11:11:9:9:6:6:9:3:3:2:2:4:8:10:2:2:5:5:2:2:9:9:7:7:3:3:2:2:2:4:17:4:6:6:6:8:8:8:8:1:1:5:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:6:2:2:10:10:4:4:17:4:6:6:11:11:3:3:3:7:7:3:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:16:6:6:6:10:17:10:4:4:2:2:2:10:10:16:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:16:5:5:7:7:16:11:11:5:17:5:11:11:11:2:2:2:16:5:4:4:6:6:9:7:7:15:6:6:8:8:16:7:7:7:7:1:1:9:9:16:4:4:5:5:15:1:3:3:5:5:9:9:9:16:11:11:11:9:9:15:9:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:15:11:11:1:1:6:1:1:7:7:4:4:16:4:9:9:1:15:1:2:2:2:4:4:4:16:6:6:1:3:3:5:5:1:15:1:8:8:8:1:1:6:6:6:5:5:4:4:2:2:2:15:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:15:7:3:3:3:2:2:3:3:1:1:5:5:5:3:3:4:15:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:15:7:7:10:6:2:2:2:1:1:7:1:11:11:2:2:2:5:5:4:4:6:6:3:3:7:7:6:6:5:5:5:8:8:5:5:9:9:9:6:6:1:1:2:2:3:3:2:2:4:2:2:6:6:10:10:10:9:9:9:2:2:4:5:5:5:3:3:2:2:2:10:10:5:5:2:2:11:11:4:4:5:5:7:7:5:5:1:1:8:8:3:3:1:1:8:8:7:7:7:3:3:3:6:6:6:10:10:4:4:11:11:10:10:11:11:9:9:10:10:2:2:1:1:1:3:3:11:11:11:6:6:6:8:8:8:1:1:10:10:7:7:3:3:4:4:10:10:7:7:5:5:4:4:4:7:7:11:5:5:7:7:1:1:1:9:9:11:11:4:4:6:6:9:9:7:4:8:8:8:1:1:8:8:6:6:10:10:11:11:11:3:3:3:9:9:9:7:7:9:9:9:3:3:3:5:5:5:1:1:1:10:10:7:7:7:7:2:2:4:4:8:8:6:6:11:11:2:2:8:8:8:8:7:7:4:4:9:9:9:11:11:4:4:11:11:2:2:10:10:1:1:1:7:10:10:1:1:8:8:3:3:3:8:8:8:6:6:8:8:10:10:10:6:6:9:9:8:8:9:9:6:6:10:10:4:4:6:6:9:9:6:6:4:10:10:8:1:2:5:5:11:11:5:5:9:9:5:5:3:9:5:8:8:8:7:7:5:5:8:8:6:6:9:9:5:5:8:8:3:3:8:8:4:4:2:2:2:3:3:10:10:10:9:9:9:1:1:1:8:8:7:7:7:4:4:4:4:10:10:3:3:5:5:8:8:2:2:10:10:1:1:8:8:7:7:7:7:9:9:10:10:10:3:3:11:11:11:2:2:1:11:11:3:3:3:4:4:1:1:1:11:11:7:7:1:1:9:9:2:2:2:1:1:4:4:6:6:7:7:7:2:2:7:9:9:11:11:6:6:9:9:9:1:1:11:11:11:3:3:11:11:2:2:6:6:10:10:5:5:5:2:10:10:10:3:3:6:6:11:9:5:2:2:5:5:2:2:9:9:7:7:3:3:2:2:2:4:17:4:6:6:6:8:8:8:8:1:1:5:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:6:2:2:10:10:4:4:17:4:6:6:11:11:3:3:3:7:7:3:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:16:6:6:6:10:17:10:4:4:2:2:2:10:10:16:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:16:5:5:7:7:16:11:11:5:17:5:11:11:11:2:2:2:16:5:4:4:6:6:9:7:7:15:6:6:8:8:16:7:7:7:7:1:1:9:9:16:4:4:5:5:15:1:3:3:5:5:9:9:9:16:11:11:11:9:9:15:9:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:15:11:11:1:1:6:1:1:7:7:4:4:16:4:9:9:1:15:1:2:2:2:4:4:4:16:6:6:1:3:3:5:5:1:15:1:8:8:8:1:1:6:6:6:5:5:4:4:2:2:2:15:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:15:7:3:3:3:2:2:3:3:1:1:5:5:5:3:3:4:15:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:15:7:7:10:6:2:2:2:1:1:7:1:5:5:7:7:7:7:4:4:4:2:2:3:3:11:11:8:8:10:10:6:6:3:3:3:7:7:7:2:2:8:11:10:10:2:9:9:4:4:4:5:5:9:9:10:10:9:9:3:3:7:7:7:10:10:10:10:6:6:11:11:6:6:6:9:8:8:9:9:1:1:1:8:8:1:1:9:9:5:9:5:5:6:6:4:4:10:10:4:4:4:6:6:11:11:7:7:7:4:4:3:3:8:8:8:9:9:8:8:8:3:3:3:7:7:7:2:2:7:7:7:2:2:1:1:3:3:3:8:8:5:5:4:4:2:2:10:5:5:6:6:6:4:4:3:3:5:5:8:8:9:9:1:1:10:10:9:9:6:6:2:2:10:10:6:6:1:1:1:6:6:4:4:4:11:11:9:9:9:9:8:8:8:5:5:6:6:11:6:6:6:11:11:11:11:7:7:5:5:11:11:10:10:11:11:9:9:10:10:1:1:10:10:9:9:9:5:5:11:11:2:2:3:7:7:1:1:8:10:10:5:5:1:1:11:11:4:4:4:2:2:3:3:3:11:11:5:5:6:6:3:3:1:1:10:10:10:10:5:5:8:8:8:1:1:8:8:1:1:2:2:8:8:8:4:4:2:2:2:2:6:6:5:5:8:6:11:9:9:9:3:3:5:5:7:7:10:5:2:2:1:10:10:10:10:9:9:6:6:6:7:7:7:9:2:2:6:6:8:8:3:3:5:5:11:11:8:8:3:3:4:4:4:1:1:2:1:1:7:7:9:9:5:5:6:6:2:2:1:1:7:7:11:11:11:8:2:2:1:1:11:11:11:11:3:3:3:4:4:10:10:11:11:2:2:7:7:7:8:8:8:10:10:2:2:2:2:7:7:1:1:6:6:3:3:3:4:4:9:9:10:10:8:8:9:9:9:3:3:3:11:11:5:5:11:11:9:9:8:8:1:1:1:5:5:5:10:10:8:8:2:2:4:4:7:7:7:10:10:8:5:9:9:9:1:1:3:3:10:4:6:2:2:5:5:2:2:9:9:7:7:3:3:2:2:2:4:17:4:6:6:6:8:8:8:8:1:1:5:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:6:2:2:10:10:4:4:17:4:6:6:11:11:3:3:3:7:7:3:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:16:6:6:6:10:17:10:4:4:2:2:2:10:10:16:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:16:5:5:7:7:16:11:11:5:17:5:11:11:11:2:2:2:16:5:4:4:6:6:9:7:7:15:6:6:8:8:16:7:7:7:7:1:1:9:9:16:4:4:5:5:15:1:3:3:5:5:9:9:9:16:11:11:11:9:9:15:9:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:15:11:11:1:1:6:1:1:7:7:4:4:16:4:9:9:1:15:1:2:2:2:4:4:4:16:6:6:1:3:3:5:5:1:15:1:8:8:8:1:1:6:6:6:5:5:4:4:2:2:2:15:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:15:7:3:3:3:2:2:3:3:1:1:5:5:5:3:3:4:15:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:15:7:7:10:6:2:2:2:1:1:7:1:9:9:8:8:10:10:10:5:5:3:3:9:9:6:4:8:8:8:10:10:1:1:11:11:11:6:6:6:3:3:9:9:9:3:3:3:7:7:6:8:8:4:4:1:1:5:5:5:5:11:11:11:7:7:7:11:11:1:1:1:9:9:2:2:11:11:1:1:11:11:4:4:2:2:3:3:3:5:5:2:2:2:2:3:3:6:6:3:3:4:4:3:3:3:7:7:2:2:11:11:10:10:1:1:6:6:8:8:2:2:10:10:10:8:8:6:6:9:9:10:10:5:8:8:10:10:10:4:4:7:1:1:1:3:3:5:5:8:8:3:3:3:7:7:4:4:7:3:3:2:2:5:5:5:4:4:1:1:4:4:4:1:1:1:5:5:5:2:2:9:9:9:7:7:11:11:2:2:2:6:6:6:6:1:1:8:8:3:11:11:5:5:5:6:6:6:2:2:2:7:7:9:9:5:5:7:7:10:10:8:8:8:6:6:10:9:9:11:11:7:7:10:10:4:4:8:8:6:6:8:10:10:8:8:8:2:2:4:4:9:9:9:9:10:10:7:7:7:6:6:8:8:6:6:10:10:9:9:6:7:7:7:10:10:5:5:6:6:8:8:10:10:1:1:4:4:4:9:9:2:11:11:6:5:5:9:9:9:9:1:1:4:4:11:11:5:5:5:11:5:5:5:11:11:9:9:10:10:4:4:2:2:8:8:8:8:11:11:11:4:2:2:2:2:10:10:10:1:1:8:8:8:11:11:11:11:9:9:3:3:9:9:6:6:5:5:8:8:7:7:7:1:1:2:2:2:1:1:5:5:11:11:10:10:4:4:8:8:9:9:6:6:3:3:4:4:4:4:5:5:7:7:7:2:2:3:3:3:5:5:3:3:10:10:10:1:1:6:6:2:2:2:7:7:11:11:11:9:9:1:1:6:6:3:3:9:9:9:9:3:3:1:1:8:8:8:3:3:10:10:7:11:6:6:7:7:1:7:7:7:7:10:10:1:1:8:2:9:10:4:2:2:5:5:2:2:9:9:7:7:3:3:2:2:2:4:17:4:6:6:6:8:8:8:8:1:1:5:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:6:2:2:10:10:4:4:17:4:6:6:11:11:3:3:3:7:7:3:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:16:6:6:6:10:17:10:4:4:2:2:2:10:10:16:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:16:5:5:7:7:16:11:11:5:17:5:11:11:11:2:2:2:5:5:4:4:6:6:9:7:7:15:6:6:8:8:16:7:7:7:7:1:1:9:9:9:4:4:5:5:1:1:3:3:5:5:9:9:9:16:11:11:11:9:9:15:9:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:15:11:11:1:1:6:1:1:7:7:4:4:16:4:9:9:1:15:1:2:2:2:4:4:4:16:6:6:1:3:3:5:5:1:15:1:8:8:8:1:1:6:6:6:5:5:4:4:2:2:2:15:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:15:7:3:3:3:2:2:3:3:1:1:5:5:5:3:3:4:15:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:15:7:7:10:6:2:2:2:1:1:7:1:5:5:7:7:7:7:4:4:4:2:2:3:3:11:11:8:8:10:10:6:6:3:3:3:7:7:7:2:2:8:11:10:10:2:9:9:4:4:4:5:5:9:9:10:10:9:9:3:3:7:7:7:10:10:10:10:6:6:11:11:6:6:6:9:8:8:9:9:1:1:1:8:8:1:1:9:9:5:9:5:5:6:6:4:4:10:10:4:4:4:6:6:11:11:7:7:7:4:4:3:3:8:8:8:9:9:8:8:8:3:3:3:7:7:7:2:2:7:7:7:2:2:1:1:3:3:3:8:8:5:5:4:4:2:2:10:5:5:6:6:6:4:4:3:3:5:5:8:8:9:9:1:1:10:10:9:9:6:6:2:2:10:10:6:6:1:1:1:6:6:4:4:4:11:11:9:9:9:9:8:8:8:5:5:6:6:11:6:6:6:11:11:11:11:7:7:5:5:11:11:10:10:11:11:9:9:10:10:1:1:10:10:9:9:9:5:5:11:11:2:2:3:7:7:1:1:8:10:10:5:5:1:1:11:11:4:4:4:2:2:3:3:3:11:11:5:5:6:6:3:3:1:1:10:10:10:10:5:5:8:8:8:1:1:8:8:1:1:2:2:8:8:8:4:4:2:2:2:2:6:6:5:5:8:6:11:9:9:9:3:3:5:5:7:7:10:5:2:2:1:9:9:8:8:2:2:10:10:4:4:3:3:1:1:11:11:11:11:10:10:8:8:8:8:6:6:7:7:7:3:3:7:7:1:1:1:3:3:11:11:4:4:4:11:11:9:9:2:2:2:2:3:3:10:10:10:8:8:8:10:10:7:7:10:10:1:1:9:9:9:1:1:6:6:7:7:1:1:8:8:9:9:7:7:11:11:9:9:2:2:2:10:10:11:11:2:2:5:5:8:8:7:8:8:3:3:3:5:5:5:3:3:10:10:2:2:3:3:6:4:4:6:6:6:5:5:1:1:1:9:9:2:2:7:7:4:4:11:11:11:9:9:5:5:6:6:4:7:1:5:</t>
+    <t>1,1&amp;300;2,301&amp;600;3,601&amp;750;4,751&amp;1050;5,1051&amp;1350;6,1351&amp;1500;7,1501&amp;1800;8,1801&amp;2100;9,2101&amp;2250;10,2251&amp;2650;11,2651&amp;2950;12,2951&amp;3100;13,3101&amp;3500;14,3501&amp;3800;15,3801&amp;3950;16,3951&amp;4350;17,4351&amp;4650;18,4651&amp;4800;19,4801&amp;5200;20,5201&amp;5500;21,5501&amp;5650</t>
+  </si>
+  <si>
+    <t>6:6:2:2:3:17:4:4:2:2:8:8:4:4:6:6:2:2:2:8:8:1:9:9:9:8:8:11:11:4:4:19:1:1:1:4:4:1:1:7:7:1:1:3:3:19:2:3:3:17:2:6:6:3:3:3:21:3:3:3:6:6:7:7:2:2:3:3:19:6:6:6:5:5:3:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:6:1:1:3:1:1:1:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:11:11:1:1:6:6:7:7:2:2:4:4:4:4:2:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:5:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:7:7:4:4:9:9:21:3:3:3:5:5:8:8:2:17:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:21:4:4:1:8:8:17:10:10:10:20:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:20:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:17:1:1:1:5:5:5:1:1:11:11:11:9:9:1:1:7:7:7:7:5:5:1:1:6:6:6:2:2:11:11:9:9:1:1:2:2:6:10:10:3:3:3:6:6:8:8:2:2:2:7:7:2:2:4:4:4:7:7:6:6:4:4:5:5:8:8:9:9:8:8:8:8:3:4:4:4:3:3:3:9:9:1:1:1:1:4:4:4:5:5:11:11:2:2:10:10:10:8:8:8:6:6:9:9:9:9:6:6:5:5:11:11:11:11:7:7:7:4:4:10:10:2:2:9:9:6:6:11:11:4:4:4:10:10:10:7:7:6:6:6:7:7:7:10:10:8:8:8:1:1:1:11:11:9:9:5:5:10:11:11:11:7:7:9:9:3:3:6:6:4:4:7:7:8:8:7:7:7:7:5:5:7:7:9:9:5:5:5:11:11:5:5:4:4:4:4:7:7:8:8:2:2:3:3:3:8:8:6:6:4:4:2:2:9:9:7:7:7:9:9:9:10:10:10:5:5:3:3:10:10:5:5:5:3:3:5:5:10:10:8:8:2:2:9:9:11:11:11:6:10:10:9:9:5:5:5:8:8:8:3:3:3:2:2:4:4:1:1:6:6:8:8:4:4:6:6:2:2:10:10:11:11:10:10:3:8:8:9:2:2:10:10:10:6:10:6:6:1:6:8:9:9:10:10:11:11:11:9:9:9:8:8:10:10:9:9:10:10:11:11:8:8:8:11:11:10:10:8:8:10:10:8:8:9:9:10:10:11:11:11:10:10:10:9:9:8:8:11:11:11:9:9:8:8:9:9:8:8:9:9:10:10:9:9:11:11:8:8:9:9:11:11:8:8:11:10:10:10:8:8:8:9:9:10:10:8:8:8:9:9:8:8:8:9:9:9:8:8:10:10:11:11:8:8:10:10:8:8:11:11:10:10:9:9:11:11:11:8:8:10:10:11:11:9:10:10:9:9:9:11:11:8:8:10:10:10:9:9:11:11:9:9:11:11:9:9:11:11:8:8:6:6:2:2:3:17:4:4:2:2:8:8:4:4:6:6:2:2:2:8:8:1:9:9:9:8:8:11:11:4:4:19:1:1:1:4:4:1:1:7:7:1:1:3:3:2:2:3:3:17:2:6:6:3:3:3:21:3:3:3:6:6:7:7:2:2:3:3:19:6:6:6:5:5:3:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:6:1:1:3:1:1:1:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:11:11:1:1:6:6:7:7:2:2:4:4:4:4:2:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:5:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:7:7:4:4:9:9:9:3:3:3:5:5:8:8:2:17:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:21:4:4:1:8:8:17:10:10:10:7:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:20:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:17:1:1:1:5:5:5:1:1:11:11:11:9:9:1:1:7:7:7:7:5:5:1:1:6:6:6:2:2:11:11:9:9:1:1:2:2:6:10:10:3:3:3:6:6:8:8:2:2:2:7:7:2:2:4:4:4:7:7:6:6:4:4:5:5:8:8:9:9:8:8:8:8:3:4:4:4:3:3:3:9:9:1:1:1:1:4:4:4:5:5:11:11:2:2:10:10:10:8:8:8:6:6:9:9:9:9:6:6:5:5:11:11:11:11:7:7:7:4:4:10:10:2:2:9:9:6:6:11:11:4:4:4:10:10:10:7:7:6:6:6:7:7:7:10:10:8:8:8:1:1:1:11:11:9:9:5:5:10:11:11:11:7:7:9:9:3:3:6:6:4:4:7:7:8:8:7:7:7:7:5:5:7:7:9:9:5:5:5:11:11:5:5:4:4:4:4:7:7:8:8:2:2:3:3:3:8:8:6:6:4:4:2:2:9:9:7:7:7:9:9:9:10:10:10:5:5:3:3:10:10:5:5:5:3:3:5:5:10:10:8:8:2:2:9:9:11:11:11:6:10:10:9:9:5:5:5:8:8:8:3:3:3:2:2:4:4:1:1:6:6:8:8:4:4:6:6:2:2:10:10:11:11:10:10:3:8:8:9:2:2:10:10:10:6:10:6:6:1:6:8:9:9:10:10:11:11:11:9:9:9:8:8:10:10:9:9:10:10:11:11:8:8:8:11:11:10:10:8:8:10:10:8:8:9:9:10:10:11:11:11:10:10:10:9:9:8:8:11:11:11:9:9:8:8:9:9:8:8:9:9:10:10:9:9:11:11:8:8:9:9:11:11:8:8:11:10:10:10:8:8:8:9:9:10:10:8:8:8:9:9:8:8:8:9:9:9:8:8:10:10:11:11:8:8:10:10:8:8:11:11:10:10:9:9:11:11:11:8:8:10:10:11:11:9:10:10:9:9:9:11:11:8:8:10:10:10:9:9:11:11:9:9:11:11:9:9:11:11:8:8:6:6:2:2:3:17:4:4:2:2:8:8:4:4:6:6:2:2:2:8:8:1:9:9:9:8:8:11:11:4:4:19:1:1:1:4:4:1:1:7:7:1:1:3:3:2:2:3:3:17:2:6:6:3:3:3:8:8:3:3:6:6:7:7:2:2:3:3:3:6:6:6:5:5:3:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:6:1:1:3:1:1:1:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:11:11:1:1:6:6:7:7:2:2:4:4:4:4:2:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:5:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:7:7:4:4:9:9:9:3:3:3:5:5:8:8:2:2:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:4:4:4:1:8:8:17:10:10:10:7:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:4:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:17:1:1:1:5:5:5:1:1:11:11:11:9:9:1:1:7:7:7:7:5:5:1:1:6:6:6:2:2:11:11:9:9:1:1:2:2:6:10:10:3:3:3:6:6:8:8:2:2:2:7:7:2:2:4:4:4:7:7:6:6:4:4:5:5:8:8:9:9:8:8:8:8:3:4:4:4:3:3:3:9:9:1:1:1:1:4:4:4:5:5:11:11:2:2:10:10:10:8:8:8:6:6:9:9:9:9:6:6:5:5:11:11:11:11:7:7:7:4:4:10:10:2:2:9:9:6:6:11:11:4:4:4:10:10:10:7:7:6:6:6:7:7:7:10:10:8:8:8:1:1:1:11:11:9:9:5:5:10:11:11:11:7:7:9:9:3:3:6:6:4:4:7:7:8:8:7:7:7:7:5:5:7:7:9:9:5:5:5:11:11:5:5:4:4:4:4:7:7:8:8:2:2:3:3:3:8:8:6:6:4:4:2:2:9:9:7:7:7:9:9:9:10:10:10:5:5:3:3:10:10:5:5:5:3:3:5:5:10:10:8:8:2:2:9:9:11:11:11:6:10:10:9:9:5:5:5:8:8:8:3:3:3:2:2:4:4:1:1:6:6:8:8:4:4:6:6:2:2:10:10:11:11:10:10:3:8:8:9:2:2:10:10:10:6:10:6:6:1:6:8:9:9:10:10:11:11:11:9:9:9:8:8:10:10:9:9:10:10:11:11:8:8:8:11:11:10:10:8:8:10:10:8:8:9:9:10:10:11:11:11:10:10:10:9:9:8:8:11:11:11:9:9:8:8:9:9:8:8:9:9:10:10:9:9:11:11:8:8:9:9:11:11:8:8:11:10:10:10:8:8:8:9:9:10:10:8:8:8:9:9:8:8:8:9:9:9:8:8:10:10:11:11:8:8:10:10:8:8:11:11:10:10:9:9:11:11:11:8:8:10:10:11:11:9:10:10:9:9:9:11:11:8:8:10:10:10:9:9:11:11:9:9:11:11:9:9:11:11:8:8:6:6:2:2:3:17:4:4:2:2:8:8:4:4:6:6:2:2:2:8:8:1:9:9:9:8:8:11:11:4:4:19:1:1:1:4:4:1:1:7:7:1:1:3:3:2:2:3:3:17:2:6:6:3:3:3:8:8:3:3:6:6:7:7:2:2:3:3:3:6:6:6:5:5:3:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:6:1:1:3:1:1:1:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:11:11:1:1:6:6:7:7:2:2:4:4:4:4:2:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:5:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:7:7:4:4:9:9:9:3:3:3:5:5:8:8:2:2:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:4:4:4:1:8:8:17:10:10:10:7:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:4:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:17:9:9:10:10:11:11:11:9:9:9:8:8:10:10:9:9:10:10:11:11:8:8:8:11:11:10:10:8:8:10:10:8:8:9:9:10:10:11:11:11:10:10:10:9:9:8:8:11:11:11:9:9:8:8:9:9:8:8:9:9:10:10:9:9:11:11:8:8:9:9:11:11:8:8:11:10:10:10:8:8:8:9:9:10:10:8:8:8:9:9:8:8:8:9:9:9:8:8:10:10:1:1:1:5:5:5:1:1:11:11:11:9:9:1:1:7:7:7:7:5:5:1:1:6:6:6:2:2:11:11:9:9:1:1:2:2:6:10:10:3:3:3:6:6:8:8:2:2:2:7:7:2:2:4:4:4:7:7:6:6:4:4:5:5:8:8:9:9:8:8:8:8:3:4:4:4:3:3:3:9:9:1:1:1:1:4:4:4:5:5:11:11:2:2:10:10:10:8:8:8:6:6:9:9:9:9:6:6:5:5:11:11:11:11:7:7:7:4:4:10:10:2:2:9:9:6:6:11:11:4:4:4:10:10:10:7:7:6:6:6:7:7:7:10:10:8:8:8:1:1:1:11:11:9:9:5:5:10:11:11:11:7:7:9:9:3:3:6:6:4:4:7:7:8:8:7:7:7:7:5:5:7:7:9:9:5:5:5:11:11:5:5:4:4:4:4:7:7:8:8:2:2:3:3:3:8:8:6:6:4:4:2:2:9:9:7:7:7:9:9:9:10:10:10:5:5:3:3:10:10:5:5:5:3:3:5:5:10:10:8:8:2:2:9:9:11:11:11:6:10:10:9:9:5:5:5:8:8:8:3:3:3:2:2:4:4:1:1:6:6:8:8:4:4:6:6:2:2:10:10:11:11:10:10:3:8:8:9:2:2:10:10:10:6:10:6:6:1:6:8:11:11:10:10:8:8:8:8:11:11:10:10:11:11:9:9:8:8:11:11:11:8:8:9:9:8:8:11:11:11:8:8:11:11:10:10:9:9:9:8:8:10:10:10:9:9:11:11:8:8:10:10:10:9:9:10:10:9:9:8:8:9:10:10:10:10:8:8:10:10:10:9:9:9:10:10:10:11:11:8:8:8:8:9:9:9:9:11:11:11:10:10:8:8:10:10:10:8:8:9:9:9:8:8:10:10:9:9:8:8:11:11:10:10:9:9:11:11:9:9:9:11:11:8:8:9:9:8:8:9:9:10:10:8:8:11:11:11:9:9:9:11:11:9:9:11:11:11:8:8:6:6:2:2:3:17:4:4:2:2:8:8:4:4:6:6:2:2:2:8:8:1:9:9:9:8:8:11:11:4:4:19:1:1:1:4:4:1:1:7:7:1:1:3:3:2:2:3:3:17:2:6:6:3:3:3:8:8:3:3:6:6:7:7:2:2:3:3:3:6:6:6:5:5:3:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:6:1:1:3:1:1:1:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:11:11:1:1:6:6:7:7:2:2:4:4:4:4:2:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:5:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:7:7:4:4:9:9:9:3:3:3:5:5:8:8:2:2:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:4:4:4:1:8:8:17:10:10:10:7:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:4:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:17:9:9:10:10:11:11:11:9:9:9:8:8:10:10:9:9:10:10:11:11:8:8:8:11:11:10:10:8:8:10:10:8:8:9:9:10:10:11:11:11:10:10:10:9:9:8:8:11:11:11:9:9:8:8:9:9:8:8:9:9:10:10:9:9:11:11:8:8:9:9:11:11:8:8:11:10:10:10:8:8:8:9:9:10:10:8:8:8:9:9:8:8:8:9:9:9:8:8:10:10:1:1:1:5:5:5:1:1:11:11:11:9:9:1:1:7:7:7:7:5:5:1:1:6:6:6:2:2:11:11:9:9:1:1:2:2:6:10:10:3:3:3:6:6:8:8:2:2:2:7:7:2:2:4:4:4:7:7:6:6:4:4:5:5:8:8:9:9:8:8:8:8:3:4:4:4:3:3:3:9:9:1:1:1:1:4:4:4:5:5:11:11:2:2:10:10:10:8:8:8:6:6:9:9:9:9:6:6:5:5:11:11:11:11:7:7:7:4:4:10:10:2:2:9:9:6:6:11:11:4:4:4:10:10:10:7:7:6:6:6:7:7:7:10:10:8:8:8:1:1:1:11:11:9:9:5:5:10:11:11:11:7:7:9:9:3:3:6:6:4:4:7:7:8:8:7:7:7:7:5:5:7:7:9:9:5:5:5:11:11:5:5:4:4:4:4:7:7:8:8:2:2:3:3:3:8:8:6:6:4:4:2:2:9:9:7:7:7:9:9:9:10:10:10:5:5:3:3:10:10:5:5:5:3:3:5:5:10:10:8:8:2:2:9:9:11:11:11:6:10:10:9:9:5:5:5:8:8:8:3:3:3:2:2:4:4:1:1:6:6:8:8:4:4:6:6:2:2:10:10:11:11:10:10:3:8:8:9:2:2:10:10:10:6:10:6:6:1:6:8:11:11:9:9:8:8:8:10:10:11:11:8:8:8:9:9:8:8:11:11:8:10:10:8:8:8:10:10:10:11:11:8:8:8:8:10:10:9:9:8:8:9:9:10:10:10:9:9:9:10:10:9:9:9:11:11:11:10:10:11:11:10:10:9:9:9:11:11:11:8:8:8:11:11:8:8:8:9:9:10:10:9:9:9:11:11:9:9:8:8:11:11:9:9:9:11:11:9:9:10:10:10:8:8:8:8:11:11:8:8:9:9:8:8:11:11:10:10:10:8:8:8:8:9:9:8:8:9:9:10:10:10:10:11:11:9:9:10:10:11:11:11:11:9:9:10:10:11:9:10:6:6:2:2:3:17:4:4:2:2:8:8:4:4:6:6:2:2:2:8:8:1:9:9:9:8:8:11:11:4:4:19:1:1:1:4:4:1:1:7:7:1:1:3:3:2:2:3:3:17:2:6:6:3:3:3:8:8:3:3:6:6:7:7:2:2:3:3:3:6:6:6:5:5:3:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:6:1:1:3:1:1:1:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:11:11:1:1:6:6:7:7:2:2:4:4:4:4:2:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:5:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:7:7:4:4:9:9:9:3:3:3:5:5:8:8:2:2:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:4:4:4:1:8:8:17:10:10:10:7:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:4:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:17:9:9:10:10:11:11:11:9:9:9:8:8:10:10:9:9:10:10:11:11:8:8:8:11:11:10:10:8:8:10:10:8:8:9:9:10:10:11:11:11:10:10:10:9:9:8:8:11:11:11:9:9:8:8:9:9:8:8:9:9:10:10:9:9:11:11:8:8:9:9:11:11:8:8:11:10:10:10:8:8:8:9:9:10:10:8:8:8:9:9:8:8:8:9:9:9:8:8:10:10:1:1:1:5:5:5:1:1:11:11:11:9:9:1:1:7:7:7:7:5:5:1:1:6:6:6:2:2:11:11:9:9:1:1:2:2:6:10:10:3:3:3:6:6:8:8:2:2:2:7:7:2:2:4:4:4:7:7:6:6:4:4:5:5:8:8:9:9:8:8:8:8:3:4:4:4:3:3:3:9:9:1:1:1:1:4:4:4:5:5:11:11:2:2:10:10:10:8:8:8:6:6:9:9:9:9:6:6:5:5:11:11:11:11:7:7:7:4:4:10:10:2:2:9:9:6:6:11:11:4:4:4:10:10:10:7:7:6:6:6:7:7:7:10:10:8:8:8:1:1:1:11:11:9:9:5:5:10:11:11:11:7:7:9:9:3:3:6:6:4:4:7:7:8:8:7:7:7:7:5:5:7:7:9:9:5:5:5:11:11:5:5:4:4:4:4:7:7:8:8:2:2:3:3:3:8:8:6:6:4:4:2:2:9:9:7:7:7:9:9:9:10:10:10:5:5:3:3:10:10:5:5:5:3:3:5:5:10:10:8:8:2:2:9:9:11:11:11:6:10:10:9:9:5:5:5:8:8:8:3:3:3:2:2:4:4:1:1:6:6:8:8:4:4:6:6:2:2:10:10:11:11:10:10:3:8:8:9:2:2:10:10:10:6:10:6:6:1:6:8:8:8:11:11:10:10:9:9:8:8:8:8:10:10:9:9:11:11:11:8:8:10:10:10:8:8:10:10:11:11:11:11:10:10:9:9:11:11:11:11:8:8:9:9:8:8:10:10:8:8:9:9:11:11:10:10:10:8:8:9:9:11:11:9:9:10:10:9:9:9:8:8:8:9:9:11:11:11:10:10:11:11:9:9:8:8:11:11:11:9:9:10:10:9:9:11:11:10:10:11:11:8:8:11:11:11:8:8:10:10:8:8:8:8:9:9:8:8:10:10:8:8:10:8:8:10:10:9:9:9:10:10:10:8:8:8:9:9:9:11:11:9:9:10:9:9:9:11:9:9:6:6:2:2:3:17:4:4:2:2:8:8:4:4:6:6:2:2:2:8:8:1:9:9:9:8:8:11:11:4:4:19:1:1:1:4:4:1:1:7:7:1:1:3:3:2:2:3:3:17:2:6:6:3:3:3:8:8:3:3:6:6:7:7:2:2:3:3:3:6:6:6:5:5:3:3:5:5:19:9:9:5:5:6:6:11:11:9:9:5:5:2:7:11:6:6:11:11:5:17:1:1:3:3:7:7:6:6:1:1:3:1:1:1:11:11:7:7:7:6:6:4:11:11:7:7:10:5:5:11:11:1:1:6:6:7:7:2:2:4:4:4:4:2:2:2:9:9:2:17:11:11:1:1:4:8:8:7:7:20:7:7:9:2:2:2:5:3:3:3:1:1:8:8:2:2:10:10:2:2:5:5:6:6:7:7:4:4:9:9:9:3:3:3:5:5:8:8:2:2:2:5:5:3:3:8:8:8:8:10:10:22:6:6:5:5:5:2:2:4:4:4:4:7:7:5:5:5:10:10:10:9:9:9:9:4:4:5:5:10:10:1:1:1:4:4:4:1:8:8:17:10:10:10:7:7:7:5:5:10:10:8:8:9:9:9:6:6:4:4:7:4:4:7:7:4:4:1:1:1:8:8:8:4:4:11:1:1:8:8:10:3:3:7:3:4:5:9:6:17:9:9:10:10:11:11:11:9:9:9:8:8:10:10:9:9:10:10:11:11:8:8:8:11:11:10:10:8:8:10:10:8:8:9:9:10:10:11:11:11:10:10:10:9:9:8:8:11:11:11:9:9:8:8:9:9:8:8:9:9:10:10:9:9:11:11:8:8:9:9:11:11:8:8:11:10:10:10:8:8:8:9:9:10:10:8:8:8:9:9:8:8:8:9:9:9:8:8:10:10:1:1:1:5:5:5:1:1:11:11:11:9:9:1:1:7:7:7:7:5:5:1:1:6:6:6:2:2:11:11:9:9:1:1:2:2:6:10:10:3:3:3:6:6:8:8:2:2:2:7:7:2:2:4:4:4:7:7:6:6:4:4:5:5:8:8:9:9:8:8:8:8:3:4:4:4:3:3:3:9:9:1:1:1:1:4:4:4:5:5:11:11:2:2:10:10:10:8:8:8:6:6:9:9:9:9:6:6:5:5:11:11:11:11:7:7:7:4:4:10:10:2:2:9:9:6:6:11:11:4:4:4:10:10:10:7:7:6:6:6:7:7:7:10:10:8:8:8:1:1:1:11:11:9:9:5:5:10:11:11:11:7:7:9:9:3:3:6:6:4:4:7:7:8:8:7:7:7:7:5:5:7:7:9:9:5:5:5:11:11:5:5:4:4:4:4:7:7:8:8:2:2:3:3:3:8:8:6:6:4:4:2:2:9:9:7:7:7:9:9:9:10:10:10:5:5:3:3:10:10:5:5:5:3:3:5:5:10:10:8:8:2:2:9:9:11:11:11:6:10:10:9:9:5:5:5:8:8:8:3:3:3:2:2:4:4:1:1:6:6:8:8:4:4:6:6:2:2:10:10:11:11:10:10:3:8:8:9:2:2:10:10:10:6:10:6:6:1:6:8:11:11:11:11:9:9:10:10:10:8:8:11:11:10:10:9:9:11:11:10:10:10:9:9:11:11:10:10:8:8:9:9:8:8:9:9:10:10:8:8:9:9:9:11:11:9:9:9:9:10:10:9:9:8:8:10:10:9:9:8:8:8:11:11:10:10:8:8:10:10:8:8:10:10:8:8:8:10:10:8:8:10:10:11:11:9:9:11:11:10:10:9:9:8:8:11:11:8:8:8:9:9:8:8:8:9:9:11:11:9:9:9:8:8:11:11:11:10:10:10:11:11:11:11:8:8:11:9:9:10:10:8:8:11:11:9:9:11:11:8:8:8:9:9:9:9:11:10:10:8:</t>
+  </si>
+  <si>
+    <t>9:9:10:7:7:7:11:11:6:6:12:10:10:10:20:21:6:6:6:2:2:12:2:2:10:10:2:2:2:9:9:5:12:5:5:10:10:10:12:2:10:11:11:12:2:2:9:9:5:17:5:5:5:3:3:3:6:6:3:3:3:21:5:5:4:4:12:4:7:7:6:20:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:9:6:6:10:10:8:8:8:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:3:1:1:5:5:9:12:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:8:8:2:2:2:17:3:4:4:4:19:2:2:3:3:12:10:10:10:8:8:1:1:12:7:7:8:8:4:12:11:11:7:7:11:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:3:8:8:8:17:6:6:8:8:12:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:12:5:4:4:4:1:1:1:7:7:7:12:4:4:8:8:17:10:1:1:1:2:2:4:9:9:9:1:1:8:11:17:8:8:7:7:1:14:1:5:5:5:7:14:7:10:10:1:1:14:3:3:5:5:5:14:8:8:8:11:11:14:11:6:6:6:3:14:3:9:9:9:10:14:10:10:10:7:7:14:7:11:11:6:6:14:2:2:5:5:8:14:7:6:6:1:1:14:3:3:2:2:5:14:5:11:11:7:7:14:5:5:10:10:9:14:9:1:1:6:6:14:4:4:5:5:5:14:5:2:2:5:5:14:11:11:10:10:10:14:11:11:11:3:3:14:3:5:5:4:4:14:4:11:11:2:2:13:2:6:6:10:10:13:3:3:3:10:10:13:7:7:6:6:9:13:9:9:2:2:2:13:3:3:1:1:1:13:4:4:4:3:3:13:7:7:11:11:11:13:9:9:9:11:11:13:11:2:2:6:6:13:6:11:11:3:3:13:8:8:4:9:9:13:5:5:5:5:3:13:3:4:4:1:1:13:4:4:8:8:10:13:10:8:8:8:7:13:7:2:8:8:10:13:10:4:4:4:10:13:10:9:9:10:10:13:10:8:8:9:9:13:9:4:4:8:8:13:8:9:9:9:4:13:4:2:2:11:11:13:4:4:4:4:3:13:3:3:3:1:1:13:9:9:9:9:7:7:10:10:2:2:1:1:6:6:11:1:1:3:8:8:7:4:1:6:6:7:7:2:7:7:7:6:6:7:7:6:6:7:7:5:5:5:6:6:5:5:7:7:7:5:5:6:6:7:7:5:5:7:6:6:6:5:5:7:7:6:6:6:5:5:6:6:6:6:7:6:6:7:7:7:6:7:7:5:5:5:6:6:6:7:7:5:5:7:7:6:5:5:7:7:7:7:6:6:5:5:6:6:6:7:7:7:6:6:5:5:7:7:6:6:5:5:7:7:5:5:6:6:5:5:5:6:6:7:7:6:6:5:5:5:7:7:5:5:5:7:7:7:6:6:7:7:7:5:5:6:6:5:5:5:6:6:5:5:7:7:6:6:5:5:5:5:6:6:5:5:7:7:7:7:9:9:10:7:7:7:11:11:6:6:6:10:10:10:20:21:6:6:6:2:2:12:2:2:10:10:2:2:2:9:9:5:12:5:5:10:10:10:2:2:10:11:11:12:2:2:9:9:5:17:5:5:5:3:3:3:6:6:3:3:3:21:5:5:4:4:12:4:7:7:6:20:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:9:6:6:10:10:8:8:8:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:3:1:1:5:5:9:12:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:8:8:2:2:2:17:3:4:4:4:19:2:2:3:3:12:10:10:10:8:8:1:1:12:7:7:8:8:4:12:11:11:7:7:11:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:3:8:8:8:17:6:6:8:8:12:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:12:5:4:4:4:1:1:1:7:7:7:12:4:4:8:8:17:10:1:1:1:2:2:4:9:9:9:1:1:8:11:17:8:8:7:7:1:14:1:5:5:5:7:14:7:10:10:1:1:14:3:3:5:5:5:14:8:8:8:11:11:14:11:6:6:6:3:14:3:9:9:9:10:14:10:10:10:7:7:14:7:11:11:6:6:14:2:2:5:5:8:14:7:6:6:1:1:14:3:3:2:2:5:14:5:11:11:7:7:14:5:5:10:10:9:14:9:1:1:6:6:14:4:4:5:5:5:14:5:2:2:5:5:14:11:11:10:10:10:14:11:11:11:3:3:14:3:5:5:4:4:14:4:11:11:2:2:13:2:6:6:10:10:13:3:3:3:10:10:13:7:7:6:6:9:13:9:9:2:2:2:13:3:3:1:1:1:13:4:4:4:3:3:13:7:7:11:11:11:13:9:9:9:11:11:13:11:2:2:6:6:13:6:11:11:3:3:13:8:8:4:9:9:13:5:5:5:5:3:13:3:4:4:1:1:13:4:4:8:8:10:13:10:8:8:8:7:13:7:2:8:8:10:13:10:4:4:4:10:13:10:9:9:10:10:13:10:8:8:9:9:13:9:4:4:8:8:13:8:9:9:9:4:13:4:2:2:11:11:13:4:4:4:4:3:13:3:3:3:1:1:13:9:9:9:9:7:7:10:10:2:2:1:1:6:6:11:1:1:3:8:8:7:4:1:6:6:7:7:2:7:7:7:6:6:7:7:6:6:7:7:5:5:5:6:6:5:5:7:7:7:5:5:6:6:7:7:5:5:7:6:6:6:5:5:7:7:6:6:6:5:5:6:6:6:6:7:6:6:7:7:7:6:7:7:5:5:5:6:6:6:7:7:5:5:7:7:6:5:5:7:7:7:7:6:6:5:5:6:6:6:7:7:7:6:6:5:5:7:7:6:6:5:5:7:7:5:5:6:6:5:5:5:6:6:7:7:6:6:5:5:5:7:7:5:5:5:7:7:7:6:6:7:7:7:5:5:6:6:5:5:5:6:6:5:5:7:7:6:6:5:5:5:5:6:6:5:5:7:7:7:7:9:9:10:7:7:7:11:11:6:6:6:10:10:10:20:21:6:6:6:2:2:12:2:2:10:10:2:2:2:9:9:5:12:5:5:10:10:10:2:2:10:11:11:12:2:2:9:9:5:17:5:5:5:3:3:3:6:6:3:3:3:5:5:5:4:4:12:4:7:7:6:20:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:9:6:6:10:10:8:8:8:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:3:1:1:5:5:9:12:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:8:8:2:2:2:17:3:4:4:4:19:2:2:3:3:12:10:10:10:8:8:1:1:12:7:7:8:8:4:12:11:11:7:7:11:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:3:8:8:8:17:6:6:8:8:12:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:12:5:4:4:4:1:1:1:7:7:7:12:4:4:8:8:17:10:1:1:1:2:2:4:9:9:9:1:1:8:11:17:8:8:7:7:1:14:1:5:5:5:7:14:7:10:10:1:1:14:3:3:5:5:5:14:8:8:8:11:11:14:11:6:6:6:3:14:3:9:9:9:10:14:10:10:10:7:7:14:7:11:11:6:6:14:2:2:5:5:8:14:7:6:6:1:1:14:3:3:2:2:5:14:5:11:11:7:7:14:5:5:10:10:9:14:9:1:1:6:6:14:4:4:5:5:5:14:5:2:2:5:5:14:11:11:10:10:10:14:11:11:11:3:3:14:3:5:5:4:4:14:4:11:11:2:2:13:2:6:6:10:10:13:3:3:3:10:10:13:7:7:6:6:9:13:9:9:2:2:2:13:3:3:1:1:1:13:4:4:4:3:3:13:7:7:11:11:11:13:9:9:9:11:11:13:11:2:2:6:6:13:6:11:11:3:3:13:8:8:4:9:9:13:5:5:5:5:3:13:3:4:4:1:1:13:4:4:8:8:10:13:10:8:8:8:7:13:7:2:8:8:10:13:10:4:4:4:10:13:10:9:9:10:10:13:10:8:8:9:9:13:9:4:4:8:8:13:8:9:9:9:4:13:4:2:2:11:11:13:4:4:4:4:3:13:3:3:3:1:1:13:9:9:9:9:7:7:10:10:2:2:1:1:6:6:11:1:1:3:8:8:7:4:1:6:6:7:7:2:7:7:7:6:6:7:7:6:6:7:7:5:5:5:6:6:5:5:7:7:7:5:5:6:6:7:7:5:5:7:6:6:6:5:5:7:7:6:6:6:5:5:6:6:6:6:7:6:6:7:7:7:6:7:7:5:5:5:6:6:6:7:7:5:5:7:7:6:5:5:7:7:7:7:6:6:5:5:6:6:6:7:7:7:6:6:5:5:7:7:6:6:5:5:7:7:5:5:6:6:5:5:5:6:6:7:7:6:6:5:5:5:7:7:5:5:5:7:7:7:6:6:7:7:7:5:5:6:6:5:5:5:6:6:5:5:7:7:6:6:5:5:5:5:6:6:5:5:7:7:7:7:9:9:10:7:7:7:11:11:6:6:6:10:10:10:20:21:6:6:6:2:2:12:2:2:10:10:2:2:2:9:9:5:5:5:5:10:10:10:2:2:10:11:11:12:2:2:9:9:5:17:5:5:5:3:3:3:6:6:3:3:3:5:5:5:4:4:12:4:7:7:6:20:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:9:6:6:10:10:8:8:8:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:3:1:1:5:5:9:12:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:8:8:2:2:2:17:3:4:4:4:19:2:2:3:3:12:10:10:10:8:8:1:1:12:7:7:8:8:4:12:11:11:7:7:11:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:3:8:8:8:6:6:6:8:8:12:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:12:5:4:4:4:1:1:1:7:7:7:12:4:4:8:8:17:10:1:1:1:2:2:4:9:9:9:1:1:8:11:17:7:6:6:7:7:6:6:7:7:5:5:5:6:6:5:5:7:7:7:5:5:6:6:7:7:5:5:7:6:6:6:5:5:7:7:6:6:6:5:5:6:6:6:6:7:6:6:7:7:7:6:7:7:5:5:5:6:6:6:7:7:5:5:7:7:6:5:5:7:7:7:7:6:6:5:5:6:6:6:7:7:7:6:6:5:5:7:7:6:6:5:5:7:7:5:5:6:6:5:5:8:8:7:7:1:14:1:5:5:5:7:14:7:10:10:1:1:14:3:3:5:5:5:14:8:8:8:11:11:14:11:6:6:6:3:14:3:9:9:9:10:14:10:10:10:7:7:14:7:11:11:6:6:14:2:2:5:5:8:14:7:6:6:1:1:14:3:3:2:2:5:5:5:11:11:7:7:14:5:5:10:10:9:14:9:1:1:6:6:4:4:4:5:5:5:14:5:2:2:5:5:14:11:11:10:10:10:14:11:11:11:3:3:14:3:5:5:4:4:14:4:11:11:2:2:13:2:6:6:10:10:13:3:3:3:10:10:13:7:7:6:6:9:13:9:9:2:2:2:13:3:3:1:1:1:13:4:4:4:3:3:7:7:7:11:11:11:13:9:9:9:11:11:13:11:2:2:6:6:13:6:11:11:3:3:13:8:8:4:9:9:13:5:5:5:5:3:13:3:4:4:1:1:13:4:4:8:8:10:13:10:8:8:8:7:13:7:2:8:8:10:13:10:4:4:4:10:13:10:9:9:10:10:13:10:8:8:9:9:13:9:4:4:8:8:13:8:9:9:9:4:13:4:2:2:11:11:13:4:4:4:4:3:13:3:3:3:1:1:13:9:9:9:9:7:7:10:10:2:2:1:1:6:6:11:1:1:3:8:8:7:4:1:6:6:7:7:2:7:7:5:5:7:7:5:5:7:7:7:6:6:7:7:6:6:6:7:7:5:5:7:7:5:6:6:7:7:5:5:6:6:7:7:6:6:5:5:6:6:5:5:7:7:5:7:7:5:5:6:7:6:6:7:7:6:5:5:6:6:5:5:5:7:6:6:7:7:6:6:5:6:6:5:5:5:7:7:7:5:5:7:7:6:6:7:7:7:6:6:6:5:5:7:7:5:5:6:6:6:7:7:5:5:7:7:5:5:7:7:7:5:5:7:7:7:7:6:6:6:5:5:6:6:6:5:5:5:6:6:5:5:6:6:7:7:6:6:6:5:5:6:6:5:5:6:6:7:7:5:5:9:9:10:7:7:7:11:11:6:6:6:10:10:10:20:21:6:6:6:2:2:12:2:2:10:10:2:2:2:9:9:5:5:5:5:10:10:10:2:2:10:11:11:12:2:2:9:9:5:17:5:5:5:3:3:3:6:6:3:3:3:5:5:5:4:4:12:4:7:7:6:20:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:9:6:6:10:10:8:8:8:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:3:1:1:5:5:9:12:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:8:8:2:2:2:17:3:4:4:4:19:2:2:3:3:12:10:10:10:8:8:1:1:12:7:7:8:8:4:12:11:11:7:7:11:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:3:8:8:8:6:6:6:8:8:12:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:12:5:4:4:4:1:1:1:7:7:7:12:4:4:8:8:17:10:1:1:1:2:2:4:9:9:9:1:1:8:11:17:7:6:6:7:7:6:6:7:7:5:5:5:6:6:5:5:7:7:7:5:5:6:6:7:7:5:5:7:6:6:6:5:5:7:7:6:6:6:5:5:6:6:6:6:7:6:6:7:7:7:6:7:7:5:5:5:6:6:6:7:7:5:5:7:7:6:5:5:7:7:7:7:6:6:5:5:6:6:6:7:7:7:6:6:5:5:7:7:6:6:5:5:7:7:5:5:6:6:5:5:8:8:7:7:1:14:1:5:5:5:7:14:7:10:10:1:1:14:3:3:5:5:5:14:8:8:8:11:11:14:11:6:6:6:3:14:3:9:9:9:10:14:10:10:10:7:7:14:7:11:11:6:6:14:2:2:5:5:8:14:7:6:6:1:1:14:3:3:2:2:5:14:5:11:11:7:7:14:5:5:10:10:9:14:9:1:1:6:6:14:4:4:5:5:5:14:5:2:2:5:5:14:11:11:10:10:10:14:11:11:11:3:3:14:3:5:5:4:4:14:4:11:11:2:2:13:2:6:6:10:10:13:3:3:3:10:10:13:7:7:6:6:9:13:9:9:2:2:2:13:3:3:1:1:1:13:4:4:4:3:3:13:7:7:11:11:11:13:9:9:9:11:11:13:11:2:2:6:6:13:6:11:11:3:3:13:8:8:4:9:9:13:5:5:5:5:3:13:3:4:4:1:1:13:4:4:8:8:10:13:10:8:8:8:7:13:7:2:8:8:10:13:10:4:4:4:10:13:10:9:9:10:10:13:10:8:8:9:9:13:9:4:4:8:8:13:8:9:9:9:4:13:4:2:2:11:11:13:4:4:4:4:3:13:3:3:3:1:1:13:9:9:9:9:7:7:10:10:2:2:1:1:6:6:11:1:1:3:8:8:7:4:1:6:6:7:7:2:7:7:5:5:5:6:6:5:5:6:6:7:7:7:5:5:5:7:7:5:5:6:6:7:5:5:6:6:5:5:6:6:7:7:6:6:6:5:5:7:7:5:5:6:6:6:7:7:5:5:7:7:5:5:7:7:6:6:7:7:7:7:6:6:6:5:5:5:6:6:7:7:6:6:6:5:5:7:7:5:5:6:6:7:5:5:7:7:5:5:6:6:6:5:6:6:7:5:5:5:7:7:7:6:6:7:7:6:6:7:7:7:7:6:6:5:5:6:6:6:5:5:5:6:6:7:7:6:6:6:5:5:5:7:7:5:5:7:6:6:7:7:6:7:7:5:5:7:7:5:7:7:9:9:10:7:7:7:11:11:6:6:6:10:10:10:20:21:6:6:6:2:2:12:2:2:10:10:2:2:2:9:9:5:5:5:5:10:10:10:2:2:10:11:11:12:2:2:9:9:5:17:5:5:5:3:3:3:6:6:3:3:3:5:5:5:4:4:12:4:7:7:6:20:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:9:6:6:10:10:8:8:8:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:3:1:1:5:5:9:12:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:8:8:2:2:2:17:3:4:4:4:19:2:2:3:3:12:10:10:10:8:8:1:1:12:7:7:8:8:4:12:11:11:7:7:11:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:3:8:8:8:6:6:6:8:8:12:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:12:5:4:4:4:1:1:1:7:7:7:12:4:4:8:8:17:10:1:1:1:2:2:4:9:9:9:1:1:8:11:17:7:6:6:7:7:6:6:7:7:5:5:5:6:6:5:5:7:7:7:5:5:6:6:7:7:5:5:7:6:6:6:5:5:7:7:6:6:6:5:5:6:6:6:6:7:6:6:7:7:7:6:7:7:5:5:5:6:6:6:7:7:5:5:7:7:6:5:5:7:7:7:7:6:6:5:5:6:6:6:7:7:7:6:6:5:5:7:7:6:6:5:5:7:7:5:5:6:6:5:5:8:8:7:7:1:14:1:5:5:5:7:14:7:10:10:1:1:14:3:3:5:5:5:14:8:8:8:11:11:14:11:6:6:6:3:14:3:9:9:9:10:14:10:10:10:7:7:14:7:11:11:6:6:14:2:2:5:5:8:14:7:6:6:1:1:14:3:3:2:2:5:14:5:11:11:7:7:14:5:5:10:10:9:14:9:1:1:6:6:14:4:4:5:5:5:14:5:2:2:5:5:14:11:11:10:10:10:14:11:11:11:3:3:14:3:5:5:4:4:14:4:11:11:2:2:13:2:6:6:10:10:13:3:3:3:10:10:13:7:7:6:6:9:13:9:9:2:2:2:13:3:3:1:1:1:13:4:4:4:3:3:13:7:7:11:11:11:13:9:9:9:11:11:13:11:2:2:6:6:13:6:11:11:3:3:13:8:8:4:9:9:13:5:5:5:5:3:13:3:4:4:1:1:13:4:4:8:8:10:13:10:8:8:8:7:13:7:2:8:8:10:13:10:4:4:4:10:13:10:9:9:10:10:13:10:8:8:9:9:13:9:4:4:8:8:13:8:9:9:9:4:13:4:2:2:11:11:13:4:4:4:4:3:13:3:3:3:1:1:13:9:9:9:9:7:7:10:10:2:2:1:1:6:6:11:1:1:3:8:8:7:4:1:6:6:7:7:2:7:7:6:6:5:5:6:6:6:7:7:6:6:7:7:7:7:6:6:6:6:5:5:7:7:7:5:5:6:6:5:5:5:6:6:6:5:5:7:7:5:5:6:6:7:7:6:6:5:5:5:6:6:7:7:7:7:6:6:6:5:5:6:6:6:7:7:6:6:5:5:5:7:7:5:5:7:7:7:6:6:6:6:7:7:5:5:7:7:6:6:5:5:7:7:6:6:7:7:6:6:6:5:5:7:7:5:5:7:7:5:5:5:7:7:5:6:6:7:7:7:5:5:7:7:5:5:6:6:7:7:5:5:6:6:7:7:7:5:5:5:7:7:6:6:6:5:5:5:5:5:5:9:9:10:7:7:7:11:11:6:6:6:10:10:10:20:21:6:6:6:2:2:12:2:2:10:10:2:2:2:9:9:5:5:5:5:10:10:10:2:2:10:11:11:12:2:2:9:9:5:17:5:5:5:3:3:3:6:6:3:3:3:5:5:5:4:4:12:4:7:7:6:20:3:3:6:6:8:12:8:5:5:5:22:3:7:7:7:5:12:5:5:9:9:6:6:10:10:8:8:8:10:10:5:5:5:12:1:1:8:8:2:12:2:9:9:3:3:1:1:5:5:9:12:9:5:5:11:11:11:19:3:3:3:12:5:9:9:10:10:19:3:2:2:8:8:8:2:2:2:17:3:4:4:4:19:2:2:3:3:12:10:10:10:8:8:1:1:12:7:7:8:8:4:12:11:11:7:7:11:11:7:7:19:5:5:3:3:6:6:12:4:4:7:7:3:3:8:8:8:6:6:6:8:8:12:3:4:4:8:8:4:4:12:4:4:6:6:19:7:8:8:9:9:12:11:11:11:9:9:20:2:2:8:8:12:7:7:1:1:21:6:6:6:6:9:12:9:1:1:17:4:4:7:7:7:9:9:12:6:6:6:1:1:20:1:1:1:5:12:5:4:4:4:1:1:1:7:7:7:12:4:4:8:8:17:10:1:1:1:2:2:4:9:9:9:1:1:8:11:17:7:6:6:7:7:6:6:7:7:5:5:5:6:6:5:5:7:7:7:5:5:6:6:7:7:5:5:7:6:6:6:5:5:7:7:6:6:6:5:5:6:6:6:6:7:6:6:7:7:7:6:7:7:5:5:5:6:6:6:7:7:5:5:7:7:6:5:5:7:7:7:7:6:6:5:5:6:6:6:7:7:7:6:6:5:5:7:7:6:6:5:5:7:7:5:5:6:6:5:5:8:8:7:7:1:14:1:5:5:5:7:14:7:10:10:1:1:14:3:3:5:5:5:14:8:8:8:11:11:14:11:6:6:6:3:14:3:9:9:9:10:14:10:10:10:7:7:14:7:11:11:6:6:14:2:2:5:5:8:14:7:6:6:1:1:14:3:3:2:2:5:14:5:11:11:7:7:14:5:5:10:10:9:14:9:1:1:6:6:14:4:4:5:5:5:14:5:2:2:5:5:14:11:11:10:10:10:14:11:11:11:3:3:14:3:5:5:4:4:14:4:11:11:2:2:13:2:6:6:10:10:13:3:3:3:10:10:13:7:7:6:6:9:13:9:9:2:2:2:13:3:3:1:1:1:13:4:4:4:3:3:13:7:7:11:11:11:13:9:9:9:11:11:13:11:2:2:6:6:13:6:11:11:3:3:13:8:8:4:9:9:13:5:5:5:5:3:13:3:4:4:1:1:13:4:4:8:8:10:13:10:8:8:8:7:13:7:2:8:8:10:13:10:4:4:4:10:13:10:9:9:10:10:13:10:8:8:9:9:13:9:4:4:8:8:13:8:9:9:9:4:13:4:2:2:11:11:13:4:4:4:4:3:13:3:3:3:1:1:13:9:9:9:9:7:7:10:10:2:2:1:1:6:6:11:1:1:3:8:8:7:4:1:6:6:7:7:2:7:7:7:7:5:5:5:7:7:5:5:6:6:5:5:7:7:5:5:5:7:7:5:5:7:7:7:6:6:7:7:6:6:7:7:6:6:7:7:7:5:5:6:6:6:5:5:7:7:7:5:5:7:7:6:6:5:5:7:7:7:6:6:5:5:6:6:6:7:7:5:5:5:5:7:7:5:5:5:6:6:7:7:6:6:5:5:5:7:7:6:6:7:7:5:7:7:6:6:6:5:5:5:6:6:5:5:6:6:6:7:7:5:5:6:6:5:5:6:6:6:7:7:5:5:7:7:6:6:5:5:6:6:6:5:5:5:6:6:7:7:6:6:5:6:6:7:7:7:6:7:6:</t>
+  </si>
+  <si>
+    <t>8:8:8:5:5:2:2:9:9:11:11:11:6:6:6:4:4:8:8:9:11:12:11:5:5:5:20:19:6:10:10:10:12:8:8:8:20:1:1:1:9:9:8:12:8:2:2:6:6:17:1:1:3:3:9:12:9:3:3:3:3:6:6:4:4:5:12:6:6:4:4:21:19:3:3:3:6:12:6:2:2:9:9:2:2:3:3:3:12:3:9:9:20:9:7:7:17:3:3:3:12:3:11:11:4:7:7:21:1:1:8:12:8:1:1:7:7:22:9:4:1:1:12:6:6:5:5:5:8:8:2:2:2:12:5:10:10:5:5:5:9:9:1:1:12:4:4:10:10:17:10:6:6:5:5:9:12:9:9:9:19:8:8:11:11:7:7:12:7:10:10:1:1:10:7:7:5:5:12:10:10:5:5:17:7:6:6:6:6:12:4:4:4:1:1:1:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:21:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:2:3:3:3:3:11:11:12:11:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:10:10:8:8:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:19:2:2:1:12:8:8:7:7:6:8:7:8:8:3:3:3:2:2:14:2:1:1:1:8:14:8:4:4:4:6:14:6:7:7:7:5:14:5:7:7:6:6:14:11:11:7:7:7:14:6:6:6:4:4:14:5:5:4:4:2:14:3:3:7:7:7:14:7:6:6:10:10:14:3:3:3:1:1:14:7:7:9:9:9:14:1:1:11:11:8:14:8:8:4:1:1:14:10:10:11:11:6:14:6:8:8:11:11:14:6:6:11:11:8:14:8:9:9:10:10:14:8:8:4:4:11:14:11:2:2:9:9:14:2:2:2:2:7:13:7:10:10:11:11:13:11:1:1:5:5:13:5:11:11:11:8:13:8:3:3:3:5:13:5:5:10:10:9:13:9:6:6:6:9:13:9:4:4:3:3:13:1:1:7:7:5:13:5:5:10:10:6:13:6:3:3:8:8:13:2:2:2:10:11:13:11:3:3:11:11:13:11:4:4:2:2:13:2:11:11:1:1:13:8:8:8:5:6:13:6:1:1:1:9:13:9:9:10:10:4:13:4:4:4:6:6:13:2:2:3:3:9:13:9:8:8:9:1:13:1:4:4:10:10:13:5:5:4:4:4:13:10:10:5:5:10:13:10:4:4:5:5:13:5:10:10:10:8:8:5:5:9:9:1:1:8:10:10:10:9:9:5:5:7:7:3:7:11:1:2:2:6:6:4:4:2:2:3:3:3:2:2:3:3:4:4:3:3:3:1:1:2:2:4:4:3:3:4:4:1:1:4:4:4:1:1:1:3:3:3:4:4:1:1:1:4:4:4:2:2:4:4:1:1:3:3:1:1:4:4:2:2:4:4:3:3:3:2:2:3:3:4:4:1:1:4:4:3:4:4:4:2:2:2:4:4:4:2:2:2:1:1:4:4:2:2:3:1:1:3:3:1:1:2:2:3:3:2:2:3:3:2:2:1:1:3:3:4:4:1:1:3:3:2:2:2:3:3:1:1:3:3:2:2:1:1:4:4:4:4:2:2:3:3:2:2:3:3:2:2:2:2:2:8:8:8:5:5:2:2:9:9:11:11:11:6:6:6:4:4:8:8:9:11:11:11:5:5:5:20:19:6:10:10:10:12:8:8:8:1:1:1:1:9:9:8:12:8:2:2:6:6:17:1:1:3:3:9:12:9:3:3:3:3:6:6:4:4:5:12:6:6:4:4:21:19:3:3:3:6:12:6:2:2:9:9:2:2:3:3:3:12:3:9:9:9:7:7:7:17:3:3:3:12:3:11:11:4:7:7:1:1:1:8:12:8:1:1:7:7:9:9:4:1:1:12:6:6:5:5:5:8:8:2:2:2:12:5:10:10:5:5:5:9:9:1:1:12:4:4:10:10:17:10:6:6:5:5:9:12:9:9:9:8:8:8:11:11:7:7:12:7:10:10:1:1:10:7:7:5:5:12:10:10:5:5:17:7:6:6:6:6:12:4:4:4:1:1:1:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:9:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:2:3:3:3:3:11:11:9:9:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:10:10:8:8:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:3:2:2:1:12:8:8:7:7:6:8:7:8:8:3:3:3:2:2:14:2:1:1:1:8:14:8:4:4:4:6:14:6:7:7:7:5:14:5:7:7:6:6:14:11:11:7:7:7:14:6:6:6:4:4:14:5:5:4:4:2:14:3:3:7:7:7:14:7:6:6:10:10:14:3:3:3:1:1:14:7:7:9:9:9:14:1:1:11:11:8:14:8:8:4:1:1:14:10:10:11:11:6:14:6:8:8:11:11:14:6:6:11:11:8:14:8:9:9:10:10:14:8:8:4:4:11:14:11:2:2:9:9:14:2:2:2:2:7:13:7:10:10:11:11:13:11:1:1:5:5:13:5:11:11:11:8:13:8:3:3:3:5:13:5:5:10:10:9:13:9:6:6:6:9:13:9:4:4:3:3:13:1:1:7:7:5:13:5:5:10:10:6:13:6:3:3:8:8:13:2:2:2:10:11:13:11:3:3:11:11:13:11:4:4:2:2:13:2:11:11:1:1:13:8:8:8:5:6:13:6:1:1:1:9:13:9:9:10:10:4:13:4:4:4:6:6:13:2:2:3:3:9:13:9:8:8:9:1:13:1:4:4:10:10:13:5:5:4:4:4:13:10:10:5:5:10:13:10:4:4:5:5:13:5:10:10:10:8:8:5:5:9:9:1:1:8:10:10:10:9:9:5:5:7:7:3:7:11:1:2:2:6:6:4:4:2:2:3:3:3:2:2:3:3:4:4:3:3:3:1:1:2:2:4:4:3:3:4:4:1:1:4:4:4:1:1:1:3:3:3:4:4:1:1:1:4:4:4:2:2:4:4:1:1:3:3:1:1:4:4:2:2:4:4:3:3:3:2:2:3:3:4:4:1:1:4:4:3:4:4:4:2:2:2:4:4:4:2:2:2:1:1:4:4:2:2:3:1:1:3:3:1:1:2:2:3:3:2:2:3:3:2:2:1:1:3:3:4:4:1:1:3:3:2:2:2:3:3:1:1:3:3:2:2:1:1:4:4:4:4:2:2:3:3:2:2:3:3:2:2:2:2:2:8:8:8:5:5:2:2:9:9:11:11:11:6:6:6:4:4:8:8:9:11:11:11:5:5:5:20:19:6:10:10:10:12:8:8:8:1:1:1:1:9:9:8:12:8:2:2:6:6:17:1:1:3:3:9:12:9:3:3:3:3:6:6:4:4:5:12:6:6:4:4:21:19:3:3:3:6:12:6:2:2:9:9:2:2:3:3:3:12:3:9:9:9:7:7:7:17:3:3:3:12:3:11:11:4:7:7:1:1:1:8:12:8:1:1:7:7:9:9:4:1:1:12:6:6:5:5:5:8:8:2:2:2:12:5:10:10:5:5:5:9:9:1:1:12:4:4:10:10:17:10:6:6:5:5:9:12:9:9:9:8:8:8:11:11:7:7:12:7:10:10:1:1:10:7:7:5:5:12:10:10:5:5:17:7:6:6:6:6:12:4:4:4:1:1:1:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:9:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:2:3:3:3:3:11:11:9:9:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:10:10:8:8:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:3:2:2:1:12:8:8:7:7:6:8:7:8:8:3:3:3:2:2:14:2:1:1:1:8:14:8:4:4:4:6:14:6:7:7:7:5:14:5:7:7:6:6:14:11:11:7:7:7:14:6:6:6:4:4:14:5:5:4:4:2:14:3:3:7:7:7:14:7:6:6:10:10:14:3:3:3:1:1:14:7:7:9:9:9:14:1:1:11:11:8:14:8:8:4:1:1:14:10:10:11:11:6:14:6:8:8:11:11:14:6:6:11:11:8:14:8:9:9:10:10:14:8:8:4:4:11:14:11:2:2:9:9:14:2:2:2:2:7:13:7:10:10:11:11:13:11:1:1:5:5:13:5:11:11:11:8:13:8:3:3:3:5:13:5:5:10:10:9:13:9:6:6:6:9:13:9:4:4:3:3:13:1:1:7:7:5:13:5:5:10:10:6:13:6:3:3:8:8:13:2:2:2:10:11:13:11:3:3:11:11:13:11:4:4:2:2:13:2:11:11:1:1:13:8:8:8:5:6:13:6:1:1:1:9:13:9:9:10:10:4:13:4:4:4:6:6:13:2:2:3:3:9:13:9:8:8:9:1:13:1:4:4:10:10:13:5:5:4:4:4:13:10:10:5:5:10:13:10:4:4:5:5:13:5:10:10:10:8:8:5:5:9:9:1:1:8:10:10:10:9:9:5:5:7:7:3:7:11:1:2:2:6:6:4:4:2:2:3:3:3:2:2:3:3:4:4:3:3:3:1:1:2:2:4:4:3:3:4:4:1:1:4:4:4:1:1:1:3:3:3:4:4:1:1:1:4:4:4:2:2:4:4:1:1:3:3:1:1:4:4:2:2:4:4:3:3:3:2:2:3:3:4:4:1:1:4:4:3:4:4:4:2:2:2:4:4:4:2:2:2:1:1:4:4:2:2:3:1:1:3:3:1:1:2:2:3:3:2:2:3:3:2:2:1:1:3:3:4:4:1:1:3:3:2:2:2:3:3:1:1:3:3:2:2:1:1:4:4:4:4:2:2:3:3:2:2:3:3:2:2:2:2:2:8:8:8:5:5:2:2:9:9:11:11:11:6:6:6:4:4:8:8:9:11:11:11:5:5:5:20:19:6:10:10:10:12:8:8:8:1:1:1:1:9:9:8:12:8:2:2:6:6:17:1:1:3:3:9:12:9:3:3:3:3:6:6:4:4:5:5:6:6:4:4:21:19:3:3:3:6:12:6:2:2:9:9:2:2:3:3:3:12:3:9:9:9:7:7:7:17:3:3:3:12:3:11:11:4:7:7:1:1:1:8:12:8:1:1:7:7:9:9:4:1:1:12:6:6:5:5:5:8:8:2:2:2:12:5:10:10:5:5:5:9:9:1:1:12:4:4:10:10:10:10:6:6:5:5:9:12:9:9:9:8:8:8:11:11:7:7:12:7:10:10:1:1:10:7:7:5:5:12:10:10:5:5:17:7:6:6:6:6:12:4:4:4:1:1:1:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:9:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:2:3:3:3:3:11:11:9:9:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:10:10:8:8:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:3:2:2:1:12:8:8:7:7:6:8:7:8:8:4:4:2:2:3:3:3:2:2:3:3:4:4:3:3:3:1:1:2:2:4:4:3:3:4:4:1:1:4:4:4:1:1:1:3:3:3:4:4:1:1:1:4:4:4:2:2:4:4:1:1:3:3:1:1:4:4:2:2:4:4:3:3:3:2:2:3:3:4:4:1:1:4:4:3:4:4:4:2:2:2:4:4:4:2:2:2:1:1:4:4:2:2:3:1:1:3:3:1:1:3:3:3:2:2:14:2:1:1:1:8:14:8:4:4:4:6:14:6:7:7:7:5:14:5:7:7:6:6:14:11:11:7:7:7:14:6:6:6:4:4:14:5:5:4:4:2:14:3:3:7:7:7:14:7:6:6:10:10:14:3:3:3:1:1:14:7:7:9:9:9:14:1:1:11:11:8:14:8:8:4:1:1:14:10:10:11:11:6:14:6:8:8:11:11:14:6:6:11:11:8:14:8:9:9:10:10:14:8:8:4:4:11:14:11:2:2:9:9:14:2:2:2:2:7:13:7:10:10:11:11:13:11:1:1:5:5:13:5:11:11:11:8:13:8:3:3:3:5:13:5:5:10:10:9:13:9:6:6:6:9:13:9:4:4:3:3:13:1:1:7:7:5:13:5:5:10:10:6:13:6:3:3:8:8:8:2:2:2:10:11:13:11:3:3:11:11:13:11:4:4:2:2:13:2:11:11:1:1:13:8:8:8:5:6:13:6:1:1:1:9:13:9:9:10:10:4:13:4:4:4:6:6:13:2:2:3:3:9:13:9:8:8:9:1:13:1:4:4:10:10:13:5:5:4:4:4:13:10:10:5:5:10:13:10:4:4:5:5:13:5:10:10:10:8:8:5:5:9:9:1:1:8:10:10:10:9:9:5:5:7:7:3:7:11:1:2:2:6:6:3:3:3:4:4:1:1:2:2:4:4:2:2:2:1:1:3:3:1:1:2:2:1:1:1:3:3:1:1:1:3:3:1:1:1:3:3:3:1:1:3:3:4:4:2:2:2:3:3:2:2:4:4:3:3:1:1:2:2:1:1:4:4:4:2:2:2:3:3:1:1:2:2:3:3:3:3:2:2:4:2:2:2:2:1:1:4:4:4:2:2:4:4:2:2:2:3:3:4:4:1:1:4:4:4:2:2:2:2:3:3:3:3:4:4:4:3:3:3:4:4:3:3:4:4:3:3:4:4:1:1:1:2:2:2:4:4:4:2:2:4:4:3:3:4:4:4:2:4:3:8:8:8:5:5:2:2:9:9:11:11:11:6:6:6:4:4:8:8:9:11:11:11:5:5:5:20:19:6:10:10:10:12:8:8:8:1:1:1:1:9:9:8:12:8:2:2:6:6:17:1:1:3:3:9:12:9:3:3:3:3:6:6:4:4:5:5:6:6:4:4:21:19:3:3:3:6:12:6:2:2:9:9:2:2:3:3:3:12:3:9:9:9:7:7:7:17:3:3:3:12:3:11:11:4:7:7:1:1:1:8:12:8:1:1:7:7:9:9:4:1:1:12:6:6:5:5:5:8:8:2:2:2:12:5:10:10:5:5:5:9:9:1:1:12:4:4:10:10:10:10:6:6:5:5:9:12:9:9:9:8:8:8:11:11:7:7:12:7:10:10:1:1:10:7:7:5:5:12:10:10:5:5:17:7:6:6:6:6:12:4:4:4:1:1:1:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:9:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:2:3:3:3:3:11:11:9:9:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:10:10:8:8:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:3:2:2:1:12:8:8:7:7:6:8:7:8:8:4:4:2:2:3:3:3:2:2:3:3:4:4:3:3:3:1:1:2:2:4:4:3:3:4:4:1:1:4:4:4:1:1:1:3:3:3:4:4:1:1:1:4:4:4:2:2:4:4:1:1:3:3:1:1:4:4:2:2:4:4:3:3:3:2:2:3:3:4:4:1:1:4:4:3:4:4:4:2:2:2:4:4:4:2:2:2:1:1:4:4:2:2:3:1:1:3:3:1:1:3:3:3:2:2:14:2:1:1:1:8:14:8:4:4:4:6:14:6:7:7:7:5:14:5:7:7:6:6:14:11:11:7:7:7:14:6:6:6:4:4:14:5:5:4:4:2:14:3:3:7:7:7:14:7:6:6:10:10:14:3:3:3:1:1:14:7:7:9:9:9:14:1:1:11:11:8:14:8:8:4:1:1:14:10:10:11:11:6:14:6:8:8:11:11:14:6:6:11:11:8:14:8:9:9:10:10:14:8:8:4:4:11:14:11:2:2:9:9:14:2:2:2:2:7:13:7:10:10:11:11:13:11:1:1:5:5:13:5:11:11:11:8:13:8:3:3:3:5:13:5:5:10:10:9:13:9:6:6:6:9:13:9:4:4:3:3:13:1:1:7:7:5:13:5:5:10:10:6:13:6:3:3:8:8:13:2:2:2:10:11:13:11:3:3:11:11:13:11:4:4:2:2:13:2:11:11:1:1:13:8:8:8:5:6:13:6:1:1:1:9:13:9:9:10:10:4:13:4:4:4:6:6:13:2:2:3:3:9:13:9:8:8:9:1:13:1:4:4:10:10:13:5:5:4:4:4:13:10:10:5:5:10:13:10:4:4:5:5:13:5:10:10:10:8:8:5:5:9:9:1:1:8:10:10:10:9:9:5:5:7:7:3:7:11:1:2:2:6:6:3:3:3:2:2:3:3:4:4:3:3:3:1:1:3:3:2:2:3:2:2:1:1:1:3:3:3:2:2:1:1:3:3:1:1:1:2:2:3:3:3:1:1:4:4:4:1:1:3:3:2:2:1:1:4:4:1:1:4:4:4:4:3:2:2:4:4:4:4:2:2:4:4:2:2:3:3:4:4:1:1:4:4:4:1:1:2:2:4:4:3:3:2:2:2:4:4:2:2:2:3:3:4:4:3:3:2:2:3:3:4:4:3:3:1:1:2:2:2:3:3:4:4:1:1:4:4:3:3:2:2:3:3:2:2:1:1:1:2:2:4:4:2:2:4:4:2:4:4:1:8:8:8:5:5:2:2:9:9:11:11:11:6:6:6:4:4:8:8:9:11:11:11:5:5:5:20:19:6:10:10:10:12:8:8:8:1:1:1:1:9:9:8:12:8:2:2:6:6:17:1:1:3:3:9:12:9:3:3:3:3:6:6:4:4:5:5:6:6:4:4:21:19:3:3:3:6:12:6:2:2:9:9:2:2:3:3:3:12:3:9:9:9:7:7:7:17:3:3:3:12:3:11:11:4:7:7:1:1:1:8:12:8:1:1:7:7:9:9:4:1:1:12:6:6:5:5:5:8:8:2:2:2:12:5:10:10:5:5:5:9:9:1:1:12:4:4:10:10:10:10:6:6:5:5:9:12:9:9:9:8:8:8:11:11:7:7:12:7:10:10:1:1:10:7:7:5:5:12:10:10:5:5:17:7:6:6:6:6:12:4:4:4:1:1:1:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:9:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:2:3:3:3:3:11:11:9:9:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:10:10:8:8:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:3:2:2:1:12:8:8:7:7:6:8:7:8:8:4:4:2:2:3:3:3:2:2:3:3:4:4:3:3:3:1:1:2:2:4:4:3:3:4:4:1:1:4:4:4:1:1:1:3:3:3:4:4:1:1:1:4:4:4:2:2:4:4:1:1:3:3:1:1:4:4:2:2:4:4:3:3:3:2:2:3:3:4:4:1:1:4:4:3:4:4:4:2:2:2:4:4:4:2:2:2:1:1:4:4:2:2:3:1:1:3:3:1:1:3:3:3:2:2:14:2:1:1:1:8:14:8:4:4:4:6:14:6:7:7:7:5:14:5:7:7:6:6:14:11:11:7:7:7:14:6:6:6:4:4:14:5:5:4:4:2:14:3:3:7:7:7:14:7:6:6:10:10:14:3:3:3:1:1:14:7:7:9:9:9:14:1:1:11:11:8:14:8:8:4:1:1:14:10:10:11:11:6:14:6:8:8:11:11:14:6:6:11:11:8:14:8:9:9:10:10:14:8:8:4:4:11:14:11:2:2:9:9:14:2:2:2:2:7:13:7:10:10:11:11:13:11:1:1:5:5:13:5:11:11:11:8:13:8:3:3:3:5:13:5:5:10:10:9:13:9:6:6:6:9:13:9:4:4:3:3:13:1:1:7:7:5:13:5:5:10:10:6:13:6:3:3:8:8:13:2:2:2:10:11:13:11:3:3:11:11:13:11:4:4:2:2:13:2:11:11:1:1:13:8:8:8:5:6:13:6:1:1:1:9:13:9:9:10:10:4:13:4:4:4:6:6:13:2:2:3:3:9:13:9:8:8:9:1:13:1:4:4:10:10:13:5:5:4:4:4:13:10:10:5:5:10:13:10:4:4:5:5:13:5:10:10:10:8:8:5:5:9:9:1:1:8:10:10:10:9:9:5:5:7:7:3:7:11:1:2:2:6:6:2:2:4:4:1:1:4:4:2:2:4:4:2:2:2:3:3:3:1:1:3:3:1:1:3:3:3:2:2:4:4:3:3:1:1:1:3:3:1:1:3:3:4:4:4:2:2:3:3:2:2:2:3:3:2:2:4:4:3:3:2:2:3:3:1:1:2:2:2:4:4:4:4:2:2:3:3:3:2:2:4:4:3:3:1:1:2:2:1:1:2:2:4:4:3:3:1:1:1:2:2:4:4:1:1:4:4:3:3:3:4:4:2:2:4:4:1:1:4:4:3:3:1:1:4:4:2:2:4:1:1:4:4:3:3:2:2:3:3:2:2:3:3:4:4:1:1:4:4:2:8:8:8:5:5:2:2:9:9:11:11:11:6:6:6:4:4:8:8:9:11:11:11:5:5:5:20:19:6:10:10:10:12:8:8:8:1:1:1:1:9:9:8:12:8:2:2:6:6:17:1:1:3:3:9:12:9:3:3:3:3:6:6:4:4:5:5:6:6:4:4:21:19:3:3:3:6:12:6:2:2:9:9:2:2:3:3:3:12:3:9:9:9:7:7:7:17:3:3:3:12:3:11:11:4:7:7:1:1:1:8:12:8:1:1:7:7:9:9:4:1:1:12:6:6:5:5:5:8:8:2:2:2:12:5:10:10:5:5:5:9:9:1:1:12:4:4:10:10:10:10:6:6:5:5:9:12:9:9:9:8:8:8:11:11:7:7:12:7:10:10:1:1:10:7:7:5:5:12:10:10:5:5:17:7:6:6:6:6:12:4:4:4:1:1:1:10:10:3:17:3:7:8:8:8:12:5:5:1:1:9:9:12:7:7:9:9:2:2:11:11:11:11:12:6:6:4:4:7:7:7:6:6:5:12:5:5:2:2:3:3:3:3:11:11:9:9:2:2:17:2:9:9:7:7:9:9:12:9:10:10:20:10:1:1:10:10:8:8:8:8:10:10:19:3:5:5:4:4:12:4:6:6:7:7:3:3:2:2:1:12:8:8:7:7:6:8:7:8:8:4:4:2:2:3:3:3:2:2:3:3:4:4:3:3:3:1:1:2:2:4:4:3:3:4:4:1:1:4:4:4:1:1:1:3:3:3:4:4:1:1:1:4:4:4:2:2:4:4:1:1:3:3:1:1:4:4:2:2:4:4:3:3:3:2:2:3:3:4:4:1:1:4:4:3:4:4:4:2:2:2:4:4:4:2:2:2:1:1:4:4:2:2:3:1:1:3:3:1:1:3:3:3:2:2:14:2:1:1:1:8:14:8:4:4:4:6:14:6:7:7:7:5:14:5:7:7:6:6:14:11:11:7:7:7:14:6:6:6:4:4:14:5:5:4:4:2:14:3:3:7:7:7:14:7:6:6:10:10:14:3:3:3:1:1:14:7:7:9:9:9:14:1:1:11:11:8:14:8:8:4:1:1:14:10:10:11:11:6:14:6:8:8:11:11:14:6:6:11:11:8:14:8:9:9:10:10:14:8:8:4:4:11:14:11:2:2:9:9:14:2:2:2:2:7:13:7:10:10:11:11:13:11:1:1:5:5:13:5:11:11:11:8:13:8:3:3:3:5:13:5:5:10:10:9:13:9:6:6:6:9:13:9:4:4:3:3:13:1:1:7:7:5:13:5:5:10:10:6:13:6:3:3:8:8:13:2:2:2:10:11:13:11:3:3:11:11:13:11:4:4:2:2:13:2:11:11:1:1:13:8:8:8:5:6:13:6:1:1:1:9:13:9:9:10:10:4:13:4:4:4:6:6:13:2:2:3:3:9:13:9:8:8:9:1:13:1:4:4:10:10:13:5:5:4:4:4:13:10:10:5:5:10:13:10:4:4:5:5:13:5:10:10:10:8:8:5:5:9:9:1:1:8:10:10:10:9:9:5:5:7:7:3:7:11:1:2:2:6:6:2:2:3:3:2:2:1:1:2:4:4:4:3:3:3:4:4:3:3:4:4:1:1:2:2:2:1:1:3:3:4:4:4:2:2:2:2:3:3:4:3:3:1:1:2:2:2:4:4:4:2:2:3:3:4:4:3:3:4:4:1:1:3:3:4:4:4:3:3:3:2:2:1:1:1:3:3:3:1:1:3:3:3:4:4:2:2:2:4:4:4:4:3:3:3:4:4:1:1:1:2:2:2:1:1:1:2:2:2:1:1:4:4:4:4:1:1:4:4:2:2:1:1:2:2:3:4:4:2:2:3:3:2:3:3:2:2:2:2:1:1:1:4:4:4:3:3:3:3:2:</t>
+  </si>
+  <si>
+    <t>8:8:4:4:4:10:10:2:2:10:10:10:4:4:4:4:10:10:8:8:8:3:19:3:3:1:1:1:11:11:11:2:2:2:8:8:2:2:7:7:2:12:2:2:9:9:10:10:9:17:7:9:9:1:1:12:8:8:3:3:3:19:7:1:1:6:12:6:5:5:2:19:3:3:10:10:5:5:5:8:8:9:9:9:3:3:3:7:12:7:9:9:5:5:5:17:3:3:3:3:12:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:12:7:7:6:6:12:6:7:7:7:20:21:11:11:7:7:12:7:6:9:9:17:3:3:3:1:1:1:10:12:11:11:3:3:5:5:5:4:4:12:4:6:6:6:21:19:10:3:3:5:5:12:10:10:2:2:22:5:5:8:8:12:8:5:5:5:12:7:7:7:7:17:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:2:1:6:6:17:4:4:8:8:12:10:10:6:6:7:7:7:9:9:10:12:10:8:8:4:4:20:9:9:9:8:12:8:4:4:8:8:11:11:12:7:7:8:8:6:6:19:4:4:6:4:17:2:2:9:9:6:14:6:10:10:1:1:14:11:11:11:3:3:14:8:8:7:7:3:14:3:1:1:8:8:14:3:3:1:1:5:14:5:5:3:3:2:14:2:2:4:4:1:14:1:10:10:8:8:14:8:4:4:4:10:14:10:6:6:3:3:14:11:11:10:10:9:14:9:9:9:6:6:14:11:11:7:7:3:14:3:5:5:10:10:14:10:9:10:10:7:14:7:7:2:2:2:14:2:4:4:3:3:14:2:2:7:7:2:14:2:10:10:6:6:14:7:7:8:8:2:13:2:6:6:5:5:13:5:3:3:6:6:13:11:11:4:4:8:13:8:8:1:1:8:13:8:8:8:9:9:13:4:4:2:2:2:13:6:6:6:10:10:13:10:10:1:1:7:13:7:7:11:11:9:13:9:5:5:5:1:13:1:9:9:9:5:13:5:8:8:8:7:13:7:10:10:4:4:13:1:1:11:11:11:13:2:2:2:1:1:13:1:8:8:3:3:13:9:9:10:10:10:13:10:6:6:11:11:13:8:8:9:9:5:13:5:6:6:9:9:13:9:6:6:6:6:13:11:11:7:7:2:13:2:6:6:4:4:13:4:5:5:9:9:13:3:3:7:7:5:5:5:1:1:7:7:5:5:5:4:4:9:9:9:1:1:4:4:10:11:11:9:8:8:11:2:2:2:6:6:6:10:10:9:9:3:3:3:1:1:7:7:7:8:8:10:10:10:1:1:6:6:4:4:6:6:8:8:10:10:2:2:2:9:9:9:9:5:5:5:8:8:11:11:11:7:7:7:1:1:4:4:3:3:11:11:1:1:10:10:4:4:8:8:11:11:9:9:7:7:8:8:6:6:5:1:1:8:8:7:7:1:1:1:7:7:5:11:11:3:3:10:10:6:7:7:7:9:9:9:4:4:10:10:10:3:3:11:11:11:8:8:2:2:2:5:5:2:2:2:11:11:11:2:2:9:1:1:5:5:5:3:3:8:10:4:4:9:9:3:3:2:3:3:9:8:8:4:4:4:10:10:2:2:10:10:10:4:4:4:4:10:10:8:8:8:3:19:3:3:1:1:1:11:11:11:2:2:2:8:8:2:2:7:7:2:12:2:2:9:9:10:10:9:17:7:9:9:1:1:12:8:8:3:3:3:19:7:1:1:6:12:6:5:5:2:19:3:3:10:10:5:5:5:8:8:9:9:9:3:3:3:7:12:7:9:9:5:5:5:17:3:3:3:3:12:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:12:7:7:6:6:12:6:7:7:7:20:21:11:11:7:7:12:7:6:9:9:17:3:3:3:1:1:1:10:12:11:11:3:3:5:5:5:4:4:12:4:6:6:6:21:19:10:3:3:5:5:12:10:10:2:2:22:5:5:8:8:12:8:5:5:5:12:7:7:7:7:17:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:2:1:6:6:17:4:4:8:8:12:10:10:6:6:7:7:7:9:9:10:12:10:8:8:4:4:20:9:9:9:8:12:8:4:4:8:8:11:11:12:7:7:8:8:6:6:19:4:4:6:4:17:2:2:9:9:6:14:6:10:10:1:1:14:11:11:11:3:3:14:8:8:7:7:3:14:3:1:1:8:8:14:3:3:1:1:5:14:5:5:3:3:2:14:2:2:4:4:1:14:1:10:10:8:8:14:8:4:4:4:10:14:10:6:6:3:3:14:11:11:10:10:9:14:9:9:9:6:6:14:11:11:7:7:3:14:3:5:5:10:10:14:10:9:10:10:7:14:7:7:2:2:2:14:2:4:4:3:3:14:2:2:7:7:2:14:2:10:10:6:6:14:7:7:8:8:2:13:2:6:6:5:5:13:5:3:3:6:6:13:11:11:4:4:8:13:8:8:1:1:8:13:8:8:8:9:9:13:4:4:2:2:2:13:6:6:6:10:10:13:10:10:1:1:7:13:7:7:11:11:9:13:9:5:5:5:1:13:1:9:9:9:5:13:5:8:8:8:7:13:7:10:10:4:4:13:1:1:11:11:11:13:2:2:2:1:1:13:1:8:8:3:3:13:9:9:10:10:10:13:10:6:6:11:11:13:8:8:9:9:5:13:5:6:6:9:9:13:9:6:6:6:6:13:11:11:7:7:2:13:2:6:6:4:4:13:4:5:5:9:9:13:3:3:7:7:5:5:5:1:1:7:7:5:5:5:4:4:9:9:9:1:1:4:4:10:11:11:9:8:8:11:2:2:2:6:6:6:10:10:9:9:3:3:3:1:1:7:7:7:8:8:10:10:10:1:1:6:6:4:4:6:6:8:8:10:10:2:2:2:9:9:9:9:5:5:5:8:8:11:11:11:7:7:7:1:1:4:4:3:3:11:11:1:1:10:10:4:4:8:8:11:11:9:9:7:7:8:8:6:6:5:1:1:8:8:7:7:1:1:1:7:7:5:11:11:3:3:10:10:6:7:7:7:9:9:9:4:4:10:10:10:3:3:11:11:11:8:8:2:2:2:5:5:2:2:2:11:11:11:2:2:9:1:1:5:5:5:3:3:8:10:4:4:9:9:3:3:2:3:3:9:8:8:4:4:4:10:10:2:2:10:10:10:4:4:4:4:10:10:8:8:8:3:19:3:3:1:1:1:11:11:11:2:2:2:8:8:2:2:7:7:2:12:2:2:9:9:10:10:9:17:7:9:9:1:1:1:8:8:3:3:3:7:7:1:1:6:12:6:5:5:2:19:3:3:10:10:5:5:5:8:8:9:9:9:3:3:3:7:7:7:9:9:5:5:5:17:3:3:3:3:12:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:4:7:7:6:6:12:6:7:7:7:20:21:11:11:7:7:12:7:6:9:9:17:3:3:3:1:1:1:10:12:11:11:3:3:5:5:5:4:4:12:4:6:6:6:19:10:10:3:3:5:5:12:10:10:2:2:22:5:5:8:8:12:8:5:5:5:12:7:7:7:7:8:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:2:1:6:6:17:4:4:8:8:12:10:10:6:6:7:7:7:9:9:10:12:10:8:8:4:4:20:9:9:9:8:12:8:4:4:8:8:11:11:12:7:7:8:8:6:6:19:4:4:6:4:17:2:2:9:9:6:14:6:10:10:1:1:14:11:11:11:3:3:14:8:8:7:7:3:14:3:1:1:8:8:14:3:3:1:1:5:14:5:5:3:3:2:14:2:2:4:4:1:14:1:10:10:8:8:14:8:4:4:4:10:14:10:6:6:3:3:14:11:11:10:10:9:14:9:9:9:6:6:14:11:11:7:7:3:14:3:5:5:10:10:14:10:9:10:10:7:14:7:7:2:2:2:14:2:4:4:3:3:14:2:2:7:7:2:14:2:10:10:6:6:14:7:7:8:8:2:13:2:6:6:5:5:13:5:3:3:6:6:13:11:11:4:4:8:13:8:8:1:1:8:13:8:8:8:9:9:13:4:4:2:2:2:13:6:6:6:10:10:13:10:10:1:1:7:13:7:7:11:11:9:13:9:5:5:5:1:13:1:9:9:9:5:13:5:8:8:8:7:13:7:10:10:4:4:13:1:1:11:11:11:13:2:2:2:1:1:13:1:8:8:3:3:13:9:9:10:10:10:13:10:6:6:11:11:13:8:8:9:9:5:13:5:6:6:9:9:13:9:6:6:6:6:13:11:11:7:7:2:13:2:6:6:4:4:13:4:5:5:9:9:13:3:3:7:7:5:5:5:1:1:7:7:5:5:5:4:4:9:9:9:1:1:4:4:10:11:11:9:8:8:11:2:2:2:6:6:6:10:10:9:9:3:3:3:1:1:7:7:7:8:8:10:10:10:1:1:6:6:4:4:6:6:8:8:10:10:2:2:2:9:9:9:9:5:5:5:8:8:11:11:11:7:7:7:1:1:4:4:3:3:11:11:1:1:10:10:4:4:8:8:11:11:9:9:7:7:8:8:6:6:5:1:1:8:8:7:7:1:1:1:7:7:5:11:11:3:3:10:10:6:7:7:7:9:9:9:4:4:10:10:10:3:3:11:11:11:8:8:2:2:2:5:5:2:2:2:11:11:11:2:2:9:1:1:5:5:5:3:3:8:10:4:4:9:9:3:3:2:3:3:9:8:8:4:4:4:10:10:2:2:10:10:10:4:4:4:4:10:10:8:8:8:3:19:3:3:1:1:1:11:11:11:2:2:2:8:8:2:2:7:7:2:12:2:2:9:9:10:10:9:17:7:9:9:1:1:1:8:8:3:3:3:7:7:1:1:6:6:6:5:5:2:19:3:3:10:10:5:5:5:8:8:9:9:9:3:3:3:7:7:7:9:9:5:5:5:17:3:3:3:3:12:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:4:7:7:6:6:12:6:7:7:7:20:21:11:11:7:7:12:7:6:9:9:17:3:3:3:1:1:1:10:12:11:11:3:3:5:5:5:4:4:12:4:6:6:6:19:10:10:3:3:5:5:12:10:10:2:2:22:5:5:8:8:12:8:5:5:5:12:7:7:7:7:8:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:2:1:6:6:17:4:4:8:8:12:10:10:6:6:7:7:7:9:9:10:12:10:8:8:4:4:20:9:9:9:8:12:8:4:4:8:8:11:11:12:7:7:8:8:6:6:19:4:4:6:4:17:2:2:2:6:6:6:10:10:9:9:3:3:3:1:1:7:7:7:8:8:10:10:10:1:1:6:6:4:4:6:6:8:8:10:10:2:2:2:9:9:9:9:5:5:5:8:8:11:11:11:7:7:7:1:1:4:4:3:3:11:11:1:1:10:10:4:4:8:8:11:11:9:9:7:7:8:8:6:6:5:1:1:8:8:7:7:1:1:1:7:7:5:11:11:3:3:10:10:6:7:2:2:9:9:6:14:6:10:10:1:1:14:11:11:11:3:3:14:8:8:7:7:3:14:3:1:1:8:8:3:3:3:1:1:5:14:5:5:3:3:2:14:2:2:4:4:1:14:1:10:10:8:8:14:8:4:4:4:10:14:10:6:6:3:3:3:11:11:10:10:9:14:9:9:9:6:6:14:11:11:7:7:3:14:3:5:5:10:10:14:10:9:10:10:7:14:7:7:2:2:2:14:2:4:4:3:3:14:2:2:7:7:2:14:2:10:10:6:6:14:7:7:8:8:2:13:2:6:6:5:5:13:5:3:3:6:6:13:11:11:4:4:8:13:8:8:1:1:8:13:8:8:8:9:9:13:4:4:2:2:2:13:6:6:6:10:10:13:10:10:1:1:7:13:7:7:11:11:9:13:9:5:5:5:1:13:1:9:9:9:5:13:5:8:8:8:7:13:7:10:10:4:4:1:1:1:11:11:11:13:2:2:2:1:1:13:1:8:8:3:3:13:9:9:10:10:10:13:10:6:6:11:11:13:8:8:9:9:5:13:5:6:6:9:9:13:9:6:6:6:6:13:11:11:7:7:2:13:2:6:6:4:4:13:4:5:5:9:9:13:3:3:7:7:5:5:5:1:1:7:7:5:5:5:4:4:9:9:9:1:1:4:4:10:11:11:9:8:8:11:2:10:10:10:10:9:9:9:1:1:1:4:4:3:3:8:8:5:5:11:11:2:11:11:1:1:9:9:1:1:11:11:7:7:7:8:8:10:10:10:11:11:3:3:9:9:7:7:11:11:11:9:9:10:10:10:5:5:1:1:4:4:6:6:8:8:1:1:6:6:5:5:10:10:9:9:6:6:7:7:7:11:11:7:7:7:10:10:3:3:8:8:8:6:6:6:8:8:4:4:2:2:2:3:3:3:2:2:3:3:2:2:8:8:6:9:9:9:2:2:4:4:3:3:5:5:3:3:4:4:1:1:7:7:7:1:1:2:2:2:7:2:11:11:10:5:5:8:8:9:8:8:4:4:4:10:10:2:2:10:10:10:4:4:4:4:10:10:8:8:8:3:19:3:3:1:1:1:11:11:11:2:2:2:8:8:2:2:7:7:2:12:2:2:9:9:10:10:9:17:7:9:9:1:1:1:8:8:3:3:3:7:7:1:1:6:6:6:5:5:2:19:3:3:10:10:5:5:5:8:8:9:9:9:3:3:3:7:7:7:9:9:5:5:5:17:3:3:3:3:12:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:4:7:7:6:6:12:6:7:7:7:20:21:11:11:7:7:12:7:6:9:9:17:3:3:3:1:1:1:10:12:11:11:3:3:5:5:5:4:4:12:4:6:6:6:19:10:10:3:3:5:5:12:10:10:2:2:22:5:5:8:8:12:8:5:5:5:12:7:7:7:7:8:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:2:1:6:6:17:4:4:8:8:12:10:10:6:6:7:7:7:9:9:10:12:10:8:8:4:4:20:9:9:9:8:12:8:4:4:8:8:11:11:12:7:7:8:8:6:6:19:4:4:6:4:17:2:2:2:6:6:6:10:10:9:9:3:3:3:1:1:7:7:7:8:8:10:10:10:1:1:6:6:4:4:6:6:8:8:10:10:2:2:2:9:9:9:9:5:5:5:8:8:11:11:11:7:7:7:1:1:4:4:3:3:11:11:1:1:10:10:4:4:8:8:11:11:9:9:7:7:8:8:6:6:5:1:1:8:8:7:7:1:1:1:7:7:5:11:11:3:3:10:10:6:7:2:2:9:9:6:14:6:10:10:1:1:14:11:11:11:3:3:14:8:8:7:7:3:14:3:1:1:8:8:14:3:3:1:1:5:14:5:5:3:3:2:14:2:2:4:4:1:14:1:10:10:8:8:14:8:4:4:4:10:14:10:6:6:3:3:14:11:11:10:10:9:14:9:9:9:6:6:14:11:11:7:7:3:14:3:5:5:10:10:14:10:9:10:10:7:14:7:7:2:2:2:14:2:4:4:3:3:14:2:2:7:7:2:14:2:10:10:6:6:14:7:7:8:8:2:13:2:6:6:5:5:13:5:3:3:6:6:13:11:11:4:4:8:13:8:8:1:1:8:13:8:8:8:9:9:13:4:4:2:2:2:13:6:6:6:10:10:13:10:10:1:1:7:13:7:7:11:11:9:13:9:5:5:5:1:13:1:9:9:9:5:13:5:8:8:8:7:13:7:10:10:4:4:13:1:1:11:11:11:13:2:2:2:1:1:13:1:8:8:3:3:13:9:9:10:10:10:13:10:6:6:11:11:13:8:8:9:9:5:13:5:6:6:9:9:13:9:6:6:6:6:13:11:11:7:7:2:13:2:6:6:4:4:13:4:5:5:9:9:13:3:3:7:7:5:5:5:1:1:7:7:5:5:5:4:4:9:9:9:1:1:4:4:10:11:11:9:8:8:11:11:11:1:1:2:2:7:7:4:4:4:4:2:2:5:5:10:10:7:7:7:2:2:2:2:5:5:5:3:3:11:11:11:7:7:8:8:3:3:4:4:4:10:10:3:3:2:2:2:7:7:4:1:1:1:11:11:9:9:10:7:7:5:8:8:10:10:10:9:9:2:2:1:1:1:3:3:1:1:3:3:10:10:10:8:8:9:9:9:4:4:10:10:8:8:5:5:8:8:9:9:7:7:7:2:11:11:3:3:3:9:9:6:6:6:3:3:8:8:11:6:6:6:1:1:1:8:8:8:7:11:11:6:6:6:9:9:2:6:5:5:11:11:1:1:9:9:11:10:10:8:8:4:4:4:10:10:2:2:10:10:10:4:4:4:4:10:10:8:8:8:3:19:3:3:1:1:1:11:11:11:2:2:2:8:8:2:2:7:7:2:12:2:2:9:9:10:10:9:17:7:9:9:1:1:1:8:8:3:3:3:7:7:1:1:6:6:6:5:5:2:19:3:3:10:10:5:5:5:8:8:9:9:9:3:3:3:7:7:7:9:9:5:5:5:17:3:3:3:3:12:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:4:7:7:6:6:12:6:7:7:7:20:21:11:11:7:7:12:7:6:9:9:17:3:3:3:1:1:1:10:12:11:11:3:3:5:5:5:4:4:12:4:6:6:6:19:10:10:3:3:5:5:12:10:10:2:2:22:5:5:8:8:12:8:5:5:5:12:7:7:7:7:8:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:2:1:6:6:17:4:4:8:8:12:10:10:6:6:7:7:7:9:9:10:12:10:8:8:4:4:20:9:9:9:8:12:8:4:4:8:8:11:11:12:7:7:8:8:6:6:19:4:4:6:4:17:2:2:2:6:6:6:10:10:9:9:3:3:3:1:1:7:7:7:8:8:10:10:10:1:1:6:6:4:4:6:6:8:8:10:10:2:2:2:9:9:9:9:5:5:5:8:8:11:11:11:7:7:7:1:1:4:4:3:3:11:11:1:1:10:10:4:4:8:8:11:11:9:9:7:7:8:8:6:6:5:1:1:8:8:7:7:1:1:1:7:7:5:11:11:3:3:10:10:6:7:2:2:9:9:6:14:6:10:10:1:1:14:11:11:11:3:3:14:8:8:7:7:3:14:3:1:1:8:8:14:3:3:1:1:5:14:5:5:3:3:2:14:2:2:4:4:1:14:1:10:10:8:8:14:8:4:4:4:10:14:10:6:6:3:3:14:11:11:10:10:9:14:9:9:9:6:6:14:11:11:7:7:3:14:3:5:5:10:10:14:10:9:10:10:7:14:7:7:2:2:2:14:2:4:4:3:3:14:2:2:7:7:2:14:2:10:10:6:6:14:7:7:8:8:2:13:2:6:6:5:5:13:5:3:3:6:6:13:11:11:4:4:8:13:8:8:1:1:8:13:8:8:8:9:9:13:4:4:2:2:2:13:6:6:6:10:10:13:10:10:1:1:7:13:7:7:11:11:9:13:9:5:5:5:1:13:1:9:9:9:5:13:5:8:8:8:7:13:7:10:10:4:4:13:1:1:11:11:11:13:2:2:2:1:1:13:1:8:8:3:3:13:9:9:10:10:10:13:10:6:6:11:11:13:8:8:9:9:5:13:5:6:6:9:9:13:9:6:6:6:6:13:11:11:7:7:2:13:2:6:6:4:4:13:4:5:5:9:9:13:3:3:7:7:5:5:5:1:1:7:7:5:5:5:4:4:9:9:9:1:1:4:4:10:11:11:9:8:8:11:1:1:4:4:4:6:6:6:8:8:2:2:9:9:10:10:1:1:2:2:2:2:1:1:3:3:9:9:9:1:10:10:7:7:10:10:10:6:6:5:5:7:7:3:3:7:7:9:9:9:8:8:11:11:11:10:10:10:3:3:11:3:3:6:6:5:5:2:2:6:8:8:8:7:7:7:8:5:5:8:8:11:11:9:9:9:11:11:11:7:7:4:4:4:5:5:3:3:7:7:6:6:8:8:3:3:11:11:11:5:5:9:9:9:8:8:10:10:11:11:1:1:8:1:1:7:2:2:1:1:3:3:3:9:2:2:2:11:2:2:4:4:10:10:1:1:10:7:4:4:8:8:4:4:4:10:10:2:2:10:10:10:4:4:4:4:10:10:8:8:8:3:19:3:3:1:1:1:11:11:11:2:2:2:8:8:2:2:7:7:2:12:2:2:9:9:10:10:9:17:7:9:9:1:1:1:8:8:3:3:3:7:7:1:1:6:6:6:5:5:2:19:3:3:10:10:5:5:5:8:8:9:9:9:3:3:3:7:7:7:9:9:5:5:5:17:3:3:3:3:12:5:5:5:2:2:21:2:2:1:1:12:10:10:9:9:6:6:2:2:2:11:12:11:11:6:6:4:4:7:7:6:6:12:6:7:7:7:20:21:11:11:7:7:12:7:6:9:9:17:3:3:3:1:1:1:10:12:11:11:3:3:5:5:5:4:4:12:4:6:6:6:19:10:10:3:3:5:5:12:10:10:2:2:22:5:5:8:8:12:8:5:5:5:12:7:7:7:7:8:8:11:11:12:4:4:4:1:1:1:1:9:12:9:9:6:6:1:1:2:2:2:6:12:6:6:6:20:3:5:1:1:1:1:12:9:9:2:2:20:8:8:7:12:5:5:5:2:2:1:6:6:17:4:4:8:8:12:10:10:6:6:7:7:7:9:9:10:12:10:8:8:4:4:20:9:9:9:8:12:8:4:4:8:8:11:11:12:7:7:8:8:6:6:19:4:4:6:4:17:2:2:2:6:6:6:10:10:9:9:3:3:3:1:1:7:7:7:8:8:10:10:10:1:1:6:6:4:4:6:6:8:8:10:10:2:2:2:9:9:9:9:5:5:5:8:8:11:11:11:7:7:7:1:1:4:4:3:3:11:11:1:1:10:10:4:4:8:8:11:11:9:9:7:7:8:8:6:6:5:1:1:8:8:7:7:1:1:1:7:7:5:11:11:3:3:10:10:6:7:2:2:9:9:6:14:6:10:10:1:1:14:11:11:11:3:3:14:8:8:7:7:3:14:3:1:1:8:8:14:3:3:1:1:5:14:5:5:3:3:2:14:2:2:4:4:1:14:1:10:10:8:8:14:8:4:4:4:10:14:10:6:6:3:3:14:11:11:10:10:9:14:9:9:9:6:6:14:11:11:7:7:3:14:3:5:5:10:10:14:10:9:10:10:7:14:7:7:2:2:2:14:2:4:4:3:3:14:2:2:7:7:2:14:2:10:10:6:6:14:7:7:8:8:2:13:2:6:6:5:5:13:5:3:3:6:6:13:11:11:4:4:8:13:8:8:1:1:8:13:8:8:8:9:9:13:4:4:2:2:2:13:6:6:6:10:10:13:10:10:1:1:7:13:7:7:11:11:9:13:9:5:5:5:1:13:1:9:9:9:5:13:5:8:8:8:7:13:7:10:10:4:4:13:1:1:11:11:11:13:2:2:2:1:1:13:1:8:8:3:3:13:9:9:10:10:10:13:10:6:6:11:11:13:8:8:9:9:5:13:5:6:6:9:9:13:9:6:6:6:6:13:11:11:7:7:2:13:2:6:6:4:4:13:4:5:5:9:9:13:3:3:7:7:5:5:5:1:1:7:7:5:5:5:4:4:9:9:9:1:1:4:4:10:11:11:9:8:8:11:1:1:10:10:1:1:1:8:8:5:5:5:10:10:2:3:3:8:8:2:2:9:10:10:5:5:2:2:7:7:3:3:3:7:7:9:9:2:2:11:11:6:6:7:7:8:8:9:9:11:11:11:5:5:11:11:4:4:8:8:8:8:6:6:11:11:1:1:11:11:1:1:3:3:2:2:3:3:1:1:1:4:4:9:7:7:10:10:5:5:10:10:5:4:4:6:6:11:11:10:10:10:2:2:7:7:7:3:3:9:9:4:4:4:7:7:9:9:9:10:10:6:6:3:3:4:11:11:9:9:9:2:2:3:3:9:1:1:7:7:2:2:6:6:8:8:1:8:8:8:</t>
+  </si>
+  <si>
+    <t>2:2:5:5:2:2:9:9:7:7:3:3:2:2:2:4:4:4:6:6:6:8:8:8:1:1:1:6:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:16:2:2:10:10:4:4:17:4:6:6:11:11:11:3:3:7:7:7:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:3:6:6:6:10:17:10:4:4:2:2:2:10:10:6:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:5:5:5:7:7:7:11:11:5:17:5:11:11:11:2:2:2:5:5:4:4:6:6:6:7:7:7:6:6:8:8:8:7:7:7:7:1:1:9:9:4:4:4:5:5:1:1:3:3:5:5:9:9:9:6:11:11:11:9:9:9:6:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:11:11:11:1:1:6:1:1:7:7:4:4:4:4:9:9:1:1:1:2:2:2:4:4:4:6:6:6:1:3:3:5:5:1:1:1:8:8:8:1:1:6:6:5:5:5:4:4:2:2:2:6:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:15:7:3:3:3:2:2:6:3:1:1:5:5:5:3:3:4:4:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:5:7:7:10:6:2:2:2:1:1:7:1:7:7:7:7:3:3:4:4:5:5:4:4:9:3:3:2:2:2:1:1:1:3:3:3:10:10:1:1:8:8:10:10:5:5:6:6:7:7:7:1:1:1:8:8:11:11:4:4:4:2:2:2:8:8:10:10:10:9:9:8:8:3:3:2:2:2:2:7:7:7:3:3:6:6:2:2:6:6:6:10:10:10:6:6:6:11:11:8:8:7:7:10:10:8:8:1:1:1:6:9:9:11:11:2:2:10:10:10:1:1:4:4:9:9:4:4:4:3:3:10:10:10:8:8:9:9:4:4:9:9:9:5:5:11:11:11:11:5:5:3:3:3:9:9:2:2:5:5:9:9:4:4:4:2:5:5:5:1:1:1:6:6:2:2:2:2:9:9:3:3:6:6:4:4:6:6:5:5:9:9:7:7:11:11:11:3:3:3:5:5:8:8:9:9:6:6:6:7:7:10:10:8:8:5:5:5:11:11:5:5:9:11:11:8:8:8:2:2:10:10:1:1:6:6:1:1:1:11:11:11:11:1:1:10:10:11:11:7:7:7:5:5:4:4:7:7:6:6:4:5:5:6:6:2:4:4:8:8:5:5:6:6:9:9:9:9:3:3:5:3:3:10:10:9:9:6:6:10:10:7:7:7:8:8:9:11:11:2:8:8:7:5:8:1:1:10:10:8:8:4:3:10:10:10:7:7:7:11:11:5:5:1:1:10:10:10:11:11:3:3:6:6:8:8:9:9:9:7:7:4:4:3:3:3:8:8:1:1:2:2:1:1:1:4:4:4:6:6:9:9:8:8:7:7:7:9:9:9:1:1:11:11:6:6:2:2:5:5:1:1:1:2:2:2:7:7:11:11:10:10:10:4:4:1:1:8:8:8:6:6:4:4:11:11:11:9:9:8:8:9:9:7:7:7:5:5:1:5:5:5:8:8:8:2:2:3:3:3:3:2:2:3:3:3:10:10:7:7:10:10:10:11:11:5:2:2:11:11:9:9:6:6:9:3:3:2:2:4:8:10:2:2:5:5:2:2:9:9:7:7:3:3:2:2:2:4:4:4:6:6:6:8:8:8:1:1:1:6:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:16:2:2:10:10:4:4:17:4:6:6:11:11:11:3:3:7:7:7:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:3:6:6:6:10:17:10:4:4:2:2:2:10:10:6:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:5:5:5:7:7:7:11:11:5:17:5:11:11:11:2:2:2:5:5:4:4:6:6:6:7:7:7:6:6:8:8:8:7:7:7:7:1:1:9:9:4:4:4:5:5:1:1:3:3:5:5:9:9:9:6:11:11:11:9:9:9:6:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:11:11:11:1:1:6:1:1:7:7:4:4:4:4:9:9:1:1:1:2:2:2:4:4:4:6:6:6:1:3:3:5:5:1:1:1:8:8:8:1:1:6:6:5:5:5:4:4:2:2:2:6:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:15:7:3:3:3:2:2:6:3:1:1:5:5:5:3:3:4:4:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:5:7:7:10:6:2:2:2:1:1:7:1:7:7:7:7:3:3:4:4:5:5:4:4:9:3:3:2:2:2:1:1:1:3:3:3:10:10:1:1:8:8:10:10:5:5:6:6:7:7:7:1:1:1:8:8:11:11:4:4:4:2:2:2:8:8:10:10:10:9:9:8:8:3:3:2:2:2:2:7:7:7:3:3:6:6:2:2:6:6:6:10:10:10:6:6:6:11:11:8:8:7:7:10:10:8:8:1:1:1:6:9:9:11:11:2:2:10:10:10:1:1:4:4:9:9:4:4:4:3:3:10:10:10:8:8:9:9:4:4:9:9:9:5:5:11:11:11:11:5:5:3:3:3:9:9:2:2:5:5:9:9:4:4:4:2:5:5:5:1:1:1:6:6:2:2:2:2:9:9:3:3:6:6:4:4:6:6:5:5:9:9:7:7:11:11:11:3:3:3:5:5:8:8:9:9:6:6:6:7:7:10:10:8:8:5:5:5:11:11:5:5:9:11:11:8:8:8:2:2:10:10:1:1:6:6:1:1:1:11:11:11:11:1:1:10:10:11:11:7:7:7:5:5:4:4:7:7:6:6:4:5:5:6:6:2:4:4:8:8:5:5:6:6:9:9:9:9:3:3:5:3:3:10:10:9:9:6:6:10:10:7:7:7:8:8:9:11:11:2:8:8:7:5:8:1:1:10:10:8:8:4:3:10:10:10:7:7:7:11:11:5:5:1:1:10:10:10:11:11:3:3:6:6:8:8:9:9:9:7:7:4:4:3:3:3:8:8:1:1:2:2:1:1:1:4:4:4:6:6:9:9:8:8:7:7:7:9:9:9:1:1:11:11:6:6:2:2:5:5:1:1:1:2:2:2:7:7:11:11:10:10:10:4:4:1:1:8:8:8:6:6:4:4:11:11:11:9:9:8:8:9:9:7:7:7:5:5:1:5:5:5:8:8:8:2:2:3:3:3:3:2:2:3:3:3:10:10:7:7:10:10:10:11:11:5:2:2:11:11:9:9:6:6:9:3:3:2:2:4:8:10:2:2:5:5:2:2:9:9:7:7:3:3:2:2:2:4:4:4:6:6:6:8:8:8:1:1:1:16:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:2:2:2:10:10:4:4:17:4:6:6:11:11:11:3:3:7:7:7:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:3:6:6:6:10:17:10:4:4:2:2:2:10:10:6:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:5:5:5:7:7:7:11:11:5:17:5:11:11:11:2:2:2:5:5:4:4:6:6:6:7:7:7:6:6:8:8:8:7:7:7:7:1:1:9:9:4:4:4:5:5:1:1:3:3:5:5:9:9:9:6:11:11:11:9:9:9:6:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:11:11:11:1:1:6:1:1:7:7:4:4:4:4:9:9:1:1:1:2:2:2:4:4:4:6:6:6:15:3:3:5:5:1:1:1:8:8:8:1:1:6:6:5:5:5:4:4:2:2:2:6:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:7:7:3:3:3:2:2:6:3:1:1:5:5:5:3:3:4:4:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:5:7:7:10:6:2:2:2:1:1:7:1:7:7:7:7:3:3:4:4:5:5:4:4:9:3:3:2:2:2:1:1:1:3:3:3:10:10:1:1:8:8:10:10:5:5:6:6:7:7:7:1:1:1:8:8:11:11:4:4:4:2:2:2:8:8:10:10:10:9:9:8:8:3:3:2:2:2:2:7:7:7:3:3:6:6:2:2:6:6:6:10:10:10:6:6:6:11:11:8:8:7:7:10:10:8:8:1:1:1:6:9:9:11:11:2:2:10:10:10:1:1:4:4:9:9:4:4:4:3:3:10:10:10:8:8:9:9:4:4:9:9:9:5:5:11:11:11:11:5:5:3:3:3:9:9:2:2:5:5:9:9:4:4:4:2:5:5:5:1:1:1:6:6:2:2:2:2:9:9:3:3:6:6:4:4:6:6:5:5:9:9:7:7:11:11:11:3:3:3:5:5:8:8:9:9:6:6:6:7:7:10:10:8:8:5:5:5:11:11:5:5:9:11:11:8:8:8:2:2:10:10:1:1:6:6:1:1:1:11:11:11:11:1:1:10:10:11:11:7:7:7:5:5:4:4:7:7:6:6:4:5:5:6:6:2:4:4:8:8:5:5:6:6:9:9:9:9:3:3:5:3:3:10:10:9:9:6:6:10:10:7:7:7:8:8:9:11:11:2:8:8:7:5:8:1:1:10:10:8:8:4:3:10:10:10:7:7:7:11:11:5:5:1:1:10:10:10:11:11:3:3:6:6:8:8:9:9:9:7:7:4:4:3:3:3:8:8:1:1:2:2:1:1:1:4:4:4:6:6:9:9:8:8:7:7:7:9:9:9:1:1:11:11:6:6:2:2:5:5:1:1:1:2:2:2:7:7:11:11:10:10:10:4:4:1:1:8:8:8:6:6:4:4:11:11:11:9:9:8:8:9:9:7:7:7:5:5:1:5:5:5:8:8:8:2:2:3:3:3:3:2:2:3:3:3:10:10:7:7:10:10:10:11:11:5:2:2:11:11:9:9:6:6:9:3:3:2:2:4:8:10:2:2:5:5:2:2:9:9:7:7:3:3:2:2:2:4:4:4:6:6:6:8:8:8:1:1:1:16:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:2:2:2:10:10:4:4:17:4:6:6:11:11:11:3:3:7:7:7:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:3:6:6:6:10:17:10:4:4:2:2:2:10:10:6:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:5:5:5:7:7:7:11:11:5:17:5:11:11:11:2:2:2:5:5:4:4:6:6:6:7:7:7:6:6:8:8:8:7:7:7:7:1:1:9:9:4:4:4:5:5:1:1:3:3:5:5:9:9:9:6:11:11:11:9:9:9:6:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:11:11:11:1:1:6:1:1:7:7:4:4:4:4:9:9:1:1:1:2:2:2:4:4:4:6:6:6:15:3:3:5:5:1:1:1:8:8:8:1:1:6:6:5:5:5:4:4:2:2:2:6:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:7:7:3:3:3:2:2:6:3:1:1:5:5:5:3:3:4:4:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:5:7:7:10:6:2:2:2:1:1:7:1:3:10:10:10:7:7:7:11:11:5:5:1:1:10:10:10:11:11:3:3:6:6:8:8:9:9:9:7:7:4:4:3:3:3:8:8:1:1:2:2:1:1:1:4:4:4:6:6:9:9:8:8:7:7:7:9:9:9:1:1:11:11:6:6:2:2:5:5:1:1:1:2:2:2:7:7:11:11:10:10:10:4:4:1:1:8:8:8:6:6:4:4:11:11:11:9:9:8:8:9:7:7:7:7:3:3:4:4:5:5:4:4:9:3:3:2:2:2:1:1:1:3:3:3:10:10:1:1:8:8:10:10:5:5:6:6:7:7:7:1:1:1:8:8:11:11:4:4:4:2:2:2:8:8:10:10:10:9:9:8:8:3:3:2:2:2:2:7:7:7:3:3:6:6:2:2:6:6:6:10:10:10:6:6:6:11:11:8:8:7:7:10:10:8:8:1:1:1:6:9:9:11:11:2:2:10:10:10:1:1:4:4:9:9:4:4:4:3:3:10:10:10:8:8:9:9:4:4:9:9:9:5:5:11:11:11:11:5:5:3:3:3:9:9:2:2:5:5:9:9:4:4:4:2:5:5:5:1:1:1:6:6:2:2:2:2:9:9:3:3:6:6:4:4:6:6:5:5:9:9:7:7:11:11:11:3:3:3:5:5:8:8:9:9:6:6:6:7:7:10:10:8:8:5:5:5:11:11:5:5:9:11:11:8:8:8:2:2:10:10:1:1:6:6:1:1:1:11:11:11:11:1:1:10:10:11:11:7:7:7:5:5:4:4:7:7:6:6:4:5:5:6:6:2:4:4:8:8:5:5:6:6:9:9:9:9:3:3:5:3:3:10:10:9:9:6:6:10:10:7:7:7:8:8:9:11:11:2:8:8:7:5:8:1:1:10:10:8:8:4:8:8:8:7:7:5:5:8:8:6:6:9:9:5:5:8:8:3:3:8:8:4:4:2:2:2:3:3:10:10:10:9:9:9:1:1:1:8:8:7:7:7:4:4:4:4:10:10:3:3:5:5:8:8:2:2:10:10:1:1:8:8:7:7:7:7:9:9:10:10:10:3:3:11:11:11:2:2:1:11:11:3:3:3:4:4:1:1:1:11:11:7:7:1:1:9:9:2:2:2:1:1:4:4:6:6:7:7:7:2:2:7:9:9:11:11:6:6:9:9:9:1:1:11:11:11:3:3:11:11:2:2:6:6:10:10:5:5:5:2:10:10:10:3:3:6:6:11:9:5:2:2:5:5:2:2:9:9:7:7:3:3:2:2:2:4:4:4:6:6:6:8:8:8:1:1:1:16:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:2:2:2:10:10:4:4:17:4:6:6:11:11:11:3:3:7:7:7:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:3:6:6:6:10:17:10:4:4:2:2:2:10:10:6:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:5:5:5:7:7:7:11:11:5:17:5:11:11:11:2:2:2:5:5:4:4:6:6:6:7:7:7:6:6:8:8:8:7:7:7:7:1:1:9:9:4:4:4:5:5:1:1:3:3:5:5:9:9:9:6:11:11:11:9:9:9:6:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:11:11:11:1:1:6:1:1:7:7:4:4:4:4:9:9:1:1:1:2:2:2:4:4:4:6:6:6:15:3:3:5:5:1:1:1:8:8:8:1:1:6:6:5:5:5:4:4:2:2:2:6:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:7:7:3:3:3:2:2:6:3:1:1:5:5:5:3:3:4:4:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:5:7:7:10:6:2:2:2:1:1:7:1:3:10:10:10:7:7:7:11:11:5:5:1:1:10:10:10:11:11:3:3:6:6:8:8:9:9:9:7:7:4:4:3:3:3:8:8:1:1:2:2:1:1:1:4:4:4:6:6:9:9:8:8:7:7:7:9:9:9:1:1:11:11:6:6:2:2:5:5:1:1:1:2:2:2:7:7:11:11:10:10:10:4:4:1:1:8:8:8:6:6:4:4:11:11:11:9:9:8:8:9:7:7:7:7:3:3:4:4:5:5:4:4:9:3:3:2:2:2:1:1:1:3:3:3:10:10:1:1:8:8:10:10:5:5:6:6:7:7:7:1:1:1:8:8:11:11:4:4:4:2:2:2:8:8:10:10:10:9:9:8:8:3:3:2:2:2:2:7:7:7:3:3:6:6:2:2:6:6:6:10:10:10:6:6:6:11:11:8:8:7:7:10:10:8:8:1:1:1:6:9:9:11:11:2:2:10:10:10:1:1:4:4:9:9:4:4:4:3:3:10:10:10:8:8:9:9:4:4:9:9:9:5:5:11:11:11:11:5:5:3:3:3:9:9:2:2:5:5:9:9:4:4:4:2:5:5:5:1:1:1:6:6:2:2:2:2:9:9:3:3:6:6:4:4:6:6:5:5:9:9:7:7:11:11:11:3:3:3:5:5:8:8:9:9:6:6:6:7:7:10:10:8:8:5:5:5:11:11:5:5:9:11:11:8:8:8:2:2:10:10:1:1:6:6:1:1:1:11:11:11:11:1:1:10:10:11:11:7:7:7:5:5:4:4:7:7:6:6:4:5:5:6:6:2:4:4:8:8:5:5:6:6:9:9:9:9:3:3:5:3:3:10:10:9:9:6:6:10:10:7:7:7:8:8:9:11:11:2:8:8:7:5:8:1:1:10:10:8:8:4:10:10:10:10:9:9:6:6:6:7:7:7:9:2:2:6:6:8:8:3:3:5:5:11:11:8:8:3:3:4:4:4:1:1:2:1:1:7:7:9:9:5:5:6:6:2:2:1:1:7:7:11:11:11:8:2:2:1:1:11:11:11:11:3:3:3:4:4:10:10:11:11:2:2:7:7:7:8:8:8:10:10:2:2:2:2:7:7:1:1:6:6:3:3:3:4:4:9:9:10:10:8:8:9:9:9:3:3:3:11:11:5:5:11:11:9:9:8:8:1:1:1:5:5:5:10:10:8:8:2:2:4:4:7:7:7:10:10:8:5:9:9:9:1:1:3:3:10:4:6:2:2:5:5:2:2:9:9:7:7:3:3:2:2:2:4:4:4:6:6:6:8:8:8:1:1:1:16:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:2:2:2:10:10:4:4:17:4:6:6:11:11:11:3:3:7:7:7:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:3:6:6:6:10:17:10:4:4:2:2:2:10:10:6:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:5:5:5:7:7:7:11:11:5:17:5:11:11:11:2:2:2:5:5:4:4:6:6:6:7:7:7:6:6:8:8:8:7:7:7:7:1:1:9:9:4:4:4:5:5:1:1:3:3:5:5:9:9:9:6:11:11:11:9:9:9:6:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:11:11:11:1:1:6:1:1:7:7:4:4:4:4:9:9:1:1:1:2:2:2:4:4:4:6:6:6:15:3:3:5:5:1:1:1:8:8:8:1:1:6:6:5:5:5:4:4:2:2:2:6:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:7:7:3:3:3:2:2:6:3:1:1:5:5:5:3:3:4:4:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:5:7:7:10:6:2:2:2:1:1:7:1:3:10:10:10:7:7:7:11:11:5:5:1:1:10:10:10:11:11:3:3:6:6:8:8:9:9:9:7:7:4:4:3:3:3:8:8:1:1:2:2:1:1:1:4:4:4:6:6:9:9:8:8:7:7:7:9:9:9:1:1:11:11:6:6:2:2:5:5:1:1:1:2:2:2:7:7:11:11:10:10:10:4:4:1:1:8:8:8:6:6:4:4:11:11:11:9:9:8:8:9:7:7:7:7:3:3:4:4:5:5:4:4:9:3:3:2:2:2:1:1:1:3:3:3:10:10:1:1:8:8:10:10:5:5:6:6:7:7:7:1:1:1:8:8:11:11:4:4:4:2:2:2:8:8:10:10:10:9:9:8:8:3:3:2:2:2:2:7:7:7:3:3:6:6:2:2:6:6:6:10:10:10:6:6:6:11:11:8:8:7:7:10:10:8:8:1:1:1:6:9:9:11:11:2:2:10:10:10:1:1:4:4:9:9:4:4:4:3:3:10:10:10:8:8:9:9:4:4:9:9:9:5:5:11:11:11:11:5:5:3:3:3:9:9:2:2:5:5:9:9:4:4:4:2:5:5:5:1:1:1:6:6:2:2:2:2:9:9:3:3:6:6:4:4:6:6:5:5:9:9:7:7:11:11:11:3:3:3:5:5:8:8:9:9:6:6:6:7:7:10:10:8:8:5:5:5:11:11:5:5:9:11:11:8:8:8:2:2:10:10:1:1:6:6:1:1:1:11:11:11:11:1:1:10:10:11:11:7:7:7:5:5:4:4:7:7:6:6:4:5:5:6:6:2:4:4:8:8:5:5:6:6:9:9:9:9:3:3:5:3:3:10:10:9:9:6:6:10:10:7:7:7:8:8:9:11:11:2:8:8:7:5:8:1:1:10:10:8:8:4:5:5:11:11:9:9:10:10:4:4:2:2:8:8:8:8:11:11:11:4:2:2:2:2:10:10:10:1:1:8:8:8:11:11:11:11:9:9:3:3:9:9:6:6:5:5:8:8:7:7:7:1:1:2:2:2:1:1:5:5:11:11:10:10:4:4:8:8:9:9:6:6:3:3:4:4:4:4:5:5:7:7:7:2:2:3:3:3:5:5:3:3:10:10:10:1:1:6:6:2:2:2:7:7:11:11:11:9:9:1:1:6:6:3:3:9:9:9:9:3:3:1:1:8:8:8:3:3:10:10:7:11:6:6:7:7:1:7:7:7:7:10:10:1:1:8:2:9:10:4:2:2:5:5:2:2:9:9:7:7:3:3:2:2:2:4:4:4:6:6:6:8:8:8:1:1:1:16:5:5:1:1:1:17:8:11:11:5:5:2:2:8:8:2:2:2:10:10:4:4:17:4:6:6:11:11:11:3:3:7:7:7:3:3:3:11:11:17:10:10:1:1:1:8:8:8:8:3:3:3:6:6:6:10:17:10:4:4:2:2:2:10:10:6:6:3:3:3:4:4:4:17:6:9:9:9:4:4:4:5:5:5:7:7:7:11:11:5:17:5:11:11:11:2:2:2:5:5:4:4:6:6:6:7:7:7:6:6:8:8:8:7:7:7:7:1:1:9:9:4:4:4:5:5:1:1:3:3:5:5:9:9:9:6:11:11:11:9:9:9:6:6:6:5:5:10:10:8:8:7:4:6:6:1:1:11:11:11:11:1:1:6:1:1:7:7:4:4:4:4:9:9:1:1:1:2:2:2:4:4:4:6:6:6:15:3:3:5:5:1:1:1:8:8:8:1:1:6:6:5:5:5:4:4:2:2:2:6:6:6:7:7:3:3:3:5:5:6:6:3:3:8:8:7:7:7:3:3:3:2:2:6:3:1:1:5:5:5:3:3:4:4:4:7:7:7:1:10:10:10:10:5:5:2:2:4:4:5:5:7:7:10:6:2:2:2:1:1:7:1:3:10:10:10:7:7:7:11:11:5:5:1:1:10:10:10:11:11:3:3:6:6:8:8:9:9:9:7:7:4:4:3:3:3:8:8:1:1:2:2:1:1:1:4:4:4:6:6:9:9:8:8:7:7:7:9:9:9:1:1:11:11:6:6:2:2:5:5:1:1:1:2:2:2:7:7:11:11:10:10:10:4:4:1:1:8:8:8:6:6:4:4:11:11:11:9:9:8:8:9:7:7:7:7:3:3:4:4:5:5:4:4:9:3:3:2:2:2:1:1:1:3:3:3:10:10:1:1:8:8:10:10:5:5:6:6:7:7:7:1:1:1:8:8:11:11:4:4:4:2:2:2:8:8:10:10:10:9:9:8:8:3:3:2:2:2:2:7:7:7:3:3:6:6:2:2:6:6:6:10:10:10:6:6:6:11:11:8:8:7:7:10:10:8:8:1:1:1:6:9:9:11:11:2:2:10:10:10:1:1:4:4:9:9:4:4:4:3:3:10:10:10:8:8:9:9:4:4:9:9:9:5:5:11:11:11:11:5:5:3:3:3:9:9:2:2:5:5:9:9:4:4:4:2:5:5:5:1:1:1:6:6:2:2:2:2:9:9:3:3:6:6:4:4:6:6:5:5:9:9:7:7:11:11:11:3:3:3:5:5:8:8:9:9:6:6:6:7:7:10:10:8:8:5:5:5:11:11:5:5:9:11:11:8:8:8:2:2:10:10:1:1:6:6:1:1:1:11:11:11:11:1:1:10:10:11:11:7:7:7:5:5:4:4:7:7:6:6:4:5:5:6:6:2:4:4:8:8:5:5:6:6:9:9:9:9:3:3:5:3:3:10:10:9:9:6:6:10:10:7:7:7:8:8:9:11:11:2:8:8:7:5:8:1:1:10:10:8:8:4:9:9:8:8:2:2:10:10:4:4:3:3:1:1:11:11:11:11:10:10:8:8:8:8:6:6:7:7:7:3:3:7:7:1:1:1:3:3:11:11:4:4:4:11:11:9:9:2:2:2:2:3:3:10:10:10:8:8:8:10:10:7:7:10:10:1:1:9:9:9:1:1:6:6:7:7:1:1:8:8:9:9:7:7:11:11:9:9:2:2:2:10:10:11:11:2:2:5:5:8:8:7:8:8:3:3:3:5:5:5:3:3:10:10:2:2:3:3:6:4:4:6:6:6:5:5:1:1:1:9:9:2:2:7:7:4:4:11:11:11:9:9:5:5:6:6:4:7:1:5:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,46 +133,171 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -186,8 +310,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -210,10 +520,252 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -230,18 +782,62 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 73" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -499,21 +1095,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="7.875" customWidth="1"/>
     <col min="4" max="4" width="41.125" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="9.75" customWidth="1"/>
+    <col min="8" max="8" width="10.625" customWidth="1"/>
+    <col min="9" max="9" width="12.625"/>
+    <col min="12" max="12" width="12.625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" ht="16.5" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -530,7 +1131,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="2" ht="16.5" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -547,7 +1148,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="16.5" hidden="1" spans="1:5">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -564,13 +1165,13 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="16.5" hidden="1" spans="2:5">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="5" ht="16.5" spans="1:5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -587,7 +1188,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="6" ht="16.5" spans="1:5">
       <c r="A6">
         <v>2</v>
       </c>
@@ -604,7 +1205,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="7" ht="16.5" spans="1:5">
       <c r="A7">
         <v>3</v>
       </c>
@@ -621,7 +1222,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="8" ht="16.5" spans="1:5">
       <c r="A8">
         <v>4</v>
       </c>
@@ -638,7 +1239,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="9" ht="16.5" spans="1:5">
       <c r="A9">
         <v>5</v>
       </c>
@@ -656,8 +1257,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="69">
   <si>
     <t>id</t>
   </si>
@@ -264,25 +264,28 @@
     <t>3_3_3_6_6_6_2_2_5_5_1_5_6_1_1_1_1_1_1_1_6_6_6_6_3_3_3_4_4_1_4_5_4_4_3_3_3_6_2_2_4_4_4_4_6_3_1_1_5_5_5_4_4_5_1_6_6_2_2_2_6_6_6_2_2_4_4_4_2_6_6_6_6_6_2_2_2_4_5_3_4_5_4_4_2_2_5_6_4_4_6_3_4_5_5_1_1_6_6_6_6_5_5_4_1_2_5_5_5_5_5_5_6_6_6_6_5_5_5_3_6_5_5_2_1_2_2_2_2_3_3_4_4_3_3_1_4_6_4_5_1_6_3_4_1_1_2_1_3_4_2_2_6_1_1_4_3_1_1_1_1_1_1_1_1_1_1_4_4_4_1_5_1_6_1_6_2_6_6_4_3_3_3_5_2_2_2_2_2_2_5_4_4_4_4_1_6_1_1_2_3_2_2_6_3_3_4_4_4_2_2_2_2_2_4_1_1_1_1_1_3_3_4_6_5_5_2_6_2_2_2_2_3_3_4_4_4_3_1_1_1_1_5_5_5_5_6_6_6_6_6_2_2_5_1_5_5_2_3_5_5_3_3_3_3_1_6_6_2_2_1_6_1_3_3_3_3_3_3_4_6_4_2_6_6_6_2_6_4_4_4_3_3_3_5_5_5_3_3_2_2_1_1_6_3_3_5_3_1_4_2_4_5_5_5_1_1_2_2_1_1_6_4_5_5_5_5_5_5_3_3_3_3_4_4_4_4_5_2_2_3_3_3_3_3_5_5_5_5_3_6_1_1_1_1_6_3_3_4_4_1_3_2_6_5_5_5_4_4_4_3_1_6_6_5_4_4_6_3_6_6_6_1_1_1_1_6_4_4_4_1_3_3_3_3_5_5_5_5_5_4_4_4_1_3_3_3_2_3_3_2_4_5_5_1_2_1_5_6_2_2_1_1_3_3_5_4_1_4_5_5_4_3_4_4_4_6_6_3_3_4_4_4_4_4_3_3_2_1_1_1_1_1_6_1_1_1_1_6_6_2_2_5_5_5_5_5_5_5_5_4_6_6_1_1_3_3_3_3_5_5_4_5_5_5_5_2_5_5_5_5_5_2_2_2_4_6_6_3_5</t>
   </si>
   <si>
-    <t>3_5_5_5_5_11_10_10_4_4_4_10_4_4_4_1_7_7_8_2_6_6_2_10_10_2_11_11_6_6_6_6_11_11_11_3_3_3_3_8_8_9_9_9_8_8_8_2_4_4_4_4_6_6_6_8_8_8_8_8_8_4_4_3_2_5_5_10_10_4_4_5_5_7_6_2_6_6_6_6_5_5_5_6_10_6_6_3_6_6_7_7_2_2_2_2_11_11_11_7_2_9_9_9_9_9_9_9_7_5_5_4_6_2_8_3_3_3_2_2_2_2_7_3_3_3_3_3_6_6_6_11_11_9_6_6_10_11_11_1_1_2_2_9_9_6_6_6_6_6_11_11_10_3_3_8_4_11_4_4_5_10_10_10_4_10_7_6_6_11_11_4_6_2_2_5_5_5_7_4_4_8_8_8_6_6_9_9_7_7_7_1_1_7_6_6_8_6_6_8_1_10_2_2_5_5_8_8_10_10_6_5_6_6_2_9_2_2_1_4_8_9_9_10_10_2_11_6_4_10_3_3_6_6_2_2_7_7_4_4_11_11_11_11_8_8_8_4_6_6_6_6_6_11_11_6_9_9_9_9_11_2_8_4_8_3_3_3_3_3_3_3_3_10_4_10_2_3_7_11_8_8_8_8_11_7_7_7_6_11_11_5_6_6_9_9_7_9_8_6_7_2_9_10_11_2_2_2_2_2_5_10_10_10_10_10_10_3_8_5_5_5_7_7_10_10_4_1_11_11_9_9_9_4_7_7_10_10_4_7_7_3_8_3_3_5_5_7_5_5_3_3_8_11_6_2_2_2_7_7_11_2_5_11_4_4_9_9_9_9_9_9_2_7_7_7_7_5_5_5_6_4_4_4_5_10_8_10_10_10_10_10_8_8_8_9_5_5_10_2_10_10_9_6_6_7_7_10_10_3_3_3_4_4_11_11_11_11_3_6_6_11_8_8_8_3_3_3_7_7_7_7_7_7_7_7_11_11_11_1_10_10_10_10_3_3_3_3_3_3_4_4_4_4_3_2_2_2_2_2_10_10_4_9_5_5_7_9_9_9_7_7_2_10_7_7_7_10_10_8_1_3_2_2_2_2_2_2_2_8_8_5_4_4_4_6_6_6_3_3</t>
+    <t>1_10_10_1_2_1_2_1_7_7_7_7_7_1_11_11_11_1_4_1_9_9_9_1_10_1_9_9_9_9_1_8_8_1_5_1_11_11_11_11_11_11_1_11_11_11_11_11_11_11_11_11_11_11_11_11_11_11_11_11_11_11_1_3_3_1_9_1_5_1_11_11_11_1_11_1_3_3_3_3_3_1_5_5_5_5_5_5_1_11_1_4_1_7_7_7_1_10_10_10_1_7_7_7_7_1_6_1_4_4_1_4_4_4_4_4_4_1_10_10_1_9_9_1_7_7_7_7_7_1_3_1_3_3_3_1_9_9_9_9_9_1_8_8_8_8_1_2_2_2_2_1_9_1_8_1_8_1_7_7_7_7_7_7_7_7_7_1_11_11_11_11_1_5_5_5_5_5_5_5_5_1_11_11_11_1_7_7_7_7_1_3_3_3_3_3_3_1_4_4_4_4_1_3_3_3_3_1_8_1_9_9_9_9_9_9_9_9_9_9_9_1_11_1_7_1_2_2_1_6_6_1_6_6_1_4_1_3_3_1_10_10_1_6_1_7_1_6_6_6_1_7_1_3_3_3_3_1_10_1_8_8_8_8_1_2_1_4_4_1_8_8_1_6_6_6_6_6_1_4_4_1_6_6_1_4_4_1_10_10_10_10_10_10_10_10_10_10_10_10_1_10_10_10_10_10_10_1_3_3_1_11_11_1_8_1_5_5_5_1_6_6_1_4_4_1_8_1_3_3_1_11_1_11_11_1_9_9_1_4_4_4_4_4_1_6_6_6_1_10_10_10_10_10_1_7_1_5_5_1_6_1_6_6_1_8_8_8_8_8_1_4_4_4_4_1_5_5_5_5_1_11_11_1_2_2_2_2_2_2_2_2_2_1_10_10_10_1_2_1_4_1_2_2_1_3_3_3_3_1_11_11_1_8_8_8_1_9_9_9_9_1_3_3_1_4_4_4_4_4_4_1_5_5_5_5_5_5_5_5_1_3_3_1_2_2_2_2_2_2_2_1_6_6_6_1_5_1_9_9_9_9_1_6_1_10_10_10_10_10_1_10_1_3_3_3_3_3_3_3_3_3_3_3_3_3_1_2_2_2_1_10_1_3_1_6_1_11_1_9</t>
   </si>
   <si>
     <t>11_3_5_4_7_9_10_5_3_11_7_7_2_5_8_6_4_7_6_9_4_10_9_5_3_9_3_10_4_3_1_1_1_3_8_3_4_1_1_10_2_6_5_4_2_3_4_4_2_3_2_1_11_1_11_7_1_4_9_1_3_4_1_2_1_9_9_1_1_2_2_1_7_10_5_2_5_2_3_3_1_10_4_1_7_1_1_4_2_6_3_7_8_5_1_2_3_2_11_1_4_3_1_6_4_5_6_1_3_6_2_2_6_10_5_9_4_1_6_6_5_6_10_6_1_8_3_8_2_2_1_1_2_1_5_3_1_8_4_4_9_2_1_2_4_1_8_6_3_5_1_4_8_6_7_6_1_4_4_5_3_8_2_2_6_1_2_4_1_10_4_1_3_3_1_6_1_4_11_5_1_5_1_4_2_9_1_2_2_2_9_5_3_3_3_7_7_2_9_8_5_3_4_4_2_3_1_2_4_1_2_4_3_2_2_8_9_7_4_6_9_1_1_3_1_2_2_2_9_8_1_5_1_1_3_4_7_9_3_7_7_3_3_2_6_6_4_1_1_5_4_3_4_2_4_10_1_6_3_7_5_10_1_7_1_5_5_3_6_5_7_2_3_3_1_5_5_3_4_3_3_3_4_3_1_4_3_5_8_5_9_1_4_3_3_1_3_1_2_8</t>
   </si>
   <si>
-    <t>5_5_2_5_5_8_8_4_4_6_6_7_7_7_7_10_10_10_1_10_3_7_7_7_7_9_9_9_9_9_7_8_5_11_11_8_3_4_2_2_2_7_10_10_10_10_5_5_5_5_5_1_1_1_1_10_10_8_8_8_11_4_4_4_4_4_4_4_4_4_4_8_8_2_9_5_8_8_8_8_4_4_4_4_4_4_4_4_4_4_4_4_4_3_3_9_7_4_4_3_10_10_10_2_2_1_2_2_3_3_3_11_6_6_6_6_6_3_3_3_5_9_11_11_11_3_7_11_11_11_5_5_6_4_4_4_4_4_7_9_6_8_5_3_5_10_10_10_3_3_3_3_6_6_6_4_11_2_2_10_10_10_10_7_7_7_5_4_11_3_3_2_2_1_1_1_4_4_4_6_3_4_9_9_9_2_2_2_9_9_9_3_3_3_6_6_9_4_6_2_2_7_7_4_4_4_4_10_9_8_3_3_9_10_10_10_8_8_8_8_8_8_8_8_8_8_11_11_5_7_5_2_2_3_3_3_3_3_5_5_6_6_6_5_5_5_2_9_9_5_11_11_11_2_2_2_4_4_4_3_2_8_6_6_6_6_5_8_2_2_2_2_2_8_8_8_8_8_7_7_7_4_4_4_11_2_2_2_2_2_9_10_3_8_8_8_8_8_6_5_6_6_6_5_2_3_5_5_5_1_1_7_6_8_10_10_9_2_6_6_6_6_6_8_10_10_10_2_2_2_2_3_3_7_7_7_7_7_7_7_11_11_11_6_6_6_2_8_8_6_6_5_5_8_8_8_8_4_4_7_6_6_5_11_11_4_5_7_4_4_4_4_7_6_6_6_6_3_8_5_5_2_10_10_10_10_10_10_2_2_10_4_9_9_10_5_5_2_2_2_11_11_11_2_2_6_8_8_8_5_5_5_5_5_8_8_8_8_9_9_2_5_5_10_11_11_11_10_7_7_3_3_10_10_10_10_7_7_3_6_6_6_6_6_3_3_5_5_1_1_1_1_2_2_2_2_11_11_9_6_9_8_2_5_5_11_5_5_5_2_11_9_9_7_9_4_4_7_10_9_6_6_6_6_10_10_10_6_3_3_9_9_9_10_8_8_8_5_9_9</t>
-  </si>
-  <si>
-    <t>8_2_10_10_10_8_3_3_3_3_9_7_7_7_7_2_7_7_1_4_8_7_8_8_4_4_4_4_4_4_4_4_2_1_1_9_9_9_9_10_10_10_2_2_2_2_9_9_11_11_11_11_2_4_4_4_11_7_7_9_10_10_10_10_8_3_3_3_4_4_4_9_11_11_11_3_10_10_10_10_10_10_6_4_4_4_4_4_4_4_6_10_10_2_2_6_13_8_3_12_3_3_3_3_7_9_1_1_1_1_1_1_1_1_2_2_2_2_9_9_9_8_9_3_3_3_1_1_12_10_12_7_11_3_10_10_12_9_2_2_2_5_8_8_2_1_1_6_6_6_1_1_11_9_3_12_3_3_3_3_3_3_3_9_3_3_3_3_3_3_8_8_5_5_1_10_10_10_8_8_4_1_10_2_2_9_9_1_1_8_7_8_7_7_5_3_3_3_3_10_2_2_3_3_3_3_3_2_2_11_3_3_1_1_1_1_1_1_13_8_7_7_7_8_3_3_8_7_8_11_8_9_9_8_7_7_6_6_8_6_6_6_2_2_2_5_12_9_9_9_9_9_9_9_9_8_4_4_12_4_4_4_4_8_8_8_1_1_1_11_9_3_9_9_9_6_6_6_6_7_5_5_5_10_7_7_7_8_1_8_8_2_2_2_11_6_6_6_9_1_11_11_6_6_6_6_5_5_5_5_5_5_1_1_8_8_11_4_4_4_4_11_11_6_6_6_6_10_7_7_11_11_12_3_8_12_3_3_7_7_7_11_11_11_8_8_8_8_8_2_2_2_2_2_2_2_2_1_4_4_4_4_9_3_6_6_6_6_9_1_1_1_1_1_1_1_10_12_1_1_3_8_12_13_8_9_6_11_11_2_7_7_5_8_4_7_7_7_1_1_3_9_9_8_8_3_1_5_5_9_9_9_9_9_2_2_4_4_4_9_3_3_7_2_5_5_12_8_8_9_9_9_9_9_5_5_5_5_1_1_1_11_4_6_6_6_6_6_8_10_4_9_9_4_4_4_4_4_7_7_7_12_4_10_4_7_7_11_6_2_2_2_2_2_5_5_8_8_2_2_7_5_5_10_9_9_9_9_9_9_9_4_4_1_1_4_3_7_7_4</t>
-  </si>
-  <si>
-    <t>3_3_3_3_3_9_9_9_10_6_12_3_3_6_7_3_3_3_9_12_9_9_12_3_3_3_3_11_11_8_9_5_6_6_4_4_11_5_5_5_7_2_5_11_9_9_10_11_7_8_10_2_2_12_6_6_6_6_6_6_6_6_6_6_6_1_1_1_1_2_2_12_8_8_9_9_9_7_9_9_9_12_5_5_5_2_2_3_5_5_13_6_6_6_6_2_2_2_2_2_7_10_10_12_1_5_5_5_5_5_5_7_7_7_7_7_9_9_9_9_9_9_1_10_10_10_11_11_9_9_9_9_9_6_5_5_9_9_12_9_9_9_9_7_7_7_7_7_7_7_7_8_12_8_3_6_6_6_1_10_5_5_12_2_2_6_12_6_6_6_9_3_11_11_11_11_9_2_12_10_10_10_1_1_12_8_8_2_12_8_8_8_8_7_7_4_4_4_1_1_1_11_11_11_11_7_7_7_11_3_3_3_3_3_4_1_11_11_10_10_10_10_12_2_4_12_11_11_11_11_3_5_5_5_5_1_7_7_7_5_5_5_3_3_3_12_8_8_3_3_3_10_4_4_5_5_5_9_8_4_4_9_6_6_6_8_8_8_8_4_8_8_12_9_9_9_9_9_9_8_8_2_2_1_1_1_2_5_4_4_4_12_9_9_6_1_4_4_12_9_9_9_9_9_8_12_7_12_12_11_11_4_9_3_3_9_2_2_4_3_3_3_6_6_4_4_4_4_4_3_3_10_11_11_1_1_5_4_4_4_12_6_7_7_7_7_7_7_3_3_3_3_3_3_5_5_5_5_2_2_12_3_3_10_10_4_4_4_11_11_1_1_6_8_8_8_8_4_5_6_6_6_6_4_4_4_4_10_7_1_10_10_10_4_8_8_9_9_9_9_9_9_9_9_9_9_3_2_2_12_4_3_2_2_6_9_12_8_8_8_8_8_8_5_5_4_4_4_12_2_2_5_5_5_5_5_5_1_11_11_11_11_7_7_7_7_12_10_10_8_8_8_8_3_7_9_9_9_7_4_3_3_1_8_8_5_4_4_11_11_4_6_5_5_13_12_11_11_3_3_3_3_7_1_2_2_2_2_2_4_4_4_2_2_7_12_2_2_2_2</t>
-  </si>
-  <si>
-    <t>6_6_6_8_8_8_4_4_1_4_4_4_4_8_8_8_8_4_4_4_6_1_6_6_2_2_2_2_8_8_4_4_8_8_8_8_8_8_8_2_2_2_8_8_8_8_2_10_10_10_4_2_2_4_10_10_4_4_4_4_10_10_10_10_4_6_6_8_8_4_4_4_6_6_6_1_1_4_4_4_10_6_6_1_1_1_2_2_2_2_2_2_2_2_2_6_10_6_6_10_10_10_2_2_2_2_2_2_8_8_4_4_10_10_4_4_4_2_10_10_6_6_6_6_6_1_1_1_1_1_10_8_8_8_8_10_10_10_10_10_10_10_10_8_2_6_6_6_10_4_4_2_2_2_2_4_4_10_10_10_8_2_4_4_4_4_10_10_10_10_10_10_10_10_10_10_10_10_10_10_10_6_10_10_2_2_4_2_2_8_8_2_4_4_4_10_10_10_10_6_6_6_6_8_6_4_4_2_2_10_10_10_10_8_8_6_2_2_2_4_4_6_6_8_8_10_6_6_6_6_6_1_10_2_2_2_6_6_8_8_8_8_8_8_8_8_8_2_2_2_2_2_2_8_8_8_8_8_2_2_2_10_10_10_8_4_2_2_2_2_2_4_4_4_4_4_4_10_10_6_6_6_6_1_1_1_1_1_6_6_2_4_4_4_4_4_1_10_2_4_4_4_4_4_4_8_8_8_8_8_4_4_4_6_8_8_1_1_8_8_10_10_10_10_10_10_10_10_10_10_2_2_2_2_4_4_4_4_4_4_4_6_10_4_4_4_10_10_4_8_8_2_2_2_2_2_4_2_2_2_2_2_2_2_4_4_10_6_6_8_8_2_2_6_2_2_8_8_8_10_6_1_1_2_2_2_2_4_4_4_10_10_4_4_8_8_8_8_8_8_10_4_4_4_8_8_8_8_8_4_4_4_6_6_2_8_2_2_6_6_6_6_4_10_1_4_4_8_8_8_2_2_2_8_10_10_10_10_10_10_4_4_10_6_6_6_6_8_8_8_8_8_8_8_4_4_8_2_8_8_8_2_6_10_4_4_4_4_10_4_4_2_2_1_1_1_4_6_2_2_10_10_10_10_6_6_6_8_8_8_10_4_4_2_2_2_2_6_8_8</t>
-  </si>
-  <si>
-    <t>9_9_9_9_9_9_11_3_9_9_1_3_3_7_1_7_7_9_11_11_11_11_5_3_5_5_9_9_3_7_5_5_3_9_1_7_7_7_7_7_7_9_9_9_9_9_11_11_11_11_3_9_7_7_5_5_5_11_3_11_3_11_9_9_9_3_5_5_5_5_5_5_11_11_11_11_11_11_11_11_3_9_9_3_3_11_11_11_11_11_11_9_3_3_3_7_7_7_9_9_9_9_9_9_9_3_7_7_7_7_7_7_7_7_3_3_3_3_11_11_11_11_11_11_11_3_7_7_7_7_7_7_7_7_7_7_7_7_9_9_9_9_9_9_9_3_9_9_1_1_1_1_1_3_7_7_11_9_9_9_11_11_11_11_9_5_5_7_11_11_11_11_9_9_9_9_11_11_11_11_11_11_7_9_9_9_9_7_7_11_3_3_3_1_11_11_11_11_11_11_11_11_9_5_7_9_9_3_3_7_11_11_11_11_11_11_11_1_1_1_1_1_5_9_3_7_3_7_11_1_1_9_11_9_3_9_9_9_9_9_11_11_5_11_9_3_3_9_9_3_7_11_3_7_7_7_7_11_3_11_9_11_11_3_1_3_3_7_5_3_3_9_9_11_7_9_7_7_9_9_7_3_3_3_9_11_11_3_3_11_11_9_5_7_7_5_5_5_11_11_11_3_1_11_5_5_5_5_7_3_5_3_3_9_9_9_1_3_11_7_9_9_9_3_7_7_7_7_1_1_1_1_1_7_11_7_7_7_7_7_5_5_5_7_9_9_9_9_9_9_5_5_5_7_11_11_11_11_9_9_9_9_11_9_11_7_7_9_7_7_7_7_7_7_3_3_3_3_3_3_3_9_7_1_1_1_5_7_11_11_3_11_11_1_1_9_7_5_7_7_7_9_9_9_9_1_1_1_1_9_9_11_9_5_11_11_5_5_3_11_11_11_7_11_11_11_5_5_5_5_5_11_7_7_5_7_7_9_9_7_7_7_9_3_3_3_3_3_5_5_5_5_7_11_11_1_1_11_11_5_5_9_3_3_3_3_9_9_9_1_1_1_1_9_11_1_1_11_3_3_3_7_11_11_7_7_7_7_7_11_3_5_5_3_7_7_7_9_11_11</t>
+    <t>1_8_8_8_1_10_10_1_7_7_7_7_1_8_8_8_1_2_2_2_2_1_6_6_6_1_6_6_6_6_1_9_9_9_9_9_9_1_7_7_1_10_10_10_10_10_10_10_1_9_1_7_7_1_5_5_5_1_8_8_8_8_8_8_8_8_8_1_4_4_4_4_4_4_1_9_9_1_2_2_2_2_1_6_1_4_4_1_6_6_1_6_6_1_5_5_1_2_1_9_1_10_10_10_10_10_10_1_10_1_4_4_1_4_4_4_4_4_1_2_2_1_6_6_6_6_6_6_6_6_6_6_6_1_11_11_11_11_1_2_1_7_7_7_7_1_5_1_5_1_8_8_8_8_8_8_8_1_7_1_10_1_3_3_3_3_1_6_1_7_1_10_10_1_4_1_6_6_6_1_3_3_3_1_2_2_2_1_8_1_6_1_9_9_9_1_7_7_1_9_9_9_9_9_9_1_10_10_10_1_9_9_1_6_6_6_6_6_1_10_1_10_10_10_1_10_1_8_1_8_8_8_1_7_7_7_1_10_1_9_9_1_3_1_6_6_6_6_6_1_7_7_7_7_1_4_1_2_1_2_2_1_9_9_9_9_1_6_6_6_6_6_6_6_6_6_1_11_11_1_8_1_8_1_5_1_5_5_5_5_5_5_5_5_5_5_5_1_11_1_2_1_4_4_1_11_11_11_1_4_4_4_4_4_4_4_4_1_10_1_4_4_4_4_4_4_1_8_1_10_10_10_10_1_7_7_7_1_4_4_1_11_11_11_1_5_5_5_5_1_9_9_9_9_1_7_7_7_7_7_7_1_2_1_11_11_11_11_11_11_11_1_5_5_5_5_5_5_1_3_3_3_1_5_5_5_5_5_5_5_5_5_5_5_5_1_4_4_4_1_10_10_1_5_5_1_8_1_7_1_9_1_11_11_1_3_3_1_4_4_1_6_6_6_1_11_1_7_1_3_3_3_3_1_5_5_1_3_3_3_3_3_3_1_10_10_10_10_10_10_1_7_7_1_2_2_2_1_11_11_1_7_1_11_11_11_11_11_11_11_11_1_8_8_1_7_7_7_1_3_1_5_5_5_5_1_10_1_8_8_8_8_8_1_10_10_10_10_1_11</t>
+  </si>
+  <si>
+    <t>1_9_9_9_9_9_9_1_4_4_4_4_1_2_2_1_3_3_3_1_10_10_10_10_1_5_5_1_5_5_1_3_1_3_3_1_9_9_9_9_9_9_1_6_6_6_6_1_5_5_5_1_4_4_4_4_4_1_9_1_7_7_7_7_7_7_1_11_11_11_11_11_11_1_10_10_1_8_8_8_8_8_8_1_5_1_5_1_6_6_1_3_3_3_1_4_4_4_4_4_4_1_2_1_7_7_7_1_10_10_10_10_10_10_1_7_1_5_5_5_1_6_6_6_6_1_3_3_3_1_6_6_6_6_6_6_1_5_5_5_5_5_5_5_1_6_6_6_1_7_7_7_7_1_2_2_2_2_2_2_1_6_6_6_6_6_6_6_6_1_8_8_8_1_8_8_1_10_10_1_5_5_5_5_1_2_2_2_1_5_5_1_5_1_10_1_11_11_11_1_8_8_1_9_9_1_8_1_4_4_4_4_4_4_1_4_4_1_7_7_7_1_9_1_6_6_6_1_2_2_2_2_2_2_1_8_8_8_8_8_1_9_1_11_11_11_11_11_11_11_11_1_10_1_7_7_1_5_5_5_5_5_5_1_9_9_1_3_3_1_4_4_4_4_1_7_1_9_1_3_1_8_8_8_8_8_1_11_11_11_11_11_1_9_9_9_9_1_9_1_9_9_1_7_7_7_7_7_7_7_7_7_7_7_7_7_7_7_1_10_10_10_10_10_10_10_10_1_5_5_1_7_7_1_10_10_10_1_8_1_8_1_11_11_1_3_3_3_3_3_3_3_1_11_11_11_11_11_11_1_4_4_4_1_9_1_5_5_5_1_9_1_4_4_4_4_4_4_4_4_4_4_4_4_4_1_5_5_5_1_9_9_9_9_1_2_2_2_1_6_1_2_2_2_2_2_2_2_1_3_3_3_3_1_5_5_5_5_5_5_5_5_5_1_4_4_4_4_4_4_4_4_4_4_4_4_1_3_1_7_7_1_8_8_1_11_11_11_1_3_3_3_1_10_10_10_10_1_11_11_11_11_11_1_7_7_1_8_8_1_10_10_10_10_10_10_1_6_1_6_6_6_6_6_6_6_1_3_3_3_3_3_3_3_3_3_3_1_4_1</t>
+  </si>
+  <si>
+    <t>1_3_3_3_3_3_3_3_3_3_3_3_1_11_11_11_1_4_4_4_4_4_1_7_7_1_4_4_4_1_9_9_9_9_1_8_1_9_9_1_6_6_6_1_12_1_9_9_9_9_1_9_9_9_1_7_7_7_1_8_8_1_4_4_1_8_8_1_2_1_2_2_2_1_8_8_1_11_11_11_1_6_6_1_2_2_2_1_4_4_4_4_4_1_12_1_5_1_2_2_1_3_3_3_3_1_4_4_1_2_2_1_4_4_4_4_4_1_12_1_3_1_8_8_8_8_8_8_8_8_1_6_1_5_5_5_5_5_5_5_1_8_1_4_4_1_12_1_9_9_1_7_1_5_1_3_3_3_3_3_3_1_2_2_2_2_2_1_4_4_1_3_3_1_7_7_7_7_7_1_5_1_6_6_1_7_7_1_10_10_1_6_6_6_1_4_4_1_9_1_8_1_9_9_9_1_3_1_11_11_1_6_6_6_1_5_1_6_1_11_11_11_11_11_11_11_11_1_10_1_4_4_1_6_1_11_11_1_6_1_5_5_5_5_5_1_7_1_12_1_11_11_11_11_11_11_11_1_10_10_1_12_1_10_1_9_9_9_9_9_9_9_1_12_1_12_1_11_11_11_11_11_11_1_7_7_7_7_7_7_1_10_10_10_10_10_10_10_10_10_10_10_10_1_9_1_7_7_1_6_6_6_1_5_5_5_5_5_5_1_12_1_2_2_2_1_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_1_2_1_2_2_1_12_1_10_1_3_3_1_5_1_2_1_5_5_1_2_2_2_1_8_8_8_8_8_1_11_1_10_1_8_8_8_8_8_1_2_1_11_1_3_3_3_1_4_4_1_9_1_2_2_2_2_2_2_2_2_1_9_9_1_12_1_12_1_11_11_11_1_12_1_2_1_8_1_11_11_11_11_11_1_6_6_6_1_7_7_7_7_1_8_1_8_8_1_5_5_5_5_5_5_5_5_5_5_1_7_7_7_1_3_3_3_1_2_2_1_12_1_11_11_11_11_11_11_1_7_7_7_7_1_10_10_10_1_2_1_5_5_1_2_2_2_2_2_2_2_1_10_10_10_10_10_10_10</t>
+  </si>
+  <si>
+    <t>1_10_10_10_10_1_2_2_1_3_3_3_1_10_10_10_1_4_4_4_4_1_8_8_1_12_1_10_1_5_5_5_5_1_6_6_6_6_6_6_6_1_4_1_10_10_1_7_1_12_1_4_4_1_4_4_4_1_6_6_1_6_6_6_6_6_6_6_6_6_6_6_6_6_6_1_8_1_9_1_9_9_9_9_9_9_9_9_9_1_6_6_6_6_6_1_8_1_2_1_9_9_1_12_1_9_1_8_8_8_8_8_8_1_7_7_7_7_1_8_8_8_8_8_8_8_8_8_1_2_2_2_1_7_7_7_1_6_6_6_6_6_6_6_1_3_3_3_3_1_5_5_5_5_1_8_8_8_1_12_1_2_1_5_5_1_10_1_8_1_3_3_3_3_3_3_3_3_3_3_1_6_6_1_8_8_8_8_8_8_8_1_10_10_1_2_2_2_2_2_2_2_1_2_2_1_8_1_7_7_1_7_7_1_11_11_11_11_1_7_7_1_5_1_2_1_2_1_6_6_6_6_6_6_6_6_1_11_11_11_1_3_3_3_1_6_1_12_1_9_1_5_5_5_1_12_1_2_2_1_9_9_9_1_12_1_11_11_11_1_7_7_7_7_7_7_1_2_2_2_2_1_8_8_8_1_10_10_1_7_1_3_1_5_5_1_4_4_1_11_1_5_5_5_5_5_5_5_1_7_1_8_8_8_1_4_4_4_4_4_4_4_1_12_1_11_11_11_11_11_11_1_2_1_4_4_4_4_4_4_1_11_11_11_11_11_1_9_9_9_9_1_9_9_9_9_9_9_1_5_1_8_8_8_8_1_4_1_4_1_8_8_8_1_11_11_11_11_11_11_11_11_1_9_9_1_8_1_8_8_8_1_12_1_12_1_11_11_11_11_1_5_5_5_5_5_5_5_1_3_3_3_1_11_1_2_2_1_2_2_2_1_2_2_2_2_2_2_2_2_1_9_9_9_9_9_9_9_1_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_1_11_11_11_11_1_10_1_4_4_4_4_4_4_4_4_4_4_1_4_4_4_4_1_3_1_9_9_1_10_10_10_10_10_10_10_1_10_1_12_1_7_1_3</t>
+  </si>
+  <si>
+    <t>1_8_1_10_10_10_1_10_10_10_10_10_1_6_6_1_10_10_1_8_1_8_1_10_10_1_2_1_8_1_6_6_6_6_6_6_6_1_4_1_6_6_6_6_6_6_1_2_2_2_2_2_2_2_1_8_8_8_1_10_10_10_10_10_10_10_1_2_2_2_2_2_2_2_2_2_1_4_4_4_4_4_4_4_4_4_1_4_4_4_4_1_8_1_2_1_4_4_1_10_10_10_10_10_10_10_10_10_10_1_10_10_10_10_10_10_1_4_1_6_6_6_6_6_6_6_1_2_2_2_2_2_2_1_6_6_6_6_6_6_1_4_4_4_4_4_1_8_8_1_4_4_4_1_4_4_4_4_1_4_1_10_1_4_4_1_10_10_10_10_10_10_10_1_2_1_6_6_6_1_8_1_4_4_4_4_4_4_4_4_4_1_4_4_4_4_4_4_4_1_2_2_2_2_2_2_2_2_2_2_2_2_1_2_2_2_1_10_10_10_10_1_10_10_10_10_10_10_10_10_10_10_10_10_10_10_1_6_6_1_10_10_10_10_10_1_6_6_6_6_1_6_6_6_1_4_4_4_4_4_4_1_8_8_8_1_6_6_6_6_6_6_1_4_4_4_4_1_8_1_8_8_8_1_6_6_6_1_8_8_8_1_6_6_6_1_6_6_6_6_1_6_6_6_6_6_1_4_4_4_1_10_1_2_2_1_8_1_4_4_4_4_4_4_4_4_4_4_4_4_4_4_1_8_8_1_10_10_1_8_8_8_8_1_4_4_1_10_10_10_1_2_1_2_2_1_6_1_6_1_8_8_8_8_8_8_8_8_8_8_1_4_4_1_10_10_1_8_8_8_8_8_1_8_8_8_8_8_8_8_8_8_1_4_4_4_1_2_2_2_2_2_2_1_2_2_1_2_2_2_2_2_2_2_1_10_10_10_10_10_10_10_10_10_10_10_10_10_10_10_10_10_10_10_1_6_1_10_1_4_4_1_2_1_2_1_4_4_1_6_6_6_6_6_6_6_6_6_1_10_1_6_6_6_6_6_6_6_6_6_6_6_1_2_2_2_2_2_1_2_1_8_8_8_8_1_6_6_1_10_1_4_1_6_6_1_10_1_8_1</t>
+  </si>
+  <si>
+    <t>1_7_7_7_1_9_9_9_9_9_1_5_1_7_1_11_11_1_7_1_9_9_9_9_1_11_11_11_11_11_11_1_11_11_11_1_5_5_5_5_5_5_5_5_5_1_3_3_1_5_1_11_11_1_3_3_3_1_5_5_5_5_1_11_1_3_1_3_1_3_3_1_9_9_9_9_9_9_9_1_9_9_9_1_9_1_11_1_7_7_7_7_7_1_9_1_9_9_9_9_1_11_11_11_1_11_11_1_11_1_11_11_11_1_11_11_11_11_1_11_11_11_11_1_11_1_3_3_3_3_1_9_9_1_5_1_7_7_7_7_7_7_7_7_7_7_7_7_7_1_5_5_5_1_7_7_7_7_7_7_7_7_1_7_7_7_7_7_7_7_1_11_11_1_9_9_9_9_9_9_1_3_3_1_11_11_11_11_11_11_1_5_5_1_11_11_11_11_1_9_1_7_7_1_3_3_3_3_3_3_3_1_5_5_1_5_5_1_7_1_5_5_5_5_5_1_3_3_3_1_7_7_7_7_7_1_11_11_11_11_1_7_7_7_7_7_1_3_3_3_3_3_3_1_9_1_11_11_11_11_1_5_1_3_3_3_1_3_1_5_5_1_3_3_1_11_11_11_1_9_9_9_9_9_9_1_9_9_9_9_9_9_9_9_1_3_3_3_3_3_3_3_1_7_1_3_3_1_11_11_11_11_11_11_11_11_11_1_7_1_5_5_5_1_7_7_7_7_7_7_7_7_7_1_7_7_1_7_7_7_7_7_1_7_7_7_7_1_5_1_11_1_9_1_11_11_11_11_1_3_3_3_3_1_5_5_5_5_1_3_3_3_3_3_3_3_3_1_5_1_9_9_1_11_1_9_9_9_9_1_3_1_7_1_9_1_3_1_11_11_11_11_1_5_5_1_11_1_11_11_1_5_1_5_5_1_3_3_3_3_1_5_5_5_5_5_1_3_1_11_11_11_11_11_1_9_9_9_9_9_1_7_7_7_1_11_1_3_3_3_1_11_11_1_3_3_3_3_3_3_3_1_7_7_7_7_7_7_7_7_7_7_7_1_3_3_3_1_3_1_9_1_5_1_11_1_3_3_3_3_1_5_5_5_1_3_3_3_3_1</t>
   </si>
 </sst>
 </file>
@@ -2514,9 +2517,8 @@
       <c r="F30" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="G30" t="str">
-        <f t="shared" ref="G30:G34" si="1">G29</f>
-        <v>3_3_3_3_3_9_9_9_10_6_12_3_3_6_7_3_3_3_9_12_9_9_12_3_3_3_3_11_11_8_9_5_6_6_4_4_11_5_5_5_7_2_5_11_9_9_10_11_7_8_10_2_2_12_6_6_6_6_6_6_6_6_6_6_6_1_1_1_1_2_2_12_8_8_9_9_9_7_9_9_9_12_5_5_5_2_2_3_5_5_13_6_6_6_6_2_2_2_2_2_7_10_10_12_1_5_5_5_5_5_5_7_7_7_7_7_9_9_9_9_9_9_1_10_10_10_11_11_9_9_9_9_9_6_5_5_9_9_12_9_9_9_9_7_7_7_7_7_7_7_7_8_12_8_3_6_6_6_1_10_5_5_12_2_2_6_12_6_6_6_9_3_11_11_11_11_9_2_12_10_10_10_1_1_12_8_8_2_12_8_8_8_8_7_7_4_4_4_1_1_1_11_11_11_11_7_7_7_11_3_3_3_3_3_4_1_11_11_10_10_10_10_12_2_4_12_11_11_11_11_3_5_5_5_5_1_7_7_7_5_5_5_3_3_3_12_8_8_3_3_3_10_4_4_5_5_5_9_8_4_4_9_6_6_6_8_8_8_8_4_8_8_12_9_9_9_9_9_9_8_8_2_2_1_1_1_2_5_4_4_4_12_9_9_6_1_4_4_12_9_9_9_9_9_8_12_7_12_12_11_11_4_9_3_3_9_2_2_4_3_3_3_6_6_4_4_4_4_4_3_3_10_11_11_1_1_5_4_4_4_12_6_7_7_7_7_7_7_3_3_3_3_3_3_5_5_5_5_2_2_12_3_3_10_10_4_4_4_11_11_1_1_6_8_8_8_8_4_5_6_6_6_6_4_4_4_4_10_7_1_10_10_10_4_8_8_9_9_9_9_9_9_9_9_9_9_3_2_2_12_4_3_2_2_6_9_12_8_8_8_8_8_8_5_5_4_4_4_12_2_2_5_5_5_5_5_5_1_11_11_11_11_7_7_7_7_12_10_10_8_8_8_8_3_7_9_9_9_7_4_3_3_1_8_8_5_4_4_11_11_4_6_5_5_13_12_11_11_3_3_3_3_7_1_2_2_2_2_2_4_4_4_2_2_7_12_2_2_2_2</v>
+      <c r="G30" t="s">
+        <v>65</v>
       </c>
       <c r="H30" s="14" t="s">
         <v>36</v>
@@ -2547,9 +2549,8 @@
       <c r="F31" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="G31" t="str">
-        <f t="shared" si="1"/>
-        <v>3_3_3_3_3_9_9_9_10_6_12_3_3_6_7_3_3_3_9_12_9_9_12_3_3_3_3_11_11_8_9_5_6_6_4_4_11_5_5_5_7_2_5_11_9_9_10_11_7_8_10_2_2_12_6_6_6_6_6_6_6_6_6_6_6_1_1_1_1_2_2_12_8_8_9_9_9_7_9_9_9_12_5_5_5_2_2_3_5_5_13_6_6_6_6_2_2_2_2_2_7_10_10_12_1_5_5_5_5_5_5_7_7_7_7_7_9_9_9_9_9_9_1_10_10_10_11_11_9_9_9_9_9_6_5_5_9_9_12_9_9_9_9_7_7_7_7_7_7_7_7_8_12_8_3_6_6_6_1_10_5_5_12_2_2_6_12_6_6_6_9_3_11_11_11_11_9_2_12_10_10_10_1_1_12_8_8_2_12_8_8_8_8_7_7_4_4_4_1_1_1_11_11_11_11_7_7_7_11_3_3_3_3_3_4_1_11_11_10_10_10_10_12_2_4_12_11_11_11_11_3_5_5_5_5_1_7_7_7_5_5_5_3_3_3_12_8_8_3_3_3_10_4_4_5_5_5_9_8_4_4_9_6_6_6_8_8_8_8_4_8_8_12_9_9_9_9_9_9_8_8_2_2_1_1_1_2_5_4_4_4_12_9_9_6_1_4_4_12_9_9_9_9_9_8_12_7_12_12_11_11_4_9_3_3_9_2_2_4_3_3_3_6_6_4_4_4_4_4_3_3_10_11_11_1_1_5_4_4_4_12_6_7_7_7_7_7_7_3_3_3_3_3_3_5_5_5_5_2_2_12_3_3_10_10_4_4_4_11_11_1_1_6_8_8_8_8_4_5_6_6_6_6_4_4_4_4_10_7_1_10_10_10_4_8_8_9_9_9_9_9_9_9_9_9_9_3_2_2_12_4_3_2_2_6_9_12_8_8_8_8_8_8_5_5_4_4_4_12_2_2_5_5_5_5_5_5_1_11_11_11_11_7_7_7_7_12_10_10_8_8_8_8_3_7_9_9_9_7_4_3_3_1_8_8_5_4_4_11_11_4_6_5_5_13_12_11_11_3_3_3_3_7_1_2_2_2_2_2_4_4_4_2_2_7_12_2_2_2_2</v>
+      <c r="G31" t="s">
+        <v>66</v>
       </c>
       <c r="H31" s="14" t="s">
         <v>36</v>
@@ -2580,8 +2581,8 @@
         <v>36</v>
       </c>
       <c r="G32" t="str">
-        <f t="shared" si="1"/>
-        <v>3_3_3_3_3_9_9_9_10_6_12_3_3_6_7_3_3_3_9_12_9_9_12_3_3_3_3_11_11_8_9_5_6_6_4_4_11_5_5_5_7_2_5_11_9_9_10_11_7_8_10_2_2_12_6_6_6_6_6_6_6_6_6_6_6_1_1_1_1_2_2_12_8_8_9_9_9_7_9_9_9_12_5_5_5_2_2_3_5_5_13_6_6_6_6_2_2_2_2_2_7_10_10_12_1_5_5_5_5_5_5_7_7_7_7_7_9_9_9_9_9_9_1_10_10_10_11_11_9_9_9_9_9_6_5_5_9_9_12_9_9_9_9_7_7_7_7_7_7_7_7_8_12_8_3_6_6_6_1_10_5_5_12_2_2_6_12_6_6_6_9_3_11_11_11_11_9_2_12_10_10_10_1_1_12_8_8_2_12_8_8_8_8_7_7_4_4_4_1_1_1_11_11_11_11_7_7_7_11_3_3_3_3_3_4_1_11_11_10_10_10_10_12_2_4_12_11_11_11_11_3_5_5_5_5_1_7_7_7_5_5_5_3_3_3_12_8_8_3_3_3_10_4_4_5_5_5_9_8_4_4_9_6_6_6_8_8_8_8_4_8_8_12_9_9_9_9_9_9_8_8_2_2_1_1_1_2_5_4_4_4_12_9_9_6_1_4_4_12_9_9_9_9_9_8_12_7_12_12_11_11_4_9_3_3_9_2_2_4_3_3_3_6_6_4_4_4_4_4_3_3_10_11_11_1_1_5_4_4_4_12_6_7_7_7_7_7_7_3_3_3_3_3_3_5_5_5_5_2_2_12_3_3_10_10_4_4_4_11_11_1_1_6_8_8_8_8_4_5_6_6_6_6_4_4_4_4_10_7_1_10_10_10_4_8_8_9_9_9_9_9_9_9_9_9_9_3_2_2_12_4_3_2_2_6_9_12_8_8_8_8_8_8_5_5_4_4_4_12_2_2_5_5_5_5_5_5_1_11_11_11_11_7_7_7_7_12_10_10_8_8_8_8_3_7_9_9_9_7_4_3_3_1_8_8_5_4_4_11_11_4_6_5_5_13_12_11_11_3_3_3_3_7_1_2_2_2_2_2_4_4_4_2_2_7_12_2_2_2_2</v>
+        <f t="shared" ref="G30:G34" si="1">G31</f>
+        <v>1_10_10_10_10_1_2_2_1_3_3_3_1_10_10_10_1_4_4_4_4_1_8_8_1_12_1_10_1_5_5_5_5_1_6_6_6_6_6_6_6_1_4_1_10_10_1_7_1_12_1_4_4_1_4_4_4_1_6_6_1_6_6_6_6_6_6_6_6_6_6_6_6_6_6_1_8_1_9_1_9_9_9_9_9_9_9_9_9_1_6_6_6_6_6_1_8_1_2_1_9_9_1_12_1_9_1_8_8_8_8_8_8_1_7_7_7_7_1_8_8_8_8_8_8_8_8_8_1_2_2_2_1_7_7_7_1_6_6_6_6_6_6_6_1_3_3_3_3_1_5_5_5_5_1_8_8_8_1_12_1_2_1_5_5_1_10_1_8_1_3_3_3_3_3_3_3_3_3_3_1_6_6_1_8_8_8_8_8_8_8_1_10_10_1_2_2_2_2_2_2_2_1_2_2_1_8_1_7_7_1_7_7_1_11_11_11_11_1_7_7_1_5_1_2_1_2_1_6_6_6_6_6_6_6_6_1_11_11_11_1_3_3_3_1_6_1_12_1_9_1_5_5_5_1_12_1_2_2_1_9_9_9_1_12_1_11_11_11_1_7_7_7_7_7_7_1_2_2_2_2_1_8_8_8_1_10_10_1_7_1_3_1_5_5_1_4_4_1_11_1_5_5_5_5_5_5_5_1_7_1_8_8_8_1_4_4_4_4_4_4_4_1_12_1_11_11_11_11_11_11_1_2_1_4_4_4_4_4_4_1_11_11_11_11_11_1_9_9_9_9_1_9_9_9_9_9_9_1_5_1_8_8_8_8_1_4_1_4_1_8_8_8_1_11_11_11_11_11_11_11_11_1_9_9_1_8_1_8_8_8_1_12_1_12_1_11_11_11_11_1_5_5_5_5_5_5_5_1_3_3_3_1_11_1_2_2_1_2_2_2_1_2_2_2_2_2_2_2_2_1_9_9_9_9_9_9_9_1_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_1_11_11_11_11_1_10_1_4_4_4_4_4_4_4_4_4_4_1_4_4_4_4_1_3_1_9_9_1_10_10_10_10_10_10_10_1_10_1_12_1_7_1_3</v>
       </c>
       <c r="H32" s="14" t="s">
         <v>36</v>
@@ -2613,7 +2614,7 @@
       </c>
       <c r="G33" t="str">
         <f t="shared" si="1"/>
-        <v>3_3_3_3_3_9_9_9_10_6_12_3_3_6_7_3_3_3_9_12_9_9_12_3_3_3_3_11_11_8_9_5_6_6_4_4_11_5_5_5_7_2_5_11_9_9_10_11_7_8_10_2_2_12_6_6_6_6_6_6_6_6_6_6_6_1_1_1_1_2_2_12_8_8_9_9_9_7_9_9_9_12_5_5_5_2_2_3_5_5_13_6_6_6_6_2_2_2_2_2_7_10_10_12_1_5_5_5_5_5_5_7_7_7_7_7_9_9_9_9_9_9_1_10_10_10_11_11_9_9_9_9_9_6_5_5_9_9_12_9_9_9_9_7_7_7_7_7_7_7_7_8_12_8_3_6_6_6_1_10_5_5_12_2_2_6_12_6_6_6_9_3_11_11_11_11_9_2_12_10_10_10_1_1_12_8_8_2_12_8_8_8_8_7_7_4_4_4_1_1_1_11_11_11_11_7_7_7_11_3_3_3_3_3_4_1_11_11_10_10_10_10_12_2_4_12_11_11_11_11_3_5_5_5_5_1_7_7_7_5_5_5_3_3_3_12_8_8_3_3_3_10_4_4_5_5_5_9_8_4_4_9_6_6_6_8_8_8_8_4_8_8_12_9_9_9_9_9_9_8_8_2_2_1_1_1_2_5_4_4_4_12_9_9_6_1_4_4_12_9_9_9_9_9_8_12_7_12_12_11_11_4_9_3_3_9_2_2_4_3_3_3_6_6_4_4_4_4_4_3_3_10_11_11_1_1_5_4_4_4_12_6_7_7_7_7_7_7_3_3_3_3_3_3_5_5_5_5_2_2_12_3_3_10_10_4_4_4_11_11_1_1_6_8_8_8_8_4_5_6_6_6_6_4_4_4_4_10_7_1_10_10_10_4_8_8_9_9_9_9_9_9_9_9_9_9_3_2_2_12_4_3_2_2_6_9_12_8_8_8_8_8_8_5_5_4_4_4_12_2_2_5_5_5_5_5_5_1_11_11_11_11_7_7_7_7_12_10_10_8_8_8_8_3_7_9_9_9_7_4_3_3_1_8_8_5_4_4_11_11_4_6_5_5_13_12_11_11_3_3_3_3_7_1_2_2_2_2_2_4_4_4_2_2_7_12_2_2_2_2</v>
+        <v>1_10_10_10_10_1_2_2_1_3_3_3_1_10_10_10_1_4_4_4_4_1_8_8_1_12_1_10_1_5_5_5_5_1_6_6_6_6_6_6_6_1_4_1_10_10_1_7_1_12_1_4_4_1_4_4_4_1_6_6_1_6_6_6_6_6_6_6_6_6_6_6_6_6_6_1_8_1_9_1_9_9_9_9_9_9_9_9_9_1_6_6_6_6_6_1_8_1_2_1_9_9_1_12_1_9_1_8_8_8_8_8_8_1_7_7_7_7_1_8_8_8_8_8_8_8_8_8_1_2_2_2_1_7_7_7_1_6_6_6_6_6_6_6_1_3_3_3_3_1_5_5_5_5_1_8_8_8_1_12_1_2_1_5_5_1_10_1_8_1_3_3_3_3_3_3_3_3_3_3_1_6_6_1_8_8_8_8_8_8_8_1_10_10_1_2_2_2_2_2_2_2_1_2_2_1_8_1_7_7_1_7_7_1_11_11_11_11_1_7_7_1_5_1_2_1_2_1_6_6_6_6_6_6_6_6_1_11_11_11_1_3_3_3_1_6_1_12_1_9_1_5_5_5_1_12_1_2_2_1_9_9_9_1_12_1_11_11_11_1_7_7_7_7_7_7_1_2_2_2_2_1_8_8_8_1_10_10_1_7_1_3_1_5_5_1_4_4_1_11_1_5_5_5_5_5_5_5_1_7_1_8_8_8_1_4_4_4_4_4_4_4_1_12_1_11_11_11_11_11_11_1_2_1_4_4_4_4_4_4_1_11_11_11_11_11_1_9_9_9_9_1_9_9_9_9_9_9_1_5_1_8_8_8_8_1_4_1_4_1_8_8_8_1_11_11_11_11_11_11_11_11_1_9_9_1_8_1_8_8_8_1_12_1_12_1_11_11_11_11_1_5_5_5_5_5_5_5_1_3_3_3_1_11_1_2_2_1_2_2_2_1_2_2_2_2_2_2_2_2_1_9_9_9_9_9_9_9_1_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_1_11_11_11_11_1_10_1_4_4_4_4_4_4_4_4_4_4_1_4_4_4_4_1_3_1_9_9_1_10_10_10_10_10_10_10_1_10_1_12_1_7_1_3</v>
       </c>
       <c r="H33" s="14" t="s">
         <v>36</v>
@@ -2645,7 +2646,7 @@
       </c>
       <c r="G34" t="str">
         <f t="shared" si="1"/>
-        <v>3_3_3_3_3_9_9_9_10_6_12_3_3_6_7_3_3_3_9_12_9_9_12_3_3_3_3_11_11_8_9_5_6_6_4_4_11_5_5_5_7_2_5_11_9_9_10_11_7_8_10_2_2_12_6_6_6_6_6_6_6_6_6_6_6_1_1_1_1_2_2_12_8_8_9_9_9_7_9_9_9_12_5_5_5_2_2_3_5_5_13_6_6_6_6_2_2_2_2_2_7_10_10_12_1_5_5_5_5_5_5_7_7_7_7_7_9_9_9_9_9_9_1_10_10_10_11_11_9_9_9_9_9_6_5_5_9_9_12_9_9_9_9_7_7_7_7_7_7_7_7_8_12_8_3_6_6_6_1_10_5_5_12_2_2_6_12_6_6_6_9_3_11_11_11_11_9_2_12_10_10_10_1_1_12_8_8_2_12_8_8_8_8_7_7_4_4_4_1_1_1_11_11_11_11_7_7_7_11_3_3_3_3_3_4_1_11_11_10_10_10_10_12_2_4_12_11_11_11_11_3_5_5_5_5_1_7_7_7_5_5_5_3_3_3_12_8_8_3_3_3_10_4_4_5_5_5_9_8_4_4_9_6_6_6_8_8_8_8_4_8_8_12_9_9_9_9_9_9_8_8_2_2_1_1_1_2_5_4_4_4_12_9_9_6_1_4_4_12_9_9_9_9_9_8_12_7_12_12_11_11_4_9_3_3_9_2_2_4_3_3_3_6_6_4_4_4_4_4_3_3_10_11_11_1_1_5_4_4_4_12_6_7_7_7_7_7_7_3_3_3_3_3_3_5_5_5_5_2_2_12_3_3_10_10_4_4_4_11_11_1_1_6_8_8_8_8_4_5_6_6_6_6_4_4_4_4_10_7_1_10_10_10_4_8_8_9_9_9_9_9_9_9_9_9_9_3_2_2_12_4_3_2_2_6_9_12_8_8_8_8_8_8_5_5_4_4_4_12_2_2_5_5_5_5_5_5_1_11_11_11_11_7_7_7_7_12_10_10_8_8_8_8_3_7_9_9_9_7_4_3_3_1_8_8_5_4_4_11_11_4_6_5_5_13_12_11_11_3_3_3_3_7_1_2_2_2_2_2_4_4_4_2_2_7_12_2_2_2_2</v>
+        <v>1_10_10_10_10_1_2_2_1_3_3_3_1_10_10_10_1_4_4_4_4_1_8_8_1_12_1_10_1_5_5_5_5_1_6_6_6_6_6_6_6_1_4_1_10_10_1_7_1_12_1_4_4_1_4_4_4_1_6_6_1_6_6_6_6_6_6_6_6_6_6_6_6_6_6_1_8_1_9_1_9_9_9_9_9_9_9_9_9_1_6_6_6_6_6_1_8_1_2_1_9_9_1_12_1_9_1_8_8_8_8_8_8_1_7_7_7_7_1_8_8_8_8_8_8_8_8_8_1_2_2_2_1_7_7_7_1_6_6_6_6_6_6_6_1_3_3_3_3_1_5_5_5_5_1_8_8_8_1_12_1_2_1_5_5_1_10_1_8_1_3_3_3_3_3_3_3_3_3_3_1_6_6_1_8_8_8_8_8_8_8_1_10_10_1_2_2_2_2_2_2_2_1_2_2_1_8_1_7_7_1_7_7_1_11_11_11_11_1_7_7_1_5_1_2_1_2_1_6_6_6_6_6_6_6_6_1_11_11_11_1_3_3_3_1_6_1_12_1_9_1_5_5_5_1_12_1_2_2_1_9_9_9_1_12_1_11_11_11_1_7_7_7_7_7_7_1_2_2_2_2_1_8_8_8_1_10_10_1_7_1_3_1_5_5_1_4_4_1_11_1_5_5_5_5_5_5_5_1_7_1_8_8_8_1_4_4_4_4_4_4_4_1_12_1_11_11_11_11_11_11_1_2_1_4_4_4_4_4_4_1_11_11_11_11_11_1_9_9_9_9_1_9_9_9_9_9_9_1_5_1_8_8_8_8_1_4_1_4_1_8_8_8_1_11_11_11_11_11_11_11_11_1_9_9_1_8_1_8_8_8_1_12_1_12_1_11_11_11_11_1_5_5_5_5_5_5_5_1_3_3_3_1_11_1_2_2_1_2_2_2_1_2_2_2_2_2_2_2_2_1_9_9_9_9_9_9_9_1_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_1_11_11_11_11_1_10_1_4_4_4_4_4_4_4_4_4_4_1_4_4_4_4_1_3_1_9_9_1_10_10_10_10_10_10_10_1_10_1_12_1_7_1_3</v>
       </c>
       <c r="H34" s="14" t="s">
         <v>36</v>
@@ -2677,7 +2678,7 @@
         <v>36</v>
       </c>
       <c r="G35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H35" s="14" t="s">
         <v>36</v>
@@ -2709,7 +2710,7 @@
         <v>36</v>
       </c>
       <c r="G36" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H36" s="14" t="s">
         <v>36</v>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -267,7 +267,7 @@
     <t>1_10_10_1_2_1_2_1_7_7_7_7_7_1_11_11_11_1_4_1_9_9_9_1_10_1_9_9_9_9_1_8_8_1_5_1_11_11_11_11_11_11_1_11_11_11_11_11_11_11_11_11_11_11_11_11_11_11_11_11_11_11_1_3_3_1_9_1_5_1_11_11_11_1_11_1_3_3_3_3_3_1_5_5_5_5_5_5_1_11_1_4_1_7_7_7_1_10_10_10_1_7_7_7_7_1_6_1_4_4_1_4_4_4_4_4_4_1_10_10_1_9_9_1_7_7_7_7_7_1_3_1_3_3_3_1_9_9_9_9_9_1_8_8_8_8_1_2_2_2_2_1_9_1_8_1_8_1_7_7_7_7_7_7_7_7_7_1_11_11_11_11_1_5_5_5_5_5_5_5_5_1_11_11_11_1_7_7_7_7_1_3_3_3_3_3_3_1_4_4_4_4_1_3_3_3_3_1_8_1_9_9_9_9_9_9_9_9_9_9_9_1_11_1_7_1_2_2_1_6_6_1_6_6_1_4_1_3_3_1_10_10_1_6_1_7_1_6_6_6_1_7_1_3_3_3_3_1_10_1_8_8_8_8_1_2_1_4_4_1_8_8_1_6_6_6_6_6_1_4_4_1_6_6_1_4_4_1_10_10_10_10_10_10_10_10_10_10_10_10_1_10_10_10_10_10_10_1_3_3_1_11_11_1_8_1_5_5_5_1_6_6_1_4_4_1_8_1_3_3_1_11_1_11_11_1_9_9_1_4_4_4_4_4_1_6_6_6_1_10_10_10_10_10_1_7_1_5_5_1_6_1_6_6_1_8_8_8_8_8_1_4_4_4_4_1_5_5_5_5_1_11_11_1_2_2_2_2_2_2_2_2_2_1_10_10_10_1_2_1_4_1_2_2_1_3_3_3_3_1_11_11_1_8_8_8_1_9_9_9_9_1_3_3_1_4_4_4_4_4_4_1_5_5_5_5_5_5_5_5_1_3_3_1_2_2_2_2_2_2_2_1_6_6_6_1_5_1_9_9_9_9_1_6_1_10_10_10_10_10_1_10_1_3_3_3_3_3_3_3_3_3_3_3_3_3_1_2_2_2_1_10_1_3_1_6_1_11_1_9</t>
   </si>
   <si>
-    <t>11_3_5_4_7_9_10_5_3_11_7_7_2_5_8_6_4_7_6_9_4_10_9_5_3_9_3_10_4_3_1_1_1_3_8_3_4_1_1_10_2_6_5_4_2_3_4_4_2_3_2_1_11_1_11_7_1_4_9_1_3_4_1_2_1_9_9_1_1_2_2_1_7_10_5_2_5_2_3_3_1_10_4_1_7_1_1_4_2_6_3_7_8_5_1_2_3_2_11_1_4_3_1_6_4_5_6_1_3_6_2_2_6_10_5_9_4_1_6_6_5_6_10_6_1_8_3_8_2_2_1_1_2_1_5_3_1_8_4_4_9_2_1_2_4_1_8_6_3_5_1_4_8_6_7_6_1_4_4_5_3_8_2_2_6_1_2_4_1_10_4_1_3_3_1_6_1_4_11_5_1_5_1_4_2_9_1_2_2_2_9_5_3_3_3_7_7_2_9_8_5_3_4_4_2_3_1_2_4_1_2_4_3_2_2_8_9_7_4_6_9_1_1_3_1_2_2_2_9_8_1_5_1_1_3_4_7_9_3_7_7_3_3_2_6_6_4_1_1_5_4_3_4_2_4_10_1_6_3_7_5_10_1_7_1_5_5_3_6_5_7_2_3_3_1_5_5_3_4_3_3_3_4_3_1_4_3_5_8_5_9_1_4_3_3_1_3_1_2_8</t>
+    <t>1_3_3_1_6_6_6_6_1_7_1_11_11_11_1_8_8_8_1_4_4_4_4_4_4_1_3_3_3_1_11_1_11_11_1_10_10_1_5_5_1_4_4_4_1_11_11_1_2_2_2_2_1_2_1_3_1_5_5_5_5_1_9_9_9_9_1_2_1_4_4_1_8_8_1_7_7_7_7_7_7_7_7_7_7_7_1_11_11_1_6_6_6_6_6_1_3_3_3_1_11_11_11_11_11_11_11_1_6_6_1_9_9_9_9_9_1_9_9_9_9_9_9_9_9_9_1_9_1_2_2_1_7_7_7_7_7_7_1_3_3_1_3_3_3_3_3_3_3_1_4_4_1_4_4_4_4_4_4_4_4_4_4_4_1_7_7_7_7_7_1_8_8_8_8_8_1_4_1_10_10_10_1_11_1_5_5_5_5_5_1_13_1_13_1_7_1_4_4_1_4_4_1_4_4_1_2_2_2_1_5_1_8_8_1_13_1_12_12_1_10_10_1_8_8_1_4_4_1_6_6_6_6_1_6_6_6_6_6_1_2_1_6_6_6_6_6_6_6_6_6_1_6_6_6_6_6_1_12_1_11_11_11_11_1_6_6_6_6_6_6_6_6_1_13_1_8_8_8_8_1_3_3_1_6_1_8_8_1_10_10_10_1_6_1_5_1_11_11_1_12_1_4_4_4_4_4_1_13_1_2_1_11_1_6_6_6_6_6_1_12_12_12_1_11_11_11_11_1_3_1_10_10_10_1_10_10_10_10_10_1_2_2_1_12_12_1_11_11_11_1_9_1_10_10_10_10_10_10_10_10_10_10_10_10_1_12_1_3_1_2_1_12_1_11_1_10_1_13_1_9_9_1_12_1_10_10_10_10_10_10_10_1_12_1_7_7_7_7_1_11_11_1_8_8_8_1_9_9_1_5_5_1_10_10_10_1_6_6_6_1_2_1_3_3_3_3_3_3_3_3_3_1_8_8_1_2_1_9_1_4_4_4_1_2_1_7_7_7_7_7_7_7_7_7_1_9_1_7_1_2_1_5_1_13_1_9_1_3_3_3_1_3_1_6_1_7_1_2_2_2_2_2_2_1_5_1_5_5_5_5_5_5_1_12_12_12_12_1_13</t>
   </si>
   <si>
     <t>1_8_8_8_1_10_10_1_7_7_7_7_1_8_8_8_1_2_2_2_2_1_6_6_6_1_6_6_6_6_1_9_9_9_9_9_9_1_7_7_1_10_10_10_10_10_10_10_1_9_1_7_7_1_5_5_5_1_8_8_8_8_8_8_8_8_8_1_4_4_4_4_4_4_1_9_9_1_2_2_2_2_1_6_1_4_4_1_6_6_1_6_6_1_5_5_1_2_1_9_1_10_10_10_10_10_10_1_10_1_4_4_1_4_4_4_4_4_1_2_2_1_6_6_6_6_6_6_6_6_6_6_6_1_11_11_11_11_1_2_1_7_7_7_7_1_5_1_5_1_8_8_8_8_8_8_8_1_7_1_10_1_3_3_3_3_1_6_1_7_1_10_10_1_4_1_6_6_6_1_3_3_3_1_2_2_2_1_8_1_6_1_9_9_9_1_7_7_1_9_9_9_9_9_9_1_10_10_10_1_9_9_1_6_6_6_6_6_1_10_1_10_10_10_1_10_1_8_1_8_8_8_1_7_7_7_1_10_1_9_9_1_3_1_6_6_6_6_6_1_7_7_7_7_1_4_1_2_1_2_2_1_9_9_9_9_1_6_6_6_6_6_6_6_6_6_1_11_11_1_8_1_8_1_5_1_5_5_5_5_5_5_5_5_5_5_5_1_11_1_2_1_4_4_1_11_11_11_1_4_4_4_4_4_4_4_4_1_10_1_4_4_4_4_4_4_1_8_1_10_10_10_10_1_7_7_7_1_4_4_1_11_11_11_1_5_5_5_5_1_9_9_9_9_1_7_7_7_7_7_7_1_2_1_11_11_11_11_11_11_11_1_5_5_5_5_5_5_1_3_3_3_1_5_5_5_5_5_5_5_5_5_5_5_5_1_4_4_4_1_10_10_1_5_5_1_8_1_7_1_9_1_11_11_1_3_3_1_4_4_1_6_6_6_1_11_1_7_1_3_3_3_3_1_5_5_1_3_3_3_3_3_3_1_10_10_10_10_10_10_1_7_7_1_2_2_2_1_11_11_1_7_1_11_11_11_11_11_11_11_11_1_8_8_1_7_7_7_1_3_1_5_5_5_5_1_10_1_8_8_8_8_8_1_10_10_10_10_1_11</t>
@@ -276,7 +276,7 @@
     <t>1_9_9_9_9_9_9_1_4_4_4_4_1_2_2_1_3_3_3_1_10_10_10_10_1_5_5_1_5_5_1_3_1_3_3_1_9_9_9_9_9_9_1_6_6_6_6_1_5_5_5_1_4_4_4_4_4_1_9_1_7_7_7_7_7_7_1_11_11_11_11_11_11_1_10_10_1_8_8_8_8_8_8_1_5_1_5_1_6_6_1_3_3_3_1_4_4_4_4_4_4_1_2_1_7_7_7_1_10_10_10_10_10_10_1_7_1_5_5_5_1_6_6_6_6_1_3_3_3_1_6_6_6_6_6_6_1_5_5_5_5_5_5_5_1_6_6_6_1_7_7_7_7_1_2_2_2_2_2_2_1_6_6_6_6_6_6_6_6_1_8_8_8_1_8_8_1_10_10_1_5_5_5_5_1_2_2_2_1_5_5_1_5_1_10_1_11_11_11_1_8_8_1_9_9_1_8_1_4_4_4_4_4_4_1_4_4_1_7_7_7_1_9_1_6_6_6_1_2_2_2_2_2_2_1_8_8_8_8_8_1_9_1_11_11_11_11_11_11_11_11_1_10_1_7_7_1_5_5_5_5_5_5_1_9_9_1_3_3_1_4_4_4_4_1_7_1_9_1_3_1_8_8_8_8_8_1_11_11_11_11_11_1_9_9_9_9_1_9_1_9_9_1_7_7_7_7_7_7_7_7_7_7_7_7_7_7_7_1_10_10_10_10_10_10_10_10_1_5_5_1_7_7_1_10_10_10_1_8_1_8_1_11_11_1_3_3_3_3_3_3_3_1_11_11_11_11_11_11_1_4_4_4_1_9_1_5_5_5_1_9_1_4_4_4_4_4_4_4_4_4_4_4_4_4_1_5_5_5_1_9_9_9_9_1_2_2_2_1_6_1_2_2_2_2_2_2_2_1_3_3_3_3_1_5_5_5_5_5_5_5_5_5_1_4_4_4_4_4_4_4_4_4_4_4_4_1_3_1_7_7_1_8_8_1_11_11_11_1_3_3_3_1_10_10_10_10_1_11_11_11_11_11_1_7_7_1_8_8_1_10_10_10_10_10_10_1_6_1_6_6_6_6_6_6_6_1_3_3_3_3_3_3_3_3_3_3_1_4_1</t>
   </si>
   <si>
-    <t>1_3_3_3_3_3_3_3_3_3_3_3_1_11_11_11_1_4_4_4_4_4_1_7_7_1_4_4_4_1_9_9_9_9_1_8_1_9_9_1_6_6_6_1_12_1_9_9_9_9_1_9_9_9_1_7_7_7_1_8_8_1_4_4_1_8_8_1_2_1_2_2_2_1_8_8_1_11_11_11_1_6_6_1_2_2_2_1_4_4_4_4_4_1_12_1_5_1_2_2_1_3_3_3_3_1_4_4_1_2_2_1_4_4_4_4_4_1_12_1_3_1_8_8_8_8_8_8_8_8_1_6_1_5_5_5_5_5_5_5_1_8_1_4_4_1_12_1_9_9_1_7_1_5_1_3_3_3_3_3_3_1_2_2_2_2_2_1_4_4_1_3_3_1_7_7_7_7_7_1_5_1_6_6_1_7_7_1_10_10_1_6_6_6_1_4_4_1_9_1_8_1_9_9_9_1_3_1_11_11_1_6_6_6_1_5_1_6_1_11_11_11_11_11_11_11_11_1_10_1_4_4_1_6_1_11_11_1_6_1_5_5_5_5_5_1_7_1_12_1_11_11_11_11_11_11_11_1_10_10_1_12_1_10_1_9_9_9_9_9_9_9_1_12_1_12_1_11_11_11_11_11_11_1_7_7_7_7_7_7_1_10_10_10_10_10_10_10_10_10_10_10_10_1_9_1_7_7_1_6_6_6_1_5_5_5_5_5_5_1_12_1_2_2_2_1_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_1_2_1_2_2_1_12_1_10_1_3_3_1_5_1_2_1_5_5_1_2_2_2_1_8_8_8_8_8_1_11_1_10_1_8_8_8_8_8_1_2_1_11_1_3_3_3_1_4_4_1_9_1_2_2_2_2_2_2_2_2_1_9_9_1_12_1_12_1_11_11_11_1_12_1_2_1_8_1_11_11_11_11_11_1_6_6_6_1_7_7_7_7_1_8_1_8_8_1_5_5_5_5_5_5_5_5_5_5_1_7_7_7_1_3_3_3_1_2_2_1_12_1_11_11_11_11_11_11_1_7_7_7_7_1_10_10_10_1_2_1_5_5_1_2_2_2_2_2_2_2_1_10_10_10_10_10_10_10</t>
+    <t>1_3_3_1_6_6_6_6_1_7_1_11_11_11_1_8_8_8_1_4_4_4_4_4_4_1_3_3_3_1_11_1_11_11_1_10_10_1_5_5_1_4_4_4_1_11_11_1_2_2_2_2_1_2_1_3_1_5_5_5_5_1_9_9_9_9_1_2_1_4_4_1_8_8_1_7_7_7_7_7_7_7_7_7_7_7_1_11_11_1_6_6_6_6_6_1_3_3_3_1_11_11_11_11_11_11_11_1_6_6_1_9_9_9_9_9_1_9_9_9_9_9_9_9_9_9_1_9_1_2_2_1_7_7_7_7_7_7_1_3_3_1_3_3_3_3_3_3_3_1_4_4_1_4_4_4_4_4_4_4_4_4_4_4_1_7_7_7_7_7_1_8_8_8_8_8_1_4_1_10_10_10_1_11_1_5_5_5_5_5_1_13_1_12_1_7_1_4_4_1_4_4_1_4_4_1_2_2_2_1_5_1_8_8_1_13_1_12_12_1_10_10_1_8_8_1_4_4_1_6_6_6_6_1_6_6_6_6_6_1_2_1_6_6_6_6_6_6_6_6_6_1_6_6_6_6_6_1_12_1_11_11_11_11_1_6_6_6_6_6_6_6_6_1_13_1_8_8_8_8_1_3_3_1_6_1_8_8_1_10_10_10_1_6_1_5_1_11_11_1_12_1_4_4_4_4_4_1_13_1_2_1_11_1_6_6_6_6_6_1_12_12_12_1_11_11_11_11_1_3_1_10_10_10_1_10_10_10_10_10_1_2_2_1_12_12_1_11_11_11_1_9_1_10_10_10_10_10_10_10_10_10_10_10_10_1_12_1_3_1_2_1_12_1_11_1_10_1_13_1_9_9_1_12_1_10_10_10_10_10_10_10_1_12_1_7_7_7_7_1_11_11_1_8_8_8_1_9_9_1_5_5_1_10_10_10_1_6_6_6_1_2_1_3_3_3_3_3_3_3_3_3_1_8_8_1_2_1_9_1_4_4_4_1_2_1_7_7_7_7_7_7_7_7_7_1_9_1_7_1_2_1_5_1_13_1_9_1_3_3_3_1_3_1_6_1_7_1_2_2_2_2_2_2_1_5_1_5_5_5_5_5_5_1_12_12_12_12_1_13</t>
   </si>
   <si>
     <t>1_10_10_10_10_1_2_2_1_3_3_3_1_10_10_10_1_4_4_4_4_1_8_8_1_12_1_10_1_5_5_5_5_1_6_6_6_6_6_6_6_1_4_1_10_10_1_7_1_12_1_4_4_1_4_4_4_1_6_6_1_6_6_6_6_6_6_6_6_6_6_6_6_6_6_1_8_1_9_1_9_9_9_9_9_9_9_9_9_1_6_6_6_6_6_1_8_1_2_1_9_9_1_12_1_9_1_8_8_8_8_8_8_1_7_7_7_7_1_8_8_8_8_8_8_8_8_8_1_2_2_2_1_7_7_7_1_6_6_6_6_6_6_6_1_3_3_3_3_1_5_5_5_5_1_8_8_8_1_12_1_2_1_5_5_1_10_1_8_1_3_3_3_3_3_3_3_3_3_3_1_6_6_1_8_8_8_8_8_8_8_1_10_10_1_2_2_2_2_2_2_2_1_2_2_1_8_1_7_7_1_7_7_1_11_11_11_11_1_7_7_1_5_1_2_1_2_1_6_6_6_6_6_6_6_6_1_11_11_11_1_3_3_3_1_6_1_12_1_9_1_5_5_5_1_12_1_2_2_1_9_9_9_1_12_1_11_11_11_1_7_7_7_7_7_7_1_2_2_2_2_1_8_8_8_1_10_10_1_7_1_3_1_5_5_1_4_4_1_11_1_5_5_5_5_5_5_5_1_7_1_8_8_8_1_4_4_4_4_4_4_4_1_12_1_11_11_11_11_11_11_1_2_1_4_4_4_4_4_4_1_11_11_11_11_11_1_9_9_9_9_1_9_9_9_9_9_9_1_5_1_8_8_8_8_1_4_1_4_1_8_8_8_1_11_11_11_11_11_11_11_11_1_9_9_1_8_1_8_8_8_1_12_1_12_1_11_11_11_11_1_5_5_5_5_5_5_5_1_3_3_3_1_11_1_2_2_1_2_2_2_1_2_2_2_2_2_2_2_2_1_9_9_9_9_9_9_9_1_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_1_11_11_11_11_1_10_1_4_4_4_4_4_4_4_4_4_4_1_4_4_4_4_1_3_1_9_9_1_10_10_10_10_10_10_10_1_10_1_12_1_7_1_3</t>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="78">
   <si>
     <t>id</t>
   </si>
@@ -216,19 +216,46 @@
     <t>1_1_1_1</t>
   </si>
   <si>
-    <t>8_2_4_3_5_7_7_4_2_8_6_5_1_4_6_4_2_5_4_7_2_7_7_4_2_7_2_8_3_2_1_1_1_2_6_2_3_1_1_8_1_4_4_2_1_2_3_2_2_2_2_1_8_1_8_5_1_3_7_1_2_3_1_1_1_7_7_1_1_1_1_1_6_7_4_1_4_1_2_2_1_7_3_1_5_1_1_3_1_4_2_5_6_4_1_1_2_1_8_1_3_2_1_4_3_4_4_1_2_4_2_2_4_7_4_7_3_1_4_4_4_4_7_5_1_6_2_6_2_1_1_1_2_1_4_2_1_6_2_3_7_2_1_1_3_1_6_5_2_3_1_3_6_4_5_5_1_3_3_4_2_6_1_2_4_1_1_3_1_8_3_1_2_2_1_4_1_2_8_4_1_4_1_2_2_7_1_1_2_1_7_4_2_2_2_6_5_2_7_6_4_2_2_3_1_2_1_1_3_1_2_3_2_1_1_6_7_5_3_4_7_1_1_2_1_1_1_2_7_6_1_4_1_1_2_2_5_7_2_5_6_2_2_1_4_5_3_1_1_4_3_2_2_1_3_8_1_4_2_5_4_8_1_5_1_4_4_2_5_4_5_1_2_2_1_4_4_2_3_2_2_2_3_2_1_2_2_4_6_4_7_1_2_2_2_1_2_1_1_6</t>
+    <t>6_5_5_5_8_3_5_3_7_3_6_3_6_2_2_2_7_5_8_2_4_6_4_5_6_8_1_8_5_4_5_5_1_7_7_7_4_4_3_8_2_8_7_2_3_3_1_7_1_1_3_1_5_7_1_6_4_7_4_2_6_6_4_4_7_7_8_7_8_8_4_5_3_8_4_8_3_3_7_4_7_8_7_6_4_1_7_1_8_2_6_1_2_6_6_2_7_2_5_4_1_4_1_5_7_8_7_8_3_7_2_5_7_7_7_3_5_2_2_2_7_7_8_8_6_3_2_1_8_6_2_8_5_1_8_4_2_2_2_6_2_6_5_1_1_1_4_3_2_2_3_1_1_1_4_1_3_7_1_8_5_2_3_7_2_5_6_4_4_6_5_2_2_7_5_6_6_6_6_2_5_1_5_4_2_2_6_3_7_3_3_5_7_8_2_2_7_8_6_6_3_3_2_4_6_6_7_2_6_8_8_3_6_7_8_7_4_6_4_7_6_1_5_2_3_7_5_5_5_5_7_7_4_7_8_8_8_8_8_7_3_1_3_6_2_5_6_4_7_2_4_2_2_8_2_6_1_6_3_6_4_2_4_2_7_7_1_6_5_6_7_3_3_5_1_4_3_3_4_4_4_6_7_2_7_5_5_6_3_4_3_7_6_2_2_8_5_3_6_1_4_1_1_3_3_3_6_6_4_7_8_8_6_8_2_1_4_1_1_8_2_1_2_7_2_3_4_7_2_5_3_6_5_7_7_3_7_1_1_6_3_6_6_1_7_7_3_1_5_1_6_4_2_5_5_6_5_8_2_4_4_2_5_5_6_4_4_4_3_1_2_1_3_6_3_6_8_5_2_7_2_8_4_2_7_2_7_7_3_6_8_3_5_2_4_3_8_3_2_1_6_3_3_2_2_2_1_8_8_6_2_7_1_3_3_5_4_8_2_5_5_6_6_6_5_1_7_2_3_3_3_2_8_8_3_5_8_2_5_3_2_8_6_6_7_7_2_3_4_4_5_5_8_8_6_5_8_1_5_5_5_5_4_7_5_7_7_8_4_6_6_2_1_5_7_4_8_8_7_6_6_8_5_2_3_8_3_3_7_5_5_5_2_8_8_6_6_2_7_1</t>
+  </si>
+  <si>
+    <t>3_11_18_18_7_7_5_15_1_17_12_14_1_1_1_13_15_4_8_3_1_11_4_1_3_14_2_6_6_4_4_4_7_7_7_12_15_4_5_15_12_6_4_4_18_18_8_8_1_4_8_1_1_3_1_5_6_5_5_5_8_8_4_15_14_1_8_4_8_1_14_14_5_17_17_6_3_18_8_16_16_16_8_7_11_8_7_5_2_16_14_14_14_7_6_6_4_4_4_14_14_4_8_4_4_8_2_9_11_11_11_3_1_13_14_7_7_8_2_1_8_2_5_3_7_3_5_8_7_4_3_3_7_7_7_9_7_17_2_4_7_4_2_3_4_8_2_4_6_2_2_2_2_8_5_5_3_1_15_13_5_11_11_11_9_3_1_17_2_1_4_5_3_5_2_15_8_7_7_12_13_4_11_4_18_5_8_4_8_7_6_6_18_8_1_16_6_6_2_8_6_6_6_6_15_6_6_7_5_6_2_11_9_9_16_15_3_4_15_4_5_5_18_4_16_18_2_12_12_13_3_3_6_18_2_17_17_2_8_6_17_15_4_3_4_4_8_7_1_3_3_5_6_8_3_3_11_14_12_13_2_11_16_13_1_1_2_9_9_6_6_12_3_6_8_8_18_8_2_1_1_7_7_2_1_7_17_14_5_14_2_2_16_2_2_1_16_16_8_18_14_14_8_18_8_13_4_8_2_2_11_12_16_12_12_5_5_6_7_7_2_2_5_15_15_15_3_4_2_11_6_11_18_8_18_16_13_4_18_1_8_8_11_6_6_5_5_7_4_6_6_15_7_16_15_8_15_12_12_4_1_1_1_3_3_3_1_8_8_8_8_9_16_2_13_12_17_17_17_1_12_12_12_12_1_1_1_11_18_18_18_18_2_11_1_9_8_2_2_6_13_5_13_13_11_13_13_8_6_7_4_12_12_17_3_7_11_3_3_14_13_13_7_7_6_5_12_1_6_14_7_2_3_4_1_1_1_14_1_1_15_7_5_2_3_15_1_3_3_3_2_1_6_6_6_3_3_5_16_4_1_5_8_1_1_13_1_17_17_15_13_14_3_11_5_4_4_4_5_17_5_11_11_5_17_17_3_11_9_16_6_1_14_1_2_5_5_16_16_7</t>
   </si>
   <si>
     <t>5_5_5_5</t>
   </si>
   <si>
+    <t>5_3_1_3_6_1_6_8_8_4_4_4_1_3_2_6_5_8_8_4_3_3_7_1_7_2_1_2_4_6_7_5_4_4_6_7_5_6_2_1_1_2_6_8_7_1_7_7_2_5_4_1_1_2_7_8_8_6_5_3_7_7_1_1_1_5_6_5_7_2_6_7_3_4_7_3_7_3_5_2_8_8_1_6_1_4_8_2_8_6_4_7_7_7_7_7_5_4_7_5_5_8_8_8_8_8_1_5_1_6_6_3_4_2_7_8_1_1_3_5_7_6_3_2_4_2_2_3_5_2_7_6_6_2_5_1_8_8_7_5_3_3_4_1_6_3_3_8_2_8_6_1_4_4_5_8_8_5_5_3_1_4_3_4_4_7_6_5_5_1_5_5_3_6_5_1_2_3_2_6_6_6_7_7_7_4_4_7_1_7_6_6_1_8_3_3_3_3_7_5_6_2_1_7_7_8_7_1_7_1_8_3_3_8_6_1_7_1_5_5_5_2_2_3_4_4_6_1_6_8_8_3_2_5_5_2_7_8_6_6_5_3_3_3_6_4_6_1_4_6_7_4_7_8_4_1_6_5_5_1_4_3_7_2_2_6_1_3_1_4_5_8_2_3_6_3_8_1_3_8_4_2_7_8_3_2_5_5_1_5_5_3_8_8_4_5_6_6_4_2_2_2_5_4_8_5_5_5_1_1_4_1_5_2_3_6_7_8_1_2_3_5_3_4_7_3_6_6_4_2_1_6_1_2_7_2_2_2_7_5_6_1_8_6_6_6_2_2_2_8_8_6_8_6_8_8_2_3_3_6_5_4_4_1_8_4_6_4_2_4_7_8_2_3_7_6_5_5_8_5_1_6_8_5_2_7_1_5_8_2_1_4_4_8_8_1_7_1_5_2_1_6_4_4_5_5_5_3_8_4_1_8_7_4_1_3_7_7_1_7_5_4_4_5_4_7_8_8_3_8_6_1_4_3_7_1_1_3_3_3_4_7_7_7_7_2_1_3_2_5_4_7_8_4_8_2_5_4_5_3_3_6_3_6_7_7_7_8_7_2_6_8_5_5_5_5_4_3_8_5_6_4_6_7_8_4_4_8_8_6_8_3_8_1_4_5_8_7_8_4</t>
+  </si>
+  <si>
+    <t>13_5_5_12_1_13_1_17_7_7_6_2_2_6_6_6_17_16_5_12_7_7_7_4_4_4_1_5_5_5_9_8_13_7_4_4_9_14_6_15_4_7_7_13_13_1_7_7_17_7_14_18_18_11_15_15_6_8_8_4_4_3_8_8_12_8_15_6_5_2_4_4_4_6_5_8_5_6_15_15_15_15_6_6_6_16_3_5_5_5_4_5_6_7_2_7_14_10_11_14_14_8_18_9_6_13_11_16_5_3_3_13_13_1_13_14_14_14_3_5_11_3_1_1_7_7_2_13_8_9_7_4_11_4_4_7_1_12_16_14_11_3_4_13_16_13_3_17_3_16_16_3_9_5_5_4_18_18_2_2_2_18_4_4_4_15_1_15_1_1_4_5_5_1_13_14_17_8_3_14_1_9_5_18_18_13_13_18_1_5_9_7_7_5_5_6_6_13_5_5_18_14_5_7_1_1_5_5_8_7_13_5_7_11_15_6_6_2_18_15_1_8_8_2_2_8_8_1_15_15_1_1_1_16_16_9_9_3_13_3_18_1_1_12_17_17_11_10_15_7_7_5_8_8_2_6_3_15_6_6_5_5_5_16_5_5_5_11_2_3_4_13_4_17_8_7_2_4_4_9_1_13_13_14_6_15_2_8_1_13_3_2_10_18_18_15_6_6_8_14_6_16_2_17_17_15_16_6_7_7_7_14_8_4_4_3_7_7_1_1_9_14_5_5_4_13_5_6_6_6_1_1_6_14_13_8_8_12_3_3_2_15_1_15_8_8_15_13_9_9_3_3_3_8_2_2_2_13_4_11_5_3_3_2_4_15_15_5_5_14_16_1_16_16_12_14_12_8_2_14_3_4_4_1_15_16_13_13_8_15_6_6_6_2_14_12_3_3_5_11_11_15_3_6_6_6_8_4_4_1_1_3_13_2_12_3_16_16_1_1_13_13_13_15_11_1_8_5_5_14_14_2_2_17_7_7_8_8_8_2_1_2_16_16_1_2_2_11_11_11_12_4_7_7_3_3_15_13_3_7_8_1_17_7_7_2_7_7_4_15_17_2_2_5_5_5_5_13_15_15_2_8_8_3_17_5_5_1_18_18_10_5_6_15_3_3_3_8_5_17</t>
+  </si>
+  <si>
     <t>8_8_8_8</t>
   </si>
   <si>
+    <t>6_4_1_2_8_4_6_6_1_1_7_7_7_4_7_5_8_5_8_5_4_4_3_6_8_4_2_1_3_8_2_2_1_1_6_7_8_4_6_3_3_8_8_1_2_7_4_3_5_7_1_1_3_8_6_6_6_8_8_6_1_1_3_3_3_6_2_7_2_4_7_3_5_4_3_7_8_2_6_3_2_5_1_8_2_1_6_4_2_4_2_2_1_2_1_7_7_8_4_4_4_4_4_6_5_1_8_2_2_6_2_7_5_7_5_3_3_5_5_7_6_4_7_4_7_4_1_5_8_6_1_5_5_6_7_1_8_5_6_3_1_6_2_7_2_1_1_4_4_6_8_8_6_1_6_1_4_4_5_3_1_2_2_1_3_7_7_6_5_1_3_3_7_6_6_7_3_6_1_8_4_4_6_6_2_5_3_4_4_2_1_3_1_3_8_8_8_4_6_5_3_3_2_3_5_1_6_6_4_5_5_1_2_2_4_7_4_6_4_1_7_4_7_8_8_8_1_1_1_2_6_3_5_6_6_5_1_1_6_6_3_8_6_5_5_3_5_8_1_1_5_1_3_3_2_5_2_1_5_6_8_3_3_1_2_1_5_3_3_8_2_4_6_6_5_4_5_5_1_4_2_8_5_5_7_3_7_8_1_8_8_6_1_6_1_2_3_4_1_3_2_8_1_2_2_4_5_3_6_6_5_1_1_2_4_4_5_1_3_3_6_1_3_5_5_8_3_4_7_5_7_6_2_8_6_8_2_8_3_8_4_4_4_7_6_1_3_7_2_6_8_8_8_7_1_8_6_2_5_2_6_1_3_3_8_8_1_4_2_6_6_2_5_3_6_6_2_2_1_4_5_2_2_4_7_2_4_6_3_3_7_3_4_8_8_6_8_7_4_2_3_4_6_3_8_5_7_7_6_1_1_7_8_4_8_8_4_3_6_4_2_7_2_2_6_2_4_7_3_1_5_5_3_8_3_3_3_2_5_2_4_1_2_4_8_7_1_7_5_4_2_7_1_6_2_4_7_5_3_4_6_5_8_7_8_1_5_5_6_2_2_2_4_5_2_1_3_7_7_1_7_3_2_5_6_3_4_1_2_6_6_4_5_8_4_6_2_6_8_5</t>
+  </si>
+  <si>
+    <t>12_7_7_16_16_1_2_2_11_15_7_7_12_3_3_11_11_7_5_3_3_10_7_6_12_2_5_12_4_13_10_15_3_4_8_8_14_8_11_14_5_7_13_15_5_5_8_13_3_3_14_14_14_14_3_15_18_1_6_6_6_2_10_10_16_2_3_8_8_17_15_1_1_13_2_6_5_8_12_5_1_1_14_14_7_7_4_5_5_2_5_5_9_9_9_18_14_8_3_10_14_14_14_3_1_2_14_18_6_2_2_5_5_5_2_6_6_18_18_18_15_18_6_12_8_8_7_7_7_3_3_4_13_16_11_14_11_11_2_6_6_6_18_16_6_5_5_16_9_5_2_10_2_2_5_2_2_8_8_2_3_3_3_7_5_5_4_12_12_13_13_8_7_4_1_13_1_3_3_11_16_18_8_14_14_5_5_2_16_5_5_5_2_14_12_2_2_6_6_5_8_10_10_9_3_3_12_3_15_10_8_13_3_14_1_1_5_14_14_1_2_2_6_15_3_15_18_7_1_1_1_7_10_12_12_12_11_12_1_1_1_1_1_2_15_15_5_5_16_2_12_12_8_3_9_4_6_13_18_3_7_7_1_1_2_12_6_4_13_8_8_15_3_2_2_12_6_6_17_17_4_4_1_8_8_8_8_5_18_7_17_4_17_6_6_6_4_2_5_1_11_4_7_5_16_4_4_7_1_7_2_7_3_15_7_7_12_12_15_2_1_1_13_3_5_2_2_7_7_7_8_5_8_12_12_2_7_6_3_16_16_16_16_13_7_7_6_6_1_2_15_7_3_3_16_17_8_7_5_2_14_9_11_3_3_3_3_18_13_3_18_4_4_16_5_6_7_7_14_14_6_6_6_16_16_1_5_17_6_2_7_7_1_10_8_10_8_7_2_6_1_1_1_4_10_14_14_6_14_8_4_17_8_4_4_14_15_1_13_4_4_4_14_3_3_2_2_13_18_18_3_8_15_6_14_9_6_5_5_18_2_8_3_13_11_14_6_11_8_4_4_7_6_5_3_3_1_1_1_7_5_14_8_14_14_13_16_4_4_8_6_2_4_5_6_14_15_1_10_8_15_15_7_7_1_8_10_3_3_2_2_14_5_8_7_17_17_17_17_3</t>
+  </si>
+  <si>
     <t>6_6_6_6</t>
   </si>
   <si>
+    <t>3_8_7_3_5_4_2_1_7_7_3_8_6_5_3_4_8_3_2_2_5_3_7_7_2_3_2_5_5_5_5_1_4_1_6_7_1_1_8_8_7_7_2_2_5_2_7_1_5_3_5_1_6_6_8_3_4_4_2_2_4_5_8_1_4_2_1_1_3_3_3_1_3_2_2_2_2_5_1_7_7_5_2_7_8_1_4_5_5_6_7_2_4_1_7_8_5_3_1_1_4_8_8_5_2_8_2_2_8_6_7_8_6_7_4_7_1_3_3_4_6_4_5_5_3_8_5_2_3_5_7_8_5_6_8_6_8_5_1_6_2_4_7_7_4_5_7_6_3_7_1_4_4_5_1_2_1_5_8_1_3_4_2_7_8_1_4_7_3_8_1_2_4_5_7_4_7_7_6_8_8_6_5_7_7_2_1_2_7_7_4_4_3_5_5_8_4_3_7_1_8_1_3_8_7_5_2_5_6_4_5_6_1_8_6_4_2_1_1_4_4_1_1_4_7_8_5_5_4_3_2_6_3_6_6_1_2_5_3_7_5_3_6_5_8_3_2_5_1_5_7_1_8_8_6_6_6_5_7_7_6_6_5_3_5_2_5_6_6_2_4_5_2_5_8_3_2_1_2_7_4_7_4_5_6_5_8_3_4_4_2_2_4_4_3_8_8_7_5_4_5_6_1_8_7_7_8_4_7_7_5_2_6_4_5_8_2_6_3_2_2_5_5_7_7_6_2_2_7_8_8_8_6_6_5_1_1_2_7_8_8_2_4_2_8_2_7_4_8_5_6_6_2_3_6_4_3_3_3_6_6_2_1_1_1_1_4_1_3_8_7_3_2_3_8_8_7_7_5_6_4_4_4_3_3_3_3_3_6_5_8_4_4_2_8_5_6_1_1_1_6_3_3_8_1_4_8_6_4_1_5_5_8_2_4_3_4_5_8_2_8_8_8_2_7_4_7_3_6_4_4_8_6_2_1_1_8_4_2_1_8_8_2_5_3_3_7_3_5_5_6_6_5_5_2_2_2_1_1_3_2_5_6_6_3_5_6_1_1_5_8_3_8_8_2_3_5_4_8_1_4_4_5_3_2_7_7_2_5_7_2_6_5_7_3_3_3_7_3_6</t>
+  </si>
+  <si>
+    <t>17_17_6_6_6_16_16_1_18_6_14_3_4_16_4_16_5_6_16_15_15_8_4_13_18_12_1_2_2_2_2_3_1_6_8_2_2_5_15_15_6_7_5_1_1_8_13_15_3_3_4_4_4_16_16_1_14_3_3_3_2_3_8_8_7_18_13_3_7_7_7_6_4_12_12_2_2_9_2_2_2_2_2_8_2_13_13_11_2_18_1_18_6_2_8_6_6_2_2_2_3_4_1_1_6_6_6_7_7_7_2_7_7_18_17_7_7_4_8_1_1_1_4_7_2_5_2_4_15_2_2_9_13_5_1_6_16_16_3_7_6_4_4_12_8_5_5_5_5_5_8_6_11_8_7_5_2_6_13_2_5_5_2_8_16_16_9_7_16_7_16_4_18_1_8_8_8_18_8_8_4_5_9_9_13_14_18_6_8_8_8_1_5_1_8_4_13_3_3_14_3_3_8_1_7_18_18_1_1_6_6_6_14_1_2_6_6_6_6_8_2_12_11_7_7_7_7_7_7_8_8_7_18_2_12_5_8_17_10_13_5_6_6_6_17_17_17_4_15_15_15_13_13_12_2_2_2_17_16_11_2_7_8_8_7_7_7_2_2_4_8_8_12_1_13_11_4_4_1_11_5_11_1_8_7_14_14_6_1_1_5_8_4_3_1_1_12_1_1_4_4_4_14_14_18_2_2_2_7_5_5_5_10_18_18_18_2_6_5_5_2_2_3_3_3_6_8_8_3_3_16_4_3_3_7_15_14_14_4_1_7_1_10_1_17_18_14_3_5_16_5_13_4_6_9_16_18_6_1_4_5_6_6_16_6_18_3_16_16_14_1_1_18_8_8_8_8_14_14_16_5_11_11_2_14_6_13_18_18_6_18_3_1_7_7_3_3_2_14_14_4_9_9_3_3_15_5_6_6_11_8_13_6_6_5_5_1_3_3_5_6_5_14_8_4_6_17_12_3_1_13_7_12_12_12_8_4_17_17_8_3_3_18_6_15_1_8_3_3_8_18_16_2_12_12_7_3_4_13_13_7_15_7_7_5_7_17_6_13_13_5_3_8_8_18_8_6_6_1_1_2_2_3_6_6_9_9_8_17_17_17_17_17_17_15_17_4_4_15_15</t>
+  </si>
+  <si>
     <t>7_7_7_7</t>
+  </si>
+  <si>
+    <t>2_8_4_7_2_7_1_7_8_7_7_4_2_5_6_6_1_2_3_3_5_8_8_2_2_8_8_6_8_3_3_7_4_6_6_1_4_1_7_7_6_8_2_6_5_3_5_2_4_7_7_8_7_8_2_8_8_4_8_8_8_8_5_5_4_7_7_2_1_4_4_4_4_2_2_7_1_8_8_8_4_5_5_5_7_2_7_5_5_5_1_2_6_7_8_3_8_7_7_5_6_5_7_5_8_3_4_6_4_2_2_3_2_5_3_3_2_8_6_5_3_5_2_2_1_6_8_7_6_2_2_2_8_2_3_4_6_5_5_3_3_2_6_6_3_7_2_4_2_7_4_5_6_1_6_8_7_7_6_6_8_3_7_2_8_5_8_7_6_5_8_2_8_1_7_3_7_5_3_6_5_5_3_3_8_2_4_1_3_8_6_4_1_1_3_3_8_3_2_2_3_3_2_4_6_8_2_2_7_8_3_3_2_2_2_6_6_3_7_8_5_2_2_8_4_1_3_1_5_8_8_3_2_1_5_2_2_1_7_4_8_8_6_6_3_5_1_6_3_6_3_7_5_6_5_5_7_4_6_3_6_5_4_8_5_1_7_7_6_5_8_4_5_6_3_3_1_8_8_2_3_5_2_5_5_6_1_1_2_5_6_3_8_4_2_2_7_1_1_3_5_1_8_7_8_6_2_2_5_3_6_5_3_6_6_6_6_8_4_3_8_3_3_3_2_8_8_3_6_4_1_5_2_2_5_5_5_1_6_2_1_1_5_5_8_8_6_1_6_6_7_1_8_5_1_8_5_7_3_5_6_6_2_3_2_1_7_1_1_3_1_6_4_6_1_6_7_8_6_3_8_8_1_1_6_3_2_3_6_2_3_6_7_1_3_3_3_7_7_1_8_6_1_8_1_4_8_8_8_6_6_2_8_6_2_3_3_1_3_7_7_3_5_2_4_2_6_7_3_7_8_6_8_3_3_3_5_3_3_7_7_5_5_3_3_7_7_3_1_1_1_4_3_5_7_2_4_3_4_5_1_5_4_4_6_8_2_7_5_3_7_4_4_8_3_8_2_7_8_7_7_5_7_3_6_5_6_3_2_8_8_3_7_7_1_7_4_3_2_6</t>
+  </si>
+  <si>
+    <t>13_6_3_12_5_5_5_4_4_3_11_3_8_8_8_3_5_7_8_8_5_5_8_17_5_2_1_14_4_4_3_8_4_15_13_13_13_13_13_5_5_5_5_17_12_8_6_6_6_18_8_18_5_2_7_6_5_5_7_15_13_2_2_4_4_16_3_8_14_7_3_8_3_3_5_8_17_18_16_1_8_7_3_7_8_3_5_5_16_3_3_8_18_2_2_13_8_15_11_4_4_5_5_6_4_4_3_5_1_1_16_1_1_1_3_8_1_12_2_4_6_3_6_5_14_5_8_15_1_1_13_12_5_6_6_8_6_8_17_7_16_6_7_16_9_9_9_5_5_5_2_2_16_2_2_2_6_6_3_3_1_4_4_15_9_13_13_7_7_7_17_18_2_5_12_4_2_6_2_7_8_14_7_6_6_4_3_17_8_1_11_1_12_15_8_7_7_8_8_7_12_5_5_11_11_8_5_1_6_18_8_15_15_8_2_4_3_15_7_3_16_5_7_18_13_5_7_3_7_16_16_4_13_13_13_7_15_15_1_1_1_1_3_2_7_8_3_16_16_11_2_2_13_13_5_18_5_5_14_14_5_4_4_7_11_11_14_7_1_5_5_5_12_16_16_15_2_1_8_8_7_12_9_5_8_12_12_2_8_14_14_14_2_13_16_4_1_18_18_5_6_12_12_4_4_2_17_17_1_4_6_12_5_5_8_6_6_11_11_11_5_5_12_12_6_17_3_3_5_12_12_12_17_2_2_2_4_7_7_17_16_13_13_13_14_6_3_3_16_1_1_1_4_17_2_2_9_12_4_1_2_11_4_7_8_11_12_1_11_6_5_7_14_14_18_17_15_18_2_2_2_4_3_3_17_15_8_4_2_2_8_1_7_7_7_17_7_18_18_5_9_3_1_3_9_15_8_5_4_4_5_5_6_2_18_7_4_13_18_18_14_7_11_11_5_8_2_2_2_18_2_1_6_11_2_14_8_14_17_5_5_5_5_1_14_8_9_9_4_11_11_11_3_3_3_18_2_7_8_5_12_8_14_2_2_2_12_6_18_4_1_1_8_8_8_8_7_1_9_9_3_7_7_3_7_1_1_3_3_12_8_11_11_5_6_11_1_11_4_4</t>
   </si>
   <si>
     <t>6_6_6</t>
@@ -468,12 +495,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2079,7 +2106,7 @@
         <v>36</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J16" s="28"/>
       <c r="K16" s="6"/>
@@ -2099,19 +2126,19 @@
         <v>2</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F17" s="14" t="s">
         <v>36</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H17" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J17" s="28"/>
       <c r="K17" s="6"/>
@@ -2131,19 +2158,19 @@
         <v>3</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14" t="s">
         <v>36</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H18" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J18" s="28"/>
       <c r="K18" s="6"/>
@@ -2163,19 +2190,19 @@
         <v>4</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F19" s="14" t="s">
         <v>36</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="H19" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="J19" s="28"/>
       <c r="K19" s="6"/>
@@ -2195,19 +2222,19 @@
         <v>5</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F20" s="14" t="s">
         <v>36</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="H20" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J20" s="28"/>
       <c r="K20" s="6"/>
@@ -2227,19 +2254,19 @@
         <v>1</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F21" s="26" t="s">
         <v>20</v>
       </c>
       <c r="G21" s="26" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H21" s="26" t="s">
         <v>20</v>
       </c>
       <c r="I21" s="26" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J21" s="26"/>
       <c r="K21" s="26"/>
@@ -2259,19 +2286,19 @@
         <v>2</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="F22" s="26" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="26" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H22" s="26" t="s">
         <v>20</v>
       </c>
       <c r="I22" s="26" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="J22" s="26"/>
       <c r="K22" s="26"/>
@@ -2291,19 +2318,19 @@
         <v>3</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F23" s="26" t="s">
         <v>20</v>
       </c>
       <c r="G23" s="26" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H23" s="26" t="s">
         <v>20</v>
       </c>
       <c r="I23" s="26" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="J23" s="26"/>
       <c r="K23" s="26"/>
@@ -2323,19 +2350,19 @@
         <v>4</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="F24" s="26" t="s">
         <v>20</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="H24" s="26" t="s">
         <v>20</v>
       </c>
       <c r="I24" s="26" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="J24" s="26"/>
       <c r="K24" s="26"/>
@@ -2355,19 +2382,19 @@
         <v>5</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F25" s="26" t="s">
         <v>20</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="H25" s="26" t="s">
         <v>20</v>
       </c>
       <c r="I25" s="26" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J25" s="26"/>
       <c r="K25" s="26"/>
@@ -2393,13 +2420,13 @@
         <v>36</v>
       </c>
       <c r="G26" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="H26" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I26" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="J26" s="28"/>
     </row>
@@ -2424,13 +2451,13 @@
         <v>36</v>
       </c>
       <c r="G27" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="H27" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I27" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="J27" s="28"/>
     </row>
@@ -2455,13 +2482,13 @@
         <v>36</v>
       </c>
       <c r="G28" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="H28" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I28" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="J28" s="28"/>
     </row>
@@ -2486,13 +2513,13 @@
         <v>36</v>
       </c>
       <c r="G29" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="H29" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I29" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="J29" s="28"/>
       <c r="K29" s="6"/>
@@ -2518,13 +2545,13 @@
         <v>36</v>
       </c>
       <c r="G30" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="H30" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I30" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="J30" s="28"/>
       <c r="K30" s="6"/>
@@ -2550,13 +2577,13 @@
         <v>36</v>
       </c>
       <c r="G31" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="H31" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I31" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="J31" s="28"/>
     </row>
@@ -2588,7 +2615,7 @@
         <v>36</v>
       </c>
       <c r="I32" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="J32" s="28"/>
     </row>
@@ -2620,7 +2647,7 @@
         <v>36</v>
       </c>
       <c r="I33" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="J33" s="28"/>
     </row>
@@ -2652,7 +2679,7 @@
         <v>36</v>
       </c>
       <c r="I34" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="J34" s="28"/>
       <c r="K34" s="6"/>
@@ -2678,13 +2705,13 @@
         <v>36</v>
       </c>
       <c r="G35" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="H35" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I35" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="J35" s="28"/>
       <c r="K35" s="6"/>
@@ -2710,13 +2737,13 @@
         <v>36</v>
       </c>
       <c r="G36" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="H36" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I36" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="J36" s="28"/>
       <c r="K36" s="6"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -219,7 +219,7 @@
     <t>6_5_5_5_8_3_5_3_7_3_6_3_6_2_2_2_7_5_8_2_4_6_4_5_6_8_1_8_5_4_5_5_1_7_7_7_4_4_3_8_2_8_7_2_3_3_1_7_1_1_3_1_5_7_1_6_4_7_4_2_6_6_4_4_7_7_8_7_8_8_4_5_3_8_4_8_3_3_7_4_7_8_7_6_4_1_7_1_8_2_6_1_2_6_6_2_7_2_5_4_1_4_1_5_7_8_7_8_3_7_2_5_7_7_7_3_5_2_2_2_7_7_8_8_6_3_2_1_8_6_2_8_5_1_8_4_2_2_2_6_2_6_5_1_1_1_4_3_2_2_3_1_1_1_4_1_3_7_1_8_5_2_3_7_2_5_6_4_4_6_5_2_2_7_5_6_6_6_6_2_5_1_5_4_2_2_6_3_7_3_3_5_7_8_2_2_7_8_6_6_3_3_2_4_6_6_7_2_6_8_8_3_6_7_8_7_4_6_4_7_6_1_5_2_3_7_5_5_5_5_7_7_4_7_8_8_8_8_8_7_3_1_3_6_2_5_6_4_7_2_4_2_2_8_2_6_1_6_3_6_4_2_4_2_7_7_1_6_5_6_7_3_3_5_1_4_3_3_4_4_4_6_7_2_7_5_5_6_3_4_3_7_6_2_2_8_5_3_6_1_4_1_1_3_3_3_6_6_4_7_8_8_6_8_2_1_4_1_1_8_2_1_2_7_2_3_4_7_2_5_3_6_5_7_7_3_7_1_1_6_3_6_6_1_7_7_3_1_5_1_6_4_2_5_5_6_5_8_2_4_4_2_5_5_6_4_4_4_3_1_2_1_3_6_3_6_8_5_2_7_2_8_4_2_7_2_7_7_3_6_8_3_5_2_4_3_8_3_2_1_6_3_3_2_2_2_1_8_8_6_2_7_1_3_3_5_4_8_2_5_5_6_6_6_5_1_7_2_3_3_3_2_8_8_3_5_8_2_5_3_2_8_6_6_7_7_2_3_4_4_5_5_8_8_6_5_8_1_5_5_5_5_4_7_5_7_7_8_4_6_6_2_1_5_7_4_8_8_7_6_6_8_5_2_3_8_3_3_7_5_5_5_2_8_8_6_6_2_7_1</t>
   </si>
   <si>
-    <t>3_11_18_18_7_7_5_15_1_17_12_14_1_1_1_13_15_4_8_3_1_11_4_1_3_14_2_6_6_4_4_4_7_7_7_12_15_4_5_15_12_6_4_4_18_18_8_8_1_4_8_1_1_3_1_5_6_5_5_5_8_8_4_15_14_1_8_4_8_1_14_14_5_17_17_6_3_18_8_16_16_16_8_7_11_8_7_5_2_16_14_14_14_7_6_6_4_4_4_14_14_4_8_4_4_8_2_9_11_11_11_3_1_13_14_7_7_8_2_1_8_2_5_3_7_3_5_8_7_4_3_3_7_7_7_9_7_17_2_4_7_4_2_3_4_8_2_4_6_2_2_2_2_8_5_5_3_1_15_13_5_11_11_11_9_3_1_17_2_1_4_5_3_5_2_15_8_7_7_12_13_4_11_4_18_5_8_4_8_7_6_6_18_8_1_16_6_6_2_8_6_6_6_6_15_6_6_7_5_6_2_11_9_9_16_15_3_4_15_4_5_5_18_4_16_18_2_12_12_13_3_3_6_18_2_17_17_2_8_6_17_15_4_3_4_4_8_7_1_3_3_5_6_8_3_3_11_14_12_13_2_11_16_13_1_1_2_9_9_6_6_12_3_6_8_8_18_8_2_1_1_7_7_2_1_7_17_14_5_14_2_2_16_2_2_1_16_16_8_18_14_14_8_18_8_13_4_8_2_2_11_12_16_12_12_5_5_6_7_7_2_2_5_15_15_15_3_4_2_11_6_11_18_8_18_16_13_4_18_1_8_8_11_6_6_5_5_7_4_6_6_15_7_16_15_8_15_12_12_4_1_1_1_3_3_3_1_8_8_8_8_9_16_2_13_12_17_17_17_1_12_12_12_12_1_1_1_11_18_18_18_18_2_11_1_9_8_2_2_6_13_5_13_13_11_13_13_8_6_7_4_12_12_17_3_7_11_3_3_14_13_13_7_7_6_5_12_1_6_14_7_2_3_4_1_1_1_14_1_1_15_7_5_2_3_15_1_3_3_3_2_1_6_6_6_3_3_5_16_4_1_5_8_1_1_13_1_17_17_15_13_14_3_11_5_4_4_4_5_17_5_11_11_5_17_17_3_11_9_16_6_1_14_1_2_5_5_16_16_7</t>
+    <t>7_1_5_3_5_1_1_2_13_5_15_17_8_3_5_6_3_16_6_8_1_13_3_3_11_4_4_4_15_5_5_2_2_4_5_8_6_3_7_1_7_17_4_14_12_13_3_4_15_5_4_4_2_12_3_5_4_1_7_17_5_7_5_8_1_4_4_5_2_17_5_5_7_5_7_6_5_8_6_7_6_6_7_7_1_17_16_11_5_6_2_3_5_18_7_1_6_8_1_11_2_3_2_2_16_8_1_16_2_16_4_7_3_12_10_14_8_6_5_4_7_15_1_1_4_12_11_8_2_5_10_2_4_5_5_8_4_10_12_4_17_7_5_17_8_3_7_10_3_12_18_8_15_16_3_7_8_2_8_3_7_2_5_4_11_17_5_5_2_6_8_6_6_14_1_11_8_4_8_3_7_6_5_2_17_4_17_2_6_6_2_1_16_2_7_7_15_11_14_10_18_7_11_5_15_4_7_11_6_15_16_7_17_5_7_7_7_4_1_13_15_5_15_3_8_3_7_11_5_15_2_4_7_7_2_17_8_8_13_1_6_12_1_2_6_3_18_3_3_13_1_5_8_4_12_8_14_3_6_4_12_11_18_11_14_1_8_3_12_14_4_13_2_4_17_18_2_2_10_16_5_2_8_7_17_8_4_14_4_1_6_3_12_3_5_1_2_4_12_7_8_1_5_17_7_2_13_4_5_14_8_5_5_6_11_17_15_3_2_11_1_5_18_13_6_3_2_4_12_6_16_4_16_5_15_3_3_2_8_1_7_8_4_4_8_8_6_13_13_15_8_3_4_7_8_7_5_8_2_12_13_3_6_7_11_1_4_1_6_6_17_3_2_1_5_3_6_13_16_10_6_8_3_18_18_2_13_3_17_8_6_15_2_6_14_3_5_13_2_10_3_3_4_4_1_15_2_6_5_3_5_16_13_10_2_15_5_6_10_1_5_8_4_7_1_7_5_6_7_1_6_14_13_10_1_3_3_8_17_10_2_6_10_5_1_2_6_8_8_11_7_5_5_7_6_2_7_4_5_17_6_7_8_15_11_8_13_6_7_7_13_8_6_8_12_10_15_8_6_5_11_2_6_14_6_13_11_2_14_18_15_3_16_4_16_12_3_12_1_1</t>
   </si>
   <si>
     <t>5_5_5_5</t>
@@ -228,7 +228,7 @@
     <t>5_3_1_3_6_1_6_8_8_4_4_4_1_3_2_6_5_8_8_4_3_3_7_1_7_2_1_2_4_6_7_5_4_4_6_7_5_6_2_1_1_2_6_8_7_1_7_7_2_5_4_1_1_2_7_8_8_6_5_3_7_7_1_1_1_5_6_5_7_2_6_7_3_4_7_3_7_3_5_2_8_8_1_6_1_4_8_2_8_6_4_7_7_7_7_7_5_4_7_5_5_8_8_8_8_8_1_5_1_6_6_3_4_2_7_8_1_1_3_5_7_6_3_2_4_2_2_3_5_2_7_6_6_2_5_1_8_8_7_5_3_3_4_1_6_3_3_8_2_8_6_1_4_4_5_8_8_5_5_3_1_4_3_4_4_7_6_5_5_1_5_5_3_6_5_1_2_3_2_6_6_6_7_7_7_4_4_7_1_7_6_6_1_8_3_3_3_3_7_5_6_2_1_7_7_8_7_1_7_1_8_3_3_8_6_1_7_1_5_5_5_2_2_3_4_4_6_1_6_8_8_3_2_5_5_2_7_8_6_6_5_3_3_3_6_4_6_1_4_6_7_4_7_8_4_1_6_5_5_1_4_3_7_2_2_6_1_3_1_4_5_8_2_3_6_3_8_1_3_8_4_2_7_8_3_2_5_5_1_5_5_3_8_8_4_5_6_6_4_2_2_2_5_4_8_5_5_5_1_1_4_1_5_2_3_6_7_8_1_2_3_5_3_4_7_3_6_6_4_2_1_6_1_2_7_2_2_2_7_5_6_1_8_6_6_6_2_2_2_8_8_6_8_6_8_8_2_3_3_6_5_4_4_1_8_4_6_4_2_4_7_8_2_3_7_6_5_5_8_5_1_6_8_5_2_7_1_5_8_2_1_4_4_8_8_1_7_1_5_2_1_6_4_4_5_5_5_3_8_4_1_8_7_4_1_3_7_7_1_7_5_4_4_5_4_7_8_8_3_8_6_1_4_3_7_1_1_3_3_3_4_7_7_7_7_2_1_3_2_5_4_7_8_4_8_2_5_4_5_3_3_6_3_6_7_7_7_8_7_2_6_8_5_5_5_5_4_3_8_5_6_4_6_7_8_4_4_8_8_6_8_3_8_1_4_5_8_7_8_4</t>
   </si>
   <si>
-    <t>13_5_5_12_1_13_1_17_7_7_6_2_2_6_6_6_17_16_5_12_7_7_7_4_4_4_1_5_5_5_9_8_13_7_4_4_9_14_6_15_4_7_7_13_13_1_7_7_17_7_14_18_18_11_15_15_6_8_8_4_4_3_8_8_12_8_15_6_5_2_4_4_4_6_5_8_5_6_15_15_15_15_6_6_6_16_3_5_5_5_4_5_6_7_2_7_14_10_11_14_14_8_18_9_6_13_11_16_5_3_3_13_13_1_13_14_14_14_3_5_11_3_1_1_7_7_2_13_8_9_7_4_11_4_4_7_1_12_16_14_11_3_4_13_16_13_3_17_3_16_16_3_9_5_5_4_18_18_2_2_2_18_4_4_4_15_1_15_1_1_4_5_5_1_13_14_17_8_3_14_1_9_5_18_18_13_13_18_1_5_9_7_7_5_5_6_6_13_5_5_18_14_5_7_1_1_5_5_8_7_13_5_7_11_15_6_6_2_18_15_1_8_8_2_2_8_8_1_15_15_1_1_1_16_16_9_9_3_13_3_18_1_1_12_17_17_11_10_15_7_7_5_8_8_2_6_3_15_6_6_5_5_5_16_5_5_5_11_2_3_4_13_4_17_8_7_2_4_4_9_1_13_13_14_6_15_2_8_1_13_3_2_10_18_18_15_6_6_8_14_6_16_2_17_17_15_16_6_7_7_7_14_8_4_4_3_7_7_1_1_9_14_5_5_4_13_5_6_6_6_1_1_6_14_13_8_8_12_3_3_2_15_1_15_8_8_15_13_9_9_3_3_3_8_2_2_2_13_4_11_5_3_3_2_4_15_15_5_5_14_16_1_16_16_12_14_12_8_2_14_3_4_4_1_15_16_13_13_8_15_6_6_6_2_14_12_3_3_5_11_11_15_3_6_6_6_8_4_4_1_1_3_13_2_12_3_16_16_1_1_13_13_13_15_11_1_8_5_5_14_14_2_2_17_7_7_8_8_8_2_1_2_16_16_1_2_2_11_11_11_12_4_7_7_3_3_15_13_3_7_8_1_17_7_7_2_7_7_4_15_17_2_2_5_5_5_5_13_15_15_2_8_8_3_17_5_5_1_18_18_10_5_6_15_3_3_3_8_5_17</t>
+    <t>11_6_2_8_3_6_10_8_1_13_7_3_5_7_3_1_3_3_6_5_3_5_8_6_5_10_7_4_1_6_18_7_3_3_15_6_3_1_7_18_6_1_7_3_1_1_4_3_17_15_12_14_7_5_17_8_3_1_3_8_1_3_2_4_2_3_17_14_3_1_6_6_2_15_8_5_8_14_11_3_7_16_2_5_8_3_17_5_6_6_10_4_6_3_12_7_2_4_13_1_5_1_14_3_8_6_4_2_6_6_8_4_17_15_4_16_7_1_2_8_11_10_5_3_6_10_16_18_14_3_17_3_2_6_3_4_17_16_15_3_6_7_12_4_13_17_1_1_10_3_12_8_14_7_8_5_6_5_8_8_17_4_17_10_3_8_6_15_2_11_3_16_6_6_8_5_14_6_15_13_16_13_4_16_7_4_17_1_2_5_15_7_4_6_5_13_11_2_18_17_12_1_6_14_18_11_5_7_5_1_3_10_18_2_6_1_6_8_7_8_6_8_15_17_2_6_3_6_8_16_2_6_8_1_2_1_12_1_1_2_1_5_2_8_13_4_6_3_16_16_18_11_2_16_6_6_8_7_1_2_2_11_3_18_15_8_8_18_2_2_2_18_3_8_7_8_2_13_5_7_18_11_8_3_4_13_7_1_6_6_14_4_6_7_18_12_6_4_2_18_16_1_1_2_6_15_12_1_10_6_15_11_17_5_1_15_2_1_6_14_1_2_4_2_1_13_6_7_6_7_3_13_7_12_3_2_15_8_2_10_2_8_12_7_1_8_1_2_17_1_3_1_10_1_8_14_1_18_6_6_17_7_5_7_6_6_3_7_4_7_2_6_17_3_4_1_6_14_5_5_3_8_5_16_16_13_5_11_18_7_16_8_6_17_3_15_1_5_5_18_6_7_14_2_6_6_12_2_3_5_10_7_7_3_13_6_2_17_13_18_2_1_7_15_7_1_14_18_5_6_7_16_8_18_4_1_3_7_1_2_1_5_3_6_8_4_4_6_7_14_14_8_1_18_13_4_3_7_5_2_12_5_8_8_1_2_6_1_10_8_6_6_6_8_2_1_6_12_4_3_7_1_2_6_6_3_16_3_1_1_2_4_5_3_8_2_5_2_7_5</t>
   </si>
   <si>
     <t>8_8_8_8</t>
@@ -237,7 +237,7 @@
     <t>6_4_1_2_8_4_6_6_1_1_7_7_7_4_7_5_8_5_8_5_4_4_3_6_8_4_2_1_3_8_2_2_1_1_6_7_8_4_6_3_3_8_8_1_2_7_4_3_5_7_1_1_3_8_6_6_6_8_8_6_1_1_3_3_3_6_2_7_2_4_7_3_5_4_3_7_8_2_6_3_2_5_1_8_2_1_6_4_2_4_2_2_1_2_1_7_7_8_4_4_4_4_4_6_5_1_8_2_2_6_2_7_5_7_5_3_3_5_5_7_6_4_7_4_7_4_1_5_8_6_1_5_5_6_7_1_8_5_6_3_1_6_2_7_2_1_1_4_4_6_8_8_6_1_6_1_4_4_5_3_1_2_2_1_3_7_7_6_5_1_3_3_7_6_6_7_3_6_1_8_4_4_6_6_2_5_3_4_4_2_1_3_1_3_8_8_8_4_6_5_3_3_2_3_5_1_6_6_4_5_5_1_2_2_4_7_4_6_4_1_7_4_7_8_8_8_1_1_1_2_6_3_5_6_6_5_1_1_6_6_3_8_6_5_5_3_5_8_1_1_5_1_3_3_2_5_2_1_5_6_8_3_3_1_2_1_5_3_3_8_2_4_6_6_5_4_5_5_1_4_2_8_5_5_7_3_7_8_1_8_8_6_1_6_1_2_3_4_1_3_2_8_1_2_2_4_5_3_6_6_5_1_1_2_4_4_5_1_3_3_6_1_3_5_5_8_3_4_7_5_7_6_2_8_6_8_2_8_3_8_4_4_4_7_6_1_3_7_2_6_8_8_8_7_1_8_6_2_5_2_6_1_3_3_8_8_1_4_2_6_6_2_5_3_6_6_2_2_1_4_5_2_2_4_7_2_4_6_3_3_7_3_4_8_8_6_8_7_4_2_3_4_6_3_8_5_7_7_6_1_1_7_8_4_8_8_4_3_6_4_2_7_2_2_6_2_4_7_3_1_5_5_3_8_3_3_3_2_5_2_4_1_2_4_8_7_1_7_5_4_2_7_1_6_2_4_7_5_3_4_6_5_8_7_8_1_5_5_6_2_2_2_4_5_2_1_3_7_7_1_7_3_2_5_6_3_4_1_2_6_6_4_5_8_4_6_2_6_8_5</t>
   </si>
   <si>
-    <t>12_7_7_16_16_1_2_2_11_15_7_7_12_3_3_11_11_7_5_3_3_10_7_6_12_2_5_12_4_13_10_15_3_4_8_8_14_8_11_14_5_7_13_15_5_5_8_13_3_3_14_14_14_14_3_15_18_1_6_6_6_2_10_10_16_2_3_8_8_17_15_1_1_13_2_6_5_8_12_5_1_1_14_14_7_7_4_5_5_2_5_5_9_9_9_18_14_8_3_10_14_14_14_3_1_2_14_18_6_2_2_5_5_5_2_6_6_18_18_18_15_18_6_12_8_8_7_7_7_3_3_4_13_16_11_14_11_11_2_6_6_6_18_16_6_5_5_16_9_5_2_10_2_2_5_2_2_8_8_2_3_3_3_7_5_5_4_12_12_13_13_8_7_4_1_13_1_3_3_11_16_18_8_14_14_5_5_2_16_5_5_5_2_14_12_2_2_6_6_5_8_10_10_9_3_3_12_3_15_10_8_13_3_14_1_1_5_14_14_1_2_2_6_15_3_15_18_7_1_1_1_7_10_12_12_12_11_12_1_1_1_1_1_2_15_15_5_5_16_2_12_12_8_3_9_4_6_13_18_3_7_7_1_1_2_12_6_4_13_8_8_15_3_2_2_12_6_6_17_17_4_4_1_8_8_8_8_5_18_7_17_4_17_6_6_6_4_2_5_1_11_4_7_5_16_4_4_7_1_7_2_7_3_15_7_7_12_12_15_2_1_1_13_3_5_2_2_7_7_7_8_5_8_12_12_2_7_6_3_16_16_16_16_13_7_7_6_6_1_2_15_7_3_3_16_17_8_7_5_2_14_9_11_3_3_3_3_18_13_3_18_4_4_16_5_6_7_7_14_14_6_6_6_16_16_1_5_17_6_2_7_7_1_10_8_10_8_7_2_6_1_1_1_4_10_14_14_6_14_8_4_17_8_4_4_14_15_1_13_4_4_4_14_3_3_2_2_13_18_18_3_8_15_6_14_9_6_5_5_18_2_8_3_13_11_14_6_11_8_4_4_7_6_5_3_3_1_1_1_7_5_14_8_14_14_13_16_4_4_8_6_2_4_5_6_14_15_1_10_8_15_15_7_7_1_8_10_3_3_2_2_14_5_8_7_17_17_17_17_3</t>
+    <t>1_2_4_8_3_17_7_6_2_4_15_5_3_17_1_1_8_14_4_12_1_17_2_17_8_5_2_8_10_14_13_7_16_2_10_3_2_2_8_5_6_8_8_3_10_8_2_3_2_3_13_8_2_2_18_11_6_1_8_1_3_5_3_6_14_3_5_8_15_1_5_12_3_1_10_13_12_3_5_17_8_1_6_5_11_1_7_4_5_7_7_13_3_7_13_3_3_12_8_7_18_7_2_4_6_8_4_5_1_10_3_3_5_12_17_7_7_7_5_3_14_5_4_16_16_16_7_8_3_13_7_3_15_5_2_7_1_5_4_7_8_10_8_8_7_15_16_8_10_8_6_6_8_2_15_2_6_6_2_3_5_17_2_11_6_2_12_4_8_3_15_1_3_2_7_3_8_7_16_3_2_17_6_7_7_7_1_3_14_3_10_18_8_4_8_12_1_5_8_13_1_2_8_2_6_14_5_15_8_5_17_13_17_17_8_8_6_2_8_3_17_6_11_3_2_4_4_1_4_15_10_6_8_5_15_17_5_6_4_1_3_8_11_4_6_3_8_3_6_18_4_14_4_1_17_5_3_6_4_8_13_2_2_4_2_3_7_18_2_6_16_1_7_16_3_8_18_4_6_3_1_3_16_1_8_8_14_2_4_12_7_1_1_8_5_16_4_6_17_13_5_10_8_18_10_7_10_16_4_18_18_11_1_14_8_5_15_12_5_5_3_1_11_3_2_16_5_13_17_5_10_16_7_1_8_12_3_2_6_6_2_13_18_5_4_7_10_2_5_4_7_6_5_8_6_7_5_13_6_3_1_12_7_8_6_6_4_6_4_14_18_3_12_4_4_4_15_7_18_2_1_8_5_3_10_2_1_8_2_6_12_3_15_16_3_1_15_1_6_11_3_1_8_2_1_7_8_1_1_16_5_5_7_1_4_3_12_2_12_7_2_2_1_6_7_11_3_12_1_12_6_18_6_14_5_7_2_3_8_12_8_18_12_4_5_5_10_8_3_3_13_6_1_2_4_14_15_7_3_8_4_2_7_6_2_11_16_5_6_6_14_3_8_14_1_7_3_8_14_7_15_8_12_6_5_2_4_17_18_1_11_15_18_12_3_8_3_12_5_1</t>
   </si>
   <si>
     <t>6_6_6_6</t>
@@ -246,7 +246,7 @@
     <t>3_8_7_3_5_4_2_1_7_7_3_8_6_5_3_4_8_3_2_2_5_3_7_7_2_3_2_5_5_5_5_1_4_1_6_7_1_1_8_8_7_7_2_2_5_2_7_1_5_3_5_1_6_6_8_3_4_4_2_2_4_5_8_1_4_2_1_1_3_3_3_1_3_2_2_2_2_5_1_7_7_5_2_7_8_1_4_5_5_6_7_2_4_1_7_8_5_3_1_1_4_8_8_5_2_8_2_2_8_6_7_8_6_7_4_7_1_3_3_4_6_4_5_5_3_8_5_2_3_5_7_8_5_6_8_6_8_5_1_6_2_4_7_7_4_5_7_6_3_7_1_4_4_5_1_2_1_5_8_1_3_4_2_7_8_1_4_7_3_8_1_2_4_5_7_4_7_7_6_8_8_6_5_7_7_2_1_2_7_7_4_4_3_5_5_8_4_3_7_1_8_1_3_8_7_5_2_5_6_4_5_6_1_8_6_4_2_1_1_4_4_1_1_4_7_8_5_5_4_3_2_6_3_6_6_1_2_5_3_7_5_3_6_5_8_3_2_5_1_5_7_1_8_8_6_6_6_5_7_7_6_6_5_3_5_2_5_6_6_2_4_5_2_5_8_3_2_1_2_7_4_7_4_5_6_5_8_3_4_4_2_2_4_4_3_8_8_7_5_4_5_6_1_8_7_7_8_4_7_7_5_2_6_4_5_8_2_6_3_2_2_5_5_7_7_6_2_2_7_8_8_8_6_6_5_1_1_2_7_8_8_2_4_2_8_2_7_4_8_5_6_6_2_3_6_4_3_3_3_6_6_2_1_1_1_1_4_1_3_8_7_3_2_3_8_8_7_7_5_6_4_4_4_3_3_3_3_3_6_5_8_4_4_2_8_5_6_1_1_1_6_3_3_8_1_4_8_6_4_1_5_5_8_2_4_3_4_5_8_2_8_8_8_2_7_4_7_3_6_4_4_8_6_2_1_1_8_4_2_1_8_8_2_5_3_3_7_3_5_5_6_6_5_5_2_2_2_1_1_3_2_5_6_6_3_5_6_1_1_5_8_3_8_8_2_3_5_4_8_1_4_4_5_3_2_7_7_2_5_7_2_6_5_7_3_3_3_7_3_6</t>
   </si>
   <si>
-    <t>17_17_6_6_6_16_16_1_18_6_14_3_4_16_4_16_5_6_16_15_15_8_4_13_18_12_1_2_2_2_2_3_1_6_8_2_2_5_15_15_6_7_5_1_1_8_13_15_3_3_4_4_4_16_16_1_14_3_3_3_2_3_8_8_7_18_13_3_7_7_7_6_4_12_12_2_2_9_2_2_2_2_2_8_2_13_13_11_2_18_1_18_6_2_8_6_6_2_2_2_3_4_1_1_6_6_6_7_7_7_2_7_7_18_17_7_7_4_8_1_1_1_4_7_2_5_2_4_15_2_2_9_13_5_1_6_16_16_3_7_6_4_4_12_8_5_5_5_5_5_8_6_11_8_7_5_2_6_13_2_5_5_2_8_16_16_9_7_16_7_16_4_18_1_8_8_8_18_8_8_4_5_9_9_13_14_18_6_8_8_8_1_5_1_8_4_13_3_3_14_3_3_8_1_7_18_18_1_1_6_6_6_14_1_2_6_6_6_6_8_2_12_11_7_7_7_7_7_7_8_8_7_18_2_12_5_8_17_10_13_5_6_6_6_17_17_17_4_15_15_15_13_13_12_2_2_2_17_16_11_2_7_8_8_7_7_7_2_2_4_8_8_12_1_13_11_4_4_1_11_5_11_1_8_7_14_14_6_1_1_5_8_4_3_1_1_12_1_1_4_4_4_14_14_18_2_2_2_7_5_5_5_10_18_18_18_2_6_5_5_2_2_3_3_3_6_8_8_3_3_16_4_3_3_7_15_14_14_4_1_7_1_10_1_17_18_14_3_5_16_5_13_4_6_9_16_18_6_1_4_5_6_6_16_6_18_3_16_16_14_1_1_18_8_8_8_8_14_14_16_5_11_11_2_14_6_13_18_18_6_18_3_1_7_7_3_3_2_14_14_4_9_9_3_3_15_5_6_6_11_8_13_6_6_5_5_1_3_3_5_6_5_14_8_4_6_17_12_3_1_13_7_12_12_12_8_4_17_17_8_3_3_18_6_15_1_8_3_3_8_18_16_2_12_12_7_3_4_13_13_7_15_7_7_5_7_17_6_13_13_5_3_8_8_18_8_6_6_1_1_2_2_3_6_6_9_9_8_17_17_17_17_17_17_15_17_4_4_15_15</t>
+    <t>5_2_15_16_8_7_14_1_5_8_3_1_6_10_5_12_17_2_2_13_5_5_1_4_6_7_4_6_3_11_1_4_14_5_14_18_8_6_11_7_14_8_7_5_10_7_6_3_8_11_7_1_7_16_7_1_6_1_5_1_3_5_1_1_2_15_8_4_7_6_6_2_1_8_8_6_6_8_6_5_5_1_5_12_2_2_16_8_12_15_2_6_8_12_10_3_16_12_14_12_11_7_7_5_8_2_1_2_1_4_16_11_5_3_12_18_16_6_3_3_6_6_8_6_8_8_16_5_13_8_17_12_8_17_4_2_1_11_5_17_14_3_4_5_2_7_5_1_15_13_4_1_3_2_17_8_17_2_8_6_8_17_3_5_13_5_7_5_1_7_14_4_3_2_3_16_8_18_1_11_12_12_18_8_5_15_2_5_15_5_8_8_7_18_14_5_18_10_8_6_3_6_5_17_3_7_12_12_3_16_4_1_6_7_13_2_16_3_3_14_6_10_2_13_8_1_5_7_6_2_4_13_12_3_7_8_11_2_4_14_11_5_8_5_8_14_10_17_5_2_2_6_6_12_6_3_17_7_5_15_6_2_8_5_12_3_8_1_2_7_3_14_15_2_8_5_3_11_5_1_5_7_7_4_18_8_13_3_1_7_16_11_12_1_14_7_4_17_2_4_6_5_7_3_4_1_11_5_11_1_4_8_1_6_8_8_1_2_17_7_16_15_1_15_13_3_16_6_2_1_2_7_1_6_2_8_15_8_15_16_4_3_16_2_4_7_2_15_1_8_6_6_1_7_3_6_17_8_13_2_7_11_1_6_2_1_6_2_4_3_3_11_11_3_6_17_6_4_5_3_16_4_5_15_5_10_6_13_16_13_18_4_4_2_3_5_17_17_3_11_10_2_10_4_8_6_15_5_1_5_16_13_3_7_6_11_2_16_5_5_8_2_18_3_8_8_3_10_2_5_6_12_13_11_6_5_14_5_2_4_8_1_16_5_8_4_7_13_7_3_13_15_14_5_2_7_3_10_15_3_5_5_6_6_16_14_5_8_8_8_17_7_4_2_15_3_17_1_8_6_14_7_1_6_3_8_1_1_5_1_4_5_6_12_15_12_7_13_13_1</t>
   </si>
   <si>
     <t>7_7_7_7</t>
@@ -255,7 +255,7 @@
     <t>2_8_4_7_2_7_1_7_8_7_7_4_2_5_6_6_1_2_3_3_5_8_8_2_2_8_8_6_8_3_3_7_4_6_6_1_4_1_7_7_6_8_2_6_5_3_5_2_4_7_7_8_7_8_2_8_8_4_8_8_8_8_5_5_4_7_7_2_1_4_4_4_4_2_2_7_1_8_8_8_4_5_5_5_7_2_7_5_5_5_1_2_6_7_8_3_8_7_7_5_6_5_7_5_8_3_4_6_4_2_2_3_2_5_3_3_2_8_6_5_3_5_2_2_1_6_8_7_6_2_2_2_8_2_3_4_6_5_5_3_3_2_6_6_3_7_2_4_2_7_4_5_6_1_6_8_7_7_6_6_8_3_7_2_8_5_8_7_6_5_8_2_8_1_7_3_7_5_3_6_5_5_3_3_8_2_4_1_3_8_6_4_1_1_3_3_8_3_2_2_3_3_2_4_6_8_2_2_7_8_3_3_2_2_2_6_6_3_7_8_5_2_2_8_4_1_3_1_5_8_8_3_2_1_5_2_2_1_7_4_8_8_6_6_3_5_1_6_3_6_3_7_5_6_5_5_7_4_6_3_6_5_4_8_5_1_7_7_6_5_8_4_5_6_3_3_1_8_8_2_3_5_2_5_5_6_1_1_2_5_6_3_8_4_2_2_7_1_1_3_5_1_8_7_8_6_2_2_5_3_6_5_3_6_6_6_6_8_4_3_8_3_3_3_2_8_8_3_6_4_1_5_2_2_5_5_5_1_6_2_1_1_5_5_8_8_6_1_6_6_7_1_8_5_1_8_5_7_3_5_6_6_2_3_2_1_7_1_1_3_1_6_4_6_1_6_7_8_6_3_8_8_1_1_6_3_2_3_6_2_3_6_7_1_3_3_3_7_7_1_8_6_1_8_1_4_8_8_8_6_6_2_8_6_2_3_3_1_3_7_7_3_5_2_4_2_6_7_3_7_8_6_8_3_3_3_5_3_3_7_7_5_5_3_3_7_7_3_1_1_1_4_3_5_7_2_4_3_4_5_1_5_4_4_6_8_2_7_5_3_7_4_4_8_3_8_2_7_8_7_7_5_7_3_6_5_6_3_2_8_8_3_7_7_1_7_4_3_2_6</t>
   </si>
   <si>
-    <t>13_6_3_12_5_5_5_4_4_3_11_3_8_8_8_3_5_7_8_8_5_5_8_17_5_2_1_14_4_4_3_8_4_15_13_13_13_13_13_5_5_5_5_17_12_8_6_6_6_18_8_18_5_2_7_6_5_5_7_15_13_2_2_4_4_16_3_8_14_7_3_8_3_3_5_8_17_18_16_1_8_7_3_7_8_3_5_5_16_3_3_8_18_2_2_13_8_15_11_4_4_5_5_6_4_4_3_5_1_1_16_1_1_1_3_8_1_12_2_4_6_3_6_5_14_5_8_15_1_1_13_12_5_6_6_8_6_8_17_7_16_6_7_16_9_9_9_5_5_5_2_2_16_2_2_2_6_6_3_3_1_4_4_15_9_13_13_7_7_7_17_18_2_5_12_4_2_6_2_7_8_14_7_6_6_4_3_17_8_1_11_1_12_15_8_7_7_8_8_7_12_5_5_11_11_8_5_1_6_18_8_15_15_8_2_4_3_15_7_3_16_5_7_18_13_5_7_3_7_16_16_4_13_13_13_7_15_15_1_1_1_1_3_2_7_8_3_16_16_11_2_2_13_13_5_18_5_5_14_14_5_4_4_7_11_11_14_7_1_5_5_5_12_16_16_15_2_1_8_8_7_12_9_5_8_12_12_2_8_14_14_14_2_13_16_4_1_18_18_5_6_12_12_4_4_2_17_17_1_4_6_12_5_5_8_6_6_11_11_11_5_5_12_12_6_17_3_3_5_12_12_12_17_2_2_2_4_7_7_17_16_13_13_13_14_6_3_3_16_1_1_1_4_17_2_2_9_12_4_1_2_11_4_7_8_11_12_1_11_6_5_7_14_14_18_17_15_18_2_2_2_4_3_3_17_15_8_4_2_2_8_1_7_7_7_17_7_18_18_5_9_3_1_3_9_15_8_5_4_4_5_5_6_2_18_7_4_13_18_18_14_7_11_11_5_8_2_2_2_18_2_1_6_11_2_14_8_14_17_5_5_5_5_1_14_8_9_9_4_11_11_11_3_3_3_18_2_7_8_5_12_8_14_2_2_2_12_6_18_4_1_1_8_8_8_8_7_1_9_9_3_7_7_3_7_1_1_3_3_12_8_11_11_5_6_11_1_11_4_4</t>
+    <t>15_12_15_6_13_12_8_3_1_6_13_8_1_7_16_3_11_5_14_7_1_3_7_1_6_18_14_7_16_5_8_18_6_13_13_5_6_5_14_1_15_13_6_2_12_5_7_8_3_14_7_1_1_8_1_7_17_7_2_10_1_5_2_11_5_6_1_8_6_13_8_8_1_1_3_8_17_2_7_3_6_10_3_12_8_15_18_5_18_2_7_4_13_5_1_7_4_14_10_5_1_2_18_1_8_1_14_10_8_6_8_8_7_17_5_4_5_4_11_7_3_16_17_6_14_15_15_2_2_15_13_12_1_2_18_11_5_8_7_5_1_11_15_6_6_10_18_2_6_1_8_3_2_11_1_10_3_6_11_4_3_2_3_3_1_16_4_6_8_5_8_8_4_18_1_10_2_18_5_5_11_8_3_16_13_2_6_1_4_2_1_5_6_4_8_5_7_18_7_14_5_7_1_14_3_3_16_6_1_16_6_3_11_4_12_14_17_2_14_16_12_2_6_5_8_17_6_13_4_10_2_3_11_7_13_6_3_17_17_1_4_5_4_2_7_18_5_4_1_5_8_8_4_12_5_6_4_12_6_7_7_3_10_4_10_4_7_6_2_5_5_18_4_10_1_2_5_6_2_12_6_13_7_10_7_7_8_6_1_1_13_14_5_2_13_16_7_10_7_5_3_2_6_3_15_1_2_1_2_3_8_8_7_18_6_6_7_7_7_10_8_16_10_2_2_11_12_7_7_13_8_2_18_12_18_12_11_15_3_13_8_5_2_3_16_14_7_18_11_5_7_1_1_7_5_2_2_1_17_2_16_2_7_1_8_7_8_8_3_2_16_5_4_12_18_3_18_8_2_8_6_6_8_8_4_8_14_6_18_6_13_2_1_3_16_12_10_4_7_17_8_4_4_8_4_15_2_13_3_7_15_3_3_6_1_3_1_7_6_4_7_4_8_10_1_11_11_13_8_17_2_8_7_16_1_4_17_2_6_10_8_8_1_13_2_16_2_4_3_15_8_2_15_10_7_1_6_8_15_2_5_8_6_12_5_4_5_13_16_1_7_8_6_2_3_2_1_1_10_7_17_5_3_4_6_4_8_6_4_4_6_3_4_4_2_10_8_8_8_18</t>
   </si>
   <si>
     <t>6_6_6</t>
@@ -495,12 +495,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -219,7 +219,7 @@
     <t>6_5_5_5_8_3_5_3_7_3_6_3_6_2_2_2_7_5_8_2_4_6_4_5_6_8_1_8_5_4_5_5_1_7_7_7_4_4_3_8_2_8_7_2_3_3_1_7_1_1_3_1_5_7_1_6_4_7_4_2_6_6_4_4_7_7_8_7_8_8_4_5_3_8_4_8_3_3_7_4_7_8_7_6_4_1_7_1_8_2_6_1_2_6_6_2_7_2_5_4_1_4_1_5_7_8_7_8_3_7_2_5_7_7_7_3_5_2_2_2_7_7_8_8_6_3_2_1_8_6_2_8_5_1_8_4_2_2_2_6_2_6_5_1_1_1_4_3_2_2_3_1_1_1_4_1_3_7_1_8_5_2_3_7_2_5_6_4_4_6_5_2_2_7_5_6_6_6_6_2_5_1_5_4_2_2_6_3_7_3_3_5_7_8_2_2_7_8_6_6_3_3_2_4_6_6_7_2_6_8_8_3_6_7_8_7_4_6_4_7_6_1_5_2_3_7_5_5_5_5_7_7_4_7_8_8_8_8_8_7_3_1_3_6_2_5_6_4_7_2_4_2_2_8_2_6_1_6_3_6_4_2_4_2_7_7_1_6_5_6_7_3_3_5_1_4_3_3_4_4_4_6_7_2_7_5_5_6_3_4_3_7_6_2_2_8_5_3_6_1_4_1_1_3_3_3_6_6_4_7_8_8_6_8_2_1_4_1_1_8_2_1_2_7_2_3_4_7_2_5_3_6_5_7_7_3_7_1_1_6_3_6_6_1_7_7_3_1_5_1_6_4_2_5_5_6_5_8_2_4_4_2_5_5_6_4_4_4_3_1_2_1_3_6_3_6_8_5_2_7_2_8_4_2_7_2_7_7_3_6_8_3_5_2_4_3_8_3_2_1_6_3_3_2_2_2_1_8_8_6_2_7_1_3_3_5_4_8_2_5_5_6_6_6_5_1_7_2_3_3_3_2_8_8_3_5_8_2_5_3_2_8_6_6_7_7_2_3_4_4_5_5_8_8_6_5_8_1_5_5_5_5_4_7_5_7_7_8_4_6_6_2_1_5_7_4_8_8_7_6_6_8_5_2_3_8_3_3_7_5_5_5_2_8_8_6_6_2_7_1</t>
   </si>
   <si>
-    <t>7_1_5_3_5_1_1_2_13_5_15_17_8_3_5_6_3_16_6_8_1_13_3_3_11_4_4_4_15_5_5_2_2_4_5_8_6_3_7_1_7_17_4_14_12_13_3_4_15_5_4_4_2_12_3_5_4_1_7_17_5_7_5_8_1_4_4_5_2_17_5_5_7_5_7_6_5_8_6_7_6_6_7_7_1_17_16_11_5_6_2_3_5_18_7_1_6_8_1_11_2_3_2_2_16_8_1_16_2_16_4_7_3_12_10_14_8_6_5_4_7_15_1_1_4_12_11_8_2_5_10_2_4_5_5_8_4_10_12_4_17_7_5_17_8_3_7_10_3_12_18_8_15_16_3_7_8_2_8_3_7_2_5_4_11_17_5_5_2_6_8_6_6_14_1_11_8_4_8_3_7_6_5_2_17_4_17_2_6_6_2_1_16_2_7_7_15_11_14_10_18_7_11_5_15_4_7_11_6_15_16_7_17_5_7_7_7_4_1_13_15_5_15_3_8_3_7_11_5_15_2_4_7_7_2_17_8_8_13_1_6_12_1_2_6_3_18_3_3_13_1_5_8_4_12_8_14_3_6_4_12_11_18_11_14_1_8_3_12_14_4_13_2_4_17_18_2_2_10_16_5_2_8_7_17_8_4_14_4_1_6_3_12_3_5_1_2_4_12_7_8_1_5_17_7_2_13_4_5_14_8_5_5_6_11_17_15_3_2_11_1_5_18_13_6_3_2_4_12_6_16_4_16_5_15_3_3_2_8_1_7_8_4_4_8_8_6_13_13_15_8_3_4_7_8_7_5_8_2_12_13_3_6_7_11_1_4_1_6_6_17_3_2_1_5_3_6_13_16_10_6_8_3_18_18_2_13_3_17_8_6_15_2_6_14_3_5_13_2_10_3_3_4_4_1_15_2_6_5_3_5_16_13_10_2_15_5_6_10_1_5_8_4_7_1_7_5_6_7_1_6_14_13_10_1_3_3_8_17_10_2_6_10_5_1_2_6_8_8_11_7_5_5_7_6_2_7_4_5_17_6_7_8_15_11_8_13_6_7_7_13_8_6_8_12_10_15_8_6_5_11_2_6_14_6_13_11_2_14_18_15_3_16_4_16_12_3_12_1_1</t>
+    <t>8_8_5_1_8_4_16_4_3_8_4_7_3_5_5_15_2_13_7_1_5_1_1_2_1_1_4_2_1_2_8_4_3_7_7_13_2_7_8_5_2_1_14_5_7_1_8_11_7_4_1_8_3_1_4_6_6_8_2_3_4_7_1_8_5_12_7_5_1_14_5_7_5_7_4_16_5_1_8_1_5_5_3_8_5_5_8_8_3_3_7_3_4_7_6_14_7_2_2_2_2_6_4_2_5_6_3_1_14_5_1_7_6_2_2_5_4_3_14_5_11_7_4_4_4_18_6_6_6_2_1_2_5_1_6_2_1_2_5_4_7_3_2_3_6_8_5_1_1_8_7_8_5_16_6_7_2_2_5_3_7_5_7_3_5_6_6_3_5_2_4_5_8_4_1_3_2_10_4_4_7_2_6_7_4_3_4_8_6_12_6_5_6_7_2_2_6_1_3_4_8_8_2_8_7_5_5_6_5_3_3_17_4_4_4_5_7_8_3_7_2_8_5_13_6_3_17_5_7_5_8_2_6_11_3_2_6_15_3_3_1_4_5_3_2_5_4_3_2_10_5_3_6_17_1_6_4_4_6_3_6_5_3_8_4_1_5_4_7_14_6_2_7_4_5_3_1_5_5_16_7_6_1_4_2_5_10_5_4_1_8_10_3_1_8_3_17_3_4_3_3_4_6_6_7_6_6_6_14_4_2_8_5_7_8_2_1_1_4_8_8_5_3_6_2_6_7_6_13_2_7_7_5_8_1_2_8_8_7_4_8_3_4_7_3_7_10_1_2_5_2_2_6_17_4_7_5_2_2_3_5_14_5_6_6_18_7_2_2_8_8_4_3_2_7_3_3_5_3_12_6_8_2_5_6_2_18_7_2_10_6_1_4_6_3_5_4_3_2_8_16_6_6_10_6_2_4_3_4_6_3_1_2_5_13_7_2_4_4_6_4_6_8_7_1_3_1_8_5_8_17_3_2_3_4_1_4_6_3_8_1_11_7_8_8_7_3_2_4_7_6_8_1_6_17_6_2_4_4_2_4_4_6_2_3_4_4_10_5_8_7_7_3_1_3_1_8_2_5_16_7_3_4_3_6_15_1_6_2_4_4_8_1_7_2_3_7_5_1_3</t>
   </si>
   <si>
     <t>5_5_5_5</t>
@@ -228,7 +228,7 @@
     <t>5_3_1_3_6_1_6_8_8_4_4_4_1_3_2_6_5_8_8_4_3_3_7_1_7_2_1_2_4_6_7_5_4_4_6_7_5_6_2_1_1_2_6_8_7_1_7_7_2_5_4_1_1_2_7_8_8_6_5_3_7_7_1_1_1_5_6_5_7_2_6_7_3_4_7_3_7_3_5_2_8_8_1_6_1_4_8_2_8_6_4_7_7_7_7_7_5_4_7_5_5_8_8_8_8_8_1_5_1_6_6_3_4_2_7_8_1_1_3_5_7_6_3_2_4_2_2_3_5_2_7_6_6_2_5_1_8_8_7_5_3_3_4_1_6_3_3_8_2_8_6_1_4_4_5_8_8_5_5_3_1_4_3_4_4_7_6_5_5_1_5_5_3_6_5_1_2_3_2_6_6_6_7_7_7_4_4_7_1_7_6_6_1_8_3_3_3_3_7_5_6_2_1_7_7_8_7_1_7_1_8_3_3_8_6_1_7_1_5_5_5_2_2_3_4_4_6_1_6_8_8_3_2_5_5_2_7_8_6_6_5_3_3_3_6_4_6_1_4_6_7_4_7_8_4_1_6_5_5_1_4_3_7_2_2_6_1_3_1_4_5_8_2_3_6_3_8_1_3_8_4_2_7_8_3_2_5_5_1_5_5_3_8_8_4_5_6_6_4_2_2_2_5_4_8_5_5_5_1_1_4_1_5_2_3_6_7_8_1_2_3_5_3_4_7_3_6_6_4_2_1_6_1_2_7_2_2_2_7_5_6_1_8_6_6_6_2_2_2_8_8_6_8_6_8_8_2_3_3_6_5_4_4_1_8_4_6_4_2_4_7_8_2_3_7_6_5_5_8_5_1_6_8_5_2_7_1_5_8_2_1_4_4_8_8_1_7_1_5_2_1_6_4_4_5_5_5_3_8_4_1_8_7_4_1_3_7_7_1_7_5_4_4_5_4_7_8_8_3_8_6_1_4_3_7_1_1_3_3_3_4_7_7_7_7_2_1_3_2_5_4_7_8_4_8_2_5_4_5_3_3_6_3_6_7_7_7_8_7_2_6_8_5_5_5_5_4_3_8_5_6_4_6_7_8_4_4_8_8_6_8_3_8_1_4_5_8_7_8_4</t>
   </si>
   <si>
-    <t>11_6_2_8_3_6_10_8_1_13_7_3_5_7_3_1_3_3_6_5_3_5_8_6_5_10_7_4_1_6_18_7_3_3_15_6_3_1_7_18_6_1_7_3_1_1_4_3_17_15_12_14_7_5_17_8_3_1_3_8_1_3_2_4_2_3_17_14_3_1_6_6_2_15_8_5_8_14_11_3_7_16_2_5_8_3_17_5_6_6_10_4_6_3_12_7_2_4_13_1_5_1_14_3_8_6_4_2_6_6_8_4_17_15_4_16_7_1_2_8_11_10_5_3_6_10_16_18_14_3_17_3_2_6_3_4_17_16_15_3_6_7_12_4_13_17_1_1_10_3_12_8_14_7_8_5_6_5_8_8_17_4_17_10_3_8_6_15_2_11_3_16_6_6_8_5_14_6_15_13_16_13_4_16_7_4_17_1_2_5_15_7_4_6_5_13_11_2_18_17_12_1_6_14_18_11_5_7_5_1_3_10_18_2_6_1_6_8_7_8_6_8_15_17_2_6_3_6_8_16_2_6_8_1_2_1_12_1_1_2_1_5_2_8_13_4_6_3_16_16_18_11_2_16_6_6_8_7_1_2_2_11_3_18_15_8_8_18_2_2_2_18_3_8_7_8_2_13_5_7_18_11_8_3_4_13_7_1_6_6_14_4_6_7_18_12_6_4_2_18_16_1_1_2_6_15_12_1_10_6_15_11_17_5_1_15_2_1_6_14_1_2_4_2_1_13_6_7_6_7_3_13_7_12_3_2_15_8_2_10_2_8_12_7_1_8_1_2_17_1_3_1_10_1_8_14_1_18_6_6_17_7_5_7_6_6_3_7_4_7_2_6_17_3_4_1_6_14_5_5_3_8_5_16_16_13_5_11_18_7_16_8_6_17_3_15_1_5_5_18_6_7_14_2_6_6_12_2_3_5_10_7_7_3_13_6_2_17_13_18_2_1_7_15_7_1_14_18_5_6_7_16_8_18_4_1_3_7_1_2_1_5_3_6_8_4_4_6_7_14_14_8_1_18_13_4_3_7_5_2_12_5_8_8_1_2_6_1_10_8_6_6_6_8_2_1_6_12_4_3_7_1_2_6_6_3_16_3_1_1_2_4_5_3_8_2_5_2_7_5</t>
+    <t>15_6_3_6_7_5_5_15_7_6_5_4_6_1_1_4_5_1_3_4_4_3_4_13_5_7_1_6_4_6_3_8_4_1_6_13_3_4_7_3_5_2_7_1_4_3_1_1_5_1_8_16_6_4_2_6_5_4_8_7_3_2_6_2_4_11_1_6_1_6_8_14_4_3_7_13_7_7_3_2_7_18_6_6_3_4_8_2_3_3_7_7_2_2_4_7_7_4_2_4_2_5_3_4_5_1_6_1_18_5_11_7_4_8_3_4_4_4_1_6_2_1_1_6_2_7_16_3_5_3_1_7_5_4_3_7_1_4_1_2_1_4_8_7_4_5_3_7_4_3_6_7_1_1_5_3_6_2_5_5_8_1_3_7_8_7_7_8_1_2_3_3_2_4_3_6_7_1_4_4_2_5_4_1_2_12_4_3_6_2_2_7_4_16_5_11_7_7_2_2_1_8_7_18_5_8_7_15_7_1_5_5_6_1_3_7_2_4_5_2_11_5_8_4_6_5_6_8_2_6_4_6_6_7_2_5_6_3_11_7_11_7_2_1_18_3_5_6_16_7_8_18_4_2_5_8_3_7_7_5_8_1_3_2_8_2_4_3_6_5_2_14_7_5_2_7_6_3_3_8_10_7_1_1_7_2_5_6_5_5_2_7_3_12_3_18_6_6_6_17_3_1_4_1_7_1_4_6_3_7_1_8_6_5_7_8_3_4_2_7_2_13_6_7_8_1_4_8_4_1_1_1_1_8_4_3_2_7_6_3_4_3_3_3_2_8_1_8_1_4_16_5_4_5_8_6_4_4_8_5_8_13_5_4_6_8_4_4_7_7_5_8_7_5_7_4_5_4_3_8_6_6_8_7_1_6_4_7_8_8_17_4_6_4_2_8_4_7_3_1_4_10_7_6_6_8_4_5_2_14_2_2_5_2_3_7_1_4_3_8_3_3_2_2_12_5_4_4_6_1_3_17_6_7_6_17_1_5_5_7_8_1_7_5_7_3_4_16_5_2_3_2_7_1_4_7_7_2_3_1_1_6_5_3_1_4_3_5_4_7_5_1_5_5_5_3_16_4_8_15_5_5_6_6_3_3_6_6_5_16_5_3_2_17_6_1_5_4_4_2</t>
   </si>
   <si>
     <t>8_8_8_8</t>
@@ -237,7 +237,7 @@
     <t>6_4_1_2_8_4_6_6_1_1_7_7_7_4_7_5_8_5_8_5_4_4_3_6_8_4_2_1_3_8_2_2_1_1_6_7_8_4_6_3_3_8_8_1_2_7_4_3_5_7_1_1_3_8_6_6_6_8_8_6_1_1_3_3_3_6_2_7_2_4_7_3_5_4_3_7_8_2_6_3_2_5_1_8_2_1_6_4_2_4_2_2_1_2_1_7_7_8_4_4_4_4_4_6_5_1_8_2_2_6_2_7_5_7_5_3_3_5_5_7_6_4_7_4_7_4_1_5_8_6_1_5_5_6_7_1_8_5_6_3_1_6_2_7_2_1_1_4_4_6_8_8_6_1_6_1_4_4_5_3_1_2_2_1_3_7_7_6_5_1_3_3_7_6_6_7_3_6_1_8_4_4_6_6_2_5_3_4_4_2_1_3_1_3_8_8_8_4_6_5_3_3_2_3_5_1_6_6_4_5_5_1_2_2_4_7_4_6_4_1_7_4_7_8_8_8_1_1_1_2_6_3_5_6_6_5_1_1_6_6_3_8_6_5_5_3_5_8_1_1_5_1_3_3_2_5_2_1_5_6_8_3_3_1_2_1_5_3_3_8_2_4_6_6_5_4_5_5_1_4_2_8_5_5_7_3_7_8_1_8_8_6_1_6_1_2_3_4_1_3_2_8_1_2_2_4_5_3_6_6_5_1_1_2_4_4_5_1_3_3_6_1_3_5_5_8_3_4_7_5_7_6_2_8_6_8_2_8_3_8_4_4_4_7_6_1_3_7_2_6_8_8_8_7_1_8_6_2_5_2_6_1_3_3_8_8_1_4_2_6_6_2_5_3_6_6_2_2_1_4_5_2_2_4_7_2_4_6_3_3_7_3_4_8_8_6_8_7_4_2_3_4_6_3_8_5_7_7_6_1_1_7_8_4_8_8_4_3_6_4_2_7_2_2_6_2_4_7_3_1_5_5_3_8_3_3_3_2_5_2_4_1_2_4_8_7_1_7_5_4_2_7_1_6_2_4_7_5_3_4_6_5_8_7_8_1_5_5_6_2_2_2_4_5_2_1_3_7_7_1_7_3_2_5_6_3_4_1_2_6_6_4_5_8_4_6_2_6_8_5</t>
   </si>
   <si>
-    <t>1_2_4_8_3_17_7_6_2_4_15_5_3_17_1_1_8_14_4_12_1_17_2_17_8_5_2_8_10_14_13_7_16_2_10_3_2_2_8_5_6_8_8_3_10_8_2_3_2_3_13_8_2_2_18_11_6_1_8_1_3_5_3_6_14_3_5_8_15_1_5_12_3_1_10_13_12_3_5_17_8_1_6_5_11_1_7_4_5_7_7_13_3_7_13_3_3_12_8_7_18_7_2_4_6_8_4_5_1_10_3_3_5_12_17_7_7_7_5_3_14_5_4_16_16_16_7_8_3_13_7_3_15_5_2_7_1_5_4_7_8_10_8_8_7_15_16_8_10_8_6_6_8_2_15_2_6_6_2_3_5_17_2_11_6_2_12_4_8_3_15_1_3_2_7_3_8_7_16_3_2_17_6_7_7_7_1_3_14_3_10_18_8_4_8_12_1_5_8_13_1_2_8_2_6_14_5_15_8_5_17_13_17_17_8_8_6_2_8_3_17_6_11_3_2_4_4_1_4_15_10_6_8_5_15_17_5_6_4_1_3_8_11_4_6_3_8_3_6_18_4_14_4_1_17_5_3_6_4_8_13_2_2_4_2_3_7_18_2_6_16_1_7_16_3_8_18_4_6_3_1_3_16_1_8_8_14_2_4_12_7_1_1_8_5_16_4_6_17_13_5_10_8_18_10_7_10_16_4_18_18_11_1_14_8_5_15_12_5_5_3_1_11_3_2_16_5_13_17_5_10_16_7_1_8_12_3_2_6_6_2_13_18_5_4_7_10_2_5_4_7_6_5_8_6_7_5_13_6_3_1_12_7_8_6_6_4_6_4_14_18_3_12_4_4_4_15_7_18_2_1_8_5_3_10_2_1_8_2_6_12_3_15_16_3_1_15_1_6_11_3_1_8_2_1_7_8_1_1_16_5_5_7_1_4_3_12_2_12_7_2_2_1_6_7_11_3_12_1_12_6_18_6_14_5_7_2_3_8_12_8_18_12_4_5_5_10_8_3_3_13_6_1_2_4_14_15_7_3_8_4_2_7_6_2_11_16_5_6_6_14_3_8_14_1_7_3_8_14_7_15_8_12_6_5_2_4_17_18_1_11_15_18_12_3_8_3_12_5_1</t>
+    <t>5_8_6_2_4_2_12_7_1_4_8_4_13_4_11_7_2_4_4_15_6_6_8_14_7_3_4_1_7_7_2_7_4_2_2_1_4_5_6_5_4_1_5_5_10_6_6_4_5_5_13_2_8_6_2_4_6_1_6_6_3_2_3_6_4_5_4_7_1_7_8_6_6_17_4_18_3_4_2_16_2_2_8_8_6_8_6_13_2_3_10_1_8_2_5_2_11_7_8_1_4_3_1_1_6_4_12_4_7_11_5_3_6_1_16_7_3_1_12_3_5_3_7_1_6_6_3_6_3_3_1_3_5_2_2_4_6_6_3_1_2_18_6_1_3_7_6_8_8_3_6_4_6_8_8_5_4_5_4_14_5_3_15_7_4_1_5_7_1_3_5_4_1_1_6_6_6_16_7_7_5_4_4_8_17_6_5_18_6_4_1_2_2_2_7_2_4_8_5_12_6_6_8_1_3_5_8_4_3_1_6_1_2_2_2_7_8_3_8_5_7_7_6_5_7_1_6_6_11_4_2_1_5_2_1_15_6_2_1_5_3_8_2_3_4_6_3_3_12_3_15_1_8_6_6_16_2_1_1_2_7_7_3_4_2_2_4_8_7_8_3_4_6_4_4_17_4_2_4_8_2_6_1_3_7_2_2_3_5_3_4_7_16_3_4_5_5_10_3_2_1_3_2_1_18_6_10_5_8_8_7_2_5_6_6_2_10_4_7_8_1_7_18_3_7_4_1_8_6_6_8_15_4_8_5_4_6_2_8_4_5_2_1_1_13_7_7_2_5_3_6_10_2_7_5_6_1_7_8_8_3_4_6_7_8_5_3_5_4_1_6_2_3_3_12_7_8_8_4_5_4_6_2_7_4_1_7_2_3_4_6_7_15_3_3_3_12_7_4_6_1_1_1_3_3_13_7_2_1_8_1_4_5_4_1_4_4_1_8_14_7_3_3_5_6_6_6_7_6_1_8_4_1_3_8_1_1_5_5_4_4_8_7_5_1_4_2_2_11_7_4_6_6_2_3_18_2_2_3_4_3_8_2_1_7_7_7_4_4_2_2_8_6_2_2_3_8_6_2_3_4_2_8_6_8_3_4_7_8_6_3_3_6_2_8_18_7_8_14_6</t>
   </si>
   <si>
     <t>6_6_6_6</t>
@@ -246,7 +246,7 @@
     <t>3_8_7_3_5_4_2_1_7_7_3_8_6_5_3_4_8_3_2_2_5_3_7_7_2_3_2_5_5_5_5_1_4_1_6_7_1_1_8_8_7_7_2_2_5_2_7_1_5_3_5_1_6_6_8_3_4_4_2_2_4_5_8_1_4_2_1_1_3_3_3_1_3_2_2_2_2_5_1_7_7_5_2_7_8_1_4_5_5_6_7_2_4_1_7_8_5_3_1_1_4_8_8_5_2_8_2_2_8_6_7_8_6_7_4_7_1_3_3_4_6_4_5_5_3_8_5_2_3_5_7_8_5_6_8_6_8_5_1_6_2_4_7_7_4_5_7_6_3_7_1_4_4_5_1_2_1_5_8_1_3_4_2_7_8_1_4_7_3_8_1_2_4_5_7_4_7_7_6_8_8_6_5_7_7_2_1_2_7_7_4_4_3_5_5_8_4_3_7_1_8_1_3_8_7_5_2_5_6_4_5_6_1_8_6_4_2_1_1_4_4_1_1_4_7_8_5_5_4_3_2_6_3_6_6_1_2_5_3_7_5_3_6_5_8_3_2_5_1_5_7_1_8_8_6_6_6_5_7_7_6_6_5_3_5_2_5_6_6_2_4_5_2_5_8_3_2_1_2_7_4_7_4_5_6_5_8_3_4_4_2_2_4_4_3_8_8_7_5_4_5_6_1_8_7_7_8_4_7_7_5_2_6_4_5_8_2_6_3_2_2_5_5_7_7_6_2_2_7_8_8_8_6_6_5_1_1_2_7_8_8_2_4_2_8_2_7_4_8_5_6_6_2_3_6_4_3_3_3_6_6_2_1_1_1_1_4_1_3_8_7_3_2_3_8_8_7_7_5_6_4_4_4_3_3_3_3_3_6_5_8_4_4_2_8_5_6_1_1_1_6_3_3_8_1_4_8_6_4_1_5_5_8_2_4_3_4_5_8_2_8_8_8_2_7_4_7_3_6_4_4_8_6_2_1_1_8_4_2_1_8_8_2_5_3_3_7_3_5_5_6_6_5_5_2_2_2_1_1_3_2_5_6_6_3_5_6_1_1_5_8_3_8_8_2_3_5_4_8_1_4_4_5_3_2_7_7_2_5_7_2_6_5_7_3_3_3_7_3_6</t>
   </si>
   <si>
-    <t>5_2_15_16_8_7_14_1_5_8_3_1_6_10_5_12_17_2_2_13_5_5_1_4_6_7_4_6_3_11_1_4_14_5_14_18_8_6_11_7_14_8_7_5_10_7_6_3_8_11_7_1_7_16_7_1_6_1_5_1_3_5_1_1_2_15_8_4_7_6_6_2_1_8_8_6_6_8_6_5_5_1_5_12_2_2_16_8_12_15_2_6_8_12_10_3_16_12_14_12_11_7_7_5_8_2_1_2_1_4_16_11_5_3_12_18_16_6_3_3_6_6_8_6_8_8_16_5_13_8_17_12_8_17_4_2_1_11_5_17_14_3_4_5_2_7_5_1_15_13_4_1_3_2_17_8_17_2_8_6_8_17_3_5_13_5_7_5_1_7_14_4_3_2_3_16_8_18_1_11_12_12_18_8_5_15_2_5_15_5_8_8_7_18_14_5_18_10_8_6_3_6_5_17_3_7_12_12_3_16_4_1_6_7_13_2_16_3_3_14_6_10_2_13_8_1_5_7_6_2_4_13_12_3_7_8_11_2_4_14_11_5_8_5_8_14_10_17_5_2_2_6_6_12_6_3_17_7_5_15_6_2_8_5_12_3_8_1_2_7_3_14_15_2_8_5_3_11_5_1_5_7_7_4_18_8_13_3_1_7_16_11_12_1_14_7_4_17_2_4_6_5_7_3_4_1_11_5_11_1_4_8_1_6_8_8_1_2_17_7_16_15_1_15_13_3_16_6_2_1_2_7_1_6_2_8_15_8_15_16_4_3_16_2_4_7_2_15_1_8_6_6_1_7_3_6_17_8_13_2_7_11_1_6_2_1_6_2_4_3_3_11_11_3_6_17_6_4_5_3_16_4_5_15_5_10_6_13_16_13_18_4_4_2_3_5_17_17_3_11_10_2_10_4_8_6_15_5_1_5_16_13_3_7_6_11_2_16_5_5_8_2_18_3_8_8_3_10_2_5_6_12_13_11_6_5_14_5_2_4_8_1_16_5_8_4_7_13_7_3_13_15_14_5_2_7_3_10_15_3_5_5_6_6_16_14_5_8_8_8_17_7_4_2_15_3_17_1_8_6_14_7_1_6_3_8_1_1_5_1_4_5_6_12_15_12_7_13_13_1</t>
+    <t>7_7_7_8_1_5_3_6_3_1_1_8_7_8_2_4_6_7_5_16_2_2_1_4_13_5_4_5_6_7_5_2_3_6_7_5_16_6_6_3_3_4_13_4_5_8_6_6_5_4_7_8_1_8_5_8_8_4_5_6_1_4_2_8_3_8_6_3_1_8_8_6_7_6_7_17_3_5_7_5_6_13_6_6_5_2_5_8_15_4_3_5_2_3_2_2_5_3_6_6_16_7_8_6_3_8_10_6_18_6_2_3_8_8_3_13_7_2_1_6_7_8_7_7_7_11_5_8_5_8_12_6_8_8_5_14_7_3_5_7_11_7_5_5_5_7_5_4_11_5_2_4_2_17_4_7_3_4_8_2_5_4_5_5_5_6_8_15_1_7_2_3_3_3_5_8_3_12_6_5_7_1_6_7_3_8_5_8_5_12_6_7_4_7_8_3_8_4_5_6_3_5_3_7_4_4_8_6_3_6_7_4_3_6_5_3_5_4_5_7_2_11_3_4_7_4_11_6_7_1_5_3_2_16_4_1_1_3_4_4_5_4_6_4_6_14_6_8_2_8_3_1_2_2_1_2_6_2_4_2_18_7_2_10_4_3_2_8_4_8_8_2_3_5_4_6_7_7_5_3_8_8_18_2_5_5_12_7_6_8_12_4_13_5_3_7_2_4_6_7_1_3_5_18_6_6_3_3_6_2_3_13_2_8_6_5_1_6_8_3_5_7_13_2_8_1_3_6_6_4_4_6_4_4_6_4_2_8_5_1_3_7_1_2_8_8_4_8_12_6_7_1_6_5_1_7_5_5_5_3_5_6_4_4_18_4_2_3_18_7_8_8_6_5_11_4_5_4_6_8_7_2_2_1_2_1_1_8_5_8_1_5_4_15_6_6_6_3_5_6_7_8_7_1_2_8_6_7_1_4_17_4_6_1_3_8_16_6_3_8_4_2_6_3_2_3_1_5_2_6_5_3_4_3_1_8_3_5_18_5_6_8_7_7_3_7_6_3_2_5_6_7_6_7_6_14_3_1_4_8_3_4_4_2_5_6_3_5_8_6_6_8_10_6_7_7_7_5_4_18_7_13_7_1_8_11_4_6_1_2_5_6_2_3_3_4_2_3_6_5</t>
   </si>
   <si>
     <t>7_7_7_7</t>
@@ -255,7 +255,7 @@
     <t>2_8_4_7_2_7_1_7_8_7_7_4_2_5_6_6_1_2_3_3_5_8_8_2_2_8_8_6_8_3_3_7_4_6_6_1_4_1_7_7_6_8_2_6_5_3_5_2_4_7_7_8_7_8_2_8_8_4_8_8_8_8_5_5_4_7_7_2_1_4_4_4_4_2_2_7_1_8_8_8_4_5_5_5_7_2_7_5_5_5_1_2_6_7_8_3_8_7_7_5_6_5_7_5_8_3_4_6_4_2_2_3_2_5_3_3_2_8_6_5_3_5_2_2_1_6_8_7_6_2_2_2_8_2_3_4_6_5_5_3_3_2_6_6_3_7_2_4_2_7_4_5_6_1_6_8_7_7_6_6_8_3_7_2_8_5_8_7_6_5_8_2_8_1_7_3_7_5_3_6_5_5_3_3_8_2_4_1_3_8_6_4_1_1_3_3_8_3_2_2_3_3_2_4_6_8_2_2_7_8_3_3_2_2_2_6_6_3_7_8_5_2_2_8_4_1_3_1_5_8_8_3_2_1_5_2_2_1_7_4_8_8_6_6_3_5_1_6_3_6_3_7_5_6_5_5_7_4_6_3_6_5_4_8_5_1_7_7_6_5_8_4_5_6_3_3_1_8_8_2_3_5_2_5_5_6_1_1_2_5_6_3_8_4_2_2_7_1_1_3_5_1_8_7_8_6_2_2_5_3_6_5_3_6_6_6_6_8_4_3_8_3_3_3_2_8_8_3_6_4_1_5_2_2_5_5_5_1_6_2_1_1_5_5_8_8_6_1_6_6_7_1_8_5_1_8_5_7_3_5_6_6_2_3_2_1_7_1_1_3_1_6_4_6_1_6_7_8_6_3_8_8_1_1_6_3_2_3_6_2_3_6_7_1_3_3_3_7_7_1_8_6_1_8_1_4_8_8_8_6_6_2_8_6_2_3_3_1_3_7_7_3_5_2_4_2_6_7_3_7_8_6_8_3_3_3_5_3_3_7_7_5_5_3_3_7_7_3_1_1_1_4_3_5_7_2_4_3_4_5_1_5_4_4_6_8_2_7_5_3_7_4_4_8_3_8_2_7_8_7_7_5_7_3_6_5_6_3_2_8_8_3_7_7_1_7_4_3_2_6</t>
   </si>
   <si>
-    <t>15_12_15_6_13_12_8_3_1_6_13_8_1_7_16_3_11_5_14_7_1_3_7_1_6_18_14_7_16_5_8_18_6_13_13_5_6_5_14_1_15_13_6_2_12_5_7_8_3_14_7_1_1_8_1_7_17_7_2_10_1_5_2_11_5_6_1_8_6_13_8_8_1_1_3_8_17_2_7_3_6_10_3_12_8_15_18_5_18_2_7_4_13_5_1_7_4_14_10_5_1_2_18_1_8_1_14_10_8_6_8_8_7_17_5_4_5_4_11_7_3_16_17_6_14_15_15_2_2_15_13_12_1_2_18_11_5_8_7_5_1_11_15_6_6_10_18_2_6_1_8_3_2_11_1_10_3_6_11_4_3_2_3_3_1_16_4_6_8_5_8_8_4_18_1_10_2_18_5_5_11_8_3_16_13_2_6_1_4_2_1_5_6_4_8_5_7_18_7_14_5_7_1_14_3_3_16_6_1_16_6_3_11_4_12_14_17_2_14_16_12_2_6_5_8_17_6_13_4_10_2_3_11_7_13_6_3_17_17_1_4_5_4_2_7_18_5_4_1_5_8_8_4_12_5_6_4_12_6_7_7_3_10_4_10_4_7_6_2_5_5_18_4_10_1_2_5_6_2_12_6_13_7_10_7_7_8_6_1_1_13_14_5_2_13_16_7_10_7_5_3_2_6_3_15_1_2_1_2_3_8_8_7_18_6_6_7_7_7_10_8_16_10_2_2_11_12_7_7_13_8_2_18_12_18_12_11_15_3_13_8_5_2_3_16_14_7_18_11_5_7_1_1_7_5_2_2_1_17_2_16_2_7_1_8_7_8_8_3_2_16_5_4_12_18_3_18_8_2_8_6_6_8_8_4_8_14_6_18_6_13_2_1_3_16_12_10_4_7_17_8_4_4_8_4_15_2_13_3_7_15_3_3_6_1_3_1_7_6_4_7_4_8_10_1_11_11_13_8_17_2_8_7_16_1_4_17_2_6_10_8_8_1_13_2_16_2_4_3_15_8_2_15_10_7_1_6_8_15_2_5_8_6_12_5_4_5_13_16_1_7_8_6_2_3_2_1_1_10_7_17_5_3_4_6_4_8_6_4_4_6_3_4_4_2_10_8_8_8_18</t>
+    <t>10_3_8_2_3_4_6_13_6_5_6_5_4_8_3_1_7_8_3_5_2_3_6_8_2_17_1_7_7_8_8_8_10_7_4_6_10_4_4_1_6_6_7_5_15_2_6_6_5_2_6_6_2_7_12_5_7_5_8_7_7_4_7_8_5_4_8_2_4_1_6_5_7_8_6_6_18_5_2_1_8_18_6_8_8_3_18_3_6_5_8_1_7_4_2_4_1_1_4_13_7_3_4_3_7_4_3_6_6_7_1_13_3_3_4_5_16_5_2_1_12_7_5_2_4_4_4_2_5_6_13_6_2_3_8_1_3_1_6_6_18_3_8_16_6_2_4_14_6_17_7_1_3_7_3_7_7_11_7_2_8_2_8_5_2_6_10_7_7_7_2_5_1_7_4_1_6_5_8_1_1_18_4_1_8_6_6_4_7_5_7_16_1_1_8_1_15_6_4_6_3_4_2_2_5_2_13_3_8_18_7_6_7_14_7_2_3_2_6_15_5_2_3_3_1_5_18_6_5_3_1_5_4_5_6_7_7_5_5_3_3_13_7_2_6_8_1_10_5_8_4_3_4_8_5_17_1_7_1_5_7_3_5_1_7_4_4_14_6_2_2_6_3_1_6_5_7_7_2_4_4_4_2_8_7_2_10_6_4_5_1_3_3_4_8_2_6_4_2_1_2_1_11_7_5_6_6_3_6_7_2_3_3_8_6_3_17_7_7_1_4_4_7_6_10_4_2_3_5_3_5_1_1_4_8_13_7_4_5_8_6_10_4_4_8_5_6_6_3_4_5_2_7_2_3_1_18_5_2_3_1_6_3_3_1_18_6_8_5_1_5_4_8_2_6_2_1_8_8_2_2_7_6_8_6_5_2_2_8_3_6_5_4_5_4_7_1_7_2_5_6_7_2_6_8_8_10_6_3_6_2_3_6_4_7_3_5_16_7_3_6_5_8_14_3_12_1_6_1_8_4_3_6_7_8_5_13_4_3_6_5_17_4_8_3_6_3_4_7_4_1_2_1_7_1_6_2_1_2_2_4_1_1_5_8_5_7_4_4_6_3_5_5_6_4_8_6_4_6_3_6_4_8_8_1_13_7_5_4_2_4_1_8_3_3_6_5_6_8_3</t>
   </si>
   <si>
     <t>6_6_6</t>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoller" sheetId="1" r:id="rId1"/>
@@ -216,7 +216,7 @@
     <t>1_1_1_1</t>
   </si>
   <si>
-    <t>6_5_5_5_8_3_5_3_7_3_6_3_6_2_2_2_7_5_8_2_4_6_4_5_6_8_1_8_5_4_5_5_1_7_7_7_4_4_3_8_2_8_7_2_3_3_1_7_1_1_3_1_5_7_1_6_4_7_4_2_6_6_4_4_7_7_8_7_8_8_4_5_3_8_4_8_3_3_7_4_7_8_7_6_4_1_7_1_8_2_6_1_2_6_6_2_7_2_5_4_1_4_1_5_7_8_7_8_3_7_2_5_7_7_7_3_5_2_2_2_7_7_8_8_6_3_2_1_8_6_2_8_5_1_8_4_2_2_2_6_2_6_5_1_1_1_4_3_2_2_3_1_1_1_4_1_3_7_1_8_5_2_3_7_2_5_6_4_4_6_5_2_2_7_5_6_6_6_6_2_5_1_5_4_2_2_6_3_7_3_3_5_7_8_2_2_7_8_6_6_3_3_2_4_6_6_7_2_6_8_8_3_6_7_8_7_4_6_4_7_6_1_5_2_3_7_5_5_5_5_7_7_4_7_8_8_8_8_8_7_3_1_3_6_2_5_6_4_7_2_4_2_2_8_2_6_1_6_3_6_4_2_4_2_7_7_1_6_5_6_7_3_3_5_1_4_3_3_4_4_4_6_7_2_7_5_5_6_3_4_3_7_6_2_2_8_5_3_6_1_4_1_1_3_3_3_6_6_4_7_8_8_6_8_2_1_4_1_1_8_2_1_2_7_2_3_4_7_2_5_3_6_5_7_7_3_7_1_1_6_3_6_6_1_7_7_3_1_5_1_6_4_2_5_5_6_5_8_2_4_4_2_5_5_6_4_4_4_3_1_2_1_3_6_3_6_8_5_2_7_2_8_4_2_7_2_7_7_3_6_8_3_5_2_4_3_8_3_2_1_6_3_3_2_2_2_1_8_8_6_2_7_1_3_3_5_4_8_2_5_5_6_6_6_5_1_7_2_3_3_3_2_8_8_3_5_8_2_5_3_2_8_6_6_7_7_2_3_4_4_5_5_8_8_6_5_8_1_5_5_5_5_4_7_5_7_7_8_4_6_6_2_1_5_7_4_8_8_7_6_6_8_5_2_3_8_3_3_7_5_5_5_2_8_8_6_6_2_7_1</t>
+    <t>5_4_6_1_2_4_2_4_2_1_8_2_3_2_5_8_3_5_6_6_4_4_2_1_4_5_5_5_2_2_4_4_4_5_1_1_3_3_2_8_8_2_1_5_5_1_2_4_4_8_1_2_3_1_5_5_3_3_3_1_1_7_7_7_5_5_7_7_3_5_5_1_5_1_1_6_3_4_6_1_5_5_8_1_2_4_3_3_3_8_6_5_2_7_7_2_6_1_7_7_3_5_5_5_5_5_3_1_4_4_6_3_1_1_7_3_6_8_5_6_6_6_8_8_5_2_6_4_3_5_6_7_1_1_2_2_2_4_4_2_4_4_1_2_7_8_2_6_1_5_4_4_6_6_4_1_3_5_8_7_7_2_4_4_3_2_4_7_2_8_3_2_2_3_5_2_6_6_1_1_1_4_3_1_1_1_5_3_7_7_5_8_1_8_8_6_1_5_6_6_4_2_3_7_3_4_2_6_6_8_3_5_2_2_4_6_8_5_8_2_1_6_7_5_4_7_7_1_1_2_2_1_1_1_6_5_2_5_3_3_4_8_8_5_2_4_2_1_1_2_1_1_2_6_4_6_1_2_2_1_6_3_2_2_5_3_7_6_1_8_6_7_1_7_2_3_1_6_6_6_3_3_1_2_4_2_3_3_6_4_5_5_5_2_1_3_4_6_2_2_7_3_3_1_1_8_2_2_8_8_7_6_1_8_6_5_2_1_4_6_6_6_6_3_3_2_2_1_1_5_5_6_1_2_3_2_4_1_1_1_1_5_1_1_5_1_4_1_1_4_2_2_3_1_6_6_2_6_7_3_3_3_3_4_5_5_2_2_5_7_8_5_2_2_2_5_2_2_1_3_5_4_6_3_3_3_6_1_5_4_2_1_5_1_3_3_3_3_4_4_4_2_2_5_2_2_1_5_5_5_7_2_4_5_2_4_1_6_1_5_2_2_4_5_1_1_4_3_4_5_6_2_3_7_8_4_8_8_8_1_4_1_5_4_4_5_5_8_8_8_8_5_2_2_6_1_4_4_5_6_2_5_3_4_1_5_7_8_5_4_1_5_7_1_8_4_1_4_4_2_1_3_5_5_2_1_1_7_4_5_3_8_6_6_2_7_7_4_1_2</t>
   </si>
   <si>
     <t>8_8_5_1_8_4_16_4_3_8_4_7_3_5_5_15_2_13_7_1_5_1_1_2_1_1_4_2_1_2_8_4_3_7_7_13_2_7_8_5_2_1_14_5_7_1_8_11_7_4_1_8_3_1_4_6_6_8_2_3_4_7_1_8_5_12_7_5_1_14_5_7_5_7_4_16_5_1_8_1_5_5_3_8_5_5_8_8_3_3_7_3_4_7_6_14_7_2_2_2_2_6_4_2_5_6_3_1_14_5_1_7_6_2_2_5_4_3_14_5_11_7_4_4_4_18_6_6_6_2_1_2_5_1_6_2_1_2_5_4_7_3_2_3_6_8_5_1_1_8_7_8_5_16_6_7_2_2_5_3_7_5_7_3_5_6_6_3_5_2_4_5_8_4_1_3_2_10_4_4_7_2_6_7_4_3_4_8_6_12_6_5_6_7_2_2_6_1_3_4_8_8_2_8_7_5_5_6_5_3_3_17_4_4_4_5_7_8_3_7_2_8_5_13_6_3_17_5_7_5_8_2_6_11_3_2_6_15_3_3_1_4_5_3_2_5_4_3_2_10_5_3_6_17_1_6_4_4_6_3_6_5_3_8_4_1_5_4_7_14_6_2_7_4_5_3_1_5_5_16_7_6_1_4_2_5_10_5_4_1_8_10_3_1_8_3_17_3_4_3_3_4_6_6_7_6_6_6_14_4_2_8_5_7_8_2_1_1_4_8_8_5_3_6_2_6_7_6_13_2_7_7_5_8_1_2_8_8_7_4_8_3_4_7_3_7_10_1_2_5_2_2_6_17_4_7_5_2_2_3_5_14_5_6_6_18_7_2_2_8_8_4_3_2_7_3_3_5_3_12_6_8_2_5_6_2_18_7_2_10_6_1_4_6_3_5_4_3_2_8_16_6_6_10_6_2_4_3_4_6_3_1_2_5_13_7_2_4_4_6_4_6_8_7_1_3_1_8_5_8_17_3_2_3_4_1_4_6_3_8_1_11_7_8_8_7_3_2_4_7_6_8_1_6_17_6_2_4_4_2_4_4_6_2_3_4_4_10_5_8_7_7_3_1_3_1_8_2_5_16_7_3_4_3_6_15_1_6_2_4_4_8_1_7_2_3_7_5_1_3</t>
@@ -225,7 +225,7 @@
     <t>5_5_5_5</t>
   </si>
   <si>
-    <t>5_3_1_3_6_1_6_8_8_4_4_4_1_3_2_6_5_8_8_4_3_3_7_1_7_2_1_2_4_6_7_5_4_4_6_7_5_6_2_1_1_2_6_8_7_1_7_7_2_5_4_1_1_2_7_8_8_6_5_3_7_7_1_1_1_5_6_5_7_2_6_7_3_4_7_3_7_3_5_2_8_8_1_6_1_4_8_2_8_6_4_7_7_7_7_7_5_4_7_5_5_8_8_8_8_8_1_5_1_6_6_3_4_2_7_8_1_1_3_5_7_6_3_2_4_2_2_3_5_2_7_6_6_2_5_1_8_8_7_5_3_3_4_1_6_3_3_8_2_8_6_1_4_4_5_8_8_5_5_3_1_4_3_4_4_7_6_5_5_1_5_5_3_6_5_1_2_3_2_6_6_6_7_7_7_4_4_7_1_7_6_6_1_8_3_3_3_3_7_5_6_2_1_7_7_8_7_1_7_1_8_3_3_8_6_1_7_1_5_5_5_2_2_3_4_4_6_1_6_8_8_3_2_5_5_2_7_8_6_6_5_3_3_3_6_4_6_1_4_6_7_4_7_8_4_1_6_5_5_1_4_3_7_2_2_6_1_3_1_4_5_8_2_3_6_3_8_1_3_8_4_2_7_8_3_2_5_5_1_5_5_3_8_8_4_5_6_6_4_2_2_2_5_4_8_5_5_5_1_1_4_1_5_2_3_6_7_8_1_2_3_5_3_4_7_3_6_6_4_2_1_6_1_2_7_2_2_2_7_5_6_1_8_6_6_6_2_2_2_8_8_6_8_6_8_8_2_3_3_6_5_4_4_1_8_4_6_4_2_4_7_8_2_3_7_6_5_5_8_5_1_6_8_5_2_7_1_5_8_2_1_4_4_8_8_1_7_1_5_2_1_6_4_4_5_5_5_3_8_4_1_8_7_4_1_3_7_7_1_7_5_4_4_5_4_7_8_8_3_8_6_1_4_3_7_1_1_3_3_3_4_7_7_7_7_2_1_3_2_5_4_7_8_4_8_2_5_4_5_3_3_6_3_6_7_7_7_8_7_2_6_8_5_5_5_5_4_3_8_5_6_4_6_7_8_4_4_8_8_6_8_3_8_1_4_5_8_7_8_4</t>
+    <t>8_6_5_8_2_6_6_6_5_8_6_5_8_7_8_8_3_2_1_6_3_5_5_5_5_1_5_6_8_1_1_8_3_5_3_7_7_4_7_7_7_7_4_1_1_5_4_3_4_6_1_5_5_3_5_6_5_5_3_3_1_4_8_4_5_2_2_8_2_8_6_8_8_3_7_2_6_7_5_3_8_5_4_4_6_1_7_2_5_2_2_3_2_7_2_8_7_3_3_2_2_6_3_2_3_3_8_2_8_4_7_6_3_8_8_7_1_1_4_6_1_7_8_2_5_6_2_6_4_3_7_6_6_3_1_3_5_5_5_8_6_4_2_5_4_2_3_3_5_5_1_1_4_4_6_3_3_8_8_2_2_1_5_2_3_6_4_4_1_1_6_5_7_5_5_1_1_7_7_5_8_2_2_6_7_4_5_1_3_7_7_5_6_2_5_2_8_4_5_3_2_1_1_8_1_6_6_7_2_5_5_5_6_4_5_5_5_3_5_2_1_1_4_7_1_8_2_7_6_8_1_1_1_8_7_3_3_1_1_8_8_1_8_6_6_1_7_8_1_6_5_3_3_7_7_6_4_1_7_3_2_7_2_7_6_1_1_5_3_7_3_7_7_3_3_1_3_6_6_4_8_5_5_6_4_5_1_4_4_4_8_7_6_6_6_6_2_5_1_8_8_3_5_4_1_4_7_7_3_8_5_2_8_7_5_8_2_8_8_2_8_8_4_3_2_6_3_4_4_5_8_8_4_4_2_3_8_5_1_5_7_7_7_5_2_6_5_3_2_8_1_4_4_5_3_3_2_5_7_6_7_6_7_7_7_8_5_5_3_7_4_4_4_5_8_7_1_1_5_4_3_6_6_4_1_6_1_4_5_7_7_4_7_2_8_6_6_1_5_3_6_3_3_4_5_3_1_4_7_1_7_7_6_5_4_3_7_8_7_7_3_6_3_4_8_8_2_6_6_8_6_4_4_8_1_6_7_3_3_3_8_8_3_5_7_4_5_1_7_5_2_8_1_4_4_6_6_6_8_1_1_5_1_5_5_5_3_1_8_7_7_1_7_7_2_2_8_2_2_8_8_8_2_8_4_3_8_8_8_8_2_5_6_6_3_7_7_1_2_6</t>
   </si>
   <si>
     <t>15_6_3_6_7_5_5_15_7_6_5_4_6_1_1_4_5_1_3_4_4_3_4_13_5_7_1_6_4_6_3_8_4_1_6_13_3_4_7_3_5_2_7_1_4_3_1_1_5_1_8_16_6_4_2_6_5_4_8_7_3_2_6_2_4_11_1_6_1_6_8_14_4_3_7_13_7_7_3_2_7_18_6_6_3_4_8_2_3_3_7_7_2_2_4_7_7_4_2_4_2_5_3_4_5_1_6_1_18_5_11_7_4_8_3_4_4_4_1_6_2_1_1_6_2_7_16_3_5_3_1_7_5_4_3_7_1_4_1_2_1_4_8_7_4_5_3_7_4_3_6_7_1_1_5_3_6_2_5_5_8_1_3_7_8_7_7_8_1_2_3_3_2_4_3_6_7_1_4_4_2_5_4_1_2_12_4_3_6_2_2_7_4_16_5_11_7_7_2_2_1_8_7_18_5_8_7_15_7_1_5_5_6_1_3_7_2_4_5_2_11_5_8_4_6_5_6_8_2_6_4_6_6_7_2_5_6_3_11_7_11_7_2_1_18_3_5_6_16_7_8_18_4_2_5_8_3_7_7_5_8_1_3_2_8_2_4_3_6_5_2_14_7_5_2_7_6_3_3_8_10_7_1_1_7_2_5_6_5_5_2_7_3_12_3_18_6_6_6_17_3_1_4_1_7_1_4_6_3_7_1_8_6_5_7_8_3_4_2_7_2_13_6_7_8_1_4_8_4_1_1_1_1_8_4_3_2_7_6_3_4_3_3_3_2_8_1_8_1_4_16_5_4_5_8_6_4_4_8_5_8_13_5_4_6_8_4_4_7_7_5_8_7_5_7_4_5_4_3_8_6_6_8_7_1_6_4_7_8_8_17_4_6_4_2_8_4_7_3_1_4_10_7_6_6_8_4_5_2_14_2_2_5_2_3_7_1_4_3_8_3_3_2_2_12_5_4_4_6_1_3_17_6_7_6_17_1_5_5_7_8_1_7_5_7_3_4_16_5_2_3_2_7_1_4_7_7_2_3_1_1_6_5_3_1_4_3_5_4_7_5_1_5_5_5_3_16_4_8_15_5_5_6_6_3_3_6_6_5_16_5_3_2_17_6_1_5_4_4_2</t>
@@ -234,7 +234,7 @@
     <t>8_8_8_8</t>
   </si>
   <si>
-    <t>6_4_1_2_8_4_6_6_1_1_7_7_7_4_7_5_8_5_8_5_4_4_3_6_8_4_2_1_3_8_2_2_1_1_6_7_8_4_6_3_3_8_8_1_2_7_4_3_5_7_1_1_3_8_6_6_6_8_8_6_1_1_3_3_3_6_2_7_2_4_7_3_5_4_3_7_8_2_6_3_2_5_1_8_2_1_6_4_2_4_2_2_1_2_1_7_7_8_4_4_4_4_4_6_5_1_8_2_2_6_2_7_5_7_5_3_3_5_5_7_6_4_7_4_7_4_1_5_8_6_1_5_5_6_7_1_8_5_6_3_1_6_2_7_2_1_1_4_4_6_8_8_6_1_6_1_4_4_5_3_1_2_2_1_3_7_7_6_5_1_3_3_7_6_6_7_3_6_1_8_4_4_6_6_2_5_3_4_4_2_1_3_1_3_8_8_8_4_6_5_3_3_2_3_5_1_6_6_4_5_5_1_2_2_4_7_4_6_4_1_7_4_7_8_8_8_1_1_1_2_6_3_5_6_6_5_1_1_6_6_3_8_6_5_5_3_5_8_1_1_5_1_3_3_2_5_2_1_5_6_8_3_3_1_2_1_5_3_3_8_2_4_6_6_5_4_5_5_1_4_2_8_5_5_7_3_7_8_1_8_8_6_1_6_1_2_3_4_1_3_2_8_1_2_2_4_5_3_6_6_5_1_1_2_4_4_5_1_3_3_6_1_3_5_5_8_3_4_7_5_7_6_2_8_6_8_2_8_3_8_4_4_4_7_6_1_3_7_2_6_8_8_8_7_1_8_6_2_5_2_6_1_3_3_8_8_1_4_2_6_6_2_5_3_6_6_2_2_1_4_5_2_2_4_7_2_4_6_3_3_7_3_4_8_8_6_8_7_4_2_3_4_6_3_8_5_7_7_6_1_1_7_8_4_8_8_4_3_6_4_2_7_2_2_6_2_4_7_3_1_5_5_3_8_3_3_3_2_5_2_4_1_2_4_8_7_1_7_5_4_2_7_1_6_2_4_7_5_3_4_6_5_8_7_8_1_5_5_6_2_2_2_4_5_2_1_3_7_7_1_7_3_2_5_6_3_4_1_2_6_6_4_5_8_4_6_2_6_8_5</t>
+    <t>4_5_7_8_6_2_7_7_7_6_7_5_8_7_1_1_7_8_7_6_6_6_3_6_7_4_5_6_7_6_4_5_8_8_2_5_1_6_6_5_8_6_5_6_7_6_4_8_7_7_7_7_3_5_7_7_5_8_7_5_2_6_6_8_8_1_6_8_6_2_4_3_4_1_7_3_5_5_2_2_3_8_8_8_2_4_7_2_3_1_7_6_6_7_4_7_6_5_5_4_5_8_7_8_7_5_3_4_4_5_5_7_8_6_6_4_3_2_4_6_3_2_8_2_7_5_5_1_8_6_6_7_7_7_7_5_8_8_5_3_8_3_8_8_6_1_1_8_6_1_3_6_6_6_5_8_5_8_8_8_8_8_8_7_8_8_3_4_1_1_7_7_5_6_7_5_4_6_6_7_8_6_4_4_4_5_7_2_1_6_4_3_3_4_5_2_5_7_7_7_7_2_2_4_2_7_7_8_5_8_3_3_2_1_3_4_8_5_6_2_1_6_6_8_1_3_5_5_5_3_3_8_7_4_5_1_5_6_5_8_5_5_1_3_8_1_7_1_5_8_8_6_5_3_7_4_5_3_3_3_3_3_4_7_7_7_7_7_5_5_7_7_8_7_5_4_5_5_8_8_6_3_1_7_5_7_4_4_8_1_1_2_2_1_7_1_7_7_3_8_2_5_1_5_8_6_7_7_8_6_2_7_8_2_8_5_5_3_6_3_2_8_2_8_5_5_7_5_2_6_4_6_4_4_4_5_7_7_6_3_6_1_8_6_8_6_3_8_3_6_7_8_8_6_8_4_6_7_1_5_1_1_1_1_1_2_5_8_8_2_7_4_8_4_4_3_7_7_5_8_5_1_5_2_8_6_5_6_5_7_7_6_8_6_7_6_6_4_1_6_5_8_8_3_6_5_1_5_5_3_7_3_3_6_1_8_4_8_4_8_5_5_1_3_7_5_4_2_8_5_5_4_4_6_4_4_7_7_6_5_5_6_1_8_6_3_7_7_4_2_7_7_6_6_3_6_3_3_7_7_7_6_3_4_4_6_3_2_6_6_3_3_5_6_2_7_8_8_1_6_5_5_5_4_3_3_3_8_8_1_8_8_7_4_5_2_6_5_1_8</t>
   </si>
   <si>
     <t>5_8_6_2_4_2_12_7_1_4_8_4_13_4_11_7_2_4_4_15_6_6_8_14_7_3_4_1_7_7_2_7_4_2_2_1_4_5_6_5_4_1_5_5_10_6_6_4_5_5_13_2_8_6_2_4_6_1_6_6_3_2_3_6_4_5_4_7_1_7_8_6_6_17_4_18_3_4_2_16_2_2_8_8_6_8_6_13_2_3_10_1_8_2_5_2_11_7_8_1_4_3_1_1_6_4_12_4_7_11_5_3_6_1_16_7_3_1_12_3_5_3_7_1_6_6_3_6_3_3_1_3_5_2_2_4_6_6_3_1_2_18_6_1_3_7_6_8_8_3_6_4_6_8_8_5_4_5_4_14_5_3_15_7_4_1_5_7_1_3_5_4_1_1_6_6_6_16_7_7_5_4_4_8_17_6_5_18_6_4_1_2_2_2_7_2_4_8_5_12_6_6_8_1_3_5_8_4_3_1_6_1_2_2_2_7_8_3_8_5_7_7_6_5_7_1_6_6_11_4_2_1_5_2_1_15_6_2_1_5_3_8_2_3_4_6_3_3_12_3_15_1_8_6_6_16_2_1_1_2_7_7_3_4_2_2_4_8_7_8_3_4_6_4_4_17_4_2_4_8_2_6_1_3_7_2_2_3_5_3_4_7_16_3_4_5_5_10_3_2_1_3_2_1_18_6_10_5_8_8_7_2_5_6_6_2_10_4_7_8_1_7_18_3_7_4_1_8_6_6_8_15_4_8_5_4_6_2_8_4_5_2_1_1_13_7_7_2_5_3_6_10_2_7_5_6_1_7_8_8_3_4_6_7_8_5_3_5_4_1_6_2_3_3_12_7_8_8_4_5_4_6_2_7_4_1_7_2_3_4_6_7_15_3_3_3_12_7_4_6_1_1_1_3_3_13_7_2_1_8_1_4_5_4_1_4_4_1_8_14_7_3_3_5_6_6_6_7_6_1_8_4_1_3_8_1_1_5_5_4_4_8_7_5_1_4_2_2_11_7_4_6_6_2_3_18_2_2_3_4_3_8_2_1_7_7_7_4_4_2_2_8_6_2_2_3_8_6_2_3_4_2_8_6_8_3_4_7_8_6_3_3_6_2_8_18_7_8_14_6</t>
@@ -243,7 +243,7 @@
     <t>6_6_6_6</t>
   </si>
   <si>
-    <t>3_8_7_3_5_4_2_1_7_7_3_8_6_5_3_4_8_3_2_2_5_3_7_7_2_3_2_5_5_5_5_1_4_1_6_7_1_1_8_8_7_7_2_2_5_2_7_1_5_3_5_1_6_6_8_3_4_4_2_2_4_5_8_1_4_2_1_1_3_3_3_1_3_2_2_2_2_5_1_7_7_5_2_7_8_1_4_5_5_6_7_2_4_1_7_8_5_3_1_1_4_8_8_5_2_8_2_2_8_6_7_8_6_7_4_7_1_3_3_4_6_4_5_5_3_8_5_2_3_5_7_8_5_6_8_6_8_5_1_6_2_4_7_7_4_5_7_6_3_7_1_4_4_5_1_2_1_5_8_1_3_4_2_7_8_1_4_7_3_8_1_2_4_5_7_4_7_7_6_8_8_6_5_7_7_2_1_2_7_7_4_4_3_5_5_8_4_3_7_1_8_1_3_8_7_5_2_5_6_4_5_6_1_8_6_4_2_1_1_4_4_1_1_4_7_8_5_5_4_3_2_6_3_6_6_1_2_5_3_7_5_3_6_5_8_3_2_5_1_5_7_1_8_8_6_6_6_5_7_7_6_6_5_3_5_2_5_6_6_2_4_5_2_5_8_3_2_1_2_7_4_7_4_5_6_5_8_3_4_4_2_2_4_4_3_8_8_7_5_4_5_6_1_8_7_7_8_4_7_7_5_2_6_4_5_8_2_6_3_2_2_5_5_7_7_6_2_2_7_8_8_8_6_6_5_1_1_2_7_8_8_2_4_2_8_2_7_4_8_5_6_6_2_3_6_4_3_3_3_6_6_2_1_1_1_1_4_1_3_8_7_3_2_3_8_8_7_7_5_6_4_4_4_3_3_3_3_3_6_5_8_4_4_2_8_5_6_1_1_1_6_3_3_8_1_4_8_6_4_1_5_5_8_2_4_3_4_5_8_2_8_8_8_2_7_4_7_3_6_4_4_8_6_2_1_1_8_4_2_1_8_8_2_5_3_3_7_3_5_5_6_6_5_5_2_2_2_1_1_3_2_5_6_6_3_5_6_1_1_5_8_3_8_8_2_3_5_4_8_1_4_4_5_3_2_7_7_2_5_7_2_6_5_7_3_3_3_7_3_6</t>
+    <t>1_3_2_1_2_2_7_4_5_3_8_8_1_2_3_4_2_2_5_8_8_5_1_1_4_2_2_2_2_1_8_7_2_8_5_1_5_5_5_5_3_6_2_5_5_3_5_8_5_8_3_2_3_4_8_1_5_1_4_4_4_4_2_3_3_3_7_5_4_3_7_1_6_7_7_2_2_1_1_1_3_4_4_5_1_5_3_8_4_5_4_4_4_4_6_4_4_1_6_6_3_7_6_5_1_3_6_2_7_4_3_3_3_3_3_1_8_3_5_3_8_1_4_1_1_1_1_5_6_4_4_6_6_6_6_5_3_2_2_4_8_4_3_3_3_6_3_4_7_5_4_3_4_4_1_1_5_5_1_1_1_8_6_1_5_7_5_3_4_8_6_3_7_3_6_4_2_4_3_8_8_1_1_2_3_4_5_8_1_4_2_2_5_2_1_4_4_4_3_7_6_4_4_4_5_5_2_3_6_6_6_1_1_1_6_6_2_7_7_1_3_8_3_3_4_4_4_3_8_8_3_6_8_8_1_8_2_5_6_2_1_7_1_3_7_8_3_6_6_4_8_5_3_3_7_1_7_7_8_5_6_6_8_8_5_7_4_7_4_5_2_2_4_5_4_7_3_3_4_4_2_5_5_4_6_1_1_6_8_8_4_4_5_1_7_7_8_6_1_4_3_1_2_6_2_6_2_3_6_3_3_4_5_8_4_7_7_5_1_8_8_3_6_6_8_4_7_7_5_5_4_4_2_2_2_5_4_7_3_2_8_4_1_7_7_6_1_7_4_2_4_7_3_7_4_4_4_4_1_2_1_2_2_2_2_3_8_3_1_8_3_3_8_2_1_8_8_1_6_1_8_5_1_5_8_6_4_1_1_2_2_5_3_3_1_3_2_2_2_8_4_1_3_6_6_2_6_6_1_7_7_2_4_4_4_5_7_5_3_7_6_4_3_3_3_2_3_2_1_4_4_4_2_2_3_7_6_4_4_2_3_6_6_6_6_4_3_1_2_5_1_2_1_4_6_3_5_2_4_5_5_5_5_3_3_7_3_4_5_3_5_1_4_1_2_6_3_3_6_2_7_7_1_3_3_5_5_5_3_2_2_3_3_7_4_4_2_6_3_1</t>
   </si>
   <si>
     <t>7_7_7_8_1_5_3_6_3_1_1_8_7_8_2_4_6_7_5_16_2_2_1_4_13_5_4_5_6_7_5_2_3_6_7_5_16_6_6_3_3_4_13_4_5_8_6_6_5_4_7_8_1_8_5_8_8_4_5_6_1_4_2_8_3_8_6_3_1_8_8_6_7_6_7_17_3_5_7_5_6_13_6_6_5_2_5_8_15_4_3_5_2_3_2_2_5_3_6_6_16_7_8_6_3_8_10_6_18_6_2_3_8_8_3_13_7_2_1_6_7_8_7_7_7_11_5_8_5_8_12_6_8_8_5_14_7_3_5_7_11_7_5_5_5_7_5_4_11_5_2_4_2_17_4_7_3_4_8_2_5_4_5_5_5_6_8_15_1_7_2_3_3_3_5_8_3_12_6_5_7_1_6_7_3_8_5_8_5_12_6_7_4_7_8_3_8_4_5_6_3_5_3_7_4_4_8_6_3_6_7_4_3_6_5_3_5_4_5_7_2_11_3_4_7_4_11_6_7_1_5_3_2_16_4_1_1_3_4_4_5_4_6_4_6_14_6_8_2_8_3_1_2_2_1_2_6_2_4_2_18_7_2_10_4_3_2_8_4_8_8_2_3_5_4_6_7_7_5_3_8_8_18_2_5_5_12_7_6_8_12_4_13_5_3_7_2_4_6_7_1_3_5_18_6_6_3_3_6_2_3_13_2_8_6_5_1_6_8_3_5_7_13_2_8_1_3_6_6_4_4_6_4_4_6_4_2_8_5_1_3_7_1_2_8_8_4_8_12_6_7_1_6_5_1_7_5_5_5_3_5_6_4_4_18_4_2_3_18_7_8_8_6_5_11_4_5_4_6_8_7_2_2_1_2_1_1_8_5_8_1_5_4_15_6_6_6_3_5_6_7_8_7_1_2_8_6_7_1_4_17_4_6_1_3_8_16_6_3_8_4_2_6_3_2_3_1_5_2_6_5_3_4_3_1_8_3_5_18_5_6_8_7_7_3_7_6_3_2_5_6_7_6_7_6_14_3_1_4_8_3_4_4_2_5_6_3_5_8_6_6_8_10_6_7_7_7_5_4_18_7_13_7_1_8_11_4_6_1_2_5_6_2_3_3_4_2_3_6_5</t>
@@ -252,7 +252,7 @@
     <t>7_7_7_7</t>
   </si>
   <si>
-    <t>2_8_4_7_2_7_1_7_8_7_7_4_2_5_6_6_1_2_3_3_5_8_8_2_2_8_8_6_8_3_3_7_4_6_6_1_4_1_7_7_6_8_2_6_5_3_5_2_4_7_7_8_7_8_2_8_8_4_8_8_8_8_5_5_4_7_7_2_1_4_4_4_4_2_2_7_1_8_8_8_4_5_5_5_7_2_7_5_5_5_1_2_6_7_8_3_8_7_7_5_6_5_7_5_8_3_4_6_4_2_2_3_2_5_3_3_2_8_6_5_3_5_2_2_1_6_8_7_6_2_2_2_8_2_3_4_6_5_5_3_3_2_6_6_3_7_2_4_2_7_4_5_6_1_6_8_7_7_6_6_8_3_7_2_8_5_8_7_6_5_8_2_8_1_7_3_7_5_3_6_5_5_3_3_8_2_4_1_3_8_6_4_1_1_3_3_8_3_2_2_3_3_2_4_6_8_2_2_7_8_3_3_2_2_2_6_6_3_7_8_5_2_2_8_4_1_3_1_5_8_8_3_2_1_5_2_2_1_7_4_8_8_6_6_3_5_1_6_3_6_3_7_5_6_5_5_7_4_6_3_6_5_4_8_5_1_7_7_6_5_8_4_5_6_3_3_1_8_8_2_3_5_2_5_5_6_1_1_2_5_6_3_8_4_2_2_7_1_1_3_5_1_8_7_8_6_2_2_5_3_6_5_3_6_6_6_6_8_4_3_8_3_3_3_2_8_8_3_6_4_1_5_2_2_5_5_5_1_6_2_1_1_5_5_8_8_6_1_6_6_7_1_8_5_1_8_5_7_3_5_6_6_2_3_2_1_7_1_1_3_1_6_4_6_1_6_7_8_6_3_8_8_1_1_6_3_2_3_6_2_3_6_7_1_3_3_3_7_7_1_8_6_1_8_1_4_8_8_8_6_6_2_8_6_2_3_3_1_3_7_7_3_5_2_4_2_6_7_3_7_8_6_8_3_3_3_5_3_3_7_7_5_5_3_3_7_7_3_1_1_1_4_3_5_7_2_4_3_4_5_1_5_4_4_6_8_2_7_5_3_7_4_4_8_3_8_2_7_8_7_7_5_7_3_6_5_6_3_2_8_8_3_7_7_1_7_4_3_2_6</t>
+    <t>5_8_1_6_1_4_1_2_8_4_4_5_7_1_6_3_4_6_2_6_6_4_4_8_2_8_3_2_4_3_3_6_3_5_5_6_5_8_7_2_2_6_3_7_4_3_3_1_4_5_2_2_8_8_7_4_4_4_3_8_2_6_6_6_1_7_1_3_3_3_5_7_8_2_6_6_1_8_7_2_7_2_2_8_7_1_1_1_1_4_2_4_3_1_1_6_6_6_4_3_5_2_2_8_4_4_6_4_8_2_3_1_1_5_5_7_3_2_1_3_1_6_1_6_6_1_4_2_2_8_4_6_5_3_2_2_8_6_2_1_4_6_1_5_4_5_7_2_2_3_3_8_6_5_5_3_8_5_6_5_2_5_4_6_2_3_6_3_6_8_1_2_5_5_2_1_4_4_2_5_8_5_6_4_4_4_4_5_3_6_4_1_5_6_7_4_4_4_6_4_4_4_6_5_3_3_8_3_5_2_7_2_2_5_1_4_1_5_5_1_1_1_2_5_1_1_3_2_3_6_4_3_4_1_8_1_1_3_3_7_2_1_8_3_5_3_4_5_1_6_1_6_8_6_5_3_8_4_4_2_2_5_8_5_8_8_6_6_5_5_4_8_5_3_3_7_2_2_1_2_6_1_4_1_1_3_3_7_7_4_1_1_4_4_4_8_7_2_1_3_5_5_6_1_3_3_7_8_2_2_1_7_3_5_1_4_6_5_5_3_4_3_5_1_7_7_7_1_8_8_1_3_1_3_3_8_5_1_6_5_4_4_4_3_2_3_1_4_1_4_1_7_7_1_2_3_3_7_7_1_1_1_7_1_4_4_4_4_4_3_5_4_4_5_3_7_4_5_5_1_6_3_3_5_1_7_6_2_2_8_7_4_1_1_6_2_3_2_3_3_5_1_3_3_8_8_3_2_2_7_8_1_6_4_2_2_7_4_2_5_7_5_2_3_6_6_4_6_6_2_4_4_4_3_3_4_6_4_3_4_4_1_2_4_7_1_2_5_8_2_4_4_4_1_6_2_6_1_2_3_7_5_5_7_2_6_6_3_1_2_7_3_7_4_2_7_6_1_1_3_4_2_2_7_5_3_3_6_5_2_3_1_1_5_5_3_7_1_1_1</t>
   </si>
   <si>
     <t>10_3_8_2_3_4_6_13_6_5_6_5_4_8_3_1_7_8_3_5_2_3_6_8_2_17_1_7_7_8_8_8_10_7_4_6_10_4_4_1_6_6_7_5_15_2_6_6_5_2_6_6_2_7_12_5_7_5_8_7_7_4_7_8_5_4_8_2_4_1_6_5_7_8_6_6_18_5_2_1_8_18_6_8_8_3_18_3_6_5_8_1_7_4_2_4_1_1_4_13_7_3_4_3_7_4_3_6_6_7_1_13_3_3_4_5_16_5_2_1_12_7_5_2_4_4_4_2_5_6_13_6_2_3_8_1_3_1_6_6_18_3_8_16_6_2_4_14_6_17_7_1_3_7_3_7_7_11_7_2_8_2_8_5_2_6_10_7_7_7_2_5_1_7_4_1_6_5_8_1_1_18_4_1_8_6_6_4_7_5_7_16_1_1_8_1_15_6_4_6_3_4_2_2_5_2_13_3_8_18_7_6_7_14_7_2_3_2_6_15_5_2_3_3_1_5_18_6_5_3_1_5_4_5_6_7_7_5_5_3_3_13_7_2_6_8_1_10_5_8_4_3_4_8_5_17_1_7_1_5_7_3_5_1_7_4_4_14_6_2_2_6_3_1_6_5_7_7_2_4_4_4_2_8_7_2_10_6_4_5_1_3_3_4_8_2_6_4_2_1_2_1_11_7_5_6_6_3_6_7_2_3_3_8_6_3_17_7_7_1_4_4_7_6_10_4_2_3_5_3_5_1_1_4_8_13_7_4_5_8_6_10_4_4_8_5_6_6_3_4_5_2_7_2_3_1_18_5_2_3_1_6_3_3_1_18_6_8_5_1_5_4_8_2_6_2_1_8_8_2_2_7_6_8_6_5_2_2_8_3_6_5_4_5_4_7_1_7_2_5_6_7_2_6_8_8_10_6_3_6_2_3_6_4_7_3_5_16_7_3_6_5_8_14_3_12_1_6_1_8_4_3_6_7_8_5_13_4_3_6_5_17_4_8_3_6_3_4_7_4_1_2_1_7_1_6_2_1_2_2_4_1_1_5_8_5_7_4_4_6_3_5_5_6_4_8_6_4_6_3_6_4_8_8_1_13_7_5_4_2_4_1_8_3_3_6_5_6_8_3</t>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="78">
   <si>
     <t>id</t>
   </si>
@@ -1612,7 +1612,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:11">
       <c r="A5">
-        <f t="shared" ref="A5:A36" si="0">C5*10+D5</f>
+        <f t="shared" ref="A5:A41" si="0">C5*10+D5</f>
         <v>20010011</v>
       </c>
       <c r="B5" s="11">
@@ -2747,6 +2747,166 @@
       </c>
       <c r="J36" s="28"/>
       <c r="K36" s="6"/>
+    </row>
+    <row r="37" ht="16.5" spans="1:11">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>20240011</v>
+      </c>
+      <c r="B37" s="11">
+        <v>102400</v>
+      </c>
+      <c r="C37" s="12">
+        <v>2024001</v>
+      </c>
+      <c r="D37" s="13">
+        <v>1</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+    </row>
+    <row r="38" ht="16.5" spans="1:11">
+      <c r="A38">
+        <f t="shared" si="0"/>
+        <v>20240012</v>
+      </c>
+      <c r="B38" s="11">
+        <v>102400</v>
+      </c>
+      <c r="C38" s="12">
+        <v>2024001</v>
+      </c>
+      <c r="D38" s="13">
+        <v>2</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J38" s="28"/>
+      <c r="K38" s="28"/>
+    </row>
+    <row r="39" ht="16.5" spans="1:11">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>20240013</v>
+      </c>
+      <c r="B39" s="11">
+        <v>102400</v>
+      </c>
+      <c r="C39" s="12">
+        <v>2024001</v>
+      </c>
+      <c r="D39" s="13">
+        <v>3</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="H39" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I39" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="J39" s="28"/>
+      <c r="K39" s="28"/>
+    </row>
+    <row r="40" ht="16.5" spans="1:11">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>20240014</v>
+      </c>
+      <c r="B40" s="11">
+        <v>102400</v>
+      </c>
+      <c r="C40" s="12">
+        <v>2024001</v>
+      </c>
+      <c r="D40" s="13">
+        <v>4</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="H40" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+    </row>
+    <row r="41" ht="16.5" spans="1:11">
+      <c r="A41">
+        <f t="shared" si="0"/>
+        <v>20240015</v>
+      </c>
+      <c r="B41" s="11">
+        <v>102400</v>
+      </c>
+      <c r="C41" s="12">
+        <v>2024001</v>
+      </c>
+      <c r="D41" s="13">
+        <v>5</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H41" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J41" s="28"/>
+      <c r="K41" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoller" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="88">
   <si>
     <t>id</t>
   </si>
@@ -313,6 +313,36 @@
   </si>
   <si>
     <t>1_7_7_7_1_9_9_9_9_9_1_5_1_7_1_11_11_1_7_1_9_9_9_9_1_11_11_11_11_11_11_1_11_11_11_1_5_5_5_5_5_5_5_5_5_1_3_3_1_5_1_11_11_1_3_3_3_1_5_5_5_5_1_11_1_3_1_3_1_3_3_1_9_9_9_9_9_9_9_1_9_9_9_1_9_1_11_1_7_7_7_7_7_1_9_1_9_9_9_9_1_11_11_11_1_11_11_1_11_1_11_11_11_1_11_11_11_11_1_11_11_11_11_1_11_1_3_3_3_3_1_9_9_1_5_1_7_7_7_7_7_7_7_7_7_7_7_7_7_1_5_5_5_1_7_7_7_7_7_7_7_7_1_7_7_7_7_7_7_7_1_11_11_1_9_9_9_9_9_9_1_3_3_1_11_11_11_11_11_11_1_5_5_1_11_11_11_11_1_9_1_7_7_1_3_3_3_3_3_3_3_1_5_5_1_5_5_1_7_1_5_5_5_5_5_1_3_3_3_1_7_7_7_7_7_1_11_11_11_11_1_7_7_7_7_7_1_3_3_3_3_3_3_1_9_1_11_11_11_11_1_5_1_3_3_3_1_3_1_5_5_1_3_3_1_11_11_11_1_9_9_9_9_9_9_1_9_9_9_9_9_9_9_9_1_3_3_3_3_3_3_3_1_7_1_3_3_1_11_11_11_11_11_11_11_11_11_1_7_1_5_5_5_1_7_7_7_7_7_7_7_7_7_1_7_7_1_7_7_7_7_7_1_7_7_7_7_1_5_1_11_1_9_1_11_11_11_11_1_3_3_3_3_1_5_5_5_5_1_3_3_3_3_3_3_3_3_1_5_1_9_9_1_11_1_9_9_9_9_1_3_1_7_1_9_1_3_1_11_11_11_11_1_5_5_1_11_1_11_11_1_5_1_5_5_1_3_3_3_3_1_5_5_5_5_5_1_3_1_11_11_11_11_11_1_9_9_9_9_9_1_7_7_7_1_11_1_3_3_3_1_11_11_1_3_3_3_3_3_3_3_1_7_7_7_7_7_7_7_7_7_7_7_1_3_3_3_1_3_1_9_1_5_1_11_1_3_3_3_3_1_5_5_5_1_3_3_3_3_1</t>
+  </si>
+  <si>
+    <t>2_6_6_9_1_4_9_4_5_7_9_5_1_7_1_10_5_10_5_7_2_4_6_1_3_10_5_10_6_1_9_3_4_9_5_14_1_2_1_7_4_5_2_5_1_10_4_2_1_6_3_10_3_3_8_10_7_14_5_2_1_8_1_2_14_7_2_3_10_6_9_2_2_4_9_1_6_4_3_4_6_8_4_6_2_5_1_3_3_10_7_8_6_1_3_3_2_4_9_2_10_7_7_5_1_1_11_7_3_5_11_5_3_1_2_1_2_8_7_10_6_4_9_3_7_8_1_2_1_1_3_2_4_1_10_5_5_4_10_6_6_5_1_7_9_9_5_6_4_5_2_6_2_4_8_6_2_9_2_5_3_8_7_10_1_2_2_8_9_10_5_6_5_7_1_9_1_6_3_11_3_7_5_14_7_4_3_4_6_10_3_4_2_8_5_10_5_8_14_1_11_7_9_5_1_10_2_1_7_10_5_5_10_3_3_14_4_2_1_1_1_1_1_7_2_6_14_3_1_3_2_8_6_7_6_5_8_6_5_8_5_4_9_2_1_2_3_2_6_4_14_5_1_11_7_2_5_7_2_4_3_4_7_4_4_1_4_10_6_10_2_5_10_6_6_5_14_7_3_3_8_5_5_4_5_8_4_2_2_10_4_6_9_1_5_1_9_5_5_5_3_6_11_6_6_2_3_1_7_8_9_2_6_1_3_3_2_8_3_6_10_1_2_3_1_3_2_6_10_6_5_4_8_9_7_2_11_5_1_8_10_6_4_4_1_1_2_3_5_3_2_4_9_3_1_7_3_2_5_10_7_6_4_5_10_1_2_1_3_5_1_1_1_1_10_1_3_2_9_14_5_2_4_3_2_8_11_3_3_10_4_10_3_8_1_10_3_11_7_14_5_5_4_6_2_7_10_7_10_7_8_11_5_1_6_1_2_8_4_2_10_7_7_1_9_10_7_9_1_7_8_7_2_5_4_2_4_6_7_4_10_5_3_4_4_1_6_7_6_1_10_2_2_6_5_14_4_3_2_10_2_2_7_14_5_1_4_1_7_4_1_2_6_9_9_2_8_2_10_7_9_1_6_1_9_14_6_3_2_1_9_7_4_6_6_9_4_5_4_7</t>
+  </si>
+  <si>
+    <t>3_3_5_4_2_4_1_1_5_6_1_2_2_2_2_1_8_8_1_1_2_2_2_4_5_8_2_2_2_1_4_4_4_7_9_9_2_2_1_3_6_2_3_3_1_4_9_4_2_2_2_4_2_1_1_2_2_2_7_1_2_4_9_8_2_6_5_5_10_6_1_5_2_3_8_4_4_7_8_6_3_4_1_2_5_2_4_1_4_6_7_6_7_6_1_2_10_4_2_4_1_4_2_3_2_6_2_3_3_3_2_5_8_1_1_1_2_1_2_7_8_2_7_3_2_5_9_9_1_1_8_2_3_7_3_10_6_2_2_9_3_1_4_7_1_2_8_1_7_3_10_1_4_3_4_8_4_4_8_1_9_3_4_4_2_2_7_6_5_5_7_4_1_2_1_4_5_3_4_1_1_5_4_5_5_6_1_9_8_5_3_7_4_1_3_5_6_3_10_1_5_3_4_9_8_8_9_8_6_2_3_6_6_3_4_3_3_8_7_2_9_9_3_1_1_1_4_4_8_5_1_3_2_10_6_4_8_2_7_4_2_4_6_2_6_2_1_5_2_2_3_3_9_2_8_9_8_6_8_1_7_1_7_6_9_5_4_6_1_4_8_1_1_4_1_2_2_4_2_1_2_1_3_4_5_2_2_6_5_6_2_4_2_9_3_1_3_8_4_1_1_5_4_4_2_2_2_4_1_6_6_4_2_7_2_3_7_1_4_6_2_3_3_7_3_2_2_2_4_1_1_5_3_1_2_9_8_6_4_2_3_2_2_7_7_1_2_4_4_1_2_2_9_3_9_6_6_1_3_3_3_4_6_6_1_1_6_3_3_8_5_2_2_3_3_10_4_4_4_5_10_2_5_5_1_1_6_6_5_9_6_6_6_1_2_3_5_5_1_9_5_3_3_4_8_2_6_4_4_6_6_4_4_3_3_7_7_7_1_2_9_9_10_6_6_3_1_5_7_4_4_8_3_5_5_2_5_2_2_2_6_4_6_4_3_2_1_2_1_10_3_1_10_4_6_7_1_6_1_3_7_7_8_3_5_5_2_5_7_2_5_4_1_4_10_9_6_4_4_3_2_2_1_3_6_4_2_8_1_1_5_7_4_10_7_7_1_4_1_4</t>
+  </si>
+  <si>
+    <t>7_7_7</t>
+  </si>
+  <si>
+    <t>7_6_9_3_7_1_11_4_2_9_5_8_6_2_2_6_4_2_7_5_4_5_1_9_8_1_6_2_3_6_4_3_8_1_5_5_5_1_3_2_2_1_8_1_1_2_7_5_5_11_5_10_7_6_1_1_6_8_2_1_7_9_1_9_2_2_1_7_6_10_3_1_9_4_7_5_3_10_7_7_6_1_2_9_8_8_1_7_2_2_4_6_1_5_7_5_11_5_8_7_5_1_3_2_3_2_4_7_3_10_5_10_1_4_4_6_7_3_7_6_11_4_8_6_6_1_7_8_10_2_4_7_6_2_1_1_6_5_5_7_1_9_14_6_5_5_2_6_2_9_7_6_8_6_8_3_2_6_3_1_6_8_4_9_3_3_10_2_8_3_7_7_7_14_1_8_9_10_7_4_8_1_14_4_10_4_6_2_3_4_1_2_1_4_9_3_2_14_3_4_14_5_5_11_2_1_8_6_3_4_10_1_1_2_9_2_2_4_3_1_5_4_11_7_8_2_9_6_7_7_2_4_14_7_4_6_1_3_6_4_8_2_3_9_2_2_5_10_5_9_6_8_4_6_6_9_8_1_4_11_6_3_9_7_7_3_2_3_5_1_3_7_7_8_11_4_11_6_10_5_1_1_4_3_9_14_5_6_3_5_10_5_1_5_5_4_3_2_10_6_2_5_2_2_1_2_4_5_3_9_7_1_6_7_3_14_5_10_4_6_8_8_7_9_7_3_1_4_3_7_14_1_1_14_3_3_4_3_4_9_8_8_10_2_6_1_9_1_4_5_8_7_5_10_4_6_7_1_4_9_5_1_7_4_5_4_7_7_1_3_5_9_9_7_3_14_5_5_10_5_6_2_4_7_6_2_2_1_6_7_5_3_9_1_9_2_1_7_10_7_3_5_4_9_6_8_3_1_4_9_5_5_1_3_4_5_4_4_6_5_3_5_10_2_4_7_9_1_3_8_4_10_5_6_5_7_7_1_1_2_7_7_2_5_10_6_3_10_7_5_7_1_10_7_2_6_7_9_3_6_10_4_1_2_9_3_3_2_2_11_6_5_2_1_7_6_1_2_2_2_14_4_6_10_4_8_9_6_9_9_7_1_6_4_10_2_8_2_1_7</t>
+  </si>
+  <si>
+    <t>8_8_8</t>
+  </si>
+  <si>
+    <t>6_1_9_4_3_1_9_5_5_7_9_2_2_8_3_4_5_4_7_7_2_1_14_5_8_6_7_9_7_8_4_4_11_5_2_3_6_8_14_3_7_5_1_8_1_2_10_6_2_1_3_14_2_9_8_2_4_6_5_9_6_3_4_11_4_6_1_7_7_3_1_10_1_4_1_6_3_8_2_6_2_2_10_6_3_3_5_6_2_4_7_1_7_11_4_7_1_6_6_5_4_7_6_3_1_5_6_6_7_5_8_8_1_7_7_9_6_2_2_2_7_2_9_4_4_6_5_11_7_1_8_9_4_3_4_6_9_8_6_3_5_2_7_10_5_7_10_6_5_5_6_10_5_2_3_6_8_3_10_2_8_10_7_2_4_7_8_7_8_9_3_8_11_7_1_4_3_14_1_1_5_4_4_2_2_6_10_3_3_2_6_2_3_1_2_10_5_1_9_1_5_8_2_14_5_5_6_1_1_3_3_7_1_7_14_2_4_2_14_3_3_1_2_8_2_3_9_6_8_7_3_5_10_1_10_5_6_4_9_3_7_10_7_7_10_3_3_3_5_10_5_8_4_2_6_2_9_5_6_2_1_2_5_6_10_6_4_9_1_4_8_14_4_9_2_3_9_9_5_10_7_5_7_8_9_3_4_8_4_4_4_6_8_7_8_8_5_9_1_6_6_6_8_5_14_2_9_8_3_5_7_7_1_3_2_14_5_8_11_2_2_5_4_8_6_10_6_2_6_5_2_5_7_14_5_8_8_1_4_11_3_9_2_4_2_3_5_3_9_3_2_4_2_7_10_7_6_4_4_3_3_1_4_4_7_2_3_1_1_8_3_7_5_3_1_9_2_14_3_6_5_2_1_9_1_1_10_6_3_3_9_14_7_2_10_5_5_5_1_2_5_7_3_8_1_8_2_14_5_9_8_8_4_1_1_2_6_4_6_8_8_8_8_6_5_8_14_4_8_1_4_6_5_3_14_6_4_8_3_6_9_2_2_3_2_6_7_4_6_4_2_5_11_7_3_1_5_4_4_3_1_2_8_4_4_10_6_7_2_10_3_2_8_6_1_8_2_1_3_8_8_2_4_5_3_14_7_11_2_8_10_5_2_7_4_1_1_14_4_2</t>
+  </si>
+  <si>
+    <t>9_9_9</t>
+  </si>
+  <si>
+    <t>5_2_3_8_2_4_7_2_8_5_10_5_4_4_11_7_8_5_3_3_7_4_7_5_9_2_10_4_2_4_2_2_7_10_7_1_1_6_7_10_7_5_10_3_8_10_6_3_14_4_7_9_2_4_10_3_3_4_1_9_2_6_8_3_2_5_10_7_3_4_7_1_8_1_2_9_2_11_2_2_4_1_10_5_1_4_9_9_3_7_2_8_7_9_3_1_3_9_2_4_2_2_6_9_3_1_8_8_3_8_8_6_11_5_3_2_5_2_8_8_4_9_7_4_6_4_1_14_3_11_7_4_1_9_8_7_6_6_3_8_2_8_10_7_1_7_4_7_9_2_4_2_3_2_8_4_4_8_5_4_3_3_4_7_4_4_2_8_1_7_4_8_9_9_6_6_5_8_1_4_1_8_9_3_7_11_6_4_6_6_4_11_6_3_1_9_1_8_2_7_6_11_3_8_7_8_7_2_6_2_3_1_8_7_2_9_4_1_3_3_6_11_7_10_5_6_4_7_10_6_4_2_9_6_3_8_3_2_2_2_4_5_6_1_8_1_7_8_1_1_3_9_10_5_3_3_2_9_6_6_7_2_10_5_7_2_6_7_8_9_1_8_7_1_2_1_4_2_9_10_2_5_10_3_6_1_1_8_10_2_10_2_2_5_14_5_4_9_9_10_4_1_9_9_11_7_10_4_7_5_2_7_4_10_5_3_7_1_3_14_4_1_10_1_5_1_5_11_6_3_9_10_6_4_3_10_4_6_3_9_2_6_10_6_11_4_14_3_7_7_1_7_10_6_14_7_8_2_10_3_7_3_9_5_3_2_10_6_4_8_4_6_6_6_8_1_5_10_7_4_3_1_7_4_9_1_1_1_1_9_1_1_9_1_4_7_5_4_3_1_5_5_4_8_5_9_2_4_10_6_6_10_6_7_5_4_3_4_1_4_9_4_3_5_8_7_10_6_2_5_1_8_5_8_1_5_4_1_4_7_6_1_3_8_6_4_4_3_5_6_2_3_6_4_2_4_2_4_1_5_1_10_7_1_3_9_4_4_5_11_5_4_7_14_3_1_7_2_1_4_3_4_5_2_4_6_5_8_2_4_1_4_8_1_6_2_3_2_9_3</t>
+  </si>
+  <si>
+    <t>10_10_10</t>
+  </si>
+  <si>
+    <t>10_7_1_6_2_1_4_6_10_5_3_4_8_10_5_8_14_4_4_5_3_1_14_4_2_8_9_3_1_2_2_2_11_4_7_4_2_8_4_2_3_7_2_14_4_1_3_11_5_4_14_7_5_3_10_2_14_2_2_8_10_1_8_8_5_4_6_5_7_9_10_2_1_3_2_6_1_11_7_1_2_1_2_2_10_5_3_8_6_14_3_10_5_7_6_10_4_1_5_2_2_2_4_7_6_11_7_10_4_5_3_5_5_7_1_5_8_4_3_3_3_2_1_3_8_1_4_14_4_7_6_10_3_6_6_10_2_5_4_2_8_9_3_2_7_10_3_11_7_7_6_3_1_7_1_7_2_2_5_9_5_6_5_4_1_4_3_6_2_14_4_2_4_14_3_5_7_1_3_4_10_2_3_3_3_6_8_4_1_4_5_1_6_1_10_6_10_5_2_6_8_2_5_2_3_1_4_3_9_3_8_6_5_8_4_3_3_14_7_2_3_5_2_1_1_3_6_9_10_5_4_10_4_3_4_8_7_1_7_8_4_10_6_2_7_5_14_6_11_6_14_4_3_8_2_4_6_7_3_7_6_7_1_4_5_9_6_5_1_8_8_9_10_6_7_1_7_2_3_9_8_10_2_4_2_14_6_8_4_3_10_5_2_5_4_7_5_8_7_4_10_7_9_3_9_8_6_1_4_1_8_3_4_3_6_10_4_5_8_1_5_1_4_2_10_7_11_4_10_2_4_2_5_1_4_5_14_5_4_5_3_6_1_3_2_2_5_1_1_5_3_7_8_2_2_8_9_6_1_2_9_8_8_7_5_6_1_9_5_3_2_4_6_8_9_7_4_8_1_2_3_9_8_5_1_5_9_3_9_1_8_10_4_7_2_2_10_4_1_3_4_2_7_14_5_4_5_3_9_8_6_10_6_1_14_5_9_3_2_2_4_3_1_2_5_5_6_4_4_8_3_4_4_11_7_7_7_7_6_8_10_4_8_2_1_3_1_11_3_3_9_10_6_1_4_2_14_6_4_5_5_11_5_6_4_9_2_7_6_5_1_2_3_10_6_11_7_2_6_7_4_2_7_4_3_1_14_6_8_6_8_5_4_14_2_2_10_5_8_6</t>
   </si>
 </sst>
 </file>
@@ -335,18 +365,18 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1011,82 +1041,91 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1612,19 +1651,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
-    <col min="2" max="2" width="9" style="5"/>
+    <col min="2" max="2" width="9" style="6"/>
     <col min="4" max="4" width="7.875" customWidth="1"/>
     <col min="5" max="5" width="28.75" customWidth="1"/>
     <col min="6" max="6" width="23.525" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
     <col min="8" max="8" width="22.5" customWidth="1"/>
     <col min="9" max="9" width="17.875" customWidth="1"/>
-    <col min="10" max="10" width="25.125" style="6" customWidth="1"/>
-    <col min="11" max="11" width="36.125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="25.125" style="7" customWidth="1"/>
+    <col min="11" max="11" width="36.125" style="7" customWidth="1"/>
     <col min="13" max="13" width="12.625"/>
   </cols>
   <sheetData>
@@ -1632,1281 +1671,1601 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
     </row>
     <row r="2" ht="16.5" spans="1:11">
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
     </row>
     <row r="3" ht="16.5" spans="1:11">
       <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-    </row>
-    <row r="4" ht="16.5" spans="2:11">
-      <c r="B4" s="11"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+    </row>
+    <row r="4" ht="16.5" spans="1:11">
+      <c r="B4" s="13"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
     </row>
     <row r="5" ht="16.5" spans="1:11">
       <c r="A5">
-        <f t="shared" ref="A5:A41" si="0">C5*10+D5</f>
+        <f t="shared" ref="A5:A51" si="0">C5*10+D5</f>
         <v>20010011</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="13">
         <v>100100</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="14">
         <v>2001001</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="14" t="s">
+      <c r="F5" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="14" t="s">
+      <c r="H5" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
     </row>
     <row r="6" ht="16.5" spans="1:11">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>20010012</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="13">
         <v>100100</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="14">
         <v>2001001</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="15">
         <v>2</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="14" t="s">
+      <c r="F6" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="14" t="s">
+      <c r="H6" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
     </row>
     <row r="7" ht="16.5" spans="1:11">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>20010013</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="13">
         <v>100100</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="14">
         <v>2001001</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="15">
         <v>3</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="14" t="s">
+      <c r="F7" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="14" t="s">
+      <c r="H7" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
     </row>
     <row r="8" ht="16.5" spans="1:11">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>20010014</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="13">
         <v>100100</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="14">
         <v>2001001</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="15">
         <v>4</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="14" t="s">
+      <c r="F8" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="14" t="s">
+      <c r="H8" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
     </row>
     <row r="9" ht="16.5" spans="1:11">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>20010015</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="13">
         <v>100100</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="14">
         <v>2001001</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="15">
         <v>5</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="14" t="s">
+      <c r="F9" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="14" t="s">
+      <c r="H9" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="16.5" spans="1:10">
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>20030011</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="19">
         <v>100300</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="20">
         <v>2003001</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="20">
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="21" t="s">
         <v>36</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="H10" s="21" t="s">
         <v>36</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J10" s="18"/>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="16.5" spans="1:10">
+      <c r="J10" s="21"/>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>20030012</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="19">
         <v>100300</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="20">
         <v>2003001</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="20">
         <v>2</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="21" t="s">
         <v>36</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H11" s="18" t="s">
+      <c r="H11" s="21" t="s">
         <v>36</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J11" s="18"/>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:10">
+      <c r="J11" s="21"/>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>20030013</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="19">
         <v>100300</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="20">
         <v>2003001</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="20">
         <v>3</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="21" t="s">
         <v>36</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H12" s="18" t="s">
+      <c r="H12" s="21" t="s">
         <v>36</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J12" s="18"/>
-    </row>
-    <row r="13" s="2" customFormat="1" ht="16.5" spans="1:10">
+      <c r="J12" s="21"/>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>20030021</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="22">
         <v>100300</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="23">
         <v>2003002</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="23">
         <v>1</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H13" s="21" t="s">
+      <c r="H13" s="24" t="s">
         <v>36</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J13" s="21"/>
-    </row>
-    <row r="14" s="2" customFormat="1" ht="16.5" spans="1:10">
+      <c r="J13" s="24"/>
+    </row>
+    <row r="14" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>20030022</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="22">
         <v>100300</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="23">
         <v>2003002</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="23">
         <v>2</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="F14" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H14" s="21" t="s">
+      <c r="H14" s="24" t="s">
         <v>36</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J14" s="21"/>
-    </row>
-    <row r="15" s="2" customFormat="1" ht="16.5" spans="1:10">
+      <c r="J14" s="24"/>
+    </row>
+    <row r="15" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>20030023</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="22">
         <v>100300</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="23">
         <v>2003002</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="23">
         <v>3</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F15" s="21" t="s">
+      <c r="F15" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H15" s="21" t="s">
+      <c r="H15" s="24" t="s">
         <v>36</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J15" s="21"/>
+      <c r="J15" s="24"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>20070011</v>
       </c>
-      <c r="B16" s="22">
+      <c r="B16" s="25">
         <v>100700</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="14">
         <v>2007001</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="26">
         <v>1</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="16" t="s">
         <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H16" s="14" t="s">
+      <c r="H16" s="16" t="s">
         <v>36</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="J16" s="28"/>
-      <c r="K16" s="6"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="7"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>20070012</v>
       </c>
-      <c r="B17" s="22">
+      <c r="B17" s="25">
         <v>100700</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="14">
         <v>2007001</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="26">
         <v>2</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="16" t="s">
         <v>36</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="H17" s="16" t="s">
         <v>36</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="J17" s="28"/>
-      <c r="K17" s="6"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="7"/>
     </row>
     <row r="18" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>20070013</v>
       </c>
-      <c r="B18" s="22">
+      <c r="B18" s="25">
         <v>100700</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="14">
         <v>2007001</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="26">
         <v>3</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="16" t="s">
         <v>36</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H18" s="14" t="s">
+      <c r="H18" s="16" t="s">
         <v>36</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J18" s="28"/>
-      <c r="K18" s="6"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="7"/>
     </row>
     <row r="19" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>20070014</v>
       </c>
-      <c r="B19" s="22">
+      <c r="B19" s="25">
         <v>100700</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="14">
         <v>2007001</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="26">
         <v>4</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="16" t="s">
         <v>36</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H19" s="14" t="s">
+      <c r="H19" s="16" t="s">
         <v>36</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="J19" s="28"/>
-      <c r="K19" s="6"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="7"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>20070015</v>
       </c>
-      <c r="B20" s="22">
+      <c r="B20" s="25">
         <v>100700</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="14">
         <v>2007001</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="26">
         <v>5</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="16" t="s">
         <v>36</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H20" s="14" t="s">
+      <c r="H20" s="16" t="s">
         <v>36</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="J20" s="28"/>
-      <c r="K20" s="6"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="7"/>
     </row>
     <row r="21" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>20120011</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B21" s="27">
         <v>101200</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="28">
         <v>2012001</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="28">
         <v>1</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="E21" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="F21" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="26" t="s">
+      <c r="F21" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="H21" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="I21" s="26" t="s">
+      <c r="H21" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="J21" s="26"/>
-      <c r="K21" s="26"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
     </row>
     <row r="22" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>20120012</v>
       </c>
-      <c r="B22" s="24">
+      <c r="B22" s="27">
         <v>101200</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="28">
         <v>2012001</v>
       </c>
-      <c r="D22" s="25">
+      <c r="D22" s="28">
         <v>2</v>
       </c>
-      <c r="E22" s="25" t="s">
+      <c r="E22" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="F22" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="26" t="s">
+      <c r="F22" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="H22" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="I22" s="26" t="s">
+      <c r="H22" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="J22" s="26"/>
-      <c r="K22" s="26"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
     </row>
     <row r="23" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>20120013</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B23" s="27">
         <v>101200</v>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="28">
         <v>2012001</v>
       </c>
-      <c r="D23" s="25">
+      <c r="D23" s="28">
         <v>3</v>
       </c>
-      <c r="E23" s="25" t="s">
+      <c r="E23" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="F23" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="26" t="s">
+      <c r="F23" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="H23" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="I23" s="26" t="s">
+      <c r="H23" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
     </row>
     <row r="24" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>20120014</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B24" s="27">
         <v>101200</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="28">
         <v>2012001</v>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="28">
         <v>4</v>
       </c>
-      <c r="E24" s="25" t="s">
+      <c r="E24" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="F24" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="G24" s="26" t="s">
+      <c r="F24" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="H24" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="I24" s="26" t="s">
+      <c r="H24" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
     </row>
     <row r="25" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>20120015</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B25" s="27">
         <v>101200</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="28">
         <v>2012001</v>
       </c>
-      <c r="D25" s="25">
+      <c r="D25" s="28">
         <v>5</v>
       </c>
-      <c r="E25" s="25" t="s">
+      <c r="E25" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="F25" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="G25" s="26" t="s">
+      <c r="F25" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="H25" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="I25" s="26" t="s">
+      <c r="H25" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="I25" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="J25" s="26"/>
-      <c r="K25" s="26"/>
-    </row>
-    <row r="26" ht="16.5" spans="1:10">
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+    </row>
+    <row r="26" ht="16.5" spans="1:11">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>20140011</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="13">
         <v>101400</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="14">
         <v>2014001</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="18">
         <v>1</v>
       </c>
       <c r="E26" t="s">
         <v>44</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="16" t="s">
         <v>36</v>
       </c>
       <c r="G26" t="s">
         <v>70</v>
       </c>
-      <c r="H26" s="14" t="s">
+      <c r="H26" s="16" t="s">
         <v>36</v>
       </c>
       <c r="I26" t="s">
         <v>71</v>
       </c>
-      <c r="J26" s="28"/>
-    </row>
-    <row r="27" ht="16.5" spans="1:10">
+      <c r="J26" s="17"/>
+    </row>
+    <row r="27" ht="16.5" spans="1:11">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>20140012</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="13">
         <v>101400</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="14">
         <v>2014001</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="18">
         <v>2</v>
       </c>
       <c r="E27" t="s">
         <v>44</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="16" t="s">
         <v>36</v>
       </c>
       <c r="G27" t="s">
         <v>72</v>
       </c>
-      <c r="H27" s="14" t="s">
+      <c r="H27" s="16" t="s">
         <v>36</v>
       </c>
       <c r="I27" t="s">
         <v>71</v>
       </c>
-      <c r="J27" s="28"/>
-    </row>
-    <row r="28" ht="16.5" spans="1:10">
+      <c r="J27" s="17"/>
+    </row>
+    <row r="28" ht="16.5" spans="1:11">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>20140013</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="13">
         <v>101400</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="14">
         <v>2014001</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="18">
         <v>3</v>
       </c>
       <c r="E28" t="s">
         <v>44</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="16" t="s">
         <v>36</v>
       </c>
       <c r="G28" t="s">
         <v>73</v>
       </c>
-      <c r="H28" s="14" t="s">
+      <c r="H28" s="16" t="s">
         <v>36</v>
       </c>
       <c r="I28" t="s">
         <v>71</v>
       </c>
-      <c r="J28" s="28"/>
+      <c r="J28" s="17"/>
     </row>
     <row r="29" customFormat="1" ht="16.5" spans="1:11">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>20140044</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="13">
         <v>101400</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="14">
         <v>2014004</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="18">
         <v>4</v>
       </c>
       <c r="E29" t="s">
         <v>44</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="16" t="s">
         <v>36</v>
       </c>
       <c r="G29" t="s">
         <v>74</v>
       </c>
-      <c r="H29" s="14" t="s">
+      <c r="H29" s="16" t="s">
         <v>36</v>
       </c>
       <c r="I29" t="s">
         <v>71</v>
       </c>
-      <c r="J29" s="28"/>
-      <c r="K29" s="6"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="7"/>
     </row>
     <row r="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>20140055</v>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="13">
         <v>101400</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="14">
         <v>2014005</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="18">
         <v>5</v>
       </c>
       <c r="E30" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="16" t="s">
         <v>36</v>
       </c>
       <c r="G30" t="s">
         <v>74</v>
       </c>
-      <c r="H30" s="14" t="s">
+      <c r="H30" s="16" t="s">
         <v>36</v>
       </c>
       <c r="I30" t="s">
         <v>71</v>
       </c>
-      <c r="J30" s="28"/>
-      <c r="K30" s="6"/>
-    </row>
-    <row r="31" ht="16.5" spans="1:10">
+      <c r="J30" s="17"/>
+      <c r="K30" s="7"/>
+    </row>
+    <row r="31" ht="16.5" spans="1:11">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>20140066</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="13">
         <v>101400</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="14">
         <v>2014006</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="18">
         <v>6</v>
       </c>
       <c r="E31" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="16" t="s">
         <v>36</v>
       </c>
       <c r="G31" t="s">
         <v>75</v>
       </c>
-      <c r="H31" s="14" t="s">
+      <c r="H31" s="16" t="s">
         <v>36</v>
       </c>
       <c r="I31" t="s">
         <v>71</v>
       </c>
-      <c r="J31" s="28"/>
-    </row>
-    <row r="32" ht="16.5" spans="1:10">
+      <c r="J31" s="17"/>
+    </row>
+    <row r="32" ht="16.5" spans="1:11">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>20140077</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="13">
         <v>101400</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="14">
         <v>2014007</v>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="18">
         <v>7</v>
       </c>
       <c r="E32" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="16" t="s">
         <v>36</v>
       </c>
       <c r="G32" t="str">
         <f t="shared" ref="G30:G34" si="1">G31</f>
         <v>1_10_10_10_10_1_2_2_1_3_3_3_1_10_10_10_1_4_4_4_4_1_8_8_1_12_1_10_1_5_5_5_5_1_6_6_6_6_6_6_6_1_4_1_10_10_1_7_1_12_1_4_4_1_4_4_4_1_6_6_1_6_6_6_6_6_6_6_6_6_6_6_6_6_6_1_8_1_9_1_9_9_9_9_9_9_9_9_9_1_6_6_6_6_6_1_8_1_2_1_9_9_1_12_1_9_1_8_8_8_8_8_8_1_7_7_7_7_1_8_8_8_8_8_8_8_8_8_1_2_2_2_1_7_7_7_1_6_6_6_6_6_6_6_1_3_3_3_3_1_5_5_5_5_1_8_8_8_1_12_1_2_1_5_5_1_10_1_8_1_3_3_3_3_3_3_3_3_3_3_1_6_6_1_8_8_8_8_8_8_8_1_10_10_1_2_2_2_2_2_2_2_1_2_2_1_8_1_7_7_1_7_7_1_11_11_11_11_1_7_7_1_5_1_2_1_2_1_6_6_6_6_6_6_6_6_1_11_11_11_1_3_3_3_1_6_1_12_1_9_1_5_5_5_1_12_1_2_2_1_9_9_9_1_12_1_11_11_11_1_7_7_7_7_7_7_1_2_2_2_2_1_8_8_8_1_10_10_1_7_1_3_1_5_5_1_4_4_1_11_1_5_5_5_5_5_5_5_1_7_1_8_8_8_1_4_4_4_4_4_4_4_1_12_1_11_11_11_11_11_11_1_2_1_4_4_4_4_4_4_1_11_11_11_11_11_1_9_9_9_9_1_9_9_9_9_9_9_1_5_1_8_8_8_8_1_4_1_4_1_8_8_8_1_11_11_11_11_11_11_11_11_1_9_9_1_8_1_8_8_8_1_12_1_12_1_11_11_11_11_1_5_5_5_5_5_5_5_1_3_3_3_1_11_1_2_2_1_2_2_2_1_2_2_2_2_2_2_2_2_1_9_9_9_9_9_9_9_1_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_1_11_11_11_11_1_10_1_4_4_4_4_4_4_4_4_4_4_1_4_4_4_4_1_3_1_9_9_1_10_10_10_10_10_10_10_1_10_1_12_1_7_1_3</v>
       </c>
-      <c r="H32" s="14" t="s">
+      <c r="H32" s="16" t="s">
         <v>36</v>
       </c>
       <c r="I32" t="s">
         <v>71</v>
       </c>
-      <c r="J32" s="28"/>
-    </row>
-    <row r="33" ht="16.5" spans="1:10">
+      <c r="J32" s="17"/>
+    </row>
+    <row r="33" ht="16.5" spans="1:11">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>20140088</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="13">
         <v>101400</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="14">
         <v>2014008</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="18">
         <v>8</v>
       </c>
       <c r="E33" t="s">
         <v>44</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="16" t="s">
         <v>36</v>
       </c>
       <c r="G33" t="str">
         <f t="shared" si="1"/>
         <v>1_10_10_10_10_1_2_2_1_3_3_3_1_10_10_10_1_4_4_4_4_1_8_8_1_12_1_10_1_5_5_5_5_1_6_6_6_6_6_6_6_1_4_1_10_10_1_7_1_12_1_4_4_1_4_4_4_1_6_6_1_6_6_6_6_6_6_6_6_6_6_6_6_6_6_1_8_1_9_1_9_9_9_9_9_9_9_9_9_1_6_6_6_6_6_1_8_1_2_1_9_9_1_12_1_9_1_8_8_8_8_8_8_1_7_7_7_7_1_8_8_8_8_8_8_8_8_8_1_2_2_2_1_7_7_7_1_6_6_6_6_6_6_6_1_3_3_3_3_1_5_5_5_5_1_8_8_8_1_12_1_2_1_5_5_1_10_1_8_1_3_3_3_3_3_3_3_3_3_3_1_6_6_1_8_8_8_8_8_8_8_1_10_10_1_2_2_2_2_2_2_2_1_2_2_1_8_1_7_7_1_7_7_1_11_11_11_11_1_7_7_1_5_1_2_1_2_1_6_6_6_6_6_6_6_6_1_11_11_11_1_3_3_3_1_6_1_12_1_9_1_5_5_5_1_12_1_2_2_1_9_9_9_1_12_1_11_11_11_1_7_7_7_7_7_7_1_2_2_2_2_1_8_8_8_1_10_10_1_7_1_3_1_5_5_1_4_4_1_11_1_5_5_5_5_5_5_5_1_7_1_8_8_8_1_4_4_4_4_4_4_4_1_12_1_11_11_11_11_11_11_1_2_1_4_4_4_4_4_4_1_11_11_11_11_11_1_9_9_9_9_1_9_9_9_9_9_9_1_5_1_8_8_8_8_1_4_1_4_1_8_8_8_1_11_11_11_11_11_11_11_11_1_9_9_1_8_1_8_8_8_1_12_1_12_1_11_11_11_11_1_5_5_5_5_5_5_5_1_3_3_3_1_11_1_2_2_1_2_2_2_1_2_2_2_2_2_2_2_2_1_9_9_9_9_9_9_9_1_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_1_11_11_11_11_1_10_1_4_4_4_4_4_4_4_4_4_4_1_4_4_4_4_1_3_1_9_9_1_10_10_10_10_10_10_10_1_10_1_12_1_7_1_3</v>
       </c>
-      <c r="H33" s="14" t="s">
+      <c r="H33" s="16" t="s">
         <v>36</v>
       </c>
       <c r="I33" t="s">
         <v>71</v>
       </c>
-      <c r="J33" s="28"/>
+      <c r="J33" s="17"/>
     </row>
     <row r="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>20140099</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="13">
         <v>101400</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="14">
         <v>2014009</v>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="18">
         <v>9</v>
       </c>
       <c r="E34" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="16" t="s">
         <v>36</v>
       </c>
       <c r="G34" t="str">
         <f t="shared" si="1"/>
         <v>1_10_10_10_10_1_2_2_1_3_3_3_1_10_10_10_1_4_4_4_4_1_8_8_1_12_1_10_1_5_5_5_5_1_6_6_6_6_6_6_6_1_4_1_10_10_1_7_1_12_1_4_4_1_4_4_4_1_6_6_1_6_6_6_6_6_6_6_6_6_6_6_6_6_6_1_8_1_9_1_9_9_9_9_9_9_9_9_9_1_6_6_6_6_6_1_8_1_2_1_9_9_1_12_1_9_1_8_8_8_8_8_8_1_7_7_7_7_1_8_8_8_8_8_8_8_8_8_1_2_2_2_1_7_7_7_1_6_6_6_6_6_6_6_1_3_3_3_3_1_5_5_5_5_1_8_8_8_1_12_1_2_1_5_5_1_10_1_8_1_3_3_3_3_3_3_3_3_3_3_1_6_6_1_8_8_8_8_8_8_8_1_10_10_1_2_2_2_2_2_2_2_1_2_2_1_8_1_7_7_1_7_7_1_11_11_11_11_1_7_7_1_5_1_2_1_2_1_6_6_6_6_6_6_6_6_1_11_11_11_1_3_3_3_1_6_1_12_1_9_1_5_5_5_1_12_1_2_2_1_9_9_9_1_12_1_11_11_11_1_7_7_7_7_7_7_1_2_2_2_2_1_8_8_8_1_10_10_1_7_1_3_1_5_5_1_4_4_1_11_1_5_5_5_5_5_5_5_1_7_1_8_8_8_1_4_4_4_4_4_4_4_1_12_1_11_11_11_11_11_11_1_2_1_4_4_4_4_4_4_1_11_11_11_11_11_1_9_9_9_9_1_9_9_9_9_9_9_1_5_1_8_8_8_8_1_4_1_4_1_8_8_8_1_11_11_11_11_11_11_11_11_1_9_9_1_8_1_8_8_8_1_12_1_12_1_11_11_11_11_1_5_5_5_5_5_5_5_1_3_3_3_1_11_1_2_2_1_2_2_2_1_2_2_2_2_2_2_2_2_1_9_9_9_9_9_9_9_1_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_1_11_11_11_11_1_10_1_4_4_4_4_4_4_4_4_4_4_1_4_4_4_4_1_3_1_9_9_1_10_10_10_10_10_10_10_1_10_1_12_1_7_1_3</v>
       </c>
-      <c r="H34" s="14" t="s">
+      <c r="H34" s="16" t="s">
         <v>36</v>
       </c>
       <c r="I34" t="s">
         <v>71</v>
       </c>
-      <c r="J34" s="28"/>
-      <c r="K34" s="6"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="7"/>
     </row>
     <row r="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>20140110</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="13">
         <v>101400</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="14">
         <v>2014010</v>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="18">
         <v>10</v>
       </c>
       <c r="E35" t="s">
         <v>44</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="16" t="s">
         <v>36</v>
       </c>
       <c r="G35" t="s">
         <v>76</v>
       </c>
-      <c r="H35" s="14" t="s">
+      <c r="H35" s="16" t="s">
         <v>36</v>
       </c>
       <c r="I35" t="s">
         <v>71</v>
       </c>
-      <c r="J35" s="28"/>
-      <c r="K35" s="6"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="7"/>
     </row>
     <row r="36" customFormat="1" ht="16.5" spans="1:11">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>20140121</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="13">
         <v>101400</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="14">
         <v>2014011</v>
       </c>
-      <c r="D36" s="15">
+      <c r="D36" s="18">
         <v>11</v>
       </c>
       <c r="E36" t="s">
         <v>44</v>
       </c>
-      <c r="F36" s="14" t="s">
+      <c r="F36" s="16" t="s">
         <v>36</v>
       </c>
       <c r="G36" t="s">
         <v>77</v>
       </c>
-      <c r="H36" s="14" t="s">
+      <c r="H36" s="16" t="s">
         <v>36</v>
       </c>
       <c r="I36" t="s">
         <v>71</v>
       </c>
-      <c r="J36" s="28"/>
-      <c r="K36" s="6"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="7"/>
     </row>
     <row r="37" ht="16.5" spans="1:11">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>20240011</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="13">
         <v>102400</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="14">
         <v>2024001</v>
       </c>
-      <c r="D37" s="13">
+      <c r="D37" s="15">
         <v>1</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="E37" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="F37" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G37" s="14" t="s">
+      <c r="F37" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="H37" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I37" s="14" t="s">
+      <c r="H37" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I37" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
     </row>
     <row r="38" ht="16.5" spans="1:11">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>20240012</v>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="13">
         <v>102400</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="14">
         <v>2024001</v>
       </c>
-      <c r="D38" s="13">
+      <c r="D38" s="15">
         <v>2</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="F38" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38" s="14" t="s">
+      <c r="F38" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H38" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I38" s="14" t="s">
+      <c r="H38" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="J38" s="28"/>
-      <c r="K38" s="28"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
     </row>
     <row r="39" ht="16.5" spans="1:11">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>20240013</v>
       </c>
-      <c r="B39" s="11">
+      <c r="B39" s="13">
         <v>102400</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C39" s="14">
         <v>2024001</v>
       </c>
-      <c r="D39" s="13">
+      <c r="D39" s="15">
         <v>3</v>
       </c>
-      <c r="E39" s="15" t="s">
+      <c r="E39" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="F39" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G39" s="14" t="s">
+      <c r="F39" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H39" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I39" s="14" t="s">
+      <c r="H39" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I39" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="J39" s="28"/>
-      <c r="K39" s="28"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
     </row>
     <row r="40" ht="16.5" spans="1:11">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>20240014</v>
       </c>
-      <c r="B40" s="11">
+      <c r="B40" s="13">
         <v>102400</v>
       </c>
-      <c r="C40" s="12">
+      <c r="C40" s="14">
         <v>2024001</v>
       </c>
-      <c r="D40" s="13">
+      <c r="D40" s="15">
         <v>4</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F40" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G40" s="14" t="s">
+      <c r="F40" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G40" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="H40" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I40" s="14" t="s">
+      <c r="H40" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I40" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
     </row>
     <row r="41" ht="16.5" spans="1:11">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>20240015</v>
       </c>
-      <c r="B41" s="11">
+      <c r="B41" s="13">
         <v>102400</v>
       </c>
-      <c r="C41" s="12">
+      <c r="C41" s="14">
         <v>2024001</v>
       </c>
-      <c r="D41" s="13">
+      <c r="D41" s="15">
         <v>5</v>
       </c>
-      <c r="E41" s="15" t="s">
+      <c r="E41" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F41" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G41" s="14" t="s">
+      <c r="F41" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="H41" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I41" s="14" t="s">
+      <c r="H41" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="28"/>
-      <c r="K41" s="28"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+    </row>
+    <row r="42" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A42" s="5">
+        <f t="shared" si="0"/>
+        <v>20170011</v>
+      </c>
+      <c r="B42" s="30">
+        <v>101700</v>
+      </c>
+      <c r="C42" s="31">
+        <v>2017001</v>
+      </c>
+      <c r="D42" s="31">
+        <v>1</v>
+      </c>
+      <c r="E42" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="F42" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="G42" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="H42" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="I42" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="J42" s="33"/>
+      <c r="K42" s="33"/>
+    </row>
+    <row r="43" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A43" s="5">
+        <f t="shared" si="0"/>
+        <v>20170012</v>
+      </c>
+      <c r="B43" s="30">
+        <v>101700</v>
+      </c>
+      <c r="C43" s="31">
+        <v>2017001</v>
+      </c>
+      <c r="D43" s="31">
+        <v>2</v>
+      </c>
+      <c r="E43" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="F43" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="G43" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="H43" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="I43" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="J43" s="33"/>
+      <c r="K43" s="33"/>
+    </row>
+    <row r="44" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A44" s="5">
+        <f t="shared" si="0"/>
+        <v>20170013</v>
+      </c>
+      <c r="B44" s="30">
+        <v>101700</v>
+      </c>
+      <c r="C44" s="31">
+        <v>2017001</v>
+      </c>
+      <c r="D44" s="31">
+        <v>3</v>
+      </c>
+      <c r="E44" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="F44" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="G44" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="H44" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="I44" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="J44" s="33"/>
+      <c r="K44" s="33"/>
+    </row>
+    <row r="45" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A45" s="5">
+        <f t="shared" si="0"/>
+        <v>20170014</v>
+      </c>
+      <c r="B45" s="30">
+        <v>101700</v>
+      </c>
+      <c r="C45" s="31">
+        <v>2017001</v>
+      </c>
+      <c r="D45" s="31">
+        <v>4</v>
+      </c>
+      <c r="E45" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="F45" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="G45" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="H45" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="I45" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J45" s="33"/>
+      <c r="K45" s="33"/>
+    </row>
+    <row r="46" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A46" s="5">
+        <f t="shared" si="0"/>
+        <v>20170015</v>
+      </c>
+      <c r="B46" s="30">
+        <v>101700</v>
+      </c>
+      <c r="C46" s="31">
+        <v>2017001</v>
+      </c>
+      <c r="D46" s="31">
+        <v>5</v>
+      </c>
+      <c r="E46" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="F46" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="G46" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H46" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="I46" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="J46" s="33"/>
+      <c r="K46" s="33"/>
+    </row>
+    <row r="47" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A47" s="5">
+        <f t="shared" si="0"/>
+        <v>20220011</v>
+      </c>
+      <c r="B47" s="13">
+        <v>102200</v>
+      </c>
+      <c r="C47" s="14">
+        <v>2022001</v>
+      </c>
+      <c r="D47" s="15">
+        <v>1</v>
+      </c>
+      <c r="E47" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="H47" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I47" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="J47" s="17"/>
+      <c r="K47" s="17"/>
+    </row>
+    <row r="48" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A48" s="5">
+        <f t="shared" si="0"/>
+        <v>20220012</v>
+      </c>
+      <c r="B48" s="13">
+        <v>102200</v>
+      </c>
+      <c r="C48" s="14">
+        <v>2022001</v>
+      </c>
+      <c r="D48" s="15">
+        <v>2</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G48" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="H48" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+    </row>
+    <row r="49" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A49" s="5">
+        <f t="shared" si="0"/>
+        <v>20220013</v>
+      </c>
+      <c r="B49" s="13">
+        <v>102200</v>
+      </c>
+      <c r="C49" s="14">
+        <v>2022001</v>
+      </c>
+      <c r="D49" s="15">
+        <v>3</v>
+      </c>
+      <c r="E49" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="H49" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="J49" s="17"/>
+      <c r="K49" s="17"/>
+    </row>
+    <row r="50" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A50" s="5">
+        <f t="shared" si="0"/>
+        <v>20220014</v>
+      </c>
+      <c r="B50" s="13">
+        <v>102200</v>
+      </c>
+      <c r="C50" s="14">
+        <v>2022001</v>
+      </c>
+      <c r="D50" s="15">
+        <v>4</v>
+      </c>
+      <c r="E50" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="H50" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I50" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+    </row>
+    <row r="51" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A51" s="5">
+        <f t="shared" si="0"/>
+        <v>20220015</v>
+      </c>
+      <c r="B51" s="13">
+        <v>102200</v>
+      </c>
+      <c r="C51" s="14">
+        <v>2022001</v>
+      </c>
+      <c r="D51" s="15">
+        <v>5</v>
+      </c>
+      <c r="E51" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="F51" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G51" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="H51" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="98">
   <si>
     <t>id</t>
   </si>
@@ -343,6 +343,36 @@
   </si>
   <si>
     <t>10_7_1_6_2_1_4_6_10_5_3_4_8_10_5_8_14_4_4_5_3_1_14_4_2_8_9_3_1_2_2_2_11_4_7_4_2_8_4_2_3_7_2_14_4_1_3_11_5_4_14_7_5_3_10_2_14_2_2_8_10_1_8_8_5_4_6_5_7_9_10_2_1_3_2_6_1_11_7_1_2_1_2_2_10_5_3_8_6_14_3_10_5_7_6_10_4_1_5_2_2_2_4_7_6_11_7_10_4_5_3_5_5_7_1_5_8_4_3_3_3_2_1_3_8_1_4_14_4_7_6_10_3_6_6_10_2_5_4_2_8_9_3_2_7_10_3_11_7_7_6_3_1_7_1_7_2_2_5_9_5_6_5_4_1_4_3_6_2_14_4_2_4_14_3_5_7_1_3_4_10_2_3_3_3_6_8_4_1_4_5_1_6_1_10_6_10_5_2_6_8_2_5_2_3_1_4_3_9_3_8_6_5_8_4_3_3_14_7_2_3_5_2_1_1_3_6_9_10_5_4_10_4_3_4_8_7_1_7_8_4_10_6_2_7_5_14_6_11_6_14_4_3_8_2_4_6_7_3_7_6_7_1_4_5_9_6_5_1_8_8_9_10_6_7_1_7_2_3_9_8_10_2_4_2_14_6_8_4_3_10_5_2_5_4_7_5_8_7_4_10_7_9_3_9_8_6_1_4_1_8_3_4_3_6_10_4_5_8_1_5_1_4_2_10_7_11_4_10_2_4_2_5_1_4_5_14_5_4_5_3_6_1_3_2_2_5_1_1_5_3_7_8_2_2_8_9_6_1_2_9_8_8_7_5_6_1_9_5_3_2_4_6_8_9_7_4_8_1_2_3_9_8_5_1_5_9_3_9_1_8_10_4_7_2_2_10_4_1_3_4_2_7_14_5_4_5_3_9_8_6_10_6_1_14_5_9_3_2_2_4_3_1_2_5_5_6_4_4_8_3_4_4_11_7_7_7_7_6_8_10_4_8_2_1_3_1_11_3_3_9_10_6_1_4_2_14_6_4_5_5_11_5_6_4_9_2_7_6_5_1_2_3_10_6_11_7_2_6_7_4_2_7_4_3_1_14_6_8_6_8_5_4_14_2_2_10_5_8_6</t>
+  </si>
+  <si>
+    <t>4_3_3_1_1_3_2_2_4_4_4_9_2_3_4_8_7_7_8_3_2_7_4_8_3_2_3_7_9_6_6_5_5_1_1_4_3_7_6_2_2_4_1_1_7_5_9_3_2_1_5_9_2_5_3_4_7_2_6_7_8_1_5_9_7_7_7_9_1_1_6_5_1_1_1_1_9_4_2_2_3_3_3_1_7_1_1_2_2_4_5_7_6_1_3_6_1_7_9_2_2_8_6_2_7_1_3_3_7_5_4_1_8_9_3_3_2_2_2_4_8_3_1_1_1_2_2_2_3_7_2_8_6_1_7_2_2_2_3_7_9_2_2_5_1_3_3_4_5_9_9_3_4_1_2_2_9_2_4_8_8_9_6_2_4_4_2_6_2_1_4_4_2_4_1_8_9_1_1_5_4_6_5_2_2_2_5_7_7_5_8_4_1_3_2_7_7_1_5_3_7_1_2_2_6_5_1_5_3_3_3_4_4_2_6_7_1_3_1_6_2_4_5_1_2_6_8_1_8_2_5_5_8_5_2_1_1_1_1_6_6_8_7_2_4_5_4_7_6_2_9_8_6_6_5_8_4_6_2_2_4_7_9_3_4_4_4_2_7_1_1_7_3_7_2_8_8_8_4_4_1_5_4_3_4_9_9_5_5_6_2_6_6_3_5_5_3_8_8_6_7_7_5_9_3_2_4_3_3_1_3_1_2_9_3_9_9_1_4_2_2_2_1_7_9_5_2_1_2_1_2_1_6_3_3_3_4_5_3_1_3_5_4_4_3_1_9_2_3_3_1_2_2_4_4_1_1_1_9_6_1_1_2_8_2_3_2_4_2_7_3_3_1_3_3_3_2_4_8_4_5_6_2_3_4_2_1_1_6_8_2_5_1_1_3_9_3_2_2_2_5_1_6_9_2_8_6_3_7_6_1_8_1_7_4_9_8_1_8_3_7_6_6_6_1_2_2_2_6_2_8_6_6_6_8_4_6_2_3_7_5_9_6_3_3_4_1_8_4_1_6_2_2_5_5_1_4_9_1_1_1_2_3_4_2_4_2_1_1_5_1_7_1_2_3_5_4_2_8_5_4_6_7_7_6_4_4_2_3_4_3_8_8_4_1_3_1_6_8_3</t>
+  </si>
+  <si>
+    <t>6_9_4_3_1_8_2_1_2_2_1_8_9_4_4_1_4_3_4_2_8_3_1_6_2_7_1_2_8_5_5_3_2_3_6_2_1_6_6_2_3_5_1_1_3_8_6_8_3_5_7_7_2_3_7_2_4_8_9_4_6_2_2_3_7_4_1_4_6_1_9_5_4_1_5_8_5_4_4_5_8_2_1_1_5_4_2_1_5_6_2_4_2_9_1_4_2_4_2_2_3_4_1_2_4_1_7_9_1_4_7_4_2_6_3_2_5_6_9_8_4_8_2_3_7_1_8_2_3_3_7_2_6_7_4_5_3_1_5_4_3_8_6_6_1_4_6_2_9_5_7_9_5_6_3_3_1_3_6_5_2_4_2_6_4_6_8_4_1_6_1_5_2_2_5_5_4_9_6_3_4_3_2_1_7_8_2_6_7_6_6_4_4_2_3_4_1_4_8_7_5_1_7_5_2_4_1_7_7_5_4_3_4_5_3_5_4_1_8_4_6_2_1_8_6_7_1_4_6_2_4_4_1_4_4_5_1_4_6_3_8_4_3_7_6_2_1_8_4_3_5_3_1_9_4_1_3_6_6_5_8_6_1_5_3_3_8_2_4_1_5_1_9_1_5_3_7_4_8_5_1_1_7_5_1_6_5_8_4_6_2_2_1_7_3_5_5_5_3_4_5_5_6_7_6_7_4_6_1_1_3_6_9_4_4_9_5_6_7_9_4_4_4_7_8_6_9_2_2_2_3_5_4_6_8_2_8_7_4_4_5_3_4_9_8_7_4_9_2_7_2_8_7_3_1_5_9_1_4_9_1_4_9_2_4_8_2_1_1_9_9_4_5_3_6_8_1_9_1_1_8_4_6_4_1_3_7_1_4_8_9_6_9_8_7_7_1_8_9_9_6_6_7_8_1_7_5_1_4_2_8_7_2_9_1_2_6_2_4_8_5_8_3_1_7_1_5_8_5_3_1_6_3_5_7_3_4_1_7_4_2_1_5_2_7_8_6_9_4_9_3_6_1_2_5_2_8_4_1_3_4_2_1_8_4_2_5_7_1_2_7_7_2_1_4_8_4_7_5_9_5_9_8_9_6_2_8_2_8_3_3_4_9_7_2_6_7_2_4_8</t>
+  </si>
+  <si>
+    <t>4_1_6_3_6_2_1_1_2_2_9_8_1_2_6_6_3_7_1_8_6_3_3_9_6_1_4_4_2_6_3_5_5_5_7_1_8_7_2_3_7_5_1_6_1_9_5_7_3_9_2_2_6_5_3_8_5_6_9_3_5_2_2_2_9_1_1_6_4_4_5_8_5_6_9_9_1_3_4_4_1_1_3_6_2_2_5_7_6_8_4_4_1_4_2_2_2_2_3_6_1_2_1_6_4_4_9_6_3_2_5_3_5_4_7_7_2_2_4_8_6_5_9_9_2_2_2_7_7_4_4_1_5_7_2_3_2_3_2_3_3_4_5_7_6_1_8_5_5_5_1_2_7_8_8_8_9_3_3_5_2_3_4_2_8_2_2_1_9_2_2_1_1_3_6_3_8_8_6_1_2_2_1_9_1_2_2_1_2_6_3_6_1_4_6_6_8_7_7_5_3_4_3_9_6_6_9_1_1_6_9_4_4_4_6_6_8_6_2_4_4_5_2_5_5_1_9_4_2_1_5_2_9_3_9_2_1_1_6_8_1_1_5_4_5_2_2_4_2_1_2_2_7_6_1_3_3_3_3_9_8_3_1_9_4_8_7_5_8_4_2_7_7_5_3_1_9_9_2_4_4_2_2_2_8_1_2_8_3_3_1_4_6_7_1_3_3_1_4_6_3_3_3_1_6_5_8_7_4_7_4_4_6_5_5_2_1_4_7_3_2_6_1_3_7_8_6_7_1_7_7_1_2_2_9_5_4_4_8_3_4_5_5_2_2_7_6_6_7_7_5_6_2_1_1_3_2_2_2_6_4_6_1_2_8_8_6_4_2_2_1_5_3_2_3_2_7_9_9_6_6_3_5_4_4_1_1_3_1_7_5_4_4_7_9_1_7_2_5_1_3_9_9_9_4_6_5_4_4_4_6_6_1_7_4_4_7_2_5_1_7_9_9_2_6_4_3_1_6_6_1_1_8_1_7_6_4_4_1_4_8_4_8_5_5_2_1_4_8_2_8_4_7_7_8_4_4_2_3_1_3_4_3_1_1_1_8_7_7_4_1_7_1_1_3_4_4_4_4_2_8_8_3_4_1_8_7_2_7_9_3_4_6_5_5_5_5_5_5_1</t>
+  </si>
+  <si>
+    <t>2_7_1_9_6_1_7_1_9_8_7_3_3_9_7_3_2_9_1_6_2_8_3_8_1_3_6_8_4_3_1_4_1_6_2_4_7_3_2_6_4_8_1_1_2_4_6_2_2_6_2_6_5_5_1_1_2_2_1_8_6_5_7_7_2_1_6_3_1_3_6_2_1_7_5_1_9_9_2_7_2_6_2_2_4_6_4_8_5_5_5_5_1_6_4_2_1_8_1_7_4_8_6_6_4_1_1_2_3_1_6_4_3_5_5_1_4_9_4_6_5_1_9_1_8_3_3_3_7_3_2_1_4_9_3_1_1_7_1_4_5_2_4_3_2_7_4_2_2_5_3_3_1_2_6_9_6_5_5_1_1_7_7_3_3_6_6_8_3_7_2_1_8_5_2_3_1_3_8_2_1_9_2_1_1_2_7_2_3_4_4_2_6_6_1_2_2_2_9_5_6_8_3_2_1_4_1_5_7_8_8_6_4_5_2_6_3_7_8_2_6_5_1_4_3_1_3_7_4_3_1_3_3_6_3_2_5_2_9_1_4_7_5_5_4_4_8_2_3_3_1_7_9_6_2_4_6_5_7_9_5_8_1_2_5_2_8_2_5_1_4_3_7_1_2_2_1_1_8_9_6_2_1_5_2_4_3_2_8_3_2_9_1_6_4_2_8_2_2_4_6_1_1_3_9_1_3_3_2_3_8_5_4_2_3_8_7_3_6_5_6_2_9_5_9_7_9_3_6_8_6_6_1_5_6_6_7_4_1_7_3_6_5_5_5_8_1_8_8_1_2_1_3_9_5_7_4_6_1_2_3_6_4_1_8_3_8_2_4_5_3_9_1_3_2_5_5_3_6_4_2_2_1_9_7_7_5_3_4_2_5_4_1_7_6_7_5_2_3_4_3_4_2_6_5_9_6_2_5_8_2_4_1_1_9_3_1_2_5_8_8_4_2_7_4_4_4_3_1_4_7_1_8_4_7_7_6_7_3_6_8_5_1_9_5_2_2_1_8_8_8_3_4_7_6_6_7_1_6_1_4_8_1_3_5_6_2_7_8_4_1_1_1_1_5_5_4_6_2_5_2_6_5_8_4_4_9_2_6_1_1_7_1_1_2_2_9_3_1_5</t>
+  </si>
+  <si>
+    <t>8_1_4_6_6_8_3_9_9_9_6_9_8_3_4_6_4_1_1_6_4_3_8_8_9_4_1_3_3_2_6_6_5_9_9_1_2_4_4_2_8_9_1_4_6_4_1_3_3_4_4_4_4_1_3_8_9_1_6_1_6_2_8_3_3_4_3_8_5_9_4_4_2_2_1_4_4_5_2_8_1_4_6_4_6_5_2_2_1_4_5_9_9_3_6_4_7_4_6_6_2_2_8_8_8_2_3_3_4_5_6_2_2_1_1_8_7_3_7_5_8_1_9_6_6_4_5_6_2_1_8_4_3_1_9_6_3_3_6_6_1_7_7_7_1_7_6_4_6_2_9_1_6_7_2_4_7_3_3_7_7_7_6_2_2_1_9_6_1_8_1_1_2_6_2_3_1_1_1_1_3_4_1_3_2_2_4_1_4_7_1_5_7_3_3_8_1_4_4_4_3_7_6_6_7_3_4_5_9_6_4_9_4_4_8_1_3_7_8_4_6_3_1_1_8_2_1_1_6_8_2_7_7_6_2_3_2_5_6_6_6_2_1_5_5_9_2_3_5_5_2_6_3_4_3_6_8_9_3_5_5_9_9_1_5_5_9_2_5_3_1_3_2_5_4_7_6_6_1_1_8_3_3_9_5_4_7_2_1_6_8_8_6_6_6_6_3_1_6_4_1_9_5_2_3_2_1_6_1_2_4_7_9_9_4_4_4_8_3_1_5_7_4_4_8_8_1_1_3_3_5_6_1_1_1_3_6_4_6_3_2_4_4_3_4_2_8_1_3_3_1_3_9_4_2_6_3_3_1_5_6_2_7_5_7_8_1_7_4_3_4_2_3_1_2_2_2_5_5_5_2_1_6_5_5_1_1_9_5_6_2_6_6_4_1_1_2_5_2_9_3_2_1_1_1_7_2_3_3_3_3_2_2_7_8_8_4_4_1_3_1_3_3_4_6_4_5_2_3_4_6_8_7_4_5_4_5_6_5_5_7_1_1_1_3_1_9_5_6_6_2_2_9_2_5_4_8_5_5_7_2_4_2_5_2_7_6_1_7_5_5_6_4_6_3_2_3_2_2_7_2_2_3_2_8_4_7_1_1_3_9_9_3_4_4_3_3_5_2_2</t>
+  </si>
+  <si>
+    <t>8_1_2_9_8_5_4_6_8_5_3_2_9_4_1_1_2_3_4_8_6_3_2_5_9_1_1_4_3_4_4_5_3_4_1_9_3_9_5_5_8_5_5_6_7_1_5_1_7_7_3_3_3_7_7_2_4_2_8_1_4_5_6_8_4_1_3_1_7_2_6_7_8_3_1_4_4_5_8_1_7_9_4_7_9_2_3_3_7_7_1_8_3_2_8_8_8_3_2_8_1_5_6_3_8_8_4_1_3_1_5_6_1_1_3_2_6_3_4_3_4_2_2_4_7_5_4_7_3_1_2_8_5_7_1_7_1_6_5_3_2_6_7_4_9_4_8_7_7_4_9_1_4_1_1_5_4_3_7_7_1_2_2_8_6_7_4_3_7_6_4_2_3_4_7_3_3_1_4_9_5_5_3_1_1_2_1_6_7_8_5_9_8_5_2_5_3_6_8_6_4_5_7_6_5_8_7_3_7_1_2_3_6_9_2_8_6_8_5_8_2_7_2_5_3_1_8_8_4_6_6_3_7_3_1_2_6_2_1_9_2_3_2_1_7_1_4_9_5_2_7_1_6_3_5_9_2_3_6_2_4_7_8_3_2_9_4_8_1_2_9_7_1_6_6_8_5_1_3_4_2_3_3_2_7_3_6_2_1_8_1_7_3_2_9_2_7_7_7_3_2_4_8_8_2_3_4_2_4_2_6_5_2_8_8_1_8_3_7_5_5_3_5_1_4_3_8_2_2_2_5_3_2_4_4_2_7_3_7_7_6_3_7_6_5_9_1_1_8_3_6_8_3_7_2_4_6_8_2_4_6_6_4_9_1_1_6_5_8_8_5_4_1_6_2_1_1_2_3_1_4_6_4_5_7_1_6_6_7_6_3_2_1_1_6_5_3_8_2_3_1_5_2_4_1_2_2_9_1_8_3_3_9_6_9_8_6_2_3_4_8_4_3_1_3_5_7_5_2_6_7_2_3_1_7_4_4_3_6_7_3_2_8_8_2_1_5_3_2_1_9_7_2_6_4_4_8_1_2_1_9_2_4_2_1_1_4_7_4_1_3_5_9_6_4_8_3_4_3_2_2_7_3_9_3_5_7_1_1_2_6_6_1_5_9_7_8_5_1_7</t>
+  </si>
+  <si>
+    <t>2_1_3_2_2_2_2_9_1_8_1_7_1_6_4_9_8_4_6_2_5_5_5_3_1_8_2_5_1_6_4_7_8_3_7_8_6_1_5_5_5_4_2_3_4_9_2_8_4_3_5_7_2_2_2_8_5_9_9_5_8_3_3_7_2_8_6_6_1_6_1_1_4_6_7_6_4_1_4_4_1_6_7_3_3_4_1_2_3_4_5_8_1_2_2_3_6_8_7_4_1_8_1_7_8_7_1_8_8_6_3_4_2_5_6_6_1_1_1_6_7_7_1_3_2_1_1_1_1_8_2_4_1_3_1_7_5_4_6_1_2_2_5_7_8_1_8_2_4_4_7_7_2_3_8_2_9_8_7_7_7_9_5_5_7_7_7_1_5_2_2_3_5_5_1_1_5_5_5_2_9_9_7_3_6_6_5_2_4_4_9_2_1_3_2_1_4_2_6_5_4_8_4_6_9_7_7_8_8_4_4_8_3_6_4_6_2_2_7_6_7_3_5_1_1_1_4_3_7_5_3_3_1_3_1_1_1_9_9_3_1_4_4_7_7_6_6_7_1_3_2_3_3_3_6_2_6_9_4_4_8_4_6_7_9_7_1_6_6_4_4_1_3_6_6_6_6_2_1_3_6_2_5_4_4_9_7_6_4_3_3_7_6_6_1_3_8_1_6_3_7_1_4_2_3_4_9_5_3_8_1_5_2_6_4_2_3_2_4_3_6_6_5_4_4_9_5_1_9_9_7_7_4_3_7_6_6_1_6_6_1_3_3_2_1_8_3_9_3_3_7_4_6_5_2_6_9_4_4_3_6_5_3_4_2_3_8_3_4_1_4_6_1_8_3_4_5_3_8_1_5_5_4_3_3_1_8_2_8_3_2_1_4_3_3_4_1_8_3_2_2_3_7_8_1_1_8_8_4_7_2_1_5_8_5_7_1_2_4_5_5_6_3_5_2_2_2_3_3_6_3_2_4_1_6_6_6_6_2_3_5_1_6_6_8_1_3_1_3_5_3_5_1_1_8_2_6_6_3_7_7_5_2_3_7_5_4_9_6_9_9_8_9_1_1_6_3_8_8_4_2_6_7_3_2_2_7_8_3_1_2_1_2_7_1_7_3_7_5_4</t>
+  </si>
+  <si>
+    <t>6_7_6_1_8_8_2_8_6_8_8_8_5_8_6_1_5_2_5_3_4_4_9_5_8_5_1_1_8_4_7_2_2_9_5_1_4_2_5_5_9_8_4_6_6_5_6_9_7_9_7_2_8_6_4_2_6_7_1_4_6_8_2_2_7_3_2_1_4_3_1_6_2_4_5_7_1_9_7_6_2_3_6_1_1_6_3_3_7_1_7_3_2_4_9_4_2_5_7_4_6_7_4_1_2_6_6_6_2_2_1_4_1_2_3_8_4_3_2_9_2_1_3_6_8_1_4_1_9_1_6_5_7_8_3_9_6_1_9_8_3_7_7_7_5_9_5_2_9_9_5_2_2_8_5_2_8_8_1_6_8_6_1_7_2_1_1_5_8_1_8_2_4_3_4_8_4_2_7_5_3_4_9_1_6_4_1_4_7_1_4_4_8_8_4_1_7_5_5_8_6_4_5_9_7_2_4_7_1_4_2_1_4_4_6_1_2_4_6_2_6_4_7_3_7_9_3_2_4_5_1_2_5_2_8_1_7_1_7_2_7_1_8_4_6_6_4_1_9_4_7_1_2_5_1_5_3_2_7_2_8_1_1_1_3_9_4_6_2_3_3_4_8_2_8_6_7_8_8_3_5_2_8_5_9_4_2_6_9_3_2_3_1_5_7_7_5_9_3_2_1_3_4_8_6_5_2_3_7_8_7_7_3_4_1_1_6_5_6_8_7_9_9_3_7_5_6_1_1_9_4_2_3_5_4_4_1_2_2_3_2_3_2_1_2_5_4_5_3_5_7_4_3_7_2_7_7_1_8_1_4_1_5_7_1_1_5_4_4_9_7_6_2_1_4_5_8_2_4_2_2_6_2_1_3_2_2_5_5_1_5_2_5_4_4_9_1_9_9_4_4_1_4_3_2_1_7_2_4_1_7_4_6_7_1_7_3_5_2_2_4_4_4_3_4_6_8_4_1_2_2_3_8_2_4_2_2_4_8_2_2_4_7_3_4_1_4_6_6_3_2_9_9_5_5_8_2_1_1_7_3_5_3_5_5_2_1_7_8_7_2_2_8_1_1_2_2_2_3_8_8_2_2_3_4_8_6_5_1_2_4_1_8_3_6_3_1_4_6_7</t>
+  </si>
+  <si>
+    <t>6_4_9_5_6_1_1_1_7_1_2_3_2_1_4_4_1_6_6_8_5_6_5_1_5_6_3_3_4_9_6_2_4_7_7_3_3_7_3_4_2_5_7_5_6_8_4_2_3_3_2_3_9_4_2_2_8_4_4_8_7_5_3_8_5_4_1_1_5_2_8_3_1_4_1_1_9_1_9_3_4_4_8_6_1_6_9_7_5_9_9_6_6_2_3_1_2_2_6_8_3_2_1_4_5_5_5_2_2_1_1_4_5_7_1_2_5_5_5_6_3_5_3_3_1_1_5_9_3_3_7_7_3_3_4_3_3_3_3_9_6_4_3_1_1_1_2_7_7_6_4_5_3_5_2_1_2_8_7_7_7_1_9_3_3_1_5_2_8_8_8_5_3_6_6_7_2_6_6_4_4_4_2_8_3_3_6_2_8_4_1_6_6_4_2_4_7_8_6_6_2_8_3_7_7_3_1_1_5_2_6_6_4_4_6_2_8_7_6_1_2_7_5_2_8_4_4_4_7_9_1_4_8_1_5_3_1_2_4_1_2_2_8_8_8_6_6_1_6_2_1_9_9_1_2_2_9_5_3_9_4_4_4_8_8_3_4_9_1_3_1_2_4_5_4_2_2_4_3_9_7_2_5_7_7_1_3_3_3_3_4_9_4_4_5_2_6_5_9_3_1_1_5_1_6_5_8_9_7_3_8_4_1_6_6_9_7_1_1_5_9_5_2_2_5_9_3_1_4_2_6_3_8_1_4_4_2_2_2_3_2_9_1_6_5_5_5_7_3_6_8_8_5_5_3_3_1_1_3_3_3_1_5_4_3_9_6_5_5_3_4_1_2_3_6_3_7_3_1_1_6_9_1_2_4_9_8_8_7_4_6_4_1_4_5_2_7_7_6_6_8_3_9_7_5_4_6_6_4_9_1_8_4_6_5_4_1_7_4_5_6_1_2_1_3_1_2_1_1_4_1_4_3_6_6_1_2_6_4_6_4_9_9_7_9_2_5_4_4_1_7_7_7_9_3_1_4_2_3_1_1_7_2_8_7_7_3_4_1_1_3_8_3_8_8_8_3_4_4_5_3_6_6_5_7_1_1_9_2_1_1_5_2_2_3_9_2_1_8_3</t>
+  </si>
+  <si>
+    <t>4_7_8_5_7_7_6_4_3_9_3_1_4_4_5_5_5_7_1_6_3_1_3_5_2_1_1_9_2_9_6_1_8_3_4_5_4_2_1_6_4_2_8_7_4_8_6_5_9_1_2_8_8_9_4_6_6_1_6_7_8_1_5_8_6_4_8_9_3_1_4_4_1_5_5_8_5_4_6_2_8_1_9_3_7_9_2_5_5_7_1_2_9_8_1_3_4_7_8_4_9_1_1_2_5_4_6_5_7_2_7_7_6_5_5_5_1_4_2_1_9_3_4_3_3_3_4_1_5_3_4_6_5_4_6_9_6_1_2_1_8_1_2_4_9_2_5_8_2_5_2_1_5_7_1_1_2_2_6_2_9_3_3_6_6_6_2_5_8_1_6_2_4_2_6_8_9_4_7_3_4_5_7_4_2_1_2_6_6_1_6_2_4_7_6_2_1_1_8_1_7_8_8_9_1_7_9_5_4_3_3_5_2_2_7_7_6_1_3_8_9_1_9_3_3_4_2_5_1_5_2_7_3_6_2_4_2_2_9_1_5_7_2_3_3_9_3_5_3_1_6_2_9_6_3_3_1_3_5_6_3_4_2_4_6_1_1_7_3_4_4_4_3_4_7_3_6_8_3_2_4_1_2_1_4_8_5_5_4_4_8_8_1_4_5_4_9_7_1_8_9_3_5_2_4_1_4_7_4_9_1_1_9_3_2_5_2_2_2_4_5_6_5_2_6_9_6_2_8_4_2_7_7_6_3_3_8_7_6_2_4_7_1_1_9_6_2_8_2_8_4_9_5_4_1_3_1_5_7_9_7_8_1_1_2_4_6_5_8_2_2_2_3_2_4_2_2_3_6_1_7_5_3_7_4_1_1_4_7_4_1_2_9_6_2_4_1_8_2_6_4_6_3_1_4_2_3_8_2_4_3_4_5_9_5_5_8_1_3_1_7_3_1_7_7_3_5_1_3_8_7_8_2_2_5_3_3_4_8_6_1_6_8_4_1_8_2_4_5_7_1_6_4_5_6_5_4_2_6_2_7_1_1_5_2_1_7_6_2_3_3_3_8_1_4_6_2_9_3_2_2_6_7_1_6_1_3_9_2_5_6_2_3_2_1_8_4_5_3_9</t>
   </si>
 </sst>
 </file>
@@ -1124,8 +1154,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1651,7 +1683,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -2961,23 +2993,23 @@
       <c r="D42" s="31">
         <v>1</v>
       </c>
-      <c r="E42" s="32" t="s">
+      <c r="E42" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F42" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="G42" s="32" t="s">
+      <c r="F42" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G42" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H42" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="I42" s="32" t="s">
+      <c r="H42" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I42" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="J42" s="33"/>
-      <c r="K42" s="33"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
     </row>
     <row r="43" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A43" s="5">
@@ -2993,23 +3025,23 @@
       <c r="D43" s="31">
         <v>2</v>
       </c>
-      <c r="E43" s="32" t="s">
+      <c r="E43" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F43" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="G43" s="32" t="s">
+      <c r="F43" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G43" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H43" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="I43" s="32" t="s">
+      <c r="H43" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I43" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="J43" s="33"/>
-      <c r="K43" s="33"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="32"/>
     </row>
     <row r="44" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A44" s="5">
@@ -3025,23 +3057,23 @@
       <c r="D44" s="31">
         <v>3</v>
       </c>
-      <c r="E44" s="32" t="s">
+      <c r="E44" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F44" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="G44" s="32" t="s">
+      <c r="F44" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G44" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H44" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="I44" s="32" t="s">
+      <c r="H44" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I44" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="J44" s="33"/>
-      <c r="K44" s="33"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="32"/>
     </row>
     <row r="45" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A45" s="5">
@@ -3057,23 +3089,23 @@
       <c r="D45" s="31">
         <v>4</v>
       </c>
-      <c r="E45" s="32" t="s">
+      <c r="E45" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F45" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="G45" s="32" t="s">
+      <c r="F45" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G45" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H45" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="I45" s="32" t="s">
+      <c r="H45" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I45" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="J45" s="33"/>
-      <c r="K45" s="33"/>
+      <c r="J45" s="32"/>
+      <c r="K45" s="32"/>
     </row>
     <row r="46" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A46" s="5">
@@ -3089,23 +3121,23 @@
       <c r="D46" s="31">
         <v>5</v>
       </c>
-      <c r="E46" s="32" t="s">
+      <c r="E46" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F46" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="G46" s="32" t="s">
+      <c r="F46" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G46" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H46" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="I46" s="32" t="s">
+      <c r="H46" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I46" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="J46" s="33"/>
-      <c r="K46" s="33"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
     </row>
     <row r="47" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A47" s="5">
@@ -3266,6 +3298,166 @@
       </c>
       <c r="J51" s="17"/>
       <c r="K51" s="17"/>
+    </row>
+    <row r="52" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A52" s="5">
+        <f>C52*10+D52</f>
+        <v>20210011</v>
+      </c>
+      <c r="B52" s="13">
+        <v>102100</v>
+      </c>
+      <c r="C52" s="33">
+        <v>2021001</v>
+      </c>
+      <c r="D52" s="33">
+        <v>1</v>
+      </c>
+      <c r="E52" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F52" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G52" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="H52" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I52" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
+    </row>
+    <row r="53" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A53" s="5">
+        <f>C53*10+D53</f>
+        <v>20210012</v>
+      </c>
+      <c r="B53" s="13">
+        <v>102100</v>
+      </c>
+      <c r="C53" s="33">
+        <v>2021001</v>
+      </c>
+      <c r="D53" s="33">
+        <v>2</v>
+      </c>
+      <c r="E53" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F53" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H53" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I53" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="J53" s="17"/>
+      <c r="K53" s="17"/>
+    </row>
+    <row r="54" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A54" s="5">
+        <f>C54*10+D54</f>
+        <v>20210013</v>
+      </c>
+      <c r="B54" s="13">
+        <v>102100</v>
+      </c>
+      <c r="C54" s="33">
+        <v>2021001</v>
+      </c>
+      <c r="D54" s="33">
+        <v>3</v>
+      </c>
+      <c r="E54" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F54" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G54" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="H54" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I54" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+    </row>
+    <row r="55" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A55" s="5">
+        <f>C55*10+D55</f>
+        <v>20210014</v>
+      </c>
+      <c r="B55" s="13">
+        <v>102100</v>
+      </c>
+      <c r="C55" s="33">
+        <v>2021001</v>
+      </c>
+      <c r="D55" s="33">
+        <v>4</v>
+      </c>
+      <c r="E55" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="F55" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G55" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="H55" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I55" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="J55" s="17"/>
+      <c r="K55" s="17"/>
+    </row>
+    <row r="56" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A56" s="5">
+        <f>C56*10+D56</f>
+        <v>20210015</v>
+      </c>
+      <c r="B56" s="13">
+        <v>102100</v>
+      </c>
+      <c r="C56" s="33">
+        <v>2021001</v>
+      </c>
+      <c r="D56" s="33">
+        <v>5</v>
+      </c>
+      <c r="E56" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F56" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G56" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="H56" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I56" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="112">
   <si>
     <t>id</t>
   </si>
@@ -318,31 +318,31 @@
     <t>2_6_6_9_1_4_9_4_5_7_9_5_1_7_1_10_5_10_5_7_2_4_6_1_3_10_5_10_6_1_9_3_4_9_5_14_1_2_1_7_4_5_2_5_1_10_4_2_1_6_3_10_3_3_8_10_7_14_5_2_1_8_1_2_14_7_2_3_10_6_9_2_2_4_9_1_6_4_3_4_6_8_4_6_2_5_1_3_3_10_7_8_6_1_3_3_2_4_9_2_10_7_7_5_1_1_11_7_3_5_11_5_3_1_2_1_2_8_7_10_6_4_9_3_7_8_1_2_1_1_3_2_4_1_10_5_5_4_10_6_6_5_1_7_9_9_5_6_4_5_2_6_2_4_8_6_2_9_2_5_3_8_7_10_1_2_2_8_9_10_5_6_5_7_1_9_1_6_3_11_3_7_5_14_7_4_3_4_6_10_3_4_2_8_5_10_5_8_14_1_11_7_9_5_1_10_2_1_7_10_5_5_10_3_3_14_4_2_1_1_1_1_1_7_2_6_14_3_1_3_2_8_6_7_6_5_8_6_5_8_5_4_9_2_1_2_3_2_6_4_14_5_1_11_7_2_5_7_2_4_3_4_7_4_4_1_4_10_6_10_2_5_10_6_6_5_14_7_3_3_8_5_5_4_5_8_4_2_2_10_4_6_9_1_5_1_9_5_5_5_3_6_11_6_6_2_3_1_7_8_9_2_6_1_3_3_2_8_3_6_10_1_2_3_1_3_2_6_10_6_5_4_8_9_7_2_11_5_1_8_10_6_4_4_1_1_2_3_5_3_2_4_9_3_1_7_3_2_5_10_7_6_4_5_10_1_2_1_3_5_1_1_1_1_10_1_3_2_9_14_5_2_4_3_2_8_11_3_3_10_4_10_3_8_1_10_3_11_7_14_5_5_4_6_2_7_10_7_10_7_8_11_5_1_6_1_2_8_4_2_10_7_7_1_9_10_7_9_1_7_8_7_2_5_4_2_4_6_7_4_10_5_3_4_4_1_6_7_6_1_10_2_2_6_5_14_4_3_2_10_2_2_7_14_5_1_4_1_7_4_1_2_6_9_9_2_8_2_10_7_9_1_6_1_9_14_6_3_2_1_9_7_4_6_6_9_4_5_4_7</t>
   </si>
   <si>
-    <t>3_3_5_4_2_4_1_1_5_6_1_2_2_2_2_1_8_8_1_1_2_2_2_4_5_8_2_2_2_1_4_4_4_7_9_9_2_2_1_3_6_2_3_3_1_4_9_4_2_2_2_4_2_1_1_2_2_2_7_1_2_4_9_8_2_6_5_5_10_6_1_5_2_3_8_4_4_7_8_6_3_4_1_2_5_2_4_1_4_6_7_6_7_6_1_2_10_4_2_4_1_4_2_3_2_6_2_3_3_3_2_5_8_1_1_1_2_1_2_7_8_2_7_3_2_5_9_9_1_1_8_2_3_7_3_10_6_2_2_9_3_1_4_7_1_2_8_1_7_3_10_1_4_3_4_8_4_4_8_1_9_3_4_4_2_2_7_6_5_5_7_4_1_2_1_4_5_3_4_1_1_5_4_5_5_6_1_9_8_5_3_7_4_1_3_5_6_3_10_1_5_3_4_9_8_8_9_8_6_2_3_6_6_3_4_3_3_8_7_2_9_9_3_1_1_1_4_4_8_5_1_3_2_10_6_4_8_2_7_4_2_4_6_2_6_2_1_5_2_2_3_3_9_2_8_9_8_6_8_1_7_1_7_6_9_5_4_6_1_4_8_1_1_4_1_2_2_4_2_1_2_1_3_4_5_2_2_6_5_6_2_4_2_9_3_1_3_8_4_1_1_5_4_4_2_2_2_4_1_6_6_4_2_7_2_3_7_1_4_6_2_3_3_7_3_2_2_2_4_1_1_5_3_1_2_9_8_6_4_2_3_2_2_7_7_1_2_4_4_1_2_2_9_3_9_6_6_1_3_3_3_4_6_6_1_1_6_3_3_8_5_2_2_3_3_10_4_4_4_5_10_2_5_5_1_1_6_6_5_9_6_6_6_1_2_3_5_5_1_9_5_3_3_4_8_2_6_4_4_6_6_4_4_3_3_7_7_7_1_2_9_9_10_6_6_3_1_5_7_4_4_8_3_5_5_2_5_2_2_2_6_4_6_4_3_2_1_2_1_10_3_1_10_4_6_7_1_6_1_3_7_7_8_3_5_5_2_5_7_2_5_4_1_4_10_9_6_4_4_3_2_2_1_3_6_4_2_8_1_1_5_7_4_10_7_7_1_4_1_4</t>
+    <t>3_3_5_4_2_4_1_1_5_6_1_2_2_2_2_1_7_7_1_1_2_2_2_4_5_8_2_2_2_1_4_4_4_7_9_9_2_2_1_3_6_2_3_3_1_4_9_4_2_2_2_4_2_1_1_2_2_2_7_1_2_4_9_8_2_6_5_5_10_6_1_5_2_3_8_4_4_7_8_6_3_4_1_2_5_2_4_1_4_6_7_6_7_6_1_2_10_4_2_4_1_4_2_3_2_6_2_3_3_3_2_5_8_1_1_1_2_1_2_7_8_2_7_3_2_5_9_9_1_1_8_2_3_7_3_10_6_2_2_9_3_1_4_7_1_2_8_1_7_3_10_1_4_3_4_8_4_4_8_1_9_3_4_4_2_2_7_6_5_5_7_4_1_2_1_4_5_3_4_1_1_5_4_5_5_6_1_9_8_5_3_7_4_1_3_5_6_3_10_1_5_3_4_9_7_7_9_8_6_2_3_6_6_3_4_3_3_8_7_2_9_9_3_1_1_1_4_4_8_5_1_3_2_10_6_4_8_2_7_4_2_4_6_2_6_2_1_5_2_2_3_3_9_2_8_9_8_6_8_1_7_1_7_6_9_5_4_6_1_4_8_1_1_4_1_2_2_4_2_1_2_1_3_4_5_2_2_6_5_6_2_4_2_9_3_1_3_8_4_1_1_5_4_4_2_2_2_4_1_6_6_4_2_7_2_3_7_1_4_6_2_3_3_7_3_2_2_2_4_1_1_5_3_1_2_9_8_6_4_2_3_2_2_7_7_1_2_4_4_1_2_2_9_3_9_6_6_1_3_3_3_4_6_6_1_1_6_3_3_8_5_2_2_3_3_10_4_4_4_5_10_2_5_5_1_1_6_6_5_9_6_6_6_1_2_3_5_5_1_9_5_3_3_4_8_2_6_4_4_6_6_4_4_3_3_7_7_7_1_2_9_9_10_6_6_3_1_5_7_4_4_8_3_5_5_2_5_2_2_2_6_4_6_4_3_2_1_2_1_10_3_1_10_4_6_7_1_6_1_3_7_7_8_3_5_5_2_5_7_2_5_4_1_4_10_9_6_4_4_3_2_2_1_3_6_4_2_8_1_1_5_7_4_10_7_7_1_4_1_4</t>
   </si>
   <si>
     <t>7_7_7</t>
   </si>
   <si>
-    <t>7_6_9_3_7_1_11_4_2_9_5_8_6_2_2_6_4_2_7_5_4_5_1_9_8_1_6_2_3_6_4_3_8_1_5_5_5_1_3_2_2_1_8_1_1_2_7_5_5_11_5_10_7_6_1_1_6_8_2_1_7_9_1_9_2_2_1_7_6_10_3_1_9_4_7_5_3_10_7_7_6_1_2_9_8_8_1_7_2_2_4_6_1_5_7_5_11_5_8_7_5_1_3_2_3_2_4_7_3_10_5_10_1_4_4_6_7_3_7_6_11_4_8_6_6_1_7_8_10_2_4_7_6_2_1_1_6_5_5_7_1_9_14_6_5_5_2_6_2_9_7_6_8_6_8_3_2_6_3_1_6_8_4_9_3_3_10_2_8_3_7_7_7_14_1_8_9_10_7_4_8_1_14_4_10_4_6_2_3_4_1_2_1_4_9_3_2_14_3_4_14_5_5_11_2_1_8_6_3_4_10_1_1_2_9_2_2_4_3_1_5_4_11_7_8_2_9_6_7_7_2_4_14_7_4_6_1_3_6_4_8_2_3_9_2_2_5_10_5_9_6_8_4_6_6_9_8_1_4_11_6_3_9_7_7_3_2_3_5_1_3_7_7_8_11_4_11_6_10_5_1_1_4_3_9_14_5_6_3_5_10_5_1_5_5_4_3_2_10_6_2_5_2_2_1_2_4_5_3_9_7_1_6_7_3_14_5_10_4_6_8_8_7_9_7_3_1_4_3_7_14_1_1_14_3_3_4_3_4_9_8_8_10_2_6_1_9_1_4_5_8_7_5_10_4_6_7_1_4_9_5_1_7_4_5_4_7_7_1_3_5_9_9_7_3_14_5_5_10_5_6_2_4_7_6_2_2_1_6_7_5_3_9_1_9_2_1_7_10_7_3_5_4_9_6_8_3_1_4_9_5_5_1_3_4_5_4_4_6_5_3_5_10_2_4_7_9_1_3_8_4_10_5_6_5_7_7_1_1_2_7_7_2_5_10_6_3_10_7_5_7_1_10_7_2_6_7_9_3_6_10_4_1_2_9_3_3_2_2_11_6_5_2_1_7_6_1_2_2_2_14_4_6_10_4_8_9_6_9_9_7_1_6_4_10_2_8_2_1_7</t>
+    <t>7_6_9_3_7_1_11_4_2_9_5_8_6_2_2_6_4_2_7_5_4_5_1_9_8_1_6_2_3_6_4_3_8_1_5_5_5_1_3_2_2_1_8_1_1_2_7_5_5_11_5_10_7_6_1_1_6_8_2_1_7_9_1_9_2_2_1_7_6_10_3_1_9_4_7_5_3_10_7_7_6_1_2_9_7_7_1_7_2_2_4_6_1_5_7_5_11_5_8_7_5_1_3_2_3_2_4_7_3_10_5_10_1_4_4_6_7_3_7_6_11_4_8_6_6_1_7_8_10_2_4_7_6_2_1_1_6_5_5_7_1_9_14_6_5_5_2_6_2_9_7_6_8_6_8_3_2_6_3_1_6_8_4_9_3_3_10_2_8_3_7_7_7_14_1_8_9_10_7_4_8_1_14_4_10_4_6_2_3_4_1_2_1_4_9_3_2_14_3_4_14_5_5_11_2_1_8_6_3_4_10_1_1_2_9_2_2_4_3_1_5_4_11_7_8_2_9_6_7_7_2_4_14_7_4_6_1_3_6_4_8_2_3_9_2_2_5_10_5_9_6_8_4_6_6_9_8_1_4_11_6_3_9_7_7_3_2_3_5_1_3_7_7_8_11_4_11_6_10_5_1_1_4_3_9_14_5_6_3_5_10_5_1_5_5_4_3_2_10_6_2_5_2_2_1_2_4_5_3_9_7_1_6_7_3_14_5_10_4_6_7_7_7_9_7_3_1_4_3_7_14_1_1_14_3_3_4_3_4_9_7_7_10_2_6_1_9_1_4_5_8_7_5_10_4_6_7_1_4_9_5_1_7_4_5_4_7_7_1_3_5_9_9_7_3_14_5_5_10_5_6_2_4_7_6_2_2_1_6_7_5_3_9_1_9_2_1_7_10_7_3_5_4_9_6_8_3_1_4_9_5_5_1_3_4_5_4_4_6_5_3_5_10_2_4_7_9_1_3_8_4_10_5_6_5_7_7_1_1_2_7_7_2_5_10_6_3_10_7_5_7_1_10_7_2_6_7_9_3_6_10_4_1_2_9_3_3_2_2_11_6_5_2_1_7_6_1_2_2_2_14_4_6_10_4_8_9_6_9_9_7_1_6_4_10_2_8_2_1_7</t>
   </si>
   <si>
     <t>8_8_8</t>
   </si>
   <si>
-    <t>6_1_9_4_3_1_9_5_5_7_9_2_2_8_3_4_5_4_7_7_2_1_14_5_8_6_7_9_7_8_4_4_11_5_2_3_6_8_14_3_7_5_1_8_1_2_10_6_2_1_3_14_2_9_8_2_4_6_5_9_6_3_4_11_4_6_1_7_7_3_1_10_1_4_1_6_3_8_2_6_2_2_10_6_3_3_5_6_2_4_7_1_7_11_4_7_1_6_6_5_4_7_6_3_1_5_6_6_7_5_8_8_1_7_7_9_6_2_2_2_7_2_9_4_4_6_5_11_7_1_8_9_4_3_4_6_9_8_6_3_5_2_7_10_5_7_10_6_5_5_6_10_5_2_3_6_8_3_10_2_8_10_7_2_4_7_8_7_8_9_3_8_11_7_1_4_3_14_1_1_5_4_4_2_2_6_10_3_3_2_6_2_3_1_2_10_5_1_9_1_5_8_2_14_5_5_6_1_1_3_3_7_1_7_14_2_4_2_14_3_3_1_2_8_2_3_9_6_8_7_3_5_10_1_10_5_6_4_9_3_7_10_7_7_10_3_3_3_5_10_5_8_4_2_6_2_9_5_6_2_1_2_5_6_10_6_4_9_1_4_8_14_4_9_2_3_9_9_5_10_7_5_7_8_9_3_4_8_4_4_4_6_8_7_8_8_5_9_1_6_6_6_8_5_14_2_9_8_3_5_7_7_1_3_2_14_5_8_11_2_2_5_4_8_6_10_6_2_6_5_2_5_7_14_5_8_8_1_4_11_3_9_2_4_2_3_5_3_9_3_2_4_2_7_10_7_6_4_4_3_3_1_4_4_7_2_3_1_1_8_3_7_5_3_1_9_2_14_3_6_5_2_1_9_1_1_10_6_3_3_9_14_7_2_10_5_5_5_1_2_5_7_3_8_1_8_2_14_5_9_8_8_4_1_1_2_6_4_6_8_8_8_8_6_5_8_14_4_8_1_4_6_5_3_14_6_4_8_3_6_9_2_2_3_2_6_7_4_6_4_2_5_11_7_3_1_5_4_4_3_1_2_8_4_4_10_6_7_2_10_3_2_8_6_1_8_2_1_3_8_8_2_4_5_3_14_7_11_2_8_10_5_2_7_4_1_1_14_4_2</t>
+    <t>6_1_9_4_3_1_9_5_5_7_9_2_2_8_3_4_5_4_7_7_2_1_14_5_8_6_7_9_7_8_4_4_11_5_2_3_6_8_14_3_7_5_1_8_1_2_10_6_2_1_3_14_2_9_8_2_4_6_5_9_6_3_4_11_4_6_1_7_7_3_1_10_1_4_1_6_3_8_2_6_2_2_10_6_3_3_5_6_2_4_7_1_7_11_4_7_1_6_6_5_4_7_6_3_1_5_6_6_7_5_7_7_1_7_7_9_6_2_2_2_7_2_9_4_4_6_5_11_7_1_8_9_4_3_4_6_9_8_6_3_5_2_7_10_5_7_10_6_5_5_6_10_5_2_3_6_8_3_10_2_8_10_7_2_4_7_8_7_8_9_3_8_11_7_1_4_3_14_1_1_5_4_4_2_2_6_10_3_3_2_6_2_3_1_2_10_5_1_9_1_5_8_2_14_5_5_6_1_1_3_3_7_1_7_14_2_4_2_14_3_3_1_2_8_2_3_9_6_8_7_3_5_10_1_10_5_6_4_9_3_7_10_7_7_10_3_3_3_5_10_5_8_4_2_6_2_9_5_6_2_1_2_5_6_10_6_4_9_1_4_8_14_4_9_2_3_9_9_5_10_7_5_7_8_9_3_4_8_4_4_4_6_8_7_7_7_5_9_1_6_6_6_8_5_14_2_9_8_3_5_7_7_1_3_2_14_5_8_11_2_2_5_4_8_6_10_6_2_6_5_2_5_7_14_5_7_7_1_4_11_3_9_2_4_2_3_5_3_9_3_2_4_2_7_10_7_6_4_4_3_3_1_4_4_7_2_3_1_1_8_3_7_5_3_1_9_2_14_3_6_5_2_1_9_1_1_10_6_3_3_9_14_7_2_10_5_5_5_1_2_5_7_3_8_1_8_2_14_5_9_7_7_4_1_1_2_6_4_6_7_7_7_7_6_5_8_14_4_8_1_4_6_5_3_14_6_4_8_3_6_9_2_2_3_2_6_7_4_6_4_2_5_11_7_3_1_5_4_4_3_1_2_8_4_4_10_6_7_2_10_3_2_8_6_1_8_2_1_3_7_7_2_4_5_3_14_7_11_2_8_10_5_2_7_4_1_1_14_4_2</t>
   </si>
   <si>
     <t>9_9_9</t>
   </si>
   <si>
-    <t>5_2_3_8_2_4_7_2_8_5_10_5_4_4_11_7_8_5_3_3_7_4_7_5_9_2_10_4_2_4_2_2_7_10_7_1_1_6_7_10_7_5_10_3_8_10_6_3_14_4_7_9_2_4_10_3_3_4_1_9_2_6_8_3_2_5_10_7_3_4_7_1_8_1_2_9_2_11_2_2_4_1_10_5_1_4_9_9_3_7_2_8_7_9_3_1_3_9_2_4_2_2_6_9_3_1_8_8_3_8_8_6_11_5_3_2_5_2_8_8_4_9_7_4_6_4_1_14_3_11_7_4_1_9_8_7_6_6_3_8_2_8_10_7_1_7_4_7_9_2_4_2_3_2_8_4_4_8_5_4_3_3_4_7_4_4_2_8_1_7_4_8_9_9_6_6_5_8_1_4_1_8_9_3_7_11_6_4_6_6_4_11_6_3_1_9_1_8_2_7_6_11_3_8_7_8_7_2_6_2_3_1_8_7_2_9_4_1_3_3_6_11_7_10_5_6_4_7_10_6_4_2_9_6_3_8_3_2_2_2_4_5_6_1_8_1_7_8_1_1_3_9_10_5_3_3_2_9_6_6_7_2_10_5_7_2_6_7_8_9_1_8_7_1_2_1_4_2_9_10_2_5_10_3_6_1_1_8_10_2_10_2_2_5_14_5_4_9_9_10_4_1_9_9_11_7_10_4_7_5_2_7_4_10_5_3_7_1_3_14_4_1_10_1_5_1_5_11_6_3_9_10_6_4_3_10_4_6_3_9_2_6_10_6_11_4_14_3_7_7_1_7_10_6_14_7_8_2_10_3_7_3_9_5_3_2_10_6_4_8_4_6_6_6_8_1_5_10_7_4_3_1_7_4_9_1_1_1_1_9_1_1_9_1_4_7_5_4_3_1_5_5_4_8_5_9_2_4_10_6_6_10_6_7_5_4_3_4_1_4_9_4_3_5_8_7_10_6_2_5_1_8_5_8_1_5_4_1_4_7_6_1_3_8_6_4_4_3_5_6_2_3_6_4_2_4_2_4_1_5_1_10_7_1_3_9_4_4_5_11_5_4_7_14_3_1_7_2_1_4_3_4_5_2_4_6_5_8_2_4_1_4_8_1_6_2_3_2_9_3</t>
+    <t>5_2_3_8_2_4_7_2_8_5_10_5_4_4_11_7_8_5_3_3_7_4_7_5_9_2_10_4_2_4_2_2_7_10_7_1_1_6_7_10_7_5_10_3_8_10_6_3_14_4_7_9_2_4_10_3_3_4_1_9_2_6_8_3_2_5_10_7_3_4_7_1_8_1_2_9_2_11_2_2_4_1_10_5_1_4_9_9_3_7_2_8_7_9_3_1_3_9_2_4_2_2_6_9_3_1_7_7_3_7_7_6_11_5_3_2_5_2_7_7_4_9_7_4_6_4_1_14_3_11_7_4_1_9_8_7_6_6_3_8_2_8_10_7_1_7_4_7_9_2_4_2_3_2_8_4_4_8_5_4_3_3_4_7_4_4_2_8_1_7_4_8_9_9_6_6_5_8_1_4_1_8_9_3_7_11_6_4_6_6_4_11_6_3_1_9_1_8_2_7_6_11_3_8_7_8_7_2_6_2_3_1_8_7_2_9_4_1_3_3_6_11_7_10_5_6_4_7_10_6_4_2_9_6_3_8_3_2_2_2_4_5_6_1_8_1_7_8_1_1_3_9_10_5_3_3_2_9_6_6_7_2_10_5_7_2_6_7_8_9_1_8_7_1_2_1_4_2_9_10_2_5_10_3_6_1_1_8_10_2_10_2_2_5_14_5_4_9_9_10_4_1_9_9_11_7_10_4_7_5_2_7_4_10_5_3_7_1_3_14_4_1_10_1_5_1_5_11_6_3_9_10_6_4_3_10_4_6_3_9_2_6_10_6_11_4_14_3_7_7_1_7_10_6_14_7_8_2_10_3_7_3_9_5_3_2_10_6_4_8_4_6_6_6_8_1_5_10_7_4_3_1_7_4_9_1_1_1_1_9_1_1_9_1_4_7_5_4_3_1_5_5_4_8_5_9_2_4_10_6_6_10_6_7_5_4_3_4_1_4_9_4_3_5_8_7_10_6_2_5_1_8_5_8_1_5_4_1_4_7_6_1_3_8_6_4_4_3_5_6_2_3_6_4_2_4_2_4_1_5_1_10_7_1_3_9_4_4_5_11_5_4_7_14_3_1_7_2_1_4_3_4_5_2_4_6_5_8_2_4_1_4_8_1_6_2_3_2_9_3</t>
   </si>
   <si>
     <t>10_10_10</t>
   </si>
   <si>
-    <t>10_7_1_6_2_1_4_6_10_5_3_4_8_10_5_8_14_4_4_5_3_1_14_4_2_8_9_3_1_2_2_2_11_4_7_4_2_8_4_2_3_7_2_14_4_1_3_11_5_4_14_7_5_3_10_2_14_2_2_8_10_1_8_8_5_4_6_5_7_9_10_2_1_3_2_6_1_11_7_1_2_1_2_2_10_5_3_8_6_14_3_10_5_7_6_10_4_1_5_2_2_2_4_7_6_11_7_10_4_5_3_5_5_7_1_5_8_4_3_3_3_2_1_3_8_1_4_14_4_7_6_10_3_6_6_10_2_5_4_2_8_9_3_2_7_10_3_11_7_7_6_3_1_7_1_7_2_2_5_9_5_6_5_4_1_4_3_6_2_14_4_2_4_14_3_5_7_1_3_4_10_2_3_3_3_6_8_4_1_4_5_1_6_1_10_6_10_5_2_6_8_2_5_2_3_1_4_3_9_3_8_6_5_8_4_3_3_14_7_2_3_5_2_1_1_3_6_9_10_5_4_10_4_3_4_8_7_1_7_8_4_10_6_2_7_5_14_6_11_6_14_4_3_8_2_4_6_7_3_7_6_7_1_4_5_9_6_5_1_8_8_9_10_6_7_1_7_2_3_9_8_10_2_4_2_14_6_8_4_3_10_5_2_5_4_7_5_8_7_4_10_7_9_3_9_8_6_1_4_1_8_3_4_3_6_10_4_5_8_1_5_1_4_2_10_7_11_4_10_2_4_2_5_1_4_5_14_5_4_5_3_6_1_3_2_2_5_1_1_5_3_7_8_2_2_8_9_6_1_2_9_8_8_7_5_6_1_9_5_3_2_4_6_8_9_7_4_8_1_2_3_9_8_5_1_5_9_3_9_1_8_10_4_7_2_2_10_4_1_3_4_2_7_14_5_4_5_3_9_8_6_10_6_1_14_5_9_3_2_2_4_3_1_2_5_5_6_4_4_8_3_4_4_11_7_7_7_7_6_8_10_4_8_2_1_3_1_11_3_3_9_10_6_1_4_2_14_6_4_5_5_11_5_6_4_9_2_7_6_5_1_2_3_10_6_11_7_2_6_7_4_2_7_4_3_1_14_6_8_6_8_5_4_14_2_2_10_5_8_6</t>
+    <t>10_7_1_6_2_1_4_6_10_5_3_4_8_10_5_8_14_4_4_5_3_1_14_4_2_8_9_3_1_2_2_2_11_4_7_4_2_8_4_2_3_7_2_14_4_1_3_11_5_4_14_7_5_3_10_2_14_2_2_8_10_1_7_7_5_4_6_5_7_9_10_2_1_3_2_6_1_11_7_1_2_1_2_2_10_5_3_8_6_14_3_10_5_7_6_10_4_1_5_2_2_2_4_7_6_11_7_10_4_5_3_5_5_7_1_5_8_4_3_3_3_2_1_3_8_1_4_14_4_7_6_10_3_6_6_10_2_5_4_2_8_9_3_2_7_10_3_11_7_7_6_3_1_7_1_7_2_2_5_9_5_6_5_4_1_4_3_6_2_14_4_2_4_14_3_5_7_1_3_4_10_2_3_3_3_6_8_4_1_4_5_1_6_1_10_6_10_5_2_6_8_2_5_2_3_1_4_3_9_3_8_6_5_8_4_3_3_14_7_2_3_5_2_1_1_3_6_9_10_5_4_10_4_3_4_8_7_1_7_8_4_10_6_2_7_5_14_6_11_6_14_4_3_8_2_4_6_7_3_7_6_7_1_4_5_9_6_5_1_7_7_9_10_6_7_1_7_2_3_9_8_10_2_4_2_14_6_8_4_3_10_5_2_5_4_7_5_8_7_4_10_7_9_3_9_8_6_1_4_1_8_3_4_3_6_10_4_5_8_1_5_1_4_2_10_7_11_4_10_2_4_2_5_1_4_5_14_5_4_5_3_6_1_3_2_2_5_1_1_5_3_7_8_2_2_8_9_6_1_2_9_7_7_7_5_6_1_9_5_3_2_4_6_8_9_7_4_8_1_2_3_9_8_5_1_5_9_3_9_1_8_10_4_7_2_2_10_4_1_3_4_2_7_14_5_4_5_3_9_8_6_10_6_1_14_5_9_3_2_2_4_3_1_2_5_5_6_4_4_8_3_4_4_11_7_7_7_7_6_8_10_4_8_2_1_3_1_11_3_3_9_10_6_1_4_2_14_6_4_5_5_11_5_6_4_9_2_7_6_5_1_2_3_10_6_11_7_2_6_7_4_2_7_4_3_1_14_6_8_6_8_5_4_14_2_2_10_5_8_6</t>
   </si>
   <si>
     <t>4_3_3_1_1_3_2_2_4_4_4_9_2_3_4_8_7_7_8_3_2_7_4_8_3_2_3_7_9_6_6_5_5_1_1_4_3_7_6_2_2_4_1_1_7_5_9_3_2_1_5_9_2_5_3_4_7_2_6_7_8_1_5_9_7_7_7_9_1_1_6_5_1_1_1_1_9_4_2_2_3_3_3_1_7_1_1_2_2_4_5_7_6_1_3_6_1_7_9_2_2_8_6_2_7_1_3_3_7_5_4_1_8_9_3_3_2_2_2_4_8_3_1_1_1_2_2_2_3_7_2_8_6_1_7_2_2_2_3_7_9_2_2_5_1_3_3_4_5_9_9_3_4_1_2_2_9_2_4_8_8_9_6_2_4_4_2_6_2_1_4_4_2_4_1_8_9_1_1_5_4_6_5_2_2_2_5_7_7_5_8_4_1_3_2_7_7_1_5_3_7_1_2_2_6_5_1_5_3_3_3_4_4_2_6_7_1_3_1_6_2_4_5_1_2_6_8_1_8_2_5_5_8_5_2_1_1_1_1_6_6_8_7_2_4_5_4_7_6_2_9_8_6_6_5_8_4_6_2_2_4_7_9_3_4_4_4_2_7_1_1_7_3_7_2_8_8_8_4_4_1_5_4_3_4_9_9_5_5_6_2_6_6_3_5_5_3_8_8_6_7_7_5_9_3_2_4_3_3_1_3_1_2_9_3_9_9_1_4_2_2_2_1_7_9_5_2_1_2_1_2_1_6_3_3_3_4_5_3_1_3_5_4_4_3_1_9_2_3_3_1_2_2_4_4_1_1_1_9_6_1_1_2_8_2_3_2_4_2_7_3_3_1_3_3_3_2_4_8_4_5_6_2_3_4_2_1_1_6_8_2_5_1_1_3_9_3_2_2_2_5_1_6_9_2_8_6_3_7_6_1_8_1_7_4_9_8_1_8_3_7_6_6_6_1_2_2_2_6_2_8_6_6_6_8_4_6_2_3_7_5_9_6_3_3_4_1_8_4_1_6_2_2_5_5_1_4_9_1_1_1_2_3_4_2_4_2_1_1_5_1_7_1_2_3_5_4_2_8_5_4_6_7_7_6_4_4_2_3_4_3_8_8_4_1_3_1_6_8_3</t>
@@ -373,6 +373,48 @@
   </si>
   <si>
     <t>4_7_8_5_7_7_6_4_3_9_3_1_4_4_5_5_5_7_1_6_3_1_3_5_2_1_1_9_2_9_6_1_8_3_4_5_4_2_1_6_4_2_8_7_4_8_6_5_9_1_2_8_8_9_4_6_6_1_6_7_8_1_5_8_6_4_8_9_3_1_4_4_1_5_5_8_5_4_6_2_8_1_9_3_7_9_2_5_5_7_1_2_9_8_1_3_4_7_8_4_9_1_1_2_5_4_6_5_7_2_7_7_6_5_5_5_1_4_2_1_9_3_4_3_3_3_4_1_5_3_4_6_5_4_6_9_6_1_2_1_8_1_2_4_9_2_5_8_2_5_2_1_5_7_1_1_2_2_6_2_9_3_3_6_6_6_2_5_8_1_6_2_4_2_6_8_9_4_7_3_4_5_7_4_2_1_2_6_6_1_6_2_4_7_6_2_1_1_8_1_7_8_8_9_1_7_9_5_4_3_3_5_2_2_7_7_6_1_3_8_9_1_9_3_3_4_2_5_1_5_2_7_3_6_2_4_2_2_9_1_5_7_2_3_3_9_3_5_3_1_6_2_9_6_3_3_1_3_5_6_3_4_2_4_6_1_1_7_3_4_4_4_3_4_7_3_6_8_3_2_4_1_2_1_4_8_5_5_4_4_8_8_1_4_5_4_9_7_1_8_9_3_5_2_4_1_4_7_4_9_1_1_9_3_2_5_2_2_2_4_5_6_5_2_6_9_6_2_8_4_2_7_7_6_3_3_8_7_6_2_4_7_1_1_9_6_2_8_2_8_4_9_5_4_1_3_1_5_7_9_7_8_1_1_2_4_6_5_8_2_2_2_3_2_4_2_2_3_6_1_7_5_3_7_4_1_1_4_7_4_1_2_9_6_2_4_1_8_2_6_4_6_3_1_4_2_3_8_2_4_3_4_5_9_5_5_8_1_3_1_7_3_1_7_7_3_5_1_3_8_7_8_2_2_5_3_3_4_8_6_1_6_8_4_1_8_2_4_5_7_1_6_4_5_6_5_4_2_6_2_7_1_1_5_2_1_7_6_2_3_3_3_8_1_4_6_2_9_3_2_2_6_7_1_6_1_3_9_2_5_6_2_3_2_1_8_4_5_3_9</t>
+  </si>
+  <si>
+    <t>10_7_2_4_3_3_1_7_3_6_3_9_9_4_10_2_2_2_9_3_3_3_1_3_2_4_2_4_4_4_5_5_2_6_5_9_10_6_1_6_1_1_1_1_2_4_9_9_5_4_6_4_6_5_6_3_3_4_4_2_1_8_2_3_9_8_6_2_6_1_1_6_4_9_9_5_4_5_4_3_1_9_3_6_3_2_2_4_2_2_9_6_8_8_7_7_5_4_4_9_1_1_1_7_6_6_5_3_1_2_1_7_6_6_4_4_1_3_2_6_9_4_4_3_2_1_2_8_3_4_4_4_5_6_6_5_1_6_2_1_5_6_9_3_6_6_1_6_3_7_2_1_3_7_5_4_8_8_7_5_3_4_4_4_6_8_2_7_7_7_1_1_7_1_1_5_5_2_3_6_1_5_4_4_5_5_8_3_4_2_6_8_6_4_1_7_5_5_2_1_1_3_3_2_7_2_5_7_6_1_3_7_8_6_1_1_3_1_4_5_8_6_1_10_7_8_4_4_1_7_6_1_6_6_4_2_4_4_7_9_7_3_1_4_8_7_3_7_8_9_8_6_6_5_1_5_5_5_6_2_10_1_4_4_6_5_4_2_2_2_3_2_2_6_9_3_3_3_6_8_8_9_9_9_10_2_7_2_7_7_8_3_3_3_1_3_1_4_8_2_2_5_6_6_5_6_5_5_2_1_6_4_4_5_1_2_3_5_6_3_7_3_5_1_1_5_5_4_2_8_8_5_2_7_7_2_7_7_6_3_2_4_3_9_6_2_2_8_6_2_1_1_8_1_2_1_1_6_10_1_4_6_4_3_1_6_5_4_5_4_6_6_2_1_3_2_6_5_4_2_2_1_1_2_10_8_1_10_3_5_6_8_6_6_1_8_5_1_1_3_4_6_4_2_5_2_1_3_3_6_5_4_8_10_3_3_2_6_2_6_1_2_5_2_6_6_2_4_3_8_1_2_2_7_4_2_4_1_10_5_1_1_3_6_9_1_5_3_1_9_9_6_9_3_6_2_8_3_3_1_4_5_7_3_4_4_4_1_1_2_2_2_8_6_4_2_8_2_2_2_6_1_1_2_2_9_7_1_2_3_2_3_1_1_2_2_10_6_4_7</t>
+  </si>
+  <si>
+    <t>5_8_2_4_10_5_3_2_6_5_1_4_9_1_1_3_4_2_1_4_7_4_1_2_4_2_8_5_7_1_8_1_2_2_2_3_1_7_7_4_2_7_5_8_1_1_6_10_6_4_3_2_7_7_4_4_9_10_7_5_7_4_8_4_3_1_10_6_9_9_8_3_9_10_6_1_8_7_8_2_2_9_10_6_1_7_7_2_4_2_2_2_2_7_1_6_1_1_5_9_1_9_9_4_1_9_8_2_2_9_2_6_5_2_4_3_9_1_1_9_2_8_4_3_5_2_3_5_8_5_4_1_3_3_1_9_4_3_8_6_8_8_10_2_3_4_9_6_4_2_2_3_3_2_4_2_9_9_6_6_4_7_1_1_2_7_2_6_5_7_6_1_4_5_4_9_3_4_1_1_3_9_8_4_7_3_5_5_3_9_8_1_5_7_3_1_5_8_2_9_3_2_2_1_6_2_7_8_4_9_6_5_6_5_2_7_5_4_4_1_4_4_7_3_6_6_9_5_3_6_2_7_7_2_7_6_8_4_5_7_6_4_7_5_7_9_9_4_7_2_4_9_7_1_4_1_2_2_7_2_9_4_8_5_3_6_1_7_1_3_5_9_1_3_2_9_4_1_2_1_1_1_6_1_5_5_4_6_2_2_2_8_1_4_8_3_1_3_7_7_3_4_2_3_6_10_5_7_10_5_5_9_2_4_2_7_3_7_5_6_2_4_1_8_9_9_5_6_6_1_4_3_3_5_10_6_5_8_1_9_6_3_4_3_6_8_3_1_8_1_5_1_8_5_4_9_1_7_6_2_7_4_8_5_3_6_1_3_5_6_9_2_5_6_3_8_8_5_6_6_2_6_6_4_6_1_5_3_6_3_9_2_2_3_4_2_5_2_3_7_3_5_4_6_3_1_9_4_3_4_1_1_3_5_1_8_1_7_6_7_1_2_4_6_10_6_4_2_1_1_6_4_6_3_4_4_10_6_1_7_6_6_4_5_5_1_6_1_3_1_1_3_4_5_3_2_3_6_1_5_9_3_7_5_8_7_4_1_1_2_2_1_5_2_8_6_1_2_4_2_1_3_6_7_5_3_1_4_1_4_3_8_9_3_3_1_8_5_8_3</t>
+  </si>
+  <si>
+    <t>2_5_6_4_7_7_2_2_4_3_7_6_6_1_2_4_6_4_4_1_10_9_4_4_4_7_5_6_8_9_5_1_5_4_6_6_3_1_8_6_6_6_7_7_7_4_6_2_3_7_1_1_7_7_1_1_1_9_2_3_9_6_1_1_1_7_3_4_4_2_2_3_1_8_4_1_6_4_8_5_7_3_4_8_10_8_2_2_5_3_8_4_9_1_1_7_4_4_3_4_7_2_2_1_4_3_9_9_3_1_5_5_2_6_1_1_5_7_1_6_2_3_1_3_7_4_4_2_2_1_5_1_3_6_3_1_2_1_4_7_7_7_4_4_2_3_4_4_3_6_4_3_1_3_3_1_3_3_4_3_2_6_6_9_1_1_8_8_1_5_2_1_5_2_2_6_1_2_2_6_8_5_3_8_3_10_5_7_7_10_4_4_3_10_1_2_3_4_7_2_3_1_2_5_5_1_3_1_1_1_5_6_3_3_4_3_8_8_8_8_6_5_4_8_5_3_3_2_2_10_6_6_1_7_1_3_6_6_3_3_7_1_9_5_3_6_6_9_1_3_5_6_3_1_8_5_6_2_9_9_9_9_4_3_2_10_6_6_4_2_8_1_4_1_1_2_2_8_8_6_1_6_6_8_7_3_3_3_4_1_3_6_5_5_6_5_1_6_9_1_1_2_5_3_1_5_2_5_4_2_3_3_2_2_2_1_1_3_1_1_8_5_1_3_2_4_4_2_5_9_9_6_7_2_7_5_7_3_2_1_5_1_1_2_1_7_6_6_4_1_8_8_2_1_4_9_3_3_1_6_6_4_10_9_9_3_3_4_4_2_2_5_3_5_6_6_2_4_3_3_3_3_9_2_1_2_2_2_8_1_4_3_5_2_6_3_2_1_3_10_7_3_6_2_2_5_7_7_3_8_8_1_8_3_2_2_6_1_2_8_3_3_6_1_2_1_7_2_5_1_2_7_7_1_3_3_8_1_5_10_8_4_2_4_10_6_2_6_4_1_7_1_1_6_4_1_7_2_4_3_3_3_7_7_3_8_8_2_6_1_5_3_3_4_4_1_1_6_6_4_2_8_5_2_2_4_6_6_4_2_9_1_7_8_9_7_5_5_1_7</t>
+  </si>
+  <si>
+    <t>7_1_3_7_4_6_4_7_6_7_3_7_1_3_5_10_6_2_5_6_5_5_2_1_1_8_7_1_4_3_3_8_3_5_4_7_2_5_6_3_9_3_6_5_5_7_7_6_9_2_3_1_2_1_6_4_5_6_6_5_9_2_5_6_4_6_9_1_9_5_2_6_2_6_2_5_9_9_2_6_7_1_10_4_1_5_4_9_2_7_5_4_4_6_1_2_3_7_1_5_9_4_1_2_8_10_5_1_5_6_10_7_6_1_6_1_3_2_8_3_10_3_4_9_5_3_4_9_1_1_6_3_3_2_2_8_9_2_7_8_5_6_6_7_5_2_10_4_3_7_2_10_4_6_1_8_5_9_3_9_5_3_6_8_9_5_6_9_7_1_1_1_1_8_8_4_1_3_4_9_3_2_10_6_7_3_3_5_3_9_3_8_5_3_5_8_3_5_1_9_5_6_5_9_7_3_4_3_7_6_6_6_2_5_2_2_2_8_1_5_2_8_7_5_3_5_7_7_7_4_7_4_8_2_5_3_3_6_4_7_8_6_7_9_6_8_3_6_5_7_3_1_9_4_8_6_3_6_5_1_4_8_5_4_2_4_3_8_8_2_6_7_9_5_2_2_7_4_2_6_1_6_4_1_7_6_3_3_2_5_9_1_5_1_7_4_3_4_5_10_7_3_2_5_1_1_3_9_7_9_4_9_3_7_8_3_2_4_7_8_9_2_2_6_2_2_7_10_5_2_2_1_7_8_7_8_7_4_10_7_8_7_1_2_2_2_9_2_4_1_2_4_3_10_2_5_1_2_2_2_3_5_1_7_7_3_1_9_3_4_4_1_4_2_5_3_2_7_8_10_6_1_4_2_3_3_2_6_7_4_8_5_4_2_4_6_1_4_4_7_1_3_10_4_5_1_5_5_4_3_10_7_7_6_6_1_9_4_4_4_3_3_4_4_2_3_1_6_5_3_4_1_4_6_4_7_8_6_3_5_2_5_2_1_2_3_1_1_1_5_8_1_3_8_7_2_10_4_1_5_5_10_6_5_2_8_10_5_4_1_7_5_4_9_7_6_5_2_6_3_2_6_3_1_2_8_5_5_9_1_2_9_7_6_1_5_3_7_4_7</t>
+  </si>
+  <si>
+    <t>5_3_2_2_1_2_5_5_4_2_3_1_1_5_5_2_1_4_5_10_1_6_4_6_6_1_5_4_3_3_6_9_7_7_5_5_3_6_1_1_1_8_7_1_3_5_1_5_3_6_8_6_1_7_6_4_4_2_5_7_6_4_8_5_7_5_4_2_7_7_8_7_9_2_8_7_9_1_2_8_2_2_2_2_9_4_4_9_2_1_2_6_9_9_5_3_6_1_3_3_1_1_5_1_6_1_5_4_4_2_2_2_2_9_6_8_2_1_1_6_3_3_3_4_8_5_5_5_1_5_3_5_3_6_8_2_3_3_2_5_8_1_4_2_8_5_4_2_1_2_1_3_1_3_1_7_1_2_2_3_3_2_4_2_7_3_3_6_2_8_8_5_2_9_1_3_3_2_8_9_1_3_3_2_7_8_9_5_1_7_7_6_6_2_8_2_8_1_1_6_2_3_3_2_3_9_8_9_6_3_5_8_5_6_1_1_5_5_8_10_3_2_2_1_1_4_5_1_3_4_8_1_5_2_6_2_4_4_4_4_8_1_1_7_8_6_1_4_4_4_4_1_2_4_6_10_7_1_2_2_3_1_7_2_1_6_3_8_4_1_2_3_3_3_6_7_5_4_1_4_3_2_8_8_5_3_8_8_5_3_3_2_2_2_1_4_2_4_2_1_8_2_1_2_1_1_7_5_2_6_6_2_2_9_3_1_8_3_7_6_1_5_6_2_2_6_3_1_1_1_8_1_2_3_1_2_9_1_2_4_6_9_1_8_3_2_2_6_1_4_3_4_5_1_9_2_8_2_4_2_5_2_1_7_4_9_3_5_1_1_7_1_8_6_3_5_3_7_6_3_6_6_2_3_1_6_3_1_7_5_1_5_9_9_6_4_8_4_9_8_1_1_2_2_1_4_1_4_4_6_2_2_2_3_6_5_7_3_4_6_6_6_1_7_7_3_8_2_1_4_7_7_7_5_1_3_5_5_1_8_7_10_2_2_6_5_1_5_10_3_3_4_4_1_4_4_6_10_8_7_3_4_2_2_6_8_5_1_7_1_3_6_7_1_10_2_1_2_2_6_6_2_10_6_6_2_8_3_8_2_9_1_3_2_2_2_10_3_3_3</t>
+  </si>
+  <si>
+    <t>5_4_3_6_1_2_9_4_3_1_4_7_1_9_4_3_9_6_3_5_4_6_7_7_2_2_7_3_7_8_2_3_4_2_3_8_2_2_1_9_6_6_3_9_6_3_9_9_2_4_3_6_1_10_5_1_9_2_3_4_9_1_7_3_6_3_6_3_8_4_2_4_10_5_3_4_9_5_7_2_2_4_9_2_4_8_2_9_1_8_3_5_3_6_3_8_9_7_8_2_6_2_10_4_4_4_6_4_6_3_2_8_9_7_2_4_6_3_7_1_5_3_5_9_3_2_6_4_1_6_1_10_1_6_10_5_3_2_10_7_9_3_4_2_2_9_9_8_6_3_1_1_2_6_3_4_6_4_9_2_6_5_1_4_4_8_7_4_4_5_1_4_10_5_1_1_4_3_6_1_5_9_10_7_1_1_2_5_5_9_8_2_7_2_1_5_4_2_6_7_5_3_3_2_7_8_3_7_5_3_8_6_2_4_5_2_2_5_7_4_6_3_8_5_3_9_5_4_9_1_9_7_7_3_9_3_1_3_4_10_4_5_1_2_5_3_8_2_5_4_9_2_7_4_3_7_3_9_1_3_10_7_2_2_5_3_1_3_8_1_1_3_4_9_6_9_1_1_9_2_10_6_6_10_6_7_7_1_5_2_1_6_1_4_2_5_4_7_3_9_6_7_6_3_4_2_1_2_5_1_2_6_5_2_5_2_7_3_7_5_6_7_8_3_8_5_3_6_2_3_7_6_7_6_2_7_8_8_7_10_4_2_9_6_9_6_5_1_2_1_3_3_7_6_1_8_2_2_2_4_4_2_2_2_6_1_6_4_6_2_4_6_5_1_5_9_1_6_3_3_4_1_7_3_5_1_8_8_5_2_3_5_4_3_8_7_2_3_1_6_4_6_4_1_4_1_3_9_4_4_5_3_4_6_6_7_3_9_4_8_3_4_5_1_1_9_1_1_4_6_1_4_4_3_5_8_4_5_5_6_2_2_8_2_10_6_2_1_4_2_4_2_3_8_2_3_9_4_1_3_8_7_5_6_8_2_5_2_5_4_8_3_8_9_1_4_2_1_2_8_9_7_5_1_8_5_3_9_1_1_8_2_9_3_7_3_4_1_2_2</t>
+  </si>
+  <si>
+    <t>7_2_9_8_5_1_1_5_4_3_8_1_3_2_8_5_1_6_5_9_3_3_6_5_1_1_10_3_7_9_6_7_1_1_3_9_1_1_5_3_4_4_4_8_3_6_7_4_10_1_4_10_8_4_1_8_5_8_8_8_1_9_1_7_4_8_4_4_1_6_7_6_6_1_7_6_1_4_5_2_5_1_6_9_2_3_3_10_10_9_3_8_1_1_9_1_6_4_9_7_5_5_2_8_1_6_5_5_1_4_1_7_5_1_10_1_2_4_5_5_5_5_5_2_5_3_3_3_3_6_1_4_2_4_9_3_6_5_5_4_3_3_1_2_1_4_1_1_1_7_3_1_2_6_4_5_3_2_2_2_6_2_1_3_6_1_4_7_4_4_4_2_9_5_2_1_5_1_7_3_7_7_4_6_9_4_1_1_1_6_4_5_4_4_8_4_4_1_2_2_8_5_10_2_5_5_5_5_6_5_1_4_5_9_5_2_8_2_4_1_5_9_2_2_7_2_2_4_4_10_6_2_7_1_4_4_4_4_4_6_6_6_1_6_8_5_4_1_2_1_4_1_6_4_8_5_1_3_5_5_4_6_4_1_6_6_2_4_4_4_8_3_3_1_1_4_8_4_8_8_3_4_6_6_6_6_7_9_2_5_8_1_10_9_3_7_7_4_10_7_1_5_2_6_1_10_2_2_3_7_2_2_1_2_4_2_1_1_5_8_7_1_8_5_9_9_8_1_4_4_2_3_3_3_3_4_4_5_7_4_3_8_5_7_7_2_4_5_8_3_7_7_6_8_9_8_4_7_5_8_6_1_10_10_6_5_5_3_6_1_3_4_3_8_2_9_9_1_6_1_3_3_3_7_2_9_5_5_1_1_9_5_4_5_3_8_4_8_8_3_7_9_9_4_6_3_1_3_2_6_9_1_3_5_5_9_9_8_5_1_1_1_6_4_3_8_8_9_8_4_3_3_1_2_10_9_6_8_1_5_4_1_4_8_4_9_1_4_2_4_2_5_4_2_6_6_6_9_5_1_4_3_8_6_6_3_1_2_3_1_6_7_1_1_5_5_1_1_2_3_5_8_8_6_5_2_3_2_2_4_1_2_3_4_2_6_3_5_2_10</t>
+  </si>
+  <si>
+    <t>4_4_6_5_8_1_5_8_5_9_3_2_3_7_8_1_7_6_9_1_8_3_3_8_6_5_1_8_9_8_3_3_3_7_3_7_8_8_1_1_9_1_5_2_1_6_4_9_3_4_7_3_5_1_8_4_2_3_1_6_2_4_1_1_3_7_10_6_1_6_1_8_5_3_4_6_5_6_3_4_5_4_5_6_8_1_1_5_3_1_9_2_5_8_4_2_5_3_6_5_4_9_3_2_6_3_2_1_3_6_1_8_9_2_7_4_6_1_7_4_1_3_2_4_1_9_1_5_1_1_2_2_4_4_2_1_7_2_2_7_6_2_3_9_6_1_9_7_4_9_2_2_2_9_4_3_10_6_3_2_2_2_6_2_2_3_6_7_9_2_8_4_5_6_2_8_1_5_1_1_6_10_7_4_3_2_9_6_9_2_4_1_4_4_2_8_5_1_6_5_2_3_7_2_4_5_2_1_1_9_5_3_5_4_5_7_4_3_3_8_9_7_6_8_3_3_2_2_4_5_10_3_6_6_4_3_2_4_6_5_7_7_1_2_1_4_10_6_1_8_4_3_4_2_1_7_7_2_8_6_2_4_6_5_2_8_1_2_3_6_1_7_1_6_3_3_1_7_5_8_2_1_5_3_4_5_4_4_1_5_2_2_3_10_6_8_6_4_6_4_9_2_7_9_1_9_4_3_3_7_6_2_6_8_6_6_1_6_3_6_6_3_3_5_5_5_1_3_1_5_8_4_6_9_3_3_6_2_1_3_3_5_9_1_10_4_6_2_4_7_8_8_3_1_4_7_10_5_6_2_4_4_4_3_5_4_1_3_10_3_6_8_7_4_4_4_1_4_7_2_7_10_5_10_3_9_8_10_3_3_1_3_8_6_8_6_3_2_7_5_5_9_1_9_5_10_7_6_1_6_9_7_6_2_1_7_4_1_3_6_3_5_8_7_3_7_3_8_3_3_5_2_6_6_1_4_1_8_5_2_4_1_1_6_6_5_5_1_3_5_3_3_4_2_2_2_2_7_2_10_6_6_6_9_7_9_2_7_7_7_1_4_8_2_3_8_10_4_7_6_3_1_1_2_1_10_6_3_9_8_9_7_2_8_9_10_5_2_6_1</t>
+  </si>
+  <si>
+    <t>9_9_9_9</t>
+  </si>
+  <si>
+    <t>8_2_3_4_1_6_1_3_2_4_9_4_6_5_10_10_3_10_9_9_9_2_5_1_8_8_4_1_9_9_9_7_9_4_8_7_6_8_7_1_5_1_5_2_7_4_7_4_7_5_1_5_8_1_6_6_1_1_7_6_1_3_7_2_4_2_5_8_5_8_3_2_2_5_4_5_5_5_9_6_2_1_4_2_10_2_6_1_1_4_7_1_4_4_3_4_8_8_8_9_3_1_1_7_1_3_3_6_9_6_1_4_2_2_9_6_1_2_7_1_5_6_2_7_3_6_3_9_4_3_3_1_5_3_4_4_3_1_5_6_4_4_3_4_6_8_4_2_4_5_2_2_5_9_9_8_2_2_7_8_7_7_2_6_3_4_8_4_2_2_6_1_6_4_4_6_6_2_2_8_7_6_1_3_3_3_6_4_8_5_7_7_9_3_4_1_2_4_5_4_1_4_6_2_3_2_2_2_3_4_8_3_4_5_1_9_1_8_3_8_9_3_3_7_4_3_4_2_6_6_6_5_1_5_4_8_4_1_6_7_5_1_1_1_1_1_6_8_8_7_9_2_3_10_1_1_3_4_7_2_8_6_3_6_8_6_1_2_2_8_5_8_9_2_5_1_8_1_3_6_1_3_4_2_4_4_9_3_2_1_1_3_5_2_1_1_7_4_3_5_5_2_2_1_3_2_2_3_6_1_2_8_1_2_1_4_4_3_4_3_9_6_6_4_2_8_3_6_1_4_7_9_6_10_8_7_7_5_6_4_8_9_2_2_1_5_4_8_1_1_5_5_8_5_3_8_7_7_7_2_3_2_5_1_4_1_5_5_5_8_6_3_5_5_9_4_3_2_1_3_4_7_2_2_2_3_2_1_1_1_1_3_1_6_5_5_8_4_5_6_9_4_10_6_1_10_1_9_3_4_7_7_1_5_4_6_8_1_3_7_7_2_6_6_6_6_2_7_2_7_3_2_3_8_3_2_8_1_4_8_4_5_2_2_4_4_6_6_5_4_4_6_7_1_8_2_6_6_1_1_3_6_2_5_4_1_1_2_10_2_5_2_2_1_3_3_2_2_1_10_6_3_2_7_9_2_7_7_9_7_1_10_3_1_3_1_8_10_6_8</t>
+  </si>
+  <si>
+    <t>1_1_1_2_3_6_2_5_1_3_9_1_10_4_1_8_5_3_1_4_4_1_1_8_6_8_2_4_4_2_2_1_1_6_1_6_4_8_9_3_3_5_8_10_6_3_8_5_5_5_4_5_7_3_3_2_3_1_9_5_6_4_9_1_4_7_3_5_1_7_9_10_7_5_1_10_1_4_2_4_6_10_4_9_4_1_3_1_2_10_7_4_6_6_8_9_2_6_4_1_9_10_3_3_1_9_8_8_5_1_4_3_6_6_10_4_1_5_2_3_5_2_1_1_8_5_5_6_7_3_8_5_6_6_8_9_7_2_4_10_6_1_3_6_6_4_4_7_1_3_6_1_2_6_8_8_7_1_1_5_9_2_6_2_6_4_2_1_5_5_6_2_2_9_6_7_4_4_8_8_2_8_1_2_1_8_1_5_2_4_7_7_1_3_6_9_5_9_1_5_1_6_4_3_2_3_3_6_1_1_3_3_2_2_8_6_7_9_8_7_1_2_3_5_5_3_4_2_3_6_9_5_1_3_4_9_2_8_3_3_7_6_3_1_9_1_1_7_2_5_9_6_6_8_4_4_8_9_10_5_9_8_3_6_9_1_1_5_8_9_1_3_3_1_3_4_3_3_5_9_5_1_8_9_6_9_6_7_2_4_6_4_4_8_9_1_2_6_8_2_2_2_6_3_3_2_9_4_3_5_3_5_8_1_6_5_9_6_2_10_2_7_3_6_3_3_9_4_2_2_9_2_8_3_4_1_10_6_10_7_3_8_2_1_1_2_9_4_5_2_4_3_8_8_3_3_1_10_1_9_6_5_1_8_2_2_6_10_3_3_1_2_2_4_6_1_10_7_6_5_1_6_3_8_7_3_5_1_1_5_4_6_6_1_2_3_9_2_2_3_8_6_4_5_6_6_7_9_4_4_8_2_7_4_1_6_6_4_4_3_4_2_2_8_2_6_6_1_7_7_2_1_7_2_1_5_6_2_6_2_5_5_1_7_4_7_2_4_4_9_6_9_1_3_4_10_2_4_8_10_5_7_1_2_7_8_3_9_6_4_2_3_8_3_9_3_4_9_2_10_1_5_3_1_4_4_5_8_7_9_1_5_5_2_1_2_4_1_2_4</t>
+  </si>
+  <si>
+    <t>10_10_10_10</t>
+  </si>
+  <si>
+    <t>2_6_9_9_3_3_6_2_2_2_2_7_7_7_4_3_1_1_2_9_3_1_3_7_7_4_2_2_2_1_5_9_3_2_5_9_3_8_2_2_9_8_1_3_10_6_7_4_4_6_2_5_6_10_5_2_2_5_8_3_3_5_9_3_2_9_3_4_5_4_5_4_9_6_5_3_3_5_4_4_3_7_8_1_9_8_7_2_4_1_6_6_10_6_6_6_4_3_3_1_3_10_3_2_7_7_8_8_5_5_1_7_1_2_1_10_2_2_5_5_2_2_10_3_5_4_4_6_6_5_6_6_3_10_4_4_2_1_1_1_1_7_9_6_6_5_1_4_2_6_4_2_6_2_8_2_6_4_3_2_1_8_6_3_5_5_4_4_7_3_1_5_1_1_4_7_7_3_5_2_6_4_1_2_2_2_7_5_5_1_4_2_5_7_4_4_2_2_2_2_1_10_9_8_5_8_9_7_5_8_4_2_1_1_5_1_6_6_8_7_4_4_4_8_6_4_4_6_5_3_10_2_4_1_5_3_3_2_2_9_5_4_2_1_6_1_5_1_6_3_4_4_5_6_7_7_8_10_6_1_4_7_7_6_8_8_8_1_9_5_8_8_8_2_3_4_6_4_2_5_4_4_9_1_8_6_6_2_2_7_3_3_7_3_9_6_5_6_2_1_8_9_7_5_5_3_3_3_2_2_2_2_6_9_3_9_6_3_7_6_9_6_1_2_4_1_7_4_6_6_1_1_2_4_8_8_1_3_1_1_8_10_7_9_6_3_9_3_6_4_1_1_3_3_3_3_3_1_10_10_4_2_3_2_2_2_4_2_2_2_2_4_3_4_4_8_2_2_8_8_8_3_1_6_1_1_2_7_1_3_3_3_1_7_8_4_5_7_1_2_1_3_5_5_8_1_5_3_6_6_5_3_1_5_5_2_6_2_4_8_4_9_6_2_1_2_4_2_5_2_5_5_10_3_4_3_6_2_10_10_2_2_6_6_2_2_4_9_7_3_1_2_1_6_5_4_5_6_7_4_9_3_9_2_9_8_1_6_1_6_1_2_5_8_1_3_8_2_1_8_9_1_2_1_2_5_7_5_1_1_1_7_5_6_6_6_7_8_2_4</t>
+  </si>
+  <si>
+    <t>4_2_4_2_1_6_1_5_4_9_6_4_2_6_3_4_1_6_7_2_8_3_9_1_8_4_1_4_7_7_6_4_4_3_1_5_5_10_6_2_1_3_2_9_3_5_7_4_9_8_5_1_4_6_1_9_8_1_9_1_7_5_6_5_3_9_6_4_3_1_7_2_4_1_3_5_4_7_4_6_3_9_1_6_2_6_5_2_4_4_8_5_6_3_2_1_1_2_3_5_3_1_1_3_6_7_9_7_1_3_7_7_2_3_1_9_1_8_4_2_2_6_8_1_3_1_5_8_9_6_1_7_4_7_9_3_6_2_2_4_5_3_3_6_8_4_5_8_1_1_8_5_2_10_2_8_2_7_7_4_1_2_8_3_3_4_3_4_1_2_9_6_3_4_2_1_9_2_3_9_8_2_3_7_4_1_1_2_2_9_5_6_8_4_8_5_7_2_1_7_6_5_6_2_9_10_3_1_4_7_2_7_3_5_1_1_6_1_4_7_4_6_4_9_1_1_6_4_7_3_1_6_7_1_8_4_9_9_8_10_6_3_1_2_4_2_5_2_2_1_6_3_9_3_8_6_10_7_4_4_6_1_3_9_2_2_2_6_3_4_4_6_9_5_2_4_7_4_1_6_6_8_5_7_8_1_6_4_4_1_8_1_4_5_3_3_3_1_2_6_4_4_9_1_6_4_5_4_5_7_2_2_1_10_3_9_5_1_7_2_4_4_2_1_4_1_2_1_8_2_1_8_2_8_3_4_3_3_7_3_1_3_4_8_1_5_2_3_9_6_8_5_8_5_7_5_2_8_1_2_6_6_3_4_2_9_3_10_2_5_1_3_4_3_6_5_3_4_6_1_3_5_2_4_9_1_2_1_7_3_9_3_8_10_7_6_2_4_9_7_8_9_2_9_7_9_5_4_7_1_9_5_2_9_5_1_5_1_3_4_5_2_8_7_1_4_9_2_1_4_8_4_8_9_10_6_7_2_1_4_2_4_8_6_4_8_8_7_2_1_9_9_4_4_2_6_4_8_9_9_2_1_8_4_8_9_4_6_8_3_1_6_3_1_7_7_2_7_6_9_1_7_3_4_5_4_2_3_1_1_5_5_7_4_1_5_7_3_4_9</t>
   </si>
 </sst>
 </file>
@@ -555,12 +597,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1683,7 +1725,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -1806,7 +1848,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:11">
       <c r="A5">
-        <f t="shared" ref="A5:A51" si="0">C5*10+D5</f>
+        <f t="shared" ref="A5:A56" si="0">C5*10+D5</f>
         <v>20010011</v>
       </c>
       <c r="B5" s="13">
@@ -3301,7 +3343,7 @@
     </row>
     <row r="52" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A52" s="5">
-        <f>C52*10+D52</f>
+        <f t="shared" si="0"/>
         <v>20210011</v>
       </c>
       <c r="B52" s="13">
@@ -3333,7 +3375,7 @@
     </row>
     <row r="53" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A53" s="5">
-        <f>C53*10+D53</f>
+        <f t="shared" si="0"/>
         <v>20210012</v>
       </c>
       <c r="B53" s="13">
@@ -3365,7 +3407,7 @@
     </row>
     <row r="54" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A54" s="5">
-        <f>C54*10+D54</f>
+        <f t="shared" si="0"/>
         <v>20210013</v>
       </c>
       <c r="B54" s="13">
@@ -3397,7 +3439,7 @@
     </row>
     <row r="55" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A55" s="5">
-        <f>C55*10+D55</f>
+        <f t="shared" si="0"/>
         <v>20210014</v>
       </c>
       <c r="B55" s="13">
@@ -3429,7 +3471,7 @@
     </row>
     <row r="56" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A56" s="5">
-        <f>C56*10+D56</f>
+        <f t="shared" si="0"/>
         <v>20210015</v>
       </c>
       <c r="B56" s="13">
@@ -3458,6 +3500,198 @@
       </c>
       <c r="J56" s="17"/>
       <c r="K56" s="17"/>
+    </row>
+    <row r="57" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A57" s="5">
+        <f t="shared" ref="A57:A62" si="2">C57*10+D57</f>
+        <v>20180011</v>
+      </c>
+      <c r="B57" s="13">
+        <v>101800</v>
+      </c>
+      <c r="C57" s="33">
+        <v>2018001</v>
+      </c>
+      <c r="D57" s="33">
+        <v>1</v>
+      </c>
+      <c r="E57" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F57" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G57" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="H57" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I57" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="J57" s="17"/>
+      <c r="K57" s="17"/>
+    </row>
+    <row r="58" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A58" s="5">
+        <f t="shared" si="2"/>
+        <v>20180012</v>
+      </c>
+      <c r="B58" s="13">
+        <v>101800</v>
+      </c>
+      <c r="C58" s="33">
+        <v>2018001</v>
+      </c>
+      <c r="D58" s="33">
+        <v>2</v>
+      </c>
+      <c r="E58" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F58" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G58" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="H58" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I58" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="J58" s="17"/>
+      <c r="K58" s="17"/>
+    </row>
+    <row r="59" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A59" s="5">
+        <f t="shared" si="2"/>
+        <v>20180013</v>
+      </c>
+      <c r="B59" s="13">
+        <v>101800</v>
+      </c>
+      <c r="C59" s="33">
+        <v>2018001</v>
+      </c>
+      <c r="D59" s="33">
+        <v>3</v>
+      </c>
+      <c r="E59" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="F59" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G59" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="H59" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I59" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="J59" s="17"/>
+      <c r="K59" s="17"/>
+    </row>
+    <row r="60" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A60" s="5">
+        <f t="shared" si="2"/>
+        <v>20180014</v>
+      </c>
+      <c r="B60" s="13">
+        <v>101800</v>
+      </c>
+      <c r="C60" s="33">
+        <v>2018001</v>
+      </c>
+      <c r="D60" s="33">
+        <v>4</v>
+      </c>
+      <c r="E60" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F60" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G60" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="H60" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="J60" s="17"/>
+      <c r="K60" s="17"/>
+    </row>
+    <row r="61" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A61" s="5">
+        <f t="shared" si="2"/>
+        <v>20180015</v>
+      </c>
+      <c r="B61" s="13">
+        <v>101800</v>
+      </c>
+      <c r="C61" s="33">
+        <v>2018001</v>
+      </c>
+      <c r="D61" s="33">
+        <v>5</v>
+      </c>
+      <c r="E61" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="F61" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G61" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="H61" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I61" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="J61" s="17"/>
+      <c r="K61" s="17"/>
+    </row>
+    <row r="62" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A62" s="5">
+        <f t="shared" si="2"/>
+        <v>20180016</v>
+      </c>
+      <c r="B62" s="13">
+        <v>101800</v>
+      </c>
+      <c r="C62" s="33">
+        <v>2018001</v>
+      </c>
+      <c r="D62" s="33">
+        <v>6</v>
+      </c>
+      <c r="E62" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F62" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G62" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H62" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I62" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="J62" s="17"/>
+      <c r="K62" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="122">
   <si>
     <t>id</t>
   </si>
@@ -415,6 +415,36 @@
   </si>
   <si>
     <t>4_2_4_2_1_6_1_5_4_9_6_4_2_6_3_4_1_6_7_2_8_3_9_1_8_4_1_4_7_7_6_4_4_3_1_5_5_10_6_2_1_3_2_9_3_5_7_4_9_8_5_1_4_6_1_9_8_1_9_1_7_5_6_5_3_9_6_4_3_1_7_2_4_1_3_5_4_7_4_6_3_9_1_6_2_6_5_2_4_4_8_5_6_3_2_1_1_2_3_5_3_1_1_3_6_7_9_7_1_3_7_7_2_3_1_9_1_8_4_2_2_6_8_1_3_1_5_8_9_6_1_7_4_7_9_3_6_2_2_4_5_3_3_6_8_4_5_8_1_1_8_5_2_10_2_8_2_7_7_4_1_2_8_3_3_4_3_4_1_2_9_6_3_4_2_1_9_2_3_9_8_2_3_7_4_1_1_2_2_9_5_6_8_4_8_5_7_2_1_7_6_5_6_2_9_10_3_1_4_7_2_7_3_5_1_1_6_1_4_7_4_6_4_9_1_1_6_4_7_3_1_6_7_1_8_4_9_9_8_10_6_3_1_2_4_2_5_2_2_1_6_3_9_3_8_6_10_7_4_4_6_1_3_9_2_2_2_6_3_4_4_6_9_5_2_4_7_4_1_6_6_8_5_7_8_1_6_4_4_1_8_1_4_5_3_3_3_1_2_6_4_4_9_1_6_4_5_4_5_7_2_2_1_10_3_9_5_1_7_2_4_4_2_1_4_1_2_1_8_2_1_8_2_8_3_4_3_3_7_3_1_3_4_8_1_5_2_3_9_6_8_5_8_5_7_5_2_8_1_2_6_6_3_4_2_9_3_10_2_5_1_3_4_3_6_5_3_4_6_1_3_5_2_4_9_1_2_1_7_3_9_3_8_10_7_6_2_4_9_7_8_9_2_9_7_9_5_4_7_1_9_5_2_9_5_1_5_1_3_4_5_2_8_7_1_4_9_2_1_4_8_4_8_9_10_6_7_2_1_4_2_4_8_6_4_8_8_7_2_1_9_9_4_4_2_6_4_8_9_9_2_1_8_4_8_9_4_6_8_3_1_6_3_1_7_7_2_7_6_9_1_7_3_4_5_4_2_3_1_1_5_5_7_4_1_5_7_3_4_9</t>
+  </si>
+  <si>
+    <t>6_3_3_2_6_6_1_8_4_4_7_5_1_2_9_6_2_8_2_1_1_4_3_5_3_6_8_9_6_4_4_1_6_5_8_3_7_6_1_2_9_3_2_5_8_6_6_4_7_5_4_4_4_3_2_7_1_5_6_6_2_2_8_4_4_2_1_3_6_8_5_4_2_7_3_8_9_4_3_7_1_4_9_2_6_5_3_4_4_3_7_8_3_3_9_9_5_3_6_4_6_1_1_1_8_4_4_8_8_6_7_3_2_2_4_8_5_5_3_7_2_1_9_1_4_9_9_3_6_9_5_5_1_1_4_1_1_2_2_1_3_3_8_1_4_8_6_3_3_1_4_4_1_3_9_6_8_2_5_6_1_2_6_2_3_9_1_4_5_8_5_1_5_7_3_2_7_9_5_5_5_7_7_3_6_7_7_2_1_1_1_6_2_2_2_6_5_3_1_1_1_5_6_3_3_3_5_4_6_6_3_5_2_1_8_3_1_1_7_3_9_8_6_9_9_4_6_4_9_3_7_1_1_8_5_5_1_3_3_4_6_5_5_1_8_5_1_3_3_5_2_3_1_4_1_7_5_8_1_5_6_2_5_6_8_8_8_9_5_8_8_4_2_4_2_2_2_3_1_5_3_9_5_5_5_7_4_9_9_1_8_6_1_1_4_7_3_2_2_9_9_3_6_6_3_6_4_2_2_4_2_9_6_7_5_3_1_8_9_2_8_2_1_3_9_5_6_9_5_9_4_2_4_4_3_9_1_1_7_7_1_4_6_6_3_7_7_8_7_4_6_4_5_7_8_4_4_3_2_2_4_5_6_1_3_1_1_5_6_1_1_1_6_3_4_2_7_4_1_7_5_6_2_7_1_1_4_8_4_2_4_5_4_3_8_2_2_5_6_4_7_9_6_4_2_4_4_4_4_4_5_3_1_1_4_9_2_3_2_5_6_3_2_2_8_3_5_2_9_1_1_2_8_3_6_3_9_1_4_1_2_8_3_5_5_5_6_9_2_6_5_1_1_8_5_4_2_2_9_6_5_5_2_4_1_9_9_9_1_1_1_6_7_7_2_1_4_7_8_6_8_9_8_4_4_3_5_5_5_4_2_9_4_1_1_2_8_2_3_9</t>
+  </si>
+  <si>
+    <t>3_6_3_5_1_5_8_5_2_1_3_2_5_7_4_7_2_6_6_6_6_7_6_3_6_5_7_2_5_5_3_2_1_4_6_4_9_9_7_7_6_1_1_2_2_9_1_3_4_9_5_5_4_9_6_2_3_4_3_6_2_7_2_2_2_5_8_9_6_6_3_3_6_2_5_1_7_9_5_7_9_2_6_6_1_2_8_5_4_5_5_1_6_4_1_3_1_2_2_7_7_1_5_6_1_1_7_3_6_6_8_4_5_9_4_8_9_1_6_1_3_2_9_6_9_6_3_9_4_6_9_1_2_1_2_7_1_6_2_5_2_5_8_7_2_4_7_5_7_7_7_2_1_3_8_8_1_7_9_2_7_2_5_2_6_6_8_5_3_3_4_7_3_6_2_7_4_5_8_1_5_5_4_6_6_8_6_2_8_7_1_6_6_5_8_3_2_2_7_2_1_4_2_1_8_8_7_6_5_7_9_9_1_6_1_8_3_1_9_2_1_2_6_3_9_8_5_4_3_9_5_1_4_9_1_4_9_6_7_5_6_9_6_1_8_7_1_5_4_7_6_7_4_2_2_2_3_2_4_2_2_5_2_1_3_7_3_1_3_3_1_3_6_8_7_7_1_4_6_2_3_6_4_8_6_4_4_3_7_1_3_4_4_6_6_3_2_9_2_9_7_4_2_7_9_1_7_6_1_3_4_4_1_5_4_9_1_5_1_4_6_2_3_6_1_4_6_7_2_5_6_2_2_4_1_5_5_3_6_3_6_7_9_5_1_7_6_3_5_3_1_9_2_3_6_4_5_1_1_1_3_2_3_9_4_6_6_1_3_2_7_9_6_5_6_3_1_4_2_2_3_4_8_3_3_4_3_6_2_5_7_6_1_8_4_4_2_3_3_1_1_7_1_7_5_1_8_3_1_5_5_1_5_8_5_4_9_2_4_2_8_7_1_2_8_1_5_2_5_1_5_4_2_6_2_2_6_9_4_8_3_2_8_9_6_9_6_6_1_1_1_7_8_3_9_9_4_5_4_8_7_4_3_2_8_8_6_3_6_2_7_6_6_3_5_4_1_7_4_2_3_1_8_6_5_6_6_6_2_5_2_6_5_5_9_4_9_6_6_4</t>
+  </si>
+  <si>
+    <t>8_3_1_1_1_1_1_1_6_4_9_2_4_4_5_3_4_8_4_3_4_9_6_7_2_3_4_6_6_2_2_3_9_2_2_1_1_6_7_7_7_7_1_7_4_3_2_3_3_4_7_8_7_1_5_9_9_8_6_7_3_1_4_4_6_1_4_4_8_2_5_7_1_7_2_1_1_1_3_4_5_2_8_1_3_7_7_1_8_2_1_1_1_1_6_4_1_3_2_5_3_6_4_1_7_6_8_8_5_2_7_5_2_1_2_6_2_6_2_8_2_2_2_2_6_1_2_2_2_8_4_5_3_3_3_4_4_4_6_6_8_3_3_4_4_2_2_3_7_1_3_6_5_5_8_1_1_8_4_6_8_4_5_5_6_4_5_3_6_4_4_8_8_8_4_6_3_1_1_4_7_3_8_6_6_6_6_6_6_6_1_2_2_1_5_3_2_2_4_4_6_2_5_5_5_4_3_5_4_6_4_1_4_4_8_1_9_2_5_4_4_2_2_1_4_6_9_2_3_2_3_2_2_6_8_4_7_4_1_3_1_1_9_6_3_3_8_3_2_1_6_1_1_5_1_5_9_9_2_8_4_8_5_1_1_4_1_6_2_4_8_6_7_5_6_6_2_6_4_8_2_3_3_1_7_5_1_3_5_1_7_5_2_7_8_4_3_9_7_7_4_1_3_5_2_4_3_3_3_8_2_5_2_2_8_2_9_2_9_2_2_2_3_3_8_3_2_6_4_1_2_5_1_4_9_3_2_4_4_4_1_8_5_5_2_4_2_4_3_6_2_1_2_2_4_1_2_2_7_2_4_3_7_8_5_4_8_4_2_2_3_7_7_6_3_3_3_5_1_2_2_4_4_4_3_6_2_2_2_6_6_2_6_4_5_5_5_5_3_1_4_4_4_1_1_1_2_4_4_1_9_6_3_3_3_5_5_6_1_3_6_2_4_4_7_4_5_8_8_7_1_4_5_2_3_9_7_7_7_9_4_4_5_8_4_4_4_2_9_9_3_2_1_1_2_7_7_5_9_4_7_5_2_5_5_3_6_3_1_7_6_9_2_1_8_5_3_3_5_9_4_1_1_2_2_6_1_4_5_2_2_5_1_7_6_6_5_1_1_2</t>
+  </si>
+  <si>
+    <t>7_4_3_2_1_7_5_4_4_5_1_1_8_1_8_6_2_8_9_2_8_1_1_5_9_7_7_1_2_4_5_6_4_8_9_6_5_5_2_9_8_8_1_8_7_7_7_6_2_3_4_3_1_8_4_5_2_7_3_5_8_4_9_1_4_1_7_2_1_5_5_9_1_9_3_9_9_7_3_7_2_6_2_6_8_3_7_4_3_9_1_6_7_6_7_9_6_4_1_3_1_3_5_4_5_7_2_2_2_4_3_2_6_5_9_8_2_3_1_1_4_6_6_1_4_5_5_2_4_3_7_4_3_9_9_2_6_2_3_4_1_5_4_4_1_7_4_1_2_7_5_7_5_5_3_7_7_8_2_6_4_6_7_8_7_8_7_8_2_2_1_6_3_9_4_4_1_4_9_8_6_5_8_7_5_9_8_5_9_1_4_2_5_8_8_6_5_8_8_1_8_2_2_2_4_7_4_6_9_5_5_2_3_3_5_6_4_5_8_3_2_4_2_8_3_8_7_4_6_7_3_6_1_1_9_8_2_2_4_4_6_5_5_7_4_1_5_4_8_6_8_5_5_4_5_4_8_4_1_5_2_6_1_9_6_2_1_3_4_7_2_6_3_5_3_4_8_9_3_2_8_6_3_7_7_5_2_5_2_5_8_6_4_9_7_4_2_4_3_2_6_8_6_2_2_1_1_4_3_7_3_1_1_8_2_6_6_2_5_3_8_1_6_2_1_5_2_3_8_8_1_7_2_2_6_9_4_1_6_6_7_9_5_5_1_1_7_1_7_3_5_3_2_1_3_5_3_7_9_4_3_6_8_2_1_4_8_8_5_1_7_5_4_7_5_2_8_1_3_4_4_2_4_7_8_1_2_5_7_1_3_9_5_2_8_7_5_4_9_2_7_7_1_7_1_5_8_3_5_8_6_1_2_7_7_8_1_5_3_6_2_1_3_4_2_2_9_1_6_1_8_5_9_2_2_2_8_8_5_9_2_2_1_6_8_4_4_6_5_4_3_8_3_8_3_6_8_6_1_4_1_2_7_4_9_3_1_1_7_2_6_2_5_5_4_1_9_1_7_2_7_3_9_3_5_7_2_5_6_5_9_7_1_9_1_6_8_4_1_7</t>
+  </si>
+  <si>
+    <t>4_1_3_1_4_8_8_7_8_5_2_8_2_9_8_4_8_5_5_5_7_8_3_2_1_1_3_2_5_4_7_2_2_2_3_4_5_8_1_8_4_4_4_4_6_3_1_7_7_3_1_6_2_1_6_8_2_7_3_6_9_2_8_6_8_4_3_1_8_9_2_3_3_1_5_5_4_7_2_2_3_3_7_3_3_3_8_5_3_8_4_2_3_3_2_1_2_3_9_4_4_2_2_4_4_8_3_2_2_7_7_1_1_8_4_2_3_5_2_8_3_3_3_7_2_2_7_3_1_7_4_1_1_7_2_4_2_9_3_3_4_1_4_1_1_2_5_5_6_8_7_9_5_5_8_9_5_3_4_3_6_1_2_2_3_3_9_7_5_8_6_2_2_7_6_8_8_8_9_5_5_4_1_1_1_2_3_6_1_6_4_3_8_2_2_1_4_2_4_5_7_3_1_6_1_9_7_7_2_3_1_1_7_2_6_6_6_1_7_7_4_2_4_4_2_4_4_5_5_6_3_1_7_3_8_6_6_6_4_2_6_1_5_2_7_9_2_4_3_3_8_6_3_8_3_3_5_6_6_1_8_3_4_3_9_2_4_8_6_6_1_6_6_1_5_6_6_5_2_4_6_1_4_4_2_2_2_8_2_5_4_9_2_7_5_2_6_3_4_4_2_4_3_2_4_6_6_2_2_3_1_7_6_2_7_7_8_9_9_9_5_4_1_4_4_1_4_3_2_2_2_3_5_6_4_4_2_4_3_2_4_4_3_5_1_9_3_5_4_3_1_1_8_8_5_7_9_5_9_2_6_6_7_7_7_4_5_4_2_3_2_1_1_8_5_1_8_6_1_3_5_4_9_5_7_5_1_6_3_4_4_1_1_2_8_8_9_6_2_4_4_6_4_7_7_1_2_1_9_7_7_2_1_9_1_7_2_4_8_8_3_8_6_9_7_6_9_9_8_3_9_8_8_8_8_4_6_1_2_6_1_1_1_3_5_5_1_3_1_3_5_4_2_4_2_3_1_6_5_3_3_6_1_5_5_1_1_8_2_2_4_2_8_2_4_4_4_8_2_4_1_2_2_2_8_7_6_8_4_4_6_2_7_7_9_9_1_4_9_5</t>
+  </si>
+  <si>
+    <t>8_9_9_2_8_4_3_6_6_4_3_8_7_3_5_5_6_3_1_7_4_5_9_8_1_8_2_1_7_3_5_7_3_4_8_6_1_3_4_8_5_6_6_2_4_3_1_6_2_3_3_7_3_4_2_5_4_4_3_6_6_7_7_6_3_4_1_3_3_2_5_5_2_2_3_3_3_5_4_2_8_7_2_2_3_7_2_7_3_3_1_9_4_2_1_1_3_2_1_7_9_1_3_2_6_9_2_7_9_1_1_7_4_9_6_2_6_4_9_9_2_3_7_4_8_3_1_8_8_2_7_1_1_1_2_1_3_5_5_1_1_1_9_1_7_1_6_3_6_3_1_5_5_6_5_2_2_9_2_5_3_3_7_2_2_7_2_7_4_7_1_3_9_9_8_5_5_1_2_2_9_1_1_9_5_8_2_7_3_2_8_2_4_7_9_4_5_3_9_3_4_4_5_4_4_4_9_7_4_1_3_8_6_4_2_7_9_2_4_5_2_5_2_5_5_9_7_5_4_6_1_5_3_5_1_8_3_3_6_1_8_9_7_1_2_2_5_2_9_1_2_9_1_3_3_8_1_1_7_1_8_7_1_1_6_6_5_5_3_2_1_4_6_4_2_1_1_3_3_5_8_2_2_8_1_2_6_7_5_2_2_8_2_2_7_7_8_2_7_3_1_8_5_4_3_3_2_8_3_4_3_2_8_7_1_1_7_9_4_4_1_8_2_7_8_1_6_5_6_4_2_3_8_5_8_6_6_3_8_5_2_1_8_2_3_9_4_9_2_5_5_3_8_9_2_5_9_9_2_6_5_1_5_4_4_9_8_1_5_1_4_2_4_2_4_9_5_8_8_1_1_3_5_3_2_9_6_1_4_2_1_3_4_4_8_2_2_5_4_1_2_4_6_9_9_1_7_2_1_7_7_9_8_9_3_8_1_2_3_4_7_8_1_7_2_6_9_6_4_2_4_2_6_4_5_1_6_5_6_8_1_1_8_5_4_1_7_1_4_3_4_5_4_7_1_4_2_6_1_1_6_3_9_5_1_1_8_7_2_1_6_6_9_2_1_4_4_6_2_7_1_2_4_2_9_3_8_9_3_6_4_3_2_2_2_4_1_4_6_9</t>
+  </si>
+  <si>
+    <t>4_4_9_3_2_2_5_7_2_2_1_4_5_4_2_2_1_7_7_7_2_2_4_1_9_8_3_1_5_4_6_1_2_1_4_1_2_3_3_8_2_6_3_3_4_4_4_3_1_2_2_5_5_1_9_1_1_1_4_6_7_3_3_3_1_2_1_3_3_1_4_1_2_3_6_2_7_1_3_5_8_6_8_5_3_5_1_5_4_5_5_2_2_4_5_4_1_1_2_9_4_1_7_9_9_8_8_2_1_6_3_4_1_1_3_1_3_6_2_4_1_4_4_1_5_7_8_4_4_2_3_3_7_7_6_6_6_4_4_3_6_6_8_8_2_2_6_5_3_8_3_6_5_1_9_1_5_5_1_8_4_4_2_4_2_7_4_8_6_6_7_1_5_5_5_1_7_8_1_1_1_8_8_8_2_1_4_4_1_2_2_2_3_5_5_8_3_9_9_1_8_3_1_2_5_1_7_7_3_6_2_6_4_8_8_3_6_6_1_9_7_7_3_4_6_2_7_5_3_3_2_9_9_6_4_4_1_3_3_2_3_5_7_1_1_1_5_4_8_2_1_5_1_6_7_3_5_6_4_8_3_3_4_7_9_4_2_3_1_7_3_6_4_9_2_2_5_1_4_6_6_2_5_8_2_8_7_7_2_5_1_1_2_6_7_1_3_2_2_4_4_6_5_7_4_2_5_3_9_2_2_6_2_6_3_1_5_4_4_2_2_6_1_1_5_1_1_1_1_8_8_8_7_8_1_2_5_6_1_4_3_3_4_9_9_7_4_4_3_2_1_7_2_1_9_3_3_5_2_2_2_6_2_4_2_8_5_8_4_3_3_6_8_2_4_8_8_8_5_7_1_3_1_3_9_1_6_6_2_4_4_3_2_2_3_5_9_7_4_8_1_8_4_4_6_1_5_2_2_2_4_4_6_6_5_2_2_7_7_7_8_6_6_4_4_3_2_3_4_1_2_2_3_6_1_2_7_4_4_2_5_2_1_1_1_6_6_4_2_3_2_2_1_4_4_6_5_4_9_5_9_3_9_1_6_1_2_6_3_1_4_4_1_1_2_2_6_9_9_3_3_8_1_3_2_4_2_2_3_1_3_7_3_3_8_4_4_5_5_1</t>
+  </si>
+  <si>
+    <t>7_8_7_4_8_1_4_4_4_2_3_3_6_1_8_5_9_1_8_2_2_3_7_2_6_8_2_4_4_2_3_8_8_6_3_4_4_8_2_2_9_2_5_8_6_2_2_4_1_1_8_5_5_3_1_1_1_4_5_2_9_8_5_3_1_8_8_2_6_6_9_1_8_3_2_5_2_6_6_2_4_7_5_2_3_2_9_3_2_2_7_5_4_2_2_7_2_9_2_5_1_6_1_6_3_1_2_6_8_7_5_2_4_1_6_9_5_4_5_3_6_3_1_9_8_8_3_3_7_5_8_3_3_6_4_1_2_4_4_7_1_6_6_8_2_8_1_8_4_5_4_1_9_1_2_2_6_2_6_9_7_7_7_3_9_7_7_4_2_5_2_3_5_1_6_4_3_6_7_5_2_3_5_6_6_1_1_4_4_5_1_2_1_6_1_9_6_7_5_8_8_2_1_2_5_6_3_3_3_4_6_9_1_4_6_4_6_5_5_2_6_7_3_4_7_3_2_2_4_1_7_7_2_2_3_8_9_9_1_1_3_6_3_6_5_2_4_6_2_9_1_5_7_4_5_8_2_5_6_4_7_3_4_8_9_6_3_5_4_4_8_6_8_8_1_6_4_6_1_1_2_2_4_9_6_4_8_1_4_4_5_9_2_5_5_1_7_2_5_1_3_3_4_2_8_2_8_2_5_9_8_1_9_7_5_2_3_4_9_8_3_2_6_7_9_7_3_2_3_2_6_6_2_9_1_1_5_7_9_4_4_5_5_2_9_8_1_2_1_6_2_5_5_9_7_1_5_6_4_4_3_3_9_6_2_2_6_3_7_4_5_8_8_5_6_5_3_5_4_2_4_6_1_1_2_7_6_2_4_1_6_4_2_1_6_8_8_5_2_8_6_3_1_7_6_3_7_9_4_3_9_2_6_1_5_3_8_5_1_7_2_6_3_8_6_6_7_1_4_2_3_8_3_2_6_3_6_1_6_1_8_3_8_5_9_2_8_1_1_9_6_4_2_9_5_8_6_4_9_1_6_5_4_3_8_8_9_8_6_2_2_3_6_5_4_6_8_5_4_9_6_5_9_4_7_1_5_2_3_2_2_1_1_2_3_1_4_1_6_4</t>
+  </si>
+  <si>
+    <t>8_5_1_6_2_2_6_3_2_7_7_9_1_7_2_8_9_8_7_4_5_4_5_5_2_8_2_2_2_2_4_4_7_5_4_1_5_8_3_5_2_3_6_1_2_8_6_6_5_6_8_6_6_1_9_3_7_7_6_1_1_5_1_7_8_7_3_7_4_1_2_2_9_6_5_3_3_4_8_3_5_4_3_3_2_3_3_6_3_3_2_2_8_4_2_4_9_2_2_3_6_9_7_3_3_5_8_7_2_3_4_1_9_8_8_2_3_4_1_5_2_9_1_2_8_2_5_5_1_1_8_5_4_2_8_1_1_1_4_3_1_4_4_1_7_4_2_1_2_6_5_7_8_1_1_2_2_7_1_8_1_1_4_4_2_6_2_1_4_2_3_4_6_8_8_7_2_2_8_3_6_3_2_2_5_5_9_9_3_1_4_4_3_6_4_3_1_6_6_2_1_1_4_4_5_1_9_5_6_9_9_9_1_5_4_1_8_5_5_9_5_7_7_5_3_1_9_9_4_7_4_1_4_4_6_6_3_5_1_3_6_9_2_3_2_2_1_1_2_6_2_6_2_1_4_3_5_6_1_6_7_7_5_2_2_3_1_5_4_1_2_3_1_5_2_1_7_7_3_1_9_5_3_4_3_2_4_6_9_3_6_5_4_1_4_3_2_7_2_6_4_2_1_1_8_5_5_2_2_6_6_5_3_1_4_8_2_7_7_5_6_7_8_2_7_1_1_2_8_9_1_7_4_5_5_8_8_3_9_3_3_1_7_5_9_1_1_5_1_1_5_5_3_1_7_5_3_6_2_1_2_1_7_9_9_2_4_2_2_2_8_1_3_4_3_4_1_4_5_2_1_3_2_2_9_3_6_4_8_8_2_7_6_1_9_7_1_6_5_3_7_7_2_4_5_8_1_6_6_3_6_6_6_4_1_6_4_5_1_2_7_3_2_6_1_8_6_7_9_1_1_5_1_8_9_5_3_5_5_9_8_4_3_3_2_3_2_1_5_3_9_9_8_5_7_5_2_2_2_3_7_1_1_4_5_6_1_9_4_2_3_9_3_3_2_6_8_8_8_4_4_4_5_5_8_1_6_1_3_4_7_2_6_2_1_6_1_2_1_8</t>
+  </si>
+  <si>
+    <t>5_9_5_4_4_2_4_3_3_1_4_3_2_4_3_1_3_9_2_7_1_8_9_4_8_2_6_4_2_1_6_4_1_4_9_2_1_9_5_1_1_4_1_5_6_1_7_4_7_8_3_1_9_5_3_2_6_8_1_7_5_2_3_5_1_2_8_7_8_1_8_8_2_6_3_1_6_4_2_1_4_3_1_9_6_3_6_1_3_1_1_1_7_8_5_5_1_7_5_6_3_7_8_9_1_2_5_8_6_7_1_1_3_8_2_8_9_5_3_5_6_6_9_8_1_1_2_1_6_1_3_7_5_5_4_9_1_3_6_6_9_5_4_4_9_3_5_4_3_7_4_4_1_5_2_7_3_5_7_2_4_1_4_8_4_2_1_9_2_2_5_1_9_2_7_3_9_4_1_2_1_2_2_4_5_3_5_3_8_4_7_5_7_4_4_8_3_9_3_6_1_6_7_7_6_6_1_6_1_1_1_1_6_2_8_4_8_5_6_4_3_8_6_1_3_3_8_4_3_4_7_2_4_4_3_1_3_1_4_1_5_4_5_2_7_7_3_7_4_1_2_2_3_8_1_7_1_4_2_4_3_8_4_7_4_1_6_1_5_7_5_1_3_5_7_2_1_8_4_5_4_2_2_6_2_8_7_1_8_3_9_6_3_1_6_1_5_6_3_4_3_2_4_7_1_2_6_2_4_4_9_5_1_2_9_1_3_9_3_2_2_8_1_6_1_8_3_5_1_2_3_4_3_6_2_5_5_3_6_1_4_2_2_9_5_3_8_3_7_7_7_6_9_5_7_7_5_8_2_6_2_8_7_1_3_3_4_5_7_3_2_6_4_3_9_8_3_8_4_1_8_3_6_2_7_5_5_1_2_1_9_5_3_6_4_9_1_4_2_7_9_6_4_8_6_1_1_3_9_6_4_5_5_3_6_1_2_4_6_5_2_1_4_9_4_2_2_2_7_8_1_7_7_2_3_9_3_3_3_5_2_7_8_8_6_5_6_4_7_2_2_8_5_8_1_9_1_2_8_6_3_8_3_3_8_2_5_2_7_4_2_6_1_2_4_7_5_8_9_3_7_5_3_6_6_4_3_6_6_1_3_4_9_3_6_3_3_4_3_4</t>
   </si>
 </sst>
 </file>
@@ -597,12 +627,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1725,7 +1755,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -3693,6 +3723,166 @@
       <c r="J62" s="17"/>
       <c r="K62" s="17"/>
     </row>
+    <row r="63" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A63" s="5">
+        <f>C63*10+D63</f>
+        <v>20250011</v>
+      </c>
+      <c r="B63" s="13">
+        <v>102500</v>
+      </c>
+      <c r="C63" s="33">
+        <v>2025001</v>
+      </c>
+      <c r="D63" s="33">
+        <v>1</v>
+      </c>
+      <c r="E63" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F63" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G63" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="H63" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I63" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="J63" s="17"/>
+      <c r="K63" s="17"/>
+    </row>
+    <row r="64" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A64" s="5">
+        <f>C64*10+D64</f>
+        <v>20250012</v>
+      </c>
+      <c r="B64" s="13">
+        <v>102500</v>
+      </c>
+      <c r="C64" s="33">
+        <v>2025001</v>
+      </c>
+      <c r="D64" s="33">
+        <v>2</v>
+      </c>
+      <c r="E64" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F64" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G64" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="H64" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I64" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="J64" s="17"/>
+      <c r="K64" s="17"/>
+    </row>
+    <row r="65" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A65" s="5">
+        <f>C65*10+D65</f>
+        <v>20250013</v>
+      </c>
+      <c r="B65" s="13">
+        <v>102500</v>
+      </c>
+      <c r="C65" s="33">
+        <v>2025001</v>
+      </c>
+      <c r="D65" s="33">
+        <v>3</v>
+      </c>
+      <c r="E65" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F65" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G65" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="H65" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I65" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="J65" s="17"/>
+      <c r="K65" s="17"/>
+    </row>
+    <row r="66" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A66" s="5">
+        <f>C66*10+D66</f>
+        <v>20250014</v>
+      </c>
+      <c r="B66" s="13">
+        <v>102500</v>
+      </c>
+      <c r="C66" s="33">
+        <v>2025001</v>
+      </c>
+      <c r="D66" s="33">
+        <v>4</v>
+      </c>
+      <c r="E66" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="F66" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G66" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="H66" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="J66" s="17"/>
+      <c r="K66" s="17"/>
+    </row>
+    <row r="67" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A67" s="5">
+        <f>C67*10+D67</f>
+        <v>20250015</v>
+      </c>
+      <c r="B67" s="13">
+        <v>102500</v>
+      </c>
+      <c r="C67" s="33">
+        <v>2025001</v>
+      </c>
+      <c r="D67" s="33">
+        <v>5</v>
+      </c>
+      <c r="E67" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F67" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G67" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="H67" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I67" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="J67" s="17"/>
+      <c r="K67" s="17"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="132">
   <si>
     <t>id</t>
   </si>
@@ -445,6 +445,36 @@
   </si>
   <si>
     <t>5_9_5_4_4_2_4_3_3_1_4_3_2_4_3_1_3_9_2_7_1_8_9_4_8_2_6_4_2_1_6_4_1_4_9_2_1_9_5_1_1_4_1_5_6_1_7_4_7_8_3_1_9_5_3_2_6_8_1_7_5_2_3_5_1_2_8_7_8_1_8_8_2_6_3_1_6_4_2_1_4_3_1_9_6_3_6_1_3_1_1_1_7_8_5_5_1_7_5_6_3_7_8_9_1_2_5_8_6_7_1_1_3_8_2_8_9_5_3_5_6_6_9_8_1_1_2_1_6_1_3_7_5_5_4_9_1_3_6_6_9_5_4_4_9_3_5_4_3_7_4_4_1_5_2_7_3_5_7_2_4_1_4_8_4_2_1_9_2_2_5_1_9_2_7_3_9_4_1_2_1_2_2_4_5_3_5_3_8_4_7_5_7_4_4_8_3_9_3_6_1_6_7_7_6_6_1_6_1_1_1_1_6_2_8_4_8_5_6_4_3_8_6_1_3_3_8_4_3_4_7_2_4_4_3_1_3_1_4_1_5_4_5_2_7_7_3_7_4_1_2_2_3_8_1_7_1_4_2_4_3_8_4_7_4_1_6_1_5_7_5_1_3_5_7_2_1_8_4_5_4_2_2_6_2_8_7_1_8_3_9_6_3_1_6_1_5_6_3_4_3_2_4_7_1_2_6_2_4_4_9_5_1_2_9_1_3_9_3_2_2_8_1_6_1_8_3_5_1_2_3_4_3_6_2_5_5_3_6_1_4_2_2_9_5_3_8_3_7_7_7_6_9_5_7_7_5_8_2_6_2_8_7_1_3_3_4_5_7_3_2_6_4_3_9_8_3_8_4_1_8_3_6_2_7_5_5_1_2_1_9_5_3_6_4_9_1_4_2_7_9_6_4_8_6_1_1_3_9_6_4_5_5_3_6_1_2_4_6_5_2_1_4_9_4_2_2_2_7_8_1_7_7_2_3_9_3_3_3_5_2_7_8_8_6_5_6_4_7_2_2_8_5_8_1_9_1_2_8_6_3_8_3_3_8_2_5_2_7_4_2_6_1_2_4_7_5_8_9_3_7_5_3_6_6_4_3_6_6_1_3_4_9_3_6_3_3_4_3_4</t>
+  </si>
+  <si>
+    <t>3_3_5_3_1_6_3_3_2_2_1_4_4_4_1_3_8_8_4_9_2_2_2_2_2_6_9_7_9_5_7_1_4_4_2_7_1_7_2_2_8_6_8_5_1_8_8_1_8_4_2_3_3_3_3_7_6_6_3_1_5_8_6_2_2_6_6_8_6_9_4_6_5_9_4_2_7_7_8_8_8_4_2_8_5_7_1_4_4_5_4_5_1_1_7_5_6_4_9_7_6_8_3_3_4_6_2_3_7_1_5_3_6_1_1_3_6_5_1_8_5_2_2_8_1_9_9_5_4_4_1_1_8_4_1_1_1_5_1_5_8_3_3_8_3_1_5_6_6_6_2_2_5_5_3_2_6_2_4_9_7_2_9_9_1_7_1_1_2_2_4_1_1_1_4_7_7_5_3_1_4_6_5_9_4_4_2_7_7_9_1_1_1_4_8_3_7_1_1_4_9_7_6_6_1_4_1_2_4_3_3_1_4_1_7_1_7_7_4_5_6_3_3_2_1_6_1_2_1_7_3_4_5_2_1_3_2_6_6_6_1_4_1_5_9_6_6_3_2_3_2_7_3_4_5_2_1_8_8_1_6_6_1_1_2_2_2_7_8_5_1_8_1_1_1_7_8_5_4_8_3_1_7_3_9_9_8_8_5_6_3_5_5_9_5_1_1_1_1_1_8_1_2_3_7_2_1_8_2_6_1_5_5_5_5_5_5_2_4_1_1_1_1_5_8_4_8_2_5_4_4_4_3_6_6_4_4_3_9_5_1_9_9_4_2_9_8_4_4_6_1_2_6_6_4_4_5_9_1_9_5_5_3_3_8_2_5_9_9_9_9_1_5_3_3_3_3_4_7_2_4_6_3_4_9_9_2_9_5_5_4_5_1_1_1_6_9_2_3_6_8_8_3_4_1_4_4_2_1_7_8_7_7_7_3_3_4_4_5_8_7_1_5_4_4_2_2_2_3_7_5_2_3_3_1_1_4_1_8_5_5_4_2_5_5_6_6_3_6_2_1_2_5_1_7_7_4_8_1_4_1_5_5_1_6_7_9_1_4_3_4_4_8_3_3_9_9_4_8_5_6_9_2_8_3_6_1_5_9_1_9_3_2_1_2_2_6_9_7_9</t>
+  </si>
+  <si>
+    <t>6_3_9_4_1_2_7_6_6_5_4_1_6_4_5_1_1_7_1_1_7_1_5_7_5_1_2_5_8_4_2_1_6_4_7_1_2_9_1_3_9_8_7_7_2_2_2_1_1_5_3_8_5_6_4_3_3_4_3_8_1_9_7_3_8_2_6_1_7_5_5_7_6_8_6_4_9_8_8_9_1_2_6_4_6_6_6_3_9_4_3_2_6_4_2_5_7_4_9_7_1_5_2_2_8_6_2_8_4_1_1_7_5_8_1_9_1_1_3_8_5_1_2_5_7_3_3_6_6_4_5_5_8_6_6_6_8_3_4_5_8_5_7_8_8_8_7_3_1_1_8_5_4_3_2_8_3_3_7_5_2_5_1_2_8_5_4_5_1_9_1_3_4_8_2_7_8_4_9_1_6_8_3_2_7_7_1_7_8_7_4_4_3_4_3_5_4_1_6_1_3_2_2_4_6_1_2_6_6_2_5_4_8_7_8_1_2_4_6_7_6_5_1_5_4_7_6_1_4_4_8_1_5_4_4_7_7_4_3_2_8_1_1_8_2_9_6_6_7_4_6_3_2_1_9_4_5_2_2_3_2_2_4_4_3_6_5_8_2_1_6_5_8_2_8_4_9_6_2_2_3_5_3_7_3_2_6_3_1_1_8_6_8_2_8_7_8_1_2_4_1_5_9_3_4_4_8_2_7_9_6_1_1_4_5_7_3_8_1_6_5_6_1_1_9_5_6_2_9_5_4_4_8_4_5_2_3_2_1_1_2_4_4_2_2_5_7_7_2_1_1_5_4_4_1_2_8_3_3_2_2_1_8_5_6_3_9_6_4_1_1_6_6_6_6_1_2_5_6_9_4_5_1_2_4_2_2_7_4_5_3_4_1_4_1_4_6_5_8_9_7_1_2_1_3_4_7_6_3_4_1_5_7_6_1_3_6_4_6_2_4_9_4_6_1_1_5_5_1_2_8_1_6_2_8_1_9_6_6_6_2_1_2_4_1_4_2_3_8_4_4_9_6_2_4_7_1_4_7_3_2_3_3_3_4_4_5_6_3_8_1_1_7_6_2_9_2_6_3_6_9_1_4_9_7_5_6_9_2_4_5_6_5_8_9_4_5_6_3_3</t>
+  </si>
+  <si>
+    <t>5_2_2_2_4_4_3_2_4_6_2_4_1_8_7_2_2_1_6_6_4_1_1_4_6_2_1_3_8_3_2_8_7_9_9_2_4_4_4_4_3_7_7_7_2_4_1_1_8_4_2_8_7_7_8_8_3_3_5_3_6_6_9_1_3_9_7_1_1_1_1_2_5_1_6_4_3_3_2_6_6_1_2_9_6_2_4_7_9_4_6_9_3_3_8_2_2_2_6_2_2_1_3_1_4_9_4_4_4_4_2_1_6_2_7_7_7_1_3_6_9_9_4_4_1_4_6_2_2_4_6_8_2_4_6_4_7_9_3_3_9_3_4_4_3_1_5_5_9_9_3_8_6_9_9_6_5_4_5_5_4_7_7_5_2_1_3_3_9_7_8_3_8_5_2_6_8_5_3_3_3_3_7_2_8_4_4_1_4_2_9_1_2_6_3_4_6_3_2_4_4_4_3_2_7_8_1_3_4_9_1_3_3_3_1_1_2_4_8_8_5_2_2_4_3_1_5_6_6_1_4_2_1_2_5_6_3_8_1_8_2_3_8_3_4_2_4_7_5_5_2_5_5_4_9_8_1_1_5_8_7_2_7_9_6_5_1_5_1_2_4_6_8_3_3_8_6_6_2_2_1_6_2_2_4_3_1_3_6_4_3_1_4_2_6_6_6_3_7_5_6_4_3_3_5_6_6_3_5_6_9_2_5_8_7_6_3_3_2_1_3_1_4_5_1_6_7_5_5_5_1_2_7_9_1_6_6_6_1_1_2_1_1_1_4_4_4_6_7_6_1_4_2_9_2_4_3_5_9_3_6_6_6_1_3_4_6_5_1_1_1_4_1_1_1_1_8_3_1_6_2_3_3_3_4_4_5_5_1_1_3_3_7_1_5_7_3_3_8_3_8_3_2_5_9_3_6_3_9_7_3_5_5_5_2_1_7_5_6_8_3_7_2_1_1_2_3_3_1_1_3_1_1_8_2_2_4_6_5_7_9_5_1_4_4_4_1_6_5_7_3_7_1_4_8_3_7_5_5_6_1_3_1_3_4_4_2_1_2_4_7_7_7_7_2_2_1_1_1_5_4_4_2_4_1_9_3_2_4_4_4_6_8_3_4_2_4_1_1_6</t>
+  </si>
+  <si>
+    <t>7_2_2_4_2_1_2_6_1_2_6_8_4_8_8_7_3_7_4_6_3_1_3_9_9_6_2_1_4_4_3_1_1_2_5_1_5_7_8_9_2_1_4_1_8_1_8_9_6_7_5_6_9_3_6_5_7_2_2_4_8_8_9_5_6_1_3_7_7_4_7_6_2_5_5_3_3_4_5_3_3_7_2_7_2_7_5_2_1_4_1_2_8_7_2_8_6_5_6_3_6_1_5_4_8_5_8_6_2_7_2_1_3_4_1_9_3_6_7_4_3_5_6_3_1_1_3_7_2_3_7_4_6_7_3_2_2_3_4_9_4_2_5_9_8_2_7_8_7_3_8_9_3_2_2_5_5_2_2_7_1_5_1_4_5_4_9_6_3_1_2_5_5_1_2_1_3_7_2_1_2_3_1_6_3_6_2_2_9_1_3_8_1_5_8_6_4_4_1_3_4_4_9_4_4_2_1_5_6_1_7_6_1_8_1_3_3_4_2_7_8_2_8_9_7_5_4_6_7_5_4_1_2_2_1_3_2_5_1_1_3_5_2_1_8_4_2_3_8_8_5_2_4_7_1_6_5_5_1_7_6_9_2_5_4_2_7_8_1_2_7_6_6_7_2_9_3_5_8_4_7_3_4_2_6_7_2_8_4_2_6_9_1_1_4_5_3_3_2_1_1_3_8_7_2_1_6_1_2_1_1_2_7_3_4_9_9_9_5_3_7_2_3_1_6_1_9_6_2_1_4_4_2_2_5_5_1_3_6_3_2_9_7_7_5_3_2_6_5_8_2_1_9_1_6_4_6_6_6_4_3_4_3_9_1_3_7_6_2_1_8_6_8_6_4_6_5_2_6_1_1_8_5_3_9_8_8_4_4_4_1_6_6_7_4_3_1_2_7_2_6_4_5_7_3_4_5_1_8_8_2_2_2_8_3_3_1_2_9_2_3_3_1_7_9_2_6_4_7_5_1_3_5_3_4_8_6_8_9_3_1_2_2_4_1_5_5_7_2_5_5_4_2_5_6_7_6_3_1_6_8_7_6_4_7_4_5_6_5_3_5_2_3_3_1_5_5_1_2_4_4_5_9_5_4_1_6_1_2_8_4_9_6_9_3_1_2_8_3_3</t>
+  </si>
+  <si>
+    <t>1_5_4_7_3_1_6_6_9_3_3_6_2_9_2_9_4_5_5_5_4_6_6_6_6_8_5_2_8_8_4_6_6_2_9_1_4_8_7_2_5_8_4_4_1_1_1_6_9_8_1_1_2_9_3_2_5_8_4_6_6_1_5_7_3_6_1_1_4_3_5_9_1_3_2_3_6_6_5_8_2_2_2_6_3_6_3_3_4_4_5_9_8_5_4_4_2_3_2_2_5_1_1_2_2_2_4_4_4_6_7_6_5_3_2_3_2_6_8_7_7_5_2_2_5_3_7_3_4_1_1_1_1_4_1_9_1_7_6_9_7_2_2_5_2_3_9_8_4_5_2_2_3_4_9_2_2_2_1_9_3_4_2_9_6_4_7_1_9_7_1_2_4_5_8_3_3_4_7_8_2_5_2_3_1_6_8_8_8_8_7_3_4_6_8_3_3_8_4_1_1_8_9_9_9_4_3_2_1_5_9_1_8_3_9_9_8_1_9_9_9_9_9_3_2_7_1_5_3_3_5_2_7_7_6_7_7_5_7_6_5_2_5_1_1_4_5_5_9_2_3_4_5_4_4_3_3_6_3_3_1_8_8_9_7_9_9_3_5_1_3_6_5_8_3_2_5_2_2_7_3_1_1_5_2_4_4_6_2_9_2_2_2_4_8_2_5_2_4_5_7_5_4_3_3_2_5_1_1_3_8_8_2_4_1_5_8_5_5_5_4_6_9_4_4_9_5_5_4_8_8_5_5_5_2_9_9_3_1_2_2_1_6_6_2_5_2_4_4_1_9_9_4_7_7_5_3_4_6_5_5_3_7_2_4_6_4_1_8_2_2_2_2_3_1_4_8_1_6_6_6_7_8_1_1_6_4_2_9_2_5_5_4_2_2_3_2_2_3_1_1_8_2_6_9_1_7_7_1_9_2_1_7_2_3_3_2_1_2_4_4_6_3_8_8_8_6_6_2_7_9_1_2_1_8_8_3_5_6_2_2_2_3_2_2_1_4_7_2_2_2_1_5_1_2_4_4_2_4_5_1_1_1_9_8_6_5_3_3_3_4_1_1_5_9_4_4_1_9_9_1_1_5_6_3_3_3_4_4_6_4_4_6_4_3_3_8_9_2_6</t>
+  </si>
+  <si>
+    <t>4_9_9_3_1_1_1_5_1_5_2_4_2_1_6_2_6_6_3_7_7_9_9_9_5_2_4_7_3_1_1_1_6_8_6_5_6_2_8_6_2_2_9_7_9_6_1_6_2_9_2_3_2_9_1_3_5_3_2_7_2_8_7_4_3_4_4_8_5_1_6_1_7_7_5_7_5_1_1_8_6_4_4_4_1_6_3_8_4_9_1_6_2_9_5_1_3_4_6_5_3_2_8_3_5_5_5_3_2_5_1_5_5_2_7_8_5_6_3_4_8_4_6_3_4_8_7_6_3_8_5_5_8_5_5_8_2_7_6_2_4_6_6_3_2_6_3_4_9_9_3_3_7_7_6_2_2_5_4_8_5_9_2_6_1_3_3_8_7_8_4_7_6_4_6_1_7_3_4_1_1_2_5_8_4_7_1_5_3_6_1_4_5_6_4_2_5_3_8_2_6_1_9_2_7_1_1_6_8_6_9_1_4_1_5_2_8_4_7_6_3_8_1_5_7_8_2_5_2_9_2_8_1_1_7_3_2_8_5_7_1_2_6_9_5_7_7_9_7_7_9_4_1_2_3_4_6_3_2_1_2_4_2_1_6_5_3_3_4_2_2_2_3_8_4_6_6_9_6_6_2_1_4_5_6_8_2_1_4_5_2_1_8_9_8_5_6_6_5_7_4_6_3_5_5_5_1_6_1_8_7_6_3_5_9_3_2_1_3_6_5_8_3_5_1_4_5_3_5_6_9_8_4_1_8_4_7_3_2_3_2_5_3_7_7_2_8_1_5_6_5_6_3_2_4_3_4_2_6_1_2_3_1_3_9_3_8_8_5_9_6_4_8_1_2_8_8_1_3_3_1_3_1_1_2_7_3_6_2_1_7_5_3_4_5_2_3_4_8_2_8_8_4_5_3_2_7_5_8_4_8_8_3_2_2_5_3_4_9_4_1_1_2_1_6_9_2_2_6_3_7_5_5_6_3_7_1_5_8_2_4_4_8_9_8_4_7_2_3_4_4_2_6_7_9_3_6_1_1_3_3_6_3_8_8_9_1_6_7_2_8_2_3_3_1_3_2_3_1_5_4_3_1_3_2_2_2_3_1_1_2_4_6_1_1_6_4_5_5_3</t>
+  </si>
+  <si>
+    <t>3_3_3_4_4_7_4_4_2_3_3_6_2_2_4_3_2_1_6_4_3_3_9_5_7_9_5_1_1_4_4_9_2_8_3_2_5_9_3_8_2_4_3_3_6_3_3_3_5_3_6_6_1_2_3_2_2_8_9_4_2_2_2_3_6_4_8_5_1_5_9_9_3_1_1_8_3_1_7_9_1_2_8_2_6_4_2_1_5_8_3_7_4_6_1_7_3_4_4_7_4_5_6_5_7_4_4_9_5_4_7_8_8_4_4_9_7_2_8_2_7_7_7_7_8_8_2_6_5_3_6_3_1_3_1_2_1_1_1_1_4_2_6_1_1_1_7_6_3_8_3_3_3_8_5_7_2_5_1_5_4_9_1_1_2_8_8_2_6_4_2_1_9_8_5_2_6_2_7_7_2_1_2_1_4_4_2_6_3_5_5_3_2_5_5_5_3_8_9_9_5_4_4_4_4_1_5_6_1_1_1_1_5_3_4_6_3_3_3_3_9_8_5_8_2_4_1_4_3_2_6_3_1_1_7_5_1_2_2_8_8_2_8_1_7_3_4_6_2_9_2_2_8_6_8_6_1_1_2_3_3_2_6_3_5_2_8_8_2_9_8_8_4_3_6_7_1_2_9_1_6_5_7_2_2_5_7_7_8_5_6_1_1_5_4_5_2_2_3_2_8_5_8_6_1_2_9_5_1_6_3_3_2_4_3_4_5_6_6_6_7_7_2_4_3_3_2_5_5_1_2_7_3_5_3_1_7_6_2_5_6_5_3_3_2_2_5_5_5_9_4_1_2_1_4_7_4_2_3_4_3_5_6_1_4_4_2_2_5_4_2_2_2_2_4_3_6_5_1_1_3_3_7_4_6_2_2_1_2_2_4_5_1_6_2_3_1_4_2_9_2_5_5_7_7_1_8_1_4_4_6_6_8_4_1_5_4_4_8_3_7_1_1_1_2_1_4_9_9_3_6_4_1_1_8_2_5_4_1_1_3_7_1_3_1_6_4_5_3_9_4_6_1_1_1_7_4_5_3_2_1_4_6_2_4_6_1_6_3_3_2_8_8_4_7_2_9_1_8_3_1_3_3_2_5_5_2_4_5_5_7_7_3_4_6_6_3_9_8_7</t>
+  </si>
+  <si>
+    <t>4_1_6_7_2_1_9_3_3_2_2_2_4_3_9_6_3_2_4_2_8_1_5_6_3_1_7_3_6_1_1_2_6_8_8_7_7_2_5_2_3_9_9_4_3_3_3_7_1_5_2_6_3_5_4_4_9_4_1_3_2_4_1_3_6_2_7_2_4_7_4_5_8_1_1_1_8_9_2_3_1_1_7_1_4_2_1_2_2_1_3_2_1_2_5_9_7_6_1_7_2_4_6_8_2_1_9_1_7_3_3_4_3_5_2_8_1_7_1_9_2_7_9_2_5_6_3_3_5_6_6_2_8_9_2_6_2_1_8_5_1_3_6_5_1_6_3_6_1_3_4_9_5_1_3_3_8_6_4_2_4_1_5_2_2_1_4_9_8_2_8_6_7_2_2_1_5_8_5_3_4_2_1_4_8_4_8_9_5_9_3_3_2_2_2_4_2_8_2_3_2_7_4_4_5_1_6_4_4_9_6_1_6_6_4_8_7_3_1_1_8_4_4_9_5_5_7_1_1_8_1_1_4_6_4_1_5_9_4_6_1_6_9_2_3_8_4_1_2_1_1_4_2_6_4_2_5_2_4_8_3_7_7_9_7_4_7_4_1_5_4_2_1_3_2_1_3_1_3_2_6_9_3_7_4_4_5_9_3_4_9_1_1_2_4_9_4_4_2_6_8_3_8_7_5_1_6_8_6_9_1_2_5_3_3_3_7_4_3_6_1_2_6_1_5_2_1_4_8_7_2_7_2_2_1_6_8_5_8_3_2_4_7_4_4_5_2_1_9_3_9_1_9_1_3_3_1_9_5_6_3_9_8_5_8_5_2_8_1_8_7_1_1_3_3_5_1_5_6_7_6_8_3_2_2_1_6_1_3_6_1_2_4_2_1_3_4_9_8_7_7_1_3_3_7_9_2_1_8_3_7_4_1_3_4_8_1_1_8_1_7_3_4_2_6_8_2_5_1_2_4_2_3_7_2_3_5_1_6_6_1_7_1_9_5_1_3_3_8_3_5_2_4_4_1_6_6_8_3_4_3_3_6_2_4_7_9_1_6_6_7_9_2_5_1_1_5_6_3_8_6_6_1_3_5_8_2_3_7_2_8_5_9_4_4_1_1_4_2_4</t>
+  </si>
+  <si>
+    <t>1_2_2_2_3_3_3_5_1_4_8_2_3_2_2_7_6_4_1_2_8_8_8_8_9_3_2_5_5_7_4_6_5_2_2_2_7_7_3_1_3_3_1_5_5_1_9_2_2_6_6_6_9_2_4_5_5_3_1_2_1_4_5_5_6_4_7_5_2_7_7_1_1_4_5_9_5_8_8_2_1_1_7_7_3_5_5_6_3_4_4_7_7_6_5_1_2_3_3_2_9_3_2_2_5_5_3_3_7_1_4_2_2_1_4_2_6_8_3_4_4_9_1_2_9_1_2_7_4_1_7_7_9_3_4_3_9_1_5_2_2_2_1_2_7_2_2_7_5_6_4_4_4_4_3_2_9_4_4_6_7_2_2_5_5_5_4_6_6_1_2_7_5_8_2_1_1_7_6_7_1_2_1_3_1_2_3_5_1_6_5_2_4_4_2_1_1_1_2_2_1_3_3_7_3_4_2_2_7_4_7_1_5_2_2_2_2_8_1_2_3_3_1_6_3_1_4_4_4_6_2_6_6_5_6_8_7_6_8_8_9_8_6_6_6_2_5_4_4_6_6_5_2_4_4_1_5_3_3_2_2_1_2_9_1_6_6_6_5_8_7_5_4_5_9_7_1_4_2_1_2_4_3_1_7_2_3_1_1_4_4_4_3_4_4_6_1_4_7_6_3_8_2_7_2_1_6_3_2_1_1_6_8_5_5_5_1_3_5_3_4_3_7_2_7_5_5_3_1_2_6_8_1_4_7_7_4_1_4_7_1_7_4_5_3_3_8_1_4_4_2_1_2_6_3_4_4_2_2_3_7_5_3_2_3_1_5_6_6_6_4_3_6_8_3_3_1_8_8_2_5_4_7_2_4_9_1_2_7_8_2_3_2_4_8_2_1_2_2_3_1_1_8_1_8_1_5_3_7_1_5_7_5_8_4_4_1_4_4_7_7_2_4_4_5_1_1_3_4_2_7_5_5_1_4_2_1_1_1_9_4_9_6_2_4_5_2_2_6_6_3_7_3_1_7_2_1_8_4_6_1_7_1_3_1_3_3_4_7_9_5_1_7_1_7_1_6_4_5_4_4_6_7_3_3_4_2_7_3_2_2_2_2_4_2_2_8_1_5_2</t>
+  </si>
+  <si>
+    <t>9_1_7_1_3_6_1_3_5_3_2_9_1_2_1_7_5_3_1_9_8_6_8_6_2_5_2_7_2_3_2_3_7_2_9_6_9_3_2_2_4_1_1_4_5_8_9_8_6_1_3_4_4_4_5_7_8_3_2_1_8_2_1_6_3_4_7_5_5_2_3_4_1_7_3_2_7_3_6_5_9_4_5_3_5_5_8_2_7_2_4_3_8_6_6_4_1_4_3_1_3_5_2_3_7_6_1_1_5_5_1_2_7_3_8_2_7_3_3_3_6_4_3_4_8_1_6_4_8_3_5_1_6_4_1_3_5_6_4_6_3_3_6_6_8_7_2_2_4_2_8_9_3_3_6_3_9_5_9_8_2_4_4_1_7_8_1_2_6_1_3_5_5_8_6_3_1_6_4_2_6_5_2_2_6_5_1_9_7_3_5_6_9_9_6_4_8_1_2_7_9_7_8_3_5_5_6_7_5_7_2_3_7_3_4_5_7_1_6_2_2_7_5_5_8_4_8_1_2_2_4_1_9_2_5_8_8_5_1_9_4_3_8_1_4_6_1_2_3_8_2_5_5_1_1_6_4_1_6_9_1_3_5_9_4_8_2_1_3_8_1_2_3_2_8_5_5_4_4_5_3_7_4_4_6_5_9_5_7_8_3_2_2_4_7_2_6_4_4_6_1_8_3_2_6_6_4_7_7_9_6_3_3_9_4_5_1_3_4_3_1_1_5_2_3_1_2_6_1_3_7_8_3_7_7_5_9_2_2_4_1_4_5_2_6_4_6_4_8_1_9_4_6_5_4_7_3_1_9_8_6_5_7_2_3_8_2_2_7_5_3_6_2_9_3_1_4_6_3_2_1_1_5_4_2_5_7_7_3_5_9_2_2_8_2_8_2_7_6_6_2_7_5_7_6_7_2_2_1_3_6_4_9_2_4_6_8_5_2_6_6_8_2_2_1_1_5_8_7_5_1_4_1_6_8_3_6_6_5_6_1_6_1_9_5_6_6_5_2_3_2_4_2_4_2_8_9_1_5_6_2_1_7_7_3_3_3_4_2_7_5_5_1_4_9_4_8_5_6_2_4_9_9_6_2_3_6_7_7_8_1_6_5_4_1_6_2_7_2_3</t>
   </si>
 </sst>
 </file>
@@ -1755,7 +1785,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -3533,7 +3563,7 @@
     </row>
     <row r="57" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A57" s="5">
-        <f t="shared" ref="A57:A62" si="2">C57*10+D57</f>
+        <f t="shared" ref="A57:A67" si="2">C57*10+D57</f>
         <v>20180011</v>
       </c>
       <c r="B57" s="13">
@@ -3725,7 +3755,7 @@
     </row>
     <row r="63" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A63" s="5">
-        <f>C63*10+D63</f>
+        <f t="shared" si="2"/>
         <v>20250011</v>
       </c>
       <c r="B63" s="13">
@@ -3757,7 +3787,7 @@
     </row>
     <row r="64" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A64" s="5">
-        <f>C64*10+D64</f>
+        <f t="shared" si="2"/>
         <v>20250012</v>
       </c>
       <c r="B64" s="13">
@@ -3789,7 +3819,7 @@
     </row>
     <row r="65" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A65" s="5">
-        <f>C65*10+D65</f>
+        <f t="shared" si="2"/>
         <v>20250013</v>
       </c>
       <c r="B65" s="13">
@@ -3821,7 +3851,7 @@
     </row>
     <row r="66" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A66" s="5">
-        <f>C66*10+D66</f>
+        <f t="shared" si="2"/>
         <v>20250014</v>
       </c>
       <c r="B66" s="13">
@@ -3853,7 +3883,7 @@
     </row>
     <row r="67" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A67" s="5">
-        <f>C67*10+D67</f>
+        <f t="shared" si="2"/>
         <v>20250015</v>
       </c>
       <c r="B67" s="13">
@@ -3882,6 +3912,166 @@
       </c>
       <c r="J67" s="17"/>
       <c r="K67" s="17"/>
+    </row>
+    <row r="68" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A68" s="5">
+        <f>C68*10+D68</f>
+        <v>20230011</v>
+      </c>
+      <c r="B68" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C68" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D68" s="33">
+        <v>1</v>
+      </c>
+      <c r="E68" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F68" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G68" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H68" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I68" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="J68" s="17"/>
+      <c r="K68" s="17"/>
+    </row>
+    <row r="69" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A69" s="5">
+        <f>C69*10+D69</f>
+        <v>20230012</v>
+      </c>
+      <c r="B69" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C69" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D69" s="33">
+        <v>2</v>
+      </c>
+      <c r="E69" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="F69" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G69" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="H69" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I69" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="J69" s="17"/>
+      <c r="K69" s="17"/>
+    </row>
+    <row r="70" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A70" s="5">
+        <f>C70*10+D70</f>
+        <v>20230013</v>
+      </c>
+      <c r="B70" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C70" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D70" s="33">
+        <v>3</v>
+      </c>
+      <c r="E70" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F70" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G70" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="H70" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I70" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="J70" s="17"/>
+      <c r="K70" s="17"/>
+    </row>
+    <row r="71" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A71" s="5">
+        <f>C71*10+D71</f>
+        <v>20230014</v>
+      </c>
+      <c r="B71" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C71" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D71" s="33">
+        <v>4</v>
+      </c>
+      <c r="E71" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="F71" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G71" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H71" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I71" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="J71" s="17"/>
+      <c r="K71" s="17"/>
+    </row>
+    <row r="72" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A72" s="5">
+        <f>C72*10+D72</f>
+        <v>20230015</v>
+      </c>
+      <c r="B72" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C72" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D72" s="33">
+        <v>5</v>
+      </c>
+      <c r="E72" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F72" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G72" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="H72" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I72" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="J72" s="17"/>
+      <c r="K72" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="148">
   <si>
     <t>id</t>
   </si>
@@ -475,6 +475,54 @@
   </si>
   <si>
     <t>9_1_7_1_3_6_1_3_5_3_2_9_1_2_1_7_5_3_1_9_8_6_8_6_2_5_2_7_2_3_2_3_7_2_9_6_9_3_2_2_4_1_1_4_5_8_9_8_6_1_3_4_4_4_5_7_8_3_2_1_8_2_1_6_3_4_7_5_5_2_3_4_1_7_3_2_7_3_6_5_9_4_5_3_5_5_8_2_7_2_4_3_8_6_6_4_1_4_3_1_3_5_2_3_7_6_1_1_5_5_1_2_7_3_8_2_7_3_3_3_6_4_3_4_8_1_6_4_8_3_5_1_6_4_1_3_5_6_4_6_3_3_6_6_8_7_2_2_4_2_8_9_3_3_6_3_9_5_9_8_2_4_4_1_7_8_1_2_6_1_3_5_5_8_6_3_1_6_4_2_6_5_2_2_6_5_1_9_7_3_5_6_9_9_6_4_8_1_2_7_9_7_8_3_5_5_6_7_5_7_2_3_7_3_4_5_7_1_6_2_2_7_5_5_8_4_8_1_2_2_4_1_9_2_5_8_8_5_1_9_4_3_8_1_4_6_1_2_3_8_2_5_5_1_1_6_4_1_6_9_1_3_5_9_4_8_2_1_3_8_1_2_3_2_8_5_5_4_4_5_3_7_4_4_6_5_9_5_7_8_3_2_2_4_7_2_6_4_4_6_1_8_3_2_6_6_4_7_7_9_6_3_3_9_4_5_1_3_4_3_1_1_5_2_3_1_2_6_1_3_7_8_3_7_7_5_9_2_2_4_1_4_5_2_6_4_6_4_8_1_9_4_6_5_4_7_3_1_9_8_6_5_7_2_3_8_2_2_7_5_3_6_2_9_3_1_4_6_3_2_1_1_5_4_2_5_7_7_3_5_9_2_2_8_2_8_2_7_6_6_2_7_5_7_6_7_2_2_1_3_6_4_9_2_4_6_8_5_2_6_6_8_2_2_1_1_5_8_7_5_1_4_1_6_8_3_6_6_5_6_1_6_1_9_5_6_6_5_2_3_2_4_2_4_2_8_9_1_5_6_2_1_7_7_3_3_3_4_2_7_5_5_1_4_9_4_8_5_6_2_4_9_9_6_2_3_6_7_7_8_1_6_5_4_1_6_2_7_2_3</t>
+  </si>
+  <si>
+    <t>5_3_2_6_1_1_1_6_6_2_5_1_9_9_9_9_8_2_2_7_1_1_4_1_2_6_1_7_4_1_5_3_3_2_2_2_4_8_1_5_2_1_6_3_1_2_8_1_6_6_9_5_5_2_1_5_5_3_1_6_1_3_5_1_1_4_4_1_2_2_2_6_5_3_10_10_8_10_2_8_8_1_4_3_4_1_4_5_6_9_7_7_8_3_7_4_4_4_4_1_7_1_2_1_7_6_9_1_3_6_1_2_2_2_3_8_1_5_2_2_9_5_7_8_3_6_6_8_5_8_1_6_7_7_2_1_1_3_5_5_5_7_7_1_1_5_1_1_8_6_10_1_3_2_5_5_6_9_3_9_5_2_2_2_2_7_4_7_2_7_3_1_4_5_9_9_9_1_4_2_6_5_7_1_5_9_3_5_10_2_7_2_6_9_10_5_8_3_2_3_8_6_4_4_8_8_4_9_9_8_6_8_8_10_2_5_5_4_1_6_4_8_3_1_5_5_8_6_3_5_5_5_5_1_4_8_6_1_6_4_1_1_6_4_3_10_1_2_7_7_3_9_8_4_4_6_5_3_3_7_6_6_9_4_6_3_3_5_10_8_3_3_1_1_1_6_3_1_1_4_5_2_4_4_10_9_2_6_2_3_9_5_1_9_5_3_4_2_2_6_6_8_1_3_2_5_4_6_10_1_4_5_6_1_8_8_4_5_7_6_7_4_8_8_2_6_6_6_2_4_8_8_1_1_10_3_3_3_1_3_7_7_7_9_6_2_5_6_2_1_1_8_5_5_4_1_5_3_4_7_2_10_2_1_9_2_7_2_2_2_1_1_6_5_5_6_3_6_4_7_2_8_2_8_4_8_5_4_5_5_6_6_6_7_7_7_1_2_3_3_1_2_2_3_4_9_2_4_8_5_6_8_1_2_4_4_2_2_4_4_9_5_5_1_5_3_6_2_6_2_1_4_8_1_10_7_2_4_3_6_1_7_8_2_10_6_7_1_6_3_1_7_6_8_8_7_9_9_9_5_4_4_2_6_4_7_7_7_10_8_4_3_3_9_6_8_6_1_2_5_1_3_4_3_9_8_3_2_8_5_5_4_5_5_3_6_6_3_1_1</t>
+  </si>
+  <si>
+    <t>1_501</t>
+  </si>
+  <si>
+    <t>7_7_6_1_5_6_1_7_3_3_2_3_7_5_1_6_4_4_6_2_1_1_1_1_6_4_7_3_6_1_2_5_4_4_6_9_4_7_1_4_5_3_7_2_5_5_2_3_5_4_4_1_3_6_2_5_6_6_6_4_4_1_1_1_1_2_2_9_1_1_1_3_3_9_8_2_7_7_2_2_8_8_3_2_8_8_8_3_3_8_3_5_7_7_8_1_7_4_6_1_1_2_6_1_5_8_6_1_7_8_1_5_5_4_4_1_1_3_2_4_2_10_8_6_4_2_9_4_5_6_2_8_4_3_1_5_1_6_6_2_9_9_5_2_9_2_3_5_4_6_3_3_1_4_4_1_1_7_4_3_3_2_8_8_2_3_1_5_3_1_4_6_1_6_2_7_8_3_1_7_7_5_1_1_1_1_1_5_5_2_6_7_7_9_1_3_1_1_4_4_2_1_3_9_1_3_3_1_3_2_7_6_1_4_4_9_8_5_1_5_6_1_5_5_2_4_1_1_6_8_9_8_4_4_4_1_1_9_8_2_1_4_7_4_1_6_6_2_2_3_10_5_2_2_3_5_6_6_2_9_5_5_10_10_3_3_2_4_6_4_7_2_1_1_1_8_2_5_2_2_9_4_4_9_3_1_6_1_1_1_3_2_2_4_4_4_1_1_1_3_7_9_6_4_1_2_3_5_5_9_9_2_5_5_5_8_3_3_3_1_6_5_7_10_1_7_6_6_3_5_3_4_2_3_6_2_2_4_1_2_3_8_4_2_9_9_5_6_6_1_6_4_2_1_6_1_3_7_1_5_1_4_10_7_2_2_2_6_4_8_4_1_7_6_1_8_8_4_1_4_4_2_2_8_1_1_1_2_1_6_4_4_3_7_3_7_6_1_9_1_10_3_3_9_9_3_2_6_5_4_2_7_3_1_1_4_8_3_2_2_1_7_1_9_7_2_6_5_4_6_8_7_1_5_4_2_9_6_1_4_3_3_9_3_5_3_4_3_5_3_9_2_9_3_1_9_2_9_8_5_8_2_5_5_4_4_1_8_8_3_4_3_3_5_1_3_1_1_2_9_9_8_9_6_8_10_5_9_4_8_1_3_3_3_3_2_1_2_2_1</t>
+  </si>
+  <si>
+    <t>1_502</t>
+  </si>
+  <si>
+    <t>10_2_2_5_3_9_9_1_3_4_4_9_5_3_5_1_6_7_3_5_3_7_5_5_4_4_1_8_8_8_6_6_4_5_5_5_5_2_4_2_5_2_4_2_2_3_4_1_1_8_1_1_1_2_2_4_4_7_3_6_7_1_4_6_7_7_3_2_4_9_7_6_6_4_1_6_1_2_9_8_3_9_2_2_2_5_2_2_9_7_9_6_9_1_1_7_1_1_7_6_5_8_4_4_9_4_5_9_6_6_1_5_8_1_5_10_5_6_3_5_1_6_1_9_2_1_2_2_3_3_9_6_8_3_4_8_3_3_4_4_4_2_4_6_5_3_9_3_2_5_7_8_2_2_1_8_1_3_4_10_5_1_8_8_3_3_6_4_3_2_10_7_3_5_1_3_1_1_2_5_6_2_4_2_5_8_3_3_3_5_7_7_2_7_7_7_10_2_8_5_1_1_1_1_4_7_2_2_5_2_4_5_4_6_4_1_1_1_9_10_6_8_10_4_6_6_3_9_7_5_1_1_4_3_1_8_7_5_7_5_1_1_2_2_9_4_2_1_1_6_7_7_6_10_2_7_6_9_1_1_6_8_1_2_5_5_10_8_9_4_8_8_3_6_7_7_4_7_5_5_8_7_5_5_3_3_5_5_6_6_9_6_9_2_5_4_4_4_2_8_4_5_2_2_3_9_5_6_10_8_2_6_9_4_4_6_7_7_2_3_3_3_4_1_7_5_2_4_8_8_5_3_7_7_1_1_3_6_6_8_7_3_7_4_4_7_3_5_5_8_5_2_5_3_1_4_2_8_8_3_8_2_8_1_4_2_6_7_4_6_6_8_2_3_6_6_7_7_3_1_8_1_1_1_4_3_10_1_8_8_3_9_7_7_3_5_9_3_2_5_5_10_8_10_1_5_5_1_1_10_1_4_3_7_7_5_7_3_9_7_3_2_3_1_1_3_6_4_3_7_9_3_4_9_4_3_4_6_7_8_1_7_2_7_7_6_7_5_2_5_5_3_8_2_7_1_2_5_1_6_5_6_3_8_5_3_1_3_8_1_1_1_5_7_1_1_2_1_7_1_6_1_1_5_9_2_1_3_3_3_1_7_2_1_1_6_5_2_4_2</t>
+  </si>
+  <si>
+    <t>1_503</t>
+  </si>
+  <si>
+    <t>5_8_7_8_7_8_4_2_2_3_6_7_3_5_2_2_6_2_6_1_6_7_6_6_6_1_3_8_8_8_2_3_3_5_4_8_8_7_4_5_6_6_4_5_3_8_4_9_4_8_4_4_4_1_3_9_3_3_2_1_1_6_5_2_1_4_5_5_5_6_9_8_4_9_1_9_7_6_4_9_3_5_6_7_2_2_1_1_9_9_5_5_6_7_5_5_8_6_9_2_1_1_6_1_2_1_1_1_2_6_3_1_6_1_1_3_7_8_1_1_5_7_7_4_6_4_10_3_10_4_2_8_8_4_2_7_7_7_7_2_1_3_3_7_5_3_3_3_6_8_9_3_3_1_6_7_2_3_4_1_6_3_9_6_4_9_4_2_3_1_1_10_3_4_9_10_10_10_6_1_1_1_9_3_5_3_3_1_2_6_3_4_3_8_1_4_1_7_6_6_6_5_2_6_6_4_4_8_8_7_4_5_7_5_7_5_5_3_4_8_7_9_8_6_9_4_3_7_2_2_4_8_3_4_3_3_8_3_2_2_4_4_2_3_3_2_7_3_5_6_2_4_9_8_1_6_1_4_1_2_2_3_1_4_2_2_9_1_2_1_9_1_1_1_1_1_9_7_1_4_5_3_5_1_6_7_1_1_1_4_7_8_1_4_4_7_4_4_1_2_4_2_6_1_8_1_5_5_5_9_1_1_7_5_2_2_3_3_4_8_3_5_3_4_2_3_3_1_3_1_2_3_4_4_4_2_9_8_4_2_10_6_4_2_6_5_8_1_1_6_2_1_1_10_1_2_1_1_3_7_8_2_5_8_1_3_2_4_8_8_3_3_9_1_3_1_5_7_4_7_9_9_1_6_2_2_8_9_1_2_2_4_4_5_4_1_4_8_3_2_8_1_3_3_6_5_5_2_1_1_8_6_7_1_10_2_1_1_1_2_2_5_5_2_2_10_4_4_2_3_4_4_9_6_2_3_2_2_2_8_4_1_6_10_4_5_1_9_3_5_2_1_1_1_3_4_1_4_7_5_9_7_3_7_3_4_2_6_5_2_8_1_1_1_7_7_5_5_1_5_5_3_5_4_2_8_6_5_7_5_5_4_6_6_3_1_9_7_4_5</t>
+  </si>
+  <si>
+    <t>1_504</t>
+  </si>
+  <si>
+    <t>1_2_6_8_4_3_2_1_3_5_8_8_1_1_2_10_2_3_2_4_4_2_4_1_4_2_9_6_5_4_4_4_7_2_2_2_2_6_3_5_2_2_9_5_1_6_7_3_1_1_3_9_9_9_2_4_4_1_1_4_7_7_8_4_7_7_6_5_3_1_1_6_8_7_7_4_4_1_3_3_9_1_1_1_3_3_3_3_3_2_6_4_3_2_7_5_9_5_5_3_3_3_7_4_7_9_2_4_4_6_10_8_5_6_1_8_3_2_6_2_5_5_1_8_4_8_2_2_2_5_6_7_4_2_7_1_1_1_4_8_1_2_9_3_3_1_2_4_1_2_7_9_2_3_4_2_2_2_1_2_8_6_2_2_4_2_3_1_3_1_3_3_1_7_1_2_6_2_1_6_10_10_1_7_7_6_4_7_2_4_5_5_7_4_5_1_8_2_9_1_4_8_1_4_9_4_10_7_6_5_4_7_6_4_6_6_4_9_9_7_3_7_9_8_8_8_1_2_5_8_8_8_2_1_2_6_2_7_2_6_6_8_2_7_4_4_2_4_2_2_9_9_2_2_1_2_4_2_8_4_3_1_1_1_1_6_4_1_4_4_4_4_3_5_3_3_8_1_9_1_3_6_3_8_2_7_1_6_8_2_5_6_7_4_4_1_2_2_2_2_3_10_8_5_3_4_9_9_1_7_1_8_4_1_3_6_9_5_6_1_7_3_5_2_1_1_5_3_6_1_7_1_9_1_3_9_8_7_3_1_1_2_6_7_2_2_1_1_5_10_6_2_3_6_1_2_6_3_2_4_1_1_3_6_6_5_3_2_2_5_5_4_5_8_10_2_3_6_2_9_3_1_1_2_4_2_7_1_7_7_4_2_8_1_5_9_8_7_6_3_9_6_3_3_5_6_6_2_1_9_2_8_3_1_6_3_8_3_2_9_1_1_5_2_4_7_6_2_1_4_1_1_5_2_6_6_9_9_3_6_7_4_5_1_1_5_2_7_9_3_2_2_5_4_4_8_4_5_4_4_3_1_2_1_2_1_2_4_4_7_8_1_2_7_1_2_5_5_7_7_6_6_1_2_4_2_6_9_1_1_3_2_4_5_9_8_2_5_9_6</t>
+  </si>
+  <si>
+    <t>1_505</t>
+  </si>
+  <si>
+    <t>4_2_6_7_4_2_2_7_4_6_6_6_6_5_9_1_3_6_1_2_2_2_4_4_1_4_7_2_2_1_1_2_4_2_6_6_3_1_1_8_6_3_1_1_6_6_5_5_2_6_2_4_1_4_2_3_6_2_3_1_2_2_6_1_3_7_4_3_3_1_6_9_6_4_3_7_1_1_1_7_5_9_4_2_1_3_3_7_8_8_3_9_2_6_8_2_1_4_3_2_4_3_3_6_4_8_3_1_1_1_7_7_7_1_4_7_8_9_2_2_8_5_2_4_4_6_5_5_5_7_9_6_1_4_2_3_2_2_3_2_4_2_1_9_4_8_9_3_4_5_3_5_5_4_2_3_5_2_4_2_2_4_8_7_1_3_2_3_4_4_4_2_7_3_2_6_8_1_8_8_9_6_7_8_1_8_4_4_2_7_9_4_2_2_8_1_1_2_6_6_6_7_3_1_1_8_8_5_8_2_5_1_1_1_8_8_5_2_6_6_8_2_8_1_1_5_7_5_6_6_5_7_5_2_1_2_2_3_5_7_7_4_2_7_1_2_6_2_2_6_8_8_6_1_1_4_2_2_6_1_3_1_3_4_3_1_2_5_8_6_6_8_1_4_1_9_5_8_8_1_1_2_1_3_4_2_3_2_5_3_2_9_3_1_7_6_2_4_7_7_2_5_4_8_3_4_3_3_3_3_3_3_3_5_2_5_3_4_6_7_7_3_5_5_5_2_6_5_4_6_6_1_5_5_9_9_1_9_2_1_2_4_5_6_6_3_7_5_9_8_2_7_2_5_9_3_7_1_2_7_5_6_3_2_2_2_4_7_8_4_4_1_3_3_6_8_2_2_7_9_7_8_4_4_1_1_4_5_6_5_7_4_5_6_4_2_1_4_9_9_3_4_5_7_9_2_5_4_9_1_3_1_2_9_4_4_2_2_9_8_8_8_1_1_1_3_8_8_9_1_5_3_5_4_7_7_4_2_1_2_2_8_3_9_9_4_5_1_3_1_3_4_4_6_2_1_2_8_1_4_5_4_3_2_5_4_3_4_7_6_1_3_9_7_7_3_5_5_2_1_1_2_2_6_4_2_2_3_3_5_4_2_9_2_2_4_1_8_8_6</t>
+  </si>
+  <si>
+    <t>1_506</t>
+  </si>
+  <si>
+    <t>1_8_1_2_2_4_4_1_1_2_1_1_4_1_2_1_8_6_2_1_2_4_1_1_2_1_8_8_2_4_6_2_2_2_1_4_1_4_1_2_1_4_1_2_2_6_6_6_1_1_8_1_1_1_2_1_1_6_6_6_8_1_2_6_1_4_2_1_4_1_6_1_1_6_2_6_2_6_4_4_6_8_1_6_2_1_1_1_1_4_1_2_4_4_1_1_1_1_2_2_2_1_1_2_1_2_4_2_2_4_6_4_4_1_2_1_1_1_2_4_2_2_4_8_6_8_6_2_4_6_1_2_2_4_4_4_2_1_1_2_2_8_8_6_2_6_6_6_2_2_2_8_6_2_6_4_1_4_4_2_4_1_2_2_1_1_2_1_2_8_2_4_2_2_4_1_8_2_1_6_4_4_1_8_8_6_1_2_2_6_6_6_8_2_2_8_1_6_2_2_6_4_1_6_4_1_2_4_2_1_6_2_2_6_2_1_1_1_1_1_2_4_1_8_8_8_1_4_4_1_1_6_2_2_4_1_8_6_6_1_1_1_4_2_8_4_2_6_4_2_2_1_1_1_2_4_4_1_1_6_4_8_1_1_4_2_8_1_1_2_1_1_6_6_4_1_1_2_4_8_1_6_6_8_6_4_4_6_2_1_1_6_4_1_4_6_1_4_1_1_1_1_2_1_6_6_4_1_1_2_2_2_1_2_6_1_1_2_1_1_4_4_8_1_1_4_4_2_1_4_1_1_6_1_1_8_6_2_4_6_1_1_1_4_4_4_1_1_2_1_6_8_2_8_1_8_8_1_2_8_2_8_1_1_6_2_1_1_4_4_2_4_2_4_6_2_6_6_1_8_1_4_1_1_1_4_2_1_1_8_6_4_6_6_1_2_4_8_4_4_6_4_4_1_2_1_2_1_1_6_4_2_1_2_1_1_8_6_8_4_8_1_4_2_1_8_2_1_8_6_1_2_8_8_4_6_6_8_8_1_1_8_1_4_4_4_4_4_6_2_4_1_1_1_1_1_1_8_2_2_6_4_2_4_4_1_2_4_2_1_2_6_6_1_1_1_2_1_4_6_8_4_6_6_4_2_4_6_2_1_4_1_6_2_1_2_1_8_8_1</t>
+  </si>
+  <si>
+    <t>1_507</t>
+  </si>
+  <si>
+    <t>1_1_3_3_3_5_1_1_3_3_3_3_5_7_1_7_1_7_5_5_3_1_7_3_3_1_1_5_3_1_5_1_3_1_1_1_1_1_1_1_7_3_1_5_1_1_1_1_1_1_1_7_5_7_1_7_3_3_7_1_1_1_1_7_1_1_1_7_3_3_3_1_3_5_5_3_5_7_7_1_3_1_5_1_7_5_5_1_7_3_1_3_7_1_3_7_1_1_7_1_3_7_1_3_1_1_5_1_7_7_7_7_1_1_5_7_5_5_1_3_3_5_1_3_7_3_5_5_5_5_5_7_7_1_3_1_3_1_1_1_1_3_1_3_3_7_3_1_3_7_3_7_7_5_1_1_1_1_3_1_3_1_5_5_5_5_1_7_7_1_3_3_3_5_1_7_7_1_3_1_3_1_7_7_1_7_3_3_5_5_1_1_1_1_3_7_1_1_1_5_3_5_5_3_1_3_7_3_5_5_5_5_7_5_7_1_1_5_3_7_3_3_1_7_7_3_3_1_7_1_5_3_3_5_5_5_7_5_3_3_5_5_5_1_1_1_7_5_3_3_1_1_5_5_1_3_3_3_1_1_1_1_3_1_7_3_5_1_3_5_5_5_1_1_1_3_5_5_5_3_3_7_1_3_5_5_1_1_1_5_3_1_3_1_5_1_5_5_3_1_5_5_7_7_3_7_3_3_3_1_3_3_5_1_3_3_5_1_1_5_7_3_5_5_1_1_7_5_5_7_1_1_5_1_7_1_3_1_1_1_1_3_5_7_1_3_3_5_3_7_5_3_7_3_3_1_1_3_1_3_5_7_7_7_1_1_1_7_3_3_1_3_3_7_3_3_7_1_5_5_1_3_5_3_3_5_5_5_5_1_7_5_1_7_7_1_5_1_3_5_5_5_3_1_3_5_3_1_7_3_1_1_7_3_3_3_3_7_7_5_5_1_7_1_1_5_5_5_5_5_1_5_5_3_1_3_1_5_1_1_3_5_5_5_1_7_3_7_5_7_1_1_1_3_3_1_3_3_5_5_5_1_1_1_1_5_1_3_3_5_5_1_7_1_1_1_7_7_1_1_1_3_1_3_5_5_1_5_1_1_5_3_3_1_3_5_1_1_1_5</t>
+  </si>
+  <si>
+    <t>1_508</t>
   </si>
 </sst>
 </file>
@@ -1785,7 +1833,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -3563,7 +3611,7 @@
     </row>
     <row r="57" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A57" s="5">
-        <f t="shared" ref="A57:A67" si="2">C57*10+D57</f>
+        <f t="shared" ref="A57:A72" si="2">C57*10+D57</f>
         <v>20180011</v>
       </c>
       <c r="B57" s="13">
@@ -3915,7 +3963,7 @@
     </row>
     <row r="68" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A68" s="5">
-        <f>C68*10+D68</f>
+        <f t="shared" si="2"/>
         <v>20230011</v>
       </c>
       <c r="B68" s="13">
@@ -3947,7 +3995,7 @@
     </row>
     <row r="69" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A69" s="5">
-        <f>C69*10+D69</f>
+        <f t="shared" si="2"/>
         <v>20230012</v>
       </c>
       <c r="B69" s="13">
@@ -3979,7 +4027,7 @@
     </row>
     <row r="70" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A70" s="5">
-        <f>C70*10+D70</f>
+        <f t="shared" si="2"/>
         <v>20230013</v>
       </c>
       <c r="B70" s="13">
@@ -4011,7 +4059,7 @@
     </row>
     <row r="71" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A71" s="5">
-        <f>C71*10+D71</f>
+        <f t="shared" si="2"/>
         <v>20230014</v>
       </c>
       <c r="B71" s="13">
@@ -4043,7 +4091,7 @@
     </row>
     <row r="72" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A72" s="5">
-        <f>C72*10+D72</f>
+        <f t="shared" si="2"/>
         <v>20230015</v>
       </c>
       <c r="B72" s="13">
@@ -4072,6 +4120,246 @@
       </c>
       <c r="J72" s="17"/>
       <c r="K72" s="17"/>
+    </row>
+    <row r="73" ht="16.5" spans="1:11">
+      <c r="A73" s="5">
+        <f t="shared" ref="A73:A80" si="3">C73*10+D73</f>
+        <v>20230016</v>
+      </c>
+      <c r="B73" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C73" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D73" s="33">
+        <v>6</v>
+      </c>
+      <c r="E73" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F73" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G73" t="s">
+        <v>132</v>
+      </c>
+      <c r="H73" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="I73" s="16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="74" ht="16.5" spans="1:11">
+      <c r="A74" s="5">
+        <f t="shared" si="3"/>
+        <v>20230017</v>
+      </c>
+      <c r="B74" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C74" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D74" s="33">
+        <v>7</v>
+      </c>
+      <c r="E74" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F74" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G74" t="s">
+        <v>134</v>
+      </c>
+      <c r="H74" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="I74" s="16" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="75" ht="16.5" spans="1:11">
+      <c r="A75" s="5">
+        <f t="shared" si="3"/>
+        <v>20230018</v>
+      </c>
+      <c r="B75" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C75" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D75" s="33">
+        <v>8</v>
+      </c>
+      <c r="E75" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F75" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G75" t="s">
+        <v>136</v>
+      </c>
+      <c r="H75" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="I75" s="16" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="76" ht="16.5" spans="1:11">
+      <c r="A76" s="5">
+        <f t="shared" si="3"/>
+        <v>20230019</v>
+      </c>
+      <c r="B76" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C76" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D76" s="33">
+        <v>9</v>
+      </c>
+      <c r="E76" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F76" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G76" t="s">
+        <v>138</v>
+      </c>
+      <c r="H76" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="I76" s="16" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="77" ht="16.5" spans="1:11">
+      <c r="A77" s="5">
+        <f t="shared" si="3"/>
+        <v>20230020</v>
+      </c>
+      <c r="B77" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C77" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D77" s="33">
+        <v>10</v>
+      </c>
+      <c r="E77" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F77" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G77" t="s">
+        <v>140</v>
+      </c>
+      <c r="H77" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="I77" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="78" ht="16.5" spans="1:11">
+      <c r="A78" s="5">
+        <f t="shared" si="3"/>
+        <v>20230021</v>
+      </c>
+      <c r="B78" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C78" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D78" s="33">
+        <v>11</v>
+      </c>
+      <c r="E78" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F78" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G78" t="s">
+        <v>142</v>
+      </c>
+      <c r="H78" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="I78" s="16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="79" ht="16.5" spans="1:11">
+      <c r="A79" s="5">
+        <f t="shared" si="3"/>
+        <v>20230022</v>
+      </c>
+      <c r="B79" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C79" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D79" s="33">
+        <v>12</v>
+      </c>
+      <c r="E79" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F79" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G79" t="s">
+        <v>144</v>
+      </c>
+      <c r="H79" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="I79" s="16" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="80" ht="16.5" spans="1:11">
+      <c r="A80" s="5">
+        <f t="shared" si="3"/>
+        <v>20230023</v>
+      </c>
+      <c r="B80" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C80" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D80" s="33">
+        <v>13</v>
+      </c>
+      <c r="E80" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F80" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G80" t="s">
+        <v>146</v>
+      </c>
+      <c r="H80" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="I80" s="16" t="s">
+        <v>125</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="140">
   <si>
     <t>id</t>
   </si>
@@ -480,49 +480,25 @@
     <t>5_3_2_6_1_1_1_6_6_2_5_1_9_9_9_9_8_2_2_7_1_1_4_1_2_6_1_7_4_1_5_3_3_2_2_2_4_8_1_5_2_1_6_3_1_2_8_1_6_6_9_5_5_2_1_5_5_3_1_6_1_3_5_1_1_4_4_1_2_2_2_6_5_3_10_10_8_10_2_8_8_1_4_3_4_1_4_5_6_9_7_7_8_3_7_4_4_4_4_1_7_1_2_1_7_6_9_1_3_6_1_2_2_2_3_8_1_5_2_2_9_5_7_8_3_6_6_8_5_8_1_6_7_7_2_1_1_3_5_5_5_7_7_1_1_5_1_1_8_6_10_1_3_2_5_5_6_9_3_9_5_2_2_2_2_7_4_7_2_7_3_1_4_5_9_9_9_1_4_2_6_5_7_1_5_9_3_5_10_2_7_2_6_9_10_5_8_3_2_3_8_6_4_4_8_8_4_9_9_8_6_8_8_10_2_5_5_4_1_6_4_8_3_1_5_5_8_6_3_5_5_5_5_1_4_8_6_1_6_4_1_1_6_4_3_10_1_2_7_7_3_9_8_4_4_6_5_3_3_7_6_6_9_4_6_3_3_5_10_8_3_3_1_1_1_6_3_1_1_4_5_2_4_4_10_9_2_6_2_3_9_5_1_9_5_3_4_2_2_6_6_8_1_3_2_5_4_6_10_1_4_5_6_1_8_8_4_5_7_6_7_4_8_8_2_6_6_6_2_4_8_8_1_1_10_3_3_3_1_3_7_7_7_9_6_2_5_6_2_1_1_8_5_5_4_1_5_3_4_7_2_10_2_1_9_2_7_2_2_2_1_1_6_5_5_6_3_6_4_7_2_8_2_8_4_8_5_4_5_5_6_6_6_7_7_7_1_2_3_3_1_2_2_3_4_9_2_4_8_5_6_8_1_2_4_4_2_2_4_4_9_5_5_1_5_3_6_2_6_2_1_4_8_1_10_7_2_4_3_6_1_7_8_2_10_6_7_1_6_3_1_7_6_8_8_7_9_9_9_5_4_4_2_6_4_7_7_7_10_8_4_3_3_9_6_8_6_1_2_5_1_3_4_3_9_8_3_2_8_5_5_4_5_5_3_6_6_3_1_1</t>
   </si>
   <si>
-    <t>1_501</t>
-  </si>
-  <si>
     <t>7_7_6_1_5_6_1_7_3_3_2_3_7_5_1_6_4_4_6_2_1_1_1_1_6_4_7_3_6_1_2_5_4_4_6_9_4_7_1_4_5_3_7_2_5_5_2_3_5_4_4_1_3_6_2_5_6_6_6_4_4_1_1_1_1_2_2_9_1_1_1_3_3_9_8_2_7_7_2_2_8_8_3_2_8_8_8_3_3_8_3_5_7_7_8_1_7_4_6_1_1_2_6_1_5_8_6_1_7_8_1_5_5_4_4_1_1_3_2_4_2_10_8_6_4_2_9_4_5_6_2_8_4_3_1_5_1_6_6_2_9_9_5_2_9_2_3_5_4_6_3_3_1_4_4_1_1_7_4_3_3_2_8_8_2_3_1_5_3_1_4_6_1_6_2_7_8_3_1_7_7_5_1_1_1_1_1_5_5_2_6_7_7_9_1_3_1_1_4_4_2_1_3_9_1_3_3_1_3_2_7_6_1_4_4_9_8_5_1_5_6_1_5_5_2_4_1_1_6_8_9_8_4_4_4_1_1_9_8_2_1_4_7_4_1_6_6_2_2_3_10_5_2_2_3_5_6_6_2_9_5_5_10_10_3_3_2_4_6_4_7_2_1_1_1_8_2_5_2_2_9_4_4_9_3_1_6_1_1_1_3_2_2_4_4_4_1_1_1_3_7_9_6_4_1_2_3_5_5_9_9_2_5_5_5_8_3_3_3_1_6_5_7_10_1_7_6_6_3_5_3_4_2_3_6_2_2_4_1_2_3_8_4_2_9_9_5_6_6_1_6_4_2_1_6_1_3_7_1_5_1_4_10_7_2_2_2_6_4_8_4_1_7_6_1_8_8_4_1_4_4_2_2_8_1_1_1_2_1_6_4_4_3_7_3_7_6_1_9_1_10_3_3_9_9_3_2_6_5_4_2_7_3_1_1_4_8_3_2_2_1_7_1_9_7_2_6_5_4_6_8_7_1_5_4_2_9_6_1_4_3_3_9_3_5_3_4_3_5_3_9_2_9_3_1_9_2_9_8_5_8_2_5_5_4_4_1_8_8_3_4_3_3_5_1_3_1_1_2_9_9_8_9_6_8_10_5_9_4_8_1_3_3_3_3_2_1_2_2_1</t>
   </si>
   <si>
-    <t>1_502</t>
-  </si>
-  <si>
     <t>10_2_2_5_3_9_9_1_3_4_4_9_5_3_5_1_6_7_3_5_3_7_5_5_4_4_1_8_8_8_6_6_4_5_5_5_5_2_4_2_5_2_4_2_2_3_4_1_1_8_1_1_1_2_2_4_4_7_3_6_7_1_4_6_7_7_3_2_4_9_7_6_6_4_1_6_1_2_9_8_3_9_2_2_2_5_2_2_9_7_9_6_9_1_1_7_1_1_7_6_5_8_4_4_9_4_5_9_6_6_1_5_8_1_5_10_5_6_3_5_1_6_1_9_2_1_2_2_3_3_9_6_8_3_4_8_3_3_4_4_4_2_4_6_5_3_9_3_2_5_7_8_2_2_1_8_1_3_4_10_5_1_8_8_3_3_6_4_3_2_10_7_3_5_1_3_1_1_2_5_6_2_4_2_5_8_3_3_3_5_7_7_2_7_7_7_10_2_8_5_1_1_1_1_4_7_2_2_5_2_4_5_4_6_4_1_1_1_9_10_6_8_10_4_6_6_3_9_7_5_1_1_4_3_1_8_7_5_7_5_1_1_2_2_9_4_2_1_1_6_7_7_6_10_2_7_6_9_1_1_6_8_1_2_5_5_10_8_9_4_8_8_3_6_7_7_4_7_5_5_8_7_5_5_3_3_5_5_6_6_9_6_9_2_5_4_4_4_2_8_4_5_2_2_3_9_5_6_10_8_2_6_9_4_4_6_7_7_2_3_3_3_4_1_7_5_2_4_8_8_5_3_7_7_1_1_3_6_6_8_7_3_7_4_4_7_3_5_5_8_5_2_5_3_1_4_2_8_8_3_8_2_8_1_4_2_6_7_4_6_6_8_2_3_6_6_7_7_3_1_8_1_1_1_4_3_10_1_8_8_3_9_7_7_3_5_9_3_2_5_5_10_8_10_1_5_5_1_1_10_1_4_3_7_7_5_7_3_9_7_3_2_3_1_1_3_6_4_3_7_9_3_4_9_4_3_4_6_7_8_1_7_2_7_7_6_7_5_2_5_5_3_8_2_7_1_2_5_1_6_5_6_3_8_5_3_1_3_8_1_1_1_5_7_1_1_2_1_7_1_6_1_1_5_9_2_1_3_3_3_1_7_2_1_1_6_5_2_4_2</t>
   </si>
   <si>
-    <t>1_503</t>
-  </si>
-  <si>
     <t>5_8_7_8_7_8_4_2_2_3_6_7_3_5_2_2_6_2_6_1_6_7_6_6_6_1_3_8_8_8_2_3_3_5_4_8_8_7_4_5_6_6_4_5_3_8_4_9_4_8_4_4_4_1_3_9_3_3_2_1_1_6_5_2_1_4_5_5_5_6_9_8_4_9_1_9_7_6_4_9_3_5_6_7_2_2_1_1_9_9_5_5_6_7_5_5_8_6_9_2_1_1_6_1_2_1_1_1_2_6_3_1_6_1_1_3_7_8_1_1_5_7_7_4_6_4_10_3_10_4_2_8_8_4_2_7_7_7_7_2_1_3_3_7_5_3_3_3_6_8_9_3_3_1_6_7_2_3_4_1_6_3_9_6_4_9_4_2_3_1_1_10_3_4_9_10_10_10_6_1_1_1_9_3_5_3_3_1_2_6_3_4_3_8_1_4_1_7_6_6_6_5_2_6_6_4_4_8_8_7_4_5_7_5_7_5_5_3_4_8_7_9_8_6_9_4_3_7_2_2_4_8_3_4_3_3_8_3_2_2_4_4_2_3_3_2_7_3_5_6_2_4_9_8_1_6_1_4_1_2_2_3_1_4_2_2_9_1_2_1_9_1_1_1_1_1_9_7_1_4_5_3_5_1_6_7_1_1_1_4_7_8_1_4_4_7_4_4_1_2_4_2_6_1_8_1_5_5_5_9_1_1_7_5_2_2_3_3_4_8_3_5_3_4_2_3_3_1_3_1_2_3_4_4_4_2_9_8_4_2_10_6_4_2_6_5_8_1_1_6_2_1_1_10_1_2_1_1_3_7_8_2_5_8_1_3_2_4_8_8_3_3_9_1_3_1_5_7_4_7_9_9_1_6_2_2_8_9_1_2_2_4_4_5_4_1_4_8_3_2_8_1_3_3_6_5_5_2_1_1_8_6_7_1_10_2_1_1_1_2_2_5_5_2_2_10_4_4_2_3_4_4_9_6_2_3_2_2_2_8_4_1_6_10_4_5_1_9_3_5_2_1_1_1_3_4_1_4_7_5_9_7_3_7_3_4_2_6_5_2_8_1_1_1_7_7_5_5_1_5_5_3_5_4_2_8_6_5_7_5_5_4_6_6_3_1_9_7_4_5</t>
   </si>
   <si>
-    <t>1_504</t>
-  </si>
-  <si>
     <t>1_2_6_8_4_3_2_1_3_5_8_8_1_1_2_10_2_3_2_4_4_2_4_1_4_2_9_6_5_4_4_4_7_2_2_2_2_6_3_5_2_2_9_5_1_6_7_3_1_1_3_9_9_9_2_4_4_1_1_4_7_7_8_4_7_7_6_5_3_1_1_6_8_7_7_4_4_1_3_3_9_1_1_1_3_3_3_3_3_2_6_4_3_2_7_5_9_5_5_3_3_3_7_4_7_9_2_4_4_6_10_8_5_6_1_8_3_2_6_2_5_5_1_8_4_8_2_2_2_5_6_7_4_2_7_1_1_1_4_8_1_2_9_3_3_1_2_4_1_2_7_9_2_3_4_2_2_2_1_2_8_6_2_2_4_2_3_1_3_1_3_3_1_7_1_2_6_2_1_6_10_10_1_7_7_6_4_7_2_4_5_5_7_4_5_1_8_2_9_1_4_8_1_4_9_4_10_7_6_5_4_7_6_4_6_6_4_9_9_7_3_7_9_8_8_8_1_2_5_8_8_8_2_1_2_6_2_7_2_6_6_8_2_7_4_4_2_4_2_2_9_9_2_2_1_2_4_2_8_4_3_1_1_1_1_6_4_1_4_4_4_4_3_5_3_3_8_1_9_1_3_6_3_8_2_7_1_6_8_2_5_6_7_4_4_1_2_2_2_2_3_10_8_5_3_4_9_9_1_7_1_8_4_1_3_6_9_5_6_1_7_3_5_2_1_1_5_3_6_1_7_1_9_1_3_9_8_7_3_1_1_2_6_7_2_2_1_1_5_10_6_2_3_6_1_2_6_3_2_4_1_1_3_6_6_5_3_2_2_5_5_4_5_8_10_2_3_6_2_9_3_1_1_2_4_2_7_1_7_7_4_2_8_1_5_9_8_7_6_3_9_6_3_3_5_6_6_2_1_9_2_8_3_1_6_3_8_3_2_9_1_1_5_2_4_7_6_2_1_4_1_1_5_2_6_6_9_9_3_6_7_4_5_1_1_5_2_7_9_3_2_2_5_4_4_8_4_5_4_4_3_1_2_1_2_1_2_4_4_7_8_1_2_7_1_2_5_5_7_7_6_6_1_2_4_2_6_9_1_1_3_2_4_5_9_8_2_5_9_6</t>
   </si>
   <si>
-    <t>1_505</t>
-  </si>
-  <si>
     <t>4_2_6_7_4_2_2_7_4_6_6_6_6_5_9_1_3_6_1_2_2_2_4_4_1_4_7_2_2_1_1_2_4_2_6_6_3_1_1_8_6_3_1_1_6_6_5_5_2_6_2_4_1_4_2_3_6_2_3_1_2_2_6_1_3_7_4_3_3_1_6_9_6_4_3_7_1_1_1_7_5_9_4_2_1_3_3_7_8_8_3_9_2_6_8_2_1_4_3_2_4_3_3_6_4_8_3_1_1_1_7_7_7_1_4_7_8_9_2_2_8_5_2_4_4_6_5_5_5_7_9_6_1_4_2_3_2_2_3_2_4_2_1_9_4_8_9_3_4_5_3_5_5_4_2_3_5_2_4_2_2_4_8_7_1_3_2_3_4_4_4_2_7_3_2_6_8_1_8_8_9_6_7_8_1_8_4_4_2_7_9_4_2_2_8_1_1_2_6_6_6_7_3_1_1_8_8_5_8_2_5_1_1_1_8_8_5_2_6_6_8_2_8_1_1_5_7_5_6_6_5_7_5_2_1_2_2_3_5_7_7_4_2_7_1_2_6_2_2_6_8_8_6_1_1_4_2_2_6_1_3_1_3_4_3_1_2_5_8_6_6_8_1_4_1_9_5_8_8_1_1_2_1_3_4_2_3_2_5_3_2_9_3_1_7_6_2_4_7_7_2_5_4_8_3_4_3_3_3_3_3_3_3_5_2_5_3_4_6_7_7_3_5_5_5_2_6_5_4_6_6_1_5_5_9_9_1_9_2_1_2_4_5_6_6_3_7_5_9_8_2_7_2_5_9_3_7_1_2_7_5_6_3_2_2_2_4_7_8_4_4_1_3_3_6_8_2_2_7_9_7_8_4_4_1_1_4_5_6_5_7_4_5_6_4_2_1_4_9_9_3_4_5_7_9_2_5_4_9_1_3_1_2_9_4_4_2_2_9_8_8_8_1_1_1_3_8_8_9_1_5_3_5_4_7_7_4_2_1_2_2_8_3_9_9_4_5_1_3_1_3_4_4_6_2_1_2_8_1_4_5_4_3_2_5_4_3_4_7_6_1_3_9_7_7_3_5_5_2_1_1_2_2_6_4_2_2_3_3_5_4_2_9_2_2_4_1_8_8_6</t>
   </si>
   <si>
-    <t>1_506</t>
-  </si>
-  <si>
     <t>1_8_1_2_2_4_4_1_1_2_1_1_4_1_2_1_8_6_2_1_2_4_1_1_2_1_8_8_2_4_6_2_2_2_1_4_1_4_1_2_1_4_1_2_2_6_6_6_1_1_8_1_1_1_2_1_1_6_6_6_8_1_2_6_1_4_2_1_4_1_6_1_1_6_2_6_2_6_4_4_6_8_1_6_2_1_1_1_1_4_1_2_4_4_1_1_1_1_2_2_2_1_1_2_1_2_4_2_2_4_6_4_4_1_2_1_1_1_2_4_2_2_4_8_6_8_6_2_4_6_1_2_2_4_4_4_2_1_1_2_2_8_8_6_2_6_6_6_2_2_2_8_6_2_6_4_1_4_4_2_4_1_2_2_1_1_2_1_2_8_2_4_2_2_4_1_8_2_1_6_4_4_1_8_8_6_1_2_2_6_6_6_8_2_2_8_1_6_2_2_6_4_1_6_4_1_2_4_2_1_6_2_2_6_2_1_1_1_1_1_2_4_1_8_8_8_1_4_4_1_1_6_2_2_4_1_8_6_6_1_1_1_4_2_8_4_2_6_4_2_2_1_1_1_2_4_4_1_1_6_4_8_1_1_4_2_8_1_1_2_1_1_6_6_4_1_1_2_4_8_1_6_6_8_6_4_4_6_2_1_1_6_4_1_4_6_1_4_1_1_1_1_2_1_6_6_4_1_1_2_2_2_1_2_6_1_1_2_1_1_4_4_8_1_1_4_4_2_1_4_1_1_6_1_1_8_6_2_4_6_1_1_1_4_4_4_1_1_2_1_6_8_2_8_1_8_8_1_2_8_2_8_1_1_6_2_1_1_4_4_2_4_2_4_6_2_6_6_1_8_1_4_1_1_1_4_2_1_1_8_6_4_6_6_1_2_4_8_4_4_6_4_4_1_2_1_2_1_1_6_4_2_1_2_1_1_8_6_8_4_8_1_4_2_1_8_2_1_8_6_1_2_8_8_4_6_6_8_8_1_1_8_1_4_4_4_4_4_6_2_4_1_1_1_1_1_1_8_2_2_6_4_2_4_4_1_2_4_2_1_2_6_6_1_1_1_2_1_4_6_8_4_6_6_4_2_4_6_2_1_4_1_6_2_1_2_1_8_8_1</t>
   </si>
   <si>
-    <t>1_507</t>
-  </si>
-  <si>
     <t>1_1_3_3_3_5_1_1_3_3_3_3_5_7_1_7_1_7_5_5_3_1_7_3_3_1_1_5_3_1_5_1_3_1_1_1_1_1_1_1_7_3_1_5_1_1_1_1_1_1_1_7_5_7_1_7_3_3_7_1_1_1_1_7_1_1_1_7_3_3_3_1_3_5_5_3_5_7_7_1_3_1_5_1_7_5_5_1_7_3_1_3_7_1_3_7_1_1_7_1_3_7_1_3_1_1_5_1_7_7_7_7_1_1_5_7_5_5_1_3_3_5_1_3_7_3_5_5_5_5_5_7_7_1_3_1_3_1_1_1_1_3_1_3_3_7_3_1_3_7_3_7_7_5_1_1_1_1_3_1_3_1_5_5_5_5_1_7_7_1_3_3_3_5_1_7_7_1_3_1_3_1_7_7_1_7_3_3_5_5_1_1_1_1_3_7_1_1_1_5_3_5_5_3_1_3_7_3_5_5_5_5_7_5_7_1_1_5_3_7_3_3_1_7_7_3_3_1_7_1_5_3_3_5_5_5_7_5_3_3_5_5_5_1_1_1_7_5_3_3_1_1_5_5_1_3_3_3_1_1_1_1_3_1_7_3_5_1_3_5_5_5_1_1_1_3_5_5_5_3_3_7_1_3_5_5_1_1_1_5_3_1_3_1_5_1_5_5_3_1_5_5_7_7_3_7_3_3_3_1_3_3_5_1_3_3_5_1_1_5_7_3_5_5_1_1_7_5_5_7_1_1_5_1_7_1_3_1_1_1_1_3_5_7_1_3_3_5_3_7_5_3_7_3_3_1_1_3_1_3_5_7_7_7_1_1_1_7_3_3_1_3_3_7_3_3_7_1_5_5_1_3_5_3_3_5_5_5_5_1_7_5_1_7_7_1_5_1_3_5_5_5_3_1_3_5_3_1_7_3_1_1_7_3_3_3_3_7_7_5_5_1_7_1_1_5_5_5_5_5_1_5_5_3_1_3_1_5_1_1_3_5_5_5_1_7_3_7_5_7_1_1_1_3_3_1_3_3_5_5_5_1_1_1_1_5_1_3_3_5_5_1_7_1_1_1_7_7_1_1_1_3_1_3_5_5_1_5_1_1_5_3_3_1_3_5_1_1_1_5</t>
-  </si>
-  <si>
-    <t>1_508</t>
   </si>
 </sst>
 </file>
@@ -4145,7 +4121,7 @@
         <v>132</v>
       </c>
       <c r="H73" s="16" t="s">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="I73" s="16" t="s">
         <v>123</v>
@@ -4172,10 +4148,10 @@
         <v>20</v>
       </c>
       <c r="G74" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="I74" s="16" t="s">
         <v>125</v>
@@ -4202,10 +4178,10 @@
         <v>20</v>
       </c>
       <c r="G75" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H75" s="16" t="s">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="I75" s="16" t="s">
         <v>127</v>
@@ -4232,10 +4208,10 @@
         <v>20</v>
       </c>
       <c r="G76" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H76" s="16" t="s">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="I76" s="16" t="s">
         <v>129</v>
@@ -4262,10 +4238,10 @@
         <v>20</v>
       </c>
       <c r="G77" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H77" s="16" t="s">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="I77" s="16" t="s">
         <v>131</v>
@@ -4292,10 +4268,10 @@
         <v>20</v>
       </c>
       <c r="G78" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H78" s="16" t="s">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="I78" s="16" t="s">
         <v>123</v>
@@ -4322,10 +4298,10 @@
         <v>20</v>
       </c>
       <c r="G79" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="H79" s="16" t="s">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="I79" s="16" t="s">
         <v>125</v>
@@ -4352,10 +4328,10 @@
         <v>20</v>
       </c>
       <c r="G80" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="H80" s="16" t="s">
-        <v>147</v>
+        <v>20</v>
       </c>
       <c r="I80" s="16" t="s">
         <v>125</v>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="147">
   <si>
     <t>id</t>
   </si>
@@ -499,6 +499,27 @@
   </si>
   <si>
     <t>1_1_3_3_3_5_1_1_3_3_3_3_5_7_1_7_1_7_5_5_3_1_7_3_3_1_1_5_3_1_5_1_3_1_1_1_1_1_1_1_7_3_1_5_1_1_1_1_1_1_1_7_5_7_1_7_3_3_7_1_1_1_1_7_1_1_1_7_3_3_3_1_3_5_5_3_5_7_7_1_3_1_5_1_7_5_5_1_7_3_1_3_7_1_3_7_1_1_7_1_3_7_1_3_1_1_5_1_7_7_7_7_1_1_5_7_5_5_1_3_3_5_1_3_7_3_5_5_5_5_5_7_7_1_3_1_3_1_1_1_1_3_1_3_3_7_3_1_3_7_3_7_7_5_1_1_1_1_3_1_3_1_5_5_5_5_1_7_7_1_3_3_3_5_1_7_7_1_3_1_3_1_7_7_1_7_3_3_5_5_1_1_1_1_3_7_1_1_1_5_3_5_5_3_1_3_7_3_5_5_5_5_7_5_7_1_1_5_3_7_3_3_1_7_7_3_3_1_7_1_5_3_3_5_5_5_7_5_3_3_5_5_5_1_1_1_7_5_3_3_1_1_5_5_1_3_3_3_1_1_1_1_3_1_7_3_5_1_3_5_5_5_1_1_1_3_5_5_5_3_3_7_1_3_5_5_1_1_1_5_3_1_3_1_5_1_5_5_3_1_5_5_7_7_3_7_3_3_3_1_3_3_5_1_3_3_5_1_1_5_7_3_5_5_1_1_7_5_5_7_1_1_5_1_7_1_3_1_1_1_1_3_5_7_1_3_3_5_3_7_5_3_7_3_3_1_1_3_1_3_5_7_7_7_1_1_1_7_3_3_1_3_3_7_3_3_7_1_5_5_1_3_5_3_3_5_5_5_5_1_7_5_1_7_7_1_5_1_3_5_5_5_3_1_3_5_3_1_7_3_1_1_7_3_3_3_3_7_7_5_5_1_7_1_1_5_5_5_5_5_1_5_5_3_1_3_1_5_1_1_3_5_5_5_1_7_3_7_5_7_1_1_1_3_3_1_3_3_5_5_5_1_1_1_1_5_1_3_3_5_5_1_7_1_1_1_7_7_1_1_1_3_1_3_5_5_1_5_1_1_5_3_3_1_3_5_1_1_1_5</t>
+  </si>
+  <si>
+    <t>4_4_4</t>
+  </si>
+  <si>
+    <t>3_3_2_4_2_4_5_1_5_1_4_6_3_6_2_1_4_1_1_3_2_3_2_2_3_5_2_1_4_4_2_2_2_3_3_3_6_3_2_6_2_5_4_3_1_3_4_4_4_1_3_4_4_3_1_3_3_1_6_3_2_1_4_2_2_3_6_1_1_5_2_2_1_1_1_1_4_2_2_4_6_1_1_1_3_2_2_3_5_3_3_5_2_3_2_5_1_4_4_4_2_3_4_3_1_5_2_1_1_3_2_2_2_4_4_3_5_5_3_5_1_2_3_2_2_2_4_5_2_1_6_2_2_2_5_1_1_1_4_3_3_1_5_5_4_3_2_3_2_1_2_2_4_2_6_6_3_3_2_1_4_1_5_5_5_4_2_3_3_3_3_1_5_5_2_3_2_2_5_5_3_4_1_1_2_2_2_4_4_3_2_1_3_3_1_3_5_4_5_2_5_5_1_1_1_4_2_2_6_4_2_2_3_1_2_1_4_5_1_2_2_2_2_1_5_5_5_5_2_1_3_3_1_4_4_5_1_5_5_3_1_2_1_3_4_4_2_5_1_5_5_3_5_2_2_4_4_1_2_2_2_1_2_2_3_2_1_2_3_4_6_5_5_3_5_1_2_2_2_4_1_4_2_2_4_3_3_3_1_3_3_6_1_3_3_2_4_3_1_5_1_2_2_3_2_2_3_1_4_4_3_1_5_4_4_2_3_1_2_3_4_4_2_2_1_4_4_3_1_2_2_1_1_1_4_3_2_2_2_2_1_1_1_2_2_1_4_4_2_2_2_2_3_1_2_2_2_2_1_2_2_2_3_3_4_1_1_1_6_6_1_1_1_4_1_3_1_4_2_6_4_2_6_3_4_4_2_4_3_2_2_4_6_2_2_5_4_4_3_1_3_1_1_4_2_3_1_2_2_1_5_6_3_2_2_2_4_1_3_2_1_1_1_2_1_3_2_2_5_4_4_3_3_4_1_5_3_2_1_5_1_6_3_3_2_3_1_3_3_4_1_1_2_6_1_2_2_2_4_4_6_2_6_4_2_3_3_1_1_3_3_1_6_5_3_2_6_4_4_1_2_2_2_5_3_4_2_4_1_2_5_2_2_5_5_5_4_4_1_3</t>
+  </si>
+  <si>
+    <t>3_2_3_2_1_6_6_4_3_7_6_2_5_3_1_6_3_4_3_1_1_7_4_3_4_1_5_3_1_2_4_1_2_1_3_4_2_6_3_2_4_1_2_1_2_7_7_5_1_5_2_4_4_3_5_1_6_6_3_2_2_4_2_6_2_1_1_3_4_1_2_4_4_1_5_1_1_1_2_1_4_4_3_2_4_3_3_3_1_1_6_3_1_4_1_1_6_3_2_2_3_4_1_2_7_3_3_6_6_3_1_5_3_4_1_3_6_3_3_3_2_3_5_4_3_5_7_5_4_1_2_1_3_3_3_2_2_6_4_1_5_7_3_6_5_2_2_4_2_4_3_1_1_6_2_1_3_6_6_1_1_3_1_1_1_6_7_1_3_3_3_6_3_2_1_5_7_6_1_1_2_3_4_6_2_1_3_3_4_2_1_2_3_2_2_2_2_4_1_2_1_7_1_5_3_2_4_3_2_1_2_3_3_1_6_3_1_6_3_3_1_1_5_6_4_4_3_4_1_3_3_7_3_2_1_4_3_2_2_2_1_1_6_6_1_2_2_6_2_2_6_1_4_3_7_1_5_4_4_4_3_1_3_2_7_6_5_5_3_2_2_1_4_6_5_2_1_1_2_7_7_6_1_5_1_1_1_4_4_1_2_4_4_7_3_1_3_1_3_5_2_4_7_2_6_6_1_4_1_4_1_3_4_3_5_1_2_2_6_3_3_3_6_6_2_6_6_1_3_3_6_5_6_4_2_3_4_1_2_3_3_2_3_6_4_5_4_3_6_2_1_1_4_2_3_3_5_2_2_6_4_7_4_3_3_3_1_6_6_7_2_1_5_5_5_3_6_5_3_5_1_4_5_2_6_5_5_4_1_1_4_7_3_2_1_1_2_3_2_2_3_3_3_5_6_5_6_1_1_6_1_4_2_3_1_5_7_3_1_6_4_2_2_2_7_4_1_4_7_1_2_6_1_4_3_1_6_1_1_5_1_1_1_2_1_6_2_6_5_6_1_1_2_1_3_3_5_1_3_5_5_1_1_1_3_7_5_4_1_6_6_3_6_5_3_3_5_2_5_7_6_6_2_1_4_6_3_7_5_4_1_3_1_6_3_6_5_3_4_4</t>
+  </si>
+  <si>
+    <t>3_4_4_4_4_4_4_2_2_2_1_4_2_2_5_1_4_5_2_3_3_3_3_1_2_1_3_3_3_3_1_3_2_2_2_5_3_6_6_2_5_1_3_4_2_1_1_1_2_2_2_2_2_2_1_2_3_2_2_2_1_3_1_2_3_1_4_5_1_3_4_4_3_4_3_3_3_4_5_2_1_2_4_4_1_2_3_2_6_5_5_1_1_1_3_4_3_5_2_2_3_5_3_3_3_4_5_2_6_2_3_2_4_4_1_3_1_3_1_1_1_6_1_1_1_1_1_3_4_1_5_1_4_2_2_6_4_1_3_3_2_2_2_1_2_4_4_1_1_5_1_3_3_3_4_2_3_1_2_1_2_2_5_4_6_3_5_3_4_4_1_1_4_5_5_5_2_6_1_3_3_1_1_4_3_5_2_5_2_4_3_1_1_2_1_2_4_3_3_2_4_3_3_3_3_3_1_4_4_3_4_2_1_1_1_4_1_1_1_1_1_5_1_4_4_6_3_3_4_2_5_2_1_2_3_3_3_3_4_2_5_1_2_1_2_2_3_5_2_2_2_1_5_3_4_1_1_2_2_3_2_2_2_2_3_3_2_2_2_2_1_2_5_3_2_3_4_1_1_1_4_5_3_3_5_3_3_3_2_3_3_3_1_1_6_1_3_2_3_4_1_3_4_4_4_2_2_3_2_4_4_2_3_1_2_1_6_4_2_1_5_5_5_5_1_3_1_6_4_2_1_2_3_1_1_1_4_3_3_6_2_2_3_4_4_5_2_4_3_5_3_5_2_5_1_2_4_4_2_2_4_2_6_2_1_4_2_3_1_3_3_2_4_6_6_2_3_3_3_2_1_1_4_2_1_1_3_1_1_4_6_6_2_2_6_2_1_1_2_3_1_1_3_1_2_4_3_2_2_1_5_2_2_1_2_2_3_1_3_5_3_3_3_6_4_6_1_1_1_2_4_2_4_4_3_4_2_1_1_1_4_1_1_5_2_2_1_1_2_1_3_3_5_2_3_3_2_1_1_4_1_4_1_2_1_1_3_2_4_4_2_1_1_2_5_2_2_1_1_1_6_1_5_1_2_2_2_3_2_2_2_4_4_1_1_1_2_5_1_1</t>
+  </si>
+  <si>
+    <t>2_3_1_2_3_3_1_4_2_7_3_5_5_2_4_4_1_4_7_1_2_2_3_1_2_2_3_5_1_3_1_1_6_5_7_3_4_3_1_4_4_4_2_3_6_5_1_1_4_5_2_1_3_1_2_2_5_4_1_1_4_1_4_3_3_5_6_4_1_5_1_2_3_4_3_3_1_4_6_6_4_5_3_2_1_1_1_2_6_6_3_1_2_1_1_1_7_1_1_3_3_2_5_1_4_1_3_4_1_1_3_5_1_5_2_5_1_2_5_4_3_3_1_3_5_4_5_3_7_1_2_2_1_7_2_4_1_2_6_3_1_2_1_3_2_4_4_7_1_5_4_2_3_4_1_4_5_7_1_1_7_5_3_3_1_1_4_5_3_2_1_2_3_3_1_2_1_4_3_3_1_2_1_5_2_1_1_5_3_3_1_1_3_3_5_3_5_4_5_1_5_6_3_3_4_3_5_5_1_1_2_1_1_5_6_5_3_1_6_3_2_7_4_2_3_3_7_6_1_1_1_1_2_1_5_3_5_6_2_7_2_1_4_2_5_2_4_3_4_4_2_4_6_1_1_5_4_1_1_2_5_6_5_2_2_1_1_2_3_5_2_3_5_6_5_2_6_3_2_1_3_2_1_3_4_2_4_4_4_4_2_1_1_1_3_3_4_4_6_1_2_7_1_3_1_4_1_5_3_1_1_5_1_1_3_2_3_2_4_7_2_2_4_6_2_3_5_2_4_1_1_3_4_2_6_1_3_7_1_4_2_3_4_1_1_1_3_3_5_5_7_3_4_3_6_3_6_5_3_5_2_1_1_2_1_1_3_6_1_3_4_5_2_6_4_2_3_1_2_1_1_2_1_2_6_1_5_2_5_5_6_1_5_5_3_4_7_2_1_1_5_6_4_4_3_3_7_3_5_1_4_1_2_7_2_4_2_3_2_4_2_3_3_1_2_1_2_5_2_2_1_2_2_3_3_3_2_6_4_5_3_3_3_5_2_4_4_2_5_6_4_2_5_2_1_2_2_2_3_3_3_2_5_2_4_4_6_2_5_6_4_7_2_6_5_2_5_1_5_4_5_4_7_6_2_2_6_6_6_3_1_2_4_6_1_4_2_4_1_4</t>
+  </si>
+  <si>
+    <t>1_1_3_3_2_2_5_1_2_2_4_2_1_1_1_2_2_1_3_2_2_5_1_2_2_2_1_1_2_6_4_4_4_5_4_2_3_1_1_3_1_1_4_5_1_1_6_2_1_6_1_5_1_2_2_2_3_2_5_2_1_3_3_2_2_3_6_3_1_1_2_1_1_6_3_3_2_1_1_1_1_1_5_5_3_1_4_4_3_1_1_1_4_1_1_1_1_2_1_1_1_2_3_5_3_5_3_4_3_3_2_2_2_2_2_4_4_4_4_1_4_4_4_2_2_2_5_1_3_2_4_5_2_1_1_3_3_4_1_1_5_3_3_3_2_3_3_3_3_3_5_5_1_2_1_1_4_1_4_4_1_1_2_6_1_2_2_2_1_4_2_3_4_2_2_1_1_1_3_6_6_3_3_1_4_3_3_1_2_3_2_5_2_5_2_2_1_5_6_1_4_1_2_3_3_2_1_1_3_3_3_2_1_3_2_2_4_2_1_5_3_3_1_2_1_1_3_3_3_3_3_3_1_1_1_2_2_3_3_1_6_3_2_2_4_1_5_2_2_2_2_6_3_3_1_3_1_1_4_2_1_3_2_4_3_2_5_5_2_6_4_3_2_1_1_5_5_1_4_3_5_2_4_4_2_4_2_2_5_2_6_6_2_5_6_1_3_3_3_2_4_4_3_1_2_6_5_1_1_1_3_4_1_1_1_6_2_2_3_4_2_1_6_1_5_2_4_5_5_4_4_1_4_5_4_1_3_2_1_1_4_4_1_3_5_1_1_5_1_6_6_6_6_6_1_4_2_1_1_4_3_2_4_1_4_4_2_3_3_3_2_3_1_1_4_3_2_4_1_3_2_2_1_1_4_1_2_6_1_4_1_1_4_4_1_2_4_1_4_2_4_5_1_1_3_5_3_2_2_2_1_1_5_1_4_2_6_2_6_1_1_1_5_1_1_6_3_2_3_4_3_3_1_2_2_2_6_1_2_4_2_4_1_1_3_2_4_1_3_1_2_6_3_4_1_3_1_1_5_1_2_5_1_5_4_6_2_3_1_1_1_1_1_2_4_3_3_1_2_1_3_2_2_4_3_3_1_3_2_1_1_2_1_1_5_3_3_3_1_1</t>
+  </si>
+  <si>
+    <t>1_1_2_5_1_3_2_2_2_3_3_6_4_1_6_2_3_2_3_1_4_4_4_2_5_5_6_3_7_5_1_4_3_5_1_2_4_5_5_7_4_3_2_2_5_7_3_4_3_3_5_1_2_5_3_1_2_4_4_2_2_1_4_4_2_5_2_1_3_6_1_1_2_5_1_1_1_1_5_7_3_3_5_2_3_6_1_5_1_3_3_5_6_2_1_1_3_1_1_4_3_3_1_2_3_2_4_1_2_1_2_3_4_2_6_1_6_1_4_3_6_6_3_1_3_1_4_5_2_1_2_1_6_2_1_6_4_1_4_5_1_3_1_5_1_3_1_1_4_1_5_1_2_7_7_1_2_7_1_1_6_3_1_1_1_4_2_7_3_1_2_1_1_7_5_2_3_2_6_1_1_5_4_1_3_1_1_3_1_3_3_3_1_5_5_2_5_1_6_6_1_7_1_3_2_1_2_2_6_2_7_1_3_1_1_4_3_4_6_3_2_1_1_5_6_4_1_2_3_4_1_4_5_4_6_1_2_2_3_5_2_6_2_6_6_4_2_5_6_1_1_2_1_4_5_1_1_1_1_3_3_5_5_4_5_6_6_6_4_5_7_4_1_4_4_3_6_6_1_4_3_1_2_5_1_4_2_2_2_2_1_1_1_3_1_7_1_2_6_3_5_2_5_3_1_2_1_6_4_2_3_1_2_1_6_1_3_3_3_2_3_3_3_4_1_1_2_5_1_6_5_5_2_2_4_2_5_5_2_6_1_2_7_2_4_3_2_5_2_2_3_5_3_2_2_4_7_6_5_6_4_2_4_2_5_1_6_4_5_7_4_3_4_7_5_2_5_4_2_6_2_2_6_1_5_1_5_2_4_1_6_5_3_3_6_3_3_2_2_2_2_5_1_2_2_1_1_2_5_1_1_1_5_1_3_6_2_6_3_2_2_6_5_5_3_1_2_4_2_5_6_2_6_6_4_3_2_2_3_6_6_7_1_4_4_2_2_1_3_2_3_3_1_2_3_1_4_4_2_2_1_2_3_1_1_4_5_4_1_6_3_2_4_3_2_1_2_3_1_3_3_4_7_6_5_2_2_4_5_5_1_5_5_6_2_2_1_1_5_3</t>
   </si>
 </sst>
 </file>
@@ -1809,7 +1830,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -4097,7 +4118,7 @@
       <c r="J72" s="17"/>
       <c r="K72" s="17"/>
     </row>
-    <row r="73" ht="16.5" spans="1:11">
+    <row r="73" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A73" s="5">
         <f t="shared" ref="A73:A80" si="3">C73*10+D73</f>
         <v>20230016</v>
@@ -4117,7 +4138,7 @@
       <c r="F73" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G73" t="s">
+      <c r="G73" s="16" t="s">
         <v>132</v>
       </c>
       <c r="H73" s="16" t="s">
@@ -4126,8 +4147,10 @@
       <c r="I73" s="16" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="74" ht="16.5" spans="1:11">
+      <c r="J73" s="17"/>
+      <c r="K73" s="17"/>
+    </row>
+    <row r="74" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A74" s="5">
         <f t="shared" si="3"/>
         <v>20230017</v>
@@ -4147,7 +4170,7 @@
       <c r="F74" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G74" t="s">
+      <c r="G74" s="16" t="s">
         <v>133</v>
       </c>
       <c r="H74" s="16" t="s">
@@ -4156,8 +4179,10 @@
       <c r="I74" s="16" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="75" ht="16.5" spans="1:11">
+      <c r="J74" s="17"/>
+      <c r="K74" s="17"/>
+    </row>
+    <row r="75" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A75" s="5">
         <f t="shared" si="3"/>
         <v>20230018</v>
@@ -4177,7 +4202,7 @@
       <c r="F75" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G75" t="s">
+      <c r="G75" s="16" t="s">
         <v>134</v>
       </c>
       <c r="H75" s="16" t="s">
@@ -4186,8 +4211,10 @@
       <c r="I75" s="16" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="76" ht="16.5" spans="1:11">
+      <c r="J75" s="17"/>
+      <c r="K75" s="17"/>
+    </row>
+    <row r="76" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A76" s="5">
         <f t="shared" si="3"/>
         <v>20230019</v>
@@ -4207,7 +4234,7 @@
       <c r="F76" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G76" t="s">
+      <c r="G76" s="16" t="s">
         <v>135</v>
       </c>
       <c r="H76" s="16" t="s">
@@ -4216,8 +4243,10 @@
       <c r="I76" s="16" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="77" ht="16.5" spans="1:11">
+      <c r="J76" s="17"/>
+      <c r="K76" s="17"/>
+    </row>
+    <row r="77" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A77" s="5">
         <f t="shared" si="3"/>
         <v>20230020</v>
@@ -4237,7 +4266,7 @@
       <c r="F77" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G77" t="s">
+      <c r="G77" s="16" t="s">
         <v>136</v>
       </c>
       <c r="H77" s="16" t="s">
@@ -4246,8 +4275,10 @@
       <c r="I77" s="16" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="78" ht="16.5" spans="1:11">
+      <c r="J77" s="17"/>
+      <c r="K77" s="17"/>
+    </row>
+    <row r="78" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A78" s="5">
         <f t="shared" si="3"/>
         <v>20230021</v>
@@ -4267,7 +4298,7 @@
       <c r="F78" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G78" t="s">
+      <c r="G78" s="16" t="s">
         <v>137</v>
       </c>
       <c r="H78" s="16" t="s">
@@ -4276,8 +4307,10 @@
       <c r="I78" s="16" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="79" ht="16.5" spans="1:11">
+      <c r="J78" s="17"/>
+      <c r="K78" s="17"/>
+    </row>
+    <row r="79" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A79" s="5">
         <f t="shared" si="3"/>
         <v>20230022</v>
@@ -4297,7 +4330,7 @@
       <c r="F79" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G79" t="s">
+      <c r="G79" s="16" t="s">
         <v>138</v>
       </c>
       <c r="H79" s="16" t="s">
@@ -4306,8 +4339,10 @@
       <c r="I79" s="16" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="80" ht="16.5" spans="1:11">
+      <c r="J79" s="17"/>
+      <c r="K79" s="17"/>
+    </row>
+    <row r="80" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A80" s="5">
         <f t="shared" si="3"/>
         <v>20230023</v>
@@ -4327,7 +4362,7 @@
       <c r="F80" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G80" t="s">
+      <c r="G80" s="16" t="s">
         <v>139</v>
       </c>
       <c r="H80" s="16" t="s">
@@ -4336,6 +4371,104 @@
       <c r="I80" s="16" t="s">
         <v>125</v>
       </c>
+      <c r="J80" s="17"/>
+      <c r="K80" s="17"/>
+    </row>
+    <row r="81" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A81" s="5">
+        <f>C81*10+D81</f>
+        <v>20340011</v>
+      </c>
+      <c r="B81" s="13">
+        <v>103400</v>
+      </c>
+      <c r="C81" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D81" s="33">
+        <v>1</v>
+      </c>
+      <c r="E81" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="F81" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G81" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="H81" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I81" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="J81" s="17"/>
+      <c r="K81" s="17"/>
+    </row>
+    <row r="82" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A82" s="5">
+        <f>C82*10+D82</f>
+        <v>20340012</v>
+      </c>
+      <c r="B82" s="13">
+        <v>103400</v>
+      </c>
+      <c r="C82" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D82" s="33">
+        <v>2</v>
+      </c>
+      <c r="E82" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F82" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G82" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="H82" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I82" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="J82" s="17"/>
+      <c r="K82" s="17"/>
+    </row>
+    <row r="83" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A83" s="5">
+        <f>C83*10+D83</f>
+        <v>20340013</v>
+      </c>
+      <c r="B83" s="13">
+        <v>103400</v>
+      </c>
+      <c r="C83" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D83" s="33">
+        <v>3</v>
+      </c>
+      <c r="E83" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F83" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G83" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="H83" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I83" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="J83" s="17"/>
+      <c r="K83" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="BaseRoller" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -79,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="153">
   <si>
     <t>id</t>
   </si>
@@ -475,6 +476,69 @@
   </si>
   <si>
     <t>9_1_7_1_3_6_1_3_5_3_2_9_1_2_1_7_5_3_1_9_8_6_8_6_2_5_2_7_2_3_2_3_7_2_9_6_9_3_2_2_4_1_1_4_5_8_9_8_6_1_3_4_4_4_5_7_8_3_2_1_8_2_1_6_3_4_7_5_5_2_3_4_1_7_3_2_7_3_6_5_9_4_5_3_5_5_8_2_7_2_4_3_8_6_6_4_1_4_3_1_3_5_2_3_7_6_1_1_5_5_1_2_7_3_8_2_7_3_3_3_6_4_3_4_8_1_6_4_8_3_5_1_6_4_1_3_5_6_4_6_3_3_6_6_8_7_2_2_4_2_8_9_3_3_6_3_9_5_9_8_2_4_4_1_7_8_1_2_6_1_3_5_5_8_6_3_1_6_4_2_6_5_2_2_6_5_1_9_7_3_5_6_9_9_6_4_8_1_2_7_9_7_8_3_5_5_6_7_5_7_2_3_7_3_4_5_7_1_6_2_2_7_5_5_8_4_8_1_2_2_4_1_9_2_5_8_8_5_1_9_4_3_8_1_4_6_1_2_3_8_2_5_5_1_1_6_4_1_6_9_1_3_5_9_4_8_2_1_3_8_1_2_3_2_8_5_5_4_4_5_3_7_4_4_6_5_9_5_7_8_3_2_2_4_7_2_6_4_4_6_1_8_3_2_6_6_4_7_7_9_6_3_3_9_4_5_1_3_4_3_1_1_5_2_3_1_2_6_1_3_7_8_3_7_7_5_9_2_2_4_1_4_5_2_6_4_6_4_8_1_9_4_6_5_4_7_3_1_9_8_6_5_7_2_3_8_2_2_7_5_3_6_2_9_3_1_4_6_3_2_1_1_5_4_2_5_7_7_3_5_9_2_2_8_2_8_2_7_6_6_2_7_5_7_6_7_2_2_1_3_6_4_9_2_4_6_8_5_2_6_6_8_2_2_1_1_5_8_7_5_1_4_1_6_8_3_6_6_5_6_1_6_1_9_5_6_6_5_2_3_2_4_2_4_2_8_9_1_5_6_2_1_7_7_3_3_3_4_2_7_5_5_1_4_9_4_8_5_6_2_4_9_9_6_2_3_6_7_7_8_1_6_5_4_1_6_2_7_2_3</t>
+  </si>
+  <si>
+    <t>5_3_2_6_1_1_1_6_6_2_5_1_9_9_9_9_8_2_2_7_1_1_4_1_2_6_1_7_4_1_5_3_3_2_2_2_4_8_1_5_2_1_6_3_1_2_8_1_6_6_9_5_5_2_1_5_5_3_1_6_1_3_5_1_1_4_4_1_2_2_2_6_5_3_10_10_8_10_2_8_8_1_4_3_4_1_4_5_6_9_7_7_8_3_7_4_4_4_4_1_7_1_2_1_7_6_9_1_3_6_1_2_2_2_3_8_1_5_2_2_9_5_7_8_3_6_6_8_5_8_1_6_7_7_2_1_1_3_5_5_5_7_7_1_1_5_1_1_8_6_10_1_3_2_5_5_6_9_3_9_5_2_2_2_2_7_4_7_2_7_3_1_4_5_9_9_9_1_4_2_6_5_7_1_5_9_3_5_10_2_7_2_6_9_10_5_8_3_2_3_8_6_4_4_8_8_4_9_9_8_6_8_8_10_2_5_5_4_1_6_4_8_3_1_5_5_8_6_3_5_5_5_5_1_4_8_6_1_6_4_1_1_6_4_3_10_1_2_7_7_3_9_8_4_4_6_5_3_3_7_6_6_9_4_6_3_3_5_10_8_3_3_1_1_1_6_3_1_1_4_5_2_4_4_10_9_2_6_2_3_9_5_1_9_5_3_4_2_2_6_6_8_1_3_2_5_4_6_10_1_4_5_6_1_8_8_4_5_7_6_7_4_8_8_2_6_6_6_2_4_8_8_1_1_10_3_3_3_1_3_7_7_7_9_6_2_5_6_2_1_1_8_5_5_4_1_5_3_4_7_2_10_2_1_9_2_7_2_2_2_1_1_6_5_5_6_3_6_4_7_2_8_2_8_4_8_5_4_5_5_6_6_6_7_7_7_1_2_3_3_1_2_2_3_4_9_2_4_8_5_6_8_1_2_4_4_2_2_4_4_9_5_5_1_5_3_6_2_6_2_1_4_8_1_10_7_2_4_3_6_1_7_8_2_10_6_7_1_6_3_1_7_6_8_8_7_9_9_9_5_4_4_2_6_4_7_7_7_10_8_4_3_3_9_6_8_6_1_2_5_1_3_4_3_9_8_3_2_8_5_5_4_5_5_3_6_6_3_1_1</t>
+  </si>
+  <si>
+    <t>7_7_6_1_5_6_1_7_3_3_2_3_7_5_1_6_4_4_6_2_1_1_1_1_6_4_7_3_6_1_2_5_4_4_6_9_4_7_1_4_5_3_7_2_5_5_2_3_5_4_4_1_3_6_2_5_6_6_6_4_4_1_1_1_1_2_2_9_1_1_1_3_3_9_8_2_7_7_2_2_8_8_3_2_8_8_8_3_3_8_3_5_7_7_8_1_7_4_6_1_1_2_6_1_5_8_6_1_7_8_1_5_5_4_4_1_1_3_2_4_2_10_8_6_4_2_9_4_5_6_2_8_4_3_1_5_1_6_6_2_9_9_5_2_9_2_3_5_4_6_3_3_1_4_4_1_1_7_4_3_3_2_8_8_2_3_1_5_3_1_4_6_1_6_2_7_8_3_1_7_7_5_1_1_1_1_1_5_5_2_6_7_7_9_1_3_1_1_4_4_2_1_3_9_1_3_3_1_3_2_7_6_1_4_4_9_8_5_1_5_6_1_5_5_2_4_1_1_6_8_9_8_4_4_4_1_1_9_8_2_1_4_7_4_1_6_6_2_2_3_10_5_2_2_3_5_6_6_2_9_5_5_10_10_3_3_2_4_6_4_7_2_1_1_1_8_2_5_2_2_9_4_4_9_3_1_6_1_1_1_3_2_2_4_4_4_1_1_1_3_7_9_6_4_1_2_3_5_5_9_9_2_5_5_5_8_3_3_3_1_6_5_7_10_1_7_6_6_3_5_3_4_2_3_6_2_2_4_1_2_3_8_4_2_9_9_5_6_6_1_6_4_2_1_6_1_3_7_1_5_1_4_10_7_2_2_2_6_4_8_4_1_7_6_1_8_8_4_1_4_4_2_2_8_1_1_1_2_1_6_4_4_3_7_3_7_6_1_9_1_10_3_3_9_9_3_2_6_5_4_2_7_3_1_1_4_8_3_2_2_1_7_1_9_7_2_6_5_4_6_8_7_1_5_4_2_9_6_1_4_3_3_9_3_5_3_4_3_5_3_9_2_9_3_1_9_2_9_8_5_8_2_5_5_4_4_1_8_8_3_4_3_3_5_1_3_1_1_2_9_9_8_9_6_8_10_5_9_4_8_1_3_3_3_3_2_1_2_2_1</t>
+  </si>
+  <si>
+    <t>10_2_2_5_3_9_9_1_3_4_4_9_5_3_5_1_6_7_3_5_3_7_5_5_4_4_1_8_8_8_6_6_4_5_5_5_5_2_4_2_5_2_4_2_2_3_4_1_1_8_1_1_1_2_2_4_4_7_3_6_7_1_4_6_7_7_3_2_4_9_7_6_6_4_1_6_1_2_9_8_3_9_2_2_2_5_2_2_9_7_9_6_9_1_1_7_1_1_7_6_5_8_4_4_9_4_5_9_6_6_1_5_8_1_5_10_5_6_3_5_1_6_1_9_2_1_2_2_3_3_9_6_8_3_4_8_3_3_4_4_4_2_4_6_5_3_9_3_2_5_7_8_2_2_1_8_1_3_4_10_5_1_8_8_3_3_6_4_3_2_10_7_3_5_1_3_1_1_2_5_6_2_4_2_5_8_3_3_3_5_7_7_2_7_7_7_10_2_8_5_1_1_1_1_4_7_2_2_5_2_4_5_4_6_4_1_1_1_9_10_6_8_10_4_6_6_3_9_7_5_1_1_4_3_1_8_7_5_7_5_1_1_2_2_9_4_2_1_1_6_7_7_6_10_2_7_6_9_1_1_6_8_1_2_5_5_10_8_9_4_8_8_3_6_7_7_4_7_5_5_8_7_5_5_3_3_5_5_6_6_9_6_9_2_5_4_4_4_2_8_4_5_2_2_3_9_5_6_10_8_2_6_9_4_4_6_7_7_2_3_3_3_4_1_7_5_2_4_8_8_5_3_7_7_1_1_3_6_6_8_7_3_7_4_4_7_3_5_5_8_5_2_5_3_1_4_2_8_8_3_8_2_8_1_4_2_6_7_4_6_6_8_2_3_6_6_7_7_3_1_8_1_1_1_4_3_10_1_8_8_3_9_7_7_3_5_9_3_2_5_5_10_8_10_1_5_5_1_1_10_1_4_3_7_7_5_7_3_9_7_3_2_3_1_1_3_6_4_3_7_9_3_4_9_4_3_4_6_7_8_1_7_2_7_7_6_7_5_2_5_5_3_8_2_7_1_2_5_1_6_5_6_3_8_5_3_1_3_8_1_1_1_5_7_1_1_2_1_7_1_6_1_1_5_9_2_1_3_3_3_1_7_2_1_1_6_5_2_4_2</t>
+  </si>
+  <si>
+    <t>5_8_7_8_7_8_4_2_2_3_6_7_3_5_2_2_6_2_6_1_6_7_6_6_6_1_3_8_8_8_2_3_3_5_4_8_8_7_4_5_6_6_4_5_3_8_4_9_4_8_4_4_4_1_3_9_3_3_2_1_1_6_5_2_1_4_5_5_5_6_9_8_4_9_1_9_7_6_4_9_3_5_6_7_2_2_1_1_9_9_5_5_6_7_5_5_8_6_9_2_1_1_6_1_2_1_1_1_2_6_3_1_6_1_1_3_7_8_1_1_5_7_7_4_6_4_10_3_10_4_2_8_8_4_2_7_7_7_7_2_1_3_3_7_5_3_3_3_6_8_9_3_3_1_6_7_2_3_4_1_6_3_9_6_4_9_4_2_3_1_1_10_3_4_9_10_10_10_6_1_1_1_9_3_5_3_3_1_2_6_3_4_3_8_1_4_1_7_6_6_6_5_2_6_6_4_4_8_8_7_4_5_7_5_7_5_5_3_4_8_7_9_8_6_9_4_3_7_2_2_4_8_3_4_3_3_8_3_2_2_4_4_2_3_3_2_7_3_5_6_2_4_9_8_1_6_1_4_1_2_2_3_1_4_2_2_9_1_2_1_9_1_1_1_1_1_9_7_1_4_5_3_5_1_6_7_1_1_1_4_7_8_1_4_4_7_4_4_1_2_4_2_6_1_8_1_5_5_5_9_1_1_7_5_2_2_3_3_4_8_3_5_3_4_2_3_3_1_3_1_2_3_4_4_4_2_9_8_4_2_10_6_4_2_6_5_8_1_1_6_2_1_1_10_1_2_1_1_3_7_8_2_5_8_1_3_2_4_8_8_3_3_9_1_3_1_5_7_4_7_9_9_1_6_2_2_8_9_1_2_2_4_4_5_4_1_4_8_3_2_8_1_3_3_6_5_5_2_1_1_8_6_7_1_10_2_1_1_1_2_2_5_5_2_2_10_4_4_2_3_4_4_9_6_2_3_2_2_2_8_4_1_6_10_4_5_1_9_3_5_2_1_1_1_3_4_1_4_7_5_9_7_3_7_3_4_2_6_5_2_8_1_1_1_7_7_5_5_1_5_5_3_5_4_2_8_6_5_7_5_5_4_6_6_3_1_9_7_4_5</t>
+  </si>
+  <si>
+    <t>1_2_6_8_4_3_2_1_3_5_8_8_1_1_2_10_2_3_2_4_4_2_4_1_4_2_9_6_5_4_4_4_7_2_2_2_2_6_3_5_2_2_9_5_1_6_7_3_1_1_3_9_9_9_2_4_4_1_1_4_7_7_8_4_7_7_6_5_3_1_1_6_8_7_7_4_4_1_3_3_9_1_1_1_3_3_3_3_3_2_6_4_3_2_7_5_9_5_5_3_3_3_7_4_7_9_2_4_4_6_10_8_5_6_1_8_3_2_6_2_5_5_1_8_4_8_2_2_2_5_6_7_4_2_7_1_1_1_4_8_1_2_9_3_3_1_2_4_1_2_7_9_2_3_4_2_2_2_1_2_8_6_2_2_4_2_3_1_3_1_3_3_1_7_1_2_6_2_1_6_10_10_1_7_7_6_4_7_2_4_5_5_7_4_5_1_8_2_9_1_4_8_1_4_9_4_10_7_6_5_4_7_6_4_6_6_4_9_9_7_3_7_9_8_8_8_1_2_5_8_8_8_2_1_2_6_2_7_2_6_6_8_2_7_4_4_2_4_2_2_9_9_2_2_1_2_4_2_8_4_3_1_1_1_1_6_4_1_4_4_4_4_3_5_3_3_8_1_9_1_3_6_3_8_2_7_1_6_8_2_5_6_7_4_4_1_2_2_2_2_3_10_8_5_3_4_9_9_1_7_1_8_4_1_3_6_9_5_6_1_7_3_5_2_1_1_5_3_6_1_7_1_9_1_3_9_8_7_3_1_1_2_6_7_2_2_1_1_5_10_6_2_3_6_1_2_6_3_2_4_1_1_3_6_6_5_3_2_2_5_5_4_5_8_10_2_3_6_2_9_3_1_1_2_4_2_7_1_7_7_4_2_8_1_5_9_8_7_6_3_9_6_3_3_5_6_6_2_1_9_2_8_3_1_6_3_8_3_2_9_1_1_5_2_4_7_6_2_1_4_1_1_5_2_6_6_9_9_3_6_7_4_5_1_1_5_2_7_9_3_2_2_5_4_4_8_4_5_4_4_3_1_2_1_2_1_2_4_4_7_8_1_2_7_1_2_5_5_7_7_6_6_1_2_4_2_6_9_1_1_3_2_4_5_9_8_2_5_9_6</t>
+  </si>
+  <si>
+    <t>4_2_6_7_4_2_2_7_4_6_6_6_6_5_9_1_3_6_1_2_2_2_4_4_1_4_7_2_2_1_1_2_4_2_6_6_3_1_1_8_6_3_1_1_6_6_5_5_2_6_2_4_1_4_2_3_6_2_3_1_2_2_6_1_3_7_4_3_3_1_6_9_6_4_3_7_1_1_1_7_5_9_4_2_1_3_3_7_8_8_3_9_2_6_8_2_1_4_3_2_4_3_3_6_4_8_3_1_1_1_7_7_7_1_4_7_8_9_2_2_8_5_2_4_4_6_5_5_5_7_9_6_1_4_2_3_2_2_3_2_4_2_1_9_4_8_9_3_4_5_3_5_5_4_2_3_5_2_4_2_2_4_8_7_1_3_2_3_4_4_4_2_7_3_2_6_8_1_8_8_9_6_7_8_1_8_4_4_2_7_9_4_2_2_8_1_1_2_6_6_6_7_3_1_1_8_8_5_8_2_5_1_1_1_8_8_5_2_6_6_8_2_8_1_1_5_7_5_6_6_5_7_5_2_1_2_2_3_5_7_7_4_2_7_1_2_6_2_2_6_8_8_6_1_1_4_2_2_6_1_3_1_3_4_3_1_2_5_8_6_6_8_1_4_1_9_5_8_8_1_1_2_1_3_4_2_3_2_5_3_2_9_3_1_7_6_2_4_7_7_2_5_4_8_3_4_3_3_3_3_3_3_3_5_2_5_3_4_6_7_7_3_5_5_5_2_6_5_4_6_6_1_5_5_9_9_1_9_2_1_2_4_5_6_6_3_7_5_9_8_2_7_2_5_9_3_7_1_2_7_5_6_3_2_2_2_4_7_8_4_4_1_3_3_6_8_2_2_7_9_7_8_4_4_1_1_4_5_6_5_7_4_5_6_4_2_1_4_9_9_3_4_5_7_9_2_5_4_9_1_3_1_2_9_4_4_2_2_9_8_8_8_1_1_1_3_8_8_9_1_5_3_5_4_7_7_4_2_1_2_2_8_3_9_9_4_5_1_3_1_3_4_4_6_2_1_2_8_1_4_5_4_3_2_5_4_3_4_7_6_1_3_9_7_7_3_5_5_2_1_1_2_2_6_4_2_2_3_3_5_4_2_9_2_2_4_1_8_8_6</t>
+  </si>
+  <si>
+    <t>1_8_1_2_2_4_4_1_1_2_1_1_4_1_2_1_8_6_2_1_2_4_1_1_2_1_8_8_2_4_6_2_2_2_1_4_1_4_1_2_1_4_1_2_2_6_6_6_1_1_8_1_1_1_2_1_1_6_6_6_8_1_2_6_1_4_2_1_4_1_6_1_1_6_2_6_2_6_4_4_6_8_1_6_2_1_1_1_1_4_1_2_4_4_1_1_1_1_2_2_2_1_1_2_1_2_4_2_2_4_6_4_4_1_2_1_1_1_2_4_2_2_4_8_6_8_6_2_4_6_1_2_2_4_4_4_2_1_1_2_2_8_8_6_2_6_6_6_2_2_2_8_6_2_6_4_1_4_4_2_4_1_2_2_1_1_2_1_2_8_2_4_2_2_4_1_8_2_1_6_4_4_1_8_8_6_1_2_2_6_6_6_8_2_2_8_1_6_2_2_6_4_1_6_4_1_2_4_2_1_6_2_2_6_2_1_1_1_1_1_2_4_1_8_8_8_1_4_4_1_1_6_2_2_4_1_8_6_6_1_1_1_4_2_8_4_2_6_4_2_2_1_1_1_2_4_4_1_1_6_4_8_1_1_4_2_8_1_1_2_1_1_6_6_4_1_1_2_4_8_1_6_6_8_6_4_4_6_2_1_1_6_4_1_4_6_1_4_1_1_1_1_2_1_6_6_4_1_1_2_2_2_1_2_6_1_1_2_1_1_4_4_8_1_1_4_4_2_1_4_1_1_6_1_1_8_6_2_4_6_1_1_1_4_4_4_1_1_2_1_6_8_2_8_1_8_8_1_2_8_2_8_1_1_6_2_1_1_4_4_2_4_2_4_6_2_6_6_1_8_1_4_1_1_1_4_2_1_1_8_6_4_6_6_1_2_4_8_4_4_6_4_4_1_2_1_2_1_1_6_4_2_1_2_1_1_8_6_8_4_8_1_4_2_1_8_2_1_8_6_1_2_8_8_4_6_6_8_8_1_1_8_1_4_4_4_4_4_6_2_4_1_1_1_1_1_1_8_2_2_6_4_2_4_4_1_2_4_2_1_2_6_6_1_1_1_2_1_4_6_8_4_6_6_4_2_4_6_2_1_4_1_6_2_1_2_1_8_8_1</t>
+  </si>
+  <si>
+    <t>1_1_3_3_3_5_1_1_3_3_3_3_5_7_1_7_1_7_5_5_3_1_7_3_3_1_1_5_3_1_5_1_3_1_1_1_1_1_1_1_7_3_1_5_1_1_1_1_1_1_1_7_5_7_1_7_3_3_7_1_1_1_1_7_1_1_1_7_3_3_3_1_3_5_5_3_5_7_7_1_3_1_5_1_7_5_5_1_7_3_1_3_7_1_3_7_1_1_7_1_3_7_1_3_1_1_5_1_7_7_7_7_1_1_5_7_5_5_1_3_3_5_1_3_7_3_5_5_5_5_5_7_7_1_3_1_3_1_1_1_1_3_1_3_3_7_3_1_3_7_3_7_7_5_1_1_1_1_3_1_3_1_5_5_5_5_1_7_7_1_3_3_3_5_1_7_7_1_3_1_3_1_7_7_1_7_3_3_5_5_1_1_1_1_3_7_1_1_1_5_3_5_5_3_1_3_7_3_5_5_5_5_7_5_7_1_1_5_3_7_3_3_1_7_7_3_3_1_7_1_5_3_3_5_5_5_7_5_3_3_5_5_5_1_1_1_7_5_3_3_1_1_5_5_1_3_3_3_1_1_1_1_3_1_7_3_5_1_3_5_5_5_1_1_1_3_5_5_5_3_3_7_1_3_5_5_1_1_1_5_3_1_3_1_5_1_5_5_3_1_5_5_7_7_3_7_3_3_3_1_3_3_5_1_3_3_5_1_1_5_7_3_5_5_1_1_7_5_5_7_1_1_5_1_7_1_3_1_1_1_1_3_5_7_1_3_3_5_3_7_5_3_7_3_3_1_1_3_1_3_5_7_7_7_1_1_1_7_3_3_1_3_3_7_3_3_7_1_5_5_1_3_5_3_3_5_5_5_5_1_7_5_1_7_7_1_5_1_3_5_5_5_3_1_3_5_3_1_7_3_1_1_7_3_3_3_3_7_7_5_5_1_7_1_1_5_5_5_5_5_1_5_5_3_1_3_1_5_1_1_3_5_5_5_1_7_3_7_5_7_1_1_1_3_3_1_3_3_5_5_5_1_1_1_1_5_1_3_3_5_5_1_7_1_1_1_7_7_1_1_1_3_1_3_5_5_1_5_1_1_5_3_3_1_3_5_1_1_1_5</t>
+  </si>
+  <si>
+    <t>4_4_4</t>
+  </si>
+  <si>
+    <t>3_3_2_4_2_4_5_1_5_1_4_6_3_6_2_1_4_1_1_3_2_3_2_2_3_5_2_1_4_4_2_2_2_3_3_3_6_3_2_6_2_5_4_3_1_3_4_4_4_1_3_4_4_3_1_3_3_1_6_3_2_1_4_2_2_3_6_1_1_5_2_2_1_1_1_1_4_2_2_4_6_1_1_1_3_2_2_3_5_3_3_5_2_3_2_5_1_4_4_4_2_3_4_3_1_5_2_1_1_3_2_2_2_4_4_3_5_5_3_5_1_2_3_2_2_2_4_5_2_1_6_2_2_2_5_1_1_1_4_3_3_1_5_5_4_3_2_3_2_1_2_2_4_2_6_6_3_3_2_1_4_1_5_5_5_4_2_3_3_3_3_1_5_5_2_3_2_2_5_5_3_4_1_1_2_2_2_4_4_3_2_1_3_3_1_3_5_4_5_2_5_5_1_1_1_4_2_2_6_4_2_2_3_1_2_1_4_5_1_2_2_2_2_1_5_5_5_5_2_1_3_3_1_4_4_5_1_5_5_3_1_2_1_3_4_4_2_5_1_5_5_3_5_2_2_4_4_1_2_2_2_1_2_2_3_2_1_2_3_4_6_5_5_3_5_1_2_2_2_4_1_4_2_2_4_3_3_3_1_3_3_6_1_3_3_2_4_3_1_5_1_2_2_3_2_2_3_1_4_4_3_1_5_4_4_2_3_1_2_3_4_4_2_2_1_4_4_3_1_2_2_1_1_1_4_3_2_2_2_2_1_1_1_2_2_1_4_4_2_2_2_2_3_1_2_2_2_2_1_2_2_2_3_3_4_1_1_1_6_6_1_1_1_4_1_3_1_4_2_6_4_2_6_3_4_4_2_4_3_2_2_4_6_2_2_5_4_4_3_1_3_1_1_4_2_3_1_2_2_1_5_6_3_2_2_2_4_1_3_2_1_1_1_2_1_3_2_2_5_4_4_3_3_4_1_5_3_2_1_5_1_6_3_3_2_3_1_3_3_4_1_1_2_6_1_2_2_2_4_4_6_2_6_4_2_3_3_1_1_3_3_1_6_5_3_2_6_4_4_1_2_2_2_5_3_4_2_4_1_2_5_2_2_5_5_5_4_4_1_3</t>
+  </si>
+  <si>
+    <t>3_2_3_2_1_6_6_4_3_7_6_2_5_3_1_6_3_4_3_1_1_7_4_3_4_1_5_3_1_2_4_1_2_1_3_4_2_6_3_2_4_1_2_1_2_7_7_5_1_5_2_4_4_3_5_1_6_6_3_2_2_4_2_6_2_1_1_3_4_1_2_4_4_1_5_1_1_1_2_1_4_4_3_2_4_3_3_3_1_1_6_3_1_4_1_1_6_3_2_2_3_4_1_2_7_3_3_6_6_3_1_5_3_4_1_3_6_3_3_3_2_3_5_4_3_5_7_5_4_1_2_1_3_3_3_2_2_6_4_1_5_7_3_6_5_2_2_4_2_4_3_1_1_6_2_1_3_6_6_1_1_3_1_1_1_6_7_1_3_3_3_6_3_2_1_5_7_6_1_1_2_3_4_6_2_1_3_3_4_2_1_2_3_2_2_2_2_4_1_2_1_7_1_5_3_2_4_3_2_1_2_3_3_1_6_3_1_6_3_3_1_1_5_6_4_4_3_4_1_3_3_7_3_2_1_4_3_2_2_2_1_1_6_6_1_2_2_6_2_2_6_1_4_3_7_1_5_4_4_4_3_1_3_2_7_6_5_5_3_2_2_1_4_6_5_2_1_1_2_7_7_6_1_5_1_1_1_4_4_1_2_4_4_7_3_1_3_1_3_5_2_4_7_2_6_6_1_4_1_4_1_3_4_3_5_1_2_2_6_3_3_3_6_6_2_6_6_1_3_3_6_5_6_4_2_3_4_1_2_3_3_2_3_6_4_5_4_3_6_2_1_1_4_2_3_3_5_2_2_6_4_7_4_3_3_3_1_6_6_7_2_1_5_5_5_3_6_5_3_5_1_4_5_2_6_5_5_4_1_1_4_7_3_2_1_1_2_3_2_2_3_3_3_5_6_5_6_1_1_6_1_4_2_3_1_5_7_3_1_6_4_2_2_2_7_4_1_4_7_1_2_6_1_4_3_1_6_1_1_5_1_1_1_2_1_6_2_6_5_6_1_1_2_1_3_3_5_1_3_5_5_1_1_1_3_7_5_4_1_6_6_3_6_5_3_3_5_2_5_7_6_6_2_1_4_6_3_7_5_4_1_3_1_6_3_6_5_3_4_4</t>
+  </si>
+  <si>
+    <t>3_4_4_4_4_4_4_2_2_2_1_4_2_2_5_1_4_5_2_3_3_3_3_1_2_1_3_3_3_3_1_3_2_2_2_5_3_6_6_2_5_1_3_4_2_1_1_1_2_2_2_2_2_2_1_2_3_2_2_2_1_3_1_2_3_1_4_5_1_3_4_4_3_4_3_3_3_4_5_2_1_2_4_4_1_2_3_2_6_5_5_1_1_1_3_4_3_5_2_2_3_5_3_3_3_4_5_2_6_2_3_2_4_4_1_3_1_3_1_1_1_6_1_1_1_1_1_3_4_1_5_1_4_2_2_6_4_1_3_3_2_2_2_1_2_4_4_1_1_5_1_3_3_3_4_2_3_1_2_1_2_2_5_4_6_3_5_3_4_4_1_1_4_5_5_5_2_6_1_3_3_1_1_4_3_5_2_5_2_4_3_1_1_2_1_2_4_3_3_2_4_3_3_3_3_3_1_4_4_3_4_2_1_1_1_4_1_1_1_1_1_5_1_4_4_6_3_3_4_2_5_2_1_2_3_3_3_3_4_2_5_1_2_1_2_2_3_5_2_2_2_1_5_3_4_1_1_2_2_3_2_2_2_2_3_3_2_2_2_2_1_2_5_3_2_3_4_1_1_1_4_5_3_3_5_3_3_3_2_3_3_3_1_1_6_1_3_2_3_4_1_3_4_4_4_2_2_3_2_4_4_2_3_1_2_1_6_4_2_1_5_5_5_5_1_3_1_6_4_2_1_2_3_1_1_1_4_3_3_6_2_2_3_4_4_5_2_4_3_5_3_5_2_5_1_2_4_4_2_2_4_2_6_2_1_4_2_3_1_3_3_2_4_6_6_2_3_3_3_2_1_1_4_2_1_1_3_1_1_4_6_6_2_2_6_2_1_1_2_3_1_1_3_1_2_4_3_2_2_1_5_2_2_1_2_2_3_1_3_5_3_3_3_6_4_6_1_1_1_2_4_2_4_4_3_4_2_1_1_1_4_1_1_5_2_2_1_1_2_1_3_3_5_2_3_3_2_1_1_4_1_4_1_2_1_1_3_2_4_4_2_1_1_2_5_2_2_1_1_1_6_1_5_1_2_2_2_3_2_2_2_4_4_1_1_1_2_5_1_1</t>
+  </si>
+  <si>
+    <t>2_3_1_2_3_3_1_4_2_7_3_5_5_2_4_4_1_4_7_1_2_2_3_1_2_2_3_5_1_3_1_1_6_5_7_3_4_3_1_4_4_4_2_3_6_5_1_1_4_5_2_1_3_1_2_2_5_4_1_1_4_1_4_3_3_5_6_4_1_5_1_2_3_4_3_3_1_4_6_6_4_5_3_2_1_1_1_2_6_6_3_1_2_1_1_1_7_1_1_3_3_2_5_1_4_1_3_4_1_1_3_5_1_5_2_5_1_2_5_4_3_3_1_3_5_4_5_3_7_1_2_2_1_7_2_4_1_2_6_3_1_2_1_3_2_4_4_7_1_5_4_2_3_4_1_4_5_7_1_1_7_5_3_3_1_1_4_5_3_2_1_2_3_3_1_2_1_4_3_3_1_2_1_5_2_1_1_5_3_3_1_1_3_3_5_3_5_4_5_1_5_6_3_3_4_3_5_5_1_1_2_1_1_5_6_5_3_1_6_3_2_7_4_2_3_3_7_6_1_1_1_1_2_1_5_3_5_6_2_7_2_1_4_2_5_2_4_3_4_4_2_4_6_1_1_5_4_1_1_2_5_6_5_2_2_1_1_2_3_5_2_3_5_6_5_2_6_3_2_1_3_2_1_3_4_2_4_4_4_4_2_1_1_1_3_3_4_4_6_1_2_7_1_3_1_4_1_5_3_1_1_5_1_1_3_2_3_2_4_7_2_2_4_6_2_3_5_2_4_1_1_3_4_2_6_1_3_7_1_4_2_3_4_1_1_1_3_3_5_5_7_3_4_3_6_3_6_5_3_5_2_1_1_2_1_1_3_6_1_3_4_5_2_6_4_2_3_1_2_1_1_2_1_2_6_1_5_2_5_5_6_1_5_5_3_4_7_2_1_1_5_6_4_4_3_3_7_3_5_1_4_1_2_7_2_4_2_3_2_4_2_3_3_1_2_1_2_5_2_2_1_2_2_3_3_3_2_6_4_5_3_3_3_5_2_4_4_2_5_6_4_2_5_2_1_2_2_2_3_3_3_2_5_2_4_4_6_2_5_6_4_7_2_6_5_2_5_1_5_4_5_4_7_6_2_2_6_6_6_3_1_2_4_6_1_4_2_4_1_4</t>
+  </si>
+  <si>
+    <t>1_1_3_3_2_2_5_1_2_2_4_2_1_1_1_2_2_1_3_2_2_5_1_2_2_2_1_1_2_6_4_4_4_5_4_2_3_1_1_3_1_1_4_5_1_1_6_2_1_6_1_5_1_2_2_2_3_2_5_2_1_3_3_2_2_3_6_3_1_1_2_1_1_6_3_3_2_1_1_1_1_1_5_5_3_1_4_4_3_1_1_1_4_1_1_1_1_2_1_1_1_2_3_5_3_5_3_4_3_3_2_2_2_2_2_4_4_4_4_1_4_4_4_2_2_2_5_1_3_2_4_5_2_1_1_3_3_4_1_1_5_3_3_3_2_3_3_3_3_3_5_5_1_2_1_1_4_1_4_4_1_1_2_6_1_2_2_2_1_4_2_3_4_2_2_1_1_1_3_6_6_3_3_1_4_3_3_1_2_3_2_5_2_5_2_2_1_5_6_1_4_1_2_3_3_2_1_1_3_3_3_2_1_3_2_2_4_2_1_5_3_3_1_2_1_1_3_3_3_3_3_3_1_1_1_2_2_3_3_1_6_3_2_2_4_1_5_2_2_2_2_6_3_3_1_3_1_1_4_2_1_3_2_4_3_2_5_5_2_6_4_3_2_1_1_5_5_1_4_3_5_2_4_4_2_4_2_2_5_2_6_6_2_5_6_1_3_3_3_2_4_4_3_1_2_6_5_1_1_1_3_4_1_1_1_6_2_2_3_4_2_1_6_1_5_2_4_5_5_4_4_1_4_5_4_1_3_2_1_1_4_4_1_3_5_1_1_5_1_6_6_6_6_6_1_4_2_1_1_4_3_2_4_1_4_4_2_3_3_3_2_3_1_1_4_3_2_4_1_3_2_2_1_1_4_1_2_6_1_4_1_1_4_4_1_2_4_1_4_2_4_5_1_1_3_5_3_2_2_2_1_1_5_1_4_2_6_2_6_1_1_1_5_1_1_6_3_2_3_4_3_3_1_2_2_2_6_1_2_4_2_4_1_1_3_2_4_1_3_1_2_6_3_4_1_3_1_1_5_1_2_5_1_5_4_6_2_3_1_1_1_1_1_2_4_3_3_1_2_1_3_2_2_4_3_3_1_3_2_1_1_2_1_1_5_3_3_3_1_1</t>
+  </si>
+  <si>
+    <t>1_1_2_5_1_3_2_2_2_3_3_6_4_1_6_2_3_2_3_1_4_4_4_2_5_5_6_3_7_5_1_4_3_5_1_2_4_5_5_7_4_3_2_2_5_7_3_4_3_3_5_1_2_5_3_1_2_4_4_2_2_1_4_4_2_5_2_1_3_6_1_1_2_5_1_1_1_1_5_7_3_3_5_2_3_6_1_5_1_3_3_5_6_2_1_1_3_1_1_4_3_3_1_2_3_2_4_1_2_1_2_3_4_2_6_1_6_1_4_3_6_6_3_1_3_1_4_5_2_1_2_1_6_2_1_6_4_1_4_5_1_3_1_5_1_3_1_1_4_1_5_1_2_7_7_1_2_7_1_1_6_3_1_1_1_4_2_7_3_1_2_1_1_7_5_2_3_2_6_1_1_5_4_1_3_1_1_3_1_3_3_3_1_5_5_2_5_1_6_6_1_7_1_3_2_1_2_2_6_2_7_1_3_1_1_4_3_4_6_3_2_1_1_5_6_4_1_2_3_4_1_4_5_4_6_1_2_2_3_5_2_6_2_6_6_4_2_5_6_1_1_2_1_4_5_1_1_1_1_3_3_5_5_4_5_6_6_6_4_5_7_4_1_4_4_3_6_6_1_4_3_1_2_5_1_4_2_2_2_2_1_1_1_3_1_7_1_2_6_3_5_2_5_3_1_2_1_6_4_2_3_1_2_1_6_1_3_3_3_2_3_3_3_4_1_1_2_5_1_6_5_5_2_2_4_2_5_5_2_6_1_2_7_2_4_3_2_5_2_2_3_5_3_2_2_4_7_6_5_6_4_2_4_2_5_1_6_4_5_7_4_3_4_7_5_2_5_4_2_6_2_2_6_1_5_1_5_2_4_1_6_5_3_3_6_3_3_2_2_2_2_5_1_2_2_1_1_2_5_1_1_1_5_1_3_6_2_6_3_2_2_6_5_5_3_1_2_4_2_5_6_2_6_6_4_3_2_2_3_6_6_7_1_4_4_2_2_1_3_2_3_3_1_2_3_1_4_4_2_2_1_2_3_1_1_4_5_4_1_6_3_2_4_3_2_1_2_3_1_3_3_4_7_6_5_2_2_4_5_5_1_5_5_6_2_2_1_1_5_3</t>
+  </si>
+  <si>
+    <t>7_7_7_7_1_7_1_1_1_1_7_7_1_1_1_1_1_1_7_1_1_1_7_7_1_1_1_1_1_1_1_1_1_7_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_7_1_1_7_1_1_1_1_1_1_1_1_1_1_1_1_1_7_7_1_7_1_1_1_1_1_1_1_7_1_1_1_1_1_1_1_1_1_1_1_7_7_1_1_1_1_1_1_1_7_1_1_7_7_1_7_1_1_1_1_1_1_1_1_1_1_7_1_1_1_1_1_7_1_1_1_7_1_1_1_1_7_1_1_7_7_1_7_7_1_1_1_1_1_1_7_1_1_7_1_7_1_1_1_1_7_7_1_1_1_1_1_1_1_1_1_7_1_1_1_1_7_7_1_1_1_7_1_1_1_1_1_1_7_1_1_1_7_7_7_1_1_7_1_1_1_1_1_7_1_1_1_1_1_7_1_1_1_1_1_1_1_7_1_1_1_1_1_1_1_1_7_7_7_7_1_7_1_1_1_7_7_1_1_7_1_1_1_1_7_1_7_1_7_1_1_1_1_1_1_1_1_1_1_1_1_7_7_1_1_1_1_1_1_7_1_1_1_1_1_1_7_1_7_1_1_1_1_1_7_1_7_1_1_1_7_7_1_1_1_1_1_7_1_7_1_1_1_1_7_1_1_1_1_7_1_1_1_1_1_1_1_1_1_7_1_1_1_1_1_1_1_7_1_7_7_1_7_7_1_1_1_7_7_1_1_1_1_1_7_1_1_1_1_1_1_1_1_7_1_1_1_1_7_1_7_1_1_1_1_7_1_1_1_7_7_1_1_1_7_1_7_1_1_7_1_1_1_1_7_1_1_1_1_1_1_1_1_1_1_1_7_7_1_1_1_1_1_7_1_1_1_1_1_1_1_7_7_1_1_1_1_1_7_1_1_1_1_1_1_1_1_1_1_1_1_7_1_1_1_1_1_1_1_1_1_1_7_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_7_1_1_1_1_1_7_1_1_1_1_7_1_1_1_7_1_7_1_1_1_1_7_1_7_7_7_1_7_1_1_1_7_7_1</t>
+  </si>
+  <si>
+    <t>7_7_7_7_2_7_2_2_2_2_7_7_2_2_2_2_2_2_7_2_2_2_7_7_2_2_2_2_2_2_2_2_2_7_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_7_2_2_7_2_2_2_2_2_2_2_2_2_2_2_2_2_7_7_2_7_2_2_2_2_2_2_2_7_2_2_2_2_2_2_2_2_2_2_2_7_7_2_2_2_2_2_2_2_7_2_2_7_7_2_7_2_2_2_2_2_2_2_2_2_2_7_2_2_2_2_2_7_2_2_2_7_2_2_2_2_7_2_2_7_7_2_7_7_2_2_2_2_2_2_7_2_2_7_2_7_2_2_2_2_7_7_2_2_2_2_2_2_2_2_2_7_2_2_2_2_7_7_2_2_2_7_2_2_2_2_2_2_7_2_2_2_7_7_7_2_2_7_2_2_2_2_2_7_2_2_2_2_2_7_2_2_2_2_2_2_2_7_2_2_2_2_2_2_2_2_7_7_7_7_2_7_2_2_2_7_7_2_2_7_2_2_2_2_7_2_7_2_7_2_2_2_2_2_2_2_2_2_2_2_2_7_7_2_2_2_2_2_2_7_2_2_2_2_2_2_7_2_7_2_2_2_2_2_7_2_7_2_2_2_7_7_2_2_2_2_2_7_2_7_2_2_2_2_7_2_2_2_2_7_2_2_2_2_2_2_2_2_2_7_2_2_2_2_2_2_2_7_2_7_7_2_7_7_2_2_2_7_7_2_2_2_2_2_7_2_2_2_2_2_2_2_2_7_2_2_2_2_7_2_7_2_2_2_2_7_2_2_2_7_7_2_2_2_7_2_7_2_2_7_2_2_2_2_7_2_2_2_2_2_2_2_2_2_2_2_7_7_2_2_2_2_2_7_2_2_2_2_2_2_2_7_7_2_2_2_2_2_7_2_2_2_2_2_2_2_2_2_2_2_2_7_2_2_2_2_2_2_2_2_2_2_7_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_7_2_2_2_2_2_7_2_2_2_2_7_2_2_2_7_2_7_2_2_2_2_7_2_7_7_7_2_7_2_2_2_7_7_2</t>
+  </si>
+  <si>
+    <t>7_7_7_7_3_7_3_3_3_3_7_7_3_3_3_3_3_3_7_3_3_3_7_7_3_3_3_3_3_3_3_3_3_7_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_7_3_3_7_3_3_3_3_3_3_3_3_3_3_3_3_3_7_7_3_7_3_3_3_3_3_3_3_7_3_3_3_3_3_3_3_3_3_3_3_7_7_3_3_3_3_3_3_3_7_3_3_7_7_3_7_3_3_3_3_3_3_3_3_3_3_7_3_3_3_3_3_7_3_3_3_7_3_3_3_3_7_3_3_7_7_3_7_7_3_3_3_3_3_3_7_3_3_7_3_7_3_3_3_3_7_7_3_3_3_3_3_3_3_3_3_7_3_3_3_3_7_7_3_3_3_7_3_3_3_3_3_3_7_3_3_3_7_7_7_3_3_7_3_3_3_3_3_7_3_3_3_3_3_7_3_3_3_3_3_3_3_7_3_3_3_3_3_3_3_3_7_7_7_7_3_7_3_3_3_7_7_3_3_7_3_3_3_3_7_3_7_3_7_3_3_3_3_3_3_3_3_3_3_3_3_7_7_3_3_3_3_3_3_7_3_3_3_3_3_3_7_3_7_3_3_3_3_3_7_3_7_3_3_3_7_7_3_3_3_3_3_7_3_7_3_3_3_3_7_3_3_3_3_7_3_3_3_3_3_3_3_3_3_7_3_3_3_3_3_3_3_7_3_7_7_3_7_7_3_3_3_7_7_3_3_3_3_3_7_3_3_3_3_3_3_3_3_7_3_3_3_3_7_3_7_3_3_3_3_7_3_3_3_7_7_3_3_3_7_3_7_3_3_7_3_3_3_3_7_3_3_3_3_3_3_3_3_3_3_3_7_7_3_3_3_3_3_7_3_3_3_3_3_3_3_7_7_3_3_3_3_3_7_3_3_3_3_3_3_3_3_3_3_3_3_7_3_3_3_3_3_3_3_3_3_3_7_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_7_3_3_3_3_3_7_3_3_3_3_7_3_3_3_7_3_7_3_3_3_3_7_3_7_7_7_3_7_3_3_3_7_7_3</t>
+  </si>
+  <si>
+    <t>7_7_7_7_4_7_4_4_4_4_7_7_4_4_4_4_4_4_7_4_4_4_7_7_4_4_4_4_4_4_4_4_4_7_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_7_4_4_7_4_4_4_4_4_4_4_4_4_4_4_4_4_7_7_4_7_4_4_4_4_4_4_4_7_4_4_4_4_4_4_4_4_4_4_4_7_7_4_4_4_4_4_4_4_7_4_4_7_7_4_7_4_4_4_4_4_4_4_4_4_4_7_4_4_4_4_4_7_4_4_4_7_4_4_4_4_7_4_4_7_7_4_7_7_4_4_4_4_4_4_7_4_4_7_4_7_4_4_4_4_7_7_4_4_4_4_4_4_4_4_4_7_4_4_4_4_7_7_4_4_4_7_4_4_4_4_4_4_7_4_4_4_7_7_7_4_4_7_4_4_4_4_4_7_4_4_4_4_4_7_4_4_4_4_4_4_4_7_4_4_4_4_4_4_4_4_7_7_7_7_4_7_4_4_4_7_7_4_4_7_4_4_4_4_7_4_7_4_7_4_4_4_4_4_4_4_4_4_4_4_4_7_7_4_4_4_4_4_4_7_4_4_4_4_4_4_7_4_7_4_4_4_4_4_7_4_7_4_4_4_7_7_4_4_4_4_4_7_4_7_4_4_4_4_7_4_4_4_4_7_4_4_4_4_4_4_4_4_4_7_4_4_4_4_4_4_4_7_4_7_7_4_7_7_4_4_4_7_7_4_4_4_4_4_7_4_4_4_4_4_4_4_4_7_4_4_4_4_7_4_7_4_4_4_4_7_4_4_4_7_7_4_4_4_7_4_7_4_4_7_4_4_4_4_7_4_4_4_4_4_4_4_4_4_4_4_7_7_4_4_4_4_4_7_4_4_4_4_4_4_4_7_7_4_4_4_4_4_7_4_4_4_4_4_4_4_4_4_4_4_4_7_4_4_4_4_4_4_4_4_4_4_7_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_7_4_4_4_4_4_7_4_4_4_4_7_4_4_4_7_4_7_4_4_4_4_7_4_7_7_7_4_7_4_4_4_7_7_4</t>
+  </si>
+  <si>
+    <t>7_7_7_7_5_7_5_5_5_5_7_7_5_5_5_5_5_5_7_5_5_5_7_7_5_5_5_5_5_5_5_5_5_7_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_7_5_5_7_5_5_5_5_5_5_5_5_5_5_5_5_5_7_7_5_7_5_5_5_5_5_5_5_7_5_5_5_5_5_5_5_5_5_5_5_7_7_5_5_5_5_5_5_5_7_5_5_7_7_5_7_5_5_5_5_5_5_5_5_5_5_7_5_5_5_5_5_7_5_5_5_7_5_5_5_5_7_5_5_7_7_5_7_7_5_5_5_5_5_5_7_5_5_7_5_7_5_5_5_5_7_7_5_5_5_5_5_5_5_5_5_7_5_5_5_5_7_7_5_5_5_7_5_5_5_5_5_5_7_5_5_5_7_7_7_5_5_7_5_5_5_5_5_7_5_5_5_5_5_7_5_5_5_5_5_5_5_7_5_5_5_5_5_5_5_5_7_7_7_7_5_7_5_5_5_7_7_5_5_7_5_5_5_5_7_5_7_5_7_5_5_5_5_5_5_5_5_5_5_5_5_7_7_5_5_5_5_5_5_7_5_5_5_5_5_5_7_5_7_5_5_5_5_5_7_5_7_5_5_5_7_7_5_5_5_5_5_7_5_7_5_5_5_5_7_5_5_5_5_7_5_5_5_5_5_5_5_5_5_7_5_5_5_5_5_5_5_7_5_7_7_5_7_7_5_5_5_7_7_5_5_5_5_5_7_5_5_5_5_5_5_5_5_7_5_5_5_5_7_5_7_5_5_5_5_7_5_5_5_7_7_5_5_5_7_5_7_5_5_7_5_5_5_5_7_5_5_5_5_5_5_5_5_5_5_5_7_7_5_5_5_5_5_7_5_5_5_5_5_5_5_7_7_5_5_5_5_5_7_5_5_5_5_5_5_5_5_5_5_5_5_7_5_5_5_5_5_5_5_5_5_5_7_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_7_5_5_5_5_5_7_5_5_5_5_7_5_5_5_7_5_7_5_5_5_5_7_5_7_7_7_5_7_5_5_5_7_7_5</t>
+  </si>
+  <si>
+    <t>7_7_7_7_6_7_6_6_6_6_7_7_6_6_6_6_6_6_7_6_6_6_7_7_6_6_6_6_6_6_6_6_6_7_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_7_6_6_7_6_6_6_6_6_6_6_6_6_6_6_6_6_7_7_6_7_6_6_6_6_6_6_6_7_6_6_6_6_6_6_6_6_6_6_6_7_7_6_6_6_6_6_6_6_7_6_6_7_7_6_7_6_6_6_6_6_6_6_6_6_6_7_6_6_6_6_6_7_6_6_6_7_6_6_6_6_7_6_6_7_7_6_7_7_6_6_6_6_6_6_7_6_6_7_6_7_6_6_6_6_7_7_6_6_6_6_6_6_6_6_6_7_6_6_6_6_7_7_6_6_6_7_6_6_6_6_6_6_7_6_6_6_7_7_7_6_6_7_6_6_6_6_6_7_6_6_6_6_6_7_6_6_6_6_6_6_6_7_6_6_6_6_6_6_6_6_7_7_7_7_6_7_6_6_6_7_7_6_6_7_6_6_6_6_7_6_7_6_7_6_6_6_6_6_6_6_6_6_6_6_6_7_7_6_6_6_6_6_6_7_6_6_6_6_6_6_7_6_7_6_6_6_6_6_7_6_7_6_6_6_7_7_6_6_6_6_6_7_6_7_6_6_6_6_7_6_6_6_6_7_6_6_6_6_6_6_6_6_6_7_6_6_6_6_6_6_6_7_6_7_7_6_7_7_6_6_6_7_7_6_6_6_6_6_7_6_6_6_6_6_6_6_6_7_6_6_6_6_7_6_7_6_6_6_6_7_6_6_6_7_7_6_6_6_7_6_7_6_6_7_6_6_6_6_7_6_6_6_6_6_6_6_6_6_6_6_7_7_6_6_6_6_6_7_6_6_6_6_6_6_6_7_7_6_6_6_6_6_7_6_6_6_6_6_6_6_6_6_6_6_6_7_6_6_6_6_6_6_6_6_6_6_7_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_7_6_6_6_6_6_7_6_6_6_6_7_6_6_6_7_6_7_6_6_6_6_7_6_7_7_7_6_7_6_6_6_7_7_6</t>
   </si>
 </sst>
 </file>
@@ -497,6 +561,11 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -504,11 +573,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1175,89 +1239,89 @@
   </cellStyleXfs>
   <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1785,19 +1849,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
-    <col min="2" max="2" width="9" style="6"/>
+    <col min="2" max="2" width="9" style="7"/>
     <col min="4" max="4" width="7.875" customWidth="1"/>
     <col min="5" max="5" width="28.75" customWidth="1"/>
     <col min="6" max="6" width="23.525" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
     <col min="8" max="8" width="22.5" customWidth="1"/>
     <col min="9" max="9" width="17.875" customWidth="1"/>
-    <col min="10" max="10" width="25.125" style="7" customWidth="1"/>
-    <col min="11" max="11" width="36.125" style="7" customWidth="1"/>
+    <col min="10" max="10" width="25.125" style="8" customWidth="1"/>
+    <col min="11" max="11" width="36.125" style="8" customWidth="1"/>
     <col min="13" max="13" width="12.625"/>
   </cols>
   <sheetData>
@@ -1805,59 +1869,59 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
     </row>
     <row r="2" ht="16.5" spans="1:11">
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J2" s="17"/>
@@ -1867,42 +1931,42 @@
       <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="J3" s="17"/>
       <c r="K3" s="17"/>
     </row>
     <row r="4" ht="16.5" spans="1:11">
-      <c r="B4" s="13"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="15"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="16"/>
       <c r="E4" s="18"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
       <c r="J4" s="17"/>
       <c r="K4" s="17"/>
     </row>
@@ -1911,28 +1975,28 @@
         <f t="shared" ref="A5:A56" si="0">C5*10+D5</f>
         <v>20010011</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="14">
         <v>100100</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="15">
         <v>2001001</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="16">
         <v>1</v>
       </c>
       <c r="E5" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="16" t="s">
+      <c r="F5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="16" t="s">
+      <c r="H5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J5" s="17"/>
@@ -1943,28 +2007,28 @@
         <f t="shared" si="0"/>
         <v>20010012</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="14">
         <v>100100</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="15">
         <v>2001001</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="16">
         <v>2</v>
       </c>
       <c r="E6" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="16" t="s">
+      <c r="F6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="16" t="s">
+      <c r="H6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J6" s="17"/>
@@ -1975,28 +2039,28 @@
         <f t="shared" si="0"/>
         <v>20010013</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="14">
         <v>100100</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="15">
         <v>2001001</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="16">
         <v>3</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="16" t="s">
+      <c r="F7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="16" t="s">
+      <c r="H7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>28</v>
       </c>
       <c r="J7" s="17"/>
@@ -2007,28 +2071,28 @@
         <f t="shared" si="0"/>
         <v>20010014</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="14">
         <v>100100</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="15">
         <v>2001001</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="16">
         <v>4</v>
       </c>
       <c r="E8" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="16" t="s">
+      <c r="F8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="16" t="s">
+      <c r="H8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>31</v>
       </c>
       <c r="J8" s="17"/>
@@ -2039,35 +2103,35 @@
         <f t="shared" si="0"/>
         <v>20010015</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="14">
         <v>100100</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="15">
         <v>2001001</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="16">
         <v>5</v>
       </c>
       <c r="E9" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="16" t="s">
+      <c r="F9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="16" t="s">
+      <c r="H9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
     </row>
-    <row r="10" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A10" s="1">
+    <row r="10" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>20030011</v>
       </c>
@@ -2080,25 +2144,25 @@
       <c r="D10" s="20">
         <v>1</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>35</v>
       </c>
       <c r="F10" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="H10" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A11" s="1">
+    <row r="11" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>20030012</v>
       </c>
@@ -2111,25 +2175,25 @@
       <c r="D11" s="20">
         <v>2</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>35</v>
       </c>
       <c r="F11" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H11" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="2" t="s">
         <v>40</v>
       </c>
       <c r="J11" s="21"/>
     </row>
-    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A12" s="1">
+    <row r="12" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>20030013</v>
       </c>
@@ -2142,25 +2206,25 @@
       <c r="D12" s="20">
         <v>3</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>35</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="2" t="s">
         <v>41</v>
       </c>
       <c r="H12" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="2" t="s">
         <v>42</v>
       </c>
       <c r="J12" s="21"/>
     </row>
-    <row r="13" s="2" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A13" s="2">
+    <row r="13" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>20030021</v>
       </c>
@@ -2173,25 +2237,25 @@
       <c r="D13" s="23">
         <v>1</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F13" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="3" t="s">
         <v>37</v>
       </c>
       <c r="H13" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="3" t="s">
         <v>37</v>
       </c>
       <c r="J13" s="24"/>
     </row>
-    <row r="14" s="2" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A14" s="2">
+    <row r="14" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>20030022</v>
       </c>
@@ -2204,25 +2268,25 @@
       <c r="D14" s="23">
         <v>2</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H14" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="3" t="s">
         <v>39</v>
       </c>
       <c r="J14" s="24"/>
     </row>
-    <row r="15" s="2" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A15" s="2">
+    <row r="15" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>20030023</v>
       </c>
@@ -2235,24 +2299,24 @@
       <c r="D15" s="23">
         <v>3</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F15" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="3" t="s">
         <v>43</v>
       </c>
       <c r="H15" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="3" t="s">
         <v>43</v>
       </c>
       <c r="J15" s="24"/>
     </row>
-    <row r="16" s="3" customFormat="1" ht="16.5" spans="1:11">
+    <row r="16" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>20070011</v>
@@ -2260,31 +2324,31 @@
       <c r="B16" s="25">
         <v>100700</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="15">
         <v>2007001</v>
       </c>
       <c r="D16" s="26">
         <v>1</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="F16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="H16" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="H16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I16" s="4" t="s">
         <v>46</v>
       </c>
       <c r="J16" s="17"/>
-      <c r="K16" s="7"/>
-    </row>
-    <row r="17" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="K16" s="8"/>
+    </row>
+    <row r="17" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>20070012</v>
@@ -2292,31 +2356,31 @@
       <c r="B17" s="25">
         <v>100700</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="15">
         <v>2007001</v>
       </c>
       <c r="D17" s="26">
         <v>2</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="F17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H17" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="H17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J17" s="17"/>
-      <c r="K17" s="7"/>
-    </row>
-    <row r="18" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="K17" s="8"/>
+    </row>
+    <row r="18" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>20070013</v>
@@ -2324,31 +2388,31 @@
       <c r="B18" s="25">
         <v>100700</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="15">
         <v>2007001</v>
       </c>
       <c r="D18" s="26">
         <v>3</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="F18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H18" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="H18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I18" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J18" s="17"/>
-      <c r="K18" s="7"/>
-    </row>
-    <row r="19" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>20070014</v>
@@ -2356,31 +2420,31 @@
       <c r="B19" s="25">
         <v>100700</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="15">
         <v>2007001</v>
       </c>
       <c r="D19" s="26">
         <v>4</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="F19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H19" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="H19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>55</v>
       </c>
       <c r="J19" s="17"/>
-      <c r="K19" s="7"/>
-    </row>
-    <row r="20" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="K19" s="8"/>
+    </row>
+    <row r="20" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>20070015</v>
@@ -2388,32 +2452,32 @@
       <c r="B20" s="25">
         <v>100700</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="15">
         <v>2007001</v>
       </c>
       <c r="D20" s="26">
         <v>5</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="F20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H20" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="H20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>58</v>
       </c>
       <c r="J20" s="17"/>
-      <c r="K20" s="7"/>
-    </row>
-    <row r="21" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A21" s="4">
+      <c r="K20" s="8"/>
+    </row>
+    <row r="21" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A21" s="5">
         <f t="shared" si="0"/>
         <v>20120011</v>
       </c>
@@ -2444,8 +2508,8 @@
       <c r="J21" s="29"/>
       <c r="K21" s="29"/>
     </row>
-    <row r="22" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A22" s="4">
+    <row r="22" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A22" s="5">
         <f t="shared" si="0"/>
         <v>20120012</v>
       </c>
@@ -2476,8 +2540,8 @@
       <c r="J22" s="29"/>
       <c r="K22" s="29"/>
     </row>
-    <row r="23" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A23" s="4">
+    <row r="23" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A23" s="5">
         <f t="shared" si="0"/>
         <v>20120013</v>
       </c>
@@ -2508,8 +2572,8 @@
       <c r="J23" s="29"/>
       <c r="K23" s="29"/>
     </row>
-    <row r="24" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A24" s="4">
+    <row r="24" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A24" s="5">
         <f t="shared" si="0"/>
         <v>20120014</v>
       </c>
@@ -2540,8 +2604,8 @@
       <c r="J24" s="29"/>
       <c r="K24" s="29"/>
     </row>
-    <row r="25" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A25" s="4">
+    <row r="25" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A25" s="5">
         <f t="shared" si="0"/>
         <v>20120015</v>
       </c>
@@ -2577,10 +2641,10 @@
         <f t="shared" si="0"/>
         <v>20140011</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="14">
         <v>101400</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="15">
         <v>2014001</v>
       </c>
       <c r="D26" s="18">
@@ -2589,13 +2653,13 @@
       <c r="E26" t="s">
         <v>44</v>
       </c>
-      <c r="F26" s="16" t="s">
+      <c r="F26" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G26" t="s">
         <v>70</v>
       </c>
-      <c r="H26" s="16" t="s">
+      <c r="H26" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I26" t="s">
@@ -2608,10 +2672,10 @@
         <f t="shared" si="0"/>
         <v>20140012</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="14">
         <v>101400</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="15">
         <v>2014001</v>
       </c>
       <c r="D27" s="18">
@@ -2620,13 +2684,13 @@
       <c r="E27" t="s">
         <v>44</v>
       </c>
-      <c r="F27" s="16" t="s">
+      <c r="F27" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G27" t="s">
         <v>72</v>
       </c>
-      <c r="H27" s="16" t="s">
+      <c r="H27" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I27" t="s">
@@ -2639,10 +2703,10 @@
         <f t="shared" si="0"/>
         <v>20140013</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="14">
         <v>101400</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="15">
         <v>2014001</v>
       </c>
       <c r="D28" s="18">
@@ -2651,13 +2715,13 @@
       <c r="E28" t="s">
         <v>44</v>
       </c>
-      <c r="F28" s="16" t="s">
+      <c r="F28" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G28" t="s">
         <v>73</v>
       </c>
-      <c r="H28" s="16" t="s">
+      <c r="H28" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I28" t="s">
@@ -2670,10 +2734,10 @@
         <f t="shared" si="0"/>
         <v>20140044</v>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="14">
         <v>101400</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="15">
         <v>2014004</v>
       </c>
       <c r="D29" s="18">
@@ -2682,30 +2746,30 @@
       <c r="E29" t="s">
         <v>44</v>
       </c>
-      <c r="F29" s="16" t="s">
+      <c r="F29" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G29" t="s">
         <v>74</v>
       </c>
-      <c r="H29" s="16" t="s">
+      <c r="H29" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I29" t="s">
         <v>71</v>
       </c>
       <c r="J29" s="17"/>
-      <c r="K29" s="7"/>
+      <c r="K29" s="8"/>
     </row>
     <row r="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>20140055</v>
       </c>
-      <c r="B30" s="13">
+      <c r="B30" s="14">
         <v>101400</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="15">
         <v>2014005</v>
       </c>
       <c r="D30" s="18">
@@ -2714,30 +2778,30 @@
       <c r="E30" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="16" t="s">
+      <c r="F30" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G30" t="s">
         <v>74</v>
       </c>
-      <c r="H30" s="16" t="s">
+      <c r="H30" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I30" t="s">
         <v>71</v>
       </c>
       <c r="J30" s="17"/>
-      <c r="K30" s="7"/>
+      <c r="K30" s="8"/>
     </row>
     <row r="31" ht="16.5" spans="1:11">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>20140066</v>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="14">
         <v>101400</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="15">
         <v>2014006</v>
       </c>
       <c r="D31" s="18">
@@ -2746,13 +2810,13 @@
       <c r="E31" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="16" t="s">
+      <c r="F31" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G31" t="s">
         <v>75</v>
       </c>
-      <c r="H31" s="16" t="s">
+      <c r="H31" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I31" t="s">
@@ -2765,10 +2829,10 @@
         <f t="shared" si="0"/>
         <v>20140077</v>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="14">
         <v>101400</v>
       </c>
-      <c r="C32" s="14">
+      <c r="C32" s="15">
         <v>2014007</v>
       </c>
       <c r="D32" s="18">
@@ -2777,14 +2841,14 @@
       <c r="E32" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="16" t="s">
+      <c r="F32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G32" t="str">
         <f t="shared" ref="G30:G34" si="1">G31</f>
         <v>1_10_10_10_10_1_2_2_1_3_3_3_1_10_10_10_1_4_4_4_4_1_8_8_1_12_1_10_1_5_5_5_5_1_6_6_6_6_6_6_6_1_4_1_10_10_1_7_1_12_1_4_4_1_4_4_4_1_6_6_1_6_6_6_6_6_6_6_6_6_6_6_6_6_6_1_8_1_9_1_9_9_9_9_9_9_9_9_9_1_6_6_6_6_6_1_8_1_2_1_9_9_1_12_1_9_1_8_8_8_8_8_8_1_7_7_7_7_1_8_8_8_8_8_8_8_8_8_1_2_2_2_1_7_7_7_1_6_6_6_6_6_6_6_1_3_3_3_3_1_5_5_5_5_1_8_8_8_1_12_1_2_1_5_5_1_10_1_8_1_3_3_3_3_3_3_3_3_3_3_1_6_6_1_8_8_8_8_8_8_8_1_10_10_1_2_2_2_2_2_2_2_1_2_2_1_8_1_7_7_1_7_7_1_11_11_11_11_1_7_7_1_5_1_2_1_2_1_6_6_6_6_6_6_6_6_1_11_11_11_1_3_3_3_1_6_1_12_1_9_1_5_5_5_1_12_1_2_2_1_9_9_9_1_12_1_11_11_11_1_7_7_7_7_7_7_1_2_2_2_2_1_8_8_8_1_10_10_1_7_1_3_1_5_5_1_4_4_1_11_1_5_5_5_5_5_5_5_1_7_1_8_8_8_1_4_4_4_4_4_4_4_1_12_1_11_11_11_11_11_11_1_2_1_4_4_4_4_4_4_1_11_11_11_11_11_1_9_9_9_9_1_9_9_9_9_9_9_1_5_1_8_8_8_8_1_4_1_4_1_8_8_8_1_11_11_11_11_11_11_11_11_1_9_9_1_8_1_8_8_8_1_12_1_12_1_11_11_11_11_1_5_5_5_5_5_5_5_1_3_3_3_1_11_1_2_2_1_2_2_2_1_2_2_2_2_2_2_2_2_1_9_9_9_9_9_9_9_1_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_1_11_11_11_11_1_10_1_4_4_4_4_4_4_4_4_4_4_1_4_4_4_4_1_3_1_9_9_1_10_10_10_10_10_10_10_1_10_1_12_1_7_1_3</v>
       </c>
-      <c r="H32" s="16" t="s">
+      <c r="H32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I32" t="s">
@@ -2797,10 +2861,10 @@
         <f t="shared" si="0"/>
         <v>20140088</v>
       </c>
-      <c r="B33" s="13">
+      <c r="B33" s="14">
         <v>101400</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="15">
         <v>2014008</v>
       </c>
       <c r="D33" s="18">
@@ -2809,14 +2873,14 @@
       <c r="E33" t="s">
         <v>44</v>
       </c>
-      <c r="F33" s="16" t="s">
+      <c r="F33" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G33" t="str">
         <f t="shared" si="1"/>
         <v>1_10_10_10_10_1_2_2_1_3_3_3_1_10_10_10_1_4_4_4_4_1_8_8_1_12_1_10_1_5_5_5_5_1_6_6_6_6_6_6_6_1_4_1_10_10_1_7_1_12_1_4_4_1_4_4_4_1_6_6_1_6_6_6_6_6_6_6_6_6_6_6_6_6_6_1_8_1_9_1_9_9_9_9_9_9_9_9_9_1_6_6_6_6_6_1_8_1_2_1_9_9_1_12_1_9_1_8_8_8_8_8_8_1_7_7_7_7_1_8_8_8_8_8_8_8_8_8_1_2_2_2_1_7_7_7_1_6_6_6_6_6_6_6_1_3_3_3_3_1_5_5_5_5_1_8_8_8_1_12_1_2_1_5_5_1_10_1_8_1_3_3_3_3_3_3_3_3_3_3_1_6_6_1_8_8_8_8_8_8_8_1_10_10_1_2_2_2_2_2_2_2_1_2_2_1_8_1_7_7_1_7_7_1_11_11_11_11_1_7_7_1_5_1_2_1_2_1_6_6_6_6_6_6_6_6_1_11_11_11_1_3_3_3_1_6_1_12_1_9_1_5_5_5_1_12_1_2_2_1_9_9_9_1_12_1_11_11_11_1_7_7_7_7_7_7_1_2_2_2_2_1_8_8_8_1_10_10_1_7_1_3_1_5_5_1_4_4_1_11_1_5_5_5_5_5_5_5_1_7_1_8_8_8_1_4_4_4_4_4_4_4_1_12_1_11_11_11_11_11_11_1_2_1_4_4_4_4_4_4_1_11_11_11_11_11_1_9_9_9_9_1_9_9_9_9_9_9_1_5_1_8_8_8_8_1_4_1_4_1_8_8_8_1_11_11_11_11_11_11_11_11_1_9_9_1_8_1_8_8_8_1_12_1_12_1_11_11_11_11_1_5_5_5_5_5_5_5_1_3_3_3_1_11_1_2_2_1_2_2_2_1_2_2_2_2_2_2_2_2_1_9_9_9_9_9_9_9_1_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_1_11_11_11_11_1_10_1_4_4_4_4_4_4_4_4_4_4_1_4_4_4_4_1_3_1_9_9_1_10_10_10_10_10_10_10_1_10_1_12_1_7_1_3</v>
       </c>
-      <c r="H33" s="16" t="s">
+      <c r="H33" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I33" t="s">
@@ -2829,10 +2893,10 @@
         <f t="shared" si="0"/>
         <v>20140099</v>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="14">
         <v>101400</v>
       </c>
-      <c r="C34" s="14">
+      <c r="C34" s="15">
         <v>2014009</v>
       </c>
       <c r="D34" s="18">
@@ -2841,31 +2905,31 @@
       <c r="E34" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="16" t="s">
+      <c r="F34" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G34" t="str">
         <f t="shared" si="1"/>
         <v>1_10_10_10_10_1_2_2_1_3_3_3_1_10_10_10_1_4_4_4_4_1_8_8_1_12_1_10_1_5_5_5_5_1_6_6_6_6_6_6_6_1_4_1_10_10_1_7_1_12_1_4_4_1_4_4_4_1_6_6_1_6_6_6_6_6_6_6_6_6_6_6_6_6_6_1_8_1_9_1_9_9_9_9_9_9_9_9_9_1_6_6_6_6_6_1_8_1_2_1_9_9_1_12_1_9_1_8_8_8_8_8_8_1_7_7_7_7_1_8_8_8_8_8_8_8_8_8_1_2_2_2_1_7_7_7_1_6_6_6_6_6_6_6_1_3_3_3_3_1_5_5_5_5_1_8_8_8_1_12_1_2_1_5_5_1_10_1_8_1_3_3_3_3_3_3_3_3_3_3_1_6_6_1_8_8_8_8_8_8_8_1_10_10_1_2_2_2_2_2_2_2_1_2_2_1_8_1_7_7_1_7_7_1_11_11_11_11_1_7_7_1_5_1_2_1_2_1_6_6_6_6_6_6_6_6_1_11_11_11_1_3_3_3_1_6_1_12_1_9_1_5_5_5_1_12_1_2_2_1_9_9_9_1_12_1_11_11_11_1_7_7_7_7_7_7_1_2_2_2_2_1_8_8_8_1_10_10_1_7_1_3_1_5_5_1_4_4_1_11_1_5_5_5_5_5_5_5_1_7_1_8_8_8_1_4_4_4_4_4_4_4_1_12_1_11_11_11_11_11_11_1_2_1_4_4_4_4_4_4_1_11_11_11_11_11_1_9_9_9_9_1_9_9_9_9_9_9_1_5_1_8_8_8_8_1_4_1_4_1_8_8_8_1_11_11_11_11_11_11_11_11_1_9_9_1_8_1_8_8_8_1_12_1_12_1_11_11_11_11_1_5_5_5_5_5_5_5_1_3_3_3_1_11_1_2_2_1_2_2_2_1_2_2_2_2_2_2_2_2_1_9_9_9_9_9_9_9_1_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_1_11_11_11_11_1_10_1_4_4_4_4_4_4_4_4_4_4_1_4_4_4_4_1_3_1_9_9_1_10_10_10_10_10_10_10_1_10_1_12_1_7_1_3</v>
       </c>
-      <c r="H34" s="16" t="s">
+      <c r="H34" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I34" t="s">
         <v>71</v>
       </c>
       <c r="J34" s="17"/>
-      <c r="K34" s="7"/>
+      <c r="K34" s="8"/>
     </row>
     <row r="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>20140110</v>
       </c>
-      <c r="B35" s="13">
+      <c r="B35" s="14">
         <v>101400</v>
       </c>
-      <c r="C35" s="14">
+      <c r="C35" s="15">
         <v>2014010</v>
       </c>
       <c r="D35" s="18">
@@ -2874,30 +2938,30 @@
       <c r="E35" t="s">
         <v>44</v>
       </c>
-      <c r="F35" s="16" t="s">
+      <c r="F35" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G35" t="s">
         <v>76</v>
       </c>
-      <c r="H35" s="16" t="s">
+      <c r="H35" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I35" t="s">
         <v>71</v>
       </c>
       <c r="J35" s="17"/>
-      <c r="K35" s="7"/>
+      <c r="K35" s="8"/>
     </row>
     <row r="36" customFormat="1" ht="16.5" spans="1:11">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>20140121</v>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="14">
         <v>101400</v>
       </c>
-      <c r="C36" s="14">
+      <c r="C36" s="15">
         <v>2014011</v>
       </c>
       <c r="D36" s="18">
@@ -2906,48 +2970,48 @@
       <c r="E36" t="s">
         <v>44</v>
       </c>
-      <c r="F36" s="16" t="s">
+      <c r="F36" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G36" t="s">
         <v>77</v>
       </c>
-      <c r="H36" s="16" t="s">
+      <c r="H36" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I36" t="s">
         <v>71</v>
       </c>
       <c r="J36" s="17"/>
-      <c r="K36" s="7"/>
+      <c r="K36" s="8"/>
     </row>
     <row r="37" ht="16.5" spans="1:11">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>20240011</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="14">
         <v>102400</v>
       </c>
-      <c r="C37" s="14">
+      <c r="C37" s="15">
         <v>2024001</v>
       </c>
-      <c r="D37" s="15">
+      <c r="D37" s="16">
         <v>1</v>
       </c>
       <c r="E37" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="F37" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G37" s="16" t="s">
+      <c r="F37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H37" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I37" s="16" t="s">
+      <c r="H37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J37" s="17"/>
@@ -2958,28 +3022,28 @@
         <f t="shared" si="0"/>
         <v>20240012</v>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="14">
         <v>102400</v>
       </c>
-      <c r="C38" s="14">
+      <c r="C38" s="15">
         <v>2024001</v>
       </c>
-      <c r="D38" s="15">
+      <c r="D38" s="16">
         <v>2</v>
       </c>
       <c r="E38" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="F38" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38" s="16" t="s">
+      <c r="F38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H38" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I38" s="16" t="s">
+      <c r="H38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J38" s="17"/>
@@ -2990,28 +3054,28 @@
         <f t="shared" si="0"/>
         <v>20240013</v>
       </c>
-      <c r="B39" s="13">
+      <c r="B39" s="14">
         <v>102400</v>
       </c>
-      <c r="C39" s="14">
+      <c r="C39" s="15">
         <v>2024001</v>
       </c>
-      <c r="D39" s="15">
+      <c r="D39" s="16">
         <v>3</v>
       </c>
       <c r="E39" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="F39" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G39" s="16" t="s">
+      <c r="F39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H39" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I39" s="16" t="s">
+      <c r="H39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I39" s="1" t="s">
         <v>28</v>
       </c>
       <c r="J39" s="17"/>
@@ -3022,28 +3086,28 @@
         <f t="shared" si="0"/>
         <v>20240014</v>
       </c>
-      <c r="B40" s="13">
+      <c r="B40" s="14">
         <v>102400</v>
       </c>
-      <c r="C40" s="14">
+      <c r="C40" s="15">
         <v>2024001</v>
       </c>
-      <c r="D40" s="15">
+      <c r="D40" s="16">
         <v>4</v>
       </c>
       <c r="E40" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F40" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G40" s="16" t="s">
+      <c r="F40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H40" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I40" s="16" t="s">
+      <c r="H40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I40" s="1" t="s">
         <v>31</v>
       </c>
       <c r="J40" s="17"/>
@@ -3054,35 +3118,35 @@
         <f t="shared" si="0"/>
         <v>20240015</v>
       </c>
-      <c r="B41" s="13">
+      <c r="B41" s="14">
         <v>102400</v>
       </c>
-      <c r="C41" s="14">
+      <c r="C41" s="15">
         <v>2024001</v>
       </c>
-      <c r="D41" s="15">
+      <c r="D41" s="16">
         <v>5</v>
       </c>
       <c r="E41" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F41" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G41" s="16" t="s">
+      <c r="F41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H41" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I41" s="16" t="s">
+      <c r="H41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="17"/>
     </row>
-    <row r="42" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A42" s="5">
+    <row r="42" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A42" s="6">
         <f t="shared" si="0"/>
         <v>20170011</v>
       </c>
@@ -3095,26 +3159,26 @@
       <c r="D42" s="31">
         <v>1</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G42" s="5" t="s">
+      <c r="F42" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H42" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I42" s="5" t="s">
+      <c r="H42" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I42" s="6" t="s">
         <v>46</v>
       </c>
       <c r="J42" s="32"/>
       <c r="K42" s="32"/>
     </row>
-    <row r="43" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A43" s="5">
+    <row r="43" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A43" s="6">
         <f t="shared" si="0"/>
         <v>20170012</v>
       </c>
@@ -3127,26 +3191,26 @@
       <c r="D43" s="31">
         <v>2</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F43" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G43" s="5" t="s">
+      <c r="F43" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G43" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="H43" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I43" s="5" t="s">
+      <c r="H43" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I43" s="6" t="s">
         <v>49</v>
       </c>
       <c r="J43" s="32"/>
       <c r="K43" s="32"/>
     </row>
-    <row r="44" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A44" s="5">
+    <row r="44" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A44" s="6">
         <f t="shared" si="0"/>
         <v>20170013</v>
       </c>
@@ -3159,26 +3223,26 @@
       <c r="D44" s="31">
         <v>3</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F44" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G44" s="5" t="s">
+      <c r="F44" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="H44" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I44" s="5" t="s">
+      <c r="H44" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I44" s="6" t="s">
         <v>52</v>
       </c>
       <c r="J44" s="32"/>
       <c r="K44" s="32"/>
     </row>
-    <row r="45" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A45" s="5">
+    <row r="45" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A45" s="6">
         <f t="shared" si="0"/>
         <v>20170014</v>
       </c>
@@ -3191,26 +3255,26 @@
       <c r="D45" s="31">
         <v>4</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F45" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G45" s="5" t="s">
+      <c r="F45" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G45" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="H45" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I45" s="5" t="s">
+      <c r="H45" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I45" s="6" t="s">
         <v>55</v>
       </c>
       <c r="J45" s="32"/>
       <c r="K45" s="32"/>
     </row>
-    <row r="46" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A46" s="5">
+    <row r="46" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A46" s="6">
         <f t="shared" si="0"/>
         <v>20170015</v>
       </c>
@@ -3223,190 +3287,190 @@
       <c r="D46" s="31">
         <v>5</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F46" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G46" s="5" t="s">
+      <c r="F46" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="H46" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I46" s="5" t="s">
+      <c r="H46" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I46" s="6" t="s">
         <v>58</v>
       </c>
       <c r="J46" s="32"/>
       <c r="K46" s="32"/>
     </row>
-    <row r="47" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A47" s="5">
+    <row r="47" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A47" s="6">
         <f t="shared" si="0"/>
         <v>20220011</v>
       </c>
-      <c r="B47" s="13">
+      <c r="B47" s="14">
         <v>102200</v>
       </c>
-      <c r="C47" s="14">
+      <c r="C47" s="15">
         <v>2022001</v>
       </c>
-      <c r="D47" s="15">
+      <c r="D47" s="16">
         <v>1</v>
       </c>
       <c r="E47" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F47" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G47" s="16" t="s">
+      <c r="F47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H47" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I47" s="16" t="s">
+      <c r="H47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>79</v>
       </c>
       <c r="J47" s="17"/>
       <c r="K47" s="17"/>
     </row>
-    <row r="48" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A48" s="5">
+    <row r="48" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A48" s="6">
         <f t="shared" si="0"/>
         <v>20220012</v>
       </c>
-      <c r="B48" s="13">
+      <c r="B48" s="14">
         <v>102200</v>
       </c>
-      <c r="C48" s="14">
+      <c r="C48" s="15">
         <v>2022001</v>
       </c>
-      <c r="D48" s="15">
+      <c r="D48" s="16">
         <v>2</v>
       </c>
       <c r="E48" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F48" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G48" s="16" t="s">
+      <c r="F48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H48" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I48" s="16" t="s">
+      <c r="H48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" s="1" t="s">
         <v>79</v>
       </c>
       <c r="J48" s="17"/>
       <c r="K48" s="17"/>
     </row>
-    <row r="49" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A49" s="5">
+    <row r="49" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A49" s="6">
         <f t="shared" si="0"/>
         <v>20220013</v>
       </c>
-      <c r="B49" s="13">
+      <c r="B49" s="14">
         <v>102200</v>
       </c>
-      <c r="C49" s="14">
+      <c r="C49" s="15">
         <v>2022001</v>
       </c>
-      <c r="D49" s="15">
+      <c r="D49" s="16">
         <v>3</v>
       </c>
       <c r="E49" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="F49" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G49" s="16" t="s">
+      <c r="F49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H49" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I49" s="16" t="s">
+      <c r="H49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" s="1" t="s">
         <v>79</v>
       </c>
       <c r="J49" s="17"/>
       <c r="K49" s="17"/>
     </row>
-    <row r="50" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A50" s="5">
+    <row r="50" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A50" s="6">
         <f t="shared" si="0"/>
         <v>20220014</v>
       </c>
-      <c r="B50" s="13">
+      <c r="B50" s="14">
         <v>102200</v>
       </c>
-      <c r="C50" s="14">
+      <c r="C50" s="15">
         <v>2022001</v>
       </c>
-      <c r="D50" s="15">
+      <c r="D50" s="16">
         <v>4</v>
       </c>
       <c r="E50" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="F50" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G50" s="16" t="s">
+      <c r="F50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H50" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I50" s="16" t="s">
+      <c r="H50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I50" s="1" t="s">
         <v>79</v>
       </c>
       <c r="J50" s="17"/>
       <c r="K50" s="17"/>
     </row>
-    <row r="51" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A51" s="5">
+    <row r="51" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A51" s="6">
         <f t="shared" si="0"/>
         <v>20220015</v>
       </c>
-      <c r="B51" s="13">
+      <c r="B51" s="14">
         <v>102200</v>
       </c>
-      <c r="C51" s="14">
+      <c r="C51" s="15">
         <v>2022001</v>
       </c>
-      <c r="D51" s="15">
+      <c r="D51" s="16">
         <v>5</v>
       </c>
       <c r="E51" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="F51" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G51" s="16" t="s">
+      <c r="F51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G51" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="H51" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I51" s="16" t="s">
+      <c r="H51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" s="1" t="s">
         <v>79</v>
       </c>
       <c r="J51" s="17"/>
       <c r="K51" s="17"/>
     </row>
-    <row r="52" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A52" s="5">
+    <row r="52" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A52" s="6">
         <f t="shared" si="0"/>
         <v>20210011</v>
       </c>
-      <c r="B52" s="13">
+      <c r="B52" s="14">
         <v>102100</v>
       </c>
       <c r="C52" s="33">
@@ -3418,27 +3482,27 @@
       <c r="E52" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="F52" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G52" s="16" t="s">
+      <c r="F52" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G52" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H52" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I52" s="16" t="s">
+      <c r="H52" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I52" s="1" t="s">
         <v>89</v>
       </c>
       <c r="J52" s="17"/>
       <c r="K52" s="17"/>
     </row>
-    <row r="53" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A53" s="5">
+    <row r="53" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A53" s="6">
         <f t="shared" si="0"/>
         <v>20210012</v>
       </c>
-      <c r="B53" s="13">
+      <c r="B53" s="14">
         <v>102100</v>
       </c>
       <c r="C53" s="33">
@@ -3450,27 +3514,27 @@
       <c r="E53" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F53" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G53" s="16" t="s">
+      <c r="F53" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H53" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I53" s="16" t="s">
+      <c r="H53" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I53" s="1" t="s">
         <v>91</v>
       </c>
       <c r="J53" s="17"/>
       <c r="K53" s="17"/>
     </row>
-    <row r="54" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A54" s="5">
+    <row r="54" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A54" s="6">
         <f t="shared" si="0"/>
         <v>20210013</v>
       </c>
-      <c r="B54" s="13">
+      <c r="B54" s="14">
         <v>102100</v>
       </c>
       <c r="C54" s="33">
@@ -3482,27 +3546,27 @@
       <c r="E54" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F54" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G54" s="16" t="s">
+      <c r="F54" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H54" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I54" s="16" t="s">
+      <c r="H54" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I54" s="1" t="s">
         <v>93</v>
       </c>
       <c r="J54" s="17"/>
       <c r="K54" s="17"/>
     </row>
-    <row r="55" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A55" s="5">
+    <row r="55" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A55" s="6">
         <f t="shared" si="0"/>
         <v>20210014</v>
       </c>
-      <c r="B55" s="13">
+      <c r="B55" s="14">
         <v>102100</v>
       </c>
       <c r="C55" s="33">
@@ -3514,27 +3578,27 @@
       <c r="E55" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="F55" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G55" s="16" t="s">
+      <c r="F55" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="H55" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I55" s="16" t="s">
+      <c r="H55" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I55" s="1" t="s">
         <v>95</v>
       </c>
       <c r="J55" s="17"/>
       <c r="K55" s="17"/>
     </row>
-    <row r="56" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A56" s="5">
+    <row r="56" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A56" s="6">
         <f t="shared" si="0"/>
         <v>20210015</v>
       </c>
-      <c r="B56" s="13">
+      <c r="B56" s="14">
         <v>102100</v>
       </c>
       <c r="C56" s="33">
@@ -3546,27 +3610,27 @@
       <c r="E56" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="F56" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G56" s="16" t="s">
+      <c r="F56" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G56" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="H56" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I56" s="16" t="s">
+      <c r="H56" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I56" s="1" t="s">
         <v>97</v>
       </c>
       <c r="J56" s="17"/>
       <c r="K56" s="17"/>
     </row>
-    <row r="57" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A57" s="5">
-        <f t="shared" ref="A57:A67" si="2">C57*10+D57</f>
+    <row r="57" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A57" s="6">
+        <f t="shared" ref="A57:A72" si="2">C57*10+D57</f>
         <v>20180011</v>
       </c>
-      <c r="B57" s="13">
+      <c r="B57" s="14">
         <v>101800</v>
       </c>
       <c r="C57" s="33">
@@ -3578,27 +3642,27 @@
       <c r="E57" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F57" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G57" s="16" t="s">
+      <c r="F57" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H57" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I57" s="16" t="s">
+      <c r="H57" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I57" s="1" t="s">
         <v>99</v>
       </c>
       <c r="J57" s="17"/>
       <c r="K57" s="17"/>
     </row>
-    <row r="58" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A58" s="5">
+    <row r="58" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A58" s="6">
         <f t="shared" si="2"/>
         <v>20180012</v>
       </c>
-      <c r="B58" s="13">
+      <c r="B58" s="14">
         <v>101800</v>
       </c>
       <c r="C58" s="33">
@@ -3610,27 +3674,27 @@
       <c r="E58" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="F58" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G58" s="16" t="s">
+      <c r="F58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G58" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H58" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I58" s="16" t="s">
+      <c r="H58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>101</v>
       </c>
       <c r="J58" s="17"/>
       <c r="K58" s="17"/>
     </row>
-    <row r="59" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A59" s="5">
+    <row r="59" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A59" s="6">
         <f t="shared" si="2"/>
         <v>20180013</v>
       </c>
-      <c r="B59" s="13">
+      <c r="B59" s="14">
         <v>101800</v>
       </c>
       <c r="C59" s="33">
@@ -3642,27 +3706,27 @@
       <c r="E59" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F59" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G59" s="16" t="s">
+      <c r="F59" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G59" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="H59" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I59" s="16" t="s">
+      <c r="H59" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>103</v>
       </c>
       <c r="J59" s="17"/>
       <c r="K59" s="17"/>
     </row>
-    <row r="60" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A60" s="5">
+    <row r="60" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A60" s="6">
         <f t="shared" si="2"/>
         <v>20180014</v>
       </c>
-      <c r="B60" s="13">
+      <c r="B60" s="14">
         <v>101800</v>
       </c>
       <c r="C60" s="33">
@@ -3674,27 +3738,27 @@
       <c r="E60" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="F60" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G60" s="16" t="s">
+      <c r="F60" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H60" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I60" s="16" t="s">
+      <c r="H60" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60" s="1" t="s">
         <v>105</v>
       </c>
       <c r="J60" s="17"/>
       <c r="K60" s="17"/>
     </row>
-    <row r="61" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A61" s="5">
+    <row r="61" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A61" s="6">
         <f t="shared" si="2"/>
         <v>20180015</v>
       </c>
-      <c r="B61" s="13">
+      <c r="B61" s="14">
         <v>101800</v>
       </c>
       <c r="C61" s="33">
@@ -3706,27 +3770,27 @@
       <c r="E61" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="F61" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G61" s="16" t="s">
+      <c r="F61" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G61" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="H61" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I61" s="16" t="s">
+      <c r="H61" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I61" s="1" t="s">
         <v>108</v>
       </c>
       <c r="J61" s="17"/>
       <c r="K61" s="17"/>
     </row>
-    <row r="62" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A62" s="5">
+    <row r="62" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A62" s="6">
         <f t="shared" si="2"/>
         <v>20180016</v>
       </c>
-      <c r="B62" s="13">
+      <c r="B62" s="14">
         <v>101800</v>
       </c>
       <c r="C62" s="33">
@@ -3738,27 +3802,27 @@
       <c r="E62" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="F62" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G62" s="16" t="s">
+      <c r="F62" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G62" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="H62" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I62" s="16" t="s">
+      <c r="H62" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I62" s="1" t="s">
         <v>111</v>
       </c>
       <c r="J62" s="17"/>
       <c r="K62" s="17"/>
     </row>
-    <row r="63" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A63" s="5">
+    <row r="63" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A63" s="6">
         <f t="shared" si="2"/>
         <v>20250011</v>
       </c>
-      <c r="B63" s="13">
+      <c r="B63" s="14">
         <v>102500</v>
       </c>
       <c r="C63" s="33">
@@ -3770,27 +3834,27 @@
       <c r="E63" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="F63" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G63" s="16" t="s">
+      <c r="F63" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G63" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H63" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I63" s="16" t="s">
+      <c r="H63" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I63" s="1" t="s">
         <v>113</v>
       </c>
       <c r="J63" s="17"/>
       <c r="K63" s="17"/>
     </row>
-    <row r="64" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A64" s="5">
+    <row r="64" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A64" s="6">
         <f t="shared" si="2"/>
         <v>20250012</v>
       </c>
-      <c r="B64" s="13">
+      <c r="B64" s="14">
         <v>102500</v>
       </c>
       <c r="C64" s="33">
@@ -3802,27 +3866,27 @@
       <c r="E64" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F64" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G64" s="16" t="s">
+      <c r="F64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G64" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H64" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I64" s="16" t="s">
+      <c r="H64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I64" s="1" t="s">
         <v>115</v>
       </c>
       <c r="J64" s="17"/>
       <c r="K64" s="17"/>
     </row>
-    <row r="65" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A65" s="5">
+    <row r="65" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A65" s="6">
         <f t="shared" si="2"/>
         <v>20250013</v>
       </c>
-      <c r="B65" s="13">
+      <c r="B65" s="14">
         <v>102500</v>
       </c>
       <c r="C65" s="33">
@@ -3834,27 +3898,27 @@
       <c r="E65" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F65" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G65" s="16" t="s">
+      <c r="F65" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G65" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H65" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I65" s="16" t="s">
+      <c r="H65" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I65" s="1" t="s">
         <v>117</v>
       </c>
       <c r="J65" s="17"/>
       <c r="K65" s="17"/>
     </row>
-    <row r="66" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A66" s="5">
+    <row r="66" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A66" s="6">
         <f t="shared" si="2"/>
         <v>20250014</v>
       </c>
-      <c r="B66" s="13">
+      <c r="B66" s="14">
         <v>102500</v>
       </c>
       <c r="C66" s="33">
@@ -3866,27 +3930,27 @@
       <c r="E66" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="F66" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G66" s="16" t="s">
+      <c r="F66" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="H66" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I66" s="16" t="s">
+      <c r="H66" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" s="1" t="s">
         <v>119</v>
       </c>
       <c r="J66" s="17"/>
       <c r="K66" s="17"/>
     </row>
-    <row r="67" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A67" s="5">
+    <row r="67" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A67" s="6">
         <f t="shared" si="2"/>
         <v>20250015</v>
       </c>
-      <c r="B67" s="13">
+      <c r="B67" s="14">
         <v>102500</v>
       </c>
       <c r="C67" s="33">
@@ -3898,27 +3962,27 @@
       <c r="E67" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="F67" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G67" s="16" t="s">
+      <c r="F67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G67" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H67" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I67" s="16" t="s">
+      <c r="H67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I67" s="1" t="s">
         <v>121</v>
       </c>
       <c r="J67" s="17"/>
       <c r="K67" s="17"/>
     </row>
-    <row r="68" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A68" s="5">
-        <f>C68*10+D68</f>
+    <row r="68" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A68" s="6">
+        <f t="shared" si="2"/>
         <v>20230011</v>
       </c>
-      <c r="B68" s="13">
+      <c r="B68" s="14">
         <v>102300</v>
       </c>
       <c r="C68" s="33">
@@ -3930,27 +3994,27 @@
       <c r="E68" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="F68" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G68" s="16" t="s">
+      <c r="F68" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H68" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I68" s="16" t="s">
+      <c r="H68" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I68" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J68" s="17"/>
       <c r="K68" s="17"/>
     </row>
-    <row r="69" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A69" s="5">
-        <f>C69*10+D69</f>
+    <row r="69" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A69" s="6">
+        <f t="shared" si="2"/>
         <v>20230012</v>
       </c>
-      <c r="B69" s="13">
+      <c r="B69" s="14">
         <v>102300</v>
       </c>
       <c r="C69" s="33">
@@ -3962,27 +4026,27 @@
       <c r="E69" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F69" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G69" s="16" t="s">
+      <c r="F69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G69" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H69" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I69" s="16" t="s">
+      <c r="H69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I69" s="1" t="s">
         <v>125</v>
       </c>
       <c r="J69" s="17"/>
       <c r="K69" s="17"/>
     </row>
-    <row r="70" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A70" s="5">
-        <f>C70*10+D70</f>
+    <row r="70" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A70" s="6">
+        <f t="shared" si="2"/>
         <v>20230013</v>
       </c>
-      <c r="B70" s="13">
+      <c r="B70" s="14">
         <v>102300</v>
       </c>
       <c r="C70" s="33">
@@ -3994,27 +4058,27 @@
       <c r="E70" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="F70" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G70" s="16" t="s">
+      <c r="F70" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G70" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="H70" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I70" s="16" t="s">
+      <c r="H70" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I70" s="1" t="s">
         <v>127</v>
       </c>
       <c r="J70" s="17"/>
       <c r="K70" s="17"/>
     </row>
-    <row r="71" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A71" s="5">
-        <f>C71*10+D71</f>
+    <row r="71" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A71" s="6">
+        <f t="shared" si="2"/>
         <v>20230014</v>
       </c>
-      <c r="B71" s="13">
+      <c r="B71" s="14">
         <v>102300</v>
       </c>
       <c r="C71" s="33">
@@ -4026,27 +4090,27 @@
       <c r="E71" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="F71" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G71" s="16" t="s">
+      <c r="F71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G71" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="H71" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I71" s="16" t="s">
+      <c r="H71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I71" s="1" t="s">
         <v>129</v>
       </c>
       <c r="J71" s="17"/>
       <c r="K71" s="17"/>
     </row>
-    <row r="72" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A72" s="5">
-        <f>C72*10+D72</f>
+    <row r="72" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A72" s="6">
+        <f t="shared" si="2"/>
         <v>20230015</v>
       </c>
-      <c r="B72" s="13">
+      <c r="B72" s="14">
         <v>102300</v>
       </c>
       <c r="C72" s="33">
@@ -4058,24 +4122,615 @@
       <c r="E72" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="F72" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G72" s="16" t="s">
+      <c r="F72" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G72" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="H72" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I72" s="16" t="s">
+      <c r="H72" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I72" s="1" t="s">
         <v>131</v>
       </c>
       <c r="J72" s="17"/>
       <c r="K72" s="17"/>
+    </row>
+    <row r="73" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A73" s="6">
+        <f t="shared" ref="A73:A80" si="3">C73*10+D73</f>
+        <v>20230016</v>
+      </c>
+      <c r="B73" s="14">
+        <v>102300</v>
+      </c>
+      <c r="C73" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D73" s="33">
+        <v>6</v>
+      </c>
+      <c r="E73" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J73" s="17"/>
+      <c r="K73" s="17"/>
+    </row>
+    <row r="74" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A74" s="6">
+        <f t="shared" si="3"/>
+        <v>20230017</v>
+      </c>
+      <c r="B74" s="14">
+        <v>102300</v>
+      </c>
+      <c r="C74" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D74" s="33">
+        <v>7</v>
+      </c>
+      <c r="E74" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J74" s="17"/>
+      <c r="K74" s="17"/>
+    </row>
+    <row r="75" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A75" s="6">
+        <f t="shared" si="3"/>
+        <v>20230018</v>
+      </c>
+      <c r="B75" s="14">
+        <v>102300</v>
+      </c>
+      <c r="C75" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D75" s="33">
+        <v>8</v>
+      </c>
+      <c r="E75" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J75" s="17"/>
+      <c r="K75" s="17"/>
+    </row>
+    <row r="76" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A76" s="6">
+        <f t="shared" si="3"/>
+        <v>20230019</v>
+      </c>
+      <c r="B76" s="14">
+        <v>102300</v>
+      </c>
+      <c r="C76" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D76" s="33">
+        <v>9</v>
+      </c>
+      <c r="E76" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J76" s="17"/>
+      <c r="K76" s="17"/>
+    </row>
+    <row r="77" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A77" s="6">
+        <f t="shared" si="3"/>
+        <v>20230020</v>
+      </c>
+      <c r="B77" s="14">
+        <v>102300</v>
+      </c>
+      <c r="C77" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D77" s="33">
+        <v>10</v>
+      </c>
+      <c r="E77" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J77" s="17"/>
+      <c r="K77" s="17"/>
+    </row>
+    <row r="78" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A78" s="6">
+        <f t="shared" si="3"/>
+        <v>20230021</v>
+      </c>
+      <c r="B78" s="14">
+        <v>102300</v>
+      </c>
+      <c r="C78" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D78" s="33">
+        <v>11</v>
+      </c>
+      <c r="E78" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J78" s="17"/>
+      <c r="K78" s="17"/>
+    </row>
+    <row r="79" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A79" s="6">
+        <f t="shared" si="3"/>
+        <v>20230022</v>
+      </c>
+      <c r="B79" s="14">
+        <v>102300</v>
+      </c>
+      <c r="C79" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D79" s="33">
+        <v>12</v>
+      </c>
+      <c r="E79" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J79" s="17"/>
+      <c r="K79" s="17"/>
+    </row>
+    <row r="80" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A80" s="6">
+        <f t="shared" si="3"/>
+        <v>20230023</v>
+      </c>
+      <c r="B80" s="14">
+        <v>102300</v>
+      </c>
+      <c r="C80" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D80" s="33">
+        <v>13</v>
+      </c>
+      <c r="E80" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J80" s="17"/>
+      <c r="K80" s="17"/>
+    </row>
+    <row r="81" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A81" s="6">
+        <f>C81*10+D81</f>
+        <v>20340011</v>
+      </c>
+      <c r="B81" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C81" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D81" s="33">
+        <v>1</v>
+      </c>
+      <c r="E81" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J81" s="17"/>
+      <c r="K81" s="17"/>
+    </row>
+    <row r="82" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A82" s="6">
+        <f>C82*10+D82</f>
+        <v>20340012</v>
+      </c>
+      <c r="B82" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C82" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D82" s="33">
+        <v>2</v>
+      </c>
+      <c r="E82" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J82" s="17"/>
+      <c r="K82" s="17"/>
+    </row>
+    <row r="83" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A83" s="6">
+        <f>C83*10+D83</f>
+        <v>20340013</v>
+      </c>
+      <c r="B83" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C83" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D83" s="33">
+        <v>3</v>
+      </c>
+      <c r="E83" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J83" s="17"/>
+      <c r="K83" s="17"/>
+    </row>
+    <row r="84" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A84" s="6">
+        <f t="shared" ref="A84:A89" si="4">C84*10+D84</f>
+        <v>20340014</v>
+      </c>
+      <c r="B84" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C84" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D84" s="33">
+        <v>4</v>
+      </c>
+      <c r="E84" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="J84" s="17"/>
+      <c r="K84" s="17"/>
+    </row>
+    <row r="85" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A85" s="6">
+        <f t="shared" si="4"/>
+        <v>20340015</v>
+      </c>
+      <c r="B85" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C85" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D85" s="33">
+        <v>5</v>
+      </c>
+      <c r="E85" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J85" s="17"/>
+      <c r="K85" s="17"/>
+    </row>
+    <row r="86" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A86" s="6">
+        <f t="shared" si="4"/>
+        <v>20340016</v>
+      </c>
+      <c r="B86" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C86" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D86" s="33">
+        <v>6</v>
+      </c>
+      <c r="E86" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J86" s="17"/>
+      <c r="K86" s="17"/>
+    </row>
+    <row r="87" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A87" s="6">
+        <f t="shared" si="4"/>
+        <v>20340017</v>
+      </c>
+      <c r="B87" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C87" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D87" s="33">
+        <v>7</v>
+      </c>
+      <c r="E87" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J87" s="17"/>
+      <c r="K87" s="17"/>
+    </row>
+    <row r="88" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A88" s="6">
+        <f t="shared" si="4"/>
+        <v>20340018</v>
+      </c>
+      <c r="B88" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C88" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D88" s="33">
+        <v>8</v>
+      </c>
+      <c r="E88" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="J88" s="17"/>
+      <c r="K88" s="17"/>
+    </row>
+    <row r="89" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A89" s="6">
+        <f t="shared" si="4"/>
+        <v>20340019</v>
+      </c>
+      <c r="B89" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C89" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D89" s="33">
+        <v>9</v>
+      </c>
+      <c r="E89" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J89" s="17"/>
+      <c r="K89" s="17"/>
+    </row>
+    <row r="90" customFormat="1" spans="1:11">
+      <c r="B90" s="7"/>
+      <c r="J90" s="8"/>
+      <c r="K90" s="8"/>
+    </row>
+    <row r="91" customFormat="1" spans="1:11">
+      <c r="B91" s="7"/>
+      <c r="J91" s="8"/>
+      <c r="K91" s="8"/>
+    </row>
+    <row r="92" customFormat="1" spans="1:11">
+      <c r="B92" s="7"/>
+      <c r="J92" s="8"/>
+      <c r="K92" s="8"/>
+    </row>
+    <row r="93" customFormat="1" spans="1:11">
+      <c r="B93" s="7"/>
+      <c r="J93" s="8"/>
+      <c r="K93" s="8"/>
+    </row>
+    <row r="94" customFormat="1" spans="1:11">
+      <c r="B94" s="7"/>
+      <c r="J94" s="8"/>
+      <c r="K94" s="8"/>
+    </row>
+    <row r="95" customFormat="1" spans="1:11">
+      <c r="B95" s="7"/>
+      <c r="J95" s="8"/>
+      <c r="K95" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="I24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="24" ht="16.5" spans="9:9">
+      <c r="I24" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="BaseRoller" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -79,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="166">
   <si>
     <t>id</t>
   </si>
@@ -475,6 +476,108 @@
   </si>
   <si>
     <t>9_1_7_1_3_6_1_3_5_3_2_9_1_2_1_7_5_3_1_9_8_6_8_6_2_5_2_7_2_3_2_3_7_2_9_6_9_3_2_2_4_1_1_4_5_8_9_8_6_1_3_4_4_4_5_7_8_3_2_1_8_2_1_6_3_4_7_5_5_2_3_4_1_7_3_2_7_3_6_5_9_4_5_3_5_5_8_2_7_2_4_3_8_6_6_4_1_4_3_1_3_5_2_3_7_6_1_1_5_5_1_2_7_3_8_2_7_3_3_3_6_4_3_4_8_1_6_4_8_3_5_1_6_4_1_3_5_6_4_6_3_3_6_6_8_7_2_2_4_2_8_9_3_3_6_3_9_5_9_8_2_4_4_1_7_8_1_2_6_1_3_5_5_8_6_3_1_6_4_2_6_5_2_2_6_5_1_9_7_3_5_6_9_9_6_4_8_1_2_7_9_7_8_3_5_5_6_7_5_7_2_3_7_3_4_5_7_1_6_2_2_7_5_5_8_4_8_1_2_2_4_1_9_2_5_8_8_5_1_9_4_3_8_1_4_6_1_2_3_8_2_5_5_1_1_6_4_1_6_9_1_3_5_9_4_8_2_1_3_8_1_2_3_2_8_5_5_4_4_5_3_7_4_4_6_5_9_5_7_8_3_2_2_4_7_2_6_4_4_6_1_8_3_2_6_6_4_7_7_9_6_3_3_9_4_5_1_3_4_3_1_1_5_2_3_1_2_6_1_3_7_8_3_7_7_5_9_2_2_4_1_4_5_2_6_4_6_4_8_1_9_4_6_5_4_7_3_1_9_8_6_5_7_2_3_8_2_2_7_5_3_6_2_9_3_1_4_6_3_2_1_1_5_4_2_5_7_7_3_5_9_2_2_8_2_8_2_7_6_6_2_7_5_7_6_7_2_2_1_3_6_4_9_2_4_6_8_5_2_6_6_8_2_2_1_1_5_8_7_5_1_4_1_6_8_3_6_6_5_6_1_6_1_9_5_6_6_5_2_3_2_4_2_4_2_8_9_1_5_6_2_1_7_7_3_3_3_4_2_7_5_5_1_4_9_4_8_5_6_2_4_9_9_6_2_3_6_7_7_8_1_6_5_4_1_6_2_7_2_3</t>
+  </si>
+  <si>
+    <t>5_3_2_6_1_1_1_6_6_2_5_1_9_9_9_9_8_2_2_7_1_1_4_1_2_6_1_7_4_1_5_3_3_2_2_2_4_8_1_5_2_1_6_3_1_2_8_1_6_6_9_5_5_2_1_5_5_3_1_6_1_3_5_1_1_4_4_1_2_2_2_6_5_3_10_10_8_10_2_8_8_1_4_3_4_1_4_5_6_9_7_7_8_3_7_4_4_4_4_1_7_1_2_1_7_6_9_1_3_6_1_2_2_2_3_8_1_5_2_2_9_5_7_8_3_6_6_8_5_8_1_6_7_7_2_1_1_3_5_5_5_7_7_1_1_5_1_1_8_6_10_1_3_2_5_5_6_9_3_9_5_2_2_2_2_7_4_7_2_7_3_1_4_5_9_9_9_1_4_2_6_5_7_1_5_9_3_5_10_2_7_2_6_9_10_5_8_3_2_3_8_6_4_4_8_8_4_9_9_8_6_8_8_10_2_5_5_4_1_6_4_8_3_1_5_5_8_6_3_5_5_5_5_1_4_8_6_1_6_4_1_1_6_4_3_10_1_2_7_7_3_9_8_4_4_6_5_3_3_7_6_6_9_4_6_3_3_5_10_8_3_3_1_1_1_6_3_1_1_4_5_2_4_4_10_9_2_6_2_3_9_5_1_9_5_3_4_2_2_6_6_8_1_3_2_5_4_6_10_1_4_5_6_1_8_8_4_5_7_6_7_4_8_8_2_6_6_6_2_4_8_8_1_1_10_3_3_3_1_3_7_7_7_9_6_2_5_6_2_1_1_8_5_5_4_1_5_3_4_7_2_10_2_1_9_2_7_2_2_2_1_1_6_5_5_6_3_6_4_7_2_8_2_8_4_8_5_4_5_5_6_6_6_7_7_7_1_2_3_3_1_2_2_3_4_9_2_4_8_5_6_8_1_2_4_4_2_2_4_4_9_5_5_1_5_3_6_2_6_2_1_4_8_1_10_7_2_4_3_6_1_7_8_2_10_6_7_1_6_3_1_7_6_8_8_7_9_9_9_5_4_4_2_6_4_7_7_7_10_8_4_3_3_9_6_8_6_1_2_5_1_3_4_3_9_8_3_2_8_5_5_4_5_5_3_6_6_3_1_1</t>
+  </si>
+  <si>
+    <t>7_7_6_1_5_6_1_7_3_3_2_3_7_5_1_6_4_4_6_2_1_1_1_1_6_4_7_3_6_1_2_5_4_4_6_9_4_7_1_4_5_3_7_2_5_5_2_3_5_4_4_1_3_6_2_5_6_6_6_4_4_1_1_1_1_2_2_9_1_1_1_3_3_9_8_2_7_7_2_2_8_8_3_2_8_8_8_3_3_8_3_5_7_7_8_1_7_4_6_1_1_2_6_1_5_8_6_1_7_8_1_5_5_4_4_1_1_3_2_4_2_10_8_6_4_2_9_4_5_6_2_8_4_3_1_5_1_6_6_2_9_9_5_2_9_2_3_5_4_6_3_3_1_4_4_1_1_7_4_3_3_2_8_8_2_3_1_5_3_1_4_6_1_6_2_7_8_3_1_7_7_5_1_1_1_1_1_5_5_2_6_7_7_9_1_3_1_1_4_4_2_1_3_9_1_3_3_1_3_2_7_6_1_4_4_9_8_5_1_5_6_1_5_5_2_4_1_1_6_8_9_8_4_4_4_1_1_9_8_2_1_4_7_4_1_6_6_2_2_3_10_5_2_2_3_5_6_6_2_9_5_5_10_10_3_3_2_4_6_4_7_2_1_1_1_8_2_5_2_2_9_4_4_9_3_1_6_1_1_1_3_2_2_4_4_4_1_1_1_3_7_9_6_4_1_2_3_5_5_9_9_2_5_5_5_8_3_3_3_1_6_5_7_10_1_7_6_6_3_5_3_4_2_3_6_2_2_4_1_2_3_8_4_2_9_9_5_6_6_1_6_4_2_1_6_1_3_7_1_5_1_4_10_7_2_2_2_6_4_8_4_1_7_6_1_8_8_4_1_4_4_2_2_8_1_1_1_2_1_6_4_4_3_7_3_7_6_1_9_1_10_3_3_9_9_3_2_6_5_4_2_7_3_1_1_4_8_3_2_2_1_7_1_9_7_2_6_5_4_6_8_7_1_5_4_2_9_6_1_4_3_3_9_3_5_3_4_3_5_3_9_2_9_3_1_9_2_9_8_5_8_2_5_5_4_4_1_8_8_3_4_3_3_5_1_3_1_1_2_9_9_8_9_6_8_10_5_9_4_8_1_3_3_3_3_2_1_2_2_1</t>
+  </si>
+  <si>
+    <t>10_2_2_5_3_9_9_1_3_4_4_9_5_3_5_1_6_7_3_5_3_7_5_5_4_4_1_8_8_8_6_6_4_5_5_5_5_2_4_2_5_2_4_2_2_3_4_1_1_8_1_1_1_2_2_4_4_7_3_6_7_1_4_6_7_7_3_2_4_9_7_6_6_4_1_6_1_2_9_8_3_9_2_2_2_5_2_2_9_7_9_6_9_1_1_7_1_1_7_6_5_8_4_4_9_4_5_9_6_6_1_5_8_1_5_10_5_6_3_5_1_6_1_9_2_1_2_2_3_3_9_6_8_3_4_8_3_3_4_4_4_2_4_6_5_3_9_3_2_5_7_8_2_2_1_8_1_3_4_10_5_1_8_8_3_3_6_4_3_2_10_7_3_5_1_3_1_1_2_5_6_2_4_2_5_8_3_3_3_5_7_7_2_7_7_7_10_2_8_5_1_1_1_1_4_7_2_2_5_2_4_5_4_6_4_1_1_1_9_10_6_8_10_4_6_6_3_9_7_5_1_1_4_3_1_8_7_5_7_5_1_1_2_2_9_4_2_1_1_6_7_7_6_10_2_7_6_9_1_1_6_8_1_2_5_5_10_8_9_4_8_8_3_6_7_7_4_7_5_5_8_7_5_5_3_3_5_5_6_6_9_6_9_2_5_4_4_4_2_8_4_5_2_2_3_9_5_6_10_8_2_6_9_4_4_6_7_7_2_3_3_3_4_1_7_5_2_4_8_8_5_3_7_7_1_1_3_6_6_8_7_3_7_4_4_7_3_5_5_8_5_2_5_3_1_4_2_8_8_3_8_2_8_1_4_2_6_7_4_6_6_8_2_3_6_6_7_7_3_1_8_1_1_1_4_3_10_1_8_8_3_9_7_7_3_5_9_3_2_5_5_10_8_10_1_5_5_1_1_10_1_4_3_7_7_5_7_3_9_7_3_2_3_1_1_3_6_4_3_7_9_3_4_9_4_3_4_6_7_8_1_7_2_7_7_6_7_5_2_5_5_3_8_2_7_1_2_5_1_6_5_6_3_8_5_3_1_3_8_1_1_1_5_7_1_1_2_1_7_1_6_1_1_5_9_2_1_3_3_3_1_7_2_1_1_6_5_2_4_2</t>
+  </si>
+  <si>
+    <t>5_8_7_8_7_8_4_2_2_3_6_7_3_5_2_2_6_2_6_1_6_7_6_6_6_1_3_8_8_8_2_3_3_5_4_8_8_7_4_5_6_6_4_5_3_8_4_9_4_8_4_4_4_1_3_9_3_3_2_1_1_6_5_2_1_4_5_5_5_6_9_8_4_9_1_9_7_6_4_9_3_5_6_7_2_2_1_1_9_9_5_5_6_7_5_5_8_6_9_2_1_1_6_1_2_1_1_1_2_6_3_1_6_1_1_3_7_8_1_1_5_7_7_4_6_4_10_3_10_4_2_8_8_4_2_7_7_7_7_2_1_3_3_7_5_3_3_3_6_8_9_3_3_1_6_7_2_3_4_1_6_3_9_6_4_9_4_2_3_1_1_10_3_4_9_10_10_10_6_1_1_1_9_3_5_3_3_1_2_6_3_4_3_8_1_4_1_7_6_6_6_5_2_6_6_4_4_8_8_7_4_5_7_5_7_5_5_3_4_8_7_9_8_6_9_4_3_7_2_2_4_8_3_4_3_3_8_3_2_2_4_4_2_3_3_2_7_3_5_6_2_4_9_8_1_6_1_4_1_2_2_3_1_4_2_2_9_1_2_1_9_1_1_1_1_1_9_7_1_4_5_3_5_1_6_7_1_1_1_4_7_8_1_4_4_7_4_4_1_2_4_2_6_1_8_1_5_5_5_9_1_1_7_5_2_2_3_3_4_8_3_5_3_4_2_3_3_1_3_1_2_3_4_4_4_2_9_8_4_2_10_6_4_2_6_5_8_1_1_6_2_1_1_10_1_2_1_1_3_7_8_2_5_8_1_3_2_4_8_8_3_3_9_1_3_1_5_7_4_7_9_9_1_6_2_2_8_9_1_2_2_4_4_5_4_1_4_8_3_2_8_1_3_3_6_5_5_2_1_1_8_6_7_1_10_2_1_1_1_2_2_5_5_2_2_10_4_4_2_3_4_4_9_6_2_3_2_2_2_8_4_1_6_10_4_5_1_9_3_5_2_1_1_1_3_4_1_4_7_5_9_7_3_7_3_4_2_6_5_2_8_1_1_1_7_7_5_5_1_5_5_3_5_4_2_8_6_5_7_5_5_4_6_6_3_1_9_7_4_5</t>
+  </si>
+  <si>
+    <t>1_2_6_8_4_3_2_1_3_5_8_8_1_1_2_10_2_3_2_4_4_2_4_1_4_2_9_6_5_4_4_4_7_2_2_2_2_6_3_5_2_2_9_5_1_6_7_3_1_1_3_9_9_9_2_4_4_1_1_4_7_7_8_4_7_7_6_5_3_1_1_6_8_7_7_4_4_1_3_3_9_1_1_1_3_3_3_3_3_2_6_4_3_2_7_5_9_5_5_3_3_3_7_4_7_9_2_4_4_6_10_8_5_6_1_8_3_2_6_2_5_5_1_8_4_8_2_2_2_5_6_7_4_2_7_1_1_1_4_8_1_2_9_3_3_1_2_4_1_2_7_9_2_3_4_2_2_2_1_2_8_6_2_2_4_2_3_1_3_1_3_3_1_7_1_2_6_2_1_6_10_10_1_7_7_6_4_7_2_4_5_5_7_4_5_1_8_2_9_1_4_8_1_4_9_4_10_7_6_5_4_7_6_4_6_6_4_9_9_7_3_7_9_8_8_8_1_2_5_8_8_8_2_1_2_6_2_7_2_6_6_8_2_7_4_4_2_4_2_2_9_9_2_2_1_2_4_2_8_4_3_1_1_1_1_6_4_1_4_4_4_4_3_5_3_3_8_1_9_1_3_6_3_8_2_7_1_6_8_2_5_6_7_4_4_1_2_2_2_2_3_10_8_5_3_4_9_9_1_7_1_8_4_1_3_6_9_5_6_1_7_3_5_2_1_1_5_3_6_1_7_1_9_1_3_9_8_7_3_1_1_2_6_7_2_2_1_1_5_10_6_2_3_6_1_2_6_3_2_4_1_1_3_6_6_5_3_2_2_5_5_4_5_8_10_2_3_6_2_9_3_1_1_2_4_2_7_1_7_7_4_2_8_1_5_9_8_7_6_3_9_6_3_3_5_6_6_2_1_9_2_8_3_1_6_3_8_3_2_9_1_1_5_2_4_7_6_2_1_4_1_1_5_2_6_6_9_9_3_6_7_4_5_1_1_5_2_7_9_3_2_2_5_4_4_8_4_5_4_4_3_1_2_1_2_1_2_4_4_7_8_1_2_7_1_2_5_5_7_7_6_6_1_2_4_2_6_9_1_1_3_2_4_5_9_8_2_5_9_6</t>
+  </si>
+  <si>
+    <t>4_2_6_7_4_2_2_7_4_6_6_6_6_5_9_1_3_6_1_2_2_2_4_4_1_4_7_2_2_1_1_2_4_2_6_6_3_1_1_8_6_3_1_1_6_6_5_5_2_6_2_4_1_4_2_3_6_2_3_1_2_2_6_1_3_7_4_3_3_1_6_9_6_4_3_7_1_1_1_7_5_9_4_2_1_3_3_7_8_8_3_9_2_6_8_2_1_4_3_2_4_3_3_6_4_8_3_1_1_1_7_7_7_1_4_7_8_9_2_2_8_5_2_4_4_6_5_5_5_7_9_6_1_4_2_3_2_2_3_2_4_2_1_9_4_8_9_3_4_5_3_5_5_4_2_3_5_2_4_2_2_4_8_7_1_3_2_3_4_4_4_2_7_3_2_6_8_1_8_8_9_6_7_8_1_8_4_4_2_7_9_4_2_2_8_1_1_2_6_6_6_7_3_1_1_8_8_5_8_2_5_1_1_1_8_8_5_2_6_6_8_2_8_1_1_5_7_5_6_6_5_7_5_2_1_2_2_3_5_7_7_4_2_7_1_2_6_2_2_6_8_8_6_1_1_4_2_2_6_1_3_1_3_4_3_1_2_5_8_6_6_8_1_4_1_9_5_8_8_1_1_2_1_3_4_2_3_2_5_3_2_9_3_1_7_6_2_4_7_7_2_5_4_8_3_4_3_3_3_3_3_3_3_5_2_5_3_4_6_7_7_3_5_5_5_2_6_5_4_6_6_1_5_5_9_9_1_9_2_1_2_4_5_6_6_3_7_5_9_8_2_7_2_5_9_3_7_1_2_7_5_6_3_2_2_2_4_7_8_4_4_1_3_3_6_8_2_2_7_9_7_8_4_4_1_1_4_5_6_5_7_4_5_6_4_2_1_4_9_9_3_4_5_7_9_2_5_4_9_1_3_1_2_9_4_4_2_2_9_8_8_8_1_1_1_3_8_8_9_1_5_3_5_4_7_7_4_2_1_2_2_8_3_9_9_4_5_1_3_1_3_4_4_6_2_1_2_8_1_4_5_4_3_2_5_4_3_4_7_6_1_3_9_7_7_3_5_5_2_1_1_2_2_6_4_2_2_3_3_5_4_2_9_2_2_4_1_8_8_6</t>
+  </si>
+  <si>
+    <t>1_8_1_2_2_4_4_1_1_2_1_1_4_1_2_1_8_6_2_1_2_4_1_1_2_1_8_8_2_4_6_2_2_2_1_4_1_4_1_2_1_4_1_2_2_6_6_6_1_1_8_1_1_1_2_1_1_6_6_6_8_1_2_6_1_4_2_1_4_1_6_1_1_6_2_6_2_6_4_4_6_8_1_6_2_1_1_1_1_4_1_2_4_4_1_1_1_1_2_2_2_1_1_2_1_2_4_2_2_4_6_4_4_1_2_1_1_1_2_4_2_2_4_8_6_8_6_2_4_6_1_2_2_4_4_4_2_1_1_2_2_8_8_6_2_6_6_6_2_2_2_8_6_2_6_4_1_4_4_2_4_1_2_2_1_1_2_1_2_8_2_4_2_2_4_1_8_2_1_6_4_4_1_8_8_6_1_2_2_6_6_6_8_2_2_8_1_6_2_2_6_4_1_6_4_1_2_4_2_1_6_2_2_6_2_1_1_1_1_1_2_4_1_8_8_8_1_4_4_1_1_6_2_2_4_1_8_6_6_1_1_1_4_2_8_4_2_6_4_2_2_1_1_1_2_4_4_1_1_6_4_8_1_1_4_2_8_1_1_2_1_1_6_6_4_1_1_2_4_8_1_6_6_8_6_4_4_6_2_1_1_6_4_1_4_6_1_4_1_1_1_1_2_1_6_6_4_1_1_2_2_2_1_2_6_1_1_2_1_1_4_4_8_1_1_4_4_2_1_4_1_1_6_1_1_8_6_2_4_6_1_1_1_4_4_4_1_1_2_1_6_8_2_8_1_8_8_1_2_8_2_8_1_1_6_2_1_1_4_4_2_4_2_4_6_2_6_6_1_8_1_4_1_1_1_4_2_1_1_8_6_4_6_6_1_2_4_8_4_4_6_4_4_1_2_1_2_1_1_6_4_2_1_2_1_1_8_6_8_4_8_1_4_2_1_8_2_1_8_6_1_2_8_8_4_6_6_8_8_1_1_8_1_4_4_4_4_4_6_2_4_1_1_1_1_1_1_8_2_2_6_4_2_4_4_1_2_4_2_1_2_6_6_1_1_1_2_1_4_6_8_4_6_6_4_2_4_6_2_1_4_1_6_2_1_2_1_8_8_1</t>
+  </si>
+  <si>
+    <t>1_1_3_3_3_5_1_1_3_3_3_3_5_7_1_7_1_7_5_5_3_1_7_3_3_1_1_5_3_1_5_1_3_1_1_1_1_1_1_1_7_3_1_5_1_1_1_1_1_1_1_7_5_7_1_7_3_3_7_1_1_1_1_7_1_1_1_7_3_3_3_1_3_5_5_3_5_7_7_1_3_1_5_1_7_5_5_1_7_3_1_3_7_1_3_7_1_1_7_1_3_7_1_3_1_1_5_1_7_7_7_7_1_1_5_7_5_5_1_3_3_5_1_3_7_3_5_5_5_5_5_7_7_1_3_1_3_1_1_1_1_3_1_3_3_7_3_1_3_7_3_7_7_5_1_1_1_1_3_1_3_1_5_5_5_5_1_7_7_1_3_3_3_5_1_7_7_1_3_1_3_1_7_7_1_7_3_3_5_5_1_1_1_1_3_7_1_1_1_5_3_5_5_3_1_3_7_3_5_5_5_5_7_5_7_1_1_5_3_7_3_3_1_7_7_3_3_1_7_1_5_3_3_5_5_5_7_5_3_3_5_5_5_1_1_1_7_5_3_3_1_1_5_5_1_3_3_3_1_1_1_1_3_1_7_3_5_1_3_5_5_5_1_1_1_3_5_5_5_3_3_7_1_3_5_5_1_1_1_5_3_1_3_1_5_1_5_5_3_1_5_5_7_7_3_7_3_3_3_1_3_3_5_1_3_3_5_1_1_5_7_3_5_5_1_1_7_5_5_7_1_1_5_1_7_1_3_1_1_1_1_3_5_7_1_3_3_5_3_7_5_3_7_3_3_1_1_3_1_3_5_7_7_7_1_1_1_7_3_3_1_3_3_7_3_3_7_1_5_5_1_3_5_3_3_5_5_5_5_1_7_5_1_7_7_1_5_1_3_5_5_5_3_1_3_5_3_1_7_3_1_1_7_3_3_3_3_7_7_5_5_1_7_1_1_5_5_5_5_5_1_5_5_3_1_3_1_5_1_1_3_5_5_5_1_7_3_7_5_7_1_1_1_3_3_1_3_3_5_5_5_1_1_1_1_5_1_3_3_5_5_1_7_1_1_1_7_7_1_1_1_3_1_3_5_5_1_5_1_1_5_3_3_1_3_5_1_1_1_5</t>
+  </si>
+  <si>
+    <t>4_4_4</t>
+  </si>
+  <si>
+    <t>3_3_2_4_2_4_5_1_5_1_4_6_3_6_2_1_4_1_1_3_2_3_2_2_3_5_2_1_4_4_2_2_2_3_3_3_6_3_2_6_2_5_4_3_1_3_4_4_4_1_3_4_4_3_1_3_3_1_6_3_2_1_4_2_2_3_6_1_1_5_2_2_1_1_1_1_4_2_2_4_6_1_1_1_3_2_2_3_5_3_3_5_2_3_2_5_1_4_4_4_2_3_4_3_1_5_2_1_1_3_2_2_2_4_4_3_5_5_3_5_1_2_3_2_2_2_4_5_2_1_6_2_2_2_5_1_1_1_4_3_3_1_5_5_4_3_2_3_2_1_2_2_4_2_6_6_3_3_2_1_4_1_5_5_5_4_2_3_3_3_3_1_5_5_2_3_2_2_5_5_3_4_1_1_2_2_2_4_4_3_2_1_3_3_1_3_5_4_5_2_5_5_1_1_1_4_2_2_6_4_2_2_3_1_2_1_4_5_1_2_2_2_2_1_5_5_5_5_2_1_3_3_1_4_4_5_1_5_5_3_1_2_1_3_4_4_2_5_1_5_5_3_5_2_2_4_4_1_2_2_2_1_2_2_3_2_1_2_3_4_6_5_5_3_5_1_2_2_2_4_1_4_2_2_4_3_3_3_1_3_3_6_1_3_3_2_4_3_1_5_1_2_2_3_2_2_3_1_4_4_3_1_5_4_4_2_3_1_2_3_4_4_2_2_1_4_4_3_1_2_2_1_1_1_4_3_2_2_2_2_1_1_1_2_2_1_4_4_2_2_2_2_3_1_2_2_2_2_1_2_2_2_3_3_4_1_1_1_6_6_1_1_1_4_1_3_1_4_2_6_4_2_6_3_4_4_2_4_3_2_2_4_6_2_2_5_4_4_3_1_3_1_1_4_2_3_1_2_2_1_5_6_3_2_2_2_4_1_3_2_1_1_1_2_1_3_2_2_5_4_4_3_3_4_1_5_3_2_1_5_1_6_3_3_2_3_1_3_3_4_1_1_2_6_1_2_2_2_4_4_6_2_6_4_2_3_3_1_1_3_3_1_6_5_3_2_6_4_4_1_2_2_2_5_3_4_2_4_1_2_5_2_2_5_5_5_4_4_1_3</t>
+  </si>
+  <si>
+    <t>3_2_3_2_1_6_6_4_3_7_6_2_5_3_1_6_3_4_3_1_1_7_4_3_4_1_5_3_1_2_4_1_2_1_3_4_2_6_3_2_4_1_2_1_2_7_7_5_1_5_2_4_4_3_5_1_6_6_3_2_2_4_2_6_2_1_1_3_4_1_2_4_4_1_5_1_1_1_2_1_4_4_3_2_4_3_3_3_1_1_6_3_1_4_1_1_6_3_2_2_3_4_1_2_7_3_3_6_6_3_1_5_3_4_1_3_6_3_3_3_2_3_5_4_3_5_7_5_4_1_2_1_3_3_3_2_2_6_4_1_5_7_3_6_5_2_2_4_2_4_3_1_1_6_2_1_3_6_6_1_1_3_1_1_1_6_7_1_3_3_3_6_3_2_1_5_7_6_1_1_2_3_4_6_2_1_3_3_4_2_1_2_3_2_2_2_2_4_1_2_1_7_1_5_3_2_4_3_2_1_2_3_3_1_6_3_1_6_3_3_1_1_5_6_4_4_3_4_1_3_3_7_3_2_1_4_3_2_2_2_1_1_6_6_1_2_2_6_2_2_6_1_4_3_7_1_5_4_4_4_3_1_3_2_7_6_5_5_3_2_2_1_4_6_5_2_1_1_2_7_7_6_1_5_1_1_1_4_4_1_2_4_4_7_3_1_3_1_3_5_2_4_7_2_6_6_1_4_1_4_1_3_4_3_5_1_2_2_6_3_3_3_6_6_2_6_6_1_3_3_6_5_6_4_2_3_4_1_2_3_3_2_3_6_4_5_4_3_6_2_1_1_4_2_3_3_5_2_2_6_4_7_4_3_3_3_1_6_6_7_2_1_5_5_5_3_6_5_3_5_1_4_5_2_6_5_5_4_1_1_4_7_3_2_1_1_2_3_2_2_3_3_3_5_6_5_6_1_1_6_1_4_2_3_1_5_7_3_1_6_4_2_2_2_7_4_1_4_7_1_2_6_1_4_3_1_6_1_1_5_1_1_1_2_1_6_2_6_5_6_1_1_2_1_3_3_5_1_3_5_5_1_1_1_3_7_5_4_1_6_6_3_6_5_3_3_5_2_5_7_6_6_2_1_4_6_3_7_5_4_1_3_1_6_3_6_5_3_4_4</t>
+  </si>
+  <si>
+    <t>3_4_4_4_4_4_4_2_2_2_1_4_2_2_5_1_4_5_2_3_3_3_3_1_2_1_3_3_3_3_1_3_2_2_2_5_3_6_6_2_5_1_3_4_2_1_1_1_2_2_2_2_2_2_1_2_3_2_2_2_1_3_1_2_3_1_4_5_1_3_4_4_3_4_3_3_3_4_5_2_1_2_4_4_1_2_3_2_6_5_5_1_1_1_3_4_3_5_2_2_3_5_3_3_3_4_5_2_6_2_3_2_4_4_1_3_1_3_1_1_1_6_1_1_1_1_1_3_4_1_5_1_4_2_2_6_4_1_3_3_2_2_2_1_2_4_4_1_1_5_1_3_3_3_4_2_3_1_2_1_2_2_5_4_6_3_5_3_4_4_1_1_4_5_5_5_2_6_1_3_3_1_1_4_3_5_2_5_2_4_3_1_1_2_1_2_4_3_3_2_4_3_3_3_3_3_1_4_4_3_4_2_1_1_1_4_1_1_1_1_1_5_1_4_4_6_3_3_4_2_5_2_1_2_3_3_3_3_4_2_5_1_2_1_2_2_3_5_2_2_2_1_5_3_4_1_1_2_2_3_2_2_2_2_3_3_2_2_2_2_1_2_5_3_2_3_4_1_1_1_4_5_3_3_5_3_3_3_2_3_3_3_1_1_6_1_3_2_3_4_1_3_4_4_4_2_2_3_2_4_4_2_3_1_2_1_6_4_2_1_5_5_5_5_1_3_1_6_4_2_1_2_3_1_1_1_4_3_3_6_2_2_3_4_4_5_2_4_3_5_3_5_2_5_1_2_4_4_2_2_4_2_6_2_1_4_2_3_1_3_3_2_4_6_6_2_3_3_3_2_1_1_4_2_1_1_3_1_1_4_6_6_2_2_6_2_1_1_2_3_1_1_3_1_2_4_3_2_2_1_5_2_2_1_2_2_3_1_3_5_3_3_3_6_4_6_1_1_1_2_4_2_4_4_3_4_2_1_1_1_4_1_1_5_2_2_1_1_2_1_3_3_5_2_3_3_2_1_1_4_1_4_1_2_1_1_3_2_4_4_2_1_1_2_5_2_2_1_1_1_6_1_5_1_2_2_2_3_2_2_2_4_4_1_1_1_2_5_1_1</t>
+  </si>
+  <si>
+    <t>2_3_1_2_3_3_1_4_2_7_3_5_5_2_4_4_1_4_7_1_2_2_3_1_2_2_3_5_1_3_1_1_6_5_7_3_4_3_1_4_4_4_2_3_6_5_1_1_4_5_2_1_3_1_2_2_5_4_1_1_4_1_4_3_3_5_6_4_1_5_1_2_3_4_3_3_1_4_6_6_4_5_3_2_1_1_1_2_6_6_3_1_2_1_1_1_7_1_1_3_3_2_5_1_4_1_3_4_1_1_3_5_1_5_2_5_1_2_5_4_3_3_1_3_5_4_5_3_7_1_2_2_1_7_2_4_1_2_6_3_1_2_1_3_2_4_4_7_1_5_4_2_3_4_1_4_5_7_1_1_7_5_3_3_1_1_4_5_3_2_1_2_3_3_1_2_1_4_3_3_1_2_1_5_2_1_1_5_3_3_1_1_3_3_5_3_5_4_5_1_5_6_3_3_4_3_5_5_1_1_2_1_1_5_6_5_3_1_6_3_2_7_4_2_3_3_7_6_1_1_1_1_2_1_5_3_5_6_2_7_2_1_4_2_5_2_4_3_4_4_2_4_6_1_1_5_4_1_1_2_5_6_5_2_2_1_1_2_3_5_2_3_5_6_5_2_6_3_2_1_3_2_1_3_4_2_4_4_4_4_2_1_1_1_3_3_4_4_6_1_2_7_1_3_1_4_1_5_3_1_1_5_1_1_3_2_3_2_4_7_2_2_4_6_2_3_5_2_4_1_1_3_4_2_6_1_3_7_1_4_2_3_4_1_1_1_3_3_5_5_7_3_4_3_6_3_6_5_3_5_2_1_1_2_1_1_3_6_1_3_4_5_2_6_4_2_3_1_2_1_1_2_1_2_6_1_5_2_5_5_6_1_5_5_3_4_7_2_1_1_5_6_4_4_3_3_7_3_5_1_4_1_2_7_2_4_2_3_2_4_2_3_3_1_2_1_2_5_2_2_1_2_2_3_3_3_2_6_4_5_3_3_3_5_2_4_4_2_5_6_4_2_5_2_1_2_2_2_3_3_3_2_5_2_4_4_6_2_5_6_4_7_2_6_5_2_5_1_5_4_5_4_7_6_2_2_6_6_6_3_1_2_4_6_1_4_2_4_1_4</t>
+  </si>
+  <si>
+    <t>1_1_3_3_2_2_5_1_2_2_4_2_1_1_1_2_2_1_3_2_2_5_1_2_2_2_1_1_2_6_4_4_4_5_4_2_3_1_1_3_1_1_4_5_1_1_6_2_1_6_1_5_1_2_2_2_3_2_5_2_1_3_3_2_2_3_6_3_1_1_2_1_1_6_3_3_2_1_1_1_1_1_5_5_3_1_4_4_3_1_1_1_4_1_1_1_1_2_1_1_1_2_3_5_3_5_3_4_3_3_2_2_2_2_2_4_4_4_4_1_4_4_4_2_2_2_5_1_3_2_4_5_2_1_1_3_3_4_1_1_5_3_3_3_2_3_3_3_3_3_5_5_1_2_1_1_4_1_4_4_1_1_2_6_1_2_2_2_1_4_2_3_4_2_2_1_1_1_3_6_6_3_3_1_4_3_3_1_2_3_2_5_2_5_2_2_1_5_6_1_4_1_2_3_3_2_1_1_3_3_3_2_1_3_2_2_4_2_1_5_3_3_1_2_1_1_3_3_3_3_3_3_1_1_1_2_2_3_3_1_6_3_2_2_4_1_5_2_2_2_2_6_3_3_1_3_1_1_4_2_1_3_2_4_3_2_5_5_2_6_4_3_2_1_1_5_5_1_4_3_5_2_4_4_2_4_2_2_5_2_6_6_2_5_6_1_3_3_3_2_4_4_3_1_2_6_5_1_1_1_3_4_1_1_1_6_2_2_3_4_2_1_6_1_5_2_4_5_5_4_4_1_4_5_4_1_3_2_1_1_4_4_1_3_5_1_1_5_1_6_6_6_6_6_1_4_2_1_1_4_3_2_4_1_4_4_2_3_3_3_2_3_1_1_4_3_2_4_1_3_2_2_1_1_4_1_2_6_1_4_1_1_4_4_1_2_4_1_4_2_4_5_1_1_3_5_3_2_2_2_1_1_5_1_4_2_6_2_6_1_1_1_5_1_1_6_3_2_3_4_3_3_1_2_2_2_6_1_2_4_2_4_1_1_3_2_4_1_3_1_2_6_3_4_1_3_1_1_5_1_2_5_1_5_4_6_2_3_1_1_1_1_1_2_4_3_3_1_2_1_3_2_2_4_3_3_1_3_2_1_1_2_1_1_5_3_3_3_1_1</t>
+  </si>
+  <si>
+    <t>1_1_2_5_1_3_2_2_2_3_3_6_4_1_6_2_3_2_3_1_4_4_4_2_5_5_6_3_7_5_1_4_3_5_1_2_4_5_5_7_4_3_2_2_5_7_3_4_3_3_5_1_2_5_3_1_2_4_4_2_2_1_4_4_2_5_2_1_3_6_1_1_2_5_1_1_1_1_5_7_3_3_5_2_3_6_1_5_1_3_3_5_6_2_1_1_3_1_1_4_3_3_1_2_3_2_4_1_2_1_2_3_4_2_6_1_6_1_4_3_6_6_3_1_3_1_4_5_2_1_2_1_6_2_1_6_4_1_4_5_1_3_1_5_1_3_1_1_4_1_5_1_2_7_7_1_2_7_1_1_6_3_1_1_1_4_2_7_3_1_2_1_1_7_5_2_3_2_6_1_1_5_4_1_3_1_1_3_1_3_3_3_1_5_5_2_5_1_6_6_1_7_1_3_2_1_2_2_6_2_7_1_3_1_1_4_3_4_6_3_2_1_1_5_6_4_1_2_3_4_1_4_5_4_6_1_2_2_3_5_2_6_2_6_6_4_2_5_6_1_1_2_1_4_5_1_1_1_1_3_3_5_5_4_5_6_6_6_4_5_7_4_1_4_4_3_6_6_1_4_3_1_2_5_1_4_2_2_2_2_1_1_1_3_1_7_1_2_6_3_5_2_5_3_1_2_1_6_4_2_3_1_2_1_6_1_3_3_3_2_3_3_3_4_1_1_2_5_1_6_5_5_2_2_4_2_5_5_2_6_1_2_7_2_4_3_2_5_2_2_3_5_3_2_2_4_7_6_5_6_4_2_4_2_5_1_6_4_5_7_4_3_4_7_5_2_5_4_2_6_2_2_6_1_5_1_5_2_4_1_6_5_3_3_6_3_3_2_2_2_2_5_1_2_2_1_1_2_5_1_1_1_5_1_3_6_2_6_3_2_2_6_5_5_3_1_2_4_2_5_6_2_6_6_4_3_2_2_3_6_6_7_1_4_4_2_2_1_3_2_3_3_1_2_3_1_4_4_2_2_1_2_3_1_1_4_5_4_1_6_3_2_4_3_2_1_2_3_1_3_3_4_7_6_5_2_2_4_5_5_1_5_5_6_2_2_1_1_5_3</t>
+  </si>
+  <si>
+    <t>7_7_7_7_1_7_1_1_1_1_7_7_1_1_1_1_1_1_7_1_1_1_7_7_1_1_1_1_1_1_1_1_1_7_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_7_1_1_7_1_1_1_1_1_1_1_1_1_1_1_1_1_7_7_1_7_1_1_1_1_1_1_1_7_1_1_1_1_1_1_1_1_1_1_1_7_7_1_1_1_1_1_1_1_7_1_1_7_7_1_7_1_1_1_1_1_1_1_1_1_1_7_1_1_1_1_1_7_1_1_1_7_1_1_1_1_7_1_1_7_7_1_7_7_1_1_1_1_1_1_7_1_1_7_1_7_1_1_1_1_7_7_1_1_1_1_1_1_1_1_1_7_1_1_1_1_7_7_1_1_1_7_1_1_1_1_1_1_7_1_1_1_7_7_7_1_1_7_1_1_1_1_1_7_1_1_1_1_1_7_1_1_1_1_1_1_1_7_1_1_1_1_1_1_1_1_7_7_7_7_1_7_1_1_1_7_7_1_1_7_1_1_1_1_7_1_7_1_7_1_1_1_1_1_1_1_1_1_1_1_1_7_7_1_1_1_1_1_1_7_1_1_1_1_1_1_7_1_7_1_1_1_1_1_7_1_7_1_1_1_7_7_1_1_1_1_1_7_1_7_1_1_1_1_7_1_1_1_1_7_1_1_1_1_1_1_1_1_1_7_1_1_1_1_1_1_1_7_1_7_7_1_7_7_1_1_1_7_7_1_1_1_1_1_7_1_1_1_1_1_1_1_1_7_1_1_1_1_7_1_7_1_1_1_1_7_1_1_1_7_7_1_1_1_7_1_7_1_1_7_1_1_1_1_7_1_1_1_1_1_1_1_1_1_1_1_7_7_1_1_1_1_1_7_1_1_1_1_1_1_1_7_7_1_1_1_1_1_7_1_1_1_1_1_1_1_1_1_1_1_1_7_1_1_1_1_1_1_1_1_1_1_7_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_7_1_1_1_1_1_7_1_1_1_1_7_1_1_1_7_1_7_1_1_1_1_7_1_7_7_7_1_7_1_1_1_7_7_1</t>
+  </si>
+  <si>
+    <t>7_7_7_7_2_7_2_2_2_2_7_7_2_2_2_2_2_2_7_2_2_2_7_7_2_2_2_2_2_2_2_2_2_7_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_7_2_2_7_2_2_2_2_2_2_2_2_2_2_2_2_2_7_7_2_7_2_2_2_2_2_2_2_7_2_2_2_2_2_2_2_2_2_2_2_7_7_2_2_2_2_2_2_2_7_2_2_7_7_2_7_2_2_2_2_2_2_2_2_2_2_7_2_2_2_2_2_7_2_2_2_7_2_2_2_2_7_2_2_7_7_2_7_7_2_2_2_2_2_2_7_2_2_7_2_7_2_2_2_2_7_7_2_2_2_2_2_2_2_2_2_7_2_2_2_2_7_7_2_2_2_7_2_2_2_2_2_2_7_2_2_2_7_7_7_2_2_7_2_2_2_2_2_7_2_2_2_2_2_7_2_2_2_2_2_2_2_7_2_2_2_2_2_2_2_2_7_7_7_7_2_7_2_2_2_7_7_2_2_7_2_2_2_2_7_2_7_2_7_2_2_2_2_2_2_2_2_2_2_2_2_7_7_2_2_2_2_2_2_7_2_2_2_2_2_2_7_2_7_2_2_2_2_2_7_2_7_2_2_2_7_7_2_2_2_2_2_7_2_7_2_2_2_2_7_2_2_2_2_7_2_2_2_2_2_2_2_2_2_7_2_2_2_2_2_2_2_7_2_7_7_2_7_7_2_2_2_7_7_2_2_2_2_2_7_2_2_2_2_2_2_2_2_7_2_2_2_2_7_2_7_2_2_2_2_7_2_2_2_7_7_2_2_2_7_2_7_2_2_7_2_2_2_2_7_2_2_2_2_2_2_2_2_2_2_2_7_7_2_2_2_2_2_7_2_2_2_2_2_2_2_7_7_2_2_2_2_2_7_2_2_2_2_2_2_2_2_2_2_2_2_7_2_2_2_2_2_2_2_2_2_2_7_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_7_2_2_2_2_2_7_2_2_2_2_7_2_2_2_7_2_7_2_2_2_2_7_2_7_7_7_2_7_2_2_2_7_7_2</t>
+  </si>
+  <si>
+    <t>7_7_7_7_3_7_3_3_3_3_7_7_3_3_3_3_3_3_7_3_3_3_7_7_3_3_3_3_3_3_3_3_3_7_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_7_3_3_7_3_3_3_3_3_3_3_3_3_3_3_3_3_7_7_3_7_3_3_3_3_3_3_3_7_3_3_3_3_3_3_3_3_3_3_3_7_7_3_3_3_3_3_3_3_7_3_3_7_7_3_7_3_3_3_3_3_3_3_3_3_3_7_3_3_3_3_3_7_3_3_3_7_3_3_3_3_7_3_3_7_7_3_7_7_3_3_3_3_3_3_7_3_3_7_3_7_3_3_3_3_7_7_3_3_3_3_3_3_3_3_3_7_3_3_3_3_7_7_3_3_3_7_3_3_3_3_3_3_7_3_3_3_7_7_7_3_3_7_3_3_3_3_3_7_3_3_3_3_3_7_3_3_3_3_3_3_3_7_3_3_3_3_3_3_3_3_7_7_7_7_3_7_3_3_3_7_7_3_3_7_3_3_3_3_7_3_7_3_7_3_3_3_3_3_3_3_3_3_3_3_3_7_7_3_3_3_3_3_3_7_3_3_3_3_3_3_7_3_7_3_3_3_3_3_7_3_7_3_3_3_7_7_3_3_3_3_3_7_3_7_3_3_3_3_7_3_3_3_3_7_3_3_3_3_3_3_3_3_3_7_3_3_3_3_3_3_3_7_3_7_7_3_7_7_3_3_3_7_7_3_3_3_3_3_7_3_3_3_3_3_3_3_3_7_3_3_3_3_7_3_7_3_3_3_3_7_3_3_3_7_7_3_3_3_7_3_7_3_3_7_3_3_3_3_7_3_3_3_3_3_3_3_3_3_3_3_7_7_3_3_3_3_3_7_3_3_3_3_3_3_3_7_7_3_3_3_3_3_7_3_3_3_3_3_3_3_3_3_3_3_3_7_3_3_3_3_3_3_3_3_3_3_7_3_3_3_3_3_3_3_3_3_3_3_3_3_3_3_7_3_3_3_3_3_7_3_3_3_3_7_3_3_3_7_3_7_3_3_3_3_7_3_7_7_7_3_7_3_3_3_7_7_3</t>
+  </si>
+  <si>
+    <t>7_7_7_7_4_7_4_4_4_4_7_7_4_4_4_4_4_4_7_4_4_4_7_7_4_4_4_4_4_4_4_4_4_7_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_7_4_4_7_4_4_4_4_4_4_4_4_4_4_4_4_4_7_7_4_7_4_4_4_4_4_4_4_7_4_4_4_4_4_4_4_4_4_4_4_7_7_4_4_4_4_4_4_4_7_4_4_7_7_4_7_4_4_4_4_4_4_4_4_4_4_7_4_4_4_4_4_7_4_4_4_7_4_4_4_4_7_4_4_7_7_4_7_7_4_4_4_4_4_4_7_4_4_7_4_7_4_4_4_4_7_7_4_4_4_4_4_4_4_4_4_7_4_4_4_4_7_7_4_4_4_7_4_4_4_4_4_4_7_4_4_4_7_7_7_4_4_7_4_4_4_4_4_7_4_4_4_4_4_7_4_4_4_4_4_4_4_7_4_4_4_4_4_4_4_4_7_7_7_7_4_7_4_4_4_7_7_4_4_7_4_4_4_4_7_4_7_4_7_4_4_4_4_4_4_4_4_4_4_4_4_7_7_4_4_4_4_4_4_7_4_4_4_4_4_4_7_4_7_4_4_4_4_4_7_4_7_4_4_4_7_7_4_4_4_4_4_7_4_7_4_4_4_4_7_4_4_4_4_7_4_4_4_4_4_4_4_4_4_7_4_4_4_4_4_4_4_7_4_7_7_4_7_7_4_4_4_7_7_4_4_4_4_4_7_4_4_4_4_4_4_4_4_7_4_4_4_4_7_4_7_4_4_4_4_7_4_4_4_7_7_4_4_4_7_4_7_4_4_7_4_4_4_4_7_4_4_4_4_4_4_4_4_4_4_4_7_7_4_4_4_4_4_7_4_4_4_4_4_4_4_7_7_4_4_4_4_4_7_4_4_4_4_4_4_4_4_4_4_4_4_7_4_4_4_4_4_4_4_4_4_4_7_4_4_4_4_4_4_4_4_4_4_4_4_4_4_4_7_4_4_4_4_4_7_4_4_4_4_7_4_4_4_7_4_7_4_4_4_4_7_4_7_7_7_4_7_4_4_4_7_7_4</t>
+  </si>
+  <si>
+    <t>7_7_7_7_5_7_5_5_5_5_7_7_5_5_5_5_5_5_7_5_5_5_7_7_5_5_5_5_5_5_5_5_5_7_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_7_5_5_7_5_5_5_5_5_5_5_5_5_5_5_5_5_7_7_5_7_5_5_5_5_5_5_5_7_5_5_5_5_5_5_5_5_5_5_5_7_7_5_5_5_5_5_5_5_7_5_5_7_7_5_7_5_5_5_5_5_5_5_5_5_5_7_5_5_5_5_5_7_5_5_5_7_5_5_5_5_7_5_5_7_7_5_7_7_5_5_5_5_5_5_7_5_5_7_5_7_5_5_5_5_7_7_5_5_5_5_5_5_5_5_5_7_5_5_5_5_7_7_5_5_5_7_5_5_5_5_5_5_7_5_5_5_7_7_7_5_5_7_5_5_5_5_5_7_5_5_5_5_5_7_5_5_5_5_5_5_5_7_5_5_5_5_5_5_5_5_7_7_7_7_5_7_5_5_5_7_7_5_5_7_5_5_5_5_7_5_7_5_7_5_5_5_5_5_5_5_5_5_5_5_5_7_7_5_5_5_5_5_5_7_5_5_5_5_5_5_7_5_7_5_5_5_5_5_7_5_7_5_5_5_7_7_5_5_5_5_5_7_5_7_5_5_5_5_7_5_5_5_5_7_5_5_5_5_5_5_5_5_5_7_5_5_5_5_5_5_5_7_5_7_7_5_7_7_5_5_5_7_7_5_5_5_5_5_7_5_5_5_5_5_5_5_5_7_5_5_5_5_7_5_7_5_5_5_5_7_5_5_5_7_7_5_5_5_7_5_7_5_5_7_5_5_5_5_7_5_5_5_5_5_5_5_5_5_5_5_7_7_5_5_5_5_5_7_5_5_5_5_5_5_5_7_7_5_5_5_5_5_7_5_5_5_5_5_5_5_5_5_5_5_5_7_5_5_5_5_5_5_5_5_5_5_7_5_5_5_5_5_5_5_5_5_5_5_5_5_5_5_7_5_5_5_5_5_7_5_5_5_5_7_5_5_5_7_5_7_5_5_5_5_7_5_7_7_7_5_7_5_5_5_7_7_5</t>
+  </si>
+  <si>
+    <t>7_7_7_7_6_7_6_6_6_6_7_7_6_6_6_6_6_6_7_6_6_6_7_7_6_6_6_6_6_6_6_6_6_7_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_7_6_6_7_6_6_6_6_6_6_6_6_6_6_6_6_6_7_7_6_7_6_6_6_6_6_6_6_7_6_6_6_6_6_6_6_6_6_6_6_7_7_6_6_6_6_6_6_6_7_6_6_7_7_6_7_6_6_6_6_6_6_6_6_6_6_7_6_6_6_6_6_7_6_6_6_7_6_6_6_6_7_6_6_7_7_6_7_7_6_6_6_6_6_6_7_6_6_7_6_7_6_6_6_6_7_7_6_6_6_6_6_6_6_6_6_7_6_6_6_6_7_7_6_6_6_7_6_6_6_6_6_6_7_6_6_6_7_7_7_6_6_7_6_6_6_6_6_7_6_6_6_6_6_7_6_6_6_6_6_6_6_7_6_6_6_6_6_6_6_6_7_7_7_7_6_7_6_6_6_7_7_6_6_7_6_6_6_6_7_6_7_6_7_6_6_6_6_6_6_6_6_6_6_6_6_7_7_6_6_6_6_6_6_7_6_6_6_6_6_6_7_6_7_6_6_6_6_6_7_6_7_6_6_6_7_7_6_6_6_6_6_7_6_7_6_6_6_6_7_6_6_6_6_7_6_6_6_6_6_6_6_6_6_7_6_6_6_6_6_6_6_7_6_7_7_6_7_7_6_6_6_7_7_6_6_6_6_6_7_6_6_6_6_6_6_6_6_7_6_6_6_6_7_6_7_6_6_6_6_7_6_6_6_7_7_6_6_6_7_6_7_6_6_7_6_6_6_6_7_6_6_6_6_6_6_6_6_6_6_6_7_7_6_6_6_6_6_7_6_6_6_6_6_6_6_7_7_6_6_6_6_6_7_6_6_6_6_6_6_6_6_6_6_6_6_7_6_6_6_6_6_6_6_6_6_6_7_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_7_6_6_6_6_6_7_6_6_6_6_7_6_6_6_7_6_7_6_6_6_6_7_6_7_7_7_6_7_6_6_6_7_7_6</t>
+  </si>
+  <si>
+    <t>4_4_4_4</t>
+  </si>
+  <si>
+    <t>5_1_2_1_5_5_2_4_1_1_1_1_1_1_1_1_3_5_4_5_2_4_1_3_3_2_5_1_1_1_2_1_5_2_4_4_3_4_2_2_5_2_2_1_1_1_2_5_6_5_3_3_2_5_6_2_3_3_3_3_1_4_4_1_4_3_2_3_4_3_3_2_2_2_3_1_1_2_1_2_5_6_4_3_2_5_4_4_3_2_3_4_1_3_2_5_3_1_4_1_2_5_2_3_3_3_5_4_1_1_1_6_1_4_2_1_3_4_3_1_2_2_2_2_4_2_2_1_3_2_4_2_1_6_1_4_1_4_4_2_1_4_1_2_1_4_2_3_6_2_3_3_1_3_1_1_3_1_3_6_2_4_4_5_5_1_1_1_1_3_3_3_3_3_4_2_2_1_1_3_3_2_1_3_1_4_6_3_2_1_3_4_1_3_4_6_2_6_3_1_3_1_5_2_2_2_3_1_3_5_2_3_4_2_5_1_1_1_1_1_3_1_4_2_2_2_5_4_5_2_5_4_3_2_2_3_4_3_3_5_2_5_4_1_4_3_1_2_1_4_3_1_1_5_3_2_2_2_4_4_3_1_3_1_2_5_2_3_3_1_3_6_2_3_6_6_3_1_1_1_5_2_2_2_2_5_6_6_1_4_2_4_1_2_2_1_4_1_2_1_2_1_1_5_2_4_4_5_6_3_3_2_1_1_3_3_4_4_4_3_2_2_1_5_1_1_1_2_2_3_3_5_5_4_6_2_5_4_1_3_3_3_1_6_1_1_4_1_1_1_1_1_4_1_1_2_2_1_4_3_3_3_3_6_3_1_2_5_1_2_3_3_1_2_3_2_1_4_1_1_1_1_2_3_4_6_5_1_5_3_1_1_5_6_2_4_1_1_2_3_2_2_3_6_3_3_2_1_4_6_3_2_2_4_4_4_1_4_5_5_5_5_2_5_3_3_1_1_4_2_3_1_5_4_2_4_4_2_1_1_3_3_1_1_2_1_4_1_5_4_3_2_1_4_4_5_2_2_3_3_4_1_3_1_2_1_3_1_5_4_1_1_1_3_3_1_6_6_1_4_1_1_1_2_3_3_3_2_3_1_5_2_1_3_3_4_4_1_5_2</t>
+  </si>
+  <si>
+    <t>1_3_2_2_4_7_2_1_3_3_6_3_6_2_1_3_1_5_1_3_1_4_1_2_3_3_1_2_2_4_5_5_1_1_5_1_1_3_1_1_4_3_2_1_4_5_1_1_2_1_4_7_2_3_6_3_2_1_2_6_2_5_1_2_1_4_4_1_1_1_3_1_2_2_1_3_6_3_6_3_7_2_7_1_3_1_1_1_2_4_2_3_3_7_4_2_1_4_2_4_2_4_5_5_2_1_2_2_7_1_3_4_2_6_6_5_4_2_1_2_6_5_5_6_4_1_1_1_1_3_2_1_1_3_2_3_1_3_4_2_3_3_2_3_2_3_1_2_6_6_2_3_4_3_4_2_2_2_3_4_6_1_1_1_3_3_5_5_1_3_2_1_2_2_3_4_6_1_1_1_1_5_2_2_4_6_3_1_4_7_1_1_1_2_1_4_5_2_4_6_3_2_2_4_5_1_5_6_1_1_4_3_1_6_1_5_4_2_6_3_6_1_3_4_2_1_2_1_2_4_5_1_2_3_5_5_2_7_3_4_4_1_4_3_6_3_5_7_3_3_2_1_2_5_2_3_6_3_3_6_5_4_5_5_6_2_6_4_7_3_2_1_1_4_1_2_6_1_5_1_1_2_1_1_2_2_1_5_4_5_4_3_1_3_5_2_6_7_4_2_5_1_6_3_1_7_5_4_4_3_3_5_5_1_4_5_2_2_3_7_4_2_6_6_3_5_2_4_2_3_2_4_2_1_7_6_6_4_5_1_2_2_6_4_1_5_3_6_3_6_7_3_1_6_1_3_6_2_1_3_5_2_5_2_1_7_3_3_1_1_4_2_2_2_1_3_3_4_2_1_2_5_5_6_2_3_5_6_5_4_4_5_2_1_1_4_1_7_2_2_3_3_1_3_3_3_1_6_4_3_2_1_1_1_3_3_5_1_6_1_1_2_4_3_4_6_2_4_1_1_7_4_5_1_3_6_5_2_3_5_6_1_2_1_1_4_2_3_2_5_3_1_4_2_1_3_4_3_7_4_6_1_1_5_2_1_2_5_1_7_1_1_4_3_3_4_5_2_1_1_6_3_4_5_1_7_6_2_3_4_2_1_5_2_4_3_2_5_5_4</t>
+  </si>
+  <si>
+    <t>1_4_2_2_1_6_2_3_4_6_2_2_1_1_1_1_1_4_2_5_5_5_2_2_1_4_5_1_2_2_2_2_2_4_1_1_1_5_4_5_5_2_1_1_2_4_1_2_2_3_3_3_1_3_4_5_1_2_3_2_2_3_3_5_5_2_2_3_3_3_2_4_2_2_5_5_2_1_1_2_2_5_4_2_3_4_3_2_2_5_2_2_2_2_4_3_5_3_2_3_1_1_1_2_2_1_6_6_3_5_2_1_1_6_1_1_4_3_1_4_6_2_1_1_3_3_3_2_6_3_3_3_3_3_1_1_1_1_5_5_3_4_5_1_1_4_1_1_3_2_2_6_4_4_5_4_5_3_3_2_4_2_2_1_3_3_1_6_3_1_1_4_3_3_4_4_5_5_3_5_2_2_1_3_1_2_2_2_1_1_1_3_3_1_4_2_4_2_2_1_2_2_3_2_5_5_5_5_1_4_4_2_3_1_2_4_5_2_1_4_4_4_4_4_6_1_3_1_1_1_2_6_2_4_5_2_1_3_2_2_1_3_1_2_1_2_1_4_5_2_2_2_3_3_2_4_2_2_5_5_2_2_5_5_1_1_2_1_4_2_5_1_2_1_1_6_2_2_5_3_1_5_1_4_3_4_4_6_1_4_3_3_6_2_4_4_3_4_3_2_4_3_3_1_1_3_3_2_5_1_3_1_5_2_1_1_3_4_4_3_1_3_3_3_5_2_4_3_2_6_6_3_3_2_1_1_1_1_2_1_3_5_3_3_3_1_4_1_5_2_1_2_2_2_2_6_2_5_1_3_3_2_2_2_2_2_1_4_3_1_4_6_4_3_1_5_6_1_4_4_2_5_1_3_4_4_4_4_2_4_1_3_2_3_2_1_1_1_4_3_1_2_2_4_5_4_4_1_1_1_2_2_1_5_5_2_4_2_4_5_2_5_5_1_2_1_1_1_6_1_5_5_4_4_4_1_2_5_5_5_2_2_3_1_1_2_1_4_4_4_3_3_2_3_3_1_1_2_2_2_1_1_4_1_3_2_1_1_4_1_4_1_3_3_4_2_3_5_3_1_1_4_4_2_2_3_4_2_1_1_3_6_1_5_2_1_1_5_1_2</t>
+  </si>
+  <si>
+    <t>6_1_6_5_7_3_4_7_5_3_3_3_5_4_3_1_1_6_1_1_7_2_5_1_3_3_5_3_3_1_4_1_2_1_5_2_1_3_7_4_7_7_2_2_1_3_4_2_1_1_2_1_2_3_4_1_4_1_5_1_1_1_1_4_2_2_4_6_7_7_3_1_4_1_4_2_7_1_6_1_4_1_4_2_7_1_6_5_1_1_2_4_3_1_4_2_2_3_2_4_4_1_6_2_3_4_4_3_2_1_3_3_7_6_2_1_6_6_4_5_3_3_3_3_2_3_2_3_2_3_6_2_1_3_2_5_1_3_2_3_7_6_2_3_6_1_4_1_4_2_1_2_2_1_6_3_1_4_6_2_5_2_1_3_1_3_2_1_2_3_3_6_6_1_6_3_2_5_2_4_3_2_4_2_1_3_3_5_7_7_5_6_1_6_2_2_1_5_5_1_7_1_1_1_4_4_3_6_2_4_1_5_2_2_5_1_3_4_4_4_1_5_1_4_6_6_1_1_1_1_2_3_1_1_4_5_5_2_1_5_2_3_1_3_2_4_5_1_2_5_1_3_4_5_2_4_2_1_2_5_6_5_3_5_1_1_2_4_7_4_1_1_1_4_4_4_3_3_1_1_4_1_6_6_2_2_3_2_6_2_3_2_7_1_3_5_2_3_6_3_5_7_5_3_1_6_1_6_2_4_6_3_1_2_4_1_7_5_3_4_5_3_6_7_2_1_1_2_2_2_5_4_3_3_6_3_1_1_1_5_6_7_5_4_1_7_6_3_1_2_2_1_5_1_3_5_3_2_2_7_1_4_5_2_6_4_1_2_4_4_5_5_3_1_2_4_3_7_5_6_5_3_4_1_2_1_4_2_4_1_4_2_5_2_2_2_3_1_2_1_3_1_5_4_4_2_4_4_1_5_1_6_6_5_2_6_4_3_5_3_5_2_7_5_5_6_2_1_7_3_5_5_1_4_5_2_6_3_1_1_1_2_1_2_1_5_5_4_2_1_2_6_2_3_1_1_5_2_2_6_5_1_5_1_5_7_3_6_1_3_7_7_5_1_5_1_4_4_1_2_2_5_1_5_4_1_1_4_1_4_2_5_2_5_4_2_6_5_2_2</t>
+  </si>
+  <si>
+    <t>3_3_2_1_2_1_5_5_5_1_3_3_2_3_4_1_2_3_3_6_5_5_3_1_4_6_1_3_1_4_1_3_3_2_2_1_3_4_3_1_4_4_6_4_1_4_4_4_2_1_1_6_1_2_4_2_2_5_6_6_3_2_6_1_2_3_3_5_3_1_2_1_1_2_4_3_3_4_2_2_3_3_4_4_4_2_2_1_3_1_1_1_1_3_4_4_4_2_4_4_1_1_2_4_2_2_1_4_1_2_6_1_5_1_1_1_1_1_2_1_1_1_1_3_4_2_4_3_1_3_1_2_1_5_2_4_4_1_3_3_1_2_1_3_3_1_3_4_4_2_1_1_3_3_1_2_2_2_1_2_5_5_1_1_2_4_4_3_2_4_4_2_3_2_2_1_3_1_1_3_3_4_4_3_1_4_6_6_2_4_2_2_2_3_4_2_2_2_3_1_1_3_2_3_1_4_2_3_3_3_1_3_1_2_2_6_6_2_2_5_1_3_5_5_6_2_1_4_3_1_3_4_5_5_3_2_2_1_2_1_2_3_4_3_3_1_2_3_3_1_1_1_3_3_2_5_3_2_5_1_1_2_2_2_3_2_3_3_3_2_3_2_2_2_1_3_6_1_3_2_4_5_5_1_1_1_3_3_3_3_1_1_2_6_4_6_3_1_4_1_1_1_2_2_4_1_1_3_5_1_3_6_4_1_3_1_1_3_5_4_2_2_1_2_1_1_3_4_3_4_4_4_2_3_1_4_4_3_1_1_3_3_3_1_1_1_1_2_1_3_3_5_2_2_5_4_4_5_1_2_2_2_2_2_1_4_1_1_3_1_1_1_2_2_4_4_4_1_1_2_1_4_1_5_4_3_2_2_5_1_1_1_2_3_3_1_4_1_6_2_2_6_3_1_1_1_2_6_6_4_4_1_2_2_2_5_3_2_5_5_2_2_5_5_2_1_2_2_5_2_3_2_4_1_1_1_5_5_1_6_6_1_2_1_6_2_4_6_1_2_5_3_1_5_6_2_1_2_1_1_1_3_2_3_3_6_1_3_2_1_1_4_2_4_2_5_4_1_2_1_2_3_2_3_1_1_6_3_3_2_3_4_1_1_1_1_6_6_1_3</t>
+  </si>
+  <si>
+    <t>5_1_7_6_2_1_2_2_4_3_4_1_1_4_1_4_5_2_7_6_6_6_3_3_1_2_4_2_3_1_2_4_3_2_7_2_4_3_4_1_3_4_1_2_4_4_1_6_3_4_3_3_2_5_1_2_1_4_1_2_3_2_3_1_5_2_4_6_4_3_7_1_5_3_2_3_7_4_4_5_2_1_1_2_3_5_1_1_6_5_1_4_5_6_2_3_1_2_1_4_3_7_3_5_2_1_2_6_6_2_5_3_4_4_1_1_2_7_6_3_2_3_1_1_5_5_5_4_6_4_2_3_3_3_5_2_1_1_1_1_5_1_6_6_3_4_6_1_3_3_6_3_4_2_3_1_1_2_2_1_2_7_4_4_1_2_2_2_2_7_6_2_2_3_5_1_1_7_6_5_1_1_1_2_5_4_5_7_1_1_1_3_2_1_5_5_3_4_4_7_2_6_1_2_2_5_7_5_1_5_3_1_3_3_2_1_1_1_1_4_1_3_1_4_2_1_5_2_5_6_1_1_6_6_5_4_3_6_6_3_3_4_5_4_5_3_5_1_3_7_1_2_1_1_3_6_1_5_3_4_6_3_7_1_1_2_1_4_2_3_2_1_1_3_3_4_3_1_1_4_5_4_1_4_4_7_2_4_6_2_3_2_4_1_5_4_2_4_1_4_6_2_1_4_1_1_1_7_1_6_6_6_2_2_6_2_1_4_3_1_5_2_4_4_2_4_1_6_2_3_1_1_1_4_3_1_2_7_2_7_5_1_1_4_4_6_4_5_6_2_1_3_1_6_6_4_2_2_2_5_6_2_6_6_1_2_4_1_1_1_6_1_2_7_3_5_1_1_3_1_4_3_6_6_5_3_4_2_3_2_3_1_3_3_1_5_1_2_6_6_3_5_5_1_3_3_1_4_2_1_4_5_1_6_2_4_4_3_4_3_2_6_6_3_4_1_5_5_3_1_4_1_1_4_5_6_2_2_1_3_4_4_1_5_2_2_3_1_7_3_4_6_2_4_2_3_2_3_6_3_2_6_2_4_7_5_3_3_7_5_2_3_1_5_3_2_5_2_1_2_2_1_5_3_1_4_4_5_2_3_3_3_3_1_4_2_4_2_6_4</t>
+  </si>
+  <si>
+    <t>8_13_13_13_8_13_13_13_8_13_13_13_13_13_13_13_13_13_8_8_8_13_8_8_8_8_8_13_8_8_8_8_13_13_13_13_8_8_8_13_13_8_8_8_8_8_8_13_8_8_13_8_8_8_13_13_8_13_13_8_8_8_13_8_8_8_8_8_13_13_8_8_13_8_8_13_8_8_8_8_13_8_8_13_13_13_8_13_13_13_8_8_8_13_13_13_8_8_13_13_13_13_8_8_8_8_13_13_13_13_8_13_13_8_8_8_8_13_13_13_13_8_13_8_13_8_8_8_13_13_8_13_8_8_8_13_13_8_8_13_8_8_13_13_13_8_8_13_13_13_13_8_8_8_8_13_13_13_8_13_8_13_8_13_8_8_8_8_8_8_13_13_8_13_8_13_13_8_8_13_8_13_8_8_13_13_8_8_8_8_8_8_8_8_8_13_8_13_13_13_8_13_8_13_13_13_8_13_13_13_13_8_13_13_13_8_8_8_13_13_13_13_13_13_13_8_8_8_8_13_8_8_8_8_8_13_8_8_8_8_13_8_8_8_13_8_13_8_13_8_13_8_8_8_13_8_8_13_8_13_8_13_8_8_13_13_8_8_8_8_8_8_8_13_8_13_8_8_13_13_13_13_13_13_13_13_13_8_13_8_8_8_8_8_8_13_13_13_8_13_13_8_8_8_13_13_13_13_8_13_13_13_13_13_8_8_13_8_13_13_8_8_8_13_13_13_13_8_8_8_13_8_8_13_8_8_8_13_13_8_13_13_8_8_8_8_8_13_8_13_8_8_13_13_13_8_13_13_13_8_13_8_8_8_8_8_8_8_13_8_13_13_8_13_8_8_13_8_13_13_13_8_8_13_13_8_13_8_13_8_8_8_13_13_13_13_8_8_8_13_13_8_8_13_8_13_13_8_8_13_8_13_8_13_13_13_13_8_13_13_8_8_13_13_8_13_8_13_13_13_8_8_13_13_13_8_8_13_13_8_13_8_13_13_8_13_8_13_13_8_13_13_8_8_8_8_13_13_13_13_8_8_8_8_13_8_8_13_8_13_13_8_13_8_8_8_8_13_8_8_8_8_13_8_13_13_13_8_13_13_13_13_8_13_13_8_8_8_13_8</t>
+  </si>
+  <si>
+    <t>8_13_8_13_13_13_13_8_8_8_8_13_13_8_8_8_13_13_8_8_13_13_13_8_8_8_8_8_13_13_13_8_8_8_13_13_13_8_13_13_8_13_8_8_8_13_13_13_13_8_8_13_8_8_8_13_8_8_8_8_13_8_8_8_13_8_8_13_8_8_13_13_13_13_8_13_8_8_8_8_8_13_13_8_13_8_13_13_8_8_13_13_8_8_8_13_13_13_8_13_8_8_8_13_13_13_8_8_8_8_8_13_13_8_13_13_13_8_13_13_13_13_8_13_8_8_8_8_8_13_8_13_8_8_8_8_8_13_8_8_13_8_8_13_8_8_8_8_8_13_13_8_13_13_13_13_8_13_13_13_8_13_13_8_13_13_13_13_13_8_8_13_8_13_8_13_8_13_13_8_13_8_13_13_8_8_13_8_13_8_13_8_8_13_8_13_8_13_13_8_13_13_13_8_13_8_8_8_8_13_8_8_13_13_8_8_8_13_13_13_13_8_8_8_13_8_8_8_13_8_8_13_8_8_8_8_8_13_8_8_8_8_8_8_8_13_8_8_13_13_13_8_8_8_8_8_8_13_13_8_13_13_13_8_13_8_8_13_13_13_13_8_8_13_8_13_13_13_13_13_13_13_13_8_8_8_13_8_8_8_8_13_8_13_13_13_13_8_8_8_8_13_13_13_13_13_13_13_13_13_8_8_13_13_13_13_13_8_13_8_13_13_13_13_8_8_8_8_8_8_8_13_8_8_8_13_8_8_8_8_8_8_8_8_8_13_13_13_8_8_13_13_13_13_13_13_13_13_8_8_13_8_13_13_8_13_8_8_13_8_13_13_8_8_8_8_13_8_13_13_13_13_8_8_8_13_13_8_8_8_13_13_13_13_13_8_13_8_13_8_13_13_8_13_13_8_8_8_13_13_8_8_13_8_8_8_8_8_8_13_13_13_8_13_8_8_13_8_8_8_13_13_8_13_13_13_13_8_8_8_13_8_13_13_13_13_8_13_8_8_13_13_13_13_13_8_8_8_13_13_13_8_8_8_8_8_13_13_13_8_13_13_8_13_8_13_13_8_13_13_13_13_8_8_13_8_13_13_13_8_13_8_8_13_8_13_8_13_13_8</t>
+  </si>
+  <si>
+    <t>8_8_8_8_13_13_13_13_8_13_13_13_13_13_8_13_8_13_13_13_13_13_13_13_8_13_8_8_8_13_13_8_8_13_8_13_8_8_8_13_13_13_8_8_13_13_13_13_13_8_8_13_8_8_8_8_13_13_8_8_13_13_8_13_8_13_13_8_8_8_13_8_13_8_8_8_13_13_8_13_8_13_13_8_13_13_13_8_8_8_8_8_13_13_13_8_13_13_13_13_13_13_13_8_8_8_8_13_13_13_13_13_13_8_13_8_13_8_8_8_13_8_8_8_8_13_13_13_8_13_13_13_8_8_13_8_8_8_8_13_13_13_13_8_13_13_8_13_8_13_13_8_13_8_13_8_13_13_8_8_13_13_13_13_8_13_13_8_13_8_8_13_13_13_8_8_13_8_13_8_13_8_8_13_8_13_13_13_13_13_13_13_8_8_8_8_8_13_13_13_13_8_8_13_13_8_8_8_8_13_8_13_13_8_13_13_8_8_8_8_13_13_8_13_13_13_8_13_8_8_8_8_8_8_8_13_8_8_8_8_13_8_8_8_13_13_8_8_13_8_8_8_13_8_8_13_13_8_8_13_8_8_8_8_8_13_13_13_8_8_8_8_13_13_13_8_8_8_8_13_13_8_13_8_8_8_8_13_13_13_8_13_13_13_13_13_13_8_8_13_13_13_8_13_8_13_13_13_13_8_8_13_13_8_8_8_13_13_13_13_13_13_8_8_8_8_8_13_13_8_8_8_8_13_8_13_8_8_13_13_8_8_8_8_13_13_8_13_8_13_8_8_8_8_13_13_8_13_8_8_13_13_8_13_13_8_8_8_13_13_8_8_8_8_8_8_13_13_13_8_8_8_8_8_8_8_13_8_13_13_8_8_8_13_8_13_13_13_13_13_8_13_8_13_8_13_8_13_8_8_8_13_8_8_8_13_13_13_13_8_13_13_13_8_13_8_8_8_8_8_8_13_13_13_13_13_8_8_8_8_8_8_13_13_8_8_13_8_8_8_8_8_8_8_13_8_13_13_13_8_8_8_8_8_13_13_13_8_8_13_13_13_8_8_8_8_13_13_8_8_13_13_13_13_13_8_13_8_13_8_8_13_13_13_13_8_13_8_8_8</t>
+  </si>
+  <si>
+    <t>1_501</t>
+  </si>
+  <si>
+    <t>1_502</t>
+  </si>
+  <si>
+    <t>1_503</t>
   </si>
 </sst>
 </file>
@@ -497,6 +600,11 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -504,11 +612,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1175,89 +1278,89 @@
   </cellStyleXfs>
   <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1785,19 +1888,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
-    <col min="2" max="2" width="9" style="6"/>
+    <col min="2" max="2" width="9" style="7"/>
     <col min="4" max="4" width="7.875" customWidth="1"/>
     <col min="5" max="5" width="28.75" customWidth="1"/>
     <col min="6" max="6" width="23.525" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
     <col min="8" max="8" width="22.5" customWidth="1"/>
     <col min="9" max="9" width="17.875" customWidth="1"/>
-    <col min="10" max="10" width="25.125" style="7" customWidth="1"/>
-    <col min="11" max="11" width="36.125" style="7" customWidth="1"/>
+    <col min="10" max="10" width="25.125" style="8" customWidth="1"/>
+    <col min="11" max="11" width="36.125" style="8" customWidth="1"/>
     <col min="13" max="13" width="12.625"/>
   </cols>
   <sheetData>
@@ -1805,59 +1908,59 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
     </row>
     <row r="2" ht="16.5" spans="1:11">
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J2" s="17"/>
@@ -1867,42 +1970,42 @@
       <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="J3" s="17"/>
       <c r="K3" s="17"/>
     </row>
     <row r="4" ht="16.5" spans="1:11">
-      <c r="B4" s="13"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="15"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="16"/>
       <c r="E4" s="18"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
       <c r="J4" s="17"/>
       <c r="K4" s="17"/>
     </row>
@@ -1911,28 +2014,28 @@
         <f t="shared" ref="A5:A56" si="0">C5*10+D5</f>
         <v>20010011</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="14">
         <v>100100</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="15">
         <v>2001001</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="16">
         <v>1</v>
       </c>
       <c r="E5" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="16" t="s">
+      <c r="F5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="16" t="s">
+      <c r="H5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J5" s="17"/>
@@ -1943,28 +2046,28 @@
         <f t="shared" si="0"/>
         <v>20010012</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="14">
         <v>100100</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="15">
         <v>2001001</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="16">
         <v>2</v>
       </c>
       <c r="E6" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="16" t="s">
+      <c r="F6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="16" t="s">
+      <c r="H6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J6" s="17"/>
@@ -1975,28 +2078,28 @@
         <f t="shared" si="0"/>
         <v>20010013</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="14">
         <v>100100</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="15">
         <v>2001001</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="16">
         <v>3</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="16" t="s">
+      <c r="F7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="16" t="s">
+      <c r="H7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>28</v>
       </c>
       <c r="J7" s="17"/>
@@ -2007,28 +2110,28 @@
         <f t="shared" si="0"/>
         <v>20010014</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="14">
         <v>100100</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="15">
         <v>2001001</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="16">
         <v>4</v>
       </c>
       <c r="E8" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="16" t="s">
+      <c r="F8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="16" t="s">
+      <c r="H8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>31</v>
       </c>
       <c r="J8" s="17"/>
@@ -2039,35 +2142,35 @@
         <f t="shared" si="0"/>
         <v>20010015</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="14">
         <v>100100</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="15">
         <v>2001001</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="16">
         <v>5</v>
       </c>
       <c r="E9" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="16" t="s">
+      <c r="F9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="16" t="s">
+      <c r="H9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
     </row>
-    <row r="10" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A10" s="1">
+    <row r="10" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>20030011</v>
       </c>
@@ -2080,25 +2183,25 @@
       <c r="D10" s="20">
         <v>1</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>35</v>
       </c>
       <c r="F10" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="H10" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A11" s="1">
+    <row r="11" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>20030012</v>
       </c>
@@ -2111,25 +2214,25 @@
       <c r="D11" s="20">
         <v>2</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>35</v>
       </c>
       <c r="F11" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H11" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="2" t="s">
         <v>40</v>
       </c>
       <c r="J11" s="21"/>
     </row>
-    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A12" s="1">
+    <row r="12" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>20030013</v>
       </c>
@@ -2142,25 +2245,25 @@
       <c r="D12" s="20">
         <v>3</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>35</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="2" t="s">
         <v>41</v>
       </c>
       <c r="H12" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="2" t="s">
         <v>42</v>
       </c>
       <c r="J12" s="21"/>
     </row>
-    <row r="13" s="2" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A13" s="2">
+    <row r="13" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>20030021</v>
       </c>
@@ -2173,25 +2276,25 @@
       <c r="D13" s="23">
         <v>1</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F13" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="3" t="s">
         <v>37</v>
       </c>
       <c r="H13" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="3" t="s">
         <v>37</v>
       </c>
       <c r="J13" s="24"/>
     </row>
-    <row r="14" s="2" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A14" s="2">
+    <row r="14" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>20030022</v>
       </c>
@@ -2204,25 +2307,25 @@
       <c r="D14" s="23">
         <v>2</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H14" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="3" t="s">
         <v>39</v>
       </c>
       <c r="J14" s="24"/>
     </row>
-    <row r="15" s="2" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A15" s="2">
+    <row r="15" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>20030023</v>
       </c>
@@ -2235,24 +2338,24 @@
       <c r="D15" s="23">
         <v>3</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F15" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="3" t="s">
         <v>43</v>
       </c>
       <c r="H15" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="3" t="s">
         <v>43</v>
       </c>
       <c r="J15" s="24"/>
     </row>
-    <row r="16" s="3" customFormat="1" ht="16.5" spans="1:11">
+    <row r="16" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>20070011</v>
@@ -2260,31 +2363,31 @@
       <c r="B16" s="25">
         <v>100700</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="15">
         <v>2007001</v>
       </c>
       <c r="D16" s="26">
         <v>1</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="F16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="H16" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="H16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I16" s="4" t="s">
         <v>46</v>
       </c>
       <c r="J16" s="17"/>
-      <c r="K16" s="7"/>
-    </row>
-    <row r="17" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="K16" s="8"/>
+    </row>
+    <row r="17" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>20070012</v>
@@ -2292,31 +2395,31 @@
       <c r="B17" s="25">
         <v>100700</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="15">
         <v>2007001</v>
       </c>
       <c r="D17" s="26">
         <v>2</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="F17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H17" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="H17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J17" s="17"/>
-      <c r="K17" s="7"/>
-    </row>
-    <row r="18" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="K17" s="8"/>
+    </row>
+    <row r="18" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>20070013</v>
@@ -2324,31 +2427,31 @@
       <c r="B18" s="25">
         <v>100700</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="15">
         <v>2007001</v>
       </c>
       <c r="D18" s="26">
         <v>3</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="F18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H18" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="H18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I18" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J18" s="17"/>
-      <c r="K18" s="7"/>
-    </row>
-    <row r="19" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>20070014</v>
@@ -2356,31 +2459,31 @@
       <c r="B19" s="25">
         <v>100700</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="15">
         <v>2007001</v>
       </c>
       <c r="D19" s="26">
         <v>4</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="F19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H19" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="H19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>55</v>
       </c>
       <c r="J19" s="17"/>
-      <c r="K19" s="7"/>
-    </row>
-    <row r="20" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="K19" s="8"/>
+    </row>
+    <row r="20" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>20070015</v>
@@ -2388,32 +2491,32 @@
       <c r="B20" s="25">
         <v>100700</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="15">
         <v>2007001</v>
       </c>
       <c r="D20" s="26">
         <v>5</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="F20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H20" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="H20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>58</v>
       </c>
       <c r="J20" s="17"/>
-      <c r="K20" s="7"/>
-    </row>
-    <row r="21" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A21" s="4">
+      <c r="K20" s="8"/>
+    </row>
+    <row r="21" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A21" s="5">
         <f t="shared" si="0"/>
         <v>20120011</v>
       </c>
@@ -2444,8 +2547,8 @@
       <c r="J21" s="29"/>
       <c r="K21" s="29"/>
     </row>
-    <row r="22" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A22" s="4">
+    <row r="22" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A22" s="5">
         <f t="shared" si="0"/>
         <v>20120012</v>
       </c>
@@ -2476,8 +2579,8 @@
       <c r="J22" s="29"/>
       <c r="K22" s="29"/>
     </row>
-    <row r="23" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A23" s="4">
+    <row r="23" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A23" s="5">
         <f t="shared" si="0"/>
         <v>20120013</v>
       </c>
@@ -2508,8 +2611,8 @@
       <c r="J23" s="29"/>
       <c r="K23" s="29"/>
     </row>
-    <row r="24" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A24" s="4">
+    <row r="24" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A24" s="5">
         <f t="shared" si="0"/>
         <v>20120014</v>
       </c>
@@ -2540,8 +2643,8 @@
       <c r="J24" s="29"/>
       <c r="K24" s="29"/>
     </row>
-    <row r="25" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A25" s="4">
+    <row r="25" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A25" s="5">
         <f t="shared" si="0"/>
         <v>20120015</v>
       </c>
@@ -2577,10 +2680,10 @@
         <f t="shared" si="0"/>
         <v>20140011</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="14">
         <v>101400</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="15">
         <v>2014001</v>
       </c>
       <c r="D26" s="18">
@@ -2589,13 +2692,13 @@
       <c r="E26" t="s">
         <v>44</v>
       </c>
-      <c r="F26" s="16" t="s">
+      <c r="F26" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G26" t="s">
         <v>70</v>
       </c>
-      <c r="H26" s="16" t="s">
+      <c r="H26" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I26" t="s">
@@ -2608,10 +2711,10 @@
         <f t="shared" si="0"/>
         <v>20140012</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="14">
         <v>101400</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="15">
         <v>2014001</v>
       </c>
       <c r="D27" s="18">
@@ -2620,13 +2723,13 @@
       <c r="E27" t="s">
         <v>44</v>
       </c>
-      <c r="F27" s="16" t="s">
+      <c r="F27" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G27" t="s">
         <v>72</v>
       </c>
-      <c r="H27" s="16" t="s">
+      <c r="H27" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I27" t="s">
@@ -2639,10 +2742,10 @@
         <f t="shared" si="0"/>
         <v>20140013</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="14">
         <v>101400</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="15">
         <v>2014001</v>
       </c>
       <c r="D28" s="18">
@@ -2651,13 +2754,13 @@
       <c r="E28" t="s">
         <v>44</v>
       </c>
-      <c r="F28" s="16" t="s">
+      <c r="F28" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G28" t="s">
         <v>73</v>
       </c>
-      <c r="H28" s="16" t="s">
+      <c r="H28" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I28" t="s">
@@ -2670,10 +2773,10 @@
         <f t="shared" si="0"/>
         <v>20140044</v>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="14">
         <v>101400</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="15">
         <v>2014004</v>
       </c>
       <c r="D29" s="18">
@@ -2682,30 +2785,30 @@
       <c r="E29" t="s">
         <v>44</v>
       </c>
-      <c r="F29" s="16" t="s">
+      <c r="F29" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G29" t="s">
         <v>74</v>
       </c>
-      <c r="H29" s="16" t="s">
+      <c r="H29" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I29" t="s">
         <v>71</v>
       </c>
       <c r="J29" s="17"/>
-      <c r="K29" s="7"/>
+      <c r="K29" s="8"/>
     </row>
     <row r="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>20140055</v>
       </c>
-      <c r="B30" s="13">
+      <c r="B30" s="14">
         <v>101400</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="15">
         <v>2014005</v>
       </c>
       <c r="D30" s="18">
@@ -2714,30 +2817,30 @@
       <c r="E30" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="16" t="s">
+      <c r="F30" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G30" t="s">
         <v>74</v>
       </c>
-      <c r="H30" s="16" t="s">
+      <c r="H30" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I30" t="s">
         <v>71</v>
       </c>
       <c r="J30" s="17"/>
-      <c r="K30" s="7"/>
+      <c r="K30" s="8"/>
     </row>
     <row r="31" ht="16.5" spans="1:11">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>20140066</v>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="14">
         <v>101400</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="15">
         <v>2014006</v>
       </c>
       <c r="D31" s="18">
@@ -2746,13 +2849,13 @@
       <c r="E31" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="16" t="s">
+      <c r="F31" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G31" t="s">
         <v>75</v>
       </c>
-      <c r="H31" s="16" t="s">
+      <c r="H31" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I31" t="s">
@@ -2765,10 +2868,10 @@
         <f t="shared" si="0"/>
         <v>20140077</v>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="14">
         <v>101400</v>
       </c>
-      <c r="C32" s="14">
+      <c r="C32" s="15">
         <v>2014007</v>
       </c>
       <c r="D32" s="18">
@@ -2777,14 +2880,14 @@
       <c r="E32" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="16" t="s">
+      <c r="F32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G32" t="str">
         <f t="shared" ref="G30:G34" si="1">G31</f>
         <v>1_10_10_10_10_1_2_2_1_3_3_3_1_10_10_10_1_4_4_4_4_1_8_8_1_12_1_10_1_5_5_5_5_1_6_6_6_6_6_6_6_1_4_1_10_10_1_7_1_12_1_4_4_1_4_4_4_1_6_6_1_6_6_6_6_6_6_6_6_6_6_6_6_6_6_1_8_1_9_1_9_9_9_9_9_9_9_9_9_1_6_6_6_6_6_1_8_1_2_1_9_9_1_12_1_9_1_8_8_8_8_8_8_1_7_7_7_7_1_8_8_8_8_8_8_8_8_8_1_2_2_2_1_7_7_7_1_6_6_6_6_6_6_6_1_3_3_3_3_1_5_5_5_5_1_8_8_8_1_12_1_2_1_5_5_1_10_1_8_1_3_3_3_3_3_3_3_3_3_3_1_6_6_1_8_8_8_8_8_8_8_1_10_10_1_2_2_2_2_2_2_2_1_2_2_1_8_1_7_7_1_7_7_1_11_11_11_11_1_7_7_1_5_1_2_1_2_1_6_6_6_6_6_6_6_6_1_11_11_11_1_3_3_3_1_6_1_12_1_9_1_5_5_5_1_12_1_2_2_1_9_9_9_1_12_1_11_11_11_1_7_7_7_7_7_7_1_2_2_2_2_1_8_8_8_1_10_10_1_7_1_3_1_5_5_1_4_4_1_11_1_5_5_5_5_5_5_5_1_7_1_8_8_8_1_4_4_4_4_4_4_4_1_12_1_11_11_11_11_11_11_1_2_1_4_4_4_4_4_4_1_11_11_11_11_11_1_9_9_9_9_1_9_9_9_9_9_9_1_5_1_8_8_8_8_1_4_1_4_1_8_8_8_1_11_11_11_11_11_11_11_11_1_9_9_1_8_1_8_8_8_1_12_1_12_1_11_11_11_11_1_5_5_5_5_5_5_5_1_3_3_3_1_11_1_2_2_1_2_2_2_1_2_2_2_2_2_2_2_2_1_9_9_9_9_9_9_9_1_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_1_11_11_11_11_1_10_1_4_4_4_4_4_4_4_4_4_4_1_4_4_4_4_1_3_1_9_9_1_10_10_10_10_10_10_10_1_10_1_12_1_7_1_3</v>
       </c>
-      <c r="H32" s="16" t="s">
+      <c r="H32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I32" t="s">
@@ -2797,10 +2900,10 @@
         <f t="shared" si="0"/>
         <v>20140088</v>
       </c>
-      <c r="B33" s="13">
+      <c r="B33" s="14">
         <v>101400</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="15">
         <v>2014008</v>
       </c>
       <c r="D33" s="18">
@@ -2809,14 +2912,14 @@
       <c r="E33" t="s">
         <v>44</v>
       </c>
-      <c r="F33" s="16" t="s">
+      <c r="F33" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G33" t="str">
         <f t="shared" si="1"/>
         <v>1_10_10_10_10_1_2_2_1_3_3_3_1_10_10_10_1_4_4_4_4_1_8_8_1_12_1_10_1_5_5_5_5_1_6_6_6_6_6_6_6_1_4_1_10_10_1_7_1_12_1_4_4_1_4_4_4_1_6_6_1_6_6_6_6_6_6_6_6_6_6_6_6_6_6_1_8_1_9_1_9_9_9_9_9_9_9_9_9_1_6_6_6_6_6_1_8_1_2_1_9_9_1_12_1_9_1_8_8_8_8_8_8_1_7_7_7_7_1_8_8_8_8_8_8_8_8_8_1_2_2_2_1_7_7_7_1_6_6_6_6_6_6_6_1_3_3_3_3_1_5_5_5_5_1_8_8_8_1_12_1_2_1_5_5_1_10_1_8_1_3_3_3_3_3_3_3_3_3_3_1_6_6_1_8_8_8_8_8_8_8_1_10_10_1_2_2_2_2_2_2_2_1_2_2_1_8_1_7_7_1_7_7_1_11_11_11_11_1_7_7_1_5_1_2_1_2_1_6_6_6_6_6_6_6_6_1_11_11_11_1_3_3_3_1_6_1_12_1_9_1_5_5_5_1_12_1_2_2_1_9_9_9_1_12_1_11_11_11_1_7_7_7_7_7_7_1_2_2_2_2_1_8_8_8_1_10_10_1_7_1_3_1_5_5_1_4_4_1_11_1_5_5_5_5_5_5_5_1_7_1_8_8_8_1_4_4_4_4_4_4_4_1_12_1_11_11_11_11_11_11_1_2_1_4_4_4_4_4_4_1_11_11_11_11_11_1_9_9_9_9_1_9_9_9_9_9_9_1_5_1_8_8_8_8_1_4_1_4_1_8_8_8_1_11_11_11_11_11_11_11_11_1_9_9_1_8_1_8_8_8_1_12_1_12_1_11_11_11_11_1_5_5_5_5_5_5_5_1_3_3_3_1_11_1_2_2_1_2_2_2_1_2_2_2_2_2_2_2_2_1_9_9_9_9_9_9_9_1_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_1_11_11_11_11_1_10_1_4_4_4_4_4_4_4_4_4_4_1_4_4_4_4_1_3_1_9_9_1_10_10_10_10_10_10_10_1_10_1_12_1_7_1_3</v>
       </c>
-      <c r="H33" s="16" t="s">
+      <c r="H33" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I33" t="s">
@@ -2829,10 +2932,10 @@
         <f t="shared" si="0"/>
         <v>20140099</v>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="14">
         <v>101400</v>
       </c>
-      <c r="C34" s="14">
+      <c r="C34" s="15">
         <v>2014009</v>
       </c>
       <c r="D34" s="18">
@@ -2841,31 +2944,31 @@
       <c r="E34" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="16" t="s">
+      <c r="F34" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G34" t="str">
         <f t="shared" si="1"/>
         <v>1_10_10_10_10_1_2_2_1_3_3_3_1_10_10_10_1_4_4_4_4_1_8_8_1_12_1_10_1_5_5_5_5_1_6_6_6_6_6_6_6_1_4_1_10_10_1_7_1_12_1_4_4_1_4_4_4_1_6_6_1_6_6_6_6_6_6_6_6_6_6_6_6_6_6_1_8_1_9_1_9_9_9_9_9_9_9_9_9_1_6_6_6_6_6_1_8_1_2_1_9_9_1_12_1_9_1_8_8_8_8_8_8_1_7_7_7_7_1_8_8_8_8_8_8_8_8_8_1_2_2_2_1_7_7_7_1_6_6_6_6_6_6_6_1_3_3_3_3_1_5_5_5_5_1_8_8_8_1_12_1_2_1_5_5_1_10_1_8_1_3_3_3_3_3_3_3_3_3_3_1_6_6_1_8_8_8_8_8_8_8_1_10_10_1_2_2_2_2_2_2_2_1_2_2_1_8_1_7_7_1_7_7_1_11_11_11_11_1_7_7_1_5_1_2_1_2_1_6_6_6_6_6_6_6_6_1_11_11_11_1_3_3_3_1_6_1_12_1_9_1_5_5_5_1_12_1_2_2_1_9_9_9_1_12_1_11_11_11_1_7_7_7_7_7_7_1_2_2_2_2_1_8_8_8_1_10_10_1_7_1_3_1_5_5_1_4_4_1_11_1_5_5_5_5_5_5_5_1_7_1_8_8_8_1_4_4_4_4_4_4_4_1_12_1_11_11_11_11_11_11_1_2_1_4_4_4_4_4_4_1_11_11_11_11_11_1_9_9_9_9_1_9_9_9_9_9_9_1_5_1_8_8_8_8_1_4_1_4_1_8_8_8_1_11_11_11_11_11_11_11_11_1_9_9_1_8_1_8_8_8_1_12_1_12_1_11_11_11_11_1_5_5_5_5_5_5_5_1_3_3_3_1_11_1_2_2_1_2_2_2_1_2_2_2_2_2_2_2_2_1_9_9_9_9_9_9_9_1_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_8_1_11_11_11_11_1_10_1_4_4_4_4_4_4_4_4_4_4_1_4_4_4_4_1_3_1_9_9_1_10_10_10_10_10_10_10_1_10_1_12_1_7_1_3</v>
       </c>
-      <c r="H34" s="16" t="s">
+      <c r="H34" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I34" t="s">
         <v>71</v>
       </c>
       <c r="J34" s="17"/>
-      <c r="K34" s="7"/>
+      <c r="K34" s="8"/>
     </row>
     <row r="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>20140110</v>
       </c>
-      <c r="B35" s="13">
+      <c r="B35" s="14">
         <v>101400</v>
       </c>
-      <c r="C35" s="14">
+      <c r="C35" s="15">
         <v>2014010</v>
       </c>
       <c r="D35" s="18">
@@ -2874,30 +2977,30 @@
       <c r="E35" t="s">
         <v>44</v>
       </c>
-      <c r="F35" s="16" t="s">
+      <c r="F35" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G35" t="s">
         <v>76</v>
       </c>
-      <c r="H35" s="16" t="s">
+      <c r="H35" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I35" t="s">
         <v>71</v>
       </c>
       <c r="J35" s="17"/>
-      <c r="K35" s="7"/>
+      <c r="K35" s="8"/>
     </row>
     <row r="36" customFormat="1" ht="16.5" spans="1:11">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>20140121</v>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="14">
         <v>101400</v>
       </c>
-      <c r="C36" s="14">
+      <c r="C36" s="15">
         <v>2014011</v>
       </c>
       <c r="D36" s="18">
@@ -2906,48 +3009,48 @@
       <c r="E36" t="s">
         <v>44</v>
       </c>
-      <c r="F36" s="16" t="s">
+      <c r="F36" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G36" t="s">
         <v>77</v>
       </c>
-      <c r="H36" s="16" t="s">
+      <c r="H36" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I36" t="s">
         <v>71</v>
       </c>
       <c r="J36" s="17"/>
-      <c r="K36" s="7"/>
+      <c r="K36" s="8"/>
     </row>
     <row r="37" ht="16.5" spans="1:11">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>20240011</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="14">
         <v>102400</v>
       </c>
-      <c r="C37" s="14">
+      <c r="C37" s="15">
         <v>2024001</v>
       </c>
-      <c r="D37" s="15">
+      <c r="D37" s="16">
         <v>1</v>
       </c>
       <c r="E37" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="F37" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G37" s="16" t="s">
+      <c r="F37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H37" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I37" s="16" t="s">
+      <c r="H37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J37" s="17"/>
@@ -2958,28 +3061,28 @@
         <f t="shared" si="0"/>
         <v>20240012</v>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="14">
         <v>102400</v>
       </c>
-      <c r="C38" s="14">
+      <c r="C38" s="15">
         <v>2024001</v>
       </c>
-      <c r="D38" s="15">
+      <c r="D38" s="16">
         <v>2</v>
       </c>
       <c r="E38" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="F38" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38" s="16" t="s">
+      <c r="F38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H38" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I38" s="16" t="s">
+      <c r="H38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J38" s="17"/>
@@ -2990,28 +3093,28 @@
         <f t="shared" si="0"/>
         <v>20240013</v>
       </c>
-      <c r="B39" s="13">
+      <c r="B39" s="14">
         <v>102400</v>
       </c>
-      <c r="C39" s="14">
+      <c r="C39" s="15">
         <v>2024001</v>
       </c>
-      <c r="D39" s="15">
+      <c r="D39" s="16">
         <v>3</v>
       </c>
       <c r="E39" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="F39" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G39" s="16" t="s">
+      <c r="F39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H39" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I39" s="16" t="s">
+      <c r="H39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I39" s="1" t="s">
         <v>28</v>
       </c>
       <c r="J39" s="17"/>
@@ -3022,28 +3125,28 @@
         <f t="shared" si="0"/>
         <v>20240014</v>
       </c>
-      <c r="B40" s="13">
+      <c r="B40" s="14">
         <v>102400</v>
       </c>
-      <c r="C40" s="14">
+      <c r="C40" s="15">
         <v>2024001</v>
       </c>
-      <c r="D40" s="15">
+      <c r="D40" s="16">
         <v>4</v>
       </c>
       <c r="E40" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F40" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G40" s="16" t="s">
+      <c r="F40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H40" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I40" s="16" t="s">
+      <c r="H40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I40" s="1" t="s">
         <v>31</v>
       </c>
       <c r="J40" s="17"/>
@@ -3054,35 +3157,35 @@
         <f t="shared" si="0"/>
         <v>20240015</v>
       </c>
-      <c r="B41" s="13">
+      <c r="B41" s="14">
         <v>102400</v>
       </c>
-      <c r="C41" s="14">
+      <c r="C41" s="15">
         <v>2024001</v>
       </c>
-      <c r="D41" s="15">
+      <c r="D41" s="16">
         <v>5</v>
       </c>
       <c r="E41" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F41" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G41" s="16" t="s">
+      <c r="F41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H41" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I41" s="16" t="s">
+      <c r="H41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="17"/>
     </row>
-    <row r="42" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A42" s="5">
+    <row r="42" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A42" s="6">
         <f t="shared" si="0"/>
         <v>20170011</v>
       </c>
@@ -3095,26 +3198,26 @@
       <c r="D42" s="31">
         <v>1</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G42" s="5" t="s">
+      <c r="F42" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H42" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I42" s="5" t="s">
+      <c r="H42" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I42" s="6" t="s">
         <v>46</v>
       </c>
       <c r="J42" s="32"/>
       <c r="K42" s="32"/>
     </row>
-    <row r="43" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A43" s="5">
+    <row r="43" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A43" s="6">
         <f t="shared" si="0"/>
         <v>20170012</v>
       </c>
@@ -3127,26 +3230,26 @@
       <c r="D43" s="31">
         <v>2</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F43" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G43" s="5" t="s">
+      <c r="F43" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G43" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="H43" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I43" s="5" t="s">
+      <c r="H43" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I43" s="6" t="s">
         <v>49</v>
       </c>
       <c r="J43" s="32"/>
       <c r="K43" s="32"/>
     </row>
-    <row r="44" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A44" s="5">
+    <row r="44" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A44" s="6">
         <f t="shared" si="0"/>
         <v>20170013</v>
       </c>
@@ -3159,26 +3262,26 @@
       <c r="D44" s="31">
         <v>3</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F44" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G44" s="5" t="s">
+      <c r="F44" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="H44" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I44" s="5" t="s">
+      <c r="H44" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I44" s="6" t="s">
         <v>52</v>
       </c>
       <c r="J44" s="32"/>
       <c r="K44" s="32"/>
     </row>
-    <row r="45" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A45" s="5">
+    <row r="45" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A45" s="6">
         <f t="shared" si="0"/>
         <v>20170014</v>
       </c>
@@ -3191,26 +3294,26 @@
       <c r="D45" s="31">
         <v>4</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F45" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G45" s="5" t="s">
+      <c r="F45" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G45" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="H45" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I45" s="5" t="s">
+      <c r="H45" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I45" s="6" t="s">
         <v>55</v>
       </c>
       <c r="J45" s="32"/>
       <c r="K45" s="32"/>
     </row>
-    <row r="46" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A46" s="5">
+    <row r="46" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A46" s="6">
         <f t="shared" si="0"/>
         <v>20170015</v>
       </c>
@@ -3223,190 +3326,190 @@
       <c r="D46" s="31">
         <v>5</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F46" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G46" s="5" t="s">
+      <c r="F46" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="H46" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I46" s="5" t="s">
+      <c r="H46" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I46" s="6" t="s">
         <v>58</v>
       </c>
       <c r="J46" s="32"/>
       <c r="K46" s="32"/>
     </row>
-    <row r="47" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A47" s="5">
+    <row r="47" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A47" s="6">
         <f t="shared" si="0"/>
         <v>20220011</v>
       </c>
-      <c r="B47" s="13">
+      <c r="B47" s="14">
         <v>102200</v>
       </c>
-      <c r="C47" s="14">
+      <c r="C47" s="15">
         <v>2022001</v>
       </c>
-      <c r="D47" s="15">
+      <c r="D47" s="16">
         <v>1</v>
       </c>
       <c r="E47" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F47" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G47" s="16" t="s">
+      <c r="F47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H47" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I47" s="16" t="s">
+      <c r="H47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>79</v>
       </c>
       <c r="J47" s="17"/>
       <c r="K47" s="17"/>
     </row>
-    <row r="48" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A48" s="5">
+    <row r="48" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A48" s="6">
         <f t="shared" si="0"/>
         <v>20220012</v>
       </c>
-      <c r="B48" s="13">
+      <c r="B48" s="14">
         <v>102200</v>
       </c>
-      <c r="C48" s="14">
+      <c r="C48" s="15">
         <v>2022001</v>
       </c>
-      <c r="D48" s="15">
+      <c r="D48" s="16">
         <v>2</v>
       </c>
       <c r="E48" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F48" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G48" s="16" t="s">
+      <c r="F48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H48" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I48" s="16" t="s">
+      <c r="H48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" s="1" t="s">
         <v>79</v>
       </c>
       <c r="J48" s="17"/>
       <c r="K48" s="17"/>
     </row>
-    <row r="49" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A49" s="5">
+    <row r="49" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A49" s="6">
         <f t="shared" si="0"/>
         <v>20220013</v>
       </c>
-      <c r="B49" s="13">
+      <c r="B49" s="14">
         <v>102200</v>
       </c>
-      <c r="C49" s="14">
+      <c r="C49" s="15">
         <v>2022001</v>
       </c>
-      <c r="D49" s="15">
+      <c r="D49" s="16">
         <v>3</v>
       </c>
       <c r="E49" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="F49" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G49" s="16" t="s">
+      <c r="F49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H49" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I49" s="16" t="s">
+      <c r="H49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" s="1" t="s">
         <v>79</v>
       </c>
       <c r="J49" s="17"/>
       <c r="K49" s="17"/>
     </row>
-    <row r="50" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A50" s="5">
+    <row r="50" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A50" s="6">
         <f t="shared" si="0"/>
         <v>20220014</v>
       </c>
-      <c r="B50" s="13">
+      <c r="B50" s="14">
         <v>102200</v>
       </c>
-      <c r="C50" s="14">
+      <c r="C50" s="15">
         <v>2022001</v>
       </c>
-      <c r="D50" s="15">
+      <c r="D50" s="16">
         <v>4</v>
       </c>
       <c r="E50" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="F50" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G50" s="16" t="s">
+      <c r="F50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H50" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I50" s="16" t="s">
+      <c r="H50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I50" s="1" t="s">
         <v>79</v>
       </c>
       <c r="J50" s="17"/>
       <c r="K50" s="17"/>
     </row>
-    <row r="51" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A51" s="5">
+    <row r="51" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A51" s="6">
         <f t="shared" si="0"/>
         <v>20220015</v>
       </c>
-      <c r="B51" s="13">
+      <c r="B51" s="14">
         <v>102200</v>
       </c>
-      <c r="C51" s="14">
+      <c r="C51" s="15">
         <v>2022001</v>
       </c>
-      <c r="D51" s="15">
+      <c r="D51" s="16">
         <v>5</v>
       </c>
       <c r="E51" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="F51" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G51" s="16" t="s">
+      <c r="F51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G51" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="H51" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I51" s="16" t="s">
+      <c r="H51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" s="1" t="s">
         <v>79</v>
       </c>
       <c r="J51" s="17"/>
       <c r="K51" s="17"/>
     </row>
-    <row r="52" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A52" s="5">
+    <row r="52" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A52" s="6">
         <f t="shared" si="0"/>
         <v>20210011</v>
       </c>
-      <c r="B52" s="13">
+      <c r="B52" s="14">
         <v>102100</v>
       </c>
       <c r="C52" s="33">
@@ -3418,27 +3521,27 @@
       <c r="E52" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="F52" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G52" s="16" t="s">
+      <c r="F52" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G52" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H52" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I52" s="16" t="s">
+      <c r="H52" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I52" s="1" t="s">
         <v>89</v>
       </c>
       <c r="J52" s="17"/>
       <c r="K52" s="17"/>
     </row>
-    <row r="53" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A53" s="5">
+    <row r="53" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A53" s="6">
         <f t="shared" si="0"/>
         <v>20210012</v>
       </c>
-      <c r="B53" s="13">
+      <c r="B53" s="14">
         <v>102100</v>
       </c>
       <c r="C53" s="33">
@@ -3450,27 +3553,27 @@
       <c r="E53" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F53" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G53" s="16" t="s">
+      <c r="F53" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H53" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I53" s="16" t="s">
+      <c r="H53" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I53" s="1" t="s">
         <v>91</v>
       </c>
       <c r="J53" s="17"/>
       <c r="K53" s="17"/>
     </row>
-    <row r="54" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A54" s="5">
+    <row r="54" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A54" s="6">
         <f t="shared" si="0"/>
         <v>20210013</v>
       </c>
-      <c r="B54" s="13">
+      <c r="B54" s="14">
         <v>102100</v>
       </c>
       <c r="C54" s="33">
@@ -3482,27 +3585,27 @@
       <c r="E54" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F54" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G54" s="16" t="s">
+      <c r="F54" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H54" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I54" s="16" t="s">
+      <c r="H54" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I54" s="1" t="s">
         <v>93</v>
       </c>
       <c r="J54" s="17"/>
       <c r="K54" s="17"/>
     </row>
-    <row r="55" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A55" s="5">
+    <row r="55" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A55" s="6">
         <f t="shared" si="0"/>
         <v>20210014</v>
       </c>
-      <c r="B55" s="13">
+      <c r="B55" s="14">
         <v>102100</v>
       </c>
       <c r="C55" s="33">
@@ -3514,27 +3617,27 @@
       <c r="E55" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="F55" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G55" s="16" t="s">
+      <c r="F55" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="H55" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I55" s="16" t="s">
+      <c r="H55" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I55" s="1" t="s">
         <v>95</v>
       </c>
       <c r="J55" s="17"/>
       <c r="K55" s="17"/>
     </row>
-    <row r="56" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A56" s="5">
+    <row r="56" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A56" s="6">
         <f t="shared" si="0"/>
         <v>20210015</v>
       </c>
-      <c r="B56" s="13">
+      <c r="B56" s="14">
         <v>102100</v>
       </c>
       <c r="C56" s="33">
@@ -3546,27 +3649,27 @@
       <c r="E56" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="F56" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G56" s="16" t="s">
+      <c r="F56" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G56" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="H56" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I56" s="16" t="s">
+      <c r="H56" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I56" s="1" t="s">
         <v>97</v>
       </c>
       <c r="J56" s="17"/>
       <c r="K56" s="17"/>
     </row>
-    <row r="57" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A57" s="5">
-        <f t="shared" ref="A57:A67" si="2">C57*10+D57</f>
+    <row r="57" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A57" s="6">
+        <f t="shared" ref="A57:A72" si="2">C57*10+D57</f>
         <v>20180011</v>
       </c>
-      <c r="B57" s="13">
+      <c r="B57" s="14">
         <v>101800</v>
       </c>
       <c r="C57" s="33">
@@ -3578,27 +3681,27 @@
       <c r="E57" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F57" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G57" s="16" t="s">
+      <c r="F57" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H57" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I57" s="16" t="s">
+      <c r="H57" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I57" s="1" t="s">
         <v>99</v>
       </c>
       <c r="J57" s="17"/>
       <c r="K57" s="17"/>
     </row>
-    <row r="58" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A58" s="5">
+    <row r="58" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A58" s="6">
         <f t="shared" si="2"/>
         <v>20180012</v>
       </c>
-      <c r="B58" s="13">
+      <c r="B58" s="14">
         <v>101800</v>
       </c>
       <c r="C58" s="33">
@@ -3610,27 +3713,27 @@
       <c r="E58" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="F58" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G58" s="16" t="s">
+      <c r="F58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G58" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H58" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I58" s="16" t="s">
+      <c r="H58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>101</v>
       </c>
       <c r="J58" s="17"/>
       <c r="K58" s="17"/>
     </row>
-    <row r="59" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A59" s="5">
+    <row r="59" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A59" s="6">
         <f t="shared" si="2"/>
         <v>20180013</v>
       </c>
-      <c r="B59" s="13">
+      <c r="B59" s="14">
         <v>101800</v>
       </c>
       <c r="C59" s="33">
@@ -3642,27 +3745,27 @@
       <c r="E59" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F59" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G59" s="16" t="s">
+      <c r="F59" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G59" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="H59" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I59" s="16" t="s">
+      <c r="H59" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>103</v>
       </c>
       <c r="J59" s="17"/>
       <c r="K59" s="17"/>
     </row>
-    <row r="60" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A60" s="5">
+    <row r="60" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A60" s="6">
         <f t="shared" si="2"/>
         <v>20180014</v>
       </c>
-      <c r="B60" s="13">
+      <c r="B60" s="14">
         <v>101800</v>
       </c>
       <c r="C60" s="33">
@@ -3674,27 +3777,27 @@
       <c r="E60" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="F60" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G60" s="16" t="s">
+      <c r="F60" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H60" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I60" s="16" t="s">
+      <c r="H60" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60" s="1" t="s">
         <v>105</v>
       </c>
       <c r="J60" s="17"/>
       <c r="K60" s="17"/>
     </row>
-    <row r="61" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A61" s="5">
+    <row r="61" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A61" s="6">
         <f t="shared" si="2"/>
         <v>20180015</v>
       </c>
-      <c r="B61" s="13">
+      <c r="B61" s="14">
         <v>101800</v>
       </c>
       <c r="C61" s="33">
@@ -3706,27 +3809,27 @@
       <c r="E61" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="F61" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G61" s="16" t="s">
+      <c r="F61" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G61" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="H61" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I61" s="16" t="s">
+      <c r="H61" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I61" s="1" t="s">
         <v>108</v>
       </c>
       <c r="J61" s="17"/>
       <c r="K61" s="17"/>
     </row>
-    <row r="62" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A62" s="5">
+    <row r="62" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A62" s="6">
         <f t="shared" si="2"/>
         <v>20180016</v>
       </c>
-      <c r="B62" s="13">
+      <c r="B62" s="14">
         <v>101800</v>
       </c>
       <c r="C62" s="33">
@@ -3738,27 +3841,27 @@
       <c r="E62" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="F62" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G62" s="16" t="s">
+      <c r="F62" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G62" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="H62" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I62" s="16" t="s">
+      <c r="H62" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I62" s="1" t="s">
         <v>111</v>
       </c>
       <c r="J62" s="17"/>
       <c r="K62" s="17"/>
     </row>
-    <row r="63" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A63" s="5">
+    <row r="63" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A63" s="6">
         <f t="shared" si="2"/>
         <v>20250011</v>
       </c>
-      <c r="B63" s="13">
+      <c r="B63" s="14">
         <v>102500</v>
       </c>
       <c r="C63" s="33">
@@ -3770,27 +3873,27 @@
       <c r="E63" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="F63" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G63" s="16" t="s">
+      <c r="F63" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G63" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H63" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I63" s="16" t="s">
+      <c r="H63" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I63" s="1" t="s">
         <v>113</v>
       </c>
       <c r="J63" s="17"/>
       <c r="K63" s="17"/>
     </row>
-    <row r="64" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A64" s="5">
+    <row r="64" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A64" s="6">
         <f t="shared" si="2"/>
         <v>20250012</v>
       </c>
-      <c r="B64" s="13">
+      <c r="B64" s="14">
         <v>102500</v>
       </c>
       <c r="C64" s="33">
@@ -3802,27 +3905,27 @@
       <c r="E64" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F64" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G64" s="16" t="s">
+      <c r="F64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G64" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H64" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I64" s="16" t="s">
+      <c r="H64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I64" s="1" t="s">
         <v>115</v>
       </c>
       <c r="J64" s="17"/>
       <c r="K64" s="17"/>
     </row>
-    <row r="65" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A65" s="5">
+    <row r="65" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A65" s="6">
         <f t="shared" si="2"/>
         <v>20250013</v>
       </c>
-      <c r="B65" s="13">
+      <c r="B65" s="14">
         <v>102500</v>
       </c>
       <c r="C65" s="33">
@@ -3834,27 +3937,27 @@
       <c r="E65" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F65" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G65" s="16" t="s">
+      <c r="F65" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G65" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H65" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I65" s="16" t="s">
+      <c r="H65" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I65" s="1" t="s">
         <v>117</v>
       </c>
       <c r="J65" s="17"/>
       <c r="K65" s="17"/>
     </row>
-    <row r="66" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A66" s="5">
+    <row r="66" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A66" s="6">
         <f t="shared" si="2"/>
         <v>20250014</v>
       </c>
-      <c r="B66" s="13">
+      <c r="B66" s="14">
         <v>102500</v>
       </c>
       <c r="C66" s="33">
@@ -3866,27 +3969,27 @@
       <c r="E66" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="F66" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G66" s="16" t="s">
+      <c r="F66" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="H66" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I66" s="16" t="s">
+      <c r="H66" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" s="1" t="s">
         <v>119</v>
       </c>
       <c r="J66" s="17"/>
       <c r="K66" s="17"/>
     </row>
-    <row r="67" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A67" s="5">
+    <row r="67" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A67" s="6">
         <f t="shared" si="2"/>
         <v>20250015</v>
       </c>
-      <c r="B67" s="13">
+      <c r="B67" s="14">
         <v>102500</v>
       </c>
       <c r="C67" s="33">
@@ -3898,27 +4001,27 @@
       <c r="E67" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="F67" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G67" s="16" t="s">
+      <c r="F67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G67" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H67" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I67" s="16" t="s">
+      <c r="H67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I67" s="1" t="s">
         <v>121</v>
       </c>
       <c r="J67" s="17"/>
       <c r="K67" s="17"/>
     </row>
-    <row r="68" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A68" s="5">
-        <f>C68*10+D68</f>
+    <row r="68" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A68" s="6">
+        <f t="shared" si="2"/>
         <v>20230011</v>
       </c>
-      <c r="B68" s="13">
+      <c r="B68" s="14">
         <v>102300</v>
       </c>
       <c r="C68" s="33">
@@ -3930,27 +4033,27 @@
       <c r="E68" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="F68" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G68" s="16" t="s">
+      <c r="F68" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H68" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I68" s="16" t="s">
+      <c r="H68" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I68" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J68" s="17"/>
       <c r="K68" s="17"/>
     </row>
-    <row r="69" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A69" s="5">
-        <f>C69*10+D69</f>
+    <row r="69" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A69" s="6">
+        <f t="shared" si="2"/>
         <v>20230012</v>
       </c>
-      <c r="B69" s="13">
+      <c r="B69" s="14">
         <v>102300</v>
       </c>
       <c r="C69" s="33">
@@ -3962,27 +4065,27 @@
       <c r="E69" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F69" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G69" s="16" t="s">
+      <c r="F69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G69" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H69" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I69" s="16" t="s">
+      <c r="H69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I69" s="1" t="s">
         <v>125</v>
       </c>
       <c r="J69" s="17"/>
       <c r="K69" s="17"/>
     </row>
-    <row r="70" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A70" s="5">
-        <f>C70*10+D70</f>
+    <row r="70" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A70" s="6">
+        <f t="shared" si="2"/>
         <v>20230013</v>
       </c>
-      <c r="B70" s="13">
+      <c r="B70" s="14">
         <v>102300</v>
       </c>
       <c r="C70" s="33">
@@ -3994,27 +4097,27 @@
       <c r="E70" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="F70" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G70" s="16" t="s">
+      <c r="F70" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G70" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="H70" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I70" s="16" t="s">
+      <c r="H70" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I70" s="1" t="s">
         <v>127</v>
       </c>
       <c r="J70" s="17"/>
       <c r="K70" s="17"/>
     </row>
-    <row r="71" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A71" s="5">
-        <f>C71*10+D71</f>
+    <row r="71" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A71" s="6">
+        <f t="shared" si="2"/>
         <v>20230014</v>
       </c>
-      <c r="B71" s="13">
+      <c r="B71" s="14">
         <v>102300</v>
       </c>
       <c r="C71" s="33">
@@ -4026,27 +4129,27 @@
       <c r="E71" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="F71" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G71" s="16" t="s">
+      <c r="F71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G71" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="H71" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I71" s="16" t="s">
+      <c r="H71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I71" s="1" t="s">
         <v>129</v>
       </c>
       <c r="J71" s="17"/>
       <c r="K71" s="17"/>
     </row>
-    <row r="72" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A72" s="5">
-        <f>C72*10+D72</f>
+    <row r="72" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A72" s="6">
+        <f t="shared" si="2"/>
         <v>20230015</v>
       </c>
-      <c r="B72" s="13">
+      <c r="B72" s="14">
         <v>102300</v>
       </c>
       <c r="C72" s="33">
@@ -4058,24 +4161,969 @@
       <c r="E72" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="F72" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G72" s="16" t="s">
+      <c r="F72" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G72" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="H72" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I72" s="16" t="s">
+      <c r="H72" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I72" s="1" t="s">
         <v>131</v>
       </c>
       <c r="J72" s="17"/>
       <c r="K72" s="17"/>
+    </row>
+    <row r="73" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A73" s="6">
+        <f t="shared" ref="A73:A83" si="3">C73*10+D73</f>
+        <v>20230016</v>
+      </c>
+      <c r="B73" s="14">
+        <v>102300</v>
+      </c>
+      <c r="C73" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D73" s="33">
+        <v>6</v>
+      </c>
+      <c r="E73" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J73" s="17"/>
+      <c r="K73" s="17"/>
+    </row>
+    <row r="74" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A74" s="6">
+        <f t="shared" si="3"/>
+        <v>20230017</v>
+      </c>
+      <c r="B74" s="14">
+        <v>102300</v>
+      </c>
+      <c r="C74" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D74" s="33">
+        <v>7</v>
+      </c>
+      <c r="E74" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J74" s="17"/>
+      <c r="K74" s="17"/>
+    </row>
+    <row r="75" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A75" s="6">
+        <f t="shared" si="3"/>
+        <v>20230018</v>
+      </c>
+      <c r="B75" s="14">
+        <v>102300</v>
+      </c>
+      <c r="C75" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D75" s="33">
+        <v>8</v>
+      </c>
+      <c r="E75" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J75" s="17"/>
+      <c r="K75" s="17"/>
+    </row>
+    <row r="76" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A76" s="6">
+        <f t="shared" si="3"/>
+        <v>20230019</v>
+      </c>
+      <c r="B76" s="14">
+        <v>102300</v>
+      </c>
+      <c r="C76" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D76" s="33">
+        <v>9</v>
+      </c>
+      <c r="E76" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J76" s="17"/>
+      <c r="K76" s="17"/>
+    </row>
+    <row r="77" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A77" s="6">
+        <f t="shared" si="3"/>
+        <v>20230020</v>
+      </c>
+      <c r="B77" s="14">
+        <v>102300</v>
+      </c>
+      <c r="C77" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D77" s="33">
+        <v>10</v>
+      </c>
+      <c r="E77" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J77" s="17"/>
+      <c r="K77" s="17"/>
+    </row>
+    <row r="78" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A78" s="6">
+        <f t="shared" si="3"/>
+        <v>20230021</v>
+      </c>
+      <c r="B78" s="14">
+        <v>102300</v>
+      </c>
+      <c r="C78" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D78" s="33">
+        <v>11</v>
+      </c>
+      <c r="E78" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J78" s="17"/>
+      <c r="K78" s="17"/>
+    </row>
+    <row r="79" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A79" s="6">
+        <f t="shared" si="3"/>
+        <v>20230022</v>
+      </c>
+      <c r="B79" s="14">
+        <v>102300</v>
+      </c>
+      <c r="C79" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D79" s="33">
+        <v>12</v>
+      </c>
+      <c r="E79" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J79" s="17"/>
+      <c r="K79" s="17"/>
+    </row>
+    <row r="80" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A80" s="6">
+        <f t="shared" si="3"/>
+        <v>20230023</v>
+      </c>
+      <c r="B80" s="14">
+        <v>102300</v>
+      </c>
+      <c r="C80" s="33">
+        <v>2023001</v>
+      </c>
+      <c r="D80" s="33">
+        <v>13</v>
+      </c>
+      <c r="E80" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J80" s="17"/>
+      <c r="K80" s="17"/>
+    </row>
+    <row r="81" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A81" s="6">
+        <f t="shared" si="3"/>
+        <v>20340011</v>
+      </c>
+      <c r="B81" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C81" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D81" s="33">
+        <v>1</v>
+      </c>
+      <c r="E81" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J81" s="17"/>
+      <c r="K81" s="17"/>
+    </row>
+    <row r="82" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A82" s="6">
+        <f t="shared" si="3"/>
+        <v>20340012</v>
+      </c>
+      <c r="B82" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C82" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D82" s="33">
+        <v>2</v>
+      </c>
+      <c r="E82" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J82" s="17"/>
+      <c r="K82" s="17"/>
+    </row>
+    <row r="83" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A83" s="6">
+        <f t="shared" si="3"/>
+        <v>20340013</v>
+      </c>
+      <c r="B83" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C83" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D83" s="33">
+        <v>3</v>
+      </c>
+      <c r="E83" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J83" s="17"/>
+      <c r="K83" s="17"/>
+    </row>
+    <row r="84" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A84" s="6">
+        <f t="shared" ref="A84:A89" si="4">C84*10+D84</f>
+        <v>20340014</v>
+      </c>
+      <c r="B84" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C84" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D84" s="33">
+        <v>4</v>
+      </c>
+      <c r="E84" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="J84" s="17"/>
+      <c r="K84" s="17"/>
+    </row>
+    <row r="85" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A85" s="6">
+        <f t="shared" si="4"/>
+        <v>20340015</v>
+      </c>
+      <c r="B85" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C85" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D85" s="33">
+        <v>5</v>
+      </c>
+      <c r="E85" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J85" s="17"/>
+      <c r="K85" s="17"/>
+    </row>
+    <row r="86" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A86" s="6">
+        <f t="shared" si="4"/>
+        <v>20340016</v>
+      </c>
+      <c r="B86" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C86" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D86" s="33">
+        <v>6</v>
+      </c>
+      <c r="E86" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J86" s="17"/>
+      <c r="K86" s="17"/>
+    </row>
+    <row r="87" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A87" s="6">
+        <f t="shared" si="4"/>
+        <v>20340017</v>
+      </c>
+      <c r="B87" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C87" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D87" s="33">
+        <v>7</v>
+      </c>
+      <c r="E87" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J87" s="17"/>
+      <c r="K87" s="17"/>
+    </row>
+    <row r="88" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A88" s="6">
+        <f t="shared" si="4"/>
+        <v>20340018</v>
+      </c>
+      <c r="B88" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C88" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D88" s="33">
+        <v>8</v>
+      </c>
+      <c r="E88" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="J88" s="17"/>
+      <c r="K88" s="17"/>
+    </row>
+    <row r="89" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A89" s="6">
+        <f t="shared" si="4"/>
+        <v>20340019</v>
+      </c>
+      <c r="B89" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C89" s="33">
+        <v>2034001</v>
+      </c>
+      <c r="D89" s="33">
+        <v>9</v>
+      </c>
+      <c r="E89" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J89" s="17"/>
+      <c r="K89" s="17"/>
+    </row>
+    <row r="90" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A90" s="6">
+        <f>C90*10+D90</f>
+        <v>20350011</v>
+      </c>
+      <c r="B90" s="14">
+        <v>103500</v>
+      </c>
+      <c r="C90" s="33">
+        <v>2035001</v>
+      </c>
+      <c r="D90" s="33">
+        <v>1</v>
+      </c>
+      <c r="E90" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J90" s="17"/>
+      <c r="K90" s="17"/>
+    </row>
+    <row r="91" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A91" s="6">
+        <f>C91*10+D91</f>
+        <v>20350012</v>
+      </c>
+      <c r="B91" s="14">
+        <v>103500</v>
+      </c>
+      <c r="C91" s="33">
+        <v>2035001</v>
+      </c>
+      <c r="D91" s="33">
+        <v>2</v>
+      </c>
+      <c r="E91" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J91" s="17"/>
+      <c r="K91" s="17"/>
+    </row>
+    <row r="92" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A92" s="6">
+        <f>C92*10+D92</f>
+        <v>20350013</v>
+      </c>
+      <c r="B92" s="14">
+        <v>103500</v>
+      </c>
+      <c r="C92" s="33">
+        <v>2035001</v>
+      </c>
+      <c r="D92" s="33">
+        <v>3</v>
+      </c>
+      <c r="E92" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J92" s="17"/>
+      <c r="K92" s="17"/>
+    </row>
+    <row r="93" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A93" s="6">
+        <f>C93*10+D93</f>
+        <v>20350014</v>
+      </c>
+      <c r="B93" s="14">
+        <v>103500</v>
+      </c>
+      <c r="C93" s="33">
+        <v>2035001</v>
+      </c>
+      <c r="D93" s="33">
+        <v>4</v>
+      </c>
+      <c r="E93" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J93" s="17"/>
+      <c r="K93" s="17"/>
+    </row>
+    <row r="94" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A94" s="6">
+        <f>C94*10+D94</f>
+        <v>20350015</v>
+      </c>
+      <c r="B94" s="14">
+        <v>103500</v>
+      </c>
+      <c r="C94" s="33">
+        <v>2035001</v>
+      </c>
+      <c r="D94" s="33">
+        <v>5</v>
+      </c>
+      <c r="E94" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J94" s="17"/>
+      <c r="K94" s="17"/>
+    </row>
+    <row r="95" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A95" s="6">
+        <f>C95*10+D95</f>
+        <v>20350016</v>
+      </c>
+      <c r="B95" s="14">
+        <v>103500</v>
+      </c>
+      <c r="C95" s="33">
+        <v>2035001</v>
+      </c>
+      <c r="D95" s="33">
+        <v>6</v>
+      </c>
+      <c r="E95" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J95" s="17"/>
+      <c r="K95" s="17"/>
+    </row>
+    <row r="96" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A96" s="6">
+        <f>C96*10+D96</f>
+        <v>20350111</v>
+      </c>
+      <c r="B96" s="14">
+        <v>103501</v>
+      </c>
+      <c r="C96" s="33">
+        <v>2035011</v>
+      </c>
+      <c r="D96" s="33">
+        <v>1</v>
+      </c>
+      <c r="E96" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J96" s="17"/>
+      <c r="K96" s="17"/>
+    </row>
+    <row r="97" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A97" s="6">
+        <f>C97*10+D97</f>
+        <v>20350112</v>
+      </c>
+      <c r="B97" s="14">
+        <v>103501</v>
+      </c>
+      <c r="C97" s="33">
+        <v>2035011</v>
+      </c>
+      <c r="D97" s="33">
+        <v>2</v>
+      </c>
+      <c r="E97" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J97" s="17"/>
+      <c r="K97" s="17"/>
+    </row>
+    <row r="98" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A98" s="6">
+        <f>C98*10+D98</f>
+        <v>20350113</v>
+      </c>
+      <c r="B98" s="14">
+        <v>103501</v>
+      </c>
+      <c r="C98" s="33">
+        <v>2035011</v>
+      </c>
+      <c r="D98" s="33">
+        <v>3</v>
+      </c>
+      <c r="E98" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J98" s="17"/>
+      <c r="K98" s="17"/>
+    </row>
+    <row r="99" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A99" s="6">
+        <f>C99*10+D99</f>
+        <v>20350114</v>
+      </c>
+      <c r="B99" s="14">
+        <v>103501</v>
+      </c>
+      <c r="C99" s="33">
+        <v>2035011</v>
+      </c>
+      <c r="D99" s="33">
+        <v>4</v>
+      </c>
+      <c r="E99" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J99" s="17"/>
+      <c r="K99" s="17"/>
+    </row>
+    <row r="100" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A100" s="6">
+        <f>C100*10+D100</f>
+        <v>20350115</v>
+      </c>
+      <c r="B100" s="14">
+        <v>103501</v>
+      </c>
+      <c r="C100" s="33">
+        <v>2035011</v>
+      </c>
+      <c r="D100" s="33">
+        <v>5</v>
+      </c>
+      <c r="E100" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J100" s="17"/>
+      <c r="K100" s="17"/>
+    </row>
+    <row r="101" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A101" s="6">
+        <f>C101*10+D101</f>
+        <v>20350116</v>
+      </c>
+      <c r="B101" s="14">
+        <v>103501</v>
+      </c>
+      <c r="C101" s="33">
+        <v>2035011</v>
+      </c>
+      <c r="D101" s="33">
+        <v>6</v>
+      </c>
+      <c r="E101" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J101" s="17"/>
+      <c r="K101" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="I24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="24" ht="16.5" spans="9:9">
+      <c r="I24" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="166">
   <si>
     <t>id</t>
   </si>
@@ -539,6 +539,45 @@
   </si>
   <si>
     <t>7_7_7_7_6_7_6_6_6_6_7_7_6_6_6_6_6_6_7_6_6_6_7_7_6_6_6_6_6_6_6_6_6_7_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_7_6_6_7_6_6_6_6_6_6_6_6_6_6_6_6_6_7_7_6_7_6_6_6_6_6_6_6_7_6_6_6_6_6_6_6_6_6_6_6_7_7_6_6_6_6_6_6_6_7_6_6_7_7_6_7_6_6_6_6_6_6_6_6_6_6_7_6_6_6_6_6_7_6_6_6_7_6_6_6_6_7_6_6_7_7_6_7_7_6_6_6_6_6_6_7_6_6_7_6_7_6_6_6_6_7_7_6_6_6_6_6_6_6_6_6_7_6_6_6_6_7_7_6_6_6_7_6_6_6_6_6_6_7_6_6_6_7_7_7_6_6_7_6_6_6_6_6_7_6_6_6_6_6_7_6_6_6_6_6_6_6_7_6_6_6_6_6_6_6_6_7_7_7_7_6_7_6_6_6_7_7_6_6_7_6_6_6_6_7_6_7_6_7_6_6_6_6_6_6_6_6_6_6_6_6_7_7_6_6_6_6_6_6_7_6_6_6_6_6_6_7_6_7_6_6_6_6_6_7_6_7_6_6_6_7_7_6_6_6_6_6_7_6_7_6_6_6_6_7_6_6_6_6_7_6_6_6_6_6_6_6_6_6_7_6_6_6_6_6_6_6_7_6_7_7_6_7_7_6_6_6_7_7_6_6_6_6_6_7_6_6_6_6_6_6_6_6_7_6_6_6_6_7_6_7_6_6_6_6_7_6_6_6_7_7_6_6_6_7_6_7_6_6_7_6_6_6_6_7_6_6_6_6_6_6_6_6_6_6_6_7_7_6_6_6_6_6_7_6_6_6_6_6_6_6_7_7_6_6_6_6_6_7_6_6_6_6_6_6_6_6_6_6_6_6_7_6_6_6_6_6_6_6_6_6_6_7_6_6_6_6_6_6_6_6_6_6_6_6_6_6_6_7_6_6_6_6_6_7_6_6_6_6_7_6_6_6_7_6_7_6_6_6_6_7_6_7_7_7_6_7_6_6_6_7_7_6</t>
+  </si>
+  <si>
+    <t>4_4_4_4</t>
+  </si>
+  <si>
+    <t>5_1_2_1_5_5_2_4_1_1_1_1_1_1_1_1_3_5_4_5_2_4_1_3_3_2_5_1_1_1_2_1_5_2_4_4_3_4_2_2_5_2_2_1_1_1_2_5_6_5_3_3_2_5_6_2_3_3_3_3_1_4_4_1_4_3_2_3_4_3_3_2_2_2_3_1_1_2_1_2_5_6_4_3_2_5_4_4_3_2_3_4_1_3_2_5_3_1_4_1_2_5_2_3_3_3_5_4_1_1_1_6_1_4_2_1_3_4_3_1_2_2_2_2_4_2_2_1_3_2_4_2_1_6_1_4_1_4_4_2_1_4_1_2_1_4_2_3_6_2_3_3_1_3_1_1_3_1_3_6_2_4_4_5_5_1_1_1_1_3_3_3_3_3_4_2_2_1_1_3_3_2_1_3_1_4_6_3_2_1_3_4_1_3_4_6_2_6_3_1_3_1_5_2_2_2_3_1_3_5_2_3_4_2_5_1_1_1_1_1_3_1_4_2_2_2_5_4_5_2_5_4_3_2_2_3_4_3_3_5_2_5_4_1_4_3_1_2_1_4_3_1_1_5_3_2_2_2_4_4_3_1_3_1_2_5_2_3_3_1_3_6_2_3_6_6_3_1_1_1_5_2_2_2_2_5_6_6_1_4_2_4_1_2_2_1_4_1_2_1_2_1_1_5_2_4_4_5_6_3_3_2_1_1_3_3_4_4_4_3_2_2_1_5_1_1_1_2_2_3_3_5_5_4_6_2_5_4_1_3_3_3_1_6_1_1_4_1_1_1_1_1_4_1_1_2_2_1_4_3_3_3_3_6_3_1_2_5_1_2_3_3_1_2_3_2_1_4_1_1_1_1_2_3_4_6_5_1_5_3_1_1_5_6_2_4_1_1_2_3_2_2_3_6_3_3_2_1_4_6_3_2_2_4_4_4_1_4_5_5_5_5_2_5_3_3_1_1_4_2_3_1_5_4_2_4_4_2_1_1_3_3_1_1_2_1_4_1_5_4_3_2_1_4_4_5_2_2_3_3_4_1_3_1_2_1_3_1_5_4_1_1_1_3_3_1_6_6_1_4_1_1_1_2_3_3_3_2_3_1_5_2_1_3_3_4_4_1_5_2</t>
+  </si>
+  <si>
+    <t>1_3_2_2_4_7_2_1_3_3_6_3_6_2_1_3_1_5_1_3_1_4_1_2_3_3_1_2_2_4_5_5_1_1_5_1_1_3_1_1_4_3_2_1_4_5_1_1_2_1_4_7_2_3_6_3_2_1_2_6_2_5_1_2_1_4_4_1_1_1_3_1_2_2_1_3_6_3_6_3_7_2_7_1_3_1_1_1_2_4_2_3_3_7_4_2_1_4_2_4_2_4_5_5_2_1_2_2_7_1_3_4_2_6_6_5_4_2_1_2_6_5_5_6_4_1_1_1_1_3_2_1_1_3_2_3_1_3_4_2_3_3_2_3_2_3_1_2_6_6_2_3_4_3_4_2_2_2_3_4_6_1_1_1_3_3_5_5_1_3_2_1_2_2_3_4_6_1_1_1_1_5_2_2_4_6_3_1_4_7_1_1_1_2_1_4_5_2_4_6_3_2_2_4_5_1_5_6_1_1_4_3_1_6_1_5_4_2_6_3_6_1_3_4_2_1_2_1_2_4_5_1_2_3_5_5_2_7_3_4_4_1_4_3_6_3_5_7_3_3_2_1_2_5_2_3_6_3_3_6_5_4_5_5_6_2_6_4_7_3_2_1_1_4_1_2_6_1_5_1_1_2_1_1_2_2_1_5_4_5_4_3_1_3_5_2_6_7_4_2_5_1_6_3_1_7_5_4_4_3_3_5_5_1_4_5_2_2_3_7_4_2_6_6_3_5_2_4_2_3_2_4_2_1_7_6_6_4_5_1_2_2_6_4_1_5_3_6_3_6_7_3_1_6_1_3_6_2_1_3_5_2_5_2_1_7_3_3_1_1_4_2_2_2_1_3_3_4_2_1_2_5_5_6_2_3_5_6_5_4_4_5_2_1_1_4_1_7_2_2_3_3_1_3_3_3_1_6_4_3_2_1_1_1_3_3_5_1_6_1_1_2_4_3_4_6_2_4_1_1_7_4_5_1_3_6_5_2_3_5_6_1_2_1_1_4_2_3_2_5_3_1_4_2_1_3_4_3_7_4_6_1_1_5_2_1_2_5_1_7_1_1_4_3_3_4_5_2_1_1_6_3_4_5_1_7_6_2_3_4_2_1_5_2_4_3_2_5_5_4</t>
+  </si>
+  <si>
+    <t>1_4_2_2_1_6_2_3_4_6_2_2_1_1_1_1_1_4_2_5_5_5_2_2_1_4_5_1_2_2_2_2_2_4_1_1_1_5_4_5_5_2_1_1_2_4_1_2_2_3_3_3_1_3_4_5_1_2_3_2_2_3_3_5_5_2_2_3_3_3_2_4_2_2_5_5_2_1_1_2_2_5_4_2_3_4_3_2_2_5_2_2_2_2_4_3_5_3_2_3_1_1_1_2_2_1_6_6_3_5_2_1_1_6_1_1_4_3_1_4_6_2_1_1_3_3_3_2_6_3_3_3_3_3_1_1_1_1_5_5_3_4_5_1_1_4_1_1_3_2_2_6_4_4_5_4_5_3_3_2_4_2_2_1_3_3_1_6_3_1_1_4_3_3_4_4_5_5_3_5_2_2_1_3_1_2_2_2_1_1_1_3_3_1_4_2_4_2_2_1_2_2_3_2_5_5_5_5_1_4_4_2_3_1_2_4_5_2_1_4_4_4_4_4_6_1_3_1_1_1_2_6_2_4_5_2_1_3_2_2_1_3_1_2_1_2_1_4_5_2_2_2_3_3_2_4_2_2_5_5_2_2_5_5_1_1_2_1_4_2_5_1_2_1_1_6_2_2_5_3_1_5_1_4_3_4_4_6_1_4_3_3_6_2_4_4_3_4_3_2_4_3_3_1_1_3_3_2_5_1_3_1_5_2_1_1_3_4_4_3_1_3_3_3_5_2_4_3_2_6_6_3_3_2_1_1_1_1_2_1_3_5_3_3_3_1_4_1_5_2_1_2_2_2_2_6_2_5_1_3_3_2_2_2_2_2_1_4_3_1_4_6_4_3_1_5_6_1_4_4_2_5_1_3_4_4_4_4_2_4_1_3_2_3_2_1_1_1_4_3_1_2_2_4_5_4_4_1_1_1_2_2_1_5_5_2_4_2_4_5_2_5_5_1_2_1_1_1_6_1_5_5_4_4_4_1_2_5_5_5_2_2_3_1_1_2_1_4_4_4_3_3_2_3_3_1_1_2_2_2_1_1_4_1_3_2_1_1_4_1_4_1_3_3_4_2_3_5_3_1_1_4_4_2_2_3_4_2_1_1_3_6_1_5_2_1_1_5_1_2</t>
+  </si>
+  <si>
+    <t>6_1_6_5_7_3_4_7_5_3_3_3_5_4_3_1_1_6_1_1_7_2_5_1_3_3_5_3_3_1_4_1_2_1_5_2_1_3_7_4_7_7_2_2_1_3_4_2_1_1_2_1_2_3_4_1_4_1_5_1_1_1_1_4_2_2_4_6_7_7_3_1_4_1_4_2_7_1_6_1_4_1_4_2_7_1_6_5_1_1_2_4_3_1_4_2_2_3_2_4_4_1_6_2_3_4_4_3_2_1_3_3_7_6_2_1_6_6_4_5_3_3_3_3_2_3_2_3_2_3_6_2_1_3_2_5_1_3_2_3_7_6_2_3_6_1_4_1_4_2_1_2_2_1_6_3_1_4_6_2_5_2_1_3_1_3_2_1_2_3_3_6_6_1_6_3_2_5_2_4_3_2_4_2_1_3_3_5_7_7_5_6_1_6_2_2_1_5_5_1_7_1_1_1_4_4_3_6_2_4_1_5_2_2_5_1_3_4_4_4_1_5_1_4_6_6_1_1_1_1_2_3_1_1_4_5_5_2_1_5_2_3_1_3_2_4_5_1_2_5_1_3_4_5_2_4_2_1_2_5_6_5_3_5_1_1_2_4_7_4_1_1_1_4_4_4_3_3_1_1_4_1_6_6_2_2_3_2_6_2_3_2_7_1_3_5_2_3_6_3_5_7_5_3_1_6_1_6_2_4_6_3_1_2_4_1_7_5_3_4_5_3_6_7_2_1_1_2_2_2_5_4_3_3_6_3_1_1_1_5_6_7_5_4_1_7_6_3_1_2_2_1_5_1_3_5_3_2_2_7_1_4_5_2_6_4_1_2_4_4_5_5_3_1_2_4_3_7_5_6_5_3_4_1_2_1_4_2_4_1_4_2_5_2_2_2_3_1_2_1_3_1_5_4_4_2_4_4_1_5_1_6_6_5_2_6_4_3_5_3_5_2_7_5_5_6_2_1_7_3_5_5_1_4_5_2_6_3_1_1_1_2_1_2_1_5_5_4_2_1_2_6_2_3_1_1_5_2_2_6_5_1_5_1_5_7_3_6_1_3_7_7_5_1_5_1_4_4_1_2_2_5_1_5_4_1_1_4_1_4_2_5_2_5_4_2_6_5_2_2</t>
+  </si>
+  <si>
+    <t>3_3_2_1_2_1_5_5_5_1_3_3_2_3_4_1_2_3_3_6_5_5_3_1_4_6_1_3_1_4_1_3_3_2_2_1_3_4_3_1_4_4_6_4_1_4_4_4_2_1_1_6_1_2_4_2_2_5_6_6_3_2_6_1_2_3_3_5_3_1_2_1_1_2_4_3_3_4_2_2_3_3_4_4_4_2_2_1_3_1_1_1_1_3_4_4_4_2_4_4_1_1_2_4_2_2_1_4_1_2_6_1_5_1_1_1_1_1_2_1_1_1_1_3_4_2_4_3_1_3_1_2_1_5_2_4_4_1_3_3_1_2_1_3_3_1_3_4_4_2_1_1_3_3_1_2_2_2_1_2_5_5_1_1_2_4_4_3_2_4_4_2_3_2_2_1_3_1_1_3_3_4_4_3_1_4_6_6_2_4_2_2_2_3_4_2_2_2_3_1_1_3_2_3_1_4_2_3_3_3_1_3_1_2_2_6_6_2_2_5_1_3_5_5_6_2_1_4_3_1_3_4_5_5_3_2_2_1_2_1_2_3_4_3_3_1_2_3_3_1_1_1_3_3_2_5_3_2_5_1_1_2_2_2_3_2_3_3_3_2_3_2_2_2_1_3_6_1_3_2_4_5_5_1_1_1_3_3_3_3_1_1_2_6_4_6_3_1_4_1_1_1_2_2_4_1_1_3_5_1_3_6_4_1_3_1_1_3_5_4_2_2_1_2_1_1_3_4_3_4_4_4_2_3_1_4_4_3_1_1_3_3_3_1_1_1_1_2_1_3_3_5_2_2_5_4_4_5_1_2_2_2_2_2_1_4_1_1_3_1_1_1_2_2_4_4_4_1_1_2_1_4_1_5_4_3_2_2_5_1_1_1_2_3_3_1_4_1_6_2_2_6_3_1_1_1_2_6_6_4_4_1_2_2_2_5_3_2_5_5_2_2_5_5_2_1_2_2_5_2_3_2_4_1_1_1_5_5_1_6_6_1_2_1_6_2_4_6_1_2_5_3_1_5_6_2_1_2_1_1_1_3_2_3_3_6_1_3_2_1_1_4_2_4_2_5_4_1_2_1_2_3_2_3_1_1_6_3_3_2_3_4_1_1_1_1_6_6_1_3</t>
+  </si>
+  <si>
+    <t>5_1_7_6_2_1_2_2_4_3_4_1_1_4_1_4_5_2_7_6_6_6_3_3_1_2_4_2_3_1_2_4_3_2_7_2_4_3_4_1_3_4_1_2_4_4_1_6_3_4_3_3_2_5_1_2_1_4_1_2_3_2_3_1_5_2_4_6_4_3_7_1_5_3_2_3_7_4_4_5_2_1_1_2_3_5_1_1_6_5_1_4_5_6_2_3_1_2_1_4_3_7_3_5_2_1_2_6_6_2_5_3_4_4_1_1_2_7_6_3_2_3_1_1_5_5_5_4_6_4_2_3_3_3_5_2_1_1_1_1_5_1_6_6_3_4_6_1_3_3_6_3_4_2_3_1_1_2_2_1_2_7_4_4_1_2_2_2_2_7_6_2_2_3_5_1_1_7_6_5_1_1_1_2_5_4_5_7_1_1_1_3_2_1_5_5_3_4_4_7_2_6_1_2_2_5_7_5_1_5_3_1_3_3_2_1_1_1_1_4_1_3_1_4_2_1_5_2_5_6_1_1_6_6_5_4_3_6_6_3_3_4_5_4_5_3_5_1_3_7_1_2_1_1_3_6_1_5_3_4_6_3_7_1_1_2_1_4_2_3_2_1_1_3_3_4_3_1_1_4_5_4_1_4_4_7_2_4_6_2_3_2_4_1_5_4_2_4_1_4_6_2_1_4_1_1_1_7_1_6_6_6_2_2_6_2_1_4_3_1_5_2_4_4_2_4_1_6_2_3_1_1_1_4_3_1_2_7_2_7_5_1_1_4_4_6_4_5_6_2_1_3_1_6_6_4_2_2_2_5_6_2_6_6_1_2_4_1_1_1_6_1_2_7_3_5_1_1_3_1_4_3_6_6_5_3_4_2_3_2_3_1_3_3_1_5_1_2_6_6_3_5_5_1_3_3_1_4_2_1_4_5_1_6_2_4_4_3_4_3_2_6_6_3_4_1_5_5_3_1_4_1_1_4_5_6_2_2_1_3_4_4_1_5_2_2_3_1_7_3_4_6_2_4_2_3_2_3_6_3_2_6_2_4_7_5_3_3_7_5_2_3_1_5_3_2_5_2_1_2_2_1_5_3_1_4_4_5_2_3_3_3_3_1_4_2_4_2_6_4</t>
+  </si>
+  <si>
+    <t>8_13_13_13_8_13_13_13_8_13_13_13_13_13_13_13_13_13_8_8_8_13_8_8_8_8_8_13_8_8_8_8_13_13_13_13_8_8_8_13_13_8_8_8_8_8_8_13_8_8_13_8_8_8_13_13_8_13_13_8_8_8_13_8_8_8_8_8_13_13_8_8_13_8_8_13_8_8_8_8_13_8_8_13_13_13_8_13_13_13_8_8_8_13_13_13_8_8_13_13_13_13_8_8_8_8_13_13_13_13_8_13_13_8_8_8_8_13_13_13_13_8_13_8_13_8_8_8_13_13_8_13_8_8_8_13_13_8_8_13_8_8_13_13_13_8_8_13_13_13_13_8_8_8_8_13_13_13_8_13_8_13_8_13_8_8_8_8_8_8_13_13_8_13_8_13_13_8_8_13_8_13_8_8_13_13_8_8_8_8_8_8_8_8_8_13_8_13_13_13_8_13_8_13_13_13_8_13_13_13_13_8_13_13_13_8_8_8_13_13_13_13_13_13_13_8_8_8_8_13_8_8_8_8_8_13_8_8_8_8_13_8_8_8_13_8_13_8_13_8_13_8_8_8_13_8_8_13_8_13_8_13_8_8_13_13_8_8_8_8_8_8_8_13_8_13_8_8_13_13_13_13_13_13_13_13_13_8_13_8_8_8_8_8_8_13_13_13_8_13_13_8_8_8_13_13_13_13_8_13_13_13_13_13_8_8_13_8_13_13_8_8_8_13_13_13_13_8_8_8_13_8_8_13_8_8_8_13_13_8_13_13_8_8_8_8_8_13_8_13_8_8_13_13_13_8_13_13_13_8_13_8_8_8_8_8_8_8_13_8_13_13_8_13_8_8_13_8_13_13_13_8_8_13_13_8_13_8_13_8_8_8_13_13_13_13_8_8_8_13_13_8_8_13_8_13_13_8_8_13_8_13_8_13_13_13_13_8_13_13_8_8_13_13_8_13_8_13_13_13_8_8_13_13_13_8_8_13_13_8_13_8_13_13_8_13_8_13_13_8_13_13_8_8_8_8_13_13_13_13_8_8_8_8_13_8_8_13_8_13_13_8_13_8_8_8_8_13_8_8_8_8_13_8_13_13_13_8_13_13_13_13_8_13_13_8_8_8_13_8</t>
+  </si>
+  <si>
+    <t>8_13_8_13_13_13_13_8_8_8_8_13_13_8_8_8_13_13_8_8_13_13_13_8_8_8_8_8_13_13_13_8_8_8_13_13_13_8_13_13_8_13_8_8_8_13_13_13_13_8_8_13_8_8_8_13_8_8_8_8_13_8_8_8_13_8_8_13_8_8_13_13_13_13_8_13_8_8_8_8_8_13_13_8_13_8_13_13_8_8_13_13_8_8_8_13_13_13_8_13_8_8_8_13_13_13_8_8_8_8_8_13_13_8_13_13_13_8_13_13_13_13_8_13_8_8_8_8_8_13_8_13_8_8_8_8_8_13_8_8_13_8_8_13_8_8_8_8_8_13_13_8_13_13_13_13_8_13_13_13_8_13_13_8_13_13_13_13_13_8_8_13_8_13_8_13_8_13_13_8_13_8_13_13_8_8_13_8_13_8_13_8_8_13_8_13_8_13_13_8_13_13_13_8_13_8_8_8_8_13_8_8_13_13_8_8_8_13_13_13_13_8_8_8_13_8_8_8_13_8_8_13_8_8_8_8_8_13_8_8_8_8_8_8_8_13_8_8_13_13_13_8_8_8_8_8_8_13_13_8_13_13_13_8_13_8_8_13_13_13_13_8_8_13_8_13_13_13_13_13_13_13_13_8_8_8_13_8_8_8_8_13_8_13_13_13_13_8_8_8_8_13_13_13_13_13_13_13_13_13_8_8_13_13_13_13_13_8_13_8_13_13_13_13_8_8_8_8_8_8_8_13_8_8_8_13_8_8_8_8_8_8_8_8_8_13_13_13_8_8_13_13_13_13_13_13_13_13_8_8_13_8_13_13_8_13_8_8_13_8_13_13_8_8_8_8_13_8_13_13_13_13_8_8_8_13_13_8_8_8_13_13_13_13_13_8_13_8_13_8_13_13_8_13_13_8_8_8_13_13_8_8_13_8_8_8_8_8_8_13_13_13_8_13_8_8_13_8_8_8_13_13_8_13_13_13_13_8_8_8_13_8_13_13_13_13_8_13_8_8_13_13_13_13_13_8_8_8_13_13_13_8_8_8_8_8_13_13_13_8_13_13_8_13_8_13_13_8_13_13_13_13_8_8_13_8_13_13_13_8_13_8_8_13_8_13_8_13_13_8</t>
+  </si>
+  <si>
+    <t>8_8_8_8_13_13_13_13_8_13_13_13_13_13_8_13_8_13_13_13_13_13_13_13_8_13_8_8_8_13_13_8_8_13_8_13_8_8_8_13_13_13_8_8_13_13_13_13_13_8_8_13_8_8_8_8_13_13_8_8_13_13_8_13_8_13_13_8_8_8_13_8_13_8_8_8_13_13_8_13_8_13_13_8_13_13_13_8_8_8_8_8_13_13_13_8_13_13_13_13_13_13_13_8_8_8_8_13_13_13_13_13_13_8_13_8_13_8_8_8_13_8_8_8_8_13_13_13_8_13_13_13_8_8_13_8_8_8_8_13_13_13_13_8_13_13_8_13_8_13_13_8_13_8_13_8_13_13_8_8_13_13_13_13_8_13_13_8_13_8_8_13_13_13_8_8_13_8_13_8_13_8_8_13_8_13_13_13_13_13_13_13_8_8_8_8_8_13_13_13_13_8_8_13_13_8_8_8_8_13_8_13_13_8_13_13_8_8_8_8_13_13_8_13_13_13_8_13_8_8_8_8_8_8_8_13_8_8_8_8_13_8_8_8_13_13_8_8_13_8_8_8_13_8_8_13_13_8_8_13_8_8_8_8_8_13_13_13_8_8_8_8_13_13_13_8_8_8_8_13_13_8_13_8_8_8_8_13_13_13_8_13_13_13_13_13_13_8_8_13_13_13_8_13_8_13_13_13_13_8_8_13_13_8_8_8_13_13_13_13_13_13_8_8_8_8_8_13_13_8_8_8_8_13_8_13_8_8_13_13_8_8_8_8_13_13_8_13_8_13_8_8_8_8_13_13_8_13_8_8_13_13_8_13_13_8_8_8_13_13_8_8_8_8_8_8_13_13_13_8_8_8_8_8_8_8_13_8_13_13_8_8_8_13_8_13_13_13_13_13_8_13_8_13_8_13_8_13_8_8_8_13_8_8_8_13_13_13_13_8_13_13_13_8_13_8_8_8_8_8_8_13_13_13_13_13_8_8_8_8_8_8_13_13_8_8_13_8_8_8_8_8_8_8_13_8_13_13_13_8_8_8_8_8_13_13_13_8_8_13_13_13_8_8_8_8_13_13_8_8_13_13_13_13_13_8_13_8_13_8_8_13_13_13_13_8_13_8_8_8</t>
+  </si>
+  <si>
+    <t>1_501</t>
+  </si>
+  <si>
+    <t>1_502</t>
+  </si>
+  <si>
+    <t>1_503</t>
   </si>
 </sst>
 </file>
@@ -1849,7 +1888,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -4139,7 +4178,7 @@
     </row>
     <row r="73" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A73" s="6">
-        <f t="shared" ref="A73:A80" si="3">C73*10+D73</f>
+        <f t="shared" ref="A73:A83" si="3">C73*10+D73</f>
         <v>20230016</v>
       </c>
       <c r="B73" s="14">
@@ -4395,7 +4434,7 @@
     </row>
     <row r="81" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A81" s="6">
-        <f>C81*10+D81</f>
+        <f t="shared" si="3"/>
         <v>20340011</v>
       </c>
       <c r="B81" s="14">
@@ -4427,7 +4466,7 @@
     </row>
     <row r="82" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A82" s="6">
-        <f>C82*10+D82</f>
+        <f t="shared" si="3"/>
         <v>20340012</v>
       </c>
       <c r="B82" s="14">
@@ -4459,7 +4498,7 @@
     </row>
     <row r="83" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A83" s="6">
-        <f>C83*10+D83</f>
+        <f t="shared" si="3"/>
         <v>20340013</v>
       </c>
       <c r="B83" s="14">
@@ -4681,35 +4720,389 @@
       <c r="J89" s="17"/>
       <c r="K89" s="17"/>
     </row>
-    <row r="90" customFormat="1" spans="1:11">
-      <c r="B90" s="7"/>
-      <c r="J90" s="8"/>
-      <c r="K90" s="8"/>
-    </row>
-    <row r="91" customFormat="1" spans="1:11">
-      <c r="B91" s="7"/>
-      <c r="J91" s="8"/>
-      <c r="K91" s="8"/>
-    </row>
-    <row r="92" customFormat="1" spans="1:11">
-      <c r="B92" s="7"/>
-      <c r="J92" s="8"/>
-      <c r="K92" s="8"/>
-    </row>
-    <row r="93" customFormat="1" spans="1:11">
-      <c r="B93" s="7"/>
-      <c r="J93" s="8"/>
-      <c r="K93" s="8"/>
-    </row>
-    <row r="94" customFormat="1" spans="1:11">
-      <c r="B94" s="7"/>
-      <c r="J94" s="8"/>
-      <c r="K94" s="8"/>
-    </row>
-    <row r="95" customFormat="1" spans="1:11">
-      <c r="B95" s="7"/>
-      <c r="J95" s="8"/>
-      <c r="K95" s="8"/>
+    <row r="90" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A90" s="6">
+        <f>C90*10+D90</f>
+        <v>20350011</v>
+      </c>
+      <c r="B90" s="14">
+        <v>103500</v>
+      </c>
+      <c r="C90" s="33">
+        <v>2035001</v>
+      </c>
+      <c r="D90" s="33">
+        <v>1</v>
+      </c>
+      <c r="E90" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J90" s="17"/>
+      <c r="K90" s="17"/>
+    </row>
+    <row r="91" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A91" s="6">
+        <f>C91*10+D91</f>
+        <v>20350012</v>
+      </c>
+      <c r="B91" s="14">
+        <v>103500</v>
+      </c>
+      <c r="C91" s="33">
+        <v>2035001</v>
+      </c>
+      <c r="D91" s="33">
+        <v>2</v>
+      </c>
+      <c r="E91" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J91" s="17"/>
+      <c r="K91" s="17"/>
+    </row>
+    <row r="92" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A92" s="6">
+        <f>C92*10+D92</f>
+        <v>20350013</v>
+      </c>
+      <c r="B92" s="14">
+        <v>103500</v>
+      </c>
+      <c r="C92" s="33">
+        <v>2035001</v>
+      </c>
+      <c r="D92" s="33">
+        <v>3</v>
+      </c>
+      <c r="E92" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J92" s="17"/>
+      <c r="K92" s="17"/>
+    </row>
+    <row r="93" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A93" s="6">
+        <f>C93*10+D93</f>
+        <v>20350014</v>
+      </c>
+      <c r="B93" s="14">
+        <v>103500</v>
+      </c>
+      <c r="C93" s="33">
+        <v>2035001</v>
+      </c>
+      <c r="D93" s="33">
+        <v>4</v>
+      </c>
+      <c r="E93" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J93" s="17"/>
+      <c r="K93" s="17"/>
+    </row>
+    <row r="94" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A94" s="6">
+        <f>C94*10+D94</f>
+        <v>20350015</v>
+      </c>
+      <c r="B94" s="14">
+        <v>103500</v>
+      </c>
+      <c r="C94" s="33">
+        <v>2035001</v>
+      </c>
+      <c r="D94" s="33">
+        <v>5</v>
+      </c>
+      <c r="E94" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J94" s="17"/>
+      <c r="K94" s="17"/>
+    </row>
+    <row r="95" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A95" s="6">
+        <f>C95*10+D95</f>
+        <v>20350016</v>
+      </c>
+      <c r="B95" s="14">
+        <v>103500</v>
+      </c>
+      <c r="C95" s="33">
+        <v>2035001</v>
+      </c>
+      <c r="D95" s="33">
+        <v>6</v>
+      </c>
+      <c r="E95" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J95" s="17"/>
+      <c r="K95" s="17"/>
+    </row>
+    <row r="96" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A96" s="6">
+        <f>C96*10+D96</f>
+        <v>20350111</v>
+      </c>
+      <c r="B96" s="14">
+        <v>103501</v>
+      </c>
+      <c r="C96" s="33">
+        <v>2035011</v>
+      </c>
+      <c r="D96" s="33">
+        <v>1</v>
+      </c>
+      <c r="E96" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J96" s="17"/>
+      <c r="K96" s="17"/>
+    </row>
+    <row r="97" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A97" s="6">
+        <f>C97*10+D97</f>
+        <v>20350112</v>
+      </c>
+      <c r="B97" s="14">
+        <v>103501</v>
+      </c>
+      <c r="C97" s="33">
+        <v>2035011</v>
+      </c>
+      <c r="D97" s="33">
+        <v>2</v>
+      </c>
+      <c r="E97" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J97" s="17"/>
+      <c r="K97" s="17"/>
+    </row>
+    <row r="98" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A98" s="6">
+        <f>C98*10+D98</f>
+        <v>20350113</v>
+      </c>
+      <c r="B98" s="14">
+        <v>103501</v>
+      </c>
+      <c r="C98" s="33">
+        <v>2035011</v>
+      </c>
+      <c r="D98" s="33">
+        <v>3</v>
+      </c>
+      <c r="E98" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J98" s="17"/>
+      <c r="K98" s="17"/>
+    </row>
+    <row r="99" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A99" s="6">
+        <f>C99*10+D99</f>
+        <v>20350114</v>
+      </c>
+      <c r="B99" s="14">
+        <v>103501</v>
+      </c>
+      <c r="C99" s="33">
+        <v>2035011</v>
+      </c>
+      <c r="D99" s="33">
+        <v>4</v>
+      </c>
+      <c r="E99" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J99" s="17"/>
+      <c r="K99" s="17"/>
+    </row>
+    <row r="100" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A100" s="6">
+        <f>C100*10+D100</f>
+        <v>20350115</v>
+      </c>
+      <c r="B100" s="14">
+        <v>103501</v>
+      </c>
+      <c r="C100" s="33">
+        <v>2035011</v>
+      </c>
+      <c r="D100" s="33">
+        <v>5</v>
+      </c>
+      <c r="E100" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J100" s="17"/>
+      <c r="K100" s="17"/>
+    </row>
+    <row r="101" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A101" s="6">
+        <f>C101*10+D101</f>
+        <v>20350116</v>
+      </c>
+      <c r="B101" s="14">
+        <v>103501</v>
+      </c>
+      <c r="C101" s="33">
+        <v>2035011</v>
+      </c>
+      <c r="D101" s="33">
+        <v>6</v>
+      </c>
+      <c r="E101" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J101" s="17"/>
+      <c r="K101" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -4530,7 +4530,7 @@
     </row>
     <row r="84" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A84" s="6">
-        <f t="shared" ref="A84:A89" si="4">C84*10+D84</f>
+        <f t="shared" ref="A84:A101" si="4">C84*10+D84</f>
         <v>20340014</v>
       </c>
       <c r="B84" s="14">
@@ -4722,7 +4722,7 @@
     </row>
     <row r="90" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A90" s="6">
-        <f>C90*10+D90</f>
+        <f t="shared" si="4"/>
         <v>20350011</v>
       </c>
       <c r="B90" s="14">
@@ -4754,7 +4754,7 @@
     </row>
     <row r="91" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A91" s="6">
-        <f>C91*10+D91</f>
+        <f t="shared" si="4"/>
         <v>20350012</v>
       </c>
       <c r="B91" s="14">
@@ -4786,7 +4786,7 @@
     </row>
     <row r="92" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A92" s="6">
-        <f>C92*10+D92</f>
+        <f t="shared" si="4"/>
         <v>20350013</v>
       </c>
       <c r="B92" s="14">
@@ -4818,17 +4818,17 @@
     </row>
     <row r="93" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A93" s="6">
-        <f>C93*10+D93</f>
-        <v>20350014</v>
+        <f t="shared" si="4"/>
+        <v>20350021</v>
       </c>
       <c r="B93" s="14">
         <v>103500</v>
       </c>
       <c r="C93" s="33">
-        <v>2035001</v>
+        <v>2035002</v>
       </c>
       <c r="D93" s="33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E93" s="18" t="s">
         <v>50</v>
@@ -4850,17 +4850,17 @@
     </row>
     <row r="94" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A94" s="6">
-        <f>C94*10+D94</f>
-        <v>20350015</v>
+        <f t="shared" si="4"/>
+        <v>20350022</v>
       </c>
       <c r="B94" s="14">
         <v>103500</v>
       </c>
       <c r="C94" s="33">
-        <v>2035001</v>
+        <v>2035002</v>
       </c>
       <c r="D94" s="33">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E94" s="18" t="s">
         <v>50</v>
@@ -4882,17 +4882,17 @@
     </row>
     <row r="95" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A95" s="6">
-        <f>C95*10+D95</f>
-        <v>20350016</v>
+        <f t="shared" si="4"/>
+        <v>20350023</v>
       </c>
       <c r="B95" s="14">
         <v>103500</v>
       </c>
       <c r="C95" s="33">
-        <v>2035001</v>
+        <v>2035002</v>
       </c>
       <c r="D95" s="33">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E95" s="18" t="s">
         <v>50</v>
@@ -4914,7 +4914,7 @@
     </row>
     <row r="96" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A96" s="6">
-        <f>C96*10+D96</f>
+        <f t="shared" si="4"/>
         <v>20350111</v>
       </c>
       <c r="B96" s="14">
@@ -4946,7 +4946,7 @@
     </row>
     <row r="97" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A97" s="6">
-        <f>C97*10+D97</f>
+        <f t="shared" si="4"/>
         <v>20350112</v>
       </c>
       <c r="B97" s="14">
@@ -4978,7 +4978,7 @@
     </row>
     <row r="98" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A98" s="6">
-        <f>C98*10+D98</f>
+        <f t="shared" si="4"/>
         <v>20350113</v>
       </c>
       <c r="B98" s="14">
@@ -5010,17 +5010,17 @@
     </row>
     <row r="99" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A99" s="6">
-        <f>C99*10+D99</f>
-        <v>20350114</v>
+        <f t="shared" si="4"/>
+        <v>20350121</v>
       </c>
       <c r="B99" s="14">
         <v>103501</v>
       </c>
       <c r="C99" s="33">
-        <v>2035011</v>
+        <v>2035012</v>
       </c>
       <c r="D99" s="33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E99" s="18" t="s">
         <v>50</v>
@@ -5042,17 +5042,17 @@
     </row>
     <row r="100" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A100" s="6">
-        <f>C100*10+D100</f>
-        <v>20350115</v>
+        <f t="shared" si="4"/>
+        <v>20350122</v>
       </c>
       <c r="B100" s="14">
         <v>103501</v>
       </c>
       <c r="C100" s="33">
-        <v>2035011</v>
+        <v>2035012</v>
       </c>
       <c r="D100" s="33">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E100" s="18" t="s">
         <v>50</v>
@@ -5074,17 +5074,17 @@
     </row>
     <row r="101" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A101" s="6">
-        <f>C101*10+D101</f>
-        <v>20350116</v>
+        <f t="shared" si="4"/>
+        <v>20350123</v>
       </c>
       <c r="B101" s="14">
         <v>103501</v>
       </c>
       <c r="C101" s="33">
-        <v>2035011</v>
+        <v>2035012</v>
       </c>
       <c r="D101" s="33">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E101" s="18" t="s">
         <v>50</v>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="172">
   <si>
     <t>id</t>
   </si>
@@ -416,6 +416,24 @@
   </si>
   <si>
     <t>4_2_4_2_1_6_1_5_4_9_6_4_2_6_3_4_1_6_7_2_8_3_9_1_8_4_1_4_7_7_6_4_4_3_1_5_5_10_6_2_1_3_2_9_3_5_7_4_9_8_5_1_4_6_1_9_8_1_9_1_7_5_6_5_3_9_6_4_3_1_7_2_4_1_3_5_4_7_4_6_3_9_1_6_2_6_5_2_4_4_8_5_6_3_2_1_1_2_3_5_3_1_1_3_6_7_9_7_1_3_7_7_2_3_1_9_1_8_4_2_2_6_8_1_3_1_5_8_9_6_1_7_4_7_9_3_6_2_2_4_5_3_3_6_8_4_5_8_1_1_8_5_2_10_2_8_2_7_7_4_1_2_8_3_3_4_3_4_1_2_9_6_3_4_2_1_9_2_3_9_8_2_3_7_4_1_1_2_2_9_5_6_8_4_8_5_7_2_1_7_6_5_6_2_9_10_3_1_4_7_2_7_3_5_1_1_6_1_4_7_4_6_4_9_1_1_6_4_7_3_1_6_7_1_8_4_9_9_8_10_6_3_1_2_4_2_5_2_2_1_6_3_9_3_8_6_10_7_4_4_6_1_3_9_2_2_2_6_3_4_4_6_9_5_2_4_7_4_1_6_6_8_5_7_8_1_6_4_4_1_8_1_4_5_3_3_3_1_2_6_4_4_9_1_6_4_5_4_5_7_2_2_1_10_3_9_5_1_7_2_4_4_2_1_4_1_2_1_8_2_1_8_2_8_3_4_3_3_7_3_1_3_4_8_1_5_2_3_9_6_8_5_8_5_7_5_2_8_1_2_6_6_3_4_2_9_3_10_2_5_1_3_4_3_6_5_3_4_6_1_3_5_2_4_9_1_2_1_7_3_9_3_8_10_7_6_2_4_9_7_8_9_2_9_7_9_5_4_7_1_9_5_2_9_5_1_5_1_3_4_5_2_8_7_1_4_9_2_1_4_8_4_8_9_10_6_7_2_1_4_2_4_8_6_4_8_8_7_2_1_9_9_4_4_2_6_4_8_9_9_2_1_8_4_8_9_4_6_8_3_1_6_3_1_7_7_2_7_6_9_1_7_3_4_5_4_2_3_1_1_5_5_7_4_1_5_7_3_4_9</t>
+  </si>
+  <si>
+    <t>4_6_9_5_8_3_9_5_10_8_7_9_9_3_9_5_5_8_7_2_2_10_8_7_2_8_8_4_6_8_8_8_7_10_10_1_9_9_4_2_9_9_7_5_8_9_8_7_7_8_8_8_8_10_2_10_4_10_7_5_7_7_2_2_9_7_9_9_5_2_8_8_3_5_8_5_5_2_7_8_2_8_4_7_8_7_6_5_5_5_7_10_1_1_8_10_5_2_4_2_6_9_4_5_5_9_5_5_10_2_2_8_7_2_10_3_1_10_1_3_10_5_3_3_8_8_7_7_6_5_7_4_8_10_9_5_5_3_9_6_2_9_5_5_3_8_8_8_8_10_9_9_10_9_4_7_9_10_4_9_7_9_7_10_8_8_7_4_10_5_2_2_6_7_8_7_2_9_1_2_10_3_4_5_2_2_3_2_2_7_3_9_6_5_10_3_1_9_3_7_6_8_6_9_4_7_8_5_10_6_8_7_2_2_7_8_6_8_10_3_7_8_8_7_7_7_9_6_1_2_4_5_9_10_4_6_7_10_8_8_5_6_8_3_9_9_5_9_6_6_6_8_8_5_7_3_9_7_6_6_8_8_8_10_9_2_8_6_7_4_3_7_9_7_8_9_3_8_8_5_3_7_7_7_3_3_5_5_5_7_9_9_8_8_9_9_6_10_5_9_4_5_5_5_5_9_6_10_8_10_7_10_8_9_5_8_7_5_5_2_9_2_2_10_8_8_9_9_9_6_5_9_8_5_6_2_8_9_10_10_8_5_7_8_8_8_2_5_10_7_7_7_9_5_8_10_3_8_9_9_4_5_4_5_5_5_10_9_9_8_5_7_10_10_9_7_7_3_5_3_8_5_5_3_6_8_3_10_1_7_6_5_1_2_6_6_9_6_8_9_2_5_6_10_8_8_4_5_6_7_4_9_9_9_10_3_9_9_5_5_7_6_6_3_7_7_9_10_5_10_5_9_7_7_10_10_1_4_4_10_5_10_10_8_10_3_10_10_10_9_10_9_5_4_9_7_8_7_10_10_3_9_9_9_8_9_10_9_7_10_3_8_8_10_3_5_9_8_1_7_6_10_7_2_2_7_10_10_6_9_7_8_7_7_10_8_3_6_8_8</t>
+  </si>
+  <si>
+    <t>9_4_4_4_4_10_2_2_10_9_9_10_10_9_10_5_3_2_5_4_10_5_10_9_9_8_9_9_9_8_10_7_10_9_7_5_5_10_10_4_4_9_1_10_10_8_9_1_1_1_10_10_10_3_8_10_3_7_9_7_6_2_9_8_5_6_6_10_5_5_7_6_2_6_5_9_5_3_9_2_4_7_5_6_5_5_10_10_3_10_1_3_9_4_7_7_4_4_4_7_2_1_4_5_3_6_6_3_4_4_8_6_8_8_10_10_7_9_5_10_5_6_5_2_3_2_2_3_10_10_5_2_9_8_8_3_3_3_1_10_8_2_6_7_7_9_5_9_9_8_10_9_1_5_3_3_9_3_9_9_9_5_6_7_9_7_6_10_5_7_7_2_4_4_8_9_9_9_5_2_10_10_2_5_9_3_10_4_7_6_7_10_5_6_2_4_10_10_8_8_10_6_6_2_5_10_10_6_7_7_5_9_10_3_10_4_2_8_8_9_4_6_5_10_8_6_10_8_8_5_5_9_9_9_4_5_10_10_7_9_8_9_5_3_4_8_7_7_3_7_9_9_9_10_1_10_8_7_5_7_8_5_7_9_4_6_4_8_4_6_8_10_8_8_7_3_2_10_8_8_7_4_7_8_7_4_9_5_7_9_9_8_3_3_5_5_1_5_5_5_9_10_6_5_1_1_9_5_7_8_9_8_10_4_9_6_8_8_10_5_9_9_9_8_6_6_10_6_4_2_2_5_6_6_6_6_6_8_10_9_6_7_7_3_9_7_8_8_9_7_3_9_9_4_10_4_7_7_7_6_9_3_4_9_8_8_2_6_6_6_8_7_9_8_2_2_9_2_8_2_7_3_10_5_9_5_6_8_8_10_10_7_2_8_7_7_5_9_9_8_4_6_6_7_6_4_9_9_10_3_9_8_8_9_10_10_1_1_4_3_4_8_9_9_9_5_7_8_1_7_8_6_3_9_9_4_4_10_10_3_7_3_6_8_3_10_5_9_8_10_2_9_5_3_9_8_10_3_4_8_10_5_3_4_9_10_5_2_10_10_9_2_5_10_10_10_9_9_6_9_6_10_10_10_4_5_9_7_7_10_9_9_7_3_10_9_10_9_8_7</t>
+  </si>
+  <si>
+    <t>8_8_4_5_5_4_4_5_5_8_9_3_8_6_6_9_8_10_5_7_1_4_4_4_9_5_5_5_5_5_8_1_4_4_6_10_9_3_4_9_5_8_7_9_9_6_6_1_9_6_10_9_9_5_4_9_8_3_7_5_8_7_5_4_3_5_10_10_2_3_7_7_8_9_9_3_4_8_8_9_7_10_10_10_1_8_7_9_5_5_9_7_9_9_7_6_8_10_5_8_10_8_8_8_9_9_9_3_4_8_3_3_9_8_5_6_10_6_8_6_3_6_7_7_7_10_6_5_10_10_5_6_9_3_6_5_2_5_5_5_5_10_8_9_7_8_10_6_4_7_9_7_7_7_3_3_8_4_10_7_8_7_10_10_10_10_10_5_8_6_9_10_9_9_9_10_5_8_4_8_9_3_3_10_10_9_7_5_5_3_6_9_2_4_10_2_5_9_1_6_5_5_4_10_2_9_3_9_4_4_6_8_8_3_3_6_6_3_8_4_4_4_3_7_7_7_8_6_5_7_8_5_8_9_4_5_5_5_5_2_5_6_9_5_5_6_6_10_8_9_10_3_3_1_10_7_8_8_5_2_7_10_10_10_7_8_7_3_10_9_9_5_6_10_9_10_10_8_7_8_8_7_8_3_5_10_8_10_1_2_3_1_5_3_4_6_10_1_9_9_9_10_9_2_8_9_9_6_10_8_8_4_8_6_7_8_4_10_2_6_3_7_10_7_5_5_8_8_10_5_7_9_7_7_6_10_10_4_10_10_2_8_8_10_10_10_8_2_8_5_6_6_9_8_7_10_9_10_6_6_9_9_9_2_7_4_2_7_7_10_4_2_3_7_10_2_3_8_5_5_9_8_9_7_7_7_7_6_6_6_1_5_6_3_3_3_4_5_6_6_2_5_7_10_4_10_6_7_6_6_10_10_8_8_10_9_10_4_8_7_9_7_7_4_8_9_5_5_5_7_3_7_9_9_9_8_3_7_6_4_4_8_10_10_10_10_8_9_4_6_6_1_7_6_7_8_8_9_9_7_5_5_10_5_6_10_9_7_4_7_8_10_10_10_7_9_9_10_6_9_2_5_7_9_7_8_6_4_9_3_8_2_4_3_9_4_4_9_6_2</t>
+  </si>
+  <si>
+    <t>3_8_7_7_4_4_9_8_4_9_7_6_8_3_3_7_3_7_10_8_10_9_9_10_5_10_8_4_8_7_7_6_9_7_10_2_4_4_9_5_2_9_7_6_7_6_4_4_5_7_8_6_6_6_5_5_5_5_8_7_9_10_3_2_9_2_2_10_5_5_3_7_8_5_10_8_3_8_8_8_5_5_8_8_10_8_10_7_5_4_8_4_7_7_3_10_1_9_8_4_6_10_9_5_8_8_8_8_4_5_10_1_9_8_8_1_6_10_8_9_10_10_5_9_9_9_7_10_2_1_9_7_9_7_2_9_4_10_9_7_5_5_10_1_10_6_7_4_4_7_9_9_9_9_4_5_3_9_10_8_9_7_1_1_8_1_8_7_8_6_8_5_8_4_1_2_10_8_8_8_1_8_7_7_10_10_2_3_6_4_3_6_9_8_8_9_4_5_6_8_8_7_5_3_6_10_9_8_10_6_6_6_8_9_1_10_2_4_6_3_5_9_10_7_6_10_4_9_6_9_6_1_6_8_1_5_1_6_10_9_9_9_5_9_6_10_10_7_10_7_7_6_7_7_10_10_5_7_9_5_5_2_6_9_4_10_10_8_8_9_8_3_10_9_2_2_5_4_10_10_7_4_2_2_4_10_3_8_10_2_5_10_4_4_6_8_5_5_8_9_3_3_3_10_8_4_4_5_3_7_6_2_2_7_5_10_4_10_8_9_9_3_9_10_5_6_9_3_5_10_10_5_5_10_4_4_10_10_5_9_9_9_6_9_3_2_2_8_8_9_10_9_10_9_3_10_5_7_5_5_6_8_6_4_8_6_6_3_4_6_10_10_1_10_10_6_8_8_10_10_8_5_5_3_5_6_5_3_4_8_5_5_5_3_8_10_8_8_7_10_5_10_7_5_10_10_6_4_4_4_2_2_9_9_3_5_7_7_7_7_10_10_4_3_5_7_10_3_2_9_4_7_4_9_10_7_9_9_9_5_5_10_10_6_9_8_10_8_9_8_7_7_8_6_6_3_4_7_4_2_8_5_8_3_3_10_4_4_8_8_8_2_3_9_9_10_9_10_2_6_6_5_9_1_1_4_10_6_10_10_9_10_7_7_3_9_10_5_9_9</t>
+  </si>
+  <si>
+    <t>8_6_5_5_2_2_6_5_6_7_6_8_5_10_7_5_7_7_3_8_8_7_5_1_7_5_6_6_3_10_10_10_10_9_3_7_6_6_7_8_8_8_4_10_8_3_3_10_10_2_8_10_1_8_8_5_10_10_4_9_7_6_6_3_9_9_3_8_9_9_9_5_8_7_7_7_9_3_2_4_10_8_7_10_7_7_10_2_7_9_6_9_6_7_10_10_6_7_9_9_10_8_2_9_10_9_6_6_8_5_6_5_6_8_9_4_9_7_9_9_4_5_4_6_8_7_10_3_9_8_8_5_9_10_9_9_3_9_9_6_9_2_9_10_9_9_9_7_10_10_7_10_2_5_9_9_8_10_8_10_10_8_6_9_6_6_8_7_4_7_10_4_10_9_9_3_5_6_8_7_10_9_9_9_7_6_10_2_5_7_1_4_6_7_7_9_10_8_10_10_10_9_6_5_3_9_1_9_7_3_4_2_9_7_6_8_8_6_4_9_7_7_5_6_8_7_4_8_2_2_10_9_9_6_3_1_6_6_7_9_6_6_6_2_10_9_8_9_5_3_9_8_8_7_5_5_3_5_10_10_5_10_10_3_8_8_8_7_4_10_3_5_10_9_4_4_2_7_2_7_6_6_5_6_9_3_6_8_5_1_10_10_7_6_3_6_6_8_5_3_8_10_9_9_6_7_5_3_7_5_9_9_1_7_6_8_3_10_7_7_7_7_10_5_10_5_10_10_8_6_8_8_4_4_3_6_7_7_6_5_10_6_6_9_3_7_1_6_6_7_5_6_10_9_7_7_6_6_6_9_8_3_10_10_4_3_3_8_8_9_10_10_2_2_5_5_9_4_4_9_1_3_7_8_3_7_8_10_6_9_2_9_10_2_10_5_5_9_4_8_9_6_9_7_3_2_5_3_5_10_7_10_10_7_5_8_7_6_10_2_8_7_9_9_6_10_10_8_10_5_8_4_5_8_8_8_8_7_7_6_6_3_4_4_10_7_6_5_9_10_9_5_4_8_6_8_8_6_4_4_7_7_9_10_7_9_8_9_10_10_9_9_7_10_5_7_7_9_7_10_4_6_7_9_7_3_8_3_2_8_4_9_2_9_3_10_10_9_10_10</t>
+  </si>
+  <si>
+    <t>2_4_5_10_10_4_10_9_8_2_10_1_9_10_10_7_3_8_2_2_4_5_6_10_10_8_8_8_6_7_8_10_9_10_8_6_5_4_4_9_5_2_9_4_2_5_1_5_5_5_5_6_7_5_4_10_7_3_2_10_4_9_7_5_8_9_10_2_9_8_5_7_6_5_2_2_4_3_10_10_8_2_7_10_3_10_4_10_4_8_10_6_5_4_2_2_6_8_3_9_7_9_7_7_5_9_9_9_2_7_7_10_6_5_8_10_8_10_10_9_10_5_8_6_8_8_6_6_9_2_5_5_10_9_5_7_3_7_4_4_10_9_3_9_9_4_4_10_5_9_6_6_7_8_8_5_5_4_5_10_7_4_7_9_8_10_9_10_4_9_8_5_10_7_5_4_3_8_6_9_2_2_4_1_7_5_9_9_10_6_2_2_2_8_3_7_4_2_2_5_6_10_5_10_8_5_5_8_9_5_10_10_6_6_3_3_10_4_7_5_3_8_2_9_7_1_1_10_9_9_8_5_4_4_10_10_10_10_8_9_10_4_4_8_10_3_5_8_10_10_5_4_6_10_7_5_8_7_5_10_10_10_10_6_6_7_3_2_10_3_1_2_4_9_7_9_6_8_5_8_8_4_5_9_9_6_10_10_9_2_10_10_10_10_4_6_10_5_8_8_8_8_10_10_7_7_9_6_7_8_10_3_10_3_4_10_10_8_3_7_7_10_10_8_7_7_10_9_7_8_8_8_10_10_6_10_3_6_3_7_4_8_5_7_9_6_4_4_4_3_3_8_3_8_3_6_3_9_4_5_7_10_9_9_10_1_4_1_3_9_9_8_7_10_3_3_3_10_8_5_5_8_9_10_9_8_8_5_3_10_7_10_6_5_5_8_8_4_9_6_10_8_8_8_9_10_2_2_2_5_2_10_5_3_9_2_4_9_10_2_8_8_3_10_9_5_5_6_4_7_10_9_10_7_8_7_4_4_1_10_10_8_8_6_6_1_8_8_8_10_4_9_3_8_7_9_7_10_10_9_2_9_9_10_10_4_9_9_9_2_9_9_7_10_6_3_9_6_6_2_2_7_5_6_5_9_7_7_7_9_5_5_10_6_4_8_10_10_7_8</t>
   </si>
   <si>
     <t>6_3_3_2_6_6_1_8_4_4_7_5_1_2_9_6_2_8_2_1_1_4_3_5_3_6_8_9_6_4_4_1_6_5_8_3_7_6_1_2_9_3_2_5_8_6_6_4_7_5_4_4_4_3_2_7_1_5_6_6_2_2_8_4_4_2_1_3_6_8_5_4_2_7_3_8_9_4_3_7_1_4_9_2_6_5_3_4_4_3_7_8_3_3_9_9_5_3_6_4_6_1_1_1_8_4_4_8_8_6_7_3_2_2_4_8_5_5_3_7_2_1_9_1_4_9_9_3_6_9_5_5_1_1_4_1_1_2_2_1_3_3_8_1_4_8_6_3_3_1_4_4_1_3_9_6_8_2_5_6_1_2_6_2_3_9_1_4_5_8_5_1_5_7_3_2_7_9_5_5_5_7_7_3_6_7_7_2_1_1_1_6_2_2_2_6_5_3_1_1_1_5_6_3_3_3_5_4_6_6_3_5_2_1_8_3_1_1_7_3_9_8_6_9_9_4_6_4_9_3_7_1_1_8_5_5_1_3_3_4_6_5_5_1_8_5_1_3_3_5_2_3_1_4_1_7_5_8_1_5_6_2_5_6_8_8_8_9_5_8_8_4_2_4_2_2_2_3_1_5_3_9_5_5_5_7_4_9_9_1_8_6_1_1_4_7_3_2_2_9_9_3_6_6_3_6_4_2_2_4_2_9_6_7_5_3_1_8_9_2_8_2_1_3_9_5_6_9_5_9_4_2_4_4_3_9_1_1_7_7_1_4_6_6_3_7_7_8_7_4_6_4_5_7_8_4_4_3_2_2_4_5_6_1_3_1_1_5_6_1_1_1_6_3_4_2_7_4_1_7_5_6_2_7_1_1_4_8_4_2_4_5_4_3_8_2_2_5_6_4_7_9_6_4_2_4_4_4_4_4_5_3_1_1_4_9_2_3_2_5_6_3_2_2_8_3_5_2_9_1_1_2_8_3_6_3_9_1_4_1_2_8_3_5_5_5_6_9_2_6_5_1_1_8_5_4_2_2_9_6_5_5_2_4_1_9_9_9_1_1_1_6_7_7_2_1_4_7_8_6_8_9_8_4_4_3_5_5_5_4_2_9_4_1_1_2_8_2_3_9</t>
@@ -1888,7 +1906,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -2011,7 +2029,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:11">
       <c r="A5">
-        <f t="shared" ref="A5:A56" si="0">C5*10+D5</f>
+        <f t="shared" ref="A5:A62" si="0">C5*10+D5</f>
         <v>20010011</v>
       </c>
       <c r="B5" s="14">
@@ -3666,7 +3684,7 @@
     </row>
     <row r="57" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A57" s="6">
-        <f t="shared" ref="A57:A72" si="2">C57*10+D57</f>
+        <f t="shared" si="0"/>
         <v>20180011</v>
       </c>
       <c r="B57" s="14">
@@ -3698,7 +3716,7 @@
     </row>
     <row r="58" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A58" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>20180012</v>
       </c>
       <c r="B58" s="14">
@@ -3730,7 +3748,7 @@
     </row>
     <row r="59" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A59" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>20180013</v>
       </c>
       <c r="B59" s="14">
@@ -3762,7 +3780,7 @@
     </row>
     <row r="60" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A60" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>20180014</v>
       </c>
       <c r="B60" s="14">
@@ -3794,7 +3812,7 @@
     </row>
     <row r="61" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A61" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>20180015</v>
       </c>
       <c r="B61" s="14">
@@ -3826,7 +3844,7 @@
     </row>
     <row r="62" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A62" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>20180016</v>
       </c>
       <c r="B62" s="14">
@@ -3858,20 +3876,20 @@
     </row>
     <row r="63" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A63" s="6">
-        <f t="shared" si="2"/>
-        <v>20250011</v>
+        <f t="shared" ref="A63:A68" si="2">C63*10+D63</f>
+        <v>20180021</v>
       </c>
       <c r="B63" s="14">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C63" s="33">
-        <v>2025001</v>
+        <v>2018002</v>
       </c>
       <c r="D63" s="33">
         <v>1</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>20</v>
@@ -3883,7 +3901,7 @@
         <v>20</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="J63" s="17"/>
       <c r="K63" s="17"/>
@@ -3891,31 +3909,31 @@
     <row r="64" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A64" s="6">
         <f t="shared" si="2"/>
-        <v>20250012</v>
+        <v>20180022</v>
       </c>
       <c r="B64" s="14">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C64" s="33">
-        <v>2025001</v>
+        <v>2018002</v>
       </c>
       <c r="D64" s="33">
         <v>2</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="J64" s="17"/>
       <c r="K64" s="17"/>
@@ -3923,31 +3941,31 @@
     <row r="65" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A65" s="6">
         <f t="shared" si="2"/>
-        <v>20250013</v>
+        <v>20180023</v>
       </c>
       <c r="B65" s="14">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C65" s="33">
-        <v>2025001</v>
+        <v>2018002</v>
       </c>
       <c r="D65" s="33">
         <v>3</v>
       </c>
       <c r="E65" s="18" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="J65" s="17"/>
       <c r="K65" s="17"/>
@@ -3955,31 +3973,31 @@
     <row r="66" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A66" s="6">
         <f t="shared" si="2"/>
-        <v>20250014</v>
+        <v>20180024</v>
       </c>
       <c r="B66" s="14">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C66" s="33">
-        <v>2025001</v>
+        <v>2018002</v>
       </c>
       <c r="D66" s="33">
         <v>4</v>
       </c>
       <c r="E66" s="18" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="J66" s="17"/>
       <c r="K66" s="17"/>
@@ -3987,31 +4005,31 @@
     <row r="67" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A67" s="6">
         <f t="shared" si="2"/>
-        <v>20250015</v>
+        <v>20180025</v>
       </c>
       <c r="B67" s="14">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C67" s="33">
-        <v>2025001</v>
+        <v>2018002</v>
       </c>
       <c r="D67" s="33">
         <v>5</v>
       </c>
       <c r="E67" s="18" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="J67" s="17"/>
       <c r="K67" s="17"/>
@@ -4019,191 +4037,191 @@
     <row r="68" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A68" s="6">
         <f t="shared" si="2"/>
-        <v>20230011</v>
+        <v>20180026</v>
       </c>
       <c r="B68" s="14">
-        <v>102300</v>
+        <v>101800</v>
       </c>
       <c r="C68" s="33">
-        <v>2023001</v>
+        <v>2018002</v>
       </c>
       <c r="D68" s="33">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E68" s="18" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="J68" s="17"/>
       <c r="K68" s="17"/>
     </row>
     <row r="69" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A69" s="6">
-        <f t="shared" si="2"/>
-        <v>20230012</v>
+        <f t="shared" ref="A69:A78" si="3">C69*10+D69</f>
+        <v>20250011</v>
       </c>
       <c r="B69" s="14">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C69" s="33">
-        <v>2023001</v>
+        <v>2025001</v>
       </c>
       <c r="D69" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" s="18" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="J69" s="17"/>
       <c r="K69" s="17"/>
     </row>
     <row r="70" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A70" s="6">
-        <f t="shared" si="2"/>
-        <v>20230013</v>
+        <f t="shared" si="3"/>
+        <v>20250012</v>
       </c>
       <c r="B70" s="14">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C70" s="33">
-        <v>2023001</v>
+        <v>2025001</v>
       </c>
       <c r="D70" s="33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70" s="18" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="J70" s="17"/>
       <c r="K70" s="17"/>
     </row>
     <row r="71" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A71" s="6">
-        <f t="shared" si="2"/>
-        <v>20230014</v>
+        <f t="shared" si="3"/>
+        <v>20250013</v>
       </c>
       <c r="B71" s="14">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C71" s="33">
-        <v>2023001</v>
+        <v>2025001</v>
       </c>
       <c r="D71" s="33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E71" s="18" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="J71" s="17"/>
       <c r="K71" s="17"/>
     </row>
     <row r="72" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A72" s="6">
-        <f t="shared" si="2"/>
-        <v>20230015</v>
+        <f t="shared" si="3"/>
+        <v>20250014</v>
       </c>
       <c r="B72" s="14">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C72" s="33">
-        <v>2023001</v>
+        <v>2025001</v>
       </c>
       <c r="D72" s="33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E72" s="18" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="J72" s="17"/>
       <c r="K72" s="17"/>
     </row>
     <row r="73" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A73" s="6">
-        <f t="shared" ref="A73:A83" si="3">C73*10+D73</f>
-        <v>20230016</v>
+        <f t="shared" si="3"/>
+        <v>20250015</v>
       </c>
       <c r="B73" s="14">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C73" s="33">
-        <v>2023001</v>
+        <v>2025001</v>
       </c>
       <c r="D73" s="33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E73" s="18" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J73" s="17"/>
       <c r="K73" s="17"/>
@@ -4211,7 +4229,7 @@
     <row r="74" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A74" s="6">
         <f t="shared" si="3"/>
-        <v>20230017</v>
+        <v>20230011</v>
       </c>
       <c r="B74" s="14">
         <v>102300</v>
@@ -4220,22 +4238,22 @@
         <v>2023001</v>
       </c>
       <c r="D74" s="33">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E74" s="18" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="J74" s="17"/>
       <c r="K74" s="17"/>
@@ -4243,7 +4261,7 @@
     <row r="75" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A75" s="6">
         <f t="shared" si="3"/>
-        <v>20230018</v>
+        <v>20230012</v>
       </c>
       <c r="B75" s="14">
         <v>102300</v>
@@ -4252,22 +4270,22 @@
         <v>2023001</v>
       </c>
       <c r="D75" s="33">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J75" s="17"/>
       <c r="K75" s="17"/>
@@ -4275,7 +4293,7 @@
     <row r="76" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A76" s="6">
         <f t="shared" si="3"/>
-        <v>20230019</v>
+        <v>20230013</v>
       </c>
       <c r="B76" s="14">
         <v>102300</v>
@@ -4284,22 +4302,22 @@
         <v>2023001</v>
       </c>
       <c r="D76" s="33">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>109</v>
+        <v>50</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="J76" s="17"/>
       <c r="K76" s="17"/>
@@ -4307,7 +4325,7 @@
     <row r="77" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A77" s="6">
         <f t="shared" si="3"/>
-        <v>20230020</v>
+        <v>20230014</v>
       </c>
       <c r="B77" s="14">
         <v>102300</v>
@@ -4316,22 +4334,22 @@
         <v>2023001</v>
       </c>
       <c r="D77" s="33">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="J77" s="17"/>
       <c r="K77" s="17"/>
@@ -4339,7 +4357,7 @@
     <row r="78" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A78" s="6">
         <f t="shared" si="3"/>
-        <v>20230021</v>
+        <v>20230015</v>
       </c>
       <c r="B78" s="14">
         <v>102300</v>
@@ -4348,7 +4366,7 @@
         <v>2023001</v>
       </c>
       <c r="D78" s="33">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E78" s="18" t="s">
         <v>109</v>
@@ -4357,21 +4375,21 @@
         <v>20</v>
       </c>
       <c r="G78" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I78" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="J78" s="17"/>
       <c r="K78" s="17"/>
     </row>
     <row r="79" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A79" s="6">
-        <f t="shared" si="3"/>
-        <v>20230022</v>
+        <f t="shared" ref="A79:A89" si="4">C79*10+D79</f>
+        <v>20230016</v>
       </c>
       <c r="B79" s="14">
         <v>102300</v>
@@ -4380,7 +4398,7 @@
         <v>2023001</v>
       </c>
       <c r="D79" s="33">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E79" s="18" t="s">
         <v>109</v>
@@ -4395,15 +4413,15 @@
         <v>20</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="J79" s="17"/>
       <c r="K79" s="17"/>
     </row>
     <row r="80" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A80" s="6">
-        <f t="shared" si="3"/>
-        <v>20230023</v>
+        <f t="shared" si="4"/>
+        <v>20230017</v>
       </c>
       <c r="B80" s="14">
         <v>102300</v>
@@ -4412,7 +4430,7 @@
         <v>2023001</v>
       </c>
       <c r="D80" s="33">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E80" s="18" t="s">
         <v>109</v>
@@ -4427,135 +4445,135 @@
         <v>20</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="J80" s="17"/>
       <c r="K80" s="17"/>
     </row>
     <row r="81" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A81" s="6">
-        <f t="shared" si="3"/>
-        <v>20340011</v>
+        <f t="shared" si="4"/>
+        <v>20230018</v>
       </c>
       <c r="B81" s="14">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C81" s="33">
-        <v>2034001</v>
+        <v>2023001</v>
       </c>
       <c r="D81" s="33">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E81" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G81" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F81" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="H81" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="J81" s="17"/>
       <c r="K81" s="17"/>
     </row>
     <row r="82" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A82" s="6">
-        <f t="shared" si="3"/>
-        <v>20340012</v>
+        <f t="shared" si="4"/>
+        <v>20230019</v>
       </c>
       <c r="B82" s="14">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C82" s="33">
-        <v>2034001</v>
+        <v>2023001</v>
       </c>
       <c r="D82" s="33">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E82" s="18" t="s">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="J82" s="17"/>
       <c r="K82" s="17"/>
     </row>
     <row r="83" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A83" s="6">
-        <f t="shared" si="3"/>
-        <v>20340013</v>
+        <f t="shared" si="4"/>
+        <v>20230020</v>
       </c>
       <c r="B83" s="14">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C83" s="33">
-        <v>2034001</v>
+        <v>2023001</v>
       </c>
       <c r="D83" s="33">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E83" s="18" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="J83" s="17"/>
       <c r="K83" s="17"/>
     </row>
     <row r="84" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A84" s="6">
-        <f t="shared" ref="A84:A101" si="4">C84*10+D84</f>
-        <v>20340014</v>
+        <f t="shared" si="4"/>
+        <v>20230021</v>
       </c>
       <c r="B84" s="14">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C84" s="33">
-        <v>2034001</v>
+        <v>2023001</v>
       </c>
       <c r="D84" s="33">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E84" s="18" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="J84" s="17"/>
       <c r="K84" s="17"/>
@@ -4563,31 +4581,31 @@
     <row r="85" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A85" s="6">
         <f t="shared" si="4"/>
-        <v>20340015</v>
+        <v>20230022</v>
       </c>
       <c r="B85" s="14">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C85" s="33">
-        <v>2034001</v>
+        <v>2023001</v>
       </c>
       <c r="D85" s="33">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E85" s="18" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="J85" s="17"/>
       <c r="K85" s="17"/>
@@ -4595,19 +4613,19 @@
     <row r="86" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A86" s="6">
         <f t="shared" si="4"/>
-        <v>20340016</v>
+        <v>20230023</v>
       </c>
       <c r="B86" s="14">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C86" s="33">
-        <v>2034001</v>
+        <v>2023001</v>
       </c>
       <c r="D86" s="33">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E86" s="18" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>20</v>
@@ -4619,7 +4637,7 @@
         <v>20</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="J86" s="17"/>
       <c r="K86" s="17"/>
@@ -4627,7 +4645,7 @@
     <row r="87" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A87" s="6">
         <f t="shared" si="4"/>
-        <v>20340017</v>
+        <v>20340011</v>
       </c>
       <c r="B87" s="14">
         <v>103400</v>
@@ -4636,22 +4654,22 @@
         <v>2034001</v>
       </c>
       <c r="D87" s="33">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E87" s="18" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J87" s="17"/>
       <c r="K87" s="17"/>
@@ -4659,7 +4677,7 @@
     <row r="88" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A88" s="6">
         <f t="shared" si="4"/>
-        <v>20340018</v>
+        <v>20340012</v>
       </c>
       <c r="B88" s="14">
         <v>103400</v>
@@ -4668,22 +4686,22 @@
         <v>2034001</v>
       </c>
       <c r="D88" s="33">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E88" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J88" s="17"/>
       <c r="K88" s="17"/>
@@ -4691,7 +4709,7 @@
     <row r="89" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A89" s="6">
         <f t="shared" si="4"/>
-        <v>20340019</v>
+        <v>20340013</v>
       </c>
       <c r="B89" s="14">
         <v>103400</v>
@@ -4700,7 +4718,7 @@
         <v>2034001</v>
       </c>
       <c r="D89" s="33">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E89" s="18" t="s">
         <v>59</v>
@@ -4709,7 +4727,7 @@
         <v>20</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>20</v>
@@ -4722,238 +4740,238 @@
     </row>
     <row r="90" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A90" s="6">
-        <f t="shared" si="4"/>
-        <v>20350011</v>
+        <f t="shared" ref="A90:A107" si="5">C90*10+D90</f>
+        <v>20340014</v>
       </c>
       <c r="B90" s="14">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C90" s="33">
-        <v>2035001</v>
+        <v>2034001</v>
       </c>
       <c r="D90" s="33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E90" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I90" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="J90" s="17"/>
       <c r="K90" s="17"/>
     </row>
     <row r="91" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A91" s="6">
-        <f t="shared" si="4"/>
-        <v>20350012</v>
+        <f t="shared" si="5"/>
+        <v>20340015</v>
       </c>
       <c r="B91" s="14">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C91" s="33">
-        <v>2035001</v>
+        <v>2034001</v>
       </c>
       <c r="D91" s="33">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E91" s="18" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J91" s="17"/>
       <c r="K91" s="17"/>
     </row>
     <row r="92" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A92" s="6">
-        <f t="shared" si="4"/>
-        <v>20350013</v>
+        <f t="shared" si="5"/>
+        <v>20340016</v>
       </c>
       <c r="B92" s="14">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C92" s="33">
-        <v>2035001</v>
+        <v>2034001</v>
       </c>
       <c r="D92" s="33">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E92" s="18" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="J92" s="17"/>
       <c r="K92" s="17"/>
     </row>
     <row r="93" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A93" s="6">
-        <f t="shared" si="4"/>
-        <v>20350021</v>
+        <f t="shared" si="5"/>
+        <v>20340017</v>
       </c>
       <c r="B93" s="14">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C93" s="33">
-        <v>2035002</v>
+        <v>2034001</v>
       </c>
       <c r="D93" s="33">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E93" s="18" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="J93" s="17"/>
       <c r="K93" s="17"/>
     </row>
     <row r="94" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A94" s="6">
-        <f t="shared" si="4"/>
-        <v>20350022</v>
+        <f t="shared" si="5"/>
+        <v>20340018</v>
       </c>
       <c r="B94" s="14">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C94" s="33">
-        <v>2035002</v>
+        <v>2034001</v>
       </c>
       <c r="D94" s="33">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E94" s="18" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J94" s="17"/>
       <c r="K94" s="17"/>
     </row>
     <row r="95" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A95" s="6">
-        <f t="shared" si="4"/>
-        <v>20350023</v>
+        <f t="shared" si="5"/>
+        <v>20340019</v>
       </c>
       <c r="B95" s="14">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C95" s="33">
-        <v>2035002</v>
+        <v>2034001</v>
       </c>
       <c r="D95" s="33">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E95" s="18" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="J95" s="17"/>
       <c r="K95" s="17"/>
     </row>
     <row r="96" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A96" s="6">
-        <f t="shared" si="4"/>
-        <v>20350111</v>
+        <f t="shared" si="5"/>
+        <v>20350011</v>
       </c>
       <c r="B96" s="14">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C96" s="33">
-        <v>2035011</v>
+        <v>2035001</v>
       </c>
       <c r="D96" s="33">
         <v>1</v>
       </c>
       <c r="E96" s="18" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="J96" s="17"/>
       <c r="K96" s="17"/>
     </row>
     <row r="97" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A97" s="6">
-        <f t="shared" si="4"/>
-        <v>20350112</v>
+        <f t="shared" si="5"/>
+        <v>20350012</v>
       </c>
       <c r="B97" s="14">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C97" s="33">
-        <v>2035011</v>
+        <v>2035001</v>
       </c>
       <c r="D97" s="33">
         <v>2</v>
@@ -4965,27 +4983,27 @@
         <v>20</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="J97" s="17"/>
       <c r="K97" s="17"/>
     </row>
     <row r="98" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A98" s="6">
-        <f t="shared" si="4"/>
-        <v>20350113</v>
+        <f t="shared" si="5"/>
+        <v>20350013</v>
       </c>
       <c r="B98" s="14">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C98" s="33">
-        <v>2035011</v>
+        <v>2035001</v>
       </c>
       <c r="D98" s="33">
         <v>3</v>
@@ -4997,27 +5015,27 @@
         <v>20</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J98" s="17"/>
       <c r="K98" s="17"/>
     </row>
     <row r="99" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A99" s="6">
-        <f t="shared" si="4"/>
-        <v>20350121</v>
+        <f t="shared" si="5"/>
+        <v>20350021</v>
       </c>
       <c r="B99" s="14">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C99" s="33">
-        <v>2035012</v>
+        <v>2035002</v>
       </c>
       <c r="D99" s="33">
         <v>1</v>
@@ -5029,27 +5047,27 @@
         <v>20</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>163</v>
+        <v>20</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="J99" s="17"/>
       <c r="K99" s="17"/>
     </row>
     <row r="100" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A100" s="6">
-        <f t="shared" si="4"/>
-        <v>20350122</v>
+        <f t="shared" si="5"/>
+        <v>20350022</v>
       </c>
       <c r="B100" s="14">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C100" s="33">
-        <v>2035012</v>
+        <v>2035002</v>
       </c>
       <c r="D100" s="33">
         <v>2</v>
@@ -5061,27 +5079,27 @@
         <v>20</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="J100" s="17"/>
       <c r="K100" s="17"/>
     </row>
     <row r="101" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A101" s="6">
-        <f t="shared" si="4"/>
-        <v>20350123</v>
+        <f t="shared" si="5"/>
+        <v>20350023</v>
       </c>
       <c r="B101" s="14">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C101" s="33">
-        <v>2035012</v>
+        <v>2035002</v>
       </c>
       <c r="D101" s="33">
         <v>3</v>
@@ -5093,16 +5111,208 @@
         <v>20</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="J101" s="17"/>
       <c r="K101" s="17"/>
+    </row>
+    <row r="102" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A102" s="6">
+        <f t="shared" si="5"/>
+        <v>20350111</v>
+      </c>
+      <c r="B102" s="14">
+        <v>103501</v>
+      </c>
+      <c r="C102" s="33">
+        <v>2035011</v>
+      </c>
+      <c r="D102" s="33">
+        <v>1</v>
+      </c>
+      <c r="E102" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J102" s="17"/>
+      <c r="K102" s="17"/>
+    </row>
+    <row r="103" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A103" s="6">
+        <f t="shared" si="5"/>
+        <v>20350112</v>
+      </c>
+      <c r="B103" s="14">
+        <v>103501</v>
+      </c>
+      <c r="C103" s="33">
+        <v>2035011</v>
+      </c>
+      <c r="D103" s="33">
+        <v>2</v>
+      </c>
+      <c r="E103" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="J103" s="17"/>
+      <c r="K103" s="17"/>
+    </row>
+    <row r="104" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A104" s="6">
+        <f t="shared" si="5"/>
+        <v>20350113</v>
+      </c>
+      <c r="B104" s="14">
+        <v>103501</v>
+      </c>
+      <c r="C104" s="33">
+        <v>2035011</v>
+      </c>
+      <c r="D104" s="33">
+        <v>3</v>
+      </c>
+      <c r="E104" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J104" s="17"/>
+      <c r="K104" s="17"/>
+    </row>
+    <row r="105" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A105" s="6">
+        <f t="shared" si="5"/>
+        <v>20350121</v>
+      </c>
+      <c r="B105" s="14">
+        <v>103501</v>
+      </c>
+      <c r="C105" s="33">
+        <v>2035012</v>
+      </c>
+      <c r="D105" s="33">
+        <v>1</v>
+      </c>
+      <c r="E105" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="J105" s="17"/>
+      <c r="K105" s="17"/>
+    </row>
+    <row r="106" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A106" s="6">
+        <f t="shared" si="5"/>
+        <v>20350122</v>
+      </c>
+      <c r="B106" s="14">
+        <v>103501</v>
+      </c>
+      <c r="C106" s="33">
+        <v>2035012</v>
+      </c>
+      <c r="D106" s="33">
+        <v>2</v>
+      </c>
+      <c r="E106" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J106" s="17"/>
+      <c r="K106" s="17"/>
+    </row>
+    <row r="107" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A107" s="6">
+        <f t="shared" si="5"/>
+        <v>20350123</v>
+      </c>
+      <c r="B107" s="14">
+        <v>103501</v>
+      </c>
+      <c r="C107" s="33">
+        <v>2035012</v>
+      </c>
+      <c r="D107" s="33">
+        <v>3</v>
+      </c>
+      <c r="E107" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="J107" s="17"/>
+      <c r="K107" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5119,7 +5329,7 @@
   <sheetData>
     <row r="24" ht="16.5" spans="9:9">
       <c r="I24" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -418,22 +418,22 @@
     <t>4_2_4_2_1_6_1_5_4_9_6_4_2_6_3_4_1_6_7_2_8_3_9_1_8_4_1_4_7_7_6_4_4_3_1_5_5_10_6_2_1_3_2_9_3_5_7_4_9_8_5_1_4_6_1_9_8_1_9_1_7_5_6_5_3_9_6_4_3_1_7_2_4_1_3_5_4_7_4_6_3_9_1_6_2_6_5_2_4_4_8_5_6_3_2_1_1_2_3_5_3_1_1_3_6_7_9_7_1_3_7_7_2_3_1_9_1_8_4_2_2_6_8_1_3_1_5_8_9_6_1_7_4_7_9_3_6_2_2_4_5_3_3_6_8_4_5_8_1_1_8_5_2_10_2_8_2_7_7_4_1_2_8_3_3_4_3_4_1_2_9_6_3_4_2_1_9_2_3_9_8_2_3_7_4_1_1_2_2_9_5_6_8_4_8_5_7_2_1_7_6_5_6_2_9_10_3_1_4_7_2_7_3_5_1_1_6_1_4_7_4_6_4_9_1_1_6_4_7_3_1_6_7_1_8_4_9_9_8_10_6_3_1_2_4_2_5_2_2_1_6_3_9_3_8_6_10_7_4_4_6_1_3_9_2_2_2_6_3_4_4_6_9_5_2_4_7_4_1_6_6_8_5_7_8_1_6_4_4_1_8_1_4_5_3_3_3_1_2_6_4_4_9_1_6_4_5_4_5_7_2_2_1_10_3_9_5_1_7_2_4_4_2_1_4_1_2_1_8_2_1_8_2_8_3_4_3_3_7_3_1_3_4_8_1_5_2_3_9_6_8_5_8_5_7_5_2_8_1_2_6_6_3_4_2_9_3_10_2_5_1_3_4_3_6_5_3_4_6_1_3_5_2_4_9_1_2_1_7_3_9_3_8_10_7_6_2_4_9_7_8_9_2_9_7_9_5_4_7_1_9_5_2_9_5_1_5_1_3_4_5_2_8_7_1_4_9_2_1_4_8_4_8_9_10_6_7_2_1_4_2_4_8_6_4_8_8_7_2_1_9_9_4_4_2_6_4_8_9_9_2_1_8_4_8_9_4_6_8_3_1_6_3_1_7_7_2_7_6_9_1_7_3_4_5_4_2_3_1_1_5_5_7_4_1_5_7_3_4_9</t>
   </si>
   <si>
-    <t>4_6_9_5_8_3_9_5_10_8_7_9_9_3_9_5_5_8_7_2_2_10_8_7_2_8_8_4_6_8_8_8_7_10_10_1_9_9_4_2_9_9_7_5_8_9_8_7_7_8_8_8_8_10_2_10_4_10_7_5_7_7_2_2_9_7_9_9_5_2_8_8_3_5_8_5_5_2_7_8_2_8_4_7_8_7_6_5_5_5_7_10_1_1_8_10_5_2_4_2_6_9_4_5_5_9_5_5_10_2_2_8_7_2_10_3_1_10_1_3_10_5_3_3_8_8_7_7_6_5_7_4_8_10_9_5_5_3_9_6_2_9_5_5_3_8_8_8_8_10_9_9_10_9_4_7_9_10_4_9_7_9_7_10_8_8_7_4_10_5_2_2_6_7_8_7_2_9_1_2_10_3_4_5_2_2_3_2_2_7_3_9_6_5_10_3_1_9_3_7_6_8_6_9_4_7_8_5_10_6_8_7_2_2_7_8_6_8_10_3_7_8_8_7_7_7_9_6_1_2_4_5_9_10_4_6_7_10_8_8_5_6_8_3_9_9_5_9_6_6_6_8_8_5_7_3_9_7_6_6_8_8_8_10_9_2_8_6_7_4_3_7_9_7_8_9_3_8_8_5_3_7_7_7_3_3_5_5_5_7_9_9_8_8_9_9_6_10_5_9_4_5_5_5_5_9_6_10_8_10_7_10_8_9_5_8_7_5_5_2_9_2_2_10_8_8_9_9_9_6_5_9_8_5_6_2_8_9_10_10_8_5_7_8_8_8_2_5_10_7_7_7_9_5_8_10_3_8_9_9_4_5_4_5_5_5_10_9_9_8_5_7_10_10_9_7_7_3_5_3_8_5_5_3_6_8_3_10_1_7_6_5_1_2_6_6_9_6_8_9_2_5_6_10_8_8_4_5_6_7_4_9_9_9_10_3_9_9_5_5_7_6_6_3_7_7_9_10_5_10_5_9_7_7_10_10_1_4_4_10_5_10_10_8_10_3_10_10_10_9_10_9_5_4_9_7_8_7_10_10_3_9_9_9_8_9_10_9_7_10_3_8_8_10_3_5_9_8_1_7_6_10_7_2_2_7_10_10_6_9_7_8_7_7_10_8_3_6_8_8</t>
-  </si>
-  <si>
-    <t>9_4_4_4_4_10_2_2_10_9_9_10_10_9_10_5_3_2_5_4_10_5_10_9_9_8_9_9_9_8_10_7_10_9_7_5_5_10_10_4_4_9_1_10_10_8_9_1_1_1_10_10_10_3_8_10_3_7_9_7_6_2_9_8_5_6_6_10_5_5_7_6_2_6_5_9_5_3_9_2_4_7_5_6_5_5_10_10_3_10_1_3_9_4_7_7_4_4_4_7_2_1_4_5_3_6_6_3_4_4_8_6_8_8_10_10_7_9_5_10_5_6_5_2_3_2_2_3_10_10_5_2_9_8_8_3_3_3_1_10_8_2_6_7_7_9_5_9_9_8_10_9_1_5_3_3_9_3_9_9_9_5_6_7_9_7_6_10_5_7_7_2_4_4_8_9_9_9_5_2_10_10_2_5_9_3_10_4_7_6_7_10_5_6_2_4_10_10_8_8_10_6_6_2_5_10_10_6_7_7_5_9_10_3_10_4_2_8_8_9_4_6_5_10_8_6_10_8_8_5_5_9_9_9_4_5_10_10_7_9_8_9_5_3_4_8_7_7_3_7_9_9_9_10_1_10_8_7_5_7_8_5_7_9_4_6_4_8_4_6_8_10_8_8_7_3_2_10_8_8_7_4_7_8_7_4_9_5_7_9_9_8_3_3_5_5_1_5_5_5_9_10_6_5_1_1_9_5_7_8_9_8_10_4_9_6_8_8_10_5_9_9_9_8_6_6_10_6_4_2_2_5_6_6_6_6_6_8_10_9_6_7_7_3_9_7_8_8_9_7_3_9_9_4_10_4_7_7_7_6_9_3_4_9_8_8_2_6_6_6_8_7_9_8_2_2_9_2_8_2_7_3_10_5_9_5_6_8_8_10_10_7_2_8_7_7_5_9_9_8_4_6_6_7_6_4_9_9_10_3_9_8_8_9_10_10_1_1_4_3_4_8_9_9_9_5_7_8_1_7_8_6_3_9_9_4_4_10_10_3_7_3_6_8_3_10_5_9_8_10_2_9_5_3_9_8_10_3_4_8_10_5_3_4_9_10_5_2_10_10_9_2_5_10_10_10_9_9_6_9_6_10_10_10_4_5_9_7_7_10_9_9_7_3_10_9_10_9_8_7</t>
-  </si>
-  <si>
-    <t>8_8_4_5_5_4_4_5_5_8_9_3_8_6_6_9_8_10_5_7_1_4_4_4_9_5_5_5_5_5_8_1_4_4_6_10_9_3_4_9_5_8_7_9_9_6_6_1_9_6_10_9_9_5_4_9_8_3_7_5_8_7_5_4_3_5_10_10_2_3_7_7_8_9_9_3_4_8_8_9_7_10_10_10_1_8_7_9_5_5_9_7_9_9_7_6_8_10_5_8_10_8_8_8_9_9_9_3_4_8_3_3_9_8_5_6_10_6_8_6_3_6_7_7_7_10_6_5_10_10_5_6_9_3_6_5_2_5_5_5_5_10_8_9_7_8_10_6_4_7_9_7_7_7_3_3_8_4_10_7_8_7_10_10_10_10_10_5_8_6_9_10_9_9_9_10_5_8_4_8_9_3_3_10_10_9_7_5_5_3_6_9_2_4_10_2_5_9_1_6_5_5_4_10_2_9_3_9_4_4_6_8_8_3_3_6_6_3_8_4_4_4_3_7_7_7_8_6_5_7_8_5_8_9_4_5_5_5_5_2_5_6_9_5_5_6_6_10_8_9_10_3_3_1_10_7_8_8_5_2_7_10_10_10_7_8_7_3_10_9_9_5_6_10_9_10_10_8_7_8_8_7_8_3_5_10_8_10_1_2_3_1_5_3_4_6_10_1_9_9_9_10_9_2_8_9_9_6_10_8_8_4_8_6_7_8_4_10_2_6_3_7_10_7_5_5_8_8_10_5_7_9_7_7_6_10_10_4_10_10_2_8_8_10_10_10_8_2_8_5_6_6_9_8_7_10_9_10_6_6_9_9_9_2_7_4_2_7_7_10_4_2_3_7_10_2_3_8_5_5_9_8_9_7_7_7_7_6_6_6_1_5_6_3_3_3_4_5_6_6_2_5_7_10_4_10_6_7_6_6_10_10_8_8_10_9_10_4_8_7_9_7_7_4_8_9_5_5_5_7_3_7_9_9_9_8_3_7_6_4_4_8_10_10_10_10_8_9_4_6_6_1_7_6_7_8_8_9_9_7_5_5_10_5_6_10_9_7_4_7_8_10_10_10_7_9_9_10_6_9_2_5_7_9_7_8_6_4_9_3_8_2_4_3_9_4_4_9_6_2</t>
-  </si>
-  <si>
-    <t>3_8_7_7_4_4_9_8_4_9_7_6_8_3_3_7_3_7_10_8_10_9_9_10_5_10_8_4_8_7_7_6_9_7_10_2_4_4_9_5_2_9_7_6_7_6_4_4_5_7_8_6_6_6_5_5_5_5_8_7_9_10_3_2_9_2_2_10_5_5_3_7_8_5_10_8_3_8_8_8_5_5_8_8_10_8_10_7_5_4_8_4_7_7_3_10_1_9_8_4_6_10_9_5_8_8_8_8_4_5_10_1_9_8_8_1_6_10_8_9_10_10_5_9_9_9_7_10_2_1_9_7_9_7_2_9_4_10_9_7_5_5_10_1_10_6_7_4_4_7_9_9_9_9_4_5_3_9_10_8_9_7_1_1_8_1_8_7_8_6_8_5_8_4_1_2_10_8_8_8_1_8_7_7_10_10_2_3_6_4_3_6_9_8_8_9_4_5_6_8_8_7_5_3_6_10_9_8_10_6_6_6_8_9_1_10_2_4_6_3_5_9_10_7_6_10_4_9_6_9_6_1_6_8_1_5_1_6_10_9_9_9_5_9_6_10_10_7_10_7_7_6_7_7_10_10_5_7_9_5_5_2_6_9_4_10_10_8_8_9_8_3_10_9_2_2_5_4_10_10_7_4_2_2_4_10_3_8_10_2_5_10_4_4_6_8_5_5_8_9_3_3_3_10_8_4_4_5_3_7_6_2_2_7_5_10_4_10_8_9_9_3_9_10_5_6_9_3_5_10_10_5_5_10_4_4_10_10_5_9_9_9_6_9_3_2_2_8_8_9_10_9_10_9_3_10_5_7_5_5_6_8_6_4_8_6_6_3_4_6_10_10_1_10_10_6_8_8_10_10_8_5_5_3_5_6_5_3_4_8_5_5_5_3_8_10_8_8_7_10_5_10_7_5_10_10_6_4_4_4_2_2_9_9_3_5_7_7_7_7_10_10_4_3_5_7_10_3_2_9_4_7_4_9_10_7_9_9_9_5_5_10_10_6_9_8_10_8_9_8_7_7_8_6_6_3_4_7_4_2_8_5_8_3_3_10_4_4_8_8_8_2_3_9_9_10_9_10_2_6_6_5_9_1_1_4_10_6_10_10_9_10_7_7_3_9_10_5_9_9</t>
-  </si>
-  <si>
-    <t>8_6_5_5_2_2_6_5_6_7_6_8_5_10_7_5_7_7_3_8_8_7_5_1_7_5_6_6_3_10_10_10_10_9_3_7_6_6_7_8_8_8_4_10_8_3_3_10_10_2_8_10_1_8_8_5_10_10_4_9_7_6_6_3_9_9_3_8_9_9_9_5_8_7_7_7_9_3_2_4_10_8_7_10_7_7_10_2_7_9_6_9_6_7_10_10_6_7_9_9_10_8_2_9_10_9_6_6_8_5_6_5_6_8_9_4_9_7_9_9_4_5_4_6_8_7_10_3_9_8_8_5_9_10_9_9_3_9_9_6_9_2_9_10_9_9_9_7_10_10_7_10_2_5_9_9_8_10_8_10_10_8_6_9_6_6_8_7_4_7_10_4_10_9_9_3_5_6_8_7_10_9_9_9_7_6_10_2_5_7_1_4_6_7_7_9_10_8_10_10_10_9_6_5_3_9_1_9_7_3_4_2_9_7_6_8_8_6_4_9_7_7_5_6_8_7_4_8_2_2_10_9_9_6_3_1_6_6_7_9_6_6_6_2_10_9_8_9_5_3_9_8_8_7_5_5_3_5_10_10_5_10_10_3_8_8_8_7_4_10_3_5_10_9_4_4_2_7_2_7_6_6_5_6_9_3_6_8_5_1_10_10_7_6_3_6_6_8_5_3_8_10_9_9_6_7_5_3_7_5_9_9_1_7_6_8_3_10_7_7_7_7_10_5_10_5_10_10_8_6_8_8_4_4_3_6_7_7_6_5_10_6_6_9_3_7_1_6_6_7_5_6_10_9_7_7_6_6_6_9_8_3_10_10_4_3_3_8_8_9_10_10_2_2_5_5_9_4_4_9_1_3_7_8_3_7_8_10_6_9_2_9_10_2_10_5_5_9_4_8_9_6_9_7_3_2_5_3_5_10_7_10_10_7_5_8_7_6_10_2_8_7_9_9_6_10_10_8_10_5_8_4_5_8_8_8_8_7_7_6_6_3_4_4_10_7_6_5_9_10_9_5_4_8_6_8_8_6_4_4_7_7_9_10_7_9_8_9_10_10_9_9_7_10_5_7_7_9_7_10_4_6_7_9_7_3_8_3_2_8_4_9_2_9_3_10_10_9_10_10</t>
-  </si>
-  <si>
-    <t>2_4_5_10_10_4_10_9_8_2_10_1_9_10_10_7_3_8_2_2_4_5_6_10_10_8_8_8_6_7_8_10_9_10_8_6_5_4_4_9_5_2_9_4_2_5_1_5_5_5_5_6_7_5_4_10_7_3_2_10_4_9_7_5_8_9_10_2_9_8_5_7_6_5_2_2_4_3_10_10_8_2_7_10_3_10_4_10_4_8_10_6_5_4_2_2_6_8_3_9_7_9_7_7_5_9_9_9_2_7_7_10_6_5_8_10_8_10_10_9_10_5_8_6_8_8_6_6_9_2_5_5_10_9_5_7_3_7_4_4_10_9_3_9_9_4_4_10_5_9_6_6_7_8_8_5_5_4_5_10_7_4_7_9_8_10_9_10_4_9_8_5_10_7_5_4_3_8_6_9_2_2_4_1_7_5_9_9_10_6_2_2_2_8_3_7_4_2_2_5_6_10_5_10_8_5_5_8_9_5_10_10_6_6_3_3_10_4_7_5_3_8_2_9_7_1_1_10_9_9_8_5_4_4_10_10_10_10_8_9_10_4_4_8_10_3_5_8_10_10_5_4_6_10_7_5_8_7_5_10_10_10_10_6_6_7_3_2_10_3_1_2_4_9_7_9_6_8_5_8_8_4_5_9_9_6_10_10_9_2_10_10_10_10_4_6_10_5_8_8_8_8_10_10_7_7_9_6_7_8_10_3_10_3_4_10_10_8_3_7_7_10_10_8_7_7_10_9_7_8_8_8_10_10_6_10_3_6_3_7_4_8_5_7_9_6_4_4_4_3_3_8_3_8_3_6_3_9_4_5_7_10_9_9_10_1_4_1_3_9_9_8_7_10_3_3_3_10_8_5_5_8_9_10_9_8_8_5_3_10_7_10_6_5_5_8_8_4_9_6_10_8_8_8_9_10_2_2_2_5_2_10_5_3_9_2_4_9_10_2_8_8_3_10_9_5_5_6_4_7_10_9_10_7_8_7_4_4_1_10_10_8_8_6_6_1_8_8_8_10_4_9_3_8_7_9_7_10_10_9_2_9_9_10_10_4_9_9_9_2_9_9_7_10_6_3_9_6_6_2_2_7_5_6_5_9_7_7_7_9_5_5_10_6_4_8_10_10_7_8</t>
+    <t>5_1_6_6_1_2_6_2_5_5_2_1_2_2_9_1_2_2_3_1_3_3_3_4_6_4_2_6_1_1_2_1_3_3_2_6_5_1_6_5_3_8_1_3_5_6_9_4_4_1_7_6_1_1_3_3_3_2_3_1_4_1_1_6_4_4_1_6_9_1_3_8_1_6_2_4_6_4_1_1_4_5_8_1_1_4_2_4_3_1_3_4_1_3_1_1_3_1_1_2_1_1_5_1_4_6_6_4_3_4_4_4_1_5_6_1_1_5_6_2_5_2_5_2_4_2_5_3_3_6_3_2_2_2_1_2_4_7_1_2_5_6_2_3_1_3_3_4_2_2_2_3_3_3_2_8_2_4_2_3_3_2_3_9_3_2_6_4_2_5_6_6_6_3_6_6_4_2_2_3_4_6_4_1_2_1_2_2_2_9_4_2_1_3_3_3_2_4_2_3_5_6_5_4_4_2_5_1_5_2_1_2_6_5_2_3_3_3_5_6_1_1_3_1_2_1_5_5_5_6_3_1_4_4_1_4_4_8_4_2_6_2_4_6_4_4_5_5_4_1_5_1_4_10_10_6_4_7_4_3_2_6_6_3_8_3_3_3_1_3_3_1_1_3_2_6_1_1_4_3_5_5_5_1_4_3_1_4_2_2_1_5_5_2_2_3_5_5_1_2_2_2_2_8_5_1_2_2_3_1_1_4_4_5_2_2_5_1_4_2_7_3_3_6_2_3_5_3_3_4_1_3_6_6_7_2_2_2_1_5_6_5_2_4_4_7_1_2_5_6_6_6_2_8_7_4_2_2_10_10_1_2_1_7_3_1_2_2_6_2_1_4_4_1_2_2_2_1_1_8_1_1_6_6_6_4_9_4_2_7_7_7_4_10_4_5_3_2_6_6_8_1_3_6_4_5_3_5_3_3_3_3_3_6_3_4_4_3_6_1_1_5_1_2_6_4_1_1_6_5_9_5_6_1_3_3_7_6_1_3_5_4_6_2_2_2_2_2_9_9_3_2_7_7_7_8_4_7_2_4_2_1_1_2_2_1_4_7_4_2_6_1_1_3_6_4_5_3_3_3_4_2_2_4_5_4_2_3_2_10_1_2_2_2_2_3_3_4_5_2</t>
+  </si>
+  <si>
+    <t>2_1_4_4_1_8_5_1_1_1_1_6_6_1_1_2_3_5_2_5_5_6_2_2_2_1_2_6_6_4_9_1_1_3_5_1_4_5_7_5_3_3_2_1_4_3_4_4_6_3_3_2_4_5_2_1_4_2_3_3_3_1_2_3_3_7_6_1_2_3_6_3_2_1_3_2_3_2_1_1_1_6_4_3_5_2_3_3_8_1_3_5_5_6_6_6_2_2_1_2_9_2_1_5_4_3_1_2_2_3_2_4_2_1_5_5_3_3_1_1_1_3_5_8_4_4_1_1_2_1_1_2_2_2_3_3_4_8_1_5_4_3_1_1_4_2_1_4_3_2_2_3_2_1_2_1_8_6_1_2_2_1_4_4_2_3_9_2_7_4_2_3_1_1_1_1_1_1_7_1_3_6_2_1_1_1_1_1_4_6_4_3_4_8_4_2_2_2_2_4_6_3_4_2_2_3_4_1_3_1_5_5_3_1_4_3_2_2_1_1_1_4_3_2_3_3_6_1_2_1_4_1_4_4_6_1_2_3_3_5_1_4_1_3_1_4_1_5_2_6_6_6_6_6_4_5_5_6_6_4_2_2_2_2_2_2_3_1_3_3_5_1_1_4_6_4_4_6_3_3_3_3_2_5_3_2_2_3_1_5_5_3_2_2_3_3_8_2_2_3_5_5_3_4_4_1_2_1_4_3_1_1_5_6_4_4_10_8_9_3_2_1_4_4_6_4_2_9_2_2_5_6_2_5_2_3_3_2_3_3_3_3_2_3_3_3_1_4_4_6_5_5_5_6_1_1_2_1_3_3_3_6_7_1_4_1_4_3_1_9_2_6_5_5_5_3_7_7_8_1_4_4_3_2_4_2_1_6_4_3_1_6_6_5_5_5_5_7_4_2_1_5_3_2_4_3_4_7_2_2_6_1_2_5_5_5_1_2_8_2_1_5_3_2_6_2_8_2_3_2_1_4_1_3_8_3_2_9_2_5_4_3_3_5_5_3_2_5_5_2_7_1_2_6_6_5_3_1_6_4_6_4_4_3_2_2_3_1_1_1_6_1_1_8_4_3_2_1_1_3_2_2_2_2_8_2_2_4_1_1_1_3_2_2_5_4_1_3_5_3</t>
+  </si>
+  <si>
+    <t>1_5_1_1_2_4_1_3_5_5_7_7_3_2_2_6_3_2_1_2_3_3_4_4_3_2_1_3_5_3_4_9_3_2_1_7_7_8_3_3_3_10_4_3_2_4_2_1_2_4_4_10_3_1_1_3_4_7_3_3_4_2_6_6_6_1_2_5_1_4_4_5_3_1_1_5_2_1_5_4_1_1_3_3_3_2_2_2_1_2_2_4_4_1_5_2_2_5_5_3_4_2_1_1_1_2_6_6_9_6_4_3_2_1_5_5_1_6_4_3_6_4_3_5_3_3_8_6_6_6_10_9_2_2_2_6_5_3_6_7_6_3_1_3_2_1_3_8_5_2_2_1_5_3_2_9_3_2_3_3_3_3_3_3_6_3_5_7_7_1_1_1_9_5_1_10_4_6_3_1_9_6_2_1_2_2_2_1_6_5_2_4_6_3_4_1_4_3_3_4_7_7_7_1_4_2_6_1_6_2_3_3_3_4_3_2_2_7_7_4_3_1_6_5_5_5_2_6_4_1_8_4_4_6_1_5_2_10_2_5_4_7_3_3_1_1_2_6_3_1_1_2_6_6_2_1_3_1_1_5_3_3_9_1_1_2_6_6_3_3_2_2_1_4_1_8_3_6_6_7_1_3_4_9_5_3_5_1_1_1_3_8_3_6_1_6_6_2_2_4_4_1_3_6_1_1_1_1_1_1_6_4_6_6_6_4_2_3_4_3_6_4_4_2_4_1_5_4_1_5_4_2_3_3_1_2_8_3_4_1_1_5_1_1_2_2_2_2_5_2_6_2_4_5_4_3_6_2_1_1_1_5_2_1_5_5_6_5_2_1_2_2_1_1_3_3_4_6_3_3_5_6_4_1_1_2_5_9_2_3_3_1_2_6_4_3_3_3_3_6_9_2_1_6_2_4_1_1_4_4_2_2_2_5_6_1_1_2_2_1_3_5_4_1_1_1_1_2_3_5_5_3_3_3_1_4_8_2_10_2_1_5_1_5_1_3_7_1_1_6_6_1_6_5_3_5_1_1_1_7_6_6_2_5_4_8_3_5_6_5_7_1_4_4_4_2_1_1_1_1_3_4_6_2_1_3_6_2_5_1_1_1_2_8_6_1_3_2_6_1</t>
+  </si>
+  <si>
+    <t>1_2_2_1_4_4_4_1_1_1_5_3_4_4_1_4_2_1_2_5_1_5_1_4_4_3_2_3_6_1_3_3_4_5_2_2_5_5_5_1_1_2_2_5_5_6_1_2_1_3_6_5_5_5_2_4_1_3_1_5_2_1_2_2_2_1_1_2_3_6_8_10_5_6_2_1_4_4_2_6_3_2_4_5_3_2_6_3_1_9_4_1_4_6_3_5_5_4_1_4_2_5_3_1_2_1_1_2_6_6_5_8_1_4_8_8_8_6_1_3_2_1_4_6_3_2_4_4_3_1_4_6_6_3_2_5_2_4_4_2_2_3_3_10_9_1_6_1_5_1_1_5_3_2_6_1_1_8_8_3_3_2_5_5_1_3_2_10_5_5_1_4_2_6_2_6_1_5_5_1_9_9_9_2_6_1_1_1_2_9_3_2_4_4_1_3_4_6_4_4_6_4_3_2_2_6_2_1_4_5_3_1_8_1_1_3_5_7_3_5_5_6_2_2_4_4_3_1_1_2_2_1_3_2_1_6_2_1_10_7_2_1_6_1_8_7_1_2_2_5_6_3_3_2_2_2_4_3_3_3_3_2_9_3_3_4_5_6_3_5_10_1_4_4_4_2_2_4_1_3_2_3_6_3_4_1_1_4_3_2_10_3_3_7_7_2_1_3_1_1_3_3_3_1_8_1_9_1_3_3_3_3_4_3_3_4_2_3_2_2_7_4_1_6_1_2_6_6_3_4_5_5_3_3_7_1_2_1_4_6_6_4_4_5_1_4_4_2_6_4_6_5_1_2_4_3_4_4_6_2_10_3_4_5_5_5_1_4_1_3_3_8_1_3_3_5_1_5_3_4_2_1_1_2_6_3_7_4_1_4_2_5_3_1_4_6_2_6_3_4_2_4_4_6_5_1_9_4_2_2_4_1_2_5_5_4_3_1_1_1_1_5_1_5_4_1_5_6_8_6_6_3_4_1_1_3_8_1_1_2_4_4_7_8_3_5_1_2_6_4_2_4_4_5_5_1_1_6_3_4_6_2_3_8_6_6_3_5_4_5_1_1_3_10_1_2_5_3_7_4_4_6_1_1_8_8_5_5_6_1_2_8_4_2_1_10_1_2_6_2</t>
+  </si>
+  <si>
+    <t>2_1_3_2_2_4_6_1_6_3_1_8_5_4_3_2_7_7_2_3_4_4_3_2_2_4_3_3_3_3_8_5_4_1_3_4_4_5_3_5_1_1_1_1_2_1_1_4_1_5_5_5_3_8_8_6_1_2_1_2_1_4_1_1_6_2_2_3_2_4_3_7_3_4_7_2_3_3_6_9_9_9_1_1_3_7_7_6_6_3_8_1_1_2_4_4_6_1_1_1_1_1_1_4_5_3_9_1_3_2_4_3_4_4_9_3_2_4_5_4_5_10_3_3_1_5_2_2_2_3_9_5_2_2_6_1_3_8_2_4_4_2_2_2_2_1_6_6_2_5_4_2_3_6_6_5_5_3_5_8_6_4_1_4_2_2_2_6_6_10_1_3_1_1_3_3_4_1_4_1_2_1_3_3_2_4_8_8_5_4_4_1_4_2_1_2_3_8_5_5_9_5_3_3_3_6_4_4_5_6_6_3_5_5_1_3_3_1_1_5_6_2_5_2_4_4_6_5_4_5_7_2_4_3_1_4_3_1_4_4_8_6_4_4_2_2_5_5_5_5_5_3_6_2_2_3_2_2_7_8_3_2_1_1_2_2_2_6_2_2_2_3_1_2_2_4_1_1_1_1_2_1_5_5_2_3_1_8_2_4_4_7_3_3_5_2_2_4_4_1_3_1_2_2_10_10_2_2_2_2_4_3_2_3_8_6_9_4_2_7_7_1_10_2_1_2_2_5_2_5_2_3_4_6_6_6_1_5_5_5_1_2_1_2_3_3_4_1_1_2_4_1_6_2_1_3_2_3_5_3_6_3_1_6_3_3_4_6_2_4_6_7_5_3_8_9_4_8_3_4_4_4_1_6_2_2_2_1_6_8_5_1_4_4_4_3_2_4_3_9_1_1_1_3_8_1_1_1_4_2_1_4_4_5_2_6_5_2_2_2_1_2_4_1_1_9_2_2_2_5_3_3_2_5_5_5_1_3_1_5_5_4_5_5_8_4_3_6_2_7_7_2_5_2_5_5_1_4_7_1_3_1_2_5_1_3_8_4_8_9_6_6_1_2_3_5_2_4_1_1_4_8_5_1_3_5_5_3_1_4_4_3_2_3_9_5_5_3_1_4</t>
+  </si>
+  <si>
+    <t>3_2_5_6_5_3_1_7_6_4_7_7_3_9_4_1_1_1_4_1_3_1_1_6_1_3_1_1_8_3_3_4_2_3_6_3_6_9_7_1_2_5_6_3_6_4_3_1_1_4_6_9_10_10_3_2_10_7_5_1_1_1_1_3_2_4_4_3_4_7_8_3_5_1_2_3_3_4_7_1_5_7_5_5_3_3_7_2_5_3_2_6_1_6_1_5_1_3_3_1_6_5_3_2_5_5_5_5_2_6_3_2_5_6_6_6_6_3_1_7_1_1_1_2_2_6_3_3_1_1_9_3_9_9_1_1_1_1_1_3_3_6_5_6_3_1_1_1_4_4_4_5_4_3_6_3_1_4_2_2_3_6_2_6_2_2_2_5_1_5_4_3_8_8_3_5_1_1_1_6_4_4_7_2_1_5_4_1_4_3_4_1_2_6_2_2_1_1_5_4_10_1_1_5_4_8_5_1_2_3_2_1_4_6_6_2_1_9_1_5_2_2_6_4_1_1_1_1_4_2_1_5_6_2_4_4_7_1_1_5_8_2_2_2_5_1_9_6_6_4_6_7_6_6_1_8_8_1_4_3_4_1_1_3_3_3_2_1_1_1_1_2_5_1_1_1_1_4_2_2_4_5_4_2_1_1_1_1_6_1_1_1_3_1_2_1_6_7_1_5_4_9_3_1_4_5_1_3_2_2_10_4_1_3_4_3_3_5_5_5_5_6_8_3_2_1_5_5_1_4_3_5_2_1_2_5_2_3_7_7_6_3_3_2_5_4_5_3_3_6_2_4_3_3_1_1_1_1_1_2_1_1_9_1_1_1_4_5_5_3_3_2_5_3_9_2_1_3_5_1_1_6_4_4_1_2_4_4_6_3_1_3_6_2_1_1_3_5_1_2_3_3_3_6_5_3_3_1_3_4_1_1_5_2_2_4_4_4_4_5_3_3_2_5_2_1_1_5_10_1_1_5_2_6_2_9_2_3_8_1_4_6_6_6_3_2_5_1_4_8_6_2_2_6_1_6_2_2_2_1_1_3_1_1_2_9_9_3_3_1_1_5_5_5_3_1_3_5_1_4_1_3_1_1_1_5_5_2_3_3_5_4_8_6_2_2_1_1_1_2</t>
   </si>
   <si>
     <t>6_3_3_2_6_6_1_8_4_4_7_5_1_2_9_6_2_8_2_1_1_4_3_5_3_6_8_9_6_4_4_1_6_5_8_3_7_6_1_2_9_3_2_5_8_6_6_4_7_5_4_4_4_3_2_7_1_5_6_6_2_2_8_4_4_2_1_3_6_8_5_4_2_7_3_8_9_4_3_7_1_4_9_2_6_5_3_4_4_3_7_8_3_3_9_9_5_3_6_4_6_1_1_1_8_4_4_8_8_6_7_3_2_2_4_8_5_5_3_7_2_1_9_1_4_9_9_3_6_9_5_5_1_1_4_1_1_2_2_1_3_3_8_1_4_8_6_3_3_1_4_4_1_3_9_6_8_2_5_6_1_2_6_2_3_9_1_4_5_8_5_1_5_7_3_2_7_9_5_5_5_7_7_3_6_7_7_2_1_1_1_6_2_2_2_6_5_3_1_1_1_5_6_3_3_3_5_4_6_6_3_5_2_1_8_3_1_1_7_3_9_8_6_9_9_4_6_4_9_3_7_1_1_8_5_5_1_3_3_4_6_5_5_1_8_5_1_3_3_5_2_3_1_4_1_7_5_8_1_5_6_2_5_6_8_8_8_9_5_8_8_4_2_4_2_2_2_3_1_5_3_9_5_5_5_7_4_9_9_1_8_6_1_1_4_7_3_2_2_9_9_3_6_6_3_6_4_2_2_4_2_9_6_7_5_3_1_8_9_2_8_2_1_3_9_5_6_9_5_9_4_2_4_4_3_9_1_1_7_7_1_4_6_6_3_7_7_8_7_4_6_4_5_7_8_4_4_3_2_2_4_5_6_1_3_1_1_5_6_1_1_1_6_3_4_2_7_4_1_7_5_6_2_7_1_1_4_8_4_2_4_5_4_3_8_2_2_5_6_4_7_9_6_4_2_4_4_4_4_4_5_3_1_1_4_9_2_3_2_5_6_3_2_2_8_3_5_2_9_1_1_2_8_3_6_3_9_1_4_1_2_8_3_5_5_5_6_9_2_6_5_1_1_8_5_4_2_2_9_6_5_5_2_4_1_9_9_9_1_1_1_6_7_7_2_1_4_7_8_6_8_9_8_4_4_3_5_5_5_4_2_9_4_1_1_2_8_2_3_9</t>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -346,31 +346,31 @@
     <t>10_7_1_6_2_1_4_6_10_5_3_4_8_10_5_8_14_4_4_5_3_1_14_4_2_8_9_3_1_2_2_2_11_4_7_4_2_8_4_2_3_7_2_14_4_1_3_11_5_4_14_7_5_3_10_2_14_2_2_8_10_1_7_7_5_4_6_5_7_9_10_2_1_3_2_6_1_11_7_1_2_1_2_2_10_5_3_8_6_14_3_10_5_7_6_10_4_1_5_2_2_2_4_7_6_11_7_10_4_5_3_5_5_7_1_5_8_4_3_3_3_2_1_3_8_1_4_14_4_7_6_10_3_6_6_10_2_5_4_2_8_9_3_2_7_10_3_11_7_7_6_3_1_7_1_7_2_2_5_9_5_6_5_4_1_4_3_6_2_14_4_2_4_14_3_5_7_1_3_4_10_2_3_3_3_6_8_4_1_4_5_1_6_1_10_6_10_5_2_6_8_2_5_2_3_1_4_3_9_3_8_6_5_8_4_3_3_14_7_2_3_5_2_1_1_3_6_9_10_5_4_10_4_3_4_8_7_1_7_8_4_10_6_2_7_5_14_6_11_6_14_4_3_8_2_4_6_7_3_7_6_7_1_4_5_9_6_5_1_7_7_9_10_6_7_1_7_2_3_9_8_10_2_4_2_14_6_8_4_3_10_5_2_5_4_7_5_8_7_4_10_7_9_3_9_8_6_1_4_1_8_3_4_3_6_10_4_5_8_1_5_1_4_2_10_7_11_4_10_2_4_2_5_1_4_5_14_5_4_5_3_6_1_3_2_2_5_1_1_5_3_7_8_2_2_8_9_6_1_2_9_7_7_7_5_6_1_9_5_3_2_4_6_8_9_7_4_8_1_2_3_9_8_5_1_5_9_3_9_1_8_10_4_7_2_2_10_4_1_3_4_2_7_14_5_4_5_3_9_8_6_10_6_1_14_5_9_3_2_2_4_3_1_2_5_5_6_4_4_8_3_4_4_11_7_7_7_7_6_8_10_4_8_2_1_3_1_11_3_3_9_10_6_1_4_2_14_6_4_5_5_11_5_6_4_9_2_7_6_5_1_2_3_10_6_11_7_2_6_7_4_2_7_4_3_1_14_6_8_6_8_5_4_14_2_2_10_5_8_6</t>
   </si>
   <si>
-    <t>4_3_3_1_1_3_2_2_4_4_4_9_2_3_4_8_7_7_8_3_2_7_4_8_3_2_3_7_9_6_6_5_5_1_1_4_3_7_6_2_2_4_1_1_7_5_9_3_2_1_5_9_2_5_3_4_7_2_6_7_8_1_5_9_7_7_7_9_1_1_6_5_1_1_1_1_9_4_2_2_3_3_3_1_7_1_1_2_2_4_5_7_6_1_3_6_1_7_9_2_2_8_6_2_7_1_3_3_7_5_4_1_8_9_3_3_2_2_2_4_8_3_1_1_1_2_2_2_3_7_2_8_6_1_7_2_2_2_3_7_9_2_2_5_1_3_3_4_5_9_9_3_4_1_2_2_9_2_4_8_8_9_6_2_4_4_2_6_2_1_4_4_2_4_1_8_9_1_1_5_4_6_5_2_2_2_5_7_7_5_8_4_1_3_2_7_7_1_5_3_7_1_2_2_6_5_1_5_3_3_3_4_4_2_6_7_1_3_1_6_2_4_5_1_2_6_8_1_8_2_5_5_8_5_2_1_1_1_1_6_6_8_7_2_4_5_4_7_6_2_9_8_6_6_5_8_4_6_2_2_4_7_9_3_4_4_4_2_7_1_1_7_3_7_2_8_8_8_4_4_1_5_4_3_4_9_9_5_5_6_2_6_6_3_5_5_3_8_8_6_7_7_5_9_3_2_4_3_3_1_3_1_2_9_3_9_9_1_4_2_2_2_1_7_9_5_2_1_2_1_2_1_6_3_3_3_4_5_3_1_3_5_4_4_3_1_9_2_3_3_1_2_2_4_4_1_1_1_9_6_1_1_2_8_2_3_2_4_2_7_3_3_1_3_3_3_2_4_8_4_5_6_2_3_4_2_1_1_6_8_2_5_1_1_3_9_3_2_2_2_5_1_6_9_2_8_6_3_7_6_1_8_1_7_4_9_8_1_8_3_7_6_6_6_1_2_2_2_6_2_8_6_6_6_8_4_6_2_3_7_5_9_6_3_3_4_1_8_4_1_6_2_2_5_5_1_4_9_1_1_1_2_3_4_2_4_2_1_1_5_1_7_1_2_3_5_4_2_8_5_4_6_7_7_6_4_4_2_3_4_3_8_8_4_1_3_1_6_8_3</t>
+    <t>2_6_7_7_2_4_2_4_7_2_2_2_6_5_4_2_3_2_3_5_6_6_6_7_1_4_4_8_6_9_7_7_2_7_6_1_1_1_5_1_2_5_4_8_1_2_3_3_8_4_2_5_8_9_9_9_2_8_1_1_6_6_2_6_6_1_1_1_5_5_2_1_6_4_8_2_2_3_6_8_1_9_8_7_8_2_1_2_2_6_2_2_8_8_6_1_3_1_3_3_3_2_4_4_2_5_1_2_2_1_2_8_2_7_8_1_5_1_1_7_6_3_3_6_8_2_7_2_7_1_1_4_7_1_1_1_2_5_6_6_5_2_1_5_5_9_1_3_9_9_6_2_3_5_5_8_1_8_8_8_4_1_6_3_5_8_8_7_8_1_7_3_3_1_2_1_4_4_4_2_2_6_1_9_8_9_3_1_8_6_2_9_3_7_7_1_1_5_4_9_2_6_2_2_3_2_2_1_8_8_4_1_9_1_2_2_5_6_6_8_4_1_1_4_7_6_6_4_6_6_2_1_4_3_2_7_4_4_1_1_2_1_2_4_8_8_8_6_3_2_5_7_6_4_4_8_1_6_6_4_1_1_4_5_8_4_6_7_6_7_2_2_5_8_2_8_2_1_1_5_1_5_7_5_3_5_5_5_5_4_3_3_3_2_1_2_7_5_2_2_2_7_4_4_6_9_9_7_2_2_2_6_3_7_3_2_2_2_4_3_4_8_2_5_4_9_9_9_5_4_3_1_1_1_4_2_2_4_4_5_5_5_9_9_1_7_2_1_5_4_4_1_6_4_4_7_2_2_4_6_1_4_6_4_4_4_3_9_1_1_2_1_1_1_2_2_5_4_4_4_3_3_6_4_5_4_2_1_2_3_6_6_7_7_5_3_3_5_2_7_7_8_2_6_7_7_1_5_6_6_7_8_3_4_1_7_7_1_5_2_4_5_3_1_1_9_5_2_8_5_7_8_9_2_5_8_8_9_2_1_6_6_4_1_8_8_2_2_7_9_3_4_4_2_6_6_3_8_2_1_3_4_9_1_1_8_2_3_3_6_8_2_3_9_5_6_4_4_6_5_2_1_2_4_3_4_4_4_3_1_4_2_4_6_2_2_3_2_1_5</t>
   </si>
   <si>
     <t>6_9_4_3_1_8_2_1_2_2_1_8_9_4_4_1_4_3_4_2_8_3_1_6_2_7_1_2_8_5_5_3_2_3_6_2_1_6_6_2_3_5_1_1_3_8_6_8_3_5_7_7_2_3_7_2_4_8_9_4_6_2_2_3_7_4_1_4_6_1_9_5_4_1_5_8_5_4_4_5_8_2_1_1_5_4_2_1_5_6_2_4_2_9_1_4_2_4_2_2_3_4_1_2_4_1_7_9_1_4_7_4_2_6_3_2_5_6_9_8_4_8_2_3_7_1_8_2_3_3_7_2_6_7_4_5_3_1_5_4_3_8_6_6_1_4_6_2_9_5_7_9_5_6_3_3_1_3_6_5_2_4_2_6_4_6_8_4_1_6_1_5_2_2_5_5_4_9_6_3_4_3_2_1_7_8_2_6_7_6_6_4_4_2_3_4_1_4_8_7_5_1_7_5_2_4_1_7_7_5_4_3_4_5_3_5_4_1_8_4_6_2_1_8_6_7_1_4_6_2_4_4_1_4_4_5_1_4_6_3_8_4_3_7_6_2_1_8_4_3_5_3_1_9_4_1_3_6_6_5_8_6_1_5_3_3_8_2_4_1_5_1_9_1_5_3_7_4_8_5_1_1_7_5_1_6_5_8_4_6_2_2_1_7_3_5_5_5_3_4_5_5_6_7_6_7_4_6_1_1_3_6_9_4_4_9_5_6_7_9_4_4_4_7_8_6_9_2_2_2_3_5_4_6_8_2_8_7_4_4_5_3_4_9_8_7_4_9_2_7_2_8_7_3_1_5_9_1_4_9_1_4_9_2_4_8_2_1_1_9_9_4_5_3_6_8_1_9_1_1_8_4_6_4_1_3_7_1_4_8_9_6_9_8_7_7_1_8_9_9_6_6_7_8_1_7_5_1_4_2_8_7_2_9_1_2_6_2_4_8_5_8_3_1_7_1_5_8_5_3_1_6_3_5_7_3_4_1_7_4_2_1_5_2_7_8_6_9_4_9_3_6_1_2_5_2_8_4_1_3_4_2_1_8_4_2_5_7_1_2_7_7_2_1_4_8_4_7_5_9_5_9_8_9_6_2_8_2_8_3_3_4_9_7_2_6_7_2_4_8</t>
   </si>
   <si>
-    <t>4_1_6_3_6_2_1_1_2_2_9_8_1_2_6_6_3_7_1_8_6_3_3_9_6_1_4_4_2_6_3_5_5_5_7_1_8_7_2_3_7_5_1_6_1_9_5_7_3_9_2_2_6_5_3_8_5_6_9_3_5_2_2_2_9_1_1_6_4_4_5_8_5_6_9_9_1_3_4_4_1_1_3_6_2_2_5_7_6_8_4_4_1_4_2_2_2_2_3_6_1_2_1_6_4_4_9_6_3_2_5_3_5_4_7_7_2_2_4_8_6_5_9_9_2_2_2_7_7_4_4_1_5_7_2_3_2_3_2_3_3_4_5_7_6_1_8_5_5_5_1_2_7_8_8_8_9_3_3_5_2_3_4_2_8_2_2_1_9_2_2_1_1_3_6_3_8_8_6_1_2_2_1_9_1_2_2_1_2_6_3_6_1_4_6_6_8_7_7_5_3_4_3_9_6_6_9_1_1_6_9_4_4_4_6_6_8_6_2_4_4_5_2_5_5_1_9_4_2_1_5_2_9_3_9_2_1_1_6_8_1_1_5_4_5_2_2_4_2_1_2_2_7_6_1_3_3_3_3_9_8_3_1_9_4_8_7_5_8_4_2_7_7_5_3_1_9_9_2_4_4_2_2_2_8_1_2_8_3_3_1_4_6_7_1_3_3_1_4_6_3_3_3_1_6_5_8_7_4_7_4_4_6_5_5_2_1_4_7_3_2_6_1_3_7_8_6_7_1_7_7_1_2_2_9_5_4_4_8_3_4_5_5_2_2_7_6_6_7_7_5_6_2_1_1_3_2_2_2_6_4_6_1_2_8_8_6_4_2_2_1_5_3_2_3_2_7_9_9_6_6_3_5_4_4_1_1_3_1_7_5_4_4_7_9_1_7_2_5_1_3_9_9_9_4_6_5_4_4_4_6_6_1_7_4_4_7_2_5_1_7_9_9_2_6_4_3_1_6_6_1_1_8_1_7_6_4_4_1_4_8_4_8_5_5_2_1_4_8_2_8_4_7_7_8_4_4_2_3_1_3_4_3_1_1_1_8_7_7_4_1_7_1_1_3_4_4_4_4_2_8_8_3_4_1_8_7_2_7_9_3_4_6_5_5_5_5_5_5_1</t>
+    <t>2_6_5_4_1_9_4_9_1_6_6_4_4_5_4_1_1_2_6_4_4_4_6_4_2_5_5_5_4_3_4_1_1_1_2_3_2_5_4_1_8_6_1_1_4_1_1_5_1_7_9_2_2_9_3_1_2_6_5_7_8_1_5_5_1_6_2_3_2_4_4_2_4_2_2_4_1_7_7_8_6_6_6_3_1_1_1_4_2_2_1_4_1_3_4_9_6_2_5_3_7_5_1_6_2_8_6_1_2_1_9_6_5_5_3_6_5_6_4_1_1_2_2_2_8_2_5_2_7_5_2_5_6_4_5_6_2_9_2_1_7_5_3_7_5_6_1_3_7_5_9_8_6_8_6_3_2_2_4_8_2_2_3_5_6_6_3_8_1_4_4_2_5_3_1_5_8_1_2_2_5_4_2_9_7_7_1_5_6_1_6_3_2_4_4_1_5_2_1_8_1_2_8_1_4_1_2_2_6_1_6_3_8_2_2_1_2_1_1_3_5_1_7_2_7_1_1_6_8_8_8_5_1_1_2_2_3_7_4_3_3_1_1_5_7_6_5_1_6_2_2_1_3_2_5_9_8_4_2_5_3_1_3_2_2_3_3_2_3_4_4_3_3_9_7_3_9_9_4_7_1_5_4_2_1_1_1_1_6_1_6_4_2_2_3_1_6_5_3_9_3_7_6_7_5_2_5_5_5_4_4_1_6_1_9_3_2_1_2_8_7_7_7_1_6_2_2_8_5_3_9_9_3_9_9_9_3_3_4_6_4_1_4_2_5_5_8_1_5_5_6_7_3_3_1_4_2_1_1_4_5_5_3_3_3_5_8_6_8_1_1_4_1_7_2_7_7_4_2_2_3_6_6_4_9_1_1_1_8_9_1_1_4_7_6_6_4_2_1_6_1_3_3_4_5_7_1_2_3_3_3_2_3_1_7_8_2_2_6_3_6_3_3_4_1_2_2_2_2_7_6_2_5_2_6_2_9_9_3_1_8_3_2_8_2_2_1_4_6_1_1_1_1_8_4_6_1_4_6_4_4_6_6_3_2_2_6_3_7_1_7_1_2_4_1_1_3_1_2_6_6_1_1_5_8_2_6_6_1_5_1_1_3_5_2_1_4_5_4_5</t>
   </si>
   <si>
     <t>2_7_1_9_6_1_7_1_9_8_7_3_3_9_7_3_2_9_1_6_2_8_3_8_1_3_6_8_4_3_1_4_1_6_2_4_7_3_2_6_4_8_1_1_2_4_6_2_2_6_2_6_5_5_1_1_2_2_1_8_6_5_7_7_2_1_6_3_1_3_6_2_1_7_5_1_9_9_2_7_2_6_2_2_4_6_4_8_5_5_5_5_1_6_4_2_1_8_1_7_4_8_6_6_4_1_1_2_3_1_6_4_3_5_5_1_4_9_4_6_5_1_9_1_8_3_3_3_7_3_2_1_4_9_3_1_1_7_1_4_5_2_4_3_2_7_4_2_2_5_3_3_1_2_6_9_6_5_5_1_1_7_7_3_3_6_6_8_3_7_2_1_8_5_2_3_1_3_8_2_1_9_2_1_1_2_7_2_3_4_4_2_6_6_1_2_2_2_9_5_6_8_3_2_1_4_1_5_7_8_8_6_4_5_2_6_3_7_8_2_6_5_1_4_3_1_3_7_4_3_1_3_3_6_3_2_5_2_9_1_4_7_5_5_4_4_8_2_3_3_1_7_9_6_2_4_6_5_7_9_5_8_1_2_5_2_8_2_5_1_4_3_7_1_2_2_1_1_8_9_6_2_1_5_2_4_3_2_8_3_2_9_1_6_4_2_8_2_2_4_6_1_1_3_9_1_3_3_2_3_8_5_4_2_3_8_7_3_6_5_6_2_9_5_9_7_9_3_6_8_6_6_1_5_6_6_7_4_1_7_3_6_5_5_5_8_1_8_8_1_2_1_3_9_5_7_4_6_1_2_3_6_4_1_8_3_8_2_4_5_3_9_1_3_2_5_5_3_6_4_2_2_1_9_7_7_5_3_4_2_5_4_1_7_6_7_5_2_3_4_3_4_2_6_5_9_6_2_5_8_2_4_1_1_9_3_1_2_5_8_8_4_2_7_4_4_4_3_1_4_7_1_8_4_7_7_6_7_3_6_8_5_1_9_5_2_2_1_8_8_8_3_4_7_6_6_7_1_6_1_4_8_1_3_5_6_2_7_8_4_1_1_1_1_5_5_4_6_2_5_2_6_5_8_4_4_9_2_6_1_1_7_1_1_2_2_9_3_1_5</t>
   </si>
   <si>
-    <t>8_1_4_6_6_8_3_9_9_9_6_9_8_3_4_6_4_1_1_6_4_3_8_8_9_4_1_3_3_2_6_6_5_9_9_1_2_4_4_2_8_9_1_4_6_4_1_3_3_4_4_4_4_1_3_8_9_1_6_1_6_2_8_3_3_4_3_8_5_9_4_4_2_2_1_4_4_5_2_8_1_4_6_4_6_5_2_2_1_4_5_9_9_3_6_4_7_4_6_6_2_2_8_8_8_2_3_3_4_5_6_2_2_1_1_8_7_3_7_5_8_1_9_6_6_4_5_6_2_1_8_4_3_1_9_6_3_3_6_6_1_7_7_7_1_7_6_4_6_2_9_1_6_7_2_4_7_3_3_7_7_7_6_2_2_1_9_6_1_8_1_1_2_6_2_3_1_1_1_1_3_4_1_3_2_2_4_1_4_7_1_5_7_3_3_8_1_4_4_4_3_7_6_6_7_3_4_5_9_6_4_9_4_4_8_1_3_7_8_4_6_3_1_1_8_2_1_1_6_8_2_7_7_6_2_3_2_5_6_6_6_2_1_5_5_9_2_3_5_5_2_6_3_4_3_6_8_9_3_5_5_9_9_1_5_5_9_2_5_3_1_3_2_5_4_7_6_6_1_1_8_3_3_9_5_4_7_2_1_6_8_8_6_6_6_6_3_1_6_4_1_9_5_2_3_2_1_6_1_2_4_7_9_9_4_4_4_8_3_1_5_7_4_4_8_8_1_1_3_3_5_6_1_1_1_3_6_4_6_3_2_4_4_3_4_2_8_1_3_3_1_3_9_4_2_6_3_3_1_5_6_2_7_5_7_8_1_7_4_3_4_2_3_1_2_2_2_5_5_5_2_1_6_5_5_1_1_9_5_6_2_6_6_4_1_1_2_5_2_9_3_2_1_1_1_7_2_3_3_3_3_2_2_7_8_8_4_4_1_3_1_3_3_4_6_4_5_2_3_4_6_8_7_4_5_4_5_6_5_5_7_1_1_1_3_1_9_5_6_6_2_2_9_2_5_4_8_5_5_7_2_4_2_5_2_7_6_1_7_5_5_6_4_6_3_2_3_2_2_7_2_2_3_2_8_4_7_1_1_3_9_9_3_4_4_3_3_5_2_2</t>
+    <t>2_5_3_7_6_5_8_4_6_3_5_1_7_4_8_4_3_1_2_2_2_4_8_8_1_8_8_7_7_3_1_1_8_1_3_4_1_8_2_7_6_3_3_2_7_5_3_3_7_4_1_5_5_4_3_6_6_7_1_6_3_3_3_2_6_2_6_1_1_2_1_4_5_5_1_9_2_1_2_2_2_2_2_1_6_1_4_5_3_3_9_3_2_1_3_6_5_2_7_2_7_2_2_3_9_6_3_5_8_1_6_7_4_2_5_7_4_1_1_9_3_4_4_5_4_1_6_1_2_5_4_4_2_1_8_7_4_1_1_4_7_4_1_1_4_2_5_8_6_8_6_2_4_5_1_9_8_8_9_1_2_1_6_1_2_7_4_1_7_5_7_8_2_7_6_2_8_7_3_4_8_2_7_4_8_1_1_2_3_2_1_4_4_5_1_2_9_1_4_3_1_6_4_4_3_4_6_7_4_5_2_4_7_4_4_8_2_4_8_7_1_2_4_5_3_3_2_5_2_8_8_4_9_9_3_2_2_4_4_2_2_7_7_6_6_3_9_7_4_1_1_2_1_4_6_6_6_3_3_3_3_8_1_1_1_5_9_4_4_6_4_8_9_1_2_2_2_3_9_3_1_5_4_1_1_7_2_3_3_1_7_1_2_1_2_2_1_3_3_4_1_2_3_1_4_1_2_9_5_3_3_1_1_2_5_6_3_4_1_5_3_3_8_1_8_6_9_7_1_5_5_8_4_6_7_9_9_9_3_2_3_3_1_4_6_7_8_6_2_3_1_2_2_5_1_9_2_6_4_2_2_3_7_3_2_6_8_1_5_5_6_2_6_3_4_4_1_1_1_7_7_6_3_5_8_6_9_6_2_4_2_6_3_5_8_4_4_7_5_6_8_2_3_3_9_9_2_2_9_9_4_1_5_5_5_8_1_8_9_2_2_2_3_8_8_1_6_1_2_1_9_9_6_3_5_7_7_1_1_4_6_6_3_2_1_4_5_8_3_9_5_9_4_2_1_4_4_7_2_3_8_7_2_5_2_2_6_4_8_8_3_3_3_7_4_7_5_5_5_1_6_2_5_4_8_1_1_1_3_3_6_2_4_6_6_6_8_4_8_4</t>
   </si>
   <si>
     <t>8_1_2_9_8_5_4_6_8_5_3_2_9_4_1_1_2_3_4_8_6_3_2_5_9_1_1_4_3_4_4_5_3_4_1_9_3_9_5_5_8_5_5_6_7_1_5_1_7_7_3_3_3_7_7_2_4_2_8_1_4_5_6_8_4_1_3_1_7_2_6_7_8_3_1_4_4_5_8_1_7_9_4_7_9_2_3_3_7_7_1_8_3_2_8_8_8_3_2_8_1_5_6_3_8_8_4_1_3_1_5_6_1_1_3_2_6_3_4_3_4_2_2_4_7_5_4_7_3_1_2_8_5_7_1_7_1_6_5_3_2_6_7_4_9_4_8_7_7_4_9_1_4_1_1_5_4_3_7_7_1_2_2_8_6_7_4_3_7_6_4_2_3_4_7_3_3_1_4_9_5_5_3_1_1_2_1_6_7_8_5_9_8_5_2_5_3_6_8_6_4_5_7_6_5_8_7_3_7_1_2_3_6_9_2_8_6_8_5_8_2_7_2_5_3_1_8_8_4_6_6_3_7_3_1_2_6_2_1_9_2_3_2_1_7_1_4_9_5_2_7_1_6_3_5_9_2_3_6_2_4_7_8_3_2_9_4_8_1_2_9_7_1_6_6_8_5_1_3_4_2_3_3_2_7_3_6_2_1_8_1_7_3_2_9_2_7_7_7_3_2_4_8_8_2_3_4_2_4_2_6_5_2_8_8_1_8_3_7_5_5_3_5_1_4_3_8_2_2_2_5_3_2_4_4_2_7_3_7_7_6_3_7_6_5_9_1_1_8_3_6_8_3_7_2_4_6_8_2_4_6_6_4_9_1_1_6_5_8_8_5_4_1_6_2_1_1_2_3_1_4_6_4_5_7_1_6_6_7_6_3_2_1_1_6_5_3_8_2_3_1_5_2_4_1_2_2_9_1_8_3_3_9_6_9_8_6_2_3_4_8_4_3_1_3_5_7_5_2_6_7_2_3_1_7_4_4_3_6_7_3_2_8_8_2_1_5_3_2_1_9_7_2_6_4_4_8_1_2_1_9_2_4_2_1_1_4_7_4_1_3_5_9_6_4_8_3_4_3_2_2_7_3_9_3_5_7_1_1_2_6_6_1_5_9_7_8_5_1_7</t>
   </si>
   <si>
-    <t>2_1_3_2_2_2_2_9_1_8_1_7_1_6_4_9_8_4_6_2_5_5_5_3_1_8_2_5_1_6_4_7_8_3_7_8_6_1_5_5_5_4_2_3_4_9_2_8_4_3_5_7_2_2_2_8_5_9_9_5_8_3_3_7_2_8_6_6_1_6_1_1_4_6_7_6_4_1_4_4_1_6_7_3_3_4_1_2_3_4_5_8_1_2_2_3_6_8_7_4_1_8_1_7_8_7_1_8_8_6_3_4_2_5_6_6_1_1_1_6_7_7_1_3_2_1_1_1_1_8_2_4_1_3_1_7_5_4_6_1_2_2_5_7_8_1_8_2_4_4_7_7_2_3_8_2_9_8_7_7_7_9_5_5_7_7_7_1_5_2_2_3_5_5_1_1_5_5_5_2_9_9_7_3_6_6_5_2_4_4_9_2_1_3_2_1_4_2_6_5_4_8_4_6_9_7_7_8_8_4_4_8_3_6_4_6_2_2_7_6_7_3_5_1_1_1_4_3_7_5_3_3_1_3_1_1_1_9_9_3_1_4_4_7_7_6_6_7_1_3_2_3_3_3_6_2_6_9_4_4_8_4_6_7_9_7_1_6_6_4_4_1_3_6_6_6_6_2_1_3_6_2_5_4_4_9_7_6_4_3_3_7_6_6_1_3_8_1_6_3_7_1_4_2_3_4_9_5_3_8_1_5_2_6_4_2_3_2_4_3_6_6_5_4_4_9_5_1_9_9_7_7_4_3_7_6_6_1_6_6_1_3_3_2_1_8_3_9_3_3_7_4_6_5_2_6_9_4_4_3_6_5_3_4_2_3_8_3_4_1_4_6_1_8_3_4_5_3_8_1_5_5_4_3_3_1_8_2_8_3_2_1_4_3_3_4_1_8_3_2_2_3_7_8_1_1_8_8_4_7_2_1_5_8_5_7_1_2_4_5_5_6_3_5_2_2_2_3_3_6_3_2_4_1_6_6_6_6_2_3_5_1_6_6_8_1_3_1_3_5_3_5_1_1_8_2_6_6_3_7_7_5_2_3_7_5_4_9_6_9_9_8_9_1_1_6_3_8_8_4_2_6_7_3_2_2_7_8_3_1_2_1_2_7_1_7_3_7_5_4</t>
+    <t>4_6_2_5_3_3_9_2_9_9_7_2_4_1_4_1_8_6_6_4_1_5_1_1_9_5_6_6_2_3_7_6_9_1_9_2_2_9_2_7_7_4_6_6_6_4_6_7_1_8_4_1_3_6_9_5_6_2_2_3_1_2_2_7_3_2_3_3_3_1_5_3_6_8_9_9_6_6_1_1_3_2_3_5_3_1_9_3_3_1_7_2_2_4_1_8_2_5_7_2_6_2_2_3_7_3_6_6_2_1_1_3_4_7_5_6_1_5_7_1_9_1_1_9_4_4_7_4_1_9_2_1_1_6_2_1_5_5_7_7_1_7_1_4_1_6_3_2_1_8_8_6_2_3_4_7_1_1_8_9_1_2_7_6_8_2_5_2_3_1_4_3_2_1_9_2_2_6_3_2_1_6_9_3_3_1_4_5_6_3_3_1_6_1_3_1_3_3_2_7_1_5_1_1_1_1_6_9_5_8_5_3_2_3_6_1_3_1_6_6_8_5_6_1_8_2_2_3_5_2_6_4_2_2_6_7_7_1_6_7_3_1_3_3_5_1_1_1_3_3_5_5_5_5_3_2_6_1_8_4_7_1_1_3_3_5_6_9_4_6_1_6_9_8_7_6_1_2_1_4_5_7_2_6_3_6_6_5_8_1_4_7_5_1_7_7_6_1_6_7_4_1_1_3_2_2_2_3_5_6_6_8_8_2_6_9_4_7_2_5_2_1_1_3_2_2_1_4_3_5_1_3_3_5_4_1_3_2_4_3_1_2_4_2_3_7_7_6_5_5_2_5_8_2_2_8_3_1_3_3_1_6_8_4_8_1_7_8_4_4_2_2_2_1_3_1_8_6_8_1_8_4_4_3_5_4_2_1_2_2_8_2_9_8_8_8_9_6_6_7_4_1_9_9_3_1_4_8_2_8_1_6_4_2_7_2_2_5_5_6_1_5_1_1_3_2_4_4_8_3_4_4_3_7_5_5_3_1_1_2_3_1_6_6_6_2_3_3_8_3_2_4_2_8_2_1_4_4_2_3_2_5_6_2_5_2_4_6_3_1_8_7_5_5_6_6_5_4_1_1_3_2_6_7_8_6_4_2_3_5_1_4_7_3_8_4_4_4_1_6</t>
   </si>
   <si>
     <t>6_7_6_1_8_8_2_8_6_8_8_8_5_8_6_1_5_2_5_3_4_4_9_5_8_5_1_1_8_4_7_2_2_9_5_1_4_2_5_5_9_8_4_6_6_5_6_9_7_9_7_2_8_6_4_2_6_7_1_4_6_8_2_2_7_3_2_1_4_3_1_6_2_4_5_7_1_9_7_6_2_3_6_1_1_6_3_3_7_1_7_3_2_4_9_4_2_5_7_4_6_7_4_1_2_6_6_6_2_2_1_4_1_2_3_8_4_3_2_9_2_1_3_6_8_1_4_1_9_1_6_5_7_8_3_9_6_1_9_8_3_7_7_7_5_9_5_2_9_9_5_2_2_8_5_2_8_8_1_6_8_6_1_7_2_1_1_5_8_1_8_2_4_3_4_8_4_2_7_5_3_4_9_1_6_4_1_4_7_1_4_4_8_8_4_1_7_5_5_8_6_4_5_9_7_2_4_7_1_4_2_1_4_4_6_1_2_4_6_2_6_4_7_3_7_9_3_2_4_5_1_2_5_2_8_1_7_1_7_2_7_1_8_4_6_6_4_1_9_4_7_1_2_5_1_5_3_2_7_2_8_1_1_1_3_9_4_6_2_3_3_4_8_2_8_6_7_8_8_3_5_2_8_5_9_4_2_6_9_3_2_3_1_5_7_7_5_9_3_2_1_3_4_8_6_5_2_3_7_8_7_7_3_4_1_1_6_5_6_8_7_9_9_3_7_5_6_1_1_9_4_2_3_5_4_4_1_2_2_3_2_3_2_1_2_5_4_5_3_5_7_4_3_7_2_7_7_1_8_1_4_1_5_7_1_1_5_4_4_9_7_6_2_1_4_5_8_2_4_2_2_6_2_1_3_2_2_5_5_1_5_2_5_4_4_9_1_9_9_4_4_1_4_3_2_1_7_2_4_1_7_4_6_7_1_7_3_5_2_2_4_4_4_3_4_6_8_4_1_2_2_3_8_2_4_2_2_4_8_2_2_4_7_3_4_1_4_6_6_3_2_9_9_5_5_8_2_1_1_7_3_5_3_5_5_2_1_7_8_7_2_2_8_1_1_2_2_2_3_8_8_2_2_3_4_8_6_5_1_2_4_1_8_3_6_3_1_4_6_7</t>
   </si>
   <si>
-    <t>6_4_9_5_6_1_1_1_7_1_2_3_2_1_4_4_1_6_6_8_5_6_5_1_5_6_3_3_4_9_6_2_4_7_7_3_3_7_3_4_2_5_7_5_6_8_4_2_3_3_2_3_9_4_2_2_8_4_4_8_7_5_3_8_5_4_1_1_5_2_8_3_1_4_1_1_9_1_9_3_4_4_8_6_1_6_9_7_5_9_9_6_6_2_3_1_2_2_6_8_3_2_1_4_5_5_5_2_2_1_1_4_5_7_1_2_5_5_5_6_3_5_3_3_1_1_5_9_3_3_7_7_3_3_4_3_3_3_3_9_6_4_3_1_1_1_2_7_7_6_4_5_3_5_2_1_2_8_7_7_7_1_9_3_3_1_5_2_8_8_8_5_3_6_6_7_2_6_6_4_4_4_2_8_3_3_6_2_8_4_1_6_6_4_2_4_7_8_6_6_2_8_3_7_7_3_1_1_5_2_6_6_4_4_6_2_8_7_6_1_2_7_5_2_8_4_4_4_7_9_1_4_8_1_5_3_1_2_4_1_2_2_8_8_8_6_6_1_6_2_1_9_9_1_2_2_9_5_3_9_4_4_4_8_8_3_4_9_1_3_1_2_4_5_4_2_2_4_3_9_7_2_5_7_7_1_3_3_3_3_4_9_4_4_5_2_6_5_9_3_1_1_5_1_6_5_8_9_7_3_8_4_1_6_6_9_7_1_1_5_9_5_2_2_5_9_3_1_4_2_6_3_8_1_4_4_2_2_2_3_2_9_1_6_5_5_5_7_3_6_8_8_5_5_3_3_1_1_3_3_3_1_5_4_3_9_6_5_5_3_4_1_2_3_6_3_7_3_1_1_6_9_1_2_4_9_8_8_7_4_6_4_1_4_5_2_7_7_6_6_8_3_9_7_5_4_6_6_4_9_1_8_4_6_5_4_1_7_4_5_6_1_2_1_3_1_2_1_1_4_1_4_3_6_6_1_2_6_4_6_4_9_9_7_9_2_5_4_4_1_7_7_7_9_3_1_4_2_3_1_1_7_2_8_7_7_3_4_1_1_3_8_3_8_8_8_3_4_4_5_3_6_6_5_7_1_1_9_2_1_1_5_2_2_3_9_2_1_8_3</t>
+    <t>8_1_8_2_4_6_4_8_1_1_6_7_9_1_7_3_6_2_2_7_8_8_1_1_1_2_7_5_6_2_1_8_8_6_2_9_3_6_8_2_2_3_6_1_8_4_4_6_6_2_2_8_4_3_3_2_7_2_6_5_3_5_1_7_4_1_3_2_3_5_1_2_2_3_7_5_2_7_9_6_1_2_1_8_4_5_3_4_1_1_6_6_9_7_5_5_6_8_1_1_1_7_2_4_4_4_2_8_2_8_8_6_7_5_4_4_3_1_7_7_2_1_1_5_4_6_7_3_2_1_1_1_5_4_1_5_1_2_2_2_8_3_8_6_1_4_4_4_1_4_4_6_7_1_6_2_3_8_5_1_1_1_5_5_5_1_1_2_5_6_2_1_1_5_8_8_8_2_2_2_1_9_1_2_2_4_4_4_1_2_1_2_2_4_3_3_4_3_3_2_3_3_1_1_1_7_3_3_6_6_4_3_3_6_5_4_4_4_3_2_6_7_3_6_7_7_7_8_1_1_4_5_4_1_1_4_8_9_1_4_1_4_5_7_7_3_3_4_5_1_4_1_9_9_5_5_6_8_3_4_7_2_8_2_4_3_1_4_6_8_8_6_8_9_2_8_8_3_1_3_6_4_3_1_3_5_9_4_8_2_2_9_1_4_1_7_3_2_2_5_5_5_2_1_2_9_1_5_3_4_4_7_9_2_2_5_2_4_2_2_4_6_9_2_8_6_1_3_3_9_8_6_2_6_6_8_4_5_2_9_1_2_9_3_1_2_2_6_6_1_7_7_7_8_6_2_5_7_1_1_1_1_3_3_8_8_1_1_6_6_6_5_5_2_7_8_7_3_2_6_9_2_8_8_2_1_2_3_1_6_6_5_3_6_6_6_3_1_3_1_5_5_8_2_9_9_4_2_4_4_4_4_6_9_1_4_1_3_6_2_3_1_1_3_2_2_2_7_7_5_5_5_3_2_1_2_2_9_5_2_4_4_8_2_3_4_2_5_5_6_1_2_9_7_8_5_5_7_7_3_1_5_8_3_7_1_8_1_3_9_1_3_8_6_6_6_1_4_2_7_2_9_3_3_7_6_3_6_7_5_5_7_2_3_8_1_2_5_2_9</t>
   </si>
   <si>
     <t>4_7_8_5_7_7_6_4_3_9_3_1_4_4_5_5_5_7_1_6_3_1_3_5_2_1_1_9_2_9_6_1_8_3_4_5_4_2_1_6_4_2_8_7_4_8_6_5_9_1_2_8_8_9_4_6_6_1_6_7_8_1_5_8_6_4_8_9_3_1_4_4_1_5_5_8_5_4_6_2_8_1_9_3_7_9_2_5_5_7_1_2_9_8_1_3_4_7_8_4_9_1_1_2_5_4_6_5_7_2_7_7_6_5_5_5_1_4_2_1_9_3_4_3_3_3_4_1_5_3_4_6_5_4_6_9_6_1_2_1_8_1_2_4_9_2_5_8_2_5_2_1_5_7_1_1_2_2_6_2_9_3_3_6_6_6_2_5_8_1_6_2_4_2_6_8_9_4_7_3_4_5_7_4_2_1_2_6_6_1_6_2_4_7_6_2_1_1_8_1_7_8_8_9_1_7_9_5_4_3_3_5_2_2_7_7_6_1_3_8_9_1_9_3_3_4_2_5_1_5_2_7_3_6_2_4_2_2_9_1_5_7_2_3_3_9_3_5_3_1_6_2_9_6_3_3_1_3_5_6_3_4_2_4_6_1_1_7_3_4_4_4_3_4_7_3_6_8_3_2_4_1_2_1_4_8_5_5_4_4_8_8_1_4_5_4_9_7_1_8_9_3_5_2_4_1_4_7_4_9_1_1_9_3_2_5_2_2_2_4_5_6_5_2_6_9_6_2_8_4_2_7_7_6_3_3_8_7_6_2_4_7_1_1_9_6_2_8_2_8_4_9_5_4_1_3_1_5_7_9_7_8_1_1_2_4_6_5_8_2_2_2_3_2_4_2_2_3_6_1_7_5_3_7_4_1_1_4_7_4_1_2_9_6_2_4_1_8_2_6_4_6_3_1_4_2_3_8_2_4_3_4_5_9_5_5_8_1_3_1_7_3_1_7_7_3_5_1_3_8_7_8_2_2_5_3_3_4_8_6_1_6_8_4_1_8_2_4_5_7_1_6_4_5_6_5_4_2_6_2_7_1_1_5_2_1_7_6_2_3_3_3_8_1_4_6_2_9_3_2_2_6_7_1_6_1_3_9_2_5_6_2_3_2_1_8_4_5_3_9</t>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="173">
   <si>
     <t>id</t>
   </si>
@@ -316,7 +316,7 @@
     <t>1_7_7_7_1_9_9_9_9_9_1_5_1_7_1_11_11_1_7_1_9_9_9_9_1_11_11_11_11_11_11_1_11_11_11_1_5_5_5_5_5_5_5_5_5_1_3_3_1_5_1_11_11_1_3_3_3_1_5_5_5_5_1_11_1_3_1_3_1_3_3_1_9_9_9_9_9_9_9_1_9_9_9_1_9_1_11_1_7_7_7_7_7_1_9_1_9_9_9_9_1_11_11_11_1_11_11_1_11_1_11_11_11_1_11_11_11_11_1_11_11_11_11_1_11_1_3_3_3_3_1_9_9_1_5_1_7_7_7_7_7_7_7_7_7_7_7_7_7_1_5_5_5_1_7_7_7_7_7_7_7_7_1_7_7_7_7_7_7_7_1_11_11_1_9_9_9_9_9_9_1_3_3_1_11_11_11_11_11_11_1_5_5_1_11_11_11_11_1_9_1_7_7_1_3_3_3_3_3_3_3_1_5_5_1_5_5_1_7_1_5_5_5_5_5_1_3_3_3_1_7_7_7_7_7_1_11_11_11_11_1_7_7_7_7_7_1_3_3_3_3_3_3_1_9_1_11_11_11_11_1_5_1_3_3_3_1_3_1_5_5_1_3_3_1_11_11_11_1_9_9_9_9_9_9_1_9_9_9_9_9_9_9_9_1_3_3_3_3_3_3_3_1_7_1_3_3_1_11_11_11_11_11_11_11_11_11_1_7_1_5_5_5_1_7_7_7_7_7_7_7_7_7_1_7_7_1_7_7_7_7_7_1_7_7_7_7_1_5_1_11_1_9_1_11_11_11_11_1_3_3_3_3_1_5_5_5_5_1_3_3_3_3_3_3_3_3_1_5_1_9_9_1_11_1_9_9_9_9_1_3_1_7_1_9_1_3_1_11_11_11_11_1_5_5_1_11_1_11_11_1_5_1_5_5_1_3_3_3_3_1_5_5_5_5_5_1_3_1_11_11_11_11_11_1_9_9_9_9_9_1_7_7_7_1_11_1_3_3_3_1_11_11_1_3_3_3_3_3_3_3_1_7_7_7_7_7_7_7_7_7_7_7_1_3_3_3_1_3_1_9_1_5_1_11_1_3_3_3_3_1_5_5_5_1_3_3_3_3_1</t>
   </si>
   <si>
-    <t>2_6_6_9_1_4_9_4_5_7_9_5_1_7_1_10_5_10_5_7_2_4_6_1_3_10_5_10_6_1_9_3_4_9_5_14_1_2_1_7_4_5_2_5_1_10_4_2_1_6_3_10_3_3_8_10_7_14_5_2_1_8_1_2_14_7_2_3_10_6_9_2_2_4_9_1_6_4_3_4_6_8_4_6_2_5_1_3_3_10_7_8_6_1_3_3_2_4_9_2_10_7_7_5_1_1_11_7_3_5_11_5_3_1_2_1_2_8_7_10_6_4_9_3_7_8_1_2_1_1_3_2_4_1_10_5_5_4_10_6_6_5_1_7_9_9_5_6_4_5_2_6_2_4_8_6_2_9_2_5_3_8_7_10_1_2_2_8_9_10_5_6_5_7_1_9_1_6_3_11_3_7_5_14_7_4_3_4_6_10_3_4_2_8_5_10_5_8_14_1_11_7_9_5_1_10_2_1_7_10_5_5_10_3_3_14_4_2_1_1_1_1_1_7_2_6_14_3_1_3_2_8_6_7_6_5_8_6_5_8_5_4_9_2_1_2_3_2_6_4_14_5_1_11_7_2_5_7_2_4_3_4_7_4_4_1_4_10_6_10_2_5_10_6_6_5_14_7_3_3_8_5_5_4_5_8_4_2_2_10_4_6_9_1_5_1_9_5_5_5_3_6_11_6_6_2_3_1_7_8_9_2_6_1_3_3_2_8_3_6_10_1_2_3_1_3_2_6_10_6_5_4_8_9_7_2_11_5_1_8_10_6_4_4_1_1_2_3_5_3_2_4_9_3_1_7_3_2_5_10_7_6_4_5_10_1_2_1_3_5_1_1_1_1_10_1_3_2_9_14_5_2_4_3_2_8_11_3_3_10_4_10_3_8_1_10_3_11_7_14_5_5_4_6_2_7_10_7_10_7_8_11_5_1_6_1_2_8_4_2_10_7_7_1_9_10_7_9_1_7_8_7_2_5_4_2_4_6_7_4_10_5_3_4_4_1_6_7_6_1_10_2_2_6_5_14_4_3_2_10_2_2_7_14_5_1_4_1_7_4_1_2_6_9_9_2_8_2_10_7_9_1_6_1_9_14_6_3_2_1_9_7_4_6_6_9_4_5_4_7</t>
+    <t>3_3_8_8_8_1_1_3_4_4_3_5_5_5_3_3_1_3_3_3_3_4_3_2_7_5_3_8_4_3_1_1_1_3_2_2_1_3_2_2_2_5_5_5_1_4_4_9_3_2_2_2_3_3_5_5_5_5_6_6_1_2_6_6_5_5_2_2_2_2_8_5_5_3_3_3_3_4_4_4_8_8_1_1_6_6_3_2_5_5_3_2_2_1_1_1_1_4_4_4_2_2_2_9_5_5_10_10_1_9_4_4_2_1_5_5_2_4_6_6_10_1_5_4_4_1_1_1_6_6_6_5_3_4_4_4_4_4_3_6_2_2_2_2_2_2_2_5_2_2_2_2_4_6_6_6_5_2_2_2_7_8_8_8_8_3_1_4_9_8_5_9_1_2_5_10_8_8_6_2_1_1_1_4_4_4_3_7_3_9_3_4_1_3_2_2_2_3_3_2_8_3_1_6_4_3_3_9_1_1_1_1_1_3_6_3_3_3_3_3_9_1_1_2_2_1_1_6_6_6_6_6_8_3_3_4_4_4_9_2_3_3_7_7_7_7_5_7_4_4_2_2_2_4_4_4_10_5_5_5_5_5_5_1_1_3_1_1_1_4_4_6_2_2_1_1_5_8_2_2_2_2_10_2_10_9_1_10_10_3_5_4_4_3_2_2_6_2_2_2_6_1_2_2_2_2_7_10_10_5_7_7_7_7_7_7_2_2_1_1_8_4_3_1_1_1_1_4_4_5_7_2_2_2_2_2_2_5_9_1_2_5_10_10_5_5_5_2_2_1_1_1_1_3_2_1_3_1_2_2_2_2_4_7_7_5_2_5_5_3_3_3_4_5_4_2_4_8_2_2_2_2_3_7_7_7_3_3_3_4_1_5_5_5_5_5_1_4_5_5_2_2_2_3_7_7_2_2_1_1_1_1_9_5_6_6_2_6_5_4_1_1_2_2_2_2_2_6_7_8_2_2_1_1_1_1_1_2_1_6_6_6_7_6_2_8_2_2_2_7_8_8_8_3_9_5_4_8_8_8_7_3_3_3_6_6_8_2_2_2_5_5_5_5_3_3_4_6_4_1_4_1_5_1_8_9_2_7_1_1_7_4_5_1_6_6_6_6_1_1</t>
   </si>
   <si>
     <t>3_3_5_4_2_4_1_1_5_6_1_2_2_2_2_1_7_7_1_1_2_2_2_4_5_8_2_2_2_1_4_4_4_7_9_9_2_2_1_3_6_2_3_3_1_4_9_4_2_2_2_4_2_1_1_2_2_2_7_1_2_4_9_8_2_6_5_5_10_6_1_5_2_3_8_4_4_7_8_6_3_4_1_2_5_2_4_1_4_6_7_6_7_6_1_2_10_4_2_4_1_4_2_3_2_6_2_3_3_3_2_5_8_1_1_1_2_1_2_7_8_2_7_3_2_5_9_9_1_1_8_2_3_7_3_10_6_2_2_9_3_1_4_7_1_2_8_1_7_3_10_1_4_3_4_8_4_4_8_1_9_3_4_4_2_2_7_6_5_5_7_4_1_2_1_4_5_3_4_1_1_5_4_5_5_6_1_9_8_5_3_7_4_1_3_5_6_3_10_1_5_3_4_9_7_7_9_8_6_2_3_6_6_3_4_3_3_8_7_2_9_9_3_1_1_1_4_4_8_5_1_3_2_10_6_4_8_2_7_4_2_4_6_2_6_2_1_5_2_2_3_3_9_2_8_9_8_6_8_1_7_1_7_6_9_5_4_6_1_4_8_1_1_4_1_2_2_4_2_1_2_1_3_4_5_2_2_6_5_6_2_4_2_9_3_1_3_8_4_1_1_5_4_4_2_2_2_4_1_6_6_4_2_7_2_3_7_1_4_6_2_3_3_7_3_2_2_2_4_1_1_5_3_1_2_9_8_6_4_2_3_2_2_7_7_1_2_4_4_1_2_2_9_3_9_6_6_1_3_3_3_4_6_6_1_1_6_3_3_8_5_2_2_3_3_10_4_4_4_5_10_2_5_5_1_1_6_6_5_9_6_6_6_1_2_3_5_5_1_9_5_3_3_4_8_2_6_4_4_6_6_4_4_3_3_7_7_7_1_2_9_9_10_6_6_3_1_5_7_4_4_8_3_5_5_2_5_2_2_2_6_4_6_4_3_2_1_2_1_10_3_1_10_4_6_7_1_6_1_3_7_7_8_3_5_5_2_5_7_2_5_4_1_4_10_9_6_4_4_3_2_2_1_3_6_4_2_8_1_1_5_7_4_10_7_7_1_4_1_4</t>
@@ -325,52 +325,52 @@
     <t>7_7_7</t>
   </si>
   <si>
-    <t>7_6_9_3_7_1_11_4_2_9_5_8_6_2_2_6_4_2_7_5_4_5_1_9_8_1_6_2_3_6_4_3_8_1_5_5_5_1_3_2_2_1_8_1_1_2_7_5_5_11_5_10_7_6_1_1_6_8_2_1_7_9_1_9_2_2_1_7_6_10_3_1_9_4_7_5_3_10_7_7_6_1_2_9_7_7_1_7_2_2_4_6_1_5_7_5_11_5_8_7_5_1_3_2_3_2_4_7_3_10_5_10_1_4_4_6_7_3_7_6_11_4_8_6_6_1_7_8_10_2_4_7_6_2_1_1_6_5_5_7_1_9_14_6_5_5_2_6_2_9_7_6_8_6_8_3_2_6_3_1_6_8_4_9_3_3_10_2_8_3_7_7_7_14_1_8_9_10_7_4_8_1_14_4_10_4_6_2_3_4_1_2_1_4_9_3_2_14_3_4_14_5_5_11_2_1_8_6_3_4_10_1_1_2_9_2_2_4_3_1_5_4_11_7_8_2_9_6_7_7_2_4_14_7_4_6_1_3_6_4_8_2_3_9_2_2_5_10_5_9_6_8_4_6_6_9_8_1_4_11_6_3_9_7_7_3_2_3_5_1_3_7_7_8_11_4_11_6_10_5_1_1_4_3_9_14_5_6_3_5_10_5_1_5_5_4_3_2_10_6_2_5_2_2_1_2_4_5_3_9_7_1_6_7_3_14_5_10_4_6_7_7_7_9_7_3_1_4_3_7_14_1_1_14_3_3_4_3_4_9_7_7_10_2_6_1_9_1_4_5_8_7_5_10_4_6_7_1_4_9_5_1_7_4_5_4_7_7_1_3_5_9_9_7_3_14_5_5_10_5_6_2_4_7_6_2_2_1_6_7_5_3_9_1_9_2_1_7_10_7_3_5_4_9_6_8_3_1_4_9_5_5_1_3_4_5_4_4_6_5_3_5_10_2_4_7_9_1_3_8_4_10_5_6_5_7_7_1_1_2_7_7_2_5_10_6_3_10_7_5_7_1_10_7_2_6_7_9_3_6_10_4_1_2_9_3_3_2_2_11_6_5_2_1_7_6_1_2_2_2_14_4_6_10_4_8_9_6_9_9_7_1_6_4_10_2_8_2_1_7</t>
+    <t>5_2_5_6_6_2_7_7_8_7_3_1_1_9_10_10_10_10_2_5_5_6_6_6_6_2_6_6_8_2_2_2_1_10_9_3_3_3_5_8_5_4_6_8_8_8_4_4_4_8_6_4_4_1_8_7_9_3_3_1_3_1_1_1_1_1_8_6_6_1_1_5_6_2_8_6_7_2_2_1_3_4_8_7_7_3_3_5_5_5_7_7_7_1_3_3_4_4_4_7_7_7_7_3_3_4_8_8_5_7_1_4_9_2_6_6_6_9_5_5_5_7_4_4_8_8_2_2_1_10_10_10_10_2_10_6_6_3_2_2_6_1_1_2_1_9_1_2_1_1_6_6_1_2_2_2_2_8_3_3_3_3_10_2_4_4_7_3_3_3_2_3_8_3_5_4_4_2_4_6_3_1_9_10_8_7_6_6_6_6_6_1_4_3_1_1_6_3_3_1_1_1_6_5_4_3_3_7_4_8_8_6_6_6_4_4_4_1_1_2_5_9_2_10_10_5_5_4_9_7_8_8_3_3_3_1_7_4_3_3_8_7_4_1_1_4_5_6_6_5_10_10_10_10_3_3_1_5_9_2_3_4_2_4_4_2_2_1_2_6_4_8_4_4_7_7_7_5_1_9_3_1_3_5_5_5_6_6_9_1_5_7_2_4_4_5_5_5_9_7_3_5_6_3_3_7_7_7_1_5_8_3_4_4_8_2_6_6_6_6_6_1_1_1_1_1_1_1_9_5_5_1_6_6_6_4_4_7_7_3_5_5_6_6_6_6_6_6_8_8_3_1_1_1_5_5_3_3_8_10_10_6_6_8_8_8_8_4_4_8_6_4_7_7_7_7_7_3_10_6_4_3_6_2_2_2_1_2_2_2_2_4_4_5_6_6_6_7_2_3_3_3_4_7_7_1_6_9_1_3_4_2_1_1_1_7_5_3_7_7_7_7_3_3_3_1_1_2_2_1_3_2_4_4_8_8_2_2_2_2_2_2_1_1_6_1_1_3_9_4_1_4_9_4_2_8_8_8_1_9_1_1_4_6_5_1_9_3_1_2_3_3_9_3_7_7_7_7_3_3_5_2_2_4_3_1_6_2_2_2_6_1_4_4_6_6_1_1_6_6</t>
   </si>
   <si>
     <t>8_8_8</t>
   </si>
   <si>
-    <t>6_1_9_4_3_1_9_5_5_7_9_2_2_8_3_4_5_4_7_7_2_1_14_5_8_6_7_9_7_8_4_4_11_5_2_3_6_8_14_3_7_5_1_8_1_2_10_6_2_1_3_14_2_9_8_2_4_6_5_9_6_3_4_11_4_6_1_7_7_3_1_10_1_4_1_6_3_8_2_6_2_2_10_6_3_3_5_6_2_4_7_1_7_11_4_7_1_6_6_5_4_7_6_3_1_5_6_6_7_5_7_7_1_7_7_9_6_2_2_2_7_2_9_4_4_6_5_11_7_1_8_9_4_3_4_6_9_8_6_3_5_2_7_10_5_7_10_6_5_5_6_10_5_2_3_6_8_3_10_2_8_10_7_2_4_7_8_7_8_9_3_8_11_7_1_4_3_14_1_1_5_4_4_2_2_6_10_3_3_2_6_2_3_1_2_10_5_1_9_1_5_8_2_14_5_5_6_1_1_3_3_7_1_7_14_2_4_2_14_3_3_1_2_8_2_3_9_6_8_7_3_5_10_1_10_5_6_4_9_3_7_10_7_7_10_3_3_3_5_10_5_8_4_2_6_2_9_5_6_2_1_2_5_6_10_6_4_9_1_4_8_14_4_9_2_3_9_9_5_10_7_5_7_8_9_3_4_8_4_4_4_6_8_7_7_7_5_9_1_6_6_6_8_5_14_2_9_8_3_5_7_7_1_3_2_14_5_8_11_2_2_5_4_8_6_10_6_2_6_5_2_5_7_14_5_7_7_1_4_11_3_9_2_4_2_3_5_3_9_3_2_4_2_7_10_7_6_4_4_3_3_1_4_4_7_2_3_1_1_8_3_7_5_3_1_9_2_14_3_6_5_2_1_9_1_1_10_6_3_3_9_14_7_2_10_5_5_5_1_2_5_7_3_8_1_8_2_14_5_9_7_7_4_1_1_2_6_4_6_7_7_7_7_6_5_8_14_4_8_1_4_6_5_3_14_6_4_8_3_6_9_2_2_3_2_6_7_4_6_4_2_5_11_7_3_1_5_4_4_3_1_2_8_4_4_10_6_7_2_10_3_2_8_6_1_8_2_1_3_7_7_2_4_5_3_14_7_11_2_8_10_5_2_7_4_1_1_14_4_2</t>
+    <t>1_9_1_1_2_5_2_7_7_5_5_4_4_7_7_3_8_8_8_8_8_1_3_1_2_2_2_8_1_2_2_2_1_1_9_5_3_3_6_6_3_3_3_3_1_2_10_9_7_7_2_2_2_2_9_1_1_10_10_4_4_1_1_10_6_5_5_1_3_1_1_1_9_1_2_3_3_8_6_1_4_4_7_1_1_3_3_1_1_8_2_5_1_10_3_9_1_6_4_4_5_1_1_2_2_2_2_2_4_8_8_8_8_4_7_7_2_4_4_8_7_3_4_4_4_4_1_6_6_5_2_2_2_7_1_1_4_4_4_4_5_6_6_6_9_5_2_2_2_2_2_4_2_2_2_2_2_4_4_6_6_6_6_6_6_1_9_3_4_10_10_10_8_8_8_4_8_8_7_7_2_3_9_1_2_3_8_8_8_8_6_6_6_8_2_2_9_2_2_2_4_4_4_4_4_7_7_7_7_2_9_2_9_1_2_7_5_5_5_9_1_2_1_2_6_9_7_1_1_9_1_7_3_3_3_4_6_6_1_1_4_4_4_4_4_1_3_3_1_4_1_4_4_6_6_6_10_1_6_1_1_2_2_6_1_1_9_5_5_6_4_4_4_4_8_8_6_6_3_3_4_2_10_4_1_4_2_2_9_2_4_4_4_3_5_5_3_3_3_3_4_1_1_4_4_10_10_1_3_3_1_9_2_2_2_2_7_7_7_7_4_4_2_3_5_9_8_8_2_1_1_1_6_10_7_1_7_8_8_7_1_7_7_7_5_5_1_1_3_3_8_2_7_9_2_1_2_2_9_2_2_9_10_10_10_4_5_8_8_4_4_2_5_7_3_4_1_1_1_1_4_4_4_8_4_4_3_5_5_1_1_1_9_2_1_9_3_3_5_5_5_5_1_6_5_5_5_1_1_1_2_9_6_4_5_5_5_2_2_9_2_6_5_6_6_3_6_5_5_5_5_5_5_6_9_2_2_1_8_4_1_1_1_1_1_2_2_2_4_1_3_3_2_2_2_1_1_2_5_5_1_2_8_2_1_6_6_6_3_1_7_7_7_7_7_3_3_9_8_2_5_6_2_2_3_3_5_5_5_5_5_1_6_6_6_4_4_1_1_6</t>
   </si>
   <si>
     <t>9_9_9</t>
   </si>
   <si>
-    <t>5_2_3_8_2_4_7_2_8_5_10_5_4_4_11_7_8_5_3_3_7_4_7_5_9_2_10_4_2_4_2_2_7_10_7_1_1_6_7_10_7_5_10_3_8_10_6_3_14_4_7_9_2_4_10_3_3_4_1_9_2_6_8_3_2_5_10_7_3_4_7_1_8_1_2_9_2_11_2_2_4_1_10_5_1_4_9_9_3_7_2_8_7_9_3_1_3_9_2_4_2_2_6_9_3_1_7_7_3_7_7_6_11_5_3_2_5_2_7_7_4_9_7_4_6_4_1_14_3_11_7_4_1_9_8_7_6_6_3_8_2_8_10_7_1_7_4_7_9_2_4_2_3_2_8_4_4_8_5_4_3_3_4_7_4_4_2_8_1_7_4_8_9_9_6_6_5_8_1_4_1_8_9_3_7_11_6_4_6_6_4_11_6_3_1_9_1_8_2_7_6_11_3_8_7_8_7_2_6_2_3_1_8_7_2_9_4_1_3_3_6_11_7_10_5_6_4_7_10_6_4_2_9_6_3_8_3_2_2_2_4_5_6_1_8_1_7_8_1_1_3_9_10_5_3_3_2_9_6_6_7_2_10_5_7_2_6_7_8_9_1_8_7_1_2_1_4_2_9_10_2_5_10_3_6_1_1_8_10_2_10_2_2_5_14_5_4_9_9_10_4_1_9_9_11_7_10_4_7_5_2_7_4_10_5_3_7_1_3_14_4_1_10_1_5_1_5_11_6_3_9_10_6_4_3_10_4_6_3_9_2_6_10_6_11_4_14_3_7_7_1_7_10_6_14_7_8_2_10_3_7_3_9_5_3_2_10_6_4_8_4_6_6_6_8_1_5_10_7_4_3_1_7_4_9_1_1_1_1_9_1_1_9_1_4_7_5_4_3_1_5_5_4_8_5_9_2_4_10_6_6_10_6_7_5_4_3_4_1_4_9_4_3_5_8_7_10_6_2_5_1_8_5_8_1_5_4_1_4_7_6_1_3_8_6_4_4_3_5_6_2_3_6_4_2_4_2_4_1_5_1_10_7_1_3_9_4_4_5_11_5_4_7_14_3_1_7_2_1_4_3_4_5_2_4_6_5_8_2_4_1_4_8_1_6_2_3_2_9_3</t>
+    <t>1_1_9_1_8_8_1_1_1_2_7_7_7_5_5_1_6_2_2_9_3_3_3_2_5_8_8_8_8_5_1_1_1_6_6_7_4_9_1_4_4_4_4_3_8_7_4_5_7_7_7_7_3_4_2_6_5_5_4_4_4_1_3_1_1_9_1_8_8_7_4_4_2_3_3_3_3_5_4_2_2_2_8_2_4_2_2_2_2_2_2_10_3_10_3_3_2_1_4_5_9_1_3_9_2_7_8_7_7_5_5_5_8_7_5_5_5_5_5_2_7_7_1_1_5_2_7_7_5_5_7_6_6_3_5_5_2_2_2_2_10_4_4_1_6_7_7_5_5_8_8_8_8_8_8_2_1_1_2_2_5_5_5_4_1_3_5_5_8_2_1_4_4_4_4_4_3_3_1_1_7_7_4_7_1_1_4_7_3_7_1_1_1_1_4_4_3_1_4_4_7_7_2_2_4_1_1_2_2_2_10_8_8_2_7_2_2_9_1_1_3_2_2_9_2_3_3_9_1_3_2_6_6_3_3_3_3_9_3_4_4_10_1_6_6_6_6_6_6_2_2_2_9_2_2_8_1_1_1_2_2_9_2_2_9_6_6_6_6_1_3_5_2_9_5_5_3_3_3_3_8_6_6_2_2_6_6_6_6_6_4_4_4_4_5_2_2_9_2_3_3_3_3_3_9_7_7_8_8_8_8_8_8_8_8_3_8_8_3_2_7_7_6_2_5_5_5_5_7_1_1_4_4_5_3_3_5_5_2_2_5_5_1_1_9_1_10_7_2_3_3_1_7_4_4_4_4_4_1_10_10_1_9_6_8_1_1_1_6_4_6_5_5_5_5_7_7_1_4_1_1_1_3_3_2_6_6_6_2_3_1_9_1_8_7_5_2_9_2_1_1_1_1_9_3_6_1_10_10_4_2_9_2_1_1_6_5_3_3_3_3_3_7_7_6_6_3_3_1_9_2_4_4_4_6_5_5_5_5_2_8_8_5_3_1_3_2_9_10_10_10_10_10_10_10_3_9_1_3_5_5_5_1_5_5_4_6_5_4_4_5_5_5_5_5_4_4_1_5_7_5_1_6_4_4_4_3_3_1_7_7_7_4_4_1_10_2_10_10_3</t>
   </si>
   <si>
     <t>10_10_10</t>
   </si>
   <si>
-    <t>10_7_1_6_2_1_4_6_10_5_3_4_8_10_5_8_14_4_4_5_3_1_14_4_2_8_9_3_1_2_2_2_11_4_7_4_2_8_4_2_3_7_2_14_4_1_3_11_5_4_14_7_5_3_10_2_14_2_2_8_10_1_7_7_5_4_6_5_7_9_10_2_1_3_2_6_1_11_7_1_2_1_2_2_10_5_3_8_6_14_3_10_5_7_6_10_4_1_5_2_2_2_4_7_6_11_7_10_4_5_3_5_5_7_1_5_8_4_3_3_3_2_1_3_8_1_4_14_4_7_6_10_3_6_6_10_2_5_4_2_8_9_3_2_7_10_3_11_7_7_6_3_1_7_1_7_2_2_5_9_5_6_5_4_1_4_3_6_2_14_4_2_4_14_3_5_7_1_3_4_10_2_3_3_3_6_8_4_1_4_5_1_6_1_10_6_10_5_2_6_8_2_5_2_3_1_4_3_9_3_8_6_5_8_4_3_3_14_7_2_3_5_2_1_1_3_6_9_10_5_4_10_4_3_4_8_7_1_7_8_4_10_6_2_7_5_14_6_11_6_14_4_3_8_2_4_6_7_3_7_6_7_1_4_5_9_6_5_1_7_7_9_10_6_7_1_7_2_3_9_8_10_2_4_2_14_6_8_4_3_10_5_2_5_4_7_5_8_7_4_10_7_9_3_9_8_6_1_4_1_8_3_4_3_6_10_4_5_8_1_5_1_4_2_10_7_11_4_10_2_4_2_5_1_4_5_14_5_4_5_3_6_1_3_2_2_5_1_1_5_3_7_8_2_2_8_9_6_1_2_9_7_7_7_5_6_1_9_5_3_2_4_6_8_9_7_4_8_1_2_3_9_8_5_1_5_9_3_9_1_8_10_4_7_2_2_10_4_1_3_4_2_7_14_5_4_5_3_9_8_6_10_6_1_14_5_9_3_2_2_4_3_1_2_5_5_6_4_4_8_3_4_4_11_7_7_7_7_6_8_10_4_8_2_1_3_1_11_3_3_9_10_6_1_4_2_14_6_4_5_5_11_5_6_4_9_2_7_6_5_1_2_3_10_6_11_7_2_6_7_4_2_7_4_3_1_14_6_8_6_8_5_4_14_2_2_10_5_8_6</t>
-  </si>
-  <si>
-    <t>4_3_3_1_1_3_2_2_4_4_4_9_2_3_4_8_7_7_8_3_2_7_4_8_3_2_3_7_9_6_6_5_5_1_1_4_3_7_6_2_2_4_1_1_7_5_9_3_2_1_5_9_2_5_3_4_7_2_6_7_8_1_5_9_7_7_7_9_1_1_6_5_1_1_1_1_9_4_2_2_3_3_3_1_7_1_1_2_2_4_5_7_6_1_3_6_1_7_9_2_2_8_6_2_7_1_3_3_7_5_4_1_8_9_3_3_2_2_2_4_8_3_1_1_1_2_2_2_3_7_2_8_6_1_7_2_2_2_3_7_9_2_2_5_1_3_3_4_5_9_9_3_4_1_2_2_9_2_4_8_8_9_6_2_4_4_2_6_2_1_4_4_2_4_1_8_9_1_1_5_4_6_5_2_2_2_5_7_7_5_8_4_1_3_2_7_7_1_5_3_7_1_2_2_6_5_1_5_3_3_3_4_4_2_6_7_1_3_1_6_2_4_5_1_2_6_8_1_8_2_5_5_8_5_2_1_1_1_1_6_6_8_7_2_4_5_4_7_6_2_9_8_6_6_5_8_4_6_2_2_4_7_9_3_4_4_4_2_7_1_1_7_3_7_2_8_8_8_4_4_1_5_4_3_4_9_9_5_5_6_2_6_6_3_5_5_3_8_8_6_7_7_5_9_3_2_4_3_3_1_3_1_2_9_3_9_9_1_4_2_2_2_1_7_9_5_2_1_2_1_2_1_6_3_3_3_4_5_3_1_3_5_4_4_3_1_9_2_3_3_1_2_2_4_4_1_1_1_9_6_1_1_2_8_2_3_2_4_2_7_3_3_1_3_3_3_2_4_8_4_5_6_2_3_4_2_1_1_6_8_2_5_1_1_3_9_3_2_2_2_5_1_6_9_2_8_6_3_7_6_1_8_1_7_4_9_8_1_8_3_7_6_6_6_1_2_2_2_6_2_8_6_6_6_8_4_6_2_3_7_5_9_6_3_3_4_1_8_4_1_6_2_2_5_5_1_4_9_1_1_1_2_3_4_2_4_2_1_1_5_1_7_1_2_3_5_4_2_8_5_4_6_7_7_6_4_4_2_3_4_3_8_8_4_1_3_1_6_8_3</t>
+    <t>9_7_1_1_4_1_1_2_9_2_5_8_8_3_1_1_4_2_2_9_2_1_8_8_1_2_8_8_4_6_6_6_6_5_5_1_2_7_6_8_10_4_5_5_5_5_5_5_5_2_2_6_6_6_6_6_3_8_8_8_4_4_4_4_3_3_8_8_5_5_5_2_3_5_6_3_3_4_4_4_10_10_6_1_7_7_7_7_5_3_4_4_4_6_6_6_6_6_1_5_5_4_4_4_1_5_10_10_2_2_1_1_3_1_1_1_2_2_9_4_4_4_6_6_9_8_2_2_8_2_2_5_2_2_2_8_8_8_8_5_5_1_1_5_6_6_2_1_1_1_1_1_6_2_2_3_3_3_7_8_3_3_2_2_9_5_6_1_8_8_8_8_8_8_8_8_4_6_2_1_1_1_2_4_4_6_7_7_7_2_4_4_4_1_1_6_6_5_3_8_1_4_9_1_1_1_9_5_5_5_6_8_4_4_9_1_5_5_7_7_4_3_5_2_2_8_8_6_5_5_5_7_7_7_7_7_7_7_6_7_3_3_1_6_6_1_6_6_6_3_3_3_3_3_3_3_3_3_3_4_4_4_7_2_2_2_3_3_7_7_7_7_7_4_4_3_4_4_4_2_1_8_1_8_8_1_5_5_5_7_7_2_2_2_2_9_5_5_3_3_3_3_3_1_9_6_8_1_1_6_3_2_2_5_1_9_1_1_9_5_5_5_4_2_2_2_2_2_9_2_2_2_1_2_3_3_3_1_1_1_1_6_2_1_1_4_7_7_7_7_8_8_3_5_4_4_1_6_1_4_2_2_2_2_3_1_4_4_4_4_4_1_1_1_7_10_2_2_2_9_4_2_2_5_5_5_5_5_3_7_4_6_8_3_3_3_6_2_2_2_1_6_6_6_6_8_6_6_2_2_2_3_5_5_3_5_5_5_4_4_4_4_6_6_4_4_4_4_10_10_6_6_6_6_6_6_4_4_4_4_4_4_4_4_2_2_2_3_3_3_3_3_3_3_3_3_2_3_3_8_3_2_2_8_2_2_4_1_1_2_2_2_2_3_8_4_5_3_3_3_5_5_8_6_4_5_5_1_3_3_3_3_3_5_5_5_5_5_5_5</t>
+  </si>
+  <si>
+    <t>2_6_7_7_2_4_2_4_7_2_2_2_6_5_4_2_3_2_3_5_6_6_6_7_1_4_4_8_6_9_7_7_2_7_6_1_1_1_5_1_2_5_4_8_1_2_3_3_8_4_2_5_8_9_9_9_2_8_1_1_6_6_2_6_6_1_1_1_5_5_2_1_6_4_8_2_2_3_6_8_1_9_8_7_8_2_1_2_2_6_2_2_8_8_6_1_3_1_3_3_3_2_4_4_2_5_1_2_2_1_2_8_2_7_8_1_5_1_1_7_6_3_3_6_8_2_7_2_7_1_1_4_7_1_1_1_2_5_6_6_5_2_1_5_5_9_1_3_9_9_6_2_3_5_5_8_1_8_8_8_4_1_6_3_5_8_8_7_8_1_7_3_3_1_2_1_4_4_4_2_2_6_1_9_8_9_3_1_8_6_2_9_3_7_7_1_1_5_4_9_2_6_2_2_3_2_2_1_8_8_4_1_9_1_2_2_5_6_6_8_4_1_1_4_7_6_6_4_6_6_2_1_4_3_2_7_4_4_1_1_2_1_2_4_8_8_8_6_3_2_5_7_6_4_4_8_1_6_6_4_1_1_4_5_8_4_6_7_6_7_2_2_5_8_2_8_2_1_1_5_1_5_7_5_3_5_5_5_5_4_3_3_3_2_1_2_7_5_2_2_2_7_4_4_6_9_9_7_2_2_2_6_3_7_3_2_2_2_4_3_4_8_2_5_4_9_9_9_5_4_3_1_1_1_4_2_2_4_4_5_5_5_9_9_1_7_2_1_5_4_4_1_6_4_4_7_2_2_4_6_1_4_6_4_4_4_3_9_1_1_2_1_1_1_2_2_5_4_4_4_3_3_6_4_5_4_2_1_2_3_6_6_7_7_5_3_3_5_2_7_7_8_2_6_7_7_1_5_6_6_7_8_3_4_1_7_7_1_5_2_4_5_3_1_1_9_5_2_8_5_7_8_9_2_5_8_8_9_2_1_6_6_4_1_8_8_2_2_7_9_3_4_4_2_6_6_3_8_2_1_3_4_9_1_1_8_2_3_3_6_8_2_3_9_5_6_4_4_6_5_2_1_2_4_3_4_4_4_3_1_4_2_4_6_2_2_3_2_1_5</t>
   </si>
   <si>
     <t>6_9_4_3_1_8_2_1_2_2_1_8_9_4_4_1_4_3_4_2_8_3_1_6_2_7_1_2_8_5_5_3_2_3_6_2_1_6_6_2_3_5_1_1_3_8_6_8_3_5_7_7_2_3_7_2_4_8_9_4_6_2_2_3_7_4_1_4_6_1_9_5_4_1_5_8_5_4_4_5_8_2_1_1_5_4_2_1_5_6_2_4_2_9_1_4_2_4_2_2_3_4_1_2_4_1_7_9_1_4_7_4_2_6_3_2_5_6_9_8_4_8_2_3_7_1_8_2_3_3_7_2_6_7_4_5_3_1_5_4_3_8_6_6_1_4_6_2_9_5_7_9_5_6_3_3_1_3_6_5_2_4_2_6_4_6_8_4_1_6_1_5_2_2_5_5_4_9_6_3_4_3_2_1_7_8_2_6_7_6_6_4_4_2_3_4_1_4_8_7_5_1_7_5_2_4_1_7_7_5_4_3_4_5_3_5_4_1_8_4_6_2_1_8_6_7_1_4_6_2_4_4_1_4_4_5_1_4_6_3_8_4_3_7_6_2_1_8_4_3_5_3_1_9_4_1_3_6_6_5_8_6_1_5_3_3_8_2_4_1_5_1_9_1_5_3_7_4_8_5_1_1_7_5_1_6_5_8_4_6_2_2_1_7_3_5_5_5_3_4_5_5_6_7_6_7_4_6_1_1_3_6_9_4_4_9_5_6_7_9_4_4_4_7_8_6_9_2_2_2_3_5_4_6_8_2_8_7_4_4_5_3_4_9_8_7_4_9_2_7_2_8_7_3_1_5_9_1_4_9_1_4_9_2_4_8_2_1_1_9_9_4_5_3_6_8_1_9_1_1_8_4_6_4_1_3_7_1_4_8_9_6_9_8_7_7_1_8_9_9_6_6_7_8_1_7_5_1_4_2_8_7_2_9_1_2_6_2_4_8_5_8_3_1_7_1_5_8_5_3_1_6_3_5_7_3_4_1_7_4_2_1_5_2_7_8_6_9_4_9_3_6_1_2_5_2_8_4_1_3_4_2_1_8_4_2_5_7_1_2_7_7_2_1_4_8_4_7_5_9_5_9_8_9_6_2_8_2_8_3_3_4_9_7_2_6_7_2_4_8</t>
   </si>
   <si>
-    <t>4_1_6_3_6_2_1_1_2_2_9_8_1_2_6_6_3_7_1_8_6_3_3_9_6_1_4_4_2_6_3_5_5_5_7_1_8_7_2_3_7_5_1_6_1_9_5_7_3_9_2_2_6_5_3_8_5_6_9_3_5_2_2_2_9_1_1_6_4_4_5_8_5_6_9_9_1_3_4_4_1_1_3_6_2_2_5_7_6_8_4_4_1_4_2_2_2_2_3_6_1_2_1_6_4_4_9_6_3_2_5_3_5_4_7_7_2_2_4_8_6_5_9_9_2_2_2_7_7_4_4_1_5_7_2_3_2_3_2_3_3_4_5_7_6_1_8_5_5_5_1_2_7_8_8_8_9_3_3_5_2_3_4_2_8_2_2_1_9_2_2_1_1_3_6_3_8_8_6_1_2_2_1_9_1_2_2_1_2_6_3_6_1_4_6_6_8_7_7_5_3_4_3_9_6_6_9_1_1_6_9_4_4_4_6_6_8_6_2_4_4_5_2_5_5_1_9_4_2_1_5_2_9_3_9_2_1_1_6_8_1_1_5_4_5_2_2_4_2_1_2_2_7_6_1_3_3_3_3_9_8_3_1_9_4_8_7_5_8_4_2_7_7_5_3_1_9_9_2_4_4_2_2_2_8_1_2_8_3_3_1_4_6_7_1_3_3_1_4_6_3_3_3_1_6_5_8_7_4_7_4_4_6_5_5_2_1_4_7_3_2_6_1_3_7_8_6_7_1_7_7_1_2_2_9_5_4_4_8_3_4_5_5_2_2_7_6_6_7_7_5_6_2_1_1_3_2_2_2_6_4_6_1_2_8_8_6_4_2_2_1_5_3_2_3_2_7_9_9_6_6_3_5_4_4_1_1_3_1_7_5_4_4_7_9_1_7_2_5_1_3_9_9_9_4_6_5_4_4_4_6_6_1_7_4_4_7_2_5_1_7_9_9_2_6_4_3_1_6_6_1_1_8_1_7_6_4_4_1_4_8_4_8_5_5_2_1_4_8_2_8_4_7_7_8_4_4_2_3_1_3_4_3_1_1_1_8_7_7_4_1_7_1_1_3_4_4_4_4_2_8_8_3_4_1_8_7_2_7_9_3_4_6_5_5_5_5_5_5_1</t>
+    <t>2_6_5_4_1_9_4_9_1_6_6_4_4_5_4_1_1_2_6_4_4_4_6_4_2_5_5_5_4_3_4_1_1_1_2_3_2_5_4_1_8_6_1_1_4_1_1_5_1_7_9_2_2_9_3_1_2_6_5_7_8_1_5_5_1_6_2_3_2_4_4_2_4_2_2_4_1_7_7_8_6_6_6_3_1_1_1_4_2_2_1_4_1_3_4_9_6_2_5_3_7_5_1_6_2_8_6_1_2_1_9_6_5_5_3_6_5_6_4_1_1_2_2_2_8_2_5_2_7_5_2_5_6_4_5_6_2_9_2_1_7_5_3_7_5_6_1_3_7_5_9_8_6_8_6_3_2_2_4_8_2_2_3_5_6_6_3_8_1_4_4_2_5_3_1_5_8_1_2_2_5_4_2_9_7_7_1_5_6_1_6_3_2_4_4_1_5_2_1_8_1_2_8_1_4_1_2_2_6_1_6_3_8_2_2_1_2_1_1_3_5_1_7_2_7_1_1_6_8_8_8_5_1_1_2_2_3_7_4_3_3_1_1_5_7_6_5_1_6_2_2_1_3_2_5_9_8_4_2_5_3_1_3_2_2_3_3_2_3_4_4_3_3_9_7_3_9_9_4_7_1_5_4_2_1_1_1_1_6_1_6_4_2_2_3_1_6_5_3_9_3_7_6_7_5_2_5_5_5_4_4_1_6_1_9_3_2_1_2_8_7_7_7_1_6_2_2_8_5_3_9_9_3_9_9_9_3_3_4_6_4_1_4_2_5_5_8_1_5_5_6_7_3_3_1_4_2_1_1_4_5_5_3_3_3_5_8_6_8_1_1_4_1_7_2_7_7_4_2_2_3_6_6_4_9_1_1_1_8_9_1_1_4_7_6_6_4_2_1_6_1_3_3_4_5_7_1_2_3_3_3_2_3_1_7_8_2_2_6_3_6_3_3_4_1_2_2_2_2_7_6_2_5_2_6_2_9_9_3_1_8_3_2_8_2_2_1_4_6_1_1_1_1_8_4_6_1_4_6_4_4_6_6_3_2_2_6_3_7_1_7_1_2_4_1_1_3_1_2_6_6_1_1_5_8_2_6_6_1_5_1_1_3_5_2_1_4_5_4_5</t>
   </si>
   <si>
     <t>2_7_1_9_6_1_7_1_9_8_7_3_3_9_7_3_2_9_1_6_2_8_3_8_1_3_6_8_4_3_1_4_1_6_2_4_7_3_2_6_4_8_1_1_2_4_6_2_2_6_2_6_5_5_1_1_2_2_1_8_6_5_7_7_2_1_6_3_1_3_6_2_1_7_5_1_9_9_2_7_2_6_2_2_4_6_4_8_5_5_5_5_1_6_4_2_1_8_1_7_4_8_6_6_4_1_1_2_3_1_6_4_3_5_5_1_4_9_4_6_5_1_9_1_8_3_3_3_7_3_2_1_4_9_3_1_1_7_1_4_5_2_4_3_2_7_4_2_2_5_3_3_1_2_6_9_6_5_5_1_1_7_7_3_3_6_6_8_3_7_2_1_8_5_2_3_1_3_8_2_1_9_2_1_1_2_7_2_3_4_4_2_6_6_1_2_2_2_9_5_6_8_3_2_1_4_1_5_7_8_8_6_4_5_2_6_3_7_8_2_6_5_1_4_3_1_3_7_4_3_1_3_3_6_3_2_5_2_9_1_4_7_5_5_4_4_8_2_3_3_1_7_9_6_2_4_6_5_7_9_5_8_1_2_5_2_8_2_5_1_4_3_7_1_2_2_1_1_8_9_6_2_1_5_2_4_3_2_8_3_2_9_1_6_4_2_8_2_2_4_6_1_1_3_9_1_3_3_2_3_8_5_4_2_3_8_7_3_6_5_6_2_9_5_9_7_9_3_6_8_6_6_1_5_6_6_7_4_1_7_3_6_5_5_5_8_1_8_8_1_2_1_3_9_5_7_4_6_1_2_3_6_4_1_8_3_8_2_4_5_3_9_1_3_2_5_5_3_6_4_2_2_1_9_7_7_5_3_4_2_5_4_1_7_6_7_5_2_3_4_3_4_2_6_5_9_6_2_5_8_2_4_1_1_9_3_1_2_5_8_8_4_2_7_4_4_4_3_1_4_7_1_8_4_7_7_6_7_3_6_8_5_1_9_5_2_2_1_8_8_8_3_4_7_6_6_7_1_6_1_4_8_1_3_5_6_2_7_8_4_1_1_1_1_5_5_4_6_2_5_2_6_5_8_4_4_9_2_6_1_1_7_1_1_2_2_9_3_1_5</t>
   </si>
   <si>
-    <t>8_1_4_6_6_8_3_9_9_9_6_9_8_3_4_6_4_1_1_6_4_3_8_8_9_4_1_3_3_2_6_6_5_9_9_1_2_4_4_2_8_9_1_4_6_4_1_3_3_4_4_4_4_1_3_8_9_1_6_1_6_2_8_3_3_4_3_8_5_9_4_4_2_2_1_4_4_5_2_8_1_4_6_4_6_5_2_2_1_4_5_9_9_3_6_4_7_4_6_6_2_2_8_8_8_2_3_3_4_5_6_2_2_1_1_8_7_3_7_5_8_1_9_6_6_4_5_6_2_1_8_4_3_1_9_6_3_3_6_6_1_7_7_7_1_7_6_4_6_2_9_1_6_7_2_4_7_3_3_7_7_7_6_2_2_1_9_6_1_8_1_1_2_6_2_3_1_1_1_1_3_4_1_3_2_2_4_1_4_7_1_5_7_3_3_8_1_4_4_4_3_7_6_6_7_3_4_5_9_6_4_9_4_4_8_1_3_7_8_4_6_3_1_1_8_2_1_1_6_8_2_7_7_6_2_3_2_5_6_6_6_2_1_5_5_9_2_3_5_5_2_6_3_4_3_6_8_9_3_5_5_9_9_1_5_5_9_2_5_3_1_3_2_5_4_7_6_6_1_1_8_3_3_9_5_4_7_2_1_6_8_8_6_6_6_6_3_1_6_4_1_9_5_2_3_2_1_6_1_2_4_7_9_9_4_4_4_8_3_1_5_7_4_4_8_8_1_1_3_3_5_6_1_1_1_3_6_4_6_3_2_4_4_3_4_2_8_1_3_3_1_3_9_4_2_6_3_3_1_5_6_2_7_5_7_8_1_7_4_3_4_2_3_1_2_2_2_5_5_5_2_1_6_5_5_1_1_9_5_6_2_6_6_4_1_1_2_5_2_9_3_2_1_1_1_7_2_3_3_3_3_2_2_7_8_8_4_4_1_3_1_3_3_4_6_4_5_2_3_4_6_8_7_4_5_4_5_6_5_5_7_1_1_1_3_1_9_5_6_6_2_2_9_2_5_4_8_5_5_7_2_4_2_5_2_7_6_1_7_5_5_6_4_6_3_2_3_2_2_7_2_2_3_2_8_4_7_1_1_3_9_9_3_4_4_3_3_5_2_2</t>
+    <t>2_5_3_7_6_5_8_4_6_3_5_1_7_4_8_4_3_1_2_2_2_4_8_8_1_8_8_7_7_3_1_1_8_1_3_4_1_8_2_7_6_3_3_2_7_5_3_3_7_4_1_5_5_4_3_6_6_7_1_6_3_3_3_2_6_2_6_1_1_2_1_4_5_5_1_9_2_1_2_2_2_2_2_1_6_1_4_5_3_3_9_3_2_1_3_6_5_2_7_2_7_2_2_3_9_6_3_5_8_1_6_7_4_2_5_7_4_1_1_9_3_4_4_5_4_1_6_1_2_5_4_4_2_1_8_7_4_1_1_4_7_4_1_1_4_2_5_8_6_8_6_2_4_5_1_9_8_8_9_1_2_1_6_1_2_7_4_1_7_5_7_8_2_7_6_2_8_7_3_4_8_2_7_4_8_1_1_2_3_2_1_4_4_5_1_2_9_1_4_3_1_6_4_4_3_4_6_7_4_5_2_4_7_4_4_8_2_4_8_7_1_2_4_5_3_3_2_5_2_8_8_4_9_9_3_2_2_4_4_2_2_7_7_6_6_3_9_7_4_1_1_2_1_4_6_6_6_3_3_3_3_8_1_1_1_5_9_4_4_6_4_8_9_1_2_2_2_3_9_3_1_5_4_1_1_7_2_3_3_1_7_1_2_1_2_2_1_3_3_4_1_2_3_1_4_1_2_9_5_3_3_1_1_2_5_6_3_4_1_5_3_3_8_1_8_6_9_7_1_5_5_8_4_6_7_9_9_9_3_2_3_3_1_4_6_7_8_6_2_3_1_2_2_5_1_9_2_6_4_2_2_3_7_3_2_6_8_1_5_5_6_2_6_3_4_4_1_1_1_7_7_6_3_5_8_6_9_6_2_4_2_6_3_5_8_4_4_7_5_6_8_2_3_3_9_9_2_2_9_9_4_1_5_5_5_8_1_8_9_2_2_2_3_8_8_1_6_1_2_1_9_9_6_3_5_7_7_1_1_4_6_6_3_2_1_4_5_8_3_9_5_9_4_2_1_4_4_7_2_3_8_7_2_5_2_2_6_4_8_8_3_3_3_7_4_7_5_5_5_1_6_2_5_4_8_1_1_1_3_3_6_2_4_6_6_6_8_4_8_4</t>
   </si>
   <si>
     <t>8_1_2_9_8_5_4_6_8_5_3_2_9_4_1_1_2_3_4_8_6_3_2_5_9_1_1_4_3_4_4_5_3_4_1_9_3_9_5_5_8_5_5_6_7_1_5_1_7_7_3_3_3_7_7_2_4_2_8_1_4_5_6_8_4_1_3_1_7_2_6_7_8_3_1_4_4_5_8_1_7_9_4_7_9_2_3_3_7_7_1_8_3_2_8_8_8_3_2_8_1_5_6_3_8_8_4_1_3_1_5_6_1_1_3_2_6_3_4_3_4_2_2_4_7_5_4_7_3_1_2_8_5_7_1_7_1_6_5_3_2_6_7_4_9_4_8_7_7_4_9_1_4_1_1_5_4_3_7_7_1_2_2_8_6_7_4_3_7_6_4_2_3_4_7_3_3_1_4_9_5_5_3_1_1_2_1_6_7_8_5_9_8_5_2_5_3_6_8_6_4_5_7_6_5_8_7_3_7_1_2_3_6_9_2_8_6_8_5_8_2_7_2_5_3_1_8_8_4_6_6_3_7_3_1_2_6_2_1_9_2_3_2_1_7_1_4_9_5_2_7_1_6_3_5_9_2_3_6_2_4_7_8_3_2_9_4_8_1_2_9_7_1_6_6_8_5_1_3_4_2_3_3_2_7_3_6_2_1_8_1_7_3_2_9_2_7_7_7_3_2_4_8_8_2_3_4_2_4_2_6_5_2_8_8_1_8_3_7_5_5_3_5_1_4_3_8_2_2_2_5_3_2_4_4_2_7_3_7_7_6_3_7_6_5_9_1_1_8_3_6_8_3_7_2_4_6_8_2_4_6_6_4_9_1_1_6_5_8_8_5_4_1_6_2_1_1_2_3_1_4_6_4_5_7_1_6_6_7_6_3_2_1_1_6_5_3_8_2_3_1_5_2_4_1_2_2_9_1_8_3_3_9_6_9_8_6_2_3_4_8_4_3_1_3_5_7_5_2_6_7_2_3_1_7_4_4_3_6_7_3_2_8_8_2_1_5_3_2_1_9_7_2_6_4_4_8_1_2_1_9_2_4_2_1_1_4_7_4_1_3_5_9_6_4_8_3_4_3_2_2_7_3_9_3_5_7_1_1_2_6_6_1_5_9_7_8_5_1_7</t>
   </si>
   <si>
-    <t>2_1_3_2_2_2_2_9_1_8_1_7_1_6_4_9_8_4_6_2_5_5_5_3_1_8_2_5_1_6_4_7_8_3_7_8_6_1_5_5_5_4_2_3_4_9_2_8_4_3_5_7_2_2_2_8_5_9_9_5_8_3_3_7_2_8_6_6_1_6_1_1_4_6_7_6_4_1_4_4_1_6_7_3_3_4_1_2_3_4_5_8_1_2_2_3_6_8_7_4_1_8_1_7_8_7_1_8_8_6_3_4_2_5_6_6_1_1_1_6_7_7_1_3_2_1_1_1_1_8_2_4_1_3_1_7_5_4_6_1_2_2_5_7_8_1_8_2_4_4_7_7_2_3_8_2_9_8_7_7_7_9_5_5_7_7_7_1_5_2_2_3_5_5_1_1_5_5_5_2_9_9_7_3_6_6_5_2_4_4_9_2_1_3_2_1_4_2_6_5_4_8_4_6_9_7_7_8_8_4_4_8_3_6_4_6_2_2_7_6_7_3_5_1_1_1_4_3_7_5_3_3_1_3_1_1_1_9_9_3_1_4_4_7_7_6_6_7_1_3_2_3_3_3_6_2_6_9_4_4_8_4_6_7_9_7_1_6_6_4_4_1_3_6_6_6_6_2_1_3_6_2_5_4_4_9_7_6_4_3_3_7_6_6_1_3_8_1_6_3_7_1_4_2_3_4_9_5_3_8_1_5_2_6_4_2_3_2_4_3_6_6_5_4_4_9_5_1_9_9_7_7_4_3_7_6_6_1_6_6_1_3_3_2_1_8_3_9_3_3_7_4_6_5_2_6_9_4_4_3_6_5_3_4_2_3_8_3_4_1_4_6_1_8_3_4_5_3_8_1_5_5_4_3_3_1_8_2_8_3_2_1_4_3_3_4_1_8_3_2_2_3_7_8_1_1_8_8_4_7_2_1_5_8_5_7_1_2_4_5_5_6_3_5_2_2_2_3_3_6_3_2_4_1_6_6_6_6_2_3_5_1_6_6_8_1_3_1_3_5_3_5_1_1_8_2_6_6_3_7_7_5_2_3_7_5_4_9_6_9_9_8_9_1_1_6_3_8_8_4_2_6_7_3_2_2_7_8_3_1_2_1_2_7_1_7_3_7_5_4</t>
+    <t>4_6_2_5_3_3_9_2_9_9_7_2_4_1_4_1_8_6_6_4_1_5_1_1_9_5_6_6_2_3_7_6_9_1_9_2_2_9_2_7_7_4_6_6_6_4_6_7_1_8_4_1_3_6_9_5_6_2_2_3_1_2_2_7_3_2_3_3_3_1_5_3_6_8_9_9_6_6_1_1_3_2_3_5_3_1_9_3_3_1_7_2_2_4_1_8_2_5_7_2_6_2_2_3_7_3_6_6_2_1_1_3_4_7_5_6_1_5_7_1_9_1_1_9_4_4_7_4_1_9_2_1_1_6_2_1_5_5_7_7_1_7_1_4_1_6_3_2_1_8_8_6_2_3_4_7_1_1_8_9_1_2_7_6_8_2_5_2_3_1_4_3_2_1_9_2_2_6_3_2_1_6_9_3_3_1_4_5_6_3_3_1_6_1_3_1_3_3_2_7_1_5_1_1_1_1_6_9_5_8_5_3_2_3_6_1_3_1_6_6_8_5_6_1_8_2_2_3_5_2_6_4_2_2_6_7_7_1_6_7_3_1_3_3_5_1_1_1_3_3_5_5_5_5_3_2_6_1_8_4_7_1_1_3_3_5_6_9_4_6_1_6_9_8_7_6_1_2_1_4_5_7_2_6_3_6_6_5_8_1_4_7_5_1_7_7_6_1_6_7_4_1_1_3_2_2_2_3_5_6_6_8_8_2_6_9_4_7_2_5_2_1_1_3_2_2_1_4_3_5_1_3_3_5_4_1_3_2_4_3_1_2_4_2_3_7_7_6_5_5_2_5_8_2_2_8_3_1_3_3_1_6_8_4_8_1_7_8_4_4_2_2_2_1_3_1_8_6_8_1_8_4_4_3_5_4_2_1_2_2_8_2_9_8_8_8_9_6_6_7_4_1_9_9_3_1_4_8_2_8_1_6_4_2_7_2_2_5_5_6_1_5_1_1_3_2_4_4_8_3_4_4_3_7_5_5_3_1_1_2_3_1_6_6_6_2_3_3_8_3_2_4_2_8_2_1_4_4_2_3_2_5_6_2_5_2_4_6_3_1_8_7_5_5_6_6_5_4_1_1_3_2_6_7_8_6_4_2_3_5_1_4_7_3_8_4_4_4_1_6</t>
   </si>
   <si>
     <t>6_7_6_1_8_8_2_8_6_8_8_8_5_8_6_1_5_2_5_3_4_4_9_5_8_5_1_1_8_4_7_2_2_9_5_1_4_2_5_5_9_8_4_6_6_5_6_9_7_9_7_2_8_6_4_2_6_7_1_4_6_8_2_2_7_3_2_1_4_3_1_6_2_4_5_7_1_9_7_6_2_3_6_1_1_6_3_3_7_1_7_3_2_4_9_4_2_5_7_4_6_7_4_1_2_6_6_6_2_2_1_4_1_2_3_8_4_3_2_9_2_1_3_6_8_1_4_1_9_1_6_5_7_8_3_9_6_1_9_8_3_7_7_7_5_9_5_2_9_9_5_2_2_8_5_2_8_8_1_6_8_6_1_7_2_1_1_5_8_1_8_2_4_3_4_8_4_2_7_5_3_4_9_1_6_4_1_4_7_1_4_4_8_8_4_1_7_5_5_8_6_4_5_9_7_2_4_7_1_4_2_1_4_4_6_1_2_4_6_2_6_4_7_3_7_9_3_2_4_5_1_2_5_2_8_1_7_1_7_2_7_1_8_4_6_6_4_1_9_4_7_1_2_5_1_5_3_2_7_2_8_1_1_1_3_9_4_6_2_3_3_4_8_2_8_6_7_8_8_3_5_2_8_5_9_4_2_6_9_3_2_3_1_5_7_7_5_9_3_2_1_3_4_8_6_5_2_3_7_8_7_7_3_4_1_1_6_5_6_8_7_9_9_3_7_5_6_1_1_9_4_2_3_5_4_4_1_2_2_3_2_3_2_1_2_5_4_5_3_5_7_4_3_7_2_7_7_1_8_1_4_1_5_7_1_1_5_4_4_9_7_6_2_1_4_5_8_2_4_2_2_6_2_1_3_2_2_5_5_1_5_2_5_4_4_9_1_9_9_4_4_1_4_3_2_1_7_2_4_1_7_4_6_7_1_7_3_5_2_2_4_4_4_3_4_6_8_4_1_2_2_3_8_2_4_2_2_4_8_2_2_4_7_3_4_1_4_6_6_3_2_9_9_5_5_8_2_1_1_7_3_5_3_5_5_2_1_7_8_7_2_2_8_1_1_2_2_2_3_8_8_2_2_3_4_8_6_5_1_2_4_1_8_3_6_3_1_4_6_7</t>
   </si>
   <si>
-    <t>6_4_9_5_6_1_1_1_7_1_2_3_2_1_4_4_1_6_6_8_5_6_5_1_5_6_3_3_4_9_6_2_4_7_7_3_3_7_3_4_2_5_7_5_6_8_4_2_3_3_2_3_9_4_2_2_8_4_4_8_7_5_3_8_5_4_1_1_5_2_8_3_1_4_1_1_9_1_9_3_4_4_8_6_1_6_9_7_5_9_9_6_6_2_3_1_2_2_6_8_3_2_1_4_5_5_5_2_2_1_1_4_5_7_1_2_5_5_5_6_3_5_3_3_1_1_5_9_3_3_7_7_3_3_4_3_3_3_3_9_6_4_3_1_1_1_2_7_7_6_4_5_3_5_2_1_2_8_7_7_7_1_9_3_3_1_5_2_8_8_8_5_3_6_6_7_2_6_6_4_4_4_2_8_3_3_6_2_8_4_1_6_6_4_2_4_7_8_6_6_2_8_3_7_7_3_1_1_5_2_6_6_4_4_6_2_8_7_6_1_2_7_5_2_8_4_4_4_7_9_1_4_8_1_5_3_1_2_4_1_2_2_8_8_8_6_6_1_6_2_1_9_9_1_2_2_9_5_3_9_4_4_4_8_8_3_4_9_1_3_1_2_4_5_4_2_2_4_3_9_7_2_5_7_7_1_3_3_3_3_4_9_4_4_5_2_6_5_9_3_1_1_5_1_6_5_8_9_7_3_8_4_1_6_6_9_7_1_1_5_9_5_2_2_5_9_3_1_4_2_6_3_8_1_4_4_2_2_2_3_2_9_1_6_5_5_5_7_3_6_8_8_5_5_3_3_1_1_3_3_3_1_5_4_3_9_6_5_5_3_4_1_2_3_6_3_7_3_1_1_6_9_1_2_4_9_8_8_7_4_6_4_1_4_5_2_7_7_6_6_8_3_9_7_5_4_6_6_4_9_1_8_4_6_5_4_1_7_4_5_6_1_2_1_3_1_2_1_1_4_1_4_3_6_6_1_2_6_4_6_4_9_9_7_9_2_5_4_4_1_7_7_7_9_3_1_4_2_3_1_1_7_2_8_7_7_3_4_1_1_3_8_3_8_8_8_3_4_4_5_3_6_6_5_7_1_1_9_2_1_1_5_2_2_3_9_2_1_8_3</t>
+    <t>8_1_8_2_4_6_4_8_1_1_6_7_9_1_7_3_6_2_2_7_8_8_1_1_1_2_7_5_6_2_1_8_8_6_2_9_3_6_8_2_2_3_6_1_8_4_4_6_6_2_2_8_4_3_3_2_7_2_6_5_3_5_1_7_4_1_3_2_3_5_1_2_2_3_7_5_2_7_9_6_1_2_1_8_4_5_3_4_1_1_6_6_9_7_5_5_6_8_1_1_1_7_2_4_4_4_2_8_2_8_8_6_7_5_4_4_3_1_7_7_2_1_1_5_4_6_7_3_2_1_1_1_5_4_1_5_1_2_2_2_8_3_8_6_1_4_4_4_1_4_4_6_7_1_6_2_3_8_5_1_1_1_5_5_5_1_1_2_5_6_2_1_1_5_8_8_8_2_2_2_1_9_1_2_2_4_4_4_1_2_1_2_2_4_3_3_4_3_3_2_3_3_1_1_1_7_3_3_6_6_4_3_3_6_5_4_4_4_3_2_6_7_3_6_7_7_7_8_1_1_4_5_4_1_1_4_8_9_1_4_1_4_5_7_7_3_3_4_5_1_4_1_9_9_5_5_6_8_3_4_7_2_8_2_4_3_1_4_6_8_8_6_8_9_2_8_8_3_1_3_6_4_3_1_3_5_9_4_8_2_2_9_1_4_1_7_3_2_2_5_5_5_2_1_2_9_1_5_3_4_4_7_9_2_2_5_2_4_2_2_4_6_9_2_8_6_1_3_3_9_8_6_2_6_6_8_4_5_2_9_1_2_9_3_1_2_2_6_6_1_7_7_7_8_6_2_5_7_1_1_1_1_3_3_8_8_1_1_6_6_6_5_5_2_7_8_7_3_2_6_9_2_8_8_2_1_2_3_1_6_6_5_3_6_6_6_3_1_3_1_5_5_8_2_9_9_4_2_4_4_4_4_6_9_1_4_1_3_6_2_3_1_1_3_2_2_2_7_7_5_5_5_3_2_1_2_2_9_5_2_4_4_8_2_3_4_2_5_5_6_1_2_9_7_8_5_5_7_7_3_1_5_8_3_7_1_8_1_3_9_1_3_8_6_6_6_1_4_2_7_2_9_3_3_7_6_3_6_7_5_5_7_2_3_8_1_2_5_2_9</t>
   </si>
   <si>
     <t>4_7_8_5_7_7_6_4_3_9_3_1_4_4_5_5_5_7_1_6_3_1_3_5_2_1_1_9_2_9_6_1_8_3_4_5_4_2_1_6_4_2_8_7_4_8_6_5_9_1_2_8_8_9_4_6_6_1_6_7_8_1_5_8_6_4_8_9_3_1_4_4_1_5_5_8_5_4_6_2_8_1_9_3_7_9_2_5_5_7_1_2_9_8_1_3_4_7_8_4_9_1_1_2_5_4_6_5_7_2_7_7_6_5_5_5_1_4_2_1_9_3_4_3_3_3_4_1_5_3_4_6_5_4_6_9_6_1_2_1_8_1_2_4_9_2_5_8_2_5_2_1_5_7_1_1_2_2_6_2_9_3_3_6_6_6_2_5_8_1_6_2_4_2_6_8_9_4_7_3_4_5_7_4_2_1_2_6_6_1_6_2_4_7_6_2_1_1_8_1_7_8_8_9_1_7_9_5_4_3_3_5_2_2_7_7_6_1_3_8_9_1_9_3_3_4_2_5_1_5_2_7_3_6_2_4_2_2_9_1_5_7_2_3_3_9_3_5_3_1_6_2_9_6_3_3_1_3_5_6_3_4_2_4_6_1_1_7_3_4_4_4_3_4_7_3_6_8_3_2_4_1_2_1_4_8_5_5_4_4_8_8_1_4_5_4_9_7_1_8_9_3_5_2_4_1_4_7_4_9_1_1_9_3_2_5_2_2_2_4_5_6_5_2_6_9_6_2_8_4_2_7_7_6_3_3_8_7_6_2_4_7_1_1_9_6_2_8_2_8_4_9_5_4_1_3_1_5_7_9_7_8_1_1_2_4_6_5_8_2_2_2_3_2_4_2_2_3_6_1_7_5_3_7_4_1_1_4_7_4_1_2_9_6_2_4_1_8_2_6_4_6_3_1_4_2_3_8_2_4_3_4_5_9_5_5_8_1_3_1_7_3_1_7_7_3_5_1_3_8_7_8_2_2_5_3_3_4_8_6_1_6_8_4_1_8_2_4_5_7_1_6_4_5_6_5_4_2_6_2_7_1_1_5_2_1_7_6_2_3_3_3_8_1_4_6_2_9_3_2_2_6_7_1_6_1_3_9_2_5_6_2_3_2_1_8_4_5_3_9</t>
@@ -578,6 +578,9 @@
   </si>
   <si>
     <t>5_1_7_6_2_1_2_2_4_3_4_1_1_4_1_4_5_2_7_6_6_6_3_3_1_2_4_2_3_1_2_4_3_2_7_2_4_3_4_1_3_4_1_2_4_4_1_6_3_4_3_3_2_5_1_2_1_4_1_2_3_2_3_1_5_2_4_6_4_3_7_1_5_3_2_3_7_4_4_5_2_1_1_2_3_5_1_1_6_5_1_4_5_6_2_3_1_2_1_4_3_7_3_5_2_1_2_6_6_2_5_3_4_4_1_1_2_7_6_3_2_3_1_1_5_5_5_4_6_4_2_3_3_3_5_2_1_1_1_1_5_1_6_6_3_4_6_1_3_3_6_3_4_2_3_1_1_2_2_1_2_7_4_4_1_2_2_2_2_7_6_2_2_3_5_1_1_7_6_5_1_1_1_2_5_4_5_7_1_1_1_3_2_1_5_5_3_4_4_7_2_6_1_2_2_5_7_5_1_5_3_1_3_3_2_1_1_1_1_4_1_3_1_4_2_1_5_2_5_6_1_1_6_6_5_4_3_6_6_3_3_4_5_4_5_3_5_1_3_7_1_2_1_1_3_6_1_5_3_4_6_3_7_1_1_2_1_4_2_3_2_1_1_3_3_4_3_1_1_4_5_4_1_4_4_7_2_4_6_2_3_2_4_1_5_4_2_4_1_4_6_2_1_4_1_1_1_7_1_6_6_6_2_2_6_2_1_4_3_1_5_2_4_4_2_4_1_6_2_3_1_1_1_4_3_1_2_7_2_7_5_1_1_4_4_6_4_5_6_2_1_3_1_6_6_4_2_2_2_5_6_2_6_6_1_2_4_1_1_1_6_1_2_7_3_5_1_1_3_1_4_3_6_6_5_3_4_2_3_2_3_1_3_3_1_5_1_2_6_6_3_5_5_1_3_3_1_4_2_1_4_5_1_6_2_4_4_3_4_3_2_6_6_3_4_1_5_5_3_1_4_1_1_4_5_6_2_2_1_3_4_4_1_5_2_2_3_1_7_3_4_6_2_4_2_3_2_3_6_3_2_6_2_4_7_5_3_3_7_5_2_3_1_5_3_2_5_2_1_2_2_1_5_3_1_4_4_5_2_3_3_3_3_1_4_2_4_2_6_4</t>
+  </si>
+  <si>
+    <t>13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13_13</t>
   </si>
   <si>
     <t>8_13_13_13_8_13_13_13_8_13_13_13_13_13_13_13_13_13_8_8_8_13_8_8_8_8_8_13_8_8_8_8_13_13_13_13_8_8_8_13_13_8_8_8_8_8_8_13_8_8_13_8_8_8_13_13_8_13_13_8_8_8_13_8_8_8_8_8_13_13_8_8_13_8_8_13_8_8_8_8_13_8_8_13_13_13_8_13_13_13_8_8_8_13_13_13_8_8_13_13_13_13_8_8_8_8_13_13_13_13_8_13_13_8_8_8_8_13_13_13_13_8_13_8_13_8_8_8_13_13_8_13_8_8_8_13_13_8_8_13_8_8_13_13_13_8_8_13_13_13_13_8_8_8_8_13_13_13_8_13_8_13_8_13_8_8_8_8_8_8_13_13_8_13_8_13_13_8_8_13_8_13_8_8_13_13_8_8_8_8_8_8_8_8_8_13_8_13_13_13_8_13_8_13_13_13_8_13_13_13_13_8_13_13_13_8_8_8_13_13_13_13_13_13_13_8_8_8_8_13_8_8_8_8_8_13_8_8_8_8_13_8_8_8_13_8_13_8_13_8_13_8_8_8_13_8_8_13_8_13_8_13_8_8_13_13_8_8_8_8_8_8_8_13_8_13_8_8_13_13_13_13_13_13_13_13_13_8_13_8_8_8_8_8_8_13_13_13_8_13_13_8_8_8_13_13_13_13_8_13_13_13_13_13_8_8_13_8_13_13_8_8_8_13_13_13_13_8_8_8_13_8_8_13_8_8_8_13_13_8_13_13_8_8_8_8_8_13_8_13_8_8_13_13_13_8_13_13_13_8_13_8_8_8_8_8_8_8_13_8_13_13_8_13_8_8_13_8_13_13_13_8_8_13_13_8_13_8_13_8_8_8_13_13_13_13_8_8_8_13_13_8_8_13_8_13_13_8_8_13_8_13_8_13_13_13_13_8_13_13_8_8_13_13_8_13_8_13_13_13_8_8_13_13_13_8_8_13_13_8_13_8_13_13_8_13_8_13_13_8_13_13_8_8_8_8_13_13_13_13_8_8_8_8_13_8_8_13_8_13_13_8_13_8_8_8_8_13_8_8_8_8_13_8_13_13_13_8_13_13_13_13_8_13_13_8_8_8_13_8</t>
@@ -1294,7 +1297,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1379,6 +1382,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -5046,14 +5052,14 @@
       <c r="F99" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G99" s="1" t="s">
+      <c r="G99" s="34" t="s">
         <v>166</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J99" s="17"/>
       <c r="K99" s="17"/>
@@ -5078,14 +5084,14 @@
       <c r="F100" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G100" s="1" t="s">
-        <v>167</v>
+      <c r="G100" s="34" t="s">
+        <v>166</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J100" s="17"/>
       <c r="K100" s="17"/>
@@ -5110,14 +5116,14 @@
       <c r="F101" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G101" s="1" t="s">
-        <v>168</v>
+      <c r="G101" s="34" t="s">
+        <v>166</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J101" s="17"/>
       <c r="K101" s="17"/>
@@ -5238,14 +5244,14 @@
       <c r="F105" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G105" s="1" t="s">
+      <c r="G105" s="34" t="s">
         <v>166</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J105" s="17"/>
       <c r="K105" s="17"/>
@@ -5270,14 +5276,14 @@
       <c r="F106" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G106" s="1" t="s">
-        <v>167</v>
+      <c r="G106" s="34" t="s">
+        <v>166</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J106" s="17"/>
       <c r="K106" s="17"/>
@@ -5302,14 +5308,14 @@
       <c r="F107" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G107" s="1" t="s">
-        <v>168</v>
+      <c r="G107" s="34" t="s">
+        <v>166</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J107" s="17"/>
       <c r="K107" s="17"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="173">
   <si>
     <t>id</t>
   </si>
@@ -1912,7 +1912,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -4746,17 +4746,17 @@
     </row>
     <row r="90" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A90" s="6">
-        <f t="shared" ref="A90:A107" si="5">C90*10+D90</f>
-        <v>20340014</v>
+        <f>C90*10+D90</f>
+        <v>20340021</v>
       </c>
       <c r="B90" s="14">
         <v>103400</v>
       </c>
       <c r="C90" s="33">
-        <v>2034001</v>
+        <v>2034002</v>
       </c>
       <c r="D90" s="33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E90" s="18" t="s">
         <v>59</v>
@@ -4765,7 +4765,7 @@
         <v>20</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>20</v>
@@ -4778,17 +4778,17 @@
     </row>
     <row r="91" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A91" s="6">
-        <f t="shared" si="5"/>
-        <v>20340015</v>
+        <f>C91*10+D91</f>
+        <v>20340022</v>
       </c>
       <c r="B91" s="14">
         <v>103400</v>
       </c>
       <c r="C91" s="33">
-        <v>2034001</v>
+        <v>2034002</v>
       </c>
       <c r="D91" s="33">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E91" s="18" t="s">
         <v>59</v>
@@ -4797,30 +4797,30 @@
         <v>20</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J91" s="17"/>
       <c r="K91" s="17"/>
     </row>
     <row r="92" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A92" s="6">
-        <f t="shared" si="5"/>
-        <v>20340016</v>
+        <f>C92*10+D92</f>
+        <v>20340023</v>
       </c>
       <c r="B92" s="14">
         <v>103400</v>
       </c>
       <c r="C92" s="33">
-        <v>2034001</v>
+        <v>2034002</v>
       </c>
       <c r="D92" s="33">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E92" s="18" t="s">
         <v>59</v>
@@ -4835,24 +4835,24 @@
         <v>20</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J92" s="17"/>
       <c r="K92" s="17"/>
     </row>
     <row r="93" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A93" s="6">
-        <f t="shared" si="5"/>
-        <v>20340017</v>
+        <f>C93*10+D93</f>
+        <v>20340031</v>
       </c>
       <c r="B93" s="14">
         <v>103400</v>
       </c>
       <c r="C93" s="33">
-        <v>2034001</v>
+        <v>2034003</v>
       </c>
       <c r="D93" s="33">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E93" s="18" t="s">
         <v>59</v>
@@ -4861,30 +4861,30 @@
         <v>20</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J93" s="17"/>
       <c r="K93" s="17"/>
     </row>
     <row r="94" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A94" s="6">
-        <f t="shared" si="5"/>
-        <v>20340018</v>
+        <f>C94*10+D94</f>
+        <v>20340032</v>
       </c>
       <c r="B94" s="14">
         <v>103400</v>
       </c>
       <c r="C94" s="33">
-        <v>2034001</v>
+        <v>2034003</v>
       </c>
       <c r="D94" s="33">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E94" s="18" t="s">
         <v>59</v>
@@ -4893,30 +4893,30 @@
         <v>20</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J94" s="17"/>
       <c r="K94" s="17"/>
     </row>
     <row r="95" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A95" s="6">
-        <f t="shared" si="5"/>
-        <v>20340019</v>
+        <f>C95*10+D95</f>
+        <v>20340033</v>
       </c>
       <c r="B95" s="14">
         <v>103400</v>
       </c>
       <c r="C95" s="33">
-        <v>2034001</v>
+        <v>2034003</v>
       </c>
       <c r="D95" s="33">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E95" s="18" t="s">
         <v>59</v>
@@ -4931,394 +4931,778 @@
         <v>20</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J95" s="17"/>
       <c r="K95" s="17"/>
     </row>
     <row r="96" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A96" s="6">
-        <f t="shared" si="5"/>
-        <v>20350011</v>
+        <f>C96*10+D96</f>
+        <v>20340041</v>
       </c>
       <c r="B96" s="14">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C96" s="33">
-        <v>2035001</v>
+        <v>2034004</v>
       </c>
       <c r="D96" s="33">
         <v>1</v>
       </c>
       <c r="E96" s="18" t="s">
-        <v>159</v>
+        <v>59</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="J96" s="17"/>
       <c r="K96" s="17"/>
     </row>
     <row r="97" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A97" s="6">
+        <f>C97*10+D97</f>
+        <v>20340042</v>
+      </c>
+      <c r="B97" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C97" s="33">
+        <v>2034004</v>
+      </c>
+      <c r="D97" s="33">
+        <v>2</v>
+      </c>
+      <c r="E97" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J97" s="17"/>
+      <c r="K97" s="17"/>
+    </row>
+    <row r="98" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A98" s="6">
+        <f>C98*10+D98</f>
+        <v>20340043</v>
+      </c>
+      <c r="B98" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C98" s="33">
+        <v>2034004</v>
+      </c>
+      <c r="D98" s="33">
+        <v>3</v>
+      </c>
+      <c r="E98" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J98" s="17"/>
+      <c r="K98" s="17"/>
+    </row>
+    <row r="99" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A99" s="6">
+        <f>C99*10+D99</f>
+        <v>20340051</v>
+      </c>
+      <c r="B99" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C99" s="33">
+        <v>2034005</v>
+      </c>
+      <c r="D99" s="33">
+        <v>1</v>
+      </c>
+      <c r="E99" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J99" s="17"/>
+      <c r="K99" s="17"/>
+    </row>
+    <row r="100" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A100" s="6">
+        <f>C100*10+D100</f>
+        <v>20340052</v>
+      </c>
+      <c r="B100" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C100" s="33">
+        <v>2034005</v>
+      </c>
+      <c r="D100" s="33">
+        <v>2</v>
+      </c>
+      <c r="E100" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J100" s="17"/>
+      <c r="K100" s="17"/>
+    </row>
+    <row r="101" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A101" s="6">
+        <f>C101*10+D101</f>
+        <v>20340053</v>
+      </c>
+      <c r="B101" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C101" s="33">
+        <v>2034005</v>
+      </c>
+      <c r="D101" s="33">
+        <v>3</v>
+      </c>
+      <c r="E101" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J101" s="17"/>
+      <c r="K101" s="17"/>
+    </row>
+    <row r="102" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A102" s="6">
+        <f>C102*10+D102</f>
+        <v>20340061</v>
+      </c>
+      <c r="B102" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C102" s="33">
+        <v>2034006</v>
+      </c>
+      <c r="D102" s="33">
+        <v>1</v>
+      </c>
+      <c r="E102" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J102" s="17"/>
+      <c r="K102" s="17"/>
+    </row>
+    <row r="103" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A103" s="6">
+        <f>C103*10+D103</f>
+        <v>20340062</v>
+      </c>
+      <c r="B103" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C103" s="33">
+        <v>2034006</v>
+      </c>
+      <c r="D103" s="33">
+        <v>2</v>
+      </c>
+      <c r="E103" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J103" s="17"/>
+      <c r="K103" s="17"/>
+    </row>
+    <row r="104" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A104" s="6">
+        <f>C104*10+D104</f>
+        <v>20340063</v>
+      </c>
+      <c r="B104" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C104" s="33">
+        <v>2034006</v>
+      </c>
+      <c r="D104" s="33">
+        <v>3</v>
+      </c>
+      <c r="E104" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J104" s="17"/>
+      <c r="K104" s="17"/>
+    </row>
+    <row r="105" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A105" s="6">
+        <f>C105*10+D105</f>
+        <v>20340071</v>
+      </c>
+      <c r="B105" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C105" s="33">
+        <v>2034007</v>
+      </c>
+      <c r="D105" s="33">
+        <v>1</v>
+      </c>
+      <c r="E105" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J105" s="17"/>
+      <c r="K105" s="17"/>
+    </row>
+    <row r="106" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A106" s="6">
+        <f>C106*10+D106</f>
+        <v>20340072</v>
+      </c>
+      <c r="B106" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C106" s="33">
+        <v>2034007</v>
+      </c>
+      <c r="D106" s="33">
+        <v>2</v>
+      </c>
+      <c r="E106" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J106" s="17"/>
+      <c r="K106" s="17"/>
+    </row>
+    <row r="107" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A107" s="6">
+        <f>C107*10+D107</f>
+        <v>20340073</v>
+      </c>
+      <c r="B107" s="14">
+        <v>103400</v>
+      </c>
+      <c r="C107" s="33">
+        <v>2034007</v>
+      </c>
+      <c r="D107" s="33">
+        <v>3</v>
+      </c>
+      <c r="E107" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J107" s="17"/>
+      <c r="K107" s="17"/>
+    </row>
+    <row r="108" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A108" s="6">
+        <f t="shared" ref="A108:A119" si="5">C108*10+D108</f>
+        <v>20350011</v>
+      </c>
+      <c r="B108" s="14">
+        <v>103500</v>
+      </c>
+      <c r="C108" s="33">
+        <v>2035001</v>
+      </c>
+      <c r="D108" s="33">
+        <v>1</v>
+      </c>
+      <c r="E108" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J108" s="17"/>
+      <c r="K108" s="17"/>
+    </row>
+    <row r="109" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A109" s="6">
         <f t="shared" si="5"/>
         <v>20350012</v>
       </c>
-      <c r="B97" s="14">
+      <c r="B109" s="14">
         <v>103500</v>
       </c>
-      <c r="C97" s="33">
+      <c r="C109" s="33">
         <v>2035001</v>
       </c>
-      <c r="D97" s="33">
+      <c r="D109" s="33">
         <v>2</v>
       </c>
-      <c r="E97" s="18" t="s">
+      <c r="E109" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F97" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G97" s="1" t="s">
+      <c r="F109" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G109" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="H97" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I97" s="1" t="s">
+      <c r="H109" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I109" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="J97" s="17"/>
-      <c r="K97" s="17"/>
-    </row>
-    <row r="98" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A98" s="6">
+      <c r="J109" s="17"/>
+      <c r="K109" s="17"/>
+    </row>
+    <row r="110" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A110" s="6">
         <f t="shared" si="5"/>
         <v>20350013</v>
       </c>
-      <c r="B98" s="14">
+      <c r="B110" s="14">
         <v>103500</v>
       </c>
-      <c r="C98" s="33">
+      <c r="C110" s="33">
         <v>2035001</v>
       </c>
-      <c r="D98" s="33">
+      <c r="D110" s="33">
         <v>3</v>
       </c>
-      <c r="E98" s="18" t="s">
+      <c r="E110" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="F98" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G98" s="1" t="s">
+      <c r="F110" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G110" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="H98" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I98" s="1" t="s">
+      <c r="H110" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I110" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J98" s="17"/>
-      <c r="K98" s="17"/>
-    </row>
-    <row r="99" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A99" s="6">
+      <c r="J110" s="17"/>
+      <c r="K110" s="17"/>
+    </row>
+    <row r="111" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A111" s="6">
         <f t="shared" si="5"/>
         <v>20350021</v>
       </c>
-      <c r="B99" s="14">
+      <c r="B111" s="14">
         <v>103500</v>
       </c>
-      <c r="C99" s="33">
+      <c r="C111" s="33">
         <v>2035002</v>
       </c>
-      <c r="D99" s="33">
+      <c r="D111" s="33">
         <v>1</v>
       </c>
-      <c r="E99" s="18" t="s">
+      <c r="E111" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="F99" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G99" s="34" t="s">
+      <c r="F111" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G111" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="H99" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I99" s="1" t="s">
+      <c r="H111" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I111" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="J99" s="17"/>
-      <c r="K99" s="17"/>
-    </row>
-    <row r="100" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A100" s="6">
+      <c r="J111" s="17"/>
+      <c r="K111" s="17"/>
+    </row>
+    <row r="112" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A112" s="6">
         <f t="shared" si="5"/>
         <v>20350022</v>
       </c>
-      <c r="B100" s="14">
+      <c r="B112" s="14">
         <v>103500</v>
       </c>
-      <c r="C100" s="33">
+      <c r="C112" s="33">
         <v>2035002</v>
       </c>
-      <c r="D100" s="33">
+      <c r="D112" s="33">
         <v>2</v>
       </c>
-      <c r="E100" s="18" t="s">
+      <c r="E112" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="F100" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G100" s="34" t="s">
+      <c r="F112" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G112" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="H100" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I100" s="1" t="s">
+      <c r="H112" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I112" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="J100" s="17"/>
-      <c r="K100" s="17"/>
-    </row>
-    <row r="101" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A101" s="6">
+      <c r="J112" s="17"/>
+      <c r="K112" s="17"/>
+    </row>
+    <row r="113" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A113" s="6">
         <f t="shared" si="5"/>
         <v>20350023</v>
       </c>
-      <c r="B101" s="14">
+      <c r="B113" s="14">
         <v>103500</v>
       </c>
-      <c r="C101" s="33">
+      <c r="C113" s="33">
         <v>2035002</v>
       </c>
-      <c r="D101" s="33">
+      <c r="D113" s="33">
         <v>3</v>
       </c>
-      <c r="E101" s="18" t="s">
+      <c r="E113" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="F101" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G101" s="34" t="s">
+      <c r="F113" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G113" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="H101" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I101" s="1" t="s">
+      <c r="H113" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I113" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="J101" s="17"/>
-      <c r="K101" s="17"/>
-    </row>
-    <row r="102" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A102" s="6">
+      <c r="J113" s="17"/>
+      <c r="K113" s="17"/>
+    </row>
+    <row r="114" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A114" s="6">
         <f t="shared" si="5"/>
         <v>20350111</v>
       </c>
-      <c r="B102" s="14">
+      <c r="B114" s="14">
         <v>103501</v>
       </c>
-      <c r="C102" s="33">
+      <c r="C114" s="33">
         <v>2035011</v>
       </c>
-      <c r="D102" s="33">
+      <c r="D114" s="33">
         <v>1</v>
       </c>
-      <c r="E102" s="18" t="s">
+      <c r="E114" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="F102" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G102" s="1" t="s">
+      <c r="F114" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G114" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="H102" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I102" s="1" t="s">
+      <c r="H114" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I114" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="J102" s="17"/>
-      <c r="K102" s="17"/>
-    </row>
-    <row r="103" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A103" s="6">
+      <c r="J114" s="17"/>
+      <c r="K114" s="17"/>
+    </row>
+    <row r="115" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A115" s="6">
         <f t="shared" si="5"/>
         <v>20350112</v>
       </c>
-      <c r="B103" s="14">
+      <c r="B115" s="14">
         <v>103501</v>
       </c>
-      <c r="C103" s="33">
+      <c r="C115" s="33">
         <v>2035011</v>
       </c>
-      <c r="D103" s="33">
+      <c r="D115" s="33">
         <v>2</v>
       </c>
-      <c r="E103" s="18" t="s">
+      <c r="E115" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F103" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G103" s="1" t="s">
+      <c r="F115" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G115" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="H103" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I103" s="1" t="s">
+      <c r="H115" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I115" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="J103" s="17"/>
-      <c r="K103" s="17"/>
-    </row>
-    <row r="104" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A104" s="6">
+      <c r="J115" s="17"/>
+      <c r="K115" s="17"/>
+    </row>
+    <row r="116" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A116" s="6">
         <f t="shared" si="5"/>
         <v>20350113</v>
       </c>
-      <c r="B104" s="14">
+      <c r="B116" s="14">
         <v>103501</v>
       </c>
-      <c r="C104" s="33">
+      <c r="C116" s="33">
         <v>2035011</v>
       </c>
-      <c r="D104" s="33">
+      <c r="D116" s="33">
         <v>3</v>
       </c>
-      <c r="E104" s="18" t="s">
+      <c r="E116" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="F104" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G104" s="1" t="s">
+      <c r="F116" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G116" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="H104" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I104" s="1" t="s">
+      <c r="H116" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I116" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J104" s="17"/>
-      <c r="K104" s="17"/>
-    </row>
-    <row r="105" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A105" s="6">
+      <c r="J116" s="17"/>
+      <c r="K116" s="17"/>
+    </row>
+    <row r="117" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A117" s="6">
         <f t="shared" si="5"/>
         <v>20350121</v>
       </c>
-      <c r="B105" s="14">
+      <c r="B117" s="14">
         <v>103501</v>
       </c>
-      <c r="C105" s="33">
+      <c r="C117" s="33">
         <v>2035012</v>
       </c>
-      <c r="D105" s="33">
+      <c r="D117" s="33">
         <v>1</v>
       </c>
-      <c r="E105" s="18" t="s">
+      <c r="E117" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="F105" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G105" s="34" t="s">
+      <c r="F117" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G117" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="H105" s="1" t="s">
+      <c r="H117" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="I105" s="1" t="s">
+      <c r="I117" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="J105" s="17"/>
-      <c r="K105" s="17"/>
-    </row>
-    <row r="106" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A106" s="6">
+      <c r="J117" s="17"/>
+      <c r="K117" s="17"/>
+    </row>
+    <row r="118" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A118" s="6">
         <f t="shared" si="5"/>
         <v>20350122</v>
       </c>
-      <c r="B106" s="14">
+      <c r="B118" s="14">
         <v>103501</v>
       </c>
-      <c r="C106" s="33">
+      <c r="C118" s="33">
         <v>2035012</v>
       </c>
-      <c r="D106" s="33">
+      <c r="D118" s="33">
         <v>2</v>
       </c>
-      <c r="E106" s="18" t="s">
+      <c r="E118" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="F106" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G106" s="34" t="s">
+      <c r="F118" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G118" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="H106" s="1" t="s">
+      <c r="H118" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="I106" s="1" t="s">
+      <c r="I118" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="J106" s="17"/>
-      <c r="K106" s="17"/>
-    </row>
-    <row r="107" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A107" s="6">
+      <c r="J118" s="17"/>
+      <c r="K118" s="17"/>
+    </row>
+    <row r="119" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A119" s="6">
         <f t="shared" si="5"/>
         <v>20350123</v>
       </c>
-      <c r="B107" s="14">
+      <c r="B119" s="14">
         <v>103501</v>
       </c>
-      <c r="C107" s="33">
+      <c r="C119" s="33">
         <v>2035012</v>
       </c>
-      <c r="D107" s="33">
+      <c r="D119" s="33">
         <v>3</v>
       </c>
-      <c r="E107" s="18" t="s">
+      <c r="E119" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="F107" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G107" s="34" t="s">
+      <c r="F119" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G119" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="H107" s="1" t="s">
+      <c r="H119" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="I107" s="1" t="s">
+      <c r="I119" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="J107" s="17"/>
-      <c r="K107" s="17"/>
+      <c r="J119" s="17"/>
+      <c r="K119" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoller" sheetId="1" r:id="rId1"/>
@@ -192,22 +192,22 @@
     <t>1_300</t>
   </si>
   <si>
+    <t>99_3_99_3_99_3_99_3_99_3_99_2_99_2_99_1_99_1_99_1_99_1_99_2_99_3_99_1_99_1_99_3_99_1_99_1_99_1_99_1_99_1_99_1_99_1_99_3_99_4_99_1_99_5_99_5_99_5_99_5_99_5_99_5_99_5_99_5_99_5_99_3_99_3_99_3_99_3_99_2_99_2_99_1_99_1_99_5_99_5_99_5_99_5_99_5_99_3_99_3_99_1_99_1_99_1_99_2_99_2_99_2_99_1_99_1_99_3_99_3_99_3_99_3_99_3_99_3_99_3_99_3_99_3_99_3_99_4_99_4_99_4_99_5_99_2_99_2_99_2_99_2_99_2_99_2_99_2_99_2_99_2_99_5_99_2_99_2_99_2_99_3_99_3_99_2_99_1_99_1_99_2_99_2_99_2_99_5_99_5_99_5_99_5_99_5_99_5_99_5_99_5_99_5_99_5_99_5_99_5_99_5_99_5_99_5_99_5_99_3_99_3_99_3_99_2_99_2_99_2_99_2_99_3_99_3_99_3_99_3_99_3_99_3_99_2_99_2_99_2_99_2_99_4_99_4_99_4_99_4_99_4_99_2_99_1_99_1_99_1_99_1_99_1_99_1_99_1_99_1_99_5_99_5_99_5_99_1_99_1_99_3_99_3_99_3_99_3_99_1_99_1_99_1_99_1_99_1_99_1_99_1_99_1_99_3_99_3_99_1_99_1_99_2_99_1_99_2_99_2_99_2_99_1_99_3_99_2_99_2_99_2_99_2_99_2_99_2_99_2_99_3_99_3_99_1_99_3_99_3_99_3_99_3_99_3_99_3_99_2_99_2_99_2_99_2_99_2_99_2_99_2_99_2_99_2_99_1_99_3_99_5_99_3_99_3_99_3_99_3_99_1_99_1_99_1_99_1_99_5_99_5_99_5_99_3_99_3_99_3_99_2_99_2_99_3_99_3_99_3_99_1_99_1_99_1_99_1_99_1_99_1_99_2_99_1_99_1_99_1_99_1_99_2_99_2_99_2_99_3_99_3_99_3_99_3_99_2_99_2_99_5_99_5_99_5_99_2_99_1_99_1_99_1_99_1_99_1_99_2_99_2_99_2_99_1_99_1_99_2</t>
+  </si>
+  <si>
+    <t>99_4_99_3_99_2_99_5_99_4_99_3_99_6_99_1_99_1_99_4_99_1_99_6_99_5_99_6_99_5_99_4_99_5_99_2_99_4_99_3_99_1_99_1_99_2_99_3_99_3_99_3_99_2_99_1_99_4_99_2_99_4_99_6_99_3_99_5_99_5_99_6_99_1_99_4_99_2_99_6_99_1_99_5_99_6_99_5_99_3_99_4_99_4_99_3_99_1_99_5_99_5_99_4_99_3_99_3_99_3_99_1_99_3_99_5_99_5_99_5_99_5_99_6_99_2_99_4_99_4_99_1_99_3_99_3_99_4_99_2_99_3_99_6_99_1_99_6_99_2_99_2_99_4_99_2_99_5_99_6_99_3_99_4_99_5_99_6_99_2_99_3_99_5_99_1_99_2_99_2_99_6_99_1_99_6_99_3_99_2_99_6_99_2_99_3_99_1_99_3_99_5_99_2_99_4_99_2_99_4_99_5_99_2_99_2_99_6_99_1_99_1_99_3_99_3_99_6_99_3_99_4_99_4_99_4_99_5_99_4_99_5_99_3_99_1_99_5_99_3_99_1_99_2_99_6_99_3_99_4_99_2_99_4_99_5_99_2_99_3_99_1_99_2_99_3_99_3_99_1_99_1_99_2_99_4_99_3_99_1_99_5_99_2_99_5_99_1_99_1_99_2_99_3_99_2_99_2_99_5_99_1_99_6_99_5_99_2_99_1_99_1_99_3_99_2_99_3_99_1_99_1_99_2_99_5_99_2_99_6_99_4_99_6_99_4_99_5_99_3_99_3_99_3_99_5_99_3_99_2_99_2_99_6_99_4_99_1_99_1_99_3_99_4_99_6_99_6_99_4_99_4_99_2_99_4_99_5_99_6_99_1_99_4_99_1_99_1_99_4_99_2_99_2_99_4_99_5_99_4_99_5_99_4_99_1_99_1_99_3_99_5_99_2_99_6_99_1_99_4_99_3_99_2_99_3_99_3_99_3_99_5_99_5_99_6_99_2_99_5_99_1_99_5_99_4_99_1_99_4_99_3_99_6_99_1_99_2_99_2_99_6_99_5_99_4_99_5_99_6_99_5_99_3_99_6_99_3_99_5_99_3_99_3_99_4_99_1_99_2</t>
+  </si>
+  <si>
+    <t>99_1_99_2_99_2_99_2_99_3_99_6_99_1_99_4_99_1_99_4_99_3_99_2_99_4_99_4_99_6_99_4_99_3_99_4_99_4_99_2_99_3_99_6_99_6_99_6_99_5_99_1_99_3_99_1_99_2_99_5_99_6_99_4_99_2_99_1_99_2_99_3_99_5_99_1_99_3_99_4_99_4_99_2_99_4_99_3_99_1_99_3_99_5_99_6_99_3_99_2_99_2_99_5_99_2_99_2_99_2_99_2_99_2_99_6_99_3_99_5_99_6_99_2_99_1_99_1_99_6_99_6_99_2_99_2_99_1_99_3_99_5_99_4_99_2_99_6_99_3_99_4_99_1_99_3_99_1_99_5_99_3_99_3_99_5_99_6_99_4_99_6_99_3_99_6_99_5_99_3_99_5_99_3_99_2_99_5_99_6_99_5_99_5_99_4_99_4_99_1_99_5_99_3_99_3_99_1_99_2_99_6_99_3_99_2_99_5_99_1_99_3_99_2_99_2_99_6_99_5_99_1_99_2_99_1_99_6_99_3_99_2_99_5_99_5_99_2_99_4_99_3_99_6_99_2_99_1_99_3_99_5_99_1_99_3_99_1_99_3_99_6_99_3_99_1_99_4_99_3_99_1_99_3_99_6_99_1_99_6_99_2_99_6_99_5_99_5_99_4_99_5_99_1_99_5_99_4_99_1_99_2_99_1_99_1_99_5_99_4_99_2_99_2_99_1_99_3_99_4_99_5_99_2_99_1_99_2_99_2_99_1_99_5_99_1_99_4_99_5_99_4_99_4_99_2_99_3_99_6_99_1_99_5_99_3_99_3_99_5_99_4_99_4_99_5_99_4_99_5_99_4_99_3_99_6_99_6_99_6_99_6_99_6_99_4_99_4_99_5_99_5_99_3_99_3_99_1_99_3_99_6_99_5_99_1_99_6_99_6_99_6_99_6_99_1_99_1_99_1_99_3_99_5_99_6_99_2_99_4_99_3_99_6_99_6_99_5_99_1_99_1_99_1_99_6_99_1_99_1_99_1_99_4_99_5_99_1_99_5_99_5_99_6_99_1_99_3_99_1_99_5_99_4_99_3_99_1_99_6_99_5_99_5_99_2_99_1_99_2</t>
+  </si>
+  <si>
+    <t>99_2_99_5_99_21_99_3_99_3_99_6_99_4_99_7_99_6_99_27_99_10_99_4_99_5_99_3_99_2_99_25_99_5_99_5_99_25_99_6_99_3_99_39_99_1_99_5_99_24_99_6_99_3_99_5_99_4_99_3_99_5_99_3_99_24_99_6_99_27_99_22_99_4_99_6_99_4_99_31_99_1_99_3_99_5_99_5_99_34_99_4_99_37_99_5_99_2_99_5_99_27_99_6_99_2_99_23_99_3_99_1_99_3_99_3_99_29_99_1_99_8_99_37_99_3_99_38_99_6_99_1_99_30_99_30_99_1_99_6_99_5_99_1_99_32_99_5_99_6_99_2_99_5_99_10_99_2_99_3_99_5_99_6_99_6_99_31_99_1_99_1_99_2_99_3_99_1_99_4_99_27_99_4_99_32_99_8_99_3_99_24_99_36_99_27_99_2_99_33_99_6_99_4_99_2_99_2_99_25_99_2_99_3_99_30_99_4_99_2_99_35_99_5_99_3_99_23_99_7_99_1_99_34_99_3_99_31_99_36_99_26_99_2_99_3_99_5_99_23_99_24_99_4_99_1_99_3_99_4_99_5_99_38_99_5_99_1_99_5_99_4_99_6_99_1_99_2_99_23_99_6_99_4_99_38_99_6_99_36_99_4_99_2_99_6_99_29_99_28_99_6_99_4_99_4_99_4_99_1_99_23_99_1_99_3_99_33_99_2_99_8_99_34_99_6_99_2_99_4_99_7_99_4_99_1_99_2_99_28_99_30_99_5_99_5_99_31_99_3_99_5_99_23_99_1_99_6_99_3_99_30_99_2_99_3_99_30_99_32_99_33_99_32_99_4_99_2_99_22_99_5_99_5_99_6_99_29_99_6_99_2_99_4_99_2_99_5_99_1_99_28_99_1_99_1_99_5_99_4_99_6_99_5_99_4_99_4_99_6_99_37_99_32_99_25_99_2_99_34_99_40_99_2_99_3_99_3_99_6_99_4_99_21_99_1_99_1_99_26_99_5_99_6_99_22_99_9_99_6_99_1_99_38_99_2_99_27_99_3_99_1_99_33_99_3_99_4_99_1_99_6_99_3_99_3_99_26_99_5_99_3_99_6_99_1_99_3_99_27</t>
+  </si>
+  <si>
     <t>99_3_99_6_99_2_99_6_99_3_99_4_99_6_99_6_99_4_99_4_99_2_99_6_99_1_99_6_99_1_99_3_99_3_99_6_99_5_99_5_99_4_99_4_99_5_99_4_99_6_99_5_99_3_99_1_99_4_99_4_99_6_99_6_99_1_99_4_99_3_99_2_99_1_99_4_99_6_99_6_99_5_99_6_99_1_99_1_99_6_99_3_99_1_99_4_99_4_99_5_99_3_99_1_99_1_99_1_99_2_99_6_99_3_99_2_99_3_99_5_99_6_99_4_99_2_99_2_99_6_99_1_99_6_99_6_99_5_99_3_99_6_99_4_99_5_99_3_99_3_99_5_99_3_99_3_99_3_99_6_99_4_99_3_99_3_99_2_99_4_99_1_99_5_99_3_99_3_99_5_99_1_99_3_99_2_99_4_99_2_99_6_99_6_99_4_99_3_99_4_99_6_99_3_99_2_99_2_99_6_99_6_99_4_99_4_99_6_99_5_99_3_99_6_99_6_99_3_99_1_99_2_99_4_99_6_99_4_99_5_99_6_99_5_99_5_99_5_99_4_99_6_99_3_99_3_99_1_99_6_99_6_99_4_99_2_99_6_99_2_99_2_99_6_99_1_99_6_99_1_99_6_99_5_99_1_99_1_99_2_99_4_99_3_99_1_99_4_99_4_99_1_99_1_99_4_99_3_99_3_99_6_99_5_99_5_99_5_99_1_99_6_99_1_99_3_99_4_99_2_99_5_99_1_99_2_99_4_99_5_99_4_99_4_99_3_99_2_99_5_99_4_99_2_99_2_99_3_99_5_99_2_99_6_99_1_99_5_99_2_99_4_99_6_99_2_99_6_99_1_99_4_99_4_99_1_99_5_99_3_99_4_99_6_99_1_99_6_99_3_99_6_99_2_99_1_99_2_99_3_99_4_99_3_99_6_99_6_99_4_99_1_99_5_99_2_99_4_99_1_99_3_99_5_99_6_99_2_99_5_99_6_99_4_99_6_99_1_99_5_99_1_99_5_99_3_99_5_99_5_99_3_99_3_99_1_99_6_99_6_99_5_99_5_99_6_99_4_99_1_99_6_99_3_99_4_99_3_99_4_99_1_99_1_99_3_99_4_99_1</t>
   </si>
   <si>
-    <t>99_4_99_3_99_2_99_5_99_4_99_3_99_6_99_1_99_1_99_4_99_1_99_6_99_5_99_6_99_5_99_4_99_5_99_2_99_4_99_3_99_1_99_1_99_2_99_3_99_3_99_3_99_2_99_1_99_4_99_2_99_4_99_6_99_3_99_5_99_5_99_6_99_1_99_4_99_2_99_6_99_1_99_5_99_6_99_5_99_3_99_4_99_4_99_3_99_1_99_5_99_5_99_4_99_3_99_3_99_3_99_1_99_3_99_5_99_5_99_5_99_5_99_6_99_2_99_4_99_4_99_1_99_3_99_3_99_4_99_2_99_3_99_6_99_1_99_6_99_2_99_2_99_4_99_2_99_5_99_6_99_3_99_4_99_5_99_6_99_2_99_3_99_5_99_1_99_2_99_2_99_6_99_1_99_6_99_3_99_2_99_6_99_2_99_3_99_1_99_3_99_5_99_2_99_4_99_2_99_4_99_5_99_2_99_2_99_6_99_1_99_1_99_3_99_3_99_6_99_3_99_4_99_4_99_4_99_5_99_4_99_5_99_3_99_1_99_5_99_3_99_1_99_2_99_6_99_3_99_4_99_2_99_4_99_5_99_2_99_3_99_1_99_2_99_3_99_3_99_1_99_1_99_2_99_4_99_3_99_1_99_5_99_2_99_5_99_1_99_1_99_2_99_3_99_2_99_2_99_5_99_1_99_6_99_5_99_2_99_1_99_1_99_3_99_2_99_3_99_1_99_1_99_2_99_5_99_2_99_6_99_4_99_6_99_4_99_5_99_3_99_3_99_3_99_5_99_3_99_2_99_2_99_6_99_4_99_1_99_1_99_3_99_4_99_6_99_6_99_4_99_4_99_2_99_4_99_5_99_6_99_1_99_4_99_1_99_1_99_4_99_2_99_2_99_4_99_5_99_4_99_5_99_4_99_1_99_1_99_3_99_5_99_2_99_6_99_1_99_4_99_3_99_2_99_3_99_3_99_3_99_5_99_5_99_6_99_2_99_5_99_1_99_5_99_4_99_1_99_4_99_3_99_6_99_1_99_2_99_2_99_6_99_5_99_4_99_5_99_6_99_5_99_3_99_6_99_3_99_5_99_3_99_3_99_4_99_1_99_2</t>
-  </si>
-  <si>
     <t>99_4_99_4_99_5_99_5_99_5_99_2_99_3_99_6_99_5_99_1_99_2_99_6_99_5_99_1_99_3_99_2_99_3_99_5_99_5_99_5_99_2_99_5_99_3_99_4_99_4_99_3_99_3_99_3_99_1_99_4_99_1_99_1_99_2_99_2_99_5_99_4_99_2_99_3_99_5_99_3_99_3_99_6_99_3_99_4_99_1_99_5_99_4_99_1_99_4_99_6_99_2_99_3_99_1_99_2_99_2_99_6_99_2_99_1_99_1_99_6_99_4_99_6_99_3_99_6_99_1_99_6_99_2_99_1_99_1_99_6_99_1_99_6_99_2_99_5_99_5_99_2_99_4_99_2_99_5_99_3_99_2_99_2_99_1_99_3_99_2_99_4_99_1_99_4_99_2_99_5_99_2_99_4_99_5_99_3_99_4_99_6_99_3_99_5_99_5_99_1_99_1_99_3_99_1_99_6_99_5_99_2_99_6_99_5_99_3_99_5_99_4_99_2_99_4_99_5_99_2_99_5_99_2_99_3_99_3_99_3_99_4_99_3_99_2_99_2_99_2_99_6_99_1_99_5_99_4_99_3_99_4_99_5_99_1_99_4_99_3_99_6_99_2_99_2_99_2_99_1_99_3_99_1_99_1_99_1_99_5_99_3_99_5_99_5_99_4_99_6_99_6_99_6_99_3_99_5_99_2_99_3_99_5_99_6_99_5_99_3_99_2_99_6_99_2_99_1_99_5_99_1_99_1_99_2_99_6_99_5_99_1_99_2_99_6_99_3_99_1_99_1_99_5_99_5_99_3_99_4_99_2_99_4_99_5_99_3_99_2_99_2_99_2_99_4_99_4_99_5_99_5_99_6_99_5_99_4_99_6_99_6_99_4_99_4_99_1_99_2_99_2_99_5_99_3_99_3_99_6_99_6_99_6_99_1_99_2_99_4_99_1_99_6_99_2_99_1_99_6_99_1_99_5_99_6_99_2_99_2_99_1_99_3_99_2_99_4_99_2_99_6_99_6_99_5_99_3_99_1_99_2_99_4_99_3_99_3_99_3_99_2_99_5_99_2_99_3_99_6_99_1_99_2_99_6_99_2_99_5_99_6_99_4_99_2_99_4_99_5</t>
-  </si>
-  <si>
-    <t>99_1_99_2_99_2_99_2_99_3_99_6_99_1_99_4_99_1_99_4_99_3_99_2_99_4_99_4_99_6_99_4_99_3_99_4_99_4_99_2_99_3_99_6_99_6_99_6_99_5_99_1_99_3_99_1_99_2_99_5_99_6_99_4_99_2_99_1_99_2_99_3_99_5_99_1_99_3_99_4_99_4_99_2_99_4_99_3_99_1_99_3_99_5_99_6_99_3_99_2_99_2_99_5_99_2_99_2_99_2_99_2_99_2_99_6_99_3_99_5_99_6_99_2_99_1_99_1_99_6_99_6_99_2_99_2_99_1_99_3_99_5_99_4_99_2_99_6_99_3_99_4_99_1_99_3_99_1_99_5_99_3_99_3_99_5_99_6_99_4_99_6_99_3_99_6_99_5_99_3_99_5_99_3_99_2_99_5_99_6_99_5_99_5_99_4_99_4_99_1_99_5_99_3_99_3_99_1_99_2_99_6_99_3_99_2_99_5_99_1_99_3_99_2_99_2_99_6_99_5_99_1_99_2_99_1_99_6_99_3_99_2_99_5_99_5_99_2_99_4_99_3_99_6_99_2_99_1_99_3_99_5_99_1_99_3_99_1_99_3_99_6_99_3_99_1_99_4_99_3_99_1_99_3_99_6_99_1_99_6_99_2_99_6_99_5_99_5_99_4_99_5_99_1_99_5_99_4_99_1_99_2_99_1_99_1_99_5_99_4_99_2_99_2_99_1_99_3_99_4_99_5_99_2_99_1_99_2_99_2_99_1_99_5_99_1_99_4_99_5_99_4_99_4_99_2_99_3_99_6_99_1_99_5_99_3_99_3_99_5_99_4_99_4_99_5_99_4_99_5_99_4_99_3_99_6_99_6_99_6_99_6_99_6_99_4_99_4_99_5_99_5_99_3_99_3_99_1_99_3_99_6_99_5_99_1_99_6_99_6_99_6_99_6_99_1_99_1_99_1_99_3_99_5_99_6_99_2_99_4_99_3_99_6_99_6_99_5_99_1_99_1_99_1_99_6_99_1_99_1_99_1_99_4_99_5_99_1_99_5_99_5_99_6_99_1_99_3_99_1_99_5_99_4_99_3_99_1_99_6_99_5_99_5_99_2_99_1_99_2</t>
-  </si>
-  <si>
-    <t>99_1_99_2_99_5_99_6_99_4_99_1_99_1_99_4_99_2_99_1_99_2_99_3_99_5_99_4_99_6_99_1_99_6_99_4_99_4_99_4_99_4_99_3_99_5_99_2_99_1_99_1_99_1_99_1_99_4_99_5_99_6_99_5_99_1_99_6_99_5_99_6_99_2_99_1_99_2_99_4_99_4_99_6_99_5_99_4_99_5_99_5_99_4_99_3_99_1_99_6_99_2_99_4_99_6_99_4_99_1_99_6_99_1_99_4_99_6_99_4_99_3_99_1_99_6_99_3_99_2_99_3_99_5_99_6_99_6_99_3_99_3_99_1_99_2_99_5_99_4_99_2_99_4_99_1_99_6_99_1_99_3_99_2_99_3_99_6_99_3_99_1_99_2_99_3_99_4_99_2_99_4_99_6_99_2_99_4_99_2_99_5_99_5_99_5_99_2_99_6_99_6_99_5_99_1_99_4_99_6_99_6_99_2_99_1_99_1_99_6_99_1_99_4_99_2_99_2_99_6_99_5_99_3_99_5_99_3_99_6_99_4_99_1_99_6_99_2_99_2_99_5_99_6_99_5_99_1_99_2_99_6_99_5_99_3_99_6_99_4_99_1_99_6_99_1_99_1_99_1_99_5_99_2_99_3_99_5_99_1_99_6_99_5_99_4_99_3_99_3_99_5_99_2_99_1_99_2_99_3_99_2_99_3_99_5_99_3_99_2_99_5_99_5_99_5_99_1_99_2_99_5_99_3_99_3_99_2_99_4_99_5_99_5_99_4_99_4_99_3_99_4_99_4_99_3_99_2_99_1_99_5_99_6_99_4_99_4_99_1_99_4_99_2_99_5_99_1_99_2_99_6_99_3_99_2_99_1_99_4_99_1_99_2_99_1_99_3_99_1_99_5_99_6_99_1_99_3_99_6_99_3_99_6_99_2_99_2_99_4_99_2_99_3_99_4_99_6_99_1_99_5_99_5_99_6_99_6_99_4_99_6_99_3_99_3_99_6_99_3_99_6_99_6_99_6_99_3_99_6_99_3_99_1_99_1_99_1_99_1_99_3_99_5_99_2_99_1_99_5_99_3_99_3_99_4_99_2_99_4_99_2_99_3_99_4_99_1_99_1</t>
-  </si>
-  <si>
-    <t>99_2_99_5_99_21_99_3_99_3_99_6_99_4_99_7_99_6_99_27_99_10_99_4_99_5_99_3_99_2_99_25_99_5_99_5_99_25_99_6_99_3_99_39_99_1_99_5_99_24_99_6_99_3_99_5_99_4_99_3_99_5_99_3_99_24_99_6_99_27_99_22_99_4_99_6_99_4_99_31_99_1_99_3_99_5_99_5_99_34_99_4_99_37_99_5_99_2_99_5_99_27_99_6_99_2_99_23_99_3_99_1_99_3_99_3_99_29_99_1_99_8_99_37_99_3_99_38_99_6_99_1_99_30_99_30_99_1_99_6_99_5_99_1_99_32_99_5_99_6_99_2_99_5_99_10_99_2_99_3_99_5_99_6_99_6_99_31_99_1_99_1_99_2_99_3_99_1_99_4_99_27_99_4_99_32_99_8_99_3_99_24_99_36_99_27_99_2_99_33_99_6_99_4_99_2_99_2_99_25_99_2_99_3_99_30_99_4_99_2_99_35_99_5_99_3_99_23_99_7_99_1_99_34_99_3_99_31_99_36_99_26_99_2_99_3_99_5_99_23_99_24_99_4_99_1_99_3_99_4_99_5_99_38_99_5_99_1_99_5_99_4_99_6_99_1_99_2_99_23_99_6_99_4_99_38_99_6_99_36_99_4_99_2_99_6_99_29_99_28_99_6_99_4_99_4_99_4_99_1_99_23_99_1_99_3_99_33_99_2_99_8_99_34_99_6_99_2_99_4_99_7_99_4_99_1_99_2_99_28_99_30_99_5_99_5_99_31_99_3_99_5_99_23_99_1_99_6_99_3_99_30_99_2_99_3_99_30_99_32_99_33_99_32_99_4_99_2_99_22_99_5_99_5_99_6_99_29_99_6_99_2_99_4_99_2_99_5_99_1_99_28_99_1_99_1_99_5_99_4_99_6_99_5_99_4_99_4_99_6_99_37_99_32_99_25_99_2_99_34_99_40_99_2_99_3_99_3_99_6_99_4_99_21_99_1_99_1_99_26_99_5_99_6_99_22_99_9_99_6_99_1_99_38_99_2_99_27_99_3_99_1_99_33_99_3_99_4_99_1_99_6_99_3_99_3_99_26_99_5_99_3_99_6_99_1_99_3_99_27</t>
   </si>
   <si>
     <t>37_34_24_40_27_39_34_36_9_24_28_23_29_40_21_30_31_35_26_38_37_38_37_34_9_39_22_32_22_40_39_23_32_22_21_30_25_40_33_22_28_37_36_40_40_36_29_23_23_25_36_26_33_39_40_35_30_31_26_34_31_30_38_35_38_23_26_29_23_8_21_33_30_26_35_40_34_39_23_34_37_30_26_9_27_7_36_40_39_33_39_24_29_24_37_29_23_22_28_25_21_36_27_36_29_23_23_31_30_23_32_26_25_25_26_34_36_38_30_27_30_25_36_23_37_27_27_21_7_37_38_24_10_40_34_33_32_30_32_21_25_22_23_37_26_37_31_24_28_35_29_33_7_38_38_35_39_36_27_39_31_36_29_31_23_31_35_25_28_34_37_25_39_25_29_31_32_26_10_23_36_38_27_31_23_30_24_21_28_7_24_34_39_36_32_7_37_38_34_36_21_29_40_27_22_36_32_37_39_21_38_25_26_35_23_23_33_34_25_33_21_33_30_39_24_28_34_29_21_22_31_40_40_37_21_32_30_33_37_30_24_28_21_25_8_38_36_40_29_27_7_23_36_24_8_25_36_37_7_40_38_7_36_27_40_32_23_32_22_9_26_38_9_40_37_39_39_24_34_32_28_36_22_40_7_21_22_21_31_24_35_25_28_33_22_32_39_28_24_28_33_40_30_21_28_22_36_35_28_36_22_21_35_40_33_36_39_37_32_34_22_40_28_33_36_31_35_25_29_30_24_38_8_38_28_40_31_29_31_32_32_26_30_34_27_24_36_25_24_40_21_35_25_21_38_40_21_32_31_22_23_38_24_31_36_25_26_23_27_35_24_38_23_22_34_28_40_22_21_32_21_36_30_33_23_25_33_28_7_30_22_38_35_37_32_32_36_23_38_32_21_30_32_35_32_30_36_30_30_28_36_38_22_35_30_33_27_36_21_27_8_30_8_36_23_33_38_36_31_22_39_33_35_37_22_39_35_39_40_21_21_22_23_26_35_24_23_27_32_28_29_40_36_23_34_29_29_32_26_22_28_29_10_38_8_30_24_22_37_29_38_28_31_36_24_39_26_26_25_25_31_35_27_37_37_35_26_23_23_40_35_38_32_36_40_35_28_31_37_21</t>
@@ -2118,13 +2118,13 @@
         <v>36</v>
       </c>
       <c r="G11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="H11" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="J11" s="21"/>
     </row>
@@ -2149,13 +2149,13 @@
         <v>36</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H12" s="21" t="s">
         <v>36</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J12" s="21"/>
     </row>
@@ -2186,7 +2186,7 @@
         <v>36</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J13" s="24"/>
     </row>
@@ -2211,13 +2211,13 @@
         <v>36</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H14" s="24" t="s">
         <v>36</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J14" s="24"/>
     </row>
@@ -3563,7 +3563,7 @@
     </row>
     <row r="57" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A57" s="5">
-        <f t="shared" ref="A57:A67" si="2">C57*10+D57</f>
+        <f t="shared" ref="A57:A72" si="2">C57*10+D57</f>
         <v>20180011</v>
       </c>
       <c r="B57" s="13">
@@ -3915,7 +3915,7 @@
     </row>
     <row r="68" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A68" s="5">
-        <f>C68*10+D68</f>
+        <f t="shared" si="2"/>
         <v>20230011</v>
       </c>
       <c r="B68" s="13">
@@ -3947,7 +3947,7 @@
     </row>
     <row r="69" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A69" s="5">
-        <f>C69*10+D69</f>
+        <f t="shared" si="2"/>
         <v>20230012</v>
       </c>
       <c r="B69" s="13">
@@ -3979,7 +3979,7 @@
     </row>
     <row r="70" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A70" s="5">
-        <f>C70*10+D70</f>
+        <f t="shared" si="2"/>
         <v>20230013</v>
       </c>
       <c r="B70" s="13">
@@ -4011,7 +4011,7 @@
     </row>
     <row r="71" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A71" s="5">
-        <f>C71*10+D71</f>
+        <f t="shared" si="2"/>
         <v>20230014</v>
       </c>
       <c r="B71" s="13">
@@ -4043,7 +4043,7 @@
     </row>
     <row r="72" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A72" s="5">
-        <f>C72*10+D72</f>
+        <f t="shared" si="2"/>
         <v>20230015</v>
       </c>
       <c r="B72" s="13">

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="178">
   <si>
     <t>id</t>
   </si>
@@ -592,13 +592,28 @@
     <t>8_8_8_8_13_13_13_13_8_13_13_13_13_13_8_13_8_13_13_13_13_13_13_13_8_13_8_8_8_13_13_8_8_13_8_13_8_8_8_13_13_13_8_8_13_13_13_13_13_8_8_13_8_8_8_8_13_13_8_8_13_13_8_13_8_13_13_8_8_8_13_8_13_8_8_8_13_13_8_13_8_13_13_8_13_13_13_8_8_8_8_8_13_13_13_8_13_13_13_13_13_13_13_8_8_8_8_13_13_13_13_13_13_8_13_8_13_8_8_8_13_8_8_8_8_13_13_13_8_13_13_13_8_8_13_8_8_8_8_13_13_13_13_8_13_13_8_13_8_13_13_8_13_8_13_8_13_13_8_8_13_13_13_13_8_13_13_8_13_8_8_13_13_13_8_8_13_8_13_8_13_8_8_13_8_13_13_13_13_13_13_13_8_8_8_8_8_13_13_13_13_8_8_13_13_8_8_8_8_13_8_13_13_8_13_13_8_8_8_8_13_13_8_13_13_13_8_13_8_8_8_8_8_8_8_13_8_8_8_8_13_8_8_8_13_13_8_8_13_8_8_8_13_8_8_13_13_8_8_13_8_8_8_8_8_13_13_13_8_8_8_8_13_13_13_8_8_8_8_13_13_8_13_8_8_8_8_13_13_13_8_13_13_13_13_13_13_8_8_13_13_13_8_13_8_13_13_13_13_8_8_13_13_8_8_8_13_13_13_13_13_13_8_8_8_8_8_13_13_8_8_8_8_13_8_13_8_8_13_13_8_8_8_8_13_13_8_13_8_13_8_8_8_8_13_13_8_13_8_8_13_13_8_13_13_8_8_8_13_13_8_8_8_8_8_8_13_13_13_8_8_8_8_8_8_8_13_8_13_13_8_8_8_13_8_13_13_13_13_13_8_13_8_13_8_13_8_13_8_8_8_13_8_8_8_13_13_13_13_8_13_13_13_8_13_8_8_8_8_8_8_13_13_13_13_13_8_8_8_8_8_8_13_13_8_8_13_8_8_8_8_8_8_8_13_8_13_13_13_8_8_8_8_8_13_13_13_8_8_13_13_13_8_8_8_8_13_13_8_8_13_13_13_13_13_8_13_8_13_8_8_13_13_13_13_8_13_8_8_8</t>
   </si>
   <si>
-    <t>1_501</t>
-  </si>
-  <si>
-    <t>1_502</t>
-  </si>
-  <si>
-    <t>1_503</t>
+    <t>4_3_4_5_1_1_3_2_1_2_4_1_5_3_2_3_6_3_4_2_2_2_4_5_4_6_1_4_1_1_2_2_2_3_4_6_2_4_4_4_2_2_3_2_2_4_3_3_4_5_1_1_2_1_1_2_2_1_1_3_4_5_4_1_1_4_5_4_2_1_4_5_3_2_5_4_5_5_1_1_1_1_1_1_3_2_2_3_3_2_3_5_2_2_2_1_5_1_3_2_3_1_2_2_1_4_3_4_4_1_4_6_5_1_6_2_4_2_6_5_1_1_5_2_1_4_3_4_6_5_6_2_1_4_6_2_3_3_3_6_4_3_2_1_1_1_3_2_6_1_1_1_2_3_2_2_3_2_2_2_4_4_4_3_2_4_5_2_1_1_4_2_2_2_1_3_2_5_3_4_6_1_2_4_1_1_4_4_2_5_2_2_1_2_3_2_3_2_1_1_2_1_3_1_2_2_4_3_5_5_6_2_4_5_2_1_5_2_2_2_2_2_1_3_2_2_3_3_6_5_5_5_3_3_4_3_4_4_5_2_1_4_1_1_2_2_5_5_5_2_4_2_1_1_4_6_1_4_3_1_3_3_1_1_2_2_1_1_1_1_3_4_1_2_2_1_2_2_4_1_1_3_4_4_3_1_4_1_5_2_1_1_2_4_4_3_1_2_5_5_4_3_4_1_3_2_3_4_5_4_3_3_3_1_4_2_1_6_4_3_5_3_3_4_3_2_4_6_1_4_3_4_4_3_3_6_1_5_1_1_4_3_3_4_1_6_2_1_1_5_5_1_2_4_2_3_3_5_5_2_1_2_2_2_1_5_5_5_2_1_6_1_4_6_3_3_3_1_3_1_3_4_3_1_1_1_1_1_6_2_4_1_4_2_5_5_2_1_3_2_5_5_5_3_3_1_4_2_4_4_2_4_3_4_1_1_3_1_2_4_4_3_1_4_3_4_2_1_1_2_4_4_5_2_4_2_1_4_5_2_6_2_3_3_2_4_5_3_4_6_3_4_2_2_3_2_4_1_2_2_4_2_2_1_5_5_5_2_3_3_6_6_3_3_1_4_2_4_2_3_5_4_3_5_2_1_2_2_3_2_5_2_2_4_5_5_3_6_6_6</t>
+  </si>
+  <si>
+    <t>7_3_2_1_5_6_1_3_1_2_2_3_7_4_2_3_6_5_2_7_5_4_7_6_2_1_2_1_5_2_3_3_1_1_3_1_5_6_7_3_1_4_2_2_1_1_7_4_1_3_5_7_7_3_5_7_3_2_1_1_4_3_1_2_5_1_3_3_2_2_4_1_3_7_4_2_7_4_2_3_1_1_2_1_2_1_4_4_2_5_5_2_1_1_5_1_5_3_6_2_4_4_5_1_1_6_3_3_7_3_4_7_3_4_2_6_4_3_2_3_3_6_4_6_7_6_3_4_1_3_1_3_1_3_4_6_1_3_1_1_2_5_2_1_4_4_2_5_6_7_3_4_5_3_5_2_1_2_5_1_2_1_3_7_2_5_3_3_2_3_2_4_3_4_3_2_1_2_4_4_3_3_6_3_1_3_2_3_5_6_2_2_3_7_4_4_1_6_3_4_2_2_5_2_4_5_2_1_3_3_1_4_7_4_5_4_4_2_6_5_2_1_3_2_5_7_4_1_4_1_3_6_2_1_2_2_6_2_2_1_3_4_1_3_1_5_1_4_3_1_5_2_4_6_2_4_4_1_6_1_2_6_7_2_5_2_2_6_1_6_3_6_2_2_6_1_1_2_6_4_4_2_1_4_3_2_2_1_5_2_5_2_6_5_4_1_5_1_2_6_4_4_5_3_3_2_4_3_2_4_7_1_1_4_4_2_2_2_4_4_6_2_6_6_3_2_5_1_6_5_3_4_5_4_2_1_6_2_4_1_3_5_2_2_1_6_2_1_5_2_2_2_2_4_3_2_6_3_3_2_2_6_1_1_1_3_2_2_1_3_4_3_2_4_7_5_6_4_1_3_4_2_1_3_5_5_1_2_2_3_2_1_7_2_2_6_2_6_2_4_7_5_5_1_4_4_1_7_7_4_6_2_4_2_3_3_3_2_4_1_6_4_3_7_6_1_6_4_4_4_5_5_1_5_4_3_5_7_3_3_1_7_4_5_3_1_4_7_3_4_3_1_3_1_4_2_1_6_1_1_6_1_1_7_5_1_1_5_2_4_4_1_3_2_5_3_2_3_2_7_6_3_2_4_6_6_5_5_2_1_1_5_1_4_1_2_4_2_4_2</t>
+  </si>
+  <si>
+    <t>5_3_6_3_1_6_1_2_2_3_2_3_2_1_4_3_4_5_5_1_1_3_3_1_1_2_1_4_3_3_5_1_2_3_2_4_3_4_1_1_2_2_3_1_4_1_1_2_1_1_2_4_1_3_4_1_2_2_5_5_6_4_2_4_1_1_4_6_1_2_2_5_5_4_5_4_2_6_2_5_1_5_5_5_1_4_2_5_5_1_6_2_2_1_2_2_2_2_1_1_2_4_5_2_1_5_3_3_3_3_1_1_3_3_3_3_6_3_3_4_2_6_1_5_5_1_6_6_6_6_6_3_3_1_6_4_3_3_4_2_4_4_1_1_5_3_1_1_4_3_5_5_4_5_6_2_1_1_4_1_3_3_4_2_1_1_5_1_2_4_6_3_1_1_5_3_3_5_5_5_1_1_5_2_2_5_2_5_1_1_1_2_3_1_3_4_3_3_5_2_4_5_3_2_1_1_1_2_2_1_2_2_2_1_1_2_3_3_6_3_4_1_3_3_1_1_1_6_6_6_1_4_1_1_2_5_1_1_2_1_2_5_4_5_5_1_4_6_3_4_5_6_2_2_4_2_1_2_1_2_1_2_1_3_6_6_6_2_3_3_6_4_1_2_2_3_3_4_2_3_1_4_3_3_5_6_4_4_2_6_1_1_4_2_3_5_2_3_2_2_3_1_5_2_6_1_2_3_3_4_3_2_2_4_4_3_2_4_1_5_4_4_4_1_2_2_6_2_4_2_2_4_4_1_5_4_1_1_2_3_6_5_2_1_2_5_4_2_1_1_1_3_2_4_3_3_6_3_1_5_4_4_1_6_2_2_4_5_6_1_4_4_4_2_1_1_1_3_5_6_1_5_4_3_3_3_5_4_4_1_1_5_4_6_1_3_3_2_4_4_5_3_2_2_1_3_3_6_1_2_2_5_5_2_6_3_1_3_5_1_4_3_5_5_3_3_2_3_1_5_3_1_3_5_3_4_1_3_4_3_5_1_4_6_5_1_3_1_1_2_4_4_1_1_1_1_4_3_6_2_2_1_5_6_2_2_2_3_1_3_5_4_2_1_6_6_1_1_2_3_4_4_2_1_1_1_2_1_3_4_6_4_6_4_4_4_3_3_2_5</t>
+  </si>
+  <si>
+    <t>2_4_2_2_6_4_4_5_4_7_3_2_1_3_3_2_1_4_3_4_2_7_6_6_7_1_2_7_1_3_2_3_2_7_5_4_3_3_2_5_3_7_7_4_6_7_2_4_6_3_1_6_1_2_4_2_3_4_5_7_4_7_5_5_4_1_5_3_2_7_2_3_1_4_7_6_1_5_7_2_5_6_3_4_2_1_1_2_1_1_1_1_1_6_3_1_5_4_3_7_4_1_1_7_7_2_5_1_3_5_2_5_2_7_5_4_3_5_7_1_3_2_3_2_1_5_3_2_4_7_7_4_5_3_3_2_5_1_6_3_4_5_1_2_7_4_3_7_4_6_3_1_2_2_1_5_4_3_5_2_5_4_3_7_5_7_6_4_3_5_1_1_4_4_2_5_3_7_4_5_1_2_2_5_6_4_1_2_1_1_5_7_2_2_1_5_1_2_1_6_1_2_4_6_4_5_6_2_1_2_1_4_2_3_3_7_3_2_1_5_3_7_3_6_1_1_7_4_7_7_2_4_3_4_2_2_4_1_2_6_2_1_1_2_5_1_3_2_1_6_3_6_6_5_3_1_5_5_2_1_5_7_5_4_1_2_4_2_5_4_7_3_3_3_2_4_1_5_3_3_3_3_1_1_1_1_4_2_7_7_1_2_3_2_2_5_1_4_1_6_5_6_7_4_1_2_5_2_5_2_4_3_5_3_7_4_7_3_5_2_2_2_5_7_5_7_6_6_4_1_4_2_4_1_1_5_3_7_3_3_1_1_1_1_3_1_1_3_6_6_1_2_1_4_5_2_6_3_2_3_5_2_1_2_1_4_1_4_2_3_3_5_4_6_2_2_6_2_5_6_1_3_1_3_6_2_5_7_1_4_6_1_1_6_2_2_1_4_1_2_6_6_4_1_1_6_3_2_2_5_5_1_2_1_1_1_2_1_2_6_4_4_4_6_5_1_3_7_1_2_1_1_3_1_6_1_4_7_7_1_1_6_2_1_6_3_5_3_4_6_7_6_2_5_2_1_5_1_2_2_2_4_5_1_7_5_6_4_4_3_3_3_1_4_4_5_3_3_4_5_1_1_6_6_5_6_5_6_3_3_2_1_2_7_1_2_6_5_1_6</t>
+  </si>
+  <si>
+    <t>1_5_2_6_4_4_4_4_1_5_5_1_1_2_5_3_1_4_4_2_6_5_2_1_5_5_3_4_2_5_3_2_5_1_2_2_3_3_1_5_1_1_3_4_4_4_5_3_5_3_1_2_6_4_3_2_6_4_3_1_2_1_5_4_6_1_4_2_5_2_5_1_4_3_3_5_1_2_2_1_6_1_1_5_1_1_1_1_4_4_2_5_5_5_5_1_4_4_4_1_3_4_3_1_2_2_5_1_1_1_2_4_3_2_1_4_5_1_2_2_4_3_6_4_2_5_5_1_1_1_4_3_5_3_6_3_5_5_2_2_2_4_4_4_3_3_1_3_6_5_1_1_3_2_2_1_4_6_2_2_2_4_4_5_4_4_2_6_3_3_4_2_3_5_4_6_1_3_4_3_5_1_5_2_1_6_2_2_3_6_3_4_5_1_3_1_5_1_5_3_2_4_4_1_4_4_3_3_2_3_3_5_5_1_2_1_3_3_5_2_3_2_1_3_3_1_5_2_4_4_2_1_1_5_4_4_2_2_2_4_4_4_3_5_2_5_1_3_5_3_1_5_2_2_2_2_2_6_3_5_5_4_2_2_3_4_3_4_2_4_2_4_1_1_5_3_6_3_4_1_2_2_3_3_6_3_3_2_2_1_5_1_5_5_3_5_2_1_1_3_4_4_5_5_5_4_4_4_4_3_2_1_6_2_3_1_1_3_3_4_3_3_4_1_3_2_2_4_1_1_6_1_3_3_1_1_1_2_3_4_5_5_4_4_6_3_4_4_2_1_5_4_4_1_3_1_2_4_2_2_5_3_5_3_5_3_3_6_3_1_2_3_4_1_2_1_1_3_3_3_2_2_2_6_2_2_3_2_2_2_4_4_4_4_4_1_1_4_2_2_2_1_4_6_2_2_2_4_1_3_2_4_4_4_5_1_3_4_2_2_2_4_5_1_6_1_2_5_5_3_4_2_2_1_3_3_2_3_3_5_3_1_1_5_3_6_5_5_4_1_3_1_3_1_2_2_4_1_6_6_6_2_3_4_1_1_4_1_6_4_4_3_2_2_1_2_1_1_1_3_2_3_1_5_5_5_5_4_4_1_1_4_6_4_4_1_1_1_3_6</t>
+  </si>
+  <si>
+    <t>1_5_2_3_5_3_5_7_4_3_4_6_3_1_3_5_5_2_1_4_1_6_1_2_2_3_6_6_5_3_3_6_7_2_1_3_5_6_2_3_2_3_7_7_3_2_1_2_5_6_2_2_1_2_1_5_7_4_5_1_7_2_2_6_3_2_3_2_3_4_6_5_1_5_3_2_7_7_7_1_3_1_5_1_5_7_4_4_2_2_7_2_1_5_6_5_5_1_3_5_6_2_4_4_5_4_1_5_5_4_1_3_7_1_7_2_2_1_4_1_5_2_1_6_7_3_2_1_3_1_4_5_4_3_1_5_5_3_4_4_3_2_7_3_7_6_2_6_1_3_1_2_5_6_2_1_2_5_6_6_7_5_4_1_1_6_2_3_3_2_2_4_1_5_7_2_5_2_5_4_1_3_1_1_1_6_1_3_4_4_3_3_1_1_2_6_2_5_2_6_7_4_4_7_6_3_2_1_6_5_3_7_1_3_1_1_7_3_2_2_6_3_5_1_1_3_7_5_2_7_4_4_5_2_2_1_5_5_6_3_1_6_6_3_5_2_1_4_3_6_1_7_3_1_2_6_1_1_4_3_2_2_3_3_6_1_3_2_2_2_6_6_6_3_3_4_3_7_1_1_1_1_5_7_2_1_3_1_4_2_2_6_5_2_4_4_7_1_7_3_6_4_1_2_2_5_4_2_2_2_1_2_2_2_6_2_5_7_5_2_4_1_5_1_2_4_2_3_7_6_4_2_1_6_6_5_1_1_6_5_5_5_2_2_1_3_7_6_6_7_3_2_7_4_4_2_4_3_2_4_3_4_3_4_7_5_3_5_2_6_2_4_4_6_7_7_2_5_5_1_3_4_6_2_2_7_2_4_5_7_3_3_3_2_4_4_3_4_3_5_6_3_1_1_6_6_6_7_1_7_3_5_7_2_3_3_2_1_2_1_4_7_2_1_4_1_1_5_5_4_1_6_3_5_3_2_3_4_2_2_7_4_4_3_5_4_1_6_4_2_3_3_4_7_7_4_2_2_7_6_2_6_1_2_5_3_1_4_1_5_1_5_1_7_4_7_6_4_4_1_5_3_4_5_3_2_5_1_3_2_3_1_5_1_1_3_3_2_7_4</t>
+  </si>
+  <si>
+    <t>1_1_1_1_1_1_1_2_2_2_2_2_2_2_2_2_6_6_6_6_6_6_4_4_4_4_4_4_4_5_5_5_5_5_5_2_2_4_4_4_2_2_1_1_1_1_1_1_3_3_3_3_2_2_2_2_2_1_1_1_1_1_1_1_1_4_4_4_4_4_4_5_5_2_5_5_5_5_1_1_1_1_1_1_2_2_2_2_2_2_4_4_2_2_2_2_2_2_2_2_3_3_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_5_1_1_1_1_1_1_1_4_4_4_4_4_4_2_2_2_2_2_3_3_3_6_6_6_6_1_1_1_6_6_6_1_1_1_2_2_2_2_2_2_2_2_4_4_4_4_4_4_5_5_5_5_2_2_2_2_2_2_2_3_3_3_3_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_1_1_1_1_1_2_2_2_2_2_2_2_2_4_4_4_4_4_2_2_2_2_2_2_2_2_2_3_3_3_5_5_5_3_3_3_3_4_4_4_4_4_4_1_1_1_1_5_5_5_4_4_4_1_1_1_1_1_1_3_3_3_3_1_1_1_1_1_1_1_1_2_2_2_2_2_2_2_2_4_4_4_4_4_4_2_2_2_2_2_2_1_1_1_1_1_1_1_1_1_5_5_5_5_5_6_6_6_6_6_3_3_3_3_3_3_2_2_2_2_2_2_3_3_3_3_3_3_3_3_3_3_4_4_4_4_4_4_4_1_1_1_1_1_1_1_1_2_2_2_2_2_2_2_2_2_3_3_3_3_3_3_2_2_2_2_5_5_5_5_5_5_1_1_1_1_1_1_1_3_3_3_3_3_1_1_1_1_1_6_6_6_6_4_4_4_4_4_1_1_1_5_5_5_3_3_1_1_1_4_4_4_4_4_4_1_1_1_1_1_4_4_4_4_4_1_1_1_1_1_2_2_2_2_2_2_2_1_1_1_1_1_1_3_3_3_3_3_3_3_3_3_2_2_2_2_2_2_2_2_2_4_4_4_4_5_5_5_6_6_6_6_6_3_3_3_3_3_2_2_2_2_2_2_2_2_1_1_1_1_1_1_2_2_2_2_2_3_3_3_3</t>
+  </si>
+  <si>
+    <t>4_4_4_4_4_4_1_1_1_1_5_5_5_4_4_4_1_1_1_1_1_1_3_3_3_3_1_1_1_1_1_1_1_1_2_2_2_2_2_2_2_2_4_4_4_4_4_4_2_2_2_2_2_2_1_1_1_1_1_1_1_1_1_5_5_5_5_5_6_6_6_6_6_3_3_3_3_3_3_2_2_2_2_2_2_3_3_3_3_3_3_3_3_3_3_4_4_4_4_4_4_4_1_1_1_1_1_1_1_1_2_2_2_2_2_2_2_2_2_3_3_3_3_3_3_2_2_2_2_5_5_5_5_5_5_1_1_1_1_1_1_1_3_3_3_3_3_1_1_1_1_1_6_6_6_6_4_4_4_4_4_1_1_1_5_5_5_3_3_1_1_1_4_4_4_4_4_4_1_1_1_1_1_4_4_4_4_4_1_1_1_1_1_2_2_2_2_2_2_2_1_1_1_1_1_1_3_3_3_3_3_3_3_3_3_2_2_2_2_2_2_2_2_2_4_4_4_4_5_5_5_6_6_6_6_6_3_3_3_3_3_2_2_2_2_2_2_2_2_1_1_1_1_1_1_2_2_2_2_2_3_3_3_3_1_1_1_1_1_1_1_2_2_2_2_2_2_2_2_2_6_6_6_6_6_6_4_4_4_4_4_4_4_5_5_5_5_5_5_2_2_4_4_4_2_2_1_1_1_1_1_1_3_3_3_3_2_2_2_2_2_1_1_1_1_1_1_1_1_4_4_4_4_4_4_5_5_2_5_5_5_5_1_1_1_1_1_1_2_2_2_2_2_2_4_4_2_2_2_2_2_2_2_2_3_3_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_5_1_1_1_1_1_1_1_4_4_4_4_4_4_2_2_2_2_2_3_3_3_6_6_6_6_1_1_1_6_6_6_1_1_1_2_2_2_2_2_2_2_2_4_4_4_4_4_4_5_5_5_5_2_2_2_2_2_2_2_3_3_3_3_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_1_1_1_1_1_2_2_2_2_2_2_2_2_4_4_4_4_4_2_2_2_2_2_2_2_2_2_3_3_3_5_5_5_3_3_3_3</t>
   </si>
 </sst>
 </file>
@@ -1912,7 +1927,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:K125"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -4394,7 +4409,7 @@
     </row>
     <row r="79" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A79" s="6">
-        <f t="shared" ref="A79:A89" si="4">C79*10+D79</f>
+        <f t="shared" ref="A79:A107" si="4">C79*10+D79</f>
         <v>20230016</v>
       </c>
       <c r="B79" s="14">
@@ -4746,7 +4761,7 @@
     </row>
     <row r="90" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A90" s="6">
-        <f>C90*10+D90</f>
+        <f t="shared" si="4"/>
         <v>20340021</v>
       </c>
       <c r="B90" s="14">
@@ -4778,7 +4793,7 @@
     </row>
     <row r="91" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A91" s="6">
-        <f>C91*10+D91</f>
+        <f t="shared" si="4"/>
         <v>20340022</v>
       </c>
       <c r="B91" s="14">
@@ -4810,7 +4825,7 @@
     </row>
     <row r="92" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A92" s="6">
-        <f>C92*10+D92</f>
+        <f t="shared" si="4"/>
         <v>20340023</v>
       </c>
       <c r="B92" s="14">
@@ -4842,7 +4857,7 @@
     </row>
     <row r="93" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A93" s="6">
-        <f>C93*10+D93</f>
+        <f t="shared" si="4"/>
         <v>20340031</v>
       </c>
       <c r="B93" s="14">
@@ -4874,7 +4889,7 @@
     </row>
     <row r="94" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A94" s="6">
-        <f>C94*10+D94</f>
+        <f t="shared" si="4"/>
         <v>20340032</v>
       </c>
       <c r="B94" s="14">
@@ -4906,7 +4921,7 @@
     </row>
     <row r="95" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A95" s="6">
-        <f>C95*10+D95</f>
+        <f t="shared" si="4"/>
         <v>20340033</v>
       </c>
       <c r="B95" s="14">
@@ -4938,7 +4953,7 @@
     </row>
     <row r="96" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A96" s="6">
-        <f>C96*10+D96</f>
+        <f t="shared" si="4"/>
         <v>20340041</v>
       </c>
       <c r="B96" s="14">
@@ -4970,7 +4985,7 @@
     </row>
     <row r="97" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A97" s="6">
-        <f>C97*10+D97</f>
+        <f t="shared" si="4"/>
         <v>20340042</v>
       </c>
       <c r="B97" s="14">
@@ -5002,7 +5017,7 @@
     </row>
     <row r="98" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A98" s="6">
-        <f>C98*10+D98</f>
+        <f t="shared" si="4"/>
         <v>20340043</v>
       </c>
       <c r="B98" s="14">
@@ -5034,7 +5049,7 @@
     </row>
     <row r="99" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A99" s="6">
-        <f>C99*10+D99</f>
+        <f t="shared" si="4"/>
         <v>20340051</v>
       </c>
       <c r="B99" s="14">
@@ -5066,7 +5081,7 @@
     </row>
     <row r="100" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A100" s="6">
-        <f>C100*10+D100</f>
+        <f t="shared" si="4"/>
         <v>20340052</v>
       </c>
       <c r="B100" s="14">
@@ -5098,7 +5113,7 @@
     </row>
     <row r="101" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A101" s="6">
-        <f>C101*10+D101</f>
+        <f t="shared" si="4"/>
         <v>20340053</v>
       </c>
       <c r="B101" s="14">
@@ -5130,7 +5145,7 @@
     </row>
     <row r="102" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A102" s="6">
-        <f>C102*10+D102</f>
+        <f t="shared" si="4"/>
         <v>20340061</v>
       </c>
       <c r="B102" s="14">
@@ -5162,7 +5177,7 @@
     </row>
     <row r="103" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A103" s="6">
-        <f>C103*10+D103</f>
+        <f t="shared" si="4"/>
         <v>20340062</v>
       </c>
       <c r="B103" s="14">
@@ -5194,7 +5209,7 @@
     </row>
     <row r="104" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A104" s="6">
-        <f>C104*10+D104</f>
+        <f t="shared" si="4"/>
         <v>20340063</v>
       </c>
       <c r="B104" s="14">
@@ -5226,7 +5241,7 @@
     </row>
     <row r="105" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A105" s="6">
-        <f>C105*10+D105</f>
+        <f t="shared" si="4"/>
         <v>20340071</v>
       </c>
       <c r="B105" s="14">
@@ -5258,7 +5273,7 @@
     </row>
     <row r="106" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A106" s="6">
-        <f>C106*10+D106</f>
+        <f t="shared" si="4"/>
         <v>20340072</v>
       </c>
       <c r="B106" s="14">
@@ -5290,7 +5305,7 @@
     </row>
     <row r="107" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A107" s="6">
-        <f>C107*10+D107</f>
+        <f t="shared" si="4"/>
         <v>20340073</v>
       </c>
       <c r="B107" s="14">
@@ -5632,7 +5647,7 @@
         <v>166</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>167</v>
@@ -5664,7 +5679,7 @@
         <v>166</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>168</v>
@@ -5696,13 +5711,205 @@
         <v>166</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>172</v>
+        <v>20</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>169</v>
       </c>
       <c r="J119" s="17"/>
       <c r="K119" s="17"/>
+    </row>
+    <row r="120" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A120" s="6">
+        <f>C120*10+D120</f>
+        <v>20360011</v>
+      </c>
+      <c r="B120" s="14">
+        <v>103600</v>
+      </c>
+      <c r="C120" s="33">
+        <v>2036001</v>
+      </c>
+      <c r="D120" s="33">
+        <v>1</v>
+      </c>
+      <c r="E120" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G120" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J120" s="17"/>
+      <c r="K120" s="17"/>
+    </row>
+    <row r="121" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A121" s="6">
+        <f>C121*10+D121</f>
+        <v>20360012</v>
+      </c>
+      <c r="B121" s="14">
+        <v>103600</v>
+      </c>
+      <c r="C121" s="33">
+        <v>2036001</v>
+      </c>
+      <c r="D121" s="33">
+        <v>2</v>
+      </c>
+      <c r="E121" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G121" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="J121" s="17"/>
+      <c r="K121" s="17"/>
+    </row>
+    <row r="122" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A122" s="6">
+        <f>C122*10+D122</f>
+        <v>20360013</v>
+      </c>
+      <c r="B122" s="14">
+        <v>103600</v>
+      </c>
+      <c r="C122" s="33">
+        <v>2036001</v>
+      </c>
+      <c r="D122" s="33">
+        <v>3</v>
+      </c>
+      <c r="E122" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G122" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J122" s="17"/>
+      <c r="K122" s="17"/>
+    </row>
+    <row r="123" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A123" s="6">
+        <f>C123*10+D123</f>
+        <v>20360021</v>
+      </c>
+      <c r="B123" s="14">
+        <v>103600</v>
+      </c>
+      <c r="C123" s="33">
+        <v>2036002</v>
+      </c>
+      <c r="D123" s="33">
+        <v>1</v>
+      </c>
+      <c r="E123" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G123" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J123" s="17"/>
+      <c r="K123" s="17"/>
+    </row>
+    <row r="124" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A124" s="6">
+        <f>C124*10+D124</f>
+        <v>20360022</v>
+      </c>
+      <c r="B124" s="14">
+        <v>103600</v>
+      </c>
+      <c r="C124" s="33">
+        <v>2036002</v>
+      </c>
+      <c r="D124" s="33">
+        <v>2</v>
+      </c>
+      <c r="E124" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G124" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="J124" s="17"/>
+      <c r="K124" s="17"/>
+    </row>
+    <row r="125" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A125" s="6">
+        <f>C125*10+D125</f>
+        <v>20360023</v>
+      </c>
+      <c r="B125" s="14">
+        <v>103600</v>
+      </c>
+      <c r="C125" s="33">
+        <v>2036002</v>
+      </c>
+      <c r="D125" s="33">
+        <v>3</v>
+      </c>
+      <c r="E125" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G125" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J125" s="17"/>
+      <c r="K125" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="231">
   <si>
     <t>id</t>
   </si>
@@ -614,6 +614,165 @@
   </si>
   <si>
     <t>4_4_4_4_4_4_1_1_1_1_5_5_5_4_4_4_1_1_1_1_1_1_3_3_3_3_1_1_1_1_1_1_1_1_2_2_2_2_2_2_2_2_4_4_4_4_4_4_2_2_2_2_2_2_1_1_1_1_1_1_1_1_1_5_5_5_5_5_6_6_6_6_6_3_3_3_3_3_3_2_2_2_2_2_2_3_3_3_3_3_3_3_3_3_3_4_4_4_4_4_4_4_1_1_1_1_1_1_1_1_2_2_2_2_2_2_2_2_2_3_3_3_3_3_3_2_2_2_2_5_5_5_5_5_5_1_1_1_1_1_1_1_3_3_3_3_3_1_1_1_1_1_6_6_6_6_4_4_4_4_4_1_1_1_5_5_5_3_3_1_1_1_4_4_4_4_4_4_1_1_1_1_1_4_4_4_4_4_1_1_1_1_1_2_2_2_2_2_2_2_1_1_1_1_1_1_3_3_3_3_3_3_3_3_3_2_2_2_2_2_2_2_2_2_4_4_4_4_5_5_5_6_6_6_6_6_3_3_3_3_3_2_2_2_2_2_2_2_2_1_1_1_1_1_1_2_2_2_2_2_3_3_3_3_1_1_1_1_1_1_1_2_2_2_2_2_2_2_2_2_6_6_6_6_6_6_4_4_4_4_4_4_4_5_5_5_5_5_5_2_2_4_4_4_2_2_1_1_1_1_1_1_3_3_3_3_2_2_2_2_2_1_1_1_1_1_1_1_1_4_4_4_4_4_4_5_5_2_5_5_5_5_1_1_1_1_1_1_2_2_2_2_2_2_4_4_2_2_2_2_2_2_2_2_3_3_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_5_1_1_1_1_1_1_1_4_4_4_4_4_4_2_2_2_2_2_3_3_3_6_6_6_6_1_1_1_6_6_6_1_1_1_2_2_2_2_2_2_2_2_4_4_4_4_4_4_5_5_5_5_2_2_2_2_2_2_2_3_3_3_3_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_1_1_1_1_1_2_2_2_2_2_2_2_2_4_4_4_4_4_2_2_2_2_2_2_2_2_2_3_3_3_5_5_5_3_3_3_3</t>
+  </si>
+  <si>
+    <t>6_6_6_6_6</t>
+  </si>
+  <si>
+    <t>4_7_5_11_5_4_6_2_2_2_1_10_7_7_3_3_4_4_4_3_1_8_4_1_1_7_4_6_5_2_11_5_9_3_9_4_7_2_11_4_4_4_4_2_3_8_8_2_7_2_3_7_5_1_10_1_9_8_11_5_5_3_1_9_9_9_1_2_9_3_7_3_1_10_3_6_4_7_4_11_2_2_6_4_9_3_6_2_5_2_4_6_10_7_9_9_1_4_4_4_1_9_8_10_1_2_2_5_9_1_4_4_4_3_1_2_1_3_6_3_6_1_10_7_6_10_11_5_3_8_2_2_6_1_8_4_6_7_3_5_2_2_6_3_3_1_1_2_2_9_1_5_7_2_6_6_2_1_3_9_4_8_10_5_9_1_7_7_10_10_7_2_2_2_3_9_4_3_3_8_8_4_2_2_4_6_7_4_1_2_5_8_3_1_5_7_3_4_1_4_10_6_10_1_2_7_5_4_5_1_5_8_4_8_1_1_5_8_6_3_1_10_5_11_4_11_9_11_3_2_6_6_5_7_7_3_3_3_2_4_4_9_9_7_4_4_3_7_4_4_10_2_7_7_5_2_4_8_8_1_4_4_9_9_1_1_4_2_3_8_1_7_7_9_3_3_9_11_1_4_9_3_6_6_6_4_5_2_7_2_2_2_4_2_10_11_3_5_5_2_2_9_1_4_2_2_6_6_6_2_5_9_10_9_9_6_6_4_3_3_1_10_6_1_6_7_10_8_9_9_5_8_6_9_5_6_9_3_8_1_6_1_10_4_2_1_1_3_5_9_1_1_1_1_2_5_3_5_3_3_3_7_2_3_3_9_9_9_4_7_9_6_5_11_1_5_3_6_1_7_1_3_2_2_11_3_3_9_5_5_5_8_3_1_9_3_3_2_1_5_1_1_2_6_2_1_3_1_4_5_3_2_9_6_6_2_1_8_7_3_7_1_5_1_1_7_8_7_8_9_1_2_5_4_4_3_2_8_10_4_5_5_6_8_4_6_4_4_2_6_6_3_5_3_4_1_2_2_5_2_10_10_1_6_5_2_11_2_5_2_1_10_10_6_5_10_7_4_10_3_10_10_1_3_2_10_9_9_4_6_7_2_2_3_5_5_3_4_5_2</t>
+  </si>
+  <si>
+    <t>5_7_4_8_4_11_3_2_5_3_2_4_3_9_4_8_1_1_4_7_11_4_12_3_6_11_5_1_5_9_7_13_5_2_5_2_8_10_6_3_3_4_3_2_10_4_6_6_6_4_2_3_3_8_8_6_3_4_3_1_4_8_5_7_4_8_8_4_1_1_7_3_2_2_7_1_4_2_6_9_6_2_4_3_6_7_3_11_3_5_7_6_12_8_2_9_4_2_7_2_5_8_1_4_11_6_1_8_6_6_6_7_3_3_11_6_10_7_4_2_3_7_13_6_3_3_11_7_9_6_11_4_1_3_4_1_6_11_5_12_2_3_4_3_11_8_2_2_1_10_8_10_7_3_2_2_1_8_4_7_11_5_13_5_1_5_6_7_1_11_6_4_6_6_3_8_10_5_5_12_4_2_8_9_6_3_4_11_8_3_7_1_11_8_3_12_6_2_6_9_6_3_3_8_4_3_6_4_9_1_6_3_6_6_6_2_8_5_4_13_8_12_1_2_8_3_4_1_5_1_10_6_12_1_1_2_13_7_6_2_3_5_3_10_5_1_12_4_3_11_8_3_1_8_3_5_8_2_2_2_3_5_9_6_3_7_11_7_9_8_8_9_6_4_1_6_10_7_6_11_7_13_8_8_2_8_8_4_4_1_5_6_3_8_5_7_11_6_1_2_10_6_1_4_4_10_7_3_3_11_5_5_7_1_4_6_6_3_11_8_4_13_5_1_3_2_4_4_6_4_10_7_11_7_2_3_1_2_2_9_13_4_3_6_10_6_10_6_2_3_6_5_11_4_3_10_7_6_12_6_2_2_8_7_10_4_2_2_7_4_6_1_1_6_1_3_3_4_8_1_7_4_8_8_10_6_7_7_2_1_10_8_7_9_1_12_7_2_3_8_2_2_6_10_7_4_3_3_2_6_9_1_4_10_4_4_2_1_1_1_4_7_4_2_7_1_11_7_2_6_2_5_8_3_1_8_5_5_9_2_1_5_9_3_10_4_6_7_6_9_3_4_1_10_7_1_6_3_10_8_3_4_4_8_3_2_11_6_3_7_2_2_5_1_4_1_3_1_2_1_3_3_5_6_2_2_5_2_1_4_6_2_4_3_9_11_6_3_10_8</t>
+  </si>
+  <si>
+    <t>7_7_7_7_7</t>
+  </si>
+  <si>
+    <t>5_5_5_5_1_1_1_2_5_5_4_8_2_2_4_4_1_6_10_2_1_3_7_1_3_1_1_5_9_4_7_10_3_8_4_5_11_4_2_4_9_3_6_10_2_10_8_4_3_5_3_6_6_3_2_1_5_9_9_2_5_5_4_3_7_1_8_8_5_3_5_4_1_1_2_6_2_2_2_4_6_8_11_4_4_7_1_6_3_3_3_1_1_2_2_4_5_10_2_1_3_3_3_1_7_6_2_2_7_2_5_1_1_5_4_1_9_4_4_3_3_1_6_4_4_1_3_11_9_1_2_5_3_4_5_2_2_1_1_11_2_7_2_6_6_2_1_11_5_5_5_6_2_9_10_6_3_2_2_1_1_10_4_1_8_6_6_9_8_10_1_8_1_3_4_4_6_8_4_1_2_3_2_7_2_10_9_1_4_3_2_2_2_3_1_4_3_5_2_1_1_7_8_10_6_5_3_7_6_7_5_1_1_3_9_2_7_2_3_6_5_9_1_1_4_2_2_3_4_3_3_2_1_1_4_4_4_6_4_4_1_5_1_6_2_1_5_5_8_8_6_4_1_10_10_6_6_2_2_5_5_10_8_2_8_9_4_7_11_6_6_2_8_6_1_2_1_2_4_4_5_5_5_6_6_2_3_3_9_7_3_5_8_6_10_2_3_5_2_6_8_2_5_2_5_10_4_6_2_3_11_3_1_9_1_3_4_2_4_1_7_4_6_9_1_9_5_8_2_4_1_1_6_6_2_7_7_4_8_3_3_1_5_1_6_3_3_1_9_9_4_2_4_4_4_4_2_2_1_7_2_2_3_1_6_9_5_6_8_4_4_4_5_5_5_5_7_7_10_11_7_7_4_4_1_9_3_3_8_11_4_7_4_2_4_2_2_1_3_7_2_2_4_4_3_9_5_4_2_2_10_4_8_4_2_4_2_6_1_8_8_1_1_6_3_7_3_7_1_5_1_9_10_5_10_5_5_3_1_2_2_9_1_1_4_7_3_1_1_2_3_3_2_2_10_5_2_3_2_2_2_1_1_3_1_2_2_11_6_4_2_5_5_2_5_11_1_2_1_3_2_2_11_2_2_9_5_1_6_8_8_3_4_4_2_11_5_5_7_5</t>
+  </si>
+  <si>
+    <t>7_12_8_6_3_7_10_8_6_10_6_5_7_2_8_8_5_10_2_2_11_3_6_5_4_3_4_5_1_6_13_6_7_8_10_4_6_5_2_7_2_11_8_4_12_8_4_6_6_13_3_3_6_4_5_5_6_9_1_2_8_2_6_2_5_2_2_5_6_6_11_8_13_4_4_9_5_3_6_10_5_2_11_8_6_2_6_6_4_1_7_4_2_8_13_4_7_1_2_3_1_4_9_7_6_1_5_10_7_11_3_1_1_7_5_8_1_4_8_1_2_2_11_3_8_6_2_4_2_3_2_11_4_3_8_2_6_2_8_7_1_7_4_10_8_6_4_7_11_4_13_8_5_3_9_3_8_2_2_7_3_3_8_1_3_3_3_7_7_1_2_6_9_5_3_6_5_12_8_1_13_3_1_5_3_4_3_2_4_5_4_5_2_11_2_11_6_3_4_5_8_4_6_8_6_5_2_7_4_2_1_4_1_2_4_2_4_6_12_6_2_11_2_13_8_2_2_1_8_6_1_11_6_1_2_6_4_3_10_7_3_1_7_10_4_2_5_5_2_3_4_13_8_8_3_3_2_11_7_6_2_6_5_4_11_4_1_10_6_3_6_5_8_1_2_12_1_1_3_13_7_1_1_10_8_10_8_6_7_11_7_5_4_5_4_6_1_8_6_9_2_4_13_1_1_4_3_12_8_8_10_2_3_11_5_3_1_1_11_6_3_1_1_8_12_8_3_3_5_3_6_5_11_2_4_2_1_2_7_5_2_6_6_3_1_13_5_7_6_10_8_5_1_8_4_7_8_1_10_2_4_1_13_8_5_2_5_1_12_8_9_1_6_11_8_7_4_4_5_7_3_9_3_4_6_1_5_3_4_1_2_9_8_13_5_4_3_9_1_7_1_1_7_1_4_13_6_1_8_2_1_4_4_6_2_9_2_4_7_10_8_2_11_6_5_10_7_8_6_3_2_8_1_2_4_3_8_2_2_8_7_7_4_6_3_6_6_1_2_12_7_2_4_3_4_2_4_13_4_13_7_7_10_6_2_13_5_4_9_6_7_1_12_7_8_3_3_7_4_9_4_1_5_4_7_9_3_12_5_7_11_8_7_10_3_8_10_8_13_2</t>
+  </si>
+  <si>
+    <t>8_8_8_8_8</t>
+  </si>
+  <si>
+    <t>5_1_2_2_2_6_6_6_10_4_4_4_5_5_4_4_4_3_3_10_6_1_4_2_2_2_10_9_6_8_3_4_1_5_5_9_1_2_2_1_2_7_10_3_4_5_2_4_4_4_6_6_11_6_1_2_5_8_8_2_2_6_10_6_3_2_2_6_8_4_4_6_1_7_7_7_10_10_6_4_4_4_5_11_10_1_1_8_8_5_3_4_6_9_1_4_4_3_3_9_9_4_3_1_6_5_7_3_2_2_2_2_8_3_7_3_8_7_2_2_2_8_8_10_10_6_6_6_10_7_5_6_2_7_5_1_2_2_11_2_4_4_2_10_3_9_4_3_10_7_8_3_5_1_8_10_10_10_2_5_3_3_1_1_4_4_7_2_3_7_2_2_2_2_10_5_9_8_6_2_3_1_11_4_5_5_7_7_7_3_3_5_8_8_8_7_5_2_5_5_4_8_7_4_1_5_2_4_2_5_8_8_4_1_4_4_10_1_3_2_1_9_2_1_2_2_7_8_5_10_6_4_3_10_4_10_2_3_1_4_8_1_6_3_2_2_2_7_1_3_3_8_11_5_3_2_8_4_5_3_2_1_1_4_5_6_6_3_5_5_10_4_3_9_6_6_6_6_11_7_5_5_9_9_1_1_2_1_6_8_8_10_4_7_11_11_4_2_6_8_2_9_1_2_1_7_1_4_6_1_1_1_10_6_9_8_6_10_6_1_1_5_3_3_6_8_8_1_5_7_8_2_10_6_3_1_4_6_6_6_3_3_9_4_6_1_2_7_8_1_4_4_4_3_7_8_8_8_1_3_9_1_6_8_6_8_8_2_2_3_5_9_10_1_6_8_1_3_1_6_6_3_6_4_7_2_2_4_1_5_5_2_2_10_1_5_8_7_4_2_2_7_6_7_3_10_4_6_1_5_3_3_4_6_7_2_4_3_6_6_6_3_2_1_4_6_5_5_8_9_4_4_5_3_2_5_5_4_5_8_1_6_4_3_9_7_7_3_9_1_8_4_5_4_4_11_3_6_7_3_11_8_9_3_8_5_4_7_1_6_5_2_8_6_4_8_1_2_4_6_1_5_7_6_2_2_7_1_9_3_3_4_6_6_8_8_2_5_3_6</t>
+  </si>
+  <si>
+    <t>8_2_11_2_9_3_4_8_13_5_3_11_6_8_4_1_6_2_6_2_8_8_7_5_1_9_4_8_9_4_3_11_5_1_11_6_7_9_9_4_2_1_1_1_9_3_3_12_7_6_6_3_3_2_6_1_6_7_7_7_9_4_6_5_2_9_13_5_3_2_2_1_1_4_5_7_7_7_6_10_6_8_7_4_7_7_10_8_1_4_6_12_6_1_4_5_5_1_3_1_2_1_8_8_2_2_8_2_8_3_8_1_1_2_5_6_1_10_7_6_4_10_3_8_3_2_13_7_11_8_1_6_2_5_8_5_7_4_3_2_3_4_11_8_3_11_3_1_13_4_6_4_2_1_7_8_4_6_8_8_9_5_5_3_7_2_2_2_1_8_6_11_7_2_4_2_3_2_2_10_4_2_2_1_4_7_2_8_5_4_10_7_2_2_11_8_2_8_3_4_8_3_3_3_1_2_7_3_9_13_6_13_2_6_1_11_3_9_13_7_11_6_1_6_3_4_12_5_10_7_1_3_2_8_6_2_11_4_1_7_1_5_6_8_8_1_1_9_3_3_9_8_2_4_2_2_4_1_6_12_7_8_13_8_1_7_1_2_13_4_3_2_4_10_2_5_10_8_13_4_4_4_1_8_8_3_4_2_8_2_13_8_3_4_2_5_9_4_8_8_1_9_2_2_4_3_6_6_4_8_4_3_11_6_3_13_8_1_4_7_8_2_6_4_11_7_9_1_8_6_8_13_6_8_2_5_5_4_8_4_4_13_4_4_3_3_1_1_5_2_1_1_6_8_4_11_5_4_7_5_4_5_3_10_7_2_7_6_3_3_3_8_4_11_2_10_3_7_5_6_1_3_2_3_6_8_11_5_4_5_5_2_3_4_8_11_5_7_8_6_4_11_3_7_5_2_4_3_5_2_4_2_2_9_10_5_2_6_1_2_2_2_3_2_7_2_1_1_5_2_5_3_1_4_8_6_2_1_9_4_8_1_5_6_5_3_4_10_7_6_3_2_5_1_9_5_6_4_9_3_2_6_2_2_7_5_2_6_3_8_11_1_1_11_3_7_5_9_13_5_1_2_2_11_8_10_2_2_7_6_1_5_7_9_4_2_12_6_4_13</t>
+  </si>
+  <si>
+    <t>9_9_9_9_9</t>
+  </si>
+  <si>
+    <t>2_5_1_2_4_4_8_4_3_2_4_4_8_8_8_11_2_3_1_2_2_1_11_1_3_7_8_6_10_10_4_4_1_6_3_1_1_1_5_1_3_2_4_5_4_8_7_1_4_2_1_4_4_9_6_9_2_3_3_8_8_6_1_1_6_9_8_3_4_4_4_3_2_3_1_9_4_1_8_3_10_10_10_6_3_5_1_4_4_4_1_11_4_1_3_11_4_9_3_5_3_1_3_1_8_8_3_8_7_11_11_1_8_3_1_1_1_4_11_5_2_1_1_10_2_1_2_1_3_3_3_4_6_6_5_1_7_2_1_8_7_7_1_3_8_1_7_6_2_8_1_4_5_7_5_4_1_8_8_7_1_2_3_2_1_2_1_7_10_2_3_2_8_8_1_3_3_10_10_3_9_1_5_11_4_4_6_6_1_5_2_6_7_9_3_5_5_5_5_4_3_11_5_4_8_1_2_7_7_8_6_6_3_2_2_1_6_6_6_7_3_2_2_1_8_2_3_4_11_8_10_10_2_5_8_4_2_5_8_2_6_3_7_7_8_4_6_4_1_2_2_2_8_4_4_6_6_1_1_5_6_2_3_1_1_2_5_6_5_9_10_10_7_5_6_1_8_2_9_9_2_4_3_1_3_2_4_5_4_5_7_7_2_7_5_7_7_10_5_3_2_2_9_10_3_3_1_4_6_11_2_8_8_3_2_4_5_3_1_8_1_1_9_5_4_8_10_10_4_6_6_5_1_1_8_2_8_11_8_2_1_5_6_6_4_4_4_6_2_1_7_7_6_4_6_4_2_10_5_5_1_8_4_4_4_4_4_4_8_7_7_9_2_5_6_7_3_10_3_3_2_6_4_6_1_5_8_10_9_4_5_1_6_2_5_9_10_9_1_10_1_1_1_3_4_3_4_4_6_2_2_2_5_3_2_8_9_3_6_6_5_4_3_3_3_3_2_1_7_8_3_2_4_6_5_9_6_8_2_2_7_8_10_2_11_3_11_9_9_6_5_1_3_4_2_8_4_4_2_2_6_3_7_4_1_2_4_9_2_8_2_5_6_2_1_5_9_5_10_4_2_5_3_3_2_4_4_4_10_1_1_1_10_6_6_6_4_3_8_3</t>
+  </si>
+  <si>
+    <t>2_5_3_6_5_2_10_7_2_6_12_3_1_8_9_4_1_2_3_6_12_8_3_1_6_5_6_3_5_5_2_1_11_8_5_4_4_3_5_3_2_4_3_1_2_7_1_2_13_5_5_5_2_4_9_1_10_7_4_9_9_3_3_2_8_7_3_2_3_4_5_3_1_1_1_11_2_7_7_8_4_4_3_1_9_1_4_4_3_6_1_3_10_6_7_9_5_1_1_10_8_3_1_7_7_1_2_9_5_3_5_8_2_6_8_2_2_13_6_10_7_9_2_1_6_7_1_7_10_3_10_7_1_6_10_2_1_6_2_11_1_8_2_9_4_8_5_6_1_4_13_5_4_6_4_9_11_2_2_9_9_6_4_9_2_10_8_9_13_7_3_2_3_9_9_7_10_7_3_7_4_10_8_4_4_6_2_6_8_10_4_8_1_3_7_8_3_10_7_6_5_9_1_1_10_5_1_5_8_7_1_3_4_1_4_5_10_8_2_11_6_1_13_4_6_9_13_8_2_3_11_8_13_6_2_2_8_3_7_8_6_4_6_1_13_5_4_5_12_8_7_6_13_2_10_6_9_11_7_1_4_3_4_4_9_3_6_4_2_2_1_3_2_1_3_5_5_3_7_6_2_2_7_10_5_1_1_2_1_5_6_8_10_7_4_3_7_1_3_11_2_2_8_6_1_11_8_6_1_4_5_5_4_7_2_13_1_8_7_5_3_4_11_1_8_6_4_6_4_5_10_8_1_7_1_1_1_2_10_1_1_10_7_1_2_1_1_7_13_2_9_4_4_3_4_12_8_8_6_2_6_6_13_4_4_1_5_10_5_4_8_1_2_9_7_6_13_7_1_1_2_4_1_2_4_10_5_3_6_6_2_2_5_5_2_4_5_2_3_1_2_3_1_6_10_6_1_1_4_5_12_4_5_5_2_8_7_10_5_1_9_5_5_3_8_5_2_1_10_5_11_8_5_4_4_4_8_1_12_6_1_4_2_7_1_4_1_8_1_1_8_1_11_7_3_6_8_3_10_2_4_1_3_1_1_4_7_7_10_8_1_6_3_4_1_1_8_4_6_6_9_2_4_9_7_2_3_3_10_8_8_1_1_4_3_1_3_2_3_1</t>
+  </si>
+  <si>
+    <t>10_10_10_10_10</t>
+  </si>
+  <si>
+    <t>2_4_7_3_11_2_5_2_5_2_8_3_6_4_7_6_4_1_8_10_8_3_4_1_8_2_5_1_10_2_6_2_1_3_5_8_4_4_4_4_3_8_4_3_3_3_3_5_4_1_10_7_6_2_1_9_2_2_5_8_1_2_4_3_10_1_4_2_10_1_6_1_6_1_9_5_3_10_9_2_5_5_2_3_1_1_1_4_2_2_5_1_2_4_4_4_5_11_6_6_7_9_3_2_8_2_1_4_10_2_4_6_3_3_1_3_9_10_1_11_5_2_6_9_1_2_2_2_1_6_4_3_3_5_3_3_4_5_7_2_3_3_4_2_2_1_2_7_7_7_1_5_2_6_5_5_5_1_8_5_2_3_1_7_6_3_4_4_3_5_5_5_10_5_5_1_3_2_7_8_8_1_3_5_9_11_11_5_5_1_1_6_9_3_2_8_7_1_2_7_11_2_8_6_5_7_4_6_8_5_5_3_6_2_2_2_11_6_4_8_1_5_5_3_1_7_2_8_6_8_9_6_8_1_1_8_5_1_1_1_6_3_10_1_3_3_6_4_1_1_6_2_8_1_5_10_3_5_8_7_2_3_9_1_9_5_3_3_5_1_5_8_8_8_4_4_2_4_8_3_5_1_7_1_1_1_6_6_5_2_1_9_4_8_5_1_1_2_2_10_8_6_6_3_3_7_8_6_7_7_2_1_1_6_10_4_2_2_7_5_5_5_2_1_5_5_8_8_7_5_2_6_8_6_3_4_1_3_1_5_2_8_8_1_3_4_9_8_6_6_6_4_4_3_1_1_4_3_1_3_10_3_3_3_4_1_3_6_10_2_9_9_1_6_5_5_5_5_5_5_5_8_5_5_9_3_3_4_11_2_9_2_11_11_2_8_5_8_8_4_7_2_2_8_4_5_7_3_4_4_1_10_5_3_3_11_1_6_4_10_4_5_7_3_3_5_3_5_2_6_1_3_2_4_9_4_5_7_7_2_2_1_6_6_4_2_4_10_5_6_1_11_4_2_2_5_2_1_10_7_7_3_3_1_3_1_4_5_5_10_2_1_2_9_7_10_9_11_3_3_3_5_4_5_10_10_2_1_3_11_1_9_8_11_3_3_4_10_6_6</t>
+  </si>
+  <si>
+    <t>4_8_1_11_8_8_3_8_1_8_3_2_3_3_4_12_5_12_5_3_8_7_2_8_1_7_8_2_4_5_11_4_2_5_10_5_6_5_8_4_6_9_7_6_7_2_5_8_2_2_1_3_6_3_12_1_10_4_1_4_9_13_3_6_8_1_11_6_3_4_7_5_2_4_3_13_4_1_1_13_4_5_13_2_6_9_3_5_4_7_2_10_7_6_3_12_7_6_1_1_4_2_6_11_2_5_3_2_6_5_1_5_1_9_3_1_2_4_5_11_4_5_11_3_3_7_1_1_4_2_4_4_5_1_3_13_6_9_3_2_6_5_3_4_8_13_2_5_8_8_9_2_4_5_4_1_6_9_5_4_2_4_1_11_7_5_11_7_3_3_8_13_8_5_4_10_8_4_7_7_6_3_8_7_1_7_1_7_12_6_8_3_5_1_5_7_1_7_5_1_6_2_3_9_3_5_2_1_6_1_4_5_7_10_6_6_11_2_8_3_4_4_13_7_5_11_3_5_5_2_5_1_1_9_1_10_5_2_1_4_1_2_3_1_1_1_2_6_10_7_6_3_6_3_4_1_6_10_6_4_4_2_10_7_6_2_11_2_7_9_6_2_2_3_3_2_2_6_2_9_2_11_7_6_5_4_6_2_3_10_7_11_7_2_12_6_8_3_3_5_2_2_8_3_5_4_9_2_2_2_2_8_2_6_4_4_6_6_9_7_9_7_6_2_11_4_1_7_4_5_5_1_4_5_2_3_10_5_4_7_2_6_8_7_2_3_5_13_8_7_1_11_8_6_5_3_2_5_5_12_8_6_1_5_3_3_8_2_7_2_4_6_12_7_3_4_5_7_2_3_1_6_5_1_12_6_4_1_1_2_1_10_6_3_5_10_8_11_8_2_12_7_7_2_7_6_1_1_3_4_10_4_8_8_12_4_2_4_1_1_1_3_1_5_5_3_3_9_2_3_8_8_3_1_8_2_2_5_9_1_1_4_7_6_12_6_2_5_2_6_1_8_4_5_4_2_3_3_3_5_2_1_13_3_2_8_5_8_8_7_11_8_9_4_1_11_8_9_9_2_11_6_6_13_5_11_7_11_4_1_11_6_6_7_4_9_2_1_3_2</t>
+  </si>
+  <si>
+    <t>11_11_11_11_11</t>
+  </si>
+  <si>
+    <t>8_1_1_8_4_7_8_5_5_3_7_6_6_6_7_10_3_8_1_3_5_10_8_1_2_8_7_5_5_2_2_5_4_11_3_4_3_8_8_4_4_7_3_2_5_1_3_5_11_3_4_1_6_3_9_5_5_10_5_1_4_1_9_9_3_2_1_1_6_6_6_8_3_6_7_9_7_1_8_7_8_2_2_4_1_8_2_2_2_1_8_10_4_8_2_1_7_7_2_1_10_2_1_8_1_2_2_1_3_3_2_10_2_7_6_2_2_1_4_8_2_2_2_2_2_2_1_3_6_6_2_10_5_10_6_8_8_1_3_3_8_8_5_10_2_6_7_7_6_4_7_4_5_7_4_6_6_2_6_4_3_3_3_6_3_7_6_2_7_7_3_4_7_9_4_1_5_5_2_7_4_2_8_5_1_9_4_1_4_8_10_7_2_2_5_6_3_3_11_10_7_2_6_2_5_4_1_9_3_3_2_8_3_3_4_4_2_4_9_6_7_8_3_4_1_3_1_9_8_2_2_4_7_2_8_1_1_9_2_3_3_3_3_1_4_1_1_6_3_9_3_3_4_6_5_1_3_1_2_3_2_1_1_1_9_5_2_2_3_2_5_6_7_1_5_4_3_7_4_2_2_1_8_6_8_7_1_4_9_10_11_2_4_4_3_9_2_1_1_6_10_6_1_8_1_1_7_7_11_9_9_1_2_8_4_3_3_3_5_9_4_2_2_2_9_3_4_1_3_1_6_9_4_2_1_8_8_7_2_4_2_8_3_8_2_5_5_2_4_6_8_3_4_8_3_1_3_3_10_5_4_6_1_1_1_2_9_3_4_10_8_8_6_1_8_8_4_1_1_4_5_4_4_1_8_10_4_8_7_4_9_3_8_8_7_10_1_9_4_1_8_7_8_8_6_2_1_1_8_9_11_1_1_5_3_10_6_1_6_8_8_2_2_2_4_1_7_7_10_10_10_5_5_3_2_8_3_3_1_8_8_1_1_7_10_1_8_1_10_9_1_5_2_10_5_9_4_2_2_2_6_7_3_6_4_1_1_6_2_2_8_2_2_6_1_10_9_2_7_4_4_4_5_2_2_2_2_7_7_7_2_8_8_8_2_2_8_9_2_3</t>
+  </si>
+  <si>
+    <t>4_3_13_6_5_4_3_1_4_5_3_4_11_7_3_4_7_8_6_4_3_2_4_7_2_2_1_11_2_11_6_13_8_10_7_2_3_4_8_4_5_4_4_1_1_4_3_7_5_4_5_6_8_1_5_11_5_8_3_4_5_8_11_5_7_4_11_6_5_11_4_10_8_10_6_5_11_6_8_4_11_6_1_4_9_3_5_1_2_8_3_9_2_3_1_7_12_6_7_1_7_8_3_4_1_13_7_5_4_2_11_7_7_2_1_12_6_3_1_9_4_3_10_2_6_7_11_5_6_2_6_4_10_4_6_2_3_11_6_8_8_13_2_6_4_7_3_4_1_7_3_4_6_1_3_11_7_5_6_11_7_4_10_4_4_9_2_4_6_10_7_2_2_7_3_1_8_5_2_9_12_2_4_2_8_2_8_2_12_8_2_1_3_4_7_4_2_9_4_6_3_1_11_5_1_1_11_8_6_3_2_8_10_1_2_3_4_5_8_4_3_7_5_4_6_5_11_8_3_1_8_6_5_5_1_6_11_5_8_1_3_6_9_9_2_6_1_9_7_4_2_8_6_10_8_2_7_3_3_4_7_8_7_1_6_4_5_2_5_4_2_5_3_6_6_4_3_6_7_5_1_5_2_7_8_7_12_7_2_9_10_3_9_9_1_2_10_5_6_3_6_6_13_4_6_7_8_10_2_9_1_4_2_3_4_8_1_7_5_3_1_7_7_1_9_4_7_1_4_10_7_5_12_8_1_2_4_1_7_5_1_5_2_5_6_12_3_7_5_5_1_5_1_3_2_9_4_8_2_7_4_6_4_9_1_13_7_4_3_3_3_10_8_4_1_12_8_12_6_10_7_11_5_13_6_8_13_8_10_8_1_8_5_3_6_3_3_3_8_6_11_8_11_8_3_5_5_6_2_11_8_9_2_4_9_6_6_1_1_13_8_4_10_7_5_7_8_10_8_2_4_11_8_12_5_5_1_6_4_4_8_1_9_3_3_5_6_7_3_1_3_4_6_7_13_5_5_6_13_3_8_10_6_4_7_7_4_3_4_4_5_10_1_10_2_10_8_4_4_2_6_8_3_1_3_5_5_2_13_5_3_4_3_2_6_6_3_3_1_4</t>
+  </si>
+  <si>
+    <t>16_16_16_16_16</t>
+  </si>
+  <si>
+    <t>16_10_3_13_13_13_10_10_4_20_20_12_12_2_2_2_11_11_2_19_7_9_9_19_1_1_1_1_11_2_16_15_14_14_11_12_7_7_12_6_2_2_2_5_5_8_14_14_15_15_15_1_18_13_13_8_4_5_15_6_2_6_6_6_6_6_16_19_6_7_4_5_5_10_10_5_1_8_6_12_12_15_15_3_7_7_15_7_7_11_18_6_14_15_17_9_9_10_10_10_10_10_10_3_10_2_2_7_7_2_1_10_6_3_3_9_18_18_18_18_5_5_2_2_2_2_3_3_3_10_10_16_13_8_8_8_8_8_10_10_13_3_3_16_8_8_2_2_1_1_1_19_11_12_12_12_5_12_10_15_15_15_15_4_4_16_16_7_10_10_10_10_5_11_3_5_2_7_14_14_18_18_7_7_7_12_19_19_19_19_1_12_12_12_12_17_17_8_8_20_7_12_8_8_8_7_7_1_15_15_3_3_3_16_3_3_6_18_1_1_8_8_8_15_3_3_3_2_11_11_19_6_6_11_17_3_3_3_11_4_1_6_8_2_4_11_11_11_11_11_6_7_7_19_19_11_11_11_11_11_11_3_3_3_17_17_17_1_1_1_19_14_6_4_4_3_20_20_20_20_20_20_20_5_5_12_7_7_7_7_18_4_7_7_7_7_5_13_4_11_11_11_11_7_3_3_3_13_8_8_8_9_15_14_14_6_4_4_4_3_1_4_16_16_5_1_1_14_15_15_15_3_3_4_2_2_2_8_1_1_1_1_7_19_12_9_9_4_11_15_15_15_15_9_6_11_11_12_12_3_14_14_7_5_10_1_11_6_6_6_4_4_4_4_10_10_19_14_2_17_20_20_6_6_6_6_6_4_14_9_9_9_14_19_19_19_9_15_15_10_10_10_7_2_12_7_2_10_3_3_3_18_18_15_1_17_17_17_6_5_5_20_10_10_9_8_18_6_6_6_6_4_2_1_12_12_15_6_6_5_2_4_19_3_8_5_5_8_8_6_6_6_16_4_2_2_20_12_8_6_10_10_3_14_14_14_14_14_14_14_11_13_13_12_12_3_3_3_3_3_11_7_10_8_8_9_10_10_4_1_10_1_6_6_6_7_6_6_6_9</t>
+  </si>
+  <si>
+    <t>16_7_9_6_10_10_14_7_7_7_20_6_6_14_14_16_15_2_10_7_7_15_15_13_13_13_13_13_13_13_5_4_14_14_14_1_1_5_16_8_8_8_8_3_3_3_3_8_2_6_6_6_6_3_8_8_8_11_11_11_16_14_14_17_17_17_17_17_6_6_9_1_1_1_1_6_14_14_10_13_13_13_15_8_8_6_8_8_10_10_10_5_14_16_16_16_16_13_6_6_1_1_15_15_10_10_5_5_4_4_4_4_16_8_8_8_8_18_13_16_17_3_4_4_5_7_7_7_7_6_4_5_12_12_8_8_8_8_1_4_11_4_4_4_9_3_3_9_12_12_12_5_5_15_15_15_16_15_6_6_6_19_18_9_2_19_19_4_5_10_4_16_4_15_15_15_6_6_17_17_4_15_15_15_12_2_2_2_2_3_7_11_2_10_4_4_16_19_4_5_15_13_3_9_9_8_8_14_8_17_17_14_3_3_3_3_1_1_6_6_5_9_9_9_6_6_4_15_15_15_2_5_2_19_18_9_17_17_17_17_17_9_8_8_9_9_9_8_3_3_8_10_14_7_7_7_7_7_8_3_9_9_19_17_17_12_12_4_7_9_14_14_5_5_9_9_9_11_10_19_11_17_11_11_11_11_9_14_7_10_14_14_4_2_7_7_14_3_3_3_5_2_3_3_11_9_9_10_16_16_14_1_1_2_14_3_18_17_17_15_15_1_1_1_1_14_9_13_4_1_1_6_6_8_10_14_18_5_12_12_6_6_16_13_13_13_5_14_14_14_9_5_4_4_16_3_3_13_13_16_9_9_3_10_2_2_14_8_8_16_5_6_2_4_7_1_15_15_5_18_18_8_9_1_4_4_5_12_7_16_16_16_8_10_3_3_3_3_1_1_1_9_9_19_3_3_2_2_9_9_2_2_9_2_2_10_2_8_8_5_5_5_5_13_13_13_13_13_13_18_11_11_11_8_3_3_3_3_13_8_9_9_2_2_17_3_3_3_1_1_1_1_1_8_8_8_7_6_6_6_10_10_10_17_18_5_14_14_14_14_4_7_11_13_13_4_4_6_6_14_9_9_9_9_7_15_15_15_4_18_1_1_6_15_12_5_16_9_4_4</t>
+  </si>
+  <si>
+    <t>17_17_17_17_17</t>
+  </si>
+  <si>
+    <t>19_19_14_14_14_14_15_6_3_2_8_16_1_6_6_3_4_6_6_6_6_7_7_6_6_6_6_10_10_4_3_5_1_3_3_3_4_4_9_9_9_19_19_19_14_12_12_16_16_16_11_2_2_4_16_16_7_16_7_6_13_17_8_8_11_7_7_7_8_8_8_16_16_12_4_4_4_8_8_8_18_2_2_3_17_9_9_15_13_6_6_7_7_7_7_16_15_16_3_3_10_18_18_9_9_2_2_14_8_10_10_6_6_5_4_15_15_10_9_9_6_16_14_14_8_8_10_4_8_13_13_13_13_8_17_12_12_12_12_2_10_17_17_9_13_13_7_2_10_7_1_3_3_5_5_5_12_6_8_8_8_8_8_8_18_18_18_18_18_18_7_7_14_2_7_8_9_11_4_1_2_2_2_2_2_11_11_1_3_11_1_16_16_7_3_2_2_2_2_16_16_4_4_7_8_8_8_16_16_16_15_10_15_1_12_3_3_3_10_10_10_1_1_1_5_5_5_6_7_7_4_4_4_15_3_3_3_3_3_3_3_3_5_5_18_13_5_5_1_1_10_20_20_20_13_13_11_10_15_15_15_8_1_7_15_15_15_15_5_10_19_5_5_5_5_5_14_2_2_2_2_11_11_15_9_9_9_9_9_5_5_7_7_1_1_7_17_9_9_3_1_16_8_8_8_8_8_14_14_14_13_10_10_10_10_10_19_14_4_8_18_11_11_8_5_5_5_5_5_2_10_10_10_10_1_1_8_8_5_18_19_19_13_11_5_5_3_20_5_5_5_6_6_6_6_6_6_16_9_9_2_2_12_6_6_6_9_9_4_6_1_1_5_2_2_1_2_2_8_9_12_12_3_3_3_3_3_8_8_9_9_1_1_8_10_4_6_4_4_14_8_12_12_10_15_6_14_14_6_6_6_20_20_8_8_8_8_8_15_13_2_2_2_2_4_11_11_19_16_9_1_1_4_8_15_15_12_12_8_7_2_5_7_17_8_7_2_10_10_4_19_7_7_17_8_8_8_8_3_3_3_12_12_3_9_9_12_12_12_2_4_2_5_9_1_16_16_1_1_2_2_3_3_2_2_3_3_11_18_1_1_3_7_7_13_13_11_2_19_12</t>
+  </si>
+  <si>
+    <t>10_17_1_11_11_11_6_6_12_2_2_2_11_11_14_14_5_5_10_20_20_20_3_8_2_2_2_2_2_11_16_10_5_13_11_11_18_18_10_10_10_11_11_4_17_7_7_17_17_17_6_6_10_3_19_19_19_9_9_11_11_11_13_13_13_20_18_16_19_6_15_2_2_3_3_8_8_8_8_5_2_2_2_6_18_18_18_20_20_20_1_1_17_17_17_17_1_13_13_13_9_16_15_15_2_13_13_13_18_18_18_13_13_11_11_11_5_5_9_16_4_4_4_8_18_16_19_4_4_4_10_10_12_5_5_3_13_16_3_2_2_2_18_12_12_12_3_1_7_7_7_7_7_7_7_8_8_8_11_9_9_9_9_10_10_10_2_2_4_4_13_13_13_2_5_8_9_13_20_20_11_13_18_18_19_19_9_20_20_20_20_20_4_14_5_5_14_1_1_9_9_10_12_12_10_15_4_4_7_10_10_3_10_7_10_10_5_9_9_9_14_14_14_14_14_11_12_15_8_3_15_15_1_10_10_10_10_10_10_18_10_5_13_13_13_3_3_3_3_16_18_17_9_9_13_13_3_12_2_2_10_6_13_13_5_6_6_11_3_3_3_2_15_4_5_5_7_7_13_18_18_18_1_1_1_1_1_1_14_3_3_9_20_5_1_1_1_5_10_16_2_8_5_8_3_12_16_8_5_5_5_7_9_9_9_13_13_13_12_7_7_5_2_2_2_6_6_12_16_16_10_10_10_10_14_14_17_13_13_7_1_4_4_8_7_15_13_13_10_15_8_13_13_7_7_2_9_9_9_19_19_19_18_8_7_12_3_12_12_10_10_10_15_20_20_20_4_4_9_9_2_2_2_10_10_16_16_19_15_15_8_7_7_7_7_18_18_12_8_16_6_6_18_20_20_20_18_2_5_5_5_5_5_1_1_1_8_14_14_19_1_1_9_9_9_4_4_12_19_13_13_13_13_13_5_1_6_6_6_6_3_17_7_18_18_3_11_12_3_3_13_13_6_3_3_3_14_13_17_6_6_4_13_6_6_6_7_7_7_7_7_6_6_6_10_10_10_10_9_11_2_2_2_19_19_10_10_13_13_11_17_7_2_2_2_8_8_3_5_5</t>
+  </si>
+  <si>
+    <t>18_18_18_18_18</t>
+  </si>
+  <si>
+    <t>2_2_2_2_7_13_13_5_8_2_2_2_2_13_13_13_9_9_4_3_3_15_3_16_15_15_15_15_15_2_4_4_9_9_9_5_17_6_6_3_16_9_9_9_8_8_8_8_13_13_19_19_19_19_20_20_20_4_4_3_1_6_6_6_6_6_3_3_6_6_9_9_9_9_3_3_3_8_6_7_6_6_6_6_5_5_5_5_5_7_20_18_17_7_7_20_3_3_3_10_10_19_19_6_6_6_5_14_14_17_17_5_4_6_6_6_6_6_8_12_12_12_10_10_6_20_11_14_14_14_1_6_6_9_4_16_16_17_8_8_8_3_5_2_2_2_6_14_10_7_13_13_7_7_7_6_6_6_3_1_1_1_12_16_4_7_9_15_9_7_20_20_11_11_2_16_16_2_2_11_15_2_12_13_13_13_13_12_12_18_18_18_17_16_16_16_2_11_11_7_16_16_8_8_2_9_9_9_2_2_2_9_9_4_4_4_6_2_3_3_3_2_2_2_12_7_14_15_15_1_1_1_16_16_7_3_6_6_9_9_9_6_5_5_5_2_11_20_20_20_10_10_10_10_11_6_6_18_11_11_14_14_14_4_4_4_4_4_9_9_9_9_9_17_15_20_20_20_20_20_20_20_13_10_6_6_1_1_1_1_12_12_3_3_1_12_9_9_9_6_12_6_6_6_6_6_8_8_18_13_3_1_1_14_3_6_6_6_11_11_13_1_20_10_7_7_8_2_7_3_3_6_6_7_7_3_3_3_3_8_8_17_8_6_7_14_9_9_9_3_3_5_11_15_15_14_11_11_10_9_12_12_13_13_15_17_5_5_7_5_5_5_15_15_15_14_17_17_20_20_6_6_6_17_2_1_1_1_10_18_12_17_9_17_11_11_11_11_3_19_19_9_8_8_8_10_10_10_10_5_11_3_3_7_9_9_15_9_9_16_3_5_4_11_4_15_14_3_15_1_20_20_16_16_3_3_5_1_1_16_14_14_14_14_6_5_5_8_4_4_14_14_14_13_3_3_3_3_3_5_4_6_11_11_11_16_16_8_8_3_3_6_8_8_7_7_12_12_1_1_1_19_9_7_12_7_3_6_6_3_3_3_3_3_3_12_14_14_15_15</t>
+  </si>
+  <si>
+    <t>5_5_5_19_1_15_5_15_15_15_5_5_2_2_2_2_9_9_20_3_10_10_8_12_2_19_7_15_15_15_15_7_6_17_8_8_8_8_8_15_3_3_14_14_10_10_10_12_16_16_16_11_11_11_11_13_6_6_10_10_9_9_9_15_6_7_14_11_11_11_6_10_8_1_1_1_1_15_20_13_13_16_16_19_13_13_10_10_17_17_5_7_15_15_8_14_6_6_3_4_14_17_17_11_10_3_3_3_3_3_3_2_8_13_9_9_4_15_13_13_4_11_5_1_19_19_16_1_1_16_16_3_3_3_18_18_10_8_8_10_4_8_8_3_3_6_6_6_2_20_5_18_1_10_13_4_4_4_3_3_3_3_3_4_11_4_4_4_4_12_15_15_2_13_19_7_7_10_14_8_8_12_14_14_14_15_16_16_16_16_1_12_12_11_16_5_14_5_5_5_3_3_4_8_8_2_13_6_6_6_17_17_15_8_5_5_5_16_5_7_9_9_5_15_15_13_8_16_4_6_15_13_13_11_16_16_5_3_17_17_20_4_11_1_1_1_1_1_4_6_13_4_4_1_1_5_16_6_3_12_3_3_3_3_3_3_11_11_11_11_4_11_11_11_3_3_14_14_3_3_11_7_7_18_18_18_18_3_3_8_2_3_11_11_7_7_16_12_7_16_6_6_19_2_15_18_15_15_15_15_15_15_12_6_6_6_1_1_1_4_20_20_1_7_1_1_1_1_1_1_18_17_17_17_11_11_11_7_8_16_16_9_4_3_3_8_10_1_14_5_5_13_13_4_7_7_7_16_16_16_11_7_7_7_7_7_11_13_16_2_20_8_7_7_11_16_16_16_16_19_7_6_5_1_1_1_7_5_2_16_1_12_12_9_9_9_9_4_1_17_17_17_17_9_9_1_1_1_1_1_4_4_8_8_8_12_12_12_12_10_2_5_5_5_5_5_10_10_17_17_13_13_13_13_13_19_6_5_10_13_2_10_10_17_17_8_15_15_17_5_16_15_13_14_8_6_6_6_5_5_4_18_2_2_5_4_10_5_5_6_18_18_18_18_1_17_4_4_7_1_4_4_9_1_5_7_3_9_5_5_8_8_8_11_11_1_1_3_3_6</t>
+  </si>
+  <si>
+    <t>19_19_19_19_19</t>
+  </si>
+  <si>
+    <t>18_18_5_5_15_15_6_6_6_2_3_5_6_9_10_10_1_16_2_2_4_4_4_5_5_5_4_11_11_11_8_4_13_10_2_2_9_9_9_9_9_2_2_6_16_15_11_18_5_12_10_10_7_7_9_3_8_3_3_3_9_1_7_7_12_12_12_12_18_18_2_4_4_8_2_7_7_1_5_10_10_10_2_4_4_10_10_10_10_10_10_6_6_6_6_6_11_11_2_15_5_7_1_1_7_7_17_17_17_1_1_1_4_4_4_7_7_17_11_9_9_9_7_7_17_17_17_2_11_11_11_11_8_8_8_8_13_13_4_4_3_3_5_9_9_9_4_6_10_8_2_13_13_1_18_4_4_3_3_2_2_17_17_1_8_3_3_3_3_10_6_6_6_8_3_3_3_1_6_16_4_4_4_7_7_2_5_9_9_9_9_9_12_12_4_4_4_11_5_10_16_3_18_1_5_5_10_10_2_14_5_11_10_4_4_4_4_4_3_3_3_18_18_12_7_9_9_9_12_3_3_3_5_5_5_5_5_14_2_2_2_15_8_8_8_8_5_7_7_18_3_14_14_17_17_18_8_8_5_5_5_5_12_8_6_6_11_11_11_11_11_11_18_18_12_12_3_3_3_18_18_18_10_10_10_10_5_6_6_15_8_8_8_8_8_8_11_11_14_14_14_16_16_9_9_12_10_2_14_4_5_2_7_7_7_1_4_4_4_4_4_4_4_4_4_4_6_6_6_19_14_16_9_12_4_7_7_1_7_7_15_15_1_12_3_5_4_7_5_7_19_19_11_1_3_3_18_7_8_8_11_10_10_10_5_5_5_10_10_5_12_12_12_18_13_9_9_9_10_9_9_9_5_15_15_15_13_6_1_2_2_2_10_10_10_11_11_11_16_2_1_7_8_3_3_1_1_1_6_13_13_13_13_3_11_11_6_6_20_20_20_8_9_9_13_9_9_1_10_7_6_19_19_19_19_6_6_6_5_5_1_5_7_7_8_8_10_10_10_15_15_12_12_12_9_8_8_16_9_9_4_9_9_11_11_11_11_11_11_17_17_17_10_13_12_6_6_12_5_9_8_8_8_11_4_4_4_3_3_2_2_2_5_16_16_16_13_13_9_9</t>
+  </si>
+  <si>
+    <t>5_5_17_17_9_9_12_9_9_2_9_9_10_10_5_10_11_2_2_15_15_17_10_18_18_14_14_14_17_8_8_8_8_11_3_8_7_13_16_7_8_8_2_7_7_7_19_19_2_2_11_14_6_6_6_5_5_15_7_7_7_2_4_4_4_4_4_18_18_18_19_18_18_3_6_6_13_8_6_4_12_4_4_2_2_3_3_3_10_13_5_12_12_3_9_11_11_8_8_8_18_18_18_18_1_6_11_6_6_14_20_20_15_11_2_2_4_3_3_20_18_6_8_6_10_4_4_4_4_2_2_2_2_16_16_2_8_8_5_5_7_18_16_13_13_14_16_7_2_4_4_8_17_5_5_14_9_3_13_6_15_15_15_16_16_18_13_11_7_7_7_7_14_14_14_15_15_15_9_19_18_10_10_10_10_10_13_10_10_10_8_14_14_14_14_14_15_15_15_15_15_2_4_7_7_7_1_6_6_10_5_9_9_7_5_5_2_10_4_14_13_12_12_11_10_10_10_15_14_17_17_17_18_18_14_3_15_15_15_15_19_19_6_18_13_4_4_10_20_19_7_7_11_10_10_11_11_13_13_10_3_3_3_3_3_20_7_4_4_13_13_13_13_7_2_12_19_3_3_9_9_8_8_15_2_2_4_14_13_19_19_19_11_4_20_20_20_20_16_8_8_5_5_10_12_3_13_13_13_15_4_7_6_3_8_11_1_6_9_9_16_17_17_17_3_3_3_10_10_10_10_6_17_6_6_16_7_4_4_4_1_10_4_4_4_4_4_6_6_7_3_3_3_10_10_13_13_13_13_7_12_12_8_8_8_20_18_16_14_14_17_17_4_16_7_17_17_10_7_8_8_8_8_8_8_5_4_4_10_4_4_7_7_19_19_14_11_3_14_12_16_16_16_16_2_1_13_6_1_1_3_14_14_14_14_2_2_7_11_14_14_20_20_1_5_5_9_8_6_6_2_12_6_17_18_18_18_9_9_16_16_2_2_2_2_9_12_9_9_9_15_11_11_11_11_2_2_16_16_16_19_20_14_14_14_8_14_14_1_13_8_8_4_11_16_12_12_12_12_17_6_6_6_6_6_11_6_6_15_15_1_1_1_1_10_20_20_20_11_11</t>
+  </si>
+  <si>
+    <t>20_20_20_20_20</t>
+  </si>
+  <si>
+    <t>15_15_11_4_4_9_9_12_17_17_2_2_4_4_6_6_6_13_7_7_7_3_12_12_2_4_4_4_7_12_12_3_9_6_1_1_19_20_9_10_11_10_8_11_5_5_14_14_13_6_8_8_10_3_3_9_3_4_17_17_13_5_15_15_15_15_15_15_6_8_7_7_13_2_2_2_13_10_10_6_6_6_7_7_7_3_2_11_5_5_18_9_9_7_7_9_12_12_12_14_7_7_9_7_7_1_1_1_15_6_4_7_7_7_7_7_7_7_7_7_10_10_6_18_18_13_5_3_3_1_9_7_7_7_7_7_7_13_13_13_6_4_2_5_1_8_14_5_13_12_6_6_6_6_6_19_18_18_10_10_11_11_17_3_14_7_3_3_15_15_15_15_2_4_2_2_2_10_9_9_19_3_2_15_2_7_7_5_10_8_2_3_3_17_6_6_18_5_5_2_2_3_3_6_9_9_1_1_17_17_17_17_17_2_19_2_9_9_2_3_6_5_5_5_3_10_10_6_4_10_10_10_3_3_9_5_5_10_10_14_14_5_5_12_12_12_18_18_15_17_4_4_4_15_9_2_13_7_7_7_14_14_14_14_16_16_16_5_5_5_1_1_1_1_20_11_11_11_11_11_11_9_9_6_6_10_13_1_18_13_3_5_5_5_5_5_18_18_18_18_18_5_8_7_7_7_14_1_16_16_15_16_9_10_14_2_2_2_8_2_4_17_8_8_14_14_14_14_14_2_4_1_8_5_5_9_8_8_8_8_8_8_8_10_2_12_14_6_6_12_17_2_12_7_8_11_11_2_2_5_5_5_5_3_2_2_2_2_2_2_2_2_2_2_10_10_10_10_10_5_5_5_5_5_10_15_2_2_10_3_9_20_7_7_20_6_9_5_19_13_1_13_1_1_1_4_4_10_4_12_12_12_3_7_16_13_13_16_16_20_9_9_9_12_12_14_14_14_14_10_5_9_9_5_5_1_10_10_10_19_8_8_16_9_16_15_13_8_9_4_16_20_20_19_19_19_19_19_9_3_18_18_10_10_10_18_16_16_17_15_10_6_6_17_7_7_10_1_16_16_4_15_5_5_10_6_6_6_6_12_12_12_3_8_8_10_10_10_6_8</t>
+  </si>
+  <si>
+    <t>15_15_15_15_1_1_7_7_7_9_16_18_8_8_8_8_9_11_13_11_10_8_8_8_5_4_19_19_14_14_14_14_4_4_5_3_3_1_9_1_16_16_8_8_17_17_13_16_16_16_4_13_13_1_10_10_9_3_3_3_2_2_18_18_18_18_18_18_16_16_16_16_9_13_13_17_10_10_10_18_18_18_17_17_17_11_6_6_6_6_13_13_13_13_13_1_5_15_1_1_1_9_9_9_2_12_12_1_6_16_7_7_14_3_10_10_10_10_10_1_1_17_17_5_10_13_13_2_5_5_8_8_7_7_17_1_8_8_8_8_8_13_13_11_9_9_14_4_1_19_19_5_10_10_20_20_11_11_11_5_5_5_13_13_10_10_2_2_3_3_3_6_1_5_12_12_12_15_15_15_15_15_4_6_11_3_3_3_3_15_20_4_3_3_3_3_16_14_5_5_5_17_9_4_16_18_18_18_6_1_1_5_2_2_12_12_12_12_12_8_1_20_9_9_9_16_8_12_2_5_8_8_11_11_11_11_11_11_17_13_5_2_8_8_8_8_8_8_3_19_16_5_12_7_6_6_10_5_20_20_20_20_20_10_10_10_3_18_5_5_5_5_13_4_4_4_4_4_4_4_7_11_5_1_1_1_4_4_4_6_6_14_18_18_6_9_9_9_9_15_15_15_5_5_5_5_14_4_3_9_6_6_11_1_15_1_9_16_1_1_15_15_15_10_19_2_2_2_2_2_7_7_10_12_12_12_12_12_12_12_12_3_3_3_2_8_6_6_4_16_16_16_8_8_8_7_15_15_14_14_15_18_18_3_3_3_15_15_18_18_1_1_18_18_20_8_8_4_18_13_5_5_11_11_11_11_12_12_18_18_13_13_13_13_5_3_3_3_3_3_20_20_2_5_2_7_7_9_6_1_4_4_14_14_7_7_7_3_8_8_4_6_2_2_2_2_18_20_10_2_10_3_2_16_16_16_16_16_16_16_8_3_18_18_18_18_18_7_7_4_7_7_7_7_4_18_18_5_20_20_4_18_7_5_5_5_5_16_13_7_7_13_7_12_10_15_15_15_5_5_5_5_10_4_4_17_3_3_3_1_14_6_6_6_6_6_6_14_11_11</t>
+  </si>
+  <si>
+    <t>9_13_13_13_17_5_11_11_19_11_5_5_1_19_5_11_11_7_11_11_11_17_5_7_7_7_7_7_9_9_9_5_5_13_7_7_19_9_13_5_11_11_11_11_11_11_3_9_7_5_5_5_5_11_11_11_7_7_7_1_1_17_17_17_5_11_11_15_15_9_11_11_11_11_11_11_13_13_13_5_7_9_15_15_9_9_13_5_11_15_11_5_19_5_5_1_1_1_1_3_9_3_5_5_3_11_19_11_5_1_1_1_1_3_3_3_3_15_3_19_5_9_15_3_9_11_11_11_9_7_3_3_3_13_13_3_11_11_11_1_1_1_1_3_7_11_1_13_13_13_9_9_3_3_11_11_11_11_13_13_13_17_19_1_9_1_13_7_7_7_7_11_11_7_7_13_3_3_9_7_7_7_7_5_5_5_17_17_17_7_1_1_1_1_1_7_7_7_15_1_11_9_19_1_1_1_3_3_3_3_19_13_3_3_9_9_13_13_13_1_1_3_3_3_19_1_7_7_17_3_11_7_7_7_5_13_13_13_13_13_19_3_9_7_11_3_3_5_5_17_1_15_15_5_5_15_15_5_5_13_13_13_13_17_17_1_1_11_13_5_5_17_5_5_7_7_7_9_9_15_15_15_15_5_5_13_11_11_9_7_3_3_1_1_9_1_1_1_1_1_1_17_17_17_17_9_9_15_15_1_5_1_11_11_17_15_15_15_5_1_19_19_19_19_7_7_9_9_9_9_9_19_5_7_7_7_5_5_5_9_15_15_11_11_11_5_5_19_13_5_7_7_7_7_9_5_5_5_5_5_5_5_19_1_17_13_3_3_3_3_3_3_9_9_9_9_11_11_5_13_11_11_7_5_7_17_9_15_15_15_13_15_7_1_3_9_9_7_3_3_3_19_19_7_13_13_9_1_1_5_11_1_1_9_17_17_17_1_1_1_11_11_11_11_1_17_9_15_1_13_13_5_5_17_17_5_1_1_1_1_9_9_9_13_13_3_11_11_3_9_9_13_3_15_15_11_13_17_7_11_19_15_15_15_9_13_5_5_5_1_3_3_5_5_3_11_19_19_19_9_7_7_9_5_17_17_17_17_17_7_7_9_9_13_13_15_19_19_19_19</t>
+  </si>
+  <si>
+    <t>7_19_17_3_3_3_3_3_3_3_9_5_5_5_5_17_17_17_17_19_3_7_7_17_5_5_5_9_7_3_9_9_3_9_5_11_9_13_13_7_3_3_3_15_1_1_5_17_11_9_9_3_1_9_9_1_1_11_9_3_3_11_15_11_11_11_11_9_19_19_13_5_5_5_5_5_5_7_17_17_17_7_7_7_3_11_3_3_1_1_1_17_17_17_17_7_7_7_7_7_7_3_11_13_13_13_13_13_1_17_3_15_13_3_17_17_17_1_9_5_3_3_17_15_1_1_13_13_13_3_9_17_1_17_5_19_19_19_19_1_1_5_9_9_9_15_15_3_3_15_5_5_5_9_3_3_9_9_9_3_3_9_9_9_9_7_7_19_19_19_19_9_15_15_9_9_9_7_5_17_17_7_9_9_5_11_5_5_13_3_17_3_7_11_11_13_13_13_13_13_3_3_3_3_3_5_7_15_3_3_3_7_1_11_7_7_3_13_3_5_5_3_7_7_7_1_11_11_9_7_11_1_1_7_5_5_5_5_11_11_11_1_11_5_1_1_11_9_3_17_13_15_1_7_13_13_13_13_13_1_1_1_1_1_1_1_1_1_1_5_5_5_7_7_11_11_11_11_5_5_13_5_5_5_3_3_5_5_5_15_15_11_11_3_3_15_15_15_15_19_9_11_11_15_5_13_13_7_15_15_15_11_11_11_9_1_15_13_15_15_9_3_13_1_7_3_15_9_9_11_5_11_11_5_13_13_13_13_13_13_13_1_3_1_1_1_9_9_3_13_13_13_13_13_13_9_9_3_3_3_3_3_7_1_1_11_1_1_17_17_11_17_11_5_9_5_11_1_11_19_19_19_19_7_7_7_19_11_9_9_7_7_7_7_1_1_1_1_3_3_3_3_1_13_5_11_11_11_3_17_1_1_17_17_7_7_7_7_7_7_7_7_11_17_3_9_9_7_15_17_17_5_5_7_7_7_7_7_15_15_15_15_7_7_7_17_5_5_5_15_3_1_1_7_13_13_3_3_3_15_15_15_5_9_3_3_3_3_3_13_15_11_11_15_15_15_15_11_11_11_3_5_13_13_15_15_15_5_5_19_19_19_13_3_9_3_3_1_1_7</t>
+  </si>
+  <si>
+    <t>15_15_1_9_9_5_11_1_1_1_11_5_7_9_9_9_9_5_5_11_7_15_15_11_11_7_17_7_7_7_9_13_13_13_13_7_5_11_15_15_15_15_13_13_13_13_13_13_13_13_1_15_11_7_11_11_11_11_17_17_13_13_15_11_11_11_19_19_19_3_3_3_3_13_15_15_5_13_19_15_15_15_13_15_13_3_3_5_15_9_9_5_11_11_3_3_1_1_3_13_13_5_5_17_1_1_1_7_7_17_17_19_19_19_19_11_11_1_15_15_15_9_3_3_3_3_3_13_15_3_17_17_3_13_13_9_11_7_17_15_15_11_3_5_1_11_13_11_11_11_19_13_13_13_13_13_13_13_1_17_17_1_1_5_5_5_7_3_19_3_3_15_15_15_15_15_5_5_5_5_5_13_15_15_7_7_5_1_1_5_1_7_7_17_17_7_1_3_3_9_11_3_3_7_7_7_7_1_1_1_1_1_7_7_5_5_11_3_3_7_11_9_9_3_9_9_5_7_5_1_5_1_3_5_7_1_1_1_7_7_9_9_9_17_1_1_5_5_5_11_1_5_15_15_7_1_1_1_15_15_15_9_3_5_5_5_9_9_9_3_7_19_3_15_13_13_13_1_15_9_3_5_11_7_13_13_15_15_9_15_1_1_7_15_15_15_11_5_5_7_7_7_19_3_17_13_3_3_11_19_7_7_7_7_7_5_13_11_15_15_1_19_3_7_3_3_7_7_7_7_15_15_15_1_13_3_3_3_5_11_13_5_5_5_5_5_9_15_9_7_9_13_19_5_9_11_13_17_7_1_3_11_11_3_3_13_13_13_13_1_9_9_13_1_15_5_9_9_9_9_9_9_15_5_5_7_9_9_9_15_15_15_17_3_3_1_15_3_9_9_9_15_3_3_3_3_5_9_3_1_17_11_5_9_5_5_5_9_9_9_9_19_19_5_5_5_5_3_11_15_15_15_11_11_15_15_9_1_1_9_11_1_1_9_15_11_11_9_9_9_15_15_13_7_7_7_7_7_17_5_17_17_9_13_13_13_11_15_9_9_9_9_9_11_11_11_11_13_11_11_19_19_19_1_1_1_9_15_15_15_11_11_11_11_11_9_5_13_15_15</t>
+  </si>
+  <si>
+    <t>11_1_1_3_3_3_3_3_5_13_7_7_7_3_3_3_9_1_1_1_7_1_1_19_19_1_1_9_11_13_3_3_7_7_7_7_7_13_13_17_9_9_9_9_9_17_17_9_9_13_1_15_15_3_3_3_3_1_5_5_5_5_9_1_1_13_13_13_13_19_15_9_3_3_19_17_17_13_17_9_9_9_9_9_7_7_7_3_3_11_5_5_3_3_3_3_3_3_15_15_15_15_15_15_11_11_11_11_11_11_11_7_3_13_3_19_19_1_11_17_3_3_3_13_13_9_9_9_5_19_17_1_7_17_11_9_11_11_11_11_5_1_11_11_5_1_1_1_13_7_7_1_1_1_1_15_15_9_9_9_9_9_11_3_1_1_5_17_17_13_1_1_1_9_11_1_11_3_13_13_13_13_15_13_7_5_9_9_9_9_9_5_9_1_1_7_7_13_13_11_13_13_7_7_5_11_11_15_3_11_7_1_1_7_5_5_17_3_11_11_7_7_3_3_15_15_15_15_3_15_15_7_7_7_9_13_5_5_5_1_5_13_15_15_15_11_5_7_5_5_11_11_17_17_17_17_3_7_7_7_17_7_17_13_5_3_9_5_3_3_5_11_13_13_13_9_9_19_19_19_11_1_13_13_9_9_11_9_7_7_19_1_3_3_3_3_17_17_9_11_11_11_11_5_5_7_7_7_7_3_3_3_13_1_3_9_11_11_9_1_1_7_7_7_15_1_17_3_11_9_1_1_3_9_11_11_11_11_11_11_11_15_3_3_3_3_1_1_1_7_3_3_3_15_7_7_7_9_9_9_9_7_7_7_7_7_7_3_17_17_17_1_13_13_19_19_19_19_3_11_15_15_1_3_3_15_15_1_1_1_1_1_1_1_1_3_17_17_15_15_1_9_9_13_19_7_5_5_5_5_9_9_9_17_17_13_13_13_1_1_1_1_13_11_15_15_7_15_3_5_5_3_3_3_3_3_1_1_1_19_9_3_3_3_15_17_17_15_15_15_15_15_15_7_7_7_13_15_7_7_1_5_5_5_13_5_5_5_5_17_15_3_9_13_9_9_13_5_19_19_1_1_17_3_3_3_3_3_9_9_9_9_9_13_1_19_5_5_15_5</t>
+  </si>
+  <si>
+    <t>7_9_5_1_1_13_13_13_13_7_5_9_3_1_1_1_1_1_1_1_11_7_11_11_17_13_5_5_1_1_1_3_7_7_7_7_7_7_7_13_9_15_15_15_13_9_17_19_11_11_3_3_1_1_5_3_3_3_9_3_11_11_9_7_9_3_1_5_11_11_11_3_7_9_3_3_3_19_9_9_9_7_7_7_7_1_7_13_9_13_7_7_15_15_15_15_1_1_9_3_3_3_3_19_19_1_1_1_1_13_15_7_3_19_19_19_11_3_9_11_11_11_11_11_1_1_5_13_3_3_3_9_9_1_3_3_11_9_9_9_9_9_9_1_9_9_1_13_7_7_7_7_13_13_17_9_9_9_9_9_9_9_9_9_11_11_11_11_11_11_1_11_19_19_19_19_11_7_19_9_9_7_3_11_11_11_15_15_11_13_15_15_9_9_7_17_17_17_17_9_9_9_1_15_15_15_3_7_7_7_11_11_7_7_9_5_17_1_5_5_3_7_15_15_13_15_15_13_7_7_7_3_3_15_9_15_1_1_13_5_5_7_7_11_11_1_5_3_19_19_19_11_7_7_7_7_7_7_7_7_9_9_15_19_9_19_5_3_3_7_13_13_5_7_7_5_5_11_3_3_3_7_7_7_11_1_1_1_1_9_9_7_7_7_11_11_11_11_11_3_3_3_7_19_13_11_3_3_3_5_13_3_17_17_17_3_3_3_11_7_7_7_7_11_11_11_9_9_9_9_5_1_1_1_3_3_3_17_1_1_1_5_17_17_17_13_13_15_19_3_3_3_3_3_3_7_3_3_11_9_7_1_19_1_5_5_19_7_19_5_5_5_13_13_13_7_11_11_5_5_5_5_5_5_7_11_11_11_3_3_5_1_9_15_13_3_9_1_1_13_13_15_13_13_19_19_19_19_19_17_9_15_7_13_1_1_5_1_19_1_7_15_15_15_15_9_3_17_5_13_5_5_9_17_9_9_13_13_15_7_11_17_15_5_11_7_7_7_7_7_13_13_5_5_13_13_13_9_7_7_11_11_11_1_1_13_9_9_9_9_9_9_3_3_9_13_11_11_13_13_13_13_13_11_7_3_3_3_13_3_3_1_11_11_17_17_17_3_19_1</t>
+  </si>
+  <si>
+    <t>7_7_7_7_7_7_7_7_7_5_13_5_9_9_19_3_3_5_13_7_7_7_17_11_11_15_15_15_15_9_9_9_17_17_3_7_7_7_7_7_7_15_15_15_11_11_13_1_15_15_7_7_9_3_11_7_7_3_1_1_1_17_1_9_9_7_17_17_9_15_9_13_9_19_19_3_15_3_3_5_5_5_11_11_13_13_15_1_1_9_9_9_7_9_1_1_1_1_1_5_5_13_13_13_13_13_7_13_13_13_13_5_5_11_9_5_9_7_11_11_11_11_7_9_19_5_1_1_1_1_3_11_11_11_11_3_11_5_17_17_7_7_7_11_5_5_5_1_1_3_13_13_13_11_11_5_15_5_5_3_5_11_11_5_1_1_1_1_1_1_7_7_7_11_1_13_9_7_15_1_13_11_11_13_13_5_5_5_5_15_7_11_11_7_11_15_13_5_5_9_7_9_13_13_11_11_11_5_3_3_9_19_5_5_5_5_5_5_5_5_17_1_1_3_17_5_5_3_3_3_11_9_9_15_15_15_15_7_9_19_7_7_7_7_7_13_19_9_13_19_3_9_17_15_5_19_19_3_3_7_1_1_1_11_15_13_13_7_15_15_15_15_13_3_11_3_3_5_3_3_3_3_3_3_3_11_1_11_9_13_7_5_5_3_1_3_1_1_1_1_1_1_11_17_7_7_7_7_7_7_7_5_1_7_7_13_5_13_13_3_13_13_9_9_9_1_5_11_9_13_11_11_7_3_5_5_5_11_11_1_3_3_1_7_7_1_1_1_3_3_3_7_7_7_7_9_13_7_13_9_5_19_19_19_19_11_11_11_11_11_17_17_17_1_1_5_5_9_3_3_19_19_9_7_7_7_11_1_9_1_11_3_13_1_1_7_7_9_9_7_1_15_15_15_9_13_13_1_1_13_7_9_9_9_9_9_13_17_11_11_11_11_3_3_1_1_3_3_1_9_17_17_1_1_1_7_7_7_11_9_11_11_5_5_13_3_3_5_5_5_9_17_3_9_9_9_5_5_3_3_11_11_11_5_19_11_11_1_7_7_13_9_11_11_11_11_11_5_11_3_5_3_17_17_7_7_7_7_3_3_19_1_5_13_13_15_13_13_1_9</t>
+  </si>
+  <si>
+    <t>5_7_11_15_3_7_7_13_5_5_3_11_3_7_5_11_11_13_13_13_3_3_11_9_9_9_9_9_9_9_1_9_9_9_3_3_7_5_5_1_3_3_3_3_7_7_5_5_5_5_15_15_15_15_15_5_11_15_13_13_1_3_3_5_5_11_11_15_15_15_3_1_5_15_13_9_9_9_19_19_1_3_17_19_9_9_9_13_13_13_13_13_13_13_9_9_9_9_11_15_15_15_15_1_11_15_9_9_15_5_5_5_1_3_3_17_17_17_17_7_7_7_1_5_5_19_1_1_3_7_3_7_11_11_9_11_7_7_7_7_1_11_11_11_13_7_17_17_17_17_7_1_3_7_7_11_1_7_7_7_15_1_1_9_9_9_15_9_7_7_7_7_1_13_13_3_5_11_13_9_9_3_3_3_3_13_1_1_1_1_13_3_1_11_11_5_19_19_19_13_5_5_13_3_7_5_11_11_3_3_5_5_15_9_9_7_1_19_1_1_9_5_5_9_9_9_15_15_15_15_15_15_1_3_5_5_7_7_7_5_3_15_19_15_15_9_9_11_11_17_19_19_3_5_5_5_5_7_7_9_13_13_9_9_13_13_17_17_17_17_7_11_9_9_5_3_15_11_9_9_9_13_13_13_13_11_11_11_1_1_1_17_9_9_11_11_7_7_19_19_11_11_3_3_3_3_1_1_9_9_9_5_3_3_7_15_9_9_11_13_13_5_3_3_3_3_3_1_1_1_1_9_11_11_13_13_13_13_13_13_3_3_3_3_15_3_17_5_17_17_1_1_3_3_17_17_17_11_7_7_9_9_9_15_11_11_11_9_9_1_7_1_5_9_9_19_19_1_7_7_13_7_11_11_9_15_15_9_13_13_13_9_9_1_9_9_9_9_9_7_11_15_13_15_15_17_15_3_11_13_13_9_17_1_7_13_11_11_11_15_11_1_1_1_1_17_17_9_9_15_15_3_3_3_3_9_17_13_17_3_15_15_15_5_15_15_13_7_7_7_15_7_9_7_15_5_5_5_5_5_11_1_5_5_5_17_17_1_1_1_1_3_7_19_19_3_15_7_7_5_5_5_3_3_5_5_5_9_7_9_9_9_7_7_11_15_9_5_5_5</t>
+  </si>
+  <si>
+    <t>1_9_9_9_13_7_3_3_3_1_1_9_11_17_1_5_3_3_13_13_13_7_5_5_13_17_1_1_5_3_9_3_3_3_13_13_5_11_11_11_11_15_15_15_19_19_19_19_11_11_7_7_19_1_1_15_15_11_11_11_11_9_1_3_11_11_7_7_7_7_7_3_11_11_11_3_7_7_7_11_11_15_19_19_19_7_5_9_9_7_1_3_3_19_5_5_19_13_1_3_3_3_9_9_19_13_15_15_9_15_15_1_3_1_1_17_3_11_11_11_1_1_1_13_13_13_7_7_7_7_5_5_5_11_13_13_9_9_9_5_5_15_3_9_9_9_9_5_3_3_1_3_3_3_3_3_5_5_5_19_7_17_1_1_1_1_13_15_3_3_11_15_3_3_3_15_1_17_3_5_5_5_7_7_13_11_11_17_17_17_7_17_17_13_15_15_11_15_9_15_11_7_5_5_5_5_3_5_5_5_1_15_15_1_1_11_3_3_3_1_1_7_7_9_5_9_9_9_1_1_5_5_9_5_13_13_13_1_1_1_9_9_3_3_3_7_1_19_3_9_9_1_1_1_1_7_7_9_9_15_15_13_1_17_17_17_17_15_15_11_15_9_19_19_19_19_11_9_9_9_9_9_9_9_13_11_11_11_11_3_3_15_15_19_19_19_19_13_1_11_17_9_1_5_3_19_9_5_5_15_15_13_13_13_13_3_7_9_15_15_1_7_15_5_5_5_5_5_1_1_7_7_7_7_13_13_13_13_1_1_1_1_1_19_3_5_5_13_7_7_7_7_7_7_1_1_13_3_9_5_7_7_7_5_3_3_11_11_11_7_9_11_11_11_11_3_3_1_11_9_9_9_9_9_9_11_9_3_13_17_15_15_15_15_15_9_9_7_3_15_3_17_19_3_3_9_9_9_7_3_3_15_15_15_5_9_17_11_15_3_1_1_17_17_15_3_13_13_3_3_19_19_11_11_11_19_5_5_5_5_11_7_7_1_1_1_1_17_17_3_3_5_5_5_7_7_15_15_15_15_1_13_13_11_19_19_9_9_9_9_9_9_13_3_19_19_17_17_1_1_1_1_1_3_5_5_7_7_7_3_17_5_5_13_13_13_3_3_3_3</t>
+  </si>
+  <si>
+    <t>1_1_15_19_17_13_13_13_13_13_11_11_11_11_11_11_11_11_11_7_3_9_7_3_3_3_3_9_15_15_7_15_3_7_7_13_13_13_5_9_1_1_15_15_15_19_19_19_17_5_5_5_15_17_17_1_15_1_1_3_3_5_5_1_1_1_7_15_15_15_15_13_13_13_1_1_1_1_7_11_11_11_11_19_7_7_19_19_19_19_1_1_11_3_3_11_5_1_1_1_13_13_13_9_7_7_7_7_17_17_17_7_7_11_11_17_17_17_15_19_19_19_19_19_19_19_19_1_1_1_19_1_1_13_3_11_9_3_11_11_13_11_5_1_11_11_19_3_3_3_1_7_5_5_17_17_17_17_9_5_5_3_5_5_5_5_5_15_15_15_13_1_15_15_3_11_7_7_7_3_3_7_7_7_7_9_9_3_11_5_5_5_17_9_7_13_13_13_13_3_3_3_17_15_3_1_1_15_13_9_5_5_5_17_7_7_9_9_9_9_9_13_13_13_13_13_7_3_17_19_19_19_1_5_11_7_7_1_1_5_15_15_9_9_13_1_19_5_7_15_15_17_17_7_7_7_7_7_19_15_11_15_3_5_5_9_11_11_11_9_9_17_17_7_1_1_9_7_7_5_5_17_9_5_5_11_17_9_9_13_13_13_11_15_15_15_15_5_5_13_13_1_11_5_5_13_17_1_1_1_9_9_11_17_9_1_7_13_5_13_13_13_9_9_9_9_9_9_1_13_13_7_5_5_7_13_13_1_13_1_13_11_13_13_13_7_13_3_17_17_17_17_1_7_3_5_17_9_13_13_13_5_5_5_13_7_7_19_19_5_11_13_19_11_11_11_11_11_11_11_11_11_5_7_7_7_3_15_15_7_7_17_5_11_11_11_15_3_13_15_7_15_15_15_15_15_15_15_15_11_1_3_13_7_7_1_19_19_19_13_13_13_13_9_5_13_5_15_15_15_17_17_17_15_3_3_3_3_9_9_9_7_15_17_17_17_3_3_3_3_3_13_13_3_3_5_13_3_3_3_3_3_3_13_11_11_15_15_7_1_1_13_17_17_17_5_17_17_17_13_3_17_9_9_9_7_7_7_5_5_1_1_1_1_1_1_7_5_11_1</t>
+  </si>
+  <si>
+    <t>11_5_15_1_5_7_9_9_17_3_13_13_11_11_5_13_13_13_5_5_15_7_15_15_15_3_3_9_1_1_1_1_13_13_1_1_11_5_5_9_3_3_1_17_17_17_17_1_15_9_9_13_5_9_9_9_3_3_3_9_9_9_9_5_5_17_7_5_15_15_15_15_9_1_1_9_5_9_5_13_13_13_15_3_7_3_3_9_9_9_11_5_5_5_5_3_3_3_3_7_7_7_13_7_7_7_7_11_13_7_7_11_17_15_15_15_15_1_9_1_1_1_1_1_5_13_3_11_11_11_9_9_17_17_7_19_3_9_1_9_9_3_19_19_15_15_5_5_5_11_11_11_5_5_9_15_3_5_13_13_13_13_11_7_7_5_5_5_11_11_11_1_5_1_9_3_3_9_7_7_1_1_1_1_7_19_13_13_17_17_9_1_19_19_5_5_3_3_3_3_5_5_13_13_13_7_7_7_7_7_1_1_1_9_3_3_3_13_7_7_9_9_9_17_17_17_17_5_5_5_5_13_15_1_5_3_3_11_11_9_9_9_7_1_9_9_9_11_17_17_17_1_1_1_11_11_15_5_7_17_9_7_7_7_7_7_3_17_1_13_13_7_7_7_17_17_3_3_3_3_3_3_1_5_5_1_1_1_1_11_19_19_3_3_3_5_9_9_3_3_3_5_3_3_3_13_13_13_11_11_1_3_11_11_11_5_5_5_5_15_15_15_15_11_11_13_13_13_19_19_1_9_9_9_11_11_1_1_1_1_7_1_1_15_3_15_9_9_5_13_15_15_15_1_7_1_7_7_7_1_1_9_9_3_3_9_9_1_3_13_17_17_17_17_3_3_9_9_3_5_5_5_5_5_13_13_11_15_13_13_13_13_3_3_3_3_9_9_9_19_7_7_15_15_5_5_5_5_3_3_3_3_3_5_1_1_9_9_9_1_1_1_7_7_15_15_9_9_9_9_9_15_15_15_1_17_17_9_9_9_13_13_3_13_13_11_11_1_13_13_17_17_17_3_3_9_9_9_3_9_9_9_19_9_9_3_9_19_5_1_1_5_9_9_17_17_17_17_17_7_5_5_5_5_5_5_5_1_1_1_1_1_5_5_5_7_7_11_11_7</t>
+  </si>
+  <si>
+    <t>10_10_8_14_18_18_20_20_20_20_20_8_8_10_4_6_8_8_4_4_10_14_12_12_2_2_20_20_4_4_14_10_12_4_4_2_8_14_8_8_8_8_2_2_18_18_14_4_2_6_4_4_4_4_16_4_2_4_2_4_8_8_14_14_14_14_14_2_10_10_10_18_18_4_18_20_20_20_20_20_16_16_4_4_14_14_10_10_10_16_16_2_2_2_18_14_20_10_10_10_6_8_12_12_14_14_12_12_6_14_4_2_12_14_14_14_14_14_4_8_8_8_10_8_2_14_14_14_4_4_8_16_12_10_8_8_6_16_16_18_18_4_12_12_12_12_8_12_12_12_16_16_8_8_2_2_2_2_14_14_18_18_4_8_14_14_14_14_14_14_14_4_18_18_14_14_14_8_12_10_10_10_16_16_16_16_6_6_8_8_10_4_14_14_18_8_2_16_16_16_2_2_10_6_6_2_2_6_6_8_10_10_10_10_10_10_10_10_10_10_10_10_10_18_16_4_4_4_4_6_6_6_8_4_4_4_4_10_20_20_2_6_6_6_14_14_10_2_12_12_8_12_10_10_2_18_18_8_8_2_10_16_4_12_18_8_8_14_12_12_18_18_18_6_6_6_6_6_6_8_10_10_8_12_12_12_12_20_16_16_16_2_16_16_16_16_14_14_14_14_20_20_6_2_2_20_18_4_14_14_14_10_10_10_8_8_10_10_8_8_8_2_6_6_8_8_16_6_6_6_2_18_18_18_2_2_4_14_14_14_6_6_6_6_6_6_6_6_4_4_20_2_12_6_16_2_4_4_4_10_10_10_6_6_18_6_14_18_18_18_8_6_6_6_6_6_6_18_8_2_2_2_2_2_2_6_6_6_6_10_12_18_16_10_8_14_6_6_8_8_10_2_4_4_6_6_18_10_16_16_18_16_16_6_16_16_2_16_16_18_18_18_18_18_18_18_18_18_18_14_12_18_2_2_2_8_2_20_12_12_18_18_18_14_14_12_14_2_2_2_18_18_12_12_14_14_12_10_10_10_16_16_6_6_6_6_20_20_20_20_20_20_16_16_14_14_8_8_8_6_6_18_18_18_18_12_12_12_12_14_14_12_10_18_8_8_6_6_8_4</t>
+  </si>
+  <si>
+    <t>16_6_6_4_4_4_8_6_2_18_18_2_2_10_8_8_4_4_4_4_4_16_16_4_4_2_8_8_2_8_4_12_2_14_14_12_10_16_10_4_18_14_14_14_12_6_8_10_10_2_2_12_14_18_18_20_4_16_2_2_2_12_12_12_10_10_6_12_12_2_18_10_10_10_6_8_14_8_8_14_14_12_12_10_14_14_14_12_12_12_8_6_16_16_8_20_4_6_12_12_6_10_10_12_12_8_12_14_14_10_12_8_8_8_8_8_18_14_16_16_10_10_8_12_12_20_20_20_2_8_6_10_10_2_6_6_6_6_4_4_4_4_12_4_12_2_12_12_8_4_2_2_2_4_6_18_14_16_10_14_14_14_14_4_2_4_8_8_2_2_2_8_8_8_2_12_8_14_12_12_10_16_16_8_4_4_2_2_2_2_18_12_8_4_4_10_10_10_2_18_18_20_20_20_10_10_8_18_6_12_4_14_2_2_6_6_6_6_20_6_10_4_8_6_6_18_18_4_4_10_2_6_6_6_6_6_6_6_12_12_16_14_10_18_16_16_14_12_10_2_2_2_14_10_18_18_18_4_4_4_14_14_14_14_8_8_2_2_6_12_8_4_4_4_2_2_2_10_2_2_6_16_18_18_18_12_12_2_2_10_14_12_12_14_12_12_12_12_16_16_16_4_12_6_6_2_8_10_10_10_10_8_10_10_10_10_10_10_12_12_12_16_16_6_6_4_4_6_6_14_14_12_12_12_6_6_6_18_6_20_20_10_6_12_20_8_20_20_4_12_14_2_8_18_2_2_2_4_4_4_2_2_18_18_18_4_4_14_6_18_12_12_4_12_12_12_8_14_4_6_6_6_20_20_20_18_18_18_18_4_18_18_8_8_8_10_10_4_12_12_12_10_6_6_18_18_12_10_10_20_4_4_4_2_12_14_4_4_14_14_14_14_2_12_6_6_12_12_6_10_10_10_18_14_14_4_4_4_4_4_4_14_14_14_14_4_4_4_8_4_14_14_16_12_12_10_6_4_12_12_12_10_10_8_8_20_10_10_14_12_12_12_12_14_12_6_6_2_2_2_8_16_8_6_6_6_6_12_10_10_10_10_10_10_10_4_2_2_8_8</t>
+  </si>
+  <si>
+    <t>16_6_12_8_4_4_4_4_4_4_10_10_10_10_10_14_14_20_20_8_8_8_18_20_20_10_6_10_2_2_6_20_20_8_8_18_18_14_14_2_16_14_14_14_14_14_16_16_4_4_6_20_20_4_4_4_4_4_12_4_4_2_2_2_2_2_10_10_10_16_16_18_18_8_4_12_14_8_20_20_14_14_4_4_2_8_10_8_8_2_2_12_10_14_14_14_14_12_12_12_18_12_6_6_6_12_10_14_10_16_16_16_8_4_4_4_10_10_12_14_14_16_4_6_14_18_10_6_16_16_16_4_18_18_10_10_10_10_12_4_14_16_16_16_16_14_16_4_2_2_2_2_18_4_18_8_10_8_12_12_12_20_20_14_2_4_4_14_8_8_4_4_4_8_4_16_8_8_2_2_18_10_4_4_20_20_20_20_16_16_2_2_2_2_2_10_10_10_10_10_2_14_14_10_14_4_4_4_14_14_4_6_16_16_16_16_16_2_14_10_10_16_16_16_20_20_20_20_10_14_4_14_10_10_12_4_2_2_2_16_10_10_10_10_10_6_6_6_12_18_16_16_16_8_8_18_18_18_18_18_4_4_8_16_16_4_14_4_10_2_16_16_16_12_12_12_10_8_8_18_8_6_16_16_16_8_8_8_8_12_12_12_2_14_8_14_20_4_4_16_8_8_8_18_10_10_4_4_2_18_8_14_10_10_4_2_10_10_10_20_8_10_14_14_2_2_2_2_2_2_4_8_14_12_10_10_4_12_6_20_12_12_12_12_10_4_4_4_4_10_20_14_14_10_12_8_10_18_2_12_6_16_10_10_10_6_4_18_2_10_8_6_12_12_10_6_6_8_18_18_18_18_18_4_2_2_2_2_2_2_14_14_14_14_14_14_14_14_14_14_14_2_2_2_10_18_2_4_12_12_10_18_6_12_14_16_16_6_6_6_6_18_18_18_12_12_12_12_12_6_6_12_6_14_16_12_12_4_4_4_8_8_20_4_4_4_16_16_10_10_10_10_10_10_14_10_20_20_12_10_20_6_10_10_10_10_10_8_8_6_18_6_6_6_6_6_6_14_18_18_4_18_18_10_10_14_14_14_16_16_16_16_2_10_6_6_6_10_10_8</t>
+  </si>
+  <si>
+    <t>8_8_8_10_4_4_16_16_16_16_12_12_4_20_18_2_4_4_4_4_12_8_8_8_8_16_12_2_2_6_4_4_16_4_4_12_12_6_8_8_8_8_10_10_10_2_2_2_6_4_20_6_6_4_10_8_16_2_12_6_8_8_4_4_4_4_16_20_10_12_14_14_14_14_20_20_14_14_8_2_12_12_8_8_10_6_6_2_2_2_10_10_8_8_2_2_2_2_8_18_14_14_10_12_6_8_8_20_16_18_16_4_18_8_2_2_2_12_12_14_4_20_20_4_4_4_4_4_4_2_2_2_18_2_2_14_6_6_6_6_18_18_12_6_6_18_10_10_10_10_14_2_6_2_2_2_10_10_2_16_16_2_6_6_2_14_14_4_4_18_12_12_14_14_2_14_8_4_8_8_8_8_8_8_8_4_8_14_14_14_20_4_16_16_12_8_8_20_16_4_4_4_14_4_2_8_14_12_14_14_18_18_18_8_8_8_8_8_8_2_2_2_2_8_8_12_12_10_10_16_20_16_16_16_16_20_8_14_6_14_16_18_6_6_6_8_8_8_8_2_2_12_8_8_8_8_14_16_16_16_12_12_4_6_2_2_18_16_16_16_12_12_16_10_12_16_18_18_18_18_20_20_20_20_20_20_20_2_8_8_8_8_6_12_12_6_6_6_12_12_12_16_6_12_2_20_4_8_8_4_4_8_12_12_12_8_8_4_10_12_8_8_12_12_18_18_18_18_10_10_6_20_6_10_10_20_14_2_18_10_2_2_2_2_2_12_6_4_4_4_4_8_8_8_10_18_16_4_14_20_12_12_12_6_6_6_2_2_2_14_14_14_14_14_12_12_12_20_20_20_14_14_14_2_2_20_20_20_20_16_16_1_8_10_10_8_8_4_4_4_8_2_16_10_10_10_8_10_8_8_8_2_2_18_4_4_4_10_20_20_20_8_8_4_4_4_10_10_16_16_16_20_2_10_4_8_16_16_16_16_16_16_16_8_20_20_12_12_20_20_20_8_8_8_10_10_10_16_16_20_20_20_20_4_18_2_2_2_2_2_2_2_2_2_8_4_4_4_16_6_6_2_2_2_8_4_4_18_18_14_14_14_18_18_18_8_8_4_4_4</t>
+  </si>
+  <si>
+    <t>4_4_8_2_4_4_20_12_12_12_18_18_6_6_4_10_20_20_2_2_2_16_6_6_10_2_2_10_10_14_4_14_6_16_10_12_2_6_2_2_2_2_2_2_2_2_2_12_12_12_6_6_16_14_6_6_6_2_2_16_20_16_16_12_4_16_16_16_16_12_10_18_18_18_18_18_18_18_20_12_8_4_4_14_14_20_4_4_18_4_16_16_16_16_12_20_4_16_2_12_12_20_10_2_6_4_4_4_14_14_6_2_16_18_18_6_2_2_4_6_6_6_6_2_20_20_20_20_20_2_4_4_4_20_2_2_10_16_16_2_8_4_12_12_12_8_18_18_18_12_12_6_6_6_6_8_8_14_14_14_6_20_6_12_4_10_10_2_2_14_14_14_8_18_2_16_2_10_10_10_10_10_6_2_2_2_2_2_12_12_4_4_4_4_2_2_16_16_16_14_14_20_20_18_10_6_6_6_4_4_16_16_14_10_8_8_2_2_6_6_10_10_4_4_6_4_12_4_12_12_8_18_4_4_14_2_2_2_2_10_10_18_10_10_14_18_18_18_16_16_14_14_14_12_12_12_2_4_4_4_2_2_8_8_4_4_4_12_8_2_2_2_2_2_2_2_2_10_20_20_6_6_8_10_10_12_2_4_4_4_10_12_18_20_20_20_16_4_4_4_12_6_6_6_6_6_12_14_14_14_10_10_10_4_14_14_14_10_16_20_20_20_20_4_12_16_12_18_2_2_20_12_20_20_14_14_6_6_14_14_4_14_18_20_6_4_4_6_14_12_2_2_2_18_10_10_8_6_20_14_14_10_14_14_2_2_2_14_14_16_16_10_10_10_18_12_12_14_14_12_12_12_6_2_10_12_12_14_8_12_12_6_8_20_14_14_14_16_16_16_6_2_8_8_8_10_2_18_18_18_14_18_8_8_8_8_10_10_12_12_14_6_8_10_10_10_10_10_10_4_14_14_6_6_6_6_14_6_8_8_8_16_16_16_6_12_10_2_8_16_8_18_2_2_4_10_10_2_2_8_8_16_16_2_8_8_8_14_4_4_4_4_12_12_18_18_2_10_6_2_6_6_2_2_2_10_10_16_16_8_4_4_4_2_6_8_8_8_12_10</t>
+  </si>
+  <si>
+    <t>14_14_8_8_8_18_12_6_8_8_16_16_6_6_12_10_8_8_8_16_16_12_4_16_8_8_2_2_8_16_10_10_10_10_12_12_20_8_4_14_6_18_18_4_2_2_6_6_6_6_6_10_12_12_12_10_10_10_4_4_18_10_10_10_2_2_2_10_2_2_10_4_4_4_4_4_10_10_12_12_8_2_16_18_18_18_18_18_2_6_8_6_6_18_18_16_16_16_14_14_8_8_14_4_8_6_4_2_2_2_14_14_12_12_12_12_14_6_6_16_16_16_2_2_6_6_6_6_6_6_6_6_18_4_4_4_4_8_4_6_6_14_14_4_10_2_12_18_4_4_14_12_12_12_12_16_16_16_16_18_18_2_2_2_14_8_8_14_2_8_16_18_2_12_12_12_10_10_16_16_2_2_2_2_2_2_18_6_6_14_16_12_4_4_4_4_18_18_8_12_12_12_4_4_20_20_2_2_8_8_2_2_2_4_10_4_4_4_6_12_12_12_14_4_8_8_6_6_6_6_16_14_14_8_4_8_16_16_10_10_8_14_14_14_14_14_4_4_4_4_2_6_6_6_14_14_14_6_6_6_6_4_2_4_12_8_2_2_10_8_8_4_6_6_4_4_4_4_4_4_4_12_6_6_4_10_10_10_10_4_14_2_2_8_8_4_10_6_8_12_8_12_14_18_10_12_12_12_12_12_12_2_4_4_2_16_10_14_2_4_4_4_2_18_12_10_8_8_8_8_2_2_10_10_4_4_8_8_10_10_20_20_20_20_4_4_4_16_8_10_8_20_20_20_10_10_10_10_10_14_14_14_8_8_8_18_18_8_4_14_6_4_4_12_12_16_16_14_8_8_16_12_12_16_16_16_16_14_14_12_6_6_6_6_2_20_10_18_10_12_16_16_4_4_20_6_6_14_14_16_16_12_4_12_10_10_10_6_20_20_12_12_16_2_10_10_10_14_14_4_6_6_6_6_6_6_6_8_8_8_12_16_16_8_8_2_10_8_8_20_16_16_16_14_14_6_6_10_8_8_8_8_18_18_4_12_2_2_6_6_8_6_16_6_12_12_6_6_10_10_6_8_8_8_2_4_18_16_16_16_18_18_2_6_6_6_6_10_10_16</t>
+  </si>
+  <si>
+    <t>4_2_2_6_16_8_8_6_8_14_6_6_12_8_8_10_2_2_2_2_12_10_10_10_12_6_6_6_6_6_6_8_2_2_2_2_2_2_2_16_4_20_20_20_12_12_8_8_8_8_2_14_16_20_20_4_2_2_12_2_6_20_6_10_10_6_8_8_8_10_14_6_2_2_2_12_2_12_6_18_20_20_14_16_4_8_4_14_12_12_4_4_12_12_10_6_18_18_16_6_2_2_2_6_4_14_2_2_6_10_14_14_18_18_8_16_8_8_10_10_10_6_14_8_8_6_12_12_12_12_12_4_2_2_4_4_4_4_4_4_4_14_4_4_2_2_18_12_6_6_6_6_4_2_2_8_8_14_14_8_2_4_16_16_12_2_2_12_12_8_4_4_6_2_12_4_18_18_18_8_2_8_8_2_14_10_10_2_14_6_6_16_16_16_4_16_2_2_14_14_14_4_8_4_16_14_16_8_14_16_14_14_14_10_2_6_6_6_16_16_16_16_10_10_10_10_10_10_10_10_8_8_14_8_8_8_8_12_12_12_8_8_8_8_6_6_8_8_2_10_10_16_16_10_10_2_4_2_2_6_6_6_16_16_16_4_16_6_6_6_6_6_6_2_6_6_2_2_2_2_14_18_18_12_18_2_12_12_12_4_2_2_8_8_20_18_18_18_18_10_12_12_20_10_2_2_2_6_6_2_2_6_18_18_18_16_8_6_4_4_16_16_8_8_4_8_4_10_10_10_6_20_20_20_10_10_10_10_10_20_10_4_14_14_20_20_4_4_12_12_4_10_10_8_6_4_8_8_8_14_2_6_6_20_14_14_14_14_14_8_10_10_10_10_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_8_2_14_14_14_18_18_2_6_8_10_2_2_2_10_10_10_20_10_14_8_2_10_10_10_10_10_10_20_8_8_8_20_8_8_4_8_8_12_12_2_14_14_6_10_10_10_8_12_20_20_20_16_16_12_12_12_6_6_6_8_8_8_10_2_2_2_2_14_14_10_12_2_2_4_4_10_6_6_4_2_2_2_8_8_8_8_8_8_12_12_8_8_8_8_14_2_4_14_16_16_16_16_16_4_4_4_4_4_4_2</t>
+  </si>
+  <si>
+    <t>6_18_12_16_6_12_2_4_6_6_14_20_20_10_10_8_8_8_18_18_18_18_14_14_2_2_2_2_2_10_8_10_10_12_12_4_20_12_12_12_12_12_16_18_18_18_18_4_14_8_10_10_14_14_16_10_18_18_12_6_10_2_10_10_6_2_2_2_20_4_4_4_8_8_2_6_14_14_18_18_10_10_10_10_6_6_8_20_14_10_10_10_20_16_16_14_18_18_2_8_8_8_8_16_16_16_16_16_16_16_6_12_2_6_14_14_12_10_18_18_18_4_4_4_4_4_6_6_6_6_6_6_2_8_8_6_6_6_14_14_8_8_6_6_6_6_6_6_6_10_10_10_14_4_4_12_8_16_10_2_14_18_8_4_4_10_12_8_12_12_14_6_4_10_4_4_10_14_14_8_8_12_12_20_20_20_20_20_20_6_6_4_20_20_4_4_14_2_10_10_16_4_4_14_2_16_16_16_2_14_16_10_10_10_10_8_8_8_16_16_16_16_12_2_14_14_2_2_2_2_2_10_4_4_16_2_6_12_12_12_12_12_4_4_16_16_2_2_4_20_6_6_6_2_2_2_6_6_16_10_10_10_8_10_10_10_10_10_4_4_18_12_6_6_10_10_10_10_4_4_4_8_10_10_2_14_14_14_14_14_12_12_12_12_10_6_4_4_2_20_8_8_20_20_8_16_16_16_6_12_12_6_6_6_6_6_6_18_18_6_18_6_6_10_12_10_10_10_10_12_2_16_16_16_6_6_6_16_8_6_2_16_6_10_20_14_12_12_18_4_4_4_4_4_18_2_10_10_10_10_6_6_16_16_20_20_8_6_20_6_6_14_4_4_4_8_8_8_10_8_8_8_8_16_4_8_2_6_12_12_8_6_6_6_4_20_4_8_8_12_6_6_6_20_10_4_8_2_2_2_18_14_4_18_18_18_14_14_16_16_16_10_20_20_20_20_20_6_16_16_16_16_10_8_6_6_10_12_6_10_10_2_6_4_4_14_4_4_8_16_16_8_8_8_6_10_10_10_10_8_4_4_2_2_2_2_10_6_6_8_8_2_12_12_12_12_12_4_4_16_16_16_16_10_6_10_2_2_2_2_2_4_8_8_10_8_8_12_4_16</t>
+  </si>
+  <si>
+    <t>10_10_10_12_12_12_2_14_14_20_6_16_14_4_12_12_8_6_6_20_20_4_4_18_2_6_6_14_16_16_4_16_10_10_10_10_10_6_6_6_14_14_14_14_6_6_6_10_6_4_4_16_16_12_12_6_6_10_12_12_12_8_6_12_12_12_4_6_4_4_10_8_8_10_2_2_10_6_18_10_10_10_10_4_4_12_10_16_12_12_14_14_8_8_18_6_10_18_18_12_12_6_16_6_6_6_6_6_6_8_6_6_6_6_6_6_6_14_14_14_14_12_16_4_4_8_6_2_20_20_20_20_20_20_20_20_20_20_16_12_6_12_20_8_10_10_10_8_8_8_4_10_8_4_8_14_14_8_8_18_14_14_14_14_16_16_4_4_4_16_12_8_8_6_16_16_10_20_20_20_20_14_2_10_10_10_4_4_4_4_4_18_6_20_4_4_18_8_8_8_8_18_8_14_8_4_4_14_8_6_6_6_4_2_14_10_10_16_16_16_6_10_12_12_16_2_2_12_4_4_10_12_10_8_6_16_10_16_12_12_8_8_8_8_14_6_6_6_16_16_2_2_2_2_10_2_18_6_6_2_12_6_4_4_4_10_10_2_12_6_14_14_14_16_8_4_16_10_8_8_20_20_20_20_20_18_20_20_20_20_20_4_4_18_14_16_16_16_20_14_18_6_6_6_8_10_10_10_10_14_14_14_18_18_14_18_4_4_14_2_2_12_4_4_4_2_2_2_2_4_14_8_10_10_10_14_6_6_20_20_4_12_12_6_6_2_2_2_2_20_20_14_14_12_12_12_14_12_12_10_12_20_4_4_18_10_6_12_12_6_6_4_10_6_6_6_6_6_14_4_8_8_4_10_20_20_20_20_2_2_10_10_12_12_8_8_8_18_2_2_4_4_10_16_18_12_16_10_10_10_10_10_10_20_4_2_4_14_14_14_18_18_10_10_10_18_20_20_16_16_8_8_20_16_6_6_6_14_14_14_14_10_4_4_4_2_6_18_8_8_8_12_14_12_16_10_10_14_14_18_16_16_10_10_2_12_10_10_10_10_18_18_18_18_8_6_18_18_18_18_20_20_20_8_20_2_6_6_18_8_4_12_8_8_4_2_4_8_8_2</t>
+  </si>
+  <si>
+    <t>18_12_12_12_12_2_2_6_2_2_18_18_18_18_4_4_6_6_2_2_2_16_16_16_6_6_8_2_2_20_2_2_2_2_12_6_6_4_4_2_6_6_6_6_18_10_10_4_2_4_4_8_8_10_8_8_8_16_16_16_18_4_4_8_14_4_4_6_6_6_12_12_8_6_6_6_4_4_4_8_8_14_14_14_14_14_14_14_2_6_4_10_10_10_10_10_10_8_8_8_8_4_10_10_10_2_10_14_14_16_2_2_6_6_12_14_14_12_14_8_8_8_6_6_6_6_12_6_6_8_2_2_2_2_4_4_18_12_2_8_4_4_10_12_16_2_2_2_2_2_2_2_18_18_18_8_12_14_20_20_16_18_12_18_18_4_2_10_10_10_8_2_2_2_14_14_14_18_18_10_12_16_16_16_16_16_10_2_8_16_14_14_12_12_18_18_18_18_16_16_4_4_12_4_6_6_12_12_14_12_12_12_4_4_4_4_4_4_4_4_10_12_12_18_4_2_2_6_6_6_6_16_16_16_16_2_2_2_12_4_4_4_12_12_12_4_4_4_4_18_14_2_2_10_6_6_6_4_4_4_2_2_2_18_4_10_10_10_8_8_4_10_10_12_8_8_16_18_18_2_2_2_6_6_6_8_2_2_2_16_16_16_16_12_20_20_4_4_4_8_4_4_4_4_14_10_6_16_18_18_18_18_10_4_4_4_4_10_10_4_4_8_8_6_8_8_2_4_4_6_4_4_8_8_4_6_14_14_10_10_8_16_12_12_20_20_10_18_12_16_18_18_18_18_18_18_18_18_10_10_10_10_10_4_4_4_4_4_4_4_4_8_12_6_6_10_4_20_20_20_20_8_4_4_4_10_18_16_16_16_12_12_12_4_8_14_8_14_12_12_12_2_2_2_8_16_16_14_10_12_12_12_6_6_12_12_16_16_20_6_8_8_8_6_4_4_4_12_12_12_12_12_8_2_2_2_2_2_2_6_6_16_16_12_2_8_8_8_4_4_8_8_8_6_2_4_4_14_18_18_2_20_10_10_12_12_6_6_6_6_12_16_16_14_14_14_8_8_2_12_12_10_10_10_10_10_18_10_2_2_4_4_10_10_16_16_16_16_16_18</t>
   </si>
 </sst>
 </file>
@@ -1927,7 +2086,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K125"/>
+  <dimension ref="A1:K167"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -5337,7 +5496,7 @@
     </row>
     <row r="108" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A108" s="6">
-        <f t="shared" ref="A108:A119" si="5">C108*10+D108</f>
+        <f t="shared" ref="A108:A125" si="5">C108*10+D108</f>
         <v>20350011</v>
       </c>
       <c r="B108" s="14">
@@ -5721,7 +5880,7 @@
     </row>
     <row r="120" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A120" s="6">
-        <f>C120*10+D120</f>
+        <f t="shared" si="5"/>
         <v>20360011</v>
       </c>
       <c r="B120" s="14">
@@ -5753,7 +5912,7 @@
     </row>
     <row r="121" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A121" s="6">
-        <f>C121*10+D121</f>
+        <f t="shared" si="5"/>
         <v>20360012</v>
       </c>
       <c r="B121" s="14">
@@ -5785,7 +5944,7 @@
     </row>
     <row r="122" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A122" s="6">
-        <f>C122*10+D122</f>
+        <f t="shared" si="5"/>
         <v>20360013</v>
       </c>
       <c r="B122" s="14">
@@ -5817,7 +5976,7 @@
     </row>
     <row r="123" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A123" s="6">
-        <f>C123*10+D123</f>
+        <f t="shared" si="5"/>
         <v>20360021</v>
       </c>
       <c r="B123" s="14">
@@ -5849,7 +6008,7 @@
     </row>
     <row r="124" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A124" s="6">
-        <f>C124*10+D124</f>
+        <f t="shared" si="5"/>
         <v>20360022</v>
       </c>
       <c r="B124" s="14">
@@ -5881,7 +6040,7 @@
     </row>
     <row r="125" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A125" s="6">
-        <f>C125*10+D125</f>
+        <f t="shared" si="5"/>
         <v>20360023</v>
       </c>
       <c r="B125" s="14">
@@ -5910,6 +6069,1350 @@
       </c>
       <c r="J125" s="17"/>
       <c r="K125" s="17"/>
+    </row>
+    <row r="126" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A126" s="6">
+        <f t="shared" ref="A126:A152" si="6">C126*10+D126</f>
+        <v>20280011</v>
+      </c>
+      <c r="B126" s="14">
+        <v>102800</v>
+      </c>
+      <c r="C126" s="33">
+        <v>2028001</v>
+      </c>
+      <c r="D126" s="33">
+        <v>1</v>
+      </c>
+      <c r="E126" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G126" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J126" s="17"/>
+      <c r="K126" s="17"/>
+    </row>
+    <row r="127" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A127" s="6">
+        <f t="shared" si="6"/>
+        <v>20280012</v>
+      </c>
+      <c r="B127" s="14">
+        <v>102800</v>
+      </c>
+      <c r="C127" s="33">
+        <v>2028001</v>
+      </c>
+      <c r="D127" s="33">
+        <v>2</v>
+      </c>
+      <c r="E127" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G127" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J127" s="17"/>
+      <c r="K127" s="17"/>
+    </row>
+    <row r="128" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A128" s="6">
+        <f t="shared" si="6"/>
+        <v>20280013</v>
+      </c>
+      <c r="B128" s="14">
+        <v>102800</v>
+      </c>
+      <c r="C128" s="33">
+        <v>2028001</v>
+      </c>
+      <c r="D128" s="33">
+        <v>3</v>
+      </c>
+      <c r="E128" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G128" s="34" t="s">
+        <v>185</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J128" s="17"/>
+      <c r="K128" s="17"/>
+    </row>
+    <row r="129" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A129" s="6">
+        <f t="shared" si="6"/>
+        <v>20280014</v>
+      </c>
+      <c r="B129" s="14">
+        <v>102800</v>
+      </c>
+      <c r="C129" s="33">
+        <v>2028001</v>
+      </c>
+      <c r="D129" s="33">
+        <v>4</v>
+      </c>
+      <c r="E129" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G129" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J129" s="17"/>
+      <c r="K129" s="17"/>
+    </row>
+    <row r="130" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A130" s="6">
+        <f t="shared" si="6"/>
+        <v>20280015</v>
+      </c>
+      <c r="B130" s="14">
+        <v>102800</v>
+      </c>
+      <c r="C130" s="33">
+        <v>2028001</v>
+      </c>
+      <c r="D130" s="33">
+        <v>5</v>
+      </c>
+      <c r="E130" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G130" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J130" s="17"/>
+      <c r="K130" s="17"/>
+    </row>
+    <row r="131" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A131" s="6">
+        <f t="shared" si="6"/>
+        <v>20280016</v>
+      </c>
+      <c r="B131" s="14">
+        <v>102800</v>
+      </c>
+      <c r="C131" s="33">
+        <v>2028001</v>
+      </c>
+      <c r="D131" s="33">
+        <v>6</v>
+      </c>
+      <c r="E131" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G131" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J131" s="17"/>
+      <c r="K131" s="17"/>
+    </row>
+    <row r="132" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A132" s="6">
+        <f t="shared" si="6"/>
+        <v>20340111</v>
+      </c>
+      <c r="B132" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C132" s="33">
+        <v>2034011</v>
+      </c>
+      <c r="D132" s="33">
+        <v>1</v>
+      </c>
+      <c r="E132" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J132" s="17"/>
+      <c r="K132" s="17"/>
+    </row>
+    <row r="133" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A133" s="6">
+        <f t="shared" si="6"/>
+        <v>20340112</v>
+      </c>
+      <c r="B133" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C133" s="33">
+        <v>2034011</v>
+      </c>
+      <c r="D133" s="33">
+        <v>2</v>
+      </c>
+      <c r="E133" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J133" s="17"/>
+      <c r="K133" s="17"/>
+    </row>
+    <row r="134" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A134" s="6">
+        <f t="shared" si="6"/>
+        <v>20340113</v>
+      </c>
+      <c r="B134" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C134" s="33">
+        <v>2034011</v>
+      </c>
+      <c r="D134" s="33">
+        <v>3</v>
+      </c>
+      <c r="E134" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J134" s="17"/>
+      <c r="K134" s="17"/>
+    </row>
+    <row r="135" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A135" s="6">
+        <f t="shared" si="6"/>
+        <v>20340121</v>
+      </c>
+      <c r="B135" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C135" s="33">
+        <v>2034012</v>
+      </c>
+      <c r="D135" s="33">
+        <v>1</v>
+      </c>
+      <c r="E135" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J135" s="17"/>
+      <c r="K135" s="17"/>
+    </row>
+    <row r="136" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A136" s="6">
+        <f t="shared" si="6"/>
+        <v>20340122</v>
+      </c>
+      <c r="B136" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C136" s="33">
+        <v>2034012</v>
+      </c>
+      <c r="D136" s="33">
+        <v>2</v>
+      </c>
+      <c r="E136" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J136" s="17"/>
+      <c r="K136" s="17"/>
+    </row>
+    <row r="137" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A137" s="6">
+        <f t="shared" si="6"/>
+        <v>20340123</v>
+      </c>
+      <c r="B137" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C137" s="33">
+        <v>2034012</v>
+      </c>
+      <c r="D137" s="33">
+        <v>3</v>
+      </c>
+      <c r="E137" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J137" s="17"/>
+      <c r="K137" s="17"/>
+    </row>
+    <row r="138" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A138" s="6">
+        <f t="shared" si="6"/>
+        <v>20340131</v>
+      </c>
+      <c r="B138" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C138" s="33">
+        <v>2034013</v>
+      </c>
+      <c r="D138" s="33">
+        <v>1</v>
+      </c>
+      <c r="E138" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J138" s="17"/>
+      <c r="K138" s="17"/>
+    </row>
+    <row r="139" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A139" s="6">
+        <f t="shared" si="6"/>
+        <v>20340132</v>
+      </c>
+      <c r="B139" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C139" s="33">
+        <v>2034013</v>
+      </c>
+      <c r="D139" s="33">
+        <v>2</v>
+      </c>
+      <c r="E139" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J139" s="17"/>
+      <c r="K139" s="17"/>
+    </row>
+    <row r="140" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A140" s="6">
+        <f t="shared" si="6"/>
+        <v>20340133</v>
+      </c>
+      <c r="B140" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C140" s="33">
+        <v>2034013</v>
+      </c>
+      <c r="D140" s="33">
+        <v>3</v>
+      </c>
+      <c r="E140" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J140" s="17"/>
+      <c r="K140" s="17"/>
+    </row>
+    <row r="141" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A141" s="6">
+        <f t="shared" si="6"/>
+        <v>20340141</v>
+      </c>
+      <c r="B141" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C141" s="33">
+        <v>2034014</v>
+      </c>
+      <c r="D141" s="33">
+        <v>1</v>
+      </c>
+      <c r="E141" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J141" s="17"/>
+      <c r="K141" s="17"/>
+    </row>
+    <row r="142" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A142" s="6">
+        <f t="shared" si="6"/>
+        <v>20340142</v>
+      </c>
+      <c r="B142" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C142" s="33">
+        <v>2034014</v>
+      </c>
+      <c r="D142" s="33">
+        <v>2</v>
+      </c>
+      <c r="E142" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J142" s="17"/>
+      <c r="K142" s="17"/>
+    </row>
+    <row r="143" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A143" s="6">
+        <f t="shared" si="6"/>
+        <v>20340143</v>
+      </c>
+      <c r="B143" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C143" s="33">
+        <v>2034014</v>
+      </c>
+      <c r="D143" s="33">
+        <v>3</v>
+      </c>
+      <c r="E143" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J143" s="17"/>
+      <c r="K143" s="17"/>
+    </row>
+    <row r="144" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A144" s="6">
+        <f t="shared" si="6"/>
+        <v>20340151</v>
+      </c>
+      <c r="B144" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C144" s="33">
+        <v>2034015</v>
+      </c>
+      <c r="D144" s="33">
+        <v>1</v>
+      </c>
+      <c r="E144" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J144" s="17"/>
+      <c r="K144" s="17"/>
+    </row>
+    <row r="145" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A145" s="6">
+        <f t="shared" si="6"/>
+        <v>20340152</v>
+      </c>
+      <c r="B145" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C145" s="33">
+        <v>2034015</v>
+      </c>
+      <c r="D145" s="33">
+        <v>2</v>
+      </c>
+      <c r="E145" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J145" s="17"/>
+      <c r="K145" s="17"/>
+    </row>
+    <row r="146" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A146" s="6">
+        <f t="shared" si="6"/>
+        <v>20340153</v>
+      </c>
+      <c r="B146" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C146" s="33">
+        <v>2034015</v>
+      </c>
+      <c r="D146" s="33">
+        <v>3</v>
+      </c>
+      <c r="E146" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H146" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J146" s="17"/>
+      <c r="K146" s="17"/>
+    </row>
+    <row r="147" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A147" s="6">
+        <f t="shared" si="6"/>
+        <v>20340161</v>
+      </c>
+      <c r="B147" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C147" s="33">
+        <v>2034016</v>
+      </c>
+      <c r="D147" s="33">
+        <v>1</v>
+      </c>
+      <c r="E147" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J147" s="17"/>
+      <c r="K147" s="17"/>
+    </row>
+    <row r="148" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A148" s="6">
+        <f t="shared" si="6"/>
+        <v>20340162</v>
+      </c>
+      <c r="B148" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C148" s="33">
+        <v>2034016</v>
+      </c>
+      <c r="D148" s="33">
+        <v>2</v>
+      </c>
+      <c r="E148" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J148" s="17"/>
+      <c r="K148" s="17"/>
+    </row>
+    <row r="149" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A149" s="6">
+        <f t="shared" si="6"/>
+        <v>20340163</v>
+      </c>
+      <c r="B149" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C149" s="33">
+        <v>2034016</v>
+      </c>
+      <c r="D149" s="33">
+        <v>3</v>
+      </c>
+      <c r="E149" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J149" s="17"/>
+      <c r="K149" s="17"/>
+    </row>
+    <row r="150" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A150" s="6">
+        <f t="shared" si="6"/>
+        <v>20340171</v>
+      </c>
+      <c r="B150" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C150" s="33">
+        <v>2034017</v>
+      </c>
+      <c r="D150" s="33">
+        <v>1</v>
+      </c>
+      <c r="E150" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J150" s="17"/>
+      <c r="K150" s="17"/>
+    </row>
+    <row r="151" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A151" s="6">
+        <f t="shared" si="6"/>
+        <v>20340172</v>
+      </c>
+      <c r="B151" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C151" s="33">
+        <v>2034017</v>
+      </c>
+      <c r="D151" s="33">
+        <v>2</v>
+      </c>
+      <c r="E151" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J151" s="17"/>
+      <c r="K151" s="17"/>
+    </row>
+    <row r="152" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A152" s="6">
+        <f t="shared" si="6"/>
+        <v>20340173</v>
+      </c>
+      <c r="B152" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C152" s="33">
+        <v>2034017</v>
+      </c>
+      <c r="D152" s="33">
+        <v>3</v>
+      </c>
+      <c r="E152" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H152" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J152" s="17"/>
+      <c r="K152" s="17"/>
+    </row>
+    <row r="153" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A153" s="6">
+        <f>C153*10+D153</f>
+        <v>20200011</v>
+      </c>
+      <c r="B153" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C153" s="33">
+        <v>2020001</v>
+      </c>
+      <c r="D153" s="33">
+        <v>1</v>
+      </c>
+      <c r="E153" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H153" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="J153" s="17"/>
+      <c r="K153" s="17"/>
+    </row>
+    <row r="154" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A154" s="6">
+        <f>C154*10+D154</f>
+        <v>20200012</v>
+      </c>
+      <c r="B154" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C154" s="33">
+        <v>2020001</v>
+      </c>
+      <c r="D154" s="33">
+        <v>2</v>
+      </c>
+      <c r="E154" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J154" s="17"/>
+      <c r="K154" s="17"/>
+    </row>
+    <row r="155" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A155" s="6">
+        <f>C155*10+D155</f>
+        <v>20200013</v>
+      </c>
+      <c r="B155" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C155" s="33">
+        <v>2020001</v>
+      </c>
+      <c r="D155" s="33">
+        <v>3</v>
+      </c>
+      <c r="E155" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="H155" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="J155" s="17"/>
+      <c r="K155" s="17"/>
+    </row>
+    <row r="156" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A156" s="6">
+        <f>C156*10+D156</f>
+        <v>20200014</v>
+      </c>
+      <c r="B156" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C156" s="33">
+        <v>2020001</v>
+      </c>
+      <c r="D156" s="33">
+        <v>4</v>
+      </c>
+      <c r="E156" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="H156" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J156" s="17"/>
+      <c r="K156" s="17"/>
+    </row>
+    <row r="157" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A157" s="6">
+        <f>C157*10+D157</f>
+        <v>20200015</v>
+      </c>
+      <c r="B157" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C157" s="33">
+        <v>2020001</v>
+      </c>
+      <c r="D157" s="33">
+        <v>5</v>
+      </c>
+      <c r="E157" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="H157" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J157" s="17"/>
+      <c r="K157" s="17"/>
+    </row>
+    <row r="158" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A158" s="6">
+        <f t="shared" ref="A158:A167" si="7">C158*10+D158</f>
+        <v>20200021</v>
+      </c>
+      <c r="B158" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C158" s="33">
+        <v>2020002</v>
+      </c>
+      <c r="D158" s="33">
+        <v>1</v>
+      </c>
+      <c r="E158" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H158" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="J158" s="17"/>
+      <c r="K158" s="17"/>
+    </row>
+    <row r="159" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A159" s="6">
+        <f t="shared" si="7"/>
+        <v>20200022</v>
+      </c>
+      <c r="B159" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C159" s="33">
+        <v>2020002</v>
+      </c>
+      <c r="D159" s="33">
+        <v>2</v>
+      </c>
+      <c r="E159" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="H159" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="J159" s="17"/>
+      <c r="K159" s="17"/>
+    </row>
+    <row r="160" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A160" s="6">
+        <f t="shared" si="7"/>
+        <v>20200023</v>
+      </c>
+      <c r="B160" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C160" s="33">
+        <v>2020002</v>
+      </c>
+      <c r="D160" s="33">
+        <v>3</v>
+      </c>
+      <c r="E160" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H160" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="J160" s="17"/>
+      <c r="K160" s="17"/>
+    </row>
+    <row r="161" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A161" s="6">
+        <f t="shared" si="7"/>
+        <v>20200024</v>
+      </c>
+      <c r="B161" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C161" s="33">
+        <v>2020002</v>
+      </c>
+      <c r="D161" s="33">
+        <v>4</v>
+      </c>
+      <c r="E161" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H161" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="J161" s="17"/>
+      <c r="K161" s="17"/>
+    </row>
+    <row r="162" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A162" s="6">
+        <f t="shared" si="7"/>
+        <v>20200025</v>
+      </c>
+      <c r="B162" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C162" s="33">
+        <v>2020002</v>
+      </c>
+      <c r="D162" s="33">
+        <v>5</v>
+      </c>
+      <c r="E162" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="H162" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I162" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="J162" s="17"/>
+      <c r="K162" s="17"/>
+    </row>
+    <row r="163" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A163" s="6">
+        <f t="shared" si="7"/>
+        <v>20200031</v>
+      </c>
+      <c r="B163" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C163" s="33">
+        <v>2020003</v>
+      </c>
+      <c r="D163" s="33">
+        <v>1</v>
+      </c>
+      <c r="E163" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H163" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="J163" s="17"/>
+      <c r="K163" s="17"/>
+    </row>
+    <row r="164" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A164" s="6">
+        <f t="shared" si="7"/>
+        <v>20200032</v>
+      </c>
+      <c r="B164" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C164" s="33">
+        <v>2020003</v>
+      </c>
+      <c r="D164" s="33">
+        <v>2</v>
+      </c>
+      <c r="E164" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="H164" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="J164" s="17"/>
+      <c r="K164" s="17"/>
+    </row>
+    <row r="165" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A165" s="6">
+        <f t="shared" si="7"/>
+        <v>20200033</v>
+      </c>
+      <c r="B165" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C165" s="33">
+        <v>2020003</v>
+      </c>
+      <c r="D165" s="33">
+        <v>3</v>
+      </c>
+      <c r="E165" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="H165" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="J165" s="17"/>
+      <c r="K165" s="17"/>
+    </row>
+    <row r="166" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A166" s="6">
+        <f t="shared" si="7"/>
+        <v>20200034</v>
+      </c>
+      <c r="B166" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C166" s="33">
+        <v>2020003</v>
+      </c>
+      <c r="D166" s="33">
+        <v>4</v>
+      </c>
+      <c r="E166" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="H166" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I166" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="J166" s="17"/>
+      <c r="K166" s="17"/>
+    </row>
+    <row r="167" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A167" s="6">
+        <f t="shared" si="7"/>
+        <v>20200035</v>
+      </c>
+      <c r="B167" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C167" s="33">
+        <v>2020003</v>
+      </c>
+      <c r="D167" s="33">
+        <v>5</v>
+      </c>
+      <c r="E167" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H167" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I167" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="J167" s="17"/>
+      <c r="K167" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5925,9 +7428,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="24" ht="16.5" spans="9:9">
-      <c r="I24" s="1" t="s">
-        <v>158</v>
-      </c>
+      <c r="I24" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="241">
   <si>
     <t>id</t>
   </si>
@@ -773,6 +773,36 @@
   </si>
   <si>
     <t>18_12_12_12_12_2_2_6_2_2_18_18_18_18_4_4_6_6_2_2_2_16_16_16_6_6_8_2_2_20_2_2_2_2_12_6_6_4_4_2_6_6_6_6_18_10_10_4_2_4_4_8_8_10_8_8_8_16_16_16_18_4_4_8_14_4_4_6_6_6_12_12_8_6_6_6_4_4_4_8_8_14_14_14_14_14_14_14_2_6_4_10_10_10_10_10_10_8_8_8_8_4_10_10_10_2_10_14_14_16_2_2_6_6_12_14_14_12_14_8_8_8_6_6_6_6_12_6_6_8_2_2_2_2_4_4_18_12_2_8_4_4_10_12_16_2_2_2_2_2_2_2_18_18_18_8_12_14_20_20_16_18_12_18_18_4_2_10_10_10_8_2_2_2_14_14_14_18_18_10_12_16_16_16_16_16_10_2_8_16_14_14_12_12_18_18_18_18_16_16_4_4_12_4_6_6_12_12_14_12_12_12_4_4_4_4_4_4_4_4_10_12_12_18_4_2_2_6_6_6_6_16_16_16_16_2_2_2_12_4_4_4_12_12_12_4_4_4_4_18_14_2_2_10_6_6_6_4_4_4_2_2_2_18_4_10_10_10_8_8_4_10_10_12_8_8_16_18_18_2_2_2_6_6_6_8_2_2_2_16_16_16_16_12_20_20_4_4_4_8_4_4_4_4_14_10_6_16_18_18_18_18_10_4_4_4_4_10_10_4_4_8_8_6_8_8_2_4_4_6_4_4_8_8_4_6_14_14_10_10_8_16_12_12_20_20_10_18_12_16_18_18_18_18_18_18_18_18_10_10_10_10_10_4_4_4_4_4_4_4_4_8_12_6_6_10_4_20_20_20_20_8_4_4_4_10_18_16_16_16_12_12_12_4_8_14_8_14_12_12_12_2_2_2_8_16_16_14_10_12_12_12_6_6_12_12_16_16_20_6_8_8_8_6_4_4_4_12_12_12_12_12_8_2_2_2_2_2_2_6_6_16_16_12_2_8_8_8_4_4_8_8_8_6_2_4_4_14_18_18_2_20_10_10_12_12_6_6_6_6_12_16_16_14_14_14_8_8_2_12_12_10_10_10_10_10_18_10_2_2_4_4_10_10_16_16_16_16_16_18</t>
+  </si>
+  <si>
+    <t>3_3_2_4_5_3_9_2_2_3_1_2_2_9_5_10_10_2_1_5_2_1_8_8_6_4_4_5_9_3_7_2_4_7_9_3_3_1_4_2_1_3_9_3_1_1_1_3_2_1_6_9_2_9_6_5_6_1_5_8_2_3_8_1_9_3_4_8_4_1_4_5_3_3_2_5_6_10_2_2_6_3_5_8_3_1_1_3_5_9_4_2_1_1_4_5_2_2_7_4_3_9_1_1_2_6_1_10_4_10_10_5_6_1_3_3_5_3_8_9_4_2_6_3_5_3_5_5_6_4_2_2_8_1_8_1_5_4_3_1_1_1_2_2_7_9_8_5_5_5_6_4_4_3_1_1_3_4_1_2_5_4_1_3_6_6_3_2_4_6_1_6_3_2_8_4_4_1_4_7_7_1_4_3_3_10_2_4_5_2_1_7_1_3_2_4_4_8_8_2_9_6_5_2_1_1_9_6_6_5_10_7_1_2_4_2_2_8_7_1_2_5_4_2_2_5_4_6_2_1_2_3_6_2_5_1_2_3_3_7_3_9_3_5_1_2_9_9_3_8_8_7_4_9_9_4_8_3_4_5_5_4_1_4_3_1_4_1_10_3_3_7_4_3_4_6_9_6_4_4_3_7_7_7_6_7_8_8_8_2_2_3_3_3_5_6_10_1_1_3_2_2_5_5_4_4_3_3_8_2_8_7_8_1_7_9_6_2_6_3_2_2_5_1_8_1_6_1_3_9_10_9_9_2_4_2_5_5_6_6_5_1_1_2_8_8_6_10_9_6_5_9_1_5_4_4_5_5_1_3_3_7_1_4_1_6_5_8_4_2_6_7_5_7_7_6_6_4_3_2_5_8_4_2_3_1_3_8_1_2_9_2_8_4_7_10_3_5_6_2_2_5_2_2_1_5_6_1_6_6_6_10_10_1_5_5_5_4_4_5_7_7_3_2_1_5_3_2_8_1_6_5_2_2_6_8_5_9_7_5_5_3_8_2_1_6_5_6_4_1_4_5_5_10_2_1_6_5_2_2_1_1_3_3_5_5_5_3_4_1_5_7_8_5_4_1_10_8_4_4_10_10_5_4_2_3_7_6_6_9_5_4_4_3_8_6_8_3_1_1</t>
+  </si>
+  <si>
+    <t>4_2_4_1_6_2_5_3_9_2_5_7_9_7_5_1_5_7_2_4_3_3_4_1_3_2_2_9_1_5_3_8_2_7_2_2_6_8_6_4_6_6_3_1_2_1_10_1_5_1_3_5_2_5_10_6_4_7_6_8_5_10_6_4_9_8_2_5_8_8_2_6_3_4_8_7_7_9_8_7_1_10_4_1_3_7_5_6_3_2_7_8_2_2_8_6_8_7_5_9_4_4_2_5_1_1_1_8_5_9_6_4_4_5_3_3_6_6_1_7_1_9_1_6_8_4_9_1_5_5_7_8_10_7_4_5_10_5_4_4_9_9_6_10_4_4_2_3_1_5_3_2_2_6_5_1_6_7_6_7_2_4_1_4_6_4_6_4_3_2_1_1_5_3_1_4_8_8_1_8_4_5_2_2_7_4_8_4_4_4_6_2_9_4_4_9_2_2_7_10_3_1_7_2_3_2_4_1_8_5_5_6_3_6_1_3_8_8_2_1_6_6_9_2_9_4_1_1_6_4_4_2_8_1_8_7_5_1_2_9_3_1_2_6_7_6_1_1_3_9_8_1_3_2_4_2_6_3_1_4_5_2_9_6_5_6_4_2_4_4_7_1_7_10_6_10_7_8_1_2_10_6_1_8_1_3_2_8_1_9_2_5_3_8_10_4_10_4_4_8_9_2_4_2_6_7_5_5_7_7_6_3_2_1_7_10_5_1_2_4_1_8_9_6_6_8_1_8_1_5_8_5_9_5_5_7_5_4_2_6_1_4_1_1_9_5_2_6_2_6_2_6_3_6_1_2_2_6_4_10_3_4_5_1_1_9_3_5_6_9_4_2_2_3_8_8_4_5_2_2_5_3_6_6_1_2_8_7_8_6_5_1_1_5_4_5_7_8_9_7_6_1_1_2_2_1_6_2_2_7_3_4_9_2_3_4_4_1_2_3_4_7_4_5_4_1_9_4_1_5_6_2_3_1_8_2_4_2_4_1_5_7_6_7_3_1_2_4_7_2_6_3_6_5_4_4_2_8_6_3_7_8_1_10_7_6_4_2_8_3_8_2_6_6_7_1_1_1_3_3_3_2_6_1_3_1_7_4_6_4_2_6_3_3_8_8_8_5_2_2</t>
+  </si>
+  <si>
+    <t>5_5_2_1_1_2_4_1_6_3_2_4_5_8_4_1_1_2_10_1_1_4_7_3_2_4_4_3_1_9_2_8_3_5_6_8_9_4_4_4_4_4_8_3_7_4_1_4_4_4_6_4_7_6_9_5_1_8_4_1_1_7_7_3_3_10_1_1_3_6_6_2_2_6_3_9_7_1_2_5_1_6_9_4_3_3_4_3_4_1_9_2_8_1_3_6_8_3_9_3_3_6_3_1_5_2_4_1_1_6_3_3_8_5_8_4_5_3_2_9_9_4_2_1_3_9_5_3_3_3_9_7_9_5_5_9_9_4_7_7_5_2_5_4_9_5_4_9_7_1_1_1_2_5_7_5_4_10_5_5_1_6_4_5_1_5_6_3_9_1_7_4_4_4_3_3_1_4_8_1_4_4_1_2_2_6_6_1_1_3_3_10_4_7_7_3_1_6_10_2_6_6_2_7_7_3_3_9_3_2_7_5_8_1_1_4_1_1_8_4_6_3_3_4_4_3_7_7_4_3_3_7_3_2_5_3_9_10_4_3_6_2_2_6_6_7_8_2_3_2_4_1_3_3_1_3_8_2_1_2_6_8_3_3_3_3_10_1_2_5_4_10_5_4_3_7_1_4_5_2_2_2_10_7_9_3_3_3_6_4_4_4_4_7_3_4_8_3_3_4_4_1_3_5_6_3_3_2_1_5_8_2_2_1_3_10_6_1_2_5_1_3_5_7_5_6_1_6_4_3_1_2_7_6_3_1_5_8_2_2_2_5_8_1_5_6_6_1_4_2_9_6_9_3_5_8_10_5_5_2_7_4_4_7_7_7_5_5_5_4_10_6_2_5_3_3_2_5_2_5_2_2_6_6_7_2_3_1_1_1_2_5_8_5_2_2_1_1_1_1_1_5_7_2_1_6_6_1_2_4_7_9_10_8_8_8_8_1_1_2_5_4_7_2_1_7_4_3_4_5_2_2_1_3_4_4_4_2_1_6_6_6_5_3_5_2_2_6_6_2_7_5_1_6_3_10_1_7_1_3_3_9_1_2_3_2_3_3_8_3_6_1_1_7_2_1_5_5_5_1_1_5_2_3_1_2_9_9_6_4_4_1_1_5_2_1_9_1_1_2</t>
+  </si>
+  <si>
+    <t>8_2_1_2_1_4_4_1_3_8_1_1_6_3_9_8_2_9_6_1_7_9_1_7_2_4_3_1_5_5_1_8_7_2_6_3_2_3_3_2_1_3_4_9_4_1_4_1_8_4_4_1_7_1_9_2_5_9_3_8_4_9_2_7_3_4_1_1_5_2_5_9_1_10_5_5_4_7_9_5_9_3_6_7_3_2_5_4_8_4_3_8_5_2_3_5_8_6_10_6_10_3_2_6_3_6_2_6_8_2_8_5_9_2_6_4_4_6_8_2_5_10_2_2_5_1_1_7_2_2_5_9_5_2_6_3_4_1_3_1_2_4_8_9_8_9_3_2_6_3_2_1_8_5_9_4_2_8_2_1_7_8_7_2_1_2_9_2_1_1_2_4_10_6_4_3_5_8_2_4_5_5_7_6_5_1_5_6_4_5_8_2_6_6_10_4_9_3_8_3_2_1_9_3_3_4_9_1_1_2_7_8_7_2_2_4_2_6_8_2_8_4_2_4_1_7_2_6_1_7_2_9_1_4_5_9_9_7_6_9_3_5_4_5_1_2_6_6_4_5_5_6_7_5_7_10_6_5_3_7_1_3_1_9_7_5_4_2_6_1_4_5_3_2_10_4_7_6_8_8_5_4_3_3_4_9_5_1_6_7_2_9_2_5_6_9_6_8_5_6_1_5_8_2_2_9_9_4_2_3_9_1_1_1_7_2_1_1_10_6_9_3_1_8_5_6_3_9_9_2_5_4_4_1_5_6_7_5_5_2_6_3_2_2_1_7_5_7_3_6_1_1_2_9_7_3_6_2_8_7_7_4_2_4_2_1_6_6_3_1_4_9_5_1_2_8_5_1_5_4_1_3_1_5_4_1_2_9_2_6_7_7_1_4_3_3_1_4_4_5_3_8_3_4_10_6_6_7_5_4_4_1_1_3_8_5_2_2_7_2_4_10_4_2_1_6_2_1_1_3_2_5_8_2_4_5_3_1_5_4_10_3_6_6_2_9_2_2_8_8_2_9_7_2_8_6_6_2_3_5_6_9_3_3_8_8_9_1_3_6_2_1_3_3_3_4_3_8_4_9_2_1_4_3_5_3_2_7_3_10_3_4_6_6_1_3_7_2_3_1</t>
+  </si>
+  <si>
+    <t>3_1_1_6_8_8_5_10_1_1_5_5_2_6_9_9_2_2_2_2_9_8_2_2_5_10_2_3_5_8_2_9_4_4_8_8_4_3_3_3_1_5_5_7_10_10_3_1_3_2_2_1_1_2_3_3_4_2_2_3_5_5_4_7_4_5_5_5_3_1_1_6_3_1_5_2_7_7_7_3_7_1_2_4_1_3_1_5_6_4_3_2_6_2_9_9_4_5_3_10_1_1_7_5_8_4_3_10_9_1_3_4_5_2_7_2_7_2_4_3_1_9_5_3_2_6_1_8_3_2_6_2_8_6_3_3_5_5_5_3_8_5_4_9_2_1_1_1_1_6_8_3_6_5_3_8_6_2_3_7_5_8_7_4_4_4_3_6_6_4_4_8_2_7_6_6_3_8_8_8_1_1_5_2_3_3_5_2_8_8_7_1_1_4_3_2_1_1_2_1_6_2_7_4_10_7_7_6_1_9_6_5_5_4_7_1_7_8_7_1_7_2_1_2_4_8_3_8_8_6_2_2_2_4_2_1_6_1_9_6_6_6_2_6_2_6_4_5_8_8_5_3_3_4_3_5_4_8_1_1_3_5_2_9_6_1_7_1_1_8_8_8_8_5_5_1_8_4_5_4_3_3_2_8_2_7_4_8_2_5_1_9_4_4_6_1_3_1_4_9_5_1_4_6_3_6_7_2_4_8_4_9_2_2_3_5_5_5_9_8_4_1_2_7_4_10_1_5_1_7_7_8_4_9_6_2_2_4_8_2_5_5_2_6_6_7_9_1_1_1_5_2_8_5_6_1_6_2_2_2_3_3_8_6_2_3_3_1_6_2_5_3_9_3_3_3_1_2_8_8_2_6_1_6_2_2_3_4_4_5_5_5_2_8_7_7_1_4_9_8_3_4_10_1_5_5_7_7_3_10_10_10_3_4_6_3_2_1_2_7_1_1_5_2_4_4_3_2_8_10_3_6_2_4_3_2_6_1_6_1_4_2_5_1_7_7_2_6_6_1_1_1_8_5_3_2_1_3_6_6_4_5_6_1_2_5_4_4_6_6_6_2_4_2_8_4_1_4_1_6_5_6_6_6_2_3_6_4_5_1_1_2_4_8_8_4_3_2_5_1</t>
+  </si>
+  <si>
+    <t>4_4_6_5_2_4_3_7_1_1_6_4_1_9_1_4_4_5_5_1_6_5_2_3_7_5_2_6_4_2_8_3_1_5_5_3_3_8_1_1_3_6_6_7_3_6_8_1_2_9_8_2_4_4_3_10_6_6_8_6_5_4_5_6_1_7_4_6_5_5_9_2_3_6_2_4_9_9_6_9_5_3_8_4_5_8_3_2_1_9_4_2_2_5_3_6_10_7_5_6_2_3_5_2_4_6_1_1_8_2_4_4_6_2_8_2_10_3_1_8_2_2_3_1_3_2_3_5_10_6_6_6_5_2_3_2_4_4_5_2_3_7_9_3_8_4_5_4_1_6_6_4_1_1_6_4_4_2_4_6_8_8_6_5_4_4_8_2_6_2_9_7_8_7_5_9_4_9_2_4_4_2_7_4_2_4_7_9_2_2_2_6_1_3_3_4_10_6_8_5_3_7_3_4_5_3_8_9_6_2_1_3_5_3_4_3_2_4_3_3_3_3_7_5_2_4_5_9_6_1_2_2_2_6_1_2_1_1_8_3_6_1_1_3_4_4_5_4_3_3_10_6_6_5_9_5_1_4_2_10_6_3_5_8_3_6_1_3_8_3_1_7_7_9_7_6_2_2_5_2_1_9_6_7_5_1_8_4_5_6_8_1_3_2_6_3_2_9_3_6_6_1_7_1_6_1_4_8_2_5_1_5_1_1_2_5_3_2_9_6_2_6_1_2_2_1_2_2_4_7_2_5_2_8_10_1_5_3_3_6_9_4_2_1_10_6_2_7_9_7_8_6_3_1_4_1_10_7_9_1_3_1_4_8_1_2_4_5_7_2_3_7_1_4_3_9_4_6_1_5_7_2_9_2_3_8_5_5_2_5_6_8_6_9_7_4_7_2_2_2_9_3_8_8_4_7_5_3_3_2_2_5_2_4_4_3_2_1_5_9_7_10_7_6_6_3_3_2_8_6_1_1_9_1_6_4_1_1_2_2_3_7_8_5_10_6_8_3_2_6_4_8_2_3_4_2_5_4_2_3_3_10_3_6_4_1_4_1_9_10_5_5_5_9_7_9_1_10_4_8_3_2_9_2_10_1_4_2_3_5_4_8_1_1_2_3_1_6_4_3</t>
+  </si>
+  <si>
+    <t>2_3_3_5_8_1_1_7_6_7_5_5_2_10_8_4_5_8_8_6_3_3_4_5_5_7_1_2_2_2_2_1_3_6_1_1_1_9_9_7_4_4_4_3_3_5_2_9_2_2_3_6_3_7_7_5_7_4_6_9_4_6_1_2_9_1_1_2_4_9_5_3_2_2_6_3_3_1_5_1_3_4_8_5_3_6_5_7_7_3_6_6_4_4_4_2_2_4_5_3_1_8_8_2_5_8_5_4_9_1_7_1_8_1_1_1_4_4_8_4_7_4_2_6_2_9_2_5_5_2_2_5_3_1_2_7_7_4_4_5_5_6_6_6_6_1_6_6_2_2_9_4_8_1_1_1_4_8_7_6_4_6_6_3_8_3_1_1_7_6_2_4_1_8_8_3_2_10_5_3_4_1_2_4_4_3_3_8_8_8_8_1_3_3_6_10_10_8_6_1_4_1_10_8_4_10_10_10_2_9_6_5_4_4_10_1_8_6_7_7_7_4_9_7_6_4_5_2_1_1_3_1_9_1_2_4_4_2_1_7_2_6_5_1_1_2_4_4_3_5_2_2_10_2_2_3_3_8_2_2_2_2_6_9_7_4_4_6_6_6_9_9_4_6_5_5_5_1_6_6_6_5_7_1_7_7_1_1_1_8_3_2_7_4_3_1_1_5_5_2_6_6_3_1_4_2_7_1_1_3_4_5_6_2_6_1_3_3_4_2_2_7_1_4_3_5_5_9_6_1_1_7_7_9_2_4_2_6_2_5_7_9_9_9_4_5_7_8_4_5_4_2_2_2_6_3_7_5_2_6_8_4_2_1_6_8_2_4_1_5_1_9_3_5_6_5_3_6_2_7_10_4_3_8_3_5_1_5_5_1_3_3_3_6_2_7_2_3_3_5_5_2_5_3_2_5_5_5_6_5_7_1_3_1_6_8_8_2_6_4_10_8_7_7_7_10_3_4_3_3_6_6_3_8_6_10_2_6_1_3_6_8_7_5_4_2_9_3_9_3_2_3_1_1_8_6_6_10_10_1_1_7_4_4_1_9_1_8_10_1_9_10_1_4_4_4_8_6_3_3_9_9_3_6_1_2_8_8_5_4_7_3_1_2_3_1_7_3_7_8</t>
+  </si>
+  <si>
+    <t>3_6_8_5_6_4_3_3_8_6_4_5_1_5_4_1_3_10_4_6_4_1_3_2_6_1_4_6_10_6_8_7_1_7_7_4_2_4_10_3_2_8_6_2_5_3_8_1_3_4_6_4_8_1_9_1_2_7_9_2_6_5_2_7_1_7_8_1_8_8_4_5_5_1_7_7_7_4_3_1_4_5_8_8_3_2_5_1_4_8_10_7_5_6_6_1_4_2_2_5_6_6_4_7_6_2_7_1_1_5_6_1_5_7_1_10_7_5_2_1_7_4_8_2_7_8_3_3_4_1_3_6_5_7_9_7_8_3_5_8_8_6_4_3_5_6_9_8_4_7_2_6_10_7_6_1_9_3_1_7_3_1_9_9_2_6_6_1_4_5_3_6_6_3_6_2_5_4_4_8_5_7_2_3_3_10_7_10_7_6_2_1_8_5_3_1_9_6_3_2_1_6_7_4_4_7_3_5_6_1_4_3_2_1_5_5_9_8_9_7_2_5_4_4_3_4_1_1_2_2_6_8_4_3_9_3_3_6_9_5_4_6_5_7_7_2_8_2_9_3_2_1_5_6_3_4_4_2_8_7_2_5_9_9_2_7_5_6_1_3_6_4_7_1_8_6_9_2_5_1_4_8_10_4_1_1_3_2_6_1_1_5_10_7_6_8_5_2_4_7_9_4_2_5_4_2_5_4_3_6_6_5_7_7_8_3_3_8_1_8_5_2_6_7_9_6_7_3_4_2_7_3_5_3_5_9_2_2_4_6_3_1_1_9_5_7_5_9_3_1_1_2_2_5_1_2_4_3_5_9_2_9_3_7_1_8_6_1_2_7_6_1_1_4_10_7_3_3_2_10_5_1_1_7_1_4_2_8_4_1_2_7_4_7_1_1_5_9_8_1_4_5_2_10_6_1_9_7_8_6_6_3_5_4_4_8_3_3_2_2_9_1_2_7_9_2_7_1_1_1_9_9_5_3_3_8_7_5_6_2_9_2_2_3_4_9_3_2_9_8_5_9_7_1_6_7_3_3_7_1_2_5_2_2_7_4_9_3_6_5_4_5_5_3_8_4_6_1_2_1_10_4_2_4_3_2_1_3_3_2_9_2_8_7_5_8_7_7_3_7</t>
+  </si>
+  <si>
+    <t>1_6_6_6_4_6_6_6_6_3_4_3_8_8_2_7_7_6_8_1_2_5_3_6_5_5_5_1_4_2_3_2_3_3_1_8_4_4_6_3_5_8_8_7_3_3_3_4_4_2_6_8_6_5_2_2_3_7_8_6_1_4_9_6_5_4_1_4_1_5_3_3_3_6_2_2_6_5_1_3_5_1_6_7_4_9_3_3_9_4_4_6_4_4_5_4_4_7_1_5_5_5_1_4_4_5_9_5_2_8_8_4_6_5_4_10_5_3_8_5_2_2_7_6_3_2_2_5_2_5_1_3_2_3_3_2_3_1_1_1_5_9_4_6_2_4_3_2_7_7_3_6_1_2_9_7_3_5_4_6_1_2_2_2_2_5_6_8_1_10_3_3_7_7_7_2_8_4_2_3_3_7_4_2_8_3_4_4_1_1_2_4_5_1_2_2_6_9_3_3_3_1_5_2_3_4_10_8_3_2_3_2_1_5_5_7_3_1_1_2_2_7_7_10_1_2_3_1_1_2_3_2_6_8_1_9_1_2_7_3_7_2_9_6_5_1_2_2_1_1_1_4_2_3_7_4_3_1_4_1_3_3_3_1_5_1_1_5_2_2_1_10_2_1_2_4_7_4_7_1_3_1_10_6_6_6_4_4_3_3_1_3_4_4_4_2_1_5_1_4_2_2_1_4_2_5_1_2_6_9_1_1_3_1_9_9_8_7_2_5_1_2_5_5_2_4_7_4_6_4_8_2_3_1_1_5_4_6_1_8_7_3_3_2_2_4_1_7_1_3_7_1_6_8_7_8_4_9_5_5_1_1_6_2_3_9_8_2_4_6_9_1_1_8_6_1_9_2_9_6_2_4_6_7_7_2_1_8_4_3_2_9_5_5_5_4_9_8_1_1_1_1_4_1_7_2_6_1_10_3_5_1_7_5_2_4_2_1_2_1_10_5_1_8_2_1_1_5_1_6_7_7_8_2_3_3_2_5_1_4_8_7_2_5_9_2_2_5_2_8_8_1_2_4_2_5_3_4_3_3_1_6_1_3_5_1_1_8_5_8_4_3_3_3_9_8_5_5_6_2_3_8_3_3_9_8_2_3_4_1_5_4_1_5_3_4_3_9_1_1</t>
+  </si>
+  <si>
+    <t>2_1_6_2_2_2_2_1_9_6_2_8_7_9_5_1_3_4_5_3_4_7_5_2_6_4_2_1_4_8_6_2_7_7_5_7_9_7_4_8_6_5_2_3_10_5_1_4_9_3_10_4_7_9_2_4_3_7_1_7_4_5_6_10_6_10_7_10_1_1_6_6_2_1_3_2_1_5_2_10_5_5_7_10_6_3_4_2_2_6_3_6_9_7_2_3_8_5_2_2_1_4_3_6_5_4_8_2_7_6_10_7_5_2_9_6_4_2_1_5_4_8_2_6_4_4_3_1_3_8_6_2_5_7_4_2_3_8_4_8_1_1_8_7_2_6_4_3_5_1_4_7_8_5_9_2_3_5_9_7_7_1_3_7_8_5_1_9_6_6_2_7_8_2_3_2_7_5_2_4_2_8_7_2_7_4_8_1_4_1_2_1_4_2_4_2_2_5_6_1_5_7_5_4_5_4_1_3_4_3_3_7_1_6_4_2_6_4_9_5_8_8_5_8_5_2_2_5_7_7_8_8_1_8_9_1_6_3_3_3_1_3_4_7_1_3_5_4_5_2_2_4_3_2_1_9_3_1_4_1_8_3_5_5_8_3_3_10_1_2_3_3_9_7_2_5_8_5_4_4_9_1_1_5_4_3_4_1_8_9_4_5_1_2_2_4_1_8_7_6_1_4_7_6_3_3_3_9_5_1_6_3_4_5_3_1_4_7_9_2_2_7_9_5_2_6_3_6_5_6_2_2_4_2_5_9_4_1_9_4_4_6_3_1_5_4_6_6_2_10_7_5_4_6_9_5_3_6_9_6_7_4_7_3_8_3_6_4_6_2_9_6_10_4_8_1_8_9_7_5_7_2_10_1_8_2_5_8_2_6_9_3_5_1_3_4_5_8_7_10_3_8_2_2_2_5_2_8_2_8_4_5_2_3_3_6_8_1_2_7_4_1_2_1_8_4_3_7_7_1_3_5_1_1_7_7_3_5_8_2_2_2_1_5_3_9_3_1_7_4_1_10_7_6_2_8_7_4_1_9_2_7_2_6_4_1_5_3_1_8_4_1_3_6_9_1_4_1_9_3_2_2_4_4_6_3_1_2_1_6_1_7_7_5_8_4_5_1_8_7</t>
   </si>
 </sst>
 </file>
@@ -2086,11 +2116,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K167"/>
+  <dimension ref="A1:K172"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
     <col min="2" max="2" width="9" style="7"/>
+    <col min="3" max="3" width="9.375"/>
     <col min="4" max="4" width="7.875" customWidth="1"/>
     <col min="5" max="5" width="28.75" customWidth="1"/>
     <col min="6" max="6" width="23.525" customWidth="1"/>
@@ -6072,7 +6103,7 @@
     </row>
     <row r="126" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A126" s="6">
-        <f t="shared" ref="A126:A152" si="6">C126*10+D126</f>
+        <f t="shared" ref="A126:A157" si="6">C126*10+D126</f>
         <v>20280011</v>
       </c>
       <c r="B126" s="14">
@@ -6936,7 +6967,7 @@
     </row>
     <row r="153" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A153" s="6">
-        <f>C153*10+D153</f>
+        <f t="shared" si="6"/>
         <v>20200011</v>
       </c>
       <c r="B153" s="14">
@@ -6968,7 +6999,7 @@
     </row>
     <row r="154" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A154" s="6">
-        <f>C154*10+D154</f>
+        <f t="shared" si="6"/>
         <v>20200012</v>
       </c>
       <c r="B154" s="14">
@@ -7000,7 +7031,7 @@
     </row>
     <row r="155" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A155" s="6">
-        <f>C155*10+D155</f>
+        <f t="shared" si="6"/>
         <v>20200013</v>
       </c>
       <c r="B155" s="14">
@@ -7032,7 +7063,7 @@
     </row>
     <row r="156" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A156" s="6">
-        <f>C156*10+D156</f>
+        <f t="shared" si="6"/>
         <v>20200014</v>
       </c>
       <c r="B156" s="14">
@@ -7064,7 +7095,7 @@
     </row>
     <row r="157" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A157" s="6">
-        <f>C157*10+D157</f>
+        <f t="shared" si="6"/>
         <v>20200015</v>
       </c>
       <c r="B157" s="14">
@@ -7413,6 +7444,166 @@
       </c>
       <c r="J167" s="17"/>
       <c r="K167" s="17"/>
+    </row>
+    <row r="168" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A168" s="6">
+        <f>C168*10+D168</f>
+        <v>20380011</v>
+      </c>
+      <c r="B168" s="14">
+        <v>103800</v>
+      </c>
+      <c r="C168" s="33">
+        <v>2038001</v>
+      </c>
+      <c r="D168" s="33">
+        <v>1</v>
+      </c>
+      <c r="E168" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="H168" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I168" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="J168" s="17"/>
+      <c r="K168" s="17"/>
+    </row>
+    <row r="169" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A169" s="6">
+        <f>C169*10+D169</f>
+        <v>20380012</v>
+      </c>
+      <c r="B169" s="14">
+        <v>103801</v>
+      </c>
+      <c r="C169" s="33">
+        <v>2038001</v>
+      </c>
+      <c r="D169" s="33">
+        <v>2</v>
+      </c>
+      <c r="E169" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H169" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I169" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="J169" s="17"/>
+      <c r="K169" s="17"/>
+    </row>
+    <row r="170" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A170" s="6">
+        <f>C170*10+D170</f>
+        <v>20380013</v>
+      </c>
+      <c r="B170" s="14">
+        <v>103802</v>
+      </c>
+      <c r="C170" s="33">
+        <v>2038001</v>
+      </c>
+      <c r="D170" s="33">
+        <v>3</v>
+      </c>
+      <c r="E170" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H170" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I170" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="J170" s="17"/>
+      <c r="K170" s="17"/>
+    </row>
+    <row r="171" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A171" s="6">
+        <f>C171*10+D171</f>
+        <v>20380014</v>
+      </c>
+      <c r="B171" s="14">
+        <v>103803</v>
+      </c>
+      <c r="C171" s="33">
+        <v>2038001</v>
+      </c>
+      <c r="D171" s="33">
+        <v>4</v>
+      </c>
+      <c r="E171" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H171" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I171" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="J171" s="17"/>
+      <c r="K171" s="17"/>
+    </row>
+    <row r="172" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A172" s="6">
+        <f>C172*10+D172</f>
+        <v>20380015</v>
+      </c>
+      <c r="B172" s="14">
+        <v>103804</v>
+      </c>
+      <c r="C172" s="33">
+        <v>2038001</v>
+      </c>
+      <c r="D172" s="33">
+        <v>5</v>
+      </c>
+      <c r="E172" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H172" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I172" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="J172" s="17"/>
+      <c r="K172" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -424,16 +424,16 @@
     <t>2_1_4_4_1_8_5_1_1_1_1_6_6_1_1_2_3_5_2_5_5_6_2_2_2_1_2_6_6_4_9_1_1_3_5_1_4_5_7_5_3_3_2_1_4_3_4_4_6_3_3_2_4_5_2_1_4_2_3_3_3_1_2_3_3_7_6_1_2_3_6_3_2_1_3_2_3_2_1_1_1_6_4_3_5_2_3_3_8_1_3_5_5_6_6_6_2_2_1_2_9_2_1_5_4_3_1_2_2_3_2_4_2_1_5_5_3_3_1_1_1_3_5_8_4_4_1_1_2_1_1_2_2_2_3_3_4_8_1_5_4_3_1_1_4_2_1_4_3_2_2_3_2_1_2_1_8_6_1_2_2_1_4_4_2_3_9_2_7_4_2_3_1_1_1_1_1_1_7_1_3_6_2_1_1_1_1_1_4_6_4_3_4_8_4_2_2_2_2_4_6_3_4_2_2_3_4_1_3_1_5_5_3_1_4_3_2_2_1_1_1_4_3_2_3_3_6_1_2_1_4_1_4_4_6_1_2_3_3_5_1_4_1_3_1_4_1_5_2_6_6_6_6_6_4_5_5_6_6_4_2_2_2_2_2_2_3_1_3_3_5_1_1_4_6_4_4_6_3_3_3_3_2_5_3_2_2_3_1_5_5_3_2_2_3_3_8_2_2_3_5_5_3_4_4_1_2_1_4_3_1_1_5_6_4_4_10_8_9_3_2_1_4_4_6_4_2_9_2_2_5_6_2_5_2_3_3_2_3_3_3_3_2_3_3_3_1_4_4_6_5_5_5_6_1_1_2_1_3_3_3_6_7_1_4_1_4_3_1_9_2_6_5_5_5_3_7_7_8_1_4_4_3_2_4_2_1_6_4_3_1_6_6_5_5_5_5_7_4_2_1_5_3_2_4_3_4_7_2_2_6_1_2_5_5_5_1_2_8_2_1_5_3_2_6_2_8_2_3_2_1_4_1_3_8_3_2_9_2_5_4_3_3_5_5_3_2_5_5_2_7_1_2_6_6_5_3_1_6_4_6_4_4_3_2_2_3_1_1_1_6_1_1_8_4_3_2_1_1_3_2_2_2_2_8_2_2_4_1_1_1_3_2_2_5_4_1_3_5_3</t>
   </si>
   <si>
-    <t>1_5_1_1_2_4_1_3_5_5_7_7_3_2_2_6_3_2_1_2_3_3_4_4_3_2_1_3_5_3_4_9_3_2_1_7_7_8_3_3_3_10_4_3_2_4_2_1_2_4_4_10_3_1_1_3_4_7_3_3_4_2_6_6_6_1_2_5_1_4_4_5_3_1_1_5_2_1_5_4_1_1_3_3_3_2_2_2_1_2_2_4_4_1_5_2_2_5_5_3_4_2_1_1_1_2_6_6_9_6_4_3_2_1_5_5_1_6_4_3_6_4_3_5_3_3_8_6_6_6_10_9_2_2_2_6_5_3_6_7_6_3_1_3_2_1_3_8_5_2_2_1_5_3_2_9_3_2_3_3_3_3_3_3_6_3_5_7_7_1_1_1_9_5_1_10_4_6_3_1_9_6_2_1_2_2_2_1_6_5_2_4_6_3_4_1_4_3_3_4_7_7_7_1_4_2_6_1_6_2_3_3_3_4_3_2_2_7_7_4_3_1_6_5_5_5_2_6_4_1_8_4_4_6_1_5_2_10_2_5_4_7_3_3_1_1_2_6_3_1_1_2_6_6_2_1_3_1_1_5_3_3_9_1_1_2_6_6_3_3_2_2_1_4_1_8_3_6_6_7_1_3_4_9_5_3_5_1_1_1_3_8_3_6_1_6_6_2_2_4_4_1_3_6_1_1_1_1_1_1_6_4_6_6_6_4_2_3_4_3_6_4_4_2_4_1_5_4_1_5_4_2_3_3_1_2_8_3_4_1_1_5_1_1_2_2_2_2_5_2_6_2_4_5_4_3_6_2_1_1_1_5_2_1_5_5_6_5_2_1_2_2_1_1_3_3_4_6_3_3_5_6_4_1_1_2_5_9_2_3_3_1_2_6_4_3_3_3_3_6_9_2_1_6_2_4_1_1_4_4_2_2_2_5_6_1_1_2_2_1_3_5_4_1_1_1_1_2_3_5_5_3_3_3_1_4_8_2_10_2_1_5_1_5_1_3_7_1_1_6_6_1_6_5_3_5_1_1_1_7_6_6_2_5_4_8_3_5_6_5_7_1_4_4_4_2_1_1_1_1_3_4_6_2_1_3_6_2_5_1_1_1_2_8_6_1_3_2_6_1</t>
-  </si>
-  <si>
-    <t>1_2_2_1_4_4_4_1_1_1_5_3_4_4_1_4_2_1_2_5_1_5_1_4_4_3_2_3_6_1_3_3_4_5_2_2_5_5_5_1_1_2_2_5_5_6_1_2_1_3_6_5_5_5_2_4_1_3_1_5_2_1_2_2_2_1_1_2_3_6_8_10_5_6_2_1_4_4_2_6_3_2_4_5_3_2_6_3_1_9_4_1_4_6_3_5_5_4_1_4_2_5_3_1_2_1_1_2_6_6_5_8_1_4_8_8_8_6_1_3_2_1_4_6_3_2_4_4_3_1_4_6_6_3_2_5_2_4_4_2_2_3_3_10_9_1_6_1_5_1_1_5_3_2_6_1_1_8_8_3_3_2_5_5_1_3_2_10_5_5_1_4_2_6_2_6_1_5_5_1_9_9_9_2_6_1_1_1_2_9_3_2_4_4_1_3_4_6_4_4_6_4_3_2_2_6_2_1_4_5_3_1_8_1_1_3_5_7_3_5_5_6_2_2_4_4_3_1_1_2_2_1_3_2_1_6_2_1_10_7_2_1_6_1_8_7_1_2_2_5_6_3_3_2_2_2_4_3_3_3_3_2_9_3_3_4_5_6_3_5_10_1_4_4_4_2_2_4_1_3_2_3_6_3_4_1_1_4_3_2_10_3_3_7_7_2_1_3_1_1_3_3_3_1_8_1_9_1_3_3_3_3_4_3_3_4_2_3_2_2_7_4_1_6_1_2_6_6_3_4_5_5_3_3_7_1_2_1_4_6_6_4_4_5_1_4_4_2_6_4_6_5_1_2_4_3_4_4_6_2_10_3_4_5_5_5_1_4_1_3_3_8_1_3_3_5_1_5_3_4_2_1_1_2_6_3_7_4_1_4_2_5_3_1_4_6_2_6_3_4_2_4_4_6_5_1_9_4_2_2_4_1_2_5_5_4_3_1_1_1_1_5_1_5_4_1_5_6_8_6_6_3_4_1_1_3_8_1_1_2_4_4_7_8_3_5_1_2_6_4_2_4_4_5_5_1_1_6_3_4_6_2_3_8_6_6_3_5_4_5_1_1_3_10_1_2_5_3_7_4_4_6_1_1_8_8_5_5_6_1_2_8_4_2_1_10_1_2_6_2</t>
-  </si>
-  <si>
-    <t>2_1_3_2_2_4_6_1_6_3_1_8_5_4_3_2_7_7_2_3_4_4_3_2_2_4_3_3_3_3_8_5_4_1_3_4_4_5_3_5_1_1_1_1_2_1_1_4_1_5_5_5_3_8_8_6_1_2_1_2_1_4_1_1_6_2_2_3_2_4_3_7_3_4_7_2_3_3_6_9_9_9_1_1_3_7_7_6_6_3_8_1_1_2_4_4_6_1_1_1_1_1_1_4_5_3_9_1_3_2_4_3_4_4_9_3_2_4_5_4_5_10_3_3_1_5_2_2_2_3_9_5_2_2_6_1_3_8_2_4_4_2_2_2_2_1_6_6_2_5_4_2_3_6_6_5_5_3_5_8_6_4_1_4_2_2_2_6_6_10_1_3_1_1_3_3_4_1_4_1_2_1_3_3_2_4_8_8_5_4_4_1_4_2_1_2_3_8_5_5_9_5_3_3_3_6_4_4_5_6_6_3_5_5_1_3_3_1_1_5_6_2_5_2_4_4_6_5_4_5_7_2_4_3_1_4_3_1_4_4_8_6_4_4_2_2_5_5_5_5_5_3_6_2_2_3_2_2_7_8_3_2_1_1_2_2_2_6_2_2_2_3_1_2_2_4_1_1_1_1_2_1_5_5_2_3_1_8_2_4_4_7_3_3_5_2_2_4_4_1_3_1_2_2_10_10_2_2_2_2_4_3_2_3_8_6_9_4_2_7_7_1_10_2_1_2_2_5_2_5_2_3_4_6_6_6_1_5_5_5_1_2_1_2_3_3_4_1_1_2_4_1_6_2_1_3_2_3_5_3_6_3_1_6_3_3_4_6_2_4_6_7_5_3_8_9_4_8_3_4_4_4_1_6_2_2_2_1_6_8_5_1_4_4_4_3_2_4_3_9_1_1_1_3_8_1_1_1_4_2_1_4_4_5_2_6_5_2_2_2_1_2_4_1_1_9_2_2_2_5_3_3_2_5_5_5_1_3_1_5_5_4_5_5_8_4_3_6_2_7_7_2_5_2_5_5_1_4_7_1_3_1_2_5_1_3_8_4_8_9_6_6_1_2_3_5_2_4_1_1_4_8_5_1_3_5_5_3_1_4_4_3_2_3_9_5_5_3_1_4</t>
-  </si>
-  <si>
-    <t>3_2_5_6_5_3_1_7_6_4_7_7_3_9_4_1_1_1_4_1_3_1_1_6_1_3_1_1_8_3_3_4_2_3_6_3_6_9_7_1_2_5_6_3_6_4_3_1_1_4_6_9_10_10_3_2_10_7_5_1_1_1_1_3_2_4_4_3_4_7_8_3_5_1_2_3_3_4_7_1_5_7_5_5_3_3_7_2_5_3_2_6_1_6_1_5_1_3_3_1_6_5_3_2_5_5_5_5_2_6_3_2_5_6_6_6_6_3_1_7_1_1_1_2_2_6_3_3_1_1_9_3_9_9_1_1_1_1_1_3_3_6_5_6_3_1_1_1_4_4_4_5_4_3_6_3_1_4_2_2_3_6_2_6_2_2_2_5_1_5_4_3_8_8_3_5_1_1_1_6_4_4_7_2_1_5_4_1_4_3_4_1_2_6_2_2_1_1_5_4_10_1_1_5_4_8_5_1_2_3_2_1_4_6_6_2_1_9_1_5_2_2_6_4_1_1_1_1_4_2_1_5_6_2_4_4_7_1_1_5_8_2_2_2_5_1_9_6_6_4_6_7_6_6_1_8_8_1_4_3_4_1_1_3_3_3_2_1_1_1_1_2_5_1_1_1_1_4_2_2_4_5_4_2_1_1_1_1_6_1_1_1_3_1_2_1_6_7_1_5_4_9_3_1_4_5_1_3_2_2_10_4_1_3_4_3_3_5_5_5_5_6_8_3_2_1_5_5_1_4_3_5_2_1_2_5_2_3_7_7_6_3_3_2_5_4_5_3_3_6_2_4_3_3_1_1_1_1_1_2_1_1_9_1_1_1_4_5_5_3_3_2_5_3_9_2_1_3_5_1_1_6_4_4_1_2_4_4_6_3_1_3_6_2_1_1_3_5_1_2_3_3_3_6_5_3_3_1_3_4_1_1_5_2_2_4_4_4_4_5_3_3_2_5_2_1_1_5_10_1_1_5_2_6_2_9_2_3_8_1_4_6_6_6_3_2_5_1_4_8_6_2_2_6_1_6_2_2_2_1_1_3_1_1_2_9_9_3_3_1_1_5_5_5_3_1_3_5_1_4_1_3_1_1_1_5_5_2_3_3_5_4_8_6_2_2_1_1_1_2</t>
+    <t>4_9_4_4_6_7_7_3_6_2_10_9_3_4_2_6_4_9_8_4_2_8_7_5_9_4_10_1_4_4_2_10_4_8_8_8_8_10_4_4_3_5_3_10_6_3_6_10_3_9_9_7_3_8_2_9_2_3_1_1_6_6_2_9_4_8_7_3_1_8_4_1_1_8_8_10_9_5_2_2_3_3_5_5_5_7_4_5_10_10_5_8_3_6_4_10_10_9_5_4_9_9_2_10_6_8_10_3_4_7_9_10_10_2_2_6_6_3_7_7_3_10_1_1_1_9_10_10_10_5_7_8_8_6_2_3_4_4_3_7_7_7_6_8_9_3_6_10_10_10_4_10_8_1_2_6_3_2_1_8_3_7_8_5_10_2_1_7_7_3_9_7_3_10_2_3_10_6_3_9_1_10_10_10_4_2_10_6_9_6_9_4_3_2_5_7_5_8_9_1_7_8_9_10_5_8_8_3_9_5_3_7_4_4_2_1_10_10_7_7_4_8_7_9_9_7_2_8_9_1_8_8_9_7_3_2_10_10_10_8_10_7_3_5_2_5_4_8_3_3_1_1_1_9_7_7_7_5_5_5_1_9_10_6_6_2_1_3_3_7_7_3_1_3_2_2_1_9_4_10_2_6_8_7_8_3_10_4_5_3_8_2_8_8_10_5_7_2_3_1_8_10_2_3_2_10_2_9_10_4_7_4_8_9_8_6_10_2_4_4_6_1_1_7_7_3_8_1_9_9_7_7_8_9_1_8_9_3_7_7_9_9_2_8_2_8_1_8_8_3_3_8_9_1_1_2_9_6_2_7_10_9_9_7_9_7_7_7_5_8_4_5_8_5_4_1_4_2_4_4_7_4_4_4_1_5_4_4_9_2_5_4_4_2_2_2_3_2_6_7_3_3_4_4_5_2_2_7_1_8_10_3_6_6_6_6_4_5_2_9_1_1_5_8_8_7_7_8_9_9_1_3_3_4_9_9_3_3_4_6_7_3_3_1_3_10_10_2_1_1_8_1_8_8_2_4_2_8_4_1_1_7_9_1_3_10_10_7_4_5_2_1_1_4_7_4_3_1_4_10_10_2_2_3_5_5_10_10_5_5_9_4_3_9_9_2_1_1_1_7</t>
+  </si>
+  <si>
+    <t>2_6_5_10_8_2_3_7_6_1_4_3_4_2_9_1_10_8_10_5_5_7_7_2_7_9_10_10_7_3_3_5_4_8_5_9_4_2_4_4_5_4_5_5_10_3_3_3_2_7_9_4_1_10_7_7_3_7_3_7_10_6_2_2_7_3_7_3_5_6_7_7_2_6_6_4_4_1_8_6_2_3_10_9_1_4_6_3_3_3_3_7_7_3_9_2_10_2_3_9_5_9_10_7_7_10_4_5_9_6_4_4_4_9_3_9_2_4_10_9_8_8_2_8_6_5_9_4_6_1_6_5_10_10_1_9_10_3_3_10_1_10_9_2_3_2_10_6_4_6_8_5_3_8_2_6_6_3_9_5_9_5_8_4_10_9_5_10_1_1_7_3_2_2_4_4_5_10_7_8_7_1_4_6_7_10_4_4_1_3_10_3_3_6_9_1_1_1_4_5_10_4_8_6_8_9_1_5_1_6_1_7_4_2_8_6_1_9_2_4_4_7_2_6_7_9_8_8_8_4_6_5_10_10_3_10_10_9_3_4_7_6_10_2_5_7_1_3_4_4_4_10_3_6_3_3_7_6_10_3_10_3_7_7_2_7_10_4_10_6_1_4_6_5_5_2_9_1_5_1_7_10_10_3_2_2_8_3_4_4_2_9_1_8_1_2_5_3_1_7_2_7_1_4_2_10_9_1_1_2_4_9_8_1_5_6_2_2_9_7_7_8_10_1_7_8_4_9_1_3_5_5_5_10_9_3_4_3_3_8_1_9_9_4_8_7_10_2_10_9_5_3_1_6_7_5_5_9_9_7_9_10_5_7_10_9_7_6_6_1_8_5_7_2_1_9_1_4_8_8_9_3_6_10_7_6_10_2_3_7_6_7_10_2_2_3_1_2_1_9_8_9_1_9_5_5_10_7_7_7_2_10_5_2_7_7_4_9_9_2_8_5_10_5_5_6_5_7_2_7_1_7_9_6_7_7_5_4_4_7_1_4_4_8_8_8_3_3_3_7_8_9_7_8_5_9_5_5_1_2_3_5_1_9_1_3_8_3_7_2_9_10_1_7_4_8_4_4_4_6_1_8_9_9_7_8_8_3_1_10_2_1_6_1_10_10_10_1_3_4</t>
+  </si>
+  <si>
+    <t>4_9_6_5_5_7_7_9_9_3_5_2_7_10_9_10_10_10_10_8_10_10_8_8_1_7_7_7_9_9_6_2_3_2_7_1_5_4_10_10_5_7_8_6_7_10_2_2_8_9_7_10_7_5_3_9_5_10_4_10_10_3_3_7_1_3_2_5_3_3_3_5_9_4_5_5_3_2_8_1_10_2_2_10_6_10_6_4_5_5_9_6_9_3_1_2_9_1_2_6_2_7_3_1_7_5_10_2_2_9_8_3_8_8_8_1_4_8_3_10_10_3_3_9_4_7_4_7_7_5_5_8_5_5_1_2_3_3_3_3_8_4_10_1_7_4_10_9_10_4_3_1_4_5_5_1_4_9_10_6_7_2_2_6_4_2_1_7_7_8_7_7_9_6_7_3_1_10_10_4_2_5_3_3_7_6_6_8_8_6_10_8_8_10_9_4_7_8_10_10_9_9_2_6_1_8_3_2_4_2_1_1_6_6_8_6_9_9_8_4_1_10_2_2_6_10_10_6_1_5_4_6_6_9_10_6_5_10_1_1_3_3_2_3_10_10_6_9_10_8_3_1_6_8_8_2_2_2_5_9_1_8_1_1_3_3_1_4_3_3_10_1_1_10_4_4_2_1_1_3_4_6_9_4_4_7_8_9_5_7_3_8_1_2_9_5_8_8_1_2_1_5_7_7_5_5_4_2_4_8_1_1_4_1_1_6_5_4_8_6_7_3_5_1_9_1_10_8_9_3_6_2_10_6_8_6_10_7_7_9_9_6_6_7_7_9_9_3_2_3_1_3_9_8_9_6_4_4_5_5_5_8_4_10_2_2_8_7_7_7_1_5_2_5_6_1_8_9_9_4_7_9_9_1_6_10_10_4_8_5_4_10_2_9_9_8_7_8_7_8_8_6_7_5_6_4_2_10_2_8_8_7_7_10_4_4_7_4_7_3_1_10_3_7_6_3_1_2_8_7_3_8_10_3_6_9_2_3_9_4_9_8_2_4_2_2_7_5_10_10_9_7_3_9_1_1_8_4_1_7_4_3_4_4_10_9_3_3_9_9_9_8_8_8_3_10_8_1_7_7_2_4_6_8_7_7_10_7_10_10_3_2_7_7_10_1_10_9_6_6</t>
+  </si>
+  <si>
+    <t>7_5_6_10_1_2_2_6_6_7_2_3_2_6_1_4_10_10_6_6_4_1_5_1_8_9_9_5_1_4_3_2_9_2_1_1_4_3_4_3_5_2_10_9_6_6_2_1_1_9_3_4_4_1_1_1_1_1_8_4_3_1_8_10_2_4_7_9_6_5_6_8_4_1_1_7_2_4_4_1_6_1_2_2_6_6_3_8_4_8_4_6_4_7_7_1_1_1_3_2_2_5_5_9_2_3_7_7_3_9_1_4_3_2_1_3_7_4_2_2_4_10_7_6_5_2_1_1_6_1_5_7_8_3_1_5_3_4_10_1_2_5_7_8_2_3_5_8_1_4_4_1_7_10_7_3_1_2_5_5_5_7_7_7_4_5_1_5_6_6_4_6_2_8_5_8_4_2_9_8_9_4_8_7_7_1_10_8_9_9_6_1_1_7_1_3_3_7_9_2_2_8_3_7_6_7_4_7_1_5_2_2_4_6_2_1_1_4_3_3_7_2_4_5_1_9_9_2_1_2_3_9_6_4_1_9_6_7_10_2_6_4_8_10_8_3_3_5_6_3_6_10_10_7_4_2_8_2_1_9_1_9_6_4_1_4_1_9_2_2_7_2_2_7_2_8_10_4_1_1_1_3_7_4_5_2_3_2_1_8_7_7_2_2_2_6_5_1_1_4_8_3_4_4_2_2_2_5_5_6_5_5_10_7_4_1_1_4_6_4_1_5_3_6_3_2_4_1_1_2_2_2_2_3_1_4_4_6_7_9_6_8_8_1_7_7_4_9_9_6_3_2_2_5_7_1_4_1_5_9_10_1_1_5_3_6_2_8_8_2_2_2_3_3_3_2_9_9_2_4_5_7_2_7_1_7_4_4_1_10_1_5_5_5_8_3_10_2_1_6_4_4_10_4_3_6_5_6_6_6_7_3_4_2_2_7_4_4_6_2_1_5_4_2_3_6_6_5_3_4_1_8_2_3_8_5_7_6_6_1_3_8_4_4_6_2_4_3_10_10_4_8_6_1_5_8_1_5_1_5_4_2_2_5_5_5_2_3_3_6_3_2_8_1_10_5_8_2_1_6_1_3_3_2_2_1_3_5_1_1_8_8_6_4_4_5_8_8_4_5</t>
   </si>
   <si>
     <t>6_3_3_2_6_6_1_8_4_4_7_5_1_2_9_6_2_8_2_1_1_4_3_5_3_6_8_9_6_4_4_1_6_5_8_3_7_6_1_2_9_3_2_5_8_6_6_4_7_5_4_4_4_3_2_7_1_5_6_6_2_2_8_4_4_2_1_3_6_8_5_4_2_7_3_8_9_4_3_7_1_4_9_2_6_5_3_4_4_3_7_8_3_3_9_9_5_3_6_4_6_1_1_1_8_4_4_8_8_6_7_3_2_2_4_8_5_5_3_7_2_1_9_1_4_9_9_3_6_9_5_5_1_1_4_1_1_2_2_1_3_3_8_1_4_8_6_3_3_1_4_4_1_3_9_6_8_2_5_6_1_2_6_2_3_9_1_4_5_8_5_1_5_7_3_2_7_9_5_5_5_7_7_3_6_7_7_2_1_1_1_6_2_2_2_6_5_3_1_1_1_5_6_3_3_3_5_4_6_6_3_5_2_1_8_3_1_1_7_3_9_8_6_9_9_4_6_4_9_3_7_1_1_8_5_5_1_3_3_4_6_5_5_1_8_5_1_3_3_5_2_3_1_4_1_7_5_8_1_5_6_2_5_6_8_8_8_9_5_8_8_4_2_4_2_2_2_3_1_5_3_9_5_5_5_7_4_9_9_1_8_6_1_1_4_7_3_2_2_9_9_3_6_6_3_6_4_2_2_4_2_9_6_7_5_3_1_8_9_2_8_2_1_3_9_5_6_9_5_9_4_2_4_4_3_9_1_1_7_7_1_4_6_6_3_7_7_8_7_4_6_4_5_7_8_4_4_3_2_2_4_5_6_1_3_1_1_5_6_1_1_1_6_3_4_2_7_4_1_7_5_6_2_7_1_1_4_8_4_2_4_5_4_3_8_2_2_5_6_4_7_9_6_4_2_4_4_4_4_4_5_3_1_1_4_9_2_3_2_5_6_3_2_2_8_3_5_2_9_1_1_2_8_3_6_3_9_1_4_1_2_8_3_5_5_5_6_9_2_6_5_1_1_8_5_4_2_2_9_6_5_5_2_4_1_9_9_9_1_1_1_6_7_7_2_1_4_7_8_6_8_9_8_4_4_3_5_5_5_4_2_9_4_1_1_2_8_2_3_9</t>
@@ -5337,7 +5337,7 @@
     </row>
     <row r="108" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A108" s="6">
-        <f t="shared" ref="A108:A119" si="5">C108*10+D108</f>
+        <f t="shared" ref="A108:A125" si="5">C108*10+D108</f>
         <v>20350011</v>
       </c>
       <c r="B108" s="14">
@@ -5721,7 +5721,7 @@
     </row>
     <row r="120" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A120" s="6">
-        <f>C120*10+D120</f>
+        <f t="shared" si="5"/>
         <v>20360011</v>
       </c>
       <c r="B120" s="14">
@@ -5753,7 +5753,7 @@
     </row>
     <row r="121" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A121" s="6">
-        <f>C121*10+D121</f>
+        <f t="shared" si="5"/>
         <v>20360012</v>
       </c>
       <c r="B121" s="14">
@@ -5785,7 +5785,7 @@
     </row>
     <row r="122" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A122" s="6">
-        <f>C122*10+D122</f>
+        <f t="shared" si="5"/>
         <v>20360013</v>
       </c>
       <c r="B122" s="14">
@@ -5817,7 +5817,7 @@
     </row>
     <row r="123" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A123" s="6">
-        <f>C123*10+D123</f>
+        <f t="shared" si="5"/>
         <v>20360021</v>
       </c>
       <c r="B123" s="14">
@@ -5849,7 +5849,7 @@
     </row>
     <row r="124" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A124" s="6">
-        <f>C124*10+D124</f>
+        <f t="shared" si="5"/>
         <v>20360022</v>
       </c>
       <c r="B124" s="14">
@@ -5881,7 +5881,7 @@
     </row>
     <row r="125" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A125" s="6">
-        <f>C125*10+D125</f>
+        <f t="shared" si="5"/>
         <v>20360023</v>
       </c>
       <c r="B125" s="14">

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -424,16 +424,16 @@
     <t>2_1_4_4_1_8_5_1_1_1_1_6_6_1_1_2_3_5_2_5_5_6_2_2_2_1_2_6_6_4_9_1_1_3_5_1_4_5_7_5_3_3_2_1_4_3_4_4_6_3_3_2_4_5_2_1_4_2_3_3_3_1_2_3_3_7_6_1_2_3_6_3_2_1_3_2_3_2_1_1_1_6_4_3_5_2_3_3_8_1_3_5_5_6_6_6_2_2_1_2_9_2_1_5_4_3_1_2_2_3_2_4_2_1_5_5_3_3_1_1_1_3_5_8_4_4_1_1_2_1_1_2_2_2_3_3_4_8_1_5_4_3_1_1_4_2_1_4_3_2_2_3_2_1_2_1_8_6_1_2_2_1_4_4_2_3_9_2_7_4_2_3_1_1_1_1_1_1_7_1_3_6_2_1_1_1_1_1_4_6_4_3_4_8_4_2_2_2_2_4_6_3_4_2_2_3_4_1_3_1_5_5_3_1_4_3_2_2_1_1_1_4_3_2_3_3_6_1_2_1_4_1_4_4_6_1_2_3_3_5_1_4_1_3_1_4_1_5_2_6_6_6_6_6_4_5_5_6_6_4_2_2_2_2_2_2_3_1_3_3_5_1_1_4_6_4_4_6_3_3_3_3_2_5_3_2_2_3_1_5_5_3_2_2_3_3_8_2_2_3_5_5_3_4_4_1_2_1_4_3_1_1_5_6_4_4_10_8_9_3_2_1_4_4_6_4_2_9_2_2_5_6_2_5_2_3_3_2_3_3_3_3_2_3_3_3_1_4_4_6_5_5_5_6_1_1_2_1_3_3_3_6_7_1_4_1_4_3_1_9_2_6_5_5_5_3_7_7_8_1_4_4_3_2_4_2_1_6_4_3_1_6_6_5_5_5_5_7_4_2_1_5_3_2_4_3_4_7_2_2_6_1_2_5_5_5_1_2_8_2_1_5_3_2_6_2_8_2_3_2_1_4_1_3_8_3_2_9_2_5_4_3_3_5_5_3_2_5_5_2_7_1_2_6_6_5_3_1_6_4_6_4_4_3_2_2_3_1_1_1_6_1_1_8_4_3_2_1_1_3_2_2_2_2_8_2_2_4_1_1_1_3_2_2_5_4_1_3_5_3</t>
   </si>
   <si>
-    <t>1_5_1_1_2_4_1_3_5_5_7_7_3_2_2_6_3_2_1_2_3_3_4_4_3_2_1_3_5_3_4_9_3_2_1_7_7_8_3_3_3_10_4_3_2_4_2_1_2_4_4_10_3_1_1_3_4_7_3_3_4_2_6_6_6_1_2_5_1_4_4_5_3_1_1_5_2_1_5_4_1_1_3_3_3_2_2_2_1_2_2_4_4_1_5_2_2_5_5_3_4_2_1_1_1_2_6_6_9_6_4_3_2_1_5_5_1_6_4_3_6_4_3_5_3_3_8_6_6_6_10_9_2_2_2_6_5_3_6_7_6_3_1_3_2_1_3_8_5_2_2_1_5_3_2_9_3_2_3_3_3_3_3_3_6_3_5_7_7_1_1_1_9_5_1_10_4_6_3_1_9_6_2_1_2_2_2_1_6_5_2_4_6_3_4_1_4_3_3_4_7_7_7_1_4_2_6_1_6_2_3_3_3_4_3_2_2_7_7_4_3_1_6_5_5_5_2_6_4_1_8_4_4_6_1_5_2_10_2_5_4_7_3_3_1_1_2_6_3_1_1_2_6_6_2_1_3_1_1_5_3_3_9_1_1_2_6_6_3_3_2_2_1_4_1_8_3_6_6_7_1_3_4_9_5_3_5_1_1_1_3_8_3_6_1_6_6_2_2_4_4_1_3_6_1_1_1_1_1_1_6_4_6_6_6_4_2_3_4_3_6_4_4_2_4_1_5_4_1_5_4_2_3_3_1_2_8_3_4_1_1_5_1_1_2_2_2_2_5_2_6_2_4_5_4_3_6_2_1_1_1_5_2_1_5_5_6_5_2_1_2_2_1_1_3_3_4_6_3_3_5_6_4_1_1_2_5_9_2_3_3_1_2_6_4_3_3_3_3_6_9_2_1_6_2_4_1_1_4_4_2_2_2_5_6_1_1_2_2_1_3_5_4_1_1_1_1_2_3_5_5_3_3_3_1_4_8_2_10_2_1_5_1_5_1_3_7_1_1_6_6_1_6_5_3_5_1_1_1_7_6_6_2_5_4_8_3_5_6_5_7_1_4_4_4_2_1_1_1_1_3_4_6_2_1_3_6_2_5_1_1_1_2_8_6_1_3_2_6_1</t>
-  </si>
-  <si>
-    <t>1_2_2_1_4_4_4_1_1_1_5_3_4_4_1_4_2_1_2_5_1_5_1_4_4_3_2_3_6_1_3_3_4_5_2_2_5_5_5_1_1_2_2_5_5_6_1_2_1_3_6_5_5_5_2_4_1_3_1_5_2_1_2_2_2_1_1_2_3_6_8_10_5_6_2_1_4_4_2_6_3_2_4_5_3_2_6_3_1_9_4_1_4_6_3_5_5_4_1_4_2_5_3_1_2_1_1_2_6_6_5_8_1_4_8_8_8_6_1_3_2_1_4_6_3_2_4_4_3_1_4_6_6_3_2_5_2_4_4_2_2_3_3_10_9_1_6_1_5_1_1_5_3_2_6_1_1_8_8_3_3_2_5_5_1_3_2_10_5_5_1_4_2_6_2_6_1_5_5_1_9_9_9_2_6_1_1_1_2_9_3_2_4_4_1_3_4_6_4_4_6_4_3_2_2_6_2_1_4_5_3_1_8_1_1_3_5_7_3_5_5_6_2_2_4_4_3_1_1_2_2_1_3_2_1_6_2_1_10_7_2_1_6_1_8_7_1_2_2_5_6_3_3_2_2_2_4_3_3_3_3_2_9_3_3_4_5_6_3_5_10_1_4_4_4_2_2_4_1_3_2_3_6_3_4_1_1_4_3_2_10_3_3_7_7_2_1_3_1_1_3_3_3_1_8_1_9_1_3_3_3_3_4_3_3_4_2_3_2_2_7_4_1_6_1_2_6_6_3_4_5_5_3_3_7_1_2_1_4_6_6_4_4_5_1_4_4_2_6_4_6_5_1_2_4_3_4_4_6_2_10_3_4_5_5_5_1_4_1_3_3_8_1_3_3_5_1_5_3_4_2_1_1_2_6_3_7_4_1_4_2_5_3_1_4_6_2_6_3_4_2_4_4_6_5_1_9_4_2_2_4_1_2_5_5_4_3_1_1_1_1_5_1_5_4_1_5_6_8_6_6_3_4_1_1_3_8_1_1_2_4_4_7_8_3_5_1_2_6_4_2_4_4_5_5_1_1_6_3_4_6_2_3_8_6_6_3_5_4_5_1_1_3_10_1_2_5_3_7_4_4_6_1_1_8_8_5_5_6_1_2_8_4_2_1_10_1_2_6_2</t>
-  </si>
-  <si>
-    <t>2_1_3_2_2_4_6_1_6_3_1_8_5_4_3_2_7_7_2_3_4_4_3_2_2_4_3_3_3_3_8_5_4_1_3_4_4_5_3_5_1_1_1_1_2_1_1_4_1_5_5_5_3_8_8_6_1_2_1_2_1_4_1_1_6_2_2_3_2_4_3_7_3_4_7_2_3_3_6_9_9_9_1_1_3_7_7_6_6_3_8_1_1_2_4_4_6_1_1_1_1_1_1_4_5_3_9_1_3_2_4_3_4_4_9_3_2_4_5_4_5_10_3_3_1_5_2_2_2_3_9_5_2_2_6_1_3_8_2_4_4_2_2_2_2_1_6_6_2_5_4_2_3_6_6_5_5_3_5_8_6_4_1_4_2_2_2_6_6_10_1_3_1_1_3_3_4_1_4_1_2_1_3_3_2_4_8_8_5_4_4_1_4_2_1_2_3_8_5_5_9_5_3_3_3_6_4_4_5_6_6_3_5_5_1_3_3_1_1_5_6_2_5_2_4_4_6_5_4_5_7_2_4_3_1_4_3_1_4_4_8_6_4_4_2_2_5_5_5_5_5_3_6_2_2_3_2_2_7_8_3_2_1_1_2_2_2_6_2_2_2_3_1_2_2_4_1_1_1_1_2_1_5_5_2_3_1_8_2_4_4_7_3_3_5_2_2_4_4_1_3_1_2_2_10_10_2_2_2_2_4_3_2_3_8_6_9_4_2_7_7_1_10_2_1_2_2_5_2_5_2_3_4_6_6_6_1_5_5_5_1_2_1_2_3_3_4_1_1_2_4_1_6_2_1_3_2_3_5_3_6_3_1_6_3_3_4_6_2_4_6_7_5_3_8_9_4_8_3_4_4_4_1_6_2_2_2_1_6_8_5_1_4_4_4_3_2_4_3_9_1_1_1_3_8_1_1_1_4_2_1_4_4_5_2_6_5_2_2_2_1_2_4_1_1_9_2_2_2_5_3_3_2_5_5_5_1_3_1_5_5_4_5_5_8_4_3_6_2_7_7_2_5_2_5_5_1_4_7_1_3_1_2_5_1_3_8_4_8_9_6_6_1_2_3_5_2_4_1_1_4_8_5_1_3_5_5_3_1_4_4_3_2_3_9_5_5_3_1_4</t>
-  </si>
-  <si>
-    <t>3_2_5_6_5_3_1_7_6_4_7_7_3_9_4_1_1_1_4_1_3_1_1_6_1_3_1_1_8_3_3_4_2_3_6_3_6_9_7_1_2_5_6_3_6_4_3_1_1_4_6_9_10_10_3_2_10_7_5_1_1_1_1_3_2_4_4_3_4_7_8_3_5_1_2_3_3_4_7_1_5_7_5_5_3_3_7_2_5_3_2_6_1_6_1_5_1_3_3_1_6_5_3_2_5_5_5_5_2_6_3_2_5_6_6_6_6_3_1_7_1_1_1_2_2_6_3_3_1_1_9_3_9_9_1_1_1_1_1_3_3_6_5_6_3_1_1_1_4_4_4_5_4_3_6_3_1_4_2_2_3_6_2_6_2_2_2_5_1_5_4_3_8_8_3_5_1_1_1_6_4_4_7_2_1_5_4_1_4_3_4_1_2_6_2_2_1_1_5_4_10_1_1_5_4_8_5_1_2_3_2_1_4_6_6_2_1_9_1_5_2_2_6_4_1_1_1_1_4_2_1_5_6_2_4_4_7_1_1_5_8_2_2_2_5_1_9_6_6_4_6_7_6_6_1_8_8_1_4_3_4_1_1_3_3_3_2_1_1_1_1_2_5_1_1_1_1_4_2_2_4_5_4_2_1_1_1_1_6_1_1_1_3_1_2_1_6_7_1_5_4_9_3_1_4_5_1_3_2_2_10_4_1_3_4_3_3_5_5_5_5_6_8_3_2_1_5_5_1_4_3_5_2_1_2_5_2_3_7_7_6_3_3_2_5_4_5_3_3_6_2_4_3_3_1_1_1_1_1_2_1_1_9_1_1_1_4_5_5_3_3_2_5_3_9_2_1_3_5_1_1_6_4_4_1_2_4_4_6_3_1_3_6_2_1_1_3_5_1_2_3_3_3_6_5_3_3_1_3_4_1_1_5_2_2_4_4_4_4_5_3_3_2_5_2_1_1_5_10_1_1_5_2_6_2_9_2_3_8_1_4_6_6_6_3_2_5_1_4_8_6_2_2_6_1_6_2_2_2_1_1_3_1_1_2_9_9_3_3_1_1_5_5_5_3_1_3_5_1_4_1_3_1_1_1_5_5_2_3_3_5_4_8_6_2_2_1_1_1_2</t>
+    <t>4_9_4_4_6_7_7_3_6_2_10_9_3_4_2_6_4_9_8_4_2_8_7_5_9_4_10_1_4_4_2_10_4_8_8_8_8_10_4_4_3_5_3_10_6_3_6_10_3_9_9_7_3_8_2_9_2_3_1_1_6_6_2_9_4_8_7_3_1_8_4_1_1_8_8_10_9_5_2_2_3_3_5_5_5_7_4_5_10_10_5_8_3_6_4_10_10_9_5_4_9_9_2_10_6_8_10_3_4_7_9_10_10_2_2_6_6_3_7_7_3_10_1_1_1_9_10_10_10_5_7_8_8_6_2_3_4_4_3_7_7_7_6_8_9_3_6_10_10_10_4_10_8_1_2_6_3_2_1_8_3_7_8_5_10_2_1_7_7_3_9_7_3_10_2_3_10_6_3_9_1_10_10_10_4_2_10_6_9_6_9_4_3_2_5_7_5_8_9_1_7_8_9_10_5_8_8_3_9_5_3_7_4_4_2_1_10_10_7_7_4_8_7_9_9_7_2_8_9_1_8_8_9_7_3_2_10_10_10_8_10_7_3_5_2_5_4_8_3_3_1_1_1_9_7_7_7_5_5_5_1_9_10_6_6_2_1_3_3_7_7_3_1_3_2_2_1_9_4_10_2_6_8_7_8_3_10_4_5_3_8_2_8_8_10_5_7_2_3_1_8_10_2_3_2_10_2_9_10_4_7_4_8_9_8_6_10_2_4_4_6_1_1_7_7_3_8_1_9_9_7_7_8_9_1_8_9_3_7_7_9_9_2_8_2_8_1_8_8_3_3_8_9_1_1_2_9_6_2_7_10_9_9_7_9_7_7_7_5_8_4_5_8_5_4_1_4_2_4_4_7_4_4_4_1_5_4_4_9_2_5_4_4_2_2_2_3_2_6_7_3_3_4_4_5_2_2_7_1_8_10_3_6_6_6_6_4_5_2_9_1_1_5_8_8_7_7_8_9_9_1_3_3_4_9_9_3_3_4_6_7_3_3_1_3_10_10_2_1_1_8_1_8_8_2_4_2_8_4_1_1_7_9_1_3_10_10_7_4_5_2_1_1_4_7_4_3_1_4_10_10_2_2_3_5_5_10_10_5_5_9_4_3_9_9_2_1_1_1_7</t>
+  </si>
+  <si>
+    <t>2_6_5_10_8_2_3_7_6_1_4_3_4_2_9_1_10_8_10_5_5_7_7_2_7_9_10_10_7_3_3_5_4_8_5_9_4_2_4_4_5_4_5_5_10_3_3_3_2_7_9_4_1_10_7_7_3_7_3_7_10_6_2_2_7_3_7_3_5_6_7_7_2_6_6_4_4_1_8_6_2_3_10_9_1_4_6_3_3_3_3_7_7_3_9_2_10_2_3_9_5_9_10_7_7_10_4_5_9_6_4_4_4_9_3_9_2_4_10_9_8_8_2_8_6_5_9_4_6_1_6_5_10_10_1_9_10_3_3_10_1_10_9_2_3_2_10_6_4_6_8_5_3_8_2_6_6_3_9_5_9_5_8_4_10_9_5_10_1_1_7_3_2_2_4_4_5_10_7_8_7_1_4_6_7_10_4_4_1_3_10_3_3_6_9_1_1_1_4_5_10_4_8_6_8_9_1_5_1_6_1_7_4_2_8_6_1_9_2_4_4_7_2_6_7_9_8_8_8_4_6_5_10_10_3_10_10_9_3_4_7_6_10_2_5_7_1_3_4_4_4_10_3_6_3_3_7_6_10_3_10_3_7_7_2_7_10_4_10_6_1_4_6_5_5_2_9_1_5_1_7_10_10_3_2_2_8_3_4_4_2_9_1_8_1_2_5_3_1_7_2_7_1_4_2_10_9_1_1_2_4_9_8_1_5_6_2_2_9_7_7_8_10_1_7_8_4_9_1_3_5_5_5_10_9_3_4_3_3_8_1_9_9_4_8_7_10_2_10_9_5_3_1_6_7_5_5_9_9_7_9_10_5_7_10_9_7_6_6_1_8_5_7_2_1_9_1_4_8_8_9_3_6_10_7_6_10_2_3_7_6_7_10_2_2_3_1_2_1_9_8_9_1_9_5_5_10_7_7_7_2_10_5_2_7_7_4_9_9_2_8_5_10_5_5_6_5_7_2_7_1_7_9_6_7_7_5_4_4_7_1_4_4_8_8_8_3_3_3_7_8_9_7_8_5_9_5_5_1_2_3_5_1_9_1_3_8_3_7_2_9_10_1_7_4_8_4_4_4_6_1_8_9_9_7_8_8_3_1_10_2_1_6_1_10_10_10_1_3_4</t>
+  </si>
+  <si>
+    <t>4_9_6_5_5_7_7_9_9_3_5_2_7_10_9_10_10_10_10_8_10_10_8_8_1_7_7_7_9_9_6_2_3_2_7_1_5_4_10_10_5_7_8_6_7_10_2_2_8_9_7_10_7_5_3_9_5_10_4_10_10_3_3_7_1_3_2_5_3_3_3_5_9_4_5_5_3_2_8_1_10_2_2_10_6_10_6_4_5_5_9_6_9_3_1_2_9_1_2_6_2_7_3_1_7_5_10_2_2_9_8_3_8_8_8_1_4_8_3_10_10_3_3_9_4_7_4_7_7_5_5_8_5_5_1_2_3_3_3_3_8_4_10_1_7_4_10_9_10_4_3_1_4_5_5_1_4_9_10_6_7_2_2_6_4_2_1_7_7_8_7_7_9_6_7_3_1_10_10_4_2_5_3_3_7_6_6_8_8_6_10_8_8_10_9_4_7_8_10_10_9_9_2_6_1_8_3_2_4_2_1_1_6_6_8_6_9_9_8_4_1_10_2_2_6_10_10_6_1_5_4_6_6_9_10_6_5_10_1_1_3_3_2_3_10_10_6_9_10_8_3_1_6_8_8_2_2_2_5_9_1_8_1_1_3_3_1_4_3_3_10_1_1_10_4_4_2_1_1_3_4_6_9_4_4_7_8_9_5_7_3_8_1_2_9_5_8_8_1_2_1_5_7_7_5_5_4_2_4_8_1_1_4_1_1_6_5_4_8_6_7_3_5_1_9_1_10_8_9_3_6_2_10_6_8_6_10_7_7_9_9_6_6_7_7_9_9_3_2_3_1_3_9_8_9_6_4_4_5_5_5_8_4_10_2_2_8_7_7_7_1_5_2_5_6_1_8_9_9_4_7_9_9_1_6_10_10_4_8_5_4_10_2_9_9_8_7_8_7_8_8_6_7_5_6_4_2_10_2_8_8_7_7_10_4_4_7_4_7_3_1_10_3_7_6_3_1_2_8_7_3_8_10_3_6_9_2_3_9_4_9_8_2_4_2_2_7_5_10_10_9_7_3_9_1_1_8_4_1_7_4_3_4_4_10_9_3_3_9_9_9_8_8_8_3_10_8_1_7_7_2_4_6_8_7_7_10_7_10_10_3_2_7_7_10_1_10_9_6_6</t>
+  </si>
+  <si>
+    <t>7_5_6_10_1_2_2_6_6_7_2_3_2_6_1_4_10_10_6_6_4_1_5_1_8_9_9_5_1_4_3_2_9_2_1_1_4_3_4_3_5_2_10_9_6_6_2_1_1_9_3_4_4_1_1_1_1_1_8_4_3_1_8_10_2_4_7_9_6_5_6_8_4_1_1_7_2_4_4_1_6_1_2_2_6_6_3_8_4_8_4_6_4_7_7_1_1_1_3_2_2_5_5_9_2_3_7_7_3_9_1_4_3_2_1_3_7_4_2_2_4_10_7_6_5_2_1_1_6_1_5_7_8_3_1_5_3_4_10_1_2_5_7_8_2_3_5_8_1_4_4_1_7_10_7_3_1_2_5_5_5_7_7_7_4_5_1_5_6_6_4_6_2_8_5_8_4_2_9_8_9_4_8_7_7_1_10_8_9_9_6_1_1_7_1_3_3_7_9_2_2_8_3_7_6_7_4_7_1_5_2_2_4_6_2_1_1_4_3_3_7_2_4_5_1_9_9_2_1_2_3_9_6_4_1_9_6_7_10_2_6_4_8_10_8_3_3_5_6_3_6_10_10_7_4_2_8_2_1_9_1_9_6_4_1_4_1_9_2_2_7_2_2_7_2_8_10_4_1_1_1_3_7_4_5_2_3_2_1_8_7_7_2_2_2_6_5_1_1_4_8_3_4_4_2_2_2_5_5_6_5_5_10_7_4_1_1_4_6_4_1_5_3_6_3_2_4_1_1_2_2_2_2_3_1_4_4_6_7_9_6_8_8_1_7_7_4_9_9_6_3_2_2_5_7_1_4_1_5_9_10_1_1_5_3_6_2_8_8_2_2_2_3_3_3_2_9_9_2_4_5_7_2_7_1_7_4_4_1_10_1_5_5_5_8_3_10_2_1_6_4_4_10_4_3_6_5_6_6_6_7_3_4_2_2_7_4_4_6_2_1_5_4_2_3_6_6_5_3_4_1_8_2_3_8_5_7_6_6_1_3_8_4_4_6_2_4_3_10_10_4_8_6_1_5_8_1_5_1_5_4_2_2_5_5_5_2_3_3_6_3_2_8_1_10_5_8_2_1_6_1_3_3_2_2_1_3_5_1_1_8_8_6_4_4_5_8_8_4_5</t>
   </si>
   <si>
     <t>6_3_3_2_6_6_1_8_4_4_7_5_1_2_9_6_2_8_2_1_1_4_3_5_3_6_8_9_6_4_4_1_6_5_8_3_7_6_1_2_9_3_2_5_8_6_6_4_7_5_4_4_4_3_2_7_1_5_6_6_2_2_8_4_4_2_1_3_6_8_5_4_2_7_3_8_9_4_3_7_1_4_9_2_6_5_3_4_4_3_7_8_3_3_9_9_5_3_6_4_6_1_1_1_8_4_4_8_8_6_7_3_2_2_4_8_5_5_3_7_2_1_9_1_4_9_9_3_6_9_5_5_1_1_4_1_1_2_2_1_3_3_8_1_4_8_6_3_3_1_4_4_1_3_9_6_8_2_5_6_1_2_6_2_3_9_1_4_5_8_5_1_5_7_3_2_7_9_5_5_5_7_7_3_6_7_7_2_1_1_1_6_2_2_2_6_5_3_1_1_1_5_6_3_3_3_5_4_6_6_3_5_2_1_8_3_1_1_7_3_9_8_6_9_9_4_6_4_9_3_7_1_1_8_5_5_1_3_3_4_6_5_5_1_8_5_1_3_3_5_2_3_1_4_1_7_5_8_1_5_6_2_5_6_8_8_8_9_5_8_8_4_2_4_2_2_2_3_1_5_3_9_5_5_5_7_4_9_9_1_8_6_1_1_4_7_3_2_2_9_9_3_6_6_3_6_4_2_2_4_2_9_6_7_5_3_1_8_9_2_8_2_1_3_9_5_6_9_5_9_4_2_4_4_3_9_1_1_7_7_1_4_6_6_3_7_7_8_7_4_6_4_5_7_8_4_4_3_2_2_4_5_6_1_3_1_1_5_6_1_1_1_6_3_4_2_7_4_1_7_5_6_2_7_1_1_4_8_4_2_4_5_4_3_8_2_2_5_6_4_7_9_6_4_2_4_4_4_4_4_5_3_1_1_4_9_2_3_2_5_6_3_2_2_8_3_5_2_9_1_1_2_8_3_6_3_9_1_4_1_2_8_3_5_5_5_6_9_2_6_5_1_1_8_5_4_2_2_9_6_5_5_2_4_1_9_9_9_1_1_1_6_7_7_2_1_4_7_8_6_8_9_8_4_4_3_5_5_5_4_2_9_4_1_1_2_8_2_3_9</t>
@@ -7127,7 +7127,7 @@
     </row>
     <row r="158" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A158" s="6">
-        <f t="shared" ref="A158:A167" si="7">C158*10+D158</f>
+        <f t="shared" ref="A158:A172" si="7">C158*10+D158</f>
         <v>20200021</v>
       </c>
       <c r="B158" s="14">
@@ -7447,7 +7447,7 @@
     </row>
     <row r="168" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A168" s="6">
-        <f>C168*10+D168</f>
+        <f t="shared" si="7"/>
         <v>20380011</v>
       </c>
       <c r="B168" s="14">
@@ -7479,11 +7479,11 @@
     </row>
     <row r="169" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A169" s="6">
-        <f>C169*10+D169</f>
+        <f t="shared" si="7"/>
         <v>20380012</v>
       </c>
       <c r="B169" s="14">
-        <v>103801</v>
+        <v>103800</v>
       </c>
       <c r="C169" s="33">
         <v>2038001</v>
@@ -7511,11 +7511,11 @@
     </row>
     <row r="170" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A170" s="6">
-        <f>C170*10+D170</f>
+        <f t="shared" si="7"/>
         <v>20380013</v>
       </c>
       <c r="B170" s="14">
-        <v>103802</v>
+        <v>103800</v>
       </c>
       <c r="C170" s="33">
         <v>2038001</v>
@@ -7543,11 +7543,11 @@
     </row>
     <row r="171" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A171" s="6">
-        <f>C171*10+D171</f>
+        <f t="shared" si="7"/>
         <v>20380014</v>
       </c>
       <c r="B171" s="14">
-        <v>103803</v>
+        <v>103800</v>
       </c>
       <c r="C171" s="33">
         <v>2038001</v>
@@ -7575,11 +7575,11 @@
     </row>
     <row r="172" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A172" s="6">
-        <f>C172*10+D172</f>
+        <f t="shared" si="7"/>
         <v>20380015</v>
       </c>
       <c r="B172" s="14">
-        <v>103804</v>
+        <v>103800</v>
       </c>
       <c r="C172" s="33">
         <v>2038001</v>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="251">
   <si>
     <t>id</t>
   </si>
@@ -614,6 +614,225 @@
   </si>
   <si>
     <t>4_4_4_4_4_4_1_1_1_1_5_5_5_4_4_4_1_1_1_1_1_1_3_3_3_3_1_1_1_1_1_1_1_1_2_2_2_2_2_2_2_2_4_4_4_4_4_4_2_2_2_2_2_2_1_1_1_1_1_1_1_1_1_5_5_5_5_5_6_6_6_6_6_3_3_3_3_3_3_2_2_2_2_2_2_3_3_3_3_3_3_3_3_3_3_4_4_4_4_4_4_4_1_1_1_1_1_1_1_1_2_2_2_2_2_2_2_2_2_3_3_3_3_3_3_2_2_2_2_5_5_5_5_5_5_1_1_1_1_1_1_1_3_3_3_3_3_1_1_1_1_1_6_6_6_6_4_4_4_4_4_1_1_1_5_5_5_3_3_1_1_1_4_4_4_4_4_4_1_1_1_1_1_4_4_4_4_4_1_1_1_1_1_2_2_2_2_2_2_2_1_1_1_1_1_1_3_3_3_3_3_3_3_3_3_2_2_2_2_2_2_2_2_2_4_4_4_4_5_5_5_6_6_6_6_6_3_3_3_3_3_2_2_2_2_2_2_2_2_1_1_1_1_1_1_2_2_2_2_2_3_3_3_3_1_1_1_1_1_1_1_2_2_2_2_2_2_2_2_2_6_6_6_6_6_6_4_4_4_4_4_4_4_5_5_5_5_5_5_2_2_4_4_4_2_2_1_1_1_1_1_1_3_3_3_3_2_2_2_2_2_1_1_1_1_1_1_1_1_4_4_4_4_4_4_5_5_2_5_5_5_5_1_1_1_1_1_1_2_2_2_2_2_2_4_4_2_2_2_2_2_2_2_2_3_3_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_5_1_1_1_1_1_1_1_4_4_4_4_4_4_2_2_2_2_2_3_3_3_6_6_6_6_1_1_1_6_6_6_1_1_1_2_2_2_2_2_2_2_2_4_4_4_4_4_4_5_5_5_5_2_2_2_2_2_2_2_3_3_3_3_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_1_1_1_1_1_2_2_2_2_2_2_2_2_4_4_4_4_4_2_2_2_2_2_2_2_2_2_3_3_3_5_5_5_3_3_3_3</t>
+  </si>
+  <si>
+    <t>6_6_6_6_6</t>
+  </si>
+  <si>
+    <t>4_7_5_11_5_4_6_2_2_2_1_10_7_7_3_3_4_4_4_3_1_8_4_1_1_7_4_6_5_2_11_5_9_3_9_4_7_2_11_4_4_4_4_2_3_8_8_2_7_2_3_7_5_1_10_1_9_8_11_5_5_3_1_9_9_9_1_2_9_3_7_3_1_10_3_6_4_7_4_11_2_2_6_4_9_3_6_2_5_2_4_6_10_7_9_9_1_4_4_4_1_9_8_10_1_2_2_5_9_1_4_4_4_3_1_2_1_3_6_3_6_1_10_7_6_10_11_5_3_8_2_2_6_1_8_4_6_7_3_5_2_2_6_3_3_1_1_2_2_9_1_5_7_2_6_6_2_1_3_9_4_8_10_5_9_1_7_7_10_10_7_2_2_2_3_9_4_3_3_8_8_4_2_2_4_6_7_4_1_2_5_8_3_1_5_7_3_4_1_4_10_6_10_1_2_7_5_4_5_1_5_8_4_8_1_1_5_8_6_3_1_10_5_11_4_11_9_11_3_2_6_6_5_7_7_3_3_3_2_4_4_9_9_7_4_4_3_7_4_4_10_2_7_7_5_2_4_8_8_1_4_4_9_9_1_1_4_2_3_8_1_7_7_9_3_3_9_11_1_4_9_3_6_6_6_4_5_2_7_2_2_2_4_2_10_11_3_5_5_2_2_9_1_4_2_2_6_6_6_2_5_9_10_9_9_6_6_4_3_3_1_10_6_1_6_7_10_8_9_9_5_8_6_9_5_6_9_3_8_1_6_1_10_4_2_1_1_3_5_9_1_1_1_1_2_5_3_5_3_3_3_7_2_3_3_9_9_9_4_7_9_6_5_11_1_5_3_6_1_7_1_3_2_2_11_3_3_9_5_5_5_8_3_1_9_3_3_2_1_5_1_1_2_6_2_1_3_1_4_5_3_2_9_6_6_2_1_8_7_3_7_1_5_1_1_7_8_7_8_9_1_2_5_4_4_3_2_8_10_4_5_5_6_8_4_6_4_4_2_6_6_3_5_3_4_1_2_2_5_2_10_10_1_6_5_2_11_2_5_2_1_10_10_6_5_10_7_4_10_3_10_10_1_3_2_10_9_9_4_6_7_2_2_3_5_5_3_4_5_2</t>
+  </si>
+  <si>
+    <t>5_7_4_8_4_11_3_2_5_3_2_4_3_9_4_8_1_1_4_7_11_4_12_3_6_11_5_1_5_9_7_13_5_2_5_2_8_10_6_3_3_4_3_2_10_4_6_6_6_4_2_3_3_8_8_6_3_4_3_1_4_8_5_7_4_8_8_4_1_1_7_3_2_2_7_1_4_2_6_9_6_2_4_3_6_7_3_11_3_5_7_6_12_8_2_9_4_2_7_2_5_8_1_4_11_6_1_8_6_6_6_7_3_3_11_6_10_7_4_2_3_7_13_6_3_3_11_7_9_6_11_4_1_3_4_1_6_11_5_12_2_3_4_3_11_8_2_2_1_10_8_10_7_3_2_2_1_8_4_7_11_5_13_5_1_5_6_7_1_11_6_4_6_6_3_8_10_5_5_12_4_2_8_9_6_3_4_11_8_3_7_1_11_8_3_12_6_2_6_9_6_3_3_8_4_3_6_4_9_1_6_3_6_6_6_2_8_5_4_13_8_12_1_2_8_3_4_1_5_1_10_6_12_1_1_2_13_7_6_2_3_5_3_10_5_1_12_4_3_11_8_3_1_8_3_5_8_2_2_2_3_5_9_6_3_7_11_7_9_8_8_9_6_4_1_6_10_7_6_11_7_13_8_8_2_8_8_4_4_1_5_6_3_8_5_7_11_6_1_2_10_6_1_4_4_10_7_3_3_11_5_5_7_1_4_6_6_3_11_8_4_13_5_1_3_2_4_4_6_4_10_7_11_7_2_3_1_2_2_9_13_4_3_6_10_6_10_6_2_3_6_5_11_4_3_10_7_6_12_6_2_2_8_7_10_4_2_2_7_4_6_1_1_6_1_3_3_4_8_1_7_4_8_8_10_6_7_7_2_1_10_8_7_9_1_12_7_2_3_8_2_2_6_10_7_4_3_3_2_6_9_1_4_10_4_4_2_1_1_1_4_7_4_2_7_1_11_7_2_6_2_5_8_3_1_8_5_5_9_2_1_5_9_3_10_4_6_7_6_9_3_4_1_10_7_1_6_3_10_8_3_4_4_8_3_2_11_6_3_7_2_2_5_1_4_1_3_1_2_1_3_3_5_6_2_2_5_2_1_4_6_2_4_3_9_11_6_3_10_8</t>
+  </si>
+  <si>
+    <t>7_7_7_7_7</t>
+  </si>
+  <si>
+    <t>5_5_5_5_1_1_1_2_5_5_4_8_2_2_4_4_1_6_10_2_1_3_7_1_3_1_1_5_9_4_7_10_3_8_4_5_11_4_2_4_9_3_6_10_2_10_8_4_3_5_3_6_6_3_2_1_5_9_9_2_5_5_4_3_7_1_8_8_5_3_5_4_1_1_2_6_2_2_2_4_6_8_11_4_4_7_1_6_3_3_3_1_1_2_2_4_5_10_2_1_3_3_3_1_7_6_2_2_7_2_5_1_1_5_4_1_9_4_4_3_3_1_6_4_4_1_3_11_9_1_2_5_3_4_5_2_2_1_1_11_2_7_2_6_6_2_1_11_5_5_5_6_2_9_10_6_3_2_2_1_1_10_4_1_8_6_6_9_8_10_1_8_1_3_4_4_6_8_4_1_2_3_2_7_2_10_9_1_4_3_2_2_2_3_1_4_3_5_2_1_1_7_8_10_6_5_3_7_6_7_5_1_1_3_9_2_7_2_3_6_5_9_1_1_4_2_2_3_4_3_3_2_1_1_4_4_4_6_4_4_1_5_1_6_2_1_5_5_8_8_6_4_1_10_10_6_6_2_2_5_5_10_8_2_8_9_4_7_11_6_6_2_8_6_1_2_1_2_4_4_5_5_5_6_6_2_3_3_9_7_3_5_8_6_10_2_3_5_2_6_8_2_5_2_5_10_4_6_2_3_11_3_1_9_1_3_4_2_4_1_7_4_6_9_1_9_5_8_2_4_1_1_6_6_2_7_7_4_8_3_3_1_5_1_6_3_3_1_9_9_4_2_4_4_4_4_2_2_1_7_2_2_3_1_6_9_5_6_8_4_4_4_5_5_5_5_7_7_10_11_7_7_4_4_1_9_3_3_8_11_4_7_4_2_4_2_2_1_3_7_2_2_4_4_3_9_5_4_2_2_10_4_8_4_2_4_2_6_1_8_8_1_1_6_3_7_3_7_1_5_1_9_10_5_10_5_5_3_1_2_2_9_1_1_4_7_3_1_1_2_3_3_2_2_10_5_2_3_2_2_2_1_1_3_1_2_2_11_6_4_2_5_5_2_5_11_1_2_1_3_2_2_11_2_2_9_5_1_6_8_8_3_4_4_2_11_5_5_7_5</t>
+  </si>
+  <si>
+    <t>7_12_8_6_3_7_10_8_6_10_6_5_7_2_8_8_5_10_2_2_11_3_6_5_4_3_4_5_1_6_13_6_7_8_10_4_6_5_2_7_2_11_8_4_12_8_4_6_6_13_3_3_6_4_5_5_6_9_1_2_8_2_6_2_5_2_2_5_6_6_11_8_13_4_4_9_5_3_6_10_5_2_11_8_6_2_6_6_4_1_7_4_2_8_13_4_7_1_2_3_1_4_9_7_6_1_5_10_7_11_3_1_1_7_5_8_1_4_8_1_2_2_11_3_8_6_2_4_2_3_2_11_4_3_8_2_6_2_8_7_1_7_4_10_8_6_4_7_11_4_13_8_5_3_9_3_8_2_2_7_3_3_8_1_3_3_3_7_7_1_2_6_9_5_3_6_5_12_8_1_13_3_1_5_3_4_3_2_4_5_4_5_2_11_2_11_6_3_4_5_8_4_6_8_6_5_2_7_4_2_1_4_1_2_4_2_4_6_12_6_2_11_2_13_8_2_2_1_8_6_1_11_6_1_2_6_4_3_10_7_3_1_7_10_4_2_5_5_2_3_4_13_8_8_3_3_2_11_7_6_2_6_5_4_11_4_1_10_6_3_6_5_8_1_2_12_1_1_3_13_7_1_1_10_8_10_8_6_7_11_7_5_4_5_4_6_1_8_6_9_2_4_13_1_1_4_3_12_8_8_10_2_3_11_5_3_1_1_11_6_3_1_1_8_12_8_3_3_5_3_6_5_11_2_4_2_1_2_7_5_2_6_6_3_1_13_5_7_6_10_8_5_1_8_4_7_8_1_10_2_4_1_13_8_5_2_5_1_12_8_9_1_6_11_8_7_4_4_5_7_3_9_3_4_6_1_5_3_4_1_2_9_8_13_5_4_3_9_1_7_1_1_7_1_4_13_6_1_8_2_1_4_4_6_2_9_2_4_7_10_8_2_11_6_5_10_7_8_6_3_2_8_1_2_4_3_8_2_2_8_7_7_4_6_3_6_6_1_2_12_7_2_4_3_4_2_4_13_4_13_7_7_10_6_2_13_5_4_9_6_7_1_12_7_8_3_3_7_4_9_4_1_5_4_7_9_3_12_5_7_11_8_7_10_3_8_10_8_13_2</t>
+  </si>
+  <si>
+    <t>8_8_8_8_8</t>
+  </si>
+  <si>
+    <t>5_1_2_2_2_6_6_6_10_4_4_4_5_5_4_4_4_3_3_10_6_1_4_2_2_2_10_9_6_8_3_4_1_5_5_9_1_2_2_1_2_7_10_3_4_5_2_4_4_4_6_6_11_6_1_2_5_8_8_2_2_6_10_6_3_2_2_6_8_4_4_6_1_7_7_7_10_10_6_4_4_4_5_11_10_1_1_8_8_5_3_4_6_9_1_4_4_3_3_9_9_4_3_1_6_5_7_3_2_2_2_2_8_3_7_3_8_7_2_2_2_8_8_10_10_6_6_6_10_7_5_6_2_7_5_1_2_2_11_2_4_4_2_10_3_9_4_3_10_7_8_3_5_1_8_10_10_10_2_5_3_3_1_1_4_4_7_2_3_7_2_2_2_2_10_5_9_8_6_2_3_1_11_4_5_5_7_7_7_3_3_5_8_8_8_7_5_2_5_5_4_8_7_4_1_5_2_4_2_5_8_8_4_1_4_4_10_1_3_2_1_9_2_1_2_2_7_8_5_10_6_4_3_10_4_10_2_3_1_4_8_1_6_3_2_2_2_7_1_3_3_8_11_5_3_2_8_4_5_3_2_1_1_4_5_6_6_3_5_5_10_4_3_9_6_6_6_6_11_7_5_5_9_9_1_1_2_1_6_8_8_10_4_7_11_11_4_2_6_8_2_9_1_2_1_7_1_4_6_1_1_1_10_6_9_8_6_10_6_1_1_5_3_3_6_8_8_1_5_7_8_2_10_6_3_1_4_6_6_6_3_3_9_4_6_1_2_7_8_1_4_4_4_3_7_8_8_8_1_3_9_1_6_8_6_8_8_2_2_3_5_9_10_1_6_8_1_3_1_6_6_3_6_4_7_2_2_4_1_5_5_2_2_10_1_5_8_7_4_2_2_7_6_7_3_10_4_6_1_5_3_3_4_6_7_2_4_3_6_6_6_3_2_1_4_6_5_5_8_9_4_4_5_3_2_5_5_4_5_8_1_6_4_3_9_7_7_3_9_1_8_4_5_4_4_11_3_6_7_3_11_8_9_3_8_5_4_7_1_6_5_2_8_6_4_8_1_2_4_6_1_5_7_6_2_2_7_1_9_3_3_4_6_6_8_8_2_5_3_6</t>
+  </si>
+  <si>
+    <t>8_2_11_2_9_3_4_8_13_5_3_11_6_8_4_1_6_2_6_2_8_8_7_5_1_9_4_8_9_4_3_11_5_1_11_6_7_9_9_4_2_1_1_1_9_3_3_12_7_6_6_3_3_2_6_1_6_7_7_7_9_4_6_5_2_9_13_5_3_2_2_1_1_4_5_7_7_7_6_10_6_8_7_4_7_7_10_8_1_4_6_12_6_1_4_5_5_1_3_1_2_1_8_8_2_2_8_2_8_3_8_1_1_2_5_6_1_10_7_6_4_10_3_8_3_2_13_7_11_8_1_6_2_5_8_5_7_4_3_2_3_4_11_8_3_11_3_1_13_4_6_4_2_1_7_8_4_6_8_8_9_5_5_3_7_2_2_2_1_8_6_11_7_2_4_2_3_2_2_10_4_2_2_1_4_7_2_8_5_4_10_7_2_2_11_8_2_8_3_4_8_3_3_3_1_2_7_3_9_13_6_13_2_6_1_11_3_9_13_7_11_6_1_6_3_4_12_5_10_7_1_3_2_8_6_2_11_4_1_7_1_5_6_8_8_1_1_9_3_3_9_8_2_4_2_2_4_1_6_12_7_8_13_8_1_7_1_2_13_4_3_2_4_10_2_5_10_8_13_4_4_4_1_8_8_3_4_2_8_2_13_8_3_4_2_5_9_4_8_8_1_9_2_2_4_3_6_6_4_8_4_3_11_6_3_13_8_1_4_7_8_2_6_4_11_7_9_1_8_6_8_13_6_8_2_5_5_4_8_4_4_13_4_4_3_3_1_1_5_2_1_1_6_8_4_11_5_4_7_5_4_5_3_10_7_2_7_6_3_3_3_8_4_11_2_10_3_7_5_6_1_3_2_3_6_8_11_5_4_5_5_2_3_4_8_11_5_7_8_6_4_11_3_7_5_2_4_3_5_2_4_2_2_9_10_5_2_6_1_2_2_2_3_2_7_2_1_1_5_2_5_3_1_4_8_6_2_1_9_4_8_1_5_6_5_3_4_10_7_6_3_2_5_1_9_5_6_4_9_3_2_6_2_2_7_5_2_6_3_8_11_1_1_11_3_7_5_9_13_5_1_2_2_11_8_10_2_2_7_6_1_5_7_9_4_2_12_6_4_13</t>
+  </si>
+  <si>
+    <t>9_9_9_9_9</t>
+  </si>
+  <si>
+    <t>2_5_1_2_4_4_8_4_3_2_4_4_8_8_8_11_2_3_1_2_2_1_11_1_3_7_8_6_10_10_4_4_1_6_3_1_1_1_5_1_3_2_4_5_4_8_7_1_4_2_1_4_4_9_6_9_2_3_3_8_8_6_1_1_6_9_8_3_4_4_4_3_2_3_1_9_4_1_8_3_10_10_10_6_3_5_1_4_4_4_1_11_4_1_3_11_4_9_3_5_3_1_3_1_8_8_3_8_7_11_11_1_8_3_1_1_1_4_11_5_2_1_1_10_2_1_2_1_3_3_3_4_6_6_5_1_7_2_1_8_7_7_1_3_8_1_7_6_2_8_1_4_5_7_5_4_1_8_8_7_1_2_3_2_1_2_1_7_10_2_3_2_8_8_1_3_3_10_10_3_9_1_5_11_4_4_6_6_1_5_2_6_7_9_3_5_5_5_5_4_3_11_5_4_8_1_2_7_7_8_6_6_3_2_2_1_6_6_6_7_3_2_2_1_8_2_3_4_11_8_10_10_2_5_8_4_2_5_8_2_6_3_7_7_8_4_6_4_1_2_2_2_8_4_4_6_6_1_1_5_6_2_3_1_1_2_5_6_5_9_10_10_7_5_6_1_8_2_9_9_2_4_3_1_3_2_4_5_4_5_7_7_2_7_5_7_7_10_5_3_2_2_9_10_3_3_1_4_6_11_2_8_8_3_2_4_5_3_1_8_1_1_9_5_4_8_10_10_4_6_6_5_1_1_8_2_8_11_8_2_1_5_6_6_4_4_4_6_2_1_7_7_6_4_6_4_2_10_5_5_1_8_4_4_4_4_4_4_8_7_7_9_2_5_6_7_3_10_3_3_2_6_4_6_1_5_8_10_9_4_5_1_6_2_5_9_10_9_1_10_1_1_1_3_4_3_4_4_6_2_2_2_5_3_2_8_9_3_6_6_5_4_3_3_3_3_2_1_7_8_3_2_4_6_5_9_6_8_2_2_7_8_10_2_11_3_11_9_9_6_5_1_3_4_2_8_4_4_2_2_6_3_7_4_1_2_4_9_2_8_2_5_6_2_1_5_9_5_10_4_2_5_3_3_2_4_4_4_10_1_1_1_10_6_6_6_4_3_8_3</t>
+  </si>
+  <si>
+    <t>2_5_3_6_5_2_10_7_2_6_12_3_1_8_9_4_1_2_3_6_12_8_3_1_6_5_6_3_5_5_2_1_11_8_5_4_4_3_5_3_2_4_3_1_2_7_1_2_13_5_5_5_2_4_9_1_10_7_4_9_9_3_3_2_8_7_3_2_3_4_5_3_1_1_1_11_2_7_7_8_4_4_3_1_9_1_4_4_3_6_1_3_10_6_7_9_5_1_1_10_8_3_1_7_7_1_2_9_5_3_5_8_2_6_8_2_2_13_6_10_7_9_2_1_6_7_1_7_10_3_10_7_1_6_10_2_1_6_2_11_1_8_2_9_4_8_5_6_1_4_13_5_4_6_4_9_11_2_2_9_9_6_4_9_2_10_8_9_13_7_3_2_3_9_9_7_10_7_3_7_4_10_8_4_4_6_2_6_8_10_4_8_1_3_7_8_3_10_7_6_5_9_1_1_10_5_1_5_8_7_1_3_4_1_4_5_10_8_2_11_6_1_13_4_6_9_13_8_2_3_11_8_13_6_2_2_8_3_7_8_6_4_6_1_13_5_4_5_12_8_7_6_13_2_10_6_9_11_7_1_4_3_4_4_9_3_6_4_2_2_1_3_2_1_3_5_5_3_7_6_2_2_7_10_5_1_1_2_1_5_6_8_10_7_4_3_7_1_3_11_2_2_8_6_1_11_8_6_1_4_5_5_4_7_2_13_1_8_7_5_3_4_11_1_8_6_4_6_4_5_10_8_1_7_1_1_1_2_10_1_1_10_7_1_2_1_1_7_13_2_9_4_4_3_4_12_8_8_6_2_6_6_13_4_4_1_5_10_5_4_8_1_2_9_7_6_13_7_1_1_2_4_1_2_4_10_5_3_6_6_2_2_5_5_2_4_5_2_3_1_2_3_1_6_10_6_1_1_4_5_12_4_5_5_2_8_7_10_5_1_9_5_5_3_8_5_2_1_10_5_11_8_5_4_4_4_8_1_12_6_1_4_2_7_1_4_1_8_1_1_8_1_11_7_3_6_8_3_10_2_4_1_3_1_1_4_7_7_10_8_1_6_3_4_1_1_8_4_6_6_9_2_4_9_7_2_3_3_10_8_8_1_1_4_3_1_3_2_3_1</t>
+  </si>
+  <si>
+    <t>10_10_10_10_10</t>
+  </si>
+  <si>
+    <t>2_4_7_3_11_2_5_2_5_2_8_3_6_4_7_6_4_1_8_10_8_3_4_1_8_2_5_1_10_2_6_2_1_3_5_8_4_4_4_4_3_8_4_3_3_3_3_5_4_1_10_7_6_2_1_9_2_2_5_8_1_2_4_3_10_1_4_2_10_1_6_1_6_1_9_5_3_10_9_2_5_5_2_3_1_1_1_4_2_2_5_1_2_4_4_4_5_11_6_6_7_9_3_2_8_2_1_4_10_2_4_6_3_3_1_3_9_10_1_11_5_2_6_9_1_2_2_2_1_6_4_3_3_5_3_3_4_5_7_2_3_3_4_2_2_1_2_7_7_7_1_5_2_6_5_5_5_1_8_5_2_3_1_7_6_3_4_4_3_5_5_5_10_5_5_1_3_2_7_8_8_1_3_5_9_11_11_5_5_1_1_6_9_3_2_8_7_1_2_7_11_2_8_6_5_7_4_6_8_5_5_3_6_2_2_2_11_6_4_8_1_5_5_3_1_7_2_8_6_8_9_6_8_1_1_8_5_1_1_1_6_3_10_1_3_3_6_4_1_1_6_2_8_1_5_10_3_5_8_7_2_3_9_1_9_5_3_3_5_1_5_8_8_8_4_4_2_4_8_3_5_1_7_1_1_1_6_6_5_2_1_9_4_8_5_1_1_2_2_10_8_6_6_3_3_7_8_6_7_7_2_1_1_6_10_4_2_2_7_5_5_5_2_1_5_5_8_8_7_5_2_6_8_6_3_4_1_3_1_5_2_8_8_1_3_4_9_8_6_6_6_4_4_3_1_1_4_3_1_3_10_3_3_3_4_1_3_6_10_2_9_9_1_6_5_5_5_5_5_5_5_8_5_5_9_3_3_4_11_2_9_2_11_11_2_8_5_8_8_4_7_2_2_8_4_5_7_3_4_4_1_10_5_3_3_11_1_6_4_10_4_5_7_3_3_5_3_5_2_6_1_3_2_4_9_4_5_7_7_2_2_1_6_6_4_2_4_10_5_6_1_11_4_2_2_5_2_1_10_7_7_3_3_1_3_1_4_5_5_10_2_1_2_9_7_10_9_11_3_3_3_5_4_5_10_10_2_1_3_11_1_9_8_11_3_3_4_10_6_6</t>
+  </si>
+  <si>
+    <t>4_8_1_11_8_8_3_8_1_8_3_2_3_3_4_12_5_12_5_3_8_7_2_8_1_7_8_2_4_5_11_4_2_5_10_5_6_5_8_4_6_9_7_6_7_2_5_8_2_2_1_3_6_3_12_1_10_4_1_4_9_13_3_6_8_1_11_6_3_4_7_5_2_4_3_13_4_1_1_13_4_5_13_2_6_9_3_5_4_7_2_10_7_6_3_12_7_6_1_1_4_2_6_11_2_5_3_2_6_5_1_5_1_9_3_1_2_4_5_11_4_5_11_3_3_7_1_1_4_2_4_4_5_1_3_13_6_9_3_2_6_5_3_4_8_13_2_5_8_8_9_2_4_5_4_1_6_9_5_4_2_4_1_11_7_5_11_7_3_3_8_13_8_5_4_10_8_4_7_7_6_3_8_7_1_7_1_7_12_6_8_3_5_1_5_7_1_7_5_1_6_2_3_9_3_5_2_1_6_1_4_5_7_10_6_6_11_2_8_3_4_4_13_7_5_11_3_5_5_2_5_1_1_9_1_10_5_2_1_4_1_2_3_1_1_1_2_6_10_7_6_3_6_3_4_1_6_10_6_4_4_2_10_7_6_2_11_2_7_9_6_2_2_3_3_2_2_6_2_9_2_11_7_6_5_4_6_2_3_10_7_11_7_2_12_6_8_3_3_5_2_2_8_3_5_4_9_2_2_2_2_8_2_6_4_4_6_6_9_7_9_7_6_2_11_4_1_7_4_5_5_1_4_5_2_3_10_5_4_7_2_6_8_7_2_3_5_13_8_7_1_11_8_6_5_3_2_5_5_12_8_6_1_5_3_3_8_2_7_2_4_6_12_7_3_4_5_7_2_3_1_6_5_1_12_6_4_1_1_2_1_10_6_3_5_10_8_11_8_2_12_7_7_2_7_6_1_1_3_4_10_4_8_8_12_4_2_4_1_1_1_3_1_5_5_3_3_9_2_3_8_8_3_1_8_2_2_5_9_1_1_4_7_6_12_6_2_5_2_6_1_8_4_5_4_2_3_3_3_5_2_1_13_3_2_8_5_8_8_7_11_8_9_4_1_11_8_9_9_2_11_6_6_13_5_11_7_11_4_1_11_6_6_7_4_9_2_1_3_2</t>
+  </si>
+  <si>
+    <t>11_11_11_11_11</t>
+  </si>
+  <si>
+    <t>8_1_1_8_4_7_8_5_5_3_7_6_6_6_7_10_3_8_1_3_5_10_8_1_2_8_7_5_5_2_2_5_4_11_3_4_3_8_8_4_4_7_3_2_5_1_3_5_11_3_4_1_6_3_9_5_5_10_5_1_4_1_9_9_3_2_1_1_6_6_6_8_3_6_7_9_7_1_8_7_8_2_2_4_1_8_2_2_2_1_8_10_4_8_2_1_7_7_2_1_10_2_1_8_1_2_2_1_3_3_2_10_2_7_6_2_2_1_4_8_2_2_2_2_2_2_1_3_6_6_2_10_5_10_6_8_8_1_3_3_8_8_5_10_2_6_7_7_6_4_7_4_5_7_4_6_6_2_6_4_3_3_3_6_3_7_6_2_7_7_3_4_7_9_4_1_5_5_2_7_4_2_8_5_1_9_4_1_4_8_10_7_2_2_5_6_3_3_11_10_7_2_6_2_5_4_1_9_3_3_2_8_3_3_4_4_2_4_9_6_7_8_3_4_1_3_1_9_8_2_2_4_7_2_8_1_1_9_2_3_3_3_3_1_4_1_1_6_3_9_3_3_4_6_5_1_3_1_2_3_2_1_1_1_9_5_2_2_3_2_5_6_7_1_5_4_3_7_4_2_2_1_8_6_8_7_1_4_9_10_11_2_4_4_3_9_2_1_1_6_10_6_1_8_1_1_7_7_11_9_9_1_2_8_4_3_3_3_5_9_4_2_2_2_9_3_4_1_3_1_6_9_4_2_1_8_8_7_2_4_2_8_3_8_2_5_5_2_4_6_8_3_4_8_3_1_3_3_10_5_4_6_1_1_1_2_9_3_4_10_8_8_6_1_8_8_4_1_1_4_5_4_4_1_8_10_4_8_7_4_9_3_8_8_7_10_1_9_4_1_8_7_8_8_6_2_1_1_8_9_11_1_1_5_3_10_6_1_6_8_8_2_2_2_4_1_7_7_10_10_10_5_5_3_2_8_3_3_1_8_8_1_1_7_10_1_8_1_10_9_1_5_2_10_5_9_4_2_2_2_6_7_3_6_4_1_1_6_2_2_8_2_2_6_1_10_9_2_7_4_4_4_5_2_2_2_2_7_7_7_2_8_8_8_2_2_8_9_2_3</t>
+  </si>
+  <si>
+    <t>4_3_13_6_5_4_3_1_4_5_3_4_11_7_3_4_7_8_6_4_3_2_4_7_2_2_1_11_2_11_6_13_8_10_7_2_3_4_8_4_5_4_4_1_1_4_3_7_5_4_5_6_8_1_5_11_5_8_3_4_5_8_11_5_7_4_11_6_5_11_4_10_8_10_6_5_11_6_8_4_11_6_1_4_9_3_5_1_2_8_3_9_2_3_1_7_12_6_7_1_7_8_3_4_1_13_7_5_4_2_11_7_7_2_1_12_6_3_1_9_4_3_10_2_6_7_11_5_6_2_6_4_10_4_6_2_3_11_6_8_8_13_2_6_4_7_3_4_1_7_3_4_6_1_3_11_7_5_6_11_7_4_10_4_4_9_2_4_6_10_7_2_2_7_3_1_8_5_2_9_12_2_4_2_8_2_8_2_12_8_2_1_3_4_7_4_2_9_4_6_3_1_11_5_1_1_11_8_6_3_2_8_10_1_2_3_4_5_8_4_3_7_5_4_6_5_11_8_3_1_8_6_5_5_1_6_11_5_8_1_3_6_9_9_2_6_1_9_7_4_2_8_6_10_8_2_7_3_3_4_7_8_7_1_6_4_5_2_5_4_2_5_3_6_6_4_3_6_7_5_1_5_2_7_8_7_12_7_2_9_10_3_9_9_1_2_10_5_6_3_6_6_13_4_6_7_8_10_2_9_1_4_2_3_4_8_1_7_5_3_1_7_7_1_9_4_7_1_4_10_7_5_12_8_1_2_4_1_7_5_1_5_2_5_6_12_3_7_5_5_1_5_1_3_2_9_4_8_2_7_4_6_4_9_1_13_7_4_3_3_3_10_8_4_1_12_8_12_6_10_7_11_5_13_6_8_13_8_10_8_1_8_5_3_6_3_3_3_8_6_11_8_11_8_3_5_5_6_2_11_8_9_2_4_9_6_6_1_1_13_8_4_10_7_5_7_8_10_8_2_4_11_8_12_5_5_1_6_4_4_8_1_9_3_3_5_6_7_3_1_3_4_6_7_13_5_5_6_13_3_8_10_6_4_7_7_4_3_4_4_5_10_1_10_2_10_8_4_4_2_6_8_3_1_3_5_5_2_13_5_3_4_3_2_6_6_3_3_1_4</t>
+  </si>
+  <si>
+    <t>16_16_16_16_16</t>
+  </si>
+  <si>
+    <t>16_10_3_13_13_13_10_10_4_20_20_12_12_2_2_2_11_11_2_19_7_9_9_19_1_1_1_1_11_2_16_15_14_14_11_12_7_7_12_6_2_2_2_5_5_8_14_14_15_15_15_1_18_13_13_8_4_5_15_6_2_6_6_6_6_6_16_19_6_7_4_5_5_10_10_5_1_8_6_12_12_15_15_3_7_7_15_7_7_11_18_6_14_15_17_9_9_10_10_10_10_10_10_3_10_2_2_7_7_2_1_10_6_3_3_9_18_18_18_18_5_5_2_2_2_2_3_3_3_10_10_16_13_8_8_8_8_8_10_10_13_3_3_16_8_8_2_2_1_1_1_19_11_12_12_12_5_12_10_15_15_15_15_4_4_16_16_7_10_10_10_10_5_11_3_5_2_7_14_14_18_18_7_7_7_12_19_19_19_19_1_12_12_12_12_17_17_8_8_20_7_12_8_8_8_7_7_1_15_15_3_3_3_16_3_3_6_18_1_1_8_8_8_15_3_3_3_2_11_11_19_6_6_11_17_3_3_3_11_4_1_6_8_2_4_11_11_11_11_11_6_7_7_19_19_11_11_11_11_11_11_3_3_3_17_17_17_1_1_1_19_14_6_4_4_3_20_20_20_20_20_20_20_5_5_12_7_7_7_7_18_4_7_7_7_7_5_13_4_11_11_11_11_7_3_3_3_13_8_8_8_9_15_14_14_6_4_4_4_3_1_4_16_16_5_1_1_14_15_15_15_3_3_4_2_2_2_8_1_1_1_1_7_19_12_9_9_4_11_15_15_15_15_9_6_11_11_12_12_3_14_14_7_5_10_1_11_6_6_6_4_4_4_4_10_10_19_14_2_17_20_20_6_6_6_6_6_4_14_9_9_9_14_19_19_19_9_15_15_10_10_10_7_2_12_7_2_10_3_3_3_18_18_15_1_17_17_17_6_5_5_20_10_10_9_8_18_6_6_6_6_4_2_1_12_12_15_6_6_5_2_4_19_3_8_5_5_8_8_6_6_6_16_4_2_2_20_12_8_6_10_10_3_14_14_14_14_14_14_14_11_13_13_12_12_3_3_3_3_3_11_7_10_8_8_9_10_10_4_1_10_1_6_6_6_7_6_6_6_9</t>
+  </si>
+  <si>
+    <t>16_7_9_6_10_10_14_7_7_7_20_6_6_14_14_16_15_2_10_7_7_15_15_13_13_13_13_13_13_13_5_4_14_14_14_1_1_5_16_8_8_8_8_3_3_3_3_8_2_6_6_6_6_3_8_8_8_11_11_11_16_14_14_17_17_17_17_17_6_6_9_1_1_1_1_6_14_14_10_13_13_13_15_8_8_6_8_8_10_10_10_5_14_16_16_16_16_13_6_6_1_1_15_15_10_10_5_5_4_4_4_4_16_8_8_8_8_18_13_16_17_3_4_4_5_7_7_7_7_6_4_5_12_12_8_8_8_8_1_4_11_4_4_4_9_3_3_9_12_12_12_5_5_15_15_15_16_15_6_6_6_19_18_9_2_19_19_4_5_10_4_16_4_15_15_15_6_6_17_17_4_15_15_15_12_2_2_2_2_3_7_11_2_10_4_4_16_19_4_5_15_13_3_9_9_8_8_14_8_17_17_14_3_3_3_3_1_1_6_6_5_9_9_9_6_6_4_15_15_15_2_5_2_19_18_9_17_17_17_17_17_9_8_8_9_9_9_8_3_3_8_10_14_7_7_7_7_7_8_3_9_9_19_17_17_12_12_4_7_9_14_14_5_5_9_9_9_11_10_19_11_17_11_11_11_11_9_14_7_10_14_14_4_2_7_7_14_3_3_3_5_2_3_3_11_9_9_10_16_16_14_1_1_2_14_3_18_17_17_15_15_1_1_1_1_14_9_13_4_1_1_6_6_8_10_14_18_5_12_12_6_6_16_13_13_13_5_14_14_14_9_5_4_4_16_3_3_13_13_16_9_9_3_10_2_2_14_8_8_16_5_6_2_4_7_1_15_15_5_18_18_8_9_1_4_4_5_12_7_16_16_16_8_10_3_3_3_3_1_1_1_9_9_19_3_3_2_2_9_9_2_2_9_2_2_10_2_8_8_5_5_5_5_13_13_13_13_13_13_18_11_11_11_8_3_3_3_3_13_8_9_9_2_2_17_3_3_3_1_1_1_1_1_8_8_8_7_6_6_6_10_10_10_17_18_5_14_14_14_14_4_7_11_13_13_4_4_6_6_14_9_9_9_9_7_15_15_15_4_18_1_1_6_15_12_5_16_9_4_4</t>
+  </si>
+  <si>
+    <t>17_17_17_17_17</t>
+  </si>
+  <si>
+    <t>19_19_14_14_14_14_15_6_3_2_8_16_1_6_6_3_4_6_6_6_6_7_7_6_6_6_6_10_10_4_3_5_1_3_3_3_4_4_9_9_9_19_19_19_14_12_12_16_16_16_11_2_2_4_16_16_7_16_7_6_13_17_8_8_11_7_7_7_8_8_8_16_16_12_4_4_4_8_8_8_18_2_2_3_17_9_9_15_13_6_6_7_7_7_7_16_15_16_3_3_10_18_18_9_9_2_2_14_8_10_10_6_6_5_4_15_15_10_9_9_6_16_14_14_8_8_10_4_8_13_13_13_13_8_17_12_12_12_12_2_10_17_17_9_13_13_7_2_10_7_1_3_3_5_5_5_12_6_8_8_8_8_8_8_18_18_18_18_18_18_7_7_14_2_7_8_9_11_4_1_2_2_2_2_2_11_11_1_3_11_1_16_16_7_3_2_2_2_2_16_16_4_4_7_8_8_8_16_16_16_15_10_15_1_12_3_3_3_10_10_10_1_1_1_5_5_5_6_7_7_4_4_4_15_3_3_3_3_3_3_3_3_5_5_18_13_5_5_1_1_10_20_20_20_13_13_11_10_15_15_15_8_1_7_15_15_15_15_5_10_19_5_5_5_5_5_14_2_2_2_2_11_11_15_9_9_9_9_9_5_5_7_7_1_1_7_17_9_9_3_1_16_8_8_8_8_8_14_14_14_13_10_10_10_10_10_19_14_4_8_18_11_11_8_5_5_5_5_5_2_10_10_10_10_1_1_8_8_5_18_19_19_13_11_5_5_3_20_5_5_5_6_6_6_6_6_6_16_9_9_2_2_12_6_6_6_9_9_4_6_1_1_5_2_2_1_2_2_8_9_12_12_3_3_3_3_3_8_8_9_9_1_1_8_10_4_6_4_4_14_8_12_12_10_15_6_14_14_6_6_6_20_20_8_8_8_8_8_15_13_2_2_2_2_4_11_11_19_16_9_1_1_4_8_15_15_12_12_8_7_2_5_7_17_8_7_2_10_10_4_19_7_7_17_8_8_8_8_3_3_3_12_12_3_9_9_12_12_12_2_4_2_5_9_1_16_16_1_1_2_2_3_3_2_2_3_3_11_18_1_1_3_7_7_13_13_11_2_19_12</t>
+  </si>
+  <si>
+    <t>10_17_1_11_11_11_6_6_12_2_2_2_11_11_14_14_5_5_10_20_20_20_3_8_2_2_2_2_2_11_16_10_5_13_11_11_18_18_10_10_10_11_11_4_17_7_7_17_17_17_6_6_10_3_19_19_19_9_9_11_11_11_13_13_13_20_18_16_19_6_15_2_2_3_3_8_8_8_8_5_2_2_2_6_18_18_18_20_20_20_1_1_17_17_17_17_1_13_13_13_9_16_15_15_2_13_13_13_18_18_18_13_13_11_11_11_5_5_9_16_4_4_4_8_18_16_19_4_4_4_10_10_12_5_5_3_13_16_3_2_2_2_18_12_12_12_3_1_7_7_7_7_7_7_7_8_8_8_11_9_9_9_9_10_10_10_2_2_4_4_13_13_13_2_5_8_9_13_20_20_11_13_18_18_19_19_9_20_20_20_20_20_4_14_5_5_14_1_1_9_9_10_12_12_10_15_4_4_7_10_10_3_10_7_10_10_5_9_9_9_14_14_14_14_14_11_12_15_8_3_15_15_1_10_10_10_10_10_10_18_10_5_13_13_13_3_3_3_3_16_18_17_9_9_13_13_3_12_2_2_10_6_13_13_5_6_6_11_3_3_3_2_15_4_5_5_7_7_13_18_18_18_1_1_1_1_1_1_14_3_3_9_20_5_1_1_1_5_10_16_2_8_5_8_3_12_16_8_5_5_5_7_9_9_9_13_13_13_12_7_7_5_2_2_2_6_6_12_16_16_10_10_10_10_14_14_17_13_13_7_1_4_4_8_7_15_13_13_10_15_8_13_13_7_7_2_9_9_9_19_19_19_18_8_7_12_3_12_12_10_10_10_15_20_20_20_4_4_9_9_2_2_2_10_10_16_16_19_15_15_8_7_7_7_7_18_18_12_8_16_6_6_18_20_20_20_18_2_5_5_5_5_5_1_1_1_8_14_14_19_1_1_9_9_9_4_4_12_19_13_13_13_13_13_5_1_6_6_6_6_3_17_7_18_18_3_11_12_3_3_13_13_6_3_3_3_14_13_17_6_6_4_13_6_6_6_7_7_7_7_7_6_6_6_10_10_10_10_9_11_2_2_2_19_19_10_10_13_13_11_17_7_2_2_2_8_8_3_5_5</t>
+  </si>
+  <si>
+    <t>18_18_18_18_18</t>
+  </si>
+  <si>
+    <t>2_2_2_2_7_13_13_5_8_2_2_2_2_13_13_13_9_9_4_3_3_15_3_16_15_15_15_15_15_2_4_4_9_9_9_5_17_6_6_3_16_9_9_9_8_8_8_8_13_13_19_19_19_19_20_20_20_4_4_3_1_6_6_6_6_6_3_3_6_6_9_9_9_9_3_3_3_8_6_7_6_6_6_6_5_5_5_5_5_7_20_18_17_7_7_20_3_3_3_10_10_19_19_6_6_6_5_14_14_17_17_5_4_6_6_6_6_6_8_12_12_12_10_10_6_20_11_14_14_14_1_6_6_9_4_16_16_17_8_8_8_3_5_2_2_2_6_14_10_7_13_13_7_7_7_6_6_6_3_1_1_1_12_16_4_7_9_15_9_7_20_20_11_11_2_16_16_2_2_11_15_2_12_13_13_13_13_12_12_18_18_18_17_16_16_16_2_11_11_7_16_16_8_8_2_9_9_9_2_2_2_9_9_4_4_4_6_2_3_3_3_2_2_2_12_7_14_15_15_1_1_1_16_16_7_3_6_6_9_9_9_6_5_5_5_2_11_20_20_20_10_10_10_10_11_6_6_18_11_11_14_14_14_4_4_4_4_4_9_9_9_9_9_17_15_20_20_20_20_20_20_20_13_10_6_6_1_1_1_1_12_12_3_3_1_12_9_9_9_6_12_6_6_6_6_6_8_8_18_13_3_1_1_14_3_6_6_6_11_11_13_1_20_10_7_7_8_2_7_3_3_6_6_7_7_3_3_3_3_8_8_17_8_6_7_14_9_9_9_3_3_5_11_15_15_14_11_11_10_9_12_12_13_13_15_17_5_5_7_5_5_5_15_15_15_14_17_17_20_20_6_6_6_17_2_1_1_1_10_18_12_17_9_17_11_11_11_11_3_19_19_9_8_8_8_10_10_10_10_5_11_3_3_7_9_9_15_9_9_16_3_5_4_11_4_15_14_3_15_1_20_20_16_16_3_3_5_1_1_16_14_14_14_14_6_5_5_8_4_4_14_14_14_13_3_3_3_3_3_5_4_6_11_11_11_16_16_8_8_3_3_6_8_8_7_7_12_12_1_1_1_19_9_7_12_7_3_6_6_3_3_3_3_3_3_12_14_14_15_15</t>
+  </si>
+  <si>
+    <t>5_5_5_19_1_15_5_15_15_15_5_5_2_2_2_2_9_9_20_3_10_10_8_12_2_19_7_15_15_15_15_7_6_17_8_8_8_8_8_15_3_3_14_14_10_10_10_12_16_16_16_11_11_11_11_13_6_6_10_10_9_9_9_15_6_7_14_11_11_11_6_10_8_1_1_1_1_15_20_13_13_16_16_19_13_13_10_10_17_17_5_7_15_15_8_14_6_6_3_4_14_17_17_11_10_3_3_3_3_3_3_2_8_13_9_9_4_15_13_13_4_11_5_1_19_19_16_1_1_16_16_3_3_3_18_18_10_8_8_10_4_8_8_3_3_6_6_6_2_20_5_18_1_10_13_4_4_4_3_3_3_3_3_4_11_4_4_4_4_12_15_15_2_13_19_7_7_10_14_8_8_12_14_14_14_15_16_16_16_16_1_12_12_11_16_5_14_5_5_5_3_3_4_8_8_2_13_6_6_6_17_17_15_8_5_5_5_16_5_7_9_9_5_15_15_13_8_16_4_6_15_13_13_11_16_16_5_3_17_17_20_4_11_1_1_1_1_1_4_6_13_4_4_1_1_5_16_6_3_12_3_3_3_3_3_3_11_11_11_11_4_11_11_11_3_3_14_14_3_3_11_7_7_18_18_18_18_3_3_8_2_3_11_11_7_7_16_12_7_16_6_6_19_2_15_18_15_15_15_15_15_15_12_6_6_6_1_1_1_4_20_20_1_7_1_1_1_1_1_1_18_17_17_17_11_11_11_7_8_16_16_9_4_3_3_8_10_1_14_5_5_13_13_4_7_7_7_16_16_16_11_7_7_7_7_7_11_13_16_2_20_8_7_7_11_16_16_16_16_19_7_6_5_1_1_1_7_5_2_16_1_12_12_9_9_9_9_4_1_17_17_17_17_9_9_1_1_1_1_1_4_4_8_8_8_12_12_12_12_10_2_5_5_5_5_5_10_10_17_17_13_13_13_13_13_19_6_5_10_13_2_10_10_17_17_8_15_15_17_5_16_15_13_14_8_6_6_6_5_5_4_18_2_2_5_4_10_5_5_6_18_18_18_18_1_17_4_4_7_1_4_4_9_1_5_7_3_9_5_5_8_8_8_11_11_1_1_3_3_6</t>
+  </si>
+  <si>
+    <t>19_19_19_19_19</t>
+  </si>
+  <si>
+    <t>18_18_5_5_15_15_6_6_6_2_3_5_6_9_10_10_1_16_2_2_4_4_4_5_5_5_4_11_11_11_8_4_13_10_2_2_9_9_9_9_9_2_2_6_16_15_11_18_5_12_10_10_7_7_9_3_8_3_3_3_9_1_7_7_12_12_12_12_18_18_2_4_4_8_2_7_7_1_5_10_10_10_2_4_4_10_10_10_10_10_10_6_6_6_6_6_11_11_2_15_5_7_1_1_7_7_17_17_17_1_1_1_4_4_4_7_7_17_11_9_9_9_7_7_17_17_17_2_11_11_11_11_8_8_8_8_13_13_4_4_3_3_5_9_9_9_4_6_10_8_2_13_13_1_18_4_4_3_3_2_2_17_17_1_8_3_3_3_3_10_6_6_6_8_3_3_3_1_6_16_4_4_4_7_7_2_5_9_9_9_9_9_12_12_4_4_4_11_5_10_16_3_18_1_5_5_10_10_2_14_5_11_10_4_4_4_4_4_3_3_3_18_18_12_7_9_9_9_12_3_3_3_5_5_5_5_5_14_2_2_2_15_8_8_8_8_5_7_7_18_3_14_14_17_17_18_8_8_5_5_5_5_12_8_6_6_11_11_11_11_11_11_18_18_12_12_3_3_3_18_18_18_10_10_10_10_5_6_6_15_8_8_8_8_8_8_11_11_14_14_14_16_16_9_9_12_10_2_14_4_5_2_7_7_7_1_4_4_4_4_4_4_4_4_4_4_6_6_6_19_14_16_9_12_4_7_7_1_7_7_15_15_1_12_3_5_4_7_5_7_19_19_11_1_3_3_18_7_8_8_11_10_10_10_5_5_5_10_10_5_12_12_12_18_13_9_9_9_10_9_9_9_5_15_15_15_13_6_1_2_2_2_10_10_10_11_11_11_16_2_1_7_8_3_3_1_1_1_6_13_13_13_13_3_11_11_6_6_20_20_20_8_9_9_13_9_9_1_10_7_6_19_19_19_19_6_6_6_5_5_1_5_7_7_8_8_10_10_10_15_15_12_12_12_9_8_8_16_9_9_4_9_9_11_11_11_11_11_11_17_17_17_10_13_12_6_6_12_5_9_8_8_8_11_4_4_4_3_3_2_2_2_5_16_16_16_13_13_9_9</t>
+  </si>
+  <si>
+    <t>5_5_17_17_9_9_12_9_9_2_9_9_10_10_5_10_11_2_2_15_15_17_10_18_18_14_14_14_17_8_8_8_8_11_3_8_7_13_16_7_8_8_2_7_7_7_19_19_2_2_11_14_6_6_6_5_5_15_7_7_7_2_4_4_4_4_4_18_18_18_19_18_18_3_6_6_13_8_6_4_12_4_4_2_2_3_3_3_10_13_5_12_12_3_9_11_11_8_8_8_18_18_18_18_1_6_11_6_6_14_20_20_15_11_2_2_4_3_3_20_18_6_8_6_10_4_4_4_4_2_2_2_2_16_16_2_8_8_5_5_7_18_16_13_13_14_16_7_2_4_4_8_17_5_5_14_9_3_13_6_15_15_15_16_16_18_13_11_7_7_7_7_14_14_14_15_15_15_9_19_18_10_10_10_10_10_13_10_10_10_8_14_14_14_14_14_15_15_15_15_15_2_4_7_7_7_1_6_6_10_5_9_9_7_5_5_2_10_4_14_13_12_12_11_10_10_10_15_14_17_17_17_18_18_14_3_15_15_15_15_19_19_6_18_13_4_4_10_20_19_7_7_11_10_10_11_11_13_13_10_3_3_3_3_3_20_7_4_4_13_13_13_13_7_2_12_19_3_3_9_9_8_8_15_2_2_4_14_13_19_19_19_11_4_20_20_20_20_16_8_8_5_5_10_12_3_13_13_13_15_4_7_6_3_8_11_1_6_9_9_16_17_17_17_3_3_3_10_10_10_10_6_17_6_6_16_7_4_4_4_1_10_4_4_4_4_4_6_6_7_3_3_3_10_10_13_13_13_13_7_12_12_8_8_8_20_18_16_14_14_17_17_4_16_7_17_17_10_7_8_8_8_8_8_8_5_4_4_10_4_4_7_7_19_19_14_11_3_14_12_16_16_16_16_2_1_13_6_1_1_3_14_14_14_14_2_2_7_11_14_14_20_20_1_5_5_9_8_6_6_2_12_6_17_18_18_18_9_9_16_16_2_2_2_2_9_12_9_9_9_15_11_11_11_11_2_2_16_16_16_19_20_14_14_14_8_14_14_1_13_8_8_4_11_16_12_12_12_12_17_6_6_6_6_6_11_6_6_15_15_1_1_1_1_10_20_20_20_11_11</t>
+  </si>
+  <si>
+    <t>20_20_20_20_20</t>
+  </si>
+  <si>
+    <t>15_15_11_4_4_9_9_12_17_17_2_2_4_4_6_6_6_13_7_7_7_3_12_12_2_4_4_4_7_12_12_3_9_6_1_1_19_20_9_10_11_10_8_11_5_5_14_14_13_6_8_8_10_3_3_9_3_4_17_17_13_5_15_15_15_15_15_15_6_8_7_7_13_2_2_2_13_10_10_6_6_6_7_7_7_3_2_11_5_5_18_9_9_7_7_9_12_12_12_14_7_7_9_7_7_1_1_1_15_6_4_7_7_7_7_7_7_7_7_7_10_10_6_18_18_13_5_3_3_1_9_7_7_7_7_7_7_13_13_13_6_4_2_5_1_8_14_5_13_12_6_6_6_6_6_19_18_18_10_10_11_11_17_3_14_7_3_3_15_15_15_15_2_4_2_2_2_10_9_9_19_3_2_15_2_7_7_5_10_8_2_3_3_17_6_6_18_5_5_2_2_3_3_6_9_9_1_1_17_17_17_17_17_2_19_2_9_9_2_3_6_5_5_5_3_10_10_6_4_10_10_10_3_3_9_5_5_10_10_14_14_5_5_12_12_12_18_18_15_17_4_4_4_15_9_2_13_7_7_7_14_14_14_14_16_16_16_5_5_5_1_1_1_1_20_11_11_11_11_11_11_9_9_6_6_10_13_1_18_13_3_5_5_5_5_5_18_18_18_18_18_5_8_7_7_7_14_1_16_16_15_16_9_10_14_2_2_2_8_2_4_17_8_8_14_14_14_14_14_2_4_1_8_5_5_9_8_8_8_8_8_8_8_10_2_12_14_6_6_12_17_2_12_7_8_11_11_2_2_5_5_5_5_3_2_2_2_2_2_2_2_2_2_2_10_10_10_10_10_5_5_5_5_5_10_15_2_2_10_3_9_20_7_7_20_6_9_5_19_13_1_13_1_1_1_4_4_10_4_12_12_12_3_7_16_13_13_16_16_20_9_9_9_12_12_14_14_14_14_10_5_9_9_5_5_1_10_10_10_19_8_8_16_9_16_15_13_8_9_4_16_20_20_19_19_19_19_19_9_3_18_18_10_10_10_18_16_16_17_15_10_6_6_17_7_7_10_1_16_16_4_15_5_5_10_6_6_6_6_12_12_12_3_8_8_10_10_10_6_8</t>
+  </si>
+  <si>
+    <t>15_15_15_15_1_1_7_7_7_9_16_18_8_8_8_8_9_11_13_11_10_8_8_8_5_4_19_19_14_14_14_14_4_4_5_3_3_1_9_1_16_16_8_8_17_17_13_16_16_16_4_13_13_1_10_10_9_3_3_3_2_2_18_18_18_18_18_18_16_16_16_16_9_13_13_17_10_10_10_18_18_18_17_17_17_11_6_6_6_6_13_13_13_13_13_1_5_15_1_1_1_9_9_9_2_12_12_1_6_16_7_7_14_3_10_10_10_10_10_1_1_17_17_5_10_13_13_2_5_5_8_8_7_7_17_1_8_8_8_8_8_13_13_11_9_9_14_4_1_19_19_5_10_10_20_20_11_11_11_5_5_5_13_13_10_10_2_2_3_3_3_6_1_5_12_12_12_15_15_15_15_15_4_6_11_3_3_3_3_15_20_4_3_3_3_3_16_14_5_5_5_17_9_4_16_18_18_18_6_1_1_5_2_2_12_12_12_12_12_8_1_20_9_9_9_16_8_12_2_5_8_8_11_11_11_11_11_11_17_13_5_2_8_8_8_8_8_8_3_19_16_5_12_7_6_6_10_5_20_20_20_20_20_10_10_10_3_18_5_5_5_5_13_4_4_4_4_4_4_4_7_11_5_1_1_1_4_4_4_6_6_14_18_18_6_9_9_9_9_15_15_15_5_5_5_5_14_4_3_9_6_6_11_1_15_1_9_16_1_1_15_15_15_10_19_2_2_2_2_2_7_7_10_12_12_12_12_12_12_12_12_3_3_3_2_8_6_6_4_16_16_16_8_8_8_7_15_15_14_14_15_18_18_3_3_3_15_15_18_18_1_1_18_18_20_8_8_4_18_13_5_5_11_11_11_11_12_12_18_18_13_13_13_13_5_3_3_3_3_3_20_20_2_5_2_7_7_9_6_1_4_4_14_14_7_7_7_3_8_8_4_6_2_2_2_2_18_20_10_2_10_3_2_16_16_16_16_16_16_16_8_3_18_18_18_18_18_7_7_4_7_7_7_7_4_18_18_5_20_20_4_18_7_5_5_5_5_16_13_7_7_13_7_12_10_15_15_15_5_5_5_5_10_4_4_17_3_3_3_1_14_6_6_6_6_6_6_14_11_11</t>
+  </si>
+  <si>
+    <t>9_13_13_13_17_5_11_11_19_11_5_5_1_19_5_11_11_7_11_11_11_17_5_7_7_7_7_7_9_9_9_5_5_13_7_7_19_9_13_5_11_11_11_11_11_11_3_9_7_5_5_5_5_11_11_11_7_7_7_1_1_17_17_17_5_11_11_15_15_9_11_11_11_11_11_11_13_13_13_5_7_9_15_15_9_9_13_5_11_15_11_5_19_5_5_1_1_1_1_3_9_3_5_5_3_11_19_11_5_1_1_1_1_3_3_3_3_15_3_19_5_9_15_3_9_11_11_11_9_7_3_3_3_13_13_3_11_11_11_1_1_1_1_3_7_11_1_13_13_13_9_9_3_3_11_11_11_11_13_13_13_17_19_1_9_1_13_7_7_7_7_11_11_7_7_13_3_3_9_7_7_7_7_5_5_5_17_17_17_7_1_1_1_1_1_7_7_7_15_1_11_9_19_1_1_1_3_3_3_3_19_13_3_3_9_9_13_13_13_1_1_3_3_3_19_1_7_7_17_3_11_7_7_7_5_13_13_13_13_13_19_3_9_7_11_3_3_5_5_17_1_15_15_5_5_15_15_5_5_13_13_13_13_17_17_1_1_11_13_5_5_17_5_5_7_7_7_9_9_15_15_15_15_5_5_13_11_11_9_7_3_3_1_1_9_1_1_1_1_1_1_17_17_17_17_9_9_15_15_1_5_1_11_11_17_15_15_15_5_1_19_19_19_19_7_7_9_9_9_9_9_19_5_7_7_7_5_5_5_9_15_15_11_11_11_5_5_19_13_5_7_7_7_7_9_5_5_5_5_5_5_5_19_1_17_13_3_3_3_3_3_3_9_9_9_9_11_11_5_13_11_11_7_5_7_17_9_15_15_15_13_15_7_1_3_9_9_7_3_3_3_19_19_7_13_13_9_1_1_5_11_1_1_9_17_17_17_1_1_1_11_11_11_11_1_17_9_15_1_13_13_5_5_17_17_5_1_1_1_1_9_9_9_13_13_3_11_11_3_9_9_13_3_15_15_11_13_17_7_11_19_15_15_15_9_13_5_5_5_1_3_3_5_5_3_11_19_19_19_9_7_7_9_5_17_17_17_17_17_7_7_9_9_13_13_15_19_19_19_19</t>
+  </si>
+  <si>
+    <t>7_19_17_3_3_3_3_3_3_3_9_5_5_5_5_17_17_17_17_19_3_7_7_17_5_5_5_9_7_3_9_9_3_9_5_11_9_13_13_7_3_3_3_15_1_1_5_17_11_9_9_3_1_9_9_1_1_11_9_3_3_11_15_11_11_11_11_9_19_19_13_5_5_5_5_5_5_7_17_17_17_7_7_7_3_11_3_3_1_1_1_17_17_17_17_7_7_7_7_7_7_3_11_13_13_13_13_13_1_17_3_15_13_3_17_17_17_1_9_5_3_3_17_15_1_1_13_13_13_3_9_17_1_17_5_19_19_19_19_1_1_5_9_9_9_15_15_3_3_15_5_5_5_9_3_3_9_9_9_3_3_9_9_9_9_7_7_19_19_19_19_9_15_15_9_9_9_7_5_17_17_7_9_9_5_11_5_5_13_3_17_3_7_11_11_13_13_13_13_13_3_3_3_3_3_5_7_15_3_3_3_7_1_11_7_7_3_13_3_5_5_3_7_7_7_1_11_11_9_7_11_1_1_7_5_5_5_5_11_11_11_1_11_5_1_1_11_9_3_17_13_15_1_7_13_13_13_13_13_1_1_1_1_1_1_1_1_1_1_5_5_5_7_7_11_11_11_11_5_5_13_5_5_5_3_3_5_5_5_15_15_11_11_3_3_15_15_15_15_19_9_11_11_15_5_13_13_7_15_15_15_11_11_11_9_1_15_13_15_15_9_3_13_1_7_3_15_9_9_11_5_11_11_5_13_13_13_13_13_13_13_1_3_1_1_1_9_9_3_13_13_13_13_13_13_9_9_3_3_3_3_3_7_1_1_11_1_1_17_17_11_17_11_5_9_5_11_1_11_19_19_19_19_7_7_7_19_11_9_9_7_7_7_7_1_1_1_1_3_3_3_3_1_13_5_11_11_11_3_17_1_1_17_17_7_7_7_7_7_7_7_7_11_17_3_9_9_7_15_17_17_5_5_7_7_7_7_7_15_15_15_15_7_7_7_17_5_5_5_15_3_1_1_7_13_13_3_3_3_15_15_15_5_9_3_3_3_3_3_13_15_11_11_15_15_15_15_11_11_11_3_5_13_13_15_15_15_5_5_19_19_19_13_3_9_3_3_1_1_7</t>
+  </si>
+  <si>
+    <t>15_15_1_9_9_5_11_1_1_1_11_5_7_9_9_9_9_5_5_11_7_15_15_11_11_7_17_7_7_7_9_13_13_13_13_7_5_11_15_15_15_15_13_13_13_13_13_13_13_13_1_15_11_7_11_11_11_11_17_17_13_13_15_11_11_11_19_19_19_3_3_3_3_13_15_15_5_13_19_15_15_15_13_15_13_3_3_5_15_9_9_5_11_11_3_3_1_1_3_13_13_5_5_17_1_1_1_7_7_17_17_19_19_19_19_11_11_1_15_15_15_9_3_3_3_3_3_13_15_3_17_17_3_13_13_9_11_7_17_15_15_11_3_5_1_11_13_11_11_11_19_13_13_13_13_13_13_13_1_17_17_1_1_5_5_5_7_3_19_3_3_15_15_15_15_15_5_5_5_5_5_13_15_15_7_7_5_1_1_5_1_7_7_17_17_7_1_3_3_9_11_3_3_7_7_7_7_1_1_1_1_1_7_7_5_5_11_3_3_7_11_9_9_3_9_9_5_7_5_1_5_1_3_5_7_1_1_1_7_7_9_9_9_17_1_1_5_5_5_11_1_5_15_15_7_1_1_1_15_15_15_9_3_5_5_5_9_9_9_3_7_19_3_15_13_13_13_1_15_9_3_5_11_7_13_13_15_15_9_15_1_1_7_15_15_15_11_5_5_7_7_7_19_3_17_13_3_3_11_19_7_7_7_7_7_5_13_11_15_15_1_19_3_7_3_3_7_7_7_7_15_15_15_1_13_3_3_3_5_11_13_5_5_5_5_5_9_15_9_7_9_13_19_5_9_11_13_17_7_1_3_11_11_3_3_13_13_13_13_1_9_9_13_1_15_5_9_9_9_9_9_9_15_5_5_7_9_9_9_15_15_15_17_3_3_1_15_3_9_9_9_15_3_3_3_3_5_9_3_1_17_11_5_9_5_5_5_9_9_9_9_19_19_5_5_5_5_3_11_15_15_15_11_11_15_15_9_1_1_9_11_1_1_9_15_11_11_9_9_9_15_15_13_7_7_7_7_7_17_5_17_17_9_13_13_13_11_15_9_9_9_9_9_11_11_11_11_13_11_11_19_19_19_1_1_1_9_15_15_15_11_11_11_11_11_9_5_13_15_15</t>
+  </si>
+  <si>
+    <t>11_1_1_3_3_3_3_3_5_13_7_7_7_3_3_3_9_1_1_1_7_1_1_19_19_1_1_9_11_13_3_3_7_7_7_7_7_13_13_17_9_9_9_9_9_17_17_9_9_13_1_15_15_3_3_3_3_1_5_5_5_5_9_1_1_13_13_13_13_19_15_9_3_3_19_17_17_13_17_9_9_9_9_9_7_7_7_3_3_11_5_5_3_3_3_3_3_3_15_15_15_15_15_15_11_11_11_11_11_11_11_7_3_13_3_19_19_1_11_17_3_3_3_13_13_9_9_9_5_19_17_1_7_17_11_9_11_11_11_11_5_1_11_11_5_1_1_1_13_7_7_1_1_1_1_15_15_9_9_9_9_9_11_3_1_1_5_17_17_13_1_1_1_9_11_1_11_3_13_13_13_13_15_13_7_5_9_9_9_9_9_5_9_1_1_7_7_13_13_11_13_13_7_7_5_11_11_15_3_11_7_1_1_7_5_5_17_3_11_11_7_7_3_3_15_15_15_15_3_15_15_7_7_7_9_13_5_5_5_1_5_13_15_15_15_11_5_7_5_5_11_11_17_17_17_17_3_7_7_7_17_7_17_13_5_3_9_5_3_3_5_11_13_13_13_9_9_19_19_19_11_1_13_13_9_9_11_9_7_7_19_1_3_3_3_3_17_17_9_11_11_11_11_5_5_7_7_7_7_3_3_3_13_1_3_9_11_11_9_1_1_7_7_7_15_1_17_3_11_9_1_1_3_9_11_11_11_11_11_11_11_15_3_3_3_3_1_1_1_7_3_3_3_15_7_7_7_9_9_9_9_7_7_7_7_7_7_3_17_17_17_1_13_13_19_19_19_19_3_11_15_15_1_3_3_15_15_1_1_1_1_1_1_1_1_3_17_17_15_15_1_9_9_13_19_7_5_5_5_5_9_9_9_17_17_13_13_13_1_1_1_1_13_11_15_15_7_15_3_5_5_3_3_3_3_3_1_1_1_19_9_3_3_3_15_17_17_15_15_15_15_15_15_7_7_7_13_15_7_7_1_5_5_5_13_5_5_5_5_17_15_3_9_13_9_9_13_5_19_19_1_1_17_3_3_3_3_3_9_9_9_9_9_13_1_19_5_5_15_5</t>
+  </si>
+  <si>
+    <t>7_9_5_1_1_13_13_13_13_7_5_9_3_1_1_1_1_1_1_1_11_7_11_11_17_13_5_5_1_1_1_3_7_7_7_7_7_7_7_13_9_15_15_15_13_9_17_19_11_11_3_3_1_1_5_3_3_3_9_3_11_11_9_7_9_3_1_5_11_11_11_3_7_9_3_3_3_19_9_9_9_7_7_7_7_1_7_13_9_13_7_7_15_15_15_15_1_1_9_3_3_3_3_19_19_1_1_1_1_13_15_7_3_19_19_19_11_3_9_11_11_11_11_11_1_1_5_13_3_3_3_9_9_1_3_3_11_9_9_9_9_9_9_1_9_9_1_13_7_7_7_7_13_13_17_9_9_9_9_9_9_9_9_9_11_11_11_11_11_11_1_11_19_19_19_19_11_7_19_9_9_7_3_11_11_11_15_15_11_13_15_15_9_9_7_17_17_17_17_9_9_9_1_15_15_15_3_7_7_7_11_11_7_7_9_5_17_1_5_5_3_7_15_15_13_15_15_13_7_7_7_3_3_15_9_15_1_1_13_5_5_7_7_11_11_1_5_3_19_19_19_11_7_7_7_7_7_7_7_7_9_9_15_19_9_19_5_3_3_7_13_13_5_7_7_5_5_11_3_3_3_7_7_7_11_1_1_1_1_9_9_7_7_7_11_11_11_11_11_3_3_3_7_19_13_11_3_3_3_5_13_3_17_17_17_3_3_3_11_7_7_7_7_11_11_11_9_9_9_9_5_1_1_1_3_3_3_17_1_1_1_5_17_17_17_13_13_15_19_3_3_3_3_3_3_7_3_3_11_9_7_1_19_1_5_5_19_7_19_5_5_5_13_13_13_7_11_11_5_5_5_5_5_5_7_11_11_11_3_3_5_1_9_15_13_3_9_1_1_13_13_15_13_13_19_19_19_19_19_17_9_15_7_13_1_1_5_1_19_1_7_15_15_15_15_9_3_17_5_13_5_5_9_17_9_9_13_13_15_7_11_17_15_5_11_7_7_7_7_7_13_13_5_5_13_13_13_9_7_7_11_11_11_1_1_13_9_9_9_9_9_9_3_3_9_13_11_11_13_13_13_13_13_11_7_3_3_3_13_3_3_1_11_11_17_17_17_3_19_1</t>
+  </si>
+  <si>
+    <t>7_7_7_7_7_7_7_7_7_5_13_5_9_9_19_3_3_5_13_7_7_7_17_11_11_15_15_15_15_9_9_9_17_17_3_7_7_7_7_7_7_15_15_15_11_11_13_1_15_15_7_7_9_3_11_7_7_3_1_1_1_17_1_9_9_7_17_17_9_15_9_13_9_19_19_3_15_3_3_5_5_5_11_11_13_13_15_1_1_9_9_9_7_9_1_1_1_1_1_5_5_13_13_13_13_13_7_13_13_13_13_5_5_11_9_5_9_7_11_11_11_11_7_9_19_5_1_1_1_1_3_11_11_11_11_3_11_5_17_17_7_7_7_11_5_5_5_1_1_3_13_13_13_11_11_5_15_5_5_3_5_11_11_5_1_1_1_1_1_1_7_7_7_11_1_13_9_7_15_1_13_11_11_13_13_5_5_5_5_15_7_11_11_7_11_15_13_5_5_9_7_9_13_13_11_11_11_5_3_3_9_19_5_5_5_5_5_5_5_5_17_1_1_3_17_5_5_3_3_3_11_9_9_15_15_15_15_7_9_19_7_7_7_7_7_13_19_9_13_19_3_9_17_15_5_19_19_3_3_7_1_1_1_11_15_13_13_7_15_15_15_15_13_3_11_3_3_5_3_3_3_3_3_3_3_11_1_11_9_13_7_5_5_3_1_3_1_1_1_1_1_1_11_17_7_7_7_7_7_7_7_5_1_7_7_13_5_13_13_3_13_13_9_9_9_1_5_11_9_13_11_11_7_3_5_5_5_11_11_1_3_3_1_7_7_1_1_1_3_3_3_7_7_7_7_9_13_7_13_9_5_19_19_19_19_11_11_11_11_11_17_17_17_1_1_5_5_9_3_3_19_19_9_7_7_7_11_1_9_1_11_3_13_1_1_7_7_9_9_7_1_15_15_15_9_13_13_1_1_13_7_9_9_9_9_9_13_17_11_11_11_11_3_3_1_1_3_3_1_9_17_17_1_1_1_7_7_7_11_9_11_11_5_5_13_3_3_5_5_5_9_17_3_9_9_9_5_5_3_3_11_11_11_5_19_11_11_1_7_7_13_9_11_11_11_11_11_5_11_3_5_3_17_17_7_7_7_7_3_3_19_1_5_13_13_15_13_13_1_9</t>
+  </si>
+  <si>
+    <t>5_7_11_15_3_7_7_13_5_5_3_11_3_7_5_11_11_13_13_13_3_3_11_9_9_9_9_9_9_9_1_9_9_9_3_3_7_5_5_1_3_3_3_3_7_7_5_5_5_5_15_15_15_15_15_5_11_15_13_13_1_3_3_5_5_11_11_15_15_15_3_1_5_15_13_9_9_9_19_19_1_3_17_19_9_9_9_13_13_13_13_13_13_13_9_9_9_9_11_15_15_15_15_1_11_15_9_9_15_5_5_5_1_3_3_17_17_17_17_7_7_7_1_5_5_19_1_1_3_7_3_7_11_11_9_11_7_7_7_7_1_11_11_11_13_7_17_17_17_17_7_1_3_7_7_11_1_7_7_7_15_1_1_9_9_9_15_9_7_7_7_7_1_13_13_3_5_11_13_9_9_3_3_3_3_13_1_1_1_1_13_3_1_11_11_5_19_19_19_13_5_5_13_3_7_5_11_11_3_3_5_5_15_9_9_7_1_19_1_1_9_5_5_9_9_9_15_15_15_15_15_15_1_3_5_5_7_7_7_5_3_15_19_15_15_9_9_11_11_17_19_19_3_5_5_5_5_7_7_9_13_13_9_9_13_13_17_17_17_17_7_11_9_9_5_3_15_11_9_9_9_13_13_13_13_11_11_11_1_1_1_17_9_9_11_11_7_7_19_19_11_11_3_3_3_3_1_1_9_9_9_5_3_3_7_15_9_9_11_13_13_5_3_3_3_3_3_1_1_1_1_9_11_11_13_13_13_13_13_13_3_3_3_3_15_3_17_5_17_17_1_1_3_3_17_17_17_11_7_7_9_9_9_15_11_11_11_9_9_1_7_1_5_9_9_19_19_1_7_7_13_7_11_11_9_15_15_9_13_13_13_9_9_1_9_9_9_9_9_7_11_15_13_15_15_17_15_3_11_13_13_9_17_1_7_13_11_11_11_15_11_1_1_1_1_17_17_9_9_15_15_3_3_3_3_9_17_13_17_3_15_15_15_5_15_15_13_7_7_7_15_7_9_7_15_5_5_5_5_5_11_1_5_5_5_17_17_1_1_1_1_3_7_19_19_3_15_7_7_5_5_5_3_3_5_5_5_9_7_9_9_9_7_7_11_15_9_5_5_5</t>
+  </si>
+  <si>
+    <t>1_9_9_9_13_7_3_3_3_1_1_9_11_17_1_5_3_3_13_13_13_7_5_5_13_17_1_1_5_3_9_3_3_3_13_13_5_11_11_11_11_15_15_15_19_19_19_19_11_11_7_7_19_1_1_15_15_11_11_11_11_9_1_3_11_11_7_7_7_7_7_3_11_11_11_3_7_7_7_11_11_15_19_19_19_7_5_9_9_7_1_3_3_19_5_5_19_13_1_3_3_3_9_9_19_13_15_15_9_15_15_1_3_1_1_17_3_11_11_11_1_1_1_13_13_13_7_7_7_7_5_5_5_11_13_13_9_9_9_5_5_15_3_9_9_9_9_5_3_3_1_3_3_3_3_3_5_5_5_19_7_17_1_1_1_1_13_15_3_3_11_15_3_3_3_15_1_17_3_5_5_5_7_7_13_11_11_17_17_17_7_17_17_13_15_15_11_15_9_15_11_7_5_5_5_5_3_5_5_5_1_15_15_1_1_11_3_3_3_1_1_7_7_9_5_9_9_9_1_1_5_5_9_5_13_13_13_1_1_1_9_9_3_3_3_7_1_19_3_9_9_1_1_1_1_7_7_9_9_15_15_13_1_17_17_17_17_15_15_11_15_9_19_19_19_19_11_9_9_9_9_9_9_9_13_11_11_11_11_3_3_15_15_19_19_19_19_13_1_11_17_9_1_5_3_19_9_5_5_15_15_13_13_13_13_3_7_9_15_15_1_7_15_5_5_5_5_5_1_1_7_7_7_7_13_13_13_13_1_1_1_1_1_19_3_5_5_13_7_7_7_7_7_7_1_1_13_3_9_5_7_7_7_5_3_3_11_11_11_7_9_11_11_11_11_3_3_1_11_9_9_9_9_9_9_11_9_3_13_17_15_15_15_15_15_9_9_7_3_15_3_17_19_3_3_9_9_9_7_3_3_15_15_15_5_9_17_11_15_3_1_1_17_17_15_3_13_13_3_3_19_19_11_11_11_19_5_5_5_5_11_7_7_1_1_1_1_17_17_3_3_5_5_5_7_7_15_15_15_15_1_13_13_11_19_19_9_9_9_9_9_9_13_3_19_19_17_17_1_1_1_1_1_3_5_5_7_7_7_3_17_5_5_13_13_13_3_3_3_3</t>
+  </si>
+  <si>
+    <t>1_1_15_19_17_13_13_13_13_13_11_11_11_11_11_11_11_11_11_7_3_9_7_3_3_3_3_9_15_15_7_15_3_7_7_13_13_13_5_9_1_1_15_15_15_19_19_19_17_5_5_5_15_17_17_1_15_1_1_3_3_5_5_1_1_1_7_15_15_15_15_13_13_13_1_1_1_1_7_11_11_11_11_19_7_7_19_19_19_19_1_1_11_3_3_11_5_1_1_1_13_13_13_9_7_7_7_7_17_17_17_7_7_11_11_17_17_17_15_19_19_19_19_19_19_19_19_1_1_1_19_1_1_13_3_11_9_3_11_11_13_11_5_1_11_11_19_3_3_3_1_7_5_5_17_17_17_17_9_5_5_3_5_5_5_5_5_15_15_15_13_1_15_15_3_11_7_7_7_3_3_7_7_7_7_9_9_3_11_5_5_5_17_9_7_13_13_13_13_3_3_3_17_15_3_1_1_15_13_9_5_5_5_17_7_7_9_9_9_9_9_13_13_13_13_13_7_3_17_19_19_19_1_5_11_7_7_1_1_5_15_15_9_9_13_1_19_5_7_15_15_17_17_7_7_7_7_7_19_15_11_15_3_5_5_9_11_11_11_9_9_17_17_7_1_1_9_7_7_5_5_17_9_5_5_11_17_9_9_13_13_13_11_15_15_15_15_5_5_13_13_1_11_5_5_13_17_1_1_1_9_9_11_17_9_1_7_13_5_13_13_13_9_9_9_9_9_9_1_13_13_7_5_5_7_13_13_1_13_1_13_11_13_13_13_7_13_3_17_17_17_17_1_7_3_5_17_9_13_13_13_5_5_5_13_7_7_19_19_5_11_13_19_11_11_11_11_11_11_11_11_11_5_7_7_7_3_15_15_7_7_17_5_11_11_11_15_3_13_15_7_15_15_15_15_15_15_15_15_11_1_3_13_7_7_1_19_19_19_13_13_13_13_9_5_13_5_15_15_15_17_17_17_15_3_3_3_3_9_9_9_7_15_17_17_17_3_3_3_3_3_13_13_3_3_5_13_3_3_3_3_3_3_13_11_11_15_15_7_1_1_13_17_17_17_5_17_17_17_13_3_17_9_9_9_7_7_7_5_5_1_1_1_1_1_1_7_5_11_1</t>
+  </si>
+  <si>
+    <t>11_5_15_1_5_7_9_9_17_3_13_13_11_11_5_13_13_13_5_5_15_7_15_15_15_3_3_9_1_1_1_1_13_13_1_1_11_5_5_9_3_3_1_17_17_17_17_1_15_9_9_13_5_9_9_9_3_3_3_9_9_9_9_5_5_17_7_5_15_15_15_15_9_1_1_9_5_9_5_13_13_13_15_3_7_3_3_9_9_9_11_5_5_5_5_3_3_3_3_7_7_7_13_7_7_7_7_11_13_7_7_11_17_15_15_15_15_1_9_1_1_1_1_1_5_13_3_11_11_11_9_9_17_17_7_19_3_9_1_9_9_3_19_19_15_15_5_5_5_11_11_11_5_5_9_15_3_5_13_13_13_13_11_7_7_5_5_5_11_11_11_1_5_1_9_3_3_9_7_7_1_1_1_1_7_19_13_13_17_17_9_1_19_19_5_5_3_3_3_3_5_5_13_13_13_7_7_7_7_7_1_1_1_9_3_3_3_13_7_7_9_9_9_17_17_17_17_5_5_5_5_13_15_1_5_3_3_11_11_9_9_9_7_1_9_9_9_11_17_17_17_1_1_1_11_11_15_5_7_17_9_7_7_7_7_7_3_17_1_13_13_7_7_7_17_17_3_3_3_3_3_3_1_5_5_1_1_1_1_11_19_19_3_3_3_5_9_9_3_3_3_5_3_3_3_13_13_13_11_11_1_3_11_11_11_5_5_5_5_15_15_15_15_11_11_13_13_13_19_19_1_9_9_9_11_11_1_1_1_1_7_1_1_15_3_15_9_9_5_13_15_15_15_1_7_1_7_7_7_1_1_9_9_3_3_9_9_1_3_13_17_17_17_17_3_3_9_9_3_5_5_5_5_5_13_13_11_15_13_13_13_13_3_3_3_3_9_9_9_19_7_7_15_15_5_5_5_5_3_3_3_3_3_5_1_1_9_9_9_1_1_1_7_7_15_15_9_9_9_9_9_15_15_15_1_17_17_9_9_9_13_13_3_13_13_11_11_1_13_13_17_17_17_3_3_9_9_9_3_9_9_9_19_9_9_3_9_19_5_1_1_5_9_9_17_17_17_17_17_7_5_5_5_5_5_5_5_1_1_1_1_1_5_5_5_7_7_11_11_7</t>
+  </si>
+  <si>
+    <t>10_10_8_14_18_18_20_20_20_20_20_8_8_10_4_6_8_8_4_4_10_14_12_12_2_2_20_20_4_4_14_10_12_4_4_2_8_14_8_8_8_8_2_2_18_18_14_4_2_6_4_4_4_4_16_4_2_4_2_4_8_8_14_14_14_14_14_2_10_10_10_18_18_4_18_20_20_20_20_20_16_16_4_4_14_14_10_10_10_16_16_2_2_2_18_14_20_10_10_10_6_8_12_12_14_14_12_12_6_14_4_2_12_14_14_14_14_14_4_8_8_8_10_8_2_14_14_14_4_4_8_16_12_10_8_8_6_16_16_18_18_4_12_12_12_12_8_12_12_12_16_16_8_8_2_2_2_2_14_14_18_18_4_8_14_14_14_14_14_14_14_4_18_18_14_14_14_8_12_10_10_10_16_16_16_16_6_6_8_8_10_4_14_14_18_8_2_16_16_16_2_2_10_6_6_2_2_6_6_8_10_10_10_10_10_10_10_10_10_10_10_10_10_18_16_4_4_4_4_6_6_6_8_4_4_4_4_10_20_20_2_6_6_6_14_14_10_2_12_12_8_12_10_10_2_18_18_8_8_2_10_16_4_12_18_8_8_14_12_12_18_18_18_6_6_6_6_6_6_8_10_10_8_12_12_12_12_20_16_16_16_2_16_16_16_16_14_14_14_14_20_20_6_2_2_20_18_4_14_14_14_10_10_10_8_8_10_10_8_8_8_2_6_6_8_8_16_6_6_6_2_18_18_18_2_2_4_14_14_14_6_6_6_6_6_6_6_6_4_4_20_2_12_6_16_2_4_4_4_10_10_10_6_6_18_6_14_18_18_18_8_6_6_6_6_6_6_18_8_2_2_2_2_2_2_6_6_6_6_10_12_18_16_10_8_14_6_6_8_8_10_2_4_4_6_6_18_10_16_16_18_16_16_6_16_16_2_16_16_18_18_18_18_18_18_18_18_18_18_14_12_18_2_2_2_8_2_20_12_12_18_18_18_14_14_12_14_2_2_2_18_18_12_12_14_14_12_10_10_10_16_16_6_6_6_6_20_20_20_20_20_20_16_16_14_14_8_8_8_6_6_18_18_18_18_12_12_12_12_14_14_12_10_18_8_8_6_6_8_4</t>
+  </si>
+  <si>
+    <t>16_6_6_4_4_4_8_6_2_18_18_2_2_10_8_8_4_4_4_4_4_16_16_4_4_2_8_8_2_8_4_12_2_14_14_12_10_16_10_4_18_14_14_14_12_6_8_10_10_2_2_12_14_18_18_20_4_16_2_2_2_12_12_12_10_10_6_12_12_2_18_10_10_10_6_8_14_8_8_14_14_12_12_10_14_14_14_12_12_12_8_6_16_16_8_20_4_6_12_12_6_10_10_12_12_8_12_14_14_10_12_8_8_8_8_8_18_14_16_16_10_10_8_12_12_20_20_20_2_8_6_10_10_2_6_6_6_6_4_4_4_4_12_4_12_2_12_12_8_4_2_2_2_4_6_18_14_16_10_14_14_14_14_4_2_4_8_8_2_2_2_8_8_8_2_12_8_14_12_12_10_16_16_8_4_4_2_2_2_2_18_12_8_4_4_10_10_10_2_18_18_20_20_20_10_10_8_18_6_12_4_14_2_2_6_6_6_6_20_6_10_4_8_6_6_18_18_4_4_10_2_6_6_6_6_6_6_6_12_12_16_14_10_18_16_16_14_12_10_2_2_2_14_10_18_18_18_4_4_4_14_14_14_14_8_8_2_2_6_12_8_4_4_4_2_2_2_10_2_2_6_16_18_18_18_12_12_2_2_10_14_12_12_14_12_12_12_12_16_16_16_4_12_6_6_2_8_10_10_10_10_8_10_10_10_10_10_10_12_12_12_16_16_6_6_4_4_6_6_14_14_12_12_12_6_6_6_18_6_20_20_10_6_12_20_8_20_20_4_12_14_2_8_18_2_2_2_4_4_4_2_2_18_18_18_4_4_14_6_18_12_12_4_12_12_12_8_14_4_6_6_6_20_20_20_18_18_18_18_4_18_18_8_8_8_10_10_4_12_12_12_10_6_6_18_18_12_10_10_20_4_4_4_2_12_14_4_4_14_14_14_14_2_12_6_6_12_12_6_10_10_10_18_14_14_4_4_4_4_4_4_14_14_14_14_4_4_4_8_4_14_14_16_12_12_10_6_4_12_12_12_10_10_8_8_20_10_10_14_12_12_12_12_14_12_6_6_2_2_2_8_16_8_6_6_6_6_12_10_10_10_10_10_10_10_4_2_2_8_8</t>
+  </si>
+  <si>
+    <t>16_6_12_8_4_4_4_4_4_4_10_10_10_10_10_14_14_20_20_8_8_8_18_20_20_10_6_10_2_2_6_20_20_8_8_18_18_14_14_2_16_14_14_14_14_14_16_16_4_4_6_20_20_4_4_4_4_4_12_4_4_2_2_2_2_2_10_10_10_16_16_18_18_8_4_12_14_8_20_20_14_14_4_4_2_8_10_8_8_2_2_12_10_14_14_14_14_12_12_12_18_12_6_6_6_12_10_14_10_16_16_16_8_4_4_4_10_10_12_14_14_16_4_6_14_18_10_6_16_16_16_4_18_18_10_10_10_10_12_4_14_16_16_16_16_14_16_4_2_2_2_2_18_4_18_8_10_8_12_12_12_20_20_14_2_4_4_14_8_8_4_4_4_8_4_16_8_8_2_2_18_10_4_4_20_20_20_20_16_16_2_2_2_2_2_10_10_10_10_10_2_14_14_10_14_4_4_4_14_14_4_6_16_16_16_16_16_2_14_10_10_16_16_16_20_20_20_20_10_14_4_14_10_10_12_4_2_2_2_16_10_10_10_10_10_6_6_6_12_18_16_16_16_8_8_18_18_18_18_18_4_4_8_16_16_4_14_4_10_2_16_16_16_12_12_12_10_8_8_18_8_6_16_16_16_8_8_8_8_12_12_12_2_14_8_14_20_4_4_16_8_8_8_18_10_10_4_4_2_18_8_14_10_10_4_2_10_10_10_20_8_10_14_14_2_2_2_2_2_2_4_8_14_12_10_10_4_12_6_20_12_12_12_12_10_4_4_4_4_10_20_14_14_10_12_8_10_18_2_12_6_16_10_10_10_6_4_18_2_10_8_6_12_12_10_6_6_8_18_18_18_18_18_4_2_2_2_2_2_2_14_14_14_14_14_14_14_14_14_14_14_2_2_2_10_18_2_4_12_12_10_18_6_12_14_16_16_6_6_6_6_18_18_18_12_12_12_12_12_6_6_12_6_14_16_12_12_4_4_4_8_8_20_4_4_4_16_16_10_10_10_10_10_10_14_10_20_20_12_10_20_6_10_10_10_10_10_8_8_6_18_6_6_6_6_6_6_14_18_18_4_18_18_10_10_14_14_14_16_16_16_16_2_10_6_6_6_10_10_8</t>
+  </si>
+  <si>
+    <t>8_8_8_10_4_4_16_16_16_16_12_12_4_20_18_2_4_4_4_4_12_8_8_8_8_16_12_2_2_6_4_4_16_4_4_12_12_6_8_8_8_8_10_10_10_2_2_2_6_4_20_6_6_4_10_8_16_2_12_6_8_8_4_4_4_4_16_20_10_12_14_14_14_14_20_20_14_14_8_2_12_12_8_8_10_6_6_2_2_2_10_10_8_8_2_2_2_2_8_18_14_14_10_12_6_8_8_20_16_18_16_4_18_8_2_2_2_12_12_14_4_20_20_4_4_4_4_4_4_2_2_2_18_2_2_14_6_6_6_6_18_18_12_6_6_18_10_10_10_10_14_2_6_2_2_2_10_10_2_16_16_2_6_6_2_14_14_4_4_18_12_12_14_14_2_14_8_4_8_8_8_8_8_8_8_4_8_14_14_14_20_4_16_16_12_8_8_20_16_4_4_4_14_4_2_8_14_12_14_14_18_18_18_8_8_8_8_8_8_2_2_2_2_8_8_12_12_10_10_16_20_16_16_16_16_20_8_14_6_14_16_18_6_6_6_8_8_8_8_2_2_12_8_8_8_8_14_16_16_16_12_12_4_6_2_2_18_16_16_16_12_12_16_10_12_16_18_18_18_18_20_20_20_20_20_20_20_2_8_8_8_8_6_12_12_6_6_6_12_12_12_16_6_12_2_20_4_8_8_4_4_8_12_12_12_8_8_4_10_12_8_8_12_12_18_18_18_18_10_10_6_20_6_10_10_20_14_2_18_10_2_2_2_2_2_12_6_4_4_4_4_8_8_8_10_18_16_4_14_20_12_12_12_6_6_6_2_2_2_14_14_14_14_14_12_12_12_20_20_20_14_14_14_2_2_20_20_20_20_16_16_1_8_10_10_8_8_4_4_4_8_2_16_10_10_10_8_10_8_8_8_2_2_18_4_4_4_10_20_20_20_8_8_4_4_4_10_10_16_16_16_20_2_10_4_8_16_16_16_16_16_16_16_8_20_20_12_12_20_20_20_8_8_8_10_10_10_16_16_20_20_20_20_4_18_2_2_2_2_2_2_2_2_2_8_4_4_4_16_6_6_2_2_2_8_4_4_18_18_14_14_14_18_18_18_8_8_4_4_4</t>
+  </si>
+  <si>
+    <t>4_4_8_2_4_4_20_12_12_12_18_18_6_6_4_10_20_20_2_2_2_16_6_6_10_2_2_10_10_14_4_14_6_16_10_12_2_6_2_2_2_2_2_2_2_2_2_12_12_12_6_6_16_14_6_6_6_2_2_16_20_16_16_12_4_16_16_16_16_12_10_18_18_18_18_18_18_18_20_12_8_4_4_14_14_20_4_4_18_4_16_16_16_16_12_20_4_16_2_12_12_20_10_2_6_4_4_4_14_14_6_2_16_18_18_6_2_2_4_6_6_6_6_2_20_20_20_20_20_2_4_4_4_20_2_2_10_16_16_2_8_4_12_12_12_8_18_18_18_12_12_6_6_6_6_8_8_14_14_14_6_20_6_12_4_10_10_2_2_14_14_14_8_18_2_16_2_10_10_10_10_10_6_2_2_2_2_2_12_12_4_4_4_4_2_2_16_16_16_14_14_20_20_18_10_6_6_6_4_4_16_16_14_10_8_8_2_2_6_6_10_10_4_4_6_4_12_4_12_12_8_18_4_4_14_2_2_2_2_10_10_18_10_10_14_18_18_18_16_16_14_14_14_12_12_12_2_4_4_4_2_2_8_8_4_4_4_12_8_2_2_2_2_2_2_2_2_10_20_20_6_6_8_10_10_12_2_4_4_4_10_12_18_20_20_20_16_4_4_4_12_6_6_6_6_6_12_14_14_14_10_10_10_4_14_14_14_10_16_20_20_20_20_4_12_16_12_18_2_2_20_12_20_20_14_14_6_6_14_14_4_14_18_20_6_4_4_6_14_12_2_2_2_18_10_10_8_6_20_14_14_10_14_14_2_2_2_14_14_16_16_10_10_10_18_12_12_14_14_12_12_12_6_2_10_12_12_14_8_12_12_6_8_20_14_14_14_16_16_16_6_2_8_8_8_10_2_18_18_18_14_18_8_8_8_8_10_10_12_12_14_6_8_10_10_10_10_10_10_4_14_14_6_6_6_6_14_6_8_8_8_16_16_16_6_12_10_2_8_16_8_18_2_2_4_10_10_2_2_8_8_16_16_2_8_8_8_14_4_4_4_4_12_12_18_18_2_10_6_2_6_6_2_2_2_10_10_16_16_8_4_4_4_2_6_8_8_8_12_10</t>
+  </si>
+  <si>
+    <t>14_14_8_8_8_18_12_6_8_8_16_16_6_6_12_10_8_8_8_16_16_12_4_16_8_8_2_2_8_16_10_10_10_10_12_12_20_8_4_14_6_18_18_4_2_2_6_6_6_6_6_10_12_12_12_10_10_10_4_4_18_10_10_10_2_2_2_10_2_2_10_4_4_4_4_4_10_10_12_12_8_2_16_18_18_18_18_18_2_6_8_6_6_18_18_16_16_16_14_14_8_8_14_4_8_6_4_2_2_2_14_14_12_12_12_12_14_6_6_16_16_16_2_2_6_6_6_6_6_6_6_6_18_4_4_4_4_8_4_6_6_14_14_4_10_2_12_18_4_4_14_12_12_12_12_16_16_16_16_18_18_2_2_2_14_8_8_14_2_8_16_18_2_12_12_12_10_10_16_16_2_2_2_2_2_2_18_6_6_14_16_12_4_4_4_4_18_18_8_12_12_12_4_4_20_20_2_2_8_8_2_2_2_4_10_4_4_4_6_12_12_12_14_4_8_8_6_6_6_6_16_14_14_8_4_8_16_16_10_10_8_14_14_14_14_14_4_4_4_4_2_6_6_6_14_14_14_6_6_6_6_4_2_4_12_8_2_2_10_8_8_4_6_6_4_4_4_4_4_4_4_12_6_6_4_10_10_10_10_4_14_2_2_8_8_4_10_6_8_12_8_12_14_18_10_12_12_12_12_12_12_2_4_4_2_16_10_14_2_4_4_4_2_18_12_10_8_8_8_8_2_2_10_10_4_4_8_8_10_10_20_20_20_20_4_4_4_16_8_10_8_20_20_20_10_10_10_10_10_14_14_14_8_8_8_18_18_8_4_14_6_4_4_12_12_16_16_14_8_8_16_12_12_16_16_16_16_14_14_12_6_6_6_6_2_20_10_18_10_12_16_16_4_4_20_6_6_14_14_16_16_12_4_12_10_10_10_6_20_20_12_12_16_2_10_10_10_14_14_4_6_6_6_6_6_6_6_8_8_8_12_16_16_8_8_2_10_8_8_20_16_16_16_14_14_6_6_10_8_8_8_8_18_18_4_12_2_2_6_6_8_6_16_6_12_12_6_6_10_10_6_8_8_8_2_4_18_16_16_16_18_18_2_6_6_6_6_10_10_16</t>
+  </si>
+  <si>
+    <t>4_2_2_6_16_8_8_6_8_14_6_6_12_8_8_10_2_2_2_2_12_10_10_10_12_6_6_6_6_6_6_8_2_2_2_2_2_2_2_16_4_20_20_20_12_12_8_8_8_8_2_14_16_20_20_4_2_2_12_2_6_20_6_10_10_6_8_8_8_10_14_6_2_2_2_12_2_12_6_18_20_20_14_16_4_8_4_14_12_12_4_4_12_12_10_6_18_18_16_6_2_2_2_6_4_14_2_2_6_10_14_14_18_18_8_16_8_8_10_10_10_6_14_8_8_6_12_12_12_12_12_4_2_2_4_4_4_4_4_4_4_14_4_4_2_2_18_12_6_6_6_6_4_2_2_8_8_14_14_8_2_4_16_16_12_2_2_12_12_8_4_4_6_2_12_4_18_18_18_8_2_8_8_2_14_10_10_2_14_6_6_16_16_16_4_16_2_2_14_14_14_4_8_4_16_14_16_8_14_16_14_14_14_10_2_6_6_6_16_16_16_16_10_10_10_10_10_10_10_10_8_8_14_8_8_8_8_12_12_12_8_8_8_8_6_6_8_8_2_10_10_16_16_10_10_2_4_2_2_6_6_6_16_16_16_4_16_6_6_6_6_6_6_2_6_6_2_2_2_2_14_18_18_12_18_2_12_12_12_4_2_2_8_8_20_18_18_18_18_10_12_12_20_10_2_2_2_6_6_2_2_6_18_18_18_16_8_6_4_4_16_16_8_8_4_8_4_10_10_10_6_20_20_20_10_10_10_10_10_20_10_4_14_14_20_20_4_4_12_12_4_10_10_8_6_4_8_8_8_14_2_6_6_20_14_14_14_14_14_8_10_10_10_10_2_2_2_2_2_2_2_2_2_2_2_2_2_2_2_8_2_14_14_14_18_18_2_6_8_10_2_2_2_10_10_10_20_10_14_8_2_10_10_10_10_10_10_20_8_8_8_20_8_8_4_8_8_12_12_2_14_14_6_10_10_10_8_12_20_20_20_16_16_12_12_12_6_6_6_8_8_8_10_2_2_2_2_14_14_10_12_2_2_4_4_10_6_6_4_2_2_2_8_8_8_8_8_8_12_12_8_8_8_8_14_2_4_14_16_16_16_16_16_4_4_4_4_4_4_2</t>
+  </si>
+  <si>
+    <t>6_18_12_16_6_12_2_4_6_6_14_20_20_10_10_8_8_8_18_18_18_18_14_14_2_2_2_2_2_10_8_10_10_12_12_4_20_12_12_12_12_12_16_18_18_18_18_4_14_8_10_10_14_14_16_10_18_18_12_6_10_2_10_10_6_2_2_2_20_4_4_4_8_8_2_6_14_14_18_18_10_10_10_10_6_6_8_20_14_10_10_10_20_16_16_14_18_18_2_8_8_8_8_16_16_16_16_16_16_16_6_12_2_6_14_14_12_10_18_18_18_4_4_4_4_4_6_6_6_6_6_6_2_8_8_6_6_6_14_14_8_8_6_6_6_6_6_6_6_10_10_10_14_4_4_12_8_16_10_2_14_18_8_4_4_10_12_8_12_12_14_6_4_10_4_4_10_14_14_8_8_12_12_20_20_20_20_20_20_6_6_4_20_20_4_4_14_2_10_10_16_4_4_14_2_16_16_16_2_14_16_10_10_10_10_8_8_8_16_16_16_16_12_2_14_14_2_2_2_2_2_10_4_4_16_2_6_12_12_12_12_12_4_4_16_16_2_2_4_20_6_6_6_2_2_2_6_6_16_10_10_10_8_10_10_10_10_10_4_4_18_12_6_6_10_10_10_10_4_4_4_8_10_10_2_14_14_14_14_14_12_12_12_12_10_6_4_4_2_20_8_8_20_20_8_16_16_16_6_12_12_6_6_6_6_6_6_18_18_6_18_6_6_10_12_10_10_10_10_12_2_16_16_16_6_6_6_16_8_6_2_16_6_10_20_14_12_12_18_4_4_4_4_4_18_2_10_10_10_10_6_6_16_16_20_20_8_6_20_6_6_14_4_4_4_8_8_8_10_8_8_8_8_16_4_8_2_6_12_12_8_6_6_6_4_20_4_8_8_12_6_6_6_20_10_4_8_2_2_2_18_14_4_18_18_18_14_14_16_16_16_10_20_20_20_20_20_6_16_16_16_16_10_8_6_6_10_12_6_10_10_2_6_4_4_14_4_4_8_16_16_8_8_8_6_10_10_10_10_8_4_4_2_2_2_2_10_6_6_8_8_2_12_12_12_12_12_4_4_16_16_16_16_10_6_10_2_2_2_2_2_4_8_8_10_8_8_12_4_16</t>
+  </si>
+  <si>
+    <t>10_10_10_12_12_12_2_14_14_20_6_16_14_4_12_12_8_6_6_20_20_4_4_18_2_6_6_14_16_16_4_16_10_10_10_10_10_6_6_6_14_14_14_14_6_6_6_10_6_4_4_16_16_12_12_6_6_10_12_12_12_8_6_12_12_12_4_6_4_4_10_8_8_10_2_2_10_6_18_10_10_10_10_4_4_12_10_16_12_12_14_14_8_8_18_6_10_18_18_12_12_6_16_6_6_6_6_6_6_8_6_6_6_6_6_6_6_14_14_14_14_12_16_4_4_8_6_2_20_20_20_20_20_20_20_20_20_20_16_12_6_12_20_8_10_10_10_8_8_8_4_10_8_4_8_14_14_8_8_18_14_14_14_14_16_16_4_4_4_16_12_8_8_6_16_16_10_20_20_20_20_14_2_10_10_10_4_4_4_4_4_18_6_20_4_4_18_8_8_8_8_18_8_14_8_4_4_14_8_6_6_6_4_2_14_10_10_16_16_16_6_10_12_12_16_2_2_12_4_4_10_12_10_8_6_16_10_16_12_12_8_8_8_8_14_6_6_6_16_16_2_2_2_2_10_2_18_6_6_2_12_6_4_4_4_10_10_2_12_6_14_14_14_16_8_4_16_10_8_8_20_20_20_20_20_18_20_20_20_20_20_4_4_18_14_16_16_16_20_14_18_6_6_6_8_10_10_10_10_14_14_14_18_18_14_18_4_4_14_2_2_12_4_4_4_2_2_2_2_4_14_8_10_10_10_14_6_6_20_20_4_12_12_6_6_2_2_2_2_20_20_14_14_12_12_12_14_12_12_10_12_20_4_4_18_10_6_12_12_6_6_4_10_6_6_6_6_6_14_4_8_8_4_10_20_20_20_20_2_2_10_10_12_12_8_8_8_18_2_2_4_4_10_16_18_12_16_10_10_10_10_10_10_20_4_2_4_14_14_14_18_18_10_10_10_18_20_20_16_16_8_8_20_16_6_6_6_14_14_14_14_10_4_4_4_2_6_18_8_8_8_12_14_12_16_10_10_14_14_18_16_16_10_10_2_12_10_10_10_10_18_18_18_18_8_6_18_18_18_18_20_20_20_8_20_2_6_6_18_8_4_12_8_8_4_2_4_8_8_2</t>
+  </si>
+  <si>
+    <t>18_12_12_12_12_2_2_6_2_2_18_18_18_18_4_4_6_6_2_2_2_16_16_16_6_6_8_2_2_20_2_2_2_2_12_6_6_4_4_2_6_6_6_6_18_10_10_4_2_4_4_8_8_10_8_8_8_16_16_16_18_4_4_8_14_4_4_6_6_6_12_12_8_6_6_6_4_4_4_8_8_14_14_14_14_14_14_14_2_6_4_10_10_10_10_10_10_8_8_8_8_4_10_10_10_2_10_14_14_16_2_2_6_6_12_14_14_12_14_8_8_8_6_6_6_6_12_6_6_8_2_2_2_2_4_4_18_12_2_8_4_4_10_12_16_2_2_2_2_2_2_2_18_18_18_8_12_14_20_20_16_18_12_18_18_4_2_10_10_10_8_2_2_2_14_14_14_18_18_10_12_16_16_16_16_16_10_2_8_16_14_14_12_12_18_18_18_18_16_16_4_4_12_4_6_6_12_12_14_12_12_12_4_4_4_4_4_4_4_4_10_12_12_18_4_2_2_6_6_6_6_16_16_16_16_2_2_2_12_4_4_4_12_12_12_4_4_4_4_18_14_2_2_10_6_6_6_4_4_4_2_2_2_18_4_10_10_10_8_8_4_10_10_12_8_8_16_18_18_2_2_2_6_6_6_8_2_2_2_16_16_16_16_12_20_20_4_4_4_8_4_4_4_4_14_10_6_16_18_18_18_18_10_4_4_4_4_10_10_4_4_8_8_6_8_8_2_4_4_6_4_4_8_8_4_6_14_14_10_10_8_16_12_12_20_20_10_18_12_16_18_18_18_18_18_18_18_18_10_10_10_10_10_4_4_4_4_4_4_4_4_8_12_6_6_10_4_20_20_20_20_8_4_4_4_10_18_16_16_16_12_12_12_4_8_14_8_14_12_12_12_2_2_2_8_16_16_14_10_12_12_12_6_6_12_12_16_16_20_6_8_8_8_6_4_4_4_12_12_12_12_12_8_2_2_2_2_2_2_6_6_16_16_12_2_8_8_8_4_4_8_8_8_6_2_4_4_14_18_18_2_20_10_10_12_12_6_6_6_6_12_16_16_14_14_14_8_8_2_12_12_10_10_10_10_10_18_10_2_2_4_4_10_10_16_16_16_16_16_18</t>
+  </si>
+  <si>
+    <t>3_3_2_4_5_3_9_2_2_3_1_2_2_9_5_10_10_2_1_5_2_1_8_8_6_4_4_5_9_3_7_2_4_7_9_3_3_1_4_2_1_3_9_3_1_1_1_3_2_1_6_9_2_9_6_5_6_1_5_8_2_3_8_1_9_3_4_8_4_1_4_5_3_3_2_5_6_10_2_2_6_3_5_8_3_1_1_3_5_9_4_2_1_1_4_5_2_2_7_4_3_9_1_1_2_6_1_10_4_10_10_5_6_1_3_3_5_3_8_9_4_2_6_3_5_3_5_5_6_4_2_2_8_1_8_1_5_4_3_1_1_1_2_2_7_9_8_5_5_5_6_4_4_3_1_1_3_4_1_2_5_4_1_3_6_6_3_2_4_6_1_6_3_2_8_4_4_1_4_7_7_1_4_3_3_10_2_4_5_2_1_7_1_3_2_4_4_8_8_2_9_6_5_2_1_1_9_6_6_5_10_7_1_2_4_2_2_8_7_1_2_5_4_2_2_5_4_6_2_1_2_3_6_2_5_1_2_3_3_7_3_9_3_5_1_2_9_9_3_8_8_7_4_9_9_4_8_3_4_5_5_4_1_4_3_1_4_1_10_3_3_7_4_3_4_6_9_6_4_4_3_7_7_7_6_7_8_8_8_2_2_3_3_3_5_6_10_1_1_3_2_2_5_5_4_4_3_3_8_2_8_7_8_1_7_9_6_2_6_3_2_2_5_1_8_1_6_1_3_9_10_9_9_2_4_2_5_5_6_6_5_1_1_2_8_8_6_10_9_6_5_9_1_5_4_4_5_5_1_3_3_7_1_4_1_6_5_8_4_2_6_7_5_7_7_6_6_4_3_2_5_8_4_2_3_1_3_8_1_2_9_2_8_4_7_10_3_5_6_2_2_5_2_2_1_5_6_1_6_6_6_10_10_1_5_5_5_4_4_5_7_7_3_2_1_5_3_2_8_1_6_5_2_2_6_8_5_9_7_5_5_3_8_2_1_6_5_6_4_1_4_5_5_10_2_1_6_5_2_2_1_1_3_3_5_5_5_3_4_1_5_7_8_5_4_1_10_8_4_4_10_10_5_4_2_3_7_6_6_9_5_4_4_3_8_6_8_3_1_1</t>
+  </si>
+  <si>
+    <t>4_2_4_1_6_2_5_3_9_2_5_7_9_7_5_1_5_7_2_4_3_3_4_1_3_2_2_9_1_5_3_8_2_7_2_2_6_8_6_4_6_6_3_1_2_1_10_1_5_1_3_5_2_5_10_6_4_7_6_8_5_10_6_4_9_8_2_5_8_8_2_6_3_4_8_7_7_9_8_7_1_10_4_1_3_7_5_6_3_2_7_8_2_2_8_6_8_7_5_9_4_4_2_5_1_1_1_8_5_9_6_4_4_5_3_3_6_6_1_7_1_9_1_6_8_4_9_1_5_5_7_8_10_7_4_5_10_5_4_4_9_9_6_10_4_4_2_3_1_5_3_2_2_6_5_1_6_7_6_7_2_4_1_4_6_4_6_4_3_2_1_1_5_3_1_4_8_8_1_8_4_5_2_2_7_4_8_4_4_4_6_2_9_4_4_9_2_2_7_10_3_1_7_2_3_2_4_1_8_5_5_6_3_6_1_3_8_8_2_1_6_6_9_2_9_4_1_1_6_4_4_2_8_1_8_7_5_1_2_9_3_1_2_6_7_6_1_1_3_9_8_1_3_2_4_2_6_3_1_4_5_2_9_6_5_6_4_2_4_4_7_1_7_10_6_10_7_8_1_2_10_6_1_8_1_3_2_8_1_9_2_5_3_8_10_4_10_4_4_8_9_2_4_2_6_7_5_5_7_7_6_3_2_1_7_10_5_1_2_4_1_8_9_6_6_8_1_8_1_5_8_5_9_5_5_7_5_4_2_6_1_4_1_1_9_5_2_6_2_6_2_6_3_6_1_2_2_6_4_10_3_4_5_1_1_9_3_5_6_9_4_2_2_3_8_8_4_5_2_2_5_3_6_6_1_2_8_7_8_6_5_1_1_5_4_5_7_8_9_7_6_1_1_2_2_1_6_2_2_7_3_4_9_2_3_4_4_1_2_3_4_7_4_5_4_1_9_4_1_5_6_2_3_1_8_2_4_2_4_1_5_7_6_7_3_1_2_4_7_2_6_3_6_5_4_4_2_8_6_3_7_8_1_10_7_6_4_2_8_3_8_2_6_6_7_1_1_1_3_3_3_2_6_1_3_1_7_4_6_4_2_6_3_3_8_8_8_5_2_2</t>
+  </si>
+  <si>
+    <t>5_5_2_1_1_2_4_1_6_3_2_4_5_8_4_1_1_2_10_1_1_4_7_3_2_4_4_3_1_9_2_8_3_5_6_8_9_4_4_4_4_4_8_3_7_4_1_4_4_4_6_4_7_6_9_5_1_8_4_1_1_7_7_3_3_10_1_1_3_6_6_2_2_6_3_9_7_1_2_5_1_6_9_4_3_3_4_3_4_1_9_2_8_1_3_6_8_3_9_3_3_6_3_1_5_2_4_1_1_6_3_3_8_5_8_4_5_3_2_9_9_4_2_1_3_9_5_3_3_3_9_7_9_5_5_9_9_4_7_7_5_2_5_4_9_5_4_9_7_1_1_1_2_5_7_5_4_10_5_5_1_6_4_5_1_5_6_3_9_1_7_4_4_4_3_3_1_4_8_1_4_4_1_2_2_6_6_1_1_3_3_10_4_7_7_3_1_6_10_2_6_6_2_7_7_3_3_9_3_2_7_5_8_1_1_4_1_1_8_4_6_3_3_4_4_3_7_7_4_3_3_7_3_2_5_3_9_10_4_3_6_2_2_6_6_7_8_2_3_2_4_1_3_3_1_3_8_2_1_2_6_8_3_3_3_3_10_1_2_5_4_10_5_4_3_7_1_4_5_2_2_2_10_7_9_3_3_3_6_4_4_4_4_7_3_4_8_3_3_4_4_1_3_5_6_3_3_2_1_5_8_2_2_1_3_10_6_1_2_5_1_3_5_7_5_6_1_6_4_3_1_2_7_6_3_1_5_8_2_2_2_5_8_1_5_6_6_1_4_2_9_6_9_3_5_8_10_5_5_2_7_4_4_7_7_7_5_5_5_4_10_6_2_5_3_3_2_5_2_5_2_2_6_6_7_2_3_1_1_1_2_5_8_5_2_2_1_1_1_1_1_5_7_2_1_6_6_1_2_4_7_9_10_8_8_8_8_1_1_2_5_4_7_2_1_7_4_3_4_5_2_2_1_3_4_4_4_2_1_6_6_6_5_3_5_2_2_6_6_2_7_5_1_6_3_10_1_7_1_3_3_9_1_2_3_2_3_3_8_3_6_1_1_7_2_1_5_5_5_1_1_5_2_3_1_2_9_9_6_4_4_1_1_5_2_1_9_1_1_2</t>
+  </si>
+  <si>
+    <t>8_2_1_2_1_4_4_1_3_8_1_1_6_3_9_8_2_9_6_1_7_9_1_7_2_4_3_1_5_5_1_8_7_2_6_3_2_3_3_2_1_3_4_9_4_1_4_1_8_4_4_1_7_1_9_2_5_9_3_8_4_9_2_7_3_4_1_1_5_2_5_9_1_10_5_5_4_7_9_5_9_3_6_7_3_2_5_4_8_4_3_8_5_2_3_5_8_6_10_6_10_3_2_6_3_6_2_6_8_2_8_5_9_2_6_4_4_6_8_2_5_10_2_2_5_1_1_7_2_2_5_9_5_2_6_3_4_1_3_1_2_4_8_9_8_9_3_2_6_3_2_1_8_5_9_4_2_8_2_1_7_8_7_2_1_2_9_2_1_1_2_4_10_6_4_3_5_8_2_4_5_5_7_6_5_1_5_6_4_5_8_2_6_6_10_4_9_3_8_3_2_1_9_3_3_4_9_1_1_2_7_8_7_2_2_4_2_6_8_2_8_4_2_4_1_7_2_6_1_7_2_9_1_4_5_9_9_7_6_9_3_5_4_5_1_2_6_6_4_5_5_6_7_5_7_10_6_5_3_7_1_3_1_9_7_5_4_2_6_1_4_5_3_2_10_4_7_6_8_8_5_4_3_3_4_9_5_1_6_7_2_9_2_5_6_9_6_8_5_6_1_5_8_2_2_9_9_4_2_3_9_1_1_1_7_2_1_1_10_6_9_3_1_8_5_6_3_9_9_2_5_4_4_1_5_6_7_5_5_2_6_3_2_2_1_7_5_7_3_6_1_1_2_9_7_3_6_2_8_7_7_4_2_4_2_1_6_6_3_1_4_9_5_1_2_8_5_1_5_4_1_3_1_5_4_1_2_9_2_6_7_7_1_4_3_3_1_4_4_5_3_8_3_4_10_6_6_7_5_4_4_1_1_3_8_5_2_2_7_2_4_10_4_2_1_6_2_1_1_3_2_5_8_2_4_5_3_1_5_4_10_3_6_6_2_9_2_2_8_8_2_9_7_2_8_6_6_2_3_5_6_9_3_3_8_8_9_1_3_6_2_1_3_3_3_4_3_8_4_9_2_1_4_3_5_3_2_7_3_10_3_4_6_6_1_3_7_2_3_1</t>
+  </si>
+  <si>
+    <t>3_1_1_6_8_8_5_10_1_1_5_5_2_6_9_9_2_2_2_2_9_8_2_2_5_10_2_3_5_8_2_9_4_4_8_8_4_3_3_3_1_5_5_7_10_10_3_1_3_2_2_1_1_2_3_3_4_2_2_3_5_5_4_7_4_5_5_5_3_1_1_6_3_1_5_2_7_7_7_3_7_1_2_4_1_3_1_5_6_4_3_2_6_2_9_9_4_5_3_10_1_1_7_5_8_4_3_10_9_1_3_4_5_2_7_2_7_2_4_3_1_9_5_3_2_6_1_8_3_2_6_2_8_6_3_3_5_5_5_3_8_5_4_9_2_1_1_1_1_6_8_3_6_5_3_8_6_2_3_7_5_8_7_4_4_4_3_6_6_4_4_8_2_7_6_6_3_8_8_8_1_1_5_2_3_3_5_2_8_8_7_1_1_4_3_2_1_1_2_1_6_2_7_4_10_7_7_6_1_9_6_5_5_4_7_1_7_8_7_1_7_2_1_2_4_8_3_8_8_6_2_2_2_4_2_1_6_1_9_6_6_6_2_6_2_6_4_5_8_8_5_3_3_4_3_5_4_8_1_1_3_5_2_9_6_1_7_1_1_8_8_8_8_5_5_1_8_4_5_4_3_3_2_8_2_7_4_8_2_5_1_9_4_4_6_1_3_1_4_9_5_1_4_6_3_6_7_2_4_8_4_9_2_2_3_5_5_5_9_8_4_1_2_7_4_10_1_5_1_7_7_8_4_9_6_2_2_4_8_2_5_5_2_6_6_7_9_1_1_1_5_2_8_5_6_1_6_2_2_2_3_3_8_6_2_3_3_1_6_2_5_3_9_3_3_3_1_2_8_8_2_6_1_6_2_2_3_4_4_5_5_5_2_8_7_7_1_4_9_8_3_4_10_1_5_5_7_7_3_10_10_10_3_4_6_3_2_1_2_7_1_1_5_2_4_4_3_2_8_10_3_6_2_4_3_2_6_1_6_1_4_2_5_1_7_7_2_6_6_1_1_1_8_5_3_2_1_3_6_6_4_5_6_1_2_5_4_4_6_6_6_2_4_2_8_4_1_4_1_6_5_6_6_6_2_3_6_4_5_1_1_2_4_8_8_4_3_2_5_1</t>
+  </si>
+  <si>
+    <t>4_4_6_5_2_4_3_7_1_1_6_4_1_9_1_4_4_5_5_1_6_5_2_3_7_5_2_6_4_2_8_3_1_5_5_3_3_8_1_1_3_6_6_7_3_6_8_1_2_9_8_2_4_4_3_10_6_6_8_6_5_4_5_6_1_7_4_6_5_5_9_2_3_6_2_4_9_9_6_9_5_3_8_4_5_8_3_2_1_9_4_2_2_5_3_6_10_7_5_6_2_3_5_2_4_6_1_1_8_2_4_4_6_2_8_2_10_3_1_8_2_2_3_1_3_2_3_5_10_6_6_6_5_2_3_2_4_4_5_2_3_7_9_3_8_4_5_4_1_6_6_4_1_1_6_4_4_2_4_6_8_8_6_5_4_4_8_2_6_2_9_7_8_7_5_9_4_9_2_4_4_2_7_4_2_4_7_9_2_2_2_6_1_3_3_4_10_6_8_5_3_7_3_4_5_3_8_9_6_2_1_3_5_3_4_3_2_4_3_3_3_3_7_5_2_4_5_9_6_1_2_2_2_6_1_2_1_1_8_3_6_1_1_3_4_4_5_4_3_3_10_6_6_5_9_5_1_4_2_10_6_3_5_8_3_6_1_3_8_3_1_7_7_9_7_6_2_2_5_2_1_9_6_7_5_1_8_4_5_6_8_1_3_2_6_3_2_9_3_6_6_1_7_1_6_1_4_8_2_5_1_5_1_1_2_5_3_2_9_6_2_6_1_2_2_1_2_2_4_7_2_5_2_8_10_1_5_3_3_6_9_4_2_1_10_6_2_7_9_7_8_6_3_1_4_1_10_7_9_1_3_1_4_8_1_2_4_5_7_2_3_7_1_4_3_9_4_6_1_5_7_2_9_2_3_8_5_5_2_5_6_8_6_9_7_4_7_2_2_2_9_3_8_8_4_7_5_3_3_2_2_5_2_4_4_3_2_1_5_9_7_10_7_6_6_3_3_2_8_6_1_1_9_1_6_4_1_1_2_2_3_7_8_5_10_6_8_3_2_6_4_8_2_3_4_2_5_4_2_3_3_10_3_6_4_1_4_1_9_10_5_5_5_9_7_9_1_10_4_8_3_2_9_2_10_1_4_2_3_5_4_8_1_1_2_3_1_6_4_3</t>
+  </si>
+  <si>
+    <t>2_3_3_5_8_1_1_7_6_7_5_5_2_10_8_4_5_8_8_6_3_3_4_5_5_7_1_2_2_2_2_1_3_6_1_1_1_9_9_7_4_4_4_3_3_5_2_9_2_2_3_6_3_7_7_5_7_4_6_9_4_6_1_2_9_1_1_2_4_9_5_3_2_2_6_3_3_1_5_1_3_4_8_5_3_6_5_7_7_3_6_6_4_4_4_2_2_4_5_3_1_8_8_2_5_8_5_4_9_1_7_1_8_1_1_1_4_4_8_4_7_4_2_6_2_9_2_5_5_2_2_5_3_1_2_7_7_4_4_5_5_6_6_6_6_1_6_6_2_2_9_4_8_1_1_1_4_8_7_6_4_6_6_3_8_3_1_1_7_6_2_4_1_8_8_3_2_10_5_3_4_1_2_4_4_3_3_8_8_8_8_1_3_3_6_10_10_8_6_1_4_1_10_8_4_10_10_10_2_9_6_5_4_4_10_1_8_6_7_7_7_4_9_7_6_4_5_2_1_1_3_1_9_1_2_4_4_2_1_7_2_6_5_1_1_2_4_4_3_5_2_2_10_2_2_3_3_8_2_2_2_2_6_9_7_4_4_6_6_6_9_9_4_6_5_5_5_1_6_6_6_5_7_1_7_7_1_1_1_8_3_2_7_4_3_1_1_5_5_2_6_6_3_1_4_2_7_1_1_3_4_5_6_2_6_1_3_3_4_2_2_7_1_4_3_5_5_9_6_1_1_7_7_9_2_4_2_6_2_5_7_9_9_9_4_5_7_8_4_5_4_2_2_2_6_3_7_5_2_6_8_4_2_1_6_8_2_4_1_5_1_9_3_5_6_5_3_6_2_7_10_4_3_8_3_5_1_5_5_1_3_3_3_6_2_7_2_3_3_5_5_2_5_3_2_5_5_5_6_5_7_1_3_1_6_8_8_2_6_4_10_8_7_7_7_10_3_4_3_3_6_6_3_8_6_10_2_6_1_3_6_8_7_5_4_2_9_3_9_3_2_3_1_1_8_6_6_10_10_1_1_7_4_4_1_9_1_8_10_1_9_10_1_4_4_4_8_6_3_3_9_9_3_6_1_2_8_8_5_4_7_3_1_2_3_1_7_3_7_8</t>
+  </si>
+  <si>
+    <t>3_6_8_5_6_4_3_3_8_6_4_5_1_5_4_1_3_10_4_6_4_1_3_2_6_1_4_6_10_6_8_7_1_7_7_4_2_4_10_3_2_8_6_2_5_3_8_1_3_4_6_4_8_1_9_1_2_7_9_2_6_5_2_7_1_7_8_1_8_8_4_5_5_1_7_7_7_4_3_1_4_5_8_8_3_2_5_1_4_8_10_7_5_6_6_1_4_2_2_5_6_6_4_7_6_2_7_1_1_5_6_1_5_7_1_10_7_5_2_1_7_4_8_2_7_8_3_3_4_1_3_6_5_7_9_7_8_3_5_8_8_6_4_3_5_6_9_8_4_7_2_6_10_7_6_1_9_3_1_7_3_1_9_9_2_6_6_1_4_5_3_6_6_3_6_2_5_4_4_8_5_7_2_3_3_10_7_10_7_6_2_1_8_5_3_1_9_6_3_2_1_6_7_4_4_7_3_5_6_1_4_3_2_1_5_5_9_8_9_7_2_5_4_4_3_4_1_1_2_2_6_8_4_3_9_3_3_6_9_5_4_6_5_7_7_2_8_2_9_3_2_1_5_6_3_4_4_2_8_7_2_5_9_9_2_7_5_6_1_3_6_4_7_1_8_6_9_2_5_1_4_8_10_4_1_1_3_2_6_1_1_5_10_7_6_8_5_2_4_7_9_4_2_5_4_2_5_4_3_6_6_5_7_7_8_3_3_8_1_8_5_2_6_7_9_6_7_3_4_2_7_3_5_3_5_9_2_2_4_6_3_1_1_9_5_7_5_9_3_1_1_2_2_5_1_2_4_3_5_9_2_9_3_7_1_8_6_1_2_7_6_1_1_4_10_7_3_3_2_10_5_1_1_7_1_4_2_8_4_1_2_7_4_7_1_1_5_9_8_1_4_5_2_10_6_1_9_7_8_6_6_3_5_4_4_8_3_3_2_2_9_1_2_7_9_2_7_1_1_1_9_9_5_3_3_8_7_5_6_2_9_2_2_3_4_9_3_2_9_8_5_9_7_1_6_7_3_3_7_1_2_5_2_2_7_4_9_3_6_5_4_5_5_3_8_4_6_1_2_1_10_4_2_4_3_2_1_3_3_2_9_2_8_7_5_8_7_7_3_7</t>
+  </si>
+  <si>
+    <t>1_6_6_6_4_6_6_6_6_3_4_3_8_8_2_7_7_6_8_1_2_5_3_6_5_5_5_1_4_2_3_2_3_3_1_8_4_4_6_3_5_8_8_7_3_3_3_4_4_2_6_8_6_5_2_2_3_7_8_6_1_4_9_6_5_4_1_4_1_5_3_3_3_6_2_2_6_5_1_3_5_1_6_7_4_9_3_3_9_4_4_6_4_4_5_4_4_7_1_5_5_5_1_4_4_5_9_5_2_8_8_4_6_5_4_10_5_3_8_5_2_2_7_6_3_2_2_5_2_5_1_3_2_3_3_2_3_1_1_1_5_9_4_6_2_4_3_2_7_7_3_6_1_2_9_7_3_5_4_6_1_2_2_2_2_5_6_8_1_10_3_3_7_7_7_2_8_4_2_3_3_7_4_2_8_3_4_4_1_1_2_4_5_1_2_2_6_9_3_3_3_1_5_2_3_4_10_8_3_2_3_2_1_5_5_7_3_1_1_2_2_7_7_10_1_2_3_1_1_2_3_2_6_8_1_9_1_2_7_3_7_2_9_6_5_1_2_2_1_1_1_4_2_3_7_4_3_1_4_1_3_3_3_1_5_1_1_5_2_2_1_10_2_1_2_4_7_4_7_1_3_1_10_6_6_6_4_4_3_3_1_3_4_4_4_2_1_5_1_4_2_2_1_4_2_5_1_2_6_9_1_1_3_1_9_9_8_7_2_5_1_2_5_5_2_4_7_4_6_4_8_2_3_1_1_5_4_6_1_8_7_3_3_2_2_4_1_7_1_3_7_1_6_8_7_8_4_9_5_5_1_1_6_2_3_9_8_2_4_6_9_1_1_8_6_1_9_2_9_6_2_4_6_7_7_2_1_8_4_3_2_9_5_5_5_4_9_8_1_1_1_1_4_1_7_2_6_1_10_3_5_1_7_5_2_4_2_1_2_1_10_5_1_8_2_1_1_5_1_6_7_7_8_2_3_3_2_5_1_4_8_7_2_5_9_2_2_5_2_8_8_1_2_4_2_5_3_4_3_3_1_6_1_3_5_1_1_8_5_8_4_3_3_3_9_8_5_5_6_2_3_8_3_3_9_8_2_3_4_1_5_4_1_5_3_4_3_9_1_1</t>
+  </si>
+  <si>
+    <t>2_1_6_2_2_2_2_1_9_6_2_8_7_9_5_1_3_4_5_3_4_7_5_2_6_4_2_1_4_8_6_2_7_7_5_7_9_7_4_8_6_5_2_3_10_5_1_4_9_3_10_4_7_9_2_4_3_7_1_7_4_5_6_10_6_10_7_10_1_1_6_6_2_1_3_2_1_5_2_10_5_5_7_10_6_3_4_2_2_6_3_6_9_7_2_3_8_5_2_2_1_4_3_6_5_4_8_2_7_6_10_7_5_2_9_6_4_2_1_5_4_8_2_6_4_4_3_1_3_8_6_2_5_7_4_2_3_8_4_8_1_1_8_7_2_6_4_3_5_1_4_7_8_5_9_2_3_5_9_7_7_1_3_7_8_5_1_9_6_6_2_7_8_2_3_2_7_5_2_4_2_8_7_2_7_4_8_1_4_1_2_1_4_2_4_2_2_5_6_1_5_7_5_4_5_4_1_3_4_3_3_7_1_6_4_2_6_4_9_5_8_8_5_8_5_2_2_5_7_7_8_8_1_8_9_1_6_3_3_3_1_3_4_7_1_3_5_4_5_2_2_4_3_2_1_9_3_1_4_1_8_3_5_5_8_3_3_10_1_2_3_3_9_7_2_5_8_5_4_4_9_1_1_5_4_3_4_1_8_9_4_5_1_2_2_4_1_8_7_6_1_4_7_6_3_3_3_9_5_1_6_3_4_5_3_1_4_7_9_2_2_7_9_5_2_6_3_6_5_6_2_2_4_2_5_9_4_1_9_4_4_6_3_1_5_4_6_6_2_10_7_5_4_6_9_5_3_6_9_6_7_4_7_3_8_3_6_4_6_2_9_6_10_4_8_1_8_9_7_5_7_2_10_1_8_2_5_8_2_6_9_3_5_1_3_4_5_8_7_10_3_8_2_2_2_5_2_8_2_8_4_5_2_3_3_6_8_1_2_7_4_1_2_1_8_4_3_7_7_1_3_5_1_1_7_7_3_5_8_2_2_2_1_5_3_9_3_1_7_4_1_10_7_6_2_8_7_4_1_9_2_7_2_6_4_1_5_3_1_8_4_1_3_6_9_1_4_1_9_3_2_2_4_4_6_3_1_2_1_6_1_7_7_5_8_4_5_1_8_7</t>
+  </si>
+  <si>
+    <t>6_4_4_3_2_2_1_3_3_1_1_2_6_3_3_3_4_3_1_1_7_1_2_7_2_3_2_2_2_1_4_3_3_2_2_6_3_5_1_7_6_6_4_8_6_6_6_7_2_2_1_5_8_5_1_5_5_5_5_7_5_6_7_3_6_2_3_6_6_1_1_1_5_5_5_3_4_3_2_2_3_3_2_2_5_1_4_1_5_1_4_1_2_7_1_4_3_5_2_2_1_2_1_4_5_3_2_3_3_3_1_1_2_2_5_2_2_2_3_5_3_6_6_2_1_2_2_1_2_5_3_8_2_2_3_7_3_8_1_3_3_2_3_6_6_8_6_4_4_2_4_4_2_6_3_4_4_2_5_1_6_1_8_2_7_3_8_1_1_2_3_7_5_4_4_6_4_1_3_2_2_3_3_4_4_1_1_5_1_1_1_4_2_8_5_3_3_3_1_2_2_7_3_2_1_1_1_1_7_7_1_4_8_2_8_1_8_3_6_3_6_6_1_1_2_2_2_2_1_2_2_4_4_2_2_2_8_3_8_6_6_1_1_2_1_6_1_4_2_1_7_6_1_4_3_5_7_1_3_4_4_4_3_3_1_1_1_1_2_4_4_7_5_6_4_2_1_6_6_3_1_3_1_3_5_4_2_4_1_1_2_2_3_6_2_2_2_2_8_4_7_6_3_3_7_1_1_2_1_1_2_2_8_2_2_1_3_1_2_7_3_2_7_3_3_1_1_4_2_4_2_2_8_4_3_7_3_7_3_3_6_6_2_2_8_3_1_7_1_3_6_3_2_2_2_2_3_3_5_1_1_4_8_5_4_7_2_5_2_6_2_1_4_3_3_5_3_2_3_3_4_5_7_7_4_4_2_5_3_6_1_8_5_6_1_2_3_5_3_1_5_2_5_8_3_2_7_4_6_3_1_1_6_1_4_4_4_1_2_2_7_2_1_5_8_4_8_3_6_4_1_2_7_3_6_3_3_6_8_5_1_5_4_2_3_6_7_2_2_7_4_4_4_2_3_2_7_5_1_1_3_1_8_7_3_5_2_7_1_1_7_1_1_1_8_1_5_6_3_1_7_7_7_1_1_6_2_3_3_8_8_2_4_3_3_4_4_3_2_1</t>
+  </si>
+  <si>
+    <t>6_6_2_4_1_1_7_3_2_4_1_4_9_6_4_8_9_6_3_7_9_9_8_1_7_10_5_10_3_6_1_3_5_3_2_5_1_5_5_6_3_8_6_5_4_3_6_8_3_2_7_1_2_8_10_2_5_9_2_8_5_6_3_6_10_4_5_4_5_7_2_10_7_6_4_3_3_3_5_2_5_1_5_8_3_1_1_5_4_9_9_2_6_2_8_4_6_4_2_3_1_9_1_7_4_6_6_9_2_7_3_5_7_2_3_10_1_4_7_2_1_9_1_8_1_2_2_4_3_5_1_1_7_2_3_4_5_6_10_5_3_5_3_9_7_9_6_1_3_7_5_6_1_1_4_9_8_6_5_1_9_7_1_2_4_3_9_1_1_7_5_5_2_6_9_3_2_3_9_1_10_6_4_3_7_6_6_1_1_4_1_3_4_6_8_1_5_5_7_9_6_1_9_3_7_2_3_1_1_5_6_1_6_2_3_7_1_2_9_4_9_9_8_8_8_6_8_4_2_3_2_4_3_7_6_1_2_4_6_5_9_2_2_6_2_3_5_6_6_5_10_7_8_5_8_2_5_3_1_7_4_1_6_2_7_2_9_9_9_3_5_2_5_2_9_2_1_6_2_3_5_5_10_2_2_2_7_9_4_4_9_4_8_2_5_3_7_5_6_8_5_2_10_5_4_6_3_9_1_6_2_6_3_7_8_6_1_8_3_6_5_7_5_4_2_8_3_8_4_1_7_2_9_3_6_6_3_8_6_7_1_2_3_8_3_1_7_4_9_4_8_2_2_1_9_4_1_9_9_3_1_1_9_9_10_5_2_1_5_2_7_2_5_1_8_2_2_6_6_9_6_8_2_3_6_2_3_4_4_10_2_6_4_10_1_4_3_2_9_4_1_9_6_4_7_5_9_6_3_8_4_7_2_4_5_2_1_2_4_8_4_8_6_1_7_5_1_1_5_1_8_8_4_7_4_6_1_2_6_3_4_10_6_3_1_5_7_3_9_1_1_10_6_7_6_3_5_7_8_5_4_2_4_10_5_3_2_8_8_3_7_7_9_5_3_6_9_2_2_2_3_7_1_3_3_2_6_2_6_1_3_3_2_1_1_9_1_5_4_9</t>
+  </si>
+  <si>
+    <t>1_2_4_1_6_3_5_4_4_6_2_5_3_6_3_3_5_3_1_2_2_6_2_1_3_3_3_3_6_5_7_2_4_6_4_6_5_2_2_6_2_1_5_4_2_2_3_7_7_1_1_3_6_4_4_2_1_4_8_7_1_3_6_7_3_2_3_7_1_4_3_8_5_3_7_5_7_2_2_7_8_4_7_7_7_3_3_4_3_3_4_6_1_3_3_5_6_1_1_8_1_7_8_2_2_2_1_5_3_3_8_4_5_2_4_4_7_7_7_2_2_4_3_2_5_1_1_2_2_1_1_5_5_5_4_8_7_3_7_5_4_1_2_3_1_5_5_2_4_8_8_3_3_1_1_4_4_5_4_3_5_4_4_2_2_2_4_8_2_1_2_7_2_1_3_2_2_3_1_3_6_4_4_4_6_1_2_1_1_2_2_3_6_6_3_4_4_4_2_2_2_1_1_5_3_5_1_2_2_1_1_7_3_6_8_1_7_2_4_1_5_5_2_1_7_1_8_3_3_3_4_4_4_2_2_4_4_4_1_2_2_1_5_3_6_8_4_3_8_7_7_7_3_1_6_5_5_1_1_5_3_2_5_7_8_5_3_6_3_3_5_3_3_3_3_4_4_2_2_6_7_1_5_1_3_2_2_5_5_5_3_1_1_7_4_7_1_2_2_8_3_5_1_7_1_5_7_7_2_4_2_7_7_4_1_2_2_3_8_7_8_8_6_4_5_1_6_3_1_1_8_7_6_2_2_7_7_5_3_4_1_4_1_6_5_7_3_4_1_6_3_8_8_4_4_4_7_3_3_2_6_1_8_5_5_4_3_1_1_3_1_3_5_8_6_1_2_5_2_1_8_8_3_4_1_6_7_3_8_3_3_4_4_4_4_4_2_1_3_5_3_1_1_7_1_1_2_6_7_1_6_5_3_2_4_4_4_4_5_3_7_2_4_2_2_2_6_6_1_3_6_1_4_4_4_4_7_4_1_4_3_3_2_7_1_5_5_1_1_6_3_1_2_2_2_7_2_4_5_3_3_3_1_1_1_4_3_2_4_1_7_7_3_2_3_7_3_2_5_2_7_7_3_1_1_4_2_4_3_2_8_5_1_7_2_4_8_3_1_1</t>
+  </si>
+  <si>
+    <t>5_2_2_6_8_1_2_1_2_4_4_2_2_8_4_2_5_1_2_7_3_7_5_7_1_1_2_6_4_2_7_3_5_7_7_1_5_5_1_2_4_3_7_1_4_1_2_2_8_1_1_6_6_6_4_5_3_8_2_4_4_8_8_4_9_7_7_7_9_2_5_3_6_4_8_6_1_9_3_2_9_6_7_9_6_9_3_3_1_7_7_5_6_6_8_2_5_2_2_4_5_9_8_10_6_6_1_8_1_3_4_9_7_7_1_8_8_5_3_7_2_2_7_6_7_4_2_4_4_2_7_6_5_6_4_6_5_2_8_7_5_4_2_2_7_5_3_5_3_7_1_4_5_1_7_5_6_5_3_7_8_4_7_5_1_2_2_2_4_5_9_3_4_3_8_7_8_3_2_6_2_3_2_1_1_2_1_9_4_2_1_3_1_5_9_6_2_2_6_7_1_6_3_8_5_1_10_3_5_3_5_9_9_5_3_5_9_3_3_5_1_1_4_4_9_9_1_6_7_3_1_7_7_10_4_5_10_6_10_5_8_2_6_7_7_8_4_1_4_2_10_2_9_7_1_4_2_2_7_2_3_3_10_6_10_2_10_6_10_3_7_5_7_1_2_5_8_1_2_3_2_3_3_1_8_2_2_2_8_9_5_3_3_1_4_8_6_6_4_9_3_5_6_6_6_5_6_1_1_2_4_2_9_5_2_8_8_7_1_2_9_10_3_7_3_10_4_1_2_7_2_8_2_1_2_4_4_1_5_1_4_3_6_1_3_7_6_6_3_1_2_4_1_7_9_1_9_7_7_3_4_1_1_2_4_1_4_3_7_6_6_6_5_10_7_5_8_8_6_5_4_3_4_5_2_1_1_3_2_5_9_1_4_6_4_6_1_2_6_4_8_1_3_2_1_4_4_1_7_2_5_1_4_8_9_1_3_6_5_8_4_1_6_1_9_5_9_2_5_7_1_9_9_3_3_1_6_5_6_3_4_2_9_1_5_6_2_6_1_10_2_3_4_3_1_7_4_6_5_7_9_3_5_3_7_7_2_5_1_3_9_2_2_10_5_6_2_4_2_1_1_1_3_2_6_1_4_10_5_1_7_3_2_1_4_1_2_1_2_5</t>
+  </si>
+  <si>
+    <t>5_8_3_2_8_4_8_8_8_3_3_4_1_2_2_3_1_1_8_1_6_2_4_8_1_3_6_7_1_3_7_6_6_3_3_3_1_1_8_7_7_5_2_2_2_4_4_4_3_3_7_3_1_1_1_7_1_1_3_1_3_3_8_1_5_5_1_7_2_2_3_4_2_3_6_1_4_4_6_7_2_8_5_1_6_1_1_2_3_1_6_6_4_2_2_7_2_4_3_3_7_2_1_1_3_2_2_1_2_6_3_2_3_1_2_3_8_2_6_6_2_1_2_1_4_1_1_1_1_3_4_2_6_2_7_5_5_1_2_3_3_2_6_6_3_6_4_2_5_7_5_2_1_1_6_2_3_7_1_3_8_6_6_1_1_6_2_2_3_2_5_8_3_1_2_1_7_5_3_2_7_2_2_5_3_1_5_4_7_7_6_2_2_3_1_1_3_3_3_3_8_2_2_3_8_7_2_5_3_8_3_3_1_3_1_1_3_3_4_4_1_3_3_4_3_3_3_3_1_8_6_2_2_2_1_1_1_2_2_2_5_6_3_2_5_4_2_4_7_5_2_3_1_1_2_2_2_3_2_4_2_2_7_2_1_4_3_6_3_3_1_1_3_6_3_4_2_2_2_2_2_1_6_2_3_2_2_2_3_7_6_1_3_4_2_2_2_2_5_5_6_2_2_2_3_7_7_2_8_8_4_4_2_2_4_5_5_8_5_3_3_8_2_1_3_3_1_4_3_2_5_2_7_2_3_1_6_4_2_2_2_2_2_4_7_7_2_7_8_4_2_2_7_6_4_1_1_1_6_2_2_1_7_2_3_5_4_1_1_6_7_7_5_3_3_5_4_6_4_6_7_2_4_1_4_5_2_1_2_1_1_6_6_6_1_3_5_5_5_1_1_2_1_4_5_2_4_5_1_4_2_8_5_8_7_1_4_1_1_7_1_2_4_2_3_7_4_3_3_2_3_5_4_2_1_4_1_2_6_6_8_1_3_8_8_3_3_4_3_5_4_2_2_2_3_3_1_5_5_1_1_2_4_4_7_3_1_2_3_7_3_6_5_1_6_3_3_1_2_2_1_4_3_2_1_7_5_1_3_4_2_4_5_1_1_2_3_2_2_4</t>
+  </si>
+  <si>
+    <t>4_3_1_6_7_8_10_6_4_6_2_3_3_2_3_1_2_5_6_2_7_4_2_9_1_4_3_6_5_3_5_6_10_6_9_9_2_1_2_2_4_6_10_7_10_7_6_4_8_1_8_10_4_3_8_3_2_6_8_6_2_4_3_2_1_2_2_1_10_4_3_9_1_8_4_2_4_2_6_6_1_2_4_5_1_3_1_4_4_7_6_4_1_5_3_10_6_7_8_1_9_7_3_7_3_10_7_5_1_6_4_9_7_2_4_4_6_4_6_8_1_1_2_9_10_7_3_2_6_4_1_7_4_10_3_3_5_7_9_4_2_4_1_6_1_6_1_10_4_2_5_2_6_8_6_8_2_8_1_5_1_2_1_3_8_5_1_3_9_5_3_2_3_2_3_9_5_1_7_5_5_3_6_1_4_7_2_10_4_4_1_8_4_6_1_2_8_9_9_6_4_9_1_3_6_3_6_4_10_5_5_9_7_4_3_2_8_1_8_7_7_3_1_2_9_3_6_5_6_4_2_7_5_5_7_6_8_8_5_6_2_5_4_9_4_8_7_5_6_1_7_7_2_4_4_8_1_2_1_8_1_7_4_5_7_2_6_10_4_2_2_5_8_4_2_3_8_2_5_3_1_6_5_3_8_8_4_4_4_6_2_2_1_8_2_3_9_5_5_1_4_4_8_4_2_1_10_1_8_10_3_2_4_5_5_5_2_4_2_10_6_1_6_2_6_6_3_6_5_1_2_2_2_9_10_7_4_7_1_9_1_4_4_4_9_1_8_4_7_1_8_8_4_3_6_9_7_10_6_1_3_3_5_1_3_8_9_2_6_1_7_5_2_1_7_6_5_7_2_8_6_6_8_1_10_6_1_6_5_2_3_8_5_8_4_2_2_4_6_9_7_8_8_5_9_7_4_5_3_2_4_8_6_6_5_7_4_7_7_8_1_9_3_6_2_5_8_4_8_4_7_1_5_8_8_5_1_5_9_4_7_10_7_1_7_8_2_2_8_5_2_1_8_4_4_2_4_1_3_1_3_5_7_3_2_4_4_2_9_2_10_5_1_4_4_6_2_10_7_8_4_2_1_7_4_9_2_9_5_8_6_10_6_4_2_2_5_7_1_4</t>
+  </si>
+  <si>
+    <t>5_7_6_1_1_1_1_6_1_1_4_4_2_2_2_2_6_4_1_3_2_4_2_2_2_6_3_1_2_2_1_1_4_4_2_1_2_4_4_7_3_4_5_2_2_2_2_6_3_7_2_1_3_3_2_1_2_6_5_2_1_7_7_1_8_8_6_3_6_2_4_3_1_5_3_6_8_8_3_1_8_1_3_3_1_3_8_8_3_1_1_1_7_7_3_3_2_6_6_4_3_2_3_1_2_3_3_4_2_2_6_6_1_1_3_7_1_8_1_1_6_6_4_5_1_6_1_1_1_3_3_6_6_2_3_1_4_5_2_8_3_5_2_3_2_3_1_8_2_2_3_1_1_5_8_2_7_2_5_2_1_3_6_6_6_3_3_7_2_3_8_1_2_1_3_3_2_6_7_2_1_1_4_6_5_4_4_7_7_1_2_5_6_1_7_8_6_2_2_8_3_1_1_5_3_2_2_1_2_3_3_1_4_3_2_2_6_2_6_6_5_6_2_4_7_6_1_3_8_4_4_2_5_3_3_4_4_4_2_4_3_4_8_8_6_2_2_2_1_8_1_4_4_5_3_3_4_4_4_6_3_4_1_4_4_6_2_5_4_4_2_1_4_2_3_5_5_1_4_7_5_5_5_5_5_5_2_1_2_6_7_7_7_2_7_3_7_1_1_2_5_5_5_8_3_1_3_1_1_3_3_4_4_7_7_4_4_5_5_7_7_3_3_5_6_5_4_1_1_1_7_1_6_4_6_6_6_3_1_6_2_3_1_7_1_1_1_4_2_2_2_4_2_1_1_8_3_3_3_4_6_3_3_3_4_7_7_2_2_8_1_1_1_5_1_6_6_6_6_4_4_4_6_2_5_1_2_2_3_3_6_4_4_5_3_3_7_2_4_7_6_4_1_4_4_8_2_4_3_6_2_5_2_5_2_1_1_2_3_4_7_8_4_1_7_6_7_1_6_3_8_8_7_8_5_1_2_6_4_1_3_3_3_2_2_8_4_2_7_1_1_4_8_4_5_4_6_1_1_7_7_1_2_1_1_2_1_1_5_8_2_5_8_3_2_7_4_4_2_4_4_6_1_3_4_1_1_3_4_6_5_4_6_5_2_8_2_2_8_2</t>
+  </si>
+  <si>
+    <t>2_6_6_6_7_6_7_6_3_1_7_6_1_4_7_1_2_1_6_2_8_9_1_1_6_7_8_4_10_3_9_9_6_10_3_1_7_7_5_7_7_8_3_3_3_3_6_2_8_8_5_3_5_9_4_2_10_6_10_3_1_2_8_7_7_2_6_6_10_6_4_7_6_2_1_6_8_1_2_1_8_4_5_6_3_9_5_5_2_1_5_10_3_1_1_8_5_8_3_1_1_7_3_2_2_10_6_6_6_2_4_2_8_2_8_2_5_2_4_1_3_10_4_8_5_1_4_8_10_6_2_8_1_9_1_6_10_6_6_4_5_7_3_4_1_9_9_2_1_1_3_8_3_6_3_5_2_4_5_4_2_8_1_6_7_6_9_6_5_5_1_5_3_4_6_4_2_6_7_2_7_5_6_5_7_6_4_6_8_8_1_3_1_1_1_8_2_5_1_7_1_6_6_6_6_9_5_3_4_4_3_3_4_4_2_6_6_2_4_6_2_9_1_3_6_7_6_9_6_1_1_1_8_4_4_3_9_7_4_7_8_2_9_6_5_6_10_5_9_10_4_1_6_1_2_10_7_3_6_4_3_5_1_7_9_4_7_3_6_1_5_5_6_2_1_1_2_8_8_7_7_9_5_9_2_5_5_2_6_6_4_7_7_7_9_4_7_2_7_7_3_3_9_1_5_6_2_4_1_8_4_1_1_3_3_2_1_5_4_5_1_2_1_2_4_3_5_2_4_3_3_4_2_8_9_4_4_2_7_9_2_4_2_9_1_4_4_5_8_2_7_5_2_2_9_5_9_3_4_7_4_3_3_1_3_5_2_7_6_3_2_7_8_8_5_4_9_1_1_9_2_1_7_2_3_8_5_1_7_8_1_6_5_8_4_5_3_1_4_6_3_4_2_1_3_8_9_2_4_1_2_6_1_7_5_3_1_4_1_1_4_1_8_2_2_1_5_8_1_1_6_4_2_2_1_9_1_5_4_8_1_10_5_3_5_2_1_3_3_5_2_8_1_4_2_2_9_6_10_3_1_2_1_9_9_1_6_1_6_2_7_1_9_7_2_7_4_2_1_2_2_10_2_4_6_3_5_6_8_8_2_7_3_3_2_2_1_1_4_3</t>
+  </si>
+  <si>
+    <t>2_4_4_3_3_3_7_4_1_3_8_1_1_5_5_3_2_3_2_7_3_3_6_8_3_1_2_1_1_2_5_8_3_4_1_1_3_1_1_4_8_8_3_3_6_4_7_4_4_5_1_3_7_4_6_2_2_5_4_1_1_4_2_5_1_4_4_3_2_7_1_7_6_5_6_1_2_2_7_1_2_5_1_4_3_4_4_8_6_2_6_4_3_4_2_5_2_4_4_4_4_3_7_7_1_4_5_4_4_4_5_1_7_2_1_5_1_2_4_8_2_7_1_3_1_2_1_2_2_2_2_7_4_5_5_8_6_4_1_2_6_1_1_3_2_3_7_1_3_1_3_4_4_7_1_3_3_6_6_2_5_2_3_1_1_1_5_2_1_2_1_1_1_7_7_6_4_3_1_1_1_2_5_2_2_2_4_2_2_2_2_1_4_2_2_5_1_1_1_3_1_3_3_1_5_5_4_2_4_3_1_2_6_7_6_6_8_8_8_3_5_3_2_3_3_6_3_5_5_7_1_3_3_6_2_2_2_5_1_3_2_5_5_4_8_2_2_6_2_3_4_6_3_1_4_3_1_1_3_4_3_4_2_4_1_1_6_1_3_1_5_7_7_7_2_4_1_1_8_1_2_6_5_6_5_1_3_3_3_4_2_7_2_2_2_2_3_4_4_2_5_5_4_5_1_5_6_1_2_2_1_1_3_6_3_2_8_4_8_7_7_4_4_4_6_7_4_3_2_1_3_3_6_6_8_7_3_1_4_3_4_4_2_1_1_2_7_4_1_2_7_2_2_1_1_7_2_2_2_1_3_3_6_1_1_2_4_2_4_3_2_3_6_4_5_1_1_5_3_8_3_4_4_4_2_2_4_5_3_2_3_5_5_1_4_5_2_2_2_2_3_3_1_4_7_3_3_1_7_7_2_2_1_8_1_5_4_4_4_2_3_4_8_1_2_3_1_1_2_3_6_1_2_2_5_8_1_3_8_4_3_5_1_3_7_7_3_3_8_1_2_2_2_1_2_2_1_1_1_1_1_2_6_6_2_1_3_5_3_1_7_1_3_7_2_3_2_2_2_4_4_4_1_2_3_7_2_3_2_2_3_3_3_4_2_1_1_6_8_1</t>
+  </si>
+  <si>
+    <t>1_3_5_6_1_2_8_5_7_2_1_4_6_1_2_2_7_9_1_1_2_4_4_1_2_3_1_7_1_5_6_6_5_3_9_5_5_1_6_9_9_10_4_7_5_10_4_6_4_5_9_3_6_3_8_8_5_5_8_8_4_9_3_4_7_9_6_7_9_3_9_3_1_7_6_5_6_1_8_7_5_2_5_7_6_7_4_3_4_3_9_6_7_3_5_6_10_7_5_7_1_6_1_1_4_6_1_6_6_8_10_6_2_8_2_1_4_3_4_8_7_1_10_6_5_2_8_4_4_6_6_8_5_4_6_6_6_7_6_4_4_9_9_4_8_3_5_2_9_3_1_2_7_9_8_9_9_9_2_1_7_6_1_5_3_4_7_5_2_4_10_5_7_2_1_4_5_1_8_1_4_2_8_6_1_3_2_8_3_2_3_4_3_7_5_10_6_3_6_8_7_2_2_2_10_6_4_2_10_5_2_2_8_5_3_1_3_3_6_6_3_6_1_3_2_3_4_2_8_2_7_2_2_2_5_2_3_6_7_1_2_4_8_2_3_3_2_2_2_5_6_3_5_5_7_8_9_1_4_3_4_6_3_2_7_7_9_7_6_5_1_6_3_6_5_1_2_1_8_8_1_7_2_5_8_2_3_6_5_5_2_7_4_2_2_1_3_3_9_5_5_7_2_5_4_3_8_1_5_1_2_6_1_2_6_2_6_7_3_6_1_1_5_1_9_6_5_7_1_2_5_7_3_7_6_4_4_6_10_4_3_4_2_1_6_10_7_9_9_1_4_4_1_2_9_4_3_1_3_4_8_2_1_5_4_2_6_3_3_4_1_9_3_5_5_3_5_4_8_5_6_1_8_8_9_8_4_5_6_9_5_5_2_4_8_7_6_1_5_2_1_8_5_4_1_4_1_2_9_5_1_7_9_1_7_5_9_5_4_2_2_1_3_2_4_1_8_1_3_4_1_3_4_3_2_1_1_3_6_1_4_5_5_9_7_9_1_4_4_8_3_9_5_9_3_7_8_3_1_8_4_9_6_4_7_3_4_1_1_5_1_8_8_6_3_1_4_2_2_1_4_2_9_4_2_9_5_5_6_4_8_3_2_3_4_1_2_6_1_3</t>
   </si>
 </sst>
 </file>
@@ -1927,11 +2146,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K125"/>
+  <dimension ref="A1:K177"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
     <col min="2" max="2" width="9" style="7"/>
+    <col min="3" max="3" width="9.375"/>
     <col min="4" max="4" width="7.875" customWidth="1"/>
     <col min="5" max="5" width="28.75" customWidth="1"/>
     <col min="6" max="6" width="23.525" customWidth="1"/>
@@ -5911,6 +6131,1670 @@
       <c r="J125" s="17"/>
       <c r="K125" s="17"/>
     </row>
+    <row r="126" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A126" s="6">
+        <f t="shared" ref="A126:A157" si="6">C126*10+D126</f>
+        <v>20280011</v>
+      </c>
+      <c r="B126" s="14">
+        <v>102800</v>
+      </c>
+      <c r="C126" s="33">
+        <v>2028001</v>
+      </c>
+      <c r="D126" s="33">
+        <v>1</v>
+      </c>
+      <c r="E126" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G126" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J126" s="17"/>
+      <c r="K126" s="17"/>
+    </row>
+    <row r="127" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A127" s="6">
+        <f t="shared" si="6"/>
+        <v>20280012</v>
+      </c>
+      <c r="B127" s="14">
+        <v>102800</v>
+      </c>
+      <c r="C127" s="33">
+        <v>2028001</v>
+      </c>
+      <c r="D127" s="33">
+        <v>2</v>
+      </c>
+      <c r="E127" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G127" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J127" s="17"/>
+      <c r="K127" s="17"/>
+    </row>
+    <row r="128" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A128" s="6">
+        <f t="shared" si="6"/>
+        <v>20280013</v>
+      </c>
+      <c r="B128" s="14">
+        <v>102800</v>
+      </c>
+      <c r="C128" s="33">
+        <v>2028001</v>
+      </c>
+      <c r="D128" s="33">
+        <v>3</v>
+      </c>
+      <c r="E128" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G128" s="34" t="s">
+        <v>185</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J128" s="17"/>
+      <c r="K128" s="17"/>
+    </row>
+    <row r="129" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A129" s="6">
+        <f t="shared" si="6"/>
+        <v>20280014</v>
+      </c>
+      <c r="B129" s="14">
+        <v>102800</v>
+      </c>
+      <c r="C129" s="33">
+        <v>2028001</v>
+      </c>
+      <c r="D129" s="33">
+        <v>4</v>
+      </c>
+      <c r="E129" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G129" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J129" s="17"/>
+      <c r="K129" s="17"/>
+    </row>
+    <row r="130" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A130" s="6">
+        <f t="shared" si="6"/>
+        <v>20280015</v>
+      </c>
+      <c r="B130" s="14">
+        <v>102800</v>
+      </c>
+      <c r="C130" s="33">
+        <v>2028001</v>
+      </c>
+      <c r="D130" s="33">
+        <v>5</v>
+      </c>
+      <c r="E130" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G130" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J130" s="17"/>
+      <c r="K130" s="17"/>
+    </row>
+    <row r="131" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A131" s="6">
+        <f t="shared" si="6"/>
+        <v>20280016</v>
+      </c>
+      <c r="B131" s="14">
+        <v>102800</v>
+      </c>
+      <c r="C131" s="33">
+        <v>2028001</v>
+      </c>
+      <c r="D131" s="33">
+        <v>6</v>
+      </c>
+      <c r="E131" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G131" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J131" s="17"/>
+      <c r="K131" s="17"/>
+    </row>
+    <row r="132" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A132" s="6">
+        <f t="shared" si="6"/>
+        <v>20340111</v>
+      </c>
+      <c r="B132" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C132" s="33">
+        <v>2034011</v>
+      </c>
+      <c r="D132" s="33">
+        <v>1</v>
+      </c>
+      <c r="E132" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J132" s="17"/>
+      <c r="K132" s="17"/>
+    </row>
+    <row r="133" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A133" s="6">
+        <f t="shared" si="6"/>
+        <v>20340112</v>
+      </c>
+      <c r="B133" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C133" s="33">
+        <v>2034011</v>
+      </c>
+      <c r="D133" s="33">
+        <v>2</v>
+      </c>
+      <c r="E133" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J133" s="17"/>
+      <c r="K133" s="17"/>
+    </row>
+    <row r="134" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A134" s="6">
+        <f t="shared" si="6"/>
+        <v>20340113</v>
+      </c>
+      <c r="B134" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C134" s="33">
+        <v>2034011</v>
+      </c>
+      <c r="D134" s="33">
+        <v>3</v>
+      </c>
+      <c r="E134" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J134" s="17"/>
+      <c r="K134" s="17"/>
+    </row>
+    <row r="135" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A135" s="6">
+        <f t="shared" si="6"/>
+        <v>20340121</v>
+      </c>
+      <c r="B135" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C135" s="33">
+        <v>2034012</v>
+      </c>
+      <c r="D135" s="33">
+        <v>1</v>
+      </c>
+      <c r="E135" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J135" s="17"/>
+      <c r="K135" s="17"/>
+    </row>
+    <row r="136" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A136" s="6">
+        <f t="shared" si="6"/>
+        <v>20340122</v>
+      </c>
+      <c r="B136" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C136" s="33">
+        <v>2034012</v>
+      </c>
+      <c r="D136" s="33">
+        <v>2</v>
+      </c>
+      <c r="E136" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J136" s="17"/>
+      <c r="K136" s="17"/>
+    </row>
+    <row r="137" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A137" s="6">
+        <f t="shared" si="6"/>
+        <v>20340123</v>
+      </c>
+      <c r="B137" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C137" s="33">
+        <v>2034012</v>
+      </c>
+      <c r="D137" s="33">
+        <v>3</v>
+      </c>
+      <c r="E137" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J137" s="17"/>
+      <c r="K137" s="17"/>
+    </row>
+    <row r="138" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A138" s="6">
+        <f t="shared" si="6"/>
+        <v>20340131</v>
+      </c>
+      <c r="B138" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C138" s="33">
+        <v>2034013</v>
+      </c>
+      <c r="D138" s="33">
+        <v>1</v>
+      </c>
+      <c r="E138" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J138" s="17"/>
+      <c r="K138" s="17"/>
+    </row>
+    <row r="139" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A139" s="6">
+        <f t="shared" si="6"/>
+        <v>20340132</v>
+      </c>
+      <c r="B139" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C139" s="33">
+        <v>2034013</v>
+      </c>
+      <c r="D139" s="33">
+        <v>2</v>
+      </c>
+      <c r="E139" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J139" s="17"/>
+      <c r="K139" s="17"/>
+    </row>
+    <row r="140" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A140" s="6">
+        <f t="shared" si="6"/>
+        <v>20340133</v>
+      </c>
+      <c r="B140" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C140" s="33">
+        <v>2034013</v>
+      </c>
+      <c r="D140" s="33">
+        <v>3</v>
+      </c>
+      <c r="E140" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J140" s="17"/>
+      <c r="K140" s="17"/>
+    </row>
+    <row r="141" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A141" s="6">
+        <f t="shared" si="6"/>
+        <v>20340141</v>
+      </c>
+      <c r="B141" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C141" s="33">
+        <v>2034014</v>
+      </c>
+      <c r="D141" s="33">
+        <v>1</v>
+      </c>
+      <c r="E141" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J141" s="17"/>
+      <c r="K141" s="17"/>
+    </row>
+    <row r="142" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A142" s="6">
+        <f t="shared" si="6"/>
+        <v>20340142</v>
+      </c>
+      <c r="B142" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C142" s="33">
+        <v>2034014</v>
+      </c>
+      <c r="D142" s="33">
+        <v>2</v>
+      </c>
+      <c r="E142" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J142" s="17"/>
+      <c r="K142" s="17"/>
+    </row>
+    <row r="143" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A143" s="6">
+        <f t="shared" si="6"/>
+        <v>20340143</v>
+      </c>
+      <c r="B143" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C143" s="33">
+        <v>2034014</v>
+      </c>
+      <c r="D143" s="33">
+        <v>3</v>
+      </c>
+      <c r="E143" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J143" s="17"/>
+      <c r="K143" s="17"/>
+    </row>
+    <row r="144" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A144" s="6">
+        <f t="shared" si="6"/>
+        <v>20340151</v>
+      </c>
+      <c r="B144" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C144" s="33">
+        <v>2034015</v>
+      </c>
+      <c r="D144" s="33">
+        <v>1</v>
+      </c>
+      <c r="E144" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J144" s="17"/>
+      <c r="K144" s="17"/>
+    </row>
+    <row r="145" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A145" s="6">
+        <f t="shared" si="6"/>
+        <v>20340152</v>
+      </c>
+      <c r="B145" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C145" s="33">
+        <v>2034015</v>
+      </c>
+      <c r="D145" s="33">
+        <v>2</v>
+      </c>
+      <c r="E145" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J145" s="17"/>
+      <c r="K145" s="17"/>
+    </row>
+    <row r="146" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A146" s="6">
+        <f t="shared" si="6"/>
+        <v>20340153</v>
+      </c>
+      <c r="B146" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C146" s="33">
+        <v>2034015</v>
+      </c>
+      <c r="D146" s="33">
+        <v>3</v>
+      </c>
+      <c r="E146" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H146" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J146" s="17"/>
+      <c r="K146" s="17"/>
+    </row>
+    <row r="147" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A147" s="6">
+        <f t="shared" si="6"/>
+        <v>20340161</v>
+      </c>
+      <c r="B147" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C147" s="33">
+        <v>2034016</v>
+      </c>
+      <c r="D147" s="33">
+        <v>1</v>
+      </c>
+      <c r="E147" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J147" s="17"/>
+      <c r="K147" s="17"/>
+    </row>
+    <row r="148" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A148" s="6">
+        <f t="shared" si="6"/>
+        <v>20340162</v>
+      </c>
+      <c r="B148" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C148" s="33">
+        <v>2034016</v>
+      </c>
+      <c r="D148" s="33">
+        <v>2</v>
+      </c>
+      <c r="E148" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J148" s="17"/>
+      <c r="K148" s="17"/>
+    </row>
+    <row r="149" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A149" s="6">
+        <f t="shared" si="6"/>
+        <v>20340163</v>
+      </c>
+      <c r="B149" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C149" s="33">
+        <v>2034016</v>
+      </c>
+      <c r="D149" s="33">
+        <v>3</v>
+      </c>
+      <c r="E149" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J149" s="17"/>
+      <c r="K149" s="17"/>
+    </row>
+    <row r="150" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A150" s="6">
+        <f t="shared" si="6"/>
+        <v>20340171</v>
+      </c>
+      <c r="B150" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C150" s="33">
+        <v>2034017</v>
+      </c>
+      <c r="D150" s="33">
+        <v>1</v>
+      </c>
+      <c r="E150" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J150" s="17"/>
+      <c r="K150" s="17"/>
+    </row>
+    <row r="151" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A151" s="6">
+        <f t="shared" si="6"/>
+        <v>20340172</v>
+      </c>
+      <c r="B151" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C151" s="33">
+        <v>2034017</v>
+      </c>
+      <c r="D151" s="33">
+        <v>2</v>
+      </c>
+      <c r="E151" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J151" s="17"/>
+      <c r="K151" s="17"/>
+    </row>
+    <row r="152" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A152" s="6">
+        <f t="shared" si="6"/>
+        <v>20340173</v>
+      </c>
+      <c r="B152" s="14">
+        <v>103401</v>
+      </c>
+      <c r="C152" s="33">
+        <v>2034017</v>
+      </c>
+      <c r="D152" s="33">
+        <v>3</v>
+      </c>
+      <c r="E152" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H152" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J152" s="17"/>
+      <c r="K152" s="17"/>
+    </row>
+    <row r="153" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A153" s="6">
+        <f t="shared" si="6"/>
+        <v>20200011</v>
+      </c>
+      <c r="B153" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C153" s="33">
+        <v>2020001</v>
+      </c>
+      <c r="D153" s="33">
+        <v>1</v>
+      </c>
+      <c r="E153" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H153" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="J153" s="17"/>
+      <c r="K153" s="17"/>
+    </row>
+    <row r="154" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A154" s="6">
+        <f t="shared" si="6"/>
+        <v>20200012</v>
+      </c>
+      <c r="B154" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C154" s="33">
+        <v>2020001</v>
+      </c>
+      <c r="D154" s="33">
+        <v>2</v>
+      </c>
+      <c r="E154" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J154" s="17"/>
+      <c r="K154" s="17"/>
+    </row>
+    <row r="155" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A155" s="6">
+        <f t="shared" si="6"/>
+        <v>20200013</v>
+      </c>
+      <c r="B155" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C155" s="33">
+        <v>2020001</v>
+      </c>
+      <c r="D155" s="33">
+        <v>3</v>
+      </c>
+      <c r="E155" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="H155" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="J155" s="17"/>
+      <c r="K155" s="17"/>
+    </row>
+    <row r="156" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A156" s="6">
+        <f t="shared" si="6"/>
+        <v>20200014</v>
+      </c>
+      <c r="B156" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C156" s="33">
+        <v>2020001</v>
+      </c>
+      <c r="D156" s="33">
+        <v>4</v>
+      </c>
+      <c r="E156" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="H156" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J156" s="17"/>
+      <c r="K156" s="17"/>
+    </row>
+    <row r="157" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A157" s="6">
+        <f t="shared" si="6"/>
+        <v>20200015</v>
+      </c>
+      <c r="B157" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C157" s="33">
+        <v>2020001</v>
+      </c>
+      <c r="D157" s="33">
+        <v>5</v>
+      </c>
+      <c r="E157" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="H157" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J157" s="17"/>
+      <c r="K157" s="17"/>
+    </row>
+    <row r="158" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A158" s="6">
+        <f t="shared" ref="A158:A172" si="7">C158*10+D158</f>
+        <v>20200021</v>
+      </c>
+      <c r="B158" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C158" s="33">
+        <v>2020002</v>
+      </c>
+      <c r="D158" s="33">
+        <v>1</v>
+      </c>
+      <c r="E158" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H158" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="J158" s="17"/>
+      <c r="K158" s="17"/>
+    </row>
+    <row r="159" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A159" s="6">
+        <f t="shared" si="7"/>
+        <v>20200022</v>
+      </c>
+      <c r="B159" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C159" s="33">
+        <v>2020002</v>
+      </c>
+      <c r="D159" s="33">
+        <v>2</v>
+      </c>
+      <c r="E159" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="H159" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="J159" s="17"/>
+      <c r="K159" s="17"/>
+    </row>
+    <row r="160" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A160" s="6">
+        <f t="shared" si="7"/>
+        <v>20200023</v>
+      </c>
+      <c r="B160" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C160" s="33">
+        <v>2020002</v>
+      </c>
+      <c r="D160" s="33">
+        <v>3</v>
+      </c>
+      <c r="E160" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H160" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="J160" s="17"/>
+      <c r="K160" s="17"/>
+    </row>
+    <row r="161" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A161" s="6">
+        <f t="shared" si="7"/>
+        <v>20200024</v>
+      </c>
+      <c r="B161" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C161" s="33">
+        <v>2020002</v>
+      </c>
+      <c r="D161" s="33">
+        <v>4</v>
+      </c>
+      <c r="E161" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H161" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="J161" s="17"/>
+      <c r="K161" s="17"/>
+    </row>
+    <row r="162" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A162" s="6">
+        <f t="shared" si="7"/>
+        <v>20200025</v>
+      </c>
+      <c r="B162" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C162" s="33">
+        <v>2020002</v>
+      </c>
+      <c r="D162" s="33">
+        <v>5</v>
+      </c>
+      <c r="E162" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="H162" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I162" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="J162" s="17"/>
+      <c r="K162" s="17"/>
+    </row>
+    <row r="163" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A163" s="6">
+        <f t="shared" si="7"/>
+        <v>20200031</v>
+      </c>
+      <c r="B163" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C163" s="33">
+        <v>2020003</v>
+      </c>
+      <c r="D163" s="33">
+        <v>1</v>
+      </c>
+      <c r="E163" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H163" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="J163" s="17"/>
+      <c r="K163" s="17"/>
+    </row>
+    <row r="164" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A164" s="6">
+        <f t="shared" si="7"/>
+        <v>20200032</v>
+      </c>
+      <c r="B164" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C164" s="33">
+        <v>2020003</v>
+      </c>
+      <c r="D164" s="33">
+        <v>2</v>
+      </c>
+      <c r="E164" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="H164" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="J164" s="17"/>
+      <c r="K164" s="17"/>
+    </row>
+    <row r="165" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A165" s="6">
+        <f t="shared" si="7"/>
+        <v>20200033</v>
+      </c>
+      <c r="B165" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C165" s="33">
+        <v>2020003</v>
+      </c>
+      <c r="D165" s="33">
+        <v>3</v>
+      </c>
+      <c r="E165" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="H165" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="J165" s="17"/>
+      <c r="K165" s="17"/>
+    </row>
+    <row r="166" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A166" s="6">
+        <f t="shared" si="7"/>
+        <v>20200034</v>
+      </c>
+      <c r="B166" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C166" s="33">
+        <v>2020003</v>
+      </c>
+      <c r="D166" s="33">
+        <v>4</v>
+      </c>
+      <c r="E166" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="H166" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I166" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="J166" s="17"/>
+      <c r="K166" s="17"/>
+    </row>
+    <row r="167" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A167" s="6">
+        <f t="shared" si="7"/>
+        <v>20200035</v>
+      </c>
+      <c r="B167" s="14">
+        <v>102000</v>
+      </c>
+      <c r="C167" s="33">
+        <v>2020003</v>
+      </c>
+      <c r="D167" s="33">
+        <v>5</v>
+      </c>
+      <c r="E167" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H167" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I167" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="J167" s="17"/>
+      <c r="K167" s="17"/>
+    </row>
+    <row r="168" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A168" s="6">
+        <f t="shared" si="7"/>
+        <v>20380011</v>
+      </c>
+      <c r="B168" s="14">
+        <v>103800</v>
+      </c>
+      <c r="C168" s="33">
+        <v>2038001</v>
+      </c>
+      <c r="D168" s="33">
+        <v>1</v>
+      </c>
+      <c r="E168" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="H168" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I168" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="J168" s="17"/>
+      <c r="K168" s="17"/>
+    </row>
+    <row r="169" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A169" s="6">
+        <f t="shared" si="7"/>
+        <v>20380012</v>
+      </c>
+      <c r="B169" s="14">
+        <v>103800</v>
+      </c>
+      <c r="C169" s="33">
+        <v>2038001</v>
+      </c>
+      <c r="D169" s="33">
+        <v>2</v>
+      </c>
+      <c r="E169" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H169" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I169" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="J169" s="17"/>
+      <c r="K169" s="17"/>
+    </row>
+    <row r="170" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A170" s="6">
+        <f t="shared" si="7"/>
+        <v>20380013</v>
+      </c>
+      <c r="B170" s="14">
+        <v>103800</v>
+      </c>
+      <c r="C170" s="33">
+        <v>2038001</v>
+      </c>
+      <c r="D170" s="33">
+        <v>3</v>
+      </c>
+      <c r="E170" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H170" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I170" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="J170" s="17"/>
+      <c r="K170" s="17"/>
+    </row>
+    <row r="171" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A171" s="6">
+        <f t="shared" si="7"/>
+        <v>20380014</v>
+      </c>
+      <c r="B171" s="14">
+        <v>103800</v>
+      </c>
+      <c r="C171" s="33">
+        <v>2038001</v>
+      </c>
+      <c r="D171" s="33">
+        <v>4</v>
+      </c>
+      <c r="E171" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H171" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I171" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="J171" s="17"/>
+      <c r="K171" s="17"/>
+    </row>
+    <row r="172" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A172" s="6">
+        <f t="shared" si="7"/>
+        <v>20380015</v>
+      </c>
+      <c r="B172" s="14">
+        <v>103800</v>
+      </c>
+      <c r="C172" s="33">
+        <v>2038001</v>
+      </c>
+      <c r="D172" s="33">
+        <v>5</v>
+      </c>
+      <c r="E172" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H172" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I172" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="J172" s="17"/>
+      <c r="K172" s="17"/>
+    </row>
+    <row r="173" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A173" s="6">
+        <f>C173*10+D173</f>
+        <v>20270011</v>
+      </c>
+      <c r="B173" s="14">
+        <v>102700</v>
+      </c>
+      <c r="C173" s="33">
+        <v>2027001</v>
+      </c>
+      <c r="D173" s="33">
+        <v>1</v>
+      </c>
+      <c r="E173" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G173" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H173" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I173" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="J173" s="17"/>
+      <c r="K173" s="17"/>
+    </row>
+    <row r="174" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A174" s="6">
+        <f>C174*10+D174</f>
+        <v>20270012</v>
+      </c>
+      <c r="B174" s="14">
+        <v>102700</v>
+      </c>
+      <c r="C174" s="33">
+        <v>2027001</v>
+      </c>
+      <c r="D174" s="33">
+        <v>2</v>
+      </c>
+      <c r="E174" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G174" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H174" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I174" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="J174" s="17"/>
+      <c r="K174" s="17"/>
+    </row>
+    <row r="175" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A175" s="6">
+        <f>C175*10+D175</f>
+        <v>20270013</v>
+      </c>
+      <c r="B175" s="14">
+        <v>102700</v>
+      </c>
+      <c r="C175" s="33">
+        <v>2027001</v>
+      </c>
+      <c r="D175" s="33">
+        <v>3</v>
+      </c>
+      <c r="E175" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H175" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I175" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="J175" s="17"/>
+      <c r="K175" s="17"/>
+    </row>
+    <row r="176" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A176" s="6">
+        <f>C176*10+D176</f>
+        <v>20270014</v>
+      </c>
+      <c r="B176" s="14">
+        <v>102700</v>
+      </c>
+      <c r="C176" s="33">
+        <v>2027001</v>
+      </c>
+      <c r="D176" s="33">
+        <v>4</v>
+      </c>
+      <c r="E176" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="H176" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I176" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J176" s="17"/>
+      <c r="K176" s="17"/>
+    </row>
+    <row r="177" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A177" s="6">
+        <f>C177*10+D177</f>
+        <v>20270015</v>
+      </c>
+      <c r="B177" s="14">
+        <v>102700</v>
+      </c>
+      <c r="C177" s="33">
+        <v>2027001</v>
+      </c>
+      <c r="D177" s="33">
+        <v>5</v>
+      </c>
+      <c r="E177" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G177" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="H177" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I177" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="J177" s="17"/>
+      <c r="K177" s="17"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -5925,9 +7809,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="24" ht="16.5" spans="9:9">
-      <c r="I24" s="1" t="s">
-        <v>158</v>
-      </c>
+      <c r="I24" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="265">
   <si>
     <t>id</t>
   </si>
@@ -833,6 +833,48 @@
   </si>
   <si>
     <t>1_3_5_6_1_2_8_5_7_2_1_4_6_1_2_2_7_9_1_1_2_4_4_1_2_3_1_7_1_5_6_6_5_3_9_5_5_1_6_9_9_10_4_7_5_10_4_6_4_5_9_3_6_3_8_8_5_5_8_8_4_9_3_4_7_9_6_7_9_3_9_3_1_7_6_5_6_1_8_7_5_2_5_7_6_7_4_3_4_3_9_6_7_3_5_6_10_7_5_7_1_6_1_1_4_6_1_6_6_8_10_6_2_8_2_1_4_3_4_8_7_1_10_6_5_2_8_4_4_6_6_8_5_4_6_6_6_7_6_4_4_9_9_4_8_3_5_2_9_3_1_2_7_9_8_9_9_9_2_1_7_6_1_5_3_4_7_5_2_4_10_5_7_2_1_4_5_1_8_1_4_2_8_6_1_3_2_8_3_2_3_4_3_7_5_10_6_3_6_8_7_2_2_2_10_6_4_2_10_5_2_2_8_5_3_1_3_3_6_6_3_6_1_3_2_3_4_2_8_2_7_2_2_2_5_2_3_6_7_1_2_4_8_2_3_3_2_2_2_5_6_3_5_5_7_8_9_1_4_3_4_6_3_2_7_7_9_7_6_5_1_6_3_6_5_1_2_1_8_8_1_7_2_5_8_2_3_6_5_5_2_7_4_2_2_1_3_3_9_5_5_7_2_5_4_3_8_1_5_1_2_6_1_2_6_2_6_7_3_6_1_1_5_1_9_6_5_7_1_2_5_7_3_7_6_4_4_6_10_4_3_4_2_1_6_10_7_9_9_1_4_4_1_2_9_4_3_1_3_4_8_2_1_5_4_2_6_3_3_4_1_9_3_5_5_3_5_4_8_5_6_1_8_8_9_8_4_5_6_9_5_5_2_4_8_7_6_1_5_2_1_8_5_4_1_4_1_2_9_5_1_7_9_1_7_5_9_5_4_2_2_1_3_2_4_1_8_1_3_4_1_3_4_3_2_1_1_3_6_1_4_5_5_9_7_9_1_4_4_8_3_9_5_9_3_7_8_3_1_8_4_9_6_4_7_3_4_1_1_5_1_8_8_6_3_1_4_2_2_1_4_2_9_4_2_9_5_5_6_4_8_3_2_3_4_1_2_6_1_3</t>
+  </si>
+  <si>
+    <t>1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_3_4_4_4_4_4_6_6_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_6_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_6_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_6_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_6_1_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_6_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4</t>
+  </si>
+  <si>
+    <t>3_3_3_3_3_3_4_4_4_4_4_6_6_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_6_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_6_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_6_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_6_1_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_6_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_1_1_1_1_2_2_2_2_2</t>
+  </si>
+  <si>
+    <t>4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_3_4_4_4_4_4_6_6_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_6_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_6_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_6_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_6_1_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_6_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3</t>
+  </si>
+  <si>
+    <t>3_5_3_1_1_2_1_2_4_1_1_2_4_5_7_6_5_8_8_6_3_3_3_6_6_4_6_2_1_2_5_4_3_3_3_6_3_5_2_1_2_7_10_4_1_7_2_5_4_8_8_1_4_4_4_4_9_5_1_5_1_5_5_4_8_9_2_9_9_5_5_4_6_7_2_7_1_9_9_1_1_5_10_8_4_1_3_1_4_7_7_2_5_2_2_2_2_1_1_6_9_1_7_1_6_2_5_1_1_3_3_6_2_8_1_1_1_4_8_8_8_4_3_3_7_7_9_9_7_6_5_10_1_3_3_7_5_1_9_2_2_2_4_2_2_2_3_5_1_4_9_5_3_2_2_3_10_7_1_4_2_6_9_8_8_6_1_7_5_8_7_5_5_10_10_1_5_3_7_8_3_8_7_3_6_7_1_8_4_8_9_9_9_5_5_1_7_7_3_3_3_1_4_7_5_1_4_6_4_9_1_2_6_5_1_2_8_2_5_2_3_3_6_1_4_4_5_5_7_9_8_10_3_1_3_2_5_8_2_4_2_3_5_2_2_2_4_6_8_4_2_2_1_8_6_8_1_3_9_5_5_5_1_1_5_10_10_4_5_6_1_5_5_5_4_9_10_2_2_1_2_7_1_2_3_6_5_5_4_3_4_1_1_4_3_3_5_6_1_1_6_6_1_1_4_1_3_1_1_6_4_2_5_7_6_1_4_1_8_4_1_1_3_5_5_2_3_7_7_7_7_7_1_6_6_8_10_1_4_2_9_2_6_6_5_2_9_3_1_4_3_3_2_1_1_7_2_4_1_6_5_3_1_9_3_8_8_10_5_3_1_5_1_2_1_2_2_4_9_2_3_1_8_9_9_1_8_6_2_4_9_1_4_4_6_5_7_2_6_6_4_4_2_6_4_9_4_5_2_5_9_9_10_8_2_6_1_1_9_3_5_5_3_4_3_5_2_1_1_6_2_3_3_8_3_8_4_4_2_8_9_9_5_2_6_1_8_1_4_4_1_1_3_4_6_6_2_2_5_4_2_7_5_3_2_5_5_4_9_6_5_4_4_9_1_10_4_4_9_2_3_9_5_10_10_5_7_9_8_6_7_9_9_3_3_3_3_3_6_6</t>
+  </si>
+  <si>
+    <t>6_6_11_4_1_5_1_8_3_3_8_9_5_6_10_4_4_9_2_8_10_5_9_11_1_7_1_3_10_6_8_9_1_5_10_4_1_4_4_2_10_7_1_10_6_10_5_10_7_2_7_10_7_2_4_5_3_2_6_6_11_5_10_5_7_5_3_7_10_2_1_9_5_3_5_6_5_3_5_1_4_9_1_3_6_6_10_6_2_2_3_10_7_2_7_5_6_3_1_5_3_2_4_6_4_1_1_4_10_7_6_4_2_5_6_2_5_1_5_4_9_7_6_5_9_3_4_10_7_6_4_6_10_3_4_1_2_2_2_1_9_4_6_3_11_3_10_5_10_6_5_5_6_6_9_1_1_5_1_5_10_6_3_7_7_2_10_6_2_5_11_4_3_9_4_7_4_3_8_2_2_9_3_10_2_1_4_2_3_9_11_7_5_10_6_3_2_4_8_3_3_2_1_3_1_2_6_4_8_3_3_10_4_3_8_4_1_4_9_10_1_2_2_10_5_4_1_3_9_6_8_1_5_3_8_1_8_6_10_2_3_7_3_5_7_2_9_2_8_2_4_11_3_4_8_4_6_9_1_9_6_8_5_10_6_3_6_10_5_2_7_6_6_3_6_2_3_1_9_1_6_1_2_9_3_2_8_1_4_8_3_4_10_2_6_5_4_2_11_4_4_4_2_2_2_1_1_1_3_3_1_1_9_3_1_5_5_4_2_4_11_6_6_8_5_3_1_6_10_3_2_2_1_2_2_2_4_1_3_7_9_8_5_8_4_5_2_3_1_3_9_2_4_2_1_4_4_7_3_9_4_10_2_2_2_7_7_5_5_4_10_7_10_4_4_11_7_4_7_1_1_4_1_8_4_7_3_2_6_2_6_3_7_3_1_4_1_7_1_7_4_1_4_8_9_2_8_4_11_3_2_4_11_6_6_3_8_4_9_8_8_10_6_3_6_7_4_6_7_1_4_9_10_5_11_6_1_10_4_11_4_4_2_2_1_3_3_11_6_6_4_2_2_1_8_1_7_5_6_3_8_1_3_4_5_6_9_2_4_7_5_4_1_4_4_2_5_6_3_4_5_2_3_10_7_8_8_4_10_2_2_6_9_2_6_5_10_3_3_5</t>
+  </si>
+  <si>
+    <t>4_4_5_5_4_2_1_2_4_4_1_1_5_2_3_5_8_9_2_3_4_3_6_1_3_3_3_1_1_4_4_4_4_2_6_7_5_3_3_4_2_3_9_6_6_1_4_4_1_4_3_8_9_7_9_8_2_1_4_3_1_6_5_4_2_8_1_5_4_6_1_5_7_8_5_3_2_4_1_4_7_2_5_4_10_10_4_2_1_7_7_9_5_4_5_8_4_4_7_6_6_3_2_6_2_2_8_4_4_1_3_1_8_2_2_1_8_8_7_5_6_6_9_5_4_4_6_2_1_9_9_9_9_1_6_5_3_2_3_6_5_5_5_5_3_3_2_3_1_4_4_6_2_2_5_4_5_2_1_1_2_5_2_2_1_1_7_7_2_3_5_1_1_3_6_8_5_2_2_2_3_9_1_10_5_8_8_2_6_4_8_4_3_3_1_7_7_7_1_5_6_4_5_4_4_6_2_5_6_5_5_3_4_3_9_1_3_5_2_7_3_6_7_3_6_6_6_6_6_7_7_4_4_4_2_3_3_8_4_2_4_1_1_1_5_8_5_5_2_7_7_8_2_7_3_2_5_7_5_7_9_4_2_2_9_6_1_2_5_1_3_6_9_1_3_5_3_4_6_8_7_3_7_10_4_1_8_7_9_3_3_7_8_5_7_9_1_2_7_5_1_5_2_3_4_6_2_6_2_1_8_9_4_2_2_7_1_2_2_5_3_6_3_8_6_2_2_1_1_9_9_1_5_1_1_10_9_4_3_2_10_2_2_8_5_9_1_7_9_3_9_9_1_5_3_2_7_4_8_2_8_3_4_4_1_7_8_9_1_5_5_5_4_4_6_1_7_1_8_8_3_4_5_6_6_2_1_10_9_9_9_1_4_4_7_2_2_2_9_4_4_4_9_9_9_1_3_8_9_6_4_2_6_5_7_1_4_8_2_6_6_3_2_1_5_2_6_4_1_3_3_8_4_3_6_6_5_1_10_6_4_3_1_4_2_1_6_6_1_5_5_10_4_7_3_1_3_8_7_1_3_7_10_2_1_3_2_3_8_3_7_1_2_6_9_4_8_9_3_10_10_4_1_3_8_5_3_2_2_2_5_5_1_6_9_3_2_6_4_2</t>
+  </si>
+  <si>
+    <t>8_2_1_10_4_4_11_4_8_2_6_1_6_6_7_1_2_3_3_6_7_1_8_1_6_11_6_4_7_1_7_8_6_2_9_3_4_1_8_10_5_3_4_4_11_4_3_1_8_9_1_8_7_5_2_10_3_11_3_2_10_7_1_10_3_10_3_2_9_4_10_6_6_1_6_1_8_5_5_7_5_8_5_6_2_8_2_3_4_5_5_9_7_4_2_3_7_3_1_4_3_10_6_2_5_2_10_5_10_6_9_5_7_4_3_5_5_5_7_5_1_8_5_5_4_8_9_8_4_8_6_2_2_5_2_5_10_6_11_4_9_3_4_4_1_5_2_4_5_4_10_2_1_6_5_6_3_9_1_6_9_11_3_10_2_3_2_7_2_4_10_4_6_4_4_2_10_2_4_1_7_10_7_8_2_6_10_3_6_2_10_4_5_7_1_2_4_5_4_9_3_6_6_5_5_1_4_3_4_7_7_3_10_5_2_11_6_5_5_5_2_3_2_1_4_2_1_6_3_9_9_4_8_3_5_6_5_2_4_4_5_7_9_5_2_1_4_4_6_4_3_3_8_3_5_1_7_3_5_5_3_7_1_5_4_6_2_9_1_1_1_2_10_3_8_1_4_11_6_4_1_10_6_4_1_10_5_4_1_4_5_6_10_1_7_2_4_6_4_5_3_4_2_5_4_1_1_8_10_4_6_5_5_6_10_3_6_10_6_3_5_7_4_7_7_11_4_8_4_1_8_3_5_1_10_7_7_6_1_9_1_1_8_4_8_1_2_6_8_9_6_9_3_7_6_5_2_4_2_1_2_10_6_1_4_4_8_7_3_3_3_8_9_7_3_4_6_4_6_10_4_5_10_7_1_1_3_11_5_6_10_4_1_4_7_10_6_2_5_10_6_2_3_4_1_1_3_10_5_2_5_1_6_5_3_3_8_10_6_3_3_2_2_10_5_4_9_3_1_11_4_6_2_6_2_4_4_8_4_4_8_6_8_7_7_1_4_11_5_1_8_1_4_1_4_11_4_4_5_9_4_3_4_9_6_6_5_10_7_8_5_2_3_2_8_2_6_3_5_1_6_2_7_8_2_3_5_5_1_2_9_11_6_2_6_6_5_5_8_8</t>
+  </si>
+  <si>
+    <t>8_3_4_2_1_4_1_10_2_2_9_5_7_2_2_6_4_6_2_3_1_1_6_4_7_10_10_10_10_9_9_7_4_2_2_7_6_2_6_9_7_8_8_8_1_5_2_2_3_7_1_9_5_5_4_4_3_1_5_5_5_3_4_3_5_6_10_4_3_6_7_2_8_1_1_3_5_2_3_3_6_10_5_4_4_7_5_5_10_9_10_4_3_6_7_3_3_7_7_1_8_2_4_4_4_5_10_6_2_4_1_1_5_4_8_2_1_2_7_3_2_6_7_6_1_2_1_1_3_2_2_3_9_1_9_2_3_6_6_6_2_2_10_10_4_2_2_7_3_5_1_7_7_7_4_2_9_2_3_1_3_7_4_5_5_2_8_1_4_2_8_3_2_2_1_1_9_5_8_8_1_1_3_4_8_1_8_8_1_5_1_6_8_8_10_4_3_10_6_2_2_3_10_5_1_2_5_5_4_2_7_4_4_5_5_1_1_4_4_4_3_7_1_4_2_2_1_4_3_3_8_8_6_8_9_1_2_10_1_8_1_4_7_5_5_1_7_8_2_1_4_1_3_9_6_8_1_3_4_4_5_6_8_1_1_7_10_3_5_5_9_9_7_5_2_4_4_5_3_5_3_4_7_7_1_1_8_2_2_1_1_1_4_4_3_2_2_5_2_9_3_1_5_9_9_8_1_10_4_6_1_6_7_1_8_5_4_4_2_3_7_1_6_1_7_2_3_3_5_2_5_6_7_7_6_6_7_2_5_4_6_2_1_2_3_5_10_10_9_10_10_9_2_4_5_5_3_3_2_3_2_2_3_3_2_8_2_8_2_8_2_6_4_9_2_5_7_3_2_8_8_1_1_3_4_4_3_5_2_2_4_9_5_2_5_5_1_1_7_7_4_3_5_1_4_7_2_4_7_7_10_4_6_2_2_3_1_1_2_7_10_5_8_7_7_5_4_1_1_9_5_2_4_6_8_2_4_7_1_6_2_1_3_1_2_4_4_8_8_5_2_10_3_8_4_4_10_5_3_7_10_10_1_5_4_2_2_1_3_5_1_9_6_2_10_1_4_1_3_2_6_1_6_3_7_6_4_8_4_2_3_3_4_9_5_3_4_6_10_1</t>
+  </si>
+  <si>
+    <t>9_9_6_9_4_6_6_7_1_5_2_6_5_1_1_10_3_4_9_10_3_6_1_1_5_3_1_1_9_1_2_2_8_9_1_1_1_1_1_7_6_8_2_9_9_5_1_1_1_5_5_4_3_5_6_9_9_2_2_7_5_4_2_8_7_8_8_3_4_4_3_9_6_7_5_7_3_2_7_3_6_5_9_2_7_10_4_6_5_2_6_4_4_8_2_2_1_1_4_7_3_2_11_4_7_7_4_5_1_3_2_11_5_6_5_1_3_2_1_6_6_7_10_7_4_9_9_1_1_4_8_1_3_2_6_8_11_6_1_7_1_6_11_6_6_9_10_7_6_10_7_2_7_2_8_4_9_6_9_8_10_6_10_7_6_2_6_10_5_2_7_7_5_6_5_2_4_7_11_3_4_7_4_7_4_2_4_6_6_6_1_6_3_1_3_3_2_3_5_1_3_4_2_3_7_4_5_3_3_2_5_2_3_8_1_10_6_3_8_9_5_9_4_11_7_10_3_1_8_2_9_4_5_4_2_2_2_6_11_7_7_6_9_4_4_4_5_1_10_6_1_1_3_3_10_6_4_3_5_9_3_6_3_2_8_4_4_1_8_10_3_9_8_6_2_7_8_1_6_9_3_4_9_5_2_2_1_8_8_8_8_8_1_4_1_6_4_4_2_6_6_4_2_8_2_8_9_5_2_2_4_6_9_8_10_3_1_1_2_4_2_8_5_6_6_6_7_3_1_1_8_4_7_2_2_1_3_7_8_10_5_6_3_10_1_4_6_5_7_1_1_1_6_3_3_7_5_6_8_4_2_3_5_5_5_7_9_1_3_4_8_3_2_3_2_1_5_2_4_10_7_7_1_10_5_3_5_7_3_8_1_2_2_1_8_8_7_5_1_6_2_2_6_10_3_1_2_10_3_5_8_6_1_11_2_8_8_8_5_8_6_5_10_7_1_3_2_7_3_5_6_8_10_2_6_3_4_3_1_3_7_4_3_1_5_10_3_3_1_8_2_6_10_2_6_4_8_3_3_9_10_6_4_7_6_10_7_9_3_2_6_3_4_4_8_3_5_7_3_5_9_8_3_6_5_4_2_4_4_10_7_9_2_5_2_4_5_3_1_2</t>
+  </si>
+  <si>
+    <t>4_6_7_7_1_1_2_3_5_1_8_1_3_4_1_1_1_7_10_2_2_1_1_1_10_5_7_7_3_8_1_3_4_1_5_8_6_8_1_8_4_2_4_4_6_2_1_4_2_1_4_1_9_4_4_9_6_4_3_5_2_5_5_3_9_3_10_8_5_8_6_5_6_6_2_3_4_5_6_2_6_6_7_4_3_6_8_9_4_5_1_8_8_5_8_5_5_2_8_3_9_9_2_3_4_4_6_8_4_5_6_8_2_2_6_8_10_2_4_2_6_9_3_2_3_1_5_9_7_9_3_3_8_6_7_2_1_1_3_1_4_4_7_7_7_2_3_2_9_1_1_2_3_3_4_1_6_6_4_3_2_5_9_6_9_2_3_4_2_8_2_4_9_7_7_5_1_7_4_6_6_4_3_3_7_1_4_1_3_4_4_3_2_9_7_4_8_3_3_9_3_1_7_6_3_1_2_6_7_8_2_2_4_8_4_2_1_2_6_4_2_6_8_3_1_5_9_1_7_10_1_2_2_8_9_10_9_4_5_3_7_5_3_3_6_9_4_4_3_10_5_6_1_1_2_8_6_6_1_6_5_3_3_9_1_1_5_1_1_4_9_1_3_2_2_5_5_9_3_4_2_4_1_1_1_10_3_1_1_8_1_6_6_6_5_2_3_8_8_5_4_3_6_6_4_4_6_6_1_4_4_1_1_2_2_5_3_10_2_4_7_4_4_2_3_2_1_4_1_2_8_8_6_8_2_1_1_8_6_7_3_4_2_4_4_3_8_4_9_5_2_1_1_3_3_3_3_8_8_8_4_4_3_7_2_7_2_1_7_10_3_4_4_5_2_2_1_1_2_6_4_3_3_2_1_5_6_6_6_6_9_6_2_1_2_1_7_6_8_3_3_2_1_1_7_1_2_9_9_2_4_3_6_5_4_10_5_5_4_3_5_1_5_7_5_10_1_3_1_8_4_2_1_5_8_9_2_2_9_6_7_9_6_1_9_4_1_8_2_4_7_3_2_5_7_8_3_1_2_5_7_9_9_4_4_2_6_6_9_1_1_4_4_2_9_9_6_3_5_5_2_3_10_10_10_4_3_2_6_3_3_5_1_5_7_4_8_4_4_5</t>
+  </si>
+  <si>
+    <t>3_5_4_9_1_10_7_3_2_6_7_6_4_6_1_2_10_7_11_6_5_1_10_7_6_4_3_2_2_1_1_5_7_5_10_7_6_7_3_2_7_6_3_9_7_1_1_1_8_4_8_5_8_1_10_7_2_2_10_3_10_5_3_2_8_7_10_7_5_7_7_9_6_2_11_7_9_4_7_7_8_3_4_9_1_9_7_2_5_7_4_5_10_5_1_6_8_2_9_7_2_9_4_8_7_4_1_5_4_2_8_3_8_1_3_2_9_9_2_5_6_6_8_7_3_5_8_4_1_7_5_3_10_6_2_7_6_9_9_6_2_2_1_8_7_3_1_7_2_4_1_4_7_4_5_6_2_2_2_5_6_4_8_2_10_6_11_3_3_10_2_2_9_8_3_7_6_7_11_2_7_7_1_8_5_4_10_5_1_4_9_5_1_9_8_6_6_6_5_6_4_7_10_7_7_3_8_6_5_1_9_3_5_6_9_11_4_8_3_4_3_3_1_2_9_5_5_2_9_5_6_2_8_2_3_2_9_3_2_3_4_4_4_5_3_10_4_6_8_5_6_1_1_10_3_1_5_2_5_1_4_3_7_8_4_2_2_1_2_4_1_7_8_8_2_1_1_2_8_5_1_1_8_2_5_5_6_1_7_6_5_1_9_4_4_10_5_2_5_1_5_5_3_8_1_4_6_8_2_1_1_6_1_11_6_2_2_4_4_10_3_6_3_10_2_2_4_7_3_2_7_7_3_2_1_8_8_4_3_8_4_2_9_7_4_5_8_9_1_3_4_3_5_1_4_7_9_2_4_10_7_3_4_8_8_6_1_4_8_2_4_5_1_6_2_3_8_6_5_2_4_4_1_10_3_10_7_10_5_3_1_5_6_7_5_7_9_6_10_4_1_3_3_1_2_4_5_8_6_9_4_8_4_5_2_6_5_7_6_1_2_1_7_3_5_4_6_8_3_8_6_2_1_7_8_5_4_8_10_2_6_8_7_4_7_1_3_4_7_1_8_9_9_7_5_5_5_2_8_7_1_4_5_3_9_8_7_6_3_1_9_9_7_8_3_1_1_1_9_3_8_3_6_6_3_3_10_5_3_8_4_2_1_2_2_6_2_6_11_6</t>
+  </si>
+  <si>
+    <t>11_11_11</t>
+  </si>
+  <si>
+    <t>8_6_6_8_4_5_10_10_5_6_1_2_1_6_8_2_10_7_8_3_9_9_4_10_1_9_9_2_3_1_3_4_5_4_4_1_5_5_5_5_1_10_9_9_2_3_3_3_2_8_5_3_1_4_1_4_6_5_6_4_5_5_3_1_7_7_7_6_2_10_1_2_2_2_2_3_3_3_8_5_2_3_9_5_7_1_4_4_2_5_1_1_3_8_6_3_1_5_1_2_3_7_2_5_3_8_2_5_10_10_4_1_4_1_4_3_8_5_6_9_1_1_3_9_6_6_5_10_3_3_2_9_6_1_1_1_1_8_1_8_9_3_8_8_3_2_2_4_5_7_7_2_1_1_6_1_2_4_7_7_8_1_1_2_9_3_9_2_9_7_7_2_2_2_10_6_4_6_6_9_1_6_4_8_5_7_6_4_10_3_7_4_9_6_1_2_2_1_1_1_5_1_5_1_3_3_5_1_1_5_8_1_6_4_7_6_2_1_2_5_1_7_5_9_3_10_5_3_2_4_6_3_9_9_1_3_1_4_10_3_3_2_5_5_5_3_5_4_3_1_4_4_8_8_1_8_3_3_2_5_4_1_7_3_1_4_4_2_1_3_5_1_2_2_9_4_4_3_2_4_9_1_5_5_1_2_5_5_2_8_9_7_9_2_2_1_1_2_2_8_4_4_8_8_8_6_8_8_8_4_1_1_3_8_4_4_10_6_2_8_9_9_6_2_2_6_4_4_4_8_2_2_1_1_4_8_1_2_3_9_8_1_4_2_4_3_7_3_5_2_1_1_4_6_6_5_3_3_2_1_3_10_5_4_1_1_7_1_8_2_2_3_4_4_8_6_4_2_3_7_2_3_5_8_2_6_6_7_1_1_6_4_3_5_5_1_8_4_5_2_10_3_4_3_4_7_4_6_10_7_7_9_1_2_7_2_9_2_5_5_7_2_7_5_3_1_3_3_5_2_3_4_3_3_2_10_10_7_4_5_3_8_8_5_2_1_6_2_6_4_5_4_2_4_5_2_3_8_5_5_10_2_6_3_5_2_7_4_5_8_5_6_4_1_1_4_4_1_3_1_1_8_6_2_5_6_6_5_8_9_1_1_3_10_6_8_4_7_10_1</t>
+  </si>
+  <si>
+    <t>2_6_4_1_1_5_10_6_2_5_3_4_1_4_10_7_3_7_3_3_9_10_7_10_4_3_6_11_7_8_2_9_9_2_4_1_3_5_5_10_7_4_9_1_2_8_2_3_1_6_5_3_8_8_6_5_11_4_1_4_10_5_1_1_3_2_2_2_5_9_3_4_2_1_4_10_5_6_3_6_2_1_10_7_5_2_3_9_11_4_6_7_1_4_5_5_3_2_5_9_7_2_6_1_1_3_6_1_5_7_7_11_7_7_11_6_4_6_5_3_5_3_2_3_8_9_10_4_4_8_3_2_7_6_5_8_3_9_9_8_2_10_5_6_3_7_6_4_4_1_1_4_8_2_4_8_3_11_6_4_2_8_6_1_3_5_2_11_7_2_9_8_9_3_1_5_9_9_1_1_4_3_4_2_10_3_2_1_2_3_4_1_5_1_7_2_6_8_4_5_8_3_5_5_2_1_5_10_6_3_1_3_8_10_7_2_1_10_2_7_1_4_2_8_1_7_3_6_4_5_1_11_4_10_4_11_5_5_3_8_2_4_2_11_2_4_3_2_9_1_1_8_2_1_4_1_8_2_4_9_3_3_1_7_9_9_8_6_2_10_3_6_1_4_1_4_4_1_1_11_5_8_9_1_5_4_1_9_9_1_9_1_1_3_6_1_4_1_10_5_6_1_11_6_11_5_2_4_1_1_5_6_4_8_3_6_2_5_9_2_5_11_7_9_4_6_1_1_9_6_7_7_3_9_1_7_2_9_5_9_6_10_5_4_6_7_8_3_7_10_4_11_7_7_5_3_6_6_7_8_3_4_9_4_3_2_5_3_3_8_4_4_7_1_9_1_8_1_4_6_5_1_8_1_7_3_7_2_2_6_11_7_1_9_4_7_9_6_8_2_6_1_2_1_7_7_2_8_4_6_11_7_1_5_1_5_7_3_5_4_4_6_3_3_9_10_2_2_2_6_9_4_1_2_3_6_10_6_7_10_4_4_4_9_3_2_5_3_2_6_10_5_2_9_6_3_1_4_7_7_5_2_5_6_6_6_9_1_11_5_5_8_3_1_1_4_8_5_2_2_2_5_2_7_6_10_4_1_8_1_2_4_6_5_5_2_2_10_2_4</t>
   </si>
 </sst>
 </file>
@@ -2146,7 +2188,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K177"/>
+  <dimension ref="A1:K188"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -4994,7 +5036,7 @@
         <v>1</v>
       </c>
       <c r="E90" s="18" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>20</v>
@@ -5026,7 +5068,7 @@
         <v>2</v>
       </c>
       <c r="E91" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>20</v>
@@ -5090,7 +5132,7 @@
         <v>1</v>
       </c>
       <c r="E93" s="18" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>20</v>
@@ -5122,7 +5164,7 @@
         <v>2</v>
       </c>
       <c r="E94" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>20</v>
@@ -5186,7 +5228,7 @@
         <v>1</v>
       </c>
       <c r="E96" s="18" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>20</v>
@@ -5218,7 +5260,7 @@
         <v>2</v>
       </c>
       <c r="E97" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>20</v>
@@ -5282,7 +5324,7 @@
         <v>1</v>
       </c>
       <c r="E99" s="18" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>20</v>
@@ -5314,7 +5356,7 @@
         <v>2</v>
       </c>
       <c r="E100" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>20</v>
@@ -5378,7 +5420,7 @@
         <v>1</v>
       </c>
       <c r="E102" s="18" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>20</v>
@@ -5410,7 +5452,7 @@
         <v>2</v>
       </c>
       <c r="E103" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>20</v>
@@ -5474,7 +5516,7 @@
         <v>1</v>
       </c>
       <c r="E105" s="18" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>20</v>
@@ -5506,7 +5548,7 @@
         <v>2</v>
       </c>
       <c r="E106" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>20</v>
@@ -6434,7 +6476,7 @@
         <v>1</v>
       </c>
       <c r="E135" s="18" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>20</v>
@@ -6466,7 +6508,7 @@
         <v>2</v>
       </c>
       <c r="E136" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>20</v>
@@ -6530,7 +6572,7 @@
         <v>1</v>
       </c>
       <c r="E138" s="18" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>20</v>
@@ -6562,7 +6604,7 @@
         <v>2</v>
       </c>
       <c r="E139" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>20</v>
@@ -6626,7 +6668,7 @@
         <v>1</v>
       </c>
       <c r="E141" s="18" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>20</v>
@@ -6658,7 +6700,7 @@
         <v>2</v>
       </c>
       <c r="E142" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>20</v>
@@ -6722,7 +6764,7 @@
         <v>1</v>
       </c>
       <c r="E144" s="18" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>20</v>
@@ -6754,7 +6796,7 @@
         <v>2</v>
       </c>
       <c r="E145" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>20</v>
@@ -6818,7 +6860,7 @@
         <v>1</v>
       </c>
       <c r="E147" s="18" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>20</v>
@@ -6850,7 +6892,7 @@
         <v>2</v>
       </c>
       <c r="E148" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>20</v>
@@ -6914,7 +6956,7 @@
         <v>1</v>
       </c>
       <c r="E150" s="18" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>20</v>
@@ -6946,7 +6988,7 @@
         <v>2</v>
       </c>
       <c r="E151" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>20</v>
@@ -7157,7 +7199,7 @@
     </row>
     <row r="158" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A158" s="6">
-        <f t="shared" ref="A158:A172" si="7">C158*10+D158</f>
+        <f t="shared" ref="A158:A177" si="7">C158*10+D158</f>
         <v>20200021</v>
       </c>
       <c r="B158" s="14">
@@ -7637,7 +7679,7 @@
     </row>
     <row r="173" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A173" s="6">
-        <f>C173*10+D173</f>
+        <f t="shared" si="7"/>
         <v>20270011</v>
       </c>
       <c r="B173" s="14">
@@ -7669,7 +7711,7 @@
     </row>
     <row r="174" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A174" s="6">
-        <f>C174*10+D174</f>
+        <f t="shared" si="7"/>
         <v>20270012</v>
       </c>
       <c r="B174" s="14">
@@ -7701,7 +7743,7 @@
     </row>
     <row r="175" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A175" s="6">
-        <f>C175*10+D175</f>
+        <f t="shared" si="7"/>
         <v>20270013</v>
       </c>
       <c r="B175" s="14">
@@ -7733,7 +7775,7 @@
     </row>
     <row r="176" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A176" s="6">
-        <f>C176*10+D176</f>
+        <f t="shared" si="7"/>
         <v>20270014</v>
       </c>
       <c r="B176" s="14">
@@ -7765,7 +7807,7 @@
     </row>
     <row r="177" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A177" s="6">
-        <f>C177*10+D177</f>
+        <f t="shared" si="7"/>
         <v>20270015</v>
       </c>
       <c r="B177" s="14">
@@ -7794,6 +7836,358 @@
       </c>
       <c r="J177" s="17"/>
       <c r="K177" s="17"/>
+    </row>
+    <row r="178" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A178" s="6">
+        <f t="shared" ref="A178:A183" si="8">C178*10+D178</f>
+        <v>20370011</v>
+      </c>
+      <c r="B178" s="14">
+        <v>103700</v>
+      </c>
+      <c r="C178" s="33">
+        <v>2037001</v>
+      </c>
+      <c r="D178" s="33">
+        <v>1</v>
+      </c>
+      <c r="E178" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H178" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I178" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J178" s="17"/>
+      <c r="K178" s="17"/>
+    </row>
+    <row r="179" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A179" s="6">
+        <f t="shared" si="8"/>
+        <v>20370012</v>
+      </c>
+      <c r="B179" s="14">
+        <v>103700</v>
+      </c>
+      <c r="C179" s="33">
+        <v>2037001</v>
+      </c>
+      <c r="D179" s="33">
+        <v>2</v>
+      </c>
+      <c r="E179" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H179" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I179" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="J179" s="17"/>
+      <c r="K179" s="17"/>
+    </row>
+    <row r="180" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A180" s="6">
+        <f t="shared" si="8"/>
+        <v>20370013</v>
+      </c>
+      <c r="B180" s="14">
+        <v>103700</v>
+      </c>
+      <c r="C180" s="33">
+        <v>2037001</v>
+      </c>
+      <c r="D180" s="33">
+        <v>3</v>
+      </c>
+      <c r="E180" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H180" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I180" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J180" s="17"/>
+      <c r="K180" s="17"/>
+    </row>
+    <row r="181" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A181" s="6">
+        <f t="shared" si="8"/>
+        <v>20370021</v>
+      </c>
+      <c r="B181" s="14">
+        <v>103700</v>
+      </c>
+      <c r="C181" s="33">
+        <v>2037002</v>
+      </c>
+      <c r="D181" s="33">
+        <v>1</v>
+      </c>
+      <c r="E181" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G181" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="H181" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I181" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="J181" s="17"/>
+      <c r="K181" s="17"/>
+    </row>
+    <row r="182" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A182" s="6">
+        <f t="shared" si="8"/>
+        <v>20370022</v>
+      </c>
+      <c r="B182" s="14">
+        <v>103700</v>
+      </c>
+      <c r="C182" s="33">
+        <v>2037002</v>
+      </c>
+      <c r="D182" s="33">
+        <v>2</v>
+      </c>
+      <c r="E182" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G182" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="H182" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I182" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="J182" s="17"/>
+      <c r="K182" s="17"/>
+    </row>
+    <row r="183" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A183" s="6">
+        <f t="shared" si="8"/>
+        <v>20370023</v>
+      </c>
+      <c r="B183" s="14">
+        <v>103700</v>
+      </c>
+      <c r="C183" s="33">
+        <v>2037002</v>
+      </c>
+      <c r="D183" s="33">
+        <v>3</v>
+      </c>
+      <c r="E183" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="H183" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I183" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="J183" s="17"/>
+      <c r="K183" s="17"/>
+    </row>
+    <row r="184" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A184" s="6">
+        <f>C184*10+D184</f>
+        <v>20310011</v>
+      </c>
+      <c r="B184" s="14">
+        <v>103100</v>
+      </c>
+      <c r="C184" s="33">
+        <v>2031001</v>
+      </c>
+      <c r="D184" s="33">
+        <v>1</v>
+      </c>
+      <c r="E184" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="H184" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I184" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="J184" s="17"/>
+      <c r="K184" s="17"/>
+    </row>
+    <row r="185" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A185" s="6">
+        <f>C185*10+D185</f>
+        <v>20310012</v>
+      </c>
+      <c r="B185" s="14">
+        <v>103100</v>
+      </c>
+      <c r="C185" s="33">
+        <v>2031001</v>
+      </c>
+      <c r="D185" s="33">
+        <v>2</v>
+      </c>
+      <c r="E185" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="H185" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I185" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="J185" s="17"/>
+      <c r="K185" s="17"/>
+    </row>
+    <row r="186" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A186" s="6">
+        <f>C186*10+D186</f>
+        <v>20310013</v>
+      </c>
+      <c r="B186" s="14">
+        <v>103100</v>
+      </c>
+      <c r="C186" s="33">
+        <v>2031001</v>
+      </c>
+      <c r="D186" s="33">
+        <v>3</v>
+      </c>
+      <c r="E186" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="H186" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I186" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="J186" s="17"/>
+      <c r="K186" s="17"/>
+    </row>
+    <row r="187" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A187" s="6">
+        <f>C187*10+D187</f>
+        <v>20310014</v>
+      </c>
+      <c r="B187" s="14">
+        <v>103100</v>
+      </c>
+      <c r="C187" s="33">
+        <v>2031001</v>
+      </c>
+      <c r="D187" s="33">
+        <v>4</v>
+      </c>
+      <c r="E187" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="H187" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I187" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="J187" s="17"/>
+      <c r="K187" s="17"/>
+    </row>
+    <row r="188" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A188" s="6">
+        <f>C188*10+D188</f>
+        <v>20310015</v>
+      </c>
+      <c r="B188" s="14">
+        <v>103100</v>
+      </c>
+      <c r="C188" s="33">
+        <v>2031001</v>
+      </c>
+      <c r="D188" s="33">
+        <v>5</v>
+      </c>
+      <c r="E188" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="H188" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I188" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="J188" s="17"/>
+      <c r="K188" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -4774,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="E90" s="18" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>20</v>
@@ -4806,7 +4806,7 @@
         <v>2</v>
       </c>
       <c r="E91" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>20</v>
@@ -4870,7 +4870,7 @@
         <v>1</v>
       </c>
       <c r="E93" s="18" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>20</v>
@@ -4902,7 +4902,7 @@
         <v>2</v>
       </c>
       <c r="E94" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>20</v>
@@ -4966,7 +4966,7 @@
         <v>1</v>
       </c>
       <c r="E96" s="18" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>20</v>
@@ -4998,7 +4998,7 @@
         <v>2</v>
       </c>
       <c r="E97" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>20</v>
@@ -5062,7 +5062,7 @@
         <v>1</v>
       </c>
       <c r="E99" s="18" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>20</v>
@@ -5094,7 +5094,7 @@
         <v>2</v>
       </c>
       <c r="E100" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>20</v>
@@ -5158,7 +5158,7 @@
         <v>1</v>
       </c>
       <c r="E102" s="18" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>20</v>
@@ -5190,7 +5190,7 @@
         <v>2</v>
       </c>
       <c r="E103" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>20</v>
@@ -5254,7 +5254,7 @@
         <v>1</v>
       </c>
       <c r="E105" s="18" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>20</v>
@@ -5286,7 +5286,7 @@
         <v>2</v>
       </c>
       <c r="E106" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>20</v>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoller" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="281">
   <si>
     <t>id</t>
   </si>
@@ -875,6 +875,54 @@
   </si>
   <si>
     <t>2_6_4_1_1_5_10_6_2_5_3_4_1_4_10_7_3_7_3_3_9_10_7_10_4_3_6_11_7_8_2_9_9_2_4_1_3_5_5_10_7_4_9_1_2_8_2_3_1_6_5_3_8_8_6_5_11_4_1_4_10_5_1_1_3_2_2_2_5_9_3_4_2_1_4_10_5_6_3_6_2_1_10_7_5_2_3_9_11_4_6_7_1_4_5_5_3_2_5_9_7_2_6_1_1_3_6_1_5_7_7_11_7_7_11_6_4_6_5_3_5_3_2_3_8_9_10_4_4_8_3_2_7_6_5_8_3_9_9_8_2_10_5_6_3_7_6_4_4_1_1_4_8_2_4_8_3_11_6_4_2_8_6_1_3_5_2_11_7_2_9_8_9_3_1_5_9_9_1_1_4_3_4_2_10_3_2_1_2_3_4_1_5_1_7_2_6_8_4_5_8_3_5_5_2_1_5_10_6_3_1_3_8_10_7_2_1_10_2_7_1_4_2_8_1_7_3_6_4_5_1_11_4_10_4_11_5_5_3_8_2_4_2_11_2_4_3_2_9_1_1_8_2_1_4_1_8_2_4_9_3_3_1_7_9_9_8_6_2_10_3_6_1_4_1_4_4_1_1_11_5_8_9_1_5_4_1_9_9_1_9_1_1_3_6_1_4_1_10_5_6_1_11_6_11_5_2_4_1_1_5_6_4_8_3_6_2_5_9_2_5_11_7_9_4_6_1_1_9_6_7_7_3_9_1_7_2_9_5_9_6_10_5_4_6_7_8_3_7_10_4_11_7_7_5_3_6_6_7_8_3_4_9_4_3_2_5_3_3_8_4_4_7_1_9_1_8_1_4_6_5_1_8_1_7_3_7_2_2_6_11_7_1_9_4_7_9_6_8_2_6_1_2_1_7_7_2_8_4_6_11_7_1_5_1_5_7_3_5_4_4_6_3_3_9_10_2_2_2_6_9_4_1_2_3_6_10_6_7_10_4_4_4_9_3_2_5_3_2_6_10_5_2_9_6_3_1_4_7_7_5_2_5_6_6_6_9_1_11_5_5_8_3_1_1_4_8_5_2_2_2_5_2_7_6_10_4_1_8_1_2_4_6_5_5_2_2_10_2_4</t>
+  </si>
+  <si>
+    <t>1_2_2_4_2_2_2_3_3_3_8_7_7_1_5_1_1_6_2_1_2_8_7_2_3_3_1_4_6_7_6_3_3_8_8_8_2_2_1_1_4_4_7_3_2_7_7_7_7_2_7_4_4_2_7_7_7_8_8_8_2_4_8_4_8_8_7_7_1_4_7_5_2_2_8_8_8_1_2_1_1_7_7_4_2_2_2_2_2_8_5_2_6_6_1_8_4_1_3_3_3_2_3_3_6_4_1_1_1_4_4_1_2_1_1_2_3_8_8_8_8_2_8_4_3_4_3_5_1_2_4_4_7_2_7_2_5_8_8_5_6_1_5_3_1_5_5_4_4_1_1_1_6_8_6_2_2_7_8_1_2_1_1_2_1_1_1_2_4_4_2_4_5_4_8_3_1_1_6_3_1_2_1_1_8_2_2_2_3_4_7_8_2_6_4_2_2_4_4_5_6_6_5_5_3_1_8_8_2_2_4_2_3_3_1_5_2_3_1_2_1_1_1_8_8_4_4_1_1_7_4_4_1_5_6_4_4_8_8_6_6_6_8_7_6_7_5_5_5_6_3_3_5_8_3_2_4_3_8_3_6_7_1_3_4_8_3_2_1_8_8_8_8_8_4_2_7_1_4_4_4_7_1_1_3_3_3_8_1_4_3_2_7_1_8_4_8_4_8_2_1_8_7_4_4_4_4_2_3_1_8_7_3_3_2_2_8_8_4_4_2_6_6_2_2_4_8_4_3_6_4_8_7_3_2_2_1_7_2_2_2_7_1_1_1_1_1_8_8_7_3_2_2_2_1_3_8_7_4_6_3_4_6_3_2_8_6_6_6_6_3_1_7_3_2_7_2_7_1_8_1_4_1_2_1_7_1_1_1_4_1_2_2_4_6_1_5_1_3_7_5_3_3_3_1_8_2_2_6_2_1_7_6_1_3_1_4_7_7_7_7_5_8_4_8_7_2_1_7_4_4_2_2_8_8_8_3_1_1_2_6_1_7_2_2_4_7_8_1_6_2_5_2_7_2_2_8_1_1_5_7_2_4_1_7_1_2_4_3_3_3_7_2_1_3_3_4_7_1_7_4_7_1_7_4_2_5_5_3_4_7_3_8_7_3_3_1_2_6_2</t>
+  </si>
+  <si>
+    <t>4_2_7_5_8_7_6_7_3_6_7_8_7_6_2_3_7_4_8_4_3_1_5_7_2_6_6_7_8_2_7_5_1_7_4_1_6_4_4_7_5_2_5_1_3_6_2_3_2_1_2_9_3_6_6_7_2_8_3_2_7_4_2_4_8_2_3_1_4_2_6_6_6_8_4_3_8_1_4_2_5_4_2_3_5_7_6_3_1_4_1_5_7_4_6_3_3_4_2_1_6_1_4_9_2_3_7_3_7_1_2_7_8_9_1_4_2_7_3_5_1_4_4_1_8_8_6_8_9_2_1_3_1_3_2_1_7_8_7_5_7_6_9_3_3_3_1_4_3_3_6_2_3_4_1_7_1_7_9_7_6_7_2_1_8_2_7_2_6_6_3_4_2_1_3_1_2_4_1_4_5_8_7_3_6_8_7_3_2_9_2_8_7_3_5_2_4_3_1_9_9_8_5_2_7_9_5_4_3_3_9_8_5_2_1_4_4_7_6_3_1_9_4_7_8_5_6_9_5_3_4_2_8_8_8_3_3_3_2_1_3_6_3_6_5_1_4_8_4_9_2_3_5_1_1_8_3_3_1_5_2_3_9_6_1_5_2_2_9_7_6_5_1_1_1_2_6_5_6_1_3_4_4_5_1_6_6_4_8_7_6_2_4_1_4_8_9_2_1_3_7_6_1_2_3_8_2_1_2_4_6_3_6_4_1_3_9_6_4_4_2_5_1_2_1_4_4_2_1_2_1_8_1_6_6_2_5_6_2_3_5_4_3_5_9_8_8_5_9_8_1_5_5_2_1_6_3_8_4_1_6_4_6_9_2_8_1_6_5_8_8_7_6_1_2_7_7_1_8_7_5_7_3_1_1_9_5_7_7_3_8_6_2_8_4_6_7_5_7_5_6_5_2_3_3_3_7_1_4_1_4_4_1_3_1_2_1_8_5_3_5_9_5_4_3_2_1_3_6_8_2_8_7_2_2_7_2_7_1_3_3_8_4_6_1_5_5_6_1_6_2_3_4_7_5_9_3_5_7_2_8_3_5_4_7_9_8_6_5_1_3_7_5_2_8_4_1_3_4_1_2_7_6_1_4_1_8_3_8_1_7_4_4_5_1_3_7_1_2_1</t>
+  </si>
+  <si>
+    <t>8_4_1_4_1_1_1_3_8_4_2_4_4_3_2_1_8_5_1_3_3_6_6_4_2_7_2_2_5_5_1_6_6_4_5_2_7_6_6_7_7_6_3_5_8_2_2_4_6_6_3_8_1_8_4_3_3_3_3_3_1_8_8_1_4_3_1_3_1_1_1_1_4_1_1_4_2_1_2_2_2_1_1_1_4_5_3_4_7_2_2_1_1_8_8_8_8_8_2_2_2_3_3_7_7_2_5_3_4_1_1_8_3_7_4_4_4_2_7_7_1_3_7_1_1_4_7_1_3_3_1_1_4_7_7_3_1_8_8_4_5_5_6_8_1_4_3_2_6_1_3_4_1_7_2_3_1_4_6_4_4_4_2_8_3_2_3_1_8_4_4_1_1_6_3_1_6_1_2_7_1_1_6_6_6_6_6_3_1_4_1_8_5_5_2_3_3_7_3_3_2_2_8_8_2_8_7_1_2_2_2_2_8_8_2_2_1_7_8_8_4_7_3_1_1_1_6_8_3_3_5_2_1_2_8_3_6_8_1_6_6_1_4_1_7_8_8_1_2_7_8_2_1_3_7_1_8_8_8_4_4_2_8_3_7_3_6_2_2_1_2_1_1_3_3_1_3_8_3_2_2_2_2_4_3_3_6_5_2_1_4_8_4_2_5_7_8_3_1_5_2_2_6_6_1_3_3_4_7_7_7_6_2_3_1_5_8_8_2_2_5_7_2_5_7_4_4_1_7_7_7_4_8_8_2_8_1_7_2_8_8_2_2_2_1_7_1_2_2_5_4_4_7_1_1_6_7_7_2_4_6_4_4_3_3_1_5_1_7_1_2_4_1_1_8_4_4_8_4_7_1_7_6_7_7_6_2_2_1_4_5_8_4_2_6_7_2_4_3_3_7_7_5_2_5_1_1_1_1_2_8_3_3_1_4_4_7_2_1_2_2_2_1_1_7_4_5_8_8_8_2_1_2_1_1_1_3_7_1_7_7_3_3_2_6_4_4_1_4_6_1_1_2_8_3_4_1_4_1_1_8_6_7_1_1_5_1_7_3_7_2_1_2_1_3_3_1_1_2_3_3_1_1_3_2_2_2_3_7_8_6_6_2_1_1_8_2_2_4_3</t>
+  </si>
+  <si>
+    <t>2_2_9_8_2_1_7_2_9_4_8_8_1_1_2_1_6_4_1_2_3_2_4_3_3_3_7_2_6_4_6_4_5_4_1_4_3_2_2_4_4_1_3_6_8_8_7_8_1_3_6_3_3_4_5_5_2_6_8_4_1_1_8_1_6_1_1_6_3_4_4_4_7_1_7_6_5_4_9_3_2_2_4_6_7_6_6_1_3_4_3_7_3_5_1_5_9_1_1_5_1_2_6_1_6_2_2_3_6_4_6_3_6_8_4_2_7_8_3_1_7_8_2_8_2_4_3_2_5_7_1_6_3_9_9_2_7_6_4_3_8_2_2_8_6_8_1_9_9_4_3_7_1_1_4_8_1_6_2_1_7_4_4_9_7_5_7_3_3_2_1_7_4_5_6_3_1_3_4_2_1_3_2_1_7_7_8_8_9_2_7_1_4_4_1_8_7_3_4_6_1_6_1_5_6_9_8_7_3_2_4_2_2_8_5_3_3_8_1_4_3_8_3_7_4_3_5_2_1_3_2_2_2_2_3_8_3_6_6_3_2_1_6_1_2_9_2_4_6_5_7_9_7_1_1_1_4_1_9_3_3_6_8_2_4_1_8_2_8_7_1_4_1_2_4_4_2_3_9_9_6_1_2_3_1_7_8_9_7_1_9_2_8_2_7_4_5_5_6_6_8_4_8_2_3_4_4_1_4_3_5_8_4_4_7_7_2_6_5_2_5_1_4_2_4_1_5_3_9_2_1_1_1_4_2_7_4_4_7_5_4_6_8_8_4_1_4_4_2_1_6_3_6_9_2_5_7_4_1_4_6_3_6_1_9_2_2_2_3_5_4_8_5_9_3_9_1_3_6_4_8_8_3_6_3_7_1_7_1_3_9_7_4_1_4_3_3_3_6_5_6_7_8_7_2_4_3_8_7_9_6_7_6_7_3_7_8_2_9_5_8_3_4_7_3_2_1_5_5_5_3_1_4_1_7_5_5_7_5_6_4_1_4_5_5_1_4_2_3_2_4_9_2_6_3_1_8_2_2_8_9_3_8_3_5_2_2_6_5_4_6_1_1_7_4_9_9_1_4_7_3_3_7_6_8_3_2_9_5_6_1_8_6_4_4_3_2_5_1_5</t>
+  </si>
+  <si>
+    <t>7_7_8_4_3_4_3_3_2_3_1_2_2_8_1_2_1_4_4_7_7_1_8_8_1_4_1_2_2_1_1_1_3_5_8_2_1_1_1_7_6_6_5_2_2_8_8_1_4_5_5_7_7_7_7_7_4_3_2_8_1_1_5_8_1_1_3_2_2_7_8_1_3_7_4_4_3_3_4_1_4_4_6_2_4_7_1_8_8_7_4_4_7_4_4_7_6_3_2_3_2_3_7_7_3_6_2_2_5_3_7_2_6_2_8_2_1_7_5_3_7_3_8_1_8_6_1_6_5_7_2_8_8_2_4_8_8_8_8_8_8_8_3_1_8_3_6_2_2_7_1_4_5_2_8_1_3_7_5_3_3_5_3_4_4_1_8_7_3_2_1_7_7_3_5_4_7_3_1_1_1_3_1_8_8_4_4_1_8_1_3_6_1_1_1_3_8_3_2_8_3_1_3_1_1_4_5_8_4_7_7_7_6_4_2_2_2_4_4_1_6_8_7_7_6_3_8_8_2_3_4_1_1_8_8_2_2_8_2_8_4_2_2_1_7_1_8_7_5_8_8_3_6_4_2_8_2_3_2_7_1_1_8_6_1_7_7_2_6_1_3_4_4_8_1_6_4_4_8_8_7_1_6_1_5_5_1_5_7_2_7_8_8_3_7_8_5_1_6_2_1_4_4_8_2_1_2_6_1_6_7_4_4_4_2_1_1_5_6_3_7_8_1_6_3_4_2_7_7_1_1_5_1_2_2_2_5_5_5_4_1_1_1_6_1_1_4_3_2_2_4_4_2_2_4_6_6_4_8_5_1_8_5_3_5_7_1_7_1_8_6_3_6_5_8_3_5_6_1_5_1_3_1_8_1_1_4_1_4_1_2_4_8_1_7_1_5_6_6_6_2_8_3_7_1_4_2_3_4_8_5_6_3_2_6_6_2_8_6_5_2_2_3_3_6_3_1_2_8_6_6_3_3_4_8_5_4_1_4_1_1_1_2_2_2_7_1_1_3_2_6_1_3_8_7_1_1_8_8_8_2_7_3_7_1_7_7_8_2_3_4_4_4_6_7_4_2_6_2_2_3_3_6_4_6_8_8_5_5_2_2_3_7_1_7_7_2_3_1_3</t>
+  </si>
+  <si>
+    <t>6_7_2_3_7_3_7_6_8_4_8_4_1_7_5_3_3_4_9_2_6_5_5_4_8_2_6_5_4_4_2_2_2_9_5_5_2_7_1_5_8_5_2_8_2_6_2_2_1_8_8_6_1_7_4_3_3_8_4_3_7_7_1_5_3_4_8_8_6_7_2_2_3_3_4_4_1_3_8_1_9_2_2_3_5_4_8_4_6_2_3_2_4_6_3_7_8_6_3_2_6_2_1_4_8_3_6_5_7_5_8_8_3_2_2_6_1_5_6_9_8_4_1_3_2_4_4_5_2_1_5_2_5_3_9_6_8_6_4_9_7_3_6_6_2_6_5_7_8_2_2_7_5_3_4_1_2_1_3_1_6_3_1_3_3_7_2_2_5_1_2_2_4_3_6_3_4_9_2_3_2_8_3_3_2_1_7_2_5_2_5_6_3_2_4_3_2_4_1_4_1_5_4_5_6_3_7_5_2_8_5_3_1_7_4_4_3_2_1_8_7_4_5_5_5_1_5_3_1_6_3_7_1_8_4_3_2_6_7_5_6_3_2_3_2_3_3_4_8_8_8_3_2_9_9_2_8_2_2_7_4_4_2_4_3_2_9_4_6_3_8_6_8_3_3_2_7_4_8_2_1_5_5_2_1_2_7_6_8_4_4_1_2_3_8_7_1_9_9_4_6_2_8_1_8_5_6_2_5_1_9_1_7_7_6_4_9_8_4_2_3_1_1_1_7_4_5_4_5_1_2_4_9_7_3_9_1_9_3_8_3_3_9_5_4_2_2_5_8_4_4_8_5_7_4_4_3_2_8_9_3_5_3_7_2_7_1_8_6_3_3_3_4_1_7_2_8_2_2_8_2_8_2_1_2_2_2_2_8_5_3_3_7_9_9_8_6_8_2_4_2_7_7_1_6_6_2_2_7_5_1_6_1_1_1_6_8_9_1_4_9_4_8_1_6_8_6_7_5_8_2_5_2_2_2_9_5_6_8_2_5_2_7_6_8_1_6_8_1_2_2_2_7_8_5_3_5_8_9_6_6_3_5_4_2_2_8_4_2_3_5_1_1_4_9_1_1_4_4_5_3_6_3_1_4_7_6_4_3_2_2_1_4_5_4_3_6_5_4_5</t>
+  </si>
+  <si>
+    <t>6_1_8_2_8_4_6_3_3_6_8_6_7_8_8_8_6_8_6_7_8_2_7_3_1_2_3_3_1_3_2_6_2_3_3_7_7_4_6_1_1_2_2_1_7_3_8_4_2_2_2_5_8_6_4_4_4_1_6_6_7_2_2_3_6_5_6_5_4_4_1_6_8_5_6_7_6_6_1_1_6_8_4_1_7_4_1_8_1_2_1_4_3_3_6_4_5_7_1_1_7_2_8_1_7_1_5_1_3_6_3_1_8_1_1_8_2_6_1_1_5_3_1_1_8_4_4_2_3_4_3_2_2_1_5_3_5_5_5_6_2_5_2_1_3_2_2_2_7_7_7_1_8_3_1_4_1_1_7_7_6_5_3_4_4_5_6_2_1_8_1_4_4_2_3_3_3_6_8_6_7_8_8_1_2_4_1_6_8_1_4_3_5_8_4_1_1_3_4_4_4_4_5_5_4_4_6_2_8_4_3_6_7_1_7_3_4_6_7_7_7_3_1_5_2_7_4_8_1_2_2_1_5_4_4_8_8_6_1_2_1_2_4_4_3_3_1_7_4_1_4_1_4_1_7_7_1_3_6_1_1_4_3_1_5_5_6_8_1_4_8_2_1_3_5_8_1_7_2_4_5_1_4_1_5_5_7_2_8_7_1_2_2_7_7_2_5_5_1_6_1_1_1_4_8_8_1_2_2_4_7_2_7_3_3_3_3_6_7_7_1_4_6_2_4_4_3_4_1_1_1_3_7_3_3_4_5_2_6_2_2_8_2_4_1_2_6_5_2_8_8_8_1_4_2_3_4_7_7_6_1_7_2_2_7_7_7_1_2_6_2_7_6_8_2_1_7_2_2_8_6_8_5_1_6_2_7_2_2_7_8_4_4_4_2_6_8_1_7_3_1_7_7_1_3_6_1_8_8_1_8_1_1_4_6_2_2_2_3_8_7_7_4_4_4_5_3_1_1_3_1_1_1_7_4_4_3_8_1_3_1_1_2_1_2_3_3_3_5_7_7_7_7_8_2_2_2_2_6_2_3_2_1_2_3_6_3_3_2_4_5_4_1_8_2_1_1_3_4_2_7_5_3_8_3_3_4_5_5_5_8_2_7_8_7_6_4_2_2_4</t>
+  </si>
+  <si>
+    <t>6_8_1_2_6_8_3_6_5_9_4_3_7_6_3_7_7_6_9_7_5_6_2_8_3_5_9_1_2_5_2_5_2_4_6_2_3_3_2_3_8_3_1_8_2_4_2_1_1_4_9_3_1_8_8_7_3_5_6_5_1_4_2_6_3_5_3_8_3_6_1_2_9_7_5_3_8_9_2_3_7_2_2_5_3_6_1_3_3_5_8_1_9_9_2_1_8_1_3_9_2_9_4_6_2_5_7_7_9_1_2_8_3_8_2_5_2_6_8_7_1_8_1_1_9_8_4_6_9_1_5_4_1_8_9_9_3_7_1_6_7_3_2_7_3_2_9_4_6_2_1_3_8_8_7_6_7_5_1_5_4_9_2_7_7_1_5_7_7_7_3_4_2_1_5_5_3_3_5_1_1_5_3_1_6_1_3_1_1_4_1_1_3_7_2_2_6_1_2_5_5_3_1_7_3_4_2_4_7_2_7_2_4_2_8_8_4_5_6_8_2_5_1_1_7_3_1_7_4_3_8_9_8_2_7_2_1_1_2_2_5_4_6_2_5_9_4_7_3_7_7_8_3_2_3_4_6_9_3_4_1_4_3_2_1_3_2_1_4_1_6_5_1_9_1_3_4_2_6_2_4_8_7_2_9_6_5_4_8_3_9_8_4_3_3_1_5_8_6_3_1_1_5_1_2_2_1_9_3_8_1_4_5_6_9_5_7_2_2_1_4_3_8_1_9_7_9_7_3_5_8_5_8_9_7_4_6_3_1_8_1_4_8_3_1_9_5_2_1_6_2_7_2_3_2_1_7_4_5_2_6_6_8_2_3_2_8_4_2_4_6_4_1_7_5_3_2_8_3_5_4_7_1_6_2_7_1_8_4_6_1_5_1_2_6_3_4_4_3_8_5_8_7_3_1_4_9_6_8_3_1_2_3_4_2_9_1_7_3_1_8_8_2_1_2_1_5_4_5_1_5_7_1_3_9_7_7_2_2_1_3_7_4_9_1_2_2_1_1_9_4_6_4_1_4_3_3_6_6_3_6_5_7_1_7_8_6_9_1_6_5_4_2_5_2_3_3_9_8_6_2_5_1_3_2_6_7_3_9_6_7_9_6_1_1_6_5_2_4_6</t>
+  </si>
+  <si>
+    <t>1_3_3_4_2_5_4_2_1_8_7_8_8_8_2_3_2_7_4_3_7_7_7_6_1_1_5_2_8_8_8_2_1_2_8_8_2_2_2_2_1_3_3_7_1_2_4_4_2_4_4_6_3_3_5_5_4_1_7_1_1_7_8_4_2_7_3_8_3_8_8_8_4_3_1_5_2_7_3_7_8_8_5_7_3_3_2_2_3_8_3_7_8_3_3_1_1_3_4_8_1_3_1_4_8_7_4_1_1_1_2_7_8_8_1_7_4_3_1_3_2_2_7_6_3_4_6_6_2_1_1_6_7_1_4_1_7_1_1_2_2_1_3_6_6_2_1_1_2_8_2_1_1_1_3_2_7_4_4_8_3_7_1_3_2_7_3_1_7_8_4_7_4_2_4_4_4_6_2_6_4_1_5_8_2_6_4_1_6_7_1_6_4_1_8_8_1_2_1_6_1_1_3_1_4_8_3_2_2_7_1_1_2_1_7_7_7_4_4_2_4_2_2_3_4_4_7_3_2_1_8_3_8_8_8_8_6_2_8_7_2_6_1_3_8_1_2_2_8_2_2_4_4_2_7_7_2_6_7_2_2_1_5_3_5_2_6_6_1_8_4_7_2_7_2_1_1_1_5_1_1_3_1_1_6_2_3_4_4_7_2_3_1_1_4_3_7_6_6_2_2_4_1_1_5_5_8_2_4_1_4_2_2_1_1_4_2_4_7_1_1_1_1_1_6_8_2_2_1_8_8_1_1_8_1_8_7_4_8_8_1_5_2_1_1_6_4_4_4_4_1_5_3_1_1_4_5_8_3_4_1_5_2_2_5_7_2_2_3_1_7_6_4_1_1_7_7_7_4_7_3_4_2_6_3_1_2_8_7_6_4_2_4_5_4_4_2_1_7_7_1_1_1_4_1_3_3_7_1_6_2_1_3_3_3_4_5_1_7_8_2_1_8_3_1_6_6_2_2_5_4_3_1_1_1_4_6_6_5_2_3_7_3_1_2_8_1_5_5_4_1_1_2_1_2_5_1_6_2_1_1_1_1_6_7_2_4_5_1_5_4_6_1_3_2_1_6_4_3_3_3_3_4_1_2_3_3_4_2_6_5_7_3_2_1_6_1_7_1_1</t>
+  </si>
+  <si>
+    <t>2_9_2_1_2_8_1_1_8_3_1_4_7_3_2_1_5_3_4_3_2_7_6_2_7_7_3_2_5_6_6_8_1_1_5_8_6_7_3_1_9_8_4_1_1_2_2_5_5_2_1_8_4_1_1_3_4_1_1_2_8_8_3_9_9_2_6_7_9_4_9_8_2_1_1_9_8_7_7_5_8_4_1_1_5_2_8_5_1_1_3_2_4_8_8_3_3_2_9_2_3_2_9_9_6_6_7_2_4_1_2_1_2_3_6_7_1_9_1_4_4_6_4_3_1_4_6_8_5_3_5_2_9_4_1_2_2_9_8_8_1_7_3_2_6_8_6_5_1_9_6_4_1_2_9_4_6_2_9_8_9_5_4_2_1_8_8_3_3_2_1_7_1_3_9_8_3_1_6_2_3_6_1_2_4_5_6_4_3_7_8_7_1_4_7_6_8_1_3_3_1_4_9_8_5_9_3_3_4_4_2_4_3_6_1_3_5_3_4_3_3_5_2_1_1_3_5_3_1_4_3_2_9_6_2_2_7_2_1_8_6_6_7_4_7_7_3_6_4_4_9_4_5_7_5_5_6_1_7_1_8_9_3_4_2_4_2_1_8_4_2_1_4_5_7_1_5_8_6_6_3_3_7_5_2_6_9_3_5_9_8_6_2_4_6_1_4_7_2_1_8_8_4_2_4_5_2_6_5_7_9_1_8_1_2_1_7_3_5_2_5_4_3_8_4_8_6_5_7_5_1_8_3_3_4_2_2_2_5_2_6_9_3_6_2_5_2_4_5_4_5_6_4_9_7_6_6_6_2_1_8_5_1_3_6_2_2_4_6_3_9_3_5_1_9_1_7_7_2_9_6_1_9_7_2_4_4_6_6_6_8_8_6_3_3_1_7_5_2_1_3_7_8_1_7_5_4_2_7_1_2_4_4_9_5_2_2_9_2_1_2_6_8_8_1_6_6_2_6_3_9_8_4_1_5_4_5_1_2_2_9_3_1_3_4_8_5_1_2_7_3_1_5_8_5_2_3_1_5_4_2_3_6_3_7_4_1_7_8_6_4_3_4_8_6_4_8_3_2_6_3_5_2_1_8_3_4_6_8_6_6_6_6_4_2_1_6_2_1_7</t>
+  </si>
+  <si>
+    <t>6_6_6_6_6_6</t>
+  </si>
+  <si>
+    <t>7_7_7_7_7_7</t>
+  </si>
+  <si>
+    <t>8_8_8_8_8_8</t>
+  </si>
+  <si>
+    <t>9_9_9_9_9_9</t>
+  </si>
+  <si>
+    <t>10_10_10_10_10_10</t>
+  </si>
+  <si>
+    <t>11_11_11_11_11_11</t>
   </si>
 </sst>
 </file>
@@ -2188,7 +2236,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K188"/>
+  <dimension ref="A1:K204"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -7839,7 +7887,7 @@
     </row>
     <row r="178" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A178" s="6">
-        <f t="shared" ref="A178:A183" si="8">C178*10+D178</f>
+        <f t="shared" ref="A178:A204" si="8">C178*10+D178</f>
         <v>20370011</v>
       </c>
       <c r="B178" s="14">
@@ -8031,7 +8079,7 @@
     </row>
     <row r="184" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A184" s="6">
-        <f>C184*10+D184</f>
+        <f t="shared" si="8"/>
         <v>20310011</v>
       </c>
       <c r="B184" s="14">
@@ -8063,7 +8111,7 @@
     </row>
     <row r="185" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A185" s="6">
-        <f>C185*10+D185</f>
+        <f t="shared" si="8"/>
         <v>20310012</v>
       </c>
       <c r="B185" s="14">
@@ -8095,7 +8143,7 @@
     </row>
     <row r="186" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A186" s="6">
-        <f>C186*10+D186</f>
+        <f t="shared" si="8"/>
         <v>20310013</v>
       </c>
       <c r="B186" s="14">
@@ -8127,7 +8175,7 @@
     </row>
     <row r="187" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A187" s="6">
-        <f>C187*10+D187</f>
+        <f t="shared" si="8"/>
         <v>20310014</v>
       </c>
       <c r="B187" s="14">
@@ -8159,7 +8207,7 @@
     </row>
     <row r="188" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A188" s="6">
-        <f>C188*10+D188</f>
+        <f t="shared" si="8"/>
         <v>20310015</v>
       </c>
       <c r="B188" s="14">
@@ -8188,6 +8236,518 @@
       </c>
       <c r="J188" s="17"/>
       <c r="K188" s="17"/>
+    </row>
+    <row r="189" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A189" s="6">
+        <f t="shared" si="8"/>
+        <v>20400011</v>
+      </c>
+      <c r="B189" s="14">
+        <v>104000</v>
+      </c>
+      <c r="C189" s="33">
+        <v>2040001</v>
+      </c>
+      <c r="D189" s="33">
+        <v>1</v>
+      </c>
+      <c r="E189" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="H189" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I189" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="J189" s="17"/>
+      <c r="K189" s="17"/>
+    </row>
+    <row r="190" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A190" s="6">
+        <f t="shared" si="8"/>
+        <v>20400012</v>
+      </c>
+      <c r="B190" s="14">
+        <v>104000</v>
+      </c>
+      <c r="C190" s="33">
+        <v>2040001</v>
+      </c>
+      <c r="D190" s="33">
+        <v>2</v>
+      </c>
+      <c r="E190" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="H190" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I190" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="J190" s="17"/>
+      <c r="K190" s="17"/>
+    </row>
+    <row r="191" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A191" s="6">
+        <f t="shared" si="8"/>
+        <v>20400013</v>
+      </c>
+      <c r="B191" s="14">
+        <v>104000</v>
+      </c>
+      <c r="C191" s="33">
+        <v>2040001</v>
+      </c>
+      <c r="D191" s="33">
+        <v>3</v>
+      </c>
+      <c r="E191" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="H191" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I191" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="J191" s="17"/>
+      <c r="K191" s="17"/>
+    </row>
+    <row r="192" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A192" s="6">
+        <f t="shared" si="8"/>
+        <v>20400014</v>
+      </c>
+      <c r="B192" s="14">
+        <v>104000</v>
+      </c>
+      <c r="C192" s="33">
+        <v>2040001</v>
+      </c>
+      <c r="D192" s="33">
+        <v>4</v>
+      </c>
+      <c r="E192" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="H192" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I192" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="J192" s="17"/>
+      <c r="K192" s="17"/>
+    </row>
+    <row r="193" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A193" s="6">
+        <f t="shared" si="8"/>
+        <v>20400015</v>
+      </c>
+      <c r="B193" s="14">
+        <v>104000</v>
+      </c>
+      <c r="C193" s="33">
+        <v>2040001</v>
+      </c>
+      <c r="D193" s="33">
+        <v>5</v>
+      </c>
+      <c r="E193" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="H193" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I193" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="J193" s="17"/>
+      <c r="K193" s="17"/>
+    </row>
+    <row r="194" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A194" s="6">
+        <f t="shared" si="8"/>
+        <v>20390011</v>
+      </c>
+      <c r="B194" s="14">
+        <v>103900</v>
+      </c>
+      <c r="C194" s="33">
+        <v>2039001</v>
+      </c>
+      <c r="D194" s="33">
+        <v>1</v>
+      </c>
+      <c r="E194" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="H194" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I194" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="J194" s="17"/>
+      <c r="K194" s="17"/>
+    </row>
+    <row r="195" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A195" s="6">
+        <f t="shared" si="8"/>
+        <v>20390012</v>
+      </c>
+      <c r="B195" s="14">
+        <v>103900</v>
+      </c>
+      <c r="C195" s="33">
+        <v>2039001</v>
+      </c>
+      <c r="D195" s="33">
+        <v>2</v>
+      </c>
+      <c r="E195" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H195" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I195" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="J195" s="17"/>
+      <c r="K195" s="17"/>
+    </row>
+    <row r="196" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A196" s="6">
+        <f t="shared" si="8"/>
+        <v>20390013</v>
+      </c>
+      <c r="B196" s="14">
+        <v>103900</v>
+      </c>
+      <c r="C196" s="33">
+        <v>2039001</v>
+      </c>
+      <c r="D196" s="33">
+        <v>3</v>
+      </c>
+      <c r="E196" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="H196" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I196" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="J196" s="17"/>
+      <c r="K196" s="17"/>
+    </row>
+    <row r="197" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A197" s="6">
+        <f t="shared" si="8"/>
+        <v>20390014</v>
+      </c>
+      <c r="B197" s="14">
+        <v>103900</v>
+      </c>
+      <c r="C197" s="33">
+        <v>2039001</v>
+      </c>
+      <c r="D197" s="33">
+        <v>4</v>
+      </c>
+      <c r="E197" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G197" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="H197" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I197" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="J197" s="17"/>
+      <c r="K197" s="17"/>
+    </row>
+    <row r="198" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A198" s="6">
+        <f t="shared" si="8"/>
+        <v>20390015</v>
+      </c>
+      <c r="B198" s="14">
+        <v>103900</v>
+      </c>
+      <c r="C198" s="33">
+        <v>2039001</v>
+      </c>
+      <c r="D198" s="33">
+        <v>5</v>
+      </c>
+      <c r="E198" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="H198" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I198" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="J198" s="17"/>
+      <c r="K198" s="17"/>
+    </row>
+    <row r="199" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A199" s="6">
+        <f t="shared" si="8"/>
+        <v>20160011</v>
+      </c>
+      <c r="B199" s="14">
+        <v>101600</v>
+      </c>
+      <c r="C199" s="33">
+        <v>2016001</v>
+      </c>
+      <c r="D199" s="33">
+        <v>1</v>
+      </c>
+      <c r="E199" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G199" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="H199" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I199" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J199" s="17"/>
+      <c r="K199" s="17"/>
+    </row>
+    <row r="200" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A200" s="6">
+        <f t="shared" si="8"/>
+        <v>20160022</v>
+      </c>
+      <c r="B200" s="14">
+        <v>101600</v>
+      </c>
+      <c r="C200" s="33">
+        <v>2016002</v>
+      </c>
+      <c r="D200" s="33">
+        <v>2</v>
+      </c>
+      <c r="E200" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G200" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="H200" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I200" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J200" s="17"/>
+      <c r="K200" s="17"/>
+    </row>
+    <row r="201" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A201" s="6">
+        <f t="shared" si="8"/>
+        <v>20160033</v>
+      </c>
+      <c r="B201" s="14">
+        <v>101600</v>
+      </c>
+      <c r="C201" s="33">
+        <v>2016003</v>
+      </c>
+      <c r="D201" s="33">
+        <v>3</v>
+      </c>
+      <c r="E201" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G201" s="34" t="s">
+        <v>185</v>
+      </c>
+      <c r="H201" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I201" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J201" s="17"/>
+      <c r="K201" s="17"/>
+    </row>
+    <row r="202" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A202" s="6">
+        <f t="shared" si="8"/>
+        <v>20160044</v>
+      </c>
+      <c r="B202" s="14">
+        <v>101600</v>
+      </c>
+      <c r="C202" s="33">
+        <v>2016004</v>
+      </c>
+      <c r="D202" s="33">
+        <v>4</v>
+      </c>
+      <c r="E202" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G202" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="H202" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I202" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J202" s="17"/>
+      <c r="K202" s="17"/>
+    </row>
+    <row r="203" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A203" s="6">
+        <f t="shared" si="8"/>
+        <v>20160055</v>
+      </c>
+      <c r="B203" s="14">
+        <v>101600</v>
+      </c>
+      <c r="C203" s="33">
+        <v>2016005</v>
+      </c>
+      <c r="D203" s="33">
+        <v>5</v>
+      </c>
+      <c r="E203" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G203" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="H203" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I203" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J203" s="17"/>
+      <c r="K203" s="17"/>
+    </row>
+    <row r="204" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A204" s="6">
+        <f t="shared" si="8"/>
+        <v>20160066</v>
+      </c>
+      <c r="B204" s="14">
+        <v>101600</v>
+      </c>
+      <c r="C204" s="33">
+        <v>2016006</v>
+      </c>
+      <c r="D204" s="33">
+        <v>6</v>
+      </c>
+      <c r="E204" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G204" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="H204" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I204" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J204" s="17"/>
+      <c r="K204" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="302">
   <si>
     <t>id</t>
   </si>
@@ -923,6 +923,69 @@
   </si>
   <si>
     <t>11_11_11_11_11_11</t>
+  </si>
+  <si>
+    <t>10_11_2_2_2_6_6_1_8_7_3_7_9_6_5_8_3_3_3_2_6_1_8_5_2_8_2_5_9_6_6_8_8_11_5_6_12_7_2_2_10_2_2_1_9_4_3_3_3_6_3_6_12_3_7_4_4_8_8_1_1_12_10_4_6_6_7_1_1_11_4_4_11_7_5_8_3_9_9_10_9_2_4_8_3_3_5_12_5_1_7_3_5_10_10_9_6_3_9_9_2_1_8_2_2_4_4_8_11_2_3_1_9_3_5_3_1_1_1_5_10_5_11_4_11_11_11_3_6_10_8_12_8_2_1_2_2_2_12_12_6_10_10_1_3_6_5_2_9_6_1_7_5_2_9_4_3_4_10_5_11_11_11_10_9_3_11_2_2_2_7_2_9_3_2_2_5_5_1_9_1_11_8_2_11_10_9_7_2_3_8_7_1_12_1_7_7_8_7_3_3_2_1_5_7_4_2_1_5_6_3_8_8_6_6_6_2_1_11_11_1_2_2_2_3_1_1_10_10_10_1_6_1_10_3_7_8_8_4_6_6_5_5_4_9_6_4_3_3_3_7_1_5_4_3_9_10_1_7_7_8_2_9_5_5_12_2_2_8_1_3_9_1_3_7_5_8_6_6_4_9_3_10_6_4_6_1_3_2_3_8_1_5_6_6_8_3_4_1_10_9_4_9_5_11_1_4_2_10_1_1_3_5_1_1_1_3_6_5_2_10_11_9_6_6_2_10_8_7_2_6_1_1_5_2_1_1_1_11_1_1_1_9_11_4_5_4_5_4_4_8_6_2_4_6_6_8_11_1_7_7_1_5_3_4_4_4_3_10_1_3_3_6_3_10_6_6_8_8_3_11_4_2_3_10_10_1_5_5_5_8_8_1_6_11_7_4_7_7_7_1_1_1_2_2_3_3_2_4_4_8_8_9_10_11_4_4_6_4_4_1_2_12_2_1_7_1_5_12_1_6_12_11_9_3_1_10_4_9_10_10_10_10_7_12_2_7_8_3_11_2_8_1_10_8_3_3_12_2_10_6_10_5_11_2_8_6_10_3_6_1_1_10_3_3_9_7_3_1_1_4_6_2_7_1_8_8_3_5_7_7_7_11_4_4_4_8_4_1_5</t>
+  </si>
+  <si>
+    <t>9_9_10_7_2_2_1_2_9_3_4_6_8_1_1_11_6_6_12_5_2_5_5_1_11_6_1_12_5_4_2_11_3_11_5_1_5_3_5_2_6_4_4_3_5_10_7_11_7_12_2_3_9_4_5_3_8_12_3_11_6_3_12_3_7_7_6_6_1_3_2_13_4_3_1_10_4_4_4_2_13_4_2_4_4_3_9_13_6_8_3_6_4_12_5_13_6_4_6_1_10_5_3_9_1_1_4_11_7_7_2_13_2_7_8_9_2_2_4_13_5_13_6_6_8_7_2_2_6_3_11_7_2_4_5_6_1_2_10_3_3_13_6_5_2_5_1_4_2_8_9_3_13_4_9_2_12_4_5_12_3_2_3_6_4_12_3_5_5_5_4_13_6_10_5_4_1_11_5_2_4_1_2_5_7_8_1_2_8_3_1_8_4_1_11_5_7_1_4_8_5_6_11_6_4_8_3_3_3_11_2_3_5_13_7_1_7_3_2_1_2_8_3_8_13_6_1_9_12_1_6_12_7_6_2_4_8_2_12_6_12_7_1_4_1_1_13_1_7_7_3_6_12_3_8_2_8_2_3_4_10_6_8_9_2_2_4_5_11_7_7_9_6_1_7_1_1_5_7_1_4_10_7_1_8_7_11_6_7_1_8_3_12_4_3_2_6_6_1_13_6_11_2_9_2_10_6_5_2_5_4_6_3_7_5_10_6_2_4_13_4_11_6_4_1_8_6_2_6_9_6_2_9_12_6_6_4_1_10_6_4_8_7_12_7_8_3_13_7_5_1_2_13_6_1_4_13_5_2_11_1_8_7_12_5_5_9_8_8_1_3_9_1_13_6_9_6_11_4_6_3_4_11_5_3_12_5_1_6_2_3_8_13_5_1_2_5_7_4_9_4_8_8_1_5_6_2_1_10_6_1_12_7_6_8_4_8_12_6_9_3_10_2_3_13_5_6_10_2_1_10_2_4_1_8_12_6_1_6_7_8_8_1_8_8_6_1_5_1_13_5_10_6_2_3_3_6_7_3_1_9_5_5_2_4_5_1_9_6_8_2_11_7_4_9_1_8_7_8_2_13_1_11_5_12_7_4_4_6_12_7_7_1_1_2_9_4_2_3_8</t>
+  </si>
+  <si>
+    <t>11_2_8_6_5_6_3_8_8_10_6_2_2_10_10_10_11_11_8_2_3_6_6_7_1_8_3_3_6_1_1_1_5_8_8_5_4_4_6_9_3_1_11_7_8_6_7_9_1_5_10_10_9_6_12_8_4_9_2_8_12_8_2_3_12_12_11_4_5_1_1_11_5_3_7_4_6_3_9_9_11_10_8_2_2_3_2_1_5_5_7_10_9_5_8_1_6_5_5_10_6_8_2_3_3_9_3_5_2_10_3_12_11_2_8_9_4_10_4_9_8_6_8_2_1_4_4_3_8_7_2_6_9_3_4_5_4_4_2_2_1_3_2_1_3_3_3_1_9_8_3_3_1_8_12_7_2_9_4_8_1_4_5_4_4_9_9_3_1_2_4_3_3_1_6_10_5_5_8_8_5_3_6_6_2_5_11_8_3_3_5_11_9_11_7_7_7_10_2_9_7_2_1_2_1_6_4_10_1_10_2_12_3_8_12_6_6_7_3_6_1_8_9_11_11_3_6_7_10_2_4_11_8_2_1_2_1_2_3_10_6_6_5_7_1_1_5_1_10_2_9_4_3_2_12_7_12_6_11_7_5_4_10_2_3_5_5_5_1_8_5_2_1_5_5_2_9_4_8_4_4_6_4_2_2_1_5_2_3_6_7_6_11_3_3_7_3_5_1_3_6_6_6_5_2_5_5_10_3_2_1_2_9_5_7_2_2_8_10_10_10_10_3_8_7_8_5_5_5_2_12_3_5_9_3_2_2_8_7_2_5_6_1_3_1_4_1_4_9_3_2_4_1_1_8_9_3_8_8_3_6_2_10_4_12_1_11_6_7_6_4_1_6_6_6_1_5_6_6_5_1_9_6_2_10_9_7_8_9_7_10_3_5_4_7_7_3_5_7_1_6_4_7_7_5_1_8_2_7_1_4_1_4_4_8_5_8_6_6_10_8_7_8_5_1_1_11_4_11_9_8_3_5_6_11_3_10_7_7_10_1_2_8_4_6_4_8_4_6_1_4_10_4_9_2_12_7_4_5_2_2_1_2_1_10_10_2_4_5_8_5_3_4_4_11_2_12_8_1_10_3_8_4_5_4_6_10_8_2_1_2_8_4_7_7_1_3_8_8_8</t>
+  </si>
+  <si>
+    <t>12_6_6_13_7_12_4_10_6_3_5_4_4_9_9_5_6_3_1_7_8_7_4_5_9_12_7_2_11_1_5_10_5_2_8_1_2_4_12_7_9_12_6_3_3_5_10_7_13_6_5_11_5_6_4_8_4_5_7_7_6_1_8_4_4_4_10_3_12_6_6_9_3_1_13_5_1_5_12_7_7_1_9_10_5_2_12_4_3_3_8_4_1_12_1_1_5_5_6_2_5_13_7_12_6_7_7_7_12_5_13_2_13_3_5_7_2_3_9_12_3_9_3_9_8_6_1_6_1_5_9_11_4_4_2_12_6_6_5_6_10_3_10_4_3_11_3_7_9_13_7_4_1_4_2_10_2_2_3_1_10_7_2_9_5_3_2_10_5_5_4_1_11_6_2_8_8_9_3_4_11_4_13_7_1_13_6_7_4_2_4_6_7_1_4_3_6_10_5_10_7_7_11_3_12_5_2_7_2_6_13_5_2_3_8_3_4_8_9_2_9_2_13_5_8_9_10_3_3_5_9_8_4_4_9_9_8_10_4_13_5_6_12_2_1_12_6_8_5_2_2_11_5_1_2_5_4_2_11_6_2_11_6_12_7_3_3_7_1_10_6_6_12_7_13_3_5_8_9_4_3_9_11_7_1_13_6_10_6_2_12_1_7_12_6_10_5_1_1_5_2_1_13_7_1_2_2_5_8_1_2_10_2_8_11_7_3_8_8_5_10_3_10_6_4_5_4_1_8_1_1_12_7_12_3_13_6_13_6_6_2_11_5_4_2_1_3_2_5_2_2_6_6_7_1_7_3_12_7_2_8_5_8_5_12_6_2_2_7_9_4_10_7_6_13_6_12_3_2_2_3_8_2_4_4_12_1_2_12_3_1_1_4_4_3_5_6_5_3_8_3_10_6_6_4_4_12_4_11_5_11_7_1_4_12_5_7_10_5_7_13_6_9_9_8_2_5_10_5_6_5_1_12_6_3_3_2_11_6_6_6_9_9_1_1_11_6_13_4_1_10_7_3_7_10_4_6_1_11_4_13_5_6_5_8_2_8_7_6_3_7_11_4_7_10_6_9_6_10_6_4_12_6_4_4_10_6_7_4_2_13_4_12_5_2_4_9_2_2_5</t>
+  </si>
+  <si>
+    <t>7_10_2_1_1_7_5_5_8_8_2_1_1_3_3_5_5_9_8_7_4_2_4_12_3_5_3_3_3_4_1_5_7_4_7_1_1_3_1_4_4_6_8_1_3_9_11_11_9_7_4_12_10_10_10_10_1_10_2_3_3_11_4_4_4_5_9_2_3_4_10_1_1_2_5_5_1_5_8_7_2_8_4_10_10_8_4_4_1_1_11_12_2_9_4_4_8_1_9_6_7_1_10_11_9_11_4_3_3_3_3_2_3_11_10_1_2_8_8_4_4_8_2_7_2_1_2_12_10_3_3_10_12_3_2_3_7_6_4_8_7_6_3_7_11_10_4_6_6_6_8_4_1_7_7_2_4_4_3_11_6_10_11_3_2_9_5_5_4_2_5_9_10_1_3_1_6_1_2_3_2_6_3_2_5_2_3_11_10_6_3_7_10_9_9_3_6_8_2_5_7_5_2_7_9_5_5_4_4_5_9_9_1_7_6_6_8_6_3_8_4_1_7_3_11_5_5_5_2_8_1_3_4_12_2_6_11_9_7_7_10_7_4_3_3_8_10_5_3_3_11_5_3_12_5_1_2_4_4_8_8_2_3_2_3_4_10_5_10_1_3_8_6_5_3_1_1_5_2_6_1_11_7_3_1_3_6_3_3_3_2_11_11_6_6_9_9_3_1_10_1_10_4_9_9_11_7_7_3_4_2_3_12_6_2_2_5_7_9_9_4_4_3_2_1_5_7_8_8_1_10_10_1_5_2_12_5_9_10_5_4_12_1_1_9_4_3_1_5_5_6_4_10_11_11_2_3_7_8_6_6_9_9_6_3_4_4_7_3_7_2_6_3_3_3_8_7_7_9_5_6_5_9_9_5_3_7_9_4_3_3_8_7_7_7_7_4_1_1_2_1_12_2_2_3_5_6_9_11_4_5_5_4_7_5_2_1_12_1_3_3_3_3_10_3_11_5_4_2_2_5_5_6_1_9_11_8_11_7_1_1_6_3_6_4_3_3_3_3_6_3_1_5_1_5_6_6_2_2_7_3_7_7_8_3_2_2_11_10_1_3_1_11_2_5_5_5_6_6_5_12_12_12_7_10_1_7_1_2_2_5_4_9_4_4_1_6_5_2_12</t>
+  </si>
+  <si>
+    <t>6_3_2_1_6_11_6_7_4_2_12_7_5_8_4_6_8_6_4_13_4_10_6_5_10_5_3_9_12_5_2_1_2_10_6_8_1_10_5_5_3_8_13_6_7_7_4_2_8_7_2_4_7_4_10_6_5_8_5_8_2_8_13_5_11_5_6_7_8_6_1_10_5_10_3_9_5_10_6_4_6_7_2_8_6_13_7_3_7_4_12_6_12_6_7_3_10_5_9_8_13_7_1_7_6_7_13_7_1_1_8_8_8_3_2_3_6_1_4_5_3_4_7_3_4_1_3_3_13_4_12_3_5_4_5_2_6_10_3_5_5_7_4_4_4_6_13_4_2_1_3_4_9_6_13_5_3_3_3_4_2_7_7_1_8_12_6_1_2_13_6_2_10_6_1_11_6_6_11_4_3_12_6_3_3_3_7_1_11_5_3_6_4_2_2_12_5_6_10_6_11_2_4_3_7_11_6_4_13_5_2_12_6_6_3_6_1_12_5_4_9_3_12_4_2_1_1_1_3_2_12_7_8_8_1_3_4_6_7_4_12_3_9_10_5_9_7_1_4_13_6_6_7_7_4_2_4_9_7_12_3_2_4_7_11_7_4_10_6_13_4_7_13_7_7_2_1_5_12_6_10_6_4_1_5_4_11_5_9_7_1_5_5_5_6_2_5_6_12_3_12_7_13_4_4_2_13_3_1_1_10_7_5_6_2_5_1_5_12_7_13_6_11_3_9_2_6_7_5_11_3_12_2_6_2_6_9_3_4_1_12_5_9_3_8_2_9_6_5_2_9_9_4_3_1_13_5_1_1_6_11_2_13_5_11_4_7_3_10_7_1_5_12_4_1_3_3_12_6_2_5_1_1_9_4_6_4_5_3_9_4_2_4_7_1_4_8_1_1_1_1_10_6_4_10_1_9_10_2_4_2_1_1_6_13_5_2_1_3_12_6_6_8_9_4_2_4_3_6_6_6_12_3_1_1_4_2_10_7_1_7_4_4_9_2_13_3_1_4_2_3_2_8_11_7_2_4_10_2_5_3_8_8_9_7_3_2_3_8_7_2_1_12_6_2_10_7_2_5_2_8_2_13_2_11_1_6_10_4_1_2_3_9_13_4_4_6_5_3_1</t>
+  </si>
+  <si>
+    <t>12_6_2_2_7_3_9_4_1_6_4_2_9_3_8_1_6_3_6_2_7_11_1_1_6_1_8_5_8_5_9_1_1_4_1_2_12_4_7_12_2_8_8_9_11_9_5_2_2_6_3_3_7_10_12_3_2_9_9_1_2_3_2_7_8_2_2_2_6_8_8_3_7_11_6_6_6_6_4_4_3_2_12_4_1_1_11_11_4_1_1_7_2_12_3_8_6_3_2_6_9_2_7_6_5_8_8_4_6_10_11_3_6_3_6_5_2_9_1_3_3_6_8_8_2_1_1_4_3_5_4_2_6_1_1_5_9_4_1_1_2_2_3_2_3_3_5_3_2_5_3_9_1_8_7_4_4_4_7_7_8_12_9_9_6_6_5_5_7_3_7_10_4_4_4_7_1_6_12_12_10_2_2_2_3_12_1_9_7_4_6_6_10_2_9_6_2_1_3_1_7_7_1_8_10_10_5_2_1_5_1_1_9_6_1_6_8_7_3_3_10_7_8_4_7_3_2_8_4_4_4_4_7_2_5_6_1_6_1_5_2_2_9_2_3_1_5_9_1_9_10_10_5_10_5_4_2_4_3_6_10_2_10_4_2_4_10_3_2_2_1_1_8_6_8_9_1_3_3_10_2_4_5_3_2_4_6_1_11_6_6_1_1_9_3_5_5_4_7_10_1_1_3_1_5_4_9_6_4_1_7_7_3_7_4_2_5_7_7_10_4_5_7_5_7_11_1_5_8_9_6_12_5_3_7_9_10_10_8_4_10_4_8_1_12_9_1_8_2_3_3_3_3_10_10_5_12_6_5_10_2_6_2_4_10_3_3_3_8_1_7_7_12_3_10_9_5_9_11_2_4_2_5_5_7_7_9_2_2_8_11_5_2_3_6_6_3_4_3_2_2_1_7_10_2_7_2_2_2_6_6_3_2_10_9_11_4_1_6_3_6_2_1_7_9_10_5_1_11_2_3_11_6_9_9_1_8_4_1_5_5_5_2_2_6_8_4_4_10_8_3_11_4_2_1_7_2_1_1_5_8_4_6_4_5_6_6_2_9_4_4_11_1_1_4_4_11_11_11_3_11_7_7_8_4_2_1_7_12_2_5_12_12_3_3_9_6_12_2_7</t>
+  </si>
+  <si>
+    <t>9_6_12_5_5_2_2_4_11_1_8_8_12_3_13_6_10_5_2_9_9_5_8_1_12_5_3_3_2_6_1_6_2_9_12_4_6_2_7_2_11_3_5_8_2_3_1_12_6_1_2_3_7_7_1_1_1_4_9_7_4_7_1_13_6_5_4_1_6_12_7_2_1_3_3_1_3_8_3_2_8_1_11_6_3_9_2_4_3_6_5_7_2_9_2_8_8_11_4_5_2_12_5_8_10_2_5_8_9_9_2_11_2_5_1_9_4_9_1_3_5_1_4_2_8_7_9_7_3_9_5_4_9_1_12_7_13_6_3_3_13_1_5_11_5_4_11_4_1_11_7_10_2_1_3_10_6_12_7_8_4_12_5_5_13_5_10_5_10_6_7_6_9_10_2_1_1_10_1_5_7_10_5_9_3_12_4_10_7_4_3_10_2_2_1_7_6_3_1_8_6_3_12_7_13_5_12_6_2_3_8_11_4_10_4_1_4_5_1_6_13_2_6_1_6_3_2_5_12_7_5_8_5_8_1_8_8_4_11_6_2_7_8_11_7_3_2_4_8_3_11_5_5_1_8_4_1_8_4_11_4_5_9_5_8_7_3_2_8_13_6_10_5_3_7_6_1_6_1_8_8_10_6_7_3_5_9_5_7_4_12_5_2_9_2_4_9_1_13_6_4_2_2_13_3_13_7_4_1_4_8_11_7_4_12_3_9_5_11_6_5_4_13_5_3_6_11_6_10_5_7_8_2_7_11_4_4_3_1_11_6_4_3_2_6_10_7_8_10_6_12_6_8_5_7_4_7_6_1_13_5_3_3_3_13_6_8_8_6_11_5_2_6_3_5_12_7_4_2_1_2_3_7_4_8_3_13_4_10_4_2_7_8_4_3_6_10_7_2_11_7_4_6_3_4_7_1_6_4_8_10_5_2_6_13_5_1_8_4_5_10_5_4_1_10_5_9_4_4_1_6_7_4_13_6_12_7_13_6_5_13_7_11_5_10_5_11_5_1_4_10_7_6_1_7_10_7_1_6_2_9_13_7_3_6_7_4_2_11_6_4_3_7_4_12_5_11_3_2_2_13_6_1_4_4_13_7_3_6_6_2_6_3_6_4_3_6_13_7_4</t>
+  </si>
+  <si>
+    <t>12_12_12</t>
+  </si>
+  <si>
+    <t>11_5_3_1_2_4_5_2_7_3_5_9_9_8_8_6_3_11_4_4_2_4_4_4_1_2_4_1_5_5_5_1_3_3_7_12_2_9_4_5_6_5_3_1_9_1_8_3_6_5_5_8_9_5_3_10_1_4_2_7_10_8_8_10_7_10_7_7_7_7_9_1_11_12_7_11_4_7_3_6_7_7_6_8_8_2_11_4_10_3_7_7_1_2_6_3_12_12_5_5_5_5_2_1_6_6_11_5_1_2_9_4_1_10_3_4_4_7_2_9_7_7_2_1_9_11_2_2_11_4_8_3_1_6_4_11_5_9_3_5_4_2_2_11_6_5_3_5_2_4_10_2_11_3_1_8_1_2_1_5_3_3_2_2_6_7_1_6_6_1_6_8_9_6_6_7_5_3_4_6_12_12_1_2_3_6_2_2_2_2_1_9_2_2_2_3_12_2_3_3_11_9_6_3_11_11_4_11_11_4_7_7_7_7_1_5_5_5_3_2_2_5_5_3_3_10_5_7_6_6_5_8_7_6_8_8_10_11_11_6_2_2_6_6_10_11_8_10_2_10_2_8_8_4_3_3_7_2_5_10_2_5_8_5_10_11_6_3_11_11_1_6_7_6_5_7_8_1_7_2_2_1_8_11_8_6_2_2_12_4_9_8_6_3_11_3_7_3_5_8_5_3_2_2_2_9_2_9_4_3_3_3_3_7_1_7_7_7_4_4_2_5_3_3_3_6_6_2_8_7_2_12_5_5_12_3_3_3_2_1_9_9_1_2_11_8_6_6_8_3_7_4_4_4_11_6_1_5_5_4_1_2_2_2_12_10_3_3_1_5_11_8_2_2_4_5_5_2_2_3_2_6_10_6_7_7_9_1_1_2_11_7_5_2_2_5_5_3_11_11_4_9_10_6_2_2_3_1_9_3_10_5_6_9_5_1_9_10_1_1_8_1_3_6_6_1_5_5_2_4_4_11_1_1_8_11_4_1_10_6_6_2_2_8_5_3_2_2_8_4_9_9_5_5_4_5_5_9_9_11_5_4_10_7_3_2_2_10_3_10_7_5_1_1_6_6_2_5_4_11_2_8_6_5_12_12_5_4_9_11_5_1_5_5_5_5_2_5_2_6</t>
+  </si>
+  <si>
+    <t>1_4_2_6_5_2_12_5_9_13_6_12_7_6_4_8_6_13_7_9_3_9_4_12_4_3_5_3_5_4_2_13_5_4_2_5_1_5_2_2_5_9_6_3_8_3_7_3_3_5_11_5_7_3_11_7_3_1_1_13_5_12_6_7_9_3_5_7_11_6_3_3_2_1_9_5_6_4_1_11_1_3_13_7_5_3_2_10_6_4_1_3_9_12_3_13_6_1_4_6_4_8_8_2_1_12_6_8_1_10_5_4_13_7_1_5_4_7_5_6_1_3_7_9_3_8_8_13_4_1_3_9_9_1_3_5_6_2_6_12_5_11_7_12_3_4_1_2_9_2_4_11_4_8_6_7_2_13_3_4_2_6_6_1_2_3_4_2_7_1_2_9_6_8_13_6_9_8_12_5_1_8_7_11_4_11_5_4_13_2_6_4_5_6_3_8_5_7_4_10_4_10_6_12_6_13_4_4_11_7_1_9_4_6_13_5_1_8_1_12_6_9_13_4_8_2_2_3_11_5_8_5_12_2_4_3_2_2_11_3_5_1_4_12_2_9_5_2_1_2_10_4_4_6_5_2_6_10_5_8_9_13_4_11_6_2_13_2_7_9_1_4_7_11_6_11_4_12_6_5_4_12_1_8_2_9_3_3_7_2_12_3_1_6_11_6_1_13_7_9_4_8_2_8_12_5_5_10_1_10_2_13_2_3_11_5_13_7_1_2_4_12_5_5_1_10_4_2_1_3_10_5_7_13_5_3_8_5_2_5_1_3_12_2_4_4_3_3_3_13_7_9_2_8_1_6_6_12_6_4_9_9_8_4_6_1_9_11_7_2_9_8_12_1_1_2_3_5_7_8_5_8_9_3_8_2_1_5_12_7_6_7_2_2_6_7_9_8_1_12_5_5_13_1_8_1_7_8_5_2_13_6_8_11_2_4_8_2_5_5_10_6_6_6_12_4_4_1_6_6_1_3_7_1_6_5_2_11_7_9_11_6_12_5_5_1_7_6_13_3_5_13_3_11_2_2_12_2_6_1_2_2_3_1_1_11_4_2_2_9_3_13_5_7_6_5_8_2_11_7_12_5_11_7_1_9_1_3_9_4_7_4_3_7_12_6_7_4_7_2</t>
+  </si>
+  <si>
+    <t>10_7_7_7_10_9_9_9_7_8_7_11_7_10_9_9_8_12_11_9_8_12_8_11_7_9_10_9_9_7_7_8_12_8_10_7_8_9_7_7_9_9_10_7_11_9_10_10_9_7_11_11_11_10_7_10_7_11_8_8_8_8_8_11_7_8_8_8_7_9_8_9_8_7_8_8_9_7_8_7_11_7_10_10_8_9_9_8_8_8_10_11_10_8_10_7_9_10_9_9_7_9_12_8_12_12_9_8_8_10_10_12_8_11_7_8_8_12_10_10_8_11_8_11_9_7_8_9_7_7_11_9_8_7_7_7_11_7_12_12_11_11_7_8_8_8_7_8_10_7_8_11_11_8_8_8_8_7_10_7_11_7_7_9_9_8_7_8_9_9_7_8_11_8_7_7_8_9_9_8_8_9_8_8_8_8_10_8_9_7_9_7_12_9_9_10_10_8_9_9_8_8_7_10_8_9_9_11_8_8_8_12_8_9_10_11_8_8_7_7_9_9_7_7_10_8_9_7_7_8_11_8_9_7_12_7_8_11_11_8_9_7_8_8_11_11_7_12_9_8_8_9_11_11_10_10_10_12_8_7_8_7_9_7_10_10_10_10_10_7_10_9_12_7_7_7_10_9_9_7_11_9_8_9_11_7_10_11_8_8_10_10_11_9_9_7_12_8_7_10_11_11_8_10_8_10_9_11_10_10_8_8_9_9_10_8_8_10_8_7_11_11_8_8_8_7_7_9_9_10_9_9_9_8_8_8_8_12_9_10_7_7_12_10_12_10_8_7_9_7_8_8_8_9_7_7_7_7_11_9_8_10_10_7_11_8_9_12_8_9_11_8_8_10_12_10_9_7_9_8_7_11_8_7_9_10_7_12_8_8_8_7_10_9_10_9_9_10_12_12_9_8_9_9_7_9_7_8_8_9_11_9_9_10_9_8_7_7_7_8_9_8_11_9_9_9_8_9_9_8_11_11_7_8_11_10_10_12_7_10_8_10_7_9_8_9_9_10_9_10_7_10_8_7_9_11_11_8_10_9_7_8_12_11_8_11_7_7_8_12_12_8_8_12_7_8_8_8_7_9_9_9_11_9_9_8_10_9_10_10_8_7_9_7_7_7_8_7_7_7</t>
+  </si>
+  <si>
+    <t>10_7_11_9_10_9_8_7_11_8_11_9_8_12_8_9_8_10_8_7_11_7_12_7_8_7_13_9_10_9_13_8_10_8_12_9_8_13_7_11_8_11_8_8_10_9_9_10_8_8_7_12_9_9_12_7_10_7_7_7_9_10_9_11_8_13_9_12_9_8_8_13_7_8_8_7_9_10_7_10_8_7_12_8_7_7_9_8_9_7_11_9_11_9_7_11_8_8_7_7_9_11_8_8_7_7_13_9_12_8_9_7_11_9_13_8_9_12_9_13_8_8_8_10_7_8_8_9_12_7_11_7_11_7_8_7_9_13_8_8_12_9_10_7_7_9_9_11_8_8_9_11_7_8_7_11_8_12_8_9_9_7_8_7_7_9_11_9_12_8_11_7_11_7_9_12_7_12_7_11_7_10_7_11_7_9_11_8_9_7_13_8_7_8_7_8_13_7_9_12_8_7_13_8_9_7_10_9_8_8_11_8_8_8_9_11_9_11_7_11_8_7_7_11_7_11_8_7_13_8_9_8_10_9_9_8_13_7_7_7_11_8_7_7_13_9_9_11_7_9_8_11_7_11_9_11_9_10_8_9_8_12_1_7_9_8_8_8_8_12_9_7_10_7_9_11_8_8_9_10_9_9_13_8_8_7_7_11_8_9_12_7_9_11_7_8_8_10_1_12_8_9_7_12_9_9_10_1_10_8_11_7_11_8_10_7_11_9_13_8_7_12_8_11_9_11_8_9_10_8_11_8_9_7_10_8_10_7_10_8_10_7_10_9_7_11_7_10_8_8_7_11_8_9_11_8_9_7_7_8_7_13_8_8_7_11_9_10_7_11_7_12_9_7_10_8_7_12_7_7_11_8_12_8_8_13_7_10_7_8_13_8_8_9_12_9_9_8_11_8_9_10_9_11_8_10_8_9_10_1_13_9_7_12_8_8_12_8_10_7_8_10_8_9_13_7_9_10_8_13_7_7_8_10_7_8_10_8_10_9_13_7_11_9_10_8_7_8_12_8_11_7_12_8_11_1_11_8_13_9_9_7_8_8_7_11_9_7_11_8_12_8_8_8_9_7_10_9_8_11_7_10_9_12_9_12_9_10_9_10_7_8_11_7_11_8_7_7_13_7</t>
+  </si>
+  <si>
+    <t>11_8_7_9_7_7_7_8_7_7_10_8_10_10_12_9_7_7_8_11_12_10_10_8_8_9_7_7_11_11_8_7_8_7_10_10_8_11_8_10_10_12_7_7_8_7_7_7_7_9_7_10_10_9_10_10_7_9_9_9_7_9_7_10_9_12_9_11_9_7_7_12_11_11_10_11_10_8_9_10_7_10_10_9_12_8_7_9_10_12_8_8_10_9_7_7_9_7_12_12_12_8_8_8_8_10_8_7_9_9_10_10_10_11_11_12_10_9_7_8_9_10_7_11_8_8_8_11_9_12_7_7_7_8_12_9_11_11_8_10_9_9_10_7_10_7_10_10_8_11_11_11_12_12_10_8_8_7_7_10_11_7_8_10_7_10_7_9_8_9_8_8_8_8_9_7_7_7_7_7_7_9_10_11_11_10_11_9_8_10_7_8_10_9_10_7_10_8_7_7_10_10_8_9_7_7_8_11_11_11_9_12_12_11_9_9_11_7_8_7_10_7_7_9_7_9_12_8_8_11_9_7_9_11_7_9_7_9_8_11_11_7_8_8_12_8_8_9_8_8_7_7_8_8_8_9_11_8_9_7_8_7_8_9_11_8_7_10_11_8_8_8_7_9_12_10_8_9_8_10_10_10_9_9_9_7_7_12_8_8_9_11_9_8_11_10_10_7_9_9_8_10_10_7_11_8_9_10_10_7_7_10_7_7_7_10_11_11_11_8_9_9_7_10_7_9_10_10_8_10_8_11_9_10_7_8_8_11_9_10_7_7_12_7_8_9_8_7_9_8_9_10_11_11_11_11_10_7_7_7_7_9_7_8_9_7_8_8_12_8_9_7_10_10_11_7_7_11_7_10_7_7_12_11_9_9_8_11_12_12_7_11_12_9_12_9_8_7_8_8_7_8_9_8_8_8_9_7_7_7_7_11_8_8_7_9_12_8_8_12_7_11_8_10_11_8_7_8_10_11_9_7_7_7_7_9_8_8_11_11_11_10_9_11_9_11_11_10_10_9_9_10_8_9_9_7_12_7_9_8_8_7_8_8_7_10_8_12_10_9_9_7_9_9_7_7_8_10_12_11_12_10_8_8_10_10_10_10_11_11_7_8_9_9_9_12_7_9_9_7</t>
+  </si>
+  <si>
+    <t>11_8_7_10_8_8_7_8_7_8_13_7_10_8_10_9_10_8_9_12_9_13_8_11_8_11_7_13_9_8_8_10_8_9_7_7_13_8_10_8_7_8_10_9_12_7_9_13_7_11_7_7_8_8_10_9_8_7_8_7_12_8_11_7_7_8_12_9_10_8_11_7_9_10_8_9_12_8_9_7_7_8_12_8_11_9_13_8_8_13_8_8_10_9_11_8_10_9_11_8_9_10_7_8_7_8_7_13_7_9_13_9_10_7_8_12_7_9_7_11_8_7_9_13_9_8_9_8_9_11_8_10_7_7_9_11_8_11_7_9_12_8_7_10_8_7_13_7_10_1_12_7_11_7_11_8_11_8_11_7_7_10_8_8_10_7_9_13_9_11_8_10_9_11_8_7_8_9_8_8_7_7_12_7_9_9_13_9_9_11_7_11_9_8_9_8_9_12_8_7_12_8_8_9_10_7_12_9_13_1_8_11_9_10_8_9_7_8_7_12_7_9_13_1_9_11_9_8_9_12_7_12_8_10_8_9_9_10_7_12_8_9_10_7_10_9_7_8_12_7_13_8_9_8_13_7_8_8_11_8_11_7_10_9_11_7_11_9_8_11_7_13_9_8_7_7_9_11_7_8_10_8_11_9_8_8_9_10_7_10_7_7_9_7_9_8_10_8_8_11_8_10_8_9_9_8_10_8_11_7_12_8_7_8_10_9_8_9_7_8_13_8_11_7_13_8_9_10_8_9_12_7_10_1_7_9_7_13_8_10_9_8_9_8_7_7_7_7_12_8_7_8_9_13_8_12_8_12_1_10_7_9_11_7_8_7_11_7_8_13_7_9_8_8_8_10_7_8_11_8_10_7_12_8_8_8_12_7_8_13_9_7_12_8_11_8_10_7_10_1_7_10_9_9_10_8_10_8_12_9_10_8_10_7_10_8_7_7_8_9_13_8_7_9_7_7_9_7_11_8_12_7_7_13_8_11_7_9_11_9_7_11_7_10_7_12_9_11_7_10_8_10_1_8_7_7_9_12_8_12_7_9_8_13_7_11_9_9_11_1_8_12_8_13_7_11_8_12_8_10_9_7_7_11_9_9_13_9_13_7_10_7_12_9_9_7_9_8_7_13</t>
+  </si>
+  <si>
+    <t>8_12_10_10_10_10_10_11_10_11_10_7_7_10_7_11_9_8_8_7_9_9_8_8_8_8_10_9_11_11_9_12_12_7_7_9_10_12_8_9_9_8_7_9_9_9_7_11_11_8_9_8_11_11_11_7_11_11_7_8_8_7_7_9_8_9_9_9_9_7_10_7_10_9_9_9_9_9_7_10_9_10_7_7_11_8_9_9_11_8_12_12_8_10_9_8_10_7_10_11_9_8_8_8_8_8_8_11_8_7_7_8_11_8_9_7_7_11_10_10_10_10_9_9_12_7_10_10_7_8_11_7_11_7_8_8_8_7_7_10_10_8_12_8_12_7_8_8_7_7_8_8_9_7_9_9_8_7_8_12_12_12_8_9_7_7_8_10_10_8_7_7_8_12_9_7_7_7_9_10_7_7_7_8_8_12_8_7_10_10_10_7_12_7_8_7_11_8_8_8_10_7_10_10_7_7_8_11_9_7_10_8_8_8_8_8_8_7_8_7_8_9_9_11_8_7_8_11_11_7_7_8_10_7_8_10_12_7_10_8_8_8_8_9_7_7_7_10_9_9_8_7_12_12_7_8_7_11_7_7_7_7_7_9_11_11_8_8_8_10_11_9_8_10_10_7_7_8_12_7_10_9_11_7_7_9_9_7_9_9_7_9_9_9_7_10_8_12_11_8_7_11_11_7_7_11_11_7_10_10_7_7_7_9_11_8_10_10_7_9_9_10_12_9_9_9_7_7_8_9_9_9_8_10_12_8_9_9_10_11_8_9_11_10_9_12_8_7_7_7_7_12_11_12_8_10_7_8_10_9_11_8_7_10_10_12_10_12_9_9_9_9_12_10_9_9_7_11_9_9_9_9_11_7_8_12_9_10_10_10_11_11_10_11_7_9_7_8_8_12_8_10_7_8_10_10_11_8_12_7_8_11_11_10_9_9_8_7_10_8_7_12_7_8_9_10_7_10_10_10_7_8_11_8_8_7_7_10_10_9_8_9_9_7_7_7_9_7_7_12_11_8_9_7_9_8_8_7_12_10_8_11_11_7_8_7_12_11_11_9_9_12_9_11_7_8_12_7_7_8_8_8_8_7_10_8_7_9_8_8_8_8_7_7_7_7_8_8_11_7</t>
+  </si>
+  <si>
+    <t>11_7_10_8_10_9_11_9_13_9_8_13_7_11_8_12_7_8_8_9_11_9_10_1_12_8_7_7_10_8_9_8_12_7_13_7_10_8_8_9_12_7_7_9_10_9_7_8_7_11_8_7_11_9_10_7_11_8_7_13_7_7_7_8_8_7_7_9_11_9_12_9_12_7_12_8_7_8_8_9_10_9_10_8_7_9_8_13_7_9_10_9_7_7_8_11_8_7_10_7_8_8_7_8_9_11_9_11_7_8_11_8_7_9_11_8_8_9_9_9_12_9_10_8_8_10_9_13_8_7_11_8_13_7_10_7_13_7_13_7_11_7_7_12_9_8_11_1_8_7_9_9_7_10_8_8_13_8_7_7_9_13_7_7_13_8_12_7_13_7_8_9_9_8_7_8_13_7_7_11_8_10_8_7_7_8_11_8_7_9_8_9_10_8_7_9_10_9_11_9_8_8_10_9_13_8_12_8_9_12_9_8_10_9_10_7_9_11_7_12_7_13_7_9_11_8_7_12_8_10_9_9_10_7_7_10_8_13_8_8_8_13_9_8_11_8_12_9_10_9_9_11_9_11_9_13_9_13_9_9_10_8_13_9_9_7_12_7_8_11_8_9_8_13_7_11_9_9_9_7_7_7_9_13_7_11_9_10_7_12_9_11_9_11_8_8_10_9_13_8_10_9_7_7_10_1_12_8_12_7_9_7_12_7_8_7_10_8_10_9_8_7_8_7_8_8_10_1_7_8_7_7_8_10_8_13_7_10_8_9_7_9_13_8_9_13_9_10_7_7_12_7_9_9_11_7_7_11_9_10_1_12_7_12_1_10_8_9_7_11_9_10_8_8_9_11_9_13_7_9_13_7_10_8_10_7_7_7_11_7_13_9_10_7_8_9_9_10_7_11_8_8_8_8_13_7_7_9_8_7_13_8_10_7_9_7_12_7_7_7_11_9_9_8_9_11_8_11_9_11_7_13_9_9_10_9_10_7_11_8_13_9_9_11_7_7_10_1_13_7_8_8_10_7_7_10_8_11_7_8_11_7_8_11_8_9_13_7_8_7_10_1_8_10_8_12_8_12_8_7_8_13_1_11_7_10_8_10_9_7_13_7_7_7_7_9_8_9_12_8</t>
+  </si>
+  <si>
+    <t>7_7_7_9_9_11_11_7_12_7_11_9_9_12_9_7_8_8_11_7_12_7_7_11_12_12_11_11_11_10_12_7_11_8_12_8_8_11_9_7_8_8_7_9_7_8_7_7_11_7_7_7_7_10_10_8_7_8_10_11_9_9_7_11_11_10_8_9_7_10_11_8_9_11_7_7_10_7_7_8_9_7_8_9_9_10_9_10_8_7_7_9_7_7_8_11_10_7_8_10_7_7_9_8_10_12_12_9_11_10_7_11_8_11_7_8_9_9_7_7_7_7_11_11_9_11_9_8_8_8_7_9_12_11_7_7_8_11_8_8_8_8_11_10_9_7_7_8_7_12_8_11_7_12_7_12_12_10_10_7_7_7_11_9_11_10_9_7_8_9_9_8_8_7_8_11_8_7_8_9_12_7_8_9_12_7_9_9_10_12_7_8_12_8_10_9_10_10_8_8_9_7_11_8_8_7_8_10_10_8_12_7_9_9_10_11_8_8_12_7_7_9_10_7_7_9_9_11_11_11_9_9_9_12_10_11_10_8_8_7_12_10_11_11_8_9_9_10_10_10_7_7_8_7_11_12_7_7_11_7_11_11_11_8_8_11_7_7_9_8_7_7_7_8_8_9_12_12_12_7_7_8_10_8_7_9_9_7_10_8_11_7_7_11_8_11_11_7_7_7_10_9_7_7_9_11_7_12_7_7_11_11_7_8_8_7_7_8_9_10_10_9_9_8_8_8_7_11_9_7_10_10_10_10_9_12_7_7_7_7_7_7_9_8_9_9_7_8_9_12_10_8_8_7_11_12_7_9_9_7_8_7_11_7_10_10_12_7_10_12_10_9_7_9_8_7_12_11_8_8_10_7_9_8_7_8_7_7_7_7_8_10_10_7_7_8_9_9_7_8_7_7_7_11_10_9_9_7_10_9_7_7_12_10_7_7_9_8_8_8_10_7_8_7_8_8_9_11_8_9_11_7_10_7_9_7_8_7_7_8_9_8_7_7_10_12_9_9_9_9_9_11_11_12_11_8_9_8_10_9_7_9_7_8_11_7_11_7_9_7_11_11_12_7_7_7_8_9_9_7_8_7_7_12_8_8_9_7_9_8_7_7_7_7_7_8_9_7_7_8</t>
+  </si>
+  <si>
+    <t>11_8_10_7_12_7_7_7_11_8_13_7_11_9_9_10_8_9_8_8_8_10_9_12_8_12_8_8_7_8_13_8_11_8_13_7_13_8_13_8_7_8_8_11_8_8_7_7_13_9_10_7_11_8_7_8_7_8_11_8_10_8_7_9_11_8_10_7_9_9_9_7_9_12_8_9_13_8_11_9_7_11_7_9_10_7_9_13_8_7_10_9_8_13_8_13_8_11_8_8_8_8_11_8_7_11_7_11_8_12_8_10_8_9_13_8_11_8_12_8_13_9_11_8_12_8_8_11_8_13_9_7_12_8_11_7_7_10_9_12_8_13_8_8_7_7_8_12_8_13_8_7_7_10_8_10_8_13_1_7_11_8_9_7_9_13_9_7_9_9_12_8_13_9_11_7_8_11_9_9_7_13_9_10_8_8_10_9_12_7_9_7_12_1_10_8_13_8_10_9_12_8_8_13_7_7_10_8_10_9_13_8_8_7_9_9_8_7_8_9_7_8_11_9_8_9_7_12_9_7_10_8_9_9_9_12_9_9_11_7_7_9_8_11_8_13_8_10_9_13_7_8_8_13_9_9_8_11_1_11_8_7_11_8_10_9_9_10_8_7_8_11_7_7_9_9_11_9_9_7_11_8_10_7_8_7_8_8_11_8_8_10_8_8_9_10_8_8_9_9_13_9_10_7_8_11_8_8_13_9_13_7_12_8_13_8_7_7_8_10_9_9_13_8_10_7_10_9_12_8_8_7_11_1_8_10_7_7_8_9_8_9_9_7_10_8_7_8_10_8_10_7_7_12_7_10_1_10_9_13_9_13_7_8_8_9_11_9_7_10_8_9_9_12_8_8_12_7_11_8_11_9_7_12_8_13_8_8_8_11_7_10_7_9_7_9_11_9_11_7_10_8_10_8_11_1_7_13_9_10_8_11_9_9_13_9_8_11_1_13_8_7_12_7_12_7_13_9_12_7_8_8_12_8_10_9_8_11_8_8_8_9_10_8_8_13_7_11_7_7_13_7_10_8_12_7_13_8_7_9_8_11_9_9_10_9_8_7_7_7_9_9_9_12_7_8_8_12_9_12_8_13_7_8_9_8_9_7_8_9_10_9_13_7_12_9_7_7_9_7</t>
+  </si>
+  <si>
+    <t>8_8_8_7_12_11_7_8_7_10_8_10_9_9_7_7_7_11_7_7_9_7_7_8_9_9_7_7_8_9_11_8_10_10_10_7_9_7_11_7_8_7_7_7_7_9_8_7_7_8_7_9_10_7_8_10_7_7_7_7_8_11_9_11_9_8_7_9_8_10_9_8_7_7_9_9_7_11_9_11_8_11_7_7_7_12_12_7_8_7_7_7_8_7_12_7_7_9_8_10_8_10_9_7_8_8_9_9_12_8_9_11_11_7_7_9_9_7_9_12_7_7_7_9_12_11_8_8_7_12_8_12_9_7_7_7_7_7_10_8_8_8_11_7_11_10_8_8_12_7_7_9_12_7_7_7_7_7_12_8_7_7_8_12_8_8_11_7_7_8_8_10_7_11_9_7_7_8_8_8_10_8_9_7_10_9_7_7_10_10_9_7_10_10_7_10_7_10_8_10_11_11_7_7_7_7_8_8_11_8_9_9_8_12_10_7_7_11_7_8_10_8_12_9_12_8_7_10_9_8_9_10_8_9_8_8_8_9_7_7_9_9_8_10_8_8_8_8_7_7_8_8_8_7_8_7_7_11_8_9_8_11_9_12_9_11_9_7_7_7_9_10_7_8_9_8_8_8_10_10_10_7_11_11_11_11_10_8_10_11_7_7_7_9_9_7_8_9_8_8_8_7_11_11_7_10_8_7_12_9_12_12_8_12_9_11_8_11_11_7_7_7_9_7_10_7_8_7_7_10_7_10_9_8_11_8_7_9_11_8_11_8_11_7_11_11_8_7_8_10_9_7_10_10_11_8_7_7_10_10_10_8_8_10_9_9_10_12_11_7_11_7_8_7_11_9_9_10_11_11_11_11_11_9_9_7_10_7_11_7_8_10_7_7_11_7_7_9_7_10_10_7_11_11_8_11_7_10_8_9_9_8_8_10_9_8_8_8_7_9_8_9_10_9_8_7_8_10_10_10_7_8_8_12_9_7_12_12_10_12_8_10_9_10_10_10_7_7_12_8_9_7_9_7_8_12_12_8_7_9_9_10_7_7_12_7_8_9_8_7_7_7_7_7_7_11_9_12_9_7_8_10_9_9_8_8_9_8_8_11_10_10_7_7_7_8_9_9_9_8</t>
+  </si>
+  <si>
+    <t>8_7_13_7_8_12_9_10_9_10_8_8_9_13_7_7_7_10_7_7_11_8_8_10_7_9_13_8_7_7_9_7_10_9_13_8_8_11_9_11_7_9_7_7_10_1_8_8_11_8_8_9_11_9_9_9_8_9_12_9_10_7_11_9_13_9_10_7_7_10_8_12_9_7_7_11_7_12_8_7_9_9_7_7_9_9_8_11_9_7_12_7_10_8_13_7_10_7_11_9_10_8_8_8_7_7_8_11_8_12_8_9_12_7_8_9_11_8_13_9_12_8_11_8_10_7_11_7_10_9_7_8_12_9_8_9_8_9_10_9_10_7_10_9_10_8_13_9_13_8_8_7_13_7_7_7_12_7_9_9_10_9_11_9_13_7_13_7_9_8_8_10_7_8_10_9_7_9_9_7_13_9_9_11_8_10_7_7_9_13_7_7_10_8_10_8_9_10_8_10_9_8_9_12_9_8_7_12_8_7_9_7_10_8_8_12_9_10_7_13_8_10_8_10_1_8_9_8_7_8_10_9_11_7_12_8_8_11_8_9_9_13_8_11_9_7_13_8_9_8_7_10_9_10_8_7_13_7_8_10_7_7_9_8_9_7_11_8_13_8_7_7_9_7_10_9_12_7_13_7_7_11_9_13_7_12_7_12_7_10_9_12_8_11_8_8_7_9_8_9_8_11_9_7_7_7_10_7_10_9_8_11_7_13_8_7_11_9_11_7_10_8_7_8_7_12_7_7_9_7_7_7_13_8_9_10_8_12_7_9_10_8_7_9_10_7_7_11_7_11_9_7_8_9_12_9_11_8_7_9_9_12_8_9_8_10_7_7_9_8_10_8_7_13_8_13_9_13_7_7_9_10_7_8_13_9_10_8_9_11_7_11_7_7_10_8_13_8_13_7_7_9_13_7_11_9_13_9_13_9_10_7_12_7_12_8_7_9_9_7_12_7_12_9_8_11_8_9_12_9_13_9_11_7_9_8_12_9_9_8_10_8_12_8_12_8_7_12_7_12_8_12_7_7_13_7_13_8_10_7_7_11_1_12_7_9_9_12_8_10_8_10_8_13_9_11_7_11_9_11_1_9_10_9_9_9_10_7_8_10_9_10_7_10_9_8_9_7_7_9</t>
   </si>
 </sst>
 </file>
@@ -2236,7 +2299,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K204"/>
+  <dimension ref="A1:K214"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -7887,7 +7950,7 @@
     </row>
     <row r="178" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A178" s="6">
-        <f t="shared" ref="A178:A204" si="8">C178*10+D178</f>
+        <f t="shared" ref="A178:A209" si="8">C178*10+D178</f>
         <v>20370011</v>
       </c>
       <c r="B178" s="14">
@@ -8748,6 +8811,326 @@
       </c>
       <c r="J204" s="17"/>
       <c r="K204" s="17"/>
+    </row>
+    <row r="205" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A205" s="6">
+        <f t="shared" si="8"/>
+        <v>20150011</v>
+      </c>
+      <c r="B205" s="14">
+        <v>101500</v>
+      </c>
+      <c r="C205" s="33">
+        <v>2015001</v>
+      </c>
+      <c r="D205" s="33">
+        <v>1</v>
+      </c>
+      <c r="E205" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G205" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="H205" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I205" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="J205" s="17"/>
+      <c r="K205" s="17"/>
+    </row>
+    <row r="206" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A206" s="6">
+        <f t="shared" si="8"/>
+        <v>20150022</v>
+      </c>
+      <c r="B206" s="14">
+        <v>101500</v>
+      </c>
+      <c r="C206" s="33">
+        <v>2015002</v>
+      </c>
+      <c r="D206" s="33">
+        <v>2</v>
+      </c>
+      <c r="E206" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G206" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="H206" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I206" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="J206" s="17"/>
+      <c r="K206" s="17"/>
+    </row>
+    <row r="207" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A207" s="6">
+        <f t="shared" si="8"/>
+        <v>20150033</v>
+      </c>
+      <c r="B207" s="14">
+        <v>101500</v>
+      </c>
+      <c r="C207" s="33">
+        <v>2015003</v>
+      </c>
+      <c r="D207" s="33">
+        <v>3</v>
+      </c>
+      <c r="E207" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G207" s="34" t="s">
+        <v>285</v>
+      </c>
+      <c r="H207" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I207" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="J207" s="17"/>
+      <c r="K207" s="17"/>
+    </row>
+    <row r="208" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A208" s="6">
+        <f t="shared" si="8"/>
+        <v>20150044</v>
+      </c>
+      <c r="B208" s="14">
+        <v>101500</v>
+      </c>
+      <c r="C208" s="33">
+        <v>2015004</v>
+      </c>
+      <c r="D208" s="33">
+        <v>4</v>
+      </c>
+      <c r="E208" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G208" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="H208" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I208" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="J208" s="17"/>
+      <c r="K208" s="17"/>
+    </row>
+    <row r="209" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A209" s="6">
+        <f t="shared" si="8"/>
+        <v>20150055</v>
+      </c>
+      <c r="B209" s="14">
+        <v>101500</v>
+      </c>
+      <c r="C209" s="33">
+        <v>2015005</v>
+      </c>
+      <c r="D209" s="33">
+        <v>5</v>
+      </c>
+      <c r="E209" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G209" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="H209" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I209" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="J209" s="17"/>
+      <c r="K209" s="17"/>
+    </row>
+    <row r="210" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A210" s="6">
+        <f>C210*10+D210</f>
+        <v>20150061</v>
+      </c>
+      <c r="B210" s="14">
+        <v>101500</v>
+      </c>
+      <c r="C210" s="33">
+        <v>2015006</v>
+      </c>
+      <c r="D210" s="33">
+        <v>1</v>
+      </c>
+      <c r="E210" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G210" s="34" t="s">
+        <v>292</v>
+      </c>
+      <c r="H210" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I210" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="J210" s="17"/>
+      <c r="K210" s="17"/>
+    </row>
+    <row r="211" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A211" s="6">
+        <f>C211*10+D211</f>
+        <v>20150072</v>
+      </c>
+      <c r="B211" s="14">
+        <v>101500</v>
+      </c>
+      <c r="C211" s="33">
+        <v>2015007</v>
+      </c>
+      <c r="D211" s="33">
+        <v>2</v>
+      </c>
+      <c r="E211" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G211" s="34" t="s">
+        <v>294</v>
+      </c>
+      <c r="H211" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I211" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="J211" s="17"/>
+      <c r="K211" s="17"/>
+    </row>
+    <row r="212" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A212" s="6">
+        <f>C212*10+D212</f>
+        <v>20150083</v>
+      </c>
+      <c r="B212" s="14">
+        <v>101500</v>
+      </c>
+      <c r="C212" s="33">
+        <v>2015008</v>
+      </c>
+      <c r="D212" s="33">
+        <v>3</v>
+      </c>
+      <c r="E212" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G212" s="34" t="s">
+        <v>296</v>
+      </c>
+      <c r="H212" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I212" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="J212" s="17"/>
+      <c r="K212" s="17"/>
+    </row>
+    <row r="213" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A213" s="6">
+        <f>C213*10+D213</f>
+        <v>20150094</v>
+      </c>
+      <c r="B213" s="14">
+        <v>101500</v>
+      </c>
+      <c r="C213" s="33">
+        <v>2015009</v>
+      </c>
+      <c r="D213" s="33">
+        <v>4</v>
+      </c>
+      <c r="E213" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G213" s="34" t="s">
+        <v>298</v>
+      </c>
+      <c r="H213" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I213" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="J213" s="17"/>
+      <c r="K213" s="17"/>
+    </row>
+    <row r="214" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A214" s="6">
+        <f>C214*10+D214</f>
+        <v>20150105</v>
+      </c>
+      <c r="B214" s="14">
+        <v>101500</v>
+      </c>
+      <c r="C214" s="33">
+        <v>2015010</v>
+      </c>
+      <c r="D214" s="33">
+        <v>5</v>
+      </c>
+      <c r="E214" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G214" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="H214" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I214" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="J214" s="17"/>
+      <c r="K214" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="307">
   <si>
     <t>id</t>
   </si>
@@ -986,6 +986,21 @@
   </si>
   <si>
     <t>8_7_13_7_8_12_9_10_9_10_8_8_9_13_7_7_7_10_7_7_11_8_8_10_7_9_13_8_7_7_9_7_10_9_13_8_8_11_9_11_7_9_7_7_10_1_8_8_11_8_8_9_11_9_9_9_8_9_12_9_10_7_11_9_13_9_10_7_7_10_8_12_9_7_7_11_7_12_8_7_9_9_7_7_9_9_8_11_9_7_12_7_10_8_13_7_10_7_11_9_10_8_8_8_7_7_8_11_8_12_8_9_12_7_8_9_11_8_13_9_12_8_11_8_10_7_11_7_10_9_7_8_12_9_8_9_8_9_10_9_10_7_10_9_10_8_13_9_13_8_8_7_13_7_7_7_12_7_9_9_10_9_11_9_13_7_13_7_9_8_8_10_7_8_10_9_7_9_9_7_13_9_9_11_8_10_7_7_9_13_7_7_10_8_10_8_9_10_8_10_9_8_9_12_9_8_7_12_8_7_9_7_10_8_8_12_9_10_7_13_8_10_8_10_1_8_9_8_7_8_10_9_11_7_12_8_8_11_8_9_9_13_8_11_9_7_13_8_9_8_7_10_9_10_8_7_13_7_8_10_7_7_9_8_9_7_11_8_13_8_7_7_9_7_10_9_12_7_13_7_7_11_9_13_7_12_7_12_7_10_9_12_8_11_8_8_7_9_8_9_8_11_9_7_7_7_10_7_10_9_8_11_7_13_8_7_11_9_11_7_10_8_7_8_7_12_7_7_9_7_7_7_13_8_9_10_8_12_7_9_10_8_7_9_10_7_7_11_7_11_9_7_8_9_12_9_11_8_7_9_9_12_8_9_8_10_7_7_9_8_10_8_7_13_8_13_9_13_7_7_9_10_7_8_13_9_10_8_9_11_7_11_7_7_10_8_13_8_13_7_7_9_13_7_11_9_13_9_13_9_10_7_12_7_12_8_7_9_9_7_12_7_12_9_8_11_8_9_12_9_13_9_11_7_9_8_12_9_9_8_10_8_12_8_12_8_7_12_7_12_8_12_7_7_13_7_13_8_10_7_7_11_1_12_7_9_9_12_8_10_8_10_8_13_9_11_7_11_9_11_1_9_10_9_9_9_10_7_8_10_9_10_7_10_9_8_9_7_7_9</t>
+  </si>
+  <si>
+    <t>2_5_7_4_3_2_8_1_6_6_7_1_3_10_4_2_10_1_5_4_3_3_1_2_1_4_4_4_6_6_6_4_7_9_5_9_9_1_2_6_8_4_2_3_3_7_1_2_5_10_4_2_2_5_7_1_4_1_1_1_5_6_7_3_11_3_5_4_2_8_7_2_2_2_1_1_6_2_3_2_8_3_7_3_5_4_3_11_2_2_2_6_6_1_5_4_4_11_11_8_2_2_2_7_7_6_2_10_10_10_6_8_1_1_1_1_6_4_5_2_3_2_8_6_2_3_5_4_7_3_2_4_5_1_4_4_2_2_6_10_2_7_1_4_3_1_8_11_7_6_10_2_10_6_3_3_6_8_1_3_11_3_2_7_7_7_7_3_5_6_6_6_4_4_4_4_4_1_8_5_2_3_1_7_7_7_2_4_8_1_2_8_6_2_2_3_5_3_3_1_2_10_1_1_3_3_3_3_7_6_9_5_1_2_8_6_5_3_3_3_6_11_8_2_1_2_2_4_5_1_3_2_11_2_4_6_2_9_6_6_8_4_4_10_6_7_5_3_7_3_2_5_8_3_4_1_1_4_1_4_1_10_6_10_7_1_3_2_5_9_9_6_5_4_2_2_5_5_3_3_4_2_3_1_1_4_7_1_3_4_1_1_3_6_7_6_1_1_1_3_1_3_2_2_8_8_2_1_3_1_3_7_1_1_6_6_4_4_5_5_6_3_3_3_10_6_1_2_5_4_10_8_3_3_3_1_1_3_1_4_8_5_8_7_4_3_4_4_1_5_10_10_7_7_5_2_1_5_2_8_4_2_5_4_8_2_4_6_10_4_2_1_1_8_1_1_2_6_6_7_4_3_5_10_10_10_8_10_5_2_8_8_3_8_3_5_2_1_1_1_2_4_4_4_8_4_1_9_3_2_5_8_8_1_1_4_7_2_1_2_7_7_4_4_3_1_5_2_3_7_7_2_2_6_2_6_7_4_7_3_10_5_3_6_7_7_7_10_1_11_10_6_7_2_1_1_8_8_1_1_1_9_6_1_1_1_6_8_8_3_6_6_5_8_4_2_7_10_3_3_2_1_2_3_3_11_2_4_7_5_7_3_8_10_8_1_1_3_2_2</t>
+  </si>
+  <si>
+    <t>7_3_7_3_4_6_2_11_8_4_1_7_9_4_7_3_7_2_4_6_13_8_12_8_2_7_8_4_3_6_8_5_7_1_2_1_4_2_3_2_1_6_2_1_9_5_8_7_2_3_3_4_6_2_1_3_4_9_11_8_7_6_6_8_5_6_8_12_1_2_3_2_3_8_5_3_6_9_2_6_4_4_4_3_12_7_11_7_4_6_4_1_3_5_5_7_1_2_1_12_4_3_7_1_1_1_3_10_8_3_4_7_3_3_8_3_1_11_5_3_11_5_5_12_5_10_3_7_3_8_1_2_3_3_8_5_6_1_8_1_10_4_11_4_2_2_11_7_5_6_4_5_5_13_8_3_1_2_5_2_3_1_2_8_5_8_11_8_2_10_5_4_8_4_3_1_7_6_8_5_4_8_2_5_1_7_11_4_4_1_7_3_7_8_7_5_11_4_1_10_8_5_3_1_4_3_10_8_13_2_9_6_10_5_3_4_5_2_11_8_7_7_5_1_7_10_8_3_12_4_1_3_12_6_2_7_8_11_4_8_1_4_1_6_2_2_12_7_8_7_3_5_8_1_7_1_6_3_8_6_1_8_4_7_7_6_10_3_8_7_1_8_3_6_2_1_7_2_1_6_6_1_2_1_10_7_2_8_5_3_8_1_1_8_3_2_3_3_3_6_3_8_4_11_6_6_2_9_4_3_2_10_6_2_4_10_7_4_2_1_2_3_5_12_7_5_10_5_1_7_8_4_8_2_10_5_9_5_10_8_5_2_1_1_1_9_2_3_3_8_13_6_3_1_3_10_4_7_8_4_4_11_5_7_7_2_4_2_6_3_7_7_1_5_5_3_10_8_6_2_8_2_2_13_8_11_8_12_8_1_6_12_7_2_2_7_6_8_6_2_2_9_2_4_5_10_6_1_7_5_8_2_6_2_6_2_8_8_2_6_8_1_4_3_6_1_1_2_3_5_1_3_8_6_7_4_2_6_1_4_3_9_3_13_8_1_8_4_3_5_4_6_1_5_10_7_2_2_3_4_2_1_1_7_10_4_1_2_7_2_8_3_4_5_1_7_6_3_9_4_1_4_1_6_4_4_5_5_2_6_8_4_2_2_8_5_1_8_6_7</t>
+  </si>
+  <si>
+    <t>12_12_12_12</t>
+  </si>
+  <si>
+    <t>7_8_2_5_2_1_10_2_1_1_8_10_10_6_4_6_3_6_2_3_9_8_8_4_3_10_4_1_5_2_1_5_2_7_5_8_7_6_8_10_8_4_11_1_6_3_3_9_2_2_7_4_3_1_7_9_8_2_8_2_2_8_10_8_6_6_5_3_1_5_4_11_5_10_6_2_4_8_1_1_2_1_6_9_1_1_6_1_3_3_6_6_4_8_3_8_2_1_1_5_2_3_2_6_9_5_2_9_2_4_5_10_3_6_3_8_1_2_1_1_1_1_7_4_3_3_8_5_1_1_2_6_4_4_1_1_4_5_5_7_6_2_5_3_4_2_2_3_9_7_10_10_4_5_7_3_3_8_9_3_5_11_11_11_3_6_5_9_1_5_2_3_1_2_3_4_3_4_3_3_7_4_2_4_7_3_3_1_5_5_7_4_2_2_8_8_5_8_5_3_3_5_1_6_2_3_5_4_5_1_2_4_4_7_6_3_4_5_8_8_1_3_3_9_1_3_3_1_6_11_2_2_3_2_5_1_3_4_2_5_4_2_5_7_4_8_5_1_5_3_4_5_1_4_1_3_4_5_8_4_4_1_2_1_8_3_3_3_5_11_2_6_6_6_3_6_2_9_2_5_4_10_8_4_6_2_2_2_2_8_8_3_2_1_3_3_11_1_2_3_10_7_3_2_4_4_2_3_2_10_4_2_5_6_7_7_3_5_3_5_7_10_1_1_6_10_10_6_1_6_6_3_1_3_6_6_6_1_4_4_9_4_4_2_4_3_4_4_6_1_4_1_4_11_8_8_1_3_1_4_2_10_5_5_6_10_4_4_3_7_5_6_6_6_5_1_4_4_1_1_3_7_2_7_1_3_6_5_8_4_9_3_2_10_10_7_9_9_9_8_1_10_2_10_7_3_2_11_5_1_1_8_3_4_10_8_8_4_1_2_6_4_9_3_5_6_5_5_6_8_7_7_11_1_5_2_2_8_9_2_6_4_4_5_1_3_8_5_1_8_8_4_8_3_4_10_2_2_8_2_5_7_10_3_9_10_3_4_1_6_3_11_11_4_4_3_3_6_7_2_2_9_6_2_1_4_4_8_9_5_2_4_4_9_3_1_3_1_7_4</t>
+  </si>
+  <si>
+    <t>9_4_2_1_3_7_2_2_7_2_8_11_5_8_8_5_5_1_5_3_1_11_5_3_3_5_10_8_10_4_4_1_1_2_7_8_4_6_10_2_1_2_5_1_2_1_6_5_8_5_7_5_1_9_3_6_1_6_8_3_5_3_3_7_8_2_3_8_10_3_6_5_2_2_10_4_2_1_6_5_2_4_9_3_9_4_9_6_3_1_1_9_5_2_2_4_12_8_7_5_6_2_13_8_6_6_8_1_3_5_2_13_8_10_4_4_6_5_5_8_5_7_2_9_11_7_1_9_8_2_1_1_1_1_11_2_6_10_7_2_8_4_1_8_9_6_6_6_6_10_2_2_1_5_1_6_1_7_12_4_5_1_1_8_1_6_13_8_2_11_3_11_2_2_11_6_1_2_5_9_3_10_1_6_8_11_7_8_5_2_9_2_1_12_6_4_2_11_3_10_5_2_4_3_1_2_7_6_9_10_5_3_9_1_8_12_7_3_6_7_1_2_5_6_11_7_11_7_8_5_4_2_10_7_1_7_11_7_11_2_9_11_7_8_1_11_5_3_3_6_5_6_6_7_7_13_1_1_2_2_11_5_3_2_1_4_6_2_3_6_3_8_5_9_4_3_7_3_4_5_2_9_4_5_1_12_7_7_9_1_8_11_7_6_3_5_1_3_2_1_3_5_2_5_2_1_13_8_11_5_3_6_4_1_5_4_4_13_7_7_4_9_6_3_5_3_4_5_3_2_7_3_10_5_9_5_8_6_2_2_9_4_2_8_4_1_2_8_6_7_5_4_3_2_5_1_8_8_4_5_8_1_5_1_4_1_2_5_2_1_1_1_3_5_12_7_2_7_10_8_4_13_5_3_4_2_7_7_1_8_5_2_7_4_4_2_11_8_5_8_6_3_1_7_12_4_8_1_6_5_9_3_2_9_4_11_7_11_7_5_7_5_8_8_6_2_4_1_1_6_1_7_2_1_2_8_4_4_10_3_4_6_4_7_5_1_3_8_8_4_1_7_2_3_2_4_2_1_8_6_6_9_1_6_5_5_1_6_10_6_2_2_6_3_12_4_6_1_10_8_4_5_5_3_2_8_8_1_11_3_12_6_2_5_5_3_8_3_11_3</t>
   </si>
 </sst>
 </file>
@@ -2299,7 +2314,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K214"/>
+  <dimension ref="A1:K221"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -7950,7 +7965,7 @@
     </row>
     <row r="178" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A178" s="6">
-        <f t="shared" ref="A178:A209" si="8">C178*10+D178</f>
+        <f t="shared" ref="A178:A214" si="8">C178*10+D178</f>
         <v>20370011</v>
       </c>
       <c r="B178" s="14">
@@ -8847,13 +8862,13 @@
     <row r="206" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A206" s="6">
         <f t="shared" si="8"/>
-        <v>20150022</v>
+        <v>20150012</v>
       </c>
       <c r="B206" s="14">
         <v>101500</v>
       </c>
       <c r="C206" s="33">
-        <v>2015002</v>
+        <v>2015001</v>
       </c>
       <c r="D206" s="33">
         <v>2</v>
@@ -8879,13 +8894,13 @@
     <row r="207" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A207" s="6">
         <f t="shared" si="8"/>
-        <v>20150033</v>
+        <v>20150013</v>
       </c>
       <c r="B207" s="14">
         <v>101500</v>
       </c>
       <c r="C207" s="33">
-        <v>2015003</v>
+        <v>2015001</v>
       </c>
       <c r="D207" s="33">
         <v>3</v>
@@ -8911,13 +8926,13 @@
     <row r="208" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A208" s="6">
         <f t="shared" si="8"/>
-        <v>20150044</v>
+        <v>20150014</v>
       </c>
       <c r="B208" s="14">
         <v>101500</v>
       </c>
       <c r="C208" s="33">
-        <v>2015004</v>
+        <v>2015001</v>
       </c>
       <c r="D208" s="33">
         <v>4</v>
@@ -8943,13 +8958,13 @@
     <row r="209" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A209" s="6">
         <f t="shared" si="8"/>
-        <v>20150055</v>
+        <v>20150015</v>
       </c>
       <c r="B209" s="14">
         <v>101500</v>
       </c>
       <c r="C209" s="33">
-        <v>2015005</v>
+        <v>2015001</v>
       </c>
       <c r="D209" s="33">
         <v>5</v>
@@ -8974,14 +8989,14 @@
     </row>
     <row r="210" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A210" s="6">
-        <f>C210*10+D210</f>
-        <v>20150061</v>
+        <f t="shared" si="8"/>
+        <v>20150021</v>
       </c>
       <c r="B210" s="14">
         <v>101500</v>
       </c>
       <c r="C210" s="33">
-        <v>2015006</v>
+        <v>2015002</v>
       </c>
       <c r="D210" s="33">
         <v>1</v>
@@ -9006,14 +9021,14 @@
     </row>
     <row r="211" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A211" s="6">
-        <f>C211*10+D211</f>
-        <v>20150072</v>
+        <f t="shared" si="8"/>
+        <v>20150022</v>
       </c>
       <c r="B211" s="14">
         <v>101500</v>
       </c>
       <c r="C211" s="33">
-        <v>2015007</v>
+        <v>2015002</v>
       </c>
       <c r="D211" s="33">
         <v>2</v>
@@ -9038,14 +9053,14 @@
     </row>
     <row r="212" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A212" s="6">
-        <f>C212*10+D212</f>
-        <v>20150083</v>
+        <f t="shared" si="8"/>
+        <v>20150023</v>
       </c>
       <c r="B212" s="14">
         <v>101500</v>
       </c>
       <c r="C212" s="33">
-        <v>2015008</v>
+        <v>2015002</v>
       </c>
       <c r="D212" s="33">
         <v>3</v>
@@ -9070,14 +9085,14 @@
     </row>
     <row r="213" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A213" s="6">
-        <f>C213*10+D213</f>
-        <v>20150094</v>
+        <f t="shared" si="8"/>
+        <v>20150024</v>
       </c>
       <c r="B213" s="14">
         <v>101500</v>
       </c>
       <c r="C213" s="33">
-        <v>2015009</v>
+        <v>2015002</v>
       </c>
       <c r="D213" s="33">
         <v>4</v>
@@ -9102,14 +9117,14 @@
     </row>
     <row r="214" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A214" s="6">
-        <f>C214*10+D214</f>
-        <v>20150105</v>
+        <f t="shared" si="8"/>
+        <v>20150025</v>
       </c>
       <c r="B214" s="14">
         <v>101500</v>
       </c>
       <c r="C214" s="33">
-        <v>2015010</v>
+        <v>2015002</v>
       </c>
       <c r="D214" s="33">
         <v>5</v>
@@ -9131,6 +9146,230 @@
       </c>
       <c r="J214" s="17"/>
       <c r="K214" s="17"/>
+    </row>
+    <row r="215" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A215" s="6">
+        <f t="shared" ref="A215:A221" si="9">C215*10+D215</f>
+        <v>20260011</v>
+      </c>
+      <c r="B215" s="14">
+        <v>202600</v>
+      </c>
+      <c r="C215" s="33">
+        <v>2026001</v>
+      </c>
+      <c r="D215" s="33">
+        <v>1</v>
+      </c>
+      <c r="E215" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G215" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="H215" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I215" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J215" s="17"/>
+      <c r="K215" s="17"/>
+    </row>
+    <row r="216" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A216" s="6">
+        <f t="shared" si="9"/>
+        <v>20260012</v>
+      </c>
+      <c r="B216" s="14">
+        <v>202600</v>
+      </c>
+      <c r="C216" s="33">
+        <v>2026001</v>
+      </c>
+      <c r="D216" s="33">
+        <v>2</v>
+      </c>
+      <c r="E216" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="F216" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G216" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="H216" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I216" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J216" s="17"/>
+      <c r="K216" s="17"/>
+    </row>
+    <row r="217" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A217" s="6">
+        <f t="shared" si="9"/>
+        <v>20260013</v>
+      </c>
+      <c r="B217" s="14">
+        <v>202600</v>
+      </c>
+      <c r="C217" s="33">
+        <v>2026001</v>
+      </c>
+      <c r="D217" s="33">
+        <v>3</v>
+      </c>
+      <c r="E217" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="F217" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G217" s="34" t="s">
+        <v>185</v>
+      </c>
+      <c r="H217" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I217" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J217" s="17"/>
+      <c r="K217" s="17"/>
+    </row>
+    <row r="218" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A218" s="6">
+        <f t="shared" si="9"/>
+        <v>20260014</v>
+      </c>
+      <c r="B218" s="14">
+        <v>202600</v>
+      </c>
+      <c r="C218" s="33">
+        <v>2026001</v>
+      </c>
+      <c r="D218" s="33">
+        <v>4</v>
+      </c>
+      <c r="E218" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G218" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="H218" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I218" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J218" s="17"/>
+      <c r="K218" s="17"/>
+    </row>
+    <row r="219" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A219" s="6">
+        <f t="shared" si="9"/>
+        <v>20260015</v>
+      </c>
+      <c r="B219" s="14">
+        <v>202600</v>
+      </c>
+      <c r="C219" s="33">
+        <v>2026001</v>
+      </c>
+      <c r="D219" s="33">
+        <v>5</v>
+      </c>
+      <c r="E219" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G219" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="H219" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I219" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J219" s="17"/>
+      <c r="K219" s="17"/>
+    </row>
+    <row r="220" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A220" s="6">
+        <f t="shared" si="9"/>
+        <v>20260016</v>
+      </c>
+      <c r="B220" s="14">
+        <v>202600</v>
+      </c>
+      <c r="C220" s="33">
+        <v>2026001</v>
+      </c>
+      <c r="D220" s="33">
+        <v>6</v>
+      </c>
+      <c r="E220" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G220" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="H220" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I220" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="J220" s="17"/>
+      <c r="K220" s="17"/>
+    </row>
+    <row r="221" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A221" s="6">
+        <f t="shared" si="9"/>
+        <v>20260017</v>
+      </c>
+      <c r="B221" s="14">
+        <v>202600</v>
+      </c>
+      <c r="C221" s="33">
+        <v>2026001</v>
+      </c>
+      <c r="D221" s="33">
+        <v>7</v>
+      </c>
+      <c r="E221" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="F221" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G221" s="34" t="s">
+        <v>305</v>
+      </c>
+      <c r="H221" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I221" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J221" s="17"/>
+      <c r="K221" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoller" sheetId="1" r:id="rId1"/>
@@ -9461,7 +9461,7 @@
         <v>10510012</v>
       </c>
       <c r="B229" s="13">
-        <v>105101</v>
+        <v>105100</v>
       </c>
       <c r="C229" s="18">
         <v>2051001</v>
@@ -9491,7 +9491,7 @@
         <v>10510013</v>
       </c>
       <c r="B230" s="13">
-        <v>105102</v>
+        <v>105100</v>
       </c>
       <c r="C230" s="18">
         <v>2051001</v>
@@ -9521,7 +9521,7 @@
         <v>10510014</v>
       </c>
       <c r="B231" s="13">
-        <v>105103</v>
+        <v>105100</v>
       </c>
       <c r="C231" s="18">
         <v>2051001</v>
@@ -9551,7 +9551,7 @@
         <v>10510015</v>
       </c>
       <c r="B232" s="13">
-        <v>105104</v>
+        <v>105100</v>
       </c>
       <c r="C232" s="18">
         <v>2051001</v>
@@ -9581,7 +9581,7 @@
         <v>10510016</v>
       </c>
       <c r="B233" s="13">
-        <v>105105</v>
+        <v>105100</v>
       </c>
       <c r="C233" s="18">
         <v>2051001</v>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoller" sheetId="1" r:id="rId1"/>
@@ -9035,7 +9035,7 @@
         <v>20260011</v>
       </c>
       <c r="B215" s="13">
-        <v>202600</v>
+        <v>102600</v>
       </c>
       <c r="C215" s="33">
         <v>2026001</v>
@@ -9066,7 +9066,7 @@
         <v>20260012</v>
       </c>
       <c r="B216" s="13">
-        <v>202600</v>
+        <v>102600</v>
       </c>
       <c r="C216" s="33">
         <v>2026001</v>
@@ -9097,7 +9097,7 @@
         <v>20260013</v>
       </c>
       <c r="B217" s="13">
-        <v>202600</v>
+        <v>102600</v>
       </c>
       <c r="C217" s="33">
         <v>2026001</v>
@@ -9128,7 +9128,7 @@
         <v>20260014</v>
       </c>
       <c r="B218" s="13">
-        <v>202600</v>
+        <v>102600</v>
       </c>
       <c r="C218" s="33">
         <v>2026001</v>
@@ -9159,7 +9159,7 @@
         <v>20260015</v>
       </c>
       <c r="B219" s="13">
-        <v>202600</v>
+        <v>102600</v>
       </c>
       <c r="C219" s="33">
         <v>2026001</v>
@@ -9190,7 +9190,7 @@
         <v>20260016</v>
       </c>
       <c r="B220" s="13">
-        <v>202600</v>
+        <v>102600</v>
       </c>
       <c r="C220" s="33">
         <v>2026001</v>
@@ -9221,7 +9221,7 @@
         <v>20260017</v>
       </c>
       <c r="B221" s="13">
-        <v>202600</v>
+        <v>102600</v>
       </c>
       <c r="C221" s="33">
         <v>2026001</v>
@@ -9461,7 +9461,7 @@
         <v>10510012</v>
       </c>
       <c r="B229" s="13">
-        <v>105100</v>
+        <v>105101</v>
       </c>
       <c r="C229" s="18">
         <v>2051001</v>
@@ -9491,7 +9491,7 @@
         <v>10510013</v>
       </c>
       <c r="B230" s="13">
-        <v>105100</v>
+        <v>105102</v>
       </c>
       <c r="C230" s="18">
         <v>2051001</v>
@@ -9521,7 +9521,7 @@
         <v>10510014</v>
       </c>
       <c r="B231" s="13">
-        <v>105100</v>
+        <v>105103</v>
       </c>
       <c r="C231" s="18">
         <v>2051001</v>
@@ -9551,7 +9551,7 @@
         <v>10510015</v>
       </c>
       <c r="B232" s="13">
-        <v>105100</v>
+        <v>105104</v>
       </c>
       <c r="C232" s="18">
         <v>2051001</v>
@@ -9581,7 +9581,7 @@
         <v>10510016</v>
       </c>
       <c r="B233" s="13">
-        <v>105100</v>
+        <v>105105</v>
       </c>
       <c r="C233" s="18">
         <v>2051001</v>
